--- a/Input_data/IST_US_trad_eco_cal_2025-01-01_to_2025-03-09.xlsx
+++ b/Input_data/IST_US_trad_eco_cal_2025-01-01_to_2025-03-09.xlsx
@@ -806,27 +806,27 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>EIA Crude Oil Stocks ChangeDEC/27</t>
+          <t>EIA Distillate Stocks ChangeDEC/27</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>-1.178M</t>
+          <t>6.406M</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>-4.237M</t>
+          <t>-1.694M</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>-2.75M</t>
+          <t>-0.1M</t>
         </is>
       </c>
       <c r="F13" t="inlineStr"/>
       <c r="G13" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="14">
@@ -837,17 +837,17 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>EIA Cushing Crude Oil Stocks ChangeDEC/27</t>
+          <t>EIA Refinery Crude Runs ChangeDEC/27</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>-0.142M</t>
+          <t>0.041M</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>-0.32M</t>
+          <t>0.205M</t>
         </is>
       </c>
       <c r="E14" t="inlineStr"/>
@@ -864,17 +864,17 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>EIA Crude Oil Imports ChangeDEC/27</t>
+          <t>EIA Gasoline Production ChangeDEC/27</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>0.323M</t>
+          <t>-0.959M</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>0.995M</t>
+          <t>0.051M</t>
         </is>
       </c>
       <c r="E15" t="inlineStr"/>
@@ -891,23 +891,27 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>EIA Heating Oil Stocks ChangeDEC/27</t>
+          <t>EIA Gasoline Stocks ChangeDEC/27</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>-0.416M</t>
+          <t>7.717M</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>-0.062M</t>
-        </is>
-      </c>
-      <c r="E16" t="inlineStr"/>
+          <t>1.63M</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>0.7M</t>
+        </is>
+      </c>
       <c r="F16" t="inlineStr"/>
       <c r="G16" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="17">
@@ -918,17 +922,17 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>EIA Distillate Fuel Production ChangeDEC/27</t>
+          <t>EIA Crude Oil Imports ChangeDEC/27</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>0.099M</t>
+          <t>0.323M</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>0.178M</t>
+          <t>0.995M</t>
         </is>
       </c>
       <c r="E17" t="inlineStr"/>
@@ -945,27 +949,23 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>EIA Gasoline Stocks ChangeDEC/27</t>
+          <t>EIA Heating Oil Stocks ChangeDEC/27</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>7.717M</t>
+          <t>-0.416M</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>1.63M</t>
-        </is>
-      </c>
-      <c r="E18" t="inlineStr">
-        <is>
-          <t>0.7M</t>
-        </is>
-      </c>
+          <t>-0.062M</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr"/>
       <c r="F18" t="inlineStr"/>
       <c r="G18" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="19">
@@ -976,17 +976,17 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>EIA Gasoline Production ChangeDEC/27</t>
+          <t>EIA Cushing Crude Oil Stocks ChangeDEC/27</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>-0.959M</t>
+          <t>-0.142M</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>0.051M</t>
+          <t>-0.32M</t>
         </is>
       </c>
       <c r="E19" t="inlineStr"/>
@@ -1003,23 +1003,27 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>EIA Refinery Crude Runs ChangeDEC/27</t>
+          <t>EIA Crude Oil Stocks ChangeDEC/27</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>0.041M</t>
+          <t>-1.178M</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>0.205M</t>
-        </is>
-      </c>
-      <c r="E20" t="inlineStr"/>
+          <t>-4.237M</t>
+        </is>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>-2.75M</t>
+        </is>
+      </c>
       <c r="F20" t="inlineStr"/>
       <c r="G20" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="21">
@@ -1030,24 +1034,20 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>EIA Distillate Stocks ChangeDEC/27</t>
+          <t>EIA Distillate Fuel Production ChangeDEC/27</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>6.406M</t>
+          <t>0.099M</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>-1.694M</t>
-        </is>
-      </c>
-      <c r="E21" t="inlineStr">
-        <is>
-          <t>-0.1M</t>
-        </is>
-      </c>
+          <t>0.178M</t>
+        </is>
+      </c>
+      <c r="E21" t="inlineStr"/>
       <c r="F21" t="inlineStr"/>
       <c r="G21" t="n">
         <v>3</v>
@@ -1223,31 +1223,31 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>ISM Manufacturing PMIDEC</t>
+          <t>ISM Manufacturing PricesDEC</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>49.3</t>
+          <t>52.5</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>48.4</t>
+          <t>50.3</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>48.4</t>
+          <t>51.7</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>48.5</t>
+          <t>50.4</t>
         </is>
       </c>
       <c r="G28" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="29">
@@ -1258,31 +1258,27 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>ISM Manufacturing EmploymentDEC</t>
+          <t>ISM Manufacturing New OrdersDEC</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>45.3</t>
+          <t>52.5</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>48.1</t>
-        </is>
-      </c>
-      <c r="E29" t="inlineStr">
-        <is>
-          <t>48</t>
-        </is>
-      </c>
+          <t>50.4</t>
+        </is>
+      </c>
+      <c r="E29" t="inlineStr"/>
       <c r="F29" t="inlineStr">
         <is>
-          <t>48.3</t>
+          <t>50.5</t>
         </is>
       </c>
       <c r="G29" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="30">
@@ -1293,27 +1289,31 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>ISM Manufacturing New OrdersDEC</t>
+          <t>ISM Manufacturing EmploymentDEC</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>52.5</t>
+          <t>45.3</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>50.4</t>
-        </is>
-      </c>
-      <c r="E30" t="inlineStr"/>
+          <t>48.1</t>
+        </is>
+      </c>
+      <c r="E30" t="inlineStr">
+        <is>
+          <t>48</t>
+        </is>
+      </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>50.5</t>
+          <t>48.3</t>
         </is>
       </c>
       <c r="G30" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="31">
@@ -1324,31 +1324,31 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>ISM Manufacturing PricesDEC</t>
+          <t>ISM Manufacturing PMIDEC</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>52.5</t>
+          <t>49.3</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>50.3</t>
+          <t>48.4</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>51.7</t>
+          <t>48.4</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>50.4</t>
+          <t>48.5</t>
         </is>
       </c>
       <c r="G31" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="32">
@@ -1609,31 +1609,27 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>Factory Orders MoMNOV</t>
+          <t>Factory Orders ex TransportationNOV</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>-0.4%</t>
+          <t>0.2%</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>0.5%</t>
-        </is>
-      </c>
-      <c r="E42" t="inlineStr">
-        <is>
-          <t>-0.3%</t>
-        </is>
-      </c>
+          <t>0.2%</t>
+        </is>
+      </c>
+      <c r="E42" t="inlineStr"/>
       <c r="F42" t="inlineStr">
         <is>
-          <t>0.3%</t>
+          <t>0.2%</t>
         </is>
       </c>
       <c r="G42" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="43">
@@ -1644,27 +1640,31 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>Factory Orders ex TransportationNOV</t>
+          <t>Factory Orders MoMNOV</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>0.2%</t>
+          <t>-0.4%</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>0.2%</t>
-        </is>
-      </c>
-      <c r="E43" t="inlineStr"/>
+          <t>0.5%</t>
+        </is>
+      </c>
+      <c r="E43" t="inlineStr">
+        <is>
+          <t>-0.3%</t>
+        </is>
+      </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>0.2%</t>
+          <t>0.3%</t>
         </is>
       </c>
       <c r="G43" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="44">
@@ -1949,31 +1949,31 @@
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>ISM Services PMIDEC</t>
+          <t>ISM Services EmploymentDEC</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>54.1</t>
+          <t>51.4</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>52.1</t>
+          <t>51.5</t>
         </is>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>53.3</t>
+          <t>51.4</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>54</t>
+          <t>52</t>
         </is>
       </c>
       <c r="G54" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="55">
@@ -1984,23 +1984,23 @@
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>JOLTs Job QuitsNOV</t>
+          <t>ISM Services Business ActivityDEC</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>3.065M</t>
+          <t>58.2</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>3.283M</t>
+          <t>53.7</t>
         </is>
       </c>
       <c r="E55" t="inlineStr"/>
       <c r="F55" t="inlineStr">
         <is>
-          <t>3.31M</t>
+          <t>54.1</t>
         </is>
       </c>
       <c r="G55" t="n">
@@ -2015,31 +2015,31 @@
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>JOLTs Job OpeningsNOV</t>
+          <t>ISM Services PricesDEC</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>8.098M</t>
+          <t>64.4</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>7.839M</t>
+          <t>58.2</t>
         </is>
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>7.70M</t>
+          <t>57.5</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>7.69M</t>
+          <t>58.4</t>
         </is>
       </c>
       <c r="G56" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="57">
@@ -2050,27 +2050,27 @@
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>ISM Services PricesDEC</t>
+          <t>ISM Services New OrdersDEC</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>64.4</t>
+          <t>54.2</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>58.2</t>
+          <t>53.7</t>
         </is>
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>57.5</t>
+          <t>54.2</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>58.4</t>
+          <t>54.1</t>
         </is>
       </c>
       <c r="G57" t="n">
@@ -2085,31 +2085,31 @@
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>ISM Services New OrdersDEC</t>
+          <t>JOLTs Job OpeningsNOV</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>54.2</t>
+          <t>8.098M</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>53.7</t>
+          <t>7.839M</t>
         </is>
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>54.2</t>
+          <t>7.70M</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>54.1</t>
+          <t>7.69M</t>
         </is>
       </c>
       <c r="G58" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="59">
@@ -2120,27 +2120,23 @@
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>ISM Services EmploymentDEC</t>
+          <t>JOLTs Job QuitsNOV</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>51.4</t>
+          <t>3.065M</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>51.5</t>
-        </is>
-      </c>
-      <c r="E59" t="inlineStr">
-        <is>
-          <t>51.4</t>
-        </is>
-      </c>
+          <t>3.283M</t>
+        </is>
+      </c>
+      <c r="E59" t="inlineStr"/>
       <c r="F59" t="inlineStr">
         <is>
-          <t>52</t>
+          <t>3.31M</t>
         </is>
       </c>
       <c r="G59" t="n">
@@ -2155,27 +2151,31 @@
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>ISM Services Business ActivityDEC</t>
+          <t>ISM Services PMIDEC</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>58.2</t>
+          <t>54.1</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>53.7</t>
-        </is>
-      </c>
-      <c r="E60" t="inlineStr"/>
+          <t>52.1</t>
+        </is>
+      </c>
+      <c r="E60" t="inlineStr">
+        <is>
+          <t>53.3</t>
+        </is>
+      </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>54.1</t>
+          <t>54</t>
         </is>
       </c>
       <c r="G60" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="61">
@@ -2271,17 +2271,17 @@
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>MBA Mortgage Refinance IndexJAN/03</t>
+          <t>MBA Purchase IndexJAN/03</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>401.1</t>
+          <t>127.7</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>395.1</t>
+          <t>136.7</t>
         </is>
       </c>
       <c r="E64" t="inlineStr"/>
@@ -2298,17 +2298,17 @@
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>MBA Mortgage Market IndexJAN/03</t>
+          <t>MBA Mortgage ApplicationsJAN/03</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>168.4</t>
+          <t>-3.7%</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>174.9</t>
+          <t>-12.6%</t>
         </is>
       </c>
       <c r="E65" t="inlineStr"/>
@@ -2325,23 +2325,23 @@
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>MBA Mortgage ApplicationsJAN/03</t>
+          <t>MBA 30-Year Mortgage RateJAN/03</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>-3.7%</t>
+          <t>6.99%</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>-12.6%</t>
+          <t>6.97%</t>
         </is>
       </c>
       <c r="E66" t="inlineStr"/>
       <c r="F66" t="inlineStr"/>
       <c r="G66" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="67">
@@ -2352,17 +2352,17 @@
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>MBA Purchase IndexJAN/03</t>
+          <t>MBA Mortgage Refinance IndexJAN/03</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>127.7</t>
+          <t>401.1</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>136.7</t>
+          <t>395.1</t>
         </is>
       </c>
       <c r="E67" t="inlineStr"/>
@@ -2379,23 +2379,23 @@
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>MBA 30-Year Mortgage RateJAN/03</t>
+          <t>MBA Mortgage Market IndexJAN/03</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>6.99%</t>
+          <t>168.4</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>6.97%</t>
+          <t>174.9</t>
         </is>
       </c>
       <c r="E68" t="inlineStr"/>
       <c r="F68" t="inlineStr"/>
       <c r="G68" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="69">
@@ -2685,17 +2685,17 @@
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>EIA Distillate Fuel Production ChangeJAN/03</t>
+          <t>EIA Gasoline Production ChangeJAN/03</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>-0.167M</t>
+          <t>-0.081M</t>
         </is>
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>0.099M</t>
+          <t>-0.959M</t>
         </is>
       </c>
       <c r="E78" t="inlineStr"/>
@@ -2712,20 +2712,24 @@
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>EIA Crude Oil Imports ChangeJAN/03</t>
+          <t>EIA Distillate Stocks ChangeJAN/03</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>0.278M</t>
+          <t>6.071M</t>
         </is>
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>0.323M</t>
-        </is>
-      </c>
-      <c r="E79" t="inlineStr"/>
+          <t>6.406M</t>
+        </is>
+      </c>
+      <c r="E79" t="inlineStr">
+        <is>
+          <t>1M</t>
+        </is>
+      </c>
       <c r="F79" t="inlineStr"/>
       <c r="G79" t="n">
         <v>3</v>
@@ -2739,27 +2743,23 @@
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>EIA Crude Oil Stocks ChangeJAN/03</t>
+          <t>EIA Heating Oil Stocks ChangeJAN/03</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>-0.959M</t>
+          <t>-0.632M</t>
         </is>
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>-1.178M</t>
-        </is>
-      </c>
-      <c r="E80" t="inlineStr">
-        <is>
-          <t>-0.6M</t>
-        </is>
-      </c>
+          <t>-0.416M</t>
+        </is>
+      </c>
+      <c r="E80" t="inlineStr"/>
       <c r="F80" t="inlineStr"/>
       <c r="G80" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="81">
@@ -2770,27 +2770,23 @@
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>EIA Gasoline Stocks ChangeJAN/03</t>
+          <t>EIA Cushing Crude Oil Stocks ChangeJAN/03</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>6.33M</t>
+          <t>-2.502M</t>
         </is>
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>7.717M</t>
-        </is>
-      </c>
-      <c r="E81" t="inlineStr">
-        <is>
-          <t>1.5M</t>
-        </is>
-      </c>
+          <t>-0.142M</t>
+        </is>
+      </c>
+      <c r="E81" t="inlineStr"/>
       <c r="F81" t="inlineStr"/>
       <c r="G81" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="82">
@@ -2801,17 +2797,17 @@
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>EIA Cushing Crude Oil Stocks ChangeJAN/03</t>
+          <t>EIA Refinery Crude Runs ChangeJAN/03</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>-2.502M</t>
+          <t>0.045M</t>
         </is>
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>-0.142M</t>
+          <t>0.041M</t>
         </is>
       </c>
       <c r="E82" t="inlineStr"/>
@@ -2828,23 +2824,27 @@
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>EIA Heating Oil Stocks ChangeJAN/03</t>
+          <t>EIA Crude Oil Stocks ChangeJAN/03</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>-0.632M</t>
+          <t>-0.959M</t>
         </is>
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>-0.416M</t>
-        </is>
-      </c>
-      <c r="E83" t="inlineStr"/>
+          <t>-1.178M</t>
+        </is>
+      </c>
+      <c r="E83" t="inlineStr">
+        <is>
+          <t>-0.6M</t>
+        </is>
+      </c>
       <c r="F83" t="inlineStr"/>
       <c r="G83" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="84">
@@ -2855,17 +2855,17 @@
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>EIA Gasoline Production ChangeJAN/03</t>
+          <t>EIA Crude Oil Imports ChangeJAN/03</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>-0.081M</t>
+          <t>0.278M</t>
         </is>
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>-0.959M</t>
+          <t>0.323M</t>
         </is>
       </c>
       <c r="E84" t="inlineStr"/>
@@ -2882,23 +2882,27 @@
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>EIA Refinery Crude Runs ChangeJAN/03</t>
+          <t>EIA Gasoline Stocks ChangeJAN/03</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>0.045M</t>
+          <t>6.33M</t>
         </is>
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>0.041M</t>
-        </is>
-      </c>
-      <c r="E85" t="inlineStr"/>
+          <t>7.717M</t>
+        </is>
+      </c>
+      <c r="E85" t="inlineStr">
+        <is>
+          <t>1.5M</t>
+        </is>
+      </c>
       <c r="F85" t="inlineStr"/>
       <c r="G85" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="86">
@@ -2909,24 +2913,20 @@
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>EIA Distillate Stocks ChangeJAN/03</t>
+          <t>EIA Distillate Fuel Production ChangeJAN/03</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>6.071M</t>
+          <t>-0.167M</t>
         </is>
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>6.406M</t>
-        </is>
-      </c>
-      <c r="E86" t="inlineStr">
-        <is>
-          <t>1M</t>
-        </is>
-      </c>
+          <t>0.099M</t>
+        </is>
+      </c>
+      <c r="E86" t="inlineStr"/>
       <c r="F86" t="inlineStr"/>
       <c r="G86" t="n">
         <v>3</v>
@@ -3171,17 +3171,17 @@
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>8-Week Bill Auction</t>
+          <t>4-Week Bill Auction</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>4.240%</t>
+          <t>4.245%</t>
         </is>
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>4.240%</t>
+          <t>4.265%</t>
         </is>
       </c>
       <c r="E96" t="inlineStr"/>
@@ -3198,17 +3198,17 @@
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>4-Week Bill Auction</t>
+          <t>8-Week Bill Auction</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>4.245%</t>
+          <t>4.240%</t>
         </is>
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>4.265%</t>
+          <t>4.240%</t>
         </is>
       </c>
       <c r="E97" t="inlineStr"/>
@@ -3336,27 +3336,27 @@
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>Manufacturing PayrollsDEC</t>
+          <t>Nonfarm Payrolls PrivateDEC</t>
         </is>
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>-13K</t>
+          <t>223K</t>
         </is>
       </c>
       <c r="D103" t="inlineStr">
         <is>
-          <t>25K</t>
+          <t>182K</t>
         </is>
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>5K</t>
+          <t>135K</t>
         </is>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>29K</t>
+          <t>185K</t>
         </is>
       </c>
       <c r="G103" t="n">
@@ -3371,27 +3371,31 @@
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>Participation RateDEC</t>
+          <t>Manufacturing PayrollsDEC</t>
         </is>
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>62.5%</t>
+          <t>-13K</t>
         </is>
       </c>
       <c r="D104" t="inlineStr">
         <is>
-          <t>62.5%</t>
-        </is>
-      </c>
-      <c r="E104" t="inlineStr"/>
+          <t>25K</t>
+        </is>
+      </c>
+      <c r="E104" t="inlineStr">
+        <is>
+          <t>5K</t>
+        </is>
+      </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>62.8%</t>
+          <t>29K</t>
         </is>
       </c>
       <c r="G104" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="105">
@@ -3402,31 +3406,27 @@
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>Non Farm PayrollsDEC</t>
+          <t>Participation RateDEC</t>
         </is>
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>256K</t>
+          <t>62.5%</t>
         </is>
       </c>
       <c r="D105" t="inlineStr">
         <is>
-          <t>212K</t>
-        </is>
-      </c>
-      <c r="E105" t="inlineStr">
-        <is>
-          <t>160K</t>
-        </is>
-      </c>
+          <t>62.5%</t>
+        </is>
+      </c>
+      <c r="E105" t="inlineStr"/>
       <c r="F105" t="inlineStr">
         <is>
-          <t>200K</t>
+          <t>62.8%</t>
         </is>
       </c>
       <c r="G105" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="106">
@@ -3437,31 +3437,31 @@
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>Average Hourly Earnings YoY</t>
+          <t>Non Farm PayrollsDEC</t>
         </is>
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>3.9%</t>
+          <t>256K</t>
         </is>
       </c>
       <c r="D106" t="inlineStr">
         <is>
-          <t>4%</t>
+          <t>212K</t>
         </is>
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>4%</t>
+          <t>160K</t>
         </is>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>4%</t>
+          <t>200K</t>
         </is>
       </c>
       <c r="G106" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="107">
@@ -3472,27 +3472,27 @@
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>Average Hourly Earnings MoMDEC</t>
+          <t>Average Hourly Earnings YoY</t>
         </is>
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>0.3%</t>
+          <t>3.9%</t>
         </is>
       </c>
       <c r="D107" t="inlineStr">
         <is>
-          <t>0.4%</t>
+          <t>4%</t>
         </is>
       </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t>0.3%</t>
+          <t>4%</t>
         </is>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>0.3%</t>
+          <t>4%</t>
         </is>
       </c>
       <c r="G107" t="n">
@@ -3507,27 +3507,31 @@
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>U-6 Unemployment Rate</t>
+          <t>Average Hourly Earnings MoMDEC</t>
         </is>
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>7.5%</t>
+          <t>0.3%</t>
         </is>
       </c>
       <c r="D108" t="inlineStr">
         <is>
-          <t>7.7%</t>
-        </is>
-      </c>
-      <c r="E108" t="inlineStr"/>
+          <t>0.4%</t>
+        </is>
+      </c>
+      <c r="E108" t="inlineStr">
+        <is>
+          <t>0.3%</t>
+        </is>
+      </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>7.9%</t>
+          <t>0.3%</t>
         </is>
       </c>
       <c r="G108" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="109">
@@ -3538,27 +3542,23 @@
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>Average Weekly HoursDEC</t>
+          <t>U-6 Unemployment Rate</t>
         </is>
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>34.3</t>
+          <t>7.5%</t>
         </is>
       </c>
       <c r="D109" t="inlineStr">
         <is>
-          <t>34.3</t>
-        </is>
-      </c>
-      <c r="E109" t="inlineStr">
-        <is>
-          <t>34.3</t>
-        </is>
-      </c>
+          <t>7.7%</t>
+        </is>
+      </c>
+      <c r="E109" t="inlineStr"/>
       <c r="F109" t="inlineStr">
         <is>
-          <t>34.3</t>
+          <t>7.9%</t>
         </is>
       </c>
       <c r="G109" t="n">
@@ -3573,23 +3573,27 @@
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>Government PayrollsDEC</t>
+          <t>Average Weekly HoursDEC</t>
         </is>
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>33K</t>
+          <t>34.3</t>
         </is>
       </c>
       <c r="D110" t="inlineStr">
         <is>
-          <t>30K</t>
-        </is>
-      </c>
-      <c r="E110" t="inlineStr"/>
+          <t>34.3</t>
+        </is>
+      </c>
+      <c r="E110" t="inlineStr">
+        <is>
+          <t>34.3</t>
+        </is>
+      </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>15K</t>
+          <t>34.3</t>
         </is>
       </c>
       <c r="G110" t="n">
@@ -3604,27 +3608,23 @@
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>Nonfarm Payrolls PrivateDEC</t>
+          <t>Government PayrollsDEC</t>
         </is>
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>223K</t>
+          <t>33K</t>
         </is>
       </c>
       <c r="D111" t="inlineStr">
         <is>
-          <t>182K</t>
-        </is>
-      </c>
-      <c r="E111" t="inlineStr">
-        <is>
-          <t>135K</t>
-        </is>
-      </c>
+          <t>30K</t>
+        </is>
+      </c>
+      <c r="E111" t="inlineStr"/>
       <c r="F111" t="inlineStr">
         <is>
-          <t>185K</t>
+          <t>15K</t>
         </is>
       </c>
       <c r="G111" t="n">
@@ -3674,31 +3674,27 @@
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>Michigan Consumer Sentiment PrelJAN</t>
+          <t>Michigan Consumer Expectations PrelJAN</t>
         </is>
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>73.2</t>
+          <t>70.2</t>
         </is>
       </c>
       <c r="D113" t="inlineStr">
         <is>
-          <t>74.0</t>
-        </is>
-      </c>
-      <c r="E113" t="inlineStr">
-        <is>
-          <t>73.8</t>
-        </is>
-      </c>
+          <t>73.3</t>
+        </is>
+      </c>
+      <c r="E113" t="inlineStr"/>
       <c r="F113" t="inlineStr">
         <is>
-          <t>75</t>
+          <t>74</t>
         </is>
       </c>
       <c r="G113" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="114">
@@ -3709,23 +3705,23 @@
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>Michigan Current Conditions PrelJAN</t>
+          <t>Michigan Inflation Expectations PrelJAN</t>
         </is>
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>77.9</t>
+          <t>3.3%</t>
         </is>
       </c>
       <c r="D114" t="inlineStr">
         <is>
-          <t>75.1</t>
+          <t>2.8%</t>
         </is>
       </c>
       <c r="E114" t="inlineStr"/>
       <c r="F114" t="inlineStr">
         <is>
-          <t>78</t>
+          <t>3.0%</t>
         </is>
       </c>
       <c r="G114" t="n">
@@ -3740,23 +3736,23 @@
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>Michigan 5 Year Inflation Expectations PrelJAN</t>
+          <t>Michigan Current Conditions PrelJAN</t>
         </is>
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>3.3%</t>
+          <t>77.9</t>
         </is>
       </c>
       <c r="D115" t="inlineStr">
         <is>
-          <t>3%</t>
+          <t>75.1</t>
         </is>
       </c>
       <c r="E115" t="inlineStr"/>
       <c r="F115" t="inlineStr">
         <is>
-          <t>3.2%</t>
+          <t>78</t>
         </is>
       </c>
       <c r="G115" t="n">
@@ -3771,27 +3767,31 @@
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t>Michigan Inflation Expectations PrelJAN</t>
+          <t>Michigan Consumer Sentiment PrelJAN</t>
         </is>
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>3.3%</t>
+          <t>73.2</t>
         </is>
       </c>
       <c r="D116" t="inlineStr">
         <is>
-          <t>2.8%</t>
-        </is>
-      </c>
-      <c r="E116" t="inlineStr"/>
+          <t>74.0</t>
+        </is>
+      </c>
+      <c r="E116" t="inlineStr">
+        <is>
+          <t>73.8</t>
+        </is>
+      </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>3.0%</t>
+          <t>75</t>
         </is>
       </c>
       <c r="G116" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="117">
@@ -3802,23 +3802,23 @@
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t>Michigan Consumer Expectations PrelJAN</t>
+          <t>Michigan 5 Year Inflation Expectations PrelJAN</t>
         </is>
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>70.2</t>
+          <t>3.3%</t>
         </is>
       </c>
       <c r="D117" t="inlineStr">
         <is>
-          <t>73.3</t>
+          <t>3%</t>
         </is>
       </c>
       <c r="E117" t="inlineStr"/>
       <c r="F117" t="inlineStr">
         <is>
-          <t>74</t>
+          <t>3.2%</t>
         </is>
       </c>
       <c r="G117" t="n">
@@ -4134,27 +4134,27 @@
       </c>
       <c r="B129" t="inlineStr">
         <is>
-          <t>Core PPI YoYDEC</t>
+          <t>PPI YoYDEC</t>
         </is>
       </c>
       <c r="C129" t="inlineStr">
         <is>
-          <t>3.5%</t>
+          <t>3.3%</t>
         </is>
       </c>
       <c r="D129" t="inlineStr">
         <is>
-          <t>3.5%</t>
+          <t>3%</t>
         </is>
       </c>
       <c r="E129" t="inlineStr">
         <is>
-          <t>3.8%</t>
+          <t>3.4%</t>
         </is>
       </c>
       <c r="F129" t="inlineStr">
         <is>
-          <t>3.5%</t>
+          <t>3.3%</t>
         </is>
       </c>
       <c r="G129" t="n">
@@ -4169,27 +4169,23 @@
       </c>
       <c r="B130" t="inlineStr">
         <is>
-          <t>PPI Ex Food, Energy and Trade MoMDEC</t>
+          <t>PPIDEC</t>
         </is>
       </c>
       <c r="C130" t="inlineStr">
         <is>
-          <t>0.1%</t>
+          <t>146.842</t>
         </is>
       </c>
       <c r="D130" t="inlineStr">
         <is>
-          <t>0.1%</t>
-        </is>
-      </c>
-      <c r="E130" t="inlineStr">
-        <is>
-          <t>0.3%</t>
-        </is>
-      </c>
+          <t>146.521</t>
+        </is>
+      </c>
+      <c r="E130" t="inlineStr"/>
       <c r="F130" t="inlineStr">
         <is>
-          <t>0.2%</t>
+          <t>146.8</t>
         </is>
       </c>
       <c r="G130" t="n">
@@ -4204,17 +4200,17 @@
       </c>
       <c r="B131" t="inlineStr">
         <is>
-          <t>Core PPI MoMDEC</t>
+          <t>PPI MoMDEC</t>
         </is>
       </c>
       <c r="C131" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>0.2%</t>
         </is>
       </c>
       <c r="D131" t="inlineStr">
         <is>
-          <t>0.2%</t>
+          <t>0.4%</t>
         </is>
       </c>
       <c r="E131" t="inlineStr">
@@ -4224,11 +4220,11 @@
       </c>
       <c r="F131" t="inlineStr">
         <is>
-          <t>0.2%</t>
+          <t>0.3%</t>
         </is>
       </c>
       <c r="G131" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="132">
@@ -4239,23 +4235,27 @@
       </c>
       <c r="B132" t="inlineStr">
         <is>
-          <t>PPI Ex Food, Energy and Trade YoYDEC</t>
+          <t>PPI Ex Food, Energy and Trade MoMDEC</t>
         </is>
       </c>
       <c r="C132" t="inlineStr">
         <is>
-          <t>3.3%</t>
+          <t>0.1%</t>
         </is>
       </c>
       <c r="D132" t="inlineStr">
         <is>
-          <t>3.5%</t>
-        </is>
-      </c>
-      <c r="E132" t="inlineStr"/>
+          <t>0.1%</t>
+        </is>
+      </c>
+      <c r="E132" t="inlineStr">
+        <is>
+          <t>0.3%</t>
+        </is>
+      </c>
       <c r="F132" t="inlineStr">
         <is>
-          <t>3.6%</t>
+          <t>0.2%</t>
         </is>
       </c>
       <c r="G132" t="n">
@@ -4270,19 +4270,19 @@
       </c>
       <c r="B133" t="inlineStr">
         <is>
-          <t>PPI MoMDEC</t>
+          <t>Core PPI MoMDEC</t>
         </is>
       </c>
       <c r="C133" t="inlineStr">
         <is>
+          <t>0%</t>
+        </is>
+      </c>
+      <c r="D133" t="inlineStr">
+        <is>
           <t>0.2%</t>
         </is>
       </c>
-      <c r="D133" t="inlineStr">
-        <is>
-          <t>0.4%</t>
-        </is>
-      </c>
       <c r="E133" t="inlineStr">
         <is>
           <t>0.3%</t>
@@ -4290,11 +4290,11 @@
       </c>
       <c r="F133" t="inlineStr">
         <is>
-          <t>0.3%</t>
+          <t>0.2%</t>
         </is>
       </c>
       <c r="G133" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="134">
@@ -4305,23 +4305,27 @@
       </c>
       <c r="B134" t="inlineStr">
         <is>
-          <t>PPIDEC</t>
+          <t>Core PPI YoYDEC</t>
         </is>
       </c>
       <c r="C134" t="inlineStr">
         <is>
-          <t>146.842</t>
+          <t>3.5%</t>
         </is>
       </c>
       <c r="D134" t="inlineStr">
         <is>
-          <t>146.521</t>
-        </is>
-      </c>
-      <c r="E134" t="inlineStr"/>
+          <t>3.5%</t>
+        </is>
+      </c>
+      <c r="E134" t="inlineStr">
+        <is>
+          <t>3.8%</t>
+        </is>
+      </c>
       <c r="F134" t="inlineStr">
         <is>
-          <t>146.8</t>
+          <t>3.5%</t>
         </is>
       </c>
       <c r="G134" t="n">
@@ -4336,7 +4340,7 @@
       </c>
       <c r="B135" t="inlineStr">
         <is>
-          <t>PPI YoYDEC</t>
+          <t>PPI Ex Food, Energy and Trade YoYDEC</t>
         </is>
       </c>
       <c r="C135" t="inlineStr">
@@ -4346,17 +4350,13 @@
       </c>
       <c r="D135" t="inlineStr">
         <is>
-          <t>3%</t>
-        </is>
-      </c>
-      <c r="E135" t="inlineStr">
-        <is>
-          <t>3.4%</t>
-        </is>
-      </c>
+          <t>3.5%</t>
+        </is>
+      </c>
+      <c r="E135" t="inlineStr"/>
       <c r="F135" t="inlineStr">
         <is>
-          <t>3.3%</t>
+          <t>3.6%</t>
         </is>
       </c>
       <c r="G135" t="n">
@@ -4564,23 +4564,23 @@
       </c>
       <c r="B143" t="inlineStr">
         <is>
-          <t>MBA Mortgage Refinance IndexJAN/10</t>
+          <t>MBA 30-Year Mortgage RateJAN/10</t>
         </is>
       </c>
       <c r="C143" t="inlineStr">
         <is>
-          <t>575.6</t>
+          <t>7.09%</t>
         </is>
       </c>
       <c r="D143" t="inlineStr">
         <is>
-          <t>401.1000</t>
+          <t>6.99%</t>
         </is>
       </c>
       <c r="E143" t="inlineStr"/>
       <c r="F143" t="inlineStr"/>
       <c r="G143" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="144">
@@ -4591,17 +4591,17 @@
       </c>
       <c r="B144" t="inlineStr">
         <is>
-          <t>MBA Mortgage ApplicationsJAN/10</t>
+          <t>MBA Purchase IndexJAN/10</t>
         </is>
       </c>
       <c r="C144" t="inlineStr">
         <is>
-          <t>33.3%</t>
+          <t>162</t>
         </is>
       </c>
       <c r="D144" t="inlineStr">
         <is>
-          <t>-3.7%</t>
+          <t>127.7000</t>
         </is>
       </c>
       <c r="E144" t="inlineStr"/>
@@ -4618,17 +4618,17 @@
       </c>
       <c r="B145" t="inlineStr">
         <is>
-          <t>MBA Purchase IndexJAN/10</t>
+          <t>MBA Mortgage Market IndexJAN/10</t>
         </is>
       </c>
       <c r="C145" t="inlineStr">
         <is>
-          <t>162</t>
+          <t>224.4</t>
         </is>
       </c>
       <c r="D145" t="inlineStr">
         <is>
-          <t>127.7000</t>
+          <t>168.4</t>
         </is>
       </c>
       <c r="E145" t="inlineStr"/>
@@ -4645,23 +4645,23 @@
       </c>
       <c r="B146" t="inlineStr">
         <is>
-          <t>MBA 30-Year Mortgage RateJAN/10</t>
+          <t>MBA Mortgage Refinance IndexJAN/10</t>
         </is>
       </c>
       <c r="C146" t="inlineStr">
         <is>
-          <t>7.09%</t>
+          <t>575.6</t>
         </is>
       </c>
       <c r="D146" t="inlineStr">
         <is>
-          <t>6.99%</t>
+          <t>401.1000</t>
         </is>
       </c>
       <c r="E146" t="inlineStr"/>
       <c r="F146" t="inlineStr"/>
       <c r="G146" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="147">
@@ -4672,17 +4672,17 @@
       </c>
       <c r="B147" t="inlineStr">
         <is>
-          <t>MBA Mortgage Market IndexJAN/10</t>
+          <t>MBA Mortgage ApplicationsJAN/10</t>
         </is>
       </c>
       <c r="C147" t="inlineStr">
         <is>
-          <t>224.4</t>
+          <t>33.3%</t>
         </is>
       </c>
       <c r="D147" t="inlineStr">
         <is>
-          <t>168.4</t>
+          <t>-3.7%</t>
         </is>
       </c>
       <c r="E147" t="inlineStr"/>
@@ -4978,17 +4978,17 @@
       </c>
       <c r="B157" t="inlineStr">
         <is>
-          <t>EIA Refinery Crude Runs ChangeJAN/10</t>
+          <t>EIA Gasoline Production ChangeJAN/10</t>
         </is>
       </c>
       <c r="C157" t="inlineStr">
         <is>
-          <t>-0.255M</t>
+          <t>0.397M</t>
         </is>
       </c>
       <c r="D157" t="inlineStr">
         <is>
-          <t>0.045M</t>
+          <t>-0.081M</t>
         </is>
       </c>
       <c r="E157" t="inlineStr"/>
@@ -5005,17 +5005,17 @@
       </c>
       <c r="B158" t="inlineStr">
         <is>
-          <t>EIA Cushing Crude Oil Stocks ChangeJAN/10</t>
+          <t>EIA Distillate Fuel Production ChangeJAN/10</t>
         </is>
       </c>
       <c r="C158" t="inlineStr">
         <is>
-          <t>0.765M</t>
+          <t>-0.021M</t>
         </is>
       </c>
       <c r="D158" t="inlineStr">
         <is>
-          <t>-2.502M</t>
+          <t>-0.167M</t>
         </is>
       </c>
       <c r="E158" t="inlineStr"/>
@@ -5032,22 +5032,22 @@
       </c>
       <c r="B159" t="inlineStr">
         <is>
-          <t>EIA Crude Oil Stocks ChangeJAN/10</t>
+          <t>EIA Gasoline Stocks ChangeJAN/10</t>
         </is>
       </c>
       <c r="C159" t="inlineStr">
         <is>
-          <t>-1.961M</t>
+          <t>5.852M</t>
         </is>
       </c>
       <c r="D159" t="inlineStr">
         <is>
-          <t>-0.959M</t>
+          <t>6.33M</t>
         </is>
       </c>
       <c r="E159" t="inlineStr">
         <is>
-          <t>-1.6M</t>
+          <t>2.60M</t>
         </is>
       </c>
       <c r="F159" t="inlineStr"/>
@@ -5063,24 +5063,20 @@
       </c>
       <c r="B160" t="inlineStr">
         <is>
-          <t>EIA Distillate Stocks ChangeJAN/10</t>
+          <t>EIA Heating Oil Stocks ChangeJAN/10</t>
         </is>
       </c>
       <c r="C160" t="inlineStr">
         <is>
-          <t>3.077M</t>
+          <t>0.646M</t>
         </is>
       </c>
       <c r="D160" t="inlineStr">
         <is>
-          <t>6.071M</t>
-        </is>
-      </c>
-      <c r="E160" t="inlineStr">
-        <is>
-          <t>1.1M</t>
-        </is>
-      </c>
+          <t>-0.632M</t>
+        </is>
+      </c>
+      <c r="E160" t="inlineStr"/>
       <c r="F160" t="inlineStr"/>
       <c r="G160" t="n">
         <v>3</v>
@@ -5094,17 +5090,17 @@
       </c>
       <c r="B161" t="inlineStr">
         <is>
-          <t>EIA Crude Oil Imports ChangeJAN/10</t>
+          <t>EIA Refinery Crude Runs ChangeJAN/10</t>
         </is>
       </c>
       <c r="C161" t="inlineStr">
         <is>
-          <t>-1.304M</t>
+          <t>-0.255M</t>
         </is>
       </c>
       <c r="D161" t="inlineStr">
         <is>
-          <t>0.278M</t>
+          <t>0.045M</t>
         </is>
       </c>
       <c r="E161" t="inlineStr"/>
@@ -5121,20 +5117,24 @@
       </c>
       <c r="B162" t="inlineStr">
         <is>
-          <t>EIA Heating Oil Stocks ChangeJAN/10</t>
+          <t>EIA Distillate Stocks ChangeJAN/10</t>
         </is>
       </c>
       <c r="C162" t="inlineStr">
         <is>
-          <t>0.646M</t>
+          <t>3.077M</t>
         </is>
       </c>
       <c r="D162" t="inlineStr">
         <is>
-          <t>-0.632M</t>
-        </is>
-      </c>
-      <c r="E162" t="inlineStr"/>
+          <t>6.071M</t>
+        </is>
+      </c>
+      <c r="E162" t="inlineStr">
+        <is>
+          <t>1.1M</t>
+        </is>
+      </c>
       <c r="F162" t="inlineStr"/>
       <c r="G162" t="n">
         <v>3</v>
@@ -5148,22 +5148,22 @@
       </c>
       <c r="B163" t="inlineStr">
         <is>
-          <t>EIA Gasoline Stocks ChangeJAN/10</t>
+          <t>EIA Crude Oil Stocks ChangeJAN/10</t>
         </is>
       </c>
       <c r="C163" t="inlineStr">
         <is>
-          <t>5.852M</t>
+          <t>-1.961M</t>
         </is>
       </c>
       <c r="D163" t="inlineStr">
         <is>
-          <t>6.33M</t>
+          <t>-0.959M</t>
         </is>
       </c>
       <c r="E163" t="inlineStr">
         <is>
-          <t>2.60M</t>
+          <t>-1.6M</t>
         </is>
       </c>
       <c r="F163" t="inlineStr"/>
@@ -5179,17 +5179,17 @@
       </c>
       <c r="B164" t="inlineStr">
         <is>
-          <t>EIA Distillate Fuel Production ChangeJAN/10</t>
+          <t>EIA Cushing Crude Oil Stocks ChangeJAN/10</t>
         </is>
       </c>
       <c r="C164" t="inlineStr">
         <is>
-          <t>-0.021M</t>
+          <t>0.765M</t>
         </is>
       </c>
       <c r="D164" t="inlineStr">
         <is>
-          <t>-0.167M</t>
+          <t>-2.502M</t>
         </is>
       </c>
       <c r="E164" t="inlineStr"/>
@@ -5206,17 +5206,17 @@
       </c>
       <c r="B165" t="inlineStr">
         <is>
-          <t>EIA Gasoline Production ChangeJAN/10</t>
+          <t>EIA Crude Oil Imports ChangeJAN/10</t>
         </is>
       </c>
       <c r="C165" t="inlineStr">
         <is>
-          <t>0.397M</t>
+          <t>-1.304M</t>
         </is>
       </c>
       <c r="D165" t="inlineStr">
         <is>
-          <t>-0.081M</t>
+          <t>0.278M</t>
         </is>
       </c>
       <c r="E165" t="inlineStr"/>
@@ -5336,27 +5336,23 @@
       </c>
       <c r="B171" t="inlineStr">
         <is>
-          <t>Import Prices YoYDEC</t>
+          <t>Export Prices YoYDEC</t>
         </is>
       </c>
       <c r="C171" t="inlineStr">
         <is>
-          <t>2.2%</t>
+          <t>1.8%</t>
         </is>
       </c>
       <c r="D171" t="inlineStr">
         <is>
-          <t>1.4%</t>
-        </is>
-      </c>
-      <c r="E171" t="inlineStr">
-        <is>
-          <t>2.1%</t>
-        </is>
-      </c>
+          <t>0.9%</t>
+        </is>
+      </c>
+      <c r="E171" t="inlineStr"/>
       <c r="F171" t="inlineStr">
         <is>
-          <t>1.6%</t>
+          <t>1.9%</t>
         </is>
       </c>
       <c r="G171" t="n">
@@ -5371,21 +5367,29 @@
       </c>
       <c r="B172" t="inlineStr">
         <is>
-          <t>Philly Fed CAPEX IndexJAN</t>
+          <t>Retail Sales Ex Gas/Autos MoMDEC</t>
         </is>
       </c>
       <c r="C172" t="inlineStr">
         <is>
-          <t>39.00</t>
+          <t>0.3%</t>
         </is>
       </c>
       <c r="D172" t="inlineStr">
         <is>
-          <t>22.20</t>
-        </is>
-      </c>
-      <c r="E172" t="inlineStr"/>
-      <c r="F172" t="inlineStr"/>
+          <t>0.2%</t>
+        </is>
+      </c>
+      <c r="E172" t="inlineStr">
+        <is>
+          <t>0.4%</t>
+        </is>
+      </c>
+      <c r="F172" t="inlineStr">
+        <is>
+          <t>0.4%</t>
+        </is>
+      </c>
       <c r="G172" t="n">
         <v>3</v>
       </c>
@@ -5398,31 +5402,23 @@
       </c>
       <c r="B173" t="inlineStr">
         <is>
-          <t>Import Prices MoMDEC</t>
+          <t>Philly Fed Business ConditionsJAN</t>
         </is>
       </c>
       <c r="C173" t="inlineStr">
         <is>
-          <t>0.1%</t>
+          <t>46.3</t>
         </is>
       </c>
       <c r="D173" t="inlineStr">
         <is>
-          <t>0.1%</t>
-        </is>
-      </c>
-      <c r="E173" t="inlineStr">
-        <is>
-          <t>0.1%</t>
-        </is>
-      </c>
-      <c r="F173" t="inlineStr">
-        <is>
-          <t>0.1%</t>
-        </is>
-      </c>
+          <t>33.8</t>
+        </is>
+      </c>
+      <c r="E173" t="inlineStr"/>
+      <c r="F173" t="inlineStr"/>
       <c r="G173" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="174">
@@ -5433,23 +5429,31 @@
       </c>
       <c r="B174" t="inlineStr">
         <is>
-          <t>Philly Fed EmploymentJAN</t>
+          <t>Retail Sales Ex Autos MoMDEC</t>
         </is>
       </c>
       <c r="C174" t="inlineStr">
         <is>
-          <t>11.9</t>
+          <t>0.4%</t>
         </is>
       </c>
       <c r="D174" t="inlineStr">
         <is>
-          <t>4.8</t>
-        </is>
-      </c>
-      <c r="E174" t="inlineStr"/>
-      <c r="F174" t="inlineStr"/>
+          <t>0.2%</t>
+        </is>
+      </c>
+      <c r="E174" t="inlineStr">
+        <is>
+          <t>0.4%</t>
+        </is>
+      </c>
+      <c r="F174" t="inlineStr">
+        <is>
+          <t>0.4%</t>
+        </is>
+      </c>
       <c r="G174" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="175">
@@ -5460,25 +5464,21 @@
       </c>
       <c r="B175" t="inlineStr">
         <is>
-          <t>Jobless Claims 4-week AverageJAN/11</t>
+          <t>Philly Fed Prices PaidJAN</t>
         </is>
       </c>
       <c r="C175" t="inlineStr">
         <is>
-          <t>212.75K</t>
+          <t>31.90</t>
         </is>
       </c>
       <c r="D175" t="inlineStr">
         <is>
-          <t>213.5K</t>
+          <t>26.60</t>
         </is>
       </c>
       <c r="E175" t="inlineStr"/>
-      <c r="F175" t="inlineStr">
-        <is>
-          <t>215.0K</t>
-        </is>
-      </c>
+      <c r="F175" t="inlineStr"/>
       <c r="G175" t="n">
         <v>3</v>
       </c>
@@ -5491,31 +5491,27 @@
       </c>
       <c r="B176" t="inlineStr">
         <is>
-          <t>Retail Sales MoMDEC</t>
+          <t>Retail Sales YoYDEC</t>
         </is>
       </c>
       <c r="C176" t="inlineStr">
         <is>
-          <t>0.4%</t>
+          <t>3.9%</t>
         </is>
       </c>
       <c r="D176" t="inlineStr">
         <is>
-          <t>0.8%</t>
-        </is>
-      </c>
-      <c r="E176" t="inlineStr">
-        <is>
-          <t>0.6%</t>
-        </is>
-      </c>
+          <t>4.1%</t>
+        </is>
+      </c>
+      <c r="E176" t="inlineStr"/>
       <c r="F176" t="inlineStr">
         <is>
-          <t>0.5%</t>
+          <t>4.0%</t>
         </is>
       </c>
       <c r="G176" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="177">
@@ -5526,21 +5522,29 @@
       </c>
       <c r="B177" t="inlineStr">
         <is>
-          <t>Philly Fed New OrdersJAN</t>
+          <t>Continuing Jobless ClaimsJAN/04</t>
         </is>
       </c>
       <c r="C177" t="inlineStr">
         <is>
-          <t>42.9</t>
+          <t>1859K</t>
         </is>
       </c>
       <c r="D177" t="inlineStr">
         <is>
-          <t>-3.6</t>
-        </is>
-      </c>
-      <c r="E177" t="inlineStr"/>
-      <c r="F177" t="inlineStr"/>
+          <t>1867K</t>
+        </is>
+      </c>
+      <c r="E177" t="inlineStr">
+        <is>
+          <t>1870K</t>
+        </is>
+      </c>
+      <c r="F177" t="inlineStr">
+        <is>
+          <t>1870.0K</t>
+        </is>
+      </c>
       <c r="G177" t="n">
         <v>3</v>
       </c>
@@ -5553,27 +5557,27 @@
       </c>
       <c r="B178" t="inlineStr">
         <is>
-          <t>Initial Jobless ClaimsJAN/11</t>
+          <t>Export Prices MoMDEC</t>
         </is>
       </c>
       <c r="C178" t="inlineStr">
         <is>
-          <t>217K</t>
+          <t>0.3%</t>
         </is>
       </c>
       <c r="D178" t="inlineStr">
         <is>
-          <t>203K</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="E178" t="inlineStr">
         <is>
-          <t>210K</t>
+          <t>0.2%</t>
         </is>
       </c>
       <c r="F178" t="inlineStr">
         <is>
-          <t>209.0K</t>
+          <t>0.5%</t>
         </is>
       </c>
       <c r="G178" t="n">
@@ -5588,31 +5592,31 @@
       </c>
       <c r="B179" t="inlineStr">
         <is>
-          <t>Philadelphia Fed Manufacturing IndexJAN</t>
+          <t>Import Prices YoYDEC</t>
         </is>
       </c>
       <c r="C179" t="inlineStr">
         <is>
-          <t>44.3</t>
+          <t>2.2%</t>
         </is>
       </c>
       <c r="D179" t="inlineStr">
         <is>
-          <t>-10.9</t>
+          <t>1.4%</t>
         </is>
       </c>
       <c r="E179" t="inlineStr">
         <is>
-          <t>-5</t>
+          <t>2.1%</t>
         </is>
       </c>
       <c r="F179" t="inlineStr">
         <is>
-          <t>-10</t>
+          <t>1.6%</t>
         </is>
       </c>
       <c r="G179" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="180">
@@ -5623,27 +5627,27 @@
       </c>
       <c r="B180" t="inlineStr">
         <is>
-          <t>Export Prices MoMDEC</t>
+          <t>Initial Jobless ClaimsJAN/11</t>
         </is>
       </c>
       <c r="C180" t="inlineStr">
         <is>
-          <t>0.3%</t>
+          <t>217K</t>
         </is>
       </c>
       <c r="D180" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>203K</t>
         </is>
       </c>
       <c r="E180" t="inlineStr">
         <is>
-          <t>0.2%</t>
+          <t>210K</t>
         </is>
       </c>
       <c r="F180" t="inlineStr">
         <is>
-          <t>0.5%</t>
+          <t>209.0K</t>
         </is>
       </c>
       <c r="G180" t="n">
@@ -5658,25 +5662,21 @@
       </c>
       <c r="B181" t="inlineStr">
         <is>
-          <t>Export Prices YoYDEC</t>
+          <t>Philly Fed CAPEX IndexJAN</t>
         </is>
       </c>
       <c r="C181" t="inlineStr">
         <is>
-          <t>1.8%</t>
+          <t>39.00</t>
         </is>
       </c>
       <c r="D181" t="inlineStr">
         <is>
-          <t>0.9%</t>
+          <t>22.20</t>
         </is>
       </c>
       <c r="E181" t="inlineStr"/>
-      <c r="F181" t="inlineStr">
-        <is>
-          <t>1.9%</t>
-        </is>
-      </c>
+      <c r="F181" t="inlineStr"/>
       <c r="G181" t="n">
         <v>3</v>
       </c>
@@ -5689,27 +5689,31 @@
       </c>
       <c r="B182" t="inlineStr">
         <is>
-          <t>Retail Sales YoYDEC</t>
+          <t>Import Prices MoMDEC</t>
         </is>
       </c>
       <c r="C182" t="inlineStr">
         <is>
-          <t>3.9%</t>
+          <t>0.1%</t>
         </is>
       </c>
       <c r="D182" t="inlineStr">
         <is>
-          <t>4.1%</t>
-        </is>
-      </c>
-      <c r="E182" t="inlineStr"/>
+          <t>0.1%</t>
+        </is>
+      </c>
+      <c r="E182" t="inlineStr">
+        <is>
+          <t>0.1%</t>
+        </is>
+      </c>
       <c r="F182" t="inlineStr">
         <is>
-          <t>4.0%</t>
+          <t>0.1%</t>
         </is>
       </c>
       <c r="G182" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="183">
@@ -5720,17 +5724,17 @@
       </c>
       <c r="B183" t="inlineStr">
         <is>
-          <t>Philly Fed Prices PaidJAN</t>
+          <t>Philly Fed EmploymentJAN</t>
         </is>
       </c>
       <c r="C183" t="inlineStr">
         <is>
-          <t>31.90</t>
+          <t>11.9</t>
         </is>
       </c>
       <c r="D183" t="inlineStr">
         <is>
-          <t>26.60</t>
+          <t>4.8</t>
         </is>
       </c>
       <c r="E183" t="inlineStr"/>
@@ -5747,27 +5751,27 @@
       </c>
       <c r="B184" t="inlineStr">
         <is>
-          <t>Retail Sales Ex Autos MoMDEC</t>
+          <t>Philadelphia Fed Manufacturing IndexJAN</t>
         </is>
       </c>
       <c r="C184" t="inlineStr">
         <is>
-          <t>0.4%</t>
+          <t>44.3</t>
         </is>
       </c>
       <c r="D184" t="inlineStr">
         <is>
-          <t>0.2%</t>
+          <t>-10.9</t>
         </is>
       </c>
       <c r="E184" t="inlineStr">
         <is>
-          <t>0.4%</t>
+          <t>-5</t>
         </is>
       </c>
       <c r="F184" t="inlineStr">
         <is>
-          <t>0.4%</t>
+          <t>-10</t>
         </is>
       </c>
       <c r="G184" t="n">
@@ -5782,23 +5786,31 @@
       </c>
       <c r="B185" t="inlineStr">
         <is>
-          <t>Philly Fed Business ConditionsJAN</t>
+          <t>Retail Sales MoMDEC</t>
         </is>
       </c>
       <c r="C185" t="inlineStr">
         <is>
-          <t>46.3</t>
+          <t>0.4%</t>
         </is>
       </c>
       <c r="D185" t="inlineStr">
         <is>
-          <t>33.8</t>
-        </is>
-      </c>
-      <c r="E185" t="inlineStr"/>
-      <c r="F185" t="inlineStr"/>
+          <t>0.8%</t>
+        </is>
+      </c>
+      <c r="E185" t="inlineStr">
+        <is>
+          <t>0.6%</t>
+        </is>
+      </c>
+      <c r="F185" t="inlineStr">
+        <is>
+          <t>0.5%</t>
+        </is>
+      </c>
       <c r="G185" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="186">
@@ -5809,29 +5821,21 @@
       </c>
       <c r="B186" t="inlineStr">
         <is>
-          <t>Retail Sales Ex Gas/Autos MoMDEC</t>
+          <t>Philly Fed New OrdersJAN</t>
         </is>
       </c>
       <c r="C186" t="inlineStr">
         <is>
-          <t>0.3%</t>
+          <t>42.9</t>
         </is>
       </c>
       <c r="D186" t="inlineStr">
         <is>
-          <t>0.2%</t>
-        </is>
-      </c>
-      <c r="E186" t="inlineStr">
-        <is>
-          <t>0.4%</t>
-        </is>
-      </c>
-      <c r="F186" t="inlineStr">
-        <is>
-          <t>0.4%</t>
-        </is>
-      </c>
+          <t>-3.6</t>
+        </is>
+      </c>
+      <c r="E186" t="inlineStr"/>
+      <c r="F186" t="inlineStr"/>
       <c r="G186" t="n">
         <v>3</v>
       </c>
@@ -5844,27 +5848,23 @@
       </c>
       <c r="B187" t="inlineStr">
         <is>
-          <t>Continuing Jobless ClaimsJAN/04</t>
+          <t>Jobless Claims 4-week AverageJAN/11</t>
         </is>
       </c>
       <c r="C187" t="inlineStr">
         <is>
-          <t>1859K</t>
+          <t>212.75K</t>
         </is>
       </c>
       <c r="D187" t="inlineStr">
         <is>
-          <t>1867K</t>
-        </is>
-      </c>
-      <c r="E187" t="inlineStr">
-        <is>
-          <t>1870K</t>
-        </is>
-      </c>
+          <t>213.5K</t>
+        </is>
+      </c>
+      <c r="E187" t="inlineStr"/>
       <c r="F187" t="inlineStr">
         <is>
-          <t>1870.0K</t>
+          <t>215.0K</t>
         </is>
       </c>
       <c r="G187" t="n">
@@ -6282,27 +6282,27 @@
       </c>
       <c r="B201" t="inlineStr">
         <is>
-          <t>Capacity UtilizationDEC</t>
+          <t>Manufacturing Production MoMDEC</t>
         </is>
       </c>
       <c r="C201" t="inlineStr">
         <is>
-          <t>77.6%</t>
+          <t>0.6%</t>
         </is>
       </c>
       <c r="D201" t="inlineStr">
         <is>
-          <t>77%</t>
+          <t>0.4%</t>
         </is>
       </c>
       <c r="E201" t="inlineStr">
         <is>
-          <t>77%</t>
+          <t>0.2%</t>
         </is>
       </c>
       <c r="F201" t="inlineStr">
         <is>
-          <t>76.9%</t>
+          <t>0.4%</t>
         </is>
       </c>
       <c r="G201" t="n">
@@ -6317,12 +6317,12 @@
       </c>
       <c r="B202" t="inlineStr">
         <is>
-          <t>Industrial Production YoYDEC</t>
+          <t>Manufacturing Production YoYDEC</t>
         </is>
       </c>
       <c r="C202" t="inlineStr">
         <is>
-          <t>0.5%</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="D202" t="inlineStr">
@@ -6333,7 +6333,7 @@
       <c r="E202" t="inlineStr"/>
       <c r="F202" t="inlineStr">
         <is>
-          <t>-0.5%</t>
+          <t>-0.7%</t>
         </is>
       </c>
       <c r="G202" t="n">
@@ -6348,31 +6348,27 @@
       </c>
       <c r="B203" t="inlineStr">
         <is>
-          <t>Industrial Production MoMDEC</t>
+          <t>Industrial Production YoYDEC</t>
         </is>
       </c>
       <c r="C203" t="inlineStr">
         <is>
-          <t>0.9%</t>
+          <t>0.5%</t>
         </is>
       </c>
       <c r="D203" t="inlineStr">
         <is>
-          <t>0.2%</t>
-        </is>
-      </c>
-      <c r="E203" t="inlineStr">
-        <is>
-          <t>0.3%</t>
-        </is>
-      </c>
+          <t>-0.6%</t>
+        </is>
+      </c>
+      <c r="E203" t="inlineStr"/>
       <c r="F203" t="inlineStr">
         <is>
-          <t>0.1%</t>
+          <t>-0.5%</t>
         </is>
       </c>
       <c r="G203" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="204">
@@ -6383,23 +6379,27 @@
       </c>
       <c r="B204" t="inlineStr">
         <is>
-          <t>Manufacturing Production YoYDEC</t>
+          <t>Capacity UtilizationDEC</t>
         </is>
       </c>
       <c r="C204" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>77.6%</t>
         </is>
       </c>
       <c r="D204" t="inlineStr">
         <is>
-          <t>-0.6%</t>
-        </is>
-      </c>
-      <c r="E204" t="inlineStr"/>
+          <t>77%</t>
+        </is>
+      </c>
+      <c r="E204" t="inlineStr">
+        <is>
+          <t>77%</t>
+        </is>
+      </c>
       <c r="F204" t="inlineStr">
         <is>
-          <t>-0.7%</t>
+          <t>76.9%</t>
         </is>
       </c>
       <c r="G204" t="n">
@@ -6414,31 +6414,31 @@
       </c>
       <c r="B205" t="inlineStr">
         <is>
-          <t>Manufacturing Production MoMDEC</t>
+          <t>Industrial Production MoMDEC</t>
         </is>
       </c>
       <c r="C205" t="inlineStr">
         <is>
-          <t>0.6%</t>
+          <t>0.9%</t>
         </is>
       </c>
       <c r="D205" t="inlineStr">
         <is>
-          <t>0.4%</t>
+          <t>0.2%</t>
         </is>
       </c>
       <c r="E205" t="inlineStr">
         <is>
-          <t>0.2%</t>
+          <t>0.3%</t>
         </is>
       </c>
       <c r="F205" t="inlineStr">
         <is>
-          <t>0.4%</t>
+          <t>0.1%</t>
         </is>
       </c>
       <c r="G205" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="206">
@@ -6661,17 +6661,17 @@
       </c>
       <c r="B214" t="inlineStr">
         <is>
-          <t>52-Week Bill Auction</t>
+          <t>42-Day Bill Auction</t>
         </is>
       </c>
       <c r="C214" t="inlineStr">
         <is>
-          <t>4.025%</t>
+          <t>4.250%</t>
         </is>
       </c>
       <c r="D214" t="inlineStr">
         <is>
-          <t>4.070%</t>
+          <t>4.210%</t>
         </is>
       </c>
       <c r="E214" t="inlineStr"/>
@@ -6688,17 +6688,17 @@
       </c>
       <c r="B215" t="inlineStr">
         <is>
-          <t>42-Day Bill Auction</t>
+          <t>52-Week Bill Auction</t>
         </is>
       </c>
       <c r="C215" t="inlineStr">
         <is>
-          <t>4.250%</t>
+          <t>4.025%</t>
         </is>
       </c>
       <c r="D215" t="inlineStr">
         <is>
-          <t>4.210%</t>
+          <t>4.070%</t>
         </is>
       </c>
       <c r="E215" t="inlineStr"/>
@@ -6993,27 +6993,23 @@
       </c>
       <c r="B226" t="inlineStr">
         <is>
-          <t>Continuing Jobless ClaimsJAN/11</t>
+          <t>Jobless Claims 4-week AverageJAN/18</t>
         </is>
       </c>
       <c r="C226" t="inlineStr">
         <is>
-          <t>1899K</t>
+          <t>213.5K</t>
         </is>
       </c>
       <c r="D226" t="inlineStr">
         <is>
-          <t>1853K</t>
-        </is>
-      </c>
-      <c r="E226" t="inlineStr">
-        <is>
-          <t>1860K</t>
-        </is>
-      </c>
+          <t>212.75K</t>
+        </is>
+      </c>
+      <c r="E226" t="inlineStr"/>
       <c r="F226" t="inlineStr">
         <is>
-          <t>1861K</t>
+          <t>213.0K</t>
         </is>
       </c>
       <c r="G226" t="n">
@@ -7063,23 +7059,27 @@
       </c>
       <c r="B228" t="inlineStr">
         <is>
-          <t>Jobless Claims 4-week AverageJAN/18</t>
+          <t>Continuing Jobless ClaimsJAN/11</t>
         </is>
       </c>
       <c r="C228" t="inlineStr">
         <is>
-          <t>213.5K</t>
+          <t>1899K</t>
         </is>
       </c>
       <c r="D228" t="inlineStr">
         <is>
-          <t>212.75K</t>
-        </is>
-      </c>
-      <c r="E228" t="inlineStr"/>
+          <t>1853K</t>
+        </is>
+      </c>
+      <c r="E228" t="inlineStr">
+        <is>
+          <t>1860K</t>
+        </is>
+      </c>
       <c r="F228" t="inlineStr">
         <is>
-          <t>213.0K</t>
+          <t>1861K</t>
         </is>
       </c>
       <c r="G228" t="n">
@@ -7241,17 +7241,17 @@
       </c>
       <c r="B234" t="inlineStr">
         <is>
-          <t>EIA Refinery Crude Runs ChangeJAN/17</t>
+          <t>EIA Distillate Fuel Production ChangeJAN/17</t>
         </is>
       </c>
       <c r="C234" t="inlineStr">
         <is>
-          <t>-1.125M</t>
+          <t>-0.473M</t>
         </is>
       </c>
       <c r="D234" t="inlineStr">
         <is>
-          <t>-0.255M</t>
+          <t>-0.021M</t>
         </is>
       </c>
       <c r="E234" t="inlineStr"/>
@@ -7268,20 +7268,24 @@
       </c>
       <c r="B235" t="inlineStr">
         <is>
-          <t>EIA Crude Oil Imports ChangeJAN/17</t>
+          <t>EIA Distillate Stocks ChangeJAN/17</t>
         </is>
       </c>
       <c r="C235" t="inlineStr">
         <is>
-          <t>0.184M</t>
+          <t>-3.07M</t>
         </is>
       </c>
       <c r="D235" t="inlineStr">
         <is>
-          <t>-1.304M</t>
-        </is>
-      </c>
-      <c r="E235" t="inlineStr"/>
+          <t>3.077M</t>
+        </is>
+      </c>
+      <c r="E235" t="inlineStr">
+        <is>
+          <t>0.6M</t>
+        </is>
+      </c>
       <c r="F235" t="inlineStr"/>
       <c r="G235" t="n">
         <v>3</v>
@@ -7295,27 +7299,23 @@
       </c>
       <c r="B236" t="inlineStr">
         <is>
-          <t>EIA Crude Oil Stocks ChangeJAN/17</t>
+          <t>EIA Heating Oil Stocks ChangeJAN/17</t>
         </is>
       </c>
       <c r="C236" t="inlineStr">
         <is>
-          <t>-1.017M</t>
+          <t>0.068M</t>
         </is>
       </c>
       <c r="D236" t="inlineStr">
         <is>
-          <t>-1.962M</t>
-        </is>
-      </c>
-      <c r="E236" t="inlineStr">
-        <is>
-          <t>-2.1M</t>
-        </is>
-      </c>
+          <t>0.646M</t>
+        </is>
+      </c>
+      <c r="E236" t="inlineStr"/>
       <c r="F236" t="inlineStr"/>
       <c r="G236" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="237">
@@ -7326,17 +7326,17 @@
       </c>
       <c r="B237" t="inlineStr">
         <is>
-          <t>EIA Cushing Crude Oil Stocks ChangeJAN/17</t>
+          <t>EIA Gasoline Production ChangeJAN/17</t>
         </is>
       </c>
       <c r="C237" t="inlineStr">
         <is>
-          <t>-0.148M</t>
+          <t>-0.043M</t>
         </is>
       </c>
       <c r="D237" t="inlineStr">
         <is>
-          <t>0.765M</t>
+          <t>0.397M</t>
         </is>
       </c>
       <c r="E237" t="inlineStr"/>
@@ -7353,27 +7353,23 @@
       </c>
       <c r="B238" t="inlineStr">
         <is>
-          <t>EIA Gasoline Stocks ChangeJAN/17</t>
+          <t>30-Year Mortgage RateJAN/23</t>
         </is>
       </c>
       <c r="C238" t="inlineStr">
         <is>
-          <t>2.332M</t>
+          <t>6.96%</t>
         </is>
       </c>
       <c r="D238" t="inlineStr">
         <is>
-          <t>5.852M</t>
-        </is>
-      </c>
-      <c r="E238" t="inlineStr">
-        <is>
-          <t>2.5M</t>
-        </is>
-      </c>
+          <t>7.04%</t>
+        </is>
+      </c>
+      <c r="E238" t="inlineStr"/>
       <c r="F238" t="inlineStr"/>
       <c r="G238" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="239">
@@ -7384,17 +7380,17 @@
       </c>
       <c r="B239" t="inlineStr">
         <is>
-          <t>30-Year Mortgage RateJAN/23</t>
+          <t>15-Year Mortgage RateJAN/23</t>
         </is>
       </c>
       <c r="C239" t="inlineStr">
         <is>
-          <t>6.96%</t>
+          <t>6.16%</t>
         </is>
       </c>
       <c r="D239" t="inlineStr">
         <is>
-          <t>7.04%</t>
+          <t>6.27%</t>
         </is>
       </c>
       <c r="E239" t="inlineStr"/>
@@ -7411,17 +7407,17 @@
       </c>
       <c r="B240" t="inlineStr">
         <is>
-          <t>15-Year Mortgage RateJAN/23</t>
+          <t>EIA Cushing Crude Oil Stocks ChangeJAN/17</t>
         </is>
       </c>
       <c r="C240" t="inlineStr">
         <is>
-          <t>6.16%</t>
+          <t>-0.148M</t>
         </is>
       </c>
       <c r="D240" t="inlineStr">
         <is>
-          <t>6.27%</t>
+          <t>0.765M</t>
         </is>
       </c>
       <c r="E240" t="inlineStr"/>
@@ -7438,23 +7434,27 @@
       </c>
       <c r="B241" t="inlineStr">
         <is>
-          <t>EIA Gasoline Production ChangeJAN/17</t>
+          <t>EIA Crude Oil Stocks ChangeJAN/17</t>
         </is>
       </c>
       <c r="C241" t="inlineStr">
         <is>
-          <t>-0.043M</t>
+          <t>-1.017M</t>
         </is>
       </c>
       <c r="D241" t="inlineStr">
         <is>
-          <t>0.397M</t>
-        </is>
-      </c>
-      <c r="E241" t="inlineStr"/>
+          <t>-1.962M</t>
+        </is>
+      </c>
+      <c r="E241" t="inlineStr">
+        <is>
+          <t>-2.1M</t>
+        </is>
+      </c>
       <c r="F241" t="inlineStr"/>
       <c r="G241" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="242">
@@ -7465,17 +7465,17 @@
       </c>
       <c r="B242" t="inlineStr">
         <is>
-          <t>EIA Heating Oil Stocks ChangeJAN/17</t>
+          <t>EIA Crude Oil Imports ChangeJAN/17</t>
         </is>
       </c>
       <c r="C242" t="inlineStr">
         <is>
-          <t>0.068M</t>
+          <t>0.184M</t>
         </is>
       </c>
       <c r="D242" t="inlineStr">
         <is>
-          <t>0.646M</t>
+          <t>-1.304M</t>
         </is>
       </c>
       <c r="E242" t="inlineStr"/>
@@ -7492,24 +7492,20 @@
       </c>
       <c r="B243" t="inlineStr">
         <is>
-          <t>EIA Distillate Stocks ChangeJAN/17</t>
+          <t>EIA Refinery Crude Runs ChangeJAN/17</t>
         </is>
       </c>
       <c r="C243" t="inlineStr">
         <is>
-          <t>-3.07M</t>
+          <t>-1.125M</t>
         </is>
       </c>
       <c r="D243" t="inlineStr">
         <is>
-          <t>3.077M</t>
-        </is>
-      </c>
-      <c r="E243" t="inlineStr">
-        <is>
-          <t>0.6M</t>
-        </is>
-      </c>
+          <t>-0.255M</t>
+        </is>
+      </c>
+      <c r="E243" t="inlineStr"/>
       <c r="F243" t="inlineStr"/>
       <c r="G243" t="n">
         <v>3</v>
@@ -7523,23 +7519,27 @@
       </c>
       <c r="B244" t="inlineStr">
         <is>
-          <t>EIA Distillate Fuel Production ChangeJAN/17</t>
+          <t>EIA Gasoline Stocks ChangeJAN/17</t>
         </is>
       </c>
       <c r="C244" t="inlineStr">
         <is>
-          <t>-0.473M</t>
+          <t>2.332M</t>
         </is>
       </c>
       <c r="D244" t="inlineStr">
         <is>
-          <t>-0.021M</t>
-        </is>
-      </c>
-      <c r="E244" t="inlineStr"/>
+          <t>5.852M</t>
+        </is>
+      </c>
+      <c r="E244" t="inlineStr">
+        <is>
+          <t>2.5M</t>
+        </is>
+      </c>
       <c r="F244" t="inlineStr"/>
       <c r="G244" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="245">
@@ -7705,17 +7705,17 @@
       </c>
       <c r="B250" t="inlineStr">
         <is>
-          <t>Michigan Inflation Expectations FinalJAN</t>
+          <t>Michigan 5 Year Inflation Expectations FinalJAN</t>
         </is>
       </c>
       <c r="C250" t="inlineStr">
         <is>
-          <t>3.3%</t>
+          <t>3.2%</t>
         </is>
       </c>
       <c r="D250" t="inlineStr">
         <is>
-          <t>2.8%</t>
+          <t>3%</t>
         </is>
       </c>
       <c r="E250" t="inlineStr">
@@ -7740,31 +7740,27 @@
       </c>
       <c r="B251" t="inlineStr">
         <is>
-          <t>Michigan Current Conditions FinalJAN</t>
+          <t>Existing Home Sales MoMDEC</t>
         </is>
       </c>
       <c r="C251" t="inlineStr">
         <is>
-          <t>74.0</t>
+          <t>2.2%</t>
         </is>
       </c>
       <c r="D251" t="inlineStr">
         <is>
-          <t>75.1</t>
-        </is>
-      </c>
-      <c r="E251" t="inlineStr">
-        <is>
-          <t>77.9</t>
-        </is>
-      </c>
+          <t>4.8%</t>
+        </is>
+      </c>
+      <c r="E251" t="inlineStr"/>
       <c r="F251" t="inlineStr">
         <is>
-          <t>77.9</t>
+          <t>0.3%</t>
         </is>
       </c>
       <c r="G251" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="252">
@@ -7775,31 +7771,31 @@
       </c>
       <c r="B252" t="inlineStr">
         <is>
-          <t>Michigan Consumer Sentiment FinalJAN</t>
+          <t>Michigan Consumer Expectations FinalJAN</t>
         </is>
       </c>
       <c r="C252" t="inlineStr">
         <is>
-          <t>71.1</t>
+          <t>69.3</t>
         </is>
       </c>
       <c r="D252" t="inlineStr">
         <is>
-          <t>74.0</t>
+          <t>73.3</t>
         </is>
       </c>
       <c r="E252" t="inlineStr">
         <is>
-          <t>73.2</t>
+          <t>70.2</t>
         </is>
       </c>
       <c r="F252" t="inlineStr">
         <is>
-          <t>73.2</t>
+          <t>70.2</t>
         </is>
       </c>
       <c r="G252" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="253">
@@ -7810,31 +7806,31 @@
       </c>
       <c r="B253" t="inlineStr">
         <is>
-          <t>Michigan Consumer Expectations FinalJAN</t>
+          <t>Existing Home SalesDEC</t>
         </is>
       </c>
       <c r="C253" t="inlineStr">
         <is>
-          <t>69.3</t>
+          <t>4.24M</t>
         </is>
       </c>
       <c r="D253" t="inlineStr">
         <is>
-          <t>73.3</t>
+          <t>4.15M</t>
         </is>
       </c>
       <c r="E253" t="inlineStr">
         <is>
-          <t>70.2</t>
+          <t>4.19M</t>
         </is>
       </c>
       <c r="F253" t="inlineStr">
         <is>
-          <t>70.2</t>
+          <t>4.1M</t>
         </is>
       </c>
       <c r="G253" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="254">
@@ -7845,27 +7841,27 @@
       </c>
       <c r="B254" t="inlineStr">
         <is>
-          <t>Michigan 5 Year Inflation Expectations FinalJAN</t>
+          <t>Michigan Current Conditions FinalJAN</t>
         </is>
       </c>
       <c r="C254" t="inlineStr">
         <is>
-          <t>3.2%</t>
+          <t>74.0</t>
         </is>
       </c>
       <c r="D254" t="inlineStr">
         <is>
-          <t>3%</t>
+          <t>75.1</t>
         </is>
       </c>
       <c r="E254" t="inlineStr">
         <is>
-          <t>3.3%</t>
+          <t>77.9</t>
         </is>
       </c>
       <c r="F254" t="inlineStr">
         <is>
-          <t>3.3%</t>
+          <t>77.9</t>
         </is>
       </c>
       <c r="G254" t="n">
@@ -7880,31 +7876,31 @@
       </c>
       <c r="B255" t="inlineStr">
         <is>
-          <t>Existing Home SalesDEC</t>
+          <t>Michigan Consumer Sentiment FinalJAN</t>
         </is>
       </c>
       <c r="C255" t="inlineStr">
         <is>
-          <t>4.24M</t>
+          <t>71.1</t>
         </is>
       </c>
       <c r="D255" t="inlineStr">
         <is>
-          <t>4.15M</t>
+          <t>74.0</t>
         </is>
       </c>
       <c r="E255" t="inlineStr">
         <is>
-          <t>4.19M</t>
+          <t>73.2</t>
         </is>
       </c>
       <c r="F255" t="inlineStr">
         <is>
-          <t>4.1M</t>
+          <t>73.2</t>
         </is>
       </c>
       <c r="G255" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="256">
@@ -7915,27 +7911,31 @@
       </c>
       <c r="B256" t="inlineStr">
         <is>
-          <t>Existing Home Sales MoMDEC</t>
+          <t>Michigan Inflation Expectations FinalJAN</t>
         </is>
       </c>
       <c r="C256" t="inlineStr">
         <is>
-          <t>2.2%</t>
+          <t>3.3%</t>
         </is>
       </c>
       <c r="D256" t="inlineStr">
         <is>
-          <t>4.8%</t>
-        </is>
-      </c>
-      <c r="E256" t="inlineStr"/>
+          <t>2.8%</t>
+        </is>
+      </c>
+      <c r="E256" t="inlineStr">
+        <is>
+          <t>3.3%</t>
+        </is>
+      </c>
       <c r="F256" t="inlineStr">
         <is>
-          <t>0.3%</t>
+          <t>3.3%</t>
         </is>
       </c>
       <c r="G256" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="257">
@@ -8252,17 +8252,17 @@
       </c>
       <c r="B267" t="inlineStr">
         <is>
-          <t>3-Month Bill Auction</t>
+          <t>5-Year Note Auction</t>
         </is>
       </c>
       <c r="C267" t="inlineStr">
         <is>
-          <t>4.195%</t>
+          <t>4.33%</t>
         </is>
       </c>
       <c r="D267" t="inlineStr">
         <is>
-          <t>4.215%</t>
+          <t>4.478%</t>
         </is>
       </c>
       <c r="E267" t="inlineStr"/>
@@ -8279,17 +8279,17 @@
       </c>
       <c r="B268" t="inlineStr">
         <is>
-          <t>5-Year Note Auction</t>
+          <t>3-Month Bill Auction</t>
         </is>
       </c>
       <c r="C268" t="inlineStr">
         <is>
-          <t>4.33%</t>
+          <t>4.195%</t>
         </is>
       </c>
       <c r="D268" t="inlineStr">
         <is>
-          <t>4.478%</t>
+          <t>4.215%</t>
         </is>
       </c>
       <c r="E268" t="inlineStr"/>
@@ -8632,31 +8632,31 @@
       </c>
       <c r="B279" t="inlineStr">
         <is>
-          <t>CB Consumer ConfidenceJAN</t>
+          <t>Richmond Fed Manufacturing IndexJAN</t>
         </is>
       </c>
       <c r="C279" t="inlineStr">
         <is>
-          <t>104.1</t>
+          <t>-4</t>
         </is>
       </c>
       <c r="D279" t="inlineStr">
         <is>
-          <t>109.5</t>
+          <t>-10</t>
         </is>
       </c>
       <c r="E279" t="inlineStr">
         <is>
-          <t>105.6</t>
+          <t>-8</t>
         </is>
       </c>
       <c r="F279" t="inlineStr">
         <is>
-          <t>104</t>
+          <t>-8</t>
         </is>
       </c>
       <c r="G279" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="280">
@@ -8667,27 +8667,31 @@
       </c>
       <c r="B280" t="inlineStr">
         <is>
-          <t>Richmond Fed Services Revenues IndexJAN</t>
+          <t>CB Consumer ConfidenceJAN</t>
         </is>
       </c>
       <c r="C280" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>104.1</t>
         </is>
       </c>
       <c r="D280" t="inlineStr">
         <is>
-          <t>23</t>
-        </is>
-      </c>
-      <c r="E280" t="inlineStr"/>
+          <t>109.5</t>
+        </is>
+      </c>
+      <c r="E280" t="inlineStr">
+        <is>
+          <t>105.6</t>
+        </is>
+      </c>
       <c r="F280" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>104</t>
         </is>
       </c>
       <c r="G280" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="281">
@@ -8698,23 +8702,23 @@
       </c>
       <c r="B281" t="inlineStr">
         <is>
-          <t>Richmond Fed Manufacturing Shipments IndexJAN</t>
+          <t>Richmond Fed Services Revenues IndexJAN</t>
         </is>
       </c>
       <c r="C281" t="inlineStr">
         <is>
-          <t>-9</t>
+          <t>4</t>
         </is>
       </c>
       <c r="D281" t="inlineStr">
         <is>
-          <t>-11</t>
+          <t>23</t>
         </is>
       </c>
       <c r="E281" t="inlineStr"/>
       <c r="F281" t="inlineStr">
         <is>
-          <t>-9</t>
+          <t>21</t>
         </is>
       </c>
       <c r="G281" t="n">
@@ -8729,27 +8733,23 @@
       </c>
       <c r="B282" t="inlineStr">
         <is>
-          <t>Richmond Fed Manufacturing IndexJAN</t>
+          <t>Richmond Fed Manufacturing Shipments IndexJAN</t>
         </is>
       </c>
       <c r="C282" t="inlineStr">
         <is>
-          <t>-4</t>
+          <t>-9</t>
         </is>
       </c>
       <c r="D282" t="inlineStr">
         <is>
-          <t>-10</t>
-        </is>
-      </c>
-      <c r="E282" t="inlineStr">
-        <is>
-          <t>-8</t>
-        </is>
-      </c>
+          <t>-11</t>
+        </is>
+      </c>
+      <c r="E282" t="inlineStr"/>
       <c r="F282" t="inlineStr">
         <is>
-          <t>-8</t>
+          <t>-9</t>
         </is>
       </c>
       <c r="G282" t="n">
@@ -8764,23 +8764,23 @@
       </c>
       <c r="B283" t="inlineStr">
         <is>
-          <t>Dallas Fed Services Revenues IndexJAN</t>
+          <t>Dallas Fed Services IndexJAN</t>
         </is>
       </c>
       <c r="C283" t="inlineStr">
         <is>
-          <t>5.7</t>
+          <t>7.4</t>
         </is>
       </c>
       <c r="D283" t="inlineStr">
         <is>
-          <t>13.9</t>
+          <t>10.8</t>
         </is>
       </c>
       <c r="E283" t="inlineStr"/>
       <c r="F283" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>9.5</t>
         </is>
       </c>
       <c r="G283" t="n">
@@ -8795,23 +8795,23 @@
       </c>
       <c r="B284" t="inlineStr">
         <is>
-          <t>Dallas Fed Services IndexJAN</t>
+          <t>Dallas Fed Services Revenues IndexJAN</t>
         </is>
       </c>
       <c r="C284" t="inlineStr">
         <is>
-          <t>7.4</t>
+          <t>5.7</t>
         </is>
       </c>
       <c r="D284" t="inlineStr">
         <is>
-          <t>10.8</t>
+          <t>13.9</t>
         </is>
       </c>
       <c r="E284" t="inlineStr"/>
       <c r="F284" t="inlineStr">
         <is>
-          <t>9.5</t>
+          <t>13</t>
         </is>
       </c>
       <c r="G284" t="n">
@@ -8965,23 +8965,23 @@
       </c>
       <c r="B290" t="inlineStr">
         <is>
-          <t>MBA Mortgage ApplicationsJAN/24</t>
+          <t>MBA 30-Year Mortgage RateJAN/24</t>
         </is>
       </c>
       <c r="C290" t="inlineStr">
         <is>
-          <t>-2%</t>
+          <t>7.02%</t>
         </is>
       </c>
       <c r="D290" t="inlineStr">
         <is>
-          <t>0.1%</t>
+          <t>7.02%</t>
         </is>
       </c>
       <c r="E290" t="inlineStr"/>
       <c r="F290" t="inlineStr"/>
       <c r="G290" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="291">
@@ -8992,17 +8992,17 @@
       </c>
       <c r="B291" t="inlineStr">
         <is>
-          <t>MBA Purchase IndexJAN/24</t>
+          <t>MBA Mortgage Refinance IndexJAN/24</t>
         </is>
       </c>
       <c r="C291" t="inlineStr">
         <is>
-          <t>162.4</t>
+          <t>520.9</t>
         </is>
       </c>
       <c r="D291" t="inlineStr">
         <is>
-          <t>163</t>
+          <t>558.8</t>
         </is>
       </c>
       <c r="E291" t="inlineStr"/>
@@ -9019,17 +9019,17 @@
       </c>
       <c r="B292" t="inlineStr">
         <is>
-          <t>MBA Mortgage Refinance IndexJAN/24</t>
+          <t>MBA Mortgage Market IndexJAN/24</t>
         </is>
       </c>
       <c r="C292" t="inlineStr">
         <is>
-          <t>520.9</t>
+          <t>220.0</t>
         </is>
       </c>
       <c r="D292" t="inlineStr">
         <is>
-          <t>558.8</t>
+          <t>224.6</t>
         </is>
       </c>
       <c r="E292" t="inlineStr"/>
@@ -9046,17 +9046,17 @@
       </c>
       <c r="B293" t="inlineStr">
         <is>
-          <t>MBA Mortgage Market IndexJAN/24</t>
+          <t>MBA Mortgage ApplicationsJAN/24</t>
         </is>
       </c>
       <c r="C293" t="inlineStr">
         <is>
-          <t>220.0</t>
+          <t>-2%</t>
         </is>
       </c>
       <c r="D293" t="inlineStr">
         <is>
-          <t>224.6</t>
+          <t>0.1%</t>
         </is>
       </c>
       <c r="E293" t="inlineStr"/>
@@ -9073,23 +9073,23 @@
       </c>
       <c r="B294" t="inlineStr">
         <is>
-          <t>MBA 30-Year Mortgage RateJAN/24</t>
+          <t>MBA Purchase IndexJAN/24</t>
         </is>
       </c>
       <c r="C294" t="inlineStr">
         <is>
-          <t>7.02%</t>
+          <t>162.4</t>
         </is>
       </c>
       <c r="D294" t="inlineStr">
         <is>
-          <t>7.02%</t>
+          <t>163</t>
         </is>
       </c>
       <c r="E294" t="inlineStr"/>
       <c r="F294" t="inlineStr"/>
       <c r="G294" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="295">
@@ -9201,17 +9201,17 @@
       </c>
       <c r="B298" t="inlineStr">
         <is>
-          <t>EIA Cushing Crude Oil Stocks ChangeJAN/24</t>
+          <t>EIA Distillate Fuel Production ChangeJAN/24</t>
         </is>
       </c>
       <c r="C298" t="inlineStr">
         <is>
-          <t>0.326M</t>
+          <t>0.028M</t>
         </is>
       </c>
       <c r="D298" t="inlineStr">
         <is>
-          <t>-0.148M</t>
+          <t>-0.473M</t>
         </is>
       </c>
       <c r="E298" t="inlineStr"/>
@@ -9228,23 +9228,27 @@
       </c>
       <c r="B299" t="inlineStr">
         <is>
-          <t>EIA Refinery Crude Runs ChangeJAN/24</t>
+          <t>EIA Crude Oil Stocks ChangeJAN/24</t>
         </is>
       </c>
       <c r="C299" t="inlineStr">
         <is>
-          <t>-0.333M</t>
+          <t>3.463M</t>
         </is>
       </c>
       <c r="D299" t="inlineStr">
         <is>
-          <t>-1.125M</t>
-        </is>
-      </c>
-      <c r="E299" t="inlineStr"/>
+          <t>-1.017M</t>
+        </is>
+      </c>
+      <c r="E299" t="inlineStr">
+        <is>
+          <t>3.2M</t>
+        </is>
+      </c>
       <c r="F299" t="inlineStr"/>
       <c r="G299" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="300">
@@ -9255,24 +9259,20 @@
       </c>
       <c r="B300" t="inlineStr">
         <is>
-          <t>EIA Distillate Stocks ChangeJAN/24</t>
+          <t>EIA Crude Oil Imports ChangeJAN/24</t>
         </is>
       </c>
       <c r="C300" t="inlineStr">
         <is>
-          <t>-4.994M</t>
+          <t>0.532M</t>
         </is>
       </c>
       <c r="D300" t="inlineStr">
         <is>
-          <t>-3.07M</t>
-        </is>
-      </c>
-      <c r="E300" t="inlineStr">
-        <is>
-          <t>-2.1M</t>
-        </is>
-      </c>
+          <t>0.184M</t>
+        </is>
+      </c>
+      <c r="E300" t="inlineStr"/>
       <c r="F300" t="inlineStr"/>
       <c r="G300" t="n">
         <v>3</v>
@@ -9286,23 +9286,27 @@
       </c>
       <c r="B301" t="inlineStr">
         <is>
-          <t>EIA Heating Oil Stocks ChangeJAN/24</t>
+          <t>EIA Gasoline Stocks ChangeJAN/24</t>
         </is>
       </c>
       <c r="C301" t="inlineStr">
         <is>
-          <t>0.128M</t>
+          <t>2.957M</t>
         </is>
       </c>
       <c r="D301" t="inlineStr">
         <is>
-          <t>0.068M</t>
-        </is>
-      </c>
-      <c r="E301" t="inlineStr"/>
+          <t>2.332M</t>
+        </is>
+      </c>
+      <c r="E301" t="inlineStr">
+        <is>
+          <t>1.5M</t>
+        </is>
+      </c>
       <c r="F301" t="inlineStr"/>
       <c r="G301" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="302">
@@ -9313,17 +9317,17 @@
       </c>
       <c r="B302" t="inlineStr">
         <is>
-          <t>EIA Gasoline Production ChangeJAN/24</t>
+          <t>EIA Refinery Crude Runs ChangeJAN/24</t>
         </is>
       </c>
       <c r="C302" t="inlineStr">
         <is>
-          <t>-0.044M</t>
+          <t>-0.333M</t>
         </is>
       </c>
       <c r="D302" t="inlineStr">
         <is>
-          <t>-0.043M</t>
+          <t>-1.125M</t>
         </is>
       </c>
       <c r="E302" t="inlineStr"/>
@@ -9340,27 +9344,23 @@
       </c>
       <c r="B303" t="inlineStr">
         <is>
-          <t>EIA Gasoline Stocks ChangeJAN/24</t>
+          <t>EIA Heating Oil Stocks ChangeJAN/24</t>
         </is>
       </c>
       <c r="C303" t="inlineStr">
         <is>
-          <t>2.957M</t>
+          <t>0.128M</t>
         </is>
       </c>
       <c r="D303" t="inlineStr">
         <is>
-          <t>2.332M</t>
-        </is>
-      </c>
-      <c r="E303" t="inlineStr">
-        <is>
-          <t>1.5M</t>
-        </is>
-      </c>
+          <t>0.068M</t>
+        </is>
+      </c>
+      <c r="E303" t="inlineStr"/>
       <c r="F303" t="inlineStr"/>
       <c r="G303" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="304">
@@ -9371,20 +9371,24 @@
       </c>
       <c r="B304" t="inlineStr">
         <is>
-          <t>EIA Distillate Fuel Production ChangeJAN/24</t>
+          <t>EIA Distillate Stocks ChangeJAN/24</t>
         </is>
       </c>
       <c r="C304" t="inlineStr">
         <is>
-          <t>0.028M</t>
+          <t>-4.994M</t>
         </is>
       </c>
       <c r="D304" t="inlineStr">
         <is>
-          <t>-0.473M</t>
-        </is>
-      </c>
-      <c r="E304" t="inlineStr"/>
+          <t>-3.07M</t>
+        </is>
+      </c>
+      <c r="E304" t="inlineStr">
+        <is>
+          <t>-2.1M</t>
+        </is>
+      </c>
       <c r="F304" t="inlineStr"/>
       <c r="G304" t="n">
         <v>3</v>
@@ -9398,17 +9402,17 @@
       </c>
       <c r="B305" t="inlineStr">
         <is>
-          <t>EIA Crude Oil Imports ChangeJAN/24</t>
+          <t>EIA Cushing Crude Oil Stocks ChangeJAN/24</t>
         </is>
       </c>
       <c r="C305" t="inlineStr">
         <is>
-          <t>0.532M</t>
+          <t>0.326M</t>
         </is>
       </c>
       <c r="D305" t="inlineStr">
         <is>
-          <t>0.184M</t>
+          <t>-0.148M</t>
         </is>
       </c>
       <c r="E305" t="inlineStr"/>
@@ -9425,27 +9429,23 @@
       </c>
       <c r="B306" t="inlineStr">
         <is>
-          <t>EIA Crude Oil Stocks ChangeJAN/24</t>
+          <t>EIA Gasoline Production ChangeJAN/24</t>
         </is>
       </c>
       <c r="C306" t="inlineStr">
         <is>
-          <t>3.463M</t>
+          <t>-0.044M</t>
         </is>
       </c>
       <c r="D306" t="inlineStr">
         <is>
-          <t>-1.017M</t>
-        </is>
-      </c>
-      <c r="E306" t="inlineStr">
-        <is>
-          <t>3.2M</t>
-        </is>
-      </c>
+          <t>-0.043M</t>
+        </is>
+      </c>
+      <c r="E306" t="inlineStr"/>
       <c r="F306" t="inlineStr"/>
       <c r="G306" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="307">
@@ -9537,31 +9537,27 @@
       </c>
       <c r="B310" t="inlineStr">
         <is>
-          <t>GDP Price Index QoQ AdvQ4</t>
+          <t>Real Consumer Spending QoQ AdvQ4</t>
         </is>
       </c>
       <c r="C310" t="inlineStr">
         <is>
-          <t>2.2%</t>
+          <t>4.2%</t>
         </is>
       </c>
       <c r="D310" t="inlineStr">
         <is>
-          <t>1.9%</t>
-        </is>
-      </c>
-      <c r="E310" t="inlineStr">
-        <is>
-          <t>2.5%</t>
-        </is>
-      </c>
+          <t>3.7%</t>
+        </is>
+      </c>
+      <c r="E310" t="inlineStr"/>
       <c r="F310" t="inlineStr">
         <is>
-          <t>2.3%</t>
+          <t>2.9%</t>
         </is>
       </c>
       <c r="G310" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="311">
@@ -9572,31 +9568,31 @@
       </c>
       <c r="B311" t="inlineStr">
         <is>
-          <t>Initial Jobless ClaimsJAN/25</t>
+          <t>Core PCE Prices QoQ AdvQ4</t>
         </is>
       </c>
       <c r="C311" t="inlineStr">
         <is>
-          <t>207K</t>
+          <t>2.5%</t>
         </is>
       </c>
       <c r="D311" t="inlineStr">
         <is>
-          <t>223K</t>
+          <t>2.2%</t>
         </is>
       </c>
       <c r="E311" t="inlineStr">
         <is>
-          <t>220K</t>
+          <t>2.5%</t>
         </is>
       </c>
       <c r="F311" t="inlineStr">
         <is>
-          <t>228.0K</t>
+          <t>2.3%</t>
         </is>
       </c>
       <c r="G311" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="312">
@@ -9607,23 +9603,27 @@
       </c>
       <c r="B312" t="inlineStr">
         <is>
-          <t>PCE Prices QoQ AdvQ4</t>
+          <t>Continuing Jobless ClaimsJAN/18</t>
         </is>
       </c>
       <c r="C312" t="inlineStr">
         <is>
-          <t>2.3%</t>
+          <t>1858K</t>
         </is>
       </c>
       <c r="D312" t="inlineStr">
         <is>
-          <t>1.5%</t>
-        </is>
-      </c>
-      <c r="E312" t="inlineStr"/>
+          <t>1900K</t>
+        </is>
+      </c>
+      <c r="E312" t="inlineStr">
+        <is>
+          <t>1890K</t>
+        </is>
+      </c>
       <c r="F312" t="inlineStr">
         <is>
-          <t>1.1%</t>
+          <t>1885.0K</t>
         </is>
       </c>
       <c r="G312" t="n">
@@ -9638,23 +9638,23 @@
       </c>
       <c r="B313" t="inlineStr">
         <is>
-          <t>Jobless Claims 4-week AverageJAN/25</t>
+          <t>GDP Sales QoQ AdvQ4</t>
         </is>
       </c>
       <c r="C313" t="inlineStr">
         <is>
-          <t>212.5K</t>
+          <t>3.2%</t>
         </is>
       </c>
       <c r="D313" t="inlineStr">
         <is>
-          <t>213.5K</t>
+          <t>3.3%</t>
         </is>
       </c>
       <c r="E313" t="inlineStr"/>
       <c r="F313" t="inlineStr">
         <is>
-          <t>214.0K</t>
+          <t>2.9%</t>
         </is>
       </c>
       <c r="G313" t="n">
@@ -9669,7 +9669,7 @@
       </c>
       <c r="B314" t="inlineStr">
         <is>
-          <t>GDP Growth Rate QoQ AdvQ4</t>
+          <t>PCE Prices QoQ AdvQ4</t>
         </is>
       </c>
       <c r="C314" t="inlineStr">
@@ -9679,21 +9679,17 @@
       </c>
       <c r="D314" t="inlineStr">
         <is>
-          <t>3.1%</t>
-        </is>
-      </c>
-      <c r="E314" t="inlineStr">
-        <is>
-          <t>2.6%</t>
-        </is>
-      </c>
+          <t>1.5%</t>
+        </is>
+      </c>
+      <c r="E314" t="inlineStr"/>
       <c r="F314" t="inlineStr">
         <is>
-          <t>3%</t>
+          <t>1.1%</t>
         </is>
       </c>
       <c r="G314" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="315">
@@ -9704,23 +9700,23 @@
       </c>
       <c r="B315" t="inlineStr">
         <is>
-          <t>GDP Sales QoQ AdvQ4</t>
+          <t>Jobless Claims 4-week AverageJAN/25</t>
         </is>
       </c>
       <c r="C315" t="inlineStr">
         <is>
-          <t>3.2%</t>
+          <t>212.5K</t>
         </is>
       </c>
       <c r="D315" t="inlineStr">
         <is>
-          <t>3.3%</t>
+          <t>213.5K</t>
         </is>
       </c>
       <c r="E315" t="inlineStr"/>
       <c r="F315" t="inlineStr">
         <is>
-          <t>2.9%</t>
+          <t>214.0K</t>
         </is>
       </c>
       <c r="G315" t="n">
@@ -9735,27 +9731,31 @@
       </c>
       <c r="B316" t="inlineStr">
         <is>
-          <t>Real Consumer Spending QoQ AdvQ4</t>
+          <t>GDP Growth Rate QoQ AdvQ4</t>
         </is>
       </c>
       <c r="C316" t="inlineStr">
         <is>
-          <t>4.2%</t>
+          <t>2.3%</t>
         </is>
       </c>
       <c r="D316" t="inlineStr">
         <is>
-          <t>3.7%</t>
-        </is>
-      </c>
-      <c r="E316" t="inlineStr"/>
+          <t>3.1%</t>
+        </is>
+      </c>
+      <c r="E316" t="inlineStr">
+        <is>
+          <t>2.6%</t>
+        </is>
+      </c>
       <c r="F316" t="inlineStr">
         <is>
-          <t>2.9%</t>
+          <t>3%</t>
         </is>
       </c>
       <c r="G316" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="317">
@@ -9766,31 +9766,31 @@
       </c>
       <c r="B317" t="inlineStr">
         <is>
-          <t>Continuing Jobless ClaimsJAN/18</t>
+          <t>Initial Jobless ClaimsJAN/25</t>
         </is>
       </c>
       <c r="C317" t="inlineStr">
         <is>
-          <t>1858K</t>
+          <t>207K</t>
         </is>
       </c>
       <c r="D317" t="inlineStr">
         <is>
-          <t>1900K</t>
+          <t>223K</t>
         </is>
       </c>
       <c r="E317" t="inlineStr">
         <is>
-          <t>1890K</t>
+          <t>220K</t>
         </is>
       </c>
       <c r="F317" t="inlineStr">
         <is>
-          <t>1885.0K</t>
+          <t>228.0K</t>
         </is>
       </c>
       <c r="G317" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="318">
@@ -9801,31 +9801,31 @@
       </c>
       <c r="B318" t="inlineStr">
         <is>
-          <t>Core PCE Prices QoQ AdvQ4</t>
+          <t>GDP Price Index QoQ AdvQ4</t>
         </is>
       </c>
       <c r="C318" t="inlineStr">
         <is>
+          <t>2.2%</t>
+        </is>
+      </c>
+      <c r="D318" t="inlineStr">
+        <is>
+          <t>1.9%</t>
+        </is>
+      </c>
+      <c r="E318" t="inlineStr">
+        <is>
           <t>2.5%</t>
         </is>
       </c>
-      <c r="D318" t="inlineStr">
-        <is>
-          <t>2.2%</t>
-        </is>
-      </c>
-      <c r="E318" t="inlineStr">
-        <is>
-          <t>2.5%</t>
-        </is>
-      </c>
       <c r="F318" t="inlineStr">
         <is>
           <t>2.3%</t>
         </is>
       </c>
       <c r="G318" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="319">
@@ -9933,17 +9933,17 @@
       </c>
       <c r="B322" t="inlineStr">
         <is>
-          <t>8-Week Bill Auction</t>
+          <t>4-Week Bill Auction</t>
         </is>
       </c>
       <c r="C322" t="inlineStr">
         <is>
-          <t>4.240%</t>
+          <t>4.250%</t>
         </is>
       </c>
       <c r="D322" t="inlineStr">
         <is>
-          <t>4.250%</t>
+          <t>4.265%</t>
         </is>
       </c>
       <c r="E322" t="inlineStr"/>
@@ -9960,17 +9960,17 @@
       </c>
       <c r="B323" t="inlineStr">
         <is>
-          <t>4-Week Bill Auction</t>
+          <t>8-Week Bill Auction</t>
         </is>
       </c>
       <c r="C323" t="inlineStr">
         <is>
+          <t>4.240%</t>
+        </is>
+      </c>
+      <c r="D323" t="inlineStr">
+        <is>
           <t>4.250%</t>
-        </is>
-      </c>
-      <c r="D323" t="inlineStr">
-        <is>
-          <t>4.265%</t>
         </is>
       </c>
       <c r="E323" t="inlineStr"/>
@@ -10068,31 +10068,31 @@
       </c>
       <c r="B327" t="inlineStr">
         <is>
-          <t>Employment Cost Index QoQQ4</t>
+          <t>Personal Income MoMDEC</t>
         </is>
       </c>
       <c r="C327" t="inlineStr">
         <is>
-          <t>0.9%</t>
+          <t>0.4%</t>
         </is>
       </c>
       <c r="D327" t="inlineStr">
         <is>
-          <t>0.8%</t>
+          <t>0.3%</t>
         </is>
       </c>
       <c r="E327" t="inlineStr">
         <is>
-          <t>0.9%</t>
+          <t>0.4%</t>
         </is>
       </c>
       <c r="F327" t="inlineStr">
         <is>
-          <t>0.7%</t>
+          <t>0.3%</t>
         </is>
       </c>
       <c r="G327" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="328">
@@ -10103,31 +10103,31 @@
       </c>
       <c r="B328" t="inlineStr">
         <is>
-          <t>PCE Price Index YoYDEC</t>
+          <t>Personal Spending MoMDEC</t>
         </is>
       </c>
       <c r="C328" t="inlineStr">
         <is>
-          <t>2.6%</t>
+          <t>0.7%</t>
         </is>
       </c>
       <c r="D328" t="inlineStr">
         <is>
-          <t>2.4%</t>
+          <t>0.6%</t>
         </is>
       </c>
       <c r="E328" t="inlineStr">
         <is>
-          <t>2.6%</t>
+          <t>0.5%</t>
         </is>
       </c>
       <c r="F328" t="inlineStr">
         <is>
-          <t>2.6%</t>
+          <t>0.5%</t>
         </is>
       </c>
       <c r="G328" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="329">
@@ -10138,31 +10138,27 @@
       </c>
       <c r="B329" t="inlineStr">
         <is>
-          <t>Core PCE Price Index YoYDEC</t>
+          <t>Employment Cost - Benefits QoQQ4</t>
         </is>
       </c>
       <c r="C329" t="inlineStr">
         <is>
-          <t>2.8%</t>
+          <t>0.8%</t>
         </is>
       </c>
       <c r="D329" t="inlineStr">
         <is>
-          <t>2.8%</t>
-        </is>
-      </c>
-      <c r="E329" t="inlineStr">
-        <is>
-          <t>2.8%</t>
-        </is>
-      </c>
+          <t>0.8%</t>
+        </is>
+      </c>
+      <c r="E329" t="inlineStr"/>
       <c r="F329" t="inlineStr">
         <is>
-          <t>2.8%</t>
+          <t>0.7%</t>
         </is>
       </c>
       <c r="G329" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="330">
@@ -10173,25 +10169,13 @@
       </c>
       <c r="B330" t="inlineStr">
         <is>
-          <t>Employment Cost - Wages QoQQ4</t>
-        </is>
-      </c>
-      <c r="C330" t="inlineStr">
-        <is>
-          <t>0.9%</t>
-        </is>
-      </c>
-      <c r="D330" t="inlineStr">
-        <is>
-          <t>0.8%</t>
-        </is>
-      </c>
+          <t>Fed Bowman Speech</t>
+        </is>
+      </c>
+      <c r="C330" t="inlineStr"/>
+      <c r="D330" t="inlineStr"/>
       <c r="E330" t="inlineStr"/>
-      <c r="F330" t="inlineStr">
-        <is>
-          <t>0.7%</t>
-        </is>
-      </c>
+      <c r="F330" t="inlineStr"/>
       <c r="G330" t="n">
         <v>2</v>
       </c>
@@ -10204,12 +10188,12 @@
       </c>
       <c r="B331" t="inlineStr">
         <is>
-          <t>PCE Price Index MoMDEC</t>
+          <t>Core PCE Price Index MoMDEC</t>
         </is>
       </c>
       <c r="C331" t="inlineStr">
         <is>
-          <t>0.3%</t>
+          <t>0.2%</t>
         </is>
       </c>
       <c r="D331" t="inlineStr">
@@ -10219,16 +10203,16 @@
       </c>
       <c r="E331" t="inlineStr">
         <is>
-          <t>0.3%</t>
+          <t>0.2%</t>
         </is>
       </c>
       <c r="F331" t="inlineStr">
         <is>
-          <t>0.3%</t>
+          <t>0.2%</t>
         </is>
       </c>
       <c r="G331" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="332">
@@ -10239,31 +10223,31 @@
       </c>
       <c r="B332" t="inlineStr">
         <is>
-          <t>Core PCE Price Index MoMDEC</t>
+          <t>Employment Cost Index QoQQ4</t>
         </is>
       </c>
       <c r="C332" t="inlineStr">
         <is>
-          <t>0.2%</t>
+          <t>0.9%</t>
         </is>
       </c>
       <c r="D332" t="inlineStr">
         <is>
-          <t>0.1%</t>
+          <t>0.8%</t>
         </is>
       </c>
       <c r="E332" t="inlineStr">
         <is>
-          <t>0.2%</t>
+          <t>0.9%</t>
         </is>
       </c>
       <c r="F332" t="inlineStr">
         <is>
-          <t>0.2%</t>
+          <t>0.7%</t>
         </is>
       </c>
       <c r="G332" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="333">
@@ -10274,31 +10258,27 @@
       </c>
       <c r="B333" t="inlineStr">
         <is>
-          <t>Personal Income MoMDEC</t>
+          <t>Employment Cost - Wages QoQQ4</t>
         </is>
       </c>
       <c r="C333" t="inlineStr">
         <is>
-          <t>0.4%</t>
+          <t>0.9%</t>
         </is>
       </c>
       <c r="D333" t="inlineStr">
         <is>
-          <t>0.3%</t>
-        </is>
-      </c>
-      <c r="E333" t="inlineStr">
-        <is>
-          <t>0.4%</t>
-        </is>
-      </c>
+          <t>0.8%</t>
+        </is>
+      </c>
+      <c r="E333" t="inlineStr"/>
       <c r="F333" t="inlineStr">
         <is>
-          <t>0.3%</t>
+          <t>0.7%</t>
         </is>
       </c>
       <c r="G333" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="334">
@@ -10309,15 +10289,31 @@
       </c>
       <c r="B334" t="inlineStr">
         <is>
-          <t>Fed Bowman Speech</t>
-        </is>
-      </c>
-      <c r="C334" t="inlineStr"/>
-      <c r="D334" t="inlineStr"/>
-      <c r="E334" t="inlineStr"/>
-      <c r="F334" t="inlineStr"/>
+          <t>Core PCE Price Index YoYDEC</t>
+        </is>
+      </c>
+      <c r="C334" t="inlineStr">
+        <is>
+          <t>2.8%</t>
+        </is>
+      </c>
+      <c r="D334" t="inlineStr">
+        <is>
+          <t>2.8%</t>
+        </is>
+      </c>
+      <c r="E334" t="inlineStr">
+        <is>
+          <t>2.8%</t>
+        </is>
+      </c>
+      <c r="F334" t="inlineStr">
+        <is>
+          <t>2.8%</t>
+        </is>
+      </c>
       <c r="G334" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="335">
@@ -10328,23 +10324,27 @@
       </c>
       <c r="B335" t="inlineStr">
         <is>
-          <t>Employment Cost - Benefits QoQQ4</t>
+          <t>PCE Price Index YoYDEC</t>
         </is>
       </c>
       <c r="C335" t="inlineStr">
         <is>
-          <t>0.8%</t>
+          <t>2.6%</t>
         </is>
       </c>
       <c r="D335" t="inlineStr">
         <is>
-          <t>0.8%</t>
-        </is>
-      </c>
-      <c r="E335" t="inlineStr"/>
+          <t>2.4%</t>
+        </is>
+      </c>
+      <c r="E335" t="inlineStr">
+        <is>
+          <t>2.6%</t>
+        </is>
+      </c>
       <c r="F335" t="inlineStr">
         <is>
-          <t>0.7%</t>
+          <t>2.6%</t>
         </is>
       </c>
       <c r="G335" t="n">
@@ -10359,31 +10359,31 @@
       </c>
       <c r="B336" t="inlineStr">
         <is>
-          <t>Personal Spending MoMDEC</t>
+          <t>PCE Price Index MoMDEC</t>
         </is>
       </c>
       <c r="C336" t="inlineStr">
         <is>
-          <t>0.7%</t>
+          <t>0.3%</t>
         </is>
       </c>
       <c r="D336" t="inlineStr">
         <is>
-          <t>0.6%</t>
+          <t>0.1%</t>
         </is>
       </c>
       <c r="E336" t="inlineStr">
         <is>
-          <t>0.5%</t>
+          <t>0.3%</t>
         </is>
       </c>
       <c r="F336" t="inlineStr">
         <is>
-          <t>0.5%</t>
+          <t>0.3%</t>
         </is>
       </c>
       <c r="G336" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="337">
@@ -11155,17 +11155,17 @@
       </c>
       <c r="B364" t="inlineStr">
         <is>
-          <t>MBA Mortgage Refinance IndexJAN/31</t>
+          <t>MBA Mortgage ApplicationsJAN/31</t>
         </is>
       </c>
       <c r="C364" t="inlineStr">
         <is>
-          <t>584.3</t>
+          <t>2.2%</t>
         </is>
       </c>
       <c r="D364" t="inlineStr">
         <is>
-          <t>520.9</t>
+          <t>-2%</t>
         </is>
       </c>
       <c r="E364" t="inlineStr"/>
@@ -11182,17 +11182,17 @@
       </c>
       <c r="B365" t="inlineStr">
         <is>
-          <t>MBA Purchase IndexJAN/31</t>
+          <t>MBA Mortgage Market IndexJAN/31</t>
         </is>
       </c>
       <c r="C365" t="inlineStr">
         <is>
-          <t>156.7</t>
+          <t>224.8</t>
         </is>
       </c>
       <c r="D365" t="inlineStr">
         <is>
-          <t>162.4</t>
+          <t>220.0</t>
         </is>
       </c>
       <c r="E365" t="inlineStr"/>
@@ -11209,23 +11209,23 @@
       </c>
       <c r="B366" t="inlineStr">
         <is>
-          <t>MBA Mortgage Market IndexJAN/31</t>
+          <t>MBA 30-Year Mortgage RateJAN/31</t>
         </is>
       </c>
       <c r="C366" t="inlineStr">
         <is>
-          <t>224.8</t>
+          <t>6.97%</t>
         </is>
       </c>
       <c r="D366" t="inlineStr">
         <is>
-          <t>220.0</t>
+          <t>7.02%</t>
         </is>
       </c>
       <c r="E366" t="inlineStr"/>
       <c r="F366" t="inlineStr"/>
       <c r="G366" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="367">
@@ -11236,17 +11236,17 @@
       </c>
       <c r="B367" t="inlineStr">
         <is>
-          <t>MBA Mortgage ApplicationsJAN/31</t>
+          <t>MBA Mortgage Refinance IndexJAN/31</t>
         </is>
       </c>
       <c r="C367" t="inlineStr">
         <is>
-          <t>2.2%</t>
+          <t>584.3</t>
         </is>
       </c>
       <c r="D367" t="inlineStr">
         <is>
-          <t>-2%</t>
+          <t>520.9</t>
         </is>
       </c>
       <c r="E367" t="inlineStr"/>
@@ -11263,23 +11263,23 @@
       </c>
       <c r="B368" t="inlineStr">
         <is>
-          <t>MBA 30-Year Mortgage RateJAN/31</t>
+          <t>MBA Purchase IndexJAN/31</t>
         </is>
       </c>
       <c r="C368" t="inlineStr">
         <is>
-          <t>6.97%</t>
+          <t>156.7</t>
         </is>
       </c>
       <c r="D368" t="inlineStr">
         <is>
-          <t>7.02%</t>
+          <t>162.4</t>
         </is>
       </c>
       <c r="E368" t="inlineStr"/>
       <c r="F368" t="inlineStr"/>
       <c r="G368" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="369">
@@ -11530,23 +11530,23 @@
       </c>
       <c r="B377" t="inlineStr">
         <is>
-          <t>ISM Services EmploymentJAN</t>
+          <t>ISM Services PricesJAN</t>
         </is>
       </c>
       <c r="C377" t="inlineStr">
         <is>
-          <t>52.3</t>
+          <t>60.4</t>
         </is>
       </c>
       <c r="D377" t="inlineStr">
         <is>
-          <t>51.3</t>
+          <t>64.4</t>
         </is>
       </c>
       <c r="E377" t="inlineStr"/>
       <c r="F377" t="inlineStr">
         <is>
-          <t>51.3</t>
+          <t>64.8</t>
         </is>
       </c>
       <c r="G377" t="n">
@@ -11561,27 +11561,31 @@
       </c>
       <c r="B378" t="inlineStr">
         <is>
-          <t>ISM Services Business ActivityJAN</t>
+          <t>ISM Services PMIJAN</t>
         </is>
       </c>
       <c r="C378" t="inlineStr">
         <is>
-          <t>54.5</t>
+          <t>52.8</t>
         </is>
       </c>
       <c r="D378" t="inlineStr">
         <is>
-          <t>58.0</t>
-        </is>
-      </c>
-      <c r="E378" t="inlineStr"/>
+          <t>54.0</t>
+        </is>
+      </c>
+      <c r="E378" t="inlineStr">
+        <is>
+          <t>54.3</t>
+        </is>
+      </c>
       <c r="F378" t="inlineStr">
         <is>
-          <t>58.1</t>
+          <t>54</t>
         </is>
       </c>
       <c r="G378" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="379">
@@ -11592,31 +11596,27 @@
       </c>
       <c r="B379" t="inlineStr">
         <is>
-          <t>ISM Services PMIJAN</t>
+          <t>ISM Services New OrdersJAN</t>
         </is>
       </c>
       <c r="C379" t="inlineStr">
         <is>
-          <t>52.8</t>
+          <t>51.3</t>
         </is>
       </c>
       <c r="D379" t="inlineStr">
         <is>
-          <t>54.0</t>
-        </is>
-      </c>
-      <c r="E379" t="inlineStr">
-        <is>
-          <t>54.3</t>
-        </is>
-      </c>
+          <t>54.4</t>
+        </is>
+      </c>
+      <c r="E379" t="inlineStr"/>
       <c r="F379" t="inlineStr">
         <is>
-          <t>54</t>
+          <t>54.1</t>
         </is>
       </c>
       <c r="G379" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="380">
@@ -11627,23 +11627,23 @@
       </c>
       <c r="B380" t="inlineStr">
         <is>
-          <t>ISM Services PricesJAN</t>
+          <t>ISM Services EmploymentJAN</t>
         </is>
       </c>
       <c r="C380" t="inlineStr">
         <is>
-          <t>60.4</t>
+          <t>52.3</t>
         </is>
       </c>
       <c r="D380" t="inlineStr">
         <is>
-          <t>64.4</t>
+          <t>51.3</t>
         </is>
       </c>
       <c r="E380" t="inlineStr"/>
       <c r="F380" t="inlineStr">
         <is>
-          <t>64.8</t>
+          <t>51.3</t>
         </is>
       </c>
       <c r="G380" t="n">
@@ -11658,23 +11658,23 @@
       </c>
       <c r="B381" t="inlineStr">
         <is>
-          <t>ISM Services New OrdersJAN</t>
+          <t>ISM Services Business ActivityJAN</t>
         </is>
       </c>
       <c r="C381" t="inlineStr">
         <is>
-          <t>51.3</t>
+          <t>54.5</t>
         </is>
       </c>
       <c r="D381" t="inlineStr">
         <is>
-          <t>54.4</t>
+          <t>58.0</t>
         </is>
       </c>
       <c r="E381" t="inlineStr"/>
       <c r="F381" t="inlineStr">
         <is>
-          <t>54.1</t>
+          <t>58.1</t>
         </is>
       </c>
       <c r="G381" t="n">
@@ -11689,23 +11689,27 @@
       </c>
       <c r="B382" t="inlineStr">
         <is>
-          <t>EIA Crude Oil Imports ChangeJAN/31</t>
+          <t>EIA Gasoline Stocks ChangeJAN/31</t>
         </is>
       </c>
       <c r="C382" t="inlineStr">
         <is>
-          <t>-0.178M</t>
+          <t>2.233M</t>
         </is>
       </c>
       <c r="D382" t="inlineStr">
         <is>
-          <t>0.532M</t>
-        </is>
-      </c>
-      <c r="E382" t="inlineStr"/>
+          <t>2.957M</t>
+        </is>
+      </c>
+      <c r="E382" t="inlineStr">
+        <is>
+          <t>1.2M</t>
+        </is>
+      </c>
       <c r="F382" t="inlineStr"/>
       <c r="G382" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="383">
@@ -11716,17 +11720,17 @@
       </c>
       <c r="B383" t="inlineStr">
         <is>
-          <t>EIA Cushing Crude Oil Stocks ChangeJAN/31</t>
+          <t>EIA Refinery Crude Runs ChangeJAN/31</t>
         </is>
       </c>
       <c r="C383" t="inlineStr">
         <is>
-          <t>-0.034M</t>
+          <t>0.16M</t>
         </is>
       </c>
       <c r="D383" t="inlineStr">
         <is>
-          <t>0.326M</t>
+          <t>-0.333M</t>
         </is>
       </c>
       <c r="E383" t="inlineStr"/>
@@ -11743,20 +11747,24 @@
       </c>
       <c r="B384" t="inlineStr">
         <is>
-          <t>EIA Heating Oil Stocks ChangeJAN/31</t>
+          <t>EIA Distillate Stocks ChangeJAN/31</t>
         </is>
       </c>
       <c r="C384" t="inlineStr">
         <is>
-          <t>0.373M</t>
+          <t>-5.471M</t>
         </is>
       </c>
       <c r="D384" t="inlineStr">
         <is>
-          <t>0.128M</t>
-        </is>
-      </c>
-      <c r="E384" t="inlineStr"/>
+          <t>-4.994M</t>
+        </is>
+      </c>
+      <c r="E384" t="inlineStr">
+        <is>
+          <t>-1.5M</t>
+        </is>
+      </c>
       <c r="F384" t="inlineStr"/>
       <c r="G384" t="n">
         <v>3</v>
@@ -11770,27 +11778,23 @@
       </c>
       <c r="B385" t="inlineStr">
         <is>
-          <t>EIA Crude Oil Stocks ChangeJAN/31</t>
+          <t>EIA Distillate Fuel Production ChangeJAN/31</t>
         </is>
       </c>
       <c r="C385" t="inlineStr">
         <is>
-          <t>8.664M</t>
+          <t>-0.186M</t>
         </is>
       </c>
       <c r="D385" t="inlineStr">
         <is>
-          <t>3.463M</t>
-        </is>
-      </c>
-      <c r="E385" t="inlineStr">
-        <is>
-          <t>2.6M</t>
-        </is>
-      </c>
+          <t>0.028M</t>
+        </is>
+      </c>
+      <c r="E385" t="inlineStr"/>
       <c r="F385" t="inlineStr"/>
       <c r="G385" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="386">
@@ -11801,17 +11805,17 @@
       </c>
       <c r="B386" t="inlineStr">
         <is>
-          <t>EIA Distillate Fuel Production ChangeJAN/31</t>
+          <t>EIA Gasoline Production ChangeJAN/31</t>
         </is>
       </c>
       <c r="C386" t="inlineStr">
         <is>
-          <t>-0.186M</t>
+          <t>-0.027M</t>
         </is>
       </c>
       <c r="D386" t="inlineStr">
         <is>
-          <t>0.028M</t>
+          <t>-0.044M</t>
         </is>
       </c>
       <c r="E386" t="inlineStr"/>
@@ -11828,24 +11832,20 @@
       </c>
       <c r="B387" t="inlineStr">
         <is>
-          <t>EIA Distillate Stocks ChangeJAN/31</t>
+          <t>EIA Heating Oil Stocks ChangeJAN/31</t>
         </is>
       </c>
       <c r="C387" t="inlineStr">
         <is>
-          <t>-5.471M</t>
+          <t>0.373M</t>
         </is>
       </c>
       <c r="D387" t="inlineStr">
         <is>
-          <t>-4.994M</t>
-        </is>
-      </c>
-      <c r="E387" t="inlineStr">
-        <is>
-          <t>-1.5M</t>
-        </is>
-      </c>
+          <t>0.128M</t>
+        </is>
+      </c>
+      <c r="E387" t="inlineStr"/>
       <c r="F387" t="inlineStr"/>
       <c r="G387" t="n">
         <v>3</v>
@@ -11859,17 +11859,17 @@
       </c>
       <c r="B388" t="inlineStr">
         <is>
-          <t>EIA Gasoline Production ChangeJAN/31</t>
+          <t>EIA Cushing Crude Oil Stocks ChangeJAN/31</t>
         </is>
       </c>
       <c r="C388" t="inlineStr">
         <is>
-          <t>-0.027M</t>
+          <t>-0.034M</t>
         </is>
       </c>
       <c r="D388" t="inlineStr">
         <is>
-          <t>-0.044M</t>
+          <t>0.326M</t>
         </is>
       </c>
       <c r="E388" t="inlineStr"/>
@@ -11886,17 +11886,17 @@
       </c>
       <c r="B389" t="inlineStr">
         <is>
-          <t>EIA Refinery Crude Runs ChangeJAN/31</t>
+          <t>EIA Crude Oil Imports ChangeJAN/31</t>
         </is>
       </c>
       <c r="C389" t="inlineStr">
         <is>
-          <t>0.16M</t>
+          <t>-0.178M</t>
         </is>
       </c>
       <c r="D389" t="inlineStr">
         <is>
-          <t>-0.333M</t>
+          <t>0.532M</t>
         </is>
       </c>
       <c r="E389" t="inlineStr"/>
@@ -11913,22 +11913,22 @@
       </c>
       <c r="B390" t="inlineStr">
         <is>
-          <t>EIA Gasoline Stocks ChangeJAN/31</t>
+          <t>EIA Crude Oil Stocks ChangeJAN/31</t>
         </is>
       </c>
       <c r="C390" t="inlineStr">
         <is>
-          <t>2.233M</t>
+          <t>8.664M</t>
         </is>
       </c>
       <c r="D390" t="inlineStr">
         <is>
-          <t>2.957M</t>
+          <t>3.463M</t>
         </is>
       </c>
       <c r="E390" t="inlineStr">
         <is>
-          <t>1.2M</t>
+          <t>2.6M</t>
         </is>
       </c>
       <c r="F390" t="inlineStr"/>
@@ -12040,27 +12040,23 @@
       </c>
       <c r="B395" t="inlineStr">
         <is>
-          <t>Continuing Jobless ClaimsJAN/25</t>
+          <t>Jobless Claims 4-week AverageFEB/01</t>
         </is>
       </c>
       <c r="C395" t="inlineStr">
         <is>
-          <t>1886K</t>
+          <t>216.75K</t>
         </is>
       </c>
       <c r="D395" t="inlineStr">
         <is>
-          <t>1850K</t>
-        </is>
-      </c>
-      <c r="E395" t="inlineStr">
-        <is>
-          <t>1870K</t>
-        </is>
-      </c>
+          <t>212.75K</t>
+        </is>
+      </c>
+      <c r="E395" t="inlineStr"/>
       <c r="F395" t="inlineStr">
         <is>
-          <t>1855.0K</t>
+          <t>215.5K</t>
         </is>
       </c>
       <c r="G395" t="n">
@@ -12075,27 +12071,27 @@
       </c>
       <c r="B396" t="inlineStr">
         <is>
-          <t>Initial Jobless ClaimsFEB/01</t>
+          <t>Unit Labour Costs QoQ PrelQ4</t>
         </is>
       </c>
       <c r="C396" t="inlineStr">
         <is>
-          <t>219K</t>
+          <t>3%</t>
         </is>
       </c>
       <c r="D396" t="inlineStr">
         <is>
-          <t>208K</t>
+          <t>0.5%</t>
         </is>
       </c>
       <c r="E396" t="inlineStr">
         <is>
-          <t>213K</t>
+          <t>3.4%</t>
         </is>
       </c>
       <c r="F396" t="inlineStr">
         <is>
-          <t>215.0K</t>
+          <t>3%</t>
         </is>
       </c>
       <c r="G396" t="n">
@@ -12145,27 +12141,27 @@
       </c>
       <c r="B398" t="inlineStr">
         <is>
-          <t>Unit Labour Costs QoQ PrelQ4</t>
+          <t>Initial Jobless ClaimsFEB/01</t>
         </is>
       </c>
       <c r="C398" t="inlineStr">
         <is>
-          <t>3%</t>
+          <t>219K</t>
         </is>
       </c>
       <c r="D398" t="inlineStr">
         <is>
-          <t>0.5%</t>
+          <t>208K</t>
         </is>
       </c>
       <c r="E398" t="inlineStr">
         <is>
-          <t>3.4%</t>
+          <t>213K</t>
         </is>
       </c>
       <c r="F398" t="inlineStr">
         <is>
-          <t>3%</t>
+          <t>215.0K</t>
         </is>
       </c>
       <c r="G398" t="n">
@@ -12180,23 +12176,27 @@
       </c>
       <c r="B399" t="inlineStr">
         <is>
-          <t>Jobless Claims 4-week AverageFEB/01</t>
+          <t>Continuing Jobless ClaimsJAN/25</t>
         </is>
       </c>
       <c r="C399" t="inlineStr">
         <is>
-          <t>216.75K</t>
+          <t>1886K</t>
         </is>
       </c>
       <c r="D399" t="inlineStr">
         <is>
-          <t>212.75K</t>
-        </is>
-      </c>
-      <c r="E399" t="inlineStr"/>
+          <t>1850K</t>
+        </is>
+      </c>
+      <c r="E399" t="inlineStr">
+        <is>
+          <t>1870K</t>
+        </is>
+      </c>
       <c r="F399" t="inlineStr">
         <is>
-          <t>215.5K</t>
+          <t>1855.0K</t>
         </is>
       </c>
       <c r="G399" t="n">
@@ -12442,27 +12442,31 @@
       </c>
       <c r="B409" t="inlineStr">
         <is>
-          <t>Participation RateJAN</t>
+          <t>Average Weekly HoursJAN</t>
         </is>
       </c>
       <c r="C409" t="inlineStr">
         <is>
-          <t>62.6%</t>
+          <t>34.1</t>
         </is>
       </c>
       <c r="D409" t="inlineStr">
         <is>
-          <t>62.5%</t>
-        </is>
-      </c>
-      <c r="E409" t="inlineStr"/>
+          <t>34.2</t>
+        </is>
+      </c>
+      <c r="E409" t="inlineStr">
+        <is>
+          <t>34.3</t>
+        </is>
+      </c>
       <c r="F409" t="inlineStr">
         <is>
-          <t>62.5%</t>
+          <t>34.3</t>
         </is>
       </c>
       <c r="G409" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="410">
@@ -12473,31 +12477,31 @@
       </c>
       <c r="B410" t="inlineStr">
         <is>
-          <t>Nonfarm Payrolls PrivateJAN</t>
+          <t>Unemployment RateJAN</t>
         </is>
       </c>
       <c r="C410" t="inlineStr">
         <is>
-          <t>111K</t>
+          <t>4%</t>
         </is>
       </c>
       <c r="D410" t="inlineStr">
         <is>
-          <t>273K</t>
+          <t>4.1%</t>
         </is>
       </c>
       <c r="E410" t="inlineStr">
         <is>
-          <t>141K</t>
+          <t>4.1%</t>
         </is>
       </c>
       <c r="F410" t="inlineStr">
         <is>
-          <t>180K</t>
+          <t>4.1%</t>
         </is>
       </c>
       <c r="G410" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="411">
@@ -12508,27 +12512,31 @@
       </c>
       <c r="B411" t="inlineStr">
         <is>
-          <t>Government PayrollsJAN</t>
+          <t>Average Hourly Earnings YoYJAN</t>
         </is>
       </c>
       <c r="C411" t="inlineStr">
         <is>
-          <t>32K</t>
+          <t>4.1%</t>
         </is>
       </c>
       <c r="D411" t="inlineStr">
         <is>
-          <t>34K</t>
-        </is>
-      </c>
-      <c r="E411" t="inlineStr"/>
+          <t>4.1%</t>
+        </is>
+      </c>
+      <c r="E411" t="inlineStr">
+        <is>
+          <t>3.8%</t>
+        </is>
+      </c>
       <c r="F411" t="inlineStr">
         <is>
-          <t>25K</t>
+          <t>3.9%</t>
         </is>
       </c>
       <c r="G411" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="412">
@@ -12539,31 +12547,31 @@
       </c>
       <c r="B412" t="inlineStr">
         <is>
-          <t>Manufacturing PayrollsJAN</t>
+          <t>Average Hourly Earnings MoMJAN</t>
         </is>
       </c>
       <c r="C412" t="inlineStr">
         <is>
-          <t>3K</t>
+          <t>0.5%</t>
         </is>
       </c>
       <c r="D412" t="inlineStr">
         <is>
-          <t>-12K</t>
+          <t>0.3%</t>
         </is>
       </c>
       <c r="E412" t="inlineStr">
         <is>
-          <t>-2K</t>
+          <t>0.3%</t>
         </is>
       </c>
       <c r="F412" t="inlineStr">
         <is>
-          <t>-5K</t>
+          <t>0.3%</t>
         </is>
       </c>
       <c r="G412" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="413">
@@ -12574,27 +12582,31 @@
       </c>
       <c r="B413" t="inlineStr">
         <is>
-          <t>U-6 Unemployment RateJAN</t>
+          <t>Non Farm PayrollsJAN</t>
         </is>
       </c>
       <c r="C413" t="inlineStr">
         <is>
-          <t>7.5%</t>
+          <t>143K</t>
         </is>
       </c>
       <c r="D413" t="inlineStr">
         <is>
-          <t>7.5%</t>
-        </is>
-      </c>
-      <c r="E413" t="inlineStr"/>
+          <t>307K</t>
+        </is>
+      </c>
+      <c r="E413" t="inlineStr">
+        <is>
+          <t>170K</t>
+        </is>
+      </c>
       <c r="F413" t="inlineStr">
         <is>
-          <t>7.5%</t>
+          <t>205K</t>
         </is>
       </c>
       <c r="G413" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="414">
@@ -12605,31 +12617,27 @@
       </c>
       <c r="B414" t="inlineStr">
         <is>
-          <t>Non Farm PayrollsJAN</t>
+          <t>Government PayrollsJAN</t>
         </is>
       </c>
       <c r="C414" t="inlineStr">
         <is>
-          <t>143K</t>
+          <t>32K</t>
         </is>
       </c>
       <c r="D414" t="inlineStr">
         <is>
-          <t>307K</t>
-        </is>
-      </c>
-      <c r="E414" t="inlineStr">
-        <is>
-          <t>170K</t>
-        </is>
-      </c>
+          <t>34K</t>
+        </is>
+      </c>
+      <c r="E414" t="inlineStr"/>
       <c r="F414" t="inlineStr">
         <is>
-          <t>205K</t>
+          <t>25K</t>
         </is>
       </c>
       <c r="G414" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="415">
@@ -12640,31 +12648,31 @@
       </c>
       <c r="B415" t="inlineStr">
         <is>
-          <t>Average Hourly Earnings MoMJAN</t>
+          <t>Manufacturing PayrollsJAN</t>
         </is>
       </c>
       <c r="C415" t="inlineStr">
         <is>
-          <t>0.5%</t>
+          <t>3K</t>
         </is>
       </c>
       <c r="D415" t="inlineStr">
         <is>
-          <t>0.3%</t>
+          <t>-12K</t>
         </is>
       </c>
       <c r="E415" t="inlineStr">
         <is>
-          <t>0.3%</t>
+          <t>-2K</t>
         </is>
       </c>
       <c r="F415" t="inlineStr">
         <is>
-          <t>0.3%</t>
+          <t>-5K</t>
         </is>
       </c>
       <c r="G415" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="416">
@@ -12675,31 +12683,31 @@
       </c>
       <c r="B416" t="inlineStr">
         <is>
-          <t>Average Hourly Earnings YoYJAN</t>
+          <t>Nonfarm Payrolls PrivateJAN</t>
         </is>
       </c>
       <c r="C416" t="inlineStr">
         <is>
-          <t>4.1%</t>
+          <t>111K</t>
         </is>
       </c>
       <c r="D416" t="inlineStr">
         <is>
-          <t>4.1%</t>
+          <t>273K</t>
         </is>
       </c>
       <c r="E416" t="inlineStr">
         <is>
-          <t>3.8%</t>
+          <t>141K</t>
         </is>
       </c>
       <c r="F416" t="inlineStr">
         <is>
-          <t>3.9%</t>
+          <t>180K</t>
         </is>
       </c>
       <c r="G416" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="417">
@@ -12710,31 +12718,27 @@
       </c>
       <c r="B417" t="inlineStr">
         <is>
-          <t>Unemployment RateJAN</t>
+          <t>Participation RateJAN</t>
         </is>
       </c>
       <c r="C417" t="inlineStr">
         <is>
-          <t>4%</t>
+          <t>62.6%</t>
         </is>
       </c>
       <c r="D417" t="inlineStr">
         <is>
-          <t>4.1%</t>
-        </is>
-      </c>
-      <c r="E417" t="inlineStr">
-        <is>
-          <t>4.1%</t>
-        </is>
-      </c>
+          <t>62.5%</t>
+        </is>
+      </c>
+      <c r="E417" t="inlineStr"/>
       <c r="F417" t="inlineStr">
         <is>
-          <t>4.1%</t>
+          <t>62.5%</t>
         </is>
       </c>
       <c r="G417" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="418">
@@ -12745,27 +12749,23 @@
       </c>
       <c r="B418" t="inlineStr">
         <is>
-          <t>Average Weekly HoursJAN</t>
+          <t>U-6 Unemployment RateJAN</t>
         </is>
       </c>
       <c r="C418" t="inlineStr">
         <is>
-          <t>34.1</t>
+          <t>7.5%</t>
         </is>
       </c>
       <c r="D418" t="inlineStr">
         <is>
-          <t>34.2</t>
-        </is>
-      </c>
-      <c r="E418" t="inlineStr">
-        <is>
-          <t>34.3</t>
-        </is>
-      </c>
+          <t>7.5%</t>
+        </is>
+      </c>
+      <c r="E418" t="inlineStr"/>
       <c r="F418" t="inlineStr">
         <is>
-          <t>34.3</t>
+          <t>7.5%</t>
         </is>
       </c>
       <c r="G418" t="n">
@@ -12872,27 +12872,23 @@
       </c>
       <c r="B423" t="inlineStr">
         <is>
-          <t>Michigan Current Conditions PrelFEB</t>
+          <t>Michigan 5 Year Inflation Expectations PrelFEB</t>
         </is>
       </c>
       <c r="C423" t="inlineStr">
         <is>
-          <t>68.7</t>
+          <t>3.3%</t>
         </is>
       </c>
       <c r="D423" t="inlineStr">
         <is>
-          <t>74</t>
-        </is>
-      </c>
-      <c r="E423" t="inlineStr">
-        <is>
-          <t>73</t>
-        </is>
-      </c>
+          <t>3.2%</t>
+        </is>
+      </c>
+      <c r="E423" t="inlineStr"/>
       <c r="F423" t="inlineStr">
         <is>
-          <t>74.3</t>
+          <t>3.3%</t>
         </is>
       </c>
       <c r="G423" t="n">
@@ -12907,31 +12903,31 @@
       </c>
       <c r="B424" t="inlineStr">
         <is>
-          <t>Wholesale Inventories MoMDEC</t>
+          <t>Michigan Consumer Sentiment PrelFEB</t>
         </is>
       </c>
       <c r="C424" t="inlineStr">
         <is>
-          <t>-0.5%</t>
+          <t>67.8</t>
         </is>
       </c>
       <c r="D424" t="inlineStr">
         <is>
-          <t>-0.1%</t>
+          <t>71.1</t>
         </is>
       </c>
       <c r="E424" t="inlineStr">
         <is>
-          <t>-0.5%</t>
+          <t>71.1</t>
         </is>
       </c>
       <c r="F424" t="inlineStr">
         <is>
-          <t>-0.5%</t>
+          <t>72</t>
         </is>
       </c>
       <c r="G424" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="425">
@@ -12942,23 +12938,27 @@
       </c>
       <c r="B425" t="inlineStr">
         <is>
-          <t>Michigan Inflation Expectations PrelFEB</t>
+          <t>Michigan Consumer Expectations PrelFEB</t>
         </is>
       </c>
       <c r="C425" t="inlineStr">
         <is>
-          <t>4.3%</t>
+          <t>67.3</t>
         </is>
       </c>
       <c r="D425" t="inlineStr">
         <is>
-          <t>3.3%</t>
-        </is>
-      </c>
-      <c r="E425" t="inlineStr"/>
+          <t>69.3</t>
+        </is>
+      </c>
+      <c r="E425" t="inlineStr">
+        <is>
+          <t>70</t>
+        </is>
+      </c>
       <c r="F425" t="inlineStr">
         <is>
-          <t>3.4%</t>
+          <t>69.5</t>
         </is>
       </c>
       <c r="G425" t="n">
@@ -12973,27 +12973,23 @@
       </c>
       <c r="B426" t="inlineStr">
         <is>
-          <t>Michigan Consumer Expectations PrelFEB</t>
+          <t>Michigan Inflation Expectations PrelFEB</t>
         </is>
       </c>
       <c r="C426" t="inlineStr">
         <is>
-          <t>67.3</t>
+          <t>4.3%</t>
         </is>
       </c>
       <c r="D426" t="inlineStr">
         <is>
-          <t>69.3</t>
-        </is>
-      </c>
-      <c r="E426" t="inlineStr">
-        <is>
-          <t>70</t>
-        </is>
-      </c>
+          <t>3.3%</t>
+        </is>
+      </c>
+      <c r="E426" t="inlineStr"/>
       <c r="F426" t="inlineStr">
         <is>
-          <t>69.5</t>
+          <t>3.4%</t>
         </is>
       </c>
       <c r="G426" t="n">
@@ -13008,23 +13004,27 @@
       </c>
       <c r="B427" t="inlineStr">
         <is>
-          <t>Michigan 5 Year Inflation Expectations PrelFEB</t>
+          <t>Wholesale Inventories MoMDEC</t>
         </is>
       </c>
       <c r="C427" t="inlineStr">
         <is>
-          <t>3.3%</t>
+          <t>-0.5%</t>
         </is>
       </c>
       <c r="D427" t="inlineStr">
         <is>
-          <t>3.2%</t>
-        </is>
-      </c>
-      <c r="E427" t="inlineStr"/>
+          <t>-0.1%</t>
+        </is>
+      </c>
+      <c r="E427" t="inlineStr">
+        <is>
+          <t>-0.5%</t>
+        </is>
+      </c>
       <c r="F427" t="inlineStr">
         <is>
-          <t>3.3%</t>
+          <t>-0.5%</t>
         </is>
       </c>
       <c r="G427" t="n">
@@ -13039,31 +13039,31 @@
       </c>
       <c r="B428" t="inlineStr">
         <is>
-          <t>Michigan Consumer Sentiment PrelFEB</t>
+          <t>Michigan Current Conditions PrelFEB</t>
         </is>
       </c>
       <c r="C428" t="inlineStr">
         <is>
-          <t>67.8</t>
+          <t>68.7</t>
         </is>
       </c>
       <c r="D428" t="inlineStr">
         <is>
-          <t>71.1</t>
+          <t>74</t>
         </is>
       </c>
       <c r="E428" t="inlineStr">
         <is>
-          <t>71.1</t>
+          <t>73</t>
         </is>
       </c>
       <c r="F428" t="inlineStr">
         <is>
-          <t>72</t>
+          <t>74.3</t>
         </is>
       </c>
       <c r="G428" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="429">
@@ -13636,27 +13636,27 @@
       </c>
       <c r="B451" t="inlineStr">
         <is>
-          <t>Core Inflation Rate MoMJAN</t>
+          <t>Inflation Rate YoYJAN</t>
         </is>
       </c>
       <c r="C451" t="inlineStr">
         <is>
-          <t>0.4%</t>
+          <t>3%</t>
         </is>
       </c>
       <c r="D451" t="inlineStr">
         <is>
-          <t>0.2%</t>
+          <t>2.9%</t>
         </is>
       </c>
       <c r="E451" t="inlineStr">
         <is>
-          <t>0.3%</t>
+          <t>2.9%</t>
         </is>
       </c>
       <c r="F451" t="inlineStr">
         <is>
-          <t>0.3%</t>
+          <t>2.9%</t>
         </is>
       </c>
       <c r="G451" t="n">
@@ -13671,31 +13671,31 @@
       </c>
       <c r="B452" t="inlineStr">
         <is>
-          <t>Core Inflation Rate YoYJAN</t>
+          <t>CPIJAN</t>
         </is>
       </c>
       <c r="C452" t="inlineStr">
         <is>
-          <t>3.3%</t>
+          <t>317.67</t>
         </is>
       </c>
       <c r="D452" t="inlineStr">
         <is>
-          <t>3.2%</t>
+          <t>315.61</t>
         </is>
       </c>
       <c r="E452" t="inlineStr">
         <is>
-          <t>3.1%</t>
+          <t>317.46</t>
         </is>
       </c>
       <c r="F452" t="inlineStr">
         <is>
-          <t>3.1%</t>
+          <t>317.3</t>
         </is>
       </c>
       <c r="G452" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="453">
@@ -13706,31 +13706,27 @@
       </c>
       <c r="B453" t="inlineStr">
         <is>
-          <t>Inflation Rate MoMJAN</t>
+          <t>CPI s.aJAN</t>
         </is>
       </c>
       <c r="C453" t="inlineStr">
         <is>
-          <t>0.5%</t>
+          <t>319.086</t>
         </is>
       </c>
       <c r="D453" t="inlineStr">
         <is>
-          <t>0.4%</t>
-        </is>
-      </c>
-      <c r="E453" t="inlineStr">
-        <is>
-          <t>0.3%</t>
-        </is>
-      </c>
+          <t>317.603</t>
+        </is>
+      </c>
+      <c r="E453" t="inlineStr"/>
       <c r="F453" t="inlineStr">
         <is>
-          <t>0.2%</t>
+          <t>318.2</t>
         </is>
       </c>
       <c r="G453" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="454">
@@ -13741,27 +13737,31 @@
       </c>
       <c r="B454" t="inlineStr">
         <is>
-          <t>CPI s.aJAN</t>
+          <t>Core Inflation Rate YoYJAN</t>
         </is>
       </c>
       <c r="C454" t="inlineStr">
         <is>
-          <t>319.086</t>
+          <t>3.3%</t>
         </is>
       </c>
       <c r="D454" t="inlineStr">
         <is>
-          <t>317.603</t>
-        </is>
-      </c>
-      <c r="E454" t="inlineStr"/>
+          <t>3.2%</t>
+        </is>
+      </c>
+      <c r="E454" t="inlineStr">
+        <is>
+          <t>3.1%</t>
+        </is>
+      </c>
       <c r="F454" t="inlineStr">
         <is>
-          <t>318.2</t>
+          <t>3.1%</t>
         </is>
       </c>
       <c r="G454" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="455">
@@ -13772,31 +13772,31 @@
       </c>
       <c r="B455" t="inlineStr">
         <is>
-          <t>CPIJAN</t>
+          <t>Inflation Rate MoMJAN</t>
         </is>
       </c>
       <c r="C455" t="inlineStr">
         <is>
-          <t>317.67</t>
+          <t>0.5%</t>
         </is>
       </c>
       <c r="D455" t="inlineStr">
         <is>
-          <t>315.61</t>
+          <t>0.4%</t>
         </is>
       </c>
       <c r="E455" t="inlineStr">
         <is>
-          <t>317.46</t>
+          <t>0.3%</t>
         </is>
       </c>
       <c r="F455" t="inlineStr">
         <is>
-          <t>317.3</t>
+          <t>0.2%</t>
         </is>
       </c>
       <c r="G455" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="456">
@@ -13807,27 +13807,27 @@
       </c>
       <c r="B456" t="inlineStr">
         <is>
-          <t>Inflation Rate YoYJAN</t>
+          <t>Core Inflation Rate MoMJAN</t>
         </is>
       </c>
       <c r="C456" t="inlineStr">
         <is>
-          <t>3%</t>
+          <t>0.4%</t>
         </is>
       </c>
       <c r="D456" t="inlineStr">
         <is>
-          <t>2.9%</t>
+          <t>0.2%</t>
         </is>
       </c>
       <c r="E456" t="inlineStr">
         <is>
-          <t>2.9%</t>
+          <t>0.3%</t>
         </is>
       </c>
       <c r="F456" t="inlineStr">
         <is>
-          <t>2.9%</t>
+          <t>0.3%</t>
         </is>
       </c>
       <c r="G456" t="n">
@@ -13842,27 +13842,23 @@
       </c>
       <c r="B457" t="inlineStr">
         <is>
-          <t>EIA Crude Oil Stocks ChangeFEB/07</t>
+          <t>EIA Refinery Crude Runs ChangeFEB/07</t>
         </is>
       </c>
       <c r="C457" t="inlineStr">
         <is>
-          <t>4.07M</t>
+          <t>0.082M</t>
         </is>
       </c>
       <c r="D457" t="inlineStr">
         <is>
-          <t>8.664M</t>
-        </is>
-      </c>
-      <c r="E457" t="inlineStr">
-        <is>
-          <t>3M</t>
-        </is>
-      </c>
+          <t>0.16M</t>
+        </is>
+      </c>
+      <c r="E457" t="inlineStr"/>
       <c r="F457" t="inlineStr"/>
       <c r="G457" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="458">
@@ -13873,17 +13869,17 @@
       </c>
       <c r="B458" t="inlineStr">
         <is>
-          <t>EIA Heating Oil Stocks ChangeFEB/07</t>
+          <t>EIA Gasoline Production ChangeFEB/07</t>
         </is>
       </c>
       <c r="C458" t="inlineStr">
         <is>
-          <t>0.159M</t>
+          <t>0.18M</t>
         </is>
       </c>
       <c r="D458" t="inlineStr">
         <is>
-          <t>0.373M</t>
+          <t>-0.027M</t>
         </is>
       </c>
       <c r="E458" t="inlineStr"/>
@@ -13900,23 +13896,27 @@
       </c>
       <c r="B459" t="inlineStr">
         <is>
-          <t>EIA Cushing Crude Oil Stocks ChangeFEB/07</t>
+          <t>EIA Gasoline Stocks ChangeFEB/07</t>
         </is>
       </c>
       <c r="C459" t="inlineStr">
         <is>
-          <t>0.872M</t>
+          <t>-3.035M</t>
         </is>
       </c>
       <c r="D459" t="inlineStr">
         <is>
-          <t>-0.034M</t>
-        </is>
-      </c>
-      <c r="E459" t="inlineStr"/>
+          <t>2.233M</t>
+        </is>
+      </c>
+      <c r="E459" t="inlineStr">
+        <is>
+          <t>1.5M</t>
+        </is>
+      </c>
       <c r="F459" t="inlineStr"/>
       <c r="G459" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="460">
@@ -13927,17 +13927,17 @@
       </c>
       <c r="B460" t="inlineStr">
         <is>
-          <t>EIA Crude Oil Imports ChangeFEB/07</t>
+          <t>EIA Distillate Fuel Production ChangeFEB/07</t>
         </is>
       </c>
       <c r="C460" t="inlineStr">
         <is>
-          <t>-0.184M</t>
+          <t>-0.009M</t>
         </is>
       </c>
       <c r="D460" t="inlineStr">
         <is>
-          <t>-0.178M</t>
+          <t>-0.186M</t>
         </is>
       </c>
       <c r="E460" t="inlineStr"/>
@@ -13954,20 +13954,24 @@
       </c>
       <c r="B461" t="inlineStr">
         <is>
-          <t>EIA Distillate Fuel Production ChangeFEB/07</t>
+          <t>EIA Distillate Stocks ChangeFEB/07</t>
         </is>
       </c>
       <c r="C461" t="inlineStr">
         <is>
-          <t>-0.009M</t>
+          <t>0.135M</t>
         </is>
       </c>
       <c r="D461" t="inlineStr">
         <is>
-          <t>-0.186M</t>
-        </is>
-      </c>
-      <c r="E461" t="inlineStr"/>
+          <t>-5.471M</t>
+        </is>
+      </c>
+      <c r="E461" t="inlineStr">
+        <is>
+          <t>-2M</t>
+        </is>
+      </c>
       <c r="F461" t="inlineStr"/>
       <c r="G461" t="n">
         <v>3</v>
@@ -13981,27 +13985,23 @@
       </c>
       <c r="B462" t="inlineStr">
         <is>
-          <t>EIA Gasoline Stocks ChangeFEB/07</t>
+          <t>EIA Cushing Crude Oil Stocks ChangeFEB/07</t>
         </is>
       </c>
       <c r="C462" t="inlineStr">
         <is>
-          <t>-3.035M</t>
+          <t>0.872M</t>
         </is>
       </c>
       <c r="D462" t="inlineStr">
         <is>
-          <t>2.233M</t>
-        </is>
-      </c>
-      <c r="E462" t="inlineStr">
-        <is>
-          <t>1.5M</t>
-        </is>
-      </c>
+          <t>-0.034M</t>
+        </is>
+      </c>
+      <c r="E462" t="inlineStr"/>
       <c r="F462" t="inlineStr"/>
       <c r="G462" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="463">
@@ -14012,17 +14012,17 @@
       </c>
       <c r="B463" t="inlineStr">
         <is>
-          <t>EIA Gasoline Production ChangeFEB/07</t>
+          <t>EIA Heating Oil Stocks ChangeFEB/07</t>
         </is>
       </c>
       <c r="C463" t="inlineStr">
         <is>
-          <t>0.18M</t>
+          <t>0.159M</t>
         </is>
       </c>
       <c r="D463" t="inlineStr">
         <is>
-          <t>-0.027M</t>
+          <t>0.373M</t>
         </is>
       </c>
       <c r="E463" t="inlineStr"/>
@@ -14039,23 +14039,27 @@
       </c>
       <c r="B464" t="inlineStr">
         <is>
-          <t>EIA Refinery Crude Runs ChangeFEB/07</t>
+          <t>EIA Crude Oil Stocks ChangeFEB/07</t>
         </is>
       </c>
       <c r="C464" t="inlineStr">
         <is>
-          <t>0.082M</t>
+          <t>4.07M</t>
         </is>
       </c>
       <c r="D464" t="inlineStr">
         <is>
-          <t>0.16M</t>
-        </is>
-      </c>
-      <c r="E464" t="inlineStr"/>
+          <t>8.664M</t>
+        </is>
+      </c>
+      <c r="E464" t="inlineStr">
+        <is>
+          <t>3M</t>
+        </is>
+      </c>
       <c r="F464" t="inlineStr"/>
       <c r="G464" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="465">
@@ -14066,24 +14070,20 @@
       </c>
       <c r="B465" t="inlineStr">
         <is>
-          <t>EIA Distillate Stocks ChangeFEB/07</t>
+          <t>EIA Crude Oil Imports ChangeFEB/07</t>
         </is>
       </c>
       <c r="C465" t="inlineStr">
         <is>
-          <t>0.135M</t>
+          <t>-0.184M</t>
         </is>
       </c>
       <c r="D465" t="inlineStr">
         <is>
-          <t>-5.471M</t>
-        </is>
-      </c>
-      <c r="E465" t="inlineStr">
-        <is>
-          <t>-2M</t>
-        </is>
-      </c>
+          <t>-0.178M</t>
+        </is>
+      </c>
+      <c r="E465" t="inlineStr"/>
       <c r="F465" t="inlineStr"/>
       <c r="G465" t="n">
         <v>3</v>
@@ -14224,23 +14224,27 @@
       </c>
       <c r="B471" t="inlineStr">
         <is>
-          <t>Jobless Claims 4-week AverageFEB/08</t>
+          <t>Core PPI YoYJAN</t>
         </is>
       </c>
       <c r="C471" t="inlineStr">
         <is>
-          <t>216K</t>
+          <t>3.6%</t>
         </is>
       </c>
       <c r="D471" t="inlineStr">
         <is>
-          <t>217K</t>
-        </is>
-      </c>
-      <c r="E471" t="inlineStr"/>
+          <t>3.7%</t>
+        </is>
+      </c>
+      <c r="E471" t="inlineStr">
+        <is>
+          <t>3.3%</t>
+        </is>
+      </c>
       <c r="F471" t="inlineStr">
         <is>
-          <t>216.0K</t>
+          <t>3.5%</t>
         </is>
       </c>
       <c r="G471" t="n">
@@ -14255,27 +14259,23 @@
       </c>
       <c r="B472" t="inlineStr">
         <is>
-          <t>PPI Ex Food, Energy and Trade YoYJAN</t>
+          <t>PPIJAN</t>
         </is>
       </c>
       <c r="C472" t="inlineStr">
         <is>
-          <t>3.4%</t>
+          <t>147.716</t>
         </is>
       </c>
       <c r="D472" t="inlineStr">
         <is>
-          <t>3.5%</t>
-        </is>
-      </c>
-      <c r="E472" t="inlineStr">
-        <is>
-          <t>3.2%</t>
-        </is>
-      </c>
+          <t>147.127</t>
+        </is>
+      </c>
+      <c r="E472" t="inlineStr"/>
       <c r="F472" t="inlineStr">
         <is>
-          <t>3.3%</t>
+          <t>147.2</t>
         </is>
       </c>
       <c r="G472" t="n">
@@ -14290,19 +14290,19 @@
       </c>
       <c r="B473" t="inlineStr">
         <is>
-          <t>PPI MoMJAN</t>
+          <t>Core PPI MoMJAN</t>
         </is>
       </c>
       <c r="C473" t="inlineStr">
         <is>
+          <t>0.3%</t>
+        </is>
+      </c>
+      <c r="D473" t="inlineStr">
+        <is>
           <t>0.4%</t>
         </is>
       </c>
-      <c r="D473" t="inlineStr">
-        <is>
-          <t>0.5%</t>
-        </is>
-      </c>
       <c r="E473" t="inlineStr">
         <is>
           <t>0.3%</t>
@@ -14310,11 +14310,11 @@
       </c>
       <c r="F473" t="inlineStr">
         <is>
-          <t>0.3%</t>
+          <t>0.1%</t>
         </is>
       </c>
       <c r="G473" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="474">
@@ -14325,23 +14325,27 @@
       </c>
       <c r="B474" t="inlineStr">
         <is>
-          <t>PPI Ex Food, Energy and Trade MoMJAN</t>
+          <t>PPI YoYJAN</t>
         </is>
       </c>
       <c r="C474" t="inlineStr">
         <is>
-          <t>0.3%</t>
+          <t>3.5%</t>
         </is>
       </c>
       <c r="D474" t="inlineStr">
         <is>
-          <t>0.4%</t>
-        </is>
-      </c>
-      <c r="E474" t="inlineStr"/>
+          <t>3.5%</t>
+        </is>
+      </c>
+      <c r="E474" t="inlineStr">
+        <is>
+          <t>3.2%</t>
+        </is>
+      </c>
       <c r="F474" t="inlineStr">
         <is>
-          <t>0.2%</t>
+          <t>3.4%</t>
         </is>
       </c>
       <c r="G474" t="n">
@@ -14356,31 +14360,31 @@
       </c>
       <c r="B475" t="inlineStr">
         <is>
-          <t>Continuing Jobless ClaimsFEB/01</t>
+          <t>Initial Jobless ClaimsFEB/08</t>
         </is>
       </c>
       <c r="C475" t="inlineStr">
         <is>
-          <t>1850K</t>
+          <t>213K</t>
         </is>
       </c>
       <c r="D475" t="inlineStr">
         <is>
-          <t>1886K</t>
+          <t>220K</t>
         </is>
       </c>
       <c r="E475" t="inlineStr">
         <is>
-          <t>1880K</t>
+          <t>215K</t>
         </is>
       </c>
       <c r="F475" t="inlineStr">
         <is>
-          <t>1875.0K</t>
+          <t>215.0K</t>
         </is>
       </c>
       <c r="G475" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="476">
@@ -14391,31 +14395,31 @@
       </c>
       <c r="B476" t="inlineStr">
         <is>
-          <t>Initial Jobless ClaimsFEB/08</t>
+          <t>PPI Ex Food, Energy and Trade YoYJAN</t>
         </is>
       </c>
       <c r="C476" t="inlineStr">
         <is>
-          <t>213K</t>
+          <t>3.4%</t>
         </is>
       </c>
       <c r="D476" t="inlineStr">
         <is>
-          <t>220K</t>
+          <t>3.5%</t>
         </is>
       </c>
       <c r="E476" t="inlineStr">
         <is>
-          <t>215K</t>
+          <t>3.2%</t>
         </is>
       </c>
       <c r="F476" t="inlineStr">
         <is>
-          <t>215.0K</t>
+          <t>3.3%</t>
         </is>
       </c>
       <c r="G476" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="477">
@@ -14426,27 +14430,23 @@
       </c>
       <c r="B477" t="inlineStr">
         <is>
-          <t>Core PPI YoYJAN</t>
+          <t>PPI Ex Food, Energy and Trade MoMJAN</t>
         </is>
       </c>
       <c r="C477" t="inlineStr">
         <is>
-          <t>3.6%</t>
+          <t>0.3%</t>
         </is>
       </c>
       <c r="D477" t="inlineStr">
         <is>
-          <t>3.7%</t>
-        </is>
-      </c>
-      <c r="E477" t="inlineStr">
-        <is>
-          <t>3.3%</t>
-        </is>
-      </c>
+          <t>0.4%</t>
+        </is>
+      </c>
+      <c r="E477" t="inlineStr"/>
       <c r="F477" t="inlineStr">
         <is>
-          <t>3.5%</t>
+          <t>0.2%</t>
         </is>
       </c>
       <c r="G477" t="n">
@@ -14461,31 +14461,31 @@
       </c>
       <c r="B478" t="inlineStr">
         <is>
-          <t>PPI YoYJAN</t>
+          <t>PPI MoMJAN</t>
         </is>
       </c>
       <c r="C478" t="inlineStr">
         <is>
-          <t>3.5%</t>
+          <t>0.4%</t>
         </is>
       </c>
       <c r="D478" t="inlineStr">
         <is>
-          <t>3.5%</t>
+          <t>0.5%</t>
         </is>
       </c>
       <c r="E478" t="inlineStr">
         <is>
-          <t>3.2%</t>
+          <t>0.3%</t>
         </is>
       </c>
       <c r="F478" t="inlineStr">
         <is>
-          <t>3.4%</t>
+          <t>0.3%</t>
         </is>
       </c>
       <c r="G478" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="479">
@@ -14496,31 +14496,27 @@
       </c>
       <c r="B479" t="inlineStr">
         <is>
-          <t>Core PPI MoMJAN</t>
+          <t>Jobless Claims 4-week AverageFEB/08</t>
         </is>
       </c>
       <c r="C479" t="inlineStr">
         <is>
-          <t>0.3%</t>
+          <t>216K</t>
         </is>
       </c>
       <c r="D479" t="inlineStr">
         <is>
-          <t>0.4%</t>
-        </is>
-      </c>
-      <c r="E479" t="inlineStr">
-        <is>
-          <t>0.3%</t>
-        </is>
-      </c>
+          <t>217K</t>
+        </is>
+      </c>
+      <c r="E479" t="inlineStr"/>
       <c r="F479" t="inlineStr">
         <is>
-          <t>0.1%</t>
+          <t>216.0K</t>
         </is>
       </c>
       <c r="G479" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="480">
@@ -14531,23 +14527,27 @@
       </c>
       <c r="B480" t="inlineStr">
         <is>
-          <t>PPIJAN</t>
+          <t>Continuing Jobless ClaimsFEB/01</t>
         </is>
       </c>
       <c r="C480" t="inlineStr">
         <is>
-          <t>147.716</t>
+          <t>1850K</t>
         </is>
       </c>
       <c r="D480" t="inlineStr">
         <is>
-          <t>147.127</t>
-        </is>
-      </c>
-      <c r="E480" t="inlineStr"/>
+          <t>1886K</t>
+        </is>
+      </c>
+      <c r="E480" t="inlineStr">
+        <is>
+          <t>1880K</t>
+        </is>
+      </c>
       <c r="F480" t="inlineStr">
         <is>
-          <t>147.2</t>
+          <t>1875.0K</t>
         </is>
       </c>
       <c r="G480" t="n">
@@ -14728,27 +14728,31 @@
       </c>
       <c r="B487" t="inlineStr">
         <is>
-          <t>Import Prices YoYJAN</t>
+          <t>Retail Sales Control Group MoMJAN</t>
         </is>
       </c>
       <c r="C487" t="inlineStr">
         <is>
-          <t>1.9%</t>
+          <t>-0.8%</t>
         </is>
       </c>
       <c r="D487" t="inlineStr">
         <is>
-          <t>2.2%</t>
-        </is>
-      </c>
-      <c r="E487" t="inlineStr"/>
+          <t>0.8%</t>
+        </is>
+      </c>
+      <c r="E487" t="inlineStr">
+        <is>
+          <t>0.3%</t>
+        </is>
+      </c>
       <c r="F487" t="inlineStr">
         <is>
-          <t>2.8%</t>
+          <t>0.4%</t>
         </is>
       </c>
       <c r="G487" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="488">
@@ -14759,22 +14763,22 @@
       </c>
       <c r="B488" t="inlineStr">
         <is>
-          <t>Import Prices MoMJAN</t>
+          <t>Export Prices MoMJAN</t>
         </is>
       </c>
       <c r="C488" t="inlineStr">
         <is>
+          <t>1.3%</t>
+        </is>
+      </c>
+      <c r="D488" t="inlineStr">
+        <is>
+          <t>0.5%</t>
+        </is>
+      </c>
+      <c r="E488" t="inlineStr">
+        <is>
           <t>0.3%</t>
-        </is>
-      </c>
-      <c r="D488" t="inlineStr">
-        <is>
-          <t>0.2%</t>
-        </is>
-      </c>
-      <c r="E488" t="inlineStr">
-        <is>
-          <t>0.4%</t>
         </is>
       </c>
       <c r="F488" t="inlineStr">
@@ -14794,31 +14798,27 @@
       </c>
       <c r="B489" t="inlineStr">
         <is>
-          <t>Retail Sales MoMJAN</t>
+          <t>Retail Sales Ex Gas/Autos MoMJAN</t>
         </is>
       </c>
       <c r="C489" t="inlineStr">
         <is>
-          <t>-0.9%</t>
+          <t>-0.5%</t>
         </is>
       </c>
       <c r="D489" t="inlineStr">
         <is>
-          <t>0.7%</t>
-        </is>
-      </c>
-      <c r="E489" t="inlineStr">
-        <is>
-          <t>-0.1%</t>
-        </is>
-      </c>
+          <t>0.5%</t>
+        </is>
+      </c>
+      <c r="E489" t="inlineStr"/>
       <c r="F489" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>0.2%</t>
         </is>
       </c>
       <c r="G489" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="490">
@@ -14829,31 +14829,27 @@
       </c>
       <c r="B490" t="inlineStr">
         <is>
-          <t>Retail Sales Ex Autos MoMJAN</t>
+          <t>Export Prices YoYJAN</t>
         </is>
       </c>
       <c r="C490" t="inlineStr">
         <is>
-          <t>-0.4%</t>
+          <t>2.7%</t>
         </is>
       </c>
       <c r="D490" t="inlineStr">
         <is>
-          <t>0.7%</t>
-        </is>
-      </c>
-      <c r="E490" t="inlineStr">
-        <is>
-          <t>0.3%</t>
-        </is>
-      </c>
+          <t>2%</t>
+        </is>
+      </c>
+      <c r="E490" t="inlineStr"/>
       <c r="F490" t="inlineStr">
         <is>
-          <t>0.3%</t>
+          <t>2.3%</t>
         </is>
       </c>
       <c r="G490" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="491">
@@ -14864,23 +14860,23 @@
       </c>
       <c r="B491" t="inlineStr">
         <is>
-          <t>Export Prices YoYJAN</t>
+          <t>Retail Sales YoYJAN</t>
         </is>
       </c>
       <c r="C491" t="inlineStr">
         <is>
-          <t>2.7%</t>
+          <t>4.2%</t>
         </is>
       </c>
       <c r="D491" t="inlineStr">
         <is>
-          <t>2%</t>
+          <t>4.4%</t>
         </is>
       </c>
       <c r="E491" t="inlineStr"/>
       <c r="F491" t="inlineStr">
         <is>
-          <t>2.3%</t>
+          <t>3.7%</t>
         </is>
       </c>
       <c r="G491" t="n">
@@ -14895,31 +14891,31 @@
       </c>
       <c r="B492" t="inlineStr">
         <is>
-          <t>Retail Sales Control Group MoMJAN</t>
+          <t>Retail Sales MoMJAN</t>
         </is>
       </c>
       <c r="C492" t="inlineStr">
         <is>
-          <t>-0.8%</t>
+          <t>-0.9%</t>
         </is>
       </c>
       <c r="D492" t="inlineStr">
         <is>
-          <t>0.8%</t>
+          <t>0.7%</t>
         </is>
       </c>
       <c r="E492" t="inlineStr">
         <is>
-          <t>0.3%</t>
+          <t>-0.1%</t>
         </is>
       </c>
       <c r="F492" t="inlineStr">
         <is>
-          <t>0.4%</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="G492" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="493">
@@ -14930,27 +14926,31 @@
       </c>
       <c r="B493" t="inlineStr">
         <is>
-          <t>Retail Sales Ex Gas/Autos MoMJAN</t>
+          <t>Retail Sales Ex Autos MoMJAN</t>
         </is>
       </c>
       <c r="C493" t="inlineStr">
         <is>
-          <t>-0.5%</t>
+          <t>-0.4%</t>
         </is>
       </c>
       <c r="D493" t="inlineStr">
         <is>
-          <t>0.5%</t>
-        </is>
-      </c>
-      <c r="E493" t="inlineStr"/>
+          <t>0.7%</t>
+        </is>
+      </c>
+      <c r="E493" t="inlineStr">
+        <is>
+          <t>0.3%</t>
+        </is>
+      </c>
       <c r="F493" t="inlineStr">
         <is>
-          <t>0.2%</t>
+          <t>0.3%</t>
         </is>
       </c>
       <c r="G493" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="494">
@@ -14961,23 +14961,23 @@
       </c>
       <c r="B494" t="inlineStr">
         <is>
-          <t>Retail Sales YoYJAN</t>
+          <t>Import Prices YoYJAN</t>
         </is>
       </c>
       <c r="C494" t="inlineStr">
         <is>
-          <t>4.2%</t>
+          <t>1.9%</t>
         </is>
       </c>
       <c r="D494" t="inlineStr">
         <is>
-          <t>4.4%</t>
+          <t>2.2%</t>
         </is>
       </c>
       <c r="E494" t="inlineStr"/>
       <c r="F494" t="inlineStr">
         <is>
-          <t>3.7%</t>
+          <t>2.8%</t>
         </is>
       </c>
       <c r="G494" t="n">
@@ -14992,22 +14992,22 @@
       </c>
       <c r="B495" t="inlineStr">
         <is>
-          <t>Export Prices MoMJAN</t>
+          <t>Import Prices MoMJAN</t>
         </is>
       </c>
       <c r="C495" t="inlineStr">
         <is>
-          <t>1.3%</t>
+          <t>0.3%</t>
         </is>
       </c>
       <c r="D495" t="inlineStr">
         <is>
-          <t>0.5%</t>
+          <t>0.2%</t>
         </is>
       </c>
       <c r="E495" t="inlineStr">
         <is>
-          <t>0.3%</t>
+          <t>0.4%</t>
         </is>
       </c>
       <c r="F495" t="inlineStr">
@@ -15714,23 +15714,23 @@
       </c>
       <c r="B521" t="inlineStr">
         <is>
-          <t>MBA Purchase IndexFEB/14</t>
+          <t>MBA 30-Year Mortgage RateFEB/14</t>
         </is>
       </c>
       <c r="C521" t="inlineStr">
         <is>
-          <t>144.0</t>
+          <t>6.93%</t>
         </is>
       </c>
       <c r="D521" t="inlineStr">
         <is>
-          <t>153.1</t>
+          <t>6.95%</t>
         </is>
       </c>
       <c r="E521" t="inlineStr"/>
       <c r="F521" t="inlineStr"/>
       <c r="G521" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="522">
@@ -15741,17 +15741,17 @@
       </c>
       <c r="B522" t="inlineStr">
         <is>
-          <t>MBA Mortgage Refinance IndexFEB/14</t>
+          <t>MBA Mortgage ApplicationsFEB/14</t>
         </is>
       </c>
       <c r="C522" t="inlineStr">
         <is>
-          <t>593.6</t>
+          <t>-6.6%</t>
         </is>
       </c>
       <c r="D522" t="inlineStr">
         <is>
-          <t>640.6</t>
+          <t>2.3%</t>
         </is>
       </c>
       <c r="E522" t="inlineStr"/>
@@ -15795,17 +15795,17 @@
       </c>
       <c r="B524" t="inlineStr">
         <is>
-          <t>MBA Mortgage ApplicationsFEB/14</t>
+          <t>MBA Purchase IndexFEB/14</t>
         </is>
       </c>
       <c r="C524" t="inlineStr">
         <is>
-          <t>-6.6%</t>
+          <t>144.0</t>
         </is>
       </c>
       <c r="D524" t="inlineStr">
         <is>
-          <t>2.3%</t>
+          <t>153.1</t>
         </is>
       </c>
       <c r="E524" t="inlineStr"/>
@@ -15822,23 +15822,23 @@
       </c>
       <c r="B525" t="inlineStr">
         <is>
-          <t>MBA 30-Year Mortgage RateFEB/14</t>
+          <t>MBA Mortgage Refinance IndexFEB/14</t>
         </is>
       </c>
       <c r="C525" t="inlineStr">
         <is>
-          <t>6.93%</t>
+          <t>593.6</t>
         </is>
       </c>
       <c r="D525" t="inlineStr">
         <is>
-          <t>6.95%</t>
+          <t>640.6</t>
         </is>
       </c>
       <c r="E525" t="inlineStr"/>
       <c r="F525" t="inlineStr"/>
       <c r="G525" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="526">
@@ -16510,17 +16510,17 @@
       </c>
       <c r="B549" t="inlineStr">
         <is>
-          <t>8-Week Bill Auction</t>
+          <t>4-Week Bill Auction</t>
         </is>
       </c>
       <c r="C549" t="inlineStr">
         <is>
-          <t>4.235%</t>
+          <t>4.245%</t>
         </is>
       </c>
       <c r="D549" t="inlineStr">
         <is>
-          <t>4.240%</t>
+          <t>4.250%</t>
         </is>
       </c>
       <c r="E549" t="inlineStr"/>
@@ -16537,17 +16537,17 @@
       </c>
       <c r="B550" t="inlineStr">
         <is>
-          <t>4-Week Bill Auction</t>
+          <t>8-Week Bill Auction</t>
         </is>
       </c>
       <c r="C550" t="inlineStr">
         <is>
-          <t>4.245%</t>
+          <t>4.235%</t>
         </is>
       </c>
       <c r="D550" t="inlineStr">
         <is>
-          <t>4.250%</t>
+          <t>4.240%</t>
         </is>
       </c>
       <c r="E550" t="inlineStr"/>
@@ -17326,7 +17326,7 @@
       </c>
       <c r="B577" t="inlineStr">
         <is>
-          <t>Fed Daly Speech</t>
+          <t>Fed Jefferson Speech</t>
         </is>
       </c>
       <c r="C577" t="inlineStr"/>
@@ -17345,7 +17345,7 @@
       </c>
       <c r="B578" t="inlineStr">
         <is>
-          <t>Fed Jefferson Speech</t>
+          <t>Fed Daly Speech</t>
         </is>
       </c>
       <c r="C578" t="inlineStr"/>
@@ -17630,23 +17630,19 @@
       </c>
       <c r="B589" t="inlineStr">
         <is>
-          <t>S&amp;P/Case-Shiller Home Price MoMDEC</t>
-        </is>
-      </c>
-      <c r="C589" t="inlineStr">
-        <is>
-          <t>-0.1%</t>
-        </is>
-      </c>
+          <t>House Price Index YoYDEC</t>
+        </is>
+      </c>
+      <c r="C589" t="inlineStr"/>
       <c r="D589" t="inlineStr">
         <is>
-          <t>-0.1%</t>
+          <t>4.2%</t>
         </is>
       </c>
       <c r="E589" t="inlineStr"/>
       <c r="F589" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>4.1%</t>
         </is>
       </c>
       <c r="G589" t="n">
@@ -17661,23 +17657,19 @@
       </c>
       <c r="B590" t="inlineStr">
         <is>
-          <t>House Price Index MoMDEC</t>
+          <t>House Price IndexDEC</t>
         </is>
       </c>
       <c r="C590" t="inlineStr"/>
       <c r="D590" t="inlineStr">
         <is>
-          <t>0.3%</t>
-        </is>
-      </c>
-      <c r="E590" t="inlineStr">
-        <is>
-          <t>0.2%</t>
-        </is>
-      </c>
+          <t>433.4</t>
+        </is>
+      </c>
+      <c r="E590" t="inlineStr"/>
       <c r="F590" t="inlineStr">
         <is>
-          <t>0.2%</t>
+          <t>434.3</t>
         </is>
       </c>
       <c r="G590" t="n">
@@ -17692,27 +17684,27 @@
       </c>
       <c r="B591" t="inlineStr">
         <is>
-          <t>House Price IndexDEC</t>
-        </is>
-      </c>
-      <c r="C591" t="inlineStr">
-        <is>
-          <t>436.1</t>
-        </is>
-      </c>
+          <t>S&amp;P/Case-Shiller Home Price YoYDEC</t>
+        </is>
+      </c>
+      <c r="C591" t="inlineStr"/>
       <c r="D591" t="inlineStr">
         <is>
-          <t>434.3</t>
-        </is>
-      </c>
-      <c r="E591" t="inlineStr"/>
+          <t>4.3%</t>
+        </is>
+      </c>
+      <c r="E591" t="inlineStr">
+        <is>
+          <t>4.4%</t>
+        </is>
+      </c>
       <c r="F591" t="inlineStr">
         <is>
-          <t>434.3</t>
+          <t>4.4%</t>
         </is>
       </c>
       <c r="G591" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="592">
@@ -17723,27 +17715,19 @@
       </c>
       <c r="B592" t="inlineStr">
         <is>
-          <t>House Price Index MoMDEC</t>
-        </is>
-      </c>
-      <c r="C592" t="inlineStr">
-        <is>
-          <t>0.4%</t>
-        </is>
-      </c>
+          <t>S&amp;P/Case-Shiller Home Price MoMDEC</t>
+        </is>
+      </c>
+      <c r="C592" t="inlineStr"/>
       <c r="D592" t="inlineStr">
         <is>
-          <t>0.4%</t>
-        </is>
-      </c>
-      <c r="E592" t="inlineStr">
-        <is>
-          <t>0.2%</t>
-        </is>
-      </c>
+          <t>-0.1%</t>
+        </is>
+      </c>
+      <c r="E592" t="inlineStr"/>
       <c r="F592" t="inlineStr">
         <is>
-          <t>0.2%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="G592" t="n">
@@ -17758,27 +17742,31 @@
       </c>
       <c r="B593" t="inlineStr">
         <is>
-          <t>House Price Index YoYDEC</t>
+          <t>S&amp;P/Case-Shiller Home Price YoYDEC</t>
         </is>
       </c>
       <c r="C593" t="inlineStr">
         <is>
-          <t>4.7%</t>
+          <t>4.5%</t>
         </is>
       </c>
       <c r="D593" t="inlineStr">
         <is>
-          <t>4.5%</t>
-        </is>
-      </c>
-      <c r="E593" t="inlineStr"/>
+          <t>4.3%</t>
+        </is>
+      </c>
+      <c r="E593" t="inlineStr">
+        <is>
+          <t>4.4%</t>
+        </is>
+      </c>
       <c r="F593" t="inlineStr">
         <is>
-          <t>4.1%</t>
+          <t>4.4%</t>
         </is>
       </c>
       <c r="G593" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="594">
@@ -17789,19 +17777,27 @@
       </c>
       <c r="B594" t="inlineStr">
         <is>
-          <t>S&amp;P/Case-Shiller Home Price MoMDEC</t>
-        </is>
-      </c>
-      <c r="C594" t="inlineStr"/>
+          <t>House Price Index MoMDEC</t>
+        </is>
+      </c>
+      <c r="C594" t="inlineStr">
+        <is>
+          <t>0.4%</t>
+        </is>
+      </c>
       <c r="D594" t="inlineStr">
         <is>
-          <t>-0.1%</t>
-        </is>
-      </c>
-      <c r="E594" t="inlineStr"/>
+          <t>0.4%</t>
+        </is>
+      </c>
+      <c r="E594" t="inlineStr">
+        <is>
+          <t>0.2%</t>
+        </is>
+      </c>
       <c r="F594" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>0.2%</t>
         </is>
       </c>
       <c r="G594" t="n">
@@ -17816,31 +17812,27 @@
       </c>
       <c r="B595" t="inlineStr">
         <is>
-          <t>S&amp;P/Case-Shiller Home Price YoYDEC</t>
+          <t>House Price IndexDEC</t>
         </is>
       </c>
       <c r="C595" t="inlineStr">
         <is>
-          <t>4.5%</t>
+          <t>436.1</t>
         </is>
       </c>
       <c r="D595" t="inlineStr">
         <is>
-          <t>4.3%</t>
-        </is>
-      </c>
-      <c r="E595" t="inlineStr">
-        <is>
-          <t>4.4%</t>
-        </is>
-      </c>
+          <t>434.3</t>
+        </is>
+      </c>
+      <c r="E595" t="inlineStr"/>
       <c r="F595" t="inlineStr">
         <is>
-          <t>4.4%</t>
+          <t>434.3</t>
         </is>
       </c>
       <c r="G595" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="596">
@@ -17851,27 +17843,27 @@
       </c>
       <c r="B596" t="inlineStr">
         <is>
-          <t>S&amp;P/Case-Shiller Home Price YoYDEC</t>
+          <t>House Price Index MoMDEC</t>
         </is>
       </c>
       <c r="C596" t="inlineStr"/>
       <c r="D596" t="inlineStr">
         <is>
-          <t>4.3%</t>
+          <t>0.3%</t>
         </is>
       </c>
       <c r="E596" t="inlineStr">
         <is>
-          <t>4.4%</t>
+          <t>0.2%</t>
         </is>
       </c>
       <c r="F596" t="inlineStr">
         <is>
-          <t>4.4%</t>
+          <t>0.2%</t>
         </is>
       </c>
       <c r="G596" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="597">
@@ -17882,19 +17874,23 @@
       </c>
       <c r="B597" t="inlineStr">
         <is>
-          <t>House Price IndexDEC</t>
-        </is>
-      </c>
-      <c r="C597" t="inlineStr"/>
+          <t>S&amp;P/Case-Shiller Home Price MoMDEC</t>
+        </is>
+      </c>
+      <c r="C597" t="inlineStr">
+        <is>
+          <t>-0.1%</t>
+        </is>
+      </c>
       <c r="D597" t="inlineStr">
         <is>
-          <t>433.4</t>
+          <t>-0.1%</t>
         </is>
       </c>
       <c r="E597" t="inlineStr"/>
       <c r="F597" t="inlineStr">
         <is>
-          <t>434.3</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="G597" t="n">
@@ -17912,10 +17908,14 @@
           <t>House Price Index YoYDEC</t>
         </is>
       </c>
-      <c r="C598" t="inlineStr"/>
+      <c r="C598" t="inlineStr">
+        <is>
+          <t>4.7%</t>
+        </is>
+      </c>
       <c r="D598" t="inlineStr">
         <is>
-          <t>4.2%</t>
+          <t>4.5%</t>
         </is>
       </c>
       <c r="E598" t="inlineStr"/>
@@ -17936,19 +17936,23 @@
       </c>
       <c r="B599" t="inlineStr">
         <is>
-          <t>Richmond Fed Manufacturing Shipments IndexFEB</t>
-        </is>
-      </c>
-      <c r="C599" t="inlineStr"/>
+          <t>Richmond Fed Services Revenues IndexFEB</t>
+        </is>
+      </c>
+      <c r="C599" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
       <c r="D599" t="inlineStr">
         <is>
-          <t>-9</t>
+          <t>4</t>
         </is>
       </c>
       <c r="E599" t="inlineStr"/>
       <c r="F599" t="inlineStr">
         <is>
-          <t>-4</t>
+          <t>7</t>
         </is>
       </c>
       <c r="G599" t="n">
@@ -17966,7 +17970,11 @@
           <t>Richmond Fed Manufacturing IndexFEB</t>
         </is>
       </c>
-      <c r="C600" t="inlineStr"/>
+      <c r="C600" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
       <c r="D600" t="inlineStr">
         <is>
           <t>-4</t>
@@ -17994,23 +18002,31 @@
       </c>
       <c r="B601" t="inlineStr">
         <is>
-          <t>Richmond Fed Services Revenues IndexFEB</t>
-        </is>
-      </c>
-      <c r="C601" t="inlineStr"/>
+          <t>CB Consumer ConfidenceFEB</t>
+        </is>
+      </c>
+      <c r="C601" t="inlineStr">
+        <is>
+          <t>98.3</t>
+        </is>
+      </c>
       <c r="D601" t="inlineStr">
         <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="E601" t="inlineStr"/>
+          <t>105.3</t>
+        </is>
+      </c>
+      <c r="E601" t="inlineStr">
+        <is>
+          <t>102.5</t>
+        </is>
+      </c>
       <c r="F601" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>103</t>
         </is>
       </c>
       <c r="G601" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="602">
@@ -18021,27 +18037,27 @@
       </c>
       <c r="B602" t="inlineStr">
         <is>
-          <t>CB Consumer ConfidenceFEB</t>
-        </is>
-      </c>
-      <c r="C602" t="inlineStr"/>
+          <t>Richmond Fed Manufacturing Shipments IndexFEB</t>
+        </is>
+      </c>
+      <c r="C602" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
       <c r="D602" t="inlineStr">
         <is>
-          <t>104.1</t>
-        </is>
-      </c>
-      <c r="E602" t="inlineStr">
-        <is>
-          <t>103</t>
-        </is>
-      </c>
+          <t>-9</t>
+        </is>
+      </c>
+      <c r="E602" t="inlineStr"/>
       <c r="F602" t="inlineStr">
         <is>
-          <t>103</t>
+          <t>-4</t>
         </is>
       </c>
       <c r="G602" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="603">
@@ -18052,31 +18068,23 @@
       </c>
       <c r="B603" t="inlineStr">
         <is>
-          <t>CB Consumer ConfidenceFEB</t>
-        </is>
-      </c>
-      <c r="C603" t="inlineStr">
-        <is>
-          <t>98.3</t>
-        </is>
-      </c>
+          <t>Richmond Fed Services Revenues IndexFEB</t>
+        </is>
+      </c>
+      <c r="C603" t="inlineStr"/>
       <c r="D603" t="inlineStr">
         <is>
-          <t>105.3</t>
-        </is>
-      </c>
-      <c r="E603" t="inlineStr">
-        <is>
-          <t>102.5</t>
-        </is>
-      </c>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="E603" t="inlineStr"/>
       <c r="F603" t="inlineStr">
         <is>
-          <t>103</t>
+          <t>7</t>
         </is>
       </c>
       <c r="G603" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="604">
@@ -18090,11 +18098,7 @@
           <t>Richmond Fed Manufacturing IndexFEB</t>
         </is>
       </c>
-      <c r="C604" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
+      <c r="C604" t="inlineStr"/>
       <c r="D604" t="inlineStr">
         <is>
           <t>-4</t>
@@ -18125,11 +18129,7 @@
           <t>Richmond Fed Manufacturing Shipments IndexFEB</t>
         </is>
       </c>
-      <c r="C605" t="inlineStr">
-        <is>
-          <t>12</t>
-        </is>
-      </c>
+      <c r="C605" t="inlineStr"/>
       <c r="D605" t="inlineStr">
         <is>
           <t>-9</t>
@@ -18153,27 +18153,27 @@
       </c>
       <c r="B606" t="inlineStr">
         <is>
-          <t>Richmond Fed Services Revenues IndexFEB</t>
-        </is>
-      </c>
-      <c r="C606" t="inlineStr">
-        <is>
-          <t>11</t>
-        </is>
-      </c>
+          <t>CB Consumer ConfidenceFEB</t>
+        </is>
+      </c>
+      <c r="C606" t="inlineStr"/>
       <c r="D606" t="inlineStr">
         <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="E606" t="inlineStr"/>
+          <t>104.1</t>
+        </is>
+      </c>
+      <c r="E606" t="inlineStr">
+        <is>
+          <t>103</t>
+        </is>
+      </c>
       <c r="F606" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>103</t>
         </is>
       </c>
       <c r="G606" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="607">
@@ -18319,23 +18319,15 @@
       </c>
       <c r="B612" t="inlineStr">
         <is>
-          <t>Money SupplyJAN</t>
-        </is>
-      </c>
-      <c r="C612" t="inlineStr">
-        <is>
-          <t>$21.56T</t>
-        </is>
-      </c>
-      <c r="D612" t="inlineStr">
-        <is>
-          <t>$21.53T</t>
-        </is>
-      </c>
+          <t>Fed Barkin Speech</t>
+        </is>
+      </c>
+      <c r="C612" t="inlineStr"/>
+      <c r="D612" t="inlineStr"/>
       <c r="E612" t="inlineStr"/>
       <c r="F612" t="inlineStr"/>
       <c r="G612" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="613">
@@ -18349,7 +18341,11 @@
           <t>Money SupplyJAN</t>
         </is>
       </c>
-      <c r="C613" t="inlineStr"/>
+      <c r="C613" t="inlineStr">
+        <is>
+          <t>$21.56T</t>
+        </is>
+      </c>
       <c r="D613" t="inlineStr">
         <is>
           <t>$21.53T</t>
@@ -18369,13 +18365,13 @@
       </c>
       <c r="B614" t="inlineStr">
         <is>
-          <t>5-Year Note Auction</t>
+          <t>Money SupplyJAN</t>
         </is>
       </c>
       <c r="C614" t="inlineStr"/>
       <c r="D614" t="inlineStr">
         <is>
-          <t>4.33%</t>
+          <t>$21.53T</t>
         </is>
       </c>
       <c r="E614" t="inlineStr"/>
@@ -18392,15 +18388,19 @@
       </c>
       <c r="B615" t="inlineStr">
         <is>
-          <t>Fed Barkin Speech</t>
+          <t>5-Year Note Auction</t>
         </is>
       </c>
       <c r="C615" t="inlineStr"/>
-      <c r="D615" t="inlineStr"/>
+      <c r="D615" t="inlineStr">
+        <is>
+          <t>4.33%</t>
+        </is>
+      </c>
       <c r="E615" t="inlineStr"/>
       <c r="F615" t="inlineStr"/>
       <c r="G615" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="616">
@@ -18654,13 +18654,13 @@
       </c>
       <c r="B625" t="inlineStr">
         <is>
-          <t>MBA Mortgage Refinance IndexFEB/21</t>
+          <t>MBA Mortgage ApplicationsFEB/21</t>
         </is>
       </c>
       <c r="C625" t="inlineStr"/>
       <c r="D625" t="inlineStr">
         <is>
-          <t>593.6</t>
+          <t>-6.6%</t>
         </is>
       </c>
       <c r="E625" t="inlineStr"/>
@@ -18677,19 +18677,19 @@
       </c>
       <c r="B626" t="inlineStr">
         <is>
-          <t>MBA Purchase IndexFEB/21</t>
+          <t>MBA 30-Year Mortgage RateFEB/21</t>
         </is>
       </c>
       <c r="C626" t="inlineStr"/>
       <c r="D626" t="inlineStr">
         <is>
-          <t>144.0</t>
+          <t>6.93%</t>
         </is>
       </c>
       <c r="E626" t="inlineStr"/>
       <c r="F626" t="inlineStr"/>
       <c r="G626" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="627">
@@ -18700,19 +18700,19 @@
       </c>
       <c r="B627" t="inlineStr">
         <is>
-          <t>MBA 30-Year Mortgage RateFEB/21</t>
+          <t>MBA Purchase IndexFEB/21</t>
         </is>
       </c>
       <c r="C627" t="inlineStr"/>
       <c r="D627" t="inlineStr">
         <is>
-          <t>6.93%</t>
+          <t>144.0</t>
         </is>
       </c>
       <c r="E627" t="inlineStr"/>
       <c r="F627" t="inlineStr"/>
       <c r="G627" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="628">
@@ -18723,13 +18723,13 @@
       </c>
       <c r="B628" t="inlineStr">
         <is>
-          <t>MBA Mortgage ApplicationsFEB/21</t>
+          <t>MBA Mortgage Refinance IndexFEB/21</t>
         </is>
       </c>
       <c r="C628" t="inlineStr"/>
       <c r="D628" t="inlineStr">
         <is>
-          <t>-6.6%</t>
+          <t>593.6</t>
         </is>
       </c>
       <c r="E628" t="inlineStr"/>
@@ -19048,13 +19048,13 @@
       </c>
       <c r="B639" t="inlineStr">
         <is>
-          <t>EIA Cushing Crude Oil Stocks ChangeFEB/21</t>
+          <t>EIA Heating Oil Stocks ChangeFEB/21</t>
         </is>
       </c>
       <c r="C639" t="inlineStr"/>
       <c r="D639" t="inlineStr">
         <is>
-          <t>1.472M</t>
+          <t>-0.343M</t>
         </is>
       </c>
       <c r="E639" t="inlineStr"/>
@@ -19071,23 +19071,19 @@
       </c>
       <c r="B640" t="inlineStr">
         <is>
-          <t>EIA Gasoline Stocks ChangeFEB/21</t>
+          <t>EIA Gasoline Production ChangeFEB/21</t>
         </is>
       </c>
       <c r="C640" t="inlineStr"/>
       <c r="D640" t="inlineStr">
         <is>
-          <t>-0.151M</t>
-        </is>
-      </c>
-      <c r="E640" t="inlineStr">
-        <is>
-          <t>-1.30M</t>
-        </is>
-      </c>
+          <t>-0.156M</t>
+        </is>
+      </c>
+      <c r="E640" t="inlineStr"/>
       <c r="F640" t="inlineStr"/>
       <c r="G640" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="641">
@@ -19098,23 +19094,23 @@
       </c>
       <c r="B641" t="inlineStr">
         <is>
-          <t>EIA Crude Oil Stocks ChangeFEB/21</t>
+          <t>EIA Distillate Stocks ChangeFEB/21</t>
         </is>
       </c>
       <c r="C641" t="inlineStr"/>
       <c r="D641" t="inlineStr">
         <is>
-          <t>4.633M</t>
+          <t>-2.051M</t>
         </is>
       </c>
       <c r="E641" t="inlineStr">
         <is>
-          <t>2.34M</t>
+          <t>1.63M</t>
         </is>
       </c>
       <c r="F641" t="inlineStr"/>
       <c r="G641" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="642">
@@ -19148,23 +19144,23 @@
       </c>
       <c r="B643" t="inlineStr">
         <is>
-          <t>EIA Distillate Stocks ChangeFEB/21</t>
+          <t>EIA Crude Oil Stocks ChangeFEB/21</t>
         </is>
       </c>
       <c r="C643" t="inlineStr"/>
       <c r="D643" t="inlineStr">
         <is>
-          <t>-2.051M</t>
+          <t>4.633M</t>
         </is>
       </c>
       <c r="E643" t="inlineStr">
         <is>
-          <t>1.63M</t>
+          <t>2.34M</t>
         </is>
       </c>
       <c r="F643" t="inlineStr"/>
       <c r="G643" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="644">
@@ -19175,19 +19171,23 @@
       </c>
       <c r="B644" t="inlineStr">
         <is>
-          <t>EIA Gasoline Production ChangeFEB/21</t>
+          <t>EIA Gasoline Stocks ChangeFEB/21</t>
         </is>
       </c>
       <c r="C644" t="inlineStr"/>
       <c r="D644" t="inlineStr">
         <is>
-          <t>-0.156M</t>
-        </is>
-      </c>
-      <c r="E644" t="inlineStr"/>
+          <t>-0.151M</t>
+        </is>
+      </c>
+      <c r="E644" t="inlineStr">
+        <is>
+          <t>-1.30M</t>
+        </is>
+      </c>
       <c r="F644" t="inlineStr"/>
       <c r="G644" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="645">
@@ -19198,13 +19198,13 @@
       </c>
       <c r="B645" t="inlineStr">
         <is>
-          <t>EIA Heating Oil Stocks ChangeFEB/21</t>
+          <t>EIA Cushing Crude Oil Stocks ChangeFEB/21</t>
         </is>
       </c>
       <c r="C645" t="inlineStr"/>
       <c r="D645" t="inlineStr">
         <is>
-          <t>-0.343M</t>
+          <t>1.472M</t>
         </is>
       </c>
       <c r="E645" t="inlineStr"/>
@@ -19221,13 +19221,13 @@
       </c>
       <c r="B646" t="inlineStr">
         <is>
-          <t>EIA Refinery Crude Runs ChangeFEB/21</t>
+          <t>EIA Crude Oil Imports ChangeFEB/21</t>
         </is>
       </c>
       <c r="C646" t="inlineStr"/>
       <c r="D646" t="inlineStr">
         <is>
-          <t>-0.015M</t>
+          <t>-0.961M</t>
         </is>
       </c>
       <c r="E646" t="inlineStr"/>
@@ -19499,13 +19499,13 @@
       </c>
       <c r="B656" t="inlineStr">
         <is>
-          <t>EIA Crude Oil Imports ChangeFEB/21</t>
+          <t>EIA Refinery Crude Runs ChangeFEB/21</t>
         </is>
       </c>
       <c r="C656" t="inlineStr"/>
       <c r="D656" t="inlineStr">
         <is>
-          <t>-0.961M</t>
+          <t>-0.015M</t>
         </is>
       </c>
       <c r="E656" t="inlineStr"/>
@@ -19772,27 +19772,27 @@
       </c>
       <c r="B667" t="inlineStr">
         <is>
-          <t>GDP Price Index QoQ 2nd EstQ4</t>
+          <t>GDP Growth Rate QoQ 2nd EstQ4</t>
         </is>
       </c>
       <c r="C667" t="inlineStr"/>
       <c r="D667" t="inlineStr">
         <is>
-          <t>1.9%</t>
+          <t>3.1%</t>
         </is>
       </c>
       <c r="E667" t="inlineStr">
         <is>
-          <t>2.2%</t>
+          <t>2.3%</t>
         </is>
       </c>
       <c r="F667" t="inlineStr">
         <is>
-          <t>2.2%</t>
+          <t>2.3%</t>
         </is>
       </c>
       <c r="G667" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="668">
@@ -20198,23 +20198,19 @@
       </c>
       <c r="B681" t="inlineStr">
         <is>
-          <t>Real Consumer Spending QoQ 2nd EstQ4</t>
+          <t>Continuing Jobless ClaimsFEB/15</t>
         </is>
       </c>
       <c r="C681" t="inlineStr"/>
       <c r="D681" t="inlineStr">
         <is>
-          <t>3.7%</t>
-        </is>
-      </c>
-      <c r="E681" t="inlineStr">
-        <is>
-          <t>4.2%</t>
-        </is>
-      </c>
+          <t>1869K</t>
+        </is>
+      </c>
+      <c r="E681" t="inlineStr"/>
       <c r="F681" t="inlineStr">
         <is>
-          <t>4.2%</t>
+          <t>1874.0K</t>
         </is>
       </c>
       <c r="G681" t="n">
@@ -20229,23 +20225,27 @@
       </c>
       <c r="B682" t="inlineStr">
         <is>
-          <t>Jobless Claims 4-week AverageFEB/22</t>
+          <t>GDP Price Index QoQ 2nd EstQ4</t>
         </is>
       </c>
       <c r="C682" t="inlineStr"/>
       <c r="D682" t="inlineStr">
         <is>
-          <t>215.25K</t>
-        </is>
-      </c>
-      <c r="E682" t="inlineStr"/>
+          <t>1.9%</t>
+        </is>
+      </c>
+      <c r="E682" t="inlineStr">
+        <is>
+          <t>2.2%</t>
+        </is>
+      </c>
       <c r="F682" t="inlineStr">
         <is>
-          <t>220.0K</t>
+          <t>2.2%</t>
         </is>
       </c>
       <c r="G682" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="683">
@@ -20256,27 +20256,27 @@
       </c>
       <c r="B683" t="inlineStr">
         <is>
-          <t>Initial Jobless ClaimsFEB/22</t>
+          <t>Real Consumer Spending QoQ 2nd EstQ4</t>
         </is>
       </c>
       <c r="C683" t="inlineStr"/>
       <c r="D683" t="inlineStr">
         <is>
-          <t>219K</t>
+          <t>3.7%</t>
         </is>
       </c>
       <c r="E683" t="inlineStr">
         <is>
-          <t>221K</t>
+          <t>4.2%</t>
         </is>
       </c>
       <c r="F683" t="inlineStr">
         <is>
-          <t>225.0K</t>
+          <t>4.2%</t>
         </is>
       </c>
       <c r="G683" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="684">
@@ -20287,27 +20287,23 @@
       </c>
       <c r="B684" t="inlineStr">
         <is>
-          <t>Durable Goods Orders MoMJAN</t>
+          <t>Jobless Claims 4-week AverageFEB/22</t>
         </is>
       </c>
       <c r="C684" t="inlineStr"/>
       <c r="D684" t="inlineStr">
         <is>
-          <t>-2.2%</t>
-        </is>
-      </c>
-      <c r="E684" t="inlineStr">
-        <is>
-          <t>2%</t>
-        </is>
-      </c>
+          <t>215.25K</t>
+        </is>
+      </c>
+      <c r="E684" t="inlineStr"/>
       <c r="F684" t="inlineStr">
         <is>
-          <t>2.2%</t>
+          <t>220.0K</t>
         </is>
       </c>
       <c r="G684" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="685">
@@ -20318,13 +20314,13 @@
       </c>
       <c r="B685" t="inlineStr">
         <is>
-          <t>GDP Growth Rate QoQ 2nd EstQ4</t>
+          <t>PCE Prices QoQ 2nd EstQ4</t>
         </is>
       </c>
       <c r="C685" t="inlineStr"/>
       <c r="D685" t="inlineStr">
         <is>
-          <t>3.1%</t>
+          <t>1.5%</t>
         </is>
       </c>
       <c r="E685" t="inlineStr">
@@ -20338,7 +20334,7 @@
         </is>
       </c>
       <c r="G685" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="686">
@@ -20349,27 +20345,27 @@
       </c>
       <c r="B686" t="inlineStr">
         <is>
-          <t>PCE Prices QoQ 2nd EstQ4</t>
+          <t>Durable Goods Orders MoMJAN</t>
         </is>
       </c>
       <c r="C686" t="inlineStr"/>
       <c r="D686" t="inlineStr">
         <is>
-          <t>1.5%</t>
+          <t>-2.2%</t>
         </is>
       </c>
       <c r="E686" t="inlineStr">
         <is>
-          <t>2.3%</t>
+          <t>2%</t>
         </is>
       </c>
       <c r="F686" t="inlineStr">
         <is>
-          <t>2.3%</t>
+          <t>2.2%</t>
         </is>
       </c>
       <c r="G686" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="687">
@@ -20380,23 +20376,27 @@
       </c>
       <c r="B687" t="inlineStr">
         <is>
-          <t>Continuing Jobless ClaimsFEB/15</t>
+          <t>Initial Jobless ClaimsFEB/22</t>
         </is>
       </c>
       <c r="C687" t="inlineStr"/>
       <c r="D687" t="inlineStr">
         <is>
-          <t>1869K</t>
-        </is>
-      </c>
-      <c r="E687" t="inlineStr"/>
+          <t>219K</t>
+        </is>
+      </c>
+      <c r="E687" t="inlineStr">
+        <is>
+          <t>221K</t>
+        </is>
+      </c>
       <c r="F687" t="inlineStr">
         <is>
-          <t>1874.0K</t>
+          <t>225.0K</t>
         </is>
       </c>
       <c r="G687" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="688">
@@ -20407,27 +20407,23 @@
       </c>
       <c r="B688" t="inlineStr">
         <is>
-          <t>Durable Goods Orders Ex Transp MoMJAN</t>
+          <t>Durable Goods Orders ex Defense MoMJAN</t>
         </is>
       </c>
       <c r="C688" t="inlineStr"/>
       <c r="D688" t="inlineStr">
         <is>
-          <t>0.3%</t>
-        </is>
-      </c>
-      <c r="E688" t="inlineStr">
-        <is>
-          <t>0.3%</t>
-        </is>
-      </c>
+          <t>-2.4%</t>
+        </is>
+      </c>
+      <c r="E688" t="inlineStr"/>
       <c r="F688" t="inlineStr">
         <is>
-          <t>0.3%</t>
+          <t>1.4%</t>
         </is>
       </c>
       <c r="G688" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="689">
@@ -20438,23 +20434,23 @@
       </c>
       <c r="B689" t="inlineStr">
         <is>
-          <t>Non Defense Goods Orders Ex AirJAN</t>
+          <t>Core PCE Prices QoQ 2nd EstQ4</t>
         </is>
       </c>
       <c r="C689" t="inlineStr"/>
       <c r="D689" t="inlineStr">
         <is>
-          <t>0.5%</t>
+          <t>2.2%</t>
         </is>
       </c>
       <c r="E689" t="inlineStr">
         <is>
-          <t>0.3%</t>
+          <t>2.5%</t>
         </is>
       </c>
       <c r="F689" t="inlineStr">
         <is>
-          <t>0.4%</t>
+          <t>2.5%</t>
         </is>
       </c>
       <c r="G689" t="n">
@@ -20500,23 +20496,23 @@
       </c>
       <c r="B691" t="inlineStr">
         <is>
-          <t>Core PCE Prices QoQ 2nd EstQ4</t>
+          <t>Non Defense Goods Orders Ex AirJAN</t>
         </is>
       </c>
       <c r="C691" t="inlineStr"/>
       <c r="D691" t="inlineStr">
         <is>
-          <t>2.2%</t>
+          <t>0.5%</t>
         </is>
       </c>
       <c r="E691" t="inlineStr">
         <is>
-          <t>2.5%</t>
+          <t>0.3%</t>
         </is>
       </c>
       <c r="F691" t="inlineStr">
         <is>
-          <t>2.5%</t>
+          <t>0.4%</t>
         </is>
       </c>
       <c r="G691" t="n">
@@ -20531,23 +20527,27 @@
       </c>
       <c r="B692" t="inlineStr">
         <is>
-          <t>Durable Goods Orders ex Defense MoMJAN</t>
+          <t>Durable Goods Orders Ex Transp MoMJAN</t>
         </is>
       </c>
       <c r="C692" t="inlineStr"/>
       <c r="D692" t="inlineStr">
         <is>
-          <t>-2.4%</t>
-        </is>
-      </c>
-      <c r="E692" t="inlineStr"/>
+          <t>0.3%</t>
+        </is>
+      </c>
+      <c r="E692" t="inlineStr">
+        <is>
+          <t>0.3%</t>
+        </is>
+      </c>
       <c r="F692" t="inlineStr">
         <is>
-          <t>1.4%</t>
+          <t>0.3%</t>
         </is>
       </c>
       <c r="G692" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="693">
@@ -20558,25 +20558,13 @@
       </c>
       <c r="B693" t="inlineStr">
         <is>
-          <t>Pending Home Sales MoMJAN</t>
+          <t>Fed Barr Speech</t>
         </is>
       </c>
       <c r="C693" t="inlineStr"/>
-      <c r="D693" t="inlineStr">
-        <is>
-          <t>-5.5%</t>
-        </is>
-      </c>
-      <c r="E693" t="inlineStr">
-        <is>
-          <t>-1.3%</t>
-        </is>
-      </c>
-      <c r="F693" t="inlineStr">
-        <is>
-          <t>-0.9%</t>
-        </is>
-      </c>
+      <c r="D693" t="inlineStr"/>
+      <c r="E693" t="inlineStr"/>
+      <c r="F693" t="inlineStr"/>
       <c r="G693" t="n">
         <v>2</v>
       </c>
@@ -20589,13 +20577,21 @@
       </c>
       <c r="B694" t="inlineStr">
         <is>
-          <t>Fed Barr Speech</t>
+          <t>Pending Home Sales YoYJAN</t>
         </is>
       </c>
       <c r="C694" t="inlineStr"/>
-      <c r="D694" t="inlineStr"/>
+      <c r="D694" t="inlineStr">
+        <is>
+          <t>-5.0%</t>
+        </is>
+      </c>
       <c r="E694" t="inlineStr"/>
-      <c r="F694" t="inlineStr"/>
+      <c r="F694" t="inlineStr">
+        <is>
+          <t>6.0%</t>
+        </is>
+      </c>
       <c r="G694" t="n">
         <v>2</v>
       </c>
@@ -20685,19 +20681,23 @@
       </c>
       <c r="B698" t="inlineStr">
         <is>
-          <t>Pending Home Sales YoYJAN</t>
+          <t>Pending Home Sales MoMJAN</t>
         </is>
       </c>
       <c r="C698" t="inlineStr"/>
       <c r="D698" t="inlineStr">
         <is>
-          <t>-5.0%</t>
-        </is>
-      </c>
-      <c r="E698" t="inlineStr"/>
+          <t>-5.5%</t>
+        </is>
+      </c>
+      <c r="E698" t="inlineStr">
+        <is>
+          <t>-1.3%</t>
+        </is>
+      </c>
       <c r="F698" t="inlineStr">
         <is>
-          <t>6.0%</t>
+          <t>-0.9%</t>
         </is>
       </c>
       <c r="G698" t="n">
@@ -20920,13 +20920,13 @@
       </c>
       <c r="B707" t="inlineStr">
         <is>
-          <t>8-Week Bill Auction</t>
+          <t>4-Week Bill Auction</t>
         </is>
       </c>
       <c r="C707" t="inlineStr"/>
       <c r="D707" t="inlineStr">
         <is>
-          <t>4.235%</t>
+          <t>4.245%</t>
         </is>
       </c>
       <c r="E707" t="inlineStr"/>
@@ -20989,13 +20989,13 @@
       </c>
       <c r="B710" t="inlineStr">
         <is>
-          <t>4-Week Bill Auction</t>
+          <t>8-Week Bill Auction</t>
         </is>
       </c>
       <c r="C710" t="inlineStr"/>
       <c r="D710" t="inlineStr">
         <is>
-          <t>4.245%</t>
+          <t>4.235%</t>
         </is>
       </c>
       <c r="E710" t="inlineStr"/>
@@ -21577,27 +21577,27 @@
       </c>
       <c r="B734" t="inlineStr">
         <is>
-          <t>Goods Trade Balance AdvJAN</t>
+          <t>Personal Spending MoMJAN</t>
         </is>
       </c>
       <c r="C734" t="inlineStr"/>
       <c r="D734" t="inlineStr">
         <is>
-          <t>$-122.11B</t>
+          <t>0.7%</t>
         </is>
       </c>
       <c r="E734" t="inlineStr">
         <is>
-          <t>$-114.7B</t>
+          <t>0.1%</t>
         </is>
       </c>
       <c r="F734" t="inlineStr">
         <is>
-          <t>$ -116.0B</t>
+          <t>0.3%</t>
         </is>
       </c>
       <c r="G734" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="735">
@@ -21608,27 +21608,23 @@
       </c>
       <c r="B735" t="inlineStr">
         <is>
-          <t>Core PCE Price Index MoMJAN</t>
+          <t>Retail Inventories Ex Autos MoM AdvJAN</t>
         </is>
       </c>
       <c r="C735" t="inlineStr"/>
       <c r="D735" t="inlineStr">
         <is>
-          <t>0.2%</t>
-        </is>
-      </c>
-      <c r="E735" t="inlineStr">
-        <is>
-          <t>0.3%</t>
-        </is>
-      </c>
+          <t>-0.1%</t>
+        </is>
+      </c>
+      <c r="E735" t="inlineStr"/>
       <c r="F735" t="inlineStr">
         <is>
-          <t>0.4%</t>
+          <t>0.1%</t>
         </is>
       </c>
       <c r="G735" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="736">
@@ -21639,27 +21635,27 @@
       </c>
       <c r="B736" t="inlineStr">
         <is>
-          <t>Personal Income MoMJAN</t>
+          <t>Wholesale Inventories MoM AdvJAN</t>
         </is>
       </c>
       <c r="C736" t="inlineStr"/>
       <c r="D736" t="inlineStr">
         <is>
-          <t>0.4%</t>
+          <t>-0.5%</t>
         </is>
       </c>
       <c r="E736" t="inlineStr">
         <is>
-          <t>0.3%</t>
+          <t>0.1%</t>
         </is>
       </c>
       <c r="F736" t="inlineStr">
         <is>
-          <t>0.3%</t>
+          <t>0.2%</t>
         </is>
       </c>
       <c r="G736" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="737">
@@ -21670,23 +21666,23 @@
       </c>
       <c r="B737" t="inlineStr">
         <is>
-          <t>Wholesale Inventories MoM AdvJAN</t>
+          <t>PCE Price Index YoYJAN</t>
         </is>
       </c>
       <c r="C737" t="inlineStr"/>
       <c r="D737" t="inlineStr">
         <is>
-          <t>-0.5%</t>
+          <t>2.6%</t>
         </is>
       </c>
       <c r="E737" t="inlineStr">
         <is>
-          <t>0.1%</t>
+          <t>2.5%</t>
         </is>
       </c>
       <c r="F737" t="inlineStr">
         <is>
-          <t>0.2%</t>
+          <t>2.5%</t>
         </is>
       </c>
       <c r="G737" t="n">
@@ -21701,23 +21697,27 @@
       </c>
       <c r="B738" t="inlineStr">
         <is>
-          <t>Retail Inventories Ex Autos MoM AdvJAN</t>
+          <t>Core PCE Price Index YoYJAN</t>
         </is>
       </c>
       <c r="C738" t="inlineStr"/>
       <c r="D738" t="inlineStr">
         <is>
-          <t>-0.1%</t>
-        </is>
-      </c>
-      <c r="E738" t="inlineStr"/>
+          <t>2.8%</t>
+        </is>
+      </c>
+      <c r="E738" t="inlineStr">
+        <is>
+          <t>2.6%</t>
+        </is>
+      </c>
       <c r="F738" t="inlineStr">
         <is>
-          <t>0.1%</t>
+          <t>2.7%</t>
         </is>
       </c>
       <c r="G738" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="739">
@@ -21759,18 +21759,18 @@
       </c>
       <c r="B740" t="inlineStr">
         <is>
-          <t>Personal Spending MoMJAN</t>
+          <t>Personal Income MoMJAN</t>
         </is>
       </c>
       <c r="C740" t="inlineStr"/>
       <c r="D740" t="inlineStr">
         <is>
-          <t>0.7%</t>
+          <t>0.4%</t>
         </is>
       </c>
       <c r="E740" t="inlineStr">
         <is>
-          <t>0.1%</t>
+          <t>0.3%</t>
         </is>
       </c>
       <c r="F740" t="inlineStr">
@@ -21790,27 +21790,27 @@
       </c>
       <c r="B741" t="inlineStr">
         <is>
-          <t>Core PCE Price Index YoYJAN</t>
+          <t>Goods Trade Balance AdvJAN</t>
         </is>
       </c>
       <c r="C741" t="inlineStr"/>
       <c r="D741" t="inlineStr">
         <is>
-          <t>2.8%</t>
+          <t>$-122.11B</t>
         </is>
       </c>
       <c r="E741" t="inlineStr">
         <is>
-          <t>2.6%</t>
+          <t>$-114.7B</t>
         </is>
       </c>
       <c r="F741" t="inlineStr">
         <is>
-          <t>2.7%</t>
+          <t>$ -116.0B</t>
         </is>
       </c>
       <c r="G741" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="742">
@@ -21821,27 +21821,27 @@
       </c>
       <c r="B742" t="inlineStr">
         <is>
-          <t>PCE Price Index YoYJAN</t>
+          <t>Core PCE Price Index MoMJAN</t>
         </is>
       </c>
       <c r="C742" t="inlineStr"/>
       <c r="D742" t="inlineStr">
         <is>
-          <t>2.6%</t>
+          <t>0.2%</t>
         </is>
       </c>
       <c r="E742" t="inlineStr">
         <is>
-          <t>2.5%</t>
+          <t>0.3%</t>
         </is>
       </c>
       <c r="F742" t="inlineStr">
         <is>
-          <t>2.5%</t>
+          <t>0.4%</t>
         </is>
       </c>
       <c r="G742" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="743">
@@ -21914,13 +21914,13 @@
       </c>
       <c r="B745" t="inlineStr">
         <is>
-          <t>Baker Hughes Total Rigs CountFEB/28</t>
+          <t>Baker Hughes Oil Rig CountFEB/28</t>
         </is>
       </c>
       <c r="C745" t="inlineStr"/>
       <c r="D745" t="inlineStr">
         <is>
-          <t>592</t>
+          <t>487</t>
         </is>
       </c>
       <c r="E745" t="inlineStr"/>
@@ -21983,13 +21983,13 @@
       </c>
       <c r="B748" t="inlineStr">
         <is>
-          <t>Baker Hughes Oil Rig CountFEB/28</t>
+          <t>Baker Hughes Total Rigs CountFEB/28</t>
         </is>
       </c>
       <c r="C748" t="inlineStr"/>
       <c r="D748" t="inlineStr">
         <is>
-          <t>487</t>
+          <t>592</t>
         </is>
       </c>
       <c r="E748" t="inlineStr"/>
@@ -22095,19 +22095,19 @@
       </c>
       <c r="B752" t="inlineStr">
         <is>
-          <t>ISM Manufacturing PricesFEB</t>
+          <t>ISM Manufacturing New OrdersFEB</t>
         </is>
       </c>
       <c r="C752" t="inlineStr"/>
       <c r="D752" t="inlineStr">
         <is>
-          <t>54.9</t>
+          <t>55.1</t>
         </is>
       </c>
       <c r="E752" t="inlineStr"/>
       <c r="F752" t="inlineStr">
         <is>
-          <t>55</t>
+          <t>55.4</t>
         </is>
       </c>
       <c r="G752" t="n">
@@ -22149,23 +22149,23 @@
       </c>
       <c r="B754" t="inlineStr">
         <is>
-          <t>ISM Manufacturing New OrdersFEB</t>
+          <t>ISM Manufacturing PMIFEB</t>
         </is>
       </c>
       <c r="C754" t="inlineStr"/>
       <c r="D754" t="inlineStr">
         <is>
-          <t>55.1</t>
+          <t>50.9</t>
         </is>
       </c>
       <c r="E754" t="inlineStr"/>
       <c r="F754" t="inlineStr">
         <is>
-          <t>55.4</t>
+          <t>51</t>
         </is>
       </c>
       <c r="G754" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="755">
@@ -22230,23 +22230,23 @@
       </c>
       <c r="B757" t="inlineStr">
         <is>
-          <t>ISM Manufacturing PMIFEB</t>
+          <t>ISM Manufacturing EmploymentFEB</t>
         </is>
       </c>
       <c r="C757" t="inlineStr"/>
       <c r="D757" t="inlineStr">
         <is>
-          <t>50.9</t>
+          <t>50.3</t>
         </is>
       </c>
       <c r="E757" t="inlineStr"/>
       <c r="F757" t="inlineStr">
         <is>
-          <t>51</t>
+          <t>50.6</t>
         </is>
       </c>
       <c r="G757" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="758">
@@ -22311,23 +22311,23 @@
       </c>
       <c r="B760" t="inlineStr">
         <is>
-          <t>ISM Manufacturing EmploymentFEB</t>
+          <t>ISM Manufacturing PricesFEB</t>
         </is>
       </c>
       <c r="C760" t="inlineStr"/>
       <c r="D760" t="inlineStr">
         <is>
-          <t>50.3</t>
+          <t>54.9</t>
         </is>
       </c>
       <c r="E760" t="inlineStr"/>
       <c r="F760" t="inlineStr">
         <is>
-          <t>50.6</t>
+          <t>55</t>
         </is>
       </c>
       <c r="G760" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="761">
@@ -22840,7 +22840,7 @@
       </c>
       <c r="B783" t="inlineStr">
         <is>
-          <t>MBA Mortgage Market IndexFEB/28</t>
+          <t>MBA 30-Year Mortgage RateFEB/28</t>
         </is>
       </c>
       <c r="C783" t="inlineStr"/>
@@ -22848,7 +22848,7 @@
       <c r="E783" t="inlineStr"/>
       <c r="F783" t="inlineStr"/>
       <c r="G783" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="784">
@@ -22859,7 +22859,7 @@
       </c>
       <c r="B784" t="inlineStr">
         <is>
-          <t>MBA 30-Year Mortgage RateFEB/28</t>
+          <t>MBA Mortgage Market IndexFEB/28</t>
         </is>
       </c>
       <c r="C784" t="inlineStr"/>
@@ -22867,7 +22867,7 @@
       <c r="E784" t="inlineStr"/>
       <c r="F784" t="inlineStr"/>
       <c r="G784" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="785">
@@ -22994,23 +22994,23 @@
       </c>
       <c r="B789" t="inlineStr">
         <is>
-          <t>S&amp;P Global Composite PMI FinalFEB</t>
+          <t>S&amp;P Global Services PMI FinalFEB</t>
         </is>
       </c>
       <c r="C789" t="inlineStr"/>
       <c r="D789" t="inlineStr">
         <is>
-          <t>52.7</t>
+          <t>52.9</t>
         </is>
       </c>
       <c r="E789" t="inlineStr">
         <is>
-          <t>50.4</t>
+          <t>49.7</t>
         </is>
       </c>
       <c r="F789" t="inlineStr">
         <is>
-          <t>50.4</t>
+          <t>49.7</t>
         </is>
       </c>
       <c r="G789" t="n">
@@ -23025,23 +23025,23 @@
       </c>
       <c r="B790" t="inlineStr">
         <is>
-          <t>S&amp;P Global Services PMI FinalFEB</t>
+          <t>S&amp;P Global Composite PMI FinalFEB</t>
         </is>
       </c>
       <c r="C790" t="inlineStr"/>
       <c r="D790" t="inlineStr">
         <is>
-          <t>52.9</t>
+          <t>52.7</t>
         </is>
       </c>
       <c r="E790" t="inlineStr">
         <is>
-          <t>49.7</t>
+          <t>50.4</t>
         </is>
       </c>
       <c r="F790" t="inlineStr">
         <is>
-          <t>49.7</t>
+          <t>50.4</t>
         </is>
       </c>
       <c r="G790" t="n">
@@ -23503,11 +23503,15 @@
       </c>
       <c r="B808" t="inlineStr">
         <is>
-          <t>EIA Distillate Stocks ChangeFEB/28</t>
+          <t>EIA Refinery Crude Runs ChangeFEB/28</t>
         </is>
       </c>
       <c r="C808" t="inlineStr"/>
-      <c r="D808" t="inlineStr"/>
+      <c r="D808" t="inlineStr">
+        <is>
+          <t>0.317M</t>
+        </is>
+      </c>
       <c r="E808" t="inlineStr"/>
       <c r="F808" t="inlineStr"/>
       <c r="G808" t="n">
@@ -23591,15 +23595,19 @@
       </c>
       <c r="B812" t="inlineStr">
         <is>
-          <t>EIA Crude Oil Imports ChangeFEB/28</t>
+          <t>EIA Gasoline Stocks ChangeFEB/28</t>
         </is>
       </c>
       <c r="C812" t="inlineStr"/>
-      <c r="D812" t="inlineStr"/>
+      <c r="D812" t="inlineStr">
+        <is>
+          <t>0.369M</t>
+        </is>
+      </c>
       <c r="E812" t="inlineStr"/>
       <c r="F812" t="inlineStr"/>
       <c r="G812" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="813">
@@ -23679,13 +23687,13 @@
       </c>
       <c r="B816" t="inlineStr">
         <is>
-          <t>EIA Refinery Crude Runs ChangeFEB/28</t>
+          <t>EIA Gasoline Production ChangeFEB/28</t>
         </is>
       </c>
       <c r="C816" t="inlineStr"/>
       <c r="D816" t="inlineStr">
         <is>
-          <t>0.317M</t>
+          <t>-0.02M</t>
         </is>
       </c>
       <c r="E816" t="inlineStr"/>
@@ -23702,19 +23710,19 @@
       </c>
       <c r="B817" t="inlineStr">
         <is>
-          <t>EIA Gasoline Stocks ChangeFEB/28</t>
+          <t>EIA Cushing Crude Oil Stocks ChangeFEB/28</t>
         </is>
       </c>
       <c r="C817" t="inlineStr"/>
       <c r="D817" t="inlineStr">
         <is>
-          <t>0.369M</t>
+          <t>1.282M</t>
         </is>
       </c>
       <c r="E817" t="inlineStr"/>
       <c r="F817" t="inlineStr"/>
       <c r="G817" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="818">
@@ -23744,15 +23752,11 @@
       </c>
       <c r="B819" t="inlineStr">
         <is>
-          <t>EIA Cushing Crude Oil Stocks ChangeFEB/28</t>
+          <t>EIA Crude Oil Imports ChangeFEB/28</t>
         </is>
       </c>
       <c r="C819" t="inlineStr"/>
-      <c r="D819" t="inlineStr">
-        <is>
-          <t>1.282M</t>
-        </is>
-      </c>
+      <c r="D819" t="inlineStr"/>
       <c r="E819" t="inlineStr"/>
       <c r="F819" t="inlineStr"/>
       <c r="G819" t="n">
@@ -23767,13 +23771,13 @@
       </c>
       <c r="B820" t="inlineStr">
         <is>
-          <t>EIA Gasoline Production ChangeFEB/28</t>
+          <t>EIA Distillate Stocks ChangeFEB/28</t>
         </is>
       </c>
       <c r="C820" t="inlineStr"/>
       <c r="D820" t="inlineStr">
         <is>
-          <t>-0.02M</t>
+          <t>3.908M</t>
         </is>
       </c>
       <c r="E820" t="inlineStr"/>
@@ -24020,23 +24024,15 @@
       </c>
       <c r="B831" t="inlineStr">
         <is>
-          <t>Unit Labour Costs QoQ FinalQ4</t>
+          <t>Initial Jobless ClaimsMAR/01</t>
         </is>
       </c>
       <c r="C831" t="inlineStr"/>
-      <c r="D831" t="inlineStr">
-        <is>
-          <t>0.5%</t>
-        </is>
-      </c>
+      <c r="D831" t="inlineStr"/>
       <c r="E831" t="inlineStr"/>
-      <c r="F831" t="inlineStr">
-        <is>
-          <t>3.0%</t>
-        </is>
-      </c>
+      <c r="F831" t="inlineStr"/>
       <c r="G831" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="832">
@@ -24047,23 +24043,23 @@
       </c>
       <c r="B832" t="inlineStr">
         <is>
-          <t>Balance of TradeJAN</t>
+          <t>Unit Labour Costs QoQ FinalQ4</t>
         </is>
       </c>
       <c r="C832" t="inlineStr"/>
       <c r="D832" t="inlineStr">
         <is>
-          <t>$-98.4B</t>
+          <t>0.5%</t>
         </is>
       </c>
       <c r="E832" t="inlineStr"/>
       <c r="F832" t="inlineStr">
         <is>
-          <t>$-103B</t>
+          <t>3.0%</t>
         </is>
       </c>
       <c r="G832" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="833">
@@ -24074,25 +24070,13 @@
       </c>
       <c r="B833" t="inlineStr">
         <is>
-          <t>Nonfarm Productivity QoQ FinalQ4</t>
+          <t>Continuing Jobless ClaimsFEB/22</t>
         </is>
       </c>
       <c r="C833" t="inlineStr"/>
-      <c r="D833" t="inlineStr">
-        <is>
-          <t>2.3%</t>
-        </is>
-      </c>
-      <c r="E833" t="inlineStr">
-        <is>
-          <t>1.2%</t>
-        </is>
-      </c>
-      <c r="F833" t="inlineStr">
-        <is>
-          <t>1.2%</t>
-        </is>
-      </c>
+      <c r="D833" t="inlineStr"/>
+      <c r="E833" t="inlineStr"/>
+      <c r="F833" t="inlineStr"/>
       <c r="G833" t="n">
         <v>3</v>
       </c>
@@ -24105,13 +24089,25 @@
       </c>
       <c r="B834" t="inlineStr">
         <is>
-          <t>Jobless Claims 4-week AverageMAR/01</t>
+          <t>Nonfarm Productivity QoQ FinalQ4</t>
         </is>
       </c>
       <c r="C834" t="inlineStr"/>
-      <c r="D834" t="inlineStr"/>
-      <c r="E834" t="inlineStr"/>
-      <c r="F834" t="inlineStr"/>
+      <c r="D834" t="inlineStr">
+        <is>
+          <t>2.3%</t>
+        </is>
+      </c>
+      <c r="E834" t="inlineStr">
+        <is>
+          <t>1.2%</t>
+        </is>
+      </c>
+      <c r="F834" t="inlineStr">
+        <is>
+          <t>1.2%</t>
+        </is>
+      </c>
       <c r="G834" t="n">
         <v>3</v>
       </c>
@@ -24293,7 +24289,7 @@
       </c>
       <c r="B842" t="inlineStr">
         <is>
-          <t>Continuing Jobless ClaimsFEB/22</t>
+          <t>Jobless Claims 4-week AverageMAR/01</t>
         </is>
       </c>
       <c r="C842" t="inlineStr"/>
@@ -24339,19 +24335,19 @@
       </c>
       <c r="B844" t="inlineStr">
         <is>
-          <t>ImportsJAN</t>
+          <t>Balance of TradeJAN</t>
         </is>
       </c>
       <c r="C844" t="inlineStr"/>
       <c r="D844" t="inlineStr">
         <is>
-          <t>$364.9B</t>
+          <t>$-98.4B</t>
         </is>
       </c>
       <c r="E844" t="inlineStr"/>
       <c r="F844" t="inlineStr">
         <is>
-          <t>$376.0B</t>
+          <t>$-103B</t>
         </is>
       </c>
       <c r="G844" t="n">
@@ -24393,13 +24389,21 @@
       </c>
       <c r="B846" t="inlineStr">
         <is>
-          <t>Initial Jobless ClaimsMAR/01</t>
+          <t>ImportsJAN</t>
         </is>
       </c>
       <c r="C846" t="inlineStr"/>
-      <c r="D846" t="inlineStr"/>
+      <c r="D846" t="inlineStr">
+        <is>
+          <t>$364.9B</t>
+        </is>
+      </c>
       <c r="E846" t="inlineStr"/>
-      <c r="F846" t="inlineStr"/>
+      <c r="F846" t="inlineStr">
+        <is>
+          <t>$376.0B</t>
+        </is>
+      </c>
       <c r="G846" t="n">
         <v>2</v>
       </c>
@@ -24944,19 +24948,23 @@
       </c>
       <c r="B871" t="inlineStr">
         <is>
-          <t>Used Car Prices MoMFEB</t>
+          <t>Participation RateFEB</t>
         </is>
       </c>
       <c r="C871" t="inlineStr"/>
       <c r="D871" t="inlineStr">
         <is>
-          <t>0.4%</t>
+          <t>62.6%</t>
         </is>
       </c>
       <c r="E871" t="inlineStr"/>
-      <c r="F871" t="inlineStr"/>
+      <c r="F871" t="inlineStr">
+        <is>
+          <t>62.6%</t>
+        </is>
+      </c>
       <c r="G871" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="872">
@@ -24967,19 +24975,19 @@
       </c>
       <c r="B872" t="inlineStr">
         <is>
-          <t>Participation RateFEB</t>
+          <t>Average Hourly Earnings YoYFEB</t>
         </is>
       </c>
       <c r="C872" t="inlineStr"/>
       <c r="D872" t="inlineStr">
         <is>
-          <t>62.6%</t>
+          <t>4.1%</t>
         </is>
       </c>
       <c r="E872" t="inlineStr"/>
       <c r="F872" t="inlineStr">
         <is>
-          <t>62.6%</t>
+          <t>4.1%</t>
         </is>
       </c>
       <c r="G872" t="n">
@@ -24994,23 +25002,23 @@
       </c>
       <c r="B873" t="inlineStr">
         <is>
-          <t>Average Hourly Earnings YoYFEB</t>
+          <t>Manufacturing PayrollsFEB</t>
         </is>
       </c>
       <c r="C873" t="inlineStr"/>
       <c r="D873" t="inlineStr">
         <is>
-          <t>4.1%</t>
+          <t>3K</t>
         </is>
       </c>
       <c r="E873" t="inlineStr"/>
       <c r="F873" t="inlineStr">
         <is>
-          <t>4.1%</t>
+          <t>6.0K</t>
         </is>
       </c>
       <c r="G873" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="874">
@@ -25021,19 +25029,19 @@
       </c>
       <c r="B874" t="inlineStr">
         <is>
-          <t>Manufacturing PayrollsFEB</t>
+          <t>Nonfarm Payrolls PrivateFEB</t>
         </is>
       </c>
       <c r="C874" t="inlineStr"/>
       <c r="D874" t="inlineStr">
         <is>
-          <t>3K</t>
+          <t>111K</t>
         </is>
       </c>
       <c r="E874" t="inlineStr"/>
       <c r="F874" t="inlineStr">
         <is>
-          <t>6.0K</t>
+          <t>170.0K</t>
         </is>
       </c>
       <c r="G874" t="n">
@@ -25075,23 +25083,23 @@
       </c>
       <c r="B876" t="inlineStr">
         <is>
-          <t>Nonfarm Payrolls PrivateFEB</t>
+          <t>Average Hourly Earnings MoMFEB</t>
         </is>
       </c>
       <c r="C876" t="inlineStr"/>
       <c r="D876" t="inlineStr">
         <is>
-          <t>111K</t>
+          <t>0.5%</t>
         </is>
       </c>
       <c r="E876" t="inlineStr"/>
       <c r="F876" t="inlineStr">
         <is>
-          <t>170.0K</t>
+          <t>0.3%</t>
         </is>
       </c>
       <c r="G876" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="877">
@@ -25210,23 +25218,19 @@
       </c>
       <c r="B881" t="inlineStr">
         <is>
-          <t>Average Hourly Earnings MoMFEB</t>
+          <t>Used Car Prices MoMFEB</t>
         </is>
       </c>
       <c r="C881" t="inlineStr"/>
       <c r="D881" t="inlineStr">
         <is>
-          <t>0.5%</t>
+          <t>0.4%</t>
         </is>
       </c>
       <c r="E881" t="inlineStr"/>
-      <c r="F881" t="inlineStr">
-        <is>
-          <t>0.3%</t>
-        </is>
-      </c>
+      <c r="F881" t="inlineStr"/>
       <c r="G881" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="882">

--- a/Input_data/IST_US_trad_eco_cal_2025-01-01_to_2025-03-09.xlsx
+++ b/Input_data/IST_US_trad_eco_cal_2025-01-01_to_2025-03-09.xlsx
@@ -806,24 +806,20 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>EIA Distillate Stocks ChangeDEC/27</t>
+          <t>EIA Distillate Fuel Production ChangeDEC/27</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>6.406M</t>
+          <t>0.099M</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>-1.694M</t>
-        </is>
-      </c>
-      <c r="E13" t="inlineStr">
-        <is>
-          <t>-0.1M</t>
-        </is>
-      </c>
+          <t>0.178M</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr"/>
       <c r="F13" t="inlineStr"/>
       <c r="G13" t="n">
         <v>3</v>
@@ -837,23 +833,27 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>EIA Refinery Crude Runs ChangeDEC/27</t>
+          <t>EIA Crude Oil Stocks ChangeDEC/27</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>0.041M</t>
+          <t>-1.178M</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>0.205M</t>
-        </is>
-      </c>
-      <c r="E14" t="inlineStr"/>
+          <t>-4.237M</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>-2.75M</t>
+        </is>
+      </c>
       <c r="F14" t="inlineStr"/>
       <c r="G14" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="15">
@@ -864,17 +864,17 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>EIA Gasoline Production ChangeDEC/27</t>
+          <t>EIA Cushing Crude Oil Stocks ChangeDEC/27</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>-0.959M</t>
+          <t>-0.142M</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>0.051M</t>
+          <t>-0.32M</t>
         </is>
       </c>
       <c r="E15" t="inlineStr"/>
@@ -891,27 +891,23 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>EIA Gasoline Stocks ChangeDEC/27</t>
+          <t>EIA Heating Oil Stocks ChangeDEC/27</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>7.717M</t>
+          <t>-0.416M</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>1.63M</t>
-        </is>
-      </c>
-      <c r="E16" t="inlineStr">
-        <is>
-          <t>0.7M</t>
-        </is>
-      </c>
+          <t>-0.062M</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr"/>
       <c r="F16" t="inlineStr"/>
       <c r="G16" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="17">
@@ -922,17 +918,17 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>EIA Crude Oil Imports ChangeDEC/27</t>
+          <t>EIA Gasoline Production ChangeDEC/27</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>0.323M</t>
+          <t>-0.959M</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>0.995M</t>
+          <t>0.051M</t>
         </is>
       </c>
       <c r="E17" t="inlineStr"/>
@@ -949,23 +945,27 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>EIA Heating Oil Stocks ChangeDEC/27</t>
+          <t>EIA Gasoline Stocks ChangeDEC/27</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>-0.416M</t>
+          <t>7.717M</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>-0.062M</t>
-        </is>
-      </c>
-      <c r="E18" t="inlineStr"/>
+          <t>1.63M</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>0.7M</t>
+        </is>
+      </c>
       <c r="F18" t="inlineStr"/>
       <c r="G18" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="19">
@@ -976,17 +976,17 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>EIA Cushing Crude Oil Stocks ChangeDEC/27</t>
+          <t>EIA Refinery Crude Runs ChangeDEC/27</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>-0.142M</t>
+          <t>0.041M</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>-0.32M</t>
+          <t>0.205M</t>
         </is>
       </c>
       <c r="E19" t="inlineStr"/>
@@ -1003,27 +1003,27 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>EIA Crude Oil Stocks ChangeDEC/27</t>
+          <t>EIA Distillate Stocks ChangeDEC/27</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>-1.178M</t>
+          <t>6.406M</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>-4.237M</t>
+          <t>-1.694M</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>-2.75M</t>
+          <t>-0.1M</t>
         </is>
       </c>
       <c r="F20" t="inlineStr"/>
       <c r="G20" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="21">
@@ -1034,17 +1034,17 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>EIA Distillate Fuel Production ChangeDEC/27</t>
+          <t>EIA Crude Oil Imports ChangeDEC/27</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>0.099M</t>
+          <t>0.323M</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>0.178M</t>
+          <t>0.995M</t>
         </is>
       </c>
       <c r="E21" t="inlineStr"/>
@@ -1223,31 +1223,31 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>ISM Manufacturing PricesDEC</t>
+          <t>ISM Manufacturing PMIDEC</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>52.5</t>
+          <t>49.3</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>50.3</t>
+          <t>48.4</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>51.7</t>
+          <t>48.4</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>50.4</t>
+          <t>48.5</t>
         </is>
       </c>
       <c r="G28" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="29">
@@ -1258,27 +1258,31 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>ISM Manufacturing New OrdersDEC</t>
+          <t>ISM Manufacturing EmploymentDEC</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>52.5</t>
+          <t>45.3</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>50.4</t>
-        </is>
-      </c>
-      <c r="E29" t="inlineStr"/>
+          <t>48.1</t>
+        </is>
+      </c>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t>48</t>
+        </is>
+      </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>50.5</t>
+          <t>48.3</t>
         </is>
       </c>
       <c r="G29" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="30">
@@ -1289,31 +1293,27 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>ISM Manufacturing EmploymentDEC</t>
+          <t>ISM Manufacturing New OrdersDEC</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>45.3</t>
+          <t>52.5</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>48.1</t>
-        </is>
-      </c>
-      <c r="E30" t="inlineStr">
-        <is>
-          <t>48</t>
-        </is>
-      </c>
+          <t>50.4</t>
+        </is>
+      </c>
+      <c r="E30" t="inlineStr"/>
       <c r="F30" t="inlineStr">
         <is>
-          <t>48.3</t>
+          <t>50.5</t>
         </is>
       </c>
       <c r="G30" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="31">
@@ -1324,31 +1324,31 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>ISM Manufacturing PMIDEC</t>
+          <t>ISM Manufacturing PricesDEC</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>49.3</t>
+          <t>52.5</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>48.4</t>
+          <t>50.3</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>48.4</t>
+          <t>51.7</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>48.5</t>
+          <t>50.4</t>
         </is>
       </c>
       <c r="G31" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="32">
@@ -1609,27 +1609,31 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>Factory Orders ex TransportationNOV</t>
+          <t>Factory Orders MoMNOV</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>0.2%</t>
+          <t>-0.4%</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>0.2%</t>
-        </is>
-      </c>
-      <c r="E42" t="inlineStr"/>
+          <t>0.5%</t>
+        </is>
+      </c>
+      <c r="E42" t="inlineStr">
+        <is>
+          <t>-0.3%</t>
+        </is>
+      </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>0.2%</t>
+          <t>0.3%</t>
         </is>
       </c>
       <c r="G42" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="43">
@@ -1640,31 +1644,27 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>Factory Orders MoMNOV</t>
+          <t>Factory Orders ex TransportationNOV</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>-0.4%</t>
+          <t>0.2%</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>0.5%</t>
-        </is>
-      </c>
-      <c r="E43" t="inlineStr">
-        <is>
-          <t>-0.3%</t>
-        </is>
-      </c>
+          <t>0.2%</t>
+        </is>
+      </c>
+      <c r="E43" t="inlineStr"/>
       <c r="F43" t="inlineStr">
         <is>
-          <t>0.3%</t>
+          <t>0.2%</t>
         </is>
       </c>
       <c r="G43" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="44">
@@ -1949,27 +1949,23 @@
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>ISM Services EmploymentDEC</t>
+          <t>JOLTs Job QuitsNOV</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>51.4</t>
+          <t>3.065M</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>51.5</t>
-        </is>
-      </c>
-      <c r="E54" t="inlineStr">
-        <is>
-          <t>51.4</t>
-        </is>
-      </c>
+          <t>3.283M</t>
+        </is>
+      </c>
+      <c r="E54" t="inlineStr"/>
       <c r="F54" t="inlineStr">
         <is>
-          <t>52</t>
+          <t>3.31M</t>
         </is>
       </c>
       <c r="G54" t="n">
@@ -1984,27 +1980,31 @@
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>ISM Services Business ActivityDEC</t>
+          <t>ISM Services PMIDEC</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>58.2</t>
+          <t>54.1</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>53.7</t>
-        </is>
-      </c>
-      <c r="E55" t="inlineStr"/>
+          <t>52.1</t>
+        </is>
+      </c>
+      <c r="E55" t="inlineStr">
+        <is>
+          <t>53.3</t>
+        </is>
+      </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>54.1</t>
+          <t>54</t>
         </is>
       </c>
       <c r="G55" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="56">
@@ -2015,27 +2015,27 @@
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>ISM Services PricesDEC</t>
+          <t>ISM Services New OrdersDEC</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>64.4</t>
+          <t>54.2</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>58.2</t>
+          <t>53.7</t>
         </is>
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>57.5</t>
+          <t>54.2</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>58.4</t>
+          <t>54.1</t>
         </is>
       </c>
       <c r="G56" t="n">
@@ -2050,31 +2050,31 @@
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>ISM Services New OrdersDEC</t>
+          <t>JOLTs Job OpeningsNOV</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>54.2</t>
+          <t>8.098M</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>53.7</t>
+          <t>7.839M</t>
         </is>
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>54.2</t>
+          <t>7.70M</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>54.1</t>
+          <t>7.69M</t>
         </is>
       </c>
       <c r="G57" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="58">
@@ -2085,31 +2085,31 @@
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>JOLTs Job OpeningsNOV</t>
+          <t>ISM Services PricesDEC</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>8.098M</t>
+          <t>64.4</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>7.839M</t>
+          <t>58.2</t>
         </is>
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>7.70M</t>
+          <t>57.5</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>7.69M</t>
+          <t>58.4</t>
         </is>
       </c>
       <c r="G58" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="59">
@@ -2120,23 +2120,23 @@
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>JOLTs Job QuitsNOV</t>
+          <t>ISM Services Business ActivityDEC</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>3.065M</t>
+          <t>58.2</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>3.283M</t>
+          <t>53.7</t>
         </is>
       </c>
       <c r="E59" t="inlineStr"/>
       <c r="F59" t="inlineStr">
         <is>
-          <t>3.31M</t>
+          <t>54.1</t>
         </is>
       </c>
       <c r="G59" t="n">
@@ -2151,31 +2151,31 @@
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>ISM Services PMIDEC</t>
+          <t>ISM Services EmploymentDEC</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>54.1</t>
+          <t>51.4</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>52.1</t>
+          <t>51.5</t>
         </is>
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>53.3</t>
+          <t>51.4</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>54</t>
+          <t>52</t>
         </is>
       </c>
       <c r="G60" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="61">
@@ -2271,17 +2271,17 @@
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>MBA Purchase IndexJAN/03</t>
+          <t>MBA Mortgage Refinance IndexJAN/03</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>127.7</t>
+          <t>401.1</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>136.7</t>
+          <t>395.1</t>
         </is>
       </c>
       <c r="E64" t="inlineStr"/>
@@ -2298,23 +2298,23 @@
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>MBA Mortgage ApplicationsJAN/03</t>
+          <t>MBA 30-Year Mortgage RateJAN/03</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>-3.7%</t>
+          <t>6.99%</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>-12.6%</t>
+          <t>6.97%</t>
         </is>
       </c>
       <c r="E65" t="inlineStr"/>
       <c r="F65" t="inlineStr"/>
       <c r="G65" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="66">
@@ -2325,23 +2325,23 @@
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>MBA 30-Year Mortgage RateJAN/03</t>
+          <t>MBA Mortgage Market IndexJAN/03</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>6.99%</t>
+          <t>168.4</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>6.97%</t>
+          <t>174.9</t>
         </is>
       </c>
       <c r="E66" t="inlineStr"/>
       <c r="F66" t="inlineStr"/>
       <c r="G66" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="67">
@@ -2352,17 +2352,17 @@
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>MBA Mortgage Refinance IndexJAN/03</t>
+          <t>MBA Purchase IndexJAN/03</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>401.1</t>
+          <t>127.7</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>395.1</t>
+          <t>136.7</t>
         </is>
       </c>
       <c r="E67" t="inlineStr"/>
@@ -2379,17 +2379,17 @@
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>MBA Mortgage Market IndexJAN/03</t>
+          <t>MBA Mortgage ApplicationsJAN/03</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>168.4</t>
+          <t>-3.7%</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>174.9</t>
+          <t>-12.6%</t>
         </is>
       </c>
       <c r="E68" t="inlineStr"/>
@@ -2685,17 +2685,17 @@
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>EIA Gasoline Production ChangeJAN/03</t>
+          <t>EIA Crude Oil Imports ChangeJAN/03</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>-0.081M</t>
+          <t>0.278M</t>
         </is>
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>-0.959M</t>
+          <t>0.323M</t>
         </is>
       </c>
       <c r="E78" t="inlineStr"/>
@@ -2712,24 +2712,20 @@
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>EIA Distillate Stocks ChangeJAN/03</t>
+          <t>EIA Distillate Fuel Production ChangeJAN/03</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>6.071M</t>
+          <t>-0.167M</t>
         </is>
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>6.406M</t>
-        </is>
-      </c>
-      <c r="E79" t="inlineStr">
-        <is>
-          <t>1M</t>
-        </is>
-      </c>
+          <t>0.099M</t>
+        </is>
+      </c>
+      <c r="E79" t="inlineStr"/>
       <c r="F79" t="inlineStr"/>
       <c r="G79" t="n">
         <v>3</v>
@@ -2743,23 +2739,27 @@
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>EIA Heating Oil Stocks ChangeJAN/03</t>
+          <t>EIA Crude Oil Stocks ChangeJAN/03</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>-0.632M</t>
+          <t>-0.959M</t>
         </is>
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>-0.416M</t>
-        </is>
-      </c>
-      <c r="E80" t="inlineStr"/>
+          <t>-1.178M</t>
+        </is>
+      </c>
+      <c r="E80" t="inlineStr">
+        <is>
+          <t>-0.6M</t>
+        </is>
+      </c>
       <c r="F80" t="inlineStr"/>
       <c r="G80" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="81">
@@ -2770,17 +2770,17 @@
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>EIA Cushing Crude Oil Stocks ChangeJAN/03</t>
+          <t>EIA Refinery Crude Runs ChangeJAN/03</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>-2.502M</t>
+          <t>0.045M</t>
         </is>
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>-0.142M</t>
+          <t>0.041M</t>
         </is>
       </c>
       <c r="E81" t="inlineStr"/>
@@ -2797,23 +2797,27 @@
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>EIA Refinery Crude Runs ChangeJAN/03</t>
+          <t>EIA Gasoline Stocks ChangeJAN/03</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>0.045M</t>
+          <t>6.33M</t>
         </is>
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>0.041M</t>
-        </is>
-      </c>
-      <c r="E82" t="inlineStr"/>
+          <t>7.717M</t>
+        </is>
+      </c>
+      <c r="E82" t="inlineStr">
+        <is>
+          <t>1.5M</t>
+        </is>
+      </c>
       <c r="F82" t="inlineStr"/>
       <c r="G82" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="83">
@@ -2824,27 +2828,23 @@
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>EIA Crude Oil Stocks ChangeJAN/03</t>
+          <t>EIA Heating Oil Stocks ChangeJAN/03</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>-0.959M</t>
+          <t>-0.632M</t>
         </is>
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>-1.178M</t>
-        </is>
-      </c>
-      <c r="E83" t="inlineStr">
-        <is>
-          <t>-0.6M</t>
-        </is>
-      </c>
+          <t>-0.416M</t>
+        </is>
+      </c>
+      <c r="E83" t="inlineStr"/>
       <c r="F83" t="inlineStr"/>
       <c r="G83" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="84">
@@ -2855,20 +2855,24 @@
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>EIA Crude Oil Imports ChangeJAN/03</t>
+          <t>EIA Distillate Stocks ChangeJAN/03</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>0.278M</t>
+          <t>6.071M</t>
         </is>
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>0.323M</t>
-        </is>
-      </c>
-      <c r="E84" t="inlineStr"/>
+          <t>6.406M</t>
+        </is>
+      </c>
+      <c r="E84" t="inlineStr">
+        <is>
+          <t>1M</t>
+        </is>
+      </c>
       <c r="F84" t="inlineStr"/>
       <c r="G84" t="n">
         <v>3</v>
@@ -2882,27 +2886,23 @@
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>EIA Gasoline Stocks ChangeJAN/03</t>
+          <t>EIA Cushing Crude Oil Stocks ChangeJAN/03</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>6.33M</t>
+          <t>-2.502M</t>
         </is>
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>7.717M</t>
-        </is>
-      </c>
-      <c r="E85" t="inlineStr">
-        <is>
-          <t>1.5M</t>
-        </is>
-      </c>
+          <t>-0.142M</t>
+        </is>
+      </c>
+      <c r="E85" t="inlineStr"/>
       <c r="F85" t="inlineStr"/>
       <c r="G85" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="86">
@@ -2913,17 +2913,17 @@
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>EIA Distillate Fuel Production ChangeJAN/03</t>
+          <t>EIA Gasoline Production ChangeJAN/03</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>-0.167M</t>
+          <t>-0.081M</t>
         </is>
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>0.099M</t>
+          <t>-0.959M</t>
         </is>
       </c>
       <c r="E86" t="inlineStr"/>
@@ -3171,17 +3171,17 @@
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>4-Week Bill Auction</t>
+          <t>8-Week Bill Auction</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>4.245%</t>
+          <t>4.240%</t>
         </is>
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>4.265%</t>
+          <t>4.240%</t>
         </is>
       </c>
       <c r="E96" t="inlineStr"/>
@@ -3198,17 +3198,17 @@
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>8-Week Bill Auction</t>
+          <t>4-Week Bill Auction</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>4.240%</t>
+          <t>4.245%</t>
         </is>
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>4.240%</t>
+          <t>4.265%</t>
         </is>
       </c>
       <c r="E97" t="inlineStr"/>
@@ -3336,27 +3336,23 @@
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>Nonfarm Payrolls PrivateDEC</t>
+          <t>Government PayrollsDEC</t>
         </is>
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>223K</t>
+          <t>33K</t>
         </is>
       </c>
       <c r="D103" t="inlineStr">
         <is>
-          <t>182K</t>
-        </is>
-      </c>
-      <c r="E103" t="inlineStr">
-        <is>
-          <t>135K</t>
-        </is>
-      </c>
+          <t>30K</t>
+        </is>
+      </c>
+      <c r="E103" t="inlineStr"/>
       <c r="F103" t="inlineStr">
         <is>
-          <t>185K</t>
+          <t>15K</t>
         </is>
       </c>
       <c r="G103" t="n">
@@ -3371,27 +3367,27 @@
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>Manufacturing PayrollsDEC</t>
+          <t>Nonfarm Payrolls PrivateDEC</t>
         </is>
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>-13K</t>
+          <t>223K</t>
         </is>
       </c>
       <c r="D104" t="inlineStr">
         <is>
-          <t>25K</t>
+          <t>182K</t>
         </is>
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>5K</t>
+          <t>135K</t>
         </is>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>29K</t>
+          <t>185K</t>
         </is>
       </c>
       <c r="G104" t="n">
@@ -3406,27 +3402,31 @@
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>Participation RateDEC</t>
+          <t>Manufacturing PayrollsDEC</t>
         </is>
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>62.5%</t>
+          <t>-13K</t>
         </is>
       </c>
       <c r="D105" t="inlineStr">
         <is>
-          <t>62.5%</t>
-        </is>
-      </c>
-      <c r="E105" t="inlineStr"/>
+          <t>25K</t>
+        </is>
+      </c>
+      <c r="E105" t="inlineStr">
+        <is>
+          <t>5K</t>
+        </is>
+      </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>62.8%</t>
+          <t>29K</t>
         </is>
       </c>
       <c r="G105" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="106">
@@ -3437,31 +3437,27 @@
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>Non Farm PayrollsDEC</t>
+          <t>Participation RateDEC</t>
         </is>
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>256K</t>
+          <t>62.5%</t>
         </is>
       </c>
       <c r="D106" t="inlineStr">
         <is>
-          <t>212K</t>
-        </is>
-      </c>
-      <c r="E106" t="inlineStr">
-        <is>
-          <t>160K</t>
-        </is>
-      </c>
+          <t>62.5%</t>
+        </is>
+      </c>
+      <c r="E106" t="inlineStr"/>
       <c r="F106" t="inlineStr">
         <is>
-          <t>200K</t>
+          <t>62.8%</t>
         </is>
       </c>
       <c r="G106" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="107">
@@ -3472,31 +3468,31 @@
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>Average Hourly Earnings YoY</t>
+          <t>Non Farm PayrollsDEC</t>
         </is>
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>3.9%</t>
+          <t>256K</t>
         </is>
       </c>
       <c r="D107" t="inlineStr">
         <is>
-          <t>4%</t>
+          <t>212K</t>
         </is>
       </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t>4%</t>
+          <t>160K</t>
         </is>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>4%</t>
+          <t>200K</t>
         </is>
       </c>
       <c r="G107" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="108">
@@ -3507,27 +3503,27 @@
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>Average Hourly Earnings MoMDEC</t>
+          <t>Average Hourly Earnings YoY</t>
         </is>
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>0.3%</t>
+          <t>3.9%</t>
         </is>
       </c>
       <c r="D108" t="inlineStr">
         <is>
-          <t>0.4%</t>
+          <t>4%</t>
         </is>
       </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t>0.3%</t>
+          <t>4%</t>
         </is>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>0.3%</t>
+          <t>4%</t>
         </is>
       </c>
       <c r="G108" t="n">
@@ -3542,27 +3538,31 @@
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>U-6 Unemployment Rate</t>
+          <t>Average Hourly Earnings MoMDEC</t>
         </is>
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>7.5%</t>
+          <t>0.3%</t>
         </is>
       </c>
       <c r="D109" t="inlineStr">
         <is>
-          <t>7.7%</t>
-        </is>
-      </c>
-      <c r="E109" t="inlineStr"/>
+          <t>0.4%</t>
+        </is>
+      </c>
+      <c r="E109" t="inlineStr">
+        <is>
+          <t>0.3%</t>
+        </is>
+      </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>7.9%</t>
+          <t>0.3%</t>
         </is>
       </c>
       <c r="G109" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="110">
@@ -3573,27 +3573,23 @@
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>Average Weekly HoursDEC</t>
+          <t>U-6 Unemployment Rate</t>
         </is>
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>34.3</t>
+          <t>7.5%</t>
         </is>
       </c>
       <c r="D110" t="inlineStr">
         <is>
-          <t>34.3</t>
-        </is>
-      </c>
-      <c r="E110" t="inlineStr">
-        <is>
-          <t>34.3</t>
-        </is>
-      </c>
+          <t>7.7%</t>
+        </is>
+      </c>
+      <c r="E110" t="inlineStr"/>
       <c r="F110" t="inlineStr">
         <is>
-          <t>34.3</t>
+          <t>7.9%</t>
         </is>
       </c>
       <c r="G110" t="n">
@@ -3608,23 +3604,27 @@
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>Government PayrollsDEC</t>
+          <t>Average Weekly HoursDEC</t>
         </is>
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>33K</t>
+          <t>34.3</t>
         </is>
       </c>
       <c r="D111" t="inlineStr">
         <is>
-          <t>30K</t>
-        </is>
-      </c>
-      <c r="E111" t="inlineStr"/>
+          <t>34.3</t>
+        </is>
+      </c>
+      <c r="E111" t="inlineStr">
+        <is>
+          <t>34.3</t>
+        </is>
+      </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>15K</t>
+          <t>34.3</t>
         </is>
       </c>
       <c r="G111" t="n">
@@ -3674,23 +3674,23 @@
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>Michigan Consumer Expectations PrelJAN</t>
+          <t>Michigan 5 Year Inflation Expectations PrelJAN</t>
         </is>
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>70.2</t>
+          <t>3.3%</t>
         </is>
       </c>
       <c r="D113" t="inlineStr">
         <is>
-          <t>73.3</t>
+          <t>3%</t>
         </is>
       </c>
       <c r="E113" t="inlineStr"/>
       <c r="F113" t="inlineStr">
         <is>
-          <t>74</t>
+          <t>3.2%</t>
         </is>
       </c>
       <c r="G113" t="n">
@@ -3705,27 +3705,31 @@
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>Michigan Inflation Expectations PrelJAN</t>
+          <t>Michigan Consumer Sentiment PrelJAN</t>
         </is>
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>3.3%</t>
+          <t>73.2</t>
         </is>
       </c>
       <c r="D114" t="inlineStr">
         <is>
-          <t>2.8%</t>
-        </is>
-      </c>
-      <c r="E114" t="inlineStr"/>
+          <t>74.0</t>
+        </is>
+      </c>
+      <c r="E114" t="inlineStr">
+        <is>
+          <t>73.8</t>
+        </is>
+      </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>3.0%</t>
+          <t>75</t>
         </is>
       </c>
       <c r="G114" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="115">
@@ -3736,23 +3740,23 @@
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>Michigan Current Conditions PrelJAN</t>
+          <t>Michigan Inflation Expectations PrelJAN</t>
         </is>
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>77.9</t>
+          <t>3.3%</t>
         </is>
       </c>
       <c r="D115" t="inlineStr">
         <is>
-          <t>75.1</t>
+          <t>2.8%</t>
         </is>
       </c>
       <c r="E115" t="inlineStr"/>
       <c r="F115" t="inlineStr">
         <is>
-          <t>78</t>
+          <t>3.0%</t>
         </is>
       </c>
       <c r="G115" t="n">
@@ -3767,31 +3771,27 @@
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t>Michigan Consumer Sentiment PrelJAN</t>
+          <t>Michigan Consumer Expectations PrelJAN</t>
         </is>
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>73.2</t>
+          <t>70.2</t>
         </is>
       </c>
       <c r="D116" t="inlineStr">
         <is>
-          <t>74.0</t>
-        </is>
-      </c>
-      <c r="E116" t="inlineStr">
-        <is>
-          <t>73.8</t>
-        </is>
-      </c>
+          <t>73.3</t>
+        </is>
+      </c>
+      <c r="E116" t="inlineStr"/>
       <c r="F116" t="inlineStr">
         <is>
-          <t>75</t>
+          <t>74</t>
         </is>
       </c>
       <c r="G116" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="117">
@@ -3802,23 +3802,23 @@
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t>Michigan 5 Year Inflation Expectations PrelJAN</t>
+          <t>Michigan Current Conditions PrelJAN</t>
         </is>
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>3.3%</t>
+          <t>77.9</t>
         </is>
       </c>
       <c r="D117" t="inlineStr">
         <is>
-          <t>3%</t>
+          <t>75.1</t>
         </is>
       </c>
       <c r="E117" t="inlineStr"/>
       <c r="F117" t="inlineStr">
         <is>
-          <t>3.2%</t>
+          <t>78</t>
         </is>
       </c>
       <c r="G117" t="n">
@@ -4134,7 +4134,7 @@
       </c>
       <c r="B129" t="inlineStr">
         <is>
-          <t>PPI YoYDEC</t>
+          <t>PPI Ex Food, Energy and Trade YoYDEC</t>
         </is>
       </c>
       <c r="C129" t="inlineStr">
@@ -4144,17 +4144,13 @@
       </c>
       <c r="D129" t="inlineStr">
         <is>
-          <t>3%</t>
-        </is>
-      </c>
-      <c r="E129" t="inlineStr">
-        <is>
-          <t>3.4%</t>
-        </is>
-      </c>
+          <t>3.5%</t>
+        </is>
+      </c>
+      <c r="E129" t="inlineStr"/>
       <c r="F129" t="inlineStr">
         <is>
-          <t>3.3%</t>
+          <t>3.6%</t>
         </is>
       </c>
       <c r="G129" t="n">
@@ -4169,23 +4165,27 @@
       </c>
       <c r="B130" t="inlineStr">
         <is>
-          <t>PPIDEC</t>
+          <t>Core PPI YoYDEC</t>
         </is>
       </c>
       <c r="C130" t="inlineStr">
         <is>
-          <t>146.842</t>
+          <t>3.5%</t>
         </is>
       </c>
       <c r="D130" t="inlineStr">
         <is>
-          <t>146.521</t>
-        </is>
-      </c>
-      <c r="E130" t="inlineStr"/>
+          <t>3.5%</t>
+        </is>
+      </c>
+      <c r="E130" t="inlineStr">
+        <is>
+          <t>3.8%</t>
+        </is>
+      </c>
       <c r="F130" t="inlineStr">
         <is>
-          <t>146.8</t>
+          <t>3.5%</t>
         </is>
       </c>
       <c r="G130" t="n">
@@ -4200,19 +4200,19 @@
       </c>
       <c r="B131" t="inlineStr">
         <is>
-          <t>PPI MoMDEC</t>
+          <t>Core PPI MoMDEC</t>
         </is>
       </c>
       <c r="C131" t="inlineStr">
         <is>
+          <t>0%</t>
+        </is>
+      </c>
+      <c r="D131" t="inlineStr">
+        <is>
           <t>0.2%</t>
         </is>
       </c>
-      <c r="D131" t="inlineStr">
-        <is>
-          <t>0.4%</t>
-        </is>
-      </c>
       <c r="E131" t="inlineStr">
         <is>
           <t>0.3%</t>
@@ -4220,11 +4220,11 @@
       </c>
       <c r="F131" t="inlineStr">
         <is>
-          <t>0.3%</t>
+          <t>0.2%</t>
         </is>
       </c>
       <c r="G131" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="132">
@@ -4235,27 +4235,23 @@
       </c>
       <c r="B132" t="inlineStr">
         <is>
-          <t>PPI Ex Food, Energy and Trade MoMDEC</t>
+          <t>PPIDEC</t>
         </is>
       </c>
       <c r="C132" t="inlineStr">
         <is>
-          <t>0.1%</t>
+          <t>146.842</t>
         </is>
       </c>
       <c r="D132" t="inlineStr">
         <is>
-          <t>0.1%</t>
-        </is>
-      </c>
-      <c r="E132" t="inlineStr">
-        <is>
-          <t>0.3%</t>
-        </is>
-      </c>
+          <t>146.521</t>
+        </is>
+      </c>
+      <c r="E132" t="inlineStr"/>
       <c r="F132" t="inlineStr">
         <is>
-          <t>0.2%</t>
+          <t>146.8</t>
         </is>
       </c>
       <c r="G132" t="n">
@@ -4270,17 +4266,17 @@
       </c>
       <c r="B133" t="inlineStr">
         <is>
-          <t>Core PPI MoMDEC</t>
+          <t>PPI MoMDEC</t>
         </is>
       </c>
       <c r="C133" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>0.2%</t>
         </is>
       </c>
       <c r="D133" t="inlineStr">
         <is>
-          <t>0.2%</t>
+          <t>0.4%</t>
         </is>
       </c>
       <c r="E133" t="inlineStr">
@@ -4290,11 +4286,11 @@
       </c>
       <c r="F133" t="inlineStr">
         <is>
-          <t>0.2%</t>
+          <t>0.3%</t>
         </is>
       </c>
       <c r="G133" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="134">
@@ -4305,27 +4301,27 @@
       </c>
       <c r="B134" t="inlineStr">
         <is>
-          <t>Core PPI YoYDEC</t>
+          <t>PPI YoYDEC</t>
         </is>
       </c>
       <c r="C134" t="inlineStr">
         <is>
-          <t>3.5%</t>
+          <t>3.3%</t>
         </is>
       </c>
       <c r="D134" t="inlineStr">
         <is>
-          <t>3.5%</t>
+          <t>3%</t>
         </is>
       </c>
       <c r="E134" t="inlineStr">
         <is>
-          <t>3.8%</t>
+          <t>3.4%</t>
         </is>
       </c>
       <c r="F134" t="inlineStr">
         <is>
-          <t>3.5%</t>
+          <t>3.3%</t>
         </is>
       </c>
       <c r="G134" t="n">
@@ -4340,23 +4336,27 @@
       </c>
       <c r="B135" t="inlineStr">
         <is>
-          <t>PPI Ex Food, Energy and Trade YoYDEC</t>
+          <t>PPI Ex Food, Energy and Trade MoMDEC</t>
         </is>
       </c>
       <c r="C135" t="inlineStr">
         <is>
-          <t>3.3%</t>
+          <t>0.1%</t>
         </is>
       </c>
       <c r="D135" t="inlineStr">
         <is>
-          <t>3.5%</t>
-        </is>
-      </c>
-      <c r="E135" t="inlineStr"/>
+          <t>0.1%</t>
+        </is>
+      </c>
+      <c r="E135" t="inlineStr">
+        <is>
+          <t>0.3%</t>
+        </is>
+      </c>
       <c r="F135" t="inlineStr">
         <is>
-          <t>3.6%</t>
+          <t>0.2%</t>
         </is>
       </c>
       <c r="G135" t="n">
@@ -4564,23 +4564,23 @@
       </c>
       <c r="B143" t="inlineStr">
         <is>
-          <t>MBA 30-Year Mortgage RateJAN/10</t>
+          <t>MBA Mortgage Refinance IndexJAN/10</t>
         </is>
       </c>
       <c r="C143" t="inlineStr">
         <is>
-          <t>7.09%</t>
+          <t>575.6</t>
         </is>
       </c>
       <c r="D143" t="inlineStr">
         <is>
-          <t>6.99%</t>
+          <t>401.1000</t>
         </is>
       </c>
       <c r="E143" t="inlineStr"/>
       <c r="F143" t="inlineStr"/>
       <c r="G143" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="144">
@@ -4591,17 +4591,17 @@
       </c>
       <c r="B144" t="inlineStr">
         <is>
-          <t>MBA Purchase IndexJAN/10</t>
+          <t>MBA Mortgage Market IndexJAN/10</t>
         </is>
       </c>
       <c r="C144" t="inlineStr">
         <is>
-          <t>162</t>
+          <t>224.4</t>
         </is>
       </c>
       <c r="D144" t="inlineStr">
         <is>
-          <t>127.7000</t>
+          <t>168.4</t>
         </is>
       </c>
       <c r="E144" t="inlineStr"/>
@@ -4618,17 +4618,17 @@
       </c>
       <c r="B145" t="inlineStr">
         <is>
-          <t>MBA Mortgage Market IndexJAN/10</t>
+          <t>MBA Mortgage ApplicationsJAN/10</t>
         </is>
       </c>
       <c r="C145" t="inlineStr">
         <is>
-          <t>224.4</t>
+          <t>33.3%</t>
         </is>
       </c>
       <c r="D145" t="inlineStr">
         <is>
-          <t>168.4</t>
+          <t>-3.7%</t>
         </is>
       </c>
       <c r="E145" t="inlineStr"/>
@@ -4645,23 +4645,23 @@
       </c>
       <c r="B146" t="inlineStr">
         <is>
-          <t>MBA Mortgage Refinance IndexJAN/10</t>
+          <t>MBA 30-Year Mortgage RateJAN/10</t>
         </is>
       </c>
       <c r="C146" t="inlineStr">
         <is>
-          <t>575.6</t>
+          <t>7.09%</t>
         </is>
       </c>
       <c r="D146" t="inlineStr">
         <is>
-          <t>401.1000</t>
+          <t>6.99%</t>
         </is>
       </c>
       <c r="E146" t="inlineStr"/>
       <c r="F146" t="inlineStr"/>
       <c r="G146" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="147">
@@ -4672,17 +4672,17 @@
       </c>
       <c r="B147" t="inlineStr">
         <is>
-          <t>MBA Mortgage ApplicationsJAN/10</t>
+          <t>MBA Purchase IndexJAN/10</t>
         </is>
       </c>
       <c r="C147" t="inlineStr">
         <is>
-          <t>33.3%</t>
+          <t>162</t>
         </is>
       </c>
       <c r="D147" t="inlineStr">
         <is>
-          <t>-3.7%</t>
+          <t>127.7000</t>
         </is>
       </c>
       <c r="E147" t="inlineStr"/>
@@ -4978,17 +4978,17 @@
       </c>
       <c r="B157" t="inlineStr">
         <is>
-          <t>EIA Gasoline Production ChangeJAN/10</t>
+          <t>EIA Crude Oil Imports ChangeJAN/10</t>
         </is>
       </c>
       <c r="C157" t="inlineStr">
         <is>
-          <t>0.397M</t>
+          <t>-1.304M</t>
         </is>
       </c>
       <c r="D157" t="inlineStr">
         <is>
-          <t>-0.081M</t>
+          <t>0.278M</t>
         </is>
       </c>
       <c r="E157" t="inlineStr"/>
@@ -5005,17 +5005,17 @@
       </c>
       <c r="B158" t="inlineStr">
         <is>
-          <t>EIA Distillate Fuel Production ChangeJAN/10</t>
+          <t>EIA Cushing Crude Oil Stocks ChangeJAN/10</t>
         </is>
       </c>
       <c r="C158" t="inlineStr">
         <is>
-          <t>-0.021M</t>
+          <t>0.765M</t>
         </is>
       </c>
       <c r="D158" t="inlineStr">
         <is>
-          <t>-0.167M</t>
+          <t>-2.502M</t>
         </is>
       </c>
       <c r="E158" t="inlineStr"/>
@@ -5032,22 +5032,22 @@
       </c>
       <c r="B159" t="inlineStr">
         <is>
-          <t>EIA Gasoline Stocks ChangeJAN/10</t>
+          <t>EIA Crude Oil Stocks ChangeJAN/10</t>
         </is>
       </c>
       <c r="C159" t="inlineStr">
         <is>
-          <t>5.852M</t>
+          <t>-1.961M</t>
         </is>
       </c>
       <c r="D159" t="inlineStr">
         <is>
-          <t>6.33M</t>
+          <t>-0.959M</t>
         </is>
       </c>
       <c r="E159" t="inlineStr">
         <is>
-          <t>2.60M</t>
+          <t>-1.6M</t>
         </is>
       </c>
       <c r="F159" t="inlineStr"/>
@@ -5063,20 +5063,24 @@
       </c>
       <c r="B160" t="inlineStr">
         <is>
-          <t>EIA Heating Oil Stocks ChangeJAN/10</t>
+          <t>EIA Distillate Stocks ChangeJAN/10</t>
         </is>
       </c>
       <c r="C160" t="inlineStr">
         <is>
-          <t>0.646M</t>
+          <t>3.077M</t>
         </is>
       </c>
       <c r="D160" t="inlineStr">
         <is>
-          <t>-0.632M</t>
-        </is>
-      </c>
-      <c r="E160" t="inlineStr"/>
+          <t>6.071M</t>
+        </is>
+      </c>
+      <c r="E160" t="inlineStr">
+        <is>
+          <t>1.1M</t>
+        </is>
+      </c>
       <c r="F160" t="inlineStr"/>
       <c r="G160" t="n">
         <v>3</v>
@@ -5090,17 +5094,17 @@
       </c>
       <c r="B161" t="inlineStr">
         <is>
-          <t>EIA Refinery Crude Runs ChangeJAN/10</t>
+          <t>EIA Gasoline Production ChangeJAN/10</t>
         </is>
       </c>
       <c r="C161" t="inlineStr">
         <is>
-          <t>-0.255M</t>
+          <t>0.397M</t>
         </is>
       </c>
       <c r="D161" t="inlineStr">
         <is>
-          <t>0.045M</t>
+          <t>-0.081M</t>
         </is>
       </c>
       <c r="E161" t="inlineStr"/>
@@ -5117,24 +5121,20 @@
       </c>
       <c r="B162" t="inlineStr">
         <is>
-          <t>EIA Distillate Stocks ChangeJAN/10</t>
+          <t>EIA Heating Oil Stocks ChangeJAN/10</t>
         </is>
       </c>
       <c r="C162" t="inlineStr">
         <is>
-          <t>3.077M</t>
+          <t>0.646M</t>
         </is>
       </c>
       <c r="D162" t="inlineStr">
         <is>
-          <t>6.071M</t>
-        </is>
-      </c>
-      <c r="E162" t="inlineStr">
-        <is>
-          <t>1.1M</t>
-        </is>
-      </c>
+          <t>-0.632M</t>
+        </is>
+      </c>
+      <c r="E162" t="inlineStr"/>
       <c r="F162" t="inlineStr"/>
       <c r="G162" t="n">
         <v>3</v>
@@ -5148,22 +5148,22 @@
       </c>
       <c r="B163" t="inlineStr">
         <is>
-          <t>EIA Crude Oil Stocks ChangeJAN/10</t>
+          <t>EIA Gasoline Stocks ChangeJAN/10</t>
         </is>
       </c>
       <c r="C163" t="inlineStr">
         <is>
-          <t>-1.961M</t>
+          <t>5.852M</t>
         </is>
       </c>
       <c r="D163" t="inlineStr">
         <is>
-          <t>-0.959M</t>
+          <t>6.33M</t>
         </is>
       </c>
       <c r="E163" t="inlineStr">
         <is>
-          <t>-1.6M</t>
+          <t>2.60M</t>
         </is>
       </c>
       <c r="F163" t="inlineStr"/>
@@ -5179,17 +5179,17 @@
       </c>
       <c r="B164" t="inlineStr">
         <is>
-          <t>EIA Cushing Crude Oil Stocks ChangeJAN/10</t>
+          <t>EIA Distillate Fuel Production ChangeJAN/10</t>
         </is>
       </c>
       <c r="C164" t="inlineStr">
         <is>
-          <t>0.765M</t>
+          <t>-0.021M</t>
         </is>
       </c>
       <c r="D164" t="inlineStr">
         <is>
-          <t>-2.502M</t>
+          <t>-0.167M</t>
         </is>
       </c>
       <c r="E164" t="inlineStr"/>
@@ -5206,17 +5206,17 @@
       </c>
       <c r="B165" t="inlineStr">
         <is>
-          <t>EIA Crude Oil Imports ChangeJAN/10</t>
+          <t>EIA Refinery Crude Runs ChangeJAN/10</t>
         </is>
       </c>
       <c r="C165" t="inlineStr">
         <is>
-          <t>-1.304M</t>
+          <t>-0.255M</t>
         </is>
       </c>
       <c r="D165" t="inlineStr">
         <is>
-          <t>0.278M</t>
+          <t>0.045M</t>
         </is>
       </c>
       <c r="E165" t="inlineStr"/>
@@ -5336,25 +5336,21 @@
       </c>
       <c r="B171" t="inlineStr">
         <is>
-          <t>Export Prices YoYDEC</t>
+          <t>Philly Fed CAPEX IndexJAN</t>
         </is>
       </c>
       <c r="C171" t="inlineStr">
         <is>
-          <t>1.8%</t>
+          <t>39.00</t>
         </is>
       </c>
       <c r="D171" t="inlineStr">
         <is>
-          <t>0.9%</t>
+          <t>22.20</t>
         </is>
       </c>
       <c r="E171" t="inlineStr"/>
-      <c r="F171" t="inlineStr">
-        <is>
-          <t>1.9%</t>
-        </is>
-      </c>
+      <c r="F171" t="inlineStr"/>
       <c r="G171" t="n">
         <v>3</v>
       </c>
@@ -5367,29 +5363,21 @@
       </c>
       <c r="B172" t="inlineStr">
         <is>
-          <t>Retail Sales Ex Gas/Autos MoMDEC</t>
+          <t>Philly Fed New OrdersJAN</t>
         </is>
       </c>
       <c r="C172" t="inlineStr">
         <is>
-          <t>0.3%</t>
+          <t>42.9</t>
         </is>
       </c>
       <c r="D172" t="inlineStr">
         <is>
-          <t>0.2%</t>
-        </is>
-      </c>
-      <c r="E172" t="inlineStr">
-        <is>
-          <t>0.4%</t>
-        </is>
-      </c>
-      <c r="F172" t="inlineStr">
-        <is>
-          <t>0.4%</t>
-        </is>
-      </c>
+          <t>-3.6</t>
+        </is>
+      </c>
+      <c r="E172" t="inlineStr"/>
+      <c r="F172" t="inlineStr"/>
       <c r="G172" t="n">
         <v>3</v>
       </c>
@@ -5402,23 +5390,31 @@
       </c>
       <c r="B173" t="inlineStr">
         <is>
-          <t>Philly Fed Business ConditionsJAN</t>
+          <t>Retail Sales MoMDEC</t>
         </is>
       </c>
       <c r="C173" t="inlineStr">
         <is>
-          <t>46.3</t>
+          <t>0.4%</t>
         </is>
       </c>
       <c r="D173" t="inlineStr">
         <is>
-          <t>33.8</t>
-        </is>
-      </c>
-      <c r="E173" t="inlineStr"/>
-      <c r="F173" t="inlineStr"/>
+          <t>0.8%</t>
+        </is>
+      </c>
+      <c r="E173" t="inlineStr">
+        <is>
+          <t>0.6%</t>
+        </is>
+      </c>
+      <c r="F173" t="inlineStr">
+        <is>
+          <t>0.5%</t>
+        </is>
+      </c>
       <c r="G173" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="174">
@@ -5429,27 +5425,27 @@
       </c>
       <c r="B174" t="inlineStr">
         <is>
-          <t>Retail Sales Ex Autos MoMDEC</t>
+          <t>Philadelphia Fed Manufacturing IndexJAN</t>
         </is>
       </c>
       <c r="C174" t="inlineStr">
         <is>
-          <t>0.4%</t>
+          <t>44.3</t>
         </is>
       </c>
       <c r="D174" t="inlineStr">
         <is>
-          <t>0.2%</t>
+          <t>-10.9</t>
         </is>
       </c>
       <c r="E174" t="inlineStr">
         <is>
-          <t>0.4%</t>
+          <t>-5</t>
         </is>
       </c>
       <c r="F174" t="inlineStr">
         <is>
-          <t>0.4%</t>
+          <t>-10</t>
         </is>
       </c>
       <c r="G174" t="n">
@@ -5464,17 +5460,17 @@
       </c>
       <c r="B175" t="inlineStr">
         <is>
-          <t>Philly Fed Prices PaidJAN</t>
+          <t>Philly Fed EmploymentJAN</t>
         </is>
       </c>
       <c r="C175" t="inlineStr">
         <is>
-          <t>31.90</t>
+          <t>11.9</t>
         </is>
       </c>
       <c r="D175" t="inlineStr">
         <is>
-          <t>26.60</t>
+          <t>4.8</t>
         </is>
       </c>
       <c r="E175" t="inlineStr"/>
@@ -5491,27 +5487,31 @@
       </c>
       <c r="B176" t="inlineStr">
         <is>
-          <t>Retail Sales YoYDEC</t>
+          <t>Import Prices MoMDEC</t>
         </is>
       </c>
       <c r="C176" t="inlineStr">
         <is>
-          <t>3.9%</t>
+          <t>0.1%</t>
         </is>
       </c>
       <c r="D176" t="inlineStr">
         <is>
-          <t>4.1%</t>
-        </is>
-      </c>
-      <c r="E176" t="inlineStr"/>
+          <t>0.1%</t>
+        </is>
+      </c>
+      <c r="E176" t="inlineStr">
+        <is>
+          <t>0.1%</t>
+        </is>
+      </c>
       <c r="F176" t="inlineStr">
         <is>
-          <t>4.0%</t>
+          <t>0.1%</t>
         </is>
       </c>
       <c r="G176" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="177">
@@ -5522,27 +5522,23 @@
       </c>
       <c r="B177" t="inlineStr">
         <is>
-          <t>Continuing Jobless ClaimsJAN/04</t>
+          <t>Jobless Claims 4-week AverageJAN/11</t>
         </is>
       </c>
       <c r="C177" t="inlineStr">
         <is>
-          <t>1859K</t>
+          <t>212.75K</t>
         </is>
       </c>
       <c r="D177" t="inlineStr">
         <is>
-          <t>1867K</t>
-        </is>
-      </c>
-      <c r="E177" t="inlineStr">
-        <is>
-          <t>1870K</t>
-        </is>
-      </c>
+          <t>213.5K</t>
+        </is>
+      </c>
+      <c r="E177" t="inlineStr"/>
       <c r="F177" t="inlineStr">
         <is>
-          <t>1870.0K</t>
+          <t>215.0K</t>
         </is>
       </c>
       <c r="G177" t="n">
@@ -5557,27 +5553,27 @@
       </c>
       <c r="B178" t="inlineStr">
         <is>
-          <t>Export Prices MoMDEC</t>
+          <t>Initial Jobless ClaimsJAN/11</t>
         </is>
       </c>
       <c r="C178" t="inlineStr">
         <is>
-          <t>0.3%</t>
+          <t>217K</t>
         </is>
       </c>
       <c r="D178" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>203K</t>
         </is>
       </c>
       <c r="E178" t="inlineStr">
         <is>
-          <t>0.2%</t>
+          <t>210K</t>
         </is>
       </c>
       <c r="F178" t="inlineStr">
         <is>
-          <t>0.5%</t>
+          <t>209.0K</t>
         </is>
       </c>
       <c r="G178" t="n">
@@ -5592,27 +5588,23 @@
       </c>
       <c r="B179" t="inlineStr">
         <is>
-          <t>Import Prices YoYDEC</t>
+          <t>Export Prices YoYDEC</t>
         </is>
       </c>
       <c r="C179" t="inlineStr">
         <is>
-          <t>2.2%</t>
+          <t>1.8%</t>
         </is>
       </c>
       <c r="D179" t="inlineStr">
         <is>
-          <t>1.4%</t>
-        </is>
-      </c>
-      <c r="E179" t="inlineStr">
-        <is>
-          <t>2.1%</t>
-        </is>
-      </c>
+          <t>0.9%</t>
+        </is>
+      </c>
+      <c r="E179" t="inlineStr"/>
       <c r="F179" t="inlineStr">
         <is>
-          <t>1.6%</t>
+          <t>1.9%</t>
         </is>
       </c>
       <c r="G179" t="n">
@@ -5627,27 +5619,27 @@
       </c>
       <c r="B180" t="inlineStr">
         <is>
-          <t>Initial Jobless ClaimsJAN/11</t>
+          <t>Export Prices MoMDEC</t>
         </is>
       </c>
       <c r="C180" t="inlineStr">
         <is>
-          <t>217K</t>
+          <t>0.3%</t>
         </is>
       </c>
       <c r="D180" t="inlineStr">
         <is>
-          <t>203K</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="E180" t="inlineStr">
         <is>
-          <t>210K</t>
+          <t>0.2%</t>
         </is>
       </c>
       <c r="F180" t="inlineStr">
         <is>
-          <t>209.0K</t>
+          <t>0.5%</t>
         </is>
       </c>
       <c r="G180" t="n">
@@ -5662,21 +5654,29 @@
       </c>
       <c r="B181" t="inlineStr">
         <is>
-          <t>Philly Fed CAPEX IndexJAN</t>
+          <t>Retail Sales Ex Gas/Autos MoMDEC</t>
         </is>
       </c>
       <c r="C181" t="inlineStr">
         <is>
-          <t>39.00</t>
+          <t>0.3%</t>
         </is>
       </c>
       <c r="D181" t="inlineStr">
         <is>
-          <t>22.20</t>
-        </is>
-      </c>
-      <c r="E181" t="inlineStr"/>
-      <c r="F181" t="inlineStr"/>
+          <t>0.2%</t>
+        </is>
+      </c>
+      <c r="E181" t="inlineStr">
+        <is>
+          <t>0.4%</t>
+        </is>
+      </c>
+      <c r="F181" t="inlineStr">
+        <is>
+          <t>0.4%</t>
+        </is>
+      </c>
       <c r="G181" t="n">
         <v>3</v>
       </c>
@@ -5689,31 +5689,23 @@
       </c>
       <c r="B182" t="inlineStr">
         <is>
-          <t>Import Prices MoMDEC</t>
+          <t>Philly Fed Business ConditionsJAN</t>
         </is>
       </c>
       <c r="C182" t="inlineStr">
         <is>
-          <t>0.1%</t>
+          <t>46.3</t>
         </is>
       </c>
       <c r="D182" t="inlineStr">
         <is>
-          <t>0.1%</t>
-        </is>
-      </c>
-      <c r="E182" t="inlineStr">
-        <is>
-          <t>0.1%</t>
-        </is>
-      </c>
-      <c r="F182" t="inlineStr">
-        <is>
-          <t>0.1%</t>
-        </is>
-      </c>
+          <t>33.8</t>
+        </is>
+      </c>
+      <c r="E182" t="inlineStr"/>
+      <c r="F182" t="inlineStr"/>
       <c r="G182" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="183">
@@ -5724,23 +5716,31 @@
       </c>
       <c r="B183" t="inlineStr">
         <is>
-          <t>Philly Fed EmploymentJAN</t>
+          <t>Retail Sales Ex Autos MoMDEC</t>
         </is>
       </c>
       <c r="C183" t="inlineStr">
         <is>
-          <t>11.9</t>
+          <t>0.4%</t>
         </is>
       </c>
       <c r="D183" t="inlineStr">
         <is>
-          <t>4.8</t>
-        </is>
-      </c>
-      <c r="E183" t="inlineStr"/>
-      <c r="F183" t="inlineStr"/>
+          <t>0.2%</t>
+        </is>
+      </c>
+      <c r="E183" t="inlineStr">
+        <is>
+          <t>0.4%</t>
+        </is>
+      </c>
+      <c r="F183" t="inlineStr">
+        <is>
+          <t>0.4%</t>
+        </is>
+      </c>
       <c r="G183" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="184">
@@ -5751,31 +5751,31 @@
       </c>
       <c r="B184" t="inlineStr">
         <is>
-          <t>Philadelphia Fed Manufacturing IndexJAN</t>
+          <t>Import Prices YoYDEC</t>
         </is>
       </c>
       <c r="C184" t="inlineStr">
         <is>
-          <t>44.3</t>
+          <t>2.2%</t>
         </is>
       </c>
       <c r="D184" t="inlineStr">
         <is>
-          <t>-10.9</t>
+          <t>1.4%</t>
         </is>
       </c>
       <c r="E184" t="inlineStr">
         <is>
-          <t>-5</t>
+          <t>2.1%</t>
         </is>
       </c>
       <c r="F184" t="inlineStr">
         <is>
-          <t>-10</t>
+          <t>1.6%</t>
         </is>
       </c>
       <c r="G184" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="185">
@@ -5786,31 +5786,27 @@
       </c>
       <c r="B185" t="inlineStr">
         <is>
-          <t>Retail Sales MoMDEC</t>
+          <t>Retail Sales YoYDEC</t>
         </is>
       </c>
       <c r="C185" t="inlineStr">
         <is>
-          <t>0.4%</t>
+          <t>3.9%</t>
         </is>
       </c>
       <c r="D185" t="inlineStr">
         <is>
-          <t>0.8%</t>
-        </is>
-      </c>
-      <c r="E185" t="inlineStr">
-        <is>
-          <t>0.6%</t>
-        </is>
-      </c>
+          <t>4.1%</t>
+        </is>
+      </c>
+      <c r="E185" t="inlineStr"/>
       <c r="F185" t="inlineStr">
         <is>
-          <t>0.5%</t>
+          <t>4.0%</t>
         </is>
       </c>
       <c r="G185" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="186">
@@ -5821,21 +5817,29 @@
       </c>
       <c r="B186" t="inlineStr">
         <is>
-          <t>Philly Fed New OrdersJAN</t>
+          <t>Continuing Jobless ClaimsJAN/04</t>
         </is>
       </c>
       <c r="C186" t="inlineStr">
         <is>
-          <t>42.9</t>
+          <t>1859K</t>
         </is>
       </c>
       <c r="D186" t="inlineStr">
         <is>
-          <t>-3.6</t>
-        </is>
-      </c>
-      <c r="E186" t="inlineStr"/>
-      <c r="F186" t="inlineStr"/>
+          <t>1867K</t>
+        </is>
+      </c>
+      <c r="E186" t="inlineStr">
+        <is>
+          <t>1870K</t>
+        </is>
+      </c>
+      <c r="F186" t="inlineStr">
+        <is>
+          <t>1870.0K</t>
+        </is>
+      </c>
       <c r="G186" t="n">
         <v>3</v>
       </c>
@@ -5848,25 +5852,21 @@
       </c>
       <c r="B187" t="inlineStr">
         <is>
-          <t>Jobless Claims 4-week AverageJAN/11</t>
+          <t>Philly Fed Prices PaidJAN</t>
         </is>
       </c>
       <c r="C187" t="inlineStr">
         <is>
-          <t>212.75K</t>
+          <t>31.90</t>
         </is>
       </c>
       <c r="D187" t="inlineStr">
         <is>
-          <t>213.5K</t>
+          <t>26.60</t>
         </is>
       </c>
       <c r="E187" t="inlineStr"/>
-      <c r="F187" t="inlineStr">
-        <is>
-          <t>215.0K</t>
-        </is>
-      </c>
+      <c r="F187" t="inlineStr"/>
       <c r="G187" t="n">
         <v>3</v>
       </c>
@@ -6282,31 +6282,31 @@
       </c>
       <c r="B201" t="inlineStr">
         <is>
-          <t>Manufacturing Production MoMDEC</t>
+          <t>Industrial Production MoMDEC</t>
         </is>
       </c>
       <c r="C201" t="inlineStr">
         <is>
-          <t>0.6%</t>
+          <t>0.9%</t>
         </is>
       </c>
       <c r="D201" t="inlineStr">
         <is>
-          <t>0.4%</t>
+          <t>0.2%</t>
         </is>
       </c>
       <c r="E201" t="inlineStr">
         <is>
-          <t>0.2%</t>
+          <t>0.3%</t>
         </is>
       </c>
       <c r="F201" t="inlineStr">
         <is>
-          <t>0.4%</t>
+          <t>0.1%</t>
         </is>
       </c>
       <c r="G201" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="202">
@@ -6317,23 +6317,27 @@
       </c>
       <c r="B202" t="inlineStr">
         <is>
-          <t>Manufacturing Production YoYDEC</t>
+          <t>Capacity UtilizationDEC</t>
         </is>
       </c>
       <c r="C202" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>77.6%</t>
         </is>
       </c>
       <c r="D202" t="inlineStr">
         <is>
-          <t>-0.6%</t>
-        </is>
-      </c>
-      <c r="E202" t="inlineStr"/>
+          <t>77%</t>
+        </is>
+      </c>
+      <c r="E202" t="inlineStr">
+        <is>
+          <t>77%</t>
+        </is>
+      </c>
       <c r="F202" t="inlineStr">
         <is>
-          <t>-0.7%</t>
+          <t>76.9%</t>
         </is>
       </c>
       <c r="G202" t="n">
@@ -6348,12 +6352,12 @@
       </c>
       <c r="B203" t="inlineStr">
         <is>
-          <t>Industrial Production YoYDEC</t>
+          <t>Manufacturing Production YoYDEC</t>
         </is>
       </c>
       <c r="C203" t="inlineStr">
         <is>
-          <t>0.5%</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="D203" t="inlineStr">
@@ -6364,7 +6368,7 @@
       <c r="E203" t="inlineStr"/>
       <c r="F203" t="inlineStr">
         <is>
-          <t>-0.5%</t>
+          <t>-0.7%</t>
         </is>
       </c>
       <c r="G203" t="n">
@@ -6379,27 +6383,27 @@
       </c>
       <c r="B204" t="inlineStr">
         <is>
-          <t>Capacity UtilizationDEC</t>
+          <t>Manufacturing Production MoMDEC</t>
         </is>
       </c>
       <c r="C204" t="inlineStr">
         <is>
-          <t>77.6%</t>
+          <t>0.6%</t>
         </is>
       </c>
       <c r="D204" t="inlineStr">
         <is>
-          <t>77%</t>
+          <t>0.4%</t>
         </is>
       </c>
       <c r="E204" t="inlineStr">
         <is>
-          <t>77%</t>
+          <t>0.2%</t>
         </is>
       </c>
       <c r="F204" t="inlineStr">
         <is>
-          <t>76.9%</t>
+          <t>0.4%</t>
         </is>
       </c>
       <c r="G204" t="n">
@@ -6414,31 +6418,27 @@
       </c>
       <c r="B205" t="inlineStr">
         <is>
-          <t>Industrial Production MoMDEC</t>
+          <t>Industrial Production YoYDEC</t>
         </is>
       </c>
       <c r="C205" t="inlineStr">
         <is>
-          <t>0.9%</t>
+          <t>0.5%</t>
         </is>
       </c>
       <c r="D205" t="inlineStr">
         <is>
-          <t>0.2%</t>
-        </is>
-      </c>
-      <c r="E205" t="inlineStr">
-        <is>
-          <t>0.3%</t>
-        </is>
-      </c>
+          <t>-0.6%</t>
+        </is>
+      </c>
+      <c r="E205" t="inlineStr"/>
       <c r="F205" t="inlineStr">
         <is>
-          <t>0.1%</t>
+          <t>-0.5%</t>
         </is>
       </c>
       <c r="G205" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="206">
@@ -6661,17 +6661,17 @@
       </c>
       <c r="B214" t="inlineStr">
         <is>
-          <t>42-Day Bill Auction</t>
+          <t>52-Week Bill Auction</t>
         </is>
       </c>
       <c r="C214" t="inlineStr">
         <is>
-          <t>4.250%</t>
+          <t>4.025%</t>
         </is>
       </c>
       <c r="D214" t="inlineStr">
         <is>
-          <t>4.210%</t>
+          <t>4.070%</t>
         </is>
       </c>
       <c r="E214" t="inlineStr"/>
@@ -6688,17 +6688,17 @@
       </c>
       <c r="B215" t="inlineStr">
         <is>
-          <t>52-Week Bill Auction</t>
+          <t>42-Day Bill Auction</t>
         </is>
       </c>
       <c r="C215" t="inlineStr">
         <is>
-          <t>4.025%</t>
+          <t>4.250%</t>
         </is>
       </c>
       <c r="D215" t="inlineStr">
         <is>
-          <t>4.070%</t>
+          <t>4.210%</t>
         </is>
       </c>
       <c r="E215" t="inlineStr"/>
@@ -6993,23 +6993,27 @@
       </c>
       <c r="B226" t="inlineStr">
         <is>
-          <t>Jobless Claims 4-week AverageJAN/18</t>
+          <t>Continuing Jobless ClaimsJAN/11</t>
         </is>
       </c>
       <c r="C226" t="inlineStr">
         <is>
-          <t>213.5K</t>
+          <t>1899K</t>
         </is>
       </c>
       <c r="D226" t="inlineStr">
         <is>
-          <t>212.75K</t>
-        </is>
-      </c>
-      <c r="E226" t="inlineStr"/>
+          <t>1853K</t>
+        </is>
+      </c>
+      <c r="E226" t="inlineStr">
+        <is>
+          <t>1860K</t>
+        </is>
+      </c>
       <c r="F226" t="inlineStr">
         <is>
-          <t>213.0K</t>
+          <t>1861K</t>
         </is>
       </c>
       <c r="G226" t="n">
@@ -7059,27 +7063,23 @@
       </c>
       <c r="B228" t="inlineStr">
         <is>
-          <t>Continuing Jobless ClaimsJAN/11</t>
+          <t>Jobless Claims 4-week AverageJAN/18</t>
         </is>
       </c>
       <c r="C228" t="inlineStr">
         <is>
-          <t>1899K</t>
+          <t>213.5K</t>
         </is>
       </c>
       <c r="D228" t="inlineStr">
         <is>
-          <t>1853K</t>
-        </is>
-      </c>
-      <c r="E228" t="inlineStr">
-        <is>
-          <t>1860K</t>
-        </is>
-      </c>
+          <t>212.75K</t>
+        </is>
+      </c>
+      <c r="E228" t="inlineStr"/>
       <c r="F228" t="inlineStr">
         <is>
-          <t>1861K</t>
+          <t>213.0K</t>
         </is>
       </c>
       <c r="G228" t="n">
@@ -7241,23 +7241,27 @@
       </c>
       <c r="B234" t="inlineStr">
         <is>
-          <t>EIA Distillate Fuel Production ChangeJAN/17</t>
+          <t>EIA Gasoline Stocks ChangeJAN/17</t>
         </is>
       </c>
       <c r="C234" t="inlineStr">
         <is>
-          <t>-0.473M</t>
+          <t>2.332M</t>
         </is>
       </c>
       <c r="D234" t="inlineStr">
         <is>
-          <t>-0.021M</t>
-        </is>
-      </c>
-      <c r="E234" t="inlineStr"/>
+          <t>5.852M</t>
+        </is>
+      </c>
+      <c r="E234" t="inlineStr">
+        <is>
+          <t>2.5M</t>
+        </is>
+      </c>
       <c r="F234" t="inlineStr"/>
       <c r="G234" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="235">
@@ -7268,24 +7272,20 @@
       </c>
       <c r="B235" t="inlineStr">
         <is>
-          <t>EIA Distillate Stocks ChangeJAN/17</t>
+          <t>EIA Refinery Crude Runs ChangeJAN/17</t>
         </is>
       </c>
       <c r="C235" t="inlineStr">
         <is>
-          <t>-3.07M</t>
+          <t>-1.125M</t>
         </is>
       </c>
       <c r="D235" t="inlineStr">
         <is>
-          <t>3.077M</t>
-        </is>
-      </c>
-      <c r="E235" t="inlineStr">
-        <is>
-          <t>0.6M</t>
-        </is>
-      </c>
+          <t>-0.255M</t>
+        </is>
+      </c>
+      <c r="E235" t="inlineStr"/>
       <c r="F235" t="inlineStr"/>
       <c r="G235" t="n">
         <v>3</v>
@@ -7299,17 +7299,17 @@
       </c>
       <c r="B236" t="inlineStr">
         <is>
-          <t>EIA Heating Oil Stocks ChangeJAN/17</t>
+          <t>EIA Crude Oil Imports ChangeJAN/17</t>
         </is>
       </c>
       <c r="C236" t="inlineStr">
         <is>
-          <t>0.068M</t>
+          <t>0.184M</t>
         </is>
       </c>
       <c r="D236" t="inlineStr">
         <is>
-          <t>0.646M</t>
+          <t>-1.304M</t>
         </is>
       </c>
       <c r="E236" t="inlineStr"/>
@@ -7326,23 +7326,27 @@
       </c>
       <c r="B237" t="inlineStr">
         <is>
-          <t>EIA Gasoline Production ChangeJAN/17</t>
+          <t>EIA Crude Oil Stocks ChangeJAN/17</t>
         </is>
       </c>
       <c r="C237" t="inlineStr">
         <is>
-          <t>-0.043M</t>
+          <t>-1.017M</t>
         </is>
       </c>
       <c r="D237" t="inlineStr">
         <is>
-          <t>0.397M</t>
-        </is>
-      </c>
-      <c r="E237" t="inlineStr"/>
+          <t>-1.962M</t>
+        </is>
+      </c>
+      <c r="E237" t="inlineStr">
+        <is>
+          <t>-2.1M</t>
+        </is>
+      </c>
       <c r="F237" t="inlineStr"/>
       <c r="G237" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="238">
@@ -7353,17 +7357,17 @@
       </c>
       <c r="B238" t="inlineStr">
         <is>
-          <t>30-Year Mortgage RateJAN/23</t>
+          <t>15-Year Mortgage RateJAN/23</t>
         </is>
       </c>
       <c r="C238" t="inlineStr">
         <is>
-          <t>6.96%</t>
+          <t>6.16%</t>
         </is>
       </c>
       <c r="D238" t="inlineStr">
         <is>
-          <t>7.04%</t>
+          <t>6.27%</t>
         </is>
       </c>
       <c r="E238" t="inlineStr"/>
@@ -7380,17 +7384,17 @@
       </c>
       <c r="B239" t="inlineStr">
         <is>
-          <t>15-Year Mortgage RateJAN/23</t>
+          <t>EIA Cushing Crude Oil Stocks ChangeJAN/17</t>
         </is>
       </c>
       <c r="C239" t="inlineStr">
         <is>
-          <t>6.16%</t>
+          <t>-0.148M</t>
         </is>
       </c>
       <c r="D239" t="inlineStr">
         <is>
-          <t>6.27%</t>
+          <t>0.765M</t>
         </is>
       </c>
       <c r="E239" t="inlineStr"/>
@@ -7407,17 +7411,17 @@
       </c>
       <c r="B240" t="inlineStr">
         <is>
-          <t>EIA Cushing Crude Oil Stocks ChangeJAN/17</t>
+          <t>EIA Gasoline Production ChangeJAN/17</t>
         </is>
       </c>
       <c r="C240" t="inlineStr">
         <is>
-          <t>-0.148M</t>
+          <t>-0.043M</t>
         </is>
       </c>
       <c r="D240" t="inlineStr">
         <is>
-          <t>0.765M</t>
+          <t>0.397M</t>
         </is>
       </c>
       <c r="E240" t="inlineStr"/>
@@ -7434,27 +7438,23 @@
       </c>
       <c r="B241" t="inlineStr">
         <is>
-          <t>EIA Crude Oil Stocks ChangeJAN/17</t>
+          <t>EIA Heating Oil Stocks ChangeJAN/17</t>
         </is>
       </c>
       <c r="C241" t="inlineStr">
         <is>
-          <t>-1.017M</t>
+          <t>0.068M</t>
         </is>
       </c>
       <c r="D241" t="inlineStr">
         <is>
-          <t>-1.962M</t>
-        </is>
-      </c>
-      <c r="E241" t="inlineStr">
-        <is>
-          <t>-2.1M</t>
-        </is>
-      </c>
+          <t>0.646M</t>
+        </is>
+      </c>
+      <c r="E241" t="inlineStr"/>
       <c r="F241" t="inlineStr"/>
       <c r="G241" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="242">
@@ -7465,20 +7465,24 @@
       </c>
       <c r="B242" t="inlineStr">
         <is>
-          <t>EIA Crude Oil Imports ChangeJAN/17</t>
+          <t>EIA Distillate Stocks ChangeJAN/17</t>
         </is>
       </c>
       <c r="C242" t="inlineStr">
         <is>
-          <t>0.184M</t>
+          <t>-3.07M</t>
         </is>
       </c>
       <c r="D242" t="inlineStr">
         <is>
-          <t>-1.304M</t>
-        </is>
-      </c>
-      <c r="E242" t="inlineStr"/>
+          <t>3.077M</t>
+        </is>
+      </c>
+      <c r="E242" t="inlineStr">
+        <is>
+          <t>0.6M</t>
+        </is>
+      </c>
       <c r="F242" t="inlineStr"/>
       <c r="G242" t="n">
         <v>3</v>
@@ -7492,17 +7496,17 @@
       </c>
       <c r="B243" t="inlineStr">
         <is>
-          <t>EIA Refinery Crude Runs ChangeJAN/17</t>
+          <t>EIA Distillate Fuel Production ChangeJAN/17</t>
         </is>
       </c>
       <c r="C243" t="inlineStr">
         <is>
-          <t>-1.125M</t>
+          <t>-0.473M</t>
         </is>
       </c>
       <c r="D243" t="inlineStr">
         <is>
-          <t>-0.255M</t>
+          <t>-0.021M</t>
         </is>
       </c>
       <c r="E243" t="inlineStr"/>
@@ -7519,27 +7523,23 @@
       </c>
       <c r="B244" t="inlineStr">
         <is>
-          <t>EIA Gasoline Stocks ChangeJAN/17</t>
+          <t>30-Year Mortgage RateJAN/23</t>
         </is>
       </c>
       <c r="C244" t="inlineStr">
         <is>
-          <t>2.332M</t>
+          <t>6.96%</t>
         </is>
       </c>
       <c r="D244" t="inlineStr">
         <is>
-          <t>5.852M</t>
-        </is>
-      </c>
-      <c r="E244" t="inlineStr">
-        <is>
-          <t>2.5M</t>
-        </is>
-      </c>
+          <t>7.04%</t>
+        </is>
+      </c>
+      <c r="E244" t="inlineStr"/>
       <c r="F244" t="inlineStr"/>
       <c r="G244" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="245">
@@ -7705,27 +7705,27 @@
       </c>
       <c r="B250" t="inlineStr">
         <is>
-          <t>Michigan 5 Year Inflation Expectations FinalJAN</t>
+          <t>Michigan Current Conditions FinalJAN</t>
         </is>
       </c>
       <c r="C250" t="inlineStr">
         <is>
-          <t>3.2%</t>
+          <t>74.0</t>
         </is>
       </c>
       <c r="D250" t="inlineStr">
         <is>
-          <t>3%</t>
+          <t>75.1</t>
         </is>
       </c>
       <c r="E250" t="inlineStr">
         <is>
-          <t>3.3%</t>
+          <t>77.9</t>
         </is>
       </c>
       <c r="F250" t="inlineStr">
         <is>
-          <t>3.3%</t>
+          <t>77.9</t>
         </is>
       </c>
       <c r="G250" t="n">
@@ -7740,27 +7740,31 @@
       </c>
       <c r="B251" t="inlineStr">
         <is>
-          <t>Existing Home Sales MoMDEC</t>
+          <t>Michigan Inflation Expectations FinalJAN</t>
         </is>
       </c>
       <c r="C251" t="inlineStr">
         <is>
-          <t>2.2%</t>
+          <t>3.3%</t>
         </is>
       </c>
       <c r="D251" t="inlineStr">
         <is>
-          <t>4.8%</t>
-        </is>
-      </c>
-      <c r="E251" t="inlineStr"/>
+          <t>2.8%</t>
+        </is>
+      </c>
+      <c r="E251" t="inlineStr">
+        <is>
+          <t>3.3%</t>
+        </is>
+      </c>
       <c r="F251" t="inlineStr">
         <is>
-          <t>0.3%</t>
+          <t>3.3%</t>
         </is>
       </c>
       <c r="G251" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="252">
@@ -7771,31 +7775,31 @@
       </c>
       <c r="B252" t="inlineStr">
         <is>
-          <t>Michigan Consumer Expectations FinalJAN</t>
+          <t>Existing Home SalesDEC</t>
         </is>
       </c>
       <c r="C252" t="inlineStr">
         <is>
-          <t>69.3</t>
+          <t>4.24M</t>
         </is>
       </c>
       <c r="D252" t="inlineStr">
         <is>
-          <t>73.3</t>
+          <t>4.15M</t>
         </is>
       </c>
       <c r="E252" t="inlineStr">
         <is>
-          <t>70.2</t>
+          <t>4.19M</t>
         </is>
       </c>
       <c r="F252" t="inlineStr">
         <is>
-          <t>70.2</t>
+          <t>4.1M</t>
         </is>
       </c>
       <c r="G252" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="253">
@@ -7806,31 +7810,31 @@
       </c>
       <c r="B253" t="inlineStr">
         <is>
-          <t>Existing Home SalesDEC</t>
+          <t>Michigan Consumer Sentiment FinalJAN</t>
         </is>
       </c>
       <c r="C253" t="inlineStr">
         <is>
-          <t>4.24M</t>
+          <t>71.1</t>
         </is>
       </c>
       <c r="D253" t="inlineStr">
         <is>
-          <t>4.15M</t>
+          <t>74.0</t>
         </is>
       </c>
       <c r="E253" t="inlineStr">
         <is>
-          <t>4.19M</t>
+          <t>73.2</t>
         </is>
       </c>
       <c r="F253" t="inlineStr">
         <is>
-          <t>4.1M</t>
+          <t>73.2</t>
         </is>
       </c>
       <c r="G253" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="254">
@@ -7841,31 +7845,27 @@
       </c>
       <c r="B254" t="inlineStr">
         <is>
-          <t>Michigan Current Conditions FinalJAN</t>
+          <t>Existing Home Sales MoMDEC</t>
         </is>
       </c>
       <c r="C254" t="inlineStr">
         <is>
-          <t>74.0</t>
+          <t>2.2%</t>
         </is>
       </c>
       <c r="D254" t="inlineStr">
         <is>
-          <t>75.1</t>
-        </is>
-      </c>
-      <c r="E254" t="inlineStr">
-        <is>
-          <t>77.9</t>
-        </is>
-      </c>
+          <t>4.8%</t>
+        </is>
+      </c>
+      <c r="E254" t="inlineStr"/>
       <c r="F254" t="inlineStr">
         <is>
-          <t>77.9</t>
+          <t>0.3%</t>
         </is>
       </c>
       <c r="G254" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="255">
@@ -7876,31 +7876,31 @@
       </c>
       <c r="B255" t="inlineStr">
         <is>
-          <t>Michigan Consumer Sentiment FinalJAN</t>
+          <t>Michigan Consumer Expectations FinalJAN</t>
         </is>
       </c>
       <c r="C255" t="inlineStr">
         <is>
-          <t>71.1</t>
+          <t>69.3</t>
         </is>
       </c>
       <c r="D255" t="inlineStr">
         <is>
-          <t>74.0</t>
+          <t>73.3</t>
         </is>
       </c>
       <c r="E255" t="inlineStr">
         <is>
-          <t>73.2</t>
+          <t>70.2</t>
         </is>
       </c>
       <c r="F255" t="inlineStr">
         <is>
-          <t>73.2</t>
+          <t>70.2</t>
         </is>
       </c>
       <c r="G255" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="256">
@@ -7911,17 +7911,17 @@
       </c>
       <c r="B256" t="inlineStr">
         <is>
-          <t>Michigan Inflation Expectations FinalJAN</t>
+          <t>Michigan 5 Year Inflation Expectations FinalJAN</t>
         </is>
       </c>
       <c r="C256" t="inlineStr">
         <is>
-          <t>3.3%</t>
+          <t>3.2%</t>
         </is>
       </c>
       <c r="D256" t="inlineStr">
         <is>
-          <t>2.8%</t>
+          <t>3%</t>
         </is>
       </c>
       <c r="E256" t="inlineStr">
@@ -8252,17 +8252,17 @@
       </c>
       <c r="B267" t="inlineStr">
         <is>
-          <t>5-Year Note Auction</t>
+          <t>3-Month Bill Auction</t>
         </is>
       </c>
       <c r="C267" t="inlineStr">
         <is>
-          <t>4.33%</t>
+          <t>4.195%</t>
         </is>
       </c>
       <c r="D267" t="inlineStr">
         <is>
-          <t>4.478%</t>
+          <t>4.215%</t>
         </is>
       </c>
       <c r="E267" t="inlineStr"/>
@@ -8279,17 +8279,17 @@
       </c>
       <c r="B268" t="inlineStr">
         <is>
-          <t>3-Month Bill Auction</t>
+          <t>5-Year Note Auction</t>
         </is>
       </c>
       <c r="C268" t="inlineStr">
         <is>
-          <t>4.195%</t>
+          <t>4.33%</t>
         </is>
       </c>
       <c r="D268" t="inlineStr">
         <is>
-          <t>4.215%</t>
+          <t>4.478%</t>
         </is>
       </c>
       <c r="E268" t="inlineStr"/>
@@ -8632,27 +8632,23 @@
       </c>
       <c r="B279" t="inlineStr">
         <is>
-          <t>Richmond Fed Manufacturing IndexJAN</t>
+          <t>Richmond Fed Manufacturing Shipments IndexJAN</t>
         </is>
       </c>
       <c r="C279" t="inlineStr">
         <is>
-          <t>-4</t>
+          <t>-9</t>
         </is>
       </c>
       <c r="D279" t="inlineStr">
         <is>
-          <t>-10</t>
-        </is>
-      </c>
-      <c r="E279" t="inlineStr">
-        <is>
-          <t>-8</t>
-        </is>
-      </c>
+          <t>-11</t>
+        </is>
+      </c>
+      <c r="E279" t="inlineStr"/>
       <c r="F279" t="inlineStr">
         <is>
-          <t>-8</t>
+          <t>-9</t>
         </is>
       </c>
       <c r="G279" t="n">
@@ -8667,31 +8663,31 @@
       </c>
       <c r="B280" t="inlineStr">
         <is>
-          <t>CB Consumer ConfidenceJAN</t>
+          <t>Richmond Fed Manufacturing IndexJAN</t>
         </is>
       </c>
       <c r="C280" t="inlineStr">
         <is>
-          <t>104.1</t>
+          <t>-4</t>
         </is>
       </c>
       <c r="D280" t="inlineStr">
         <is>
-          <t>109.5</t>
+          <t>-10</t>
         </is>
       </c>
       <c r="E280" t="inlineStr">
         <is>
-          <t>105.6</t>
+          <t>-8</t>
         </is>
       </c>
       <c r="F280" t="inlineStr">
         <is>
-          <t>104</t>
+          <t>-8</t>
         </is>
       </c>
       <c r="G280" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="281">
@@ -8702,27 +8698,31 @@
       </c>
       <c r="B281" t="inlineStr">
         <is>
-          <t>Richmond Fed Services Revenues IndexJAN</t>
+          <t>CB Consumer ConfidenceJAN</t>
         </is>
       </c>
       <c r="C281" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>104.1</t>
         </is>
       </c>
       <c r="D281" t="inlineStr">
         <is>
-          <t>23</t>
-        </is>
-      </c>
-      <c r="E281" t="inlineStr"/>
+          <t>109.5</t>
+        </is>
+      </c>
+      <c r="E281" t="inlineStr">
+        <is>
+          <t>105.6</t>
+        </is>
+      </c>
       <c r="F281" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>104</t>
         </is>
       </c>
       <c r="G281" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="282">
@@ -8733,23 +8733,23 @@
       </c>
       <c r="B282" t="inlineStr">
         <is>
-          <t>Richmond Fed Manufacturing Shipments IndexJAN</t>
+          <t>Richmond Fed Services Revenues IndexJAN</t>
         </is>
       </c>
       <c r="C282" t="inlineStr">
         <is>
-          <t>-9</t>
+          <t>4</t>
         </is>
       </c>
       <c r="D282" t="inlineStr">
         <is>
-          <t>-11</t>
+          <t>23</t>
         </is>
       </c>
       <c r="E282" t="inlineStr"/>
       <c r="F282" t="inlineStr">
         <is>
-          <t>-9</t>
+          <t>21</t>
         </is>
       </c>
       <c r="G282" t="n">
@@ -8764,23 +8764,23 @@
       </c>
       <c r="B283" t="inlineStr">
         <is>
-          <t>Dallas Fed Services IndexJAN</t>
+          <t>Dallas Fed Services Revenues IndexJAN</t>
         </is>
       </c>
       <c r="C283" t="inlineStr">
         <is>
-          <t>7.4</t>
+          <t>5.7</t>
         </is>
       </c>
       <c r="D283" t="inlineStr">
         <is>
-          <t>10.8</t>
+          <t>13.9</t>
         </is>
       </c>
       <c r="E283" t="inlineStr"/>
       <c r="F283" t="inlineStr">
         <is>
-          <t>9.5</t>
+          <t>13</t>
         </is>
       </c>
       <c r="G283" t="n">
@@ -8795,23 +8795,23 @@
       </c>
       <c r="B284" t="inlineStr">
         <is>
-          <t>Dallas Fed Services Revenues IndexJAN</t>
+          <t>Dallas Fed Services IndexJAN</t>
         </is>
       </c>
       <c r="C284" t="inlineStr">
         <is>
-          <t>5.7</t>
+          <t>7.4</t>
         </is>
       </c>
       <c r="D284" t="inlineStr">
         <is>
-          <t>13.9</t>
+          <t>10.8</t>
         </is>
       </c>
       <c r="E284" t="inlineStr"/>
       <c r="F284" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>9.5</t>
         </is>
       </c>
       <c r="G284" t="n">
@@ -8965,23 +8965,23 @@
       </c>
       <c r="B290" t="inlineStr">
         <is>
-          <t>MBA 30-Year Mortgage RateJAN/24</t>
+          <t>MBA Purchase IndexJAN/24</t>
         </is>
       </c>
       <c r="C290" t="inlineStr">
         <is>
-          <t>7.02%</t>
+          <t>162.4</t>
         </is>
       </c>
       <c r="D290" t="inlineStr">
         <is>
-          <t>7.02%</t>
+          <t>163</t>
         </is>
       </c>
       <c r="E290" t="inlineStr"/>
       <c r="F290" t="inlineStr"/>
       <c r="G290" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="291">
@@ -8992,17 +8992,17 @@
       </c>
       <c r="B291" t="inlineStr">
         <is>
-          <t>MBA Mortgage Refinance IndexJAN/24</t>
+          <t>MBA Mortgage Market IndexJAN/24</t>
         </is>
       </c>
       <c r="C291" t="inlineStr">
         <is>
-          <t>520.9</t>
+          <t>220.0</t>
         </is>
       </c>
       <c r="D291" t="inlineStr">
         <is>
-          <t>558.8</t>
+          <t>224.6</t>
         </is>
       </c>
       <c r="E291" t="inlineStr"/>
@@ -9019,17 +9019,17 @@
       </c>
       <c r="B292" t="inlineStr">
         <is>
-          <t>MBA Mortgage Market IndexJAN/24</t>
+          <t>MBA Mortgage ApplicationsJAN/24</t>
         </is>
       </c>
       <c r="C292" t="inlineStr">
         <is>
-          <t>220.0</t>
+          <t>-2%</t>
         </is>
       </c>
       <c r="D292" t="inlineStr">
         <is>
-          <t>224.6</t>
+          <t>0.1%</t>
         </is>
       </c>
       <c r="E292" t="inlineStr"/>
@@ -9046,23 +9046,23 @@
       </c>
       <c r="B293" t="inlineStr">
         <is>
-          <t>MBA Mortgage ApplicationsJAN/24</t>
+          <t>MBA 30-Year Mortgage RateJAN/24</t>
         </is>
       </c>
       <c r="C293" t="inlineStr">
         <is>
-          <t>-2%</t>
+          <t>7.02%</t>
         </is>
       </c>
       <c r="D293" t="inlineStr">
         <is>
-          <t>0.1%</t>
+          <t>7.02%</t>
         </is>
       </c>
       <c r="E293" t="inlineStr"/>
       <c r="F293" t="inlineStr"/>
       <c r="G293" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="294">
@@ -9073,17 +9073,17 @@
       </c>
       <c r="B294" t="inlineStr">
         <is>
-          <t>MBA Purchase IndexJAN/24</t>
+          <t>MBA Mortgage Refinance IndexJAN/24</t>
         </is>
       </c>
       <c r="C294" t="inlineStr">
         <is>
-          <t>162.4</t>
+          <t>520.9</t>
         </is>
       </c>
       <c r="D294" t="inlineStr">
         <is>
-          <t>163</t>
+          <t>558.8</t>
         </is>
       </c>
       <c r="E294" t="inlineStr"/>
@@ -9201,20 +9201,24 @@
       </c>
       <c r="B298" t="inlineStr">
         <is>
-          <t>EIA Distillate Fuel Production ChangeJAN/24</t>
+          <t>EIA Distillate Stocks ChangeJAN/24</t>
         </is>
       </c>
       <c r="C298" t="inlineStr">
         <is>
-          <t>0.028M</t>
+          <t>-4.994M</t>
         </is>
       </c>
       <c r="D298" t="inlineStr">
         <is>
-          <t>-0.473M</t>
-        </is>
-      </c>
-      <c r="E298" t="inlineStr"/>
+          <t>-3.07M</t>
+        </is>
+      </c>
+      <c r="E298" t="inlineStr">
+        <is>
+          <t>-2.1M</t>
+        </is>
+      </c>
       <c r="F298" t="inlineStr"/>
       <c r="G298" t="n">
         <v>3</v>
@@ -9228,27 +9232,23 @@
       </c>
       <c r="B299" t="inlineStr">
         <is>
-          <t>EIA Crude Oil Stocks ChangeJAN/24</t>
+          <t>EIA Gasoline Production ChangeJAN/24</t>
         </is>
       </c>
       <c r="C299" t="inlineStr">
         <is>
-          <t>3.463M</t>
+          <t>-0.044M</t>
         </is>
       </c>
       <c r="D299" t="inlineStr">
         <is>
-          <t>-1.017M</t>
-        </is>
-      </c>
-      <c r="E299" t="inlineStr">
-        <is>
-          <t>3.2M</t>
-        </is>
-      </c>
+          <t>-0.043M</t>
+        </is>
+      </c>
+      <c r="E299" t="inlineStr"/>
       <c r="F299" t="inlineStr"/>
       <c r="G299" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="300">
@@ -9259,17 +9259,17 @@
       </c>
       <c r="B300" t="inlineStr">
         <is>
-          <t>EIA Crude Oil Imports ChangeJAN/24</t>
+          <t>EIA Cushing Crude Oil Stocks ChangeJAN/24</t>
         </is>
       </c>
       <c r="C300" t="inlineStr">
         <is>
-          <t>0.532M</t>
+          <t>0.326M</t>
         </is>
       </c>
       <c r="D300" t="inlineStr">
         <is>
-          <t>0.184M</t>
+          <t>-0.148M</t>
         </is>
       </c>
       <c r="E300" t="inlineStr"/>
@@ -9286,27 +9286,23 @@
       </c>
       <c r="B301" t="inlineStr">
         <is>
-          <t>EIA Gasoline Stocks ChangeJAN/24</t>
+          <t>EIA Heating Oil Stocks ChangeJAN/24</t>
         </is>
       </c>
       <c r="C301" t="inlineStr">
         <is>
-          <t>2.957M</t>
+          <t>0.128M</t>
         </is>
       </c>
       <c r="D301" t="inlineStr">
         <is>
-          <t>2.332M</t>
-        </is>
-      </c>
-      <c r="E301" t="inlineStr">
-        <is>
-          <t>1.5M</t>
-        </is>
-      </c>
+          <t>0.068M</t>
+        </is>
+      </c>
+      <c r="E301" t="inlineStr"/>
       <c r="F301" t="inlineStr"/>
       <c r="G301" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="302">
@@ -9317,23 +9313,27 @@
       </c>
       <c r="B302" t="inlineStr">
         <is>
-          <t>EIA Refinery Crude Runs ChangeJAN/24</t>
+          <t>EIA Crude Oil Stocks ChangeJAN/24</t>
         </is>
       </c>
       <c r="C302" t="inlineStr">
         <is>
-          <t>-0.333M</t>
+          <t>3.463M</t>
         </is>
       </c>
       <c r="D302" t="inlineStr">
         <is>
-          <t>-1.125M</t>
-        </is>
-      </c>
-      <c r="E302" t="inlineStr"/>
+          <t>-1.017M</t>
+        </is>
+      </c>
+      <c r="E302" t="inlineStr">
+        <is>
+          <t>3.2M</t>
+        </is>
+      </c>
       <c r="F302" t="inlineStr"/>
       <c r="G302" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="303">
@@ -9344,23 +9344,27 @@
       </c>
       <c r="B303" t="inlineStr">
         <is>
-          <t>EIA Heating Oil Stocks ChangeJAN/24</t>
+          <t>EIA Gasoline Stocks ChangeJAN/24</t>
         </is>
       </c>
       <c r="C303" t="inlineStr">
         <is>
-          <t>0.128M</t>
+          <t>2.957M</t>
         </is>
       </c>
       <c r="D303" t="inlineStr">
         <is>
-          <t>0.068M</t>
-        </is>
-      </c>
-      <c r="E303" t="inlineStr"/>
+          <t>2.332M</t>
+        </is>
+      </c>
+      <c r="E303" t="inlineStr">
+        <is>
+          <t>1.5M</t>
+        </is>
+      </c>
       <c r="F303" t="inlineStr"/>
       <c r="G303" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="304">
@@ -9371,24 +9375,20 @@
       </c>
       <c r="B304" t="inlineStr">
         <is>
-          <t>EIA Distillate Stocks ChangeJAN/24</t>
+          <t>EIA Crude Oil Imports ChangeJAN/24</t>
         </is>
       </c>
       <c r="C304" t="inlineStr">
         <is>
-          <t>-4.994M</t>
+          <t>0.532M</t>
         </is>
       </c>
       <c r="D304" t="inlineStr">
         <is>
-          <t>-3.07M</t>
-        </is>
-      </c>
-      <c r="E304" t="inlineStr">
-        <is>
-          <t>-2.1M</t>
-        </is>
-      </c>
+          <t>0.184M</t>
+        </is>
+      </c>
+      <c r="E304" t="inlineStr"/>
       <c r="F304" t="inlineStr"/>
       <c r="G304" t="n">
         <v>3</v>
@@ -9402,17 +9402,17 @@
       </c>
       <c r="B305" t="inlineStr">
         <is>
-          <t>EIA Cushing Crude Oil Stocks ChangeJAN/24</t>
+          <t>EIA Distillate Fuel Production ChangeJAN/24</t>
         </is>
       </c>
       <c r="C305" t="inlineStr">
         <is>
-          <t>0.326M</t>
+          <t>0.028M</t>
         </is>
       </c>
       <c r="D305" t="inlineStr">
         <is>
-          <t>-0.148M</t>
+          <t>-0.473M</t>
         </is>
       </c>
       <c r="E305" t="inlineStr"/>
@@ -9429,17 +9429,17 @@
       </c>
       <c r="B306" t="inlineStr">
         <is>
-          <t>EIA Gasoline Production ChangeJAN/24</t>
+          <t>EIA Refinery Crude Runs ChangeJAN/24</t>
         </is>
       </c>
       <c r="C306" t="inlineStr">
         <is>
-          <t>-0.044M</t>
+          <t>-0.333M</t>
         </is>
       </c>
       <c r="D306" t="inlineStr">
         <is>
-          <t>-0.043M</t>
+          <t>-1.125M</t>
         </is>
       </c>
       <c r="E306" t="inlineStr"/>
@@ -9537,27 +9537,31 @@
       </c>
       <c r="B310" t="inlineStr">
         <is>
-          <t>Real Consumer Spending QoQ AdvQ4</t>
+          <t>GDP Growth Rate QoQ AdvQ4</t>
         </is>
       </c>
       <c r="C310" t="inlineStr">
         <is>
-          <t>4.2%</t>
+          <t>2.3%</t>
         </is>
       </c>
       <c r="D310" t="inlineStr">
         <is>
-          <t>3.7%</t>
-        </is>
-      </c>
-      <c r="E310" t="inlineStr"/>
+          <t>3.1%</t>
+        </is>
+      </c>
+      <c r="E310" t="inlineStr">
+        <is>
+          <t>2.6%</t>
+        </is>
+      </c>
       <c r="F310" t="inlineStr">
         <is>
-          <t>2.9%</t>
+          <t>3%</t>
         </is>
       </c>
       <c r="G310" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="311">
@@ -9568,31 +9572,31 @@
       </c>
       <c r="B311" t="inlineStr">
         <is>
-          <t>Core PCE Prices QoQ AdvQ4</t>
+          <t>GDP Price Index QoQ AdvQ4</t>
         </is>
       </c>
       <c r="C311" t="inlineStr">
         <is>
+          <t>2.2%</t>
+        </is>
+      </c>
+      <c r="D311" t="inlineStr">
+        <is>
+          <t>1.9%</t>
+        </is>
+      </c>
+      <c r="E311" t="inlineStr">
+        <is>
           <t>2.5%</t>
         </is>
       </c>
-      <c r="D311" t="inlineStr">
-        <is>
-          <t>2.2%</t>
-        </is>
-      </c>
-      <c r="E311" t="inlineStr">
-        <is>
-          <t>2.5%</t>
-        </is>
-      </c>
       <c r="F311" t="inlineStr">
         <is>
           <t>2.3%</t>
         </is>
       </c>
       <c r="G311" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="312">
@@ -9603,31 +9607,31 @@
       </c>
       <c r="B312" t="inlineStr">
         <is>
-          <t>Continuing Jobless ClaimsJAN/18</t>
+          <t>Initial Jobless ClaimsJAN/25</t>
         </is>
       </c>
       <c r="C312" t="inlineStr">
         <is>
-          <t>1858K</t>
+          <t>207K</t>
         </is>
       </c>
       <c r="D312" t="inlineStr">
         <is>
-          <t>1900K</t>
+          <t>223K</t>
         </is>
       </c>
       <c r="E312" t="inlineStr">
         <is>
-          <t>1890K</t>
+          <t>220K</t>
         </is>
       </c>
       <c r="F312" t="inlineStr">
         <is>
-          <t>1885.0K</t>
+          <t>228.0K</t>
         </is>
       </c>
       <c r="G312" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="313">
@@ -9638,23 +9642,23 @@
       </c>
       <c r="B313" t="inlineStr">
         <is>
-          <t>GDP Sales QoQ AdvQ4</t>
+          <t>Jobless Claims 4-week AverageJAN/25</t>
         </is>
       </c>
       <c r="C313" t="inlineStr">
         <is>
-          <t>3.2%</t>
+          <t>212.5K</t>
         </is>
       </c>
       <c r="D313" t="inlineStr">
         <is>
-          <t>3.3%</t>
+          <t>213.5K</t>
         </is>
       </c>
       <c r="E313" t="inlineStr"/>
       <c r="F313" t="inlineStr">
         <is>
-          <t>2.9%</t>
+          <t>214.0K</t>
         </is>
       </c>
       <c r="G313" t="n">
@@ -9669,23 +9673,27 @@
       </c>
       <c r="B314" t="inlineStr">
         <is>
-          <t>PCE Prices QoQ AdvQ4</t>
+          <t>Continuing Jobless ClaimsJAN/18</t>
         </is>
       </c>
       <c r="C314" t="inlineStr">
         <is>
-          <t>2.3%</t>
+          <t>1858K</t>
         </is>
       </c>
       <c r="D314" t="inlineStr">
         <is>
-          <t>1.5%</t>
-        </is>
-      </c>
-      <c r="E314" t="inlineStr"/>
+          <t>1900K</t>
+        </is>
+      </c>
+      <c r="E314" t="inlineStr">
+        <is>
+          <t>1890K</t>
+        </is>
+      </c>
       <c r="F314" t="inlineStr">
         <is>
-          <t>1.1%</t>
+          <t>1885.0K</t>
         </is>
       </c>
       <c r="G314" t="n">
@@ -9700,23 +9708,23 @@
       </c>
       <c r="B315" t="inlineStr">
         <is>
-          <t>Jobless Claims 4-week AverageJAN/25</t>
+          <t>GDP Sales QoQ AdvQ4</t>
         </is>
       </c>
       <c r="C315" t="inlineStr">
         <is>
-          <t>212.5K</t>
+          <t>3.2%</t>
         </is>
       </c>
       <c r="D315" t="inlineStr">
         <is>
-          <t>213.5K</t>
+          <t>3.3%</t>
         </is>
       </c>
       <c r="E315" t="inlineStr"/>
       <c r="F315" t="inlineStr">
         <is>
-          <t>214.0K</t>
+          <t>2.9%</t>
         </is>
       </c>
       <c r="G315" t="n">
@@ -9731,7 +9739,7 @@
       </c>
       <c r="B316" t="inlineStr">
         <is>
-          <t>GDP Growth Rate QoQ AdvQ4</t>
+          <t>PCE Prices QoQ AdvQ4</t>
         </is>
       </c>
       <c r="C316" t="inlineStr">
@@ -9741,21 +9749,17 @@
       </c>
       <c r="D316" t="inlineStr">
         <is>
-          <t>3.1%</t>
-        </is>
-      </c>
-      <c r="E316" t="inlineStr">
-        <is>
-          <t>2.6%</t>
-        </is>
-      </c>
+          <t>1.5%</t>
+        </is>
+      </c>
+      <c r="E316" t="inlineStr"/>
       <c r="F316" t="inlineStr">
         <is>
-          <t>3%</t>
+          <t>1.1%</t>
         </is>
       </c>
       <c r="G316" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="317">
@@ -9766,31 +9770,31 @@
       </c>
       <c r="B317" t="inlineStr">
         <is>
-          <t>Initial Jobless ClaimsJAN/25</t>
+          <t>Core PCE Prices QoQ AdvQ4</t>
         </is>
       </c>
       <c r="C317" t="inlineStr">
         <is>
-          <t>207K</t>
+          <t>2.5%</t>
         </is>
       </c>
       <c r="D317" t="inlineStr">
         <is>
-          <t>223K</t>
+          <t>2.2%</t>
         </is>
       </c>
       <c r="E317" t="inlineStr">
         <is>
-          <t>220K</t>
+          <t>2.5%</t>
         </is>
       </c>
       <c r="F317" t="inlineStr">
         <is>
-          <t>228.0K</t>
+          <t>2.3%</t>
         </is>
       </c>
       <c r="G317" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="318">
@@ -9801,31 +9805,27 @@
       </c>
       <c r="B318" t="inlineStr">
         <is>
-          <t>GDP Price Index QoQ AdvQ4</t>
+          <t>Real Consumer Spending QoQ AdvQ4</t>
         </is>
       </c>
       <c r="C318" t="inlineStr">
         <is>
-          <t>2.2%</t>
+          <t>4.2%</t>
         </is>
       </c>
       <c r="D318" t="inlineStr">
         <is>
-          <t>1.9%</t>
-        </is>
-      </c>
-      <c r="E318" t="inlineStr">
-        <is>
-          <t>2.5%</t>
-        </is>
-      </c>
+          <t>3.7%</t>
+        </is>
+      </c>
+      <c r="E318" t="inlineStr"/>
       <c r="F318" t="inlineStr">
         <is>
-          <t>2.3%</t>
+          <t>2.9%</t>
         </is>
       </c>
       <c r="G318" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="319">
@@ -9933,17 +9933,17 @@
       </c>
       <c r="B322" t="inlineStr">
         <is>
-          <t>4-Week Bill Auction</t>
+          <t>8-Week Bill Auction</t>
         </is>
       </c>
       <c r="C322" t="inlineStr">
         <is>
+          <t>4.240%</t>
+        </is>
+      </c>
+      <c r="D322" t="inlineStr">
+        <is>
           <t>4.250%</t>
-        </is>
-      </c>
-      <c r="D322" t="inlineStr">
-        <is>
-          <t>4.265%</t>
         </is>
       </c>
       <c r="E322" t="inlineStr"/>
@@ -9960,17 +9960,17 @@
       </c>
       <c r="B323" t="inlineStr">
         <is>
-          <t>8-Week Bill Auction</t>
+          <t>4-Week Bill Auction</t>
         </is>
       </c>
       <c r="C323" t="inlineStr">
         <is>
-          <t>4.240%</t>
+          <t>4.250%</t>
         </is>
       </c>
       <c r="D323" t="inlineStr">
         <is>
-          <t>4.250%</t>
+          <t>4.265%</t>
         </is>
       </c>
       <c r="E323" t="inlineStr"/>
@@ -10068,31 +10068,27 @@
       </c>
       <c r="B327" t="inlineStr">
         <is>
-          <t>Personal Income MoMDEC</t>
+          <t>Employment Cost - Wages QoQQ4</t>
         </is>
       </c>
       <c r="C327" t="inlineStr">
         <is>
-          <t>0.4%</t>
+          <t>0.9%</t>
         </is>
       </c>
       <c r="D327" t="inlineStr">
         <is>
-          <t>0.3%</t>
-        </is>
-      </c>
-      <c r="E327" t="inlineStr">
-        <is>
-          <t>0.4%</t>
-        </is>
-      </c>
+          <t>0.8%</t>
+        </is>
+      </c>
+      <c r="E327" t="inlineStr"/>
       <c r="F327" t="inlineStr">
         <is>
-          <t>0.3%</t>
+          <t>0.7%</t>
         </is>
       </c>
       <c r="G327" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="328">
@@ -10103,31 +10099,31 @@
       </c>
       <c r="B328" t="inlineStr">
         <is>
-          <t>Personal Spending MoMDEC</t>
+          <t>PCE Price Index MoMDEC</t>
         </is>
       </c>
       <c r="C328" t="inlineStr">
         <is>
-          <t>0.7%</t>
+          <t>0.3%</t>
         </is>
       </c>
       <c r="D328" t="inlineStr">
         <is>
-          <t>0.6%</t>
+          <t>0.1%</t>
         </is>
       </c>
       <c r="E328" t="inlineStr">
         <is>
-          <t>0.5%</t>
+          <t>0.3%</t>
         </is>
       </c>
       <c r="F328" t="inlineStr">
         <is>
-          <t>0.5%</t>
+          <t>0.3%</t>
         </is>
       </c>
       <c r="G328" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="329">
@@ -10138,23 +10134,27 @@
       </c>
       <c r="B329" t="inlineStr">
         <is>
-          <t>Employment Cost - Benefits QoQQ4</t>
+          <t>PCE Price Index YoYDEC</t>
         </is>
       </c>
       <c r="C329" t="inlineStr">
         <is>
-          <t>0.8%</t>
+          <t>2.6%</t>
         </is>
       </c>
       <c r="D329" t="inlineStr">
         <is>
-          <t>0.8%</t>
-        </is>
-      </c>
-      <c r="E329" t="inlineStr"/>
+          <t>2.4%</t>
+        </is>
+      </c>
+      <c r="E329" t="inlineStr">
+        <is>
+          <t>2.6%</t>
+        </is>
+      </c>
       <c r="F329" t="inlineStr">
         <is>
-          <t>0.7%</t>
+          <t>2.6%</t>
         </is>
       </c>
       <c r="G329" t="n">
@@ -10169,15 +10169,31 @@
       </c>
       <c r="B330" t="inlineStr">
         <is>
-          <t>Fed Bowman Speech</t>
-        </is>
-      </c>
-      <c r="C330" t="inlineStr"/>
-      <c r="D330" t="inlineStr"/>
-      <c r="E330" t="inlineStr"/>
-      <c r="F330" t="inlineStr"/>
+          <t>Core PCE Price Index YoYDEC</t>
+        </is>
+      </c>
+      <c r="C330" t="inlineStr">
+        <is>
+          <t>2.8%</t>
+        </is>
+      </c>
+      <c r="D330" t="inlineStr">
+        <is>
+          <t>2.8%</t>
+        </is>
+      </c>
+      <c r="E330" t="inlineStr">
+        <is>
+          <t>2.8%</t>
+        </is>
+      </c>
+      <c r="F330" t="inlineStr">
+        <is>
+          <t>2.8%</t>
+        </is>
+      </c>
       <c r="G330" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="331">
@@ -10188,31 +10204,31 @@
       </c>
       <c r="B331" t="inlineStr">
         <is>
-          <t>Core PCE Price Index MoMDEC</t>
+          <t>Employment Cost Index QoQQ4</t>
         </is>
       </c>
       <c r="C331" t="inlineStr">
         <is>
-          <t>0.2%</t>
+          <t>0.9%</t>
         </is>
       </c>
       <c r="D331" t="inlineStr">
         <is>
-          <t>0.1%</t>
+          <t>0.8%</t>
         </is>
       </c>
       <c r="E331" t="inlineStr">
         <is>
-          <t>0.2%</t>
+          <t>0.9%</t>
         </is>
       </c>
       <c r="F331" t="inlineStr">
         <is>
-          <t>0.2%</t>
+          <t>0.7%</t>
         </is>
       </c>
       <c r="G331" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="332">
@@ -10223,31 +10239,31 @@
       </c>
       <c r="B332" t="inlineStr">
         <is>
-          <t>Employment Cost Index QoQQ4</t>
+          <t>Personal Income MoMDEC</t>
         </is>
       </c>
       <c r="C332" t="inlineStr">
         <is>
-          <t>0.9%</t>
+          <t>0.4%</t>
         </is>
       </c>
       <c r="D332" t="inlineStr">
         <is>
-          <t>0.8%</t>
+          <t>0.3%</t>
         </is>
       </c>
       <c r="E332" t="inlineStr">
         <is>
-          <t>0.9%</t>
+          <t>0.4%</t>
         </is>
       </c>
       <c r="F332" t="inlineStr">
         <is>
-          <t>0.7%</t>
+          <t>0.3%</t>
         </is>
       </c>
       <c r="G332" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="333">
@@ -10258,25 +10274,13 @@
       </c>
       <c r="B333" t="inlineStr">
         <is>
-          <t>Employment Cost - Wages QoQQ4</t>
-        </is>
-      </c>
-      <c r="C333" t="inlineStr">
-        <is>
-          <t>0.9%</t>
-        </is>
-      </c>
-      <c r="D333" t="inlineStr">
-        <is>
-          <t>0.8%</t>
-        </is>
-      </c>
+          <t>Fed Bowman Speech</t>
+        </is>
+      </c>
+      <c r="C333" t="inlineStr"/>
+      <c r="D333" t="inlineStr"/>
       <c r="E333" t="inlineStr"/>
-      <c r="F333" t="inlineStr">
-        <is>
-          <t>0.7%</t>
-        </is>
-      </c>
+      <c r="F333" t="inlineStr"/>
       <c r="G333" t="n">
         <v>2</v>
       </c>
@@ -10289,31 +10293,27 @@
       </c>
       <c r="B334" t="inlineStr">
         <is>
-          <t>Core PCE Price Index YoYDEC</t>
+          <t>Employment Cost - Benefits QoQQ4</t>
         </is>
       </c>
       <c r="C334" t="inlineStr">
         <is>
-          <t>2.8%</t>
+          <t>0.8%</t>
         </is>
       </c>
       <c r="D334" t="inlineStr">
         <is>
-          <t>2.8%</t>
-        </is>
-      </c>
-      <c r="E334" t="inlineStr">
-        <is>
-          <t>2.8%</t>
-        </is>
-      </c>
+          <t>0.8%</t>
+        </is>
+      </c>
+      <c r="E334" t="inlineStr"/>
       <c r="F334" t="inlineStr">
         <is>
-          <t>2.8%</t>
+          <t>0.7%</t>
         </is>
       </c>
       <c r="G334" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="335">
@@ -10324,31 +10324,31 @@
       </c>
       <c r="B335" t="inlineStr">
         <is>
-          <t>PCE Price Index YoYDEC</t>
+          <t>Personal Spending MoMDEC</t>
         </is>
       </c>
       <c r="C335" t="inlineStr">
         <is>
-          <t>2.6%</t>
+          <t>0.7%</t>
         </is>
       </c>
       <c r="D335" t="inlineStr">
         <is>
-          <t>2.4%</t>
+          <t>0.6%</t>
         </is>
       </c>
       <c r="E335" t="inlineStr">
         <is>
-          <t>2.6%</t>
+          <t>0.5%</t>
         </is>
       </c>
       <c r="F335" t="inlineStr">
         <is>
-          <t>2.6%</t>
+          <t>0.5%</t>
         </is>
       </c>
       <c r="G335" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="336">
@@ -10359,12 +10359,12 @@
       </c>
       <c r="B336" t="inlineStr">
         <is>
-          <t>PCE Price Index MoMDEC</t>
+          <t>Core PCE Price Index MoMDEC</t>
         </is>
       </c>
       <c r="C336" t="inlineStr">
         <is>
-          <t>0.3%</t>
+          <t>0.2%</t>
         </is>
       </c>
       <c r="D336" t="inlineStr">
@@ -10374,16 +10374,16 @@
       </c>
       <c r="E336" t="inlineStr">
         <is>
-          <t>0.3%</t>
+          <t>0.2%</t>
         </is>
       </c>
       <c r="F336" t="inlineStr">
         <is>
-          <t>0.3%</t>
+          <t>0.2%</t>
         </is>
       </c>
       <c r="G336" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="337">
@@ -11155,17 +11155,17 @@
       </c>
       <c r="B364" t="inlineStr">
         <is>
-          <t>MBA Mortgage ApplicationsJAN/31</t>
+          <t>MBA Mortgage Refinance IndexJAN/31</t>
         </is>
       </c>
       <c r="C364" t="inlineStr">
         <is>
-          <t>2.2%</t>
+          <t>584.3</t>
         </is>
       </c>
       <c r="D364" t="inlineStr">
         <is>
-          <t>-2%</t>
+          <t>520.9</t>
         </is>
       </c>
       <c r="E364" t="inlineStr"/>
@@ -11182,23 +11182,23 @@
       </c>
       <c r="B365" t="inlineStr">
         <is>
-          <t>MBA Mortgage Market IndexJAN/31</t>
+          <t>MBA 30-Year Mortgage RateJAN/31</t>
         </is>
       </c>
       <c r="C365" t="inlineStr">
         <is>
-          <t>224.8</t>
+          <t>6.97%</t>
         </is>
       </c>
       <c r="D365" t="inlineStr">
         <is>
-          <t>220.0</t>
+          <t>7.02%</t>
         </is>
       </c>
       <c r="E365" t="inlineStr"/>
       <c r="F365" t="inlineStr"/>
       <c r="G365" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="366">
@@ -11209,23 +11209,23 @@
       </c>
       <c r="B366" t="inlineStr">
         <is>
-          <t>MBA 30-Year Mortgage RateJAN/31</t>
+          <t>MBA Purchase IndexJAN/31</t>
         </is>
       </c>
       <c r="C366" t="inlineStr">
         <is>
-          <t>6.97%</t>
+          <t>156.7</t>
         </is>
       </c>
       <c r="D366" t="inlineStr">
         <is>
-          <t>7.02%</t>
+          <t>162.4</t>
         </is>
       </c>
       <c r="E366" t="inlineStr"/>
       <c r="F366" t="inlineStr"/>
       <c r="G366" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="367">
@@ -11236,17 +11236,17 @@
       </c>
       <c r="B367" t="inlineStr">
         <is>
-          <t>MBA Mortgage Refinance IndexJAN/31</t>
+          <t>MBA Mortgage ApplicationsJAN/31</t>
         </is>
       </c>
       <c r="C367" t="inlineStr">
         <is>
-          <t>584.3</t>
+          <t>2.2%</t>
         </is>
       </c>
       <c r="D367" t="inlineStr">
         <is>
-          <t>520.9</t>
+          <t>-2%</t>
         </is>
       </c>
       <c r="E367" t="inlineStr"/>
@@ -11263,17 +11263,17 @@
       </c>
       <c r="B368" t="inlineStr">
         <is>
-          <t>MBA Purchase IndexJAN/31</t>
+          <t>MBA Mortgage Market IndexJAN/31</t>
         </is>
       </c>
       <c r="C368" t="inlineStr">
         <is>
-          <t>156.7</t>
+          <t>224.8</t>
         </is>
       </c>
       <c r="D368" t="inlineStr">
         <is>
-          <t>162.4</t>
+          <t>220.0</t>
         </is>
       </c>
       <c r="E368" t="inlineStr"/>
@@ -11530,23 +11530,23 @@
       </c>
       <c r="B377" t="inlineStr">
         <is>
-          <t>ISM Services PricesJAN</t>
+          <t>ISM Services EmploymentJAN</t>
         </is>
       </c>
       <c r="C377" t="inlineStr">
         <is>
-          <t>60.4</t>
+          <t>52.3</t>
         </is>
       </c>
       <c r="D377" t="inlineStr">
         <is>
-          <t>64.4</t>
+          <t>51.3</t>
         </is>
       </c>
       <c r="E377" t="inlineStr"/>
       <c r="F377" t="inlineStr">
         <is>
-          <t>64.8</t>
+          <t>51.3</t>
         </is>
       </c>
       <c r="G377" t="n">
@@ -11561,31 +11561,27 @@
       </c>
       <c r="B378" t="inlineStr">
         <is>
-          <t>ISM Services PMIJAN</t>
+          <t>ISM Services New OrdersJAN</t>
         </is>
       </c>
       <c r="C378" t="inlineStr">
         <is>
-          <t>52.8</t>
+          <t>51.3</t>
         </is>
       </c>
       <c r="D378" t="inlineStr">
         <is>
-          <t>54.0</t>
-        </is>
-      </c>
-      <c r="E378" t="inlineStr">
-        <is>
-          <t>54.3</t>
-        </is>
-      </c>
+          <t>54.4</t>
+        </is>
+      </c>
+      <c r="E378" t="inlineStr"/>
       <c r="F378" t="inlineStr">
         <is>
-          <t>54</t>
+          <t>54.1</t>
         </is>
       </c>
       <c r="G378" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="379">
@@ -11596,23 +11592,23 @@
       </c>
       <c r="B379" t="inlineStr">
         <is>
-          <t>ISM Services New OrdersJAN</t>
+          <t>ISM Services Business ActivityJAN</t>
         </is>
       </c>
       <c r="C379" t="inlineStr">
         <is>
-          <t>51.3</t>
+          <t>54.5</t>
         </is>
       </c>
       <c r="D379" t="inlineStr">
         <is>
-          <t>54.4</t>
+          <t>58.0</t>
         </is>
       </c>
       <c r="E379" t="inlineStr"/>
       <c r="F379" t="inlineStr">
         <is>
-          <t>54.1</t>
+          <t>58.1</t>
         </is>
       </c>
       <c r="G379" t="n">
@@ -11627,23 +11623,23 @@
       </c>
       <c r="B380" t="inlineStr">
         <is>
-          <t>ISM Services EmploymentJAN</t>
+          <t>ISM Services PricesJAN</t>
         </is>
       </c>
       <c r="C380" t="inlineStr">
         <is>
-          <t>52.3</t>
+          <t>60.4</t>
         </is>
       </c>
       <c r="D380" t="inlineStr">
         <is>
-          <t>51.3</t>
+          <t>64.4</t>
         </is>
       </c>
       <c r="E380" t="inlineStr"/>
       <c r="F380" t="inlineStr">
         <is>
-          <t>51.3</t>
+          <t>64.8</t>
         </is>
       </c>
       <c r="G380" t="n">
@@ -11658,27 +11654,31 @@
       </c>
       <c r="B381" t="inlineStr">
         <is>
-          <t>ISM Services Business ActivityJAN</t>
+          <t>ISM Services PMIJAN</t>
         </is>
       </c>
       <c r="C381" t="inlineStr">
         <is>
-          <t>54.5</t>
+          <t>52.8</t>
         </is>
       </c>
       <c r="D381" t="inlineStr">
         <is>
-          <t>58.0</t>
-        </is>
-      </c>
-      <c r="E381" t="inlineStr"/>
+          <t>54.0</t>
+        </is>
+      </c>
+      <c r="E381" t="inlineStr">
+        <is>
+          <t>54.3</t>
+        </is>
+      </c>
       <c r="F381" t="inlineStr">
         <is>
-          <t>58.1</t>
+          <t>54</t>
         </is>
       </c>
       <c r="G381" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="382">
@@ -11689,22 +11689,22 @@
       </c>
       <c r="B382" t="inlineStr">
         <is>
-          <t>EIA Gasoline Stocks ChangeJAN/31</t>
+          <t>EIA Crude Oil Stocks ChangeJAN/31</t>
         </is>
       </c>
       <c r="C382" t="inlineStr">
         <is>
-          <t>2.233M</t>
+          <t>8.664M</t>
         </is>
       </c>
       <c r="D382" t="inlineStr">
         <is>
-          <t>2.957M</t>
+          <t>3.463M</t>
         </is>
       </c>
       <c r="E382" t="inlineStr">
         <is>
-          <t>1.2M</t>
+          <t>2.6M</t>
         </is>
       </c>
       <c r="F382" t="inlineStr"/>
@@ -11720,17 +11720,17 @@
       </c>
       <c r="B383" t="inlineStr">
         <is>
-          <t>EIA Refinery Crude Runs ChangeJAN/31</t>
+          <t>EIA Crude Oil Imports ChangeJAN/31</t>
         </is>
       </c>
       <c r="C383" t="inlineStr">
         <is>
-          <t>0.16M</t>
+          <t>-0.178M</t>
         </is>
       </c>
       <c r="D383" t="inlineStr">
         <is>
-          <t>-0.333M</t>
+          <t>0.532M</t>
         </is>
       </c>
       <c r="E383" t="inlineStr"/>
@@ -11747,24 +11747,20 @@
       </c>
       <c r="B384" t="inlineStr">
         <is>
-          <t>EIA Distillate Stocks ChangeJAN/31</t>
+          <t>EIA Heating Oil Stocks ChangeJAN/31</t>
         </is>
       </c>
       <c r="C384" t="inlineStr">
         <is>
-          <t>-5.471M</t>
+          <t>0.373M</t>
         </is>
       </c>
       <c r="D384" t="inlineStr">
         <is>
-          <t>-4.994M</t>
-        </is>
-      </c>
-      <c r="E384" t="inlineStr">
-        <is>
-          <t>-1.5M</t>
-        </is>
-      </c>
+          <t>0.128M</t>
+        </is>
+      </c>
+      <c r="E384" t="inlineStr"/>
       <c r="F384" t="inlineStr"/>
       <c r="G384" t="n">
         <v>3</v>
@@ -11778,17 +11774,17 @@
       </c>
       <c r="B385" t="inlineStr">
         <is>
-          <t>EIA Distillate Fuel Production ChangeJAN/31</t>
+          <t>EIA Gasoline Production ChangeJAN/31</t>
         </is>
       </c>
       <c r="C385" t="inlineStr">
         <is>
-          <t>-0.186M</t>
+          <t>-0.027M</t>
         </is>
       </c>
       <c r="D385" t="inlineStr">
         <is>
-          <t>0.028M</t>
+          <t>-0.044M</t>
         </is>
       </c>
       <c r="E385" t="inlineStr"/>
@@ -11805,17 +11801,17 @@
       </c>
       <c r="B386" t="inlineStr">
         <is>
-          <t>EIA Gasoline Production ChangeJAN/31</t>
+          <t>EIA Cushing Crude Oil Stocks ChangeJAN/31</t>
         </is>
       </c>
       <c r="C386" t="inlineStr">
         <is>
-          <t>-0.027M</t>
+          <t>-0.034M</t>
         </is>
       </c>
       <c r="D386" t="inlineStr">
         <is>
-          <t>-0.044M</t>
+          <t>0.326M</t>
         </is>
       </c>
       <c r="E386" t="inlineStr"/>
@@ -11832,20 +11828,24 @@
       </c>
       <c r="B387" t="inlineStr">
         <is>
-          <t>EIA Heating Oil Stocks ChangeJAN/31</t>
+          <t>EIA Distillate Stocks ChangeJAN/31</t>
         </is>
       </c>
       <c r="C387" t="inlineStr">
         <is>
-          <t>0.373M</t>
+          <t>-5.471M</t>
         </is>
       </c>
       <c r="D387" t="inlineStr">
         <is>
-          <t>0.128M</t>
-        </is>
-      </c>
-      <c r="E387" t="inlineStr"/>
+          <t>-4.994M</t>
+        </is>
+      </c>
+      <c r="E387" t="inlineStr">
+        <is>
+          <t>-1.5M</t>
+        </is>
+      </c>
       <c r="F387" t="inlineStr"/>
       <c r="G387" t="n">
         <v>3</v>
@@ -11859,17 +11859,17 @@
       </c>
       <c r="B388" t="inlineStr">
         <is>
-          <t>EIA Cushing Crude Oil Stocks ChangeJAN/31</t>
+          <t>EIA Refinery Crude Runs ChangeJAN/31</t>
         </is>
       </c>
       <c r="C388" t="inlineStr">
         <is>
-          <t>-0.034M</t>
+          <t>0.16M</t>
         </is>
       </c>
       <c r="D388" t="inlineStr">
         <is>
-          <t>0.326M</t>
+          <t>-0.333M</t>
         </is>
       </c>
       <c r="E388" t="inlineStr"/>
@@ -11886,23 +11886,27 @@
       </c>
       <c r="B389" t="inlineStr">
         <is>
-          <t>EIA Crude Oil Imports ChangeJAN/31</t>
+          <t>EIA Gasoline Stocks ChangeJAN/31</t>
         </is>
       </c>
       <c r="C389" t="inlineStr">
         <is>
-          <t>-0.178M</t>
+          <t>2.233M</t>
         </is>
       </c>
       <c r="D389" t="inlineStr">
         <is>
-          <t>0.532M</t>
-        </is>
-      </c>
-      <c r="E389" t="inlineStr"/>
+          <t>2.957M</t>
+        </is>
+      </c>
+      <c r="E389" t="inlineStr">
+        <is>
+          <t>1.2M</t>
+        </is>
+      </c>
       <c r="F389" t="inlineStr"/>
       <c r="G389" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="390">
@@ -11913,27 +11917,23 @@
       </c>
       <c r="B390" t="inlineStr">
         <is>
-          <t>EIA Crude Oil Stocks ChangeJAN/31</t>
+          <t>EIA Distillate Fuel Production ChangeJAN/31</t>
         </is>
       </c>
       <c r="C390" t="inlineStr">
         <is>
-          <t>8.664M</t>
+          <t>-0.186M</t>
         </is>
       </c>
       <c r="D390" t="inlineStr">
         <is>
-          <t>3.463M</t>
-        </is>
-      </c>
-      <c r="E390" t="inlineStr">
-        <is>
-          <t>2.6M</t>
-        </is>
-      </c>
+          <t>0.028M</t>
+        </is>
+      </c>
+      <c r="E390" t="inlineStr"/>
       <c r="F390" t="inlineStr"/>
       <c r="G390" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="391">
@@ -12040,23 +12040,27 @@
       </c>
       <c r="B395" t="inlineStr">
         <is>
-          <t>Jobless Claims 4-week AverageFEB/01</t>
+          <t>Continuing Jobless ClaimsJAN/25</t>
         </is>
       </c>
       <c r="C395" t="inlineStr">
         <is>
-          <t>216.75K</t>
+          <t>1886K</t>
         </is>
       </c>
       <c r="D395" t="inlineStr">
         <is>
-          <t>212.75K</t>
-        </is>
-      </c>
-      <c r="E395" t="inlineStr"/>
+          <t>1850K</t>
+        </is>
+      </c>
+      <c r="E395" t="inlineStr">
+        <is>
+          <t>1870K</t>
+        </is>
+      </c>
       <c r="F395" t="inlineStr">
         <is>
-          <t>215.5K</t>
+          <t>1855.0K</t>
         </is>
       </c>
       <c r="G395" t="n">
@@ -12071,27 +12075,27 @@
       </c>
       <c r="B396" t="inlineStr">
         <is>
-          <t>Unit Labour Costs QoQ PrelQ4</t>
+          <t>Initial Jobless ClaimsFEB/01</t>
         </is>
       </c>
       <c r="C396" t="inlineStr">
         <is>
-          <t>3%</t>
+          <t>219K</t>
         </is>
       </c>
       <c r="D396" t="inlineStr">
         <is>
-          <t>0.5%</t>
+          <t>208K</t>
         </is>
       </c>
       <c r="E396" t="inlineStr">
         <is>
-          <t>3.4%</t>
+          <t>213K</t>
         </is>
       </c>
       <c r="F396" t="inlineStr">
         <is>
-          <t>3%</t>
+          <t>215.0K</t>
         </is>
       </c>
       <c r="G396" t="n">
@@ -12141,27 +12145,27 @@
       </c>
       <c r="B398" t="inlineStr">
         <is>
-          <t>Initial Jobless ClaimsFEB/01</t>
+          <t>Unit Labour Costs QoQ PrelQ4</t>
         </is>
       </c>
       <c r="C398" t="inlineStr">
         <is>
-          <t>219K</t>
+          <t>3%</t>
         </is>
       </c>
       <c r="D398" t="inlineStr">
         <is>
-          <t>208K</t>
+          <t>0.5%</t>
         </is>
       </c>
       <c r="E398" t="inlineStr">
         <is>
-          <t>213K</t>
+          <t>3.4%</t>
         </is>
       </c>
       <c r="F398" t="inlineStr">
         <is>
-          <t>215.0K</t>
+          <t>3%</t>
         </is>
       </c>
       <c r="G398" t="n">
@@ -12176,27 +12180,23 @@
       </c>
       <c r="B399" t="inlineStr">
         <is>
-          <t>Continuing Jobless ClaimsJAN/25</t>
+          <t>Jobless Claims 4-week AverageFEB/01</t>
         </is>
       </c>
       <c r="C399" t="inlineStr">
         <is>
-          <t>1886K</t>
+          <t>216.75K</t>
         </is>
       </c>
       <c r="D399" t="inlineStr">
         <is>
-          <t>1850K</t>
-        </is>
-      </c>
-      <c r="E399" t="inlineStr">
-        <is>
-          <t>1870K</t>
-        </is>
-      </c>
+          <t>212.75K</t>
+        </is>
+      </c>
+      <c r="E399" t="inlineStr"/>
       <c r="F399" t="inlineStr">
         <is>
-          <t>1855.0K</t>
+          <t>215.5K</t>
         </is>
       </c>
       <c r="G399" t="n">
@@ -12442,27 +12442,23 @@
       </c>
       <c r="B409" t="inlineStr">
         <is>
-          <t>Average Weekly HoursJAN</t>
+          <t>U-6 Unemployment RateJAN</t>
         </is>
       </c>
       <c r="C409" t="inlineStr">
         <is>
-          <t>34.1</t>
+          <t>7.5%</t>
         </is>
       </c>
       <c r="D409" t="inlineStr">
         <is>
-          <t>34.2</t>
-        </is>
-      </c>
-      <c r="E409" t="inlineStr">
-        <is>
-          <t>34.3</t>
-        </is>
-      </c>
+          <t>7.5%</t>
+        </is>
+      </c>
+      <c r="E409" t="inlineStr"/>
       <c r="F409" t="inlineStr">
         <is>
-          <t>34.3</t>
+          <t>7.5%</t>
         </is>
       </c>
       <c r="G409" t="n">
@@ -12477,31 +12473,27 @@
       </c>
       <c r="B410" t="inlineStr">
         <is>
-          <t>Unemployment RateJAN</t>
+          <t>Participation RateJAN</t>
         </is>
       </c>
       <c r="C410" t="inlineStr">
         <is>
-          <t>4%</t>
+          <t>62.6%</t>
         </is>
       </c>
       <c r="D410" t="inlineStr">
         <is>
-          <t>4.1%</t>
-        </is>
-      </c>
-      <c r="E410" t="inlineStr">
-        <is>
-          <t>4.1%</t>
-        </is>
-      </c>
+          <t>62.5%</t>
+        </is>
+      </c>
+      <c r="E410" t="inlineStr"/>
       <c r="F410" t="inlineStr">
         <is>
-          <t>4.1%</t>
+          <t>62.5%</t>
         </is>
       </c>
       <c r="G410" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="411">
@@ -12512,31 +12504,31 @@
       </c>
       <c r="B411" t="inlineStr">
         <is>
-          <t>Average Hourly Earnings YoYJAN</t>
+          <t>Nonfarm Payrolls PrivateJAN</t>
         </is>
       </c>
       <c r="C411" t="inlineStr">
         <is>
-          <t>4.1%</t>
+          <t>111K</t>
         </is>
       </c>
       <c r="D411" t="inlineStr">
         <is>
-          <t>4.1%</t>
+          <t>273K</t>
         </is>
       </c>
       <c r="E411" t="inlineStr">
         <is>
-          <t>3.8%</t>
+          <t>141K</t>
         </is>
       </c>
       <c r="F411" t="inlineStr">
         <is>
-          <t>3.9%</t>
+          <t>180K</t>
         </is>
       </c>
       <c r="G411" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="412">
@@ -12547,31 +12539,31 @@
       </c>
       <c r="B412" t="inlineStr">
         <is>
-          <t>Average Hourly Earnings MoMJAN</t>
+          <t>Manufacturing PayrollsJAN</t>
         </is>
       </c>
       <c r="C412" t="inlineStr">
         <is>
-          <t>0.5%</t>
+          <t>3K</t>
         </is>
       </c>
       <c r="D412" t="inlineStr">
         <is>
-          <t>0.3%</t>
+          <t>-12K</t>
         </is>
       </c>
       <c r="E412" t="inlineStr">
         <is>
-          <t>0.3%</t>
+          <t>-2K</t>
         </is>
       </c>
       <c r="F412" t="inlineStr">
         <is>
-          <t>0.3%</t>
+          <t>-5K</t>
         </is>
       </c>
       <c r="G412" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="413">
@@ -12582,31 +12574,27 @@
       </c>
       <c r="B413" t="inlineStr">
         <is>
-          <t>Non Farm PayrollsJAN</t>
+          <t>Government PayrollsJAN</t>
         </is>
       </c>
       <c r="C413" t="inlineStr">
         <is>
-          <t>143K</t>
+          <t>32K</t>
         </is>
       </c>
       <c r="D413" t="inlineStr">
         <is>
-          <t>307K</t>
-        </is>
-      </c>
-      <c r="E413" t="inlineStr">
-        <is>
-          <t>170K</t>
-        </is>
-      </c>
+          <t>34K</t>
+        </is>
+      </c>
+      <c r="E413" t="inlineStr"/>
       <c r="F413" t="inlineStr">
         <is>
-          <t>205K</t>
+          <t>25K</t>
         </is>
       </c>
       <c r="G413" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="414">
@@ -12617,27 +12605,31 @@
       </c>
       <c r="B414" t="inlineStr">
         <is>
-          <t>Government PayrollsJAN</t>
+          <t>Average Hourly Earnings YoYJAN</t>
         </is>
       </c>
       <c r="C414" t="inlineStr">
         <is>
-          <t>32K</t>
+          <t>4.1%</t>
         </is>
       </c>
       <c r="D414" t="inlineStr">
         <is>
-          <t>34K</t>
-        </is>
-      </c>
-      <c r="E414" t="inlineStr"/>
+          <t>4.1%</t>
+        </is>
+      </c>
+      <c r="E414" t="inlineStr">
+        <is>
+          <t>3.8%</t>
+        </is>
+      </c>
       <c r="F414" t="inlineStr">
         <is>
-          <t>25K</t>
+          <t>3.9%</t>
         </is>
       </c>
       <c r="G414" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="415">
@@ -12648,31 +12640,31 @@
       </c>
       <c r="B415" t="inlineStr">
         <is>
-          <t>Manufacturing PayrollsJAN</t>
+          <t>Average Hourly Earnings MoMJAN</t>
         </is>
       </c>
       <c r="C415" t="inlineStr">
         <is>
-          <t>3K</t>
+          <t>0.5%</t>
         </is>
       </c>
       <c r="D415" t="inlineStr">
         <is>
-          <t>-12K</t>
+          <t>0.3%</t>
         </is>
       </c>
       <c r="E415" t="inlineStr">
         <is>
-          <t>-2K</t>
+          <t>0.3%</t>
         </is>
       </c>
       <c r="F415" t="inlineStr">
         <is>
-          <t>-5K</t>
+          <t>0.3%</t>
         </is>
       </c>
       <c r="G415" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="416">
@@ -12683,31 +12675,31 @@
       </c>
       <c r="B416" t="inlineStr">
         <is>
-          <t>Nonfarm Payrolls PrivateJAN</t>
+          <t>Unemployment RateJAN</t>
         </is>
       </c>
       <c r="C416" t="inlineStr">
         <is>
-          <t>111K</t>
+          <t>4%</t>
         </is>
       </c>
       <c r="D416" t="inlineStr">
         <is>
-          <t>273K</t>
+          <t>4.1%</t>
         </is>
       </c>
       <c r="E416" t="inlineStr">
         <is>
-          <t>141K</t>
+          <t>4.1%</t>
         </is>
       </c>
       <c r="F416" t="inlineStr">
         <is>
-          <t>180K</t>
+          <t>4.1%</t>
         </is>
       </c>
       <c r="G416" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="417">
@@ -12718,27 +12710,31 @@
       </c>
       <c r="B417" t="inlineStr">
         <is>
-          <t>Participation RateJAN</t>
+          <t>Average Weekly HoursJAN</t>
         </is>
       </c>
       <c r="C417" t="inlineStr">
         <is>
-          <t>62.6%</t>
+          <t>34.1</t>
         </is>
       </c>
       <c r="D417" t="inlineStr">
         <is>
-          <t>62.5%</t>
-        </is>
-      </c>
-      <c r="E417" t="inlineStr"/>
+          <t>34.2</t>
+        </is>
+      </c>
+      <c r="E417" t="inlineStr">
+        <is>
+          <t>34.3</t>
+        </is>
+      </c>
       <c r="F417" t="inlineStr">
         <is>
-          <t>62.5%</t>
+          <t>34.3</t>
         </is>
       </c>
       <c r="G417" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="418">
@@ -12749,27 +12745,31 @@
       </c>
       <c r="B418" t="inlineStr">
         <is>
-          <t>U-6 Unemployment RateJAN</t>
+          <t>Non Farm PayrollsJAN</t>
         </is>
       </c>
       <c r="C418" t="inlineStr">
         <is>
-          <t>7.5%</t>
+          <t>143K</t>
         </is>
       </c>
       <c r="D418" t="inlineStr">
         <is>
-          <t>7.5%</t>
-        </is>
-      </c>
-      <c r="E418" t="inlineStr"/>
+          <t>307K</t>
+        </is>
+      </c>
+      <c r="E418" t="inlineStr">
+        <is>
+          <t>170K</t>
+        </is>
+      </c>
       <c r="F418" t="inlineStr">
         <is>
-          <t>7.5%</t>
+          <t>205K</t>
         </is>
       </c>
       <c r="G418" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="419">
@@ -12872,23 +12872,27 @@
       </c>
       <c r="B423" t="inlineStr">
         <is>
-          <t>Michigan 5 Year Inflation Expectations PrelFEB</t>
+          <t>Wholesale Inventories MoMDEC</t>
         </is>
       </c>
       <c r="C423" t="inlineStr">
         <is>
-          <t>3.3%</t>
+          <t>-0.5%</t>
         </is>
       </c>
       <c r="D423" t="inlineStr">
         <is>
-          <t>3.2%</t>
-        </is>
-      </c>
-      <c r="E423" t="inlineStr"/>
+          <t>-0.1%</t>
+        </is>
+      </c>
+      <c r="E423" t="inlineStr">
+        <is>
+          <t>-0.5%</t>
+        </is>
+      </c>
       <c r="F423" t="inlineStr">
         <is>
-          <t>3.3%</t>
+          <t>-0.5%</t>
         </is>
       </c>
       <c r="G423" t="n">
@@ -12903,31 +12907,31 @@
       </c>
       <c r="B424" t="inlineStr">
         <is>
-          <t>Michigan Consumer Sentiment PrelFEB</t>
+          <t>Michigan Current Conditions PrelFEB</t>
         </is>
       </c>
       <c r="C424" t="inlineStr">
         <is>
-          <t>67.8</t>
+          <t>68.7</t>
         </is>
       </c>
       <c r="D424" t="inlineStr">
         <is>
-          <t>71.1</t>
+          <t>74</t>
         </is>
       </c>
       <c r="E424" t="inlineStr">
         <is>
-          <t>71.1</t>
+          <t>73</t>
         </is>
       </c>
       <c r="F424" t="inlineStr">
         <is>
-          <t>72</t>
+          <t>74.3</t>
         </is>
       </c>
       <c r="G424" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="425">
@@ -12938,27 +12942,23 @@
       </c>
       <c r="B425" t="inlineStr">
         <is>
-          <t>Michigan Consumer Expectations PrelFEB</t>
+          <t>Michigan Inflation Expectations PrelFEB</t>
         </is>
       </c>
       <c r="C425" t="inlineStr">
         <is>
-          <t>67.3</t>
+          <t>4.3%</t>
         </is>
       </c>
       <c r="D425" t="inlineStr">
         <is>
-          <t>69.3</t>
-        </is>
-      </c>
-      <c r="E425" t="inlineStr">
-        <is>
-          <t>70</t>
-        </is>
-      </c>
+          <t>3.3%</t>
+        </is>
+      </c>
+      <c r="E425" t="inlineStr"/>
       <c r="F425" t="inlineStr">
         <is>
-          <t>69.5</t>
+          <t>3.4%</t>
         </is>
       </c>
       <c r="G425" t="n">
@@ -12973,23 +12973,27 @@
       </c>
       <c r="B426" t="inlineStr">
         <is>
-          <t>Michigan Inflation Expectations PrelFEB</t>
+          <t>Michigan Consumer Expectations PrelFEB</t>
         </is>
       </c>
       <c r="C426" t="inlineStr">
         <is>
-          <t>4.3%</t>
+          <t>67.3</t>
         </is>
       </c>
       <c r="D426" t="inlineStr">
         <is>
-          <t>3.3%</t>
-        </is>
-      </c>
-      <c r="E426" t="inlineStr"/>
+          <t>69.3</t>
+        </is>
+      </c>
+      <c r="E426" t="inlineStr">
+        <is>
+          <t>70</t>
+        </is>
+      </c>
       <c r="F426" t="inlineStr">
         <is>
-          <t>3.4%</t>
+          <t>69.5</t>
         </is>
       </c>
       <c r="G426" t="n">
@@ -13004,31 +13008,31 @@
       </c>
       <c r="B427" t="inlineStr">
         <is>
-          <t>Wholesale Inventories MoMDEC</t>
+          <t>Michigan Consumer Sentiment PrelFEB</t>
         </is>
       </c>
       <c r="C427" t="inlineStr">
         <is>
-          <t>-0.5%</t>
+          <t>67.8</t>
         </is>
       </c>
       <c r="D427" t="inlineStr">
         <is>
-          <t>-0.1%</t>
+          <t>71.1</t>
         </is>
       </c>
       <c r="E427" t="inlineStr">
         <is>
-          <t>-0.5%</t>
+          <t>71.1</t>
         </is>
       </c>
       <c r="F427" t="inlineStr">
         <is>
-          <t>-0.5%</t>
+          <t>72</t>
         </is>
       </c>
       <c r="G427" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="428">
@@ -13039,27 +13043,23 @@
       </c>
       <c r="B428" t="inlineStr">
         <is>
-          <t>Michigan Current Conditions PrelFEB</t>
+          <t>Michigan 5 Year Inflation Expectations PrelFEB</t>
         </is>
       </c>
       <c r="C428" t="inlineStr">
         <is>
-          <t>68.7</t>
+          <t>3.3%</t>
         </is>
       </c>
       <c r="D428" t="inlineStr">
         <is>
-          <t>74</t>
-        </is>
-      </c>
-      <c r="E428" t="inlineStr">
-        <is>
-          <t>73</t>
-        </is>
-      </c>
+          <t>3.2%</t>
+        </is>
+      </c>
+      <c r="E428" t="inlineStr"/>
       <c r="F428" t="inlineStr">
         <is>
-          <t>74.3</t>
+          <t>3.3%</t>
         </is>
       </c>
       <c r="G428" t="n">
@@ -13636,27 +13636,27 @@
       </c>
       <c r="B451" t="inlineStr">
         <is>
-          <t>Inflation Rate YoYJAN</t>
+          <t>Core Inflation Rate MoMJAN</t>
         </is>
       </c>
       <c r="C451" t="inlineStr">
         <is>
-          <t>3%</t>
+          <t>0.4%</t>
         </is>
       </c>
       <c r="D451" t="inlineStr">
         <is>
-          <t>2.9%</t>
+          <t>0.2%</t>
         </is>
       </c>
       <c r="E451" t="inlineStr">
         <is>
-          <t>2.9%</t>
+          <t>0.3%</t>
         </is>
       </c>
       <c r="F451" t="inlineStr">
         <is>
-          <t>2.9%</t>
+          <t>0.3%</t>
         </is>
       </c>
       <c r="G451" t="n">
@@ -13671,31 +13671,31 @@
       </c>
       <c r="B452" t="inlineStr">
         <is>
-          <t>CPIJAN</t>
+          <t>Inflation Rate MoMJAN</t>
         </is>
       </c>
       <c r="C452" t="inlineStr">
         <is>
-          <t>317.67</t>
+          <t>0.5%</t>
         </is>
       </c>
       <c r="D452" t="inlineStr">
         <is>
-          <t>315.61</t>
+          <t>0.4%</t>
         </is>
       </c>
       <c r="E452" t="inlineStr">
         <is>
-          <t>317.46</t>
+          <t>0.3%</t>
         </is>
       </c>
       <c r="F452" t="inlineStr">
         <is>
-          <t>317.3</t>
+          <t>0.2%</t>
         </is>
       </c>
       <c r="G452" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="453">
@@ -13706,27 +13706,31 @@
       </c>
       <c r="B453" t="inlineStr">
         <is>
-          <t>CPI s.aJAN</t>
+          <t>Core Inflation Rate YoYJAN</t>
         </is>
       </c>
       <c r="C453" t="inlineStr">
         <is>
-          <t>319.086</t>
+          <t>3.3%</t>
         </is>
       </c>
       <c r="D453" t="inlineStr">
         <is>
-          <t>317.603</t>
-        </is>
-      </c>
-      <c r="E453" t="inlineStr"/>
+          <t>3.2%</t>
+        </is>
+      </c>
+      <c r="E453" t="inlineStr">
+        <is>
+          <t>3.1%</t>
+        </is>
+      </c>
       <c r="F453" t="inlineStr">
         <is>
-          <t>318.2</t>
+          <t>3.1%</t>
         </is>
       </c>
       <c r="G453" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="454">
@@ -13737,31 +13741,31 @@
       </c>
       <c r="B454" t="inlineStr">
         <is>
-          <t>Core Inflation Rate YoYJAN</t>
+          <t>CPIJAN</t>
         </is>
       </c>
       <c r="C454" t="inlineStr">
         <is>
-          <t>3.3%</t>
+          <t>317.67</t>
         </is>
       </c>
       <c r="D454" t="inlineStr">
         <is>
-          <t>3.2%</t>
+          <t>315.61</t>
         </is>
       </c>
       <c r="E454" t="inlineStr">
         <is>
-          <t>3.1%</t>
+          <t>317.46</t>
         </is>
       </c>
       <c r="F454" t="inlineStr">
         <is>
-          <t>3.1%</t>
+          <t>317.3</t>
         </is>
       </c>
       <c r="G454" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="455">
@@ -13772,31 +13776,27 @@
       </c>
       <c r="B455" t="inlineStr">
         <is>
-          <t>Inflation Rate MoMJAN</t>
+          <t>CPI s.aJAN</t>
         </is>
       </c>
       <c r="C455" t="inlineStr">
         <is>
-          <t>0.5%</t>
+          <t>319.086</t>
         </is>
       </c>
       <c r="D455" t="inlineStr">
         <is>
-          <t>0.4%</t>
-        </is>
-      </c>
-      <c r="E455" t="inlineStr">
-        <is>
-          <t>0.3%</t>
-        </is>
-      </c>
+          <t>317.603</t>
+        </is>
+      </c>
+      <c r="E455" t="inlineStr"/>
       <c r="F455" t="inlineStr">
         <is>
-          <t>0.2%</t>
+          <t>318.2</t>
         </is>
       </c>
       <c r="G455" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="456">
@@ -13807,27 +13807,27 @@
       </c>
       <c r="B456" t="inlineStr">
         <is>
-          <t>Core Inflation Rate MoMJAN</t>
+          <t>Inflation Rate YoYJAN</t>
         </is>
       </c>
       <c r="C456" t="inlineStr">
         <is>
-          <t>0.4%</t>
+          <t>3%</t>
         </is>
       </c>
       <c r="D456" t="inlineStr">
         <is>
-          <t>0.2%</t>
+          <t>2.9%</t>
         </is>
       </c>
       <c r="E456" t="inlineStr">
         <is>
-          <t>0.3%</t>
+          <t>2.9%</t>
         </is>
       </c>
       <c r="F456" t="inlineStr">
         <is>
-          <t>0.3%</t>
+          <t>2.9%</t>
         </is>
       </c>
       <c r="G456" t="n">
@@ -13842,23 +13842,27 @@
       </c>
       <c r="B457" t="inlineStr">
         <is>
-          <t>EIA Refinery Crude Runs ChangeFEB/07</t>
+          <t>EIA Crude Oil Stocks ChangeFEB/07</t>
         </is>
       </c>
       <c r="C457" t="inlineStr">
         <is>
-          <t>0.082M</t>
+          <t>4.07M</t>
         </is>
       </c>
       <c r="D457" t="inlineStr">
         <is>
-          <t>0.16M</t>
-        </is>
-      </c>
-      <c r="E457" t="inlineStr"/>
+          <t>8.664M</t>
+        </is>
+      </c>
+      <c r="E457" t="inlineStr">
+        <is>
+          <t>3M</t>
+        </is>
+      </c>
       <c r="F457" t="inlineStr"/>
       <c r="G457" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="458">
@@ -13869,17 +13873,17 @@
       </c>
       <c r="B458" t="inlineStr">
         <is>
-          <t>EIA Gasoline Production ChangeFEB/07</t>
+          <t>EIA Heating Oil Stocks ChangeFEB/07</t>
         </is>
       </c>
       <c r="C458" t="inlineStr">
         <is>
-          <t>0.18M</t>
+          <t>0.159M</t>
         </is>
       </c>
       <c r="D458" t="inlineStr">
         <is>
-          <t>-0.027M</t>
+          <t>0.373M</t>
         </is>
       </c>
       <c r="E458" t="inlineStr"/>
@@ -13896,27 +13900,23 @@
       </c>
       <c r="B459" t="inlineStr">
         <is>
-          <t>EIA Gasoline Stocks ChangeFEB/07</t>
+          <t>EIA Cushing Crude Oil Stocks ChangeFEB/07</t>
         </is>
       </c>
       <c r="C459" t="inlineStr">
         <is>
-          <t>-3.035M</t>
+          <t>0.872M</t>
         </is>
       </c>
       <c r="D459" t="inlineStr">
         <is>
-          <t>2.233M</t>
-        </is>
-      </c>
-      <c r="E459" t="inlineStr">
-        <is>
-          <t>1.5M</t>
-        </is>
-      </c>
+          <t>-0.034M</t>
+        </is>
+      </c>
+      <c r="E459" t="inlineStr"/>
       <c r="F459" t="inlineStr"/>
       <c r="G459" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="460">
@@ -13927,20 +13927,24 @@
       </c>
       <c r="B460" t="inlineStr">
         <is>
-          <t>EIA Distillate Fuel Production ChangeFEB/07</t>
+          <t>EIA Distillate Stocks ChangeFEB/07</t>
         </is>
       </c>
       <c r="C460" t="inlineStr">
         <is>
-          <t>-0.009M</t>
+          <t>0.135M</t>
         </is>
       </c>
       <c r="D460" t="inlineStr">
         <is>
-          <t>-0.186M</t>
-        </is>
-      </c>
-      <c r="E460" t="inlineStr"/>
+          <t>-5.471M</t>
+        </is>
+      </c>
+      <c r="E460" t="inlineStr">
+        <is>
+          <t>-2M</t>
+        </is>
+      </c>
       <c r="F460" t="inlineStr"/>
       <c r="G460" t="n">
         <v>3</v>
@@ -13954,24 +13958,20 @@
       </c>
       <c r="B461" t="inlineStr">
         <is>
-          <t>EIA Distillate Stocks ChangeFEB/07</t>
+          <t>EIA Crude Oil Imports ChangeFEB/07</t>
         </is>
       </c>
       <c r="C461" t="inlineStr">
         <is>
-          <t>0.135M</t>
+          <t>-0.184M</t>
         </is>
       </c>
       <c r="D461" t="inlineStr">
         <is>
-          <t>-5.471M</t>
-        </is>
-      </c>
-      <c r="E461" t="inlineStr">
-        <is>
-          <t>-2M</t>
-        </is>
-      </c>
+          <t>-0.178M</t>
+        </is>
+      </c>
+      <c r="E461" t="inlineStr"/>
       <c r="F461" t="inlineStr"/>
       <c r="G461" t="n">
         <v>3</v>
@@ -13985,23 +13985,27 @@
       </c>
       <c r="B462" t="inlineStr">
         <is>
-          <t>EIA Cushing Crude Oil Stocks ChangeFEB/07</t>
+          <t>EIA Gasoline Stocks ChangeFEB/07</t>
         </is>
       </c>
       <c r="C462" t="inlineStr">
         <is>
-          <t>0.872M</t>
+          <t>-3.035M</t>
         </is>
       </c>
       <c r="D462" t="inlineStr">
         <is>
-          <t>-0.034M</t>
-        </is>
-      </c>
-      <c r="E462" t="inlineStr"/>
+          <t>2.233M</t>
+        </is>
+      </c>
+      <c r="E462" t="inlineStr">
+        <is>
+          <t>1.5M</t>
+        </is>
+      </c>
       <c r="F462" t="inlineStr"/>
       <c r="G462" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="463">
@@ -14012,17 +14016,17 @@
       </c>
       <c r="B463" t="inlineStr">
         <is>
-          <t>EIA Heating Oil Stocks ChangeFEB/07</t>
+          <t>EIA Gasoline Production ChangeFEB/07</t>
         </is>
       </c>
       <c r="C463" t="inlineStr">
         <is>
-          <t>0.159M</t>
+          <t>0.18M</t>
         </is>
       </c>
       <c r="D463" t="inlineStr">
         <is>
-          <t>0.373M</t>
+          <t>-0.027M</t>
         </is>
       </c>
       <c r="E463" t="inlineStr"/>
@@ -14039,27 +14043,23 @@
       </c>
       <c r="B464" t="inlineStr">
         <is>
-          <t>EIA Crude Oil Stocks ChangeFEB/07</t>
+          <t>EIA Refinery Crude Runs ChangeFEB/07</t>
         </is>
       </c>
       <c r="C464" t="inlineStr">
         <is>
-          <t>4.07M</t>
+          <t>0.082M</t>
         </is>
       </c>
       <c r="D464" t="inlineStr">
         <is>
-          <t>8.664M</t>
-        </is>
-      </c>
-      <c r="E464" t="inlineStr">
-        <is>
-          <t>3M</t>
-        </is>
-      </c>
+          <t>0.16M</t>
+        </is>
+      </c>
+      <c r="E464" t="inlineStr"/>
       <c r="F464" t="inlineStr"/>
       <c r="G464" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="465">
@@ -14070,17 +14070,17 @@
       </c>
       <c r="B465" t="inlineStr">
         <is>
-          <t>EIA Crude Oil Imports ChangeFEB/07</t>
+          <t>EIA Distillate Fuel Production ChangeFEB/07</t>
         </is>
       </c>
       <c r="C465" t="inlineStr">
         <is>
-          <t>-0.184M</t>
+          <t>-0.009M</t>
         </is>
       </c>
       <c r="D465" t="inlineStr">
         <is>
-          <t>-0.178M</t>
+          <t>-0.186M</t>
         </is>
       </c>
       <c r="E465" t="inlineStr"/>
@@ -14224,27 +14224,23 @@
       </c>
       <c r="B471" t="inlineStr">
         <is>
-          <t>Core PPI YoYJAN</t>
+          <t>PPI Ex Food, Energy and Trade MoMJAN</t>
         </is>
       </c>
       <c r="C471" t="inlineStr">
         <is>
-          <t>3.6%</t>
+          <t>0.3%</t>
         </is>
       </c>
       <c r="D471" t="inlineStr">
         <is>
-          <t>3.7%</t>
-        </is>
-      </c>
-      <c r="E471" t="inlineStr">
-        <is>
-          <t>3.3%</t>
-        </is>
-      </c>
+          <t>0.4%</t>
+        </is>
+      </c>
+      <c r="E471" t="inlineStr"/>
       <c r="F471" t="inlineStr">
         <is>
-          <t>3.5%</t>
+          <t>0.2%</t>
         </is>
       </c>
       <c r="G471" t="n">
@@ -14259,23 +14255,27 @@
       </c>
       <c r="B472" t="inlineStr">
         <is>
-          <t>PPIJAN</t>
+          <t>Continuing Jobless ClaimsFEB/01</t>
         </is>
       </c>
       <c r="C472" t="inlineStr">
         <is>
-          <t>147.716</t>
+          <t>1850K</t>
         </is>
       </c>
       <c r="D472" t="inlineStr">
         <is>
-          <t>147.127</t>
-        </is>
-      </c>
-      <c r="E472" t="inlineStr"/>
+          <t>1886K</t>
+        </is>
+      </c>
+      <c r="E472" t="inlineStr">
+        <is>
+          <t>1880K</t>
+        </is>
+      </c>
       <c r="F472" t="inlineStr">
         <is>
-          <t>147.2</t>
+          <t>1875.0K</t>
         </is>
       </c>
       <c r="G472" t="n">
@@ -14290,31 +14290,27 @@
       </c>
       <c r="B473" t="inlineStr">
         <is>
-          <t>Core PPI MoMJAN</t>
+          <t>Jobless Claims 4-week AverageFEB/08</t>
         </is>
       </c>
       <c r="C473" t="inlineStr">
         <is>
-          <t>0.3%</t>
+          <t>216K</t>
         </is>
       </c>
       <c r="D473" t="inlineStr">
         <is>
-          <t>0.4%</t>
-        </is>
-      </c>
-      <c r="E473" t="inlineStr">
-        <is>
-          <t>0.3%</t>
-        </is>
-      </c>
+          <t>217K</t>
+        </is>
+      </c>
+      <c r="E473" t="inlineStr"/>
       <c r="F473" t="inlineStr">
         <is>
-          <t>0.1%</t>
+          <t>216.0K</t>
         </is>
       </c>
       <c r="G473" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="474">
@@ -14325,31 +14321,31 @@
       </c>
       <c r="B474" t="inlineStr">
         <is>
-          <t>PPI YoYJAN</t>
+          <t>PPI MoMJAN</t>
         </is>
       </c>
       <c r="C474" t="inlineStr">
         <is>
-          <t>3.5%</t>
+          <t>0.4%</t>
         </is>
       </c>
       <c r="D474" t="inlineStr">
         <is>
-          <t>3.5%</t>
+          <t>0.5%</t>
         </is>
       </c>
       <c r="E474" t="inlineStr">
         <is>
-          <t>3.2%</t>
+          <t>0.3%</t>
         </is>
       </c>
       <c r="F474" t="inlineStr">
         <is>
-          <t>3.4%</t>
+          <t>0.3%</t>
         </is>
       </c>
       <c r="G474" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="475">
@@ -14360,31 +14356,31 @@
       </c>
       <c r="B475" t="inlineStr">
         <is>
-          <t>Initial Jobless ClaimsFEB/08</t>
+          <t>PPI Ex Food, Energy and Trade YoYJAN</t>
         </is>
       </c>
       <c r="C475" t="inlineStr">
         <is>
-          <t>213K</t>
+          <t>3.4%</t>
         </is>
       </c>
       <c r="D475" t="inlineStr">
         <is>
-          <t>220K</t>
+          <t>3.5%</t>
         </is>
       </c>
       <c r="E475" t="inlineStr">
         <is>
-          <t>215K</t>
+          <t>3.2%</t>
         </is>
       </c>
       <c r="F475" t="inlineStr">
         <is>
-          <t>215.0K</t>
+          <t>3.3%</t>
         </is>
       </c>
       <c r="G475" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="476">
@@ -14395,27 +14391,23 @@
       </c>
       <c r="B476" t="inlineStr">
         <is>
-          <t>PPI Ex Food, Energy and Trade YoYJAN</t>
+          <t>PPIJAN</t>
         </is>
       </c>
       <c r="C476" t="inlineStr">
         <is>
-          <t>3.4%</t>
+          <t>147.716</t>
         </is>
       </c>
       <c r="D476" t="inlineStr">
         <is>
-          <t>3.5%</t>
-        </is>
-      </c>
-      <c r="E476" t="inlineStr">
-        <is>
-          <t>3.2%</t>
-        </is>
-      </c>
+          <t>147.127</t>
+        </is>
+      </c>
+      <c r="E476" t="inlineStr"/>
       <c r="F476" t="inlineStr">
         <is>
-          <t>3.3%</t>
+          <t>147.2</t>
         </is>
       </c>
       <c r="G476" t="n">
@@ -14430,23 +14422,27 @@
       </c>
       <c r="B477" t="inlineStr">
         <is>
-          <t>PPI Ex Food, Energy and Trade MoMJAN</t>
+          <t>PPI YoYJAN</t>
         </is>
       </c>
       <c r="C477" t="inlineStr">
         <is>
-          <t>0.3%</t>
+          <t>3.5%</t>
         </is>
       </c>
       <c r="D477" t="inlineStr">
         <is>
-          <t>0.4%</t>
-        </is>
-      </c>
-      <c r="E477" t="inlineStr"/>
+          <t>3.5%</t>
+        </is>
+      </c>
+      <c r="E477" t="inlineStr">
+        <is>
+          <t>3.2%</t>
+        </is>
+      </c>
       <c r="F477" t="inlineStr">
         <is>
-          <t>0.2%</t>
+          <t>3.4%</t>
         </is>
       </c>
       <c r="G477" t="n">
@@ -14461,19 +14457,19 @@
       </c>
       <c r="B478" t="inlineStr">
         <is>
-          <t>PPI MoMJAN</t>
+          <t>Core PPI MoMJAN</t>
         </is>
       </c>
       <c r="C478" t="inlineStr">
         <is>
+          <t>0.3%</t>
+        </is>
+      </c>
+      <c r="D478" t="inlineStr">
+        <is>
           <t>0.4%</t>
         </is>
       </c>
-      <c r="D478" t="inlineStr">
-        <is>
-          <t>0.5%</t>
-        </is>
-      </c>
       <c r="E478" t="inlineStr">
         <is>
           <t>0.3%</t>
@@ -14481,11 +14477,11 @@
       </c>
       <c r="F478" t="inlineStr">
         <is>
-          <t>0.3%</t>
+          <t>0.1%</t>
         </is>
       </c>
       <c r="G478" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="479">
@@ -14496,23 +14492,27 @@
       </c>
       <c r="B479" t="inlineStr">
         <is>
-          <t>Jobless Claims 4-week AverageFEB/08</t>
+          <t>Core PPI YoYJAN</t>
         </is>
       </c>
       <c r="C479" t="inlineStr">
         <is>
-          <t>216K</t>
+          <t>3.6%</t>
         </is>
       </c>
       <c r="D479" t="inlineStr">
         <is>
-          <t>217K</t>
-        </is>
-      </c>
-      <c r="E479" t="inlineStr"/>
+          <t>3.7%</t>
+        </is>
+      </c>
+      <c r="E479" t="inlineStr">
+        <is>
+          <t>3.3%</t>
+        </is>
+      </c>
       <c r="F479" t="inlineStr">
         <is>
-          <t>216.0K</t>
+          <t>3.5%</t>
         </is>
       </c>
       <c r="G479" t="n">
@@ -14527,31 +14527,31 @@
       </c>
       <c r="B480" t="inlineStr">
         <is>
-          <t>Continuing Jobless ClaimsFEB/01</t>
+          <t>Initial Jobless ClaimsFEB/08</t>
         </is>
       </c>
       <c r="C480" t="inlineStr">
         <is>
-          <t>1850K</t>
+          <t>213K</t>
         </is>
       </c>
       <c r="D480" t="inlineStr">
         <is>
-          <t>1886K</t>
+          <t>220K</t>
         </is>
       </c>
       <c r="E480" t="inlineStr">
         <is>
-          <t>1880K</t>
+          <t>215K</t>
         </is>
       </c>
       <c r="F480" t="inlineStr">
         <is>
-          <t>1875.0K</t>
+          <t>215.0K</t>
         </is>
       </c>
       <c r="G480" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="481">
@@ -14728,31 +14728,31 @@
       </c>
       <c r="B487" t="inlineStr">
         <is>
-          <t>Retail Sales Control Group MoMJAN</t>
+          <t>Retail Sales MoMJAN</t>
         </is>
       </c>
       <c r="C487" t="inlineStr">
         <is>
-          <t>-0.8%</t>
+          <t>-0.9%</t>
         </is>
       </c>
       <c r="D487" t="inlineStr">
         <is>
-          <t>0.8%</t>
+          <t>0.7%</t>
         </is>
       </c>
       <c r="E487" t="inlineStr">
         <is>
-          <t>0.3%</t>
+          <t>-0.1%</t>
         </is>
       </c>
       <c r="F487" t="inlineStr">
         <is>
-          <t>0.4%</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="G487" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="488">
@@ -14763,22 +14763,22 @@
       </c>
       <c r="B488" t="inlineStr">
         <is>
-          <t>Export Prices MoMJAN</t>
+          <t>Import Prices MoMJAN</t>
         </is>
       </c>
       <c r="C488" t="inlineStr">
         <is>
-          <t>1.3%</t>
+          <t>0.3%</t>
         </is>
       </c>
       <c r="D488" t="inlineStr">
         <is>
-          <t>0.5%</t>
+          <t>0.2%</t>
         </is>
       </c>
       <c r="E488" t="inlineStr">
         <is>
-          <t>0.3%</t>
+          <t>0.4%</t>
         </is>
       </c>
       <c r="F488" t="inlineStr">
@@ -14798,27 +14798,31 @@
       </c>
       <c r="B489" t="inlineStr">
         <is>
-          <t>Retail Sales Ex Gas/Autos MoMJAN</t>
+          <t>Retail Sales Ex Autos MoMJAN</t>
         </is>
       </c>
       <c r="C489" t="inlineStr">
         <is>
-          <t>-0.5%</t>
+          <t>-0.4%</t>
         </is>
       </c>
       <c r="D489" t="inlineStr">
         <is>
-          <t>0.5%</t>
-        </is>
-      </c>
-      <c r="E489" t="inlineStr"/>
+          <t>0.7%</t>
+        </is>
+      </c>
+      <c r="E489" t="inlineStr">
+        <is>
+          <t>0.3%</t>
+        </is>
+      </c>
       <c r="F489" t="inlineStr">
         <is>
-          <t>0.2%</t>
+          <t>0.3%</t>
         </is>
       </c>
       <c r="G489" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="490">
@@ -14829,23 +14833,23 @@
       </c>
       <c r="B490" t="inlineStr">
         <is>
-          <t>Export Prices YoYJAN</t>
+          <t>Retail Sales YoYJAN</t>
         </is>
       </c>
       <c r="C490" t="inlineStr">
         <is>
-          <t>2.7%</t>
+          <t>4.2%</t>
         </is>
       </c>
       <c r="D490" t="inlineStr">
         <is>
-          <t>2%</t>
+          <t>4.4%</t>
         </is>
       </c>
       <c r="E490" t="inlineStr"/>
       <c r="F490" t="inlineStr">
         <is>
-          <t>2.3%</t>
+          <t>3.7%</t>
         </is>
       </c>
       <c r="G490" t="n">
@@ -14860,23 +14864,23 @@
       </c>
       <c r="B491" t="inlineStr">
         <is>
-          <t>Retail Sales YoYJAN</t>
+          <t>Import Prices YoYJAN</t>
         </is>
       </c>
       <c r="C491" t="inlineStr">
         <is>
-          <t>4.2%</t>
+          <t>1.9%</t>
         </is>
       </c>
       <c r="D491" t="inlineStr">
         <is>
-          <t>4.4%</t>
+          <t>2.2%</t>
         </is>
       </c>
       <c r="E491" t="inlineStr"/>
       <c r="F491" t="inlineStr">
         <is>
-          <t>3.7%</t>
+          <t>2.8%</t>
         </is>
       </c>
       <c r="G491" t="n">
@@ -14891,31 +14895,27 @@
       </c>
       <c r="B492" t="inlineStr">
         <is>
-          <t>Retail Sales MoMJAN</t>
+          <t>Retail Sales Ex Gas/Autos MoMJAN</t>
         </is>
       </c>
       <c r="C492" t="inlineStr">
         <is>
-          <t>-0.9%</t>
+          <t>-0.5%</t>
         </is>
       </c>
       <c r="D492" t="inlineStr">
         <is>
-          <t>0.7%</t>
-        </is>
-      </c>
-      <c r="E492" t="inlineStr">
-        <is>
-          <t>-0.1%</t>
-        </is>
-      </c>
+          <t>0.5%</t>
+        </is>
+      </c>
+      <c r="E492" t="inlineStr"/>
       <c r="F492" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>0.2%</t>
         </is>
       </c>
       <c r="G492" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="493">
@@ -14926,31 +14926,27 @@
       </c>
       <c r="B493" t="inlineStr">
         <is>
-          <t>Retail Sales Ex Autos MoMJAN</t>
+          <t>Export Prices YoYJAN</t>
         </is>
       </c>
       <c r="C493" t="inlineStr">
         <is>
-          <t>-0.4%</t>
+          <t>2.7%</t>
         </is>
       </c>
       <c r="D493" t="inlineStr">
         <is>
-          <t>0.7%</t>
-        </is>
-      </c>
-      <c r="E493" t="inlineStr">
-        <is>
-          <t>0.3%</t>
-        </is>
-      </c>
+          <t>2%</t>
+        </is>
+      </c>
+      <c r="E493" t="inlineStr"/>
       <c r="F493" t="inlineStr">
         <is>
-          <t>0.3%</t>
+          <t>2.3%</t>
         </is>
       </c>
       <c r="G493" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="494">
@@ -14961,27 +14957,31 @@
       </c>
       <c r="B494" t="inlineStr">
         <is>
-          <t>Import Prices YoYJAN</t>
+          <t>Retail Sales Control Group MoMJAN</t>
         </is>
       </c>
       <c r="C494" t="inlineStr">
         <is>
-          <t>1.9%</t>
+          <t>-0.8%</t>
         </is>
       </c>
       <c r="D494" t="inlineStr">
         <is>
-          <t>2.2%</t>
-        </is>
-      </c>
-      <c r="E494" t="inlineStr"/>
+          <t>0.8%</t>
+        </is>
+      </c>
+      <c r="E494" t="inlineStr">
+        <is>
+          <t>0.3%</t>
+        </is>
+      </c>
       <c r="F494" t="inlineStr">
         <is>
-          <t>2.8%</t>
+          <t>0.4%</t>
         </is>
       </c>
       <c r="G494" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="495">
@@ -14992,22 +14992,22 @@
       </c>
       <c r="B495" t="inlineStr">
         <is>
-          <t>Import Prices MoMJAN</t>
+          <t>Export Prices MoMJAN</t>
         </is>
       </c>
       <c r="C495" t="inlineStr">
         <is>
+          <t>1.3%</t>
+        </is>
+      </c>
+      <c r="D495" t="inlineStr">
+        <is>
+          <t>0.5%</t>
+        </is>
+      </c>
+      <c r="E495" t="inlineStr">
+        <is>
           <t>0.3%</t>
-        </is>
-      </c>
-      <c r="D495" t="inlineStr">
-        <is>
-          <t>0.2%</t>
-        </is>
-      </c>
-      <c r="E495" t="inlineStr">
-        <is>
-          <t>0.4%</t>
         </is>
       </c>
       <c r="F495" t="inlineStr">
@@ -15714,23 +15714,23 @@
       </c>
       <c r="B521" t="inlineStr">
         <is>
-          <t>MBA 30-Year Mortgage RateFEB/14</t>
+          <t>MBA Mortgage Refinance IndexFEB/14</t>
         </is>
       </c>
       <c r="C521" t="inlineStr">
         <is>
-          <t>6.93%</t>
+          <t>593.6</t>
         </is>
       </c>
       <c r="D521" t="inlineStr">
         <is>
-          <t>6.95%</t>
+          <t>640.6</t>
         </is>
       </c>
       <c r="E521" t="inlineStr"/>
       <c r="F521" t="inlineStr"/>
       <c r="G521" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="522">
@@ -15741,17 +15741,17 @@
       </c>
       <c r="B522" t="inlineStr">
         <is>
-          <t>MBA Mortgage ApplicationsFEB/14</t>
+          <t>MBA Purchase IndexFEB/14</t>
         </is>
       </c>
       <c r="C522" t="inlineStr">
         <is>
-          <t>-6.6%</t>
+          <t>144.0</t>
         </is>
       </c>
       <c r="D522" t="inlineStr">
         <is>
-          <t>2.3%</t>
+          <t>153.1</t>
         </is>
       </c>
       <c r="E522" t="inlineStr"/>
@@ -15795,23 +15795,23 @@
       </c>
       <c r="B524" t="inlineStr">
         <is>
-          <t>MBA Purchase IndexFEB/14</t>
+          <t>MBA 30-Year Mortgage RateFEB/14</t>
         </is>
       </c>
       <c r="C524" t="inlineStr">
         <is>
-          <t>144.0</t>
+          <t>6.93%</t>
         </is>
       </c>
       <c r="D524" t="inlineStr">
         <is>
-          <t>153.1</t>
+          <t>6.95%</t>
         </is>
       </c>
       <c r="E524" t="inlineStr"/>
       <c r="F524" t="inlineStr"/>
       <c r="G524" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="525">
@@ -15822,17 +15822,17 @@
       </c>
       <c r="B525" t="inlineStr">
         <is>
-          <t>MBA Mortgage Refinance IndexFEB/14</t>
+          <t>MBA Mortgage ApplicationsFEB/14</t>
         </is>
       </c>
       <c r="C525" t="inlineStr">
         <is>
-          <t>593.6</t>
+          <t>-6.6%</t>
         </is>
       </c>
       <c r="D525" t="inlineStr">
         <is>
-          <t>640.6</t>
+          <t>2.3%</t>
         </is>
       </c>
       <c r="E525" t="inlineStr"/>
@@ -16510,17 +16510,17 @@
       </c>
       <c r="B549" t="inlineStr">
         <is>
-          <t>4-Week Bill Auction</t>
+          <t>8-Week Bill Auction</t>
         </is>
       </c>
       <c r="C549" t="inlineStr">
         <is>
-          <t>4.245%</t>
+          <t>4.235%</t>
         </is>
       </c>
       <c r="D549" t="inlineStr">
         <is>
-          <t>4.250%</t>
+          <t>4.240%</t>
         </is>
       </c>
       <c r="E549" t="inlineStr"/>
@@ -16537,17 +16537,17 @@
       </c>
       <c r="B550" t="inlineStr">
         <is>
-          <t>8-Week Bill Auction</t>
+          <t>4-Week Bill Auction</t>
         </is>
       </c>
       <c r="C550" t="inlineStr">
         <is>
-          <t>4.235%</t>
+          <t>4.245%</t>
         </is>
       </c>
       <c r="D550" t="inlineStr">
         <is>
-          <t>4.240%</t>
+          <t>4.250%</t>
         </is>
       </c>
       <c r="E550" t="inlineStr"/>
@@ -17326,7 +17326,7 @@
       </c>
       <c r="B577" t="inlineStr">
         <is>
-          <t>Fed Jefferson Speech</t>
+          <t>Fed Daly Speech</t>
         </is>
       </c>
       <c r="C577" t="inlineStr"/>
@@ -17345,7 +17345,7 @@
       </c>
       <c r="B578" t="inlineStr">
         <is>
-          <t>Fed Daly Speech</t>
+          <t>Fed Jefferson Speech</t>
         </is>
       </c>
       <c r="C578" t="inlineStr"/>
@@ -17633,10 +17633,14 @@
           <t>House Price Index YoYDEC</t>
         </is>
       </c>
-      <c r="C589" t="inlineStr"/>
+      <c r="C589" t="inlineStr">
+        <is>
+          <t>4.7%</t>
+        </is>
+      </c>
       <c r="D589" t="inlineStr">
         <is>
-          <t>4.2%</t>
+          <t>4.5%</t>
         </is>
       </c>
       <c r="E589" t="inlineStr"/>
@@ -17657,19 +17661,23 @@
       </c>
       <c r="B590" t="inlineStr">
         <is>
-          <t>House Price IndexDEC</t>
-        </is>
-      </c>
-      <c r="C590" t="inlineStr"/>
+          <t>S&amp;P/Case-Shiller Home Price MoMDEC</t>
+        </is>
+      </c>
+      <c r="C590" t="inlineStr">
+        <is>
+          <t>-0.1%</t>
+        </is>
+      </c>
       <c r="D590" t="inlineStr">
         <is>
-          <t>433.4</t>
+          <t>-0.1%</t>
         </is>
       </c>
       <c r="E590" t="inlineStr"/>
       <c r="F590" t="inlineStr">
         <is>
-          <t>434.3</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="G590" t="n">
@@ -17684,27 +17692,27 @@
       </c>
       <c r="B591" t="inlineStr">
         <is>
-          <t>S&amp;P/Case-Shiller Home Price YoYDEC</t>
+          <t>House Price Index MoMDEC</t>
         </is>
       </c>
       <c r="C591" t="inlineStr"/>
       <c r="D591" t="inlineStr">
         <is>
-          <t>4.3%</t>
+          <t>0.3%</t>
         </is>
       </c>
       <c r="E591" t="inlineStr">
         <is>
-          <t>4.4%</t>
+          <t>0.2%</t>
         </is>
       </c>
       <c r="F591" t="inlineStr">
         <is>
-          <t>4.4%</t>
+          <t>0.2%</t>
         </is>
       </c>
       <c r="G591" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="592">
@@ -17715,19 +17723,27 @@
       </c>
       <c r="B592" t="inlineStr">
         <is>
-          <t>S&amp;P/Case-Shiller Home Price MoMDEC</t>
-        </is>
-      </c>
-      <c r="C592" t="inlineStr"/>
+          <t>House Price Index MoMDEC</t>
+        </is>
+      </c>
+      <c r="C592" t="inlineStr">
+        <is>
+          <t>0.4%</t>
+        </is>
+      </c>
       <c r="D592" t="inlineStr">
         <is>
-          <t>-0.1%</t>
-        </is>
-      </c>
-      <c r="E592" t="inlineStr"/>
+          <t>0.4%</t>
+        </is>
+      </c>
+      <c r="E592" t="inlineStr">
+        <is>
+          <t>0.2%</t>
+        </is>
+      </c>
       <c r="F592" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>0.2%</t>
         </is>
       </c>
       <c r="G592" t="n">
@@ -17742,31 +17758,27 @@
       </c>
       <c r="B593" t="inlineStr">
         <is>
-          <t>S&amp;P/Case-Shiller Home Price YoYDEC</t>
+          <t>House Price IndexDEC</t>
         </is>
       </c>
       <c r="C593" t="inlineStr">
         <is>
-          <t>4.5%</t>
+          <t>436.1</t>
         </is>
       </c>
       <c r="D593" t="inlineStr">
         <is>
-          <t>4.3%</t>
-        </is>
-      </c>
-      <c r="E593" t="inlineStr">
-        <is>
-          <t>4.4%</t>
-        </is>
-      </c>
+          <t>434.3</t>
+        </is>
+      </c>
+      <c r="E593" t="inlineStr"/>
       <c r="F593" t="inlineStr">
         <is>
-          <t>4.4%</t>
+          <t>434.3</t>
         </is>
       </c>
       <c r="G593" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="594">
@@ -17777,27 +17789,19 @@
       </c>
       <c r="B594" t="inlineStr">
         <is>
-          <t>House Price Index MoMDEC</t>
-        </is>
-      </c>
-      <c r="C594" t="inlineStr">
-        <is>
-          <t>0.4%</t>
-        </is>
-      </c>
+          <t>S&amp;P/Case-Shiller Home Price MoMDEC</t>
+        </is>
+      </c>
+      <c r="C594" t="inlineStr"/>
       <c r="D594" t="inlineStr">
         <is>
-          <t>0.4%</t>
-        </is>
-      </c>
-      <c r="E594" t="inlineStr">
-        <is>
-          <t>0.2%</t>
-        </is>
-      </c>
+          <t>-0.1%</t>
+        </is>
+      </c>
+      <c r="E594" t="inlineStr"/>
       <c r="F594" t="inlineStr">
         <is>
-          <t>0.2%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="G594" t="n">
@@ -17812,27 +17816,27 @@
       </c>
       <c r="B595" t="inlineStr">
         <is>
-          <t>House Price IndexDEC</t>
-        </is>
-      </c>
-      <c r="C595" t="inlineStr">
-        <is>
-          <t>436.1</t>
-        </is>
-      </c>
+          <t>S&amp;P/Case-Shiller Home Price YoYDEC</t>
+        </is>
+      </c>
+      <c r="C595" t="inlineStr"/>
       <c r="D595" t="inlineStr">
         <is>
-          <t>434.3</t>
-        </is>
-      </c>
-      <c r="E595" t="inlineStr"/>
+          <t>4.3%</t>
+        </is>
+      </c>
+      <c r="E595" t="inlineStr">
+        <is>
+          <t>4.4%</t>
+        </is>
+      </c>
       <c r="F595" t="inlineStr">
         <is>
-          <t>434.3</t>
+          <t>4.4%</t>
         </is>
       </c>
       <c r="G595" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="596">
@@ -17843,23 +17847,19 @@
       </c>
       <c r="B596" t="inlineStr">
         <is>
-          <t>House Price Index MoMDEC</t>
+          <t>House Price IndexDEC</t>
         </is>
       </c>
       <c r="C596" t="inlineStr"/>
       <c r="D596" t="inlineStr">
         <is>
-          <t>0.3%</t>
-        </is>
-      </c>
-      <c r="E596" t="inlineStr">
-        <is>
-          <t>0.2%</t>
-        </is>
-      </c>
+          <t>433.4</t>
+        </is>
+      </c>
+      <c r="E596" t="inlineStr"/>
       <c r="F596" t="inlineStr">
         <is>
-          <t>0.2%</t>
+          <t>434.3</t>
         </is>
       </c>
       <c r="G596" t="n">
@@ -17874,23 +17874,19 @@
       </c>
       <c r="B597" t="inlineStr">
         <is>
-          <t>S&amp;P/Case-Shiller Home Price MoMDEC</t>
-        </is>
-      </c>
-      <c r="C597" t="inlineStr">
-        <is>
-          <t>-0.1%</t>
-        </is>
-      </c>
+          <t>House Price Index YoYDEC</t>
+        </is>
+      </c>
+      <c r="C597" t="inlineStr"/>
       <c r="D597" t="inlineStr">
         <is>
-          <t>-0.1%</t>
+          <t>4.2%</t>
         </is>
       </c>
       <c r="E597" t="inlineStr"/>
       <c r="F597" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>4.1%</t>
         </is>
       </c>
       <c r="G597" t="n">
@@ -17905,27 +17901,31 @@
       </c>
       <c r="B598" t="inlineStr">
         <is>
-          <t>House Price Index YoYDEC</t>
+          <t>S&amp;P/Case-Shiller Home Price YoYDEC</t>
         </is>
       </c>
       <c r="C598" t="inlineStr">
         <is>
-          <t>4.7%</t>
+          <t>4.5%</t>
         </is>
       </c>
       <c r="D598" t="inlineStr">
         <is>
-          <t>4.5%</t>
-        </is>
-      </c>
-      <c r="E598" t="inlineStr"/>
+          <t>4.3%</t>
+        </is>
+      </c>
+      <c r="E598" t="inlineStr">
+        <is>
+          <t>4.4%</t>
+        </is>
+      </c>
       <c r="F598" t="inlineStr">
         <is>
-          <t>4.1%</t>
+          <t>4.4%</t>
         </is>
       </c>
       <c r="G598" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="599">
@@ -17936,27 +17936,27 @@
       </c>
       <c r="B599" t="inlineStr">
         <is>
-          <t>Richmond Fed Services Revenues IndexFEB</t>
-        </is>
-      </c>
-      <c r="C599" t="inlineStr">
-        <is>
-          <t>11</t>
-        </is>
-      </c>
+          <t>CB Consumer ConfidenceFEB</t>
+        </is>
+      </c>
+      <c r="C599" t="inlineStr"/>
       <c r="D599" t="inlineStr">
         <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="E599" t="inlineStr"/>
+          <t>104.1</t>
+        </is>
+      </c>
+      <c r="E599" t="inlineStr">
+        <is>
+          <t>103</t>
+        </is>
+      </c>
       <c r="F599" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>103</t>
         </is>
       </c>
       <c r="G599" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="600">
@@ -17970,11 +17970,7 @@
           <t>Richmond Fed Manufacturing IndexFEB</t>
         </is>
       </c>
-      <c r="C600" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
+      <c r="C600" t="inlineStr"/>
       <c r="D600" t="inlineStr">
         <is>
           <t>-4</t>
@@ -18002,31 +17998,23 @@
       </c>
       <c r="B601" t="inlineStr">
         <is>
-          <t>CB Consumer ConfidenceFEB</t>
-        </is>
-      </c>
-      <c r="C601" t="inlineStr">
-        <is>
-          <t>98.3</t>
-        </is>
-      </c>
+          <t>Richmond Fed Services Revenues IndexFEB</t>
+        </is>
+      </c>
+      <c r="C601" t="inlineStr"/>
       <c r="D601" t="inlineStr">
         <is>
-          <t>105.3</t>
-        </is>
-      </c>
-      <c r="E601" t="inlineStr">
-        <is>
-          <t>102.5</t>
-        </is>
-      </c>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="E601" t="inlineStr"/>
       <c r="F601" t="inlineStr">
         <is>
-          <t>103</t>
+          <t>7</t>
         </is>
       </c>
       <c r="G601" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="602">
@@ -18040,11 +18028,7 @@
           <t>Richmond Fed Manufacturing Shipments IndexFEB</t>
         </is>
       </c>
-      <c r="C602" t="inlineStr">
-        <is>
-          <t>12</t>
-        </is>
-      </c>
+      <c r="C602" t="inlineStr"/>
       <c r="D602" t="inlineStr">
         <is>
           <t>-9</t>
@@ -18068,23 +18052,31 @@
       </c>
       <c r="B603" t="inlineStr">
         <is>
-          <t>Richmond Fed Services Revenues IndexFEB</t>
-        </is>
-      </c>
-      <c r="C603" t="inlineStr"/>
+          <t>CB Consumer ConfidenceFEB</t>
+        </is>
+      </c>
+      <c r="C603" t="inlineStr">
+        <is>
+          <t>98.3</t>
+        </is>
+      </c>
       <c r="D603" t="inlineStr">
         <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="E603" t="inlineStr"/>
+          <t>105.3</t>
+        </is>
+      </c>
+      <c r="E603" t="inlineStr">
+        <is>
+          <t>102.5</t>
+        </is>
+      </c>
       <c r="F603" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>103</t>
         </is>
       </c>
       <c r="G603" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="604">
@@ -18098,7 +18090,11 @@
           <t>Richmond Fed Manufacturing IndexFEB</t>
         </is>
       </c>
-      <c r="C604" t="inlineStr"/>
+      <c r="C604" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
       <c r="D604" t="inlineStr">
         <is>
           <t>-4</t>
@@ -18126,19 +18122,23 @@
       </c>
       <c r="B605" t="inlineStr">
         <is>
-          <t>Richmond Fed Manufacturing Shipments IndexFEB</t>
-        </is>
-      </c>
-      <c r="C605" t="inlineStr"/>
+          <t>Richmond Fed Services Revenues IndexFEB</t>
+        </is>
+      </c>
+      <c r="C605" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
       <c r="D605" t="inlineStr">
         <is>
-          <t>-9</t>
+          <t>4</t>
         </is>
       </c>
       <c r="E605" t="inlineStr"/>
       <c r="F605" t="inlineStr">
         <is>
-          <t>-4</t>
+          <t>7</t>
         </is>
       </c>
       <c r="G605" t="n">
@@ -18153,27 +18153,27 @@
       </c>
       <c r="B606" t="inlineStr">
         <is>
-          <t>CB Consumer ConfidenceFEB</t>
-        </is>
-      </c>
-      <c r="C606" t="inlineStr"/>
+          <t>Richmond Fed Manufacturing Shipments IndexFEB</t>
+        </is>
+      </c>
+      <c r="C606" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
       <c r="D606" t="inlineStr">
         <is>
-          <t>104.1</t>
-        </is>
-      </c>
-      <c r="E606" t="inlineStr">
-        <is>
-          <t>103</t>
-        </is>
-      </c>
+          <t>-9</t>
+        </is>
+      </c>
+      <c r="E606" t="inlineStr"/>
       <c r="F606" t="inlineStr">
         <is>
-          <t>103</t>
+          <t>-4</t>
         </is>
       </c>
       <c r="G606" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="607">
@@ -18319,15 +18319,19 @@
       </c>
       <c r="B612" t="inlineStr">
         <is>
-          <t>Fed Barkin Speech</t>
+          <t>5-Year Note Auction</t>
         </is>
       </c>
       <c r="C612" t="inlineStr"/>
-      <c r="D612" t="inlineStr"/>
+      <c r="D612" t="inlineStr">
+        <is>
+          <t>4.33%</t>
+        </is>
+      </c>
       <c r="E612" t="inlineStr"/>
       <c r="F612" t="inlineStr"/>
       <c r="G612" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="613">
@@ -18338,23 +18342,15 @@
       </c>
       <c r="B613" t="inlineStr">
         <is>
-          <t>Money SupplyJAN</t>
-        </is>
-      </c>
-      <c r="C613" t="inlineStr">
-        <is>
-          <t>$21.56T</t>
-        </is>
-      </c>
-      <c r="D613" t="inlineStr">
-        <is>
-          <t>$21.53T</t>
-        </is>
-      </c>
+          <t>Fed Barkin Speech</t>
+        </is>
+      </c>
+      <c r="C613" t="inlineStr"/>
+      <c r="D613" t="inlineStr"/>
       <c r="E613" t="inlineStr"/>
       <c r="F613" t="inlineStr"/>
       <c r="G613" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="614">
@@ -18368,7 +18364,11 @@
           <t>Money SupplyJAN</t>
         </is>
       </c>
-      <c r="C614" t="inlineStr"/>
+      <c r="C614" t="inlineStr">
+        <is>
+          <t>$21.56T</t>
+        </is>
+      </c>
       <c r="D614" t="inlineStr">
         <is>
           <t>$21.53T</t>
@@ -18388,13 +18388,13 @@
       </c>
       <c r="B615" t="inlineStr">
         <is>
-          <t>5-Year Note Auction</t>
+          <t>Money SupplyJAN</t>
         </is>
       </c>
       <c r="C615" t="inlineStr"/>
       <c r="D615" t="inlineStr">
         <is>
-          <t>4.33%</t>
+          <t>$21.53T</t>
         </is>
       </c>
       <c r="E615" t="inlineStr"/>
@@ -18654,13 +18654,13 @@
       </c>
       <c r="B625" t="inlineStr">
         <is>
-          <t>MBA Mortgage ApplicationsFEB/21</t>
+          <t>MBA Mortgage Refinance IndexFEB/21</t>
         </is>
       </c>
       <c r="C625" t="inlineStr"/>
       <c r="D625" t="inlineStr">
         <is>
-          <t>-6.6%</t>
+          <t>593.6</t>
         </is>
       </c>
       <c r="E625" t="inlineStr"/>
@@ -18677,19 +18677,19 @@
       </c>
       <c r="B626" t="inlineStr">
         <is>
-          <t>MBA 30-Year Mortgage RateFEB/21</t>
+          <t>MBA Purchase IndexFEB/21</t>
         </is>
       </c>
       <c r="C626" t="inlineStr"/>
       <c r="D626" t="inlineStr">
         <is>
-          <t>6.93%</t>
+          <t>144.0</t>
         </is>
       </c>
       <c r="E626" t="inlineStr"/>
       <c r="F626" t="inlineStr"/>
       <c r="G626" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="627">
@@ -18700,19 +18700,19 @@
       </c>
       <c r="B627" t="inlineStr">
         <is>
-          <t>MBA Purchase IndexFEB/21</t>
+          <t>MBA 30-Year Mortgage RateFEB/21</t>
         </is>
       </c>
       <c r="C627" t="inlineStr"/>
       <c r="D627" t="inlineStr">
         <is>
-          <t>144.0</t>
+          <t>6.93%</t>
         </is>
       </c>
       <c r="E627" t="inlineStr"/>
       <c r="F627" t="inlineStr"/>
       <c r="G627" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="628">
@@ -18723,13 +18723,13 @@
       </c>
       <c r="B628" t="inlineStr">
         <is>
-          <t>MBA Mortgage Refinance IndexFEB/21</t>
+          <t>MBA Mortgage ApplicationsFEB/21</t>
         </is>
       </c>
       <c r="C628" t="inlineStr"/>
       <c r="D628" t="inlineStr">
         <is>
-          <t>593.6</t>
+          <t>-6.6%</t>
         </is>
       </c>
       <c r="E628" t="inlineStr"/>
@@ -19048,13 +19048,13 @@
       </c>
       <c r="B639" t="inlineStr">
         <is>
-          <t>EIA Heating Oil Stocks ChangeFEB/21</t>
+          <t>EIA Cushing Crude Oil Stocks ChangeFEB/21</t>
         </is>
       </c>
       <c r="C639" t="inlineStr"/>
       <c r="D639" t="inlineStr">
         <is>
-          <t>-0.343M</t>
+          <t>1.472M</t>
         </is>
       </c>
       <c r="E639" t="inlineStr"/>
@@ -19071,19 +19071,23 @@
       </c>
       <c r="B640" t="inlineStr">
         <is>
-          <t>EIA Gasoline Production ChangeFEB/21</t>
+          <t>EIA Gasoline Stocks ChangeFEB/21</t>
         </is>
       </c>
       <c r="C640" t="inlineStr"/>
       <c r="D640" t="inlineStr">
         <is>
-          <t>-0.156M</t>
-        </is>
-      </c>
-      <c r="E640" t="inlineStr"/>
+          <t>-0.151M</t>
+        </is>
+      </c>
+      <c r="E640" t="inlineStr">
+        <is>
+          <t>-1.30M</t>
+        </is>
+      </c>
       <c r="F640" t="inlineStr"/>
       <c r="G640" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="641">
@@ -19094,23 +19098,23 @@
       </c>
       <c r="B641" t="inlineStr">
         <is>
-          <t>EIA Distillate Stocks ChangeFEB/21</t>
+          <t>EIA Crude Oil Stocks ChangeFEB/21</t>
         </is>
       </c>
       <c r="C641" t="inlineStr"/>
       <c r="D641" t="inlineStr">
         <is>
-          <t>-2.051M</t>
+          <t>4.633M</t>
         </is>
       </c>
       <c r="E641" t="inlineStr">
         <is>
-          <t>1.63M</t>
+          <t>2.34M</t>
         </is>
       </c>
       <c r="F641" t="inlineStr"/>
       <c r="G641" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="642">
@@ -19144,23 +19148,23 @@
       </c>
       <c r="B643" t="inlineStr">
         <is>
-          <t>EIA Crude Oil Stocks ChangeFEB/21</t>
+          <t>EIA Distillate Stocks ChangeFEB/21</t>
         </is>
       </c>
       <c r="C643" t="inlineStr"/>
       <c r="D643" t="inlineStr">
         <is>
-          <t>4.633M</t>
+          <t>-2.051M</t>
         </is>
       </c>
       <c r="E643" t="inlineStr">
         <is>
-          <t>2.34M</t>
+          <t>1.63M</t>
         </is>
       </c>
       <c r="F643" t="inlineStr"/>
       <c r="G643" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="644">
@@ -19171,23 +19175,19 @@
       </c>
       <c r="B644" t="inlineStr">
         <is>
-          <t>EIA Gasoline Stocks ChangeFEB/21</t>
+          <t>EIA Gasoline Production ChangeFEB/21</t>
         </is>
       </c>
       <c r="C644" t="inlineStr"/>
       <c r="D644" t="inlineStr">
         <is>
-          <t>-0.151M</t>
-        </is>
-      </c>
-      <c r="E644" t="inlineStr">
-        <is>
-          <t>-1.30M</t>
-        </is>
-      </c>
+          <t>-0.156M</t>
+        </is>
+      </c>
+      <c r="E644" t="inlineStr"/>
       <c r="F644" t="inlineStr"/>
       <c r="G644" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="645">
@@ -19198,13 +19198,13 @@
       </c>
       <c r="B645" t="inlineStr">
         <is>
-          <t>EIA Cushing Crude Oil Stocks ChangeFEB/21</t>
+          <t>EIA Heating Oil Stocks ChangeFEB/21</t>
         </is>
       </c>
       <c r="C645" t="inlineStr"/>
       <c r="D645" t="inlineStr">
         <is>
-          <t>1.472M</t>
+          <t>-0.343M</t>
         </is>
       </c>
       <c r="E645" t="inlineStr"/>
@@ -19221,13 +19221,13 @@
       </c>
       <c r="B646" t="inlineStr">
         <is>
-          <t>EIA Crude Oil Imports ChangeFEB/21</t>
+          <t>EIA Refinery Crude Runs ChangeFEB/21</t>
         </is>
       </c>
       <c r="C646" t="inlineStr"/>
       <c r="D646" t="inlineStr">
         <is>
-          <t>-0.961M</t>
+          <t>-0.015M</t>
         </is>
       </c>
       <c r="E646" t="inlineStr"/>
@@ -19499,13 +19499,13 @@
       </c>
       <c r="B656" t="inlineStr">
         <is>
-          <t>EIA Refinery Crude Runs ChangeFEB/21</t>
+          <t>EIA Crude Oil Imports ChangeFEB/21</t>
         </is>
       </c>
       <c r="C656" t="inlineStr"/>
       <c r="D656" t="inlineStr">
         <is>
-          <t>-0.015M</t>
+          <t>-0.961M</t>
         </is>
       </c>
       <c r="E656" t="inlineStr"/>
@@ -19772,13 +19772,13 @@
       </c>
       <c r="B667" t="inlineStr">
         <is>
-          <t>GDP Growth Rate QoQ 2nd EstQ4</t>
+          <t>PCE Prices QoQ 2nd EstQ4</t>
         </is>
       </c>
       <c r="C667" t="inlineStr"/>
       <c r="D667" t="inlineStr">
         <is>
-          <t>3.1%</t>
+          <t>1.5%</t>
         </is>
       </c>
       <c r="E667" t="inlineStr">
@@ -19792,7 +19792,7 @@
         </is>
       </c>
       <c r="G667" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="668">
@@ -20198,23 +20198,27 @@
       </c>
       <c r="B681" t="inlineStr">
         <is>
-          <t>Continuing Jobless ClaimsFEB/15</t>
+          <t>Initial Jobless ClaimsFEB/22</t>
         </is>
       </c>
       <c r="C681" t="inlineStr"/>
       <c r="D681" t="inlineStr">
         <is>
-          <t>1869K</t>
-        </is>
-      </c>
-      <c r="E681" t="inlineStr"/>
+          <t>219K</t>
+        </is>
+      </c>
+      <c r="E681" t="inlineStr">
+        <is>
+          <t>221K</t>
+        </is>
+      </c>
       <c r="F681" t="inlineStr">
         <is>
-          <t>1874.0K</t>
+          <t>225.0K</t>
         </is>
       </c>
       <c r="G681" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="682">
@@ -20225,27 +20229,27 @@
       </c>
       <c r="B682" t="inlineStr">
         <is>
-          <t>GDP Price Index QoQ 2nd EstQ4</t>
+          <t>GDP Growth Rate QoQ 2nd EstQ4</t>
         </is>
       </c>
       <c r="C682" t="inlineStr"/>
       <c r="D682" t="inlineStr">
         <is>
-          <t>1.9%</t>
+          <t>3.1%</t>
         </is>
       </c>
       <c r="E682" t="inlineStr">
         <is>
-          <t>2.2%</t>
+          <t>2.3%</t>
         </is>
       </c>
       <c r="F682" t="inlineStr">
         <is>
-          <t>2.2%</t>
+          <t>2.3%</t>
         </is>
       </c>
       <c r="G682" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="683">
@@ -20256,23 +20260,19 @@
       </c>
       <c r="B683" t="inlineStr">
         <is>
-          <t>Real Consumer Spending QoQ 2nd EstQ4</t>
+          <t>Continuing Jobless ClaimsFEB/15</t>
         </is>
       </c>
       <c r="C683" t="inlineStr"/>
       <c r="D683" t="inlineStr">
         <is>
-          <t>3.7%</t>
-        </is>
-      </c>
-      <c r="E683" t="inlineStr">
-        <is>
-          <t>4.2%</t>
-        </is>
-      </c>
+          <t>1869K</t>
+        </is>
+      </c>
+      <c r="E683" t="inlineStr"/>
       <c r="F683" t="inlineStr">
         <is>
-          <t>4.2%</t>
+          <t>1874.0K</t>
         </is>
       </c>
       <c r="G683" t="n">
@@ -20287,23 +20287,27 @@
       </c>
       <c r="B684" t="inlineStr">
         <is>
-          <t>Jobless Claims 4-week AverageFEB/22</t>
+          <t>GDP Price Index QoQ 2nd EstQ4</t>
         </is>
       </c>
       <c r="C684" t="inlineStr"/>
       <c r="D684" t="inlineStr">
         <is>
-          <t>215.25K</t>
-        </is>
-      </c>
-      <c r="E684" t="inlineStr"/>
+          <t>1.9%</t>
+        </is>
+      </c>
+      <c r="E684" t="inlineStr">
+        <is>
+          <t>2.2%</t>
+        </is>
+      </c>
       <c r="F684" t="inlineStr">
         <is>
-          <t>220.0K</t>
+          <t>2.2%</t>
         </is>
       </c>
       <c r="G684" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="685">
@@ -20314,27 +20318,27 @@
       </c>
       <c r="B685" t="inlineStr">
         <is>
-          <t>PCE Prices QoQ 2nd EstQ4</t>
+          <t>Durable Goods Orders MoMJAN</t>
         </is>
       </c>
       <c r="C685" t="inlineStr"/>
       <c r="D685" t="inlineStr">
         <is>
-          <t>1.5%</t>
+          <t>-2.2%</t>
         </is>
       </c>
       <c r="E685" t="inlineStr">
         <is>
-          <t>2.3%</t>
+          <t>2%</t>
         </is>
       </c>
       <c r="F685" t="inlineStr">
         <is>
-          <t>2.3%</t>
+          <t>2.2%</t>
         </is>
       </c>
       <c r="G685" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="686">
@@ -20345,27 +20349,23 @@
       </c>
       <c r="B686" t="inlineStr">
         <is>
-          <t>Durable Goods Orders MoMJAN</t>
+          <t>Jobless Claims 4-week AverageFEB/22</t>
         </is>
       </c>
       <c r="C686" t="inlineStr"/>
       <c r="D686" t="inlineStr">
         <is>
-          <t>-2.2%</t>
-        </is>
-      </c>
-      <c r="E686" t="inlineStr">
-        <is>
-          <t>2%</t>
-        </is>
-      </c>
+          <t>215.25K</t>
+        </is>
+      </c>
+      <c r="E686" t="inlineStr"/>
       <c r="F686" t="inlineStr">
         <is>
-          <t>2.2%</t>
+          <t>220.0K</t>
         </is>
       </c>
       <c r="G686" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="687">
@@ -20376,27 +20376,27 @@
       </c>
       <c r="B687" t="inlineStr">
         <is>
-          <t>Initial Jobless ClaimsFEB/22</t>
+          <t>Real Consumer Spending QoQ 2nd EstQ4</t>
         </is>
       </c>
       <c r="C687" t="inlineStr"/>
       <c r="D687" t="inlineStr">
         <is>
-          <t>219K</t>
+          <t>3.7%</t>
         </is>
       </c>
       <c r="E687" t="inlineStr">
         <is>
-          <t>221K</t>
+          <t>4.2%</t>
         </is>
       </c>
       <c r="F687" t="inlineStr">
         <is>
-          <t>225.0K</t>
+          <t>4.2%</t>
         </is>
       </c>
       <c r="G687" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="688">
@@ -20407,23 +20407,27 @@
       </c>
       <c r="B688" t="inlineStr">
         <is>
-          <t>Durable Goods Orders ex Defense MoMJAN</t>
+          <t>Durable Goods Orders Ex Transp MoMJAN</t>
         </is>
       </c>
       <c r="C688" t="inlineStr"/>
       <c r="D688" t="inlineStr">
         <is>
-          <t>-2.4%</t>
-        </is>
-      </c>
-      <c r="E688" t="inlineStr"/>
+          <t>0.3%</t>
+        </is>
+      </c>
+      <c r="E688" t="inlineStr">
+        <is>
+          <t>0.3%</t>
+        </is>
+      </c>
       <c r="F688" t="inlineStr">
         <is>
-          <t>1.4%</t>
+          <t>0.3%</t>
         </is>
       </c>
       <c r="G688" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="689">
@@ -20434,23 +20438,23 @@
       </c>
       <c r="B689" t="inlineStr">
         <is>
-          <t>Core PCE Prices QoQ 2nd EstQ4</t>
+          <t>Non Defense Goods Orders Ex AirJAN</t>
         </is>
       </c>
       <c r="C689" t="inlineStr"/>
       <c r="D689" t="inlineStr">
         <is>
-          <t>2.2%</t>
+          <t>0.5%</t>
         </is>
       </c>
       <c r="E689" t="inlineStr">
         <is>
-          <t>2.5%</t>
+          <t>0.3%</t>
         </is>
       </c>
       <c r="F689" t="inlineStr">
         <is>
-          <t>2.5%</t>
+          <t>0.4%</t>
         </is>
       </c>
       <c r="G689" t="n">
@@ -20496,23 +20500,23 @@
       </c>
       <c r="B691" t="inlineStr">
         <is>
-          <t>Non Defense Goods Orders Ex AirJAN</t>
+          <t>Core PCE Prices QoQ 2nd EstQ4</t>
         </is>
       </c>
       <c r="C691" t="inlineStr"/>
       <c r="D691" t="inlineStr">
         <is>
-          <t>0.5%</t>
+          <t>2.2%</t>
         </is>
       </c>
       <c r="E691" t="inlineStr">
         <is>
-          <t>0.3%</t>
+          <t>2.5%</t>
         </is>
       </c>
       <c r="F691" t="inlineStr">
         <is>
-          <t>0.4%</t>
+          <t>2.5%</t>
         </is>
       </c>
       <c r="G691" t="n">
@@ -20527,27 +20531,23 @@
       </c>
       <c r="B692" t="inlineStr">
         <is>
-          <t>Durable Goods Orders Ex Transp MoMJAN</t>
+          <t>Durable Goods Orders ex Defense MoMJAN</t>
         </is>
       </c>
       <c r="C692" t="inlineStr"/>
       <c r="D692" t="inlineStr">
         <is>
-          <t>0.3%</t>
-        </is>
-      </c>
-      <c r="E692" t="inlineStr">
-        <is>
-          <t>0.3%</t>
-        </is>
-      </c>
+          <t>-2.4%</t>
+        </is>
+      </c>
+      <c r="E692" t="inlineStr"/>
       <c r="F692" t="inlineStr">
         <is>
-          <t>0.3%</t>
+          <t>1.4%</t>
         </is>
       </c>
       <c r="G692" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="693">
@@ -20577,19 +20577,23 @@
       </c>
       <c r="B694" t="inlineStr">
         <is>
-          <t>Pending Home Sales YoYJAN</t>
+          <t>Pending Home Sales MoMJAN</t>
         </is>
       </c>
       <c r="C694" t="inlineStr"/>
       <c r="D694" t="inlineStr">
         <is>
-          <t>-5.0%</t>
-        </is>
-      </c>
-      <c r="E694" t="inlineStr"/>
+          <t>-5.5%</t>
+        </is>
+      </c>
+      <c r="E694" t="inlineStr">
+        <is>
+          <t>-1.3%</t>
+        </is>
+      </c>
       <c r="F694" t="inlineStr">
         <is>
-          <t>6.0%</t>
+          <t>-0.9%</t>
         </is>
       </c>
       <c r="G694" t="n">
@@ -20681,23 +20685,19 @@
       </c>
       <c r="B698" t="inlineStr">
         <is>
-          <t>Pending Home Sales MoMJAN</t>
+          <t>Pending Home Sales YoYJAN</t>
         </is>
       </c>
       <c r="C698" t="inlineStr"/>
       <c r="D698" t="inlineStr">
         <is>
-          <t>-5.5%</t>
-        </is>
-      </c>
-      <c r="E698" t="inlineStr">
-        <is>
-          <t>-1.3%</t>
-        </is>
-      </c>
+          <t>-5.0%</t>
+        </is>
+      </c>
+      <c r="E698" t="inlineStr"/>
       <c r="F698" t="inlineStr">
         <is>
-          <t>-0.9%</t>
+          <t>6.0%</t>
         </is>
       </c>
       <c r="G698" t="n">
@@ -20920,13 +20920,13 @@
       </c>
       <c r="B707" t="inlineStr">
         <is>
-          <t>4-Week Bill Auction</t>
+          <t>8-Week Bill Auction</t>
         </is>
       </c>
       <c r="C707" t="inlineStr"/>
       <c r="D707" t="inlineStr">
         <is>
-          <t>4.245%</t>
+          <t>4.235%</t>
         </is>
       </c>
       <c r="E707" t="inlineStr"/>
@@ -20989,13 +20989,13 @@
       </c>
       <c r="B710" t="inlineStr">
         <is>
-          <t>8-Week Bill Auction</t>
+          <t>4-Week Bill Auction</t>
         </is>
       </c>
       <c r="C710" t="inlineStr"/>
       <c r="D710" t="inlineStr">
         <is>
-          <t>4.235%</t>
+          <t>4.245%</t>
         </is>
       </c>
       <c r="E710" t="inlineStr"/>
@@ -21577,18 +21577,18 @@
       </c>
       <c r="B734" t="inlineStr">
         <is>
-          <t>Personal Spending MoMJAN</t>
+          <t>Personal Income MoMJAN</t>
         </is>
       </c>
       <c r="C734" t="inlineStr"/>
       <c r="D734" t="inlineStr">
         <is>
-          <t>0.7%</t>
+          <t>0.4%</t>
         </is>
       </c>
       <c r="E734" t="inlineStr">
         <is>
-          <t>0.1%</t>
+          <t>0.3%</t>
         </is>
       </c>
       <c r="F734" t="inlineStr">
@@ -21608,23 +21608,27 @@
       </c>
       <c r="B735" t="inlineStr">
         <is>
-          <t>Retail Inventories Ex Autos MoM AdvJAN</t>
+          <t>Core PCE Price Index YoYJAN</t>
         </is>
       </c>
       <c r="C735" t="inlineStr"/>
       <c r="D735" t="inlineStr">
         <is>
-          <t>-0.1%</t>
-        </is>
-      </c>
-      <c r="E735" t="inlineStr"/>
+          <t>2.8%</t>
+        </is>
+      </c>
+      <c r="E735" t="inlineStr">
+        <is>
+          <t>2.6%</t>
+        </is>
+      </c>
       <c r="F735" t="inlineStr">
         <is>
-          <t>0.1%</t>
+          <t>2.7%</t>
         </is>
       </c>
       <c r="G735" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="736">
@@ -21635,23 +21639,23 @@
       </c>
       <c r="B736" t="inlineStr">
         <is>
-          <t>Wholesale Inventories MoM AdvJAN</t>
+          <t>PCE Price Index YoYJAN</t>
         </is>
       </c>
       <c r="C736" t="inlineStr"/>
       <c r="D736" t="inlineStr">
         <is>
-          <t>-0.5%</t>
+          <t>2.6%</t>
         </is>
       </c>
       <c r="E736" t="inlineStr">
         <is>
-          <t>0.1%</t>
+          <t>2.5%</t>
         </is>
       </c>
       <c r="F736" t="inlineStr">
         <is>
-          <t>0.2%</t>
+          <t>2.5%</t>
         </is>
       </c>
       <c r="G736" t="n">
@@ -21666,27 +21670,27 @@
       </c>
       <c r="B737" t="inlineStr">
         <is>
-          <t>PCE Price Index YoYJAN</t>
+          <t>Core PCE Price Index MoMJAN</t>
         </is>
       </c>
       <c r="C737" t="inlineStr"/>
       <c r="D737" t="inlineStr">
         <is>
-          <t>2.6%</t>
+          <t>0.2%</t>
         </is>
       </c>
       <c r="E737" t="inlineStr">
         <is>
-          <t>2.5%</t>
+          <t>0.3%</t>
         </is>
       </c>
       <c r="F737" t="inlineStr">
         <is>
-          <t>2.5%</t>
+          <t>0.4%</t>
         </is>
       </c>
       <c r="G737" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="738">
@@ -21697,27 +21701,27 @@
       </c>
       <c r="B738" t="inlineStr">
         <is>
-          <t>Core PCE Price Index YoYJAN</t>
+          <t>Goods Trade Balance AdvJAN</t>
         </is>
       </c>
       <c r="C738" t="inlineStr"/>
       <c r="D738" t="inlineStr">
         <is>
-          <t>2.8%</t>
+          <t>$-122.11B</t>
         </is>
       </c>
       <c r="E738" t="inlineStr">
         <is>
-          <t>2.6%</t>
+          <t>$-114.7B</t>
         </is>
       </c>
       <c r="F738" t="inlineStr">
         <is>
-          <t>2.7%</t>
+          <t>$ -116.0B</t>
         </is>
       </c>
       <c r="G738" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="739">
@@ -21759,27 +21763,27 @@
       </c>
       <c r="B740" t="inlineStr">
         <is>
-          <t>Personal Income MoMJAN</t>
+          <t>Wholesale Inventories MoM AdvJAN</t>
         </is>
       </c>
       <c r="C740" t="inlineStr"/>
       <c r="D740" t="inlineStr">
         <is>
-          <t>0.4%</t>
+          <t>-0.5%</t>
         </is>
       </c>
       <c r="E740" t="inlineStr">
         <is>
-          <t>0.3%</t>
+          <t>0.1%</t>
         </is>
       </c>
       <c r="F740" t="inlineStr">
         <is>
-          <t>0.3%</t>
+          <t>0.2%</t>
         </is>
       </c>
       <c r="G740" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="741">
@@ -21790,27 +21794,27 @@
       </c>
       <c r="B741" t="inlineStr">
         <is>
-          <t>Goods Trade Balance AdvJAN</t>
+          <t>Personal Spending MoMJAN</t>
         </is>
       </c>
       <c r="C741" t="inlineStr"/>
       <c r="D741" t="inlineStr">
         <is>
-          <t>$-122.11B</t>
+          <t>0.7%</t>
         </is>
       </c>
       <c r="E741" t="inlineStr">
         <is>
-          <t>$-114.7B</t>
+          <t>0.1%</t>
         </is>
       </c>
       <c r="F741" t="inlineStr">
         <is>
-          <t>$ -116.0B</t>
+          <t>0.3%</t>
         </is>
       </c>
       <c r="G741" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="742">
@@ -21821,27 +21825,23 @@
       </c>
       <c r="B742" t="inlineStr">
         <is>
-          <t>Core PCE Price Index MoMJAN</t>
+          <t>Retail Inventories Ex Autos MoM AdvJAN</t>
         </is>
       </c>
       <c r="C742" t="inlineStr"/>
       <c r="D742" t="inlineStr">
         <is>
-          <t>0.2%</t>
-        </is>
-      </c>
-      <c r="E742" t="inlineStr">
-        <is>
-          <t>0.3%</t>
-        </is>
-      </c>
+          <t>-0.1%</t>
+        </is>
+      </c>
+      <c r="E742" t="inlineStr"/>
       <c r="F742" t="inlineStr">
         <is>
-          <t>0.4%</t>
+          <t>0.1%</t>
         </is>
       </c>
       <c r="G742" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="743">
@@ -21914,13 +21914,13 @@
       </c>
       <c r="B745" t="inlineStr">
         <is>
-          <t>Baker Hughes Oil Rig CountFEB/28</t>
+          <t>Baker Hughes Total Rigs CountFEB/28</t>
         </is>
       </c>
       <c r="C745" t="inlineStr"/>
       <c r="D745" t="inlineStr">
         <is>
-          <t>487</t>
+          <t>592</t>
         </is>
       </c>
       <c r="E745" t="inlineStr"/>
@@ -21983,13 +21983,13 @@
       </c>
       <c r="B748" t="inlineStr">
         <is>
-          <t>Baker Hughes Total Rigs CountFEB/28</t>
+          <t>Baker Hughes Oil Rig CountFEB/28</t>
         </is>
       </c>
       <c r="C748" t="inlineStr"/>
       <c r="D748" t="inlineStr">
         <is>
-          <t>592</t>
+          <t>487</t>
         </is>
       </c>
       <c r="E748" t="inlineStr"/>
@@ -22095,23 +22095,23 @@
       </c>
       <c r="B752" t="inlineStr">
         <is>
-          <t>ISM Manufacturing New OrdersFEB</t>
+          <t>ISM Manufacturing EmploymentFEB</t>
         </is>
       </c>
       <c r="C752" t="inlineStr"/>
       <c r="D752" t="inlineStr">
         <is>
-          <t>55.1</t>
+          <t>50.3</t>
         </is>
       </c>
       <c r="E752" t="inlineStr"/>
       <c r="F752" t="inlineStr">
         <is>
-          <t>55.4</t>
+          <t>50.6</t>
         </is>
       </c>
       <c r="G752" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="753">
@@ -22230,23 +22230,23 @@
       </c>
       <c r="B757" t="inlineStr">
         <is>
-          <t>ISM Manufacturing EmploymentFEB</t>
+          <t>ISM Manufacturing PricesFEB</t>
         </is>
       </c>
       <c r="C757" t="inlineStr"/>
       <c r="D757" t="inlineStr">
         <is>
-          <t>50.3</t>
+          <t>54.9</t>
         </is>
       </c>
       <c r="E757" t="inlineStr"/>
       <c r="F757" t="inlineStr">
         <is>
-          <t>50.6</t>
+          <t>55</t>
         </is>
       </c>
       <c r="G757" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="758">
@@ -22311,19 +22311,19 @@
       </c>
       <c r="B760" t="inlineStr">
         <is>
-          <t>ISM Manufacturing PricesFEB</t>
+          <t>ISM Manufacturing New OrdersFEB</t>
         </is>
       </c>
       <c r="C760" t="inlineStr"/>
       <c r="D760" t="inlineStr">
         <is>
-          <t>54.9</t>
+          <t>55.1</t>
         </is>
       </c>
       <c r="E760" t="inlineStr"/>
       <c r="F760" t="inlineStr">
         <is>
-          <t>55</t>
+          <t>55.4</t>
         </is>
       </c>
       <c r="G760" t="n">
@@ -22840,7 +22840,7 @@
       </c>
       <c r="B783" t="inlineStr">
         <is>
-          <t>MBA 30-Year Mortgage RateFEB/28</t>
+          <t>MBA Mortgage Market IndexFEB/28</t>
         </is>
       </c>
       <c r="C783" t="inlineStr"/>
@@ -22848,7 +22848,7 @@
       <c r="E783" t="inlineStr"/>
       <c r="F783" t="inlineStr"/>
       <c r="G783" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="784">
@@ -22859,7 +22859,7 @@
       </c>
       <c r="B784" t="inlineStr">
         <is>
-          <t>MBA Mortgage Market IndexFEB/28</t>
+          <t>MBA 30-Year Mortgage RateFEB/28</t>
         </is>
       </c>
       <c r="C784" t="inlineStr"/>
@@ -22867,7 +22867,7 @@
       <c r="E784" t="inlineStr"/>
       <c r="F784" t="inlineStr"/>
       <c r="G784" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="785">
@@ -22994,23 +22994,23 @@
       </c>
       <c r="B789" t="inlineStr">
         <is>
-          <t>S&amp;P Global Services PMI FinalFEB</t>
+          <t>S&amp;P Global Composite PMI FinalFEB</t>
         </is>
       </c>
       <c r="C789" t="inlineStr"/>
       <c r="D789" t="inlineStr">
         <is>
-          <t>52.9</t>
+          <t>52.7</t>
         </is>
       </c>
       <c r="E789" t="inlineStr">
         <is>
-          <t>49.7</t>
+          <t>50.4</t>
         </is>
       </c>
       <c r="F789" t="inlineStr">
         <is>
-          <t>49.7</t>
+          <t>50.4</t>
         </is>
       </c>
       <c r="G789" t="n">
@@ -23025,23 +23025,23 @@
       </c>
       <c r="B790" t="inlineStr">
         <is>
-          <t>S&amp;P Global Composite PMI FinalFEB</t>
+          <t>S&amp;P Global Services PMI FinalFEB</t>
         </is>
       </c>
       <c r="C790" t="inlineStr"/>
       <c r="D790" t="inlineStr">
         <is>
-          <t>52.7</t>
+          <t>52.9</t>
         </is>
       </c>
       <c r="E790" t="inlineStr">
         <is>
-          <t>50.4</t>
+          <t>49.7</t>
         </is>
       </c>
       <c r="F790" t="inlineStr">
         <is>
-          <t>50.4</t>
+          <t>49.7</t>
         </is>
       </c>
       <c r="G790" t="n">
@@ -23503,13 +23503,13 @@
       </c>
       <c r="B808" t="inlineStr">
         <is>
-          <t>EIA Refinery Crude Runs ChangeFEB/28</t>
+          <t>EIA Gasoline Production ChangeFEB/28</t>
         </is>
       </c>
       <c r="C808" t="inlineStr"/>
       <c r="D808" t="inlineStr">
         <is>
-          <t>0.317M</t>
+          <t>-0.02M</t>
         </is>
       </c>
       <c r="E808" t="inlineStr"/>
@@ -23595,19 +23595,19 @@
       </c>
       <c r="B812" t="inlineStr">
         <is>
-          <t>EIA Gasoline Stocks ChangeFEB/28</t>
+          <t>EIA Cushing Crude Oil Stocks ChangeFEB/28</t>
         </is>
       </c>
       <c r="C812" t="inlineStr"/>
       <c r="D812" t="inlineStr">
         <is>
-          <t>0.369M</t>
+          <t>1.282M</t>
         </is>
       </c>
       <c r="E812" t="inlineStr"/>
       <c r="F812" t="inlineStr"/>
       <c r="G812" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="813">
@@ -23687,13 +23687,13 @@
       </c>
       <c r="B816" t="inlineStr">
         <is>
-          <t>EIA Gasoline Production ChangeFEB/28</t>
+          <t>EIA Distillate Stocks ChangeFEB/28</t>
         </is>
       </c>
       <c r="C816" t="inlineStr"/>
       <c r="D816" t="inlineStr">
         <is>
-          <t>-0.02M</t>
+          <t>3.908M</t>
         </is>
       </c>
       <c r="E816" t="inlineStr"/>
@@ -23710,15 +23710,11 @@
       </c>
       <c r="B817" t="inlineStr">
         <is>
-          <t>EIA Cushing Crude Oil Stocks ChangeFEB/28</t>
+          <t>EIA Crude Oil Imports ChangeFEB/28</t>
         </is>
       </c>
       <c r="C817" t="inlineStr"/>
-      <c r="D817" t="inlineStr">
-        <is>
-          <t>1.282M</t>
-        </is>
-      </c>
+      <c r="D817" t="inlineStr"/>
       <c r="E817" t="inlineStr"/>
       <c r="F817" t="inlineStr"/>
       <c r="G817" t="n">
@@ -23752,11 +23748,15 @@
       </c>
       <c r="B819" t="inlineStr">
         <is>
-          <t>EIA Crude Oil Imports ChangeFEB/28</t>
+          <t>EIA Refinery Crude Runs ChangeFEB/28</t>
         </is>
       </c>
       <c r="C819" t="inlineStr"/>
-      <c r="D819" t="inlineStr"/>
+      <c r="D819" t="inlineStr">
+        <is>
+          <t>0.317M</t>
+        </is>
+      </c>
       <c r="E819" t="inlineStr"/>
       <c r="F819" t="inlineStr"/>
       <c r="G819" t="n">
@@ -23771,19 +23771,19 @@
       </c>
       <c r="B820" t="inlineStr">
         <is>
-          <t>EIA Distillate Stocks ChangeFEB/28</t>
+          <t>EIA Gasoline Stocks ChangeFEB/28</t>
         </is>
       </c>
       <c r="C820" t="inlineStr"/>
       <c r="D820" t="inlineStr">
         <is>
-          <t>3.908M</t>
+          <t>0.369M</t>
         </is>
       </c>
       <c r="E820" t="inlineStr"/>
       <c r="F820" t="inlineStr"/>
       <c r="G820" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="821">
@@ -24024,13 +24024,21 @@
       </c>
       <c r="B831" t="inlineStr">
         <is>
-          <t>Initial Jobless ClaimsMAR/01</t>
+          <t>ImportsJAN</t>
         </is>
       </c>
       <c r="C831" t="inlineStr"/>
-      <c r="D831" t="inlineStr"/>
+      <c r="D831" t="inlineStr">
+        <is>
+          <t>$364.9B</t>
+        </is>
+      </c>
       <c r="E831" t="inlineStr"/>
-      <c r="F831" t="inlineStr"/>
+      <c r="F831" t="inlineStr">
+        <is>
+          <t>$376.0B</t>
+        </is>
+      </c>
       <c r="G831" t="n">
         <v>2</v>
       </c>
@@ -24070,7 +24078,7 @@
       </c>
       <c r="B833" t="inlineStr">
         <is>
-          <t>Continuing Jobless ClaimsFEB/22</t>
+          <t>Jobless Claims 4-week AverageMAR/01</t>
         </is>
       </c>
       <c r="C833" t="inlineStr"/>
@@ -24289,7 +24297,7 @@
       </c>
       <c r="B842" t="inlineStr">
         <is>
-          <t>Jobless Claims 4-week AverageMAR/01</t>
+          <t>Continuing Jobless ClaimsFEB/22</t>
         </is>
       </c>
       <c r="C842" t="inlineStr"/>
@@ -24335,21 +24343,13 @@
       </c>
       <c r="B844" t="inlineStr">
         <is>
-          <t>Balance of TradeJAN</t>
+          <t>Initial Jobless ClaimsMAR/01</t>
         </is>
       </c>
       <c r="C844" t="inlineStr"/>
-      <c r="D844" t="inlineStr">
-        <is>
-          <t>$-98.4B</t>
-        </is>
-      </c>
+      <c r="D844" t="inlineStr"/>
       <c r="E844" t="inlineStr"/>
-      <c r="F844" t="inlineStr">
-        <is>
-          <t>$-103B</t>
-        </is>
-      </c>
+      <c r="F844" t="inlineStr"/>
       <c r="G844" t="n">
         <v>2</v>
       </c>
@@ -24389,19 +24389,19 @@
       </c>
       <c r="B846" t="inlineStr">
         <is>
-          <t>ImportsJAN</t>
+          <t>Balance of TradeJAN</t>
         </is>
       </c>
       <c r="C846" t="inlineStr"/>
       <c r="D846" t="inlineStr">
         <is>
-          <t>$364.9B</t>
+          <t>$-98.4B</t>
         </is>
       </c>
       <c r="E846" t="inlineStr"/>
       <c r="F846" t="inlineStr">
         <is>
-          <t>$376.0B</t>
+          <t>$-103B</t>
         </is>
       </c>
       <c r="G846" t="n">
@@ -24948,19 +24948,19 @@
       </c>
       <c r="B871" t="inlineStr">
         <is>
-          <t>Participation RateFEB</t>
+          <t>Average Hourly Earnings YoYFEB</t>
         </is>
       </c>
       <c r="C871" t="inlineStr"/>
       <c r="D871" t="inlineStr">
         <is>
-          <t>62.6%</t>
+          <t>4.1%</t>
         </is>
       </c>
       <c r="E871" t="inlineStr"/>
       <c r="F871" t="inlineStr">
         <is>
-          <t>62.6%</t>
+          <t>4.1%</t>
         </is>
       </c>
       <c r="G871" t="n">
@@ -24975,19 +24975,19 @@
       </c>
       <c r="B872" t="inlineStr">
         <is>
-          <t>Average Hourly Earnings YoYFEB</t>
+          <t>Average Hourly Earnings MoMFEB</t>
         </is>
       </c>
       <c r="C872" t="inlineStr"/>
       <c r="D872" t="inlineStr">
         <is>
-          <t>4.1%</t>
+          <t>0.5%</t>
         </is>
       </c>
       <c r="E872" t="inlineStr"/>
       <c r="F872" t="inlineStr">
         <is>
-          <t>4.1%</t>
+          <t>0.3%</t>
         </is>
       </c>
       <c r="G872" t="n">
@@ -25083,23 +25083,19 @@
       </c>
       <c r="B876" t="inlineStr">
         <is>
-          <t>Average Hourly Earnings MoMFEB</t>
+          <t>Used Car Prices MoMFEB</t>
         </is>
       </c>
       <c r="C876" t="inlineStr"/>
       <c r="D876" t="inlineStr">
         <is>
-          <t>0.5%</t>
+          <t>0.4%</t>
         </is>
       </c>
       <c r="E876" t="inlineStr"/>
-      <c r="F876" t="inlineStr">
-        <is>
-          <t>0.3%</t>
-        </is>
-      </c>
+      <c r="F876" t="inlineStr"/>
       <c r="G876" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="877">
@@ -25218,19 +25214,23 @@
       </c>
       <c r="B881" t="inlineStr">
         <is>
-          <t>Used Car Prices MoMFEB</t>
+          <t>Participation RateFEB</t>
         </is>
       </c>
       <c r="C881" t="inlineStr"/>
       <c r="D881" t="inlineStr">
         <is>
-          <t>0.4%</t>
+          <t>62.6%</t>
         </is>
       </c>
       <c r="E881" t="inlineStr"/>
-      <c r="F881" t="inlineStr"/>
+      <c r="F881" t="inlineStr">
+        <is>
+          <t>62.6%</t>
+        </is>
+      </c>
       <c r="G881" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="882">

--- a/Input_data/IST_US_trad_eco_cal_2025-01-01_to_2025-03-09.xlsx
+++ b/Input_data/IST_US_trad_eco_cal_2025-01-01_to_2025-03-09.xlsx
@@ -806,17 +806,17 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>EIA Distillate Fuel Production ChangeDEC/27</t>
+          <t>EIA Crude Oil Imports ChangeDEC/27</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>0.099M</t>
+          <t>0.323M</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>0.178M</t>
+          <t>0.995M</t>
         </is>
       </c>
       <c r="E13" t="inlineStr"/>
@@ -833,27 +833,27 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>EIA Crude Oil Stocks ChangeDEC/27</t>
+          <t>EIA Distillate Stocks ChangeDEC/27</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>-1.178M</t>
+          <t>6.406M</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>-4.237M</t>
+          <t>-1.694M</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>-2.75M</t>
+          <t>-0.1M</t>
         </is>
       </c>
       <c r="F14" t="inlineStr"/>
       <c r="G14" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="15">
@@ -864,17 +864,17 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>EIA Cushing Crude Oil Stocks ChangeDEC/27</t>
+          <t>EIA Refinery Crude Runs ChangeDEC/27</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>-0.142M</t>
+          <t>0.041M</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>-0.32M</t>
+          <t>0.205M</t>
         </is>
       </c>
       <c r="E15" t="inlineStr"/>
@@ -891,23 +891,27 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>EIA Heating Oil Stocks ChangeDEC/27</t>
+          <t>EIA Gasoline Stocks ChangeDEC/27</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>-0.416M</t>
+          <t>7.717M</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>-0.062M</t>
-        </is>
-      </c>
-      <c r="E16" t="inlineStr"/>
+          <t>1.63M</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>0.7M</t>
+        </is>
+      </c>
       <c r="F16" t="inlineStr"/>
       <c r="G16" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="17">
@@ -918,17 +922,17 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>EIA Gasoline Production ChangeDEC/27</t>
+          <t>EIA Cushing Crude Oil Stocks ChangeDEC/27</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>-0.959M</t>
+          <t>-0.142M</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>0.051M</t>
+          <t>-0.32M</t>
         </is>
       </c>
       <c r="E17" t="inlineStr"/>
@@ -945,27 +949,23 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>EIA Gasoline Stocks ChangeDEC/27</t>
+          <t>EIA Heating Oil Stocks ChangeDEC/27</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>7.717M</t>
+          <t>-0.416M</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>1.63M</t>
-        </is>
-      </c>
-      <c r="E18" t="inlineStr">
-        <is>
-          <t>0.7M</t>
-        </is>
-      </c>
+          <t>-0.062M</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr"/>
       <c r="F18" t="inlineStr"/>
       <c r="G18" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="19">
@@ -976,23 +976,27 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>EIA Refinery Crude Runs ChangeDEC/27</t>
+          <t>EIA Crude Oil Stocks ChangeDEC/27</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>0.041M</t>
+          <t>-1.178M</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>0.205M</t>
-        </is>
-      </c>
-      <c r="E19" t="inlineStr"/>
+          <t>-4.237M</t>
+        </is>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>-2.75M</t>
+        </is>
+      </c>
       <c r="F19" t="inlineStr"/>
       <c r="G19" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="20">
@@ -1003,24 +1007,20 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>EIA Distillate Stocks ChangeDEC/27</t>
+          <t>EIA Distillate Fuel Production ChangeDEC/27</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>6.406M</t>
+          <t>0.099M</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>-1.694M</t>
-        </is>
-      </c>
-      <c r="E20" t="inlineStr">
-        <is>
-          <t>-0.1M</t>
-        </is>
-      </c>
+          <t>0.178M</t>
+        </is>
+      </c>
+      <c r="E20" t="inlineStr"/>
       <c r="F20" t="inlineStr"/>
       <c r="G20" t="n">
         <v>3</v>
@@ -1034,17 +1034,17 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>EIA Crude Oil Imports ChangeDEC/27</t>
+          <t>EIA Gasoline Production ChangeDEC/27</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>0.323M</t>
+          <t>-0.959M</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>0.995M</t>
+          <t>0.051M</t>
         </is>
       </c>
       <c r="E21" t="inlineStr"/>
@@ -1223,31 +1223,31 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>ISM Manufacturing PMIDEC</t>
+          <t>ISM Manufacturing PricesDEC</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>49.3</t>
+          <t>52.5</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>48.4</t>
+          <t>50.3</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>48.4</t>
+          <t>51.7</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>48.5</t>
+          <t>50.4</t>
         </is>
       </c>
       <c r="G28" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="29">
@@ -1258,31 +1258,27 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>ISM Manufacturing EmploymentDEC</t>
+          <t>ISM Manufacturing New OrdersDEC</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>45.3</t>
+          <t>52.5</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>48.1</t>
-        </is>
-      </c>
-      <c r="E29" t="inlineStr">
-        <is>
-          <t>48</t>
-        </is>
-      </c>
+          <t>50.4</t>
+        </is>
+      </c>
+      <c r="E29" t="inlineStr"/>
       <c r="F29" t="inlineStr">
         <is>
-          <t>48.3</t>
+          <t>50.5</t>
         </is>
       </c>
       <c r="G29" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="30">
@@ -1293,27 +1289,31 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>ISM Manufacturing New OrdersDEC</t>
+          <t>ISM Manufacturing EmploymentDEC</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>52.5</t>
+          <t>45.3</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>50.4</t>
-        </is>
-      </c>
-      <c r="E30" t="inlineStr"/>
+          <t>48.1</t>
+        </is>
+      </c>
+      <c r="E30" t="inlineStr">
+        <is>
+          <t>48</t>
+        </is>
+      </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>50.5</t>
+          <t>48.3</t>
         </is>
       </c>
       <c r="G30" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="31">
@@ -1324,31 +1324,31 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>ISM Manufacturing PricesDEC</t>
+          <t>ISM Manufacturing PMIDEC</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>52.5</t>
+          <t>49.3</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>50.3</t>
+          <t>48.4</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>51.7</t>
+          <t>48.4</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>50.4</t>
+          <t>48.5</t>
         </is>
       </c>
       <c r="G31" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="32">
@@ -1609,31 +1609,27 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>Factory Orders MoMNOV</t>
+          <t>Factory Orders ex TransportationNOV</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>-0.4%</t>
+          <t>0.2%</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>0.5%</t>
-        </is>
-      </c>
-      <c r="E42" t="inlineStr">
-        <is>
-          <t>-0.3%</t>
-        </is>
-      </c>
+          <t>0.2%</t>
+        </is>
+      </c>
+      <c r="E42" t="inlineStr"/>
       <c r="F42" t="inlineStr">
         <is>
-          <t>0.3%</t>
+          <t>0.2%</t>
         </is>
       </c>
       <c r="G42" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="43">
@@ -1644,27 +1640,31 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>Factory Orders ex TransportationNOV</t>
+          <t>Factory Orders MoMNOV</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>0.2%</t>
+          <t>-0.4%</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>0.2%</t>
-        </is>
-      </c>
-      <c r="E43" t="inlineStr"/>
+          <t>0.5%</t>
+        </is>
+      </c>
+      <c r="E43" t="inlineStr">
+        <is>
+          <t>-0.3%</t>
+        </is>
+      </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>0.2%</t>
+          <t>0.3%</t>
         </is>
       </c>
       <c r="G43" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="44">
@@ -1949,23 +1949,23 @@
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>JOLTs Job QuitsNOV</t>
+          <t>ISM Services Business ActivityDEC</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>3.065M</t>
+          <t>58.2</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>3.283M</t>
+          <t>53.7</t>
         </is>
       </c>
       <c r="E54" t="inlineStr"/>
       <c r="F54" t="inlineStr">
         <is>
-          <t>3.31M</t>
+          <t>54.1</t>
         </is>
       </c>
       <c r="G54" t="n">
@@ -1980,31 +1980,31 @@
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>ISM Services PMIDEC</t>
+          <t>ISM Services EmploymentDEC</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>54.1</t>
+          <t>51.4</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>52.1</t>
+          <t>51.5</t>
         </is>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>53.3</t>
+          <t>51.4</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>54</t>
+          <t>52</t>
         </is>
       </c>
       <c r="G55" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="56">
@@ -2015,31 +2015,31 @@
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>ISM Services New OrdersDEC</t>
+          <t>JOLTs Job OpeningsNOV</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>54.2</t>
+          <t>8.098M</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>53.7</t>
+          <t>7.839M</t>
         </is>
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>54.2</t>
+          <t>7.70M</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>54.1</t>
+          <t>7.69M</t>
         </is>
       </c>
       <c r="G56" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="57">
@@ -2050,31 +2050,31 @@
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>JOLTs Job OpeningsNOV</t>
+          <t>ISM Services PricesDEC</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>8.098M</t>
+          <t>64.4</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>7.839M</t>
+          <t>58.2</t>
         </is>
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>7.70M</t>
+          <t>57.5</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>7.69M</t>
+          <t>58.4</t>
         </is>
       </c>
       <c r="G57" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="58">
@@ -2085,27 +2085,27 @@
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>ISM Services PricesDEC</t>
+          <t>ISM Services New OrdersDEC</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>64.4</t>
+          <t>54.2</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>58.2</t>
+          <t>53.7</t>
         </is>
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>57.5</t>
+          <t>54.2</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>58.4</t>
+          <t>54.1</t>
         </is>
       </c>
       <c r="G58" t="n">
@@ -2120,27 +2120,31 @@
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>ISM Services Business ActivityDEC</t>
+          <t>ISM Services PMIDEC</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>58.2</t>
+          <t>54.1</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>53.7</t>
-        </is>
-      </c>
-      <c r="E59" t="inlineStr"/>
+          <t>52.1</t>
+        </is>
+      </c>
+      <c r="E59" t="inlineStr">
+        <is>
+          <t>53.3</t>
+        </is>
+      </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>54.1</t>
+          <t>54</t>
         </is>
       </c>
       <c r="G59" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="60">
@@ -2151,27 +2155,23 @@
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>ISM Services EmploymentDEC</t>
+          <t>JOLTs Job QuitsNOV</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>51.4</t>
+          <t>3.065M</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>51.5</t>
-        </is>
-      </c>
-      <c r="E60" t="inlineStr">
-        <is>
-          <t>51.4</t>
-        </is>
-      </c>
+          <t>3.283M</t>
+        </is>
+      </c>
+      <c r="E60" t="inlineStr"/>
       <c r="F60" t="inlineStr">
         <is>
-          <t>52</t>
+          <t>3.31M</t>
         </is>
       </c>
       <c r="G60" t="n">
@@ -2271,17 +2271,17 @@
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>MBA Mortgage Refinance IndexJAN/03</t>
+          <t>MBA Purchase IndexJAN/03</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>401.1</t>
+          <t>127.7</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>395.1</t>
+          <t>136.7</t>
         </is>
       </c>
       <c r="E64" t="inlineStr"/>
@@ -2298,23 +2298,23 @@
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>MBA 30-Year Mortgage RateJAN/03</t>
+          <t>MBA Mortgage Market IndexJAN/03</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>6.99%</t>
+          <t>168.4</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>6.97%</t>
+          <t>174.9</t>
         </is>
       </c>
       <c r="E65" t="inlineStr"/>
       <c r="F65" t="inlineStr"/>
       <c r="G65" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="66">
@@ -2325,17 +2325,17 @@
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>MBA Mortgage Market IndexJAN/03</t>
+          <t>MBA Mortgage ApplicationsJAN/03</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>168.4</t>
+          <t>-3.7%</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>174.9</t>
+          <t>-12.6%</t>
         </is>
       </c>
       <c r="E66" t="inlineStr"/>
@@ -2352,17 +2352,17 @@
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>MBA Purchase IndexJAN/03</t>
+          <t>MBA Mortgage Refinance IndexJAN/03</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>127.7</t>
+          <t>401.1</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>136.7</t>
+          <t>395.1</t>
         </is>
       </c>
       <c r="E67" t="inlineStr"/>
@@ -2379,23 +2379,23 @@
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>MBA Mortgage ApplicationsJAN/03</t>
+          <t>MBA 30-Year Mortgage RateJAN/03</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>-3.7%</t>
+          <t>6.99%</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>-12.6%</t>
+          <t>6.97%</t>
         </is>
       </c>
       <c r="E68" t="inlineStr"/>
       <c r="F68" t="inlineStr"/>
       <c r="G68" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="69">
@@ -2685,20 +2685,24 @@
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>EIA Crude Oil Imports ChangeJAN/03</t>
+          <t>EIA Distillate Stocks ChangeJAN/03</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>0.278M</t>
+          <t>6.071M</t>
         </is>
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>0.323M</t>
-        </is>
-      </c>
-      <c r="E78" t="inlineStr"/>
+          <t>6.406M</t>
+        </is>
+      </c>
+      <c r="E78" t="inlineStr">
+        <is>
+          <t>1M</t>
+        </is>
+      </c>
       <c r="F78" t="inlineStr"/>
       <c r="G78" t="n">
         <v>3</v>
@@ -2712,17 +2716,17 @@
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>EIA Distillate Fuel Production ChangeJAN/03</t>
+          <t>EIA Gasoline Production ChangeJAN/03</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>-0.167M</t>
+          <t>-0.081M</t>
         </is>
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>0.099M</t>
+          <t>-0.959M</t>
         </is>
       </c>
       <c r="E79" t="inlineStr"/>
@@ -2739,27 +2743,23 @@
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>EIA Crude Oil Stocks ChangeJAN/03</t>
+          <t>EIA Heating Oil Stocks ChangeJAN/03</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>-0.959M</t>
+          <t>-0.632M</t>
         </is>
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>-1.178M</t>
-        </is>
-      </c>
-      <c r="E80" t="inlineStr">
-        <is>
-          <t>-0.6M</t>
-        </is>
-      </c>
+          <t>-0.416M</t>
+        </is>
+      </c>
+      <c r="E80" t="inlineStr"/>
       <c r="F80" t="inlineStr"/>
       <c r="G80" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="81">
@@ -2770,23 +2770,27 @@
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>EIA Refinery Crude Runs ChangeJAN/03</t>
+          <t>EIA Gasoline Stocks ChangeJAN/03</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>0.045M</t>
+          <t>6.33M</t>
         </is>
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>0.041M</t>
-        </is>
-      </c>
-      <c r="E81" t="inlineStr"/>
+          <t>7.717M</t>
+        </is>
+      </c>
+      <c r="E81" t="inlineStr">
+        <is>
+          <t>1.5M</t>
+        </is>
+      </c>
       <c r="F81" t="inlineStr"/>
       <c r="G81" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="82">
@@ -2797,27 +2801,23 @@
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>EIA Gasoline Stocks ChangeJAN/03</t>
+          <t>EIA Cushing Crude Oil Stocks ChangeJAN/03</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>6.33M</t>
+          <t>-2.502M</t>
         </is>
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>7.717M</t>
-        </is>
-      </c>
-      <c r="E82" t="inlineStr">
-        <is>
-          <t>1.5M</t>
-        </is>
-      </c>
+          <t>-0.142M</t>
+        </is>
+      </c>
+      <c r="E82" t="inlineStr"/>
       <c r="F82" t="inlineStr"/>
       <c r="G82" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="83">
@@ -2828,23 +2828,27 @@
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>EIA Heating Oil Stocks ChangeJAN/03</t>
+          <t>EIA Crude Oil Stocks ChangeJAN/03</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>-0.632M</t>
+          <t>-0.959M</t>
         </is>
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>-0.416M</t>
-        </is>
-      </c>
-      <c r="E83" t="inlineStr"/>
+          <t>-1.178M</t>
+        </is>
+      </c>
+      <c r="E83" t="inlineStr">
+        <is>
+          <t>-0.6M</t>
+        </is>
+      </c>
       <c r="F83" t="inlineStr"/>
       <c r="G83" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="84">
@@ -2855,24 +2859,20 @@
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>EIA Distillate Stocks ChangeJAN/03</t>
+          <t>EIA Distillate Fuel Production ChangeJAN/03</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>6.071M</t>
+          <t>-0.167M</t>
         </is>
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>6.406M</t>
-        </is>
-      </c>
-      <c r="E84" t="inlineStr">
-        <is>
-          <t>1M</t>
-        </is>
-      </c>
+          <t>0.099M</t>
+        </is>
+      </c>
+      <c r="E84" t="inlineStr"/>
       <c r="F84" t="inlineStr"/>
       <c r="G84" t="n">
         <v>3</v>
@@ -2886,17 +2886,17 @@
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>EIA Cushing Crude Oil Stocks ChangeJAN/03</t>
+          <t>EIA Refinery Crude Runs ChangeJAN/03</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>-2.502M</t>
+          <t>0.045M</t>
         </is>
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>-0.142M</t>
+          <t>0.041M</t>
         </is>
       </c>
       <c r="E85" t="inlineStr"/>
@@ -2913,17 +2913,17 @@
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>EIA Gasoline Production ChangeJAN/03</t>
+          <t>EIA Crude Oil Imports ChangeJAN/03</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>-0.081M</t>
+          <t>0.278M</t>
         </is>
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>-0.959M</t>
+          <t>0.323M</t>
         </is>
       </c>
       <c r="E86" t="inlineStr"/>
@@ -3171,17 +3171,17 @@
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>8-Week Bill Auction</t>
+          <t>4-Week Bill Auction</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>4.240%</t>
+          <t>4.245%</t>
         </is>
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>4.240%</t>
+          <t>4.265%</t>
         </is>
       </c>
       <c r="E96" t="inlineStr"/>
@@ -3198,17 +3198,17 @@
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>4-Week Bill Auction</t>
+          <t>8-Week Bill Auction</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>4.245%</t>
+          <t>4.240%</t>
         </is>
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>4.265%</t>
+          <t>4.240%</t>
         </is>
       </c>
       <c r="E97" t="inlineStr"/>
@@ -3336,23 +3336,27 @@
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>Government PayrollsDEC</t>
+          <t>Average Weekly HoursDEC</t>
         </is>
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>33K</t>
+          <t>34.3</t>
         </is>
       </c>
       <c r="D103" t="inlineStr">
         <is>
-          <t>30K</t>
-        </is>
-      </c>
-      <c r="E103" t="inlineStr"/>
+          <t>34.3</t>
+        </is>
+      </c>
+      <c r="E103" t="inlineStr">
+        <is>
+          <t>34.3</t>
+        </is>
+      </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>15K</t>
+          <t>34.3</t>
         </is>
       </c>
       <c r="G103" t="n">
@@ -3367,27 +3371,23 @@
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>Nonfarm Payrolls PrivateDEC</t>
+          <t>Government PayrollsDEC</t>
         </is>
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>223K</t>
+          <t>33K</t>
         </is>
       </c>
       <c r="D104" t="inlineStr">
         <is>
-          <t>182K</t>
-        </is>
-      </c>
-      <c r="E104" t="inlineStr">
-        <is>
-          <t>135K</t>
-        </is>
-      </c>
+          <t>30K</t>
+        </is>
+      </c>
+      <c r="E104" t="inlineStr"/>
       <c r="F104" t="inlineStr">
         <is>
-          <t>185K</t>
+          <t>15K</t>
         </is>
       </c>
       <c r="G104" t="n">
@@ -3402,27 +3402,27 @@
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>Manufacturing PayrollsDEC</t>
+          <t>Nonfarm Payrolls PrivateDEC</t>
         </is>
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>-13K</t>
+          <t>223K</t>
         </is>
       </c>
       <c r="D105" t="inlineStr">
         <is>
-          <t>25K</t>
+          <t>182K</t>
         </is>
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>5K</t>
+          <t>135K</t>
         </is>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>29K</t>
+          <t>185K</t>
         </is>
       </c>
       <c r="G105" t="n">
@@ -3437,27 +3437,31 @@
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>Participation RateDEC</t>
+          <t>Manufacturing PayrollsDEC</t>
         </is>
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>62.5%</t>
+          <t>-13K</t>
         </is>
       </c>
       <c r="D106" t="inlineStr">
         <is>
-          <t>62.5%</t>
-        </is>
-      </c>
-      <c r="E106" t="inlineStr"/>
+          <t>25K</t>
+        </is>
+      </c>
+      <c r="E106" t="inlineStr">
+        <is>
+          <t>5K</t>
+        </is>
+      </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>62.8%</t>
+          <t>29K</t>
         </is>
       </c>
       <c r="G106" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="107">
@@ -3468,31 +3472,27 @@
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>Non Farm PayrollsDEC</t>
+          <t>Participation RateDEC</t>
         </is>
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>256K</t>
+          <t>62.5%</t>
         </is>
       </c>
       <c r="D107" t="inlineStr">
         <is>
-          <t>212K</t>
-        </is>
-      </c>
-      <c r="E107" t="inlineStr">
-        <is>
-          <t>160K</t>
-        </is>
-      </c>
+          <t>62.5%</t>
+        </is>
+      </c>
+      <c r="E107" t="inlineStr"/>
       <c r="F107" t="inlineStr">
         <is>
-          <t>200K</t>
+          <t>62.8%</t>
         </is>
       </c>
       <c r="G107" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="108">
@@ -3503,31 +3503,31 @@
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>Average Hourly Earnings YoY</t>
+          <t>Non Farm PayrollsDEC</t>
         </is>
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>3.9%</t>
+          <t>256K</t>
         </is>
       </c>
       <c r="D108" t="inlineStr">
         <is>
-          <t>4%</t>
+          <t>212K</t>
         </is>
       </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t>4%</t>
+          <t>160K</t>
         </is>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>4%</t>
+          <t>200K</t>
         </is>
       </c>
       <c r="G108" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="109">
@@ -3538,27 +3538,27 @@
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>Average Hourly Earnings MoMDEC</t>
+          <t>Average Hourly Earnings YoY</t>
         </is>
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>0.3%</t>
+          <t>3.9%</t>
         </is>
       </c>
       <c r="D109" t="inlineStr">
         <is>
-          <t>0.4%</t>
+          <t>4%</t>
         </is>
       </c>
       <c r="E109" t="inlineStr">
         <is>
-          <t>0.3%</t>
+          <t>4%</t>
         </is>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>0.3%</t>
+          <t>4%</t>
         </is>
       </c>
       <c r="G109" t="n">
@@ -3573,27 +3573,31 @@
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>U-6 Unemployment Rate</t>
+          <t>Average Hourly Earnings MoMDEC</t>
         </is>
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>7.5%</t>
+          <t>0.3%</t>
         </is>
       </c>
       <c r="D110" t="inlineStr">
         <is>
-          <t>7.7%</t>
-        </is>
-      </c>
-      <c r="E110" t="inlineStr"/>
+          <t>0.4%</t>
+        </is>
+      </c>
+      <c r="E110" t="inlineStr">
+        <is>
+          <t>0.3%</t>
+        </is>
+      </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>7.9%</t>
+          <t>0.3%</t>
         </is>
       </c>
       <c r="G110" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="111">
@@ -3604,27 +3608,23 @@
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>Average Weekly HoursDEC</t>
+          <t>U-6 Unemployment Rate</t>
         </is>
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>34.3</t>
+          <t>7.5%</t>
         </is>
       </c>
       <c r="D111" t="inlineStr">
         <is>
-          <t>34.3</t>
-        </is>
-      </c>
-      <c r="E111" t="inlineStr">
-        <is>
-          <t>34.3</t>
-        </is>
-      </c>
+          <t>7.7%</t>
+        </is>
+      </c>
+      <c r="E111" t="inlineStr"/>
       <c r="F111" t="inlineStr">
         <is>
-          <t>34.3</t>
+          <t>7.9%</t>
         </is>
       </c>
       <c r="G111" t="n">
@@ -3674,23 +3674,23 @@
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>Michigan 5 Year Inflation Expectations PrelJAN</t>
+          <t>Michigan Current Conditions PrelJAN</t>
         </is>
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>3.3%</t>
+          <t>77.9</t>
         </is>
       </c>
       <c r="D113" t="inlineStr">
         <is>
-          <t>3%</t>
+          <t>75.1</t>
         </is>
       </c>
       <c r="E113" t="inlineStr"/>
       <c r="F113" t="inlineStr">
         <is>
-          <t>3.2%</t>
+          <t>78</t>
         </is>
       </c>
       <c r="G113" t="n">
@@ -3705,31 +3705,27 @@
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>Michigan Consumer Sentiment PrelJAN</t>
+          <t>Michigan Consumer Expectations PrelJAN</t>
         </is>
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>73.2</t>
+          <t>70.2</t>
         </is>
       </c>
       <c r="D114" t="inlineStr">
         <is>
-          <t>74.0</t>
-        </is>
-      </c>
-      <c r="E114" t="inlineStr">
-        <is>
-          <t>73.8</t>
-        </is>
-      </c>
+          <t>73.3</t>
+        </is>
+      </c>
+      <c r="E114" t="inlineStr"/>
       <c r="F114" t="inlineStr">
         <is>
-          <t>75</t>
+          <t>74</t>
         </is>
       </c>
       <c r="G114" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="115">
@@ -3740,27 +3736,31 @@
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>Michigan Inflation Expectations PrelJAN</t>
+          <t>Michigan Consumer Sentiment PrelJAN</t>
         </is>
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>3.3%</t>
+          <t>73.2</t>
         </is>
       </c>
       <c r="D115" t="inlineStr">
         <is>
-          <t>2.8%</t>
-        </is>
-      </c>
-      <c r="E115" t="inlineStr"/>
+          <t>74.0</t>
+        </is>
+      </c>
+      <c r="E115" t="inlineStr">
+        <is>
+          <t>73.8</t>
+        </is>
+      </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>3.0%</t>
+          <t>75</t>
         </is>
       </c>
       <c r="G115" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="116">
@@ -3771,23 +3771,23 @@
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t>Michigan Consumer Expectations PrelJAN</t>
+          <t>Michigan 5 Year Inflation Expectations PrelJAN</t>
         </is>
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>70.2</t>
+          <t>3.3%</t>
         </is>
       </c>
       <c r="D116" t="inlineStr">
         <is>
-          <t>73.3</t>
+          <t>3%</t>
         </is>
       </c>
       <c r="E116" t="inlineStr"/>
       <c r="F116" t="inlineStr">
         <is>
-          <t>74</t>
+          <t>3.2%</t>
         </is>
       </c>
       <c r="G116" t="n">
@@ -3802,23 +3802,23 @@
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t>Michigan Current Conditions PrelJAN</t>
+          <t>Michigan Inflation Expectations PrelJAN</t>
         </is>
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>77.9</t>
+          <t>3.3%</t>
         </is>
       </c>
       <c r="D117" t="inlineStr">
         <is>
-          <t>75.1</t>
+          <t>2.8%</t>
         </is>
       </c>
       <c r="E117" t="inlineStr"/>
       <c r="F117" t="inlineStr">
         <is>
-          <t>78</t>
+          <t>3.0%</t>
         </is>
       </c>
       <c r="G117" t="n">
@@ -4134,23 +4134,27 @@
       </c>
       <c r="B129" t="inlineStr">
         <is>
-          <t>PPI Ex Food, Energy and Trade YoYDEC</t>
+          <t>PPI Ex Food, Energy and Trade MoMDEC</t>
         </is>
       </c>
       <c r="C129" t="inlineStr">
         <is>
-          <t>3.3%</t>
+          <t>0.1%</t>
         </is>
       </c>
       <c r="D129" t="inlineStr">
         <is>
-          <t>3.5%</t>
-        </is>
-      </c>
-      <c r="E129" t="inlineStr"/>
+          <t>0.1%</t>
+        </is>
+      </c>
+      <c r="E129" t="inlineStr">
+        <is>
+          <t>0.3%</t>
+        </is>
+      </c>
       <c r="F129" t="inlineStr">
         <is>
-          <t>3.6%</t>
+          <t>0.2%</t>
         </is>
       </c>
       <c r="G129" t="n">
@@ -4165,27 +4169,27 @@
       </c>
       <c r="B130" t="inlineStr">
         <is>
-          <t>Core PPI YoYDEC</t>
+          <t>PPI YoYDEC</t>
         </is>
       </c>
       <c r="C130" t="inlineStr">
         <is>
-          <t>3.5%</t>
+          <t>3.3%</t>
         </is>
       </c>
       <c r="D130" t="inlineStr">
         <is>
-          <t>3.5%</t>
+          <t>3%</t>
         </is>
       </c>
       <c r="E130" t="inlineStr">
         <is>
-          <t>3.8%</t>
+          <t>3.4%</t>
         </is>
       </c>
       <c r="F130" t="inlineStr">
         <is>
-          <t>3.5%</t>
+          <t>3.3%</t>
         </is>
       </c>
       <c r="G130" t="n">
@@ -4200,17 +4204,17 @@
       </c>
       <c r="B131" t="inlineStr">
         <is>
-          <t>Core PPI MoMDEC</t>
+          <t>PPI MoMDEC</t>
         </is>
       </c>
       <c r="C131" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>0.2%</t>
         </is>
       </c>
       <c r="D131" t="inlineStr">
         <is>
-          <t>0.2%</t>
+          <t>0.4%</t>
         </is>
       </c>
       <c r="E131" t="inlineStr">
@@ -4220,11 +4224,11 @@
       </c>
       <c r="F131" t="inlineStr">
         <is>
-          <t>0.2%</t>
+          <t>0.3%</t>
         </is>
       </c>
       <c r="G131" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="132">
@@ -4235,23 +4239,27 @@
       </c>
       <c r="B132" t="inlineStr">
         <is>
-          <t>PPIDEC</t>
+          <t>Core PPI YoYDEC</t>
         </is>
       </c>
       <c r="C132" t="inlineStr">
         <is>
-          <t>146.842</t>
+          <t>3.5%</t>
         </is>
       </c>
       <c r="D132" t="inlineStr">
         <is>
-          <t>146.521</t>
-        </is>
-      </c>
-      <c r="E132" t="inlineStr"/>
+          <t>3.5%</t>
+        </is>
+      </c>
+      <c r="E132" t="inlineStr">
+        <is>
+          <t>3.8%</t>
+        </is>
+      </c>
       <c r="F132" t="inlineStr">
         <is>
-          <t>146.8</t>
+          <t>3.5%</t>
         </is>
       </c>
       <c r="G132" t="n">
@@ -4266,19 +4274,19 @@
       </c>
       <c r="B133" t="inlineStr">
         <is>
-          <t>PPI MoMDEC</t>
+          <t>Core PPI MoMDEC</t>
         </is>
       </c>
       <c r="C133" t="inlineStr">
         <is>
+          <t>0%</t>
+        </is>
+      </c>
+      <c r="D133" t="inlineStr">
+        <is>
           <t>0.2%</t>
         </is>
       </c>
-      <c r="D133" t="inlineStr">
-        <is>
-          <t>0.4%</t>
-        </is>
-      </c>
       <c r="E133" t="inlineStr">
         <is>
           <t>0.3%</t>
@@ -4286,11 +4294,11 @@
       </c>
       <c r="F133" t="inlineStr">
         <is>
-          <t>0.3%</t>
+          <t>0.2%</t>
         </is>
       </c>
       <c r="G133" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="134">
@@ -4301,7 +4309,7 @@
       </c>
       <c r="B134" t="inlineStr">
         <is>
-          <t>PPI YoYDEC</t>
+          <t>PPI Ex Food, Energy and Trade YoYDEC</t>
         </is>
       </c>
       <c r="C134" t="inlineStr">
@@ -4311,17 +4319,13 @@
       </c>
       <c r="D134" t="inlineStr">
         <is>
-          <t>3%</t>
-        </is>
-      </c>
-      <c r="E134" t="inlineStr">
-        <is>
-          <t>3.4%</t>
-        </is>
-      </c>
+          <t>3.5%</t>
+        </is>
+      </c>
+      <c r="E134" t="inlineStr"/>
       <c r="F134" t="inlineStr">
         <is>
-          <t>3.3%</t>
+          <t>3.6%</t>
         </is>
       </c>
       <c r="G134" t="n">
@@ -4336,27 +4340,23 @@
       </c>
       <c r="B135" t="inlineStr">
         <is>
-          <t>PPI Ex Food, Energy and Trade MoMDEC</t>
+          <t>PPIDEC</t>
         </is>
       </c>
       <c r="C135" t="inlineStr">
         <is>
-          <t>0.1%</t>
+          <t>146.842</t>
         </is>
       </c>
       <c r="D135" t="inlineStr">
         <is>
-          <t>0.1%</t>
-        </is>
-      </c>
-      <c r="E135" t="inlineStr">
-        <is>
-          <t>0.3%</t>
-        </is>
-      </c>
+          <t>146.521</t>
+        </is>
+      </c>
+      <c r="E135" t="inlineStr"/>
       <c r="F135" t="inlineStr">
         <is>
-          <t>0.2%</t>
+          <t>146.8</t>
         </is>
       </c>
       <c r="G135" t="n">
@@ -4564,23 +4564,23 @@
       </c>
       <c r="B143" t="inlineStr">
         <is>
-          <t>MBA Mortgage Refinance IndexJAN/10</t>
+          <t>MBA 30-Year Mortgage RateJAN/10</t>
         </is>
       </c>
       <c r="C143" t="inlineStr">
         <is>
-          <t>575.6</t>
+          <t>7.09%</t>
         </is>
       </c>
       <c r="D143" t="inlineStr">
         <is>
-          <t>401.1000</t>
+          <t>6.99%</t>
         </is>
       </c>
       <c r="E143" t="inlineStr"/>
       <c r="F143" t="inlineStr"/>
       <c r="G143" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="144">
@@ -4591,17 +4591,17 @@
       </c>
       <c r="B144" t="inlineStr">
         <is>
-          <t>MBA Mortgage Market IndexJAN/10</t>
+          <t>MBA Mortgage ApplicationsJAN/10</t>
         </is>
       </c>
       <c r="C144" t="inlineStr">
         <is>
-          <t>224.4</t>
+          <t>33.3%</t>
         </is>
       </c>
       <c r="D144" t="inlineStr">
         <is>
-          <t>168.4</t>
+          <t>-3.7%</t>
         </is>
       </c>
       <c r="E144" t="inlineStr"/>
@@ -4618,17 +4618,17 @@
       </c>
       <c r="B145" t="inlineStr">
         <is>
-          <t>MBA Mortgage ApplicationsJAN/10</t>
+          <t>MBA Purchase IndexJAN/10</t>
         </is>
       </c>
       <c r="C145" t="inlineStr">
         <is>
-          <t>33.3%</t>
+          <t>162</t>
         </is>
       </c>
       <c r="D145" t="inlineStr">
         <is>
-          <t>-3.7%</t>
+          <t>127.7000</t>
         </is>
       </c>
       <c r="E145" t="inlineStr"/>
@@ -4645,23 +4645,23 @@
       </c>
       <c r="B146" t="inlineStr">
         <is>
-          <t>MBA 30-Year Mortgage RateJAN/10</t>
+          <t>MBA Mortgage Refinance IndexJAN/10</t>
         </is>
       </c>
       <c r="C146" t="inlineStr">
         <is>
-          <t>7.09%</t>
+          <t>575.6</t>
         </is>
       </c>
       <c r="D146" t="inlineStr">
         <is>
-          <t>6.99%</t>
+          <t>401.1000</t>
         </is>
       </c>
       <c r="E146" t="inlineStr"/>
       <c r="F146" t="inlineStr"/>
       <c r="G146" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="147">
@@ -4672,17 +4672,17 @@
       </c>
       <c r="B147" t="inlineStr">
         <is>
-          <t>MBA Purchase IndexJAN/10</t>
+          <t>MBA Mortgage Market IndexJAN/10</t>
         </is>
       </c>
       <c r="C147" t="inlineStr">
         <is>
-          <t>162</t>
+          <t>224.4</t>
         </is>
       </c>
       <c r="D147" t="inlineStr">
         <is>
-          <t>127.7000</t>
+          <t>168.4</t>
         </is>
       </c>
       <c r="E147" t="inlineStr"/>
@@ -4978,17 +4978,17 @@
       </c>
       <c r="B157" t="inlineStr">
         <is>
-          <t>EIA Crude Oil Imports ChangeJAN/10</t>
+          <t>EIA Refinery Crude Runs ChangeJAN/10</t>
         </is>
       </c>
       <c r="C157" t="inlineStr">
         <is>
-          <t>-1.304M</t>
+          <t>-0.255M</t>
         </is>
       </c>
       <c r="D157" t="inlineStr">
         <is>
-          <t>0.278M</t>
+          <t>0.045M</t>
         </is>
       </c>
       <c r="E157" t="inlineStr"/>
@@ -5005,17 +5005,17 @@
       </c>
       <c r="B158" t="inlineStr">
         <is>
-          <t>EIA Cushing Crude Oil Stocks ChangeJAN/10</t>
+          <t>EIA Distillate Fuel Production ChangeJAN/10</t>
         </is>
       </c>
       <c r="C158" t="inlineStr">
         <is>
-          <t>0.765M</t>
+          <t>-0.021M</t>
         </is>
       </c>
       <c r="D158" t="inlineStr">
         <is>
-          <t>-2.502M</t>
+          <t>-0.167M</t>
         </is>
       </c>
       <c r="E158" t="inlineStr"/>
@@ -5032,22 +5032,22 @@
       </c>
       <c r="B159" t="inlineStr">
         <is>
-          <t>EIA Crude Oil Stocks ChangeJAN/10</t>
+          <t>EIA Gasoline Stocks ChangeJAN/10</t>
         </is>
       </c>
       <c r="C159" t="inlineStr">
         <is>
-          <t>-1.961M</t>
+          <t>5.852M</t>
         </is>
       </c>
       <c r="D159" t="inlineStr">
         <is>
-          <t>-0.959M</t>
+          <t>6.33M</t>
         </is>
       </c>
       <c r="E159" t="inlineStr">
         <is>
-          <t>-1.6M</t>
+          <t>2.60M</t>
         </is>
       </c>
       <c r="F159" t="inlineStr"/>
@@ -5063,24 +5063,20 @@
       </c>
       <c r="B160" t="inlineStr">
         <is>
-          <t>EIA Distillate Stocks ChangeJAN/10</t>
+          <t>EIA Heating Oil Stocks ChangeJAN/10</t>
         </is>
       </c>
       <c r="C160" t="inlineStr">
         <is>
-          <t>3.077M</t>
+          <t>0.646M</t>
         </is>
       </c>
       <c r="D160" t="inlineStr">
         <is>
-          <t>6.071M</t>
-        </is>
-      </c>
-      <c r="E160" t="inlineStr">
-        <is>
-          <t>1.1M</t>
-        </is>
-      </c>
+          <t>-0.632M</t>
+        </is>
+      </c>
+      <c r="E160" t="inlineStr"/>
       <c r="F160" t="inlineStr"/>
       <c r="G160" t="n">
         <v>3</v>
@@ -5094,17 +5090,17 @@
       </c>
       <c r="B161" t="inlineStr">
         <is>
-          <t>EIA Gasoline Production ChangeJAN/10</t>
+          <t>EIA Crude Oil Imports ChangeJAN/10</t>
         </is>
       </c>
       <c r="C161" t="inlineStr">
         <is>
-          <t>0.397M</t>
+          <t>-1.304M</t>
         </is>
       </c>
       <c r="D161" t="inlineStr">
         <is>
-          <t>-0.081M</t>
+          <t>0.278M</t>
         </is>
       </c>
       <c r="E161" t="inlineStr"/>
@@ -5121,20 +5117,24 @@
       </c>
       <c r="B162" t="inlineStr">
         <is>
-          <t>EIA Heating Oil Stocks ChangeJAN/10</t>
+          <t>EIA Distillate Stocks ChangeJAN/10</t>
         </is>
       </c>
       <c r="C162" t="inlineStr">
         <is>
-          <t>0.646M</t>
+          <t>3.077M</t>
         </is>
       </c>
       <c r="D162" t="inlineStr">
         <is>
-          <t>-0.632M</t>
-        </is>
-      </c>
-      <c r="E162" t="inlineStr"/>
+          <t>6.071M</t>
+        </is>
+      </c>
+      <c r="E162" t="inlineStr">
+        <is>
+          <t>1.1M</t>
+        </is>
+      </c>
       <c r="F162" t="inlineStr"/>
       <c r="G162" t="n">
         <v>3</v>
@@ -5148,22 +5148,22 @@
       </c>
       <c r="B163" t="inlineStr">
         <is>
-          <t>EIA Gasoline Stocks ChangeJAN/10</t>
+          <t>EIA Crude Oil Stocks ChangeJAN/10</t>
         </is>
       </c>
       <c r="C163" t="inlineStr">
         <is>
-          <t>5.852M</t>
+          <t>-1.961M</t>
         </is>
       </c>
       <c r="D163" t="inlineStr">
         <is>
-          <t>6.33M</t>
+          <t>-0.959M</t>
         </is>
       </c>
       <c r="E163" t="inlineStr">
         <is>
-          <t>2.60M</t>
+          <t>-1.6M</t>
         </is>
       </c>
       <c r="F163" t="inlineStr"/>
@@ -5179,17 +5179,17 @@
       </c>
       <c r="B164" t="inlineStr">
         <is>
-          <t>EIA Distillate Fuel Production ChangeJAN/10</t>
+          <t>EIA Cushing Crude Oil Stocks ChangeJAN/10</t>
         </is>
       </c>
       <c r="C164" t="inlineStr">
         <is>
-          <t>-0.021M</t>
+          <t>0.765M</t>
         </is>
       </c>
       <c r="D164" t="inlineStr">
         <is>
-          <t>-0.167M</t>
+          <t>-2.502M</t>
         </is>
       </c>
       <c r="E164" t="inlineStr"/>
@@ -5206,17 +5206,17 @@
       </c>
       <c r="B165" t="inlineStr">
         <is>
-          <t>EIA Refinery Crude Runs ChangeJAN/10</t>
+          <t>EIA Gasoline Production ChangeJAN/10</t>
         </is>
       </c>
       <c r="C165" t="inlineStr">
         <is>
-          <t>-0.255M</t>
+          <t>0.397M</t>
         </is>
       </c>
       <c r="D165" t="inlineStr">
         <is>
-          <t>0.045M</t>
+          <t>-0.081M</t>
         </is>
       </c>
       <c r="E165" t="inlineStr"/>
@@ -5336,21 +5336,29 @@
       </c>
       <c r="B171" t="inlineStr">
         <is>
-          <t>Philly Fed CAPEX IndexJAN</t>
+          <t>Retail Sales Ex Gas/Autos MoMDEC</t>
         </is>
       </c>
       <c r="C171" t="inlineStr">
         <is>
-          <t>39.00</t>
+          <t>0.3%</t>
         </is>
       </c>
       <c r="D171" t="inlineStr">
         <is>
-          <t>22.20</t>
-        </is>
-      </c>
-      <c r="E171" t="inlineStr"/>
-      <c r="F171" t="inlineStr"/>
+          <t>0.2%</t>
+        </is>
+      </c>
+      <c r="E171" t="inlineStr">
+        <is>
+          <t>0.4%</t>
+        </is>
+      </c>
+      <c r="F171" t="inlineStr">
+        <is>
+          <t>0.4%</t>
+        </is>
+      </c>
       <c r="G171" t="n">
         <v>3</v>
       </c>
@@ -5363,21 +5371,29 @@
       </c>
       <c r="B172" t="inlineStr">
         <is>
-          <t>Philly Fed New OrdersJAN</t>
+          <t>Continuing Jobless ClaimsJAN/04</t>
         </is>
       </c>
       <c r="C172" t="inlineStr">
         <is>
-          <t>42.9</t>
+          <t>1859K</t>
         </is>
       </c>
       <c r="D172" t="inlineStr">
         <is>
-          <t>-3.6</t>
-        </is>
-      </c>
-      <c r="E172" t="inlineStr"/>
-      <c r="F172" t="inlineStr"/>
+          <t>1867K</t>
+        </is>
+      </c>
+      <c r="E172" t="inlineStr">
+        <is>
+          <t>1870K</t>
+        </is>
+      </c>
+      <c r="F172" t="inlineStr">
+        <is>
+          <t>1870.0K</t>
+        </is>
+      </c>
       <c r="G172" t="n">
         <v>3</v>
       </c>
@@ -5390,31 +5406,27 @@
       </c>
       <c r="B173" t="inlineStr">
         <is>
-          <t>Retail Sales MoMDEC</t>
+          <t>Retail Sales YoYDEC</t>
         </is>
       </c>
       <c r="C173" t="inlineStr">
         <is>
-          <t>0.4%</t>
+          <t>3.9%</t>
         </is>
       </c>
       <c r="D173" t="inlineStr">
         <is>
-          <t>0.8%</t>
-        </is>
-      </c>
-      <c r="E173" t="inlineStr">
-        <is>
-          <t>0.6%</t>
-        </is>
-      </c>
+          <t>4.1%</t>
+        </is>
+      </c>
+      <c r="E173" t="inlineStr"/>
       <c r="F173" t="inlineStr">
         <is>
-          <t>0.5%</t>
+          <t>4.0%</t>
         </is>
       </c>
       <c r="G173" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="174">
@@ -5425,31 +5437,31 @@
       </c>
       <c r="B174" t="inlineStr">
         <is>
-          <t>Philadelphia Fed Manufacturing IndexJAN</t>
+          <t>Import Prices YoYDEC</t>
         </is>
       </c>
       <c r="C174" t="inlineStr">
         <is>
-          <t>44.3</t>
+          <t>2.2%</t>
         </is>
       </c>
       <c r="D174" t="inlineStr">
         <is>
-          <t>-10.9</t>
+          <t>1.4%</t>
         </is>
       </c>
       <c r="E174" t="inlineStr">
         <is>
-          <t>-5</t>
+          <t>2.1%</t>
         </is>
       </c>
       <c r="F174" t="inlineStr">
         <is>
-          <t>-10</t>
+          <t>1.6%</t>
         </is>
       </c>
       <c r="G174" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="175">
@@ -5460,23 +5472,31 @@
       </c>
       <c r="B175" t="inlineStr">
         <is>
-          <t>Philly Fed EmploymentJAN</t>
+          <t>Retail Sales Ex Autos MoMDEC</t>
         </is>
       </c>
       <c r="C175" t="inlineStr">
         <is>
-          <t>11.9</t>
+          <t>0.4%</t>
         </is>
       </c>
       <c r="D175" t="inlineStr">
         <is>
-          <t>4.8</t>
-        </is>
-      </c>
-      <c r="E175" t="inlineStr"/>
-      <c r="F175" t="inlineStr"/>
+          <t>0.2%</t>
+        </is>
+      </c>
+      <c r="E175" t="inlineStr">
+        <is>
+          <t>0.4%</t>
+        </is>
+      </c>
+      <c r="F175" t="inlineStr">
+        <is>
+          <t>0.4%</t>
+        </is>
+      </c>
       <c r="G175" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="176">
@@ -5487,31 +5507,23 @@
       </c>
       <c r="B176" t="inlineStr">
         <is>
-          <t>Import Prices MoMDEC</t>
+          <t>Philly Fed Business ConditionsJAN</t>
         </is>
       </c>
       <c r="C176" t="inlineStr">
         <is>
-          <t>0.1%</t>
+          <t>46.3</t>
         </is>
       </c>
       <c r="D176" t="inlineStr">
         <is>
-          <t>0.1%</t>
-        </is>
-      </c>
-      <c r="E176" t="inlineStr">
-        <is>
-          <t>0.1%</t>
-        </is>
-      </c>
-      <c r="F176" t="inlineStr">
-        <is>
-          <t>0.1%</t>
-        </is>
-      </c>
+          <t>33.8</t>
+        </is>
+      </c>
+      <c r="E176" t="inlineStr"/>
+      <c r="F176" t="inlineStr"/>
       <c r="G176" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="177">
@@ -5522,25 +5534,21 @@
       </c>
       <c r="B177" t="inlineStr">
         <is>
-          <t>Jobless Claims 4-week AverageJAN/11</t>
+          <t>Philly Fed Prices PaidJAN</t>
         </is>
       </c>
       <c r="C177" t="inlineStr">
         <is>
-          <t>212.75K</t>
+          <t>31.90</t>
         </is>
       </c>
       <c r="D177" t="inlineStr">
         <is>
-          <t>213.5K</t>
+          <t>26.60</t>
         </is>
       </c>
       <c r="E177" t="inlineStr"/>
-      <c r="F177" t="inlineStr">
-        <is>
-          <t>215.0K</t>
-        </is>
-      </c>
+      <c r="F177" t="inlineStr"/>
       <c r="G177" t="n">
         <v>3</v>
       </c>
@@ -5553,27 +5561,27 @@
       </c>
       <c r="B178" t="inlineStr">
         <is>
-          <t>Initial Jobless ClaimsJAN/11</t>
+          <t>Export Prices MoMDEC</t>
         </is>
       </c>
       <c r="C178" t="inlineStr">
         <is>
-          <t>217K</t>
+          <t>0.3%</t>
         </is>
       </c>
       <c r="D178" t="inlineStr">
         <is>
-          <t>203K</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="E178" t="inlineStr">
         <is>
-          <t>210K</t>
+          <t>0.2%</t>
         </is>
       </c>
       <c r="F178" t="inlineStr">
         <is>
-          <t>209.0K</t>
+          <t>0.5%</t>
         </is>
       </c>
       <c r="G178" t="n">
@@ -5588,25 +5596,21 @@
       </c>
       <c r="B179" t="inlineStr">
         <is>
-          <t>Export Prices YoYDEC</t>
+          <t>Philly Fed CAPEX IndexJAN</t>
         </is>
       </c>
       <c r="C179" t="inlineStr">
         <is>
-          <t>1.8%</t>
+          <t>39.00</t>
         </is>
       </c>
       <c r="D179" t="inlineStr">
         <is>
-          <t>0.9%</t>
+          <t>22.20</t>
         </is>
       </c>
       <c r="E179" t="inlineStr"/>
-      <c r="F179" t="inlineStr">
-        <is>
-          <t>1.9%</t>
-        </is>
-      </c>
+      <c r="F179" t="inlineStr"/>
       <c r="G179" t="n">
         <v>3</v>
       </c>
@@ -5619,27 +5623,27 @@
       </c>
       <c r="B180" t="inlineStr">
         <is>
-          <t>Export Prices MoMDEC</t>
+          <t>Initial Jobless ClaimsJAN/11</t>
         </is>
       </c>
       <c r="C180" t="inlineStr">
         <is>
-          <t>0.3%</t>
+          <t>217K</t>
         </is>
       </c>
       <c r="D180" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>203K</t>
         </is>
       </c>
       <c r="E180" t="inlineStr">
         <is>
-          <t>0.2%</t>
+          <t>210K</t>
         </is>
       </c>
       <c r="F180" t="inlineStr">
         <is>
-          <t>0.5%</t>
+          <t>209.0K</t>
         </is>
       </c>
       <c r="G180" t="n">
@@ -5654,29 +5658,21 @@
       </c>
       <c r="B181" t="inlineStr">
         <is>
-          <t>Retail Sales Ex Gas/Autos MoMDEC</t>
+          <t>Philly Fed New OrdersJAN</t>
         </is>
       </c>
       <c r="C181" t="inlineStr">
         <is>
-          <t>0.3%</t>
+          <t>42.9</t>
         </is>
       </c>
       <c r="D181" t="inlineStr">
         <is>
-          <t>0.2%</t>
-        </is>
-      </c>
-      <c r="E181" t="inlineStr">
-        <is>
-          <t>0.4%</t>
-        </is>
-      </c>
-      <c r="F181" t="inlineStr">
-        <is>
-          <t>0.4%</t>
-        </is>
-      </c>
+          <t>-3.6</t>
+        </is>
+      </c>
+      <c r="E181" t="inlineStr"/>
+      <c r="F181" t="inlineStr"/>
       <c r="G181" t="n">
         <v>3</v>
       </c>
@@ -5689,23 +5685,31 @@
       </c>
       <c r="B182" t="inlineStr">
         <is>
-          <t>Philly Fed Business ConditionsJAN</t>
+          <t>Retail Sales MoMDEC</t>
         </is>
       </c>
       <c r="C182" t="inlineStr">
         <is>
-          <t>46.3</t>
+          <t>0.4%</t>
         </is>
       </c>
       <c r="D182" t="inlineStr">
         <is>
-          <t>33.8</t>
-        </is>
-      </c>
-      <c r="E182" t="inlineStr"/>
-      <c r="F182" t="inlineStr"/>
+          <t>0.8%</t>
+        </is>
+      </c>
+      <c r="E182" t="inlineStr">
+        <is>
+          <t>0.6%</t>
+        </is>
+      </c>
+      <c r="F182" t="inlineStr">
+        <is>
+          <t>0.5%</t>
+        </is>
+      </c>
       <c r="G182" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="183">
@@ -5716,27 +5720,27 @@
       </c>
       <c r="B183" t="inlineStr">
         <is>
-          <t>Retail Sales Ex Autos MoMDEC</t>
+          <t>Philadelphia Fed Manufacturing IndexJAN</t>
         </is>
       </c>
       <c r="C183" t="inlineStr">
         <is>
-          <t>0.4%</t>
+          <t>44.3</t>
         </is>
       </c>
       <c r="D183" t="inlineStr">
         <is>
-          <t>0.2%</t>
+          <t>-10.9</t>
         </is>
       </c>
       <c r="E183" t="inlineStr">
         <is>
-          <t>0.4%</t>
+          <t>-5</t>
         </is>
       </c>
       <c r="F183" t="inlineStr">
         <is>
-          <t>0.4%</t>
+          <t>-10</t>
         </is>
       </c>
       <c r="G183" t="n">
@@ -5751,27 +5755,23 @@
       </c>
       <c r="B184" t="inlineStr">
         <is>
-          <t>Import Prices YoYDEC</t>
+          <t>Export Prices YoYDEC</t>
         </is>
       </c>
       <c r="C184" t="inlineStr">
         <is>
-          <t>2.2%</t>
+          <t>1.8%</t>
         </is>
       </c>
       <c r="D184" t="inlineStr">
         <is>
-          <t>1.4%</t>
-        </is>
-      </c>
-      <c r="E184" t="inlineStr">
-        <is>
-          <t>2.1%</t>
-        </is>
-      </c>
+          <t>0.9%</t>
+        </is>
+      </c>
+      <c r="E184" t="inlineStr"/>
       <c r="F184" t="inlineStr">
         <is>
-          <t>1.6%</t>
+          <t>1.9%</t>
         </is>
       </c>
       <c r="G184" t="n">
@@ -5786,27 +5786,31 @@
       </c>
       <c r="B185" t="inlineStr">
         <is>
-          <t>Retail Sales YoYDEC</t>
+          <t>Import Prices MoMDEC</t>
         </is>
       </c>
       <c r="C185" t="inlineStr">
         <is>
-          <t>3.9%</t>
+          <t>0.1%</t>
         </is>
       </c>
       <c r="D185" t="inlineStr">
         <is>
-          <t>4.1%</t>
-        </is>
-      </c>
-      <c r="E185" t="inlineStr"/>
+          <t>0.1%</t>
+        </is>
+      </c>
+      <c r="E185" t="inlineStr">
+        <is>
+          <t>0.1%</t>
+        </is>
+      </c>
       <c r="F185" t="inlineStr">
         <is>
-          <t>4.0%</t>
+          <t>0.1%</t>
         </is>
       </c>
       <c r="G185" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="186">
@@ -5817,27 +5821,23 @@
       </c>
       <c r="B186" t="inlineStr">
         <is>
-          <t>Continuing Jobless ClaimsJAN/04</t>
+          <t>Jobless Claims 4-week AverageJAN/11</t>
         </is>
       </c>
       <c r="C186" t="inlineStr">
         <is>
-          <t>1859K</t>
+          <t>212.75K</t>
         </is>
       </c>
       <c r="D186" t="inlineStr">
         <is>
-          <t>1867K</t>
-        </is>
-      </c>
-      <c r="E186" t="inlineStr">
-        <is>
-          <t>1870K</t>
-        </is>
-      </c>
+          <t>213.5K</t>
+        </is>
+      </c>
+      <c r="E186" t="inlineStr"/>
       <c r="F186" t="inlineStr">
         <is>
-          <t>1870.0K</t>
+          <t>215.0K</t>
         </is>
       </c>
       <c r="G186" t="n">
@@ -5852,17 +5852,17 @@
       </c>
       <c r="B187" t="inlineStr">
         <is>
-          <t>Philly Fed Prices PaidJAN</t>
+          <t>Philly Fed EmploymentJAN</t>
         </is>
       </c>
       <c r="C187" t="inlineStr">
         <is>
-          <t>31.90</t>
+          <t>11.9</t>
         </is>
       </c>
       <c r="D187" t="inlineStr">
         <is>
-          <t>26.60</t>
+          <t>4.8</t>
         </is>
       </c>
       <c r="E187" t="inlineStr"/>
@@ -6282,31 +6282,27 @@
       </c>
       <c r="B201" t="inlineStr">
         <is>
-          <t>Industrial Production MoMDEC</t>
+          <t>Industrial Production YoYDEC</t>
         </is>
       </c>
       <c r="C201" t="inlineStr">
         <is>
-          <t>0.9%</t>
+          <t>0.5%</t>
         </is>
       </c>
       <c r="D201" t="inlineStr">
         <is>
-          <t>0.2%</t>
-        </is>
-      </c>
-      <c r="E201" t="inlineStr">
-        <is>
-          <t>0.3%</t>
-        </is>
-      </c>
+          <t>-0.6%</t>
+        </is>
+      </c>
+      <c r="E201" t="inlineStr"/>
       <c r="F201" t="inlineStr">
         <is>
-          <t>0.1%</t>
+          <t>-0.5%</t>
         </is>
       </c>
       <c r="G201" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="202">
@@ -6317,27 +6313,27 @@
       </c>
       <c r="B202" t="inlineStr">
         <is>
-          <t>Capacity UtilizationDEC</t>
+          <t>Manufacturing Production MoMDEC</t>
         </is>
       </c>
       <c r="C202" t="inlineStr">
         <is>
-          <t>77.6%</t>
+          <t>0.6%</t>
         </is>
       </c>
       <c r="D202" t="inlineStr">
         <is>
-          <t>77%</t>
+          <t>0.4%</t>
         </is>
       </c>
       <c r="E202" t="inlineStr">
         <is>
-          <t>77%</t>
+          <t>0.2%</t>
         </is>
       </c>
       <c r="F202" t="inlineStr">
         <is>
-          <t>76.9%</t>
+          <t>0.4%</t>
         </is>
       </c>
       <c r="G202" t="n">
@@ -6352,23 +6348,27 @@
       </c>
       <c r="B203" t="inlineStr">
         <is>
-          <t>Manufacturing Production YoYDEC</t>
+          <t>Capacity UtilizationDEC</t>
         </is>
       </c>
       <c r="C203" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>77.6%</t>
         </is>
       </c>
       <c r="D203" t="inlineStr">
         <is>
-          <t>-0.6%</t>
-        </is>
-      </c>
-      <c r="E203" t="inlineStr"/>
+          <t>77%</t>
+        </is>
+      </c>
+      <c r="E203" t="inlineStr">
+        <is>
+          <t>77%</t>
+        </is>
+      </c>
       <c r="F203" t="inlineStr">
         <is>
-          <t>-0.7%</t>
+          <t>76.9%</t>
         </is>
       </c>
       <c r="G203" t="n">
@@ -6383,31 +6383,31 @@
       </c>
       <c r="B204" t="inlineStr">
         <is>
-          <t>Manufacturing Production MoMDEC</t>
+          <t>Industrial Production MoMDEC</t>
         </is>
       </c>
       <c r="C204" t="inlineStr">
         <is>
-          <t>0.6%</t>
+          <t>0.9%</t>
         </is>
       </c>
       <c r="D204" t="inlineStr">
         <is>
-          <t>0.4%</t>
+          <t>0.2%</t>
         </is>
       </c>
       <c r="E204" t="inlineStr">
         <is>
-          <t>0.2%</t>
+          <t>0.3%</t>
         </is>
       </c>
       <c r="F204" t="inlineStr">
         <is>
-          <t>0.4%</t>
+          <t>0.1%</t>
         </is>
       </c>
       <c r="G204" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="205">
@@ -6418,12 +6418,12 @@
       </c>
       <c r="B205" t="inlineStr">
         <is>
-          <t>Industrial Production YoYDEC</t>
+          <t>Manufacturing Production YoYDEC</t>
         </is>
       </c>
       <c r="C205" t="inlineStr">
         <is>
-          <t>0.5%</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="D205" t="inlineStr">
@@ -6434,7 +6434,7 @@
       <c r="E205" t="inlineStr"/>
       <c r="F205" t="inlineStr">
         <is>
-          <t>-0.5%</t>
+          <t>-0.7%</t>
         </is>
       </c>
       <c r="G205" t="n">
@@ -6661,17 +6661,17 @@
       </c>
       <c r="B214" t="inlineStr">
         <is>
-          <t>52-Week Bill Auction</t>
+          <t>42-Day Bill Auction</t>
         </is>
       </c>
       <c r="C214" t="inlineStr">
         <is>
-          <t>4.025%</t>
+          <t>4.250%</t>
         </is>
       </c>
       <c r="D214" t="inlineStr">
         <is>
-          <t>4.070%</t>
+          <t>4.210%</t>
         </is>
       </c>
       <c r="E214" t="inlineStr"/>
@@ -6688,17 +6688,17 @@
       </c>
       <c r="B215" t="inlineStr">
         <is>
-          <t>42-Day Bill Auction</t>
+          <t>52-Week Bill Auction</t>
         </is>
       </c>
       <c r="C215" t="inlineStr">
         <is>
-          <t>4.250%</t>
+          <t>4.025%</t>
         </is>
       </c>
       <c r="D215" t="inlineStr">
         <is>
-          <t>4.210%</t>
+          <t>4.070%</t>
         </is>
       </c>
       <c r="E215" t="inlineStr"/>
@@ -6993,27 +6993,23 @@
       </c>
       <c r="B226" t="inlineStr">
         <is>
-          <t>Continuing Jobless ClaimsJAN/11</t>
+          <t>Jobless Claims 4-week AverageJAN/18</t>
         </is>
       </c>
       <c r="C226" t="inlineStr">
         <is>
-          <t>1899K</t>
+          <t>213.5K</t>
         </is>
       </c>
       <c r="D226" t="inlineStr">
         <is>
-          <t>1853K</t>
-        </is>
-      </c>
-      <c r="E226" t="inlineStr">
-        <is>
-          <t>1860K</t>
-        </is>
-      </c>
+          <t>212.75K</t>
+        </is>
+      </c>
+      <c r="E226" t="inlineStr"/>
       <c r="F226" t="inlineStr">
         <is>
-          <t>1861K</t>
+          <t>213.0K</t>
         </is>
       </c>
       <c r="G226" t="n">
@@ -7063,23 +7059,27 @@
       </c>
       <c r="B228" t="inlineStr">
         <is>
-          <t>Jobless Claims 4-week AverageJAN/18</t>
+          <t>Continuing Jobless ClaimsJAN/11</t>
         </is>
       </c>
       <c r="C228" t="inlineStr">
         <is>
-          <t>213.5K</t>
+          <t>1899K</t>
         </is>
       </c>
       <c r="D228" t="inlineStr">
         <is>
-          <t>212.75K</t>
-        </is>
-      </c>
-      <c r="E228" t="inlineStr"/>
+          <t>1853K</t>
+        </is>
+      </c>
+      <c r="E228" t="inlineStr">
+        <is>
+          <t>1860K</t>
+        </is>
+      </c>
       <c r="F228" t="inlineStr">
         <is>
-          <t>213.0K</t>
+          <t>1861K</t>
         </is>
       </c>
       <c r="G228" t="n">
@@ -7241,27 +7241,23 @@
       </c>
       <c r="B234" t="inlineStr">
         <is>
-          <t>EIA Gasoline Stocks ChangeJAN/17</t>
+          <t>30-Year Mortgage RateJAN/23</t>
         </is>
       </c>
       <c r="C234" t="inlineStr">
         <is>
-          <t>2.332M</t>
+          <t>6.96%</t>
         </is>
       </c>
       <c r="D234" t="inlineStr">
         <is>
-          <t>5.852M</t>
-        </is>
-      </c>
-      <c r="E234" t="inlineStr">
-        <is>
-          <t>2.5M</t>
-        </is>
-      </c>
+          <t>7.04%</t>
+        </is>
+      </c>
+      <c r="E234" t="inlineStr"/>
       <c r="F234" t="inlineStr"/>
       <c r="G234" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="235">
@@ -7272,17 +7268,17 @@
       </c>
       <c r="B235" t="inlineStr">
         <is>
-          <t>EIA Refinery Crude Runs ChangeJAN/17</t>
+          <t>EIA Distillate Fuel Production ChangeJAN/17</t>
         </is>
       </c>
       <c r="C235" t="inlineStr">
         <is>
-          <t>-1.125M</t>
+          <t>-0.473M</t>
         </is>
       </c>
       <c r="D235" t="inlineStr">
         <is>
-          <t>-0.255M</t>
+          <t>-0.021M</t>
         </is>
       </c>
       <c r="E235" t="inlineStr"/>
@@ -7299,20 +7295,24 @@
       </c>
       <c r="B236" t="inlineStr">
         <is>
-          <t>EIA Crude Oil Imports ChangeJAN/17</t>
+          <t>EIA Distillate Stocks ChangeJAN/17</t>
         </is>
       </c>
       <c r="C236" t="inlineStr">
         <is>
-          <t>0.184M</t>
+          <t>-3.07M</t>
         </is>
       </c>
       <c r="D236" t="inlineStr">
         <is>
-          <t>-1.304M</t>
-        </is>
-      </c>
-      <c r="E236" t="inlineStr"/>
+          <t>3.077M</t>
+        </is>
+      </c>
+      <c r="E236" t="inlineStr">
+        <is>
+          <t>0.6M</t>
+        </is>
+      </c>
       <c r="F236" t="inlineStr"/>
       <c r="G236" t="n">
         <v>3</v>
@@ -7326,27 +7326,23 @@
       </c>
       <c r="B237" t="inlineStr">
         <is>
-          <t>EIA Crude Oil Stocks ChangeJAN/17</t>
+          <t>EIA Heating Oil Stocks ChangeJAN/17</t>
         </is>
       </c>
       <c r="C237" t="inlineStr">
         <is>
-          <t>-1.017M</t>
+          <t>0.068M</t>
         </is>
       </c>
       <c r="D237" t="inlineStr">
         <is>
-          <t>-1.962M</t>
-        </is>
-      </c>
-      <c r="E237" t="inlineStr">
-        <is>
-          <t>-2.1M</t>
-        </is>
-      </c>
+          <t>0.646M</t>
+        </is>
+      </c>
+      <c r="E237" t="inlineStr"/>
       <c r="F237" t="inlineStr"/>
       <c r="G237" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="238">
@@ -7357,17 +7353,17 @@
       </c>
       <c r="B238" t="inlineStr">
         <is>
-          <t>15-Year Mortgage RateJAN/23</t>
+          <t>EIA Cushing Crude Oil Stocks ChangeJAN/17</t>
         </is>
       </c>
       <c r="C238" t="inlineStr">
         <is>
-          <t>6.16%</t>
+          <t>-0.148M</t>
         </is>
       </c>
       <c r="D238" t="inlineStr">
         <is>
-          <t>6.27%</t>
+          <t>0.765M</t>
         </is>
       </c>
       <c r="E238" t="inlineStr"/>
@@ -7384,17 +7380,17 @@
       </c>
       <c r="B239" t="inlineStr">
         <is>
-          <t>EIA Cushing Crude Oil Stocks ChangeJAN/17</t>
+          <t>EIA Gasoline Production ChangeJAN/17</t>
         </is>
       </c>
       <c r="C239" t="inlineStr">
         <is>
-          <t>-0.148M</t>
+          <t>-0.043M</t>
         </is>
       </c>
       <c r="D239" t="inlineStr">
         <is>
-          <t>0.765M</t>
+          <t>0.397M</t>
         </is>
       </c>
       <c r="E239" t="inlineStr"/>
@@ -7411,23 +7407,27 @@
       </c>
       <c r="B240" t="inlineStr">
         <is>
-          <t>EIA Gasoline Production ChangeJAN/17</t>
+          <t>EIA Crude Oil Stocks ChangeJAN/17</t>
         </is>
       </c>
       <c r="C240" t="inlineStr">
         <is>
-          <t>-0.043M</t>
+          <t>-1.017M</t>
         </is>
       </c>
       <c r="D240" t="inlineStr">
         <is>
-          <t>0.397M</t>
-        </is>
-      </c>
-      <c r="E240" t="inlineStr"/>
+          <t>-1.962M</t>
+        </is>
+      </c>
+      <c r="E240" t="inlineStr">
+        <is>
+          <t>-2.1M</t>
+        </is>
+      </c>
       <c r="F240" t="inlineStr"/>
       <c r="G240" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="241">
@@ -7438,17 +7438,17 @@
       </c>
       <c r="B241" t="inlineStr">
         <is>
-          <t>EIA Heating Oil Stocks ChangeJAN/17</t>
+          <t>EIA Crude Oil Imports ChangeJAN/17</t>
         </is>
       </c>
       <c r="C241" t="inlineStr">
         <is>
-          <t>0.068M</t>
+          <t>0.184M</t>
         </is>
       </c>
       <c r="D241" t="inlineStr">
         <is>
-          <t>0.646M</t>
+          <t>-1.304M</t>
         </is>
       </c>
       <c r="E241" t="inlineStr"/>
@@ -7465,24 +7465,20 @@
       </c>
       <c r="B242" t="inlineStr">
         <is>
-          <t>EIA Distillate Stocks ChangeJAN/17</t>
+          <t>EIA Refinery Crude Runs ChangeJAN/17</t>
         </is>
       </c>
       <c r="C242" t="inlineStr">
         <is>
-          <t>-3.07M</t>
+          <t>-1.125M</t>
         </is>
       </c>
       <c r="D242" t="inlineStr">
         <is>
-          <t>3.077M</t>
-        </is>
-      </c>
-      <c r="E242" t="inlineStr">
-        <is>
-          <t>0.6M</t>
-        </is>
-      </c>
+          <t>-0.255M</t>
+        </is>
+      </c>
+      <c r="E242" t="inlineStr"/>
       <c r="F242" t="inlineStr"/>
       <c r="G242" t="n">
         <v>3</v>
@@ -7496,23 +7492,27 @@
       </c>
       <c r="B243" t="inlineStr">
         <is>
-          <t>EIA Distillate Fuel Production ChangeJAN/17</t>
+          <t>EIA Gasoline Stocks ChangeJAN/17</t>
         </is>
       </c>
       <c r="C243" t="inlineStr">
         <is>
-          <t>-0.473M</t>
+          <t>2.332M</t>
         </is>
       </c>
       <c r="D243" t="inlineStr">
         <is>
-          <t>-0.021M</t>
-        </is>
-      </c>
-      <c r="E243" t="inlineStr"/>
+          <t>5.852M</t>
+        </is>
+      </c>
+      <c r="E243" t="inlineStr">
+        <is>
+          <t>2.5M</t>
+        </is>
+      </c>
       <c r="F243" t="inlineStr"/>
       <c r="G243" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="244">
@@ -7523,17 +7523,17 @@
       </c>
       <c r="B244" t="inlineStr">
         <is>
-          <t>30-Year Mortgage RateJAN/23</t>
+          <t>15-Year Mortgage RateJAN/23</t>
         </is>
       </c>
       <c r="C244" t="inlineStr">
         <is>
-          <t>6.96%</t>
+          <t>6.16%</t>
         </is>
       </c>
       <c r="D244" t="inlineStr">
         <is>
-          <t>7.04%</t>
+          <t>6.27%</t>
         </is>
       </c>
       <c r="E244" t="inlineStr"/>
@@ -7705,31 +7705,27 @@
       </c>
       <c r="B250" t="inlineStr">
         <is>
-          <t>Michigan Current Conditions FinalJAN</t>
+          <t>Existing Home Sales MoMDEC</t>
         </is>
       </c>
       <c r="C250" t="inlineStr">
         <is>
-          <t>74.0</t>
+          <t>2.2%</t>
         </is>
       </c>
       <c r="D250" t="inlineStr">
         <is>
-          <t>75.1</t>
-        </is>
-      </c>
-      <c r="E250" t="inlineStr">
-        <is>
-          <t>77.9</t>
-        </is>
-      </c>
+          <t>4.8%</t>
+        </is>
+      </c>
+      <c r="E250" t="inlineStr"/>
       <c r="F250" t="inlineStr">
         <is>
-          <t>77.9</t>
+          <t>0.3%</t>
         </is>
       </c>
       <c r="G250" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="251">
@@ -7740,17 +7736,17 @@
       </c>
       <c r="B251" t="inlineStr">
         <is>
-          <t>Michigan Inflation Expectations FinalJAN</t>
+          <t>Michigan 5 Year Inflation Expectations FinalJAN</t>
         </is>
       </c>
       <c r="C251" t="inlineStr">
         <is>
-          <t>3.3%</t>
+          <t>3.2%</t>
         </is>
       </c>
       <c r="D251" t="inlineStr">
         <is>
-          <t>2.8%</t>
+          <t>3%</t>
         </is>
       </c>
       <c r="E251" t="inlineStr">
@@ -7775,31 +7771,31 @@
       </c>
       <c r="B252" t="inlineStr">
         <is>
-          <t>Existing Home SalesDEC</t>
+          <t>Michigan Consumer Sentiment FinalJAN</t>
         </is>
       </c>
       <c r="C252" t="inlineStr">
         <is>
-          <t>4.24M</t>
+          <t>71.1</t>
         </is>
       </c>
       <c r="D252" t="inlineStr">
         <is>
-          <t>4.15M</t>
+          <t>74.0</t>
         </is>
       </c>
       <c r="E252" t="inlineStr">
         <is>
-          <t>4.19M</t>
+          <t>73.2</t>
         </is>
       </c>
       <c r="F252" t="inlineStr">
         <is>
-          <t>4.1M</t>
+          <t>73.2</t>
         </is>
       </c>
       <c r="G252" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="253">
@@ -7810,31 +7806,31 @@
       </c>
       <c r="B253" t="inlineStr">
         <is>
-          <t>Michigan Consumer Sentiment FinalJAN</t>
+          <t>Michigan Consumer Expectations FinalJAN</t>
         </is>
       </c>
       <c r="C253" t="inlineStr">
         <is>
-          <t>71.1</t>
+          <t>69.3</t>
         </is>
       </c>
       <c r="D253" t="inlineStr">
         <is>
-          <t>74.0</t>
+          <t>73.3</t>
         </is>
       </c>
       <c r="E253" t="inlineStr">
         <is>
-          <t>73.2</t>
+          <t>70.2</t>
         </is>
       </c>
       <c r="F253" t="inlineStr">
         <is>
-          <t>73.2</t>
+          <t>70.2</t>
         </is>
       </c>
       <c r="G253" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="254">
@@ -7845,27 +7841,31 @@
       </c>
       <c r="B254" t="inlineStr">
         <is>
-          <t>Existing Home Sales MoMDEC</t>
+          <t>Michigan Inflation Expectations FinalJAN</t>
         </is>
       </c>
       <c r="C254" t="inlineStr">
         <is>
-          <t>2.2%</t>
+          <t>3.3%</t>
         </is>
       </c>
       <c r="D254" t="inlineStr">
         <is>
-          <t>4.8%</t>
-        </is>
-      </c>
-      <c r="E254" t="inlineStr"/>
+          <t>2.8%</t>
+        </is>
+      </c>
+      <c r="E254" t="inlineStr">
+        <is>
+          <t>3.3%</t>
+        </is>
+      </c>
       <c r="F254" t="inlineStr">
         <is>
-          <t>0.3%</t>
+          <t>3.3%</t>
         </is>
       </c>
       <c r="G254" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="255">
@@ -7876,31 +7876,31 @@
       </c>
       <c r="B255" t="inlineStr">
         <is>
-          <t>Michigan Consumer Expectations FinalJAN</t>
+          <t>Existing Home SalesDEC</t>
         </is>
       </c>
       <c r="C255" t="inlineStr">
         <is>
-          <t>69.3</t>
+          <t>4.24M</t>
         </is>
       </c>
       <c r="D255" t="inlineStr">
         <is>
-          <t>73.3</t>
+          <t>4.15M</t>
         </is>
       </c>
       <c r="E255" t="inlineStr">
         <is>
-          <t>70.2</t>
+          <t>4.19M</t>
         </is>
       </c>
       <c r="F255" t="inlineStr">
         <is>
-          <t>70.2</t>
+          <t>4.1M</t>
         </is>
       </c>
       <c r="G255" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="256">
@@ -7911,27 +7911,27 @@
       </c>
       <c r="B256" t="inlineStr">
         <is>
-          <t>Michigan 5 Year Inflation Expectations FinalJAN</t>
+          <t>Michigan Current Conditions FinalJAN</t>
         </is>
       </c>
       <c r="C256" t="inlineStr">
         <is>
-          <t>3.2%</t>
+          <t>74.0</t>
         </is>
       </c>
       <c r="D256" t="inlineStr">
         <is>
-          <t>3%</t>
+          <t>75.1</t>
         </is>
       </c>
       <c r="E256" t="inlineStr">
         <is>
-          <t>3.3%</t>
+          <t>77.9</t>
         </is>
       </c>
       <c r="F256" t="inlineStr">
         <is>
-          <t>3.3%</t>
+          <t>77.9</t>
         </is>
       </c>
       <c r="G256" t="n">
@@ -8252,17 +8252,17 @@
       </c>
       <c r="B267" t="inlineStr">
         <is>
-          <t>3-Month Bill Auction</t>
+          <t>5-Year Note Auction</t>
         </is>
       </c>
       <c r="C267" t="inlineStr">
         <is>
-          <t>4.195%</t>
+          <t>4.33%</t>
         </is>
       </c>
       <c r="D267" t="inlineStr">
         <is>
-          <t>4.215%</t>
+          <t>4.478%</t>
         </is>
       </c>
       <c r="E267" t="inlineStr"/>
@@ -8279,17 +8279,17 @@
       </c>
       <c r="B268" t="inlineStr">
         <is>
-          <t>5-Year Note Auction</t>
+          <t>3-Month Bill Auction</t>
         </is>
       </c>
       <c r="C268" t="inlineStr">
         <is>
-          <t>4.33%</t>
+          <t>4.195%</t>
         </is>
       </c>
       <c r="D268" t="inlineStr">
         <is>
-          <t>4.478%</t>
+          <t>4.215%</t>
         </is>
       </c>
       <c r="E268" t="inlineStr"/>
@@ -8632,23 +8632,23 @@
       </c>
       <c r="B279" t="inlineStr">
         <is>
-          <t>Richmond Fed Manufacturing Shipments IndexJAN</t>
+          <t>Richmond Fed Services Revenues IndexJAN</t>
         </is>
       </c>
       <c r="C279" t="inlineStr">
         <is>
-          <t>-9</t>
+          <t>4</t>
         </is>
       </c>
       <c r="D279" t="inlineStr">
         <is>
-          <t>-11</t>
+          <t>23</t>
         </is>
       </c>
       <c r="E279" t="inlineStr"/>
       <c r="F279" t="inlineStr">
         <is>
-          <t>-9</t>
+          <t>21</t>
         </is>
       </c>
       <c r="G279" t="n">
@@ -8663,27 +8663,23 @@
       </c>
       <c r="B280" t="inlineStr">
         <is>
-          <t>Richmond Fed Manufacturing IndexJAN</t>
+          <t>Richmond Fed Manufacturing Shipments IndexJAN</t>
         </is>
       </c>
       <c r="C280" t="inlineStr">
         <is>
-          <t>-4</t>
+          <t>-9</t>
         </is>
       </c>
       <c r="D280" t="inlineStr">
         <is>
-          <t>-10</t>
-        </is>
-      </c>
-      <c r="E280" t="inlineStr">
-        <is>
-          <t>-8</t>
-        </is>
-      </c>
+          <t>-11</t>
+        </is>
+      </c>
+      <c r="E280" t="inlineStr"/>
       <c r="F280" t="inlineStr">
         <is>
-          <t>-8</t>
+          <t>-9</t>
         </is>
       </c>
       <c r="G280" t="n">
@@ -8698,31 +8694,31 @@
       </c>
       <c r="B281" t="inlineStr">
         <is>
-          <t>CB Consumer ConfidenceJAN</t>
+          <t>Richmond Fed Manufacturing IndexJAN</t>
         </is>
       </c>
       <c r="C281" t="inlineStr">
         <is>
-          <t>104.1</t>
+          <t>-4</t>
         </is>
       </c>
       <c r="D281" t="inlineStr">
         <is>
-          <t>109.5</t>
+          <t>-10</t>
         </is>
       </c>
       <c r="E281" t="inlineStr">
         <is>
-          <t>105.6</t>
+          <t>-8</t>
         </is>
       </c>
       <c r="F281" t="inlineStr">
         <is>
-          <t>104</t>
+          <t>-8</t>
         </is>
       </c>
       <c r="G281" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="282">
@@ -8733,27 +8729,31 @@
       </c>
       <c r="B282" t="inlineStr">
         <is>
-          <t>Richmond Fed Services Revenues IndexJAN</t>
+          <t>CB Consumer ConfidenceJAN</t>
         </is>
       </c>
       <c r="C282" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>104.1</t>
         </is>
       </c>
       <c r="D282" t="inlineStr">
         <is>
-          <t>23</t>
-        </is>
-      </c>
-      <c r="E282" t="inlineStr"/>
+          <t>109.5</t>
+        </is>
+      </c>
+      <c r="E282" t="inlineStr">
+        <is>
+          <t>105.6</t>
+        </is>
+      </c>
       <c r="F282" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>104</t>
         </is>
       </c>
       <c r="G282" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="283">
@@ -8764,23 +8764,23 @@
       </c>
       <c r="B283" t="inlineStr">
         <is>
-          <t>Dallas Fed Services Revenues IndexJAN</t>
+          <t>Dallas Fed Services IndexJAN</t>
         </is>
       </c>
       <c r="C283" t="inlineStr">
         <is>
-          <t>5.7</t>
+          <t>7.4</t>
         </is>
       </c>
       <c r="D283" t="inlineStr">
         <is>
-          <t>13.9</t>
+          <t>10.8</t>
         </is>
       </c>
       <c r="E283" t="inlineStr"/>
       <c r="F283" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>9.5</t>
         </is>
       </c>
       <c r="G283" t="n">
@@ -8795,23 +8795,23 @@
       </c>
       <c r="B284" t="inlineStr">
         <is>
-          <t>Dallas Fed Services IndexJAN</t>
+          <t>Dallas Fed Services Revenues IndexJAN</t>
         </is>
       </c>
       <c r="C284" t="inlineStr">
         <is>
-          <t>7.4</t>
+          <t>5.7</t>
         </is>
       </c>
       <c r="D284" t="inlineStr">
         <is>
-          <t>10.8</t>
+          <t>13.9</t>
         </is>
       </c>
       <c r="E284" t="inlineStr"/>
       <c r="F284" t="inlineStr">
         <is>
-          <t>9.5</t>
+          <t>13</t>
         </is>
       </c>
       <c r="G284" t="n">
@@ -8965,17 +8965,17 @@
       </c>
       <c r="B290" t="inlineStr">
         <is>
-          <t>MBA Purchase IndexJAN/24</t>
+          <t>MBA Mortgage Refinance IndexJAN/24</t>
         </is>
       </c>
       <c r="C290" t="inlineStr">
         <is>
-          <t>162.4</t>
+          <t>520.9</t>
         </is>
       </c>
       <c r="D290" t="inlineStr">
         <is>
-          <t>163</t>
+          <t>558.8</t>
         </is>
       </c>
       <c r="E290" t="inlineStr"/>
@@ -8992,17 +8992,17 @@
       </c>
       <c r="B291" t="inlineStr">
         <is>
-          <t>MBA Mortgage Market IndexJAN/24</t>
+          <t>MBA Mortgage ApplicationsJAN/24</t>
         </is>
       </c>
       <c r="C291" t="inlineStr">
         <is>
-          <t>220.0</t>
+          <t>-2%</t>
         </is>
       </c>
       <c r="D291" t="inlineStr">
         <is>
-          <t>224.6</t>
+          <t>0.1%</t>
         </is>
       </c>
       <c r="E291" t="inlineStr"/>
@@ -9019,23 +9019,23 @@
       </c>
       <c r="B292" t="inlineStr">
         <is>
-          <t>MBA Mortgage ApplicationsJAN/24</t>
+          <t>MBA 30-Year Mortgage RateJAN/24</t>
         </is>
       </c>
       <c r="C292" t="inlineStr">
         <is>
-          <t>-2%</t>
+          <t>7.02%</t>
         </is>
       </c>
       <c r="D292" t="inlineStr">
         <is>
-          <t>0.1%</t>
+          <t>7.02%</t>
         </is>
       </c>
       <c r="E292" t="inlineStr"/>
       <c r="F292" t="inlineStr"/>
       <c r="G292" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="293">
@@ -9046,23 +9046,23 @@
       </c>
       <c r="B293" t="inlineStr">
         <is>
-          <t>MBA 30-Year Mortgage RateJAN/24</t>
+          <t>MBA Purchase IndexJAN/24</t>
         </is>
       </c>
       <c r="C293" t="inlineStr">
         <is>
-          <t>7.02%</t>
+          <t>162.4</t>
         </is>
       </c>
       <c r="D293" t="inlineStr">
         <is>
-          <t>7.02%</t>
+          <t>163</t>
         </is>
       </c>
       <c r="E293" t="inlineStr"/>
       <c r="F293" t="inlineStr"/>
       <c r="G293" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="294">
@@ -9073,17 +9073,17 @@
       </c>
       <c r="B294" t="inlineStr">
         <is>
-          <t>MBA Mortgage Refinance IndexJAN/24</t>
+          <t>MBA Mortgage Market IndexJAN/24</t>
         </is>
       </c>
       <c r="C294" t="inlineStr">
         <is>
-          <t>520.9</t>
+          <t>220.0</t>
         </is>
       </c>
       <c r="D294" t="inlineStr">
         <is>
-          <t>558.8</t>
+          <t>224.6</t>
         </is>
       </c>
       <c r="E294" t="inlineStr"/>
@@ -9201,24 +9201,20 @@
       </c>
       <c r="B298" t="inlineStr">
         <is>
-          <t>EIA Distillate Stocks ChangeJAN/24</t>
+          <t>EIA Crude Oil Imports ChangeJAN/24</t>
         </is>
       </c>
       <c r="C298" t="inlineStr">
         <is>
-          <t>-4.994M</t>
+          <t>0.532M</t>
         </is>
       </c>
       <c r="D298" t="inlineStr">
         <is>
-          <t>-3.07M</t>
-        </is>
-      </c>
-      <c r="E298" t="inlineStr">
-        <is>
-          <t>-2.1M</t>
-        </is>
-      </c>
+          <t>0.184M</t>
+        </is>
+      </c>
+      <c r="E298" t="inlineStr"/>
       <c r="F298" t="inlineStr"/>
       <c r="G298" t="n">
         <v>3</v>
@@ -9232,17 +9228,17 @@
       </c>
       <c r="B299" t="inlineStr">
         <is>
-          <t>EIA Gasoline Production ChangeJAN/24</t>
+          <t>EIA Refinery Crude Runs ChangeJAN/24</t>
         </is>
       </c>
       <c r="C299" t="inlineStr">
         <is>
-          <t>-0.044M</t>
+          <t>-0.333M</t>
         </is>
       </c>
       <c r="D299" t="inlineStr">
         <is>
-          <t>-0.043M</t>
+          <t>-1.125M</t>
         </is>
       </c>
       <c r="E299" t="inlineStr"/>
@@ -9259,17 +9255,17 @@
       </c>
       <c r="B300" t="inlineStr">
         <is>
-          <t>EIA Cushing Crude Oil Stocks ChangeJAN/24</t>
+          <t>EIA Distillate Fuel Production ChangeJAN/24</t>
         </is>
       </c>
       <c r="C300" t="inlineStr">
         <is>
-          <t>0.326M</t>
+          <t>0.028M</t>
         </is>
       </c>
       <c r="D300" t="inlineStr">
         <is>
-          <t>-0.148M</t>
+          <t>-0.473M</t>
         </is>
       </c>
       <c r="E300" t="inlineStr"/>
@@ -9286,23 +9282,27 @@
       </c>
       <c r="B301" t="inlineStr">
         <is>
-          <t>EIA Heating Oil Stocks ChangeJAN/24</t>
+          <t>EIA Gasoline Stocks ChangeJAN/24</t>
         </is>
       </c>
       <c r="C301" t="inlineStr">
         <is>
-          <t>0.128M</t>
+          <t>2.957M</t>
         </is>
       </c>
       <c r="D301" t="inlineStr">
         <is>
-          <t>0.068M</t>
-        </is>
-      </c>
-      <c r="E301" t="inlineStr"/>
+          <t>2.332M</t>
+        </is>
+      </c>
+      <c r="E301" t="inlineStr">
+        <is>
+          <t>1.5M</t>
+        </is>
+      </c>
       <c r="F301" t="inlineStr"/>
       <c r="G301" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="302">
@@ -9313,27 +9313,23 @@
       </c>
       <c r="B302" t="inlineStr">
         <is>
-          <t>EIA Crude Oil Stocks ChangeJAN/24</t>
+          <t>EIA Gasoline Production ChangeJAN/24</t>
         </is>
       </c>
       <c r="C302" t="inlineStr">
         <is>
-          <t>3.463M</t>
+          <t>-0.044M</t>
         </is>
       </c>
       <c r="D302" t="inlineStr">
         <is>
-          <t>-1.017M</t>
-        </is>
-      </c>
-      <c r="E302" t="inlineStr">
-        <is>
-          <t>3.2M</t>
-        </is>
-      </c>
+          <t>-0.043M</t>
+        </is>
+      </c>
+      <c r="E302" t="inlineStr"/>
       <c r="F302" t="inlineStr"/>
       <c r="G302" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="303">
@@ -9344,27 +9340,23 @@
       </c>
       <c r="B303" t="inlineStr">
         <is>
-          <t>EIA Gasoline Stocks ChangeJAN/24</t>
+          <t>EIA Heating Oil Stocks ChangeJAN/24</t>
         </is>
       </c>
       <c r="C303" t="inlineStr">
         <is>
-          <t>2.957M</t>
+          <t>0.128M</t>
         </is>
       </c>
       <c r="D303" t="inlineStr">
         <is>
-          <t>2.332M</t>
-        </is>
-      </c>
-      <c r="E303" t="inlineStr">
-        <is>
-          <t>1.5M</t>
-        </is>
-      </c>
+          <t>0.068M</t>
+        </is>
+      </c>
+      <c r="E303" t="inlineStr"/>
       <c r="F303" t="inlineStr"/>
       <c r="G303" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="304">
@@ -9375,17 +9367,17 @@
       </c>
       <c r="B304" t="inlineStr">
         <is>
-          <t>EIA Crude Oil Imports ChangeJAN/24</t>
+          <t>EIA Cushing Crude Oil Stocks ChangeJAN/24</t>
         </is>
       </c>
       <c r="C304" t="inlineStr">
         <is>
-          <t>0.532M</t>
+          <t>0.326M</t>
         </is>
       </c>
       <c r="D304" t="inlineStr">
         <is>
-          <t>0.184M</t>
+          <t>-0.148M</t>
         </is>
       </c>
       <c r="E304" t="inlineStr"/>
@@ -9402,20 +9394,24 @@
       </c>
       <c r="B305" t="inlineStr">
         <is>
-          <t>EIA Distillate Fuel Production ChangeJAN/24</t>
+          <t>EIA Distillate Stocks ChangeJAN/24</t>
         </is>
       </c>
       <c r="C305" t="inlineStr">
         <is>
-          <t>0.028M</t>
+          <t>-4.994M</t>
         </is>
       </c>
       <c r="D305" t="inlineStr">
         <is>
-          <t>-0.473M</t>
-        </is>
-      </c>
-      <c r="E305" t="inlineStr"/>
+          <t>-3.07M</t>
+        </is>
+      </c>
+      <c r="E305" t="inlineStr">
+        <is>
+          <t>-2.1M</t>
+        </is>
+      </c>
       <c r="F305" t="inlineStr"/>
       <c r="G305" t="n">
         <v>3</v>
@@ -9429,23 +9425,27 @@
       </c>
       <c r="B306" t="inlineStr">
         <is>
-          <t>EIA Refinery Crude Runs ChangeJAN/24</t>
+          <t>EIA Crude Oil Stocks ChangeJAN/24</t>
         </is>
       </c>
       <c r="C306" t="inlineStr">
         <is>
-          <t>-0.333M</t>
+          <t>3.463M</t>
         </is>
       </c>
       <c r="D306" t="inlineStr">
         <is>
-          <t>-1.125M</t>
-        </is>
-      </c>
-      <c r="E306" t="inlineStr"/>
+          <t>-1.017M</t>
+        </is>
+      </c>
+      <c r="E306" t="inlineStr">
+        <is>
+          <t>3.2M</t>
+        </is>
+      </c>
       <c r="F306" t="inlineStr"/>
       <c r="G306" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="307">
@@ -9537,7 +9537,7 @@
       </c>
       <c r="B310" t="inlineStr">
         <is>
-          <t>GDP Growth Rate QoQ AdvQ4</t>
+          <t>PCE Prices QoQ AdvQ4</t>
         </is>
       </c>
       <c r="C310" t="inlineStr">
@@ -9547,21 +9547,17 @@
       </c>
       <c r="D310" t="inlineStr">
         <is>
-          <t>3.1%</t>
-        </is>
-      </c>
-      <c r="E310" t="inlineStr">
-        <is>
-          <t>2.6%</t>
-        </is>
-      </c>
+          <t>1.5%</t>
+        </is>
+      </c>
+      <c r="E310" t="inlineStr"/>
       <c r="F310" t="inlineStr">
         <is>
-          <t>3%</t>
+          <t>1.1%</t>
         </is>
       </c>
       <c r="G310" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="311">
@@ -9572,31 +9568,27 @@
       </c>
       <c r="B311" t="inlineStr">
         <is>
-          <t>GDP Price Index QoQ AdvQ4</t>
+          <t>Real Consumer Spending QoQ AdvQ4</t>
         </is>
       </c>
       <c r="C311" t="inlineStr">
         <is>
-          <t>2.2%</t>
+          <t>4.2%</t>
         </is>
       </c>
       <c r="D311" t="inlineStr">
         <is>
-          <t>1.9%</t>
-        </is>
-      </c>
-      <c r="E311" t="inlineStr">
-        <is>
-          <t>2.5%</t>
-        </is>
-      </c>
+          <t>3.7%</t>
+        </is>
+      </c>
+      <c r="E311" t="inlineStr"/>
       <c r="F311" t="inlineStr">
         <is>
-          <t>2.3%</t>
+          <t>2.9%</t>
         </is>
       </c>
       <c r="G311" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="312">
@@ -9607,31 +9599,31 @@
       </c>
       <c r="B312" t="inlineStr">
         <is>
-          <t>Initial Jobless ClaimsJAN/25</t>
+          <t>Core PCE Prices QoQ AdvQ4</t>
         </is>
       </c>
       <c r="C312" t="inlineStr">
         <is>
-          <t>207K</t>
+          <t>2.5%</t>
         </is>
       </c>
       <c r="D312" t="inlineStr">
         <is>
-          <t>223K</t>
+          <t>2.2%</t>
         </is>
       </c>
       <c r="E312" t="inlineStr">
         <is>
-          <t>220K</t>
+          <t>2.5%</t>
         </is>
       </c>
       <c r="F312" t="inlineStr">
         <is>
-          <t>228.0K</t>
+          <t>2.3%</t>
         </is>
       </c>
       <c r="G312" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="313">
@@ -9642,23 +9634,23 @@
       </c>
       <c r="B313" t="inlineStr">
         <is>
-          <t>Jobless Claims 4-week AverageJAN/25</t>
+          <t>GDP Sales QoQ AdvQ4</t>
         </is>
       </c>
       <c r="C313" t="inlineStr">
         <is>
-          <t>212.5K</t>
+          <t>3.2%</t>
         </is>
       </c>
       <c r="D313" t="inlineStr">
         <is>
-          <t>213.5K</t>
+          <t>3.3%</t>
         </is>
       </c>
       <c r="E313" t="inlineStr"/>
       <c r="F313" t="inlineStr">
         <is>
-          <t>214.0K</t>
+          <t>2.9%</t>
         </is>
       </c>
       <c r="G313" t="n">
@@ -9673,31 +9665,31 @@
       </c>
       <c r="B314" t="inlineStr">
         <is>
-          <t>Continuing Jobless ClaimsJAN/18</t>
+          <t>Initial Jobless ClaimsJAN/25</t>
         </is>
       </c>
       <c r="C314" t="inlineStr">
         <is>
-          <t>1858K</t>
+          <t>207K</t>
         </is>
       </c>
       <c r="D314" t="inlineStr">
         <is>
-          <t>1900K</t>
+          <t>223K</t>
         </is>
       </c>
       <c r="E314" t="inlineStr">
         <is>
-          <t>1890K</t>
+          <t>220K</t>
         </is>
       </c>
       <c r="F314" t="inlineStr">
         <is>
-          <t>1885.0K</t>
+          <t>228.0K</t>
         </is>
       </c>
       <c r="G314" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="315">
@@ -9708,23 +9700,23 @@
       </c>
       <c r="B315" t="inlineStr">
         <is>
-          <t>GDP Sales QoQ AdvQ4</t>
+          <t>Jobless Claims 4-week AverageJAN/25</t>
         </is>
       </c>
       <c r="C315" t="inlineStr">
         <is>
-          <t>3.2%</t>
+          <t>212.5K</t>
         </is>
       </c>
       <c r="D315" t="inlineStr">
         <is>
-          <t>3.3%</t>
+          <t>213.5K</t>
         </is>
       </c>
       <c r="E315" t="inlineStr"/>
       <c r="F315" t="inlineStr">
         <is>
-          <t>2.9%</t>
+          <t>214.0K</t>
         </is>
       </c>
       <c r="G315" t="n">
@@ -9739,23 +9731,27 @@
       </c>
       <c r="B316" t="inlineStr">
         <is>
-          <t>PCE Prices QoQ AdvQ4</t>
+          <t>Continuing Jobless ClaimsJAN/18</t>
         </is>
       </c>
       <c r="C316" t="inlineStr">
         <is>
-          <t>2.3%</t>
+          <t>1858K</t>
         </is>
       </c>
       <c r="D316" t="inlineStr">
         <is>
-          <t>1.5%</t>
-        </is>
-      </c>
-      <c r="E316" t="inlineStr"/>
+          <t>1900K</t>
+        </is>
+      </c>
+      <c r="E316" t="inlineStr">
+        <is>
+          <t>1890K</t>
+        </is>
+      </c>
       <c r="F316" t="inlineStr">
         <is>
-          <t>1.1%</t>
+          <t>1885.0K</t>
         </is>
       </c>
       <c r="G316" t="n">
@@ -9770,31 +9766,31 @@
       </c>
       <c r="B317" t="inlineStr">
         <is>
-          <t>Core PCE Prices QoQ AdvQ4</t>
+          <t>GDP Price Index QoQ AdvQ4</t>
         </is>
       </c>
       <c r="C317" t="inlineStr">
         <is>
+          <t>2.2%</t>
+        </is>
+      </c>
+      <c r="D317" t="inlineStr">
+        <is>
+          <t>1.9%</t>
+        </is>
+      </c>
+      <c r="E317" t="inlineStr">
+        <is>
           <t>2.5%</t>
         </is>
       </c>
-      <c r="D317" t="inlineStr">
-        <is>
-          <t>2.2%</t>
-        </is>
-      </c>
-      <c r="E317" t="inlineStr">
-        <is>
-          <t>2.5%</t>
-        </is>
-      </c>
       <c r="F317" t="inlineStr">
         <is>
           <t>2.3%</t>
         </is>
       </c>
       <c r="G317" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="318">
@@ -9805,27 +9801,31 @@
       </c>
       <c r="B318" t="inlineStr">
         <is>
-          <t>Real Consumer Spending QoQ AdvQ4</t>
+          <t>GDP Growth Rate QoQ AdvQ4</t>
         </is>
       </c>
       <c r="C318" t="inlineStr">
         <is>
-          <t>4.2%</t>
+          <t>2.3%</t>
         </is>
       </c>
       <c r="D318" t="inlineStr">
         <is>
-          <t>3.7%</t>
-        </is>
-      </c>
-      <c r="E318" t="inlineStr"/>
+          <t>3.1%</t>
+        </is>
+      </c>
+      <c r="E318" t="inlineStr">
+        <is>
+          <t>2.6%</t>
+        </is>
+      </c>
       <c r="F318" t="inlineStr">
         <is>
-          <t>2.9%</t>
+          <t>3%</t>
         </is>
       </c>
       <c r="G318" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="319">
@@ -9933,17 +9933,17 @@
       </c>
       <c r="B322" t="inlineStr">
         <is>
-          <t>8-Week Bill Auction</t>
+          <t>4-Week Bill Auction</t>
         </is>
       </c>
       <c r="C322" t="inlineStr">
         <is>
-          <t>4.240%</t>
+          <t>4.250%</t>
         </is>
       </c>
       <c r="D322" t="inlineStr">
         <is>
-          <t>4.250%</t>
+          <t>4.265%</t>
         </is>
       </c>
       <c r="E322" t="inlineStr"/>
@@ -9960,17 +9960,17 @@
       </c>
       <c r="B323" t="inlineStr">
         <is>
-          <t>4-Week Bill Auction</t>
+          <t>8-Week Bill Auction</t>
         </is>
       </c>
       <c r="C323" t="inlineStr">
         <is>
+          <t>4.240%</t>
+        </is>
+      </c>
+      <c r="D323" t="inlineStr">
+        <is>
           <t>4.250%</t>
-        </is>
-      </c>
-      <c r="D323" t="inlineStr">
-        <is>
-          <t>4.265%</t>
         </is>
       </c>
       <c r="E323" t="inlineStr"/>
@@ -10068,25 +10068,13 @@
       </c>
       <c r="B327" t="inlineStr">
         <is>
-          <t>Employment Cost - Wages QoQQ4</t>
-        </is>
-      </c>
-      <c r="C327" t="inlineStr">
-        <is>
-          <t>0.9%</t>
-        </is>
-      </c>
-      <c r="D327" t="inlineStr">
-        <is>
-          <t>0.8%</t>
-        </is>
-      </c>
+          <t>Fed Bowman Speech</t>
+        </is>
+      </c>
+      <c r="C327" t="inlineStr"/>
+      <c r="D327" t="inlineStr"/>
       <c r="E327" t="inlineStr"/>
-      <c r="F327" t="inlineStr">
-        <is>
-          <t>0.7%</t>
-        </is>
-      </c>
+      <c r="F327" t="inlineStr"/>
       <c r="G327" t="n">
         <v>2</v>
       </c>
@@ -10099,12 +10087,12 @@
       </c>
       <c r="B328" t="inlineStr">
         <is>
-          <t>PCE Price Index MoMDEC</t>
+          <t>Core PCE Price Index MoMDEC</t>
         </is>
       </c>
       <c r="C328" t="inlineStr">
         <is>
-          <t>0.3%</t>
+          <t>0.2%</t>
         </is>
       </c>
       <c r="D328" t="inlineStr">
@@ -10114,16 +10102,16 @@
       </c>
       <c r="E328" t="inlineStr">
         <is>
-          <t>0.3%</t>
+          <t>0.2%</t>
         </is>
       </c>
       <c r="F328" t="inlineStr">
         <is>
-          <t>0.3%</t>
+          <t>0.2%</t>
         </is>
       </c>
       <c r="G328" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="329">
@@ -10134,31 +10122,31 @@
       </c>
       <c r="B329" t="inlineStr">
         <is>
-          <t>PCE Price Index YoYDEC</t>
+          <t>Personal Spending MoMDEC</t>
         </is>
       </c>
       <c r="C329" t="inlineStr">
         <is>
-          <t>2.6%</t>
+          <t>0.7%</t>
         </is>
       </c>
       <c r="D329" t="inlineStr">
         <is>
-          <t>2.4%</t>
+          <t>0.6%</t>
         </is>
       </c>
       <c r="E329" t="inlineStr">
         <is>
-          <t>2.6%</t>
+          <t>0.5%</t>
         </is>
       </c>
       <c r="F329" t="inlineStr">
         <is>
-          <t>2.6%</t>
+          <t>0.5%</t>
         </is>
       </c>
       <c r="G329" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="330">
@@ -10169,31 +10157,27 @@
       </c>
       <c r="B330" t="inlineStr">
         <is>
-          <t>Core PCE Price Index YoYDEC</t>
+          <t>Employment Cost - Benefits QoQQ4</t>
         </is>
       </c>
       <c r="C330" t="inlineStr">
         <is>
-          <t>2.8%</t>
+          <t>0.8%</t>
         </is>
       </c>
       <c r="D330" t="inlineStr">
         <is>
-          <t>2.8%</t>
-        </is>
-      </c>
-      <c r="E330" t="inlineStr">
-        <is>
-          <t>2.8%</t>
-        </is>
-      </c>
+          <t>0.8%</t>
+        </is>
+      </c>
+      <c r="E330" t="inlineStr"/>
       <c r="F330" t="inlineStr">
         <is>
-          <t>2.8%</t>
+          <t>0.7%</t>
         </is>
       </c>
       <c r="G330" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="331">
@@ -10204,31 +10188,31 @@
       </c>
       <c r="B331" t="inlineStr">
         <is>
-          <t>Employment Cost Index QoQQ4</t>
+          <t>Personal Income MoMDEC</t>
         </is>
       </c>
       <c r="C331" t="inlineStr">
         <is>
-          <t>0.9%</t>
+          <t>0.4%</t>
         </is>
       </c>
       <c r="D331" t="inlineStr">
         <is>
-          <t>0.8%</t>
+          <t>0.3%</t>
         </is>
       </c>
       <c r="E331" t="inlineStr">
         <is>
-          <t>0.9%</t>
+          <t>0.4%</t>
         </is>
       </c>
       <c r="F331" t="inlineStr">
         <is>
-          <t>0.7%</t>
+          <t>0.3%</t>
         </is>
       </c>
       <c r="G331" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="332">
@@ -10239,31 +10223,27 @@
       </c>
       <c r="B332" t="inlineStr">
         <is>
-          <t>Personal Income MoMDEC</t>
+          <t>Employment Cost - Wages QoQQ4</t>
         </is>
       </c>
       <c r="C332" t="inlineStr">
         <is>
-          <t>0.4%</t>
+          <t>0.9%</t>
         </is>
       </c>
       <c r="D332" t="inlineStr">
         <is>
-          <t>0.3%</t>
-        </is>
-      </c>
-      <c r="E332" t="inlineStr">
-        <is>
-          <t>0.4%</t>
-        </is>
-      </c>
+          <t>0.8%</t>
+        </is>
+      </c>
+      <c r="E332" t="inlineStr"/>
       <c r="F332" t="inlineStr">
         <is>
-          <t>0.3%</t>
+          <t>0.7%</t>
         </is>
       </c>
       <c r="G332" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="333">
@@ -10274,15 +10254,31 @@
       </c>
       <c r="B333" t="inlineStr">
         <is>
-          <t>Fed Bowman Speech</t>
-        </is>
-      </c>
-      <c r="C333" t="inlineStr"/>
-      <c r="D333" t="inlineStr"/>
-      <c r="E333" t="inlineStr"/>
-      <c r="F333" t="inlineStr"/>
+          <t>Core PCE Price Index YoYDEC</t>
+        </is>
+      </c>
+      <c r="C333" t="inlineStr">
+        <is>
+          <t>2.8%</t>
+        </is>
+      </c>
+      <c r="D333" t="inlineStr">
+        <is>
+          <t>2.8%</t>
+        </is>
+      </c>
+      <c r="E333" t="inlineStr">
+        <is>
+          <t>2.8%</t>
+        </is>
+      </c>
+      <c r="F333" t="inlineStr">
+        <is>
+          <t>2.8%</t>
+        </is>
+      </c>
       <c r="G333" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="334">
@@ -10293,23 +10289,27 @@
       </c>
       <c r="B334" t="inlineStr">
         <is>
-          <t>Employment Cost - Benefits QoQQ4</t>
+          <t>PCE Price Index YoYDEC</t>
         </is>
       </c>
       <c r="C334" t="inlineStr">
         <is>
-          <t>0.8%</t>
+          <t>2.6%</t>
         </is>
       </c>
       <c r="D334" t="inlineStr">
         <is>
-          <t>0.8%</t>
-        </is>
-      </c>
-      <c r="E334" t="inlineStr"/>
+          <t>2.4%</t>
+        </is>
+      </c>
+      <c r="E334" t="inlineStr">
+        <is>
+          <t>2.6%</t>
+        </is>
+      </c>
       <c r="F334" t="inlineStr">
         <is>
-          <t>0.7%</t>
+          <t>2.6%</t>
         </is>
       </c>
       <c r="G334" t="n">
@@ -10324,31 +10324,31 @@
       </c>
       <c r="B335" t="inlineStr">
         <is>
-          <t>Personal Spending MoMDEC</t>
+          <t>PCE Price Index MoMDEC</t>
         </is>
       </c>
       <c r="C335" t="inlineStr">
         <is>
-          <t>0.7%</t>
+          <t>0.3%</t>
         </is>
       </c>
       <c r="D335" t="inlineStr">
         <is>
-          <t>0.6%</t>
+          <t>0.1%</t>
         </is>
       </c>
       <c r="E335" t="inlineStr">
         <is>
-          <t>0.5%</t>
+          <t>0.3%</t>
         </is>
       </c>
       <c r="F335" t="inlineStr">
         <is>
-          <t>0.5%</t>
+          <t>0.3%</t>
         </is>
       </c>
       <c r="G335" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="336">
@@ -10359,31 +10359,31 @@
       </c>
       <c r="B336" t="inlineStr">
         <is>
-          <t>Core PCE Price Index MoMDEC</t>
+          <t>Employment Cost Index QoQQ4</t>
         </is>
       </c>
       <c r="C336" t="inlineStr">
         <is>
-          <t>0.2%</t>
+          <t>0.9%</t>
         </is>
       </c>
       <c r="D336" t="inlineStr">
         <is>
-          <t>0.1%</t>
+          <t>0.8%</t>
         </is>
       </c>
       <c r="E336" t="inlineStr">
         <is>
-          <t>0.2%</t>
+          <t>0.9%</t>
         </is>
       </c>
       <c r="F336" t="inlineStr">
         <is>
-          <t>0.2%</t>
+          <t>0.7%</t>
         </is>
       </c>
       <c r="G336" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="337">
@@ -11155,17 +11155,17 @@
       </c>
       <c r="B364" t="inlineStr">
         <is>
-          <t>MBA Mortgage Refinance IndexJAN/31</t>
+          <t>MBA Mortgage ApplicationsJAN/31</t>
         </is>
       </c>
       <c r="C364" t="inlineStr">
         <is>
-          <t>584.3</t>
+          <t>2.2%</t>
         </is>
       </c>
       <c r="D364" t="inlineStr">
         <is>
-          <t>520.9</t>
+          <t>-2%</t>
         </is>
       </c>
       <c r="E364" t="inlineStr"/>
@@ -11182,23 +11182,23 @@
       </c>
       <c r="B365" t="inlineStr">
         <is>
-          <t>MBA 30-Year Mortgage RateJAN/31</t>
+          <t>MBA Purchase IndexJAN/31</t>
         </is>
       </c>
       <c r="C365" t="inlineStr">
         <is>
-          <t>6.97%</t>
+          <t>156.7</t>
         </is>
       </c>
       <c r="D365" t="inlineStr">
         <is>
-          <t>7.02%</t>
+          <t>162.4</t>
         </is>
       </c>
       <c r="E365" t="inlineStr"/>
       <c r="F365" t="inlineStr"/>
       <c r="G365" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="366">
@@ -11209,17 +11209,17 @@
       </c>
       <c r="B366" t="inlineStr">
         <is>
-          <t>MBA Purchase IndexJAN/31</t>
+          <t>MBA Mortgage Market IndexJAN/31</t>
         </is>
       </c>
       <c r="C366" t="inlineStr">
         <is>
-          <t>156.7</t>
+          <t>224.8</t>
         </is>
       </c>
       <c r="D366" t="inlineStr">
         <is>
-          <t>162.4</t>
+          <t>220.0</t>
         </is>
       </c>
       <c r="E366" t="inlineStr"/>
@@ -11236,17 +11236,17 @@
       </c>
       <c r="B367" t="inlineStr">
         <is>
-          <t>MBA Mortgage ApplicationsJAN/31</t>
+          <t>MBA Mortgage Refinance IndexJAN/31</t>
         </is>
       </c>
       <c r="C367" t="inlineStr">
         <is>
-          <t>2.2%</t>
+          <t>584.3</t>
         </is>
       </c>
       <c r="D367" t="inlineStr">
         <is>
-          <t>-2%</t>
+          <t>520.9</t>
         </is>
       </c>
       <c r="E367" t="inlineStr"/>
@@ -11263,23 +11263,23 @@
       </c>
       <c r="B368" t="inlineStr">
         <is>
-          <t>MBA Mortgage Market IndexJAN/31</t>
+          <t>MBA 30-Year Mortgage RateJAN/31</t>
         </is>
       </c>
       <c r="C368" t="inlineStr">
         <is>
-          <t>224.8</t>
+          <t>6.97%</t>
         </is>
       </c>
       <c r="D368" t="inlineStr">
         <is>
-          <t>220.0</t>
+          <t>7.02%</t>
         </is>
       </c>
       <c r="E368" t="inlineStr"/>
       <c r="F368" t="inlineStr"/>
       <c r="G368" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="369">
@@ -11530,23 +11530,23 @@
       </c>
       <c r="B377" t="inlineStr">
         <is>
-          <t>ISM Services EmploymentJAN</t>
+          <t>ISM Services PricesJAN</t>
         </is>
       </c>
       <c r="C377" t="inlineStr">
         <is>
-          <t>52.3</t>
+          <t>60.4</t>
         </is>
       </c>
       <c r="D377" t="inlineStr">
         <is>
-          <t>51.3</t>
+          <t>64.4</t>
         </is>
       </c>
       <c r="E377" t="inlineStr"/>
       <c r="F377" t="inlineStr">
         <is>
-          <t>51.3</t>
+          <t>64.8</t>
         </is>
       </c>
       <c r="G377" t="n">
@@ -11561,23 +11561,23 @@
       </c>
       <c r="B378" t="inlineStr">
         <is>
-          <t>ISM Services New OrdersJAN</t>
+          <t>ISM Services Business ActivityJAN</t>
         </is>
       </c>
       <c r="C378" t="inlineStr">
         <is>
-          <t>51.3</t>
+          <t>54.5</t>
         </is>
       </c>
       <c r="D378" t="inlineStr">
         <is>
-          <t>54.4</t>
+          <t>58.0</t>
         </is>
       </c>
       <c r="E378" t="inlineStr"/>
       <c r="F378" t="inlineStr">
         <is>
-          <t>54.1</t>
+          <t>58.1</t>
         </is>
       </c>
       <c r="G378" t="n">
@@ -11592,27 +11592,31 @@
       </c>
       <c r="B379" t="inlineStr">
         <is>
-          <t>ISM Services Business ActivityJAN</t>
+          <t>ISM Services PMIJAN</t>
         </is>
       </c>
       <c r="C379" t="inlineStr">
         <is>
-          <t>54.5</t>
+          <t>52.8</t>
         </is>
       </c>
       <c r="D379" t="inlineStr">
         <is>
-          <t>58.0</t>
-        </is>
-      </c>
-      <c r="E379" t="inlineStr"/>
+          <t>54.0</t>
+        </is>
+      </c>
+      <c r="E379" t="inlineStr">
+        <is>
+          <t>54.3</t>
+        </is>
+      </c>
       <c r="F379" t="inlineStr">
         <is>
-          <t>58.1</t>
+          <t>54</t>
         </is>
       </c>
       <c r="G379" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="380">
@@ -11623,23 +11627,23 @@
       </c>
       <c r="B380" t="inlineStr">
         <is>
-          <t>ISM Services PricesJAN</t>
+          <t>ISM Services EmploymentJAN</t>
         </is>
       </c>
       <c r="C380" t="inlineStr">
         <is>
-          <t>60.4</t>
+          <t>52.3</t>
         </is>
       </c>
       <c r="D380" t="inlineStr">
         <is>
-          <t>64.4</t>
+          <t>51.3</t>
         </is>
       </c>
       <c r="E380" t="inlineStr"/>
       <c r="F380" t="inlineStr">
         <is>
-          <t>64.8</t>
+          <t>51.3</t>
         </is>
       </c>
       <c r="G380" t="n">
@@ -11654,31 +11658,27 @@
       </c>
       <c r="B381" t="inlineStr">
         <is>
-          <t>ISM Services PMIJAN</t>
+          <t>ISM Services New OrdersJAN</t>
         </is>
       </c>
       <c r="C381" t="inlineStr">
         <is>
-          <t>52.8</t>
+          <t>51.3</t>
         </is>
       </c>
       <c r="D381" t="inlineStr">
         <is>
-          <t>54.0</t>
-        </is>
-      </c>
-      <c r="E381" t="inlineStr">
-        <is>
-          <t>54.3</t>
-        </is>
-      </c>
+          <t>54.4</t>
+        </is>
+      </c>
+      <c r="E381" t="inlineStr"/>
       <c r="F381" t="inlineStr">
         <is>
-          <t>54</t>
+          <t>54.1</t>
         </is>
       </c>
       <c r="G381" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="382">
@@ -11689,27 +11689,23 @@
       </c>
       <c r="B382" t="inlineStr">
         <is>
-          <t>EIA Crude Oil Stocks ChangeJAN/31</t>
+          <t>EIA Distillate Fuel Production ChangeJAN/31</t>
         </is>
       </c>
       <c r="C382" t="inlineStr">
         <is>
-          <t>8.664M</t>
+          <t>-0.186M</t>
         </is>
       </c>
       <c r="D382" t="inlineStr">
         <is>
-          <t>3.463M</t>
-        </is>
-      </c>
-      <c r="E382" t="inlineStr">
-        <is>
-          <t>2.6M</t>
-        </is>
-      </c>
+          <t>0.028M</t>
+        </is>
+      </c>
+      <c r="E382" t="inlineStr"/>
       <c r="F382" t="inlineStr"/>
       <c r="G382" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="383">
@@ -11720,23 +11716,27 @@
       </c>
       <c r="B383" t="inlineStr">
         <is>
-          <t>EIA Crude Oil Imports ChangeJAN/31</t>
+          <t>EIA Gasoline Stocks ChangeJAN/31</t>
         </is>
       </c>
       <c r="C383" t="inlineStr">
         <is>
-          <t>-0.178M</t>
+          <t>2.233M</t>
         </is>
       </c>
       <c r="D383" t="inlineStr">
         <is>
-          <t>0.532M</t>
-        </is>
-      </c>
-      <c r="E383" t="inlineStr"/>
+          <t>2.957M</t>
+        </is>
+      </c>
+      <c r="E383" t="inlineStr">
+        <is>
+          <t>1.2M</t>
+        </is>
+      </c>
       <c r="F383" t="inlineStr"/>
       <c r="G383" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="384">
@@ -11747,20 +11747,24 @@
       </c>
       <c r="B384" t="inlineStr">
         <is>
-          <t>EIA Heating Oil Stocks ChangeJAN/31</t>
+          <t>EIA Distillate Stocks ChangeJAN/31</t>
         </is>
       </c>
       <c r="C384" t="inlineStr">
         <is>
-          <t>0.373M</t>
+          <t>-5.471M</t>
         </is>
       </c>
       <c r="D384" t="inlineStr">
         <is>
-          <t>0.128M</t>
-        </is>
-      </c>
-      <c r="E384" t="inlineStr"/>
+          <t>-4.994M</t>
+        </is>
+      </c>
+      <c r="E384" t="inlineStr">
+        <is>
+          <t>-1.5M</t>
+        </is>
+      </c>
       <c r="F384" t="inlineStr"/>
       <c r="G384" t="n">
         <v>3</v>
@@ -11774,17 +11778,17 @@
       </c>
       <c r="B385" t="inlineStr">
         <is>
-          <t>EIA Gasoline Production ChangeJAN/31</t>
+          <t>EIA Cushing Crude Oil Stocks ChangeJAN/31</t>
         </is>
       </c>
       <c r="C385" t="inlineStr">
         <is>
-          <t>-0.027M</t>
+          <t>-0.034M</t>
         </is>
       </c>
       <c r="D385" t="inlineStr">
         <is>
-          <t>-0.044M</t>
+          <t>0.326M</t>
         </is>
       </c>
       <c r="E385" t="inlineStr"/>
@@ -11801,17 +11805,17 @@
       </c>
       <c r="B386" t="inlineStr">
         <is>
-          <t>EIA Cushing Crude Oil Stocks ChangeJAN/31</t>
+          <t>EIA Refinery Crude Runs ChangeJAN/31</t>
         </is>
       </c>
       <c r="C386" t="inlineStr">
         <is>
-          <t>-0.034M</t>
+          <t>0.16M</t>
         </is>
       </c>
       <c r="D386" t="inlineStr">
         <is>
-          <t>0.326M</t>
+          <t>-0.333M</t>
         </is>
       </c>
       <c r="E386" t="inlineStr"/>
@@ -11828,24 +11832,20 @@
       </c>
       <c r="B387" t="inlineStr">
         <is>
-          <t>EIA Distillate Stocks ChangeJAN/31</t>
+          <t>EIA Heating Oil Stocks ChangeJAN/31</t>
         </is>
       </c>
       <c r="C387" t="inlineStr">
         <is>
-          <t>-5.471M</t>
+          <t>0.373M</t>
         </is>
       </c>
       <c r="D387" t="inlineStr">
         <is>
-          <t>-4.994M</t>
-        </is>
-      </c>
-      <c r="E387" t="inlineStr">
-        <is>
-          <t>-1.5M</t>
-        </is>
-      </c>
+          <t>0.128M</t>
+        </is>
+      </c>
+      <c r="E387" t="inlineStr"/>
       <c r="F387" t="inlineStr"/>
       <c r="G387" t="n">
         <v>3</v>
@@ -11859,17 +11859,17 @@
       </c>
       <c r="B388" t="inlineStr">
         <is>
-          <t>EIA Refinery Crude Runs ChangeJAN/31</t>
+          <t>EIA Crude Oil Imports ChangeJAN/31</t>
         </is>
       </c>
       <c r="C388" t="inlineStr">
         <is>
-          <t>0.16M</t>
+          <t>-0.178M</t>
         </is>
       </c>
       <c r="D388" t="inlineStr">
         <is>
-          <t>-0.333M</t>
+          <t>0.532M</t>
         </is>
       </c>
       <c r="E388" t="inlineStr"/>
@@ -11886,22 +11886,22 @@
       </c>
       <c r="B389" t="inlineStr">
         <is>
-          <t>EIA Gasoline Stocks ChangeJAN/31</t>
+          <t>EIA Crude Oil Stocks ChangeJAN/31</t>
         </is>
       </c>
       <c r="C389" t="inlineStr">
         <is>
-          <t>2.233M</t>
+          <t>8.664M</t>
         </is>
       </c>
       <c r="D389" t="inlineStr">
         <is>
-          <t>2.957M</t>
+          <t>3.463M</t>
         </is>
       </c>
       <c r="E389" t="inlineStr">
         <is>
-          <t>1.2M</t>
+          <t>2.6M</t>
         </is>
       </c>
       <c r="F389" t="inlineStr"/>
@@ -11917,17 +11917,17 @@
       </c>
       <c r="B390" t="inlineStr">
         <is>
-          <t>EIA Distillate Fuel Production ChangeJAN/31</t>
+          <t>EIA Gasoline Production ChangeJAN/31</t>
         </is>
       </c>
       <c r="C390" t="inlineStr">
         <is>
-          <t>-0.186M</t>
+          <t>-0.027M</t>
         </is>
       </c>
       <c r="D390" t="inlineStr">
         <is>
-          <t>0.028M</t>
+          <t>-0.044M</t>
         </is>
       </c>
       <c r="E390" t="inlineStr"/>
@@ -12040,27 +12040,23 @@
       </c>
       <c r="B395" t="inlineStr">
         <is>
-          <t>Continuing Jobless ClaimsJAN/25</t>
+          <t>Jobless Claims 4-week AverageFEB/01</t>
         </is>
       </c>
       <c r="C395" t="inlineStr">
         <is>
-          <t>1886K</t>
+          <t>216.75K</t>
         </is>
       </c>
       <c r="D395" t="inlineStr">
         <is>
-          <t>1850K</t>
-        </is>
-      </c>
-      <c r="E395" t="inlineStr">
-        <is>
-          <t>1870K</t>
-        </is>
-      </c>
+          <t>212.75K</t>
+        </is>
+      </c>
+      <c r="E395" t="inlineStr"/>
       <c r="F395" t="inlineStr">
         <is>
-          <t>1855.0K</t>
+          <t>215.5K</t>
         </is>
       </c>
       <c r="G395" t="n">
@@ -12075,27 +12071,27 @@
       </c>
       <c r="B396" t="inlineStr">
         <is>
-          <t>Initial Jobless ClaimsFEB/01</t>
+          <t>Unit Labour Costs QoQ PrelQ4</t>
         </is>
       </c>
       <c r="C396" t="inlineStr">
         <is>
-          <t>219K</t>
+          <t>3%</t>
         </is>
       </c>
       <c r="D396" t="inlineStr">
         <is>
-          <t>208K</t>
+          <t>0.5%</t>
         </is>
       </c>
       <c r="E396" t="inlineStr">
         <is>
-          <t>213K</t>
+          <t>3.4%</t>
         </is>
       </c>
       <c r="F396" t="inlineStr">
         <is>
-          <t>215.0K</t>
+          <t>3%</t>
         </is>
       </c>
       <c r="G396" t="n">
@@ -12145,27 +12141,27 @@
       </c>
       <c r="B398" t="inlineStr">
         <is>
-          <t>Unit Labour Costs QoQ PrelQ4</t>
+          <t>Initial Jobless ClaimsFEB/01</t>
         </is>
       </c>
       <c r="C398" t="inlineStr">
         <is>
-          <t>3%</t>
+          <t>219K</t>
         </is>
       </c>
       <c r="D398" t="inlineStr">
         <is>
-          <t>0.5%</t>
+          <t>208K</t>
         </is>
       </c>
       <c r="E398" t="inlineStr">
         <is>
-          <t>3.4%</t>
+          <t>213K</t>
         </is>
       </c>
       <c r="F398" t="inlineStr">
         <is>
-          <t>3%</t>
+          <t>215.0K</t>
         </is>
       </c>
       <c r="G398" t="n">
@@ -12180,23 +12176,27 @@
       </c>
       <c r="B399" t="inlineStr">
         <is>
-          <t>Jobless Claims 4-week AverageFEB/01</t>
+          <t>Continuing Jobless ClaimsJAN/25</t>
         </is>
       </c>
       <c r="C399" t="inlineStr">
         <is>
-          <t>216.75K</t>
+          <t>1886K</t>
         </is>
       </c>
       <c r="D399" t="inlineStr">
         <is>
-          <t>212.75K</t>
-        </is>
-      </c>
-      <c r="E399" t="inlineStr"/>
+          <t>1850K</t>
+        </is>
+      </c>
+      <c r="E399" t="inlineStr">
+        <is>
+          <t>1870K</t>
+        </is>
+      </c>
       <c r="F399" t="inlineStr">
         <is>
-          <t>215.5K</t>
+          <t>1855.0K</t>
         </is>
       </c>
       <c r="G399" t="n">
@@ -12442,27 +12442,31 @@
       </c>
       <c r="B409" t="inlineStr">
         <is>
-          <t>U-6 Unemployment RateJAN</t>
+          <t>Non Farm PayrollsJAN</t>
         </is>
       </c>
       <c r="C409" t="inlineStr">
         <is>
-          <t>7.5%</t>
+          <t>143K</t>
         </is>
       </c>
       <c r="D409" t="inlineStr">
         <is>
-          <t>7.5%</t>
-        </is>
-      </c>
-      <c r="E409" t="inlineStr"/>
+          <t>307K</t>
+        </is>
+      </c>
+      <c r="E409" t="inlineStr">
+        <is>
+          <t>170K</t>
+        </is>
+      </c>
       <c r="F409" t="inlineStr">
         <is>
-          <t>7.5%</t>
+          <t>205K</t>
         </is>
       </c>
       <c r="G409" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="410">
@@ -12473,27 +12477,31 @@
       </c>
       <c r="B410" t="inlineStr">
         <is>
-          <t>Participation RateJAN</t>
+          <t>Average Weekly HoursJAN</t>
         </is>
       </c>
       <c r="C410" t="inlineStr">
         <is>
-          <t>62.6%</t>
+          <t>34.1</t>
         </is>
       </c>
       <c r="D410" t="inlineStr">
         <is>
-          <t>62.5%</t>
-        </is>
-      </c>
-      <c r="E410" t="inlineStr"/>
+          <t>34.2</t>
+        </is>
+      </c>
+      <c r="E410" t="inlineStr">
+        <is>
+          <t>34.3</t>
+        </is>
+      </c>
       <c r="F410" t="inlineStr">
         <is>
-          <t>62.5%</t>
+          <t>34.3</t>
         </is>
       </c>
       <c r="G410" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="411">
@@ -12504,31 +12512,31 @@
       </c>
       <c r="B411" t="inlineStr">
         <is>
-          <t>Nonfarm Payrolls PrivateJAN</t>
+          <t>Unemployment RateJAN</t>
         </is>
       </c>
       <c r="C411" t="inlineStr">
         <is>
-          <t>111K</t>
+          <t>4%</t>
         </is>
       </c>
       <c r="D411" t="inlineStr">
         <is>
-          <t>273K</t>
+          <t>4.1%</t>
         </is>
       </c>
       <c r="E411" t="inlineStr">
         <is>
-          <t>141K</t>
+          <t>4.1%</t>
         </is>
       </c>
       <c r="F411" t="inlineStr">
         <is>
-          <t>180K</t>
+          <t>4.1%</t>
         </is>
       </c>
       <c r="G411" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="412">
@@ -12539,31 +12547,31 @@
       </c>
       <c r="B412" t="inlineStr">
         <is>
-          <t>Manufacturing PayrollsJAN</t>
+          <t>Average Hourly Earnings MoMJAN</t>
         </is>
       </c>
       <c r="C412" t="inlineStr">
         <is>
-          <t>3K</t>
+          <t>0.5%</t>
         </is>
       </c>
       <c r="D412" t="inlineStr">
         <is>
-          <t>-12K</t>
+          <t>0.3%</t>
         </is>
       </c>
       <c r="E412" t="inlineStr">
         <is>
-          <t>-2K</t>
+          <t>0.3%</t>
         </is>
       </c>
       <c r="F412" t="inlineStr">
         <is>
-          <t>-5K</t>
+          <t>0.3%</t>
         </is>
       </c>
       <c r="G412" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="413">
@@ -12574,27 +12582,31 @@
       </c>
       <c r="B413" t="inlineStr">
         <is>
-          <t>Government PayrollsJAN</t>
+          <t>Average Hourly Earnings YoYJAN</t>
         </is>
       </c>
       <c r="C413" t="inlineStr">
         <is>
-          <t>32K</t>
+          <t>4.1%</t>
         </is>
       </c>
       <c r="D413" t="inlineStr">
         <is>
-          <t>34K</t>
-        </is>
-      </c>
-      <c r="E413" t="inlineStr"/>
+          <t>4.1%</t>
+        </is>
+      </c>
+      <c r="E413" t="inlineStr">
+        <is>
+          <t>3.8%</t>
+        </is>
+      </c>
       <c r="F413" t="inlineStr">
         <is>
-          <t>25K</t>
+          <t>3.9%</t>
         </is>
       </c>
       <c r="G413" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="414">
@@ -12605,31 +12617,31 @@
       </c>
       <c r="B414" t="inlineStr">
         <is>
-          <t>Average Hourly Earnings YoYJAN</t>
+          <t>Nonfarm Payrolls PrivateJAN</t>
         </is>
       </c>
       <c r="C414" t="inlineStr">
         <is>
-          <t>4.1%</t>
+          <t>111K</t>
         </is>
       </c>
       <c r="D414" t="inlineStr">
         <is>
-          <t>4.1%</t>
+          <t>273K</t>
         </is>
       </c>
       <c r="E414" t="inlineStr">
         <is>
-          <t>3.8%</t>
+          <t>141K</t>
         </is>
       </c>
       <c r="F414" t="inlineStr">
         <is>
-          <t>3.9%</t>
+          <t>180K</t>
         </is>
       </c>
       <c r="G414" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="415">
@@ -12640,31 +12652,31 @@
       </c>
       <c r="B415" t="inlineStr">
         <is>
-          <t>Average Hourly Earnings MoMJAN</t>
+          <t>Manufacturing PayrollsJAN</t>
         </is>
       </c>
       <c r="C415" t="inlineStr">
         <is>
-          <t>0.5%</t>
+          <t>3K</t>
         </is>
       </c>
       <c r="D415" t="inlineStr">
         <is>
-          <t>0.3%</t>
+          <t>-12K</t>
         </is>
       </c>
       <c r="E415" t="inlineStr">
         <is>
-          <t>0.3%</t>
+          <t>-2K</t>
         </is>
       </c>
       <c r="F415" t="inlineStr">
         <is>
-          <t>0.3%</t>
+          <t>-5K</t>
         </is>
       </c>
       <c r="G415" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="416">
@@ -12675,31 +12687,27 @@
       </c>
       <c r="B416" t="inlineStr">
         <is>
-          <t>Unemployment RateJAN</t>
+          <t>Participation RateJAN</t>
         </is>
       </c>
       <c r="C416" t="inlineStr">
         <is>
-          <t>4%</t>
+          <t>62.6%</t>
         </is>
       </c>
       <c r="D416" t="inlineStr">
         <is>
-          <t>4.1%</t>
-        </is>
-      </c>
-      <c r="E416" t="inlineStr">
-        <is>
-          <t>4.1%</t>
-        </is>
-      </c>
+          <t>62.5%</t>
+        </is>
+      </c>
+      <c r="E416" t="inlineStr"/>
       <c r="F416" t="inlineStr">
         <is>
-          <t>4.1%</t>
+          <t>62.5%</t>
         </is>
       </c>
       <c r="G416" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="417">
@@ -12710,27 +12718,23 @@
       </c>
       <c r="B417" t="inlineStr">
         <is>
-          <t>Average Weekly HoursJAN</t>
+          <t>U-6 Unemployment RateJAN</t>
         </is>
       </c>
       <c r="C417" t="inlineStr">
         <is>
-          <t>34.1</t>
+          <t>7.5%</t>
         </is>
       </c>
       <c r="D417" t="inlineStr">
         <is>
-          <t>34.2</t>
-        </is>
-      </c>
-      <c r="E417" t="inlineStr">
-        <is>
-          <t>34.3</t>
-        </is>
-      </c>
+          <t>7.5%</t>
+        </is>
+      </c>
+      <c r="E417" t="inlineStr"/>
       <c r="F417" t="inlineStr">
         <is>
-          <t>34.3</t>
+          <t>7.5%</t>
         </is>
       </c>
       <c r="G417" t="n">
@@ -12745,31 +12749,27 @@
       </c>
       <c r="B418" t="inlineStr">
         <is>
-          <t>Non Farm PayrollsJAN</t>
+          <t>Government PayrollsJAN</t>
         </is>
       </c>
       <c r="C418" t="inlineStr">
         <is>
-          <t>143K</t>
+          <t>32K</t>
         </is>
       </c>
       <c r="D418" t="inlineStr">
         <is>
-          <t>307K</t>
-        </is>
-      </c>
-      <c r="E418" t="inlineStr">
-        <is>
-          <t>170K</t>
-        </is>
-      </c>
+          <t>34K</t>
+        </is>
+      </c>
+      <c r="E418" t="inlineStr"/>
       <c r="F418" t="inlineStr">
         <is>
-          <t>205K</t>
+          <t>25K</t>
         </is>
       </c>
       <c r="G418" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="419">
@@ -12872,31 +12872,31 @@
       </c>
       <c r="B423" t="inlineStr">
         <is>
-          <t>Wholesale Inventories MoMDEC</t>
+          <t>Michigan Consumer Sentiment PrelFEB</t>
         </is>
       </c>
       <c r="C423" t="inlineStr">
         <is>
-          <t>-0.5%</t>
+          <t>67.8</t>
         </is>
       </c>
       <c r="D423" t="inlineStr">
         <is>
-          <t>-0.1%</t>
+          <t>71.1</t>
         </is>
       </c>
       <c r="E423" t="inlineStr">
         <is>
-          <t>-0.5%</t>
+          <t>71.1</t>
         </is>
       </c>
       <c r="F423" t="inlineStr">
         <is>
-          <t>-0.5%</t>
+          <t>72</t>
         </is>
       </c>
       <c r="G423" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="424">
@@ -12907,27 +12907,23 @@
       </c>
       <c r="B424" t="inlineStr">
         <is>
-          <t>Michigan Current Conditions PrelFEB</t>
+          <t>Michigan 5 Year Inflation Expectations PrelFEB</t>
         </is>
       </c>
       <c r="C424" t="inlineStr">
         <is>
-          <t>68.7</t>
+          <t>3.3%</t>
         </is>
       </c>
       <c r="D424" t="inlineStr">
         <is>
-          <t>74</t>
-        </is>
-      </c>
-      <c r="E424" t="inlineStr">
-        <is>
-          <t>73</t>
-        </is>
-      </c>
+          <t>3.2%</t>
+        </is>
+      </c>
+      <c r="E424" t="inlineStr"/>
       <c r="F424" t="inlineStr">
         <is>
-          <t>74.3</t>
+          <t>3.3%</t>
         </is>
       </c>
       <c r="G424" t="n">
@@ -12942,23 +12938,27 @@
       </c>
       <c r="B425" t="inlineStr">
         <is>
-          <t>Michigan Inflation Expectations PrelFEB</t>
+          <t>Michigan Consumer Expectations PrelFEB</t>
         </is>
       </c>
       <c r="C425" t="inlineStr">
         <is>
-          <t>4.3%</t>
+          <t>67.3</t>
         </is>
       </c>
       <c r="D425" t="inlineStr">
         <is>
-          <t>3.3%</t>
-        </is>
-      </c>
-      <c r="E425" t="inlineStr"/>
+          <t>69.3</t>
+        </is>
+      </c>
+      <c r="E425" t="inlineStr">
+        <is>
+          <t>70</t>
+        </is>
+      </c>
       <c r="F425" t="inlineStr">
         <is>
-          <t>3.4%</t>
+          <t>69.5</t>
         </is>
       </c>
       <c r="G425" t="n">
@@ -12973,27 +12973,23 @@
       </c>
       <c r="B426" t="inlineStr">
         <is>
-          <t>Michigan Consumer Expectations PrelFEB</t>
+          <t>Michigan Inflation Expectations PrelFEB</t>
         </is>
       </c>
       <c r="C426" t="inlineStr">
         <is>
-          <t>67.3</t>
+          <t>4.3%</t>
         </is>
       </c>
       <c r="D426" t="inlineStr">
         <is>
-          <t>69.3</t>
-        </is>
-      </c>
-      <c r="E426" t="inlineStr">
-        <is>
-          <t>70</t>
-        </is>
-      </c>
+          <t>3.3%</t>
+        </is>
+      </c>
+      <c r="E426" t="inlineStr"/>
       <c r="F426" t="inlineStr">
         <is>
-          <t>69.5</t>
+          <t>3.4%</t>
         </is>
       </c>
       <c r="G426" t="n">
@@ -13008,31 +13004,31 @@
       </c>
       <c r="B427" t="inlineStr">
         <is>
-          <t>Michigan Consumer Sentiment PrelFEB</t>
+          <t>Michigan Current Conditions PrelFEB</t>
         </is>
       </c>
       <c r="C427" t="inlineStr">
         <is>
-          <t>67.8</t>
+          <t>68.7</t>
         </is>
       </c>
       <c r="D427" t="inlineStr">
         <is>
-          <t>71.1</t>
+          <t>74</t>
         </is>
       </c>
       <c r="E427" t="inlineStr">
         <is>
-          <t>71.1</t>
+          <t>73</t>
         </is>
       </c>
       <c r="F427" t="inlineStr">
         <is>
-          <t>72</t>
+          <t>74.3</t>
         </is>
       </c>
       <c r="G427" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="428">
@@ -13043,23 +13039,27 @@
       </c>
       <c r="B428" t="inlineStr">
         <is>
-          <t>Michigan 5 Year Inflation Expectations PrelFEB</t>
+          <t>Wholesale Inventories MoMDEC</t>
         </is>
       </c>
       <c r="C428" t="inlineStr">
         <is>
-          <t>3.3%</t>
+          <t>-0.5%</t>
         </is>
       </c>
       <c r="D428" t="inlineStr">
         <is>
-          <t>3.2%</t>
-        </is>
-      </c>
-      <c r="E428" t="inlineStr"/>
+          <t>-0.1%</t>
+        </is>
+      </c>
+      <c r="E428" t="inlineStr">
+        <is>
+          <t>-0.5%</t>
+        </is>
+      </c>
       <c r="F428" t="inlineStr">
         <is>
-          <t>3.3%</t>
+          <t>-0.5%</t>
         </is>
       </c>
       <c r="G428" t="n">
@@ -13636,27 +13636,27 @@
       </c>
       <c r="B451" t="inlineStr">
         <is>
-          <t>Core Inflation Rate MoMJAN</t>
+          <t>Inflation Rate YoYJAN</t>
         </is>
       </c>
       <c r="C451" t="inlineStr">
         <is>
-          <t>0.4%</t>
+          <t>3%</t>
         </is>
       </c>
       <c r="D451" t="inlineStr">
         <is>
-          <t>0.2%</t>
+          <t>2.9%</t>
         </is>
       </c>
       <c r="E451" t="inlineStr">
         <is>
-          <t>0.3%</t>
+          <t>2.9%</t>
         </is>
       </c>
       <c r="F451" t="inlineStr">
         <is>
-          <t>0.3%</t>
+          <t>2.9%</t>
         </is>
       </c>
       <c r="G451" t="n">
@@ -13671,31 +13671,27 @@
       </c>
       <c r="B452" t="inlineStr">
         <is>
-          <t>Inflation Rate MoMJAN</t>
+          <t>CPI s.aJAN</t>
         </is>
       </c>
       <c r="C452" t="inlineStr">
         <is>
-          <t>0.5%</t>
+          <t>319.086</t>
         </is>
       </c>
       <c r="D452" t="inlineStr">
         <is>
-          <t>0.4%</t>
-        </is>
-      </c>
-      <c r="E452" t="inlineStr">
-        <is>
-          <t>0.3%</t>
-        </is>
-      </c>
+          <t>317.603</t>
+        </is>
+      </c>
+      <c r="E452" t="inlineStr"/>
       <c r="F452" t="inlineStr">
         <is>
-          <t>0.2%</t>
+          <t>318.2</t>
         </is>
       </c>
       <c r="G452" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="453">
@@ -13706,31 +13702,31 @@
       </c>
       <c r="B453" t="inlineStr">
         <is>
-          <t>Core Inflation Rate YoYJAN</t>
+          <t>CPIJAN</t>
         </is>
       </c>
       <c r="C453" t="inlineStr">
         <is>
-          <t>3.3%</t>
+          <t>317.67</t>
         </is>
       </c>
       <c r="D453" t="inlineStr">
         <is>
-          <t>3.2%</t>
+          <t>315.61</t>
         </is>
       </c>
       <c r="E453" t="inlineStr">
         <is>
-          <t>3.1%</t>
+          <t>317.46</t>
         </is>
       </c>
       <c r="F453" t="inlineStr">
         <is>
-          <t>3.1%</t>
+          <t>317.3</t>
         </is>
       </c>
       <c r="G453" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="454">
@@ -13741,31 +13737,31 @@
       </c>
       <c r="B454" t="inlineStr">
         <is>
-          <t>CPIJAN</t>
+          <t>Inflation Rate MoMJAN</t>
         </is>
       </c>
       <c r="C454" t="inlineStr">
         <is>
-          <t>317.67</t>
+          <t>0.5%</t>
         </is>
       </c>
       <c r="D454" t="inlineStr">
         <is>
-          <t>315.61</t>
+          <t>0.4%</t>
         </is>
       </c>
       <c r="E454" t="inlineStr">
         <is>
-          <t>317.46</t>
+          <t>0.3%</t>
         </is>
       </c>
       <c r="F454" t="inlineStr">
         <is>
-          <t>317.3</t>
+          <t>0.2%</t>
         </is>
       </c>
       <c r="G454" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="455">
@@ -13776,27 +13772,31 @@
       </c>
       <c r="B455" t="inlineStr">
         <is>
-          <t>CPI s.aJAN</t>
+          <t>Core Inflation Rate YoYJAN</t>
         </is>
       </c>
       <c r="C455" t="inlineStr">
         <is>
-          <t>319.086</t>
+          <t>3.3%</t>
         </is>
       </c>
       <c r="D455" t="inlineStr">
         <is>
-          <t>317.603</t>
-        </is>
-      </c>
-      <c r="E455" t="inlineStr"/>
+          <t>3.2%</t>
+        </is>
+      </c>
+      <c r="E455" t="inlineStr">
+        <is>
+          <t>3.1%</t>
+        </is>
+      </c>
       <c r="F455" t="inlineStr">
         <is>
-          <t>318.2</t>
+          <t>3.1%</t>
         </is>
       </c>
       <c r="G455" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="456">
@@ -13807,27 +13807,27 @@
       </c>
       <c r="B456" t="inlineStr">
         <is>
-          <t>Inflation Rate YoYJAN</t>
+          <t>Core Inflation Rate MoMJAN</t>
         </is>
       </c>
       <c r="C456" t="inlineStr">
         <is>
-          <t>3%</t>
+          <t>0.4%</t>
         </is>
       </c>
       <c r="D456" t="inlineStr">
         <is>
-          <t>2.9%</t>
+          <t>0.2%</t>
         </is>
       </c>
       <c r="E456" t="inlineStr">
         <is>
-          <t>2.9%</t>
+          <t>0.3%</t>
         </is>
       </c>
       <c r="F456" t="inlineStr">
         <is>
-          <t>2.9%</t>
+          <t>0.3%</t>
         </is>
       </c>
       <c r="G456" t="n">
@@ -13842,27 +13842,23 @@
       </c>
       <c r="B457" t="inlineStr">
         <is>
-          <t>EIA Crude Oil Stocks ChangeFEB/07</t>
+          <t>EIA Refinery Crude Runs ChangeFEB/07</t>
         </is>
       </c>
       <c r="C457" t="inlineStr">
         <is>
-          <t>4.07M</t>
+          <t>0.082M</t>
         </is>
       </c>
       <c r="D457" t="inlineStr">
         <is>
-          <t>8.664M</t>
-        </is>
-      </c>
-      <c r="E457" t="inlineStr">
-        <is>
-          <t>3M</t>
-        </is>
-      </c>
+          <t>0.16M</t>
+        </is>
+      </c>
+      <c r="E457" t="inlineStr"/>
       <c r="F457" t="inlineStr"/>
       <c r="G457" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="458">
@@ -13873,17 +13869,17 @@
       </c>
       <c r="B458" t="inlineStr">
         <is>
-          <t>EIA Heating Oil Stocks ChangeFEB/07</t>
+          <t>EIA Gasoline Production ChangeFEB/07</t>
         </is>
       </c>
       <c r="C458" t="inlineStr">
         <is>
-          <t>0.159M</t>
+          <t>0.18M</t>
         </is>
       </c>
       <c r="D458" t="inlineStr">
         <is>
-          <t>0.373M</t>
+          <t>-0.027M</t>
         </is>
       </c>
       <c r="E458" t="inlineStr"/>
@@ -13900,23 +13896,27 @@
       </c>
       <c r="B459" t="inlineStr">
         <is>
-          <t>EIA Cushing Crude Oil Stocks ChangeFEB/07</t>
+          <t>EIA Gasoline Stocks ChangeFEB/07</t>
         </is>
       </c>
       <c r="C459" t="inlineStr">
         <is>
-          <t>0.872M</t>
+          <t>-3.035M</t>
         </is>
       </c>
       <c r="D459" t="inlineStr">
         <is>
-          <t>-0.034M</t>
-        </is>
-      </c>
-      <c r="E459" t="inlineStr"/>
+          <t>2.233M</t>
+        </is>
+      </c>
+      <c r="E459" t="inlineStr">
+        <is>
+          <t>1.5M</t>
+        </is>
+      </c>
       <c r="F459" t="inlineStr"/>
       <c r="G459" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="460">
@@ -13927,24 +13927,20 @@
       </c>
       <c r="B460" t="inlineStr">
         <is>
-          <t>EIA Distillate Stocks ChangeFEB/07</t>
+          <t>EIA Crude Oil Imports ChangeFEB/07</t>
         </is>
       </c>
       <c r="C460" t="inlineStr">
         <is>
-          <t>0.135M</t>
+          <t>-0.184M</t>
         </is>
       </c>
       <c r="D460" t="inlineStr">
         <is>
-          <t>-5.471M</t>
-        </is>
-      </c>
-      <c r="E460" t="inlineStr">
-        <is>
-          <t>-2M</t>
-        </is>
-      </c>
+          <t>-0.178M</t>
+        </is>
+      </c>
+      <c r="E460" t="inlineStr"/>
       <c r="F460" t="inlineStr"/>
       <c r="G460" t="n">
         <v>3</v>
@@ -13958,17 +13954,17 @@
       </c>
       <c r="B461" t="inlineStr">
         <is>
-          <t>EIA Crude Oil Imports ChangeFEB/07</t>
+          <t>EIA Distillate Fuel Production ChangeFEB/07</t>
         </is>
       </c>
       <c r="C461" t="inlineStr">
         <is>
-          <t>-0.184M</t>
+          <t>-0.009M</t>
         </is>
       </c>
       <c r="D461" t="inlineStr">
         <is>
-          <t>-0.178M</t>
+          <t>-0.186M</t>
         </is>
       </c>
       <c r="E461" t="inlineStr"/>
@@ -13985,27 +13981,23 @@
       </c>
       <c r="B462" t="inlineStr">
         <is>
-          <t>EIA Gasoline Stocks ChangeFEB/07</t>
+          <t>EIA Cushing Crude Oil Stocks ChangeFEB/07</t>
         </is>
       </c>
       <c r="C462" t="inlineStr">
         <is>
-          <t>-3.035M</t>
+          <t>0.872M</t>
         </is>
       </c>
       <c r="D462" t="inlineStr">
         <is>
-          <t>2.233M</t>
-        </is>
-      </c>
-      <c r="E462" t="inlineStr">
-        <is>
-          <t>1.5M</t>
-        </is>
-      </c>
+          <t>-0.034M</t>
+        </is>
+      </c>
+      <c r="E462" t="inlineStr"/>
       <c r="F462" t="inlineStr"/>
       <c r="G462" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="463">
@@ -14016,17 +14008,17 @@
       </c>
       <c r="B463" t="inlineStr">
         <is>
-          <t>EIA Gasoline Production ChangeFEB/07</t>
+          <t>EIA Heating Oil Stocks ChangeFEB/07</t>
         </is>
       </c>
       <c r="C463" t="inlineStr">
         <is>
-          <t>0.18M</t>
+          <t>0.159M</t>
         </is>
       </c>
       <c r="D463" t="inlineStr">
         <is>
-          <t>-0.027M</t>
+          <t>0.373M</t>
         </is>
       </c>
       <c r="E463" t="inlineStr"/>
@@ -14043,23 +14035,27 @@
       </c>
       <c r="B464" t="inlineStr">
         <is>
-          <t>EIA Refinery Crude Runs ChangeFEB/07</t>
+          <t>EIA Crude Oil Stocks ChangeFEB/07</t>
         </is>
       </c>
       <c r="C464" t="inlineStr">
         <is>
-          <t>0.082M</t>
+          <t>4.07M</t>
         </is>
       </c>
       <c r="D464" t="inlineStr">
         <is>
-          <t>0.16M</t>
-        </is>
-      </c>
-      <c r="E464" t="inlineStr"/>
+          <t>8.664M</t>
+        </is>
+      </c>
+      <c r="E464" t="inlineStr">
+        <is>
+          <t>3M</t>
+        </is>
+      </c>
       <c r="F464" t="inlineStr"/>
       <c r="G464" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="465">
@@ -14070,20 +14066,24 @@
       </c>
       <c r="B465" t="inlineStr">
         <is>
-          <t>EIA Distillate Fuel Production ChangeFEB/07</t>
+          <t>EIA Distillate Stocks ChangeFEB/07</t>
         </is>
       </c>
       <c r="C465" t="inlineStr">
         <is>
-          <t>-0.009M</t>
+          <t>0.135M</t>
         </is>
       </c>
       <c r="D465" t="inlineStr">
         <is>
-          <t>-0.186M</t>
-        </is>
-      </c>
-      <c r="E465" t="inlineStr"/>
+          <t>-5.471M</t>
+        </is>
+      </c>
+      <c r="E465" t="inlineStr">
+        <is>
+          <t>-2M</t>
+        </is>
+      </c>
       <c r="F465" t="inlineStr"/>
       <c r="G465" t="n">
         <v>3</v>
@@ -14224,23 +14224,27 @@
       </c>
       <c r="B471" t="inlineStr">
         <is>
-          <t>PPI Ex Food, Energy and Trade MoMJAN</t>
+          <t>PPI YoYJAN</t>
         </is>
       </c>
       <c r="C471" t="inlineStr">
         <is>
-          <t>0.3%</t>
+          <t>3.5%</t>
         </is>
       </c>
       <c r="D471" t="inlineStr">
         <is>
-          <t>0.4%</t>
-        </is>
-      </c>
-      <c r="E471" t="inlineStr"/>
+          <t>3.5%</t>
+        </is>
+      </c>
+      <c r="E471" t="inlineStr">
+        <is>
+          <t>3.2%</t>
+        </is>
+      </c>
       <c r="F471" t="inlineStr">
         <is>
-          <t>0.2%</t>
+          <t>3.4%</t>
         </is>
       </c>
       <c r="G471" t="n">
@@ -14255,31 +14259,31 @@
       </c>
       <c r="B472" t="inlineStr">
         <is>
-          <t>Continuing Jobless ClaimsFEB/01</t>
+          <t>Initial Jobless ClaimsFEB/08</t>
         </is>
       </c>
       <c r="C472" t="inlineStr">
         <is>
-          <t>1850K</t>
+          <t>213K</t>
         </is>
       </c>
       <c r="D472" t="inlineStr">
         <is>
-          <t>1886K</t>
+          <t>220K</t>
         </is>
       </c>
       <c r="E472" t="inlineStr">
         <is>
-          <t>1880K</t>
+          <t>215K</t>
         </is>
       </c>
       <c r="F472" t="inlineStr">
         <is>
-          <t>1875.0K</t>
+          <t>215.0K</t>
         </is>
       </c>
       <c r="G472" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="473">
@@ -14290,23 +14294,27 @@
       </c>
       <c r="B473" t="inlineStr">
         <is>
-          <t>Jobless Claims 4-week AverageFEB/08</t>
+          <t>Core PPI YoYJAN</t>
         </is>
       </c>
       <c r="C473" t="inlineStr">
         <is>
-          <t>216K</t>
+          <t>3.6%</t>
         </is>
       </c>
       <c r="D473" t="inlineStr">
         <is>
-          <t>217K</t>
-        </is>
-      </c>
-      <c r="E473" t="inlineStr"/>
+          <t>3.7%</t>
+        </is>
+      </c>
+      <c r="E473" t="inlineStr">
+        <is>
+          <t>3.3%</t>
+        </is>
+      </c>
       <c r="F473" t="inlineStr">
         <is>
-          <t>216.0K</t>
+          <t>3.5%</t>
         </is>
       </c>
       <c r="G473" t="n">
@@ -14321,19 +14329,19 @@
       </c>
       <c r="B474" t="inlineStr">
         <is>
-          <t>PPI MoMJAN</t>
+          <t>Core PPI MoMJAN</t>
         </is>
       </c>
       <c r="C474" t="inlineStr">
         <is>
+          <t>0.3%</t>
+        </is>
+      </c>
+      <c r="D474" t="inlineStr">
+        <is>
           <t>0.4%</t>
         </is>
       </c>
-      <c r="D474" t="inlineStr">
-        <is>
-          <t>0.5%</t>
-        </is>
-      </c>
       <c r="E474" t="inlineStr">
         <is>
           <t>0.3%</t>
@@ -14341,11 +14349,11 @@
       </c>
       <c r="F474" t="inlineStr">
         <is>
-          <t>0.3%</t>
+          <t>0.1%</t>
         </is>
       </c>
       <c r="G474" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="475">
@@ -14356,27 +14364,23 @@
       </c>
       <c r="B475" t="inlineStr">
         <is>
-          <t>PPI Ex Food, Energy and Trade YoYJAN</t>
+          <t>PPIJAN</t>
         </is>
       </c>
       <c r="C475" t="inlineStr">
         <is>
-          <t>3.4%</t>
+          <t>147.716</t>
         </is>
       </c>
       <c r="D475" t="inlineStr">
         <is>
-          <t>3.5%</t>
-        </is>
-      </c>
-      <c r="E475" t="inlineStr">
-        <is>
-          <t>3.2%</t>
-        </is>
-      </c>
+          <t>147.127</t>
+        </is>
+      </c>
+      <c r="E475" t="inlineStr"/>
       <c r="F475" t="inlineStr">
         <is>
-          <t>3.3%</t>
+          <t>147.2</t>
         </is>
       </c>
       <c r="G475" t="n">
@@ -14391,23 +14395,27 @@
       </c>
       <c r="B476" t="inlineStr">
         <is>
-          <t>PPIJAN</t>
+          <t>Continuing Jobless ClaimsFEB/01</t>
         </is>
       </c>
       <c r="C476" t="inlineStr">
         <is>
-          <t>147.716</t>
+          <t>1850K</t>
         </is>
       </c>
       <c r="D476" t="inlineStr">
         <is>
-          <t>147.127</t>
-        </is>
-      </c>
-      <c r="E476" t="inlineStr"/>
+          <t>1886K</t>
+        </is>
+      </c>
+      <c r="E476" t="inlineStr">
+        <is>
+          <t>1880K</t>
+        </is>
+      </c>
       <c r="F476" t="inlineStr">
         <is>
-          <t>147.2</t>
+          <t>1875.0K</t>
         </is>
       </c>
       <c r="G476" t="n">
@@ -14422,31 +14430,31 @@
       </c>
       <c r="B477" t="inlineStr">
         <is>
-          <t>PPI YoYJAN</t>
+          <t>PPI MoMJAN</t>
         </is>
       </c>
       <c r="C477" t="inlineStr">
         <is>
-          <t>3.5%</t>
+          <t>0.4%</t>
         </is>
       </c>
       <c r="D477" t="inlineStr">
         <is>
-          <t>3.5%</t>
+          <t>0.5%</t>
         </is>
       </c>
       <c r="E477" t="inlineStr">
         <is>
-          <t>3.2%</t>
+          <t>0.3%</t>
         </is>
       </c>
       <c r="F477" t="inlineStr">
         <is>
-          <t>3.4%</t>
+          <t>0.3%</t>
         </is>
       </c>
       <c r="G477" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="478">
@@ -14457,31 +14465,27 @@
       </c>
       <c r="B478" t="inlineStr">
         <is>
-          <t>Core PPI MoMJAN</t>
+          <t>Jobless Claims 4-week AverageFEB/08</t>
         </is>
       </c>
       <c r="C478" t="inlineStr">
         <is>
-          <t>0.3%</t>
+          <t>216K</t>
         </is>
       </c>
       <c r="D478" t="inlineStr">
         <is>
-          <t>0.4%</t>
-        </is>
-      </c>
-      <c r="E478" t="inlineStr">
-        <is>
-          <t>0.3%</t>
-        </is>
-      </c>
+          <t>217K</t>
+        </is>
+      </c>
+      <c r="E478" t="inlineStr"/>
       <c r="F478" t="inlineStr">
         <is>
-          <t>0.1%</t>
+          <t>216.0K</t>
         </is>
       </c>
       <c r="G478" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="479">
@@ -14492,27 +14496,23 @@
       </c>
       <c r="B479" t="inlineStr">
         <is>
-          <t>Core PPI YoYJAN</t>
+          <t>PPI Ex Food, Energy and Trade MoMJAN</t>
         </is>
       </c>
       <c r="C479" t="inlineStr">
         <is>
-          <t>3.6%</t>
+          <t>0.3%</t>
         </is>
       </c>
       <c r="D479" t="inlineStr">
         <is>
-          <t>3.7%</t>
-        </is>
-      </c>
-      <c r="E479" t="inlineStr">
-        <is>
-          <t>3.3%</t>
-        </is>
-      </c>
+          <t>0.4%</t>
+        </is>
+      </c>
+      <c r="E479" t="inlineStr"/>
       <c r="F479" t="inlineStr">
         <is>
-          <t>3.5%</t>
+          <t>0.2%</t>
         </is>
       </c>
       <c r="G479" t="n">
@@ -14527,31 +14527,31 @@
       </c>
       <c r="B480" t="inlineStr">
         <is>
-          <t>Initial Jobless ClaimsFEB/08</t>
+          <t>PPI Ex Food, Energy and Trade YoYJAN</t>
         </is>
       </c>
       <c r="C480" t="inlineStr">
         <is>
-          <t>213K</t>
+          <t>3.4%</t>
         </is>
       </c>
       <c r="D480" t="inlineStr">
         <is>
-          <t>220K</t>
+          <t>3.5%</t>
         </is>
       </c>
       <c r="E480" t="inlineStr">
         <is>
-          <t>215K</t>
+          <t>3.2%</t>
         </is>
       </c>
       <c r="F480" t="inlineStr">
         <is>
-          <t>215.0K</t>
+          <t>3.3%</t>
         </is>
       </c>
       <c r="G480" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="481">
@@ -14728,31 +14728,27 @@
       </c>
       <c r="B487" t="inlineStr">
         <is>
-          <t>Retail Sales MoMJAN</t>
+          <t>Retail Sales Ex Gas/Autos MoMJAN</t>
         </is>
       </c>
       <c r="C487" t="inlineStr">
         <is>
-          <t>-0.9%</t>
+          <t>-0.5%</t>
         </is>
       </c>
       <c r="D487" t="inlineStr">
         <is>
-          <t>0.7%</t>
-        </is>
-      </c>
-      <c r="E487" t="inlineStr">
-        <is>
-          <t>-0.1%</t>
-        </is>
-      </c>
+          <t>0.5%</t>
+        </is>
+      </c>
+      <c r="E487" t="inlineStr"/>
       <c r="F487" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>0.2%</t>
         </is>
       </c>
       <c r="G487" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="488">
@@ -14763,22 +14759,22 @@
       </c>
       <c r="B488" t="inlineStr">
         <is>
-          <t>Import Prices MoMJAN</t>
+          <t>Export Prices MoMJAN</t>
         </is>
       </c>
       <c r="C488" t="inlineStr">
         <is>
+          <t>1.3%</t>
+        </is>
+      </c>
+      <c r="D488" t="inlineStr">
+        <is>
+          <t>0.5%</t>
+        </is>
+      </c>
+      <c r="E488" t="inlineStr">
+        <is>
           <t>0.3%</t>
-        </is>
-      </c>
-      <c r="D488" t="inlineStr">
-        <is>
-          <t>0.2%</t>
-        </is>
-      </c>
-      <c r="E488" t="inlineStr">
-        <is>
-          <t>0.4%</t>
         </is>
       </c>
       <c r="F488" t="inlineStr">
@@ -14798,31 +14794,27 @@
       </c>
       <c r="B489" t="inlineStr">
         <is>
-          <t>Retail Sales Ex Autos MoMJAN</t>
+          <t>Export Prices YoYJAN</t>
         </is>
       </c>
       <c r="C489" t="inlineStr">
         <is>
-          <t>-0.4%</t>
+          <t>2.7%</t>
         </is>
       </c>
       <c r="D489" t="inlineStr">
         <is>
-          <t>0.7%</t>
-        </is>
-      </c>
-      <c r="E489" t="inlineStr">
-        <is>
-          <t>0.3%</t>
-        </is>
-      </c>
+          <t>2%</t>
+        </is>
+      </c>
+      <c r="E489" t="inlineStr"/>
       <c r="F489" t="inlineStr">
         <is>
-          <t>0.3%</t>
+          <t>2.3%</t>
         </is>
       </c>
       <c r="G489" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="490">
@@ -14833,23 +14825,23 @@
       </c>
       <c r="B490" t="inlineStr">
         <is>
-          <t>Retail Sales YoYJAN</t>
+          <t>Import Prices YoYJAN</t>
         </is>
       </c>
       <c r="C490" t="inlineStr">
         <is>
-          <t>4.2%</t>
+          <t>1.9%</t>
         </is>
       </c>
       <c r="D490" t="inlineStr">
         <is>
-          <t>4.4%</t>
+          <t>2.2%</t>
         </is>
       </c>
       <c r="E490" t="inlineStr"/>
       <c r="F490" t="inlineStr">
         <is>
-          <t>3.7%</t>
+          <t>2.8%</t>
         </is>
       </c>
       <c r="G490" t="n">
@@ -14864,27 +14856,31 @@
       </c>
       <c r="B491" t="inlineStr">
         <is>
-          <t>Import Prices YoYJAN</t>
+          <t>Retail Sales Control Group MoMJAN</t>
         </is>
       </c>
       <c r="C491" t="inlineStr">
         <is>
-          <t>1.9%</t>
+          <t>-0.8%</t>
         </is>
       </c>
       <c r="D491" t="inlineStr">
         <is>
-          <t>2.2%</t>
-        </is>
-      </c>
-      <c r="E491" t="inlineStr"/>
+          <t>0.8%</t>
+        </is>
+      </c>
+      <c r="E491" t="inlineStr">
+        <is>
+          <t>0.3%</t>
+        </is>
+      </c>
       <c r="F491" t="inlineStr">
         <is>
-          <t>2.8%</t>
+          <t>0.4%</t>
         </is>
       </c>
       <c r="G491" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="492">
@@ -14895,27 +14891,31 @@
       </c>
       <c r="B492" t="inlineStr">
         <is>
-          <t>Retail Sales Ex Gas/Autos MoMJAN</t>
+          <t>Retail Sales Ex Autos MoMJAN</t>
         </is>
       </c>
       <c r="C492" t="inlineStr">
         <is>
-          <t>-0.5%</t>
+          <t>-0.4%</t>
         </is>
       </c>
       <c r="D492" t="inlineStr">
         <is>
-          <t>0.5%</t>
-        </is>
-      </c>
-      <c r="E492" t="inlineStr"/>
+          <t>0.7%</t>
+        </is>
+      </c>
+      <c r="E492" t="inlineStr">
+        <is>
+          <t>0.3%</t>
+        </is>
+      </c>
       <c r="F492" t="inlineStr">
         <is>
-          <t>0.2%</t>
+          <t>0.3%</t>
         </is>
       </c>
       <c r="G492" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="493">
@@ -14926,23 +14926,23 @@
       </c>
       <c r="B493" t="inlineStr">
         <is>
-          <t>Export Prices YoYJAN</t>
+          <t>Retail Sales YoYJAN</t>
         </is>
       </c>
       <c r="C493" t="inlineStr">
         <is>
-          <t>2.7%</t>
+          <t>4.2%</t>
         </is>
       </c>
       <c r="D493" t="inlineStr">
         <is>
-          <t>2%</t>
+          <t>4.4%</t>
         </is>
       </c>
       <c r="E493" t="inlineStr"/>
       <c r="F493" t="inlineStr">
         <is>
-          <t>2.3%</t>
+          <t>3.7%</t>
         </is>
       </c>
       <c r="G493" t="n">
@@ -14957,31 +14957,31 @@
       </c>
       <c r="B494" t="inlineStr">
         <is>
-          <t>Retail Sales Control Group MoMJAN</t>
+          <t>Retail Sales MoMJAN</t>
         </is>
       </c>
       <c r="C494" t="inlineStr">
         <is>
-          <t>-0.8%</t>
+          <t>-0.9%</t>
         </is>
       </c>
       <c r="D494" t="inlineStr">
         <is>
-          <t>0.8%</t>
+          <t>0.7%</t>
         </is>
       </c>
       <c r="E494" t="inlineStr">
         <is>
-          <t>0.3%</t>
+          <t>-0.1%</t>
         </is>
       </c>
       <c r="F494" t="inlineStr">
         <is>
-          <t>0.4%</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="G494" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="495">
@@ -14992,22 +14992,22 @@
       </c>
       <c r="B495" t="inlineStr">
         <is>
-          <t>Export Prices MoMJAN</t>
+          <t>Import Prices MoMJAN</t>
         </is>
       </c>
       <c r="C495" t="inlineStr">
         <is>
-          <t>1.3%</t>
+          <t>0.3%</t>
         </is>
       </c>
       <c r="D495" t="inlineStr">
         <is>
-          <t>0.5%</t>
+          <t>0.2%</t>
         </is>
       </c>
       <c r="E495" t="inlineStr">
         <is>
-          <t>0.3%</t>
+          <t>0.4%</t>
         </is>
       </c>
       <c r="F495" t="inlineStr">
@@ -15714,17 +15714,17 @@
       </c>
       <c r="B521" t="inlineStr">
         <is>
-          <t>MBA Mortgage Refinance IndexFEB/14</t>
+          <t>MBA Mortgage ApplicationsFEB/14</t>
         </is>
       </c>
       <c r="C521" t="inlineStr">
         <is>
-          <t>593.6</t>
+          <t>-6.6%</t>
         </is>
       </c>
       <c r="D521" t="inlineStr">
         <is>
-          <t>640.6</t>
+          <t>2.3%</t>
         </is>
       </c>
       <c r="E521" t="inlineStr"/>
@@ -15741,23 +15741,23 @@
       </c>
       <c r="B522" t="inlineStr">
         <is>
-          <t>MBA Purchase IndexFEB/14</t>
+          <t>MBA 30-Year Mortgage RateFEB/14</t>
         </is>
       </c>
       <c r="C522" t="inlineStr">
         <is>
-          <t>144.0</t>
+          <t>6.93%</t>
         </is>
       </c>
       <c r="D522" t="inlineStr">
         <is>
-          <t>153.1</t>
+          <t>6.95%</t>
         </is>
       </c>
       <c r="E522" t="inlineStr"/>
       <c r="F522" t="inlineStr"/>
       <c r="G522" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="523">
@@ -15795,23 +15795,23 @@
       </c>
       <c r="B524" t="inlineStr">
         <is>
-          <t>MBA 30-Year Mortgage RateFEB/14</t>
+          <t>MBA Mortgage Refinance IndexFEB/14</t>
         </is>
       </c>
       <c r="C524" t="inlineStr">
         <is>
-          <t>6.93%</t>
+          <t>593.6</t>
         </is>
       </c>
       <c r="D524" t="inlineStr">
         <is>
-          <t>6.95%</t>
+          <t>640.6</t>
         </is>
       </c>
       <c r="E524" t="inlineStr"/>
       <c r="F524" t="inlineStr"/>
       <c r="G524" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="525">
@@ -15822,17 +15822,17 @@
       </c>
       <c r="B525" t="inlineStr">
         <is>
-          <t>MBA Mortgage ApplicationsFEB/14</t>
+          <t>MBA Purchase IndexFEB/14</t>
         </is>
       </c>
       <c r="C525" t="inlineStr">
         <is>
-          <t>-6.6%</t>
+          <t>144.0</t>
         </is>
       </c>
       <c r="D525" t="inlineStr">
         <is>
-          <t>2.3%</t>
+          <t>153.1</t>
         </is>
       </c>
       <c r="E525" t="inlineStr"/>
@@ -16510,17 +16510,17 @@
       </c>
       <c r="B549" t="inlineStr">
         <is>
-          <t>8-Week Bill Auction</t>
+          <t>4-Week Bill Auction</t>
         </is>
       </c>
       <c r="C549" t="inlineStr">
         <is>
-          <t>4.235%</t>
+          <t>4.245%</t>
         </is>
       </c>
       <c r="D549" t="inlineStr">
         <is>
-          <t>4.240%</t>
+          <t>4.250%</t>
         </is>
       </c>
       <c r="E549" t="inlineStr"/>
@@ -16537,17 +16537,17 @@
       </c>
       <c r="B550" t="inlineStr">
         <is>
-          <t>4-Week Bill Auction</t>
+          <t>8-Week Bill Auction</t>
         </is>
       </c>
       <c r="C550" t="inlineStr">
         <is>
-          <t>4.245%</t>
+          <t>4.235%</t>
         </is>
       </c>
       <c r="D550" t="inlineStr">
         <is>
-          <t>4.250%</t>
+          <t>4.240%</t>
         </is>
       </c>
       <c r="E550" t="inlineStr"/>
@@ -17326,7 +17326,7 @@
       </c>
       <c r="B577" t="inlineStr">
         <is>
-          <t>Fed Daly Speech</t>
+          <t>Fed Jefferson Speech</t>
         </is>
       </c>
       <c r="C577" t="inlineStr"/>
@@ -17345,7 +17345,7 @@
       </c>
       <c r="B578" t="inlineStr">
         <is>
-          <t>Fed Jefferson Speech</t>
+          <t>Fed Daly Speech</t>
         </is>
       </c>
       <c r="C578" t="inlineStr"/>
@@ -17630,27 +17630,31 @@
       </c>
       <c r="B589" t="inlineStr">
         <is>
-          <t>House Price Index YoYDEC</t>
+          <t>S&amp;P/Case-Shiller Home Price YoYDEC</t>
         </is>
       </c>
       <c r="C589" t="inlineStr">
         <is>
-          <t>4.7%</t>
+          <t>4.5%</t>
         </is>
       </c>
       <c r="D589" t="inlineStr">
         <is>
-          <t>4.5%</t>
-        </is>
-      </c>
-      <c r="E589" t="inlineStr"/>
+          <t>4.3%</t>
+        </is>
+      </c>
+      <c r="E589" t="inlineStr">
+        <is>
+          <t>4.4%</t>
+        </is>
+      </c>
       <c r="F589" t="inlineStr">
         <is>
-          <t>4.1%</t>
+          <t>4.4%</t>
         </is>
       </c>
       <c r="G589" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="590">
@@ -17661,23 +17665,19 @@
       </c>
       <c r="B590" t="inlineStr">
         <is>
-          <t>S&amp;P/Case-Shiller Home Price MoMDEC</t>
-        </is>
-      </c>
-      <c r="C590" t="inlineStr">
-        <is>
-          <t>-0.1%</t>
-        </is>
-      </c>
+          <t>House Price Index YoYDEC</t>
+        </is>
+      </c>
+      <c r="C590" t="inlineStr"/>
       <c r="D590" t="inlineStr">
         <is>
-          <t>-0.1%</t>
+          <t>4.2%</t>
         </is>
       </c>
       <c r="E590" t="inlineStr"/>
       <c r="F590" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>4.1%</t>
         </is>
       </c>
       <c r="G590" t="n">
@@ -17692,23 +17692,19 @@
       </c>
       <c r="B591" t="inlineStr">
         <is>
-          <t>House Price Index MoMDEC</t>
+          <t>House Price IndexDEC</t>
         </is>
       </c>
       <c r="C591" t="inlineStr"/>
       <c r="D591" t="inlineStr">
         <is>
-          <t>0.3%</t>
-        </is>
-      </c>
-      <c r="E591" t="inlineStr">
-        <is>
-          <t>0.2%</t>
-        </is>
-      </c>
+          <t>433.4</t>
+        </is>
+      </c>
+      <c r="E591" t="inlineStr"/>
       <c r="F591" t="inlineStr">
         <is>
-          <t>0.2%</t>
+          <t>434.3</t>
         </is>
       </c>
       <c r="G591" t="n">
@@ -17723,27 +17719,19 @@
       </c>
       <c r="B592" t="inlineStr">
         <is>
-          <t>House Price Index MoMDEC</t>
-        </is>
-      </c>
-      <c r="C592" t="inlineStr">
-        <is>
-          <t>0.4%</t>
-        </is>
-      </c>
+          <t>S&amp;P/Case-Shiller Home Price MoMDEC</t>
+        </is>
+      </c>
+      <c r="C592" t="inlineStr"/>
       <c r="D592" t="inlineStr">
         <is>
-          <t>0.4%</t>
-        </is>
-      </c>
-      <c r="E592" t="inlineStr">
-        <is>
-          <t>0.2%</t>
-        </is>
-      </c>
+          <t>-0.1%</t>
+        </is>
+      </c>
+      <c r="E592" t="inlineStr"/>
       <c r="F592" t="inlineStr">
         <is>
-          <t>0.2%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="G592" t="n">
@@ -17758,27 +17746,27 @@
       </c>
       <c r="B593" t="inlineStr">
         <is>
-          <t>House Price IndexDEC</t>
-        </is>
-      </c>
-      <c r="C593" t="inlineStr">
-        <is>
-          <t>436.1</t>
-        </is>
-      </c>
+          <t>S&amp;P/Case-Shiller Home Price YoYDEC</t>
+        </is>
+      </c>
+      <c r="C593" t="inlineStr"/>
       <c r="D593" t="inlineStr">
         <is>
-          <t>434.3</t>
-        </is>
-      </c>
-      <c r="E593" t="inlineStr"/>
+          <t>4.3%</t>
+        </is>
+      </c>
+      <c r="E593" t="inlineStr">
+        <is>
+          <t>4.4%</t>
+        </is>
+      </c>
       <c r="F593" t="inlineStr">
         <is>
-          <t>434.3</t>
+          <t>4.4%</t>
         </is>
       </c>
       <c r="G593" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="594">
@@ -17789,19 +17777,27 @@
       </c>
       <c r="B594" t="inlineStr">
         <is>
-          <t>S&amp;P/Case-Shiller Home Price MoMDEC</t>
-        </is>
-      </c>
-      <c r="C594" t="inlineStr"/>
+          <t>House Price Index MoMDEC</t>
+        </is>
+      </c>
+      <c r="C594" t="inlineStr">
+        <is>
+          <t>0.4%</t>
+        </is>
+      </c>
       <c r="D594" t="inlineStr">
         <is>
-          <t>-0.1%</t>
-        </is>
-      </c>
-      <c r="E594" t="inlineStr"/>
+          <t>0.4%</t>
+        </is>
+      </c>
+      <c r="E594" t="inlineStr">
+        <is>
+          <t>0.2%</t>
+        </is>
+      </c>
       <c r="F594" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>0.2%</t>
         </is>
       </c>
       <c r="G594" t="n">
@@ -17816,27 +17812,27 @@
       </c>
       <c r="B595" t="inlineStr">
         <is>
-          <t>S&amp;P/Case-Shiller Home Price YoYDEC</t>
+          <t>House Price Index MoMDEC</t>
         </is>
       </c>
       <c r="C595" t="inlineStr"/>
       <c r="D595" t="inlineStr">
         <is>
-          <t>4.3%</t>
+          <t>0.3%</t>
         </is>
       </c>
       <c r="E595" t="inlineStr">
         <is>
-          <t>4.4%</t>
+          <t>0.2%</t>
         </is>
       </c>
       <c r="F595" t="inlineStr">
         <is>
-          <t>4.4%</t>
+          <t>0.2%</t>
         </is>
       </c>
       <c r="G595" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="596">
@@ -17847,19 +17843,23 @@
       </c>
       <c r="B596" t="inlineStr">
         <is>
-          <t>House Price IndexDEC</t>
-        </is>
-      </c>
-      <c r="C596" t="inlineStr"/>
+          <t>S&amp;P/Case-Shiller Home Price MoMDEC</t>
+        </is>
+      </c>
+      <c r="C596" t="inlineStr">
+        <is>
+          <t>-0.1%</t>
+        </is>
+      </c>
       <c r="D596" t="inlineStr">
         <is>
-          <t>433.4</t>
+          <t>-0.1%</t>
         </is>
       </c>
       <c r="E596" t="inlineStr"/>
       <c r="F596" t="inlineStr">
         <is>
-          <t>434.3</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="G596" t="n">
@@ -17877,10 +17877,14 @@
           <t>House Price Index YoYDEC</t>
         </is>
       </c>
-      <c r="C597" t="inlineStr"/>
+      <c r="C597" t="inlineStr">
+        <is>
+          <t>4.7%</t>
+        </is>
+      </c>
       <c r="D597" t="inlineStr">
         <is>
-          <t>4.2%</t>
+          <t>4.5%</t>
         </is>
       </c>
       <c r="E597" t="inlineStr"/>
@@ -17901,31 +17905,27 @@
       </c>
       <c r="B598" t="inlineStr">
         <is>
-          <t>S&amp;P/Case-Shiller Home Price YoYDEC</t>
+          <t>House Price IndexDEC</t>
         </is>
       </c>
       <c r="C598" t="inlineStr">
         <is>
-          <t>4.5%</t>
+          <t>436.1</t>
         </is>
       </c>
       <c r="D598" t="inlineStr">
         <is>
-          <t>4.3%</t>
-        </is>
-      </c>
-      <c r="E598" t="inlineStr">
-        <is>
-          <t>4.4%</t>
-        </is>
-      </c>
+          <t>434.3</t>
+        </is>
+      </c>
+      <c r="E598" t="inlineStr"/>
       <c r="F598" t="inlineStr">
         <is>
-          <t>4.4%</t>
+          <t>434.3</t>
         </is>
       </c>
       <c r="G598" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="599">
@@ -17936,27 +17936,27 @@
       </c>
       <c r="B599" t="inlineStr">
         <is>
-          <t>CB Consumer ConfidenceFEB</t>
-        </is>
-      </c>
-      <c r="C599" t="inlineStr"/>
+          <t>Richmond Fed Manufacturing Shipments IndexFEB</t>
+        </is>
+      </c>
+      <c r="C599" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
       <c r="D599" t="inlineStr">
         <is>
-          <t>104.1</t>
-        </is>
-      </c>
-      <c r="E599" t="inlineStr">
-        <is>
-          <t>103</t>
-        </is>
-      </c>
+          <t>-9</t>
+        </is>
+      </c>
+      <c r="E599" t="inlineStr"/>
       <c r="F599" t="inlineStr">
         <is>
-          <t>103</t>
+          <t>-4</t>
         </is>
       </c>
       <c r="G599" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="600">
@@ -17970,7 +17970,11 @@
           <t>Richmond Fed Manufacturing IndexFEB</t>
         </is>
       </c>
-      <c r="C600" t="inlineStr"/>
+      <c r="C600" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
       <c r="D600" t="inlineStr">
         <is>
           <t>-4</t>
@@ -17998,23 +18002,31 @@
       </c>
       <c r="B601" t="inlineStr">
         <is>
-          <t>Richmond Fed Services Revenues IndexFEB</t>
-        </is>
-      </c>
-      <c r="C601" t="inlineStr"/>
+          <t>CB Consumer ConfidenceFEB</t>
+        </is>
+      </c>
+      <c r="C601" t="inlineStr">
+        <is>
+          <t>98.3</t>
+        </is>
+      </c>
       <c r="D601" t="inlineStr">
         <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="E601" t="inlineStr"/>
+          <t>105.3</t>
+        </is>
+      </c>
+      <c r="E601" t="inlineStr">
+        <is>
+          <t>102.5</t>
+        </is>
+      </c>
       <c r="F601" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>103</t>
         </is>
       </c>
       <c r="G601" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="602">
@@ -18025,19 +18037,23 @@
       </c>
       <c r="B602" t="inlineStr">
         <is>
-          <t>Richmond Fed Manufacturing Shipments IndexFEB</t>
-        </is>
-      </c>
-      <c r="C602" t="inlineStr"/>
+          <t>Richmond Fed Services Revenues IndexFEB</t>
+        </is>
+      </c>
+      <c r="C602" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
       <c r="D602" t="inlineStr">
         <is>
-          <t>-9</t>
+          <t>4</t>
         </is>
       </c>
       <c r="E602" t="inlineStr"/>
       <c r="F602" t="inlineStr">
         <is>
-          <t>-4</t>
+          <t>7</t>
         </is>
       </c>
       <c r="G602" t="n">
@@ -18052,31 +18068,23 @@
       </c>
       <c r="B603" t="inlineStr">
         <is>
-          <t>CB Consumer ConfidenceFEB</t>
-        </is>
-      </c>
-      <c r="C603" t="inlineStr">
-        <is>
-          <t>98.3</t>
-        </is>
-      </c>
+          <t>Richmond Fed Services Revenues IndexFEB</t>
+        </is>
+      </c>
+      <c r="C603" t="inlineStr"/>
       <c r="D603" t="inlineStr">
         <is>
-          <t>105.3</t>
-        </is>
-      </c>
-      <c r="E603" t="inlineStr">
-        <is>
-          <t>102.5</t>
-        </is>
-      </c>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="E603" t="inlineStr"/>
       <c r="F603" t="inlineStr">
         <is>
-          <t>103</t>
+          <t>7</t>
         </is>
       </c>
       <c r="G603" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="604">
@@ -18090,11 +18098,7 @@
           <t>Richmond Fed Manufacturing IndexFEB</t>
         </is>
       </c>
-      <c r="C604" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
+      <c r="C604" t="inlineStr"/>
       <c r="D604" t="inlineStr">
         <is>
           <t>-4</t>
@@ -18122,27 +18126,27 @@
       </c>
       <c r="B605" t="inlineStr">
         <is>
-          <t>Richmond Fed Services Revenues IndexFEB</t>
-        </is>
-      </c>
-      <c r="C605" t="inlineStr">
-        <is>
-          <t>11</t>
-        </is>
-      </c>
+          <t>CB Consumer ConfidenceFEB</t>
+        </is>
+      </c>
+      <c r="C605" t="inlineStr"/>
       <c r="D605" t="inlineStr">
         <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="E605" t="inlineStr"/>
+          <t>104.1</t>
+        </is>
+      </c>
+      <c r="E605" t="inlineStr">
+        <is>
+          <t>103</t>
+        </is>
+      </c>
       <c r="F605" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>103</t>
         </is>
       </c>
       <c r="G605" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="606">
@@ -18156,11 +18160,7 @@
           <t>Richmond Fed Manufacturing Shipments IndexFEB</t>
         </is>
       </c>
-      <c r="C606" t="inlineStr">
-        <is>
-          <t>12</t>
-        </is>
-      </c>
+      <c r="C606" t="inlineStr"/>
       <c r="D606" t="inlineStr">
         <is>
           <t>-9</t>
@@ -18319,13 +18319,13 @@
       </c>
       <c r="B612" t="inlineStr">
         <is>
-          <t>5-Year Note Auction</t>
+          <t>Money SupplyJAN</t>
         </is>
       </c>
       <c r="C612" t="inlineStr"/>
       <c r="D612" t="inlineStr">
         <is>
-          <t>4.33%</t>
+          <t>$21.53T</t>
         </is>
       </c>
       <c r="E612" t="inlineStr"/>
@@ -18342,15 +18342,19 @@
       </c>
       <c r="B613" t="inlineStr">
         <is>
-          <t>Fed Barkin Speech</t>
+          <t>5-Year Note Auction</t>
         </is>
       </c>
       <c r="C613" t="inlineStr"/>
-      <c r="D613" t="inlineStr"/>
+      <c r="D613" t="inlineStr">
+        <is>
+          <t>4.33%</t>
+        </is>
+      </c>
       <c r="E613" t="inlineStr"/>
       <c r="F613" t="inlineStr"/>
       <c r="G613" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="614">
@@ -18361,23 +18365,15 @@
       </c>
       <c r="B614" t="inlineStr">
         <is>
-          <t>Money SupplyJAN</t>
-        </is>
-      </c>
-      <c r="C614" t="inlineStr">
-        <is>
-          <t>$21.56T</t>
-        </is>
-      </c>
-      <c r="D614" t="inlineStr">
-        <is>
-          <t>$21.53T</t>
-        </is>
-      </c>
+          <t>Fed Barkin Speech</t>
+        </is>
+      </c>
+      <c r="C614" t="inlineStr"/>
+      <c r="D614" t="inlineStr"/>
       <c r="E614" t="inlineStr"/>
       <c r="F614" t="inlineStr"/>
       <c r="G614" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="615">
@@ -18391,7 +18387,11 @@
           <t>Money SupplyJAN</t>
         </is>
       </c>
-      <c r="C615" t="inlineStr"/>
+      <c r="C615" t="inlineStr">
+        <is>
+          <t>$21.56T</t>
+        </is>
+      </c>
       <c r="D615" t="inlineStr">
         <is>
           <t>$21.53T</t>
@@ -18654,13 +18654,13 @@
       </c>
       <c r="B625" t="inlineStr">
         <is>
-          <t>MBA Mortgage Refinance IndexFEB/21</t>
+          <t>MBA Mortgage ApplicationsFEB/21</t>
         </is>
       </c>
       <c r="C625" t="inlineStr"/>
       <c r="D625" t="inlineStr">
         <is>
-          <t>593.6</t>
+          <t>-6.6%</t>
         </is>
       </c>
       <c r="E625" t="inlineStr"/>
@@ -18677,19 +18677,19 @@
       </c>
       <c r="B626" t="inlineStr">
         <is>
-          <t>MBA Purchase IndexFEB/21</t>
+          <t>MBA 30-Year Mortgage RateFEB/21</t>
         </is>
       </c>
       <c r="C626" t="inlineStr"/>
       <c r="D626" t="inlineStr">
         <is>
-          <t>144.0</t>
+          <t>6.93%</t>
         </is>
       </c>
       <c r="E626" t="inlineStr"/>
       <c r="F626" t="inlineStr"/>
       <c r="G626" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="627">
@@ -18700,19 +18700,19 @@
       </c>
       <c r="B627" t="inlineStr">
         <is>
-          <t>MBA 30-Year Mortgage RateFEB/21</t>
+          <t>MBA Purchase IndexFEB/21</t>
         </is>
       </c>
       <c r="C627" t="inlineStr"/>
       <c r="D627" t="inlineStr">
         <is>
-          <t>6.93%</t>
+          <t>144.0</t>
         </is>
       </c>
       <c r="E627" t="inlineStr"/>
       <c r="F627" t="inlineStr"/>
       <c r="G627" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="628">
@@ -18723,13 +18723,13 @@
       </c>
       <c r="B628" t="inlineStr">
         <is>
-          <t>MBA Mortgage ApplicationsFEB/21</t>
+          <t>MBA Mortgage Refinance IndexFEB/21</t>
         </is>
       </c>
       <c r="C628" t="inlineStr"/>
       <c r="D628" t="inlineStr">
         <is>
-          <t>-6.6%</t>
+          <t>593.6</t>
         </is>
       </c>
       <c r="E628" t="inlineStr"/>
@@ -19048,13 +19048,13 @@
       </c>
       <c r="B639" t="inlineStr">
         <is>
-          <t>EIA Cushing Crude Oil Stocks ChangeFEB/21</t>
+          <t>EIA Heating Oil Stocks ChangeFEB/21</t>
         </is>
       </c>
       <c r="C639" t="inlineStr"/>
       <c r="D639" t="inlineStr">
         <is>
-          <t>1.472M</t>
+          <t>-0.343M</t>
         </is>
       </c>
       <c r="E639" t="inlineStr"/>
@@ -19071,23 +19071,19 @@
       </c>
       <c r="B640" t="inlineStr">
         <is>
-          <t>EIA Gasoline Stocks ChangeFEB/21</t>
+          <t>EIA Gasoline Production ChangeFEB/21</t>
         </is>
       </c>
       <c r="C640" t="inlineStr"/>
       <c r="D640" t="inlineStr">
         <is>
-          <t>-0.151M</t>
-        </is>
-      </c>
-      <c r="E640" t="inlineStr">
-        <is>
-          <t>-1.30M</t>
-        </is>
-      </c>
+          <t>-0.156M</t>
+        </is>
+      </c>
+      <c r="E640" t="inlineStr"/>
       <c r="F640" t="inlineStr"/>
       <c r="G640" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="641">
@@ -19098,23 +19094,23 @@
       </c>
       <c r="B641" t="inlineStr">
         <is>
-          <t>EIA Crude Oil Stocks ChangeFEB/21</t>
+          <t>EIA Distillate Stocks ChangeFEB/21</t>
         </is>
       </c>
       <c r="C641" t="inlineStr"/>
       <c r="D641" t="inlineStr">
         <is>
-          <t>4.633M</t>
+          <t>-2.051M</t>
         </is>
       </c>
       <c r="E641" t="inlineStr">
         <is>
-          <t>2.34M</t>
+          <t>1.63M</t>
         </is>
       </c>
       <c r="F641" t="inlineStr"/>
       <c r="G641" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="642">
@@ -19148,23 +19144,23 @@
       </c>
       <c r="B643" t="inlineStr">
         <is>
-          <t>EIA Distillate Stocks ChangeFEB/21</t>
+          <t>EIA Crude Oil Stocks ChangeFEB/21</t>
         </is>
       </c>
       <c r="C643" t="inlineStr"/>
       <c r="D643" t="inlineStr">
         <is>
-          <t>-2.051M</t>
+          <t>4.633M</t>
         </is>
       </c>
       <c r="E643" t="inlineStr">
         <is>
-          <t>1.63M</t>
+          <t>2.34M</t>
         </is>
       </c>
       <c r="F643" t="inlineStr"/>
       <c r="G643" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="644">
@@ -19175,19 +19171,23 @@
       </c>
       <c r="B644" t="inlineStr">
         <is>
-          <t>EIA Gasoline Production ChangeFEB/21</t>
+          <t>EIA Gasoline Stocks ChangeFEB/21</t>
         </is>
       </c>
       <c r="C644" t="inlineStr"/>
       <c r="D644" t="inlineStr">
         <is>
-          <t>-0.156M</t>
-        </is>
-      </c>
-      <c r="E644" t="inlineStr"/>
+          <t>-0.151M</t>
+        </is>
+      </c>
+      <c r="E644" t="inlineStr">
+        <is>
+          <t>-1.30M</t>
+        </is>
+      </c>
       <c r="F644" t="inlineStr"/>
       <c r="G644" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="645">
@@ -19198,13 +19198,13 @@
       </c>
       <c r="B645" t="inlineStr">
         <is>
-          <t>EIA Heating Oil Stocks ChangeFEB/21</t>
+          <t>EIA Cushing Crude Oil Stocks ChangeFEB/21</t>
         </is>
       </c>
       <c r="C645" t="inlineStr"/>
       <c r="D645" t="inlineStr">
         <is>
-          <t>-0.343M</t>
+          <t>1.472M</t>
         </is>
       </c>
       <c r="E645" t="inlineStr"/>
@@ -19221,13 +19221,13 @@
       </c>
       <c r="B646" t="inlineStr">
         <is>
-          <t>EIA Refinery Crude Runs ChangeFEB/21</t>
+          <t>EIA Crude Oil Imports ChangeFEB/21</t>
         </is>
       </c>
       <c r="C646" t="inlineStr"/>
       <c r="D646" t="inlineStr">
         <is>
-          <t>-0.015M</t>
+          <t>-0.961M</t>
         </is>
       </c>
       <c r="E646" t="inlineStr"/>
@@ -19499,13 +19499,13 @@
       </c>
       <c r="B656" t="inlineStr">
         <is>
-          <t>EIA Crude Oil Imports ChangeFEB/21</t>
+          <t>EIA Refinery Crude Runs ChangeFEB/21</t>
         </is>
       </c>
       <c r="C656" t="inlineStr"/>
       <c r="D656" t="inlineStr">
         <is>
-          <t>-0.961M</t>
+          <t>-0.015M</t>
         </is>
       </c>
       <c r="E656" t="inlineStr"/>
@@ -19772,27 +19772,27 @@
       </c>
       <c r="B667" t="inlineStr">
         <is>
-          <t>PCE Prices QoQ 2nd EstQ4</t>
+          <t>Durable Goods Orders MoMJAN</t>
         </is>
       </c>
       <c r="C667" t="inlineStr"/>
       <c r="D667" t="inlineStr">
         <is>
-          <t>1.5%</t>
+          <t>-2.2%</t>
         </is>
       </c>
       <c r="E667" t="inlineStr">
         <is>
-          <t>2.3%</t>
+          <t>2%</t>
         </is>
       </c>
       <c r="F667" t="inlineStr">
         <is>
-          <t>2.3%</t>
+          <t>2.2%</t>
         </is>
       </c>
       <c r="G667" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="668">
@@ -20198,27 +20198,27 @@
       </c>
       <c r="B681" t="inlineStr">
         <is>
-          <t>Initial Jobless ClaimsFEB/22</t>
+          <t>Real Consumer Spending QoQ 2nd EstQ4</t>
         </is>
       </c>
       <c r="C681" t="inlineStr"/>
       <c r="D681" t="inlineStr">
         <is>
-          <t>219K</t>
+          <t>3.7%</t>
         </is>
       </c>
       <c r="E681" t="inlineStr">
         <is>
-          <t>221K</t>
+          <t>4.2%</t>
         </is>
       </c>
       <c r="F681" t="inlineStr">
         <is>
-          <t>225.0K</t>
+          <t>4.2%</t>
         </is>
       </c>
       <c r="G681" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="682">
@@ -20229,13 +20229,13 @@
       </c>
       <c r="B682" t="inlineStr">
         <is>
-          <t>GDP Growth Rate QoQ 2nd EstQ4</t>
+          <t>PCE Prices QoQ 2nd EstQ4</t>
         </is>
       </c>
       <c r="C682" t="inlineStr"/>
       <c r="D682" t="inlineStr">
         <is>
-          <t>3.1%</t>
+          <t>1.5%</t>
         </is>
       </c>
       <c r="E682" t="inlineStr">
@@ -20249,7 +20249,7 @@
         </is>
       </c>
       <c r="G682" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="683">
@@ -20260,23 +20260,27 @@
       </c>
       <c r="B683" t="inlineStr">
         <is>
-          <t>Continuing Jobless ClaimsFEB/15</t>
+          <t>Initial Jobless ClaimsFEB/22</t>
         </is>
       </c>
       <c r="C683" t="inlineStr"/>
       <c r="D683" t="inlineStr">
         <is>
-          <t>1869K</t>
-        </is>
-      </c>
-      <c r="E683" t="inlineStr"/>
+          <t>219K</t>
+        </is>
+      </c>
+      <c r="E683" t="inlineStr">
+        <is>
+          <t>221K</t>
+        </is>
+      </c>
       <c r="F683" t="inlineStr">
         <is>
-          <t>1874.0K</t>
+          <t>225.0K</t>
         </is>
       </c>
       <c r="G683" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="684">
@@ -20287,27 +20291,27 @@
       </c>
       <c r="B684" t="inlineStr">
         <is>
-          <t>GDP Price Index QoQ 2nd EstQ4</t>
+          <t>GDP Growth Rate QoQ 2nd EstQ4</t>
         </is>
       </c>
       <c r="C684" t="inlineStr"/>
       <c r="D684" t="inlineStr">
         <is>
-          <t>1.9%</t>
+          <t>3.1%</t>
         </is>
       </c>
       <c r="E684" t="inlineStr">
         <is>
-          <t>2.2%</t>
+          <t>2.3%</t>
         </is>
       </c>
       <c r="F684" t="inlineStr">
         <is>
-          <t>2.2%</t>
+          <t>2.3%</t>
         </is>
       </c>
       <c r="G684" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="685">
@@ -20318,27 +20322,23 @@
       </c>
       <c r="B685" t="inlineStr">
         <is>
-          <t>Durable Goods Orders MoMJAN</t>
+          <t>Jobless Claims 4-week AverageFEB/22</t>
         </is>
       </c>
       <c r="C685" t="inlineStr"/>
       <c r="D685" t="inlineStr">
         <is>
-          <t>-2.2%</t>
-        </is>
-      </c>
-      <c r="E685" t="inlineStr">
-        <is>
-          <t>2%</t>
-        </is>
-      </c>
+          <t>215.25K</t>
+        </is>
+      </c>
+      <c r="E685" t="inlineStr"/>
       <c r="F685" t="inlineStr">
         <is>
-          <t>2.2%</t>
+          <t>220.0K</t>
         </is>
       </c>
       <c r="G685" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="686">
@@ -20349,23 +20349,27 @@
       </c>
       <c r="B686" t="inlineStr">
         <is>
-          <t>Jobless Claims 4-week AverageFEB/22</t>
+          <t>GDP Price Index QoQ 2nd EstQ4</t>
         </is>
       </c>
       <c r="C686" t="inlineStr"/>
       <c r="D686" t="inlineStr">
         <is>
-          <t>215.25K</t>
-        </is>
-      </c>
-      <c r="E686" t="inlineStr"/>
+          <t>1.9%</t>
+        </is>
+      </c>
+      <c r="E686" t="inlineStr">
+        <is>
+          <t>2.2%</t>
+        </is>
+      </c>
       <c r="F686" t="inlineStr">
         <is>
-          <t>220.0K</t>
+          <t>2.2%</t>
         </is>
       </c>
       <c r="G686" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="687">
@@ -20376,23 +20380,19 @@
       </c>
       <c r="B687" t="inlineStr">
         <is>
-          <t>Real Consumer Spending QoQ 2nd EstQ4</t>
+          <t>Continuing Jobless ClaimsFEB/15</t>
         </is>
       </c>
       <c r="C687" t="inlineStr"/>
       <c r="D687" t="inlineStr">
         <is>
-          <t>3.7%</t>
-        </is>
-      </c>
-      <c r="E687" t="inlineStr">
-        <is>
-          <t>4.2%</t>
-        </is>
-      </c>
+          <t>1869K</t>
+        </is>
+      </c>
+      <c r="E687" t="inlineStr"/>
       <c r="F687" t="inlineStr">
         <is>
-          <t>4.2%</t>
+          <t>1874.0K</t>
         </is>
       </c>
       <c r="G687" t="n">
@@ -20407,27 +20407,23 @@
       </c>
       <c r="B688" t="inlineStr">
         <is>
-          <t>Durable Goods Orders Ex Transp MoMJAN</t>
+          <t>Durable Goods Orders ex Defense MoMJAN</t>
         </is>
       </c>
       <c r="C688" t="inlineStr"/>
       <c r="D688" t="inlineStr">
         <is>
-          <t>0.3%</t>
-        </is>
-      </c>
-      <c r="E688" t="inlineStr">
-        <is>
-          <t>0.3%</t>
-        </is>
-      </c>
+          <t>-2.4%</t>
+        </is>
+      </c>
+      <c r="E688" t="inlineStr"/>
       <c r="F688" t="inlineStr">
         <is>
-          <t>0.3%</t>
+          <t>1.4%</t>
         </is>
       </c>
       <c r="G688" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="689">
@@ -20438,23 +20434,23 @@
       </c>
       <c r="B689" t="inlineStr">
         <is>
-          <t>Non Defense Goods Orders Ex AirJAN</t>
+          <t>Core PCE Prices QoQ 2nd EstQ4</t>
         </is>
       </c>
       <c r="C689" t="inlineStr"/>
       <c r="D689" t="inlineStr">
         <is>
-          <t>0.5%</t>
+          <t>2.2%</t>
         </is>
       </c>
       <c r="E689" t="inlineStr">
         <is>
-          <t>0.3%</t>
+          <t>2.5%</t>
         </is>
       </c>
       <c r="F689" t="inlineStr">
         <is>
-          <t>0.4%</t>
+          <t>2.5%</t>
         </is>
       </c>
       <c r="G689" t="n">
@@ -20500,23 +20496,23 @@
       </c>
       <c r="B691" t="inlineStr">
         <is>
-          <t>Core PCE Prices QoQ 2nd EstQ4</t>
+          <t>Non Defense Goods Orders Ex AirJAN</t>
         </is>
       </c>
       <c r="C691" t="inlineStr"/>
       <c r="D691" t="inlineStr">
         <is>
-          <t>2.2%</t>
+          <t>0.5%</t>
         </is>
       </c>
       <c r="E691" t="inlineStr">
         <is>
-          <t>2.5%</t>
+          <t>0.3%</t>
         </is>
       </c>
       <c r="F691" t="inlineStr">
         <is>
-          <t>2.5%</t>
+          <t>0.4%</t>
         </is>
       </c>
       <c r="G691" t="n">
@@ -20531,23 +20527,27 @@
       </c>
       <c r="B692" t="inlineStr">
         <is>
-          <t>Durable Goods Orders ex Defense MoMJAN</t>
+          <t>Durable Goods Orders Ex Transp MoMJAN</t>
         </is>
       </c>
       <c r="C692" t="inlineStr"/>
       <c r="D692" t="inlineStr">
         <is>
-          <t>-2.4%</t>
-        </is>
-      </c>
-      <c r="E692" t="inlineStr"/>
+          <t>0.3%</t>
+        </is>
+      </c>
+      <c r="E692" t="inlineStr">
+        <is>
+          <t>0.3%</t>
+        </is>
+      </c>
       <c r="F692" t="inlineStr">
         <is>
-          <t>1.4%</t>
+          <t>0.3%</t>
         </is>
       </c>
       <c r="G692" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="693">
@@ -20577,23 +20577,19 @@
       </c>
       <c r="B694" t="inlineStr">
         <is>
-          <t>Pending Home Sales MoMJAN</t>
+          <t>Pending Home Sales YoYJAN</t>
         </is>
       </c>
       <c r="C694" t="inlineStr"/>
       <c r="D694" t="inlineStr">
         <is>
-          <t>-5.5%</t>
-        </is>
-      </c>
-      <c r="E694" t="inlineStr">
-        <is>
-          <t>-1.3%</t>
-        </is>
-      </c>
+          <t>-5.0%</t>
+        </is>
+      </c>
+      <c r="E694" t="inlineStr"/>
       <c r="F694" t="inlineStr">
         <is>
-          <t>-0.9%</t>
+          <t>6.0%</t>
         </is>
       </c>
       <c r="G694" t="n">
@@ -20685,19 +20681,23 @@
       </c>
       <c r="B698" t="inlineStr">
         <is>
-          <t>Pending Home Sales YoYJAN</t>
+          <t>Pending Home Sales MoMJAN</t>
         </is>
       </c>
       <c r="C698" t="inlineStr"/>
       <c r="D698" t="inlineStr">
         <is>
-          <t>-5.0%</t>
-        </is>
-      </c>
-      <c r="E698" t="inlineStr"/>
+          <t>-5.5%</t>
+        </is>
+      </c>
+      <c r="E698" t="inlineStr">
+        <is>
+          <t>-1.3%</t>
+        </is>
+      </c>
       <c r="F698" t="inlineStr">
         <is>
-          <t>6.0%</t>
+          <t>-0.9%</t>
         </is>
       </c>
       <c r="G698" t="n">
@@ -20920,13 +20920,13 @@
       </c>
       <c r="B707" t="inlineStr">
         <is>
-          <t>8-Week Bill Auction</t>
+          <t>4-Week Bill Auction</t>
         </is>
       </c>
       <c r="C707" t="inlineStr"/>
       <c r="D707" t="inlineStr">
         <is>
-          <t>4.235%</t>
+          <t>4.245%</t>
         </is>
       </c>
       <c r="E707" t="inlineStr"/>
@@ -20989,13 +20989,13 @@
       </c>
       <c r="B710" t="inlineStr">
         <is>
-          <t>4-Week Bill Auction</t>
+          <t>8-Week Bill Auction</t>
         </is>
       </c>
       <c r="C710" t="inlineStr"/>
       <c r="D710" t="inlineStr">
         <is>
-          <t>4.245%</t>
+          <t>4.235%</t>
         </is>
       </c>
       <c r="E710" t="inlineStr"/>
@@ -21577,27 +21577,27 @@
       </c>
       <c r="B734" t="inlineStr">
         <is>
-          <t>Personal Income MoMJAN</t>
+          <t>Wholesale Inventories MoM AdvJAN</t>
         </is>
       </c>
       <c r="C734" t="inlineStr"/>
       <c r="D734" t="inlineStr">
         <is>
-          <t>0.4%</t>
+          <t>-0.5%</t>
         </is>
       </c>
       <c r="E734" t="inlineStr">
         <is>
-          <t>0.3%</t>
+          <t>0.1%</t>
         </is>
       </c>
       <c r="F734" t="inlineStr">
         <is>
-          <t>0.3%</t>
+          <t>0.2%</t>
         </is>
       </c>
       <c r="G734" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="735">
@@ -21608,27 +21608,27 @@
       </c>
       <c r="B735" t="inlineStr">
         <is>
-          <t>Core PCE Price Index YoYJAN</t>
+          <t>Goods Trade Balance AdvJAN</t>
         </is>
       </c>
       <c r="C735" t="inlineStr"/>
       <c r="D735" t="inlineStr">
         <is>
-          <t>2.8%</t>
+          <t>$-122.11B</t>
         </is>
       </c>
       <c r="E735" t="inlineStr">
         <is>
-          <t>2.6%</t>
+          <t>$-114.7B</t>
         </is>
       </c>
       <c r="F735" t="inlineStr">
         <is>
-          <t>2.7%</t>
+          <t>$ -116.0B</t>
         </is>
       </c>
       <c r="G735" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="736">
@@ -21639,27 +21639,27 @@
       </c>
       <c r="B736" t="inlineStr">
         <is>
-          <t>PCE Price Index YoYJAN</t>
+          <t>Core PCE Price Index MoMJAN</t>
         </is>
       </c>
       <c r="C736" t="inlineStr"/>
       <c r="D736" t="inlineStr">
         <is>
-          <t>2.6%</t>
+          <t>0.2%</t>
         </is>
       </c>
       <c r="E736" t="inlineStr">
         <is>
-          <t>2.5%</t>
+          <t>0.3%</t>
         </is>
       </c>
       <c r="F736" t="inlineStr">
         <is>
-          <t>2.5%</t>
+          <t>0.4%</t>
         </is>
       </c>
       <c r="G736" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="737">
@@ -21670,27 +21670,23 @@
       </c>
       <c r="B737" t="inlineStr">
         <is>
-          <t>Core PCE Price Index MoMJAN</t>
+          <t>Retail Inventories Ex Autos MoM AdvJAN</t>
         </is>
       </c>
       <c r="C737" t="inlineStr"/>
       <c r="D737" t="inlineStr">
         <is>
-          <t>0.2%</t>
-        </is>
-      </c>
-      <c r="E737" t="inlineStr">
-        <is>
-          <t>0.3%</t>
-        </is>
-      </c>
+          <t>-0.1%</t>
+        </is>
+      </c>
+      <c r="E737" t="inlineStr"/>
       <c r="F737" t="inlineStr">
         <is>
-          <t>0.4%</t>
+          <t>0.1%</t>
         </is>
       </c>
       <c r="G737" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="738">
@@ -21701,27 +21697,27 @@
       </c>
       <c r="B738" t="inlineStr">
         <is>
-          <t>Goods Trade Balance AdvJAN</t>
+          <t>Personal Spending MoMJAN</t>
         </is>
       </c>
       <c r="C738" t="inlineStr"/>
       <c r="D738" t="inlineStr">
         <is>
-          <t>$-122.11B</t>
+          <t>0.7%</t>
         </is>
       </c>
       <c r="E738" t="inlineStr">
         <is>
-          <t>$-114.7B</t>
+          <t>0.1%</t>
         </is>
       </c>
       <c r="F738" t="inlineStr">
         <is>
-          <t>$ -116.0B</t>
+          <t>0.3%</t>
         </is>
       </c>
       <c r="G738" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="739">
@@ -21763,23 +21759,23 @@
       </c>
       <c r="B740" t="inlineStr">
         <is>
-          <t>Wholesale Inventories MoM AdvJAN</t>
+          <t>PCE Price Index YoYJAN</t>
         </is>
       </c>
       <c r="C740" t="inlineStr"/>
       <c r="D740" t="inlineStr">
         <is>
-          <t>-0.5%</t>
+          <t>2.6%</t>
         </is>
       </c>
       <c r="E740" t="inlineStr">
         <is>
-          <t>0.1%</t>
+          <t>2.5%</t>
         </is>
       </c>
       <c r="F740" t="inlineStr">
         <is>
-          <t>0.2%</t>
+          <t>2.5%</t>
         </is>
       </c>
       <c r="G740" t="n">
@@ -21794,18 +21790,18 @@
       </c>
       <c r="B741" t="inlineStr">
         <is>
-          <t>Personal Spending MoMJAN</t>
+          <t>Personal Income MoMJAN</t>
         </is>
       </c>
       <c r="C741" t="inlineStr"/>
       <c r="D741" t="inlineStr">
         <is>
-          <t>0.7%</t>
+          <t>0.4%</t>
         </is>
       </c>
       <c r="E741" t="inlineStr">
         <is>
-          <t>0.1%</t>
+          <t>0.3%</t>
         </is>
       </c>
       <c r="F741" t="inlineStr">
@@ -21825,23 +21821,27 @@
       </c>
       <c r="B742" t="inlineStr">
         <is>
-          <t>Retail Inventories Ex Autos MoM AdvJAN</t>
+          <t>Core PCE Price Index YoYJAN</t>
         </is>
       </c>
       <c r="C742" t="inlineStr"/>
       <c r="D742" t="inlineStr">
         <is>
-          <t>-0.1%</t>
-        </is>
-      </c>
-      <c r="E742" t="inlineStr"/>
+          <t>2.8%</t>
+        </is>
+      </c>
+      <c r="E742" t="inlineStr">
+        <is>
+          <t>2.6%</t>
+        </is>
+      </c>
       <c r="F742" t="inlineStr">
         <is>
-          <t>0.1%</t>
+          <t>2.7%</t>
         </is>
       </c>
       <c r="G742" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="743">
@@ -21914,13 +21914,13 @@
       </c>
       <c r="B745" t="inlineStr">
         <is>
-          <t>Baker Hughes Total Rigs CountFEB/28</t>
+          <t>Baker Hughes Oil Rig CountFEB/28</t>
         </is>
       </c>
       <c r="C745" t="inlineStr"/>
       <c r="D745" t="inlineStr">
         <is>
-          <t>592</t>
+          <t>487</t>
         </is>
       </c>
       <c r="E745" t="inlineStr"/>
@@ -21983,13 +21983,13 @@
       </c>
       <c r="B748" t="inlineStr">
         <is>
-          <t>Baker Hughes Oil Rig CountFEB/28</t>
+          <t>Baker Hughes Total Rigs CountFEB/28</t>
         </is>
       </c>
       <c r="C748" t="inlineStr"/>
       <c r="D748" t="inlineStr">
         <is>
-          <t>487</t>
+          <t>592</t>
         </is>
       </c>
       <c r="E748" t="inlineStr"/>
@@ -22095,23 +22095,23 @@
       </c>
       <c r="B752" t="inlineStr">
         <is>
-          <t>ISM Manufacturing EmploymentFEB</t>
+          <t>ISM Manufacturing PricesFEB</t>
         </is>
       </c>
       <c r="C752" t="inlineStr"/>
       <c r="D752" t="inlineStr">
         <is>
-          <t>50.3</t>
+          <t>54.9</t>
         </is>
       </c>
       <c r="E752" t="inlineStr"/>
       <c r="F752" t="inlineStr">
         <is>
-          <t>50.6</t>
+          <t>55</t>
         </is>
       </c>
       <c r="G752" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="753">
@@ -22230,19 +22230,19 @@
       </c>
       <c r="B757" t="inlineStr">
         <is>
-          <t>ISM Manufacturing PricesFEB</t>
+          <t>ISM Manufacturing New OrdersFEB</t>
         </is>
       </c>
       <c r="C757" t="inlineStr"/>
       <c r="D757" t="inlineStr">
         <is>
-          <t>54.9</t>
+          <t>55.1</t>
         </is>
       </c>
       <c r="E757" t="inlineStr"/>
       <c r="F757" t="inlineStr">
         <is>
-          <t>55</t>
+          <t>55.4</t>
         </is>
       </c>
       <c r="G757" t="n">
@@ -22311,23 +22311,23 @@
       </c>
       <c r="B760" t="inlineStr">
         <is>
-          <t>ISM Manufacturing New OrdersFEB</t>
+          <t>ISM Manufacturing EmploymentFEB</t>
         </is>
       </c>
       <c r="C760" t="inlineStr"/>
       <c r="D760" t="inlineStr">
         <is>
-          <t>55.1</t>
+          <t>50.3</t>
         </is>
       </c>
       <c r="E760" t="inlineStr"/>
       <c r="F760" t="inlineStr">
         <is>
-          <t>55.4</t>
+          <t>50.6</t>
         </is>
       </c>
       <c r="G760" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="761">
@@ -22840,7 +22840,7 @@
       </c>
       <c r="B783" t="inlineStr">
         <is>
-          <t>MBA Mortgage Market IndexFEB/28</t>
+          <t>MBA 30-Year Mortgage RateFEB/28</t>
         </is>
       </c>
       <c r="C783" t="inlineStr"/>
@@ -22848,7 +22848,7 @@
       <c r="E783" t="inlineStr"/>
       <c r="F783" t="inlineStr"/>
       <c r="G783" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="784">
@@ -22859,7 +22859,7 @@
       </c>
       <c r="B784" t="inlineStr">
         <is>
-          <t>MBA 30-Year Mortgage RateFEB/28</t>
+          <t>MBA Mortgage Market IndexFEB/28</t>
         </is>
       </c>
       <c r="C784" t="inlineStr"/>
@@ -22867,7 +22867,7 @@
       <c r="E784" t="inlineStr"/>
       <c r="F784" t="inlineStr"/>
       <c r="G784" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="785">
@@ -22994,23 +22994,23 @@
       </c>
       <c r="B789" t="inlineStr">
         <is>
-          <t>S&amp;P Global Composite PMI FinalFEB</t>
+          <t>S&amp;P Global Services PMI FinalFEB</t>
         </is>
       </c>
       <c r="C789" t="inlineStr"/>
       <c r="D789" t="inlineStr">
         <is>
-          <t>52.7</t>
+          <t>52.9</t>
         </is>
       </c>
       <c r="E789" t="inlineStr">
         <is>
-          <t>50.4</t>
+          <t>49.7</t>
         </is>
       </c>
       <c r="F789" t="inlineStr">
         <is>
-          <t>50.4</t>
+          <t>49.7</t>
         </is>
       </c>
       <c r="G789" t="n">
@@ -23025,23 +23025,23 @@
       </c>
       <c r="B790" t="inlineStr">
         <is>
-          <t>S&amp;P Global Services PMI FinalFEB</t>
+          <t>S&amp;P Global Composite PMI FinalFEB</t>
         </is>
       </c>
       <c r="C790" t="inlineStr"/>
       <c r="D790" t="inlineStr">
         <is>
-          <t>52.9</t>
+          <t>52.7</t>
         </is>
       </c>
       <c r="E790" t="inlineStr">
         <is>
-          <t>49.7</t>
+          <t>50.4</t>
         </is>
       </c>
       <c r="F790" t="inlineStr">
         <is>
-          <t>49.7</t>
+          <t>50.4</t>
         </is>
       </c>
       <c r="G790" t="n">
@@ -23503,13 +23503,13 @@
       </c>
       <c r="B808" t="inlineStr">
         <is>
-          <t>EIA Gasoline Production ChangeFEB/28</t>
+          <t>EIA Distillate Stocks ChangeFEB/28</t>
         </is>
       </c>
       <c r="C808" t="inlineStr"/>
       <c r="D808" t="inlineStr">
         <is>
-          <t>-0.02M</t>
+          <t>3.908M</t>
         </is>
       </c>
       <c r="E808" t="inlineStr"/>
@@ -23595,15 +23595,11 @@
       </c>
       <c r="B812" t="inlineStr">
         <is>
-          <t>EIA Cushing Crude Oil Stocks ChangeFEB/28</t>
+          <t>EIA Crude Oil Imports ChangeFEB/28</t>
         </is>
       </c>
       <c r="C812" t="inlineStr"/>
-      <c r="D812" t="inlineStr">
-        <is>
-          <t>1.282M</t>
-        </is>
-      </c>
+      <c r="D812" t="inlineStr"/>
       <c r="E812" t="inlineStr"/>
       <c r="F812" t="inlineStr"/>
       <c r="G812" t="n">
@@ -23687,19 +23683,19 @@
       </c>
       <c r="B816" t="inlineStr">
         <is>
-          <t>EIA Distillate Stocks ChangeFEB/28</t>
+          <t>EIA Gasoline Stocks ChangeFEB/28</t>
         </is>
       </c>
       <c r="C816" t="inlineStr"/>
       <c r="D816" t="inlineStr">
         <is>
-          <t>3.908M</t>
+          <t>0.369M</t>
         </is>
       </c>
       <c r="E816" t="inlineStr"/>
       <c r="F816" t="inlineStr"/>
       <c r="G816" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="817">
@@ -23710,11 +23706,15 @@
       </c>
       <c r="B817" t="inlineStr">
         <is>
-          <t>EIA Crude Oil Imports ChangeFEB/28</t>
+          <t>EIA Refinery Crude Runs ChangeFEB/28</t>
         </is>
       </c>
       <c r="C817" t="inlineStr"/>
-      <c r="D817" t="inlineStr"/>
+      <c r="D817" t="inlineStr">
+        <is>
+          <t>0.317M</t>
+        </is>
+      </c>
       <c r="E817" t="inlineStr"/>
       <c r="F817" t="inlineStr"/>
       <c r="G817" t="n">
@@ -23748,13 +23748,13 @@
       </c>
       <c r="B819" t="inlineStr">
         <is>
-          <t>EIA Refinery Crude Runs ChangeFEB/28</t>
+          <t>EIA Cushing Crude Oil Stocks ChangeFEB/28</t>
         </is>
       </c>
       <c r="C819" t="inlineStr"/>
       <c r="D819" t="inlineStr">
         <is>
-          <t>0.317M</t>
+          <t>1.282M</t>
         </is>
       </c>
       <c r="E819" t="inlineStr"/>
@@ -23771,19 +23771,19 @@
       </c>
       <c r="B820" t="inlineStr">
         <is>
-          <t>EIA Gasoline Stocks ChangeFEB/28</t>
+          <t>EIA Gasoline Production ChangeFEB/28</t>
         </is>
       </c>
       <c r="C820" t="inlineStr"/>
       <c r="D820" t="inlineStr">
         <is>
-          <t>0.369M</t>
+          <t>-0.02M</t>
         </is>
       </c>
       <c r="E820" t="inlineStr"/>
       <c r="F820" t="inlineStr"/>
       <c r="G820" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="821">
@@ -24024,19 +24024,19 @@
       </c>
       <c r="B831" t="inlineStr">
         <is>
-          <t>ImportsJAN</t>
+          <t>Balance of TradeJAN</t>
         </is>
       </c>
       <c r="C831" t="inlineStr"/>
       <c r="D831" t="inlineStr">
         <is>
-          <t>$364.9B</t>
+          <t>$-98.4B</t>
         </is>
       </c>
       <c r="E831" t="inlineStr"/>
       <c r="F831" t="inlineStr">
         <is>
-          <t>$376.0B</t>
+          <t>$-103B</t>
         </is>
       </c>
       <c r="G831" t="n">
@@ -24078,7 +24078,7 @@
       </c>
       <c r="B833" t="inlineStr">
         <is>
-          <t>Jobless Claims 4-week AverageMAR/01</t>
+          <t>Continuing Jobless ClaimsFEB/22</t>
         </is>
       </c>
       <c r="C833" t="inlineStr"/>
@@ -24297,7 +24297,7 @@
       </c>
       <c r="B842" t="inlineStr">
         <is>
-          <t>Continuing Jobless ClaimsFEB/22</t>
+          <t>Jobless Claims 4-week AverageMAR/01</t>
         </is>
       </c>
       <c r="C842" t="inlineStr"/>
@@ -24343,13 +24343,21 @@
       </c>
       <c r="B844" t="inlineStr">
         <is>
-          <t>Initial Jobless ClaimsMAR/01</t>
+          <t>ImportsJAN</t>
         </is>
       </c>
       <c r="C844" t="inlineStr"/>
-      <c r="D844" t="inlineStr"/>
+      <c r="D844" t="inlineStr">
+        <is>
+          <t>$364.9B</t>
+        </is>
+      </c>
       <c r="E844" t="inlineStr"/>
-      <c r="F844" t="inlineStr"/>
+      <c r="F844" t="inlineStr">
+        <is>
+          <t>$376.0B</t>
+        </is>
+      </c>
       <c r="G844" t="n">
         <v>2</v>
       </c>
@@ -24389,21 +24397,13 @@
       </c>
       <c r="B846" t="inlineStr">
         <is>
-          <t>Balance of TradeJAN</t>
+          <t>Initial Jobless ClaimsMAR/01</t>
         </is>
       </c>
       <c r="C846" t="inlineStr"/>
-      <c r="D846" t="inlineStr">
-        <is>
-          <t>$-98.4B</t>
-        </is>
-      </c>
+      <c r="D846" t="inlineStr"/>
       <c r="E846" t="inlineStr"/>
-      <c r="F846" t="inlineStr">
-        <is>
-          <t>$-103B</t>
-        </is>
-      </c>
+      <c r="F846" t="inlineStr"/>
       <c r="G846" t="n">
         <v>2</v>
       </c>
@@ -24948,19 +24948,19 @@
       </c>
       <c r="B871" t="inlineStr">
         <is>
-          <t>Average Hourly Earnings YoYFEB</t>
+          <t>Average Hourly Earnings MoMFEB</t>
         </is>
       </c>
       <c r="C871" t="inlineStr"/>
       <c r="D871" t="inlineStr">
         <is>
-          <t>4.1%</t>
+          <t>0.5%</t>
         </is>
       </c>
       <c r="E871" t="inlineStr"/>
       <c r="F871" t="inlineStr">
         <is>
-          <t>4.1%</t>
+          <t>0.3%</t>
         </is>
       </c>
       <c r="G871" t="n">
@@ -24975,23 +24975,19 @@
       </c>
       <c r="B872" t="inlineStr">
         <is>
-          <t>Average Hourly Earnings MoMFEB</t>
+          <t>Used Car Prices MoMFEB</t>
         </is>
       </c>
       <c r="C872" t="inlineStr"/>
       <c r="D872" t="inlineStr">
         <is>
-          <t>0.5%</t>
+          <t>0.4%</t>
         </is>
       </c>
       <c r="E872" t="inlineStr"/>
-      <c r="F872" t="inlineStr">
-        <is>
-          <t>0.3%</t>
-        </is>
-      </c>
+      <c r="F872" t="inlineStr"/>
       <c r="G872" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="873">
@@ -25083,19 +25079,23 @@
       </c>
       <c r="B876" t="inlineStr">
         <is>
-          <t>Used Car Prices MoMFEB</t>
+          <t>Participation RateFEB</t>
         </is>
       </c>
       <c r="C876" t="inlineStr"/>
       <c r="D876" t="inlineStr">
         <is>
-          <t>0.4%</t>
+          <t>62.6%</t>
         </is>
       </c>
       <c r="E876" t="inlineStr"/>
-      <c r="F876" t="inlineStr"/>
+      <c r="F876" t="inlineStr">
+        <is>
+          <t>62.6%</t>
+        </is>
+      </c>
       <c r="G876" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="877">
@@ -25214,19 +25214,19 @@
       </c>
       <c r="B881" t="inlineStr">
         <is>
-          <t>Participation RateFEB</t>
+          <t>Average Hourly Earnings YoYFEB</t>
         </is>
       </c>
       <c r="C881" t="inlineStr"/>
       <c r="D881" t="inlineStr">
         <is>
-          <t>62.6%</t>
+          <t>4.1%</t>
         </is>
       </c>
       <c r="E881" t="inlineStr"/>
       <c r="F881" t="inlineStr">
         <is>
-          <t>62.6%</t>
+          <t>4.1%</t>
         </is>
       </c>
       <c r="G881" t="n">

--- a/Input_data/IST_US_trad_eco_cal_2025-01-01_to_2025-03-09.xlsx
+++ b/Input_data/IST_US_trad_eco_cal_2025-01-01_to_2025-03-09.xlsx
@@ -806,17 +806,17 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>EIA Crude Oil Imports ChangeDEC/27</t>
+          <t>EIA Gasoline Production ChangeDEC/27</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>0.323M</t>
+          <t>-0.959M</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>0.995M</t>
+          <t>0.051M</t>
         </is>
       </c>
       <c r="E13" t="inlineStr"/>
@@ -833,24 +833,20 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>EIA Distillate Stocks ChangeDEC/27</t>
+          <t>EIA Distillate Fuel Production ChangeDEC/27</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>6.406M</t>
+          <t>0.099M</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>-1.694M</t>
-        </is>
-      </c>
-      <c r="E14" t="inlineStr">
-        <is>
-          <t>-0.1M</t>
-        </is>
-      </c>
+          <t>0.178M</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr"/>
       <c r="F14" t="inlineStr"/>
       <c r="G14" t="n">
         <v>3</v>
@@ -864,23 +860,27 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>EIA Refinery Crude Runs ChangeDEC/27</t>
+          <t>EIA Crude Oil Stocks ChangeDEC/27</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>0.041M</t>
+          <t>-1.178M</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>0.205M</t>
-        </is>
-      </c>
-      <c r="E15" t="inlineStr"/>
+          <t>-4.237M</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>-2.75M</t>
+        </is>
+      </c>
       <c r="F15" t="inlineStr"/>
       <c r="G15" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="16">
@@ -891,27 +891,23 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>EIA Gasoline Stocks ChangeDEC/27</t>
+          <t>EIA Heating Oil Stocks ChangeDEC/27</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>7.717M</t>
+          <t>-0.416M</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>1.63M</t>
-        </is>
-      </c>
-      <c r="E16" t="inlineStr">
-        <is>
-          <t>0.7M</t>
-        </is>
-      </c>
+          <t>-0.062M</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr"/>
       <c r="F16" t="inlineStr"/>
       <c r="G16" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="17">
@@ -922,17 +918,17 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>EIA Cushing Crude Oil Stocks ChangeDEC/27</t>
+          <t>EIA Refinery Crude Runs ChangeDEC/27</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>-0.142M</t>
+          <t>0.041M</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>-0.32M</t>
+          <t>0.205M</t>
         </is>
       </c>
       <c r="E17" t="inlineStr"/>
@@ -949,23 +945,27 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>EIA Heating Oil Stocks ChangeDEC/27</t>
+          <t>EIA Gasoline Stocks ChangeDEC/27</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>-0.416M</t>
+          <t>7.717M</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>-0.062M</t>
-        </is>
-      </c>
-      <c r="E18" t="inlineStr"/>
+          <t>1.63M</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>0.7M</t>
+        </is>
+      </c>
       <c r="F18" t="inlineStr"/>
       <c r="G18" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="19">
@@ -976,27 +976,27 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>EIA Crude Oil Stocks ChangeDEC/27</t>
+          <t>EIA Distillate Stocks ChangeDEC/27</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>-1.178M</t>
+          <t>6.406M</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>-4.237M</t>
+          <t>-1.694M</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>-2.75M</t>
+          <t>-0.1M</t>
         </is>
       </c>
       <c r="F19" t="inlineStr"/>
       <c r="G19" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="20">
@@ -1007,17 +1007,17 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>EIA Distillate Fuel Production ChangeDEC/27</t>
+          <t>EIA Crude Oil Imports ChangeDEC/27</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>0.099M</t>
+          <t>0.323M</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>0.178M</t>
+          <t>0.995M</t>
         </is>
       </c>
       <c r="E20" t="inlineStr"/>
@@ -1034,17 +1034,17 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>EIA Gasoline Production ChangeDEC/27</t>
+          <t>EIA Cushing Crude Oil Stocks ChangeDEC/27</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>-0.959M</t>
+          <t>-0.142M</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>0.051M</t>
+          <t>-0.32M</t>
         </is>
       </c>
       <c r="E21" t="inlineStr"/>
@@ -1223,31 +1223,31 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>ISM Manufacturing PricesDEC</t>
+          <t>ISM Manufacturing PMIDEC</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>52.5</t>
+          <t>49.3</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>50.3</t>
+          <t>48.4</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>51.7</t>
+          <t>48.4</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>50.4</t>
+          <t>48.5</t>
         </is>
       </c>
       <c r="G28" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="29">
@@ -1258,27 +1258,31 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>ISM Manufacturing New OrdersDEC</t>
+          <t>ISM Manufacturing EmploymentDEC</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>52.5</t>
+          <t>45.3</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>50.4</t>
-        </is>
-      </c>
-      <c r="E29" t="inlineStr"/>
+          <t>48.1</t>
+        </is>
+      </c>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t>48</t>
+        </is>
+      </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>50.5</t>
+          <t>48.3</t>
         </is>
       </c>
       <c r="G29" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="30">
@@ -1289,31 +1293,27 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>ISM Manufacturing EmploymentDEC</t>
+          <t>ISM Manufacturing New OrdersDEC</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>45.3</t>
+          <t>52.5</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>48.1</t>
-        </is>
-      </c>
-      <c r="E30" t="inlineStr">
-        <is>
-          <t>48</t>
-        </is>
-      </c>
+          <t>50.4</t>
+        </is>
+      </c>
+      <c r="E30" t="inlineStr"/>
       <c r="F30" t="inlineStr">
         <is>
-          <t>48.3</t>
+          <t>50.5</t>
         </is>
       </c>
       <c r="G30" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="31">
@@ -1324,31 +1324,31 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>ISM Manufacturing PMIDEC</t>
+          <t>ISM Manufacturing PricesDEC</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>49.3</t>
+          <t>52.5</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>48.4</t>
+          <t>50.3</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>48.4</t>
+          <t>51.7</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>48.5</t>
+          <t>50.4</t>
         </is>
       </c>
       <c r="G31" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="32">
@@ -1609,27 +1609,31 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>Factory Orders ex TransportationNOV</t>
+          <t>Factory Orders MoMNOV</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>0.2%</t>
+          <t>-0.4%</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>0.2%</t>
-        </is>
-      </c>
-      <c r="E42" t="inlineStr"/>
+          <t>0.5%</t>
+        </is>
+      </c>
+      <c r="E42" t="inlineStr">
+        <is>
+          <t>-0.3%</t>
+        </is>
+      </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>0.2%</t>
+          <t>0.3%</t>
         </is>
       </c>
       <c r="G42" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="43">
@@ -1640,31 +1644,27 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>Factory Orders MoMNOV</t>
+          <t>Factory Orders ex TransportationNOV</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>-0.4%</t>
+          <t>0.2%</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>0.5%</t>
-        </is>
-      </c>
-      <c r="E43" t="inlineStr">
-        <is>
-          <t>-0.3%</t>
-        </is>
-      </c>
+          <t>0.2%</t>
+        </is>
+      </c>
+      <c r="E43" t="inlineStr"/>
       <c r="F43" t="inlineStr">
         <is>
-          <t>0.3%</t>
+          <t>0.2%</t>
         </is>
       </c>
       <c r="G43" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="44">
@@ -1949,27 +1949,31 @@
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>ISM Services Business ActivityDEC</t>
+          <t>ISM Services PMIDEC</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>58.2</t>
+          <t>54.1</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>53.7</t>
-        </is>
-      </c>
-      <c r="E54" t="inlineStr"/>
+          <t>52.1</t>
+        </is>
+      </c>
+      <c r="E54" t="inlineStr">
+        <is>
+          <t>53.3</t>
+        </is>
+      </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>54.1</t>
+          <t>54</t>
         </is>
       </c>
       <c r="G54" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="55">
@@ -1980,27 +1984,23 @@
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>ISM Services EmploymentDEC</t>
+          <t>JOLTs Job QuitsNOV</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>51.4</t>
+          <t>3.065M</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>51.5</t>
-        </is>
-      </c>
-      <c r="E55" t="inlineStr">
-        <is>
-          <t>51.4</t>
-        </is>
-      </c>
+          <t>3.283M</t>
+        </is>
+      </c>
+      <c r="E55" t="inlineStr"/>
       <c r="F55" t="inlineStr">
         <is>
-          <t>52</t>
+          <t>3.31M</t>
         </is>
       </c>
       <c r="G55" t="n">
@@ -2015,31 +2015,31 @@
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>JOLTs Job OpeningsNOV</t>
+          <t>ISM Services PricesDEC</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>8.098M</t>
+          <t>64.4</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>7.839M</t>
+          <t>58.2</t>
         </is>
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>7.70M</t>
+          <t>57.5</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>7.69M</t>
+          <t>58.4</t>
         </is>
       </c>
       <c r="G56" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="57">
@@ -2050,27 +2050,27 @@
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>ISM Services PricesDEC</t>
+          <t>ISM Services New OrdersDEC</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>64.4</t>
+          <t>54.2</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>58.2</t>
+          <t>53.7</t>
         </is>
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>57.5</t>
+          <t>54.2</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>58.4</t>
+          <t>54.1</t>
         </is>
       </c>
       <c r="G57" t="n">
@@ -2085,31 +2085,31 @@
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>ISM Services New OrdersDEC</t>
+          <t>JOLTs Job OpeningsNOV</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>54.2</t>
+          <t>8.098M</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>53.7</t>
+          <t>7.839M</t>
         </is>
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>54.2</t>
+          <t>7.70M</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>54.1</t>
+          <t>7.69M</t>
         </is>
       </c>
       <c r="G58" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="59">
@@ -2120,31 +2120,31 @@
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>ISM Services PMIDEC</t>
+          <t>ISM Services EmploymentDEC</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>54.1</t>
+          <t>51.4</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>52.1</t>
+          <t>51.5</t>
         </is>
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>53.3</t>
+          <t>51.4</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>54</t>
+          <t>52</t>
         </is>
       </c>
       <c r="G59" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="60">
@@ -2155,23 +2155,23 @@
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>JOLTs Job QuitsNOV</t>
+          <t>ISM Services Business ActivityDEC</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>3.065M</t>
+          <t>58.2</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>3.283M</t>
+          <t>53.7</t>
         </is>
       </c>
       <c r="E60" t="inlineStr"/>
       <c r="F60" t="inlineStr">
         <is>
-          <t>3.31M</t>
+          <t>54.1</t>
         </is>
       </c>
       <c r="G60" t="n">
@@ -2271,17 +2271,17 @@
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>MBA Purchase IndexJAN/03</t>
+          <t>MBA Mortgage Refinance IndexJAN/03</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>127.7</t>
+          <t>401.1</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>136.7</t>
+          <t>395.1</t>
         </is>
       </c>
       <c r="E64" t="inlineStr"/>
@@ -2298,17 +2298,17 @@
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>MBA Mortgage Market IndexJAN/03</t>
+          <t>MBA Mortgage ApplicationsJAN/03</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>168.4</t>
+          <t>-3.7%</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>174.9</t>
+          <t>-12.6%</t>
         </is>
       </c>
       <c r="E65" t="inlineStr"/>
@@ -2325,23 +2325,23 @@
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>MBA Mortgage ApplicationsJAN/03</t>
+          <t>MBA 30-Year Mortgage RateJAN/03</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>-3.7%</t>
+          <t>6.99%</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>-12.6%</t>
+          <t>6.97%</t>
         </is>
       </c>
       <c r="E66" t="inlineStr"/>
       <c r="F66" t="inlineStr"/>
       <c r="G66" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="67">
@@ -2352,17 +2352,17 @@
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>MBA Mortgage Refinance IndexJAN/03</t>
+          <t>MBA Purchase IndexJAN/03</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>401.1</t>
+          <t>127.7</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>395.1</t>
+          <t>136.7</t>
         </is>
       </c>
       <c r="E67" t="inlineStr"/>
@@ -2379,23 +2379,23 @@
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>MBA 30-Year Mortgage RateJAN/03</t>
+          <t>MBA Mortgage Market IndexJAN/03</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>6.99%</t>
+          <t>168.4</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>6.97%</t>
+          <t>174.9</t>
         </is>
       </c>
       <c r="E68" t="inlineStr"/>
       <c r="F68" t="inlineStr"/>
       <c r="G68" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="69">
@@ -2685,24 +2685,20 @@
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>EIA Distillate Stocks ChangeJAN/03</t>
+          <t>EIA Distillate Fuel Production ChangeJAN/03</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>6.071M</t>
+          <t>-0.167M</t>
         </is>
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>6.406M</t>
-        </is>
-      </c>
-      <c r="E78" t="inlineStr">
-        <is>
-          <t>1M</t>
-        </is>
-      </c>
+          <t>0.099M</t>
+        </is>
+      </c>
+      <c r="E78" t="inlineStr"/>
       <c r="F78" t="inlineStr"/>
       <c r="G78" t="n">
         <v>3</v>
@@ -2716,17 +2712,17 @@
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>EIA Gasoline Production ChangeJAN/03</t>
+          <t>EIA Crude Oil Imports ChangeJAN/03</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>-0.081M</t>
+          <t>0.278M</t>
         </is>
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>-0.959M</t>
+          <t>0.323M</t>
         </is>
       </c>
       <c r="E79" t="inlineStr"/>
@@ -2743,23 +2739,27 @@
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>EIA Heating Oil Stocks ChangeJAN/03</t>
+          <t>EIA Crude Oil Stocks ChangeJAN/03</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>-0.632M</t>
+          <t>-0.959M</t>
         </is>
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>-0.416M</t>
-        </is>
-      </c>
-      <c r="E80" t="inlineStr"/>
+          <t>-1.178M</t>
+        </is>
+      </c>
+      <c r="E80" t="inlineStr">
+        <is>
+          <t>-0.6M</t>
+        </is>
+      </c>
       <c r="F80" t="inlineStr"/>
       <c r="G80" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="81">
@@ -2770,27 +2770,23 @@
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>EIA Gasoline Stocks ChangeJAN/03</t>
+          <t>EIA Cushing Crude Oil Stocks ChangeJAN/03</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>6.33M</t>
+          <t>-2.502M</t>
         </is>
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>7.717M</t>
-        </is>
-      </c>
-      <c r="E81" t="inlineStr">
-        <is>
-          <t>1.5M</t>
-        </is>
-      </c>
+          <t>-0.142M</t>
+        </is>
+      </c>
+      <c r="E81" t="inlineStr"/>
       <c r="F81" t="inlineStr"/>
       <c r="G81" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="82">
@@ -2801,17 +2797,17 @@
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>EIA Cushing Crude Oil Stocks ChangeJAN/03</t>
+          <t>EIA Refinery Crude Runs ChangeJAN/03</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>-2.502M</t>
+          <t>0.045M</t>
         </is>
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>-0.142M</t>
+          <t>0.041M</t>
         </is>
       </c>
       <c r="E82" t="inlineStr"/>
@@ -2828,27 +2824,23 @@
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>EIA Crude Oil Stocks ChangeJAN/03</t>
+          <t>EIA Heating Oil Stocks ChangeJAN/03</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>-0.959M</t>
+          <t>-0.632M</t>
         </is>
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>-1.178M</t>
-        </is>
-      </c>
-      <c r="E83" t="inlineStr">
-        <is>
-          <t>-0.6M</t>
-        </is>
-      </c>
+          <t>-0.416M</t>
+        </is>
+      </c>
+      <c r="E83" t="inlineStr"/>
       <c r="F83" t="inlineStr"/>
       <c r="G83" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="84">
@@ -2859,17 +2851,17 @@
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>EIA Distillate Fuel Production ChangeJAN/03</t>
+          <t>EIA Gasoline Production ChangeJAN/03</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>-0.167M</t>
+          <t>-0.081M</t>
         </is>
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>0.099M</t>
+          <t>-0.959M</t>
         </is>
       </c>
       <c r="E84" t="inlineStr"/>
@@ -2886,23 +2878,27 @@
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>EIA Refinery Crude Runs ChangeJAN/03</t>
+          <t>EIA Gasoline Stocks ChangeJAN/03</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>0.045M</t>
+          <t>6.33M</t>
         </is>
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>0.041M</t>
-        </is>
-      </c>
-      <c r="E85" t="inlineStr"/>
+          <t>7.717M</t>
+        </is>
+      </c>
+      <c r="E85" t="inlineStr">
+        <is>
+          <t>1.5M</t>
+        </is>
+      </c>
       <c r="F85" t="inlineStr"/>
       <c r="G85" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="86">
@@ -2913,20 +2909,24 @@
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>EIA Crude Oil Imports ChangeJAN/03</t>
+          <t>EIA Distillate Stocks ChangeJAN/03</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>0.278M</t>
+          <t>6.071M</t>
         </is>
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>0.323M</t>
-        </is>
-      </c>
-      <c r="E86" t="inlineStr"/>
+          <t>6.406M</t>
+        </is>
+      </c>
+      <c r="E86" t="inlineStr">
+        <is>
+          <t>1M</t>
+        </is>
+      </c>
       <c r="F86" t="inlineStr"/>
       <c r="G86" t="n">
         <v>3</v>
@@ -3171,17 +3171,17 @@
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>4-Week Bill Auction</t>
+          <t>8-Week Bill Auction</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>4.245%</t>
+          <t>4.240%</t>
         </is>
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>4.265%</t>
+          <t>4.240%</t>
         </is>
       </c>
       <c r="E96" t="inlineStr"/>
@@ -3198,17 +3198,17 @@
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>8-Week Bill Auction</t>
+          <t>4-Week Bill Auction</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>4.240%</t>
+          <t>4.245%</t>
         </is>
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>4.240%</t>
+          <t>4.265%</t>
         </is>
       </c>
       <c r="E97" t="inlineStr"/>
@@ -3336,27 +3336,23 @@
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>Average Weekly HoursDEC</t>
+          <t>U-6 Unemployment Rate</t>
         </is>
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>34.3</t>
+          <t>7.5%</t>
         </is>
       </c>
       <c r="D103" t="inlineStr">
         <is>
-          <t>34.3</t>
-        </is>
-      </c>
-      <c r="E103" t="inlineStr">
-        <is>
-          <t>34.3</t>
-        </is>
-      </c>
+          <t>7.7%</t>
+        </is>
+      </c>
+      <c r="E103" t="inlineStr"/>
       <c r="F103" t="inlineStr">
         <is>
-          <t>34.3</t>
+          <t>7.9%</t>
         </is>
       </c>
       <c r="G103" t="n">
@@ -3371,23 +3367,27 @@
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>Government PayrollsDEC</t>
+          <t>Average Weekly HoursDEC</t>
         </is>
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>33K</t>
+          <t>34.3</t>
         </is>
       </c>
       <c r="D104" t="inlineStr">
         <is>
-          <t>30K</t>
-        </is>
-      </c>
-      <c r="E104" t="inlineStr"/>
+          <t>34.3</t>
+        </is>
+      </c>
+      <c r="E104" t="inlineStr">
+        <is>
+          <t>34.3</t>
+        </is>
+      </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>15K</t>
+          <t>34.3</t>
         </is>
       </c>
       <c r="G104" t="n">
@@ -3402,27 +3402,23 @@
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>Nonfarm Payrolls PrivateDEC</t>
+          <t>Government PayrollsDEC</t>
         </is>
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>223K</t>
+          <t>33K</t>
         </is>
       </c>
       <c r="D105" t="inlineStr">
         <is>
-          <t>182K</t>
-        </is>
-      </c>
-      <c r="E105" t="inlineStr">
-        <is>
-          <t>135K</t>
-        </is>
-      </c>
+          <t>30K</t>
+        </is>
+      </c>
+      <c r="E105" t="inlineStr"/>
       <c r="F105" t="inlineStr">
         <is>
-          <t>185K</t>
+          <t>15K</t>
         </is>
       </c>
       <c r="G105" t="n">
@@ -3437,27 +3433,27 @@
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>Manufacturing PayrollsDEC</t>
+          <t>Nonfarm Payrolls PrivateDEC</t>
         </is>
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>-13K</t>
+          <t>223K</t>
         </is>
       </c>
       <c r="D106" t="inlineStr">
         <is>
-          <t>25K</t>
+          <t>182K</t>
         </is>
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>5K</t>
+          <t>135K</t>
         </is>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>29K</t>
+          <t>185K</t>
         </is>
       </c>
       <c r="G106" t="n">
@@ -3472,27 +3468,31 @@
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>Participation RateDEC</t>
+          <t>Manufacturing PayrollsDEC</t>
         </is>
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>62.5%</t>
+          <t>-13K</t>
         </is>
       </c>
       <c r="D107" t="inlineStr">
         <is>
-          <t>62.5%</t>
-        </is>
-      </c>
-      <c r="E107" t="inlineStr"/>
+          <t>25K</t>
+        </is>
+      </c>
+      <c r="E107" t="inlineStr">
+        <is>
+          <t>5K</t>
+        </is>
+      </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>62.8%</t>
+          <t>29K</t>
         </is>
       </c>
       <c r="G107" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="108">
@@ -3503,31 +3503,27 @@
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>Non Farm PayrollsDEC</t>
+          <t>Participation RateDEC</t>
         </is>
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>256K</t>
+          <t>62.5%</t>
         </is>
       </c>
       <c r="D108" t="inlineStr">
         <is>
-          <t>212K</t>
-        </is>
-      </c>
-      <c r="E108" t="inlineStr">
-        <is>
-          <t>160K</t>
-        </is>
-      </c>
+          <t>62.5%</t>
+        </is>
+      </c>
+      <c r="E108" t="inlineStr"/>
       <c r="F108" t="inlineStr">
         <is>
-          <t>200K</t>
+          <t>62.8%</t>
         </is>
       </c>
       <c r="G108" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="109">
@@ -3538,31 +3534,31 @@
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>Average Hourly Earnings YoY</t>
+          <t>Non Farm PayrollsDEC</t>
         </is>
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>3.9%</t>
+          <t>256K</t>
         </is>
       </c>
       <c r="D109" t="inlineStr">
         <is>
-          <t>4%</t>
+          <t>212K</t>
         </is>
       </c>
       <c r="E109" t="inlineStr">
         <is>
-          <t>4%</t>
+          <t>160K</t>
         </is>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>4%</t>
+          <t>200K</t>
         </is>
       </c>
       <c r="G109" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="110">
@@ -3573,27 +3569,27 @@
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>Average Hourly Earnings MoMDEC</t>
+          <t>Average Hourly Earnings YoY</t>
         </is>
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>0.3%</t>
+          <t>3.9%</t>
         </is>
       </c>
       <c r="D110" t="inlineStr">
         <is>
-          <t>0.4%</t>
+          <t>4%</t>
         </is>
       </c>
       <c r="E110" t="inlineStr">
         <is>
-          <t>0.3%</t>
+          <t>4%</t>
         </is>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>0.3%</t>
+          <t>4%</t>
         </is>
       </c>
       <c r="G110" t="n">
@@ -3608,27 +3604,31 @@
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>U-6 Unemployment Rate</t>
+          <t>Average Hourly Earnings MoMDEC</t>
         </is>
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>7.5%</t>
+          <t>0.3%</t>
         </is>
       </c>
       <c r="D111" t="inlineStr">
         <is>
-          <t>7.7%</t>
-        </is>
-      </c>
-      <c r="E111" t="inlineStr"/>
+          <t>0.4%</t>
+        </is>
+      </c>
+      <c r="E111" t="inlineStr">
+        <is>
+          <t>0.3%</t>
+        </is>
+      </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>7.9%</t>
+          <t>0.3%</t>
         </is>
       </c>
       <c r="G111" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="112">
@@ -3674,23 +3674,23 @@
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>Michigan Current Conditions PrelJAN</t>
+          <t>Michigan Inflation Expectations PrelJAN</t>
         </is>
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>77.9</t>
+          <t>3.3%</t>
         </is>
       </c>
       <c r="D113" t="inlineStr">
         <is>
-          <t>75.1</t>
+          <t>2.8%</t>
         </is>
       </c>
       <c r="E113" t="inlineStr"/>
       <c r="F113" t="inlineStr">
         <is>
-          <t>78</t>
+          <t>3.0%</t>
         </is>
       </c>
       <c r="G113" t="n">
@@ -3705,23 +3705,23 @@
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>Michigan Consumer Expectations PrelJAN</t>
+          <t>Michigan 5 Year Inflation Expectations PrelJAN</t>
         </is>
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>70.2</t>
+          <t>3.3%</t>
         </is>
       </c>
       <c r="D114" t="inlineStr">
         <is>
-          <t>73.3</t>
+          <t>3%</t>
         </is>
       </c>
       <c r="E114" t="inlineStr"/>
       <c r="F114" t="inlineStr">
         <is>
-          <t>74</t>
+          <t>3.2%</t>
         </is>
       </c>
       <c r="G114" t="n">
@@ -3736,31 +3736,27 @@
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>Michigan Consumer Sentiment PrelJAN</t>
+          <t>Michigan Consumer Expectations PrelJAN</t>
         </is>
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>73.2</t>
+          <t>70.2</t>
         </is>
       </c>
       <c r="D115" t="inlineStr">
         <is>
-          <t>74.0</t>
-        </is>
-      </c>
-      <c r="E115" t="inlineStr">
-        <is>
-          <t>73.8</t>
-        </is>
-      </c>
+          <t>73.3</t>
+        </is>
+      </c>
+      <c r="E115" t="inlineStr"/>
       <c r="F115" t="inlineStr">
         <is>
-          <t>75</t>
+          <t>74</t>
         </is>
       </c>
       <c r="G115" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="116">
@@ -3771,23 +3767,23 @@
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t>Michigan 5 Year Inflation Expectations PrelJAN</t>
+          <t>Michigan Current Conditions PrelJAN</t>
         </is>
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>3.3%</t>
+          <t>77.9</t>
         </is>
       </c>
       <c r="D116" t="inlineStr">
         <is>
-          <t>3%</t>
+          <t>75.1</t>
         </is>
       </c>
       <c r="E116" t="inlineStr"/>
       <c r="F116" t="inlineStr">
         <is>
-          <t>3.2%</t>
+          <t>78</t>
         </is>
       </c>
       <c r="G116" t="n">
@@ -3802,27 +3798,31 @@
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t>Michigan Inflation Expectations PrelJAN</t>
+          <t>Michigan Consumer Sentiment PrelJAN</t>
         </is>
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>3.3%</t>
+          <t>73.2</t>
         </is>
       </c>
       <c r="D117" t="inlineStr">
         <is>
-          <t>2.8%</t>
-        </is>
-      </c>
-      <c r="E117" t="inlineStr"/>
+          <t>74.0</t>
+        </is>
+      </c>
+      <c r="E117" t="inlineStr">
+        <is>
+          <t>73.8</t>
+        </is>
+      </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>3.0%</t>
+          <t>75</t>
         </is>
       </c>
       <c r="G117" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="118">
@@ -4134,27 +4134,23 @@
       </c>
       <c r="B129" t="inlineStr">
         <is>
-          <t>PPI Ex Food, Energy and Trade MoMDEC</t>
+          <t>PPIDEC</t>
         </is>
       </c>
       <c r="C129" t="inlineStr">
         <is>
-          <t>0.1%</t>
+          <t>146.842</t>
         </is>
       </c>
       <c r="D129" t="inlineStr">
         <is>
-          <t>0.1%</t>
-        </is>
-      </c>
-      <c r="E129" t="inlineStr">
-        <is>
-          <t>0.3%</t>
-        </is>
-      </c>
+          <t>146.521</t>
+        </is>
+      </c>
+      <c r="E129" t="inlineStr"/>
       <c r="F129" t="inlineStr">
         <is>
-          <t>0.2%</t>
+          <t>146.8</t>
         </is>
       </c>
       <c r="G129" t="n">
@@ -4169,7 +4165,7 @@
       </c>
       <c r="B130" t="inlineStr">
         <is>
-          <t>PPI YoYDEC</t>
+          <t>PPI Ex Food, Energy and Trade YoYDEC</t>
         </is>
       </c>
       <c r="C130" t="inlineStr">
@@ -4179,17 +4175,13 @@
       </c>
       <c r="D130" t="inlineStr">
         <is>
-          <t>3%</t>
-        </is>
-      </c>
-      <c r="E130" t="inlineStr">
-        <is>
-          <t>3.4%</t>
-        </is>
-      </c>
+          <t>3.5%</t>
+        </is>
+      </c>
+      <c r="E130" t="inlineStr"/>
       <c r="F130" t="inlineStr">
         <is>
-          <t>3.3%</t>
+          <t>3.6%</t>
         </is>
       </c>
       <c r="G130" t="n">
@@ -4204,19 +4196,19 @@
       </c>
       <c r="B131" t="inlineStr">
         <is>
-          <t>PPI MoMDEC</t>
+          <t>Core PPI MoMDEC</t>
         </is>
       </c>
       <c r="C131" t="inlineStr">
         <is>
+          <t>0%</t>
+        </is>
+      </c>
+      <c r="D131" t="inlineStr">
+        <is>
           <t>0.2%</t>
         </is>
       </c>
-      <c r="D131" t="inlineStr">
-        <is>
-          <t>0.4%</t>
-        </is>
-      </c>
       <c r="E131" t="inlineStr">
         <is>
           <t>0.3%</t>
@@ -4224,11 +4216,11 @@
       </c>
       <c r="F131" t="inlineStr">
         <is>
-          <t>0.3%</t>
+          <t>0.2%</t>
         </is>
       </c>
       <c r="G131" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="132">
@@ -4239,27 +4231,27 @@
       </c>
       <c r="B132" t="inlineStr">
         <is>
-          <t>Core PPI YoYDEC</t>
+          <t>PPI YoYDEC</t>
         </is>
       </c>
       <c r="C132" t="inlineStr">
         <is>
-          <t>3.5%</t>
+          <t>3.3%</t>
         </is>
       </c>
       <c r="D132" t="inlineStr">
         <is>
-          <t>3.5%</t>
+          <t>3%</t>
         </is>
       </c>
       <c r="E132" t="inlineStr">
         <is>
-          <t>3.8%</t>
+          <t>3.4%</t>
         </is>
       </c>
       <c r="F132" t="inlineStr">
         <is>
-          <t>3.5%</t>
+          <t>3.3%</t>
         </is>
       </c>
       <c r="G132" t="n">
@@ -4274,17 +4266,17 @@
       </c>
       <c r="B133" t="inlineStr">
         <is>
-          <t>Core PPI MoMDEC</t>
+          <t>PPI MoMDEC</t>
         </is>
       </c>
       <c r="C133" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>0.2%</t>
         </is>
       </c>
       <c r="D133" t="inlineStr">
         <is>
-          <t>0.2%</t>
+          <t>0.4%</t>
         </is>
       </c>
       <c r="E133" t="inlineStr">
@@ -4294,11 +4286,11 @@
       </c>
       <c r="F133" t="inlineStr">
         <is>
-          <t>0.2%</t>
+          <t>0.3%</t>
         </is>
       </c>
       <c r="G133" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="134">
@@ -4309,23 +4301,27 @@
       </c>
       <c r="B134" t="inlineStr">
         <is>
-          <t>PPI Ex Food, Energy and Trade YoYDEC</t>
+          <t>PPI Ex Food, Energy and Trade MoMDEC</t>
         </is>
       </c>
       <c r="C134" t="inlineStr">
         <is>
-          <t>3.3%</t>
+          <t>0.1%</t>
         </is>
       </c>
       <c r="D134" t="inlineStr">
         <is>
-          <t>3.5%</t>
-        </is>
-      </c>
-      <c r="E134" t="inlineStr"/>
+          <t>0.1%</t>
+        </is>
+      </c>
+      <c r="E134" t="inlineStr">
+        <is>
+          <t>0.3%</t>
+        </is>
+      </c>
       <c r="F134" t="inlineStr">
         <is>
-          <t>3.6%</t>
+          <t>0.2%</t>
         </is>
       </c>
       <c r="G134" t="n">
@@ -4340,23 +4336,27 @@
       </c>
       <c r="B135" t="inlineStr">
         <is>
-          <t>PPIDEC</t>
+          <t>Core PPI YoYDEC</t>
         </is>
       </c>
       <c r="C135" t="inlineStr">
         <is>
-          <t>146.842</t>
+          <t>3.5%</t>
         </is>
       </c>
       <c r="D135" t="inlineStr">
         <is>
-          <t>146.521</t>
-        </is>
-      </c>
-      <c r="E135" t="inlineStr"/>
+          <t>3.5%</t>
+        </is>
+      </c>
+      <c r="E135" t="inlineStr">
+        <is>
+          <t>3.8%</t>
+        </is>
+      </c>
       <c r="F135" t="inlineStr">
         <is>
-          <t>146.8</t>
+          <t>3.5%</t>
         </is>
       </c>
       <c r="G135" t="n">
@@ -4564,23 +4564,23 @@
       </c>
       <c r="B143" t="inlineStr">
         <is>
-          <t>MBA 30-Year Mortgage RateJAN/10</t>
+          <t>MBA Mortgage Refinance IndexJAN/10</t>
         </is>
       </c>
       <c r="C143" t="inlineStr">
         <is>
-          <t>7.09%</t>
+          <t>575.6</t>
         </is>
       </c>
       <c r="D143" t="inlineStr">
         <is>
-          <t>6.99%</t>
+          <t>401.1000</t>
         </is>
       </c>
       <c r="E143" t="inlineStr"/>
       <c r="F143" t="inlineStr"/>
       <c r="G143" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="144">
@@ -4591,17 +4591,17 @@
       </c>
       <c r="B144" t="inlineStr">
         <is>
-          <t>MBA Mortgage ApplicationsJAN/10</t>
+          <t>MBA Purchase IndexJAN/10</t>
         </is>
       </c>
       <c r="C144" t="inlineStr">
         <is>
-          <t>33.3%</t>
+          <t>162</t>
         </is>
       </c>
       <c r="D144" t="inlineStr">
         <is>
-          <t>-3.7%</t>
+          <t>127.7000</t>
         </is>
       </c>
       <c r="E144" t="inlineStr"/>
@@ -4618,17 +4618,17 @@
       </c>
       <c r="B145" t="inlineStr">
         <is>
-          <t>MBA Purchase IndexJAN/10</t>
+          <t>MBA Mortgage Market IndexJAN/10</t>
         </is>
       </c>
       <c r="C145" t="inlineStr">
         <is>
-          <t>162</t>
+          <t>224.4</t>
         </is>
       </c>
       <c r="D145" t="inlineStr">
         <is>
-          <t>127.7000</t>
+          <t>168.4</t>
         </is>
       </c>
       <c r="E145" t="inlineStr"/>
@@ -4645,23 +4645,23 @@
       </c>
       <c r="B146" t="inlineStr">
         <is>
-          <t>MBA Mortgage Refinance IndexJAN/10</t>
+          <t>MBA 30-Year Mortgage RateJAN/10</t>
         </is>
       </c>
       <c r="C146" t="inlineStr">
         <is>
-          <t>575.6</t>
+          <t>7.09%</t>
         </is>
       </c>
       <c r="D146" t="inlineStr">
         <is>
-          <t>401.1000</t>
+          <t>6.99%</t>
         </is>
       </c>
       <c r="E146" t="inlineStr"/>
       <c r="F146" t="inlineStr"/>
       <c r="G146" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="147">
@@ -4672,17 +4672,17 @@
       </c>
       <c r="B147" t="inlineStr">
         <is>
-          <t>MBA Mortgage Market IndexJAN/10</t>
+          <t>MBA Mortgage ApplicationsJAN/10</t>
         </is>
       </c>
       <c r="C147" t="inlineStr">
         <is>
-          <t>224.4</t>
+          <t>33.3%</t>
         </is>
       </c>
       <c r="D147" t="inlineStr">
         <is>
-          <t>168.4</t>
+          <t>-3.7%</t>
         </is>
       </c>
       <c r="E147" t="inlineStr"/>
@@ -4978,17 +4978,17 @@
       </c>
       <c r="B157" t="inlineStr">
         <is>
-          <t>EIA Refinery Crude Runs ChangeJAN/10</t>
+          <t>EIA Gasoline Production ChangeJAN/10</t>
         </is>
       </c>
       <c r="C157" t="inlineStr">
         <is>
-          <t>-0.255M</t>
+          <t>0.397M</t>
         </is>
       </c>
       <c r="D157" t="inlineStr">
         <is>
-          <t>0.045M</t>
+          <t>-0.081M</t>
         </is>
       </c>
       <c r="E157" t="inlineStr"/>
@@ -5005,17 +5005,17 @@
       </c>
       <c r="B158" t="inlineStr">
         <is>
-          <t>EIA Distillate Fuel Production ChangeJAN/10</t>
+          <t>EIA Cushing Crude Oil Stocks ChangeJAN/10</t>
         </is>
       </c>
       <c r="C158" t="inlineStr">
         <is>
-          <t>-0.021M</t>
+          <t>0.765M</t>
         </is>
       </c>
       <c r="D158" t="inlineStr">
         <is>
-          <t>-0.167M</t>
+          <t>-2.502M</t>
         </is>
       </c>
       <c r="E158" t="inlineStr"/>
@@ -5032,22 +5032,22 @@
       </c>
       <c r="B159" t="inlineStr">
         <is>
-          <t>EIA Gasoline Stocks ChangeJAN/10</t>
+          <t>EIA Crude Oil Stocks ChangeJAN/10</t>
         </is>
       </c>
       <c r="C159" t="inlineStr">
         <is>
-          <t>5.852M</t>
+          <t>-1.961M</t>
         </is>
       </c>
       <c r="D159" t="inlineStr">
         <is>
-          <t>6.33M</t>
+          <t>-0.959M</t>
         </is>
       </c>
       <c r="E159" t="inlineStr">
         <is>
-          <t>2.60M</t>
+          <t>-1.6M</t>
         </is>
       </c>
       <c r="F159" t="inlineStr"/>
@@ -5063,20 +5063,24 @@
       </c>
       <c r="B160" t="inlineStr">
         <is>
-          <t>EIA Heating Oil Stocks ChangeJAN/10</t>
+          <t>EIA Distillate Stocks ChangeJAN/10</t>
         </is>
       </c>
       <c r="C160" t="inlineStr">
         <is>
-          <t>0.646M</t>
+          <t>3.077M</t>
         </is>
       </c>
       <c r="D160" t="inlineStr">
         <is>
-          <t>-0.632M</t>
-        </is>
-      </c>
-      <c r="E160" t="inlineStr"/>
+          <t>6.071M</t>
+        </is>
+      </c>
+      <c r="E160" t="inlineStr">
+        <is>
+          <t>1.1M</t>
+        </is>
+      </c>
       <c r="F160" t="inlineStr"/>
       <c r="G160" t="n">
         <v>3</v>
@@ -5090,17 +5094,17 @@
       </c>
       <c r="B161" t="inlineStr">
         <is>
-          <t>EIA Crude Oil Imports ChangeJAN/10</t>
+          <t>EIA Refinery Crude Runs ChangeJAN/10</t>
         </is>
       </c>
       <c r="C161" t="inlineStr">
         <is>
-          <t>-1.304M</t>
+          <t>-0.255M</t>
         </is>
       </c>
       <c r="D161" t="inlineStr">
         <is>
-          <t>0.278M</t>
+          <t>0.045M</t>
         </is>
       </c>
       <c r="E161" t="inlineStr"/>
@@ -5117,24 +5121,20 @@
       </c>
       <c r="B162" t="inlineStr">
         <is>
-          <t>EIA Distillate Stocks ChangeJAN/10</t>
+          <t>EIA Heating Oil Stocks ChangeJAN/10</t>
         </is>
       </c>
       <c r="C162" t="inlineStr">
         <is>
-          <t>3.077M</t>
+          <t>0.646M</t>
         </is>
       </c>
       <c r="D162" t="inlineStr">
         <is>
-          <t>6.071M</t>
-        </is>
-      </c>
-      <c r="E162" t="inlineStr">
-        <is>
-          <t>1.1M</t>
-        </is>
-      </c>
+          <t>-0.632M</t>
+        </is>
+      </c>
+      <c r="E162" t="inlineStr"/>
       <c r="F162" t="inlineStr"/>
       <c r="G162" t="n">
         <v>3</v>
@@ -5148,22 +5148,22 @@
       </c>
       <c r="B163" t="inlineStr">
         <is>
-          <t>EIA Crude Oil Stocks ChangeJAN/10</t>
+          <t>EIA Gasoline Stocks ChangeJAN/10</t>
         </is>
       </c>
       <c r="C163" t="inlineStr">
         <is>
-          <t>-1.961M</t>
+          <t>5.852M</t>
         </is>
       </c>
       <c r="D163" t="inlineStr">
         <is>
-          <t>-0.959M</t>
+          <t>6.33M</t>
         </is>
       </c>
       <c r="E163" t="inlineStr">
         <is>
-          <t>-1.6M</t>
+          <t>2.60M</t>
         </is>
       </c>
       <c r="F163" t="inlineStr"/>
@@ -5179,17 +5179,17 @@
       </c>
       <c r="B164" t="inlineStr">
         <is>
-          <t>EIA Cushing Crude Oil Stocks ChangeJAN/10</t>
+          <t>EIA Distillate Fuel Production ChangeJAN/10</t>
         </is>
       </c>
       <c r="C164" t="inlineStr">
         <is>
-          <t>0.765M</t>
+          <t>-0.021M</t>
         </is>
       </c>
       <c r="D164" t="inlineStr">
         <is>
-          <t>-2.502M</t>
+          <t>-0.167M</t>
         </is>
       </c>
       <c r="E164" t="inlineStr"/>
@@ -5206,17 +5206,17 @@
       </c>
       <c r="B165" t="inlineStr">
         <is>
-          <t>EIA Gasoline Production ChangeJAN/10</t>
+          <t>EIA Crude Oil Imports ChangeJAN/10</t>
         </is>
       </c>
       <c r="C165" t="inlineStr">
         <is>
-          <t>0.397M</t>
+          <t>-1.304M</t>
         </is>
       </c>
       <c r="D165" t="inlineStr">
         <is>
-          <t>-0.081M</t>
+          <t>0.278M</t>
         </is>
       </c>
       <c r="E165" t="inlineStr"/>
@@ -5336,29 +5336,21 @@
       </c>
       <c r="B171" t="inlineStr">
         <is>
-          <t>Retail Sales Ex Gas/Autos MoMDEC</t>
+          <t>Philly Fed New OrdersJAN</t>
         </is>
       </c>
       <c r="C171" t="inlineStr">
         <is>
-          <t>0.3%</t>
+          <t>42.9</t>
         </is>
       </c>
       <c r="D171" t="inlineStr">
         <is>
-          <t>0.2%</t>
-        </is>
-      </c>
-      <c r="E171" t="inlineStr">
-        <is>
-          <t>0.4%</t>
-        </is>
-      </c>
-      <c r="F171" t="inlineStr">
-        <is>
-          <t>0.4%</t>
-        </is>
-      </c>
+          <t>-3.6</t>
+        </is>
+      </c>
+      <c r="E171" t="inlineStr"/>
+      <c r="F171" t="inlineStr"/>
       <c r="G171" t="n">
         <v>3</v>
       </c>
@@ -5371,27 +5363,23 @@
       </c>
       <c r="B172" t="inlineStr">
         <is>
-          <t>Continuing Jobless ClaimsJAN/04</t>
+          <t>Jobless Claims 4-week AverageJAN/11</t>
         </is>
       </c>
       <c r="C172" t="inlineStr">
         <is>
-          <t>1859K</t>
+          <t>212.75K</t>
         </is>
       </c>
       <c r="D172" t="inlineStr">
         <is>
-          <t>1867K</t>
-        </is>
-      </c>
-      <c r="E172" t="inlineStr">
-        <is>
-          <t>1870K</t>
-        </is>
-      </c>
+          <t>213.5K</t>
+        </is>
+      </c>
+      <c r="E172" t="inlineStr"/>
       <c r="F172" t="inlineStr">
         <is>
-          <t>1870.0K</t>
+          <t>215.0K</t>
         </is>
       </c>
       <c r="G172" t="n">
@@ -5406,27 +5394,31 @@
       </c>
       <c r="B173" t="inlineStr">
         <is>
-          <t>Retail Sales YoYDEC</t>
+          <t>Import Prices MoMDEC</t>
         </is>
       </c>
       <c r="C173" t="inlineStr">
         <is>
-          <t>3.9%</t>
+          <t>0.1%</t>
         </is>
       </c>
       <c r="D173" t="inlineStr">
         <is>
-          <t>4.1%</t>
-        </is>
-      </c>
-      <c r="E173" t="inlineStr"/>
+          <t>0.1%</t>
+        </is>
+      </c>
+      <c r="E173" t="inlineStr">
+        <is>
+          <t>0.1%</t>
+        </is>
+      </c>
       <c r="F173" t="inlineStr">
         <is>
-          <t>4.0%</t>
+          <t>0.1%</t>
         </is>
       </c>
       <c r="G173" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="174">
@@ -5437,27 +5429,23 @@
       </c>
       <c r="B174" t="inlineStr">
         <is>
-          <t>Import Prices YoYDEC</t>
+          <t>Export Prices YoYDEC</t>
         </is>
       </c>
       <c r="C174" t="inlineStr">
         <is>
-          <t>2.2%</t>
+          <t>1.8%</t>
         </is>
       </c>
       <c r="D174" t="inlineStr">
         <is>
-          <t>1.4%</t>
-        </is>
-      </c>
-      <c r="E174" t="inlineStr">
-        <is>
-          <t>2.1%</t>
-        </is>
-      </c>
+          <t>0.9%</t>
+        </is>
+      </c>
+      <c r="E174" t="inlineStr"/>
       <c r="F174" t="inlineStr">
         <is>
-          <t>1.6%</t>
+          <t>1.9%</t>
         </is>
       </c>
       <c r="G174" t="n">
@@ -5472,27 +5460,27 @@
       </c>
       <c r="B175" t="inlineStr">
         <is>
-          <t>Retail Sales Ex Autos MoMDEC</t>
+          <t>Philadelphia Fed Manufacturing IndexJAN</t>
         </is>
       </c>
       <c r="C175" t="inlineStr">
         <is>
-          <t>0.4%</t>
+          <t>44.3</t>
         </is>
       </c>
       <c r="D175" t="inlineStr">
         <is>
-          <t>0.2%</t>
+          <t>-10.9</t>
         </is>
       </c>
       <c r="E175" t="inlineStr">
         <is>
-          <t>0.4%</t>
+          <t>-5</t>
         </is>
       </c>
       <c r="F175" t="inlineStr">
         <is>
-          <t>0.4%</t>
+          <t>-10</t>
         </is>
       </c>
       <c r="G175" t="n">
@@ -5507,23 +5495,31 @@
       </c>
       <c r="B176" t="inlineStr">
         <is>
-          <t>Philly Fed Business ConditionsJAN</t>
+          <t>Retail Sales MoMDEC</t>
         </is>
       </c>
       <c r="C176" t="inlineStr">
         <is>
-          <t>46.3</t>
+          <t>0.4%</t>
         </is>
       </c>
       <c r="D176" t="inlineStr">
         <is>
-          <t>33.8</t>
-        </is>
-      </c>
-      <c r="E176" t="inlineStr"/>
-      <c r="F176" t="inlineStr"/>
+          <t>0.8%</t>
+        </is>
+      </c>
+      <c r="E176" t="inlineStr">
+        <is>
+          <t>0.6%</t>
+        </is>
+      </c>
+      <c r="F176" t="inlineStr">
+        <is>
+          <t>0.5%</t>
+        </is>
+      </c>
       <c r="G176" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="177">
@@ -5534,17 +5530,17 @@
       </c>
       <c r="B177" t="inlineStr">
         <is>
-          <t>Philly Fed Prices PaidJAN</t>
+          <t>Philly Fed EmploymentJAN</t>
         </is>
       </c>
       <c r="C177" t="inlineStr">
         <is>
-          <t>31.90</t>
+          <t>11.9</t>
         </is>
       </c>
       <c r="D177" t="inlineStr">
         <is>
-          <t>26.60</t>
+          <t>4.8</t>
         </is>
       </c>
       <c r="E177" t="inlineStr"/>
@@ -5561,27 +5557,27 @@
       </c>
       <c r="B178" t="inlineStr">
         <is>
-          <t>Export Prices MoMDEC</t>
+          <t>Initial Jobless ClaimsJAN/11</t>
         </is>
       </c>
       <c r="C178" t="inlineStr">
         <is>
-          <t>0.3%</t>
+          <t>217K</t>
         </is>
       </c>
       <c r="D178" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>203K</t>
         </is>
       </c>
       <c r="E178" t="inlineStr">
         <is>
-          <t>0.2%</t>
+          <t>210K</t>
         </is>
       </c>
       <c r="F178" t="inlineStr">
         <is>
-          <t>0.5%</t>
+          <t>209.0K</t>
         </is>
       </c>
       <c r="G178" t="n">
@@ -5596,21 +5592,29 @@
       </c>
       <c r="B179" t="inlineStr">
         <is>
-          <t>Philly Fed CAPEX IndexJAN</t>
+          <t>Retail Sales Ex Gas/Autos MoMDEC</t>
         </is>
       </c>
       <c r="C179" t="inlineStr">
         <is>
-          <t>39.00</t>
+          <t>0.3%</t>
         </is>
       </c>
       <c r="D179" t="inlineStr">
         <is>
-          <t>22.20</t>
-        </is>
-      </c>
-      <c r="E179" t="inlineStr"/>
-      <c r="F179" t="inlineStr"/>
+          <t>0.2%</t>
+        </is>
+      </c>
+      <c r="E179" t="inlineStr">
+        <is>
+          <t>0.4%</t>
+        </is>
+      </c>
+      <c r="F179" t="inlineStr">
+        <is>
+          <t>0.4%</t>
+        </is>
+      </c>
       <c r="G179" t="n">
         <v>3</v>
       </c>
@@ -5623,27 +5627,27 @@
       </c>
       <c r="B180" t="inlineStr">
         <is>
-          <t>Initial Jobless ClaimsJAN/11</t>
+          <t>Export Prices MoMDEC</t>
         </is>
       </c>
       <c r="C180" t="inlineStr">
         <is>
-          <t>217K</t>
+          <t>0.3%</t>
         </is>
       </c>
       <c r="D180" t="inlineStr">
         <is>
-          <t>203K</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="E180" t="inlineStr">
         <is>
-          <t>210K</t>
+          <t>0.2%</t>
         </is>
       </c>
       <c r="F180" t="inlineStr">
         <is>
-          <t>209.0K</t>
+          <t>0.5%</t>
         </is>
       </c>
       <c r="G180" t="n">
@@ -5658,21 +5662,29 @@
       </c>
       <c r="B181" t="inlineStr">
         <is>
-          <t>Philly Fed New OrdersJAN</t>
+          <t>Continuing Jobless ClaimsJAN/04</t>
         </is>
       </c>
       <c r="C181" t="inlineStr">
         <is>
-          <t>42.9</t>
+          <t>1859K</t>
         </is>
       </c>
       <c r="D181" t="inlineStr">
         <is>
-          <t>-3.6</t>
-        </is>
-      </c>
-      <c r="E181" t="inlineStr"/>
-      <c r="F181" t="inlineStr"/>
+          <t>1867K</t>
+        </is>
+      </c>
+      <c r="E181" t="inlineStr">
+        <is>
+          <t>1870K</t>
+        </is>
+      </c>
+      <c r="F181" t="inlineStr">
+        <is>
+          <t>1870.0K</t>
+        </is>
+      </c>
       <c r="G181" t="n">
         <v>3</v>
       </c>
@@ -5685,31 +5697,27 @@
       </c>
       <c r="B182" t="inlineStr">
         <is>
-          <t>Retail Sales MoMDEC</t>
+          <t>Retail Sales YoYDEC</t>
         </is>
       </c>
       <c r="C182" t="inlineStr">
         <is>
-          <t>0.4%</t>
+          <t>3.9%</t>
         </is>
       </c>
       <c r="D182" t="inlineStr">
         <is>
-          <t>0.8%</t>
-        </is>
-      </c>
-      <c r="E182" t="inlineStr">
-        <is>
-          <t>0.6%</t>
-        </is>
-      </c>
+          <t>4.1%</t>
+        </is>
+      </c>
+      <c r="E182" t="inlineStr"/>
       <c r="F182" t="inlineStr">
         <is>
-          <t>0.5%</t>
+          <t>4.0%</t>
         </is>
       </c>
       <c r="G182" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="183">
@@ -5720,31 +5728,31 @@
       </c>
       <c r="B183" t="inlineStr">
         <is>
-          <t>Philadelphia Fed Manufacturing IndexJAN</t>
+          <t>Import Prices YoYDEC</t>
         </is>
       </c>
       <c r="C183" t="inlineStr">
         <is>
-          <t>44.3</t>
+          <t>2.2%</t>
         </is>
       </c>
       <c r="D183" t="inlineStr">
         <is>
-          <t>-10.9</t>
+          <t>1.4%</t>
         </is>
       </c>
       <c r="E183" t="inlineStr">
         <is>
-          <t>-5</t>
+          <t>2.1%</t>
         </is>
       </c>
       <c r="F183" t="inlineStr">
         <is>
-          <t>-10</t>
+          <t>1.6%</t>
         </is>
       </c>
       <c r="G183" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="184">
@@ -5755,25 +5763,21 @@
       </c>
       <c r="B184" t="inlineStr">
         <is>
-          <t>Export Prices YoYDEC</t>
+          <t>Philly Fed CAPEX IndexJAN</t>
         </is>
       </c>
       <c r="C184" t="inlineStr">
         <is>
-          <t>1.8%</t>
+          <t>39.00</t>
         </is>
       </c>
       <c r="D184" t="inlineStr">
         <is>
-          <t>0.9%</t>
+          <t>22.20</t>
         </is>
       </c>
       <c r="E184" t="inlineStr"/>
-      <c r="F184" t="inlineStr">
-        <is>
-          <t>1.9%</t>
-        </is>
-      </c>
+      <c r="F184" t="inlineStr"/>
       <c r="G184" t="n">
         <v>3</v>
       </c>
@@ -5786,31 +5790,23 @@
       </c>
       <c r="B185" t="inlineStr">
         <is>
-          <t>Import Prices MoMDEC</t>
+          <t>Philly Fed Business ConditionsJAN</t>
         </is>
       </c>
       <c r="C185" t="inlineStr">
         <is>
-          <t>0.1%</t>
+          <t>46.3</t>
         </is>
       </c>
       <c r="D185" t="inlineStr">
         <is>
-          <t>0.1%</t>
-        </is>
-      </c>
-      <c r="E185" t="inlineStr">
-        <is>
-          <t>0.1%</t>
-        </is>
-      </c>
-      <c r="F185" t="inlineStr">
-        <is>
-          <t>0.1%</t>
-        </is>
-      </c>
+          <t>33.8</t>
+        </is>
+      </c>
+      <c r="E185" t="inlineStr"/>
+      <c r="F185" t="inlineStr"/>
       <c r="G185" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="186">
@@ -5821,25 +5817,21 @@
       </c>
       <c r="B186" t="inlineStr">
         <is>
-          <t>Jobless Claims 4-week AverageJAN/11</t>
+          <t>Philly Fed Prices PaidJAN</t>
         </is>
       </c>
       <c r="C186" t="inlineStr">
         <is>
-          <t>212.75K</t>
+          <t>31.90</t>
         </is>
       </c>
       <c r="D186" t="inlineStr">
         <is>
-          <t>213.5K</t>
+          <t>26.60</t>
         </is>
       </c>
       <c r="E186" t="inlineStr"/>
-      <c r="F186" t="inlineStr">
-        <is>
-          <t>215.0K</t>
-        </is>
-      </c>
+      <c r="F186" t="inlineStr"/>
       <c r="G186" t="n">
         <v>3</v>
       </c>
@@ -5852,23 +5844,31 @@
       </c>
       <c r="B187" t="inlineStr">
         <is>
-          <t>Philly Fed EmploymentJAN</t>
+          <t>Retail Sales Ex Autos MoMDEC</t>
         </is>
       </c>
       <c r="C187" t="inlineStr">
         <is>
-          <t>11.9</t>
+          <t>0.4%</t>
         </is>
       </c>
       <c r="D187" t="inlineStr">
         <is>
-          <t>4.8</t>
-        </is>
-      </c>
-      <c r="E187" t="inlineStr"/>
-      <c r="F187" t="inlineStr"/>
+          <t>0.2%</t>
+        </is>
+      </c>
+      <c r="E187" t="inlineStr">
+        <is>
+          <t>0.4%</t>
+        </is>
+      </c>
+      <c r="F187" t="inlineStr">
+        <is>
+          <t>0.4%</t>
+        </is>
+      </c>
       <c r="G187" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="188">
@@ -6282,12 +6282,12 @@
       </c>
       <c r="B201" t="inlineStr">
         <is>
-          <t>Industrial Production YoYDEC</t>
+          <t>Manufacturing Production YoYDEC</t>
         </is>
       </c>
       <c r="C201" t="inlineStr">
         <is>
-          <t>0.5%</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="D201" t="inlineStr">
@@ -6298,7 +6298,7 @@
       <c r="E201" t="inlineStr"/>
       <c r="F201" t="inlineStr">
         <is>
-          <t>-0.5%</t>
+          <t>-0.7%</t>
         </is>
       </c>
       <c r="G201" t="n">
@@ -6313,31 +6313,31 @@
       </c>
       <c r="B202" t="inlineStr">
         <is>
-          <t>Manufacturing Production MoMDEC</t>
+          <t>Industrial Production MoMDEC</t>
         </is>
       </c>
       <c r="C202" t="inlineStr">
         <is>
-          <t>0.6%</t>
+          <t>0.9%</t>
         </is>
       </c>
       <c r="D202" t="inlineStr">
         <is>
-          <t>0.4%</t>
+          <t>0.2%</t>
         </is>
       </c>
       <c r="E202" t="inlineStr">
         <is>
-          <t>0.2%</t>
+          <t>0.3%</t>
         </is>
       </c>
       <c r="F202" t="inlineStr">
         <is>
-          <t>0.4%</t>
+          <t>0.1%</t>
         </is>
       </c>
       <c r="G202" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="203">
@@ -6348,27 +6348,27 @@
       </c>
       <c r="B203" t="inlineStr">
         <is>
-          <t>Capacity UtilizationDEC</t>
+          <t>Manufacturing Production MoMDEC</t>
         </is>
       </c>
       <c r="C203" t="inlineStr">
         <is>
-          <t>77.6%</t>
+          <t>0.6%</t>
         </is>
       </c>
       <c r="D203" t="inlineStr">
         <is>
-          <t>77%</t>
+          <t>0.4%</t>
         </is>
       </c>
       <c r="E203" t="inlineStr">
         <is>
-          <t>77%</t>
+          <t>0.2%</t>
         </is>
       </c>
       <c r="F203" t="inlineStr">
         <is>
-          <t>76.9%</t>
+          <t>0.4%</t>
         </is>
       </c>
       <c r="G203" t="n">
@@ -6383,31 +6383,27 @@
       </c>
       <c r="B204" t="inlineStr">
         <is>
-          <t>Industrial Production MoMDEC</t>
+          <t>Industrial Production YoYDEC</t>
         </is>
       </c>
       <c r="C204" t="inlineStr">
         <is>
-          <t>0.9%</t>
+          <t>0.5%</t>
         </is>
       </c>
       <c r="D204" t="inlineStr">
         <is>
-          <t>0.2%</t>
-        </is>
-      </c>
-      <c r="E204" t="inlineStr">
-        <is>
-          <t>0.3%</t>
-        </is>
-      </c>
+          <t>-0.6%</t>
+        </is>
+      </c>
+      <c r="E204" t="inlineStr"/>
       <c r="F204" t="inlineStr">
         <is>
-          <t>0.1%</t>
+          <t>-0.5%</t>
         </is>
       </c>
       <c r="G204" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="205">
@@ -6418,23 +6414,27 @@
       </c>
       <c r="B205" t="inlineStr">
         <is>
-          <t>Manufacturing Production YoYDEC</t>
+          <t>Capacity UtilizationDEC</t>
         </is>
       </c>
       <c r="C205" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>77.6%</t>
         </is>
       </c>
       <c r="D205" t="inlineStr">
         <is>
-          <t>-0.6%</t>
-        </is>
-      </c>
-      <c r="E205" t="inlineStr"/>
+          <t>77%</t>
+        </is>
+      </c>
+      <c r="E205" t="inlineStr">
+        <is>
+          <t>77%</t>
+        </is>
+      </c>
       <c r="F205" t="inlineStr">
         <is>
-          <t>-0.7%</t>
+          <t>76.9%</t>
         </is>
       </c>
       <c r="G205" t="n">
@@ -6661,17 +6661,17 @@
       </c>
       <c r="B214" t="inlineStr">
         <is>
-          <t>42-Day Bill Auction</t>
+          <t>52-Week Bill Auction</t>
         </is>
       </c>
       <c r="C214" t="inlineStr">
         <is>
-          <t>4.250%</t>
+          <t>4.025%</t>
         </is>
       </c>
       <c r="D214" t="inlineStr">
         <is>
-          <t>4.210%</t>
+          <t>4.070%</t>
         </is>
       </c>
       <c r="E214" t="inlineStr"/>
@@ -6688,17 +6688,17 @@
       </c>
       <c r="B215" t="inlineStr">
         <is>
-          <t>52-Week Bill Auction</t>
+          <t>42-Day Bill Auction</t>
         </is>
       </c>
       <c r="C215" t="inlineStr">
         <is>
-          <t>4.025%</t>
+          <t>4.250%</t>
         </is>
       </c>
       <c r="D215" t="inlineStr">
         <is>
-          <t>4.070%</t>
+          <t>4.210%</t>
         </is>
       </c>
       <c r="E215" t="inlineStr"/>
@@ -6993,23 +6993,27 @@
       </c>
       <c r="B226" t="inlineStr">
         <is>
-          <t>Jobless Claims 4-week AverageJAN/18</t>
+          <t>Continuing Jobless ClaimsJAN/11</t>
         </is>
       </c>
       <c r="C226" t="inlineStr">
         <is>
-          <t>213.5K</t>
+          <t>1899K</t>
         </is>
       </c>
       <c r="D226" t="inlineStr">
         <is>
-          <t>212.75K</t>
-        </is>
-      </c>
-      <c r="E226" t="inlineStr"/>
+          <t>1853K</t>
+        </is>
+      </c>
+      <c r="E226" t="inlineStr">
+        <is>
+          <t>1860K</t>
+        </is>
+      </c>
       <c r="F226" t="inlineStr">
         <is>
-          <t>213.0K</t>
+          <t>1861K</t>
         </is>
       </c>
       <c r="G226" t="n">
@@ -7059,27 +7063,23 @@
       </c>
       <c r="B228" t="inlineStr">
         <is>
-          <t>Continuing Jobless ClaimsJAN/11</t>
+          <t>Jobless Claims 4-week AverageJAN/18</t>
         </is>
       </c>
       <c r="C228" t="inlineStr">
         <is>
-          <t>1899K</t>
+          <t>213.5K</t>
         </is>
       </c>
       <c r="D228" t="inlineStr">
         <is>
-          <t>1853K</t>
-        </is>
-      </c>
-      <c r="E228" t="inlineStr">
-        <is>
-          <t>1860K</t>
-        </is>
-      </c>
+          <t>212.75K</t>
+        </is>
+      </c>
+      <c r="E228" t="inlineStr"/>
       <c r="F228" t="inlineStr">
         <is>
-          <t>1861K</t>
+          <t>213.0K</t>
         </is>
       </c>
       <c r="G228" t="n">
@@ -7241,17 +7241,17 @@
       </c>
       <c r="B234" t="inlineStr">
         <is>
-          <t>30-Year Mortgage RateJAN/23</t>
+          <t>15-Year Mortgage RateJAN/23</t>
         </is>
       </c>
       <c r="C234" t="inlineStr">
         <is>
-          <t>6.96%</t>
+          <t>6.16%</t>
         </is>
       </c>
       <c r="D234" t="inlineStr">
         <is>
-          <t>7.04%</t>
+          <t>6.27%</t>
         </is>
       </c>
       <c r="E234" t="inlineStr"/>
@@ -7268,23 +7268,27 @@
       </c>
       <c r="B235" t="inlineStr">
         <is>
-          <t>EIA Distillate Fuel Production ChangeJAN/17</t>
+          <t>EIA Gasoline Stocks ChangeJAN/17</t>
         </is>
       </c>
       <c r="C235" t="inlineStr">
         <is>
-          <t>-0.473M</t>
+          <t>2.332M</t>
         </is>
       </c>
       <c r="D235" t="inlineStr">
         <is>
-          <t>-0.021M</t>
-        </is>
-      </c>
-      <c r="E235" t="inlineStr"/>
+          <t>5.852M</t>
+        </is>
+      </c>
+      <c r="E235" t="inlineStr">
+        <is>
+          <t>2.5M</t>
+        </is>
+      </c>
       <c r="F235" t="inlineStr"/>
       <c r="G235" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="236">
@@ -7295,24 +7299,20 @@
       </c>
       <c r="B236" t="inlineStr">
         <is>
-          <t>EIA Distillate Stocks ChangeJAN/17</t>
+          <t>EIA Refinery Crude Runs ChangeJAN/17</t>
         </is>
       </c>
       <c r="C236" t="inlineStr">
         <is>
-          <t>-3.07M</t>
+          <t>-1.125M</t>
         </is>
       </c>
       <c r="D236" t="inlineStr">
         <is>
-          <t>3.077M</t>
-        </is>
-      </c>
-      <c r="E236" t="inlineStr">
-        <is>
-          <t>0.6M</t>
-        </is>
-      </c>
+          <t>-0.255M</t>
+        </is>
+      </c>
+      <c r="E236" t="inlineStr"/>
       <c r="F236" t="inlineStr"/>
       <c r="G236" t="n">
         <v>3</v>
@@ -7326,17 +7326,17 @@
       </c>
       <c r="B237" t="inlineStr">
         <is>
-          <t>EIA Heating Oil Stocks ChangeJAN/17</t>
+          <t>EIA Crude Oil Imports ChangeJAN/17</t>
         </is>
       </c>
       <c r="C237" t="inlineStr">
         <is>
-          <t>0.068M</t>
+          <t>0.184M</t>
         </is>
       </c>
       <c r="D237" t="inlineStr">
         <is>
-          <t>0.646M</t>
+          <t>-1.304M</t>
         </is>
       </c>
       <c r="E237" t="inlineStr"/>
@@ -7353,17 +7353,17 @@
       </c>
       <c r="B238" t="inlineStr">
         <is>
-          <t>EIA Cushing Crude Oil Stocks ChangeJAN/17</t>
+          <t>EIA Gasoline Production ChangeJAN/17</t>
         </is>
       </c>
       <c r="C238" t="inlineStr">
         <is>
-          <t>-0.148M</t>
+          <t>-0.043M</t>
         </is>
       </c>
       <c r="D238" t="inlineStr">
         <is>
-          <t>0.765M</t>
+          <t>0.397M</t>
         </is>
       </c>
       <c r="E238" t="inlineStr"/>
@@ -7380,23 +7380,27 @@
       </c>
       <c r="B239" t="inlineStr">
         <is>
-          <t>EIA Gasoline Production ChangeJAN/17</t>
+          <t>EIA Crude Oil Stocks ChangeJAN/17</t>
         </is>
       </c>
       <c r="C239" t="inlineStr">
         <is>
-          <t>-0.043M</t>
+          <t>-1.017M</t>
         </is>
       </c>
       <c r="D239" t="inlineStr">
         <is>
-          <t>0.397M</t>
-        </is>
-      </c>
-      <c r="E239" t="inlineStr"/>
+          <t>-1.962M</t>
+        </is>
+      </c>
+      <c r="E239" t="inlineStr">
+        <is>
+          <t>-2.1M</t>
+        </is>
+      </c>
       <c r="F239" t="inlineStr"/>
       <c r="G239" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="240">
@@ -7407,27 +7411,23 @@
       </c>
       <c r="B240" t="inlineStr">
         <is>
-          <t>EIA Crude Oil Stocks ChangeJAN/17</t>
+          <t>EIA Heating Oil Stocks ChangeJAN/17</t>
         </is>
       </c>
       <c r="C240" t="inlineStr">
         <is>
-          <t>-1.017M</t>
+          <t>0.068M</t>
         </is>
       </c>
       <c r="D240" t="inlineStr">
         <is>
-          <t>-1.962M</t>
-        </is>
-      </c>
-      <c r="E240" t="inlineStr">
-        <is>
-          <t>-2.1M</t>
-        </is>
-      </c>
+          <t>0.646M</t>
+        </is>
+      </c>
+      <c r="E240" t="inlineStr"/>
       <c r="F240" t="inlineStr"/>
       <c r="G240" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="241">
@@ -7438,20 +7438,24 @@
       </c>
       <c r="B241" t="inlineStr">
         <is>
-          <t>EIA Crude Oil Imports ChangeJAN/17</t>
+          <t>EIA Distillate Stocks ChangeJAN/17</t>
         </is>
       </c>
       <c r="C241" t="inlineStr">
         <is>
-          <t>0.184M</t>
+          <t>-3.07M</t>
         </is>
       </c>
       <c r="D241" t="inlineStr">
         <is>
-          <t>-1.304M</t>
-        </is>
-      </c>
-      <c r="E241" t="inlineStr"/>
+          <t>3.077M</t>
+        </is>
+      </c>
+      <c r="E241" t="inlineStr">
+        <is>
+          <t>0.6M</t>
+        </is>
+      </c>
       <c r="F241" t="inlineStr"/>
       <c r="G241" t="n">
         <v>3</v>
@@ -7465,17 +7469,17 @@
       </c>
       <c r="B242" t="inlineStr">
         <is>
-          <t>EIA Refinery Crude Runs ChangeJAN/17</t>
+          <t>EIA Distillate Fuel Production ChangeJAN/17</t>
         </is>
       </c>
       <c r="C242" t="inlineStr">
         <is>
-          <t>-1.125M</t>
+          <t>-0.473M</t>
         </is>
       </c>
       <c r="D242" t="inlineStr">
         <is>
-          <t>-0.255M</t>
+          <t>-0.021M</t>
         </is>
       </c>
       <c r="E242" t="inlineStr"/>
@@ -7492,27 +7496,23 @@
       </c>
       <c r="B243" t="inlineStr">
         <is>
-          <t>EIA Gasoline Stocks ChangeJAN/17</t>
+          <t>30-Year Mortgage RateJAN/23</t>
         </is>
       </c>
       <c r="C243" t="inlineStr">
         <is>
-          <t>2.332M</t>
+          <t>6.96%</t>
         </is>
       </c>
       <c r="D243" t="inlineStr">
         <is>
-          <t>5.852M</t>
-        </is>
-      </c>
-      <c r="E243" t="inlineStr">
-        <is>
-          <t>2.5M</t>
-        </is>
-      </c>
+          <t>7.04%</t>
+        </is>
+      </c>
+      <c r="E243" t="inlineStr"/>
       <c r="F243" t="inlineStr"/>
       <c r="G243" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="244">
@@ -7523,17 +7523,17 @@
       </c>
       <c r="B244" t="inlineStr">
         <is>
-          <t>15-Year Mortgage RateJAN/23</t>
+          <t>EIA Cushing Crude Oil Stocks ChangeJAN/17</t>
         </is>
       </c>
       <c r="C244" t="inlineStr">
         <is>
-          <t>6.16%</t>
+          <t>-0.148M</t>
         </is>
       </c>
       <c r="D244" t="inlineStr">
         <is>
-          <t>6.27%</t>
+          <t>0.765M</t>
         </is>
       </c>
       <c r="E244" t="inlineStr"/>
@@ -7705,27 +7705,31 @@
       </c>
       <c r="B250" t="inlineStr">
         <is>
-          <t>Existing Home Sales MoMDEC</t>
+          <t>Michigan Inflation Expectations FinalJAN</t>
         </is>
       </c>
       <c r="C250" t="inlineStr">
         <is>
-          <t>2.2%</t>
+          <t>3.3%</t>
         </is>
       </c>
       <c r="D250" t="inlineStr">
         <is>
-          <t>4.8%</t>
-        </is>
-      </c>
-      <c r="E250" t="inlineStr"/>
+          <t>2.8%</t>
+        </is>
+      </c>
+      <c r="E250" t="inlineStr">
+        <is>
+          <t>3.3%</t>
+        </is>
+      </c>
       <c r="F250" t="inlineStr">
         <is>
-          <t>0.3%</t>
+          <t>3.3%</t>
         </is>
       </c>
       <c r="G250" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="251">
@@ -7736,27 +7740,27 @@
       </c>
       <c r="B251" t="inlineStr">
         <is>
-          <t>Michigan 5 Year Inflation Expectations FinalJAN</t>
+          <t>Michigan Current Conditions FinalJAN</t>
         </is>
       </c>
       <c r="C251" t="inlineStr">
         <is>
-          <t>3.2%</t>
+          <t>74.0</t>
         </is>
       </c>
       <c r="D251" t="inlineStr">
         <is>
-          <t>3%</t>
+          <t>75.1</t>
         </is>
       </c>
       <c r="E251" t="inlineStr">
         <is>
-          <t>3.3%</t>
+          <t>77.9</t>
         </is>
       </c>
       <c r="F251" t="inlineStr">
         <is>
-          <t>3.3%</t>
+          <t>77.9</t>
         </is>
       </c>
       <c r="G251" t="n">
@@ -7771,31 +7775,31 @@
       </c>
       <c r="B252" t="inlineStr">
         <is>
-          <t>Michigan Consumer Sentiment FinalJAN</t>
+          <t>Michigan Consumer Expectations FinalJAN</t>
         </is>
       </c>
       <c r="C252" t="inlineStr">
         <is>
-          <t>71.1</t>
+          <t>69.3</t>
         </is>
       </c>
       <c r="D252" t="inlineStr">
         <is>
-          <t>74.0</t>
+          <t>73.3</t>
         </is>
       </c>
       <c r="E252" t="inlineStr">
         <is>
-          <t>73.2</t>
+          <t>70.2</t>
         </is>
       </c>
       <c r="F252" t="inlineStr">
         <is>
-          <t>73.2</t>
+          <t>70.2</t>
         </is>
       </c>
       <c r="G252" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="253">
@@ -7806,31 +7810,31 @@
       </c>
       <c r="B253" t="inlineStr">
         <is>
-          <t>Michigan Consumer Expectations FinalJAN</t>
+          <t>Existing Home SalesDEC</t>
         </is>
       </c>
       <c r="C253" t="inlineStr">
         <is>
-          <t>69.3</t>
+          <t>4.24M</t>
         </is>
       </c>
       <c r="D253" t="inlineStr">
         <is>
-          <t>73.3</t>
+          <t>4.15M</t>
         </is>
       </c>
       <c r="E253" t="inlineStr">
         <is>
-          <t>70.2</t>
+          <t>4.19M</t>
         </is>
       </c>
       <c r="F253" t="inlineStr">
         <is>
-          <t>70.2</t>
+          <t>4.1M</t>
         </is>
       </c>
       <c r="G253" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="254">
@@ -7841,17 +7845,17 @@
       </c>
       <c r="B254" t="inlineStr">
         <is>
-          <t>Michigan Inflation Expectations FinalJAN</t>
+          <t>Michigan 5 Year Inflation Expectations FinalJAN</t>
         </is>
       </c>
       <c r="C254" t="inlineStr">
         <is>
-          <t>3.3%</t>
+          <t>3.2%</t>
         </is>
       </c>
       <c r="D254" t="inlineStr">
         <is>
-          <t>2.8%</t>
+          <t>3%</t>
         </is>
       </c>
       <c r="E254" t="inlineStr">
@@ -7876,31 +7880,31 @@
       </c>
       <c r="B255" t="inlineStr">
         <is>
-          <t>Existing Home SalesDEC</t>
+          <t>Michigan Consumer Sentiment FinalJAN</t>
         </is>
       </c>
       <c r="C255" t="inlineStr">
         <is>
-          <t>4.24M</t>
+          <t>71.1</t>
         </is>
       </c>
       <c r="D255" t="inlineStr">
         <is>
-          <t>4.15M</t>
+          <t>74.0</t>
         </is>
       </c>
       <c r="E255" t="inlineStr">
         <is>
-          <t>4.19M</t>
+          <t>73.2</t>
         </is>
       </c>
       <c r="F255" t="inlineStr">
         <is>
-          <t>4.1M</t>
+          <t>73.2</t>
         </is>
       </c>
       <c r="G255" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="256">
@@ -7911,31 +7915,27 @@
       </c>
       <c r="B256" t="inlineStr">
         <is>
-          <t>Michigan Current Conditions FinalJAN</t>
+          <t>Existing Home Sales MoMDEC</t>
         </is>
       </c>
       <c r="C256" t="inlineStr">
         <is>
-          <t>74.0</t>
+          <t>2.2%</t>
         </is>
       </c>
       <c r="D256" t="inlineStr">
         <is>
-          <t>75.1</t>
-        </is>
-      </c>
-      <c r="E256" t="inlineStr">
-        <is>
-          <t>77.9</t>
-        </is>
-      </c>
+          <t>4.8%</t>
+        </is>
+      </c>
+      <c r="E256" t="inlineStr"/>
       <c r="F256" t="inlineStr">
         <is>
-          <t>77.9</t>
+          <t>0.3%</t>
         </is>
       </c>
       <c r="G256" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="257">
@@ -8252,17 +8252,17 @@
       </c>
       <c r="B267" t="inlineStr">
         <is>
-          <t>5-Year Note Auction</t>
+          <t>3-Month Bill Auction</t>
         </is>
       </c>
       <c r="C267" t="inlineStr">
         <is>
-          <t>4.33%</t>
+          <t>4.195%</t>
         </is>
       </c>
       <c r="D267" t="inlineStr">
         <is>
-          <t>4.478%</t>
+          <t>4.215%</t>
         </is>
       </c>
       <c r="E267" t="inlineStr"/>
@@ -8279,17 +8279,17 @@
       </c>
       <c r="B268" t="inlineStr">
         <is>
-          <t>3-Month Bill Auction</t>
+          <t>5-Year Note Auction</t>
         </is>
       </c>
       <c r="C268" t="inlineStr">
         <is>
-          <t>4.195%</t>
+          <t>4.33%</t>
         </is>
       </c>
       <c r="D268" t="inlineStr">
         <is>
-          <t>4.215%</t>
+          <t>4.478%</t>
         </is>
       </c>
       <c r="E268" t="inlineStr"/>
@@ -8632,27 +8632,31 @@
       </c>
       <c r="B279" t="inlineStr">
         <is>
-          <t>Richmond Fed Services Revenues IndexJAN</t>
+          <t>CB Consumer ConfidenceJAN</t>
         </is>
       </c>
       <c r="C279" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>104.1</t>
         </is>
       </c>
       <c r="D279" t="inlineStr">
         <is>
-          <t>23</t>
-        </is>
-      </c>
-      <c r="E279" t="inlineStr"/>
+          <t>109.5</t>
+        </is>
+      </c>
+      <c r="E279" t="inlineStr">
+        <is>
+          <t>105.6</t>
+        </is>
+      </c>
       <c r="F279" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>104</t>
         </is>
       </c>
       <c r="G279" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="280">
@@ -8663,23 +8667,23 @@
       </c>
       <c r="B280" t="inlineStr">
         <is>
-          <t>Richmond Fed Manufacturing Shipments IndexJAN</t>
+          <t>Richmond Fed Services Revenues IndexJAN</t>
         </is>
       </c>
       <c r="C280" t="inlineStr">
         <is>
-          <t>-9</t>
+          <t>4</t>
         </is>
       </c>
       <c r="D280" t="inlineStr">
         <is>
-          <t>-11</t>
+          <t>23</t>
         </is>
       </c>
       <c r="E280" t="inlineStr"/>
       <c r="F280" t="inlineStr">
         <is>
-          <t>-9</t>
+          <t>21</t>
         </is>
       </c>
       <c r="G280" t="n">
@@ -8694,27 +8698,23 @@
       </c>
       <c r="B281" t="inlineStr">
         <is>
-          <t>Richmond Fed Manufacturing IndexJAN</t>
+          <t>Richmond Fed Manufacturing Shipments IndexJAN</t>
         </is>
       </c>
       <c r="C281" t="inlineStr">
         <is>
-          <t>-4</t>
+          <t>-9</t>
         </is>
       </c>
       <c r="D281" t="inlineStr">
         <is>
-          <t>-10</t>
-        </is>
-      </c>
-      <c r="E281" t="inlineStr">
-        <is>
-          <t>-8</t>
-        </is>
-      </c>
+          <t>-11</t>
+        </is>
+      </c>
+      <c r="E281" t="inlineStr"/>
       <c r="F281" t="inlineStr">
         <is>
-          <t>-8</t>
+          <t>-9</t>
         </is>
       </c>
       <c r="G281" t="n">
@@ -8729,31 +8729,31 @@
       </c>
       <c r="B282" t="inlineStr">
         <is>
-          <t>CB Consumer ConfidenceJAN</t>
+          <t>Richmond Fed Manufacturing IndexJAN</t>
         </is>
       </c>
       <c r="C282" t="inlineStr">
         <is>
-          <t>104.1</t>
+          <t>-4</t>
         </is>
       </c>
       <c r="D282" t="inlineStr">
         <is>
-          <t>109.5</t>
+          <t>-10</t>
         </is>
       </c>
       <c r="E282" t="inlineStr">
         <is>
-          <t>105.6</t>
+          <t>-8</t>
         </is>
       </c>
       <c r="F282" t="inlineStr">
         <is>
-          <t>104</t>
+          <t>-8</t>
         </is>
       </c>
       <c r="G282" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="283">
@@ -8764,23 +8764,23 @@
       </c>
       <c r="B283" t="inlineStr">
         <is>
-          <t>Dallas Fed Services IndexJAN</t>
+          <t>Dallas Fed Services Revenues IndexJAN</t>
         </is>
       </c>
       <c r="C283" t="inlineStr">
         <is>
-          <t>7.4</t>
+          <t>5.7</t>
         </is>
       </c>
       <c r="D283" t="inlineStr">
         <is>
-          <t>10.8</t>
+          <t>13.9</t>
         </is>
       </c>
       <c r="E283" t="inlineStr"/>
       <c r="F283" t="inlineStr">
         <is>
-          <t>9.5</t>
+          <t>13</t>
         </is>
       </c>
       <c r="G283" t="n">
@@ -8795,23 +8795,23 @@
       </c>
       <c r="B284" t="inlineStr">
         <is>
-          <t>Dallas Fed Services Revenues IndexJAN</t>
+          <t>Dallas Fed Services IndexJAN</t>
         </is>
       </c>
       <c r="C284" t="inlineStr">
         <is>
-          <t>5.7</t>
+          <t>7.4</t>
         </is>
       </c>
       <c r="D284" t="inlineStr">
         <is>
-          <t>13.9</t>
+          <t>10.8</t>
         </is>
       </c>
       <c r="E284" t="inlineStr"/>
       <c r="F284" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>9.5</t>
         </is>
       </c>
       <c r="G284" t="n">
@@ -8965,17 +8965,17 @@
       </c>
       <c r="B290" t="inlineStr">
         <is>
-          <t>MBA Mortgage Refinance IndexJAN/24</t>
+          <t>MBA Mortgage Market IndexJAN/24</t>
         </is>
       </c>
       <c r="C290" t="inlineStr">
         <is>
-          <t>520.9</t>
+          <t>220.0</t>
         </is>
       </c>
       <c r="D290" t="inlineStr">
         <is>
-          <t>558.8</t>
+          <t>224.6</t>
         </is>
       </c>
       <c r="E290" t="inlineStr"/>
@@ -8992,23 +8992,23 @@
       </c>
       <c r="B291" t="inlineStr">
         <is>
-          <t>MBA Mortgage ApplicationsJAN/24</t>
+          <t>MBA 30-Year Mortgage RateJAN/24</t>
         </is>
       </c>
       <c r="C291" t="inlineStr">
         <is>
-          <t>-2%</t>
+          <t>7.02%</t>
         </is>
       </c>
       <c r="D291" t="inlineStr">
         <is>
-          <t>0.1%</t>
+          <t>7.02%</t>
         </is>
       </c>
       <c r="E291" t="inlineStr"/>
       <c r="F291" t="inlineStr"/>
       <c r="G291" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="292">
@@ -9019,23 +9019,23 @@
       </c>
       <c r="B292" t="inlineStr">
         <is>
-          <t>MBA 30-Year Mortgage RateJAN/24</t>
+          <t>MBA Purchase IndexJAN/24</t>
         </is>
       </c>
       <c r="C292" t="inlineStr">
         <is>
-          <t>7.02%</t>
+          <t>162.4</t>
         </is>
       </c>
       <c r="D292" t="inlineStr">
         <is>
-          <t>7.02%</t>
+          <t>163</t>
         </is>
       </c>
       <c r="E292" t="inlineStr"/>
       <c r="F292" t="inlineStr"/>
       <c r="G292" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="293">
@@ -9046,17 +9046,17 @@
       </c>
       <c r="B293" t="inlineStr">
         <is>
-          <t>MBA Purchase IndexJAN/24</t>
+          <t>MBA Mortgage Refinance IndexJAN/24</t>
         </is>
       </c>
       <c r="C293" t="inlineStr">
         <is>
-          <t>162.4</t>
+          <t>520.9</t>
         </is>
       </c>
       <c r="D293" t="inlineStr">
         <is>
-          <t>163</t>
+          <t>558.8</t>
         </is>
       </c>
       <c r="E293" t="inlineStr"/>
@@ -9073,17 +9073,17 @@
       </c>
       <c r="B294" t="inlineStr">
         <is>
-          <t>MBA Mortgage Market IndexJAN/24</t>
+          <t>MBA Mortgage ApplicationsJAN/24</t>
         </is>
       </c>
       <c r="C294" t="inlineStr">
         <is>
-          <t>220.0</t>
+          <t>-2%</t>
         </is>
       </c>
       <c r="D294" t="inlineStr">
         <is>
-          <t>224.6</t>
+          <t>0.1%</t>
         </is>
       </c>
       <c r="E294" t="inlineStr"/>
@@ -9201,17 +9201,17 @@
       </c>
       <c r="B298" t="inlineStr">
         <is>
-          <t>EIA Crude Oil Imports ChangeJAN/24</t>
+          <t>EIA Cushing Crude Oil Stocks ChangeJAN/24</t>
         </is>
       </c>
       <c r="C298" t="inlineStr">
         <is>
-          <t>0.532M</t>
+          <t>0.326M</t>
         </is>
       </c>
       <c r="D298" t="inlineStr">
         <is>
-          <t>0.184M</t>
+          <t>-0.148M</t>
         </is>
       </c>
       <c r="E298" t="inlineStr"/>
@@ -9228,23 +9228,27 @@
       </c>
       <c r="B299" t="inlineStr">
         <is>
-          <t>EIA Refinery Crude Runs ChangeJAN/24</t>
+          <t>EIA Crude Oil Stocks ChangeJAN/24</t>
         </is>
       </c>
       <c r="C299" t="inlineStr">
         <is>
-          <t>-0.333M</t>
+          <t>3.463M</t>
         </is>
       </c>
       <c r="D299" t="inlineStr">
         <is>
-          <t>-1.125M</t>
-        </is>
-      </c>
-      <c r="E299" t="inlineStr"/>
+          <t>-1.017M</t>
+        </is>
+      </c>
+      <c r="E299" t="inlineStr">
+        <is>
+          <t>3.2M</t>
+        </is>
+      </c>
       <c r="F299" t="inlineStr"/>
       <c r="G299" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="300">
@@ -9255,20 +9259,24 @@
       </c>
       <c r="B300" t="inlineStr">
         <is>
-          <t>EIA Distillate Fuel Production ChangeJAN/24</t>
+          <t>EIA Distillate Stocks ChangeJAN/24</t>
         </is>
       </c>
       <c r="C300" t="inlineStr">
         <is>
-          <t>0.028M</t>
+          <t>-4.994M</t>
         </is>
       </c>
       <c r="D300" t="inlineStr">
         <is>
-          <t>-0.473M</t>
-        </is>
-      </c>
-      <c r="E300" t="inlineStr"/>
+          <t>-3.07M</t>
+        </is>
+      </c>
+      <c r="E300" t="inlineStr">
+        <is>
+          <t>-2.1M</t>
+        </is>
+      </c>
       <c r="F300" t="inlineStr"/>
       <c r="G300" t="n">
         <v>3</v>
@@ -9282,27 +9290,23 @@
       </c>
       <c r="B301" t="inlineStr">
         <is>
-          <t>EIA Gasoline Stocks ChangeJAN/24</t>
+          <t>EIA Heating Oil Stocks ChangeJAN/24</t>
         </is>
       </c>
       <c r="C301" t="inlineStr">
         <is>
-          <t>2.957M</t>
+          <t>0.128M</t>
         </is>
       </c>
       <c r="D301" t="inlineStr">
         <is>
-          <t>2.332M</t>
-        </is>
-      </c>
-      <c r="E301" t="inlineStr">
-        <is>
-          <t>1.5M</t>
-        </is>
-      </c>
+          <t>0.068M</t>
+        </is>
+      </c>
+      <c r="E301" t="inlineStr"/>
       <c r="F301" t="inlineStr"/>
       <c r="G301" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="302">
@@ -9313,17 +9317,17 @@
       </c>
       <c r="B302" t="inlineStr">
         <is>
-          <t>EIA Gasoline Production ChangeJAN/24</t>
+          <t>EIA Refinery Crude Runs ChangeJAN/24</t>
         </is>
       </c>
       <c r="C302" t="inlineStr">
         <is>
-          <t>-0.044M</t>
+          <t>-0.333M</t>
         </is>
       </c>
       <c r="D302" t="inlineStr">
         <is>
-          <t>-0.043M</t>
+          <t>-1.125M</t>
         </is>
       </c>
       <c r="E302" t="inlineStr"/>
@@ -9340,23 +9344,27 @@
       </c>
       <c r="B303" t="inlineStr">
         <is>
-          <t>EIA Heating Oil Stocks ChangeJAN/24</t>
+          <t>EIA Gasoline Stocks ChangeJAN/24</t>
         </is>
       </c>
       <c r="C303" t="inlineStr">
         <is>
-          <t>0.128M</t>
+          <t>2.957M</t>
         </is>
       </c>
       <c r="D303" t="inlineStr">
         <is>
-          <t>0.068M</t>
-        </is>
-      </c>
-      <c r="E303" t="inlineStr"/>
+          <t>2.332M</t>
+        </is>
+      </c>
+      <c r="E303" t="inlineStr">
+        <is>
+          <t>1.5M</t>
+        </is>
+      </c>
       <c r="F303" t="inlineStr"/>
       <c r="G303" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="304">
@@ -9367,17 +9375,17 @@
       </c>
       <c r="B304" t="inlineStr">
         <is>
-          <t>EIA Cushing Crude Oil Stocks ChangeJAN/24</t>
+          <t>EIA Distillate Fuel Production ChangeJAN/24</t>
         </is>
       </c>
       <c r="C304" t="inlineStr">
         <is>
-          <t>0.326M</t>
+          <t>0.028M</t>
         </is>
       </c>
       <c r="D304" t="inlineStr">
         <is>
-          <t>-0.148M</t>
+          <t>-0.473M</t>
         </is>
       </c>
       <c r="E304" t="inlineStr"/>
@@ -9394,24 +9402,20 @@
       </c>
       <c r="B305" t="inlineStr">
         <is>
-          <t>EIA Distillate Stocks ChangeJAN/24</t>
+          <t>EIA Crude Oil Imports ChangeJAN/24</t>
         </is>
       </c>
       <c r="C305" t="inlineStr">
         <is>
-          <t>-4.994M</t>
+          <t>0.532M</t>
         </is>
       </c>
       <c r="D305" t="inlineStr">
         <is>
-          <t>-3.07M</t>
-        </is>
-      </c>
-      <c r="E305" t="inlineStr">
-        <is>
-          <t>-2.1M</t>
-        </is>
-      </c>
+          <t>0.184M</t>
+        </is>
+      </c>
+      <c r="E305" t="inlineStr"/>
       <c r="F305" t="inlineStr"/>
       <c r="G305" t="n">
         <v>3</v>
@@ -9425,27 +9429,23 @@
       </c>
       <c r="B306" t="inlineStr">
         <is>
-          <t>EIA Crude Oil Stocks ChangeJAN/24</t>
+          <t>EIA Gasoline Production ChangeJAN/24</t>
         </is>
       </c>
       <c r="C306" t="inlineStr">
         <is>
-          <t>3.463M</t>
+          <t>-0.044M</t>
         </is>
       </c>
       <c r="D306" t="inlineStr">
         <is>
-          <t>-1.017M</t>
-        </is>
-      </c>
-      <c r="E306" t="inlineStr">
-        <is>
-          <t>3.2M</t>
-        </is>
-      </c>
+          <t>-0.043M</t>
+        </is>
+      </c>
+      <c r="E306" t="inlineStr"/>
       <c r="F306" t="inlineStr"/>
       <c r="G306" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="307">
@@ -9537,23 +9537,27 @@
       </c>
       <c r="B310" t="inlineStr">
         <is>
-          <t>PCE Prices QoQ AdvQ4</t>
+          <t>Continuing Jobless ClaimsJAN/18</t>
         </is>
       </c>
       <c r="C310" t="inlineStr">
         <is>
-          <t>2.3%</t>
+          <t>1858K</t>
         </is>
       </c>
       <c r="D310" t="inlineStr">
         <is>
-          <t>1.5%</t>
-        </is>
-      </c>
-      <c r="E310" t="inlineStr"/>
+          <t>1900K</t>
+        </is>
+      </c>
+      <c r="E310" t="inlineStr">
+        <is>
+          <t>1890K</t>
+        </is>
+      </c>
       <c r="F310" t="inlineStr">
         <is>
-          <t>1.1%</t>
+          <t>1885.0K</t>
         </is>
       </c>
       <c r="G310" t="n">
@@ -9568,27 +9572,31 @@
       </c>
       <c r="B311" t="inlineStr">
         <is>
-          <t>Real Consumer Spending QoQ AdvQ4</t>
+          <t>GDP Growth Rate QoQ AdvQ4</t>
         </is>
       </c>
       <c r="C311" t="inlineStr">
         <is>
-          <t>4.2%</t>
+          <t>2.3%</t>
         </is>
       </c>
       <c r="D311" t="inlineStr">
         <is>
-          <t>3.7%</t>
-        </is>
-      </c>
-      <c r="E311" t="inlineStr"/>
+          <t>3.1%</t>
+        </is>
+      </c>
+      <c r="E311" t="inlineStr">
+        <is>
+          <t>2.6%</t>
+        </is>
+      </c>
       <c r="F311" t="inlineStr">
         <is>
-          <t>2.9%</t>
+          <t>3%</t>
         </is>
       </c>
       <c r="G311" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="312">
@@ -9599,31 +9607,31 @@
       </c>
       <c r="B312" t="inlineStr">
         <is>
-          <t>Core PCE Prices QoQ AdvQ4</t>
+          <t>GDP Price Index QoQ AdvQ4</t>
         </is>
       </c>
       <c r="C312" t="inlineStr">
         <is>
+          <t>2.2%</t>
+        </is>
+      </c>
+      <c r="D312" t="inlineStr">
+        <is>
+          <t>1.9%</t>
+        </is>
+      </c>
+      <c r="E312" t="inlineStr">
+        <is>
           <t>2.5%</t>
         </is>
       </c>
-      <c r="D312" t="inlineStr">
-        <is>
-          <t>2.2%</t>
-        </is>
-      </c>
-      <c r="E312" t="inlineStr">
-        <is>
-          <t>2.5%</t>
-        </is>
-      </c>
       <c r="F312" t="inlineStr">
         <is>
           <t>2.3%</t>
         </is>
       </c>
       <c r="G312" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="313">
@@ -9634,23 +9642,23 @@
       </c>
       <c r="B313" t="inlineStr">
         <is>
-          <t>GDP Sales QoQ AdvQ4</t>
+          <t>Jobless Claims 4-week AverageJAN/25</t>
         </is>
       </c>
       <c r="C313" t="inlineStr">
         <is>
-          <t>3.2%</t>
+          <t>212.5K</t>
         </is>
       </c>
       <c r="D313" t="inlineStr">
         <is>
-          <t>3.3%</t>
+          <t>213.5K</t>
         </is>
       </c>
       <c r="E313" t="inlineStr"/>
       <c r="F313" t="inlineStr">
         <is>
-          <t>2.9%</t>
+          <t>214.0K</t>
         </is>
       </c>
       <c r="G313" t="n">
@@ -9665,31 +9673,31 @@
       </c>
       <c r="B314" t="inlineStr">
         <is>
-          <t>Initial Jobless ClaimsJAN/25</t>
+          <t>Core PCE Prices QoQ AdvQ4</t>
         </is>
       </c>
       <c r="C314" t="inlineStr">
         <is>
-          <t>207K</t>
+          <t>2.5%</t>
         </is>
       </c>
       <c r="D314" t="inlineStr">
         <is>
-          <t>223K</t>
+          <t>2.2%</t>
         </is>
       </c>
       <c r="E314" t="inlineStr">
         <is>
-          <t>220K</t>
+          <t>2.5%</t>
         </is>
       </c>
       <c r="F314" t="inlineStr">
         <is>
-          <t>228.0K</t>
+          <t>2.3%</t>
         </is>
       </c>
       <c r="G314" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="315">
@@ -9700,23 +9708,23 @@
       </c>
       <c r="B315" t="inlineStr">
         <is>
-          <t>Jobless Claims 4-week AverageJAN/25</t>
+          <t>GDP Sales QoQ AdvQ4</t>
         </is>
       </c>
       <c r="C315" t="inlineStr">
         <is>
-          <t>212.5K</t>
+          <t>3.2%</t>
         </is>
       </c>
       <c r="D315" t="inlineStr">
         <is>
-          <t>213.5K</t>
+          <t>3.3%</t>
         </is>
       </c>
       <c r="E315" t="inlineStr"/>
       <c r="F315" t="inlineStr">
         <is>
-          <t>214.0K</t>
+          <t>2.9%</t>
         </is>
       </c>
       <c r="G315" t="n">
@@ -9731,31 +9739,31 @@
       </c>
       <c r="B316" t="inlineStr">
         <is>
-          <t>Continuing Jobless ClaimsJAN/18</t>
+          <t>Initial Jobless ClaimsJAN/25</t>
         </is>
       </c>
       <c r="C316" t="inlineStr">
         <is>
-          <t>1858K</t>
+          <t>207K</t>
         </is>
       </c>
       <c r="D316" t="inlineStr">
         <is>
-          <t>1900K</t>
+          <t>223K</t>
         </is>
       </c>
       <c r="E316" t="inlineStr">
         <is>
-          <t>1890K</t>
+          <t>220K</t>
         </is>
       </c>
       <c r="F316" t="inlineStr">
         <is>
-          <t>1885.0K</t>
+          <t>228.0K</t>
         </is>
       </c>
       <c r="G316" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="317">
@@ -9766,31 +9774,27 @@
       </c>
       <c r="B317" t="inlineStr">
         <is>
-          <t>GDP Price Index QoQ AdvQ4</t>
+          <t>Real Consumer Spending QoQ AdvQ4</t>
         </is>
       </c>
       <c r="C317" t="inlineStr">
         <is>
-          <t>2.2%</t>
+          <t>4.2%</t>
         </is>
       </c>
       <c r="D317" t="inlineStr">
         <is>
-          <t>1.9%</t>
-        </is>
-      </c>
-      <c r="E317" t="inlineStr">
-        <is>
-          <t>2.5%</t>
-        </is>
-      </c>
+          <t>3.7%</t>
+        </is>
+      </c>
+      <c r="E317" t="inlineStr"/>
       <c r="F317" t="inlineStr">
         <is>
-          <t>2.3%</t>
+          <t>2.9%</t>
         </is>
       </c>
       <c r="G317" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="318">
@@ -9801,7 +9805,7 @@
       </c>
       <c r="B318" t="inlineStr">
         <is>
-          <t>GDP Growth Rate QoQ AdvQ4</t>
+          <t>PCE Prices QoQ AdvQ4</t>
         </is>
       </c>
       <c r="C318" t="inlineStr">
@@ -9811,21 +9815,17 @@
       </c>
       <c r="D318" t="inlineStr">
         <is>
-          <t>3.1%</t>
-        </is>
-      </c>
-      <c r="E318" t="inlineStr">
-        <is>
-          <t>2.6%</t>
-        </is>
-      </c>
+          <t>1.5%</t>
+        </is>
+      </c>
+      <c r="E318" t="inlineStr"/>
       <c r="F318" t="inlineStr">
         <is>
-          <t>3%</t>
+          <t>1.1%</t>
         </is>
       </c>
       <c r="G318" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="319">
@@ -9933,17 +9933,17 @@
       </c>
       <c r="B322" t="inlineStr">
         <is>
-          <t>4-Week Bill Auction</t>
+          <t>8-Week Bill Auction</t>
         </is>
       </c>
       <c r="C322" t="inlineStr">
         <is>
+          <t>4.240%</t>
+        </is>
+      </c>
+      <c r="D322" t="inlineStr">
+        <is>
           <t>4.250%</t>
-        </is>
-      </c>
-      <c r="D322" t="inlineStr">
-        <is>
-          <t>4.265%</t>
         </is>
       </c>
       <c r="E322" t="inlineStr"/>
@@ -9960,17 +9960,17 @@
       </c>
       <c r="B323" t="inlineStr">
         <is>
-          <t>8-Week Bill Auction</t>
+          <t>4-Week Bill Auction</t>
         </is>
       </c>
       <c r="C323" t="inlineStr">
         <is>
-          <t>4.240%</t>
+          <t>4.250%</t>
         </is>
       </c>
       <c r="D323" t="inlineStr">
         <is>
-          <t>4.250%</t>
+          <t>4.265%</t>
         </is>
       </c>
       <c r="E323" t="inlineStr"/>
@@ -10068,15 +10068,31 @@
       </c>
       <c r="B327" t="inlineStr">
         <is>
-          <t>Fed Bowman Speech</t>
-        </is>
-      </c>
-      <c r="C327" t="inlineStr"/>
-      <c r="D327" t="inlineStr"/>
-      <c r="E327" t="inlineStr"/>
-      <c r="F327" t="inlineStr"/>
+          <t>Core PCE Price Index YoYDEC</t>
+        </is>
+      </c>
+      <c r="C327" t="inlineStr">
+        <is>
+          <t>2.8%</t>
+        </is>
+      </c>
+      <c r="D327" t="inlineStr">
+        <is>
+          <t>2.8%</t>
+        </is>
+      </c>
+      <c r="E327" t="inlineStr">
+        <is>
+          <t>2.8%</t>
+        </is>
+      </c>
+      <c r="F327" t="inlineStr">
+        <is>
+          <t>2.8%</t>
+        </is>
+      </c>
       <c r="G327" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="328">
@@ -10087,31 +10103,31 @@
       </c>
       <c r="B328" t="inlineStr">
         <is>
-          <t>Core PCE Price Index MoMDEC</t>
+          <t>Employment Cost Index QoQQ4</t>
         </is>
       </c>
       <c r="C328" t="inlineStr">
         <is>
-          <t>0.2%</t>
+          <t>0.9%</t>
         </is>
       </c>
       <c r="D328" t="inlineStr">
         <is>
-          <t>0.1%</t>
+          <t>0.8%</t>
         </is>
       </c>
       <c r="E328" t="inlineStr">
         <is>
-          <t>0.2%</t>
+          <t>0.9%</t>
         </is>
       </c>
       <c r="F328" t="inlineStr">
         <is>
-          <t>0.2%</t>
+          <t>0.7%</t>
         </is>
       </c>
       <c r="G328" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="329">
@@ -10122,31 +10138,31 @@
       </c>
       <c r="B329" t="inlineStr">
         <is>
-          <t>Personal Spending MoMDEC</t>
+          <t>PCE Price Index MoMDEC</t>
         </is>
       </c>
       <c r="C329" t="inlineStr">
         <is>
-          <t>0.7%</t>
+          <t>0.3%</t>
         </is>
       </c>
       <c r="D329" t="inlineStr">
         <is>
-          <t>0.6%</t>
+          <t>0.1%</t>
         </is>
       </c>
       <c r="E329" t="inlineStr">
         <is>
-          <t>0.5%</t>
+          <t>0.3%</t>
         </is>
       </c>
       <c r="F329" t="inlineStr">
         <is>
-          <t>0.5%</t>
+          <t>0.3%</t>
         </is>
       </c>
       <c r="G329" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="330">
@@ -10157,23 +10173,27 @@
       </c>
       <c r="B330" t="inlineStr">
         <is>
-          <t>Employment Cost - Benefits QoQQ4</t>
+          <t>PCE Price Index YoYDEC</t>
         </is>
       </c>
       <c r="C330" t="inlineStr">
         <is>
-          <t>0.8%</t>
+          <t>2.6%</t>
         </is>
       </c>
       <c r="D330" t="inlineStr">
         <is>
-          <t>0.8%</t>
-        </is>
-      </c>
-      <c r="E330" t="inlineStr"/>
+          <t>2.4%</t>
+        </is>
+      </c>
+      <c r="E330" t="inlineStr">
+        <is>
+          <t>2.6%</t>
+        </is>
+      </c>
       <c r="F330" t="inlineStr">
         <is>
-          <t>0.7%</t>
+          <t>2.6%</t>
         </is>
       </c>
       <c r="G330" t="n">
@@ -10188,31 +10208,27 @@
       </c>
       <c r="B331" t="inlineStr">
         <is>
-          <t>Personal Income MoMDEC</t>
+          <t>Employment Cost - Wages QoQQ4</t>
         </is>
       </c>
       <c r="C331" t="inlineStr">
         <is>
-          <t>0.4%</t>
+          <t>0.9%</t>
         </is>
       </c>
       <c r="D331" t="inlineStr">
         <is>
-          <t>0.3%</t>
-        </is>
-      </c>
-      <c r="E331" t="inlineStr">
-        <is>
-          <t>0.4%</t>
-        </is>
-      </c>
+          <t>0.8%</t>
+        </is>
+      </c>
+      <c r="E331" t="inlineStr"/>
       <c r="F331" t="inlineStr">
         <is>
-          <t>0.3%</t>
+          <t>0.7%</t>
         </is>
       </c>
       <c r="G331" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="332">
@@ -10223,25 +10239,13 @@
       </c>
       <c r="B332" t="inlineStr">
         <is>
-          <t>Employment Cost - Wages QoQQ4</t>
-        </is>
-      </c>
-      <c r="C332" t="inlineStr">
-        <is>
-          <t>0.9%</t>
-        </is>
-      </c>
-      <c r="D332" t="inlineStr">
-        <is>
-          <t>0.8%</t>
-        </is>
-      </c>
+          <t>Fed Bowman Speech</t>
+        </is>
+      </c>
+      <c r="C332" t="inlineStr"/>
+      <c r="D332" t="inlineStr"/>
       <c r="E332" t="inlineStr"/>
-      <c r="F332" t="inlineStr">
-        <is>
-          <t>0.7%</t>
-        </is>
-      </c>
+      <c r="F332" t="inlineStr"/>
       <c r="G332" t="n">
         <v>2</v>
       </c>
@@ -10254,31 +10258,27 @@
       </c>
       <c r="B333" t="inlineStr">
         <is>
-          <t>Core PCE Price Index YoYDEC</t>
+          <t>Employment Cost - Benefits QoQQ4</t>
         </is>
       </c>
       <c r="C333" t="inlineStr">
         <is>
-          <t>2.8%</t>
+          <t>0.8%</t>
         </is>
       </c>
       <c r="D333" t="inlineStr">
         <is>
-          <t>2.8%</t>
-        </is>
-      </c>
-      <c r="E333" t="inlineStr">
-        <is>
-          <t>2.8%</t>
-        </is>
-      </c>
+          <t>0.8%</t>
+        </is>
+      </c>
+      <c r="E333" t="inlineStr"/>
       <c r="F333" t="inlineStr">
         <is>
-          <t>2.8%</t>
+          <t>0.7%</t>
         </is>
       </c>
       <c r="G333" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="334">
@@ -10289,31 +10289,31 @@
       </c>
       <c r="B334" t="inlineStr">
         <is>
-          <t>PCE Price Index YoYDEC</t>
+          <t>Personal Spending MoMDEC</t>
         </is>
       </c>
       <c r="C334" t="inlineStr">
         <is>
-          <t>2.6%</t>
+          <t>0.7%</t>
         </is>
       </c>
       <c r="D334" t="inlineStr">
         <is>
-          <t>2.4%</t>
+          <t>0.6%</t>
         </is>
       </c>
       <c r="E334" t="inlineStr">
         <is>
-          <t>2.6%</t>
+          <t>0.5%</t>
         </is>
       </c>
       <c r="F334" t="inlineStr">
         <is>
-          <t>2.6%</t>
+          <t>0.5%</t>
         </is>
       </c>
       <c r="G334" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="335">
@@ -10324,12 +10324,12 @@
       </c>
       <c r="B335" t="inlineStr">
         <is>
-          <t>PCE Price Index MoMDEC</t>
+          <t>Core PCE Price Index MoMDEC</t>
         </is>
       </c>
       <c r="C335" t="inlineStr">
         <is>
-          <t>0.3%</t>
+          <t>0.2%</t>
         </is>
       </c>
       <c r="D335" t="inlineStr">
@@ -10339,16 +10339,16 @@
       </c>
       <c r="E335" t="inlineStr">
         <is>
-          <t>0.3%</t>
+          <t>0.2%</t>
         </is>
       </c>
       <c r="F335" t="inlineStr">
         <is>
-          <t>0.3%</t>
+          <t>0.2%</t>
         </is>
       </c>
       <c r="G335" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="336">
@@ -10359,31 +10359,31 @@
       </c>
       <c r="B336" t="inlineStr">
         <is>
-          <t>Employment Cost Index QoQQ4</t>
+          <t>Personal Income MoMDEC</t>
         </is>
       </c>
       <c r="C336" t="inlineStr">
         <is>
-          <t>0.9%</t>
+          <t>0.4%</t>
         </is>
       </c>
       <c r="D336" t="inlineStr">
         <is>
-          <t>0.8%</t>
+          <t>0.3%</t>
         </is>
       </c>
       <c r="E336" t="inlineStr">
         <is>
-          <t>0.9%</t>
+          <t>0.4%</t>
         </is>
       </c>
       <c r="F336" t="inlineStr">
         <is>
-          <t>0.7%</t>
+          <t>0.3%</t>
         </is>
       </c>
       <c r="G336" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="337">
@@ -11155,17 +11155,17 @@
       </c>
       <c r="B364" t="inlineStr">
         <is>
-          <t>MBA Mortgage ApplicationsJAN/31</t>
+          <t>MBA Mortgage Refinance IndexJAN/31</t>
         </is>
       </c>
       <c r="C364" t="inlineStr">
         <is>
-          <t>2.2%</t>
+          <t>584.3</t>
         </is>
       </c>
       <c r="D364" t="inlineStr">
         <is>
-          <t>-2%</t>
+          <t>520.9</t>
         </is>
       </c>
       <c r="E364" t="inlineStr"/>
@@ -11182,17 +11182,17 @@
       </c>
       <c r="B365" t="inlineStr">
         <is>
-          <t>MBA Purchase IndexJAN/31</t>
+          <t>MBA Mortgage Market IndexJAN/31</t>
         </is>
       </c>
       <c r="C365" t="inlineStr">
         <is>
-          <t>156.7</t>
+          <t>224.8</t>
         </is>
       </c>
       <c r="D365" t="inlineStr">
         <is>
-          <t>162.4</t>
+          <t>220.0</t>
         </is>
       </c>
       <c r="E365" t="inlineStr"/>
@@ -11209,23 +11209,23 @@
       </c>
       <c r="B366" t="inlineStr">
         <is>
-          <t>MBA Mortgage Market IndexJAN/31</t>
+          <t>MBA 30-Year Mortgage RateJAN/31</t>
         </is>
       </c>
       <c r="C366" t="inlineStr">
         <is>
-          <t>224.8</t>
+          <t>6.97%</t>
         </is>
       </c>
       <c r="D366" t="inlineStr">
         <is>
-          <t>220.0</t>
+          <t>7.02%</t>
         </is>
       </c>
       <c r="E366" t="inlineStr"/>
       <c r="F366" t="inlineStr"/>
       <c r="G366" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="367">
@@ -11236,17 +11236,17 @@
       </c>
       <c r="B367" t="inlineStr">
         <is>
-          <t>MBA Mortgage Refinance IndexJAN/31</t>
+          <t>MBA Mortgage ApplicationsJAN/31</t>
         </is>
       </c>
       <c r="C367" t="inlineStr">
         <is>
-          <t>584.3</t>
+          <t>2.2%</t>
         </is>
       </c>
       <c r="D367" t="inlineStr">
         <is>
-          <t>520.9</t>
+          <t>-2%</t>
         </is>
       </c>
       <c r="E367" t="inlineStr"/>
@@ -11263,23 +11263,23 @@
       </c>
       <c r="B368" t="inlineStr">
         <is>
-          <t>MBA 30-Year Mortgage RateJAN/31</t>
+          <t>MBA Purchase IndexJAN/31</t>
         </is>
       </c>
       <c r="C368" t="inlineStr">
         <is>
-          <t>6.97%</t>
+          <t>156.7</t>
         </is>
       </c>
       <c r="D368" t="inlineStr">
         <is>
-          <t>7.02%</t>
+          <t>162.4</t>
         </is>
       </c>
       <c r="E368" t="inlineStr"/>
       <c r="F368" t="inlineStr"/>
       <c r="G368" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="369">
@@ -11530,23 +11530,23 @@
       </c>
       <c r="B377" t="inlineStr">
         <is>
-          <t>ISM Services PricesJAN</t>
+          <t>ISM Services EmploymentJAN</t>
         </is>
       </c>
       <c r="C377" t="inlineStr">
         <is>
-          <t>60.4</t>
+          <t>52.3</t>
         </is>
       </c>
       <c r="D377" t="inlineStr">
         <is>
-          <t>64.4</t>
+          <t>51.3</t>
         </is>
       </c>
       <c r="E377" t="inlineStr"/>
       <c r="F377" t="inlineStr">
         <is>
-          <t>64.8</t>
+          <t>51.3</t>
         </is>
       </c>
       <c r="G377" t="n">
@@ -11561,27 +11561,31 @@
       </c>
       <c r="B378" t="inlineStr">
         <is>
-          <t>ISM Services Business ActivityJAN</t>
+          <t>ISM Services PMIJAN</t>
         </is>
       </c>
       <c r="C378" t="inlineStr">
         <is>
-          <t>54.5</t>
+          <t>52.8</t>
         </is>
       </c>
       <c r="D378" t="inlineStr">
         <is>
-          <t>58.0</t>
-        </is>
-      </c>
-      <c r="E378" t="inlineStr"/>
+          <t>54.0</t>
+        </is>
+      </c>
+      <c r="E378" t="inlineStr">
+        <is>
+          <t>54.3</t>
+        </is>
+      </c>
       <c r="F378" t="inlineStr">
         <is>
-          <t>58.1</t>
+          <t>54</t>
         </is>
       </c>
       <c r="G378" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="379">
@@ -11592,31 +11596,27 @@
       </c>
       <c r="B379" t="inlineStr">
         <is>
-          <t>ISM Services PMIJAN</t>
+          <t>ISM Services New OrdersJAN</t>
         </is>
       </c>
       <c r="C379" t="inlineStr">
         <is>
-          <t>52.8</t>
+          <t>51.3</t>
         </is>
       </c>
       <c r="D379" t="inlineStr">
         <is>
-          <t>54.0</t>
-        </is>
-      </c>
-      <c r="E379" t="inlineStr">
-        <is>
-          <t>54.3</t>
-        </is>
-      </c>
+          <t>54.4</t>
+        </is>
+      </c>
+      <c r="E379" t="inlineStr"/>
       <c r="F379" t="inlineStr">
         <is>
-          <t>54</t>
+          <t>54.1</t>
         </is>
       </c>
       <c r="G379" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="380">
@@ -11627,23 +11627,23 @@
       </c>
       <c r="B380" t="inlineStr">
         <is>
-          <t>ISM Services EmploymentJAN</t>
+          <t>ISM Services PricesJAN</t>
         </is>
       </c>
       <c r="C380" t="inlineStr">
         <is>
-          <t>52.3</t>
+          <t>60.4</t>
         </is>
       </c>
       <c r="D380" t="inlineStr">
         <is>
-          <t>51.3</t>
+          <t>64.4</t>
         </is>
       </c>
       <c r="E380" t="inlineStr"/>
       <c r="F380" t="inlineStr">
         <is>
-          <t>51.3</t>
+          <t>64.8</t>
         </is>
       </c>
       <c r="G380" t="n">
@@ -11658,23 +11658,23 @@
       </c>
       <c r="B381" t="inlineStr">
         <is>
-          <t>ISM Services New OrdersJAN</t>
+          <t>ISM Services Business ActivityJAN</t>
         </is>
       </c>
       <c r="C381" t="inlineStr">
         <is>
-          <t>51.3</t>
+          <t>54.5</t>
         </is>
       </c>
       <c r="D381" t="inlineStr">
         <is>
-          <t>54.4</t>
+          <t>58.0</t>
         </is>
       </c>
       <c r="E381" t="inlineStr"/>
       <c r="F381" t="inlineStr">
         <is>
-          <t>54.1</t>
+          <t>58.1</t>
         </is>
       </c>
       <c r="G381" t="n">
@@ -11689,17 +11689,17 @@
       </c>
       <c r="B382" t="inlineStr">
         <is>
-          <t>EIA Distillate Fuel Production ChangeJAN/31</t>
+          <t>EIA Gasoline Production ChangeJAN/31</t>
         </is>
       </c>
       <c r="C382" t="inlineStr">
         <is>
-          <t>-0.186M</t>
+          <t>-0.027M</t>
         </is>
       </c>
       <c r="D382" t="inlineStr">
         <is>
-          <t>0.028M</t>
+          <t>-0.044M</t>
         </is>
       </c>
       <c r="E382" t="inlineStr"/>
@@ -11716,22 +11716,22 @@
       </c>
       <c r="B383" t="inlineStr">
         <is>
-          <t>EIA Gasoline Stocks ChangeJAN/31</t>
+          <t>EIA Crude Oil Stocks ChangeJAN/31</t>
         </is>
       </c>
       <c r="C383" t="inlineStr">
         <is>
-          <t>2.233M</t>
+          <t>8.664M</t>
         </is>
       </c>
       <c r="D383" t="inlineStr">
         <is>
-          <t>2.957M</t>
+          <t>3.463M</t>
         </is>
       </c>
       <c r="E383" t="inlineStr">
         <is>
-          <t>1.2M</t>
+          <t>2.6M</t>
         </is>
       </c>
       <c r="F383" t="inlineStr"/>
@@ -11747,24 +11747,20 @@
       </c>
       <c r="B384" t="inlineStr">
         <is>
-          <t>EIA Distillate Stocks ChangeJAN/31</t>
+          <t>EIA Heating Oil Stocks ChangeJAN/31</t>
         </is>
       </c>
       <c r="C384" t="inlineStr">
         <is>
-          <t>-5.471M</t>
+          <t>0.373M</t>
         </is>
       </c>
       <c r="D384" t="inlineStr">
         <is>
-          <t>-4.994M</t>
-        </is>
-      </c>
-      <c r="E384" t="inlineStr">
-        <is>
-          <t>-1.5M</t>
-        </is>
-      </c>
+          <t>0.128M</t>
+        </is>
+      </c>
+      <c r="E384" t="inlineStr"/>
       <c r="F384" t="inlineStr"/>
       <c r="G384" t="n">
         <v>3</v>
@@ -11778,17 +11774,17 @@
       </c>
       <c r="B385" t="inlineStr">
         <is>
-          <t>EIA Cushing Crude Oil Stocks ChangeJAN/31</t>
+          <t>EIA Refinery Crude Runs ChangeJAN/31</t>
         </is>
       </c>
       <c r="C385" t="inlineStr">
         <is>
-          <t>-0.034M</t>
+          <t>0.16M</t>
         </is>
       </c>
       <c r="D385" t="inlineStr">
         <is>
-          <t>0.326M</t>
+          <t>-0.333M</t>
         </is>
       </c>
       <c r="E385" t="inlineStr"/>
@@ -11805,17 +11801,17 @@
       </c>
       <c r="B386" t="inlineStr">
         <is>
-          <t>EIA Refinery Crude Runs ChangeJAN/31</t>
+          <t>EIA Crude Oil Imports ChangeJAN/31</t>
         </is>
       </c>
       <c r="C386" t="inlineStr">
         <is>
-          <t>0.16M</t>
+          <t>-0.178M</t>
         </is>
       </c>
       <c r="D386" t="inlineStr">
         <is>
-          <t>-0.333M</t>
+          <t>0.532M</t>
         </is>
       </c>
       <c r="E386" t="inlineStr"/>
@@ -11832,20 +11828,24 @@
       </c>
       <c r="B387" t="inlineStr">
         <is>
-          <t>EIA Heating Oil Stocks ChangeJAN/31</t>
+          <t>EIA Distillate Stocks ChangeJAN/31</t>
         </is>
       </c>
       <c r="C387" t="inlineStr">
         <is>
-          <t>0.373M</t>
+          <t>-5.471M</t>
         </is>
       </c>
       <c r="D387" t="inlineStr">
         <is>
-          <t>0.128M</t>
-        </is>
-      </c>
-      <c r="E387" t="inlineStr"/>
+          <t>-4.994M</t>
+        </is>
+      </c>
+      <c r="E387" t="inlineStr">
+        <is>
+          <t>-1.5M</t>
+        </is>
+      </c>
       <c r="F387" t="inlineStr"/>
       <c r="G387" t="n">
         <v>3</v>
@@ -11859,23 +11859,27 @@
       </c>
       <c r="B388" t="inlineStr">
         <is>
-          <t>EIA Crude Oil Imports ChangeJAN/31</t>
+          <t>EIA Gasoline Stocks ChangeJAN/31</t>
         </is>
       </c>
       <c r="C388" t="inlineStr">
         <is>
-          <t>-0.178M</t>
+          <t>2.233M</t>
         </is>
       </c>
       <c r="D388" t="inlineStr">
         <is>
-          <t>0.532M</t>
-        </is>
-      </c>
-      <c r="E388" t="inlineStr"/>
+          <t>2.957M</t>
+        </is>
+      </c>
+      <c r="E388" t="inlineStr">
+        <is>
+          <t>1.2M</t>
+        </is>
+      </c>
       <c r="F388" t="inlineStr"/>
       <c r="G388" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="389">
@@ -11886,27 +11890,23 @@
       </c>
       <c r="B389" t="inlineStr">
         <is>
-          <t>EIA Crude Oil Stocks ChangeJAN/31</t>
+          <t>EIA Distillate Fuel Production ChangeJAN/31</t>
         </is>
       </c>
       <c r="C389" t="inlineStr">
         <is>
-          <t>8.664M</t>
+          <t>-0.186M</t>
         </is>
       </c>
       <c r="D389" t="inlineStr">
         <is>
-          <t>3.463M</t>
-        </is>
-      </c>
-      <c r="E389" t="inlineStr">
-        <is>
-          <t>2.6M</t>
-        </is>
-      </c>
+          <t>0.028M</t>
+        </is>
+      </c>
+      <c r="E389" t="inlineStr"/>
       <c r="F389" t="inlineStr"/>
       <c r="G389" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="390">
@@ -11917,17 +11917,17 @@
       </c>
       <c r="B390" t="inlineStr">
         <is>
-          <t>EIA Gasoline Production ChangeJAN/31</t>
+          <t>EIA Cushing Crude Oil Stocks ChangeJAN/31</t>
         </is>
       </c>
       <c r="C390" t="inlineStr">
         <is>
-          <t>-0.027M</t>
+          <t>-0.034M</t>
         </is>
       </c>
       <c r="D390" t="inlineStr">
         <is>
-          <t>-0.044M</t>
+          <t>0.326M</t>
         </is>
       </c>
       <c r="E390" t="inlineStr"/>
@@ -12040,23 +12040,27 @@
       </c>
       <c r="B395" t="inlineStr">
         <is>
-          <t>Jobless Claims 4-week AverageFEB/01</t>
+          <t>Continuing Jobless ClaimsJAN/25</t>
         </is>
       </c>
       <c r="C395" t="inlineStr">
         <is>
-          <t>216.75K</t>
+          <t>1886K</t>
         </is>
       </c>
       <c r="D395" t="inlineStr">
         <is>
-          <t>212.75K</t>
-        </is>
-      </c>
-      <c r="E395" t="inlineStr"/>
+          <t>1850K</t>
+        </is>
+      </c>
+      <c r="E395" t="inlineStr">
+        <is>
+          <t>1870K</t>
+        </is>
+      </c>
       <c r="F395" t="inlineStr">
         <is>
-          <t>215.5K</t>
+          <t>1855.0K</t>
         </is>
       </c>
       <c r="G395" t="n">
@@ -12071,27 +12075,27 @@
       </c>
       <c r="B396" t="inlineStr">
         <is>
-          <t>Unit Labour Costs QoQ PrelQ4</t>
+          <t>Initial Jobless ClaimsFEB/01</t>
         </is>
       </c>
       <c r="C396" t="inlineStr">
         <is>
-          <t>3%</t>
+          <t>219K</t>
         </is>
       </c>
       <c r="D396" t="inlineStr">
         <is>
-          <t>0.5%</t>
+          <t>208K</t>
         </is>
       </c>
       <c r="E396" t="inlineStr">
         <is>
-          <t>3.4%</t>
+          <t>213K</t>
         </is>
       </c>
       <c r="F396" t="inlineStr">
         <is>
-          <t>3%</t>
+          <t>215.0K</t>
         </is>
       </c>
       <c r="G396" t="n">
@@ -12141,27 +12145,27 @@
       </c>
       <c r="B398" t="inlineStr">
         <is>
-          <t>Initial Jobless ClaimsFEB/01</t>
+          <t>Unit Labour Costs QoQ PrelQ4</t>
         </is>
       </c>
       <c r="C398" t="inlineStr">
         <is>
-          <t>219K</t>
+          <t>3%</t>
         </is>
       </c>
       <c r="D398" t="inlineStr">
         <is>
-          <t>208K</t>
+          <t>0.5%</t>
         </is>
       </c>
       <c r="E398" t="inlineStr">
         <is>
-          <t>213K</t>
+          <t>3.4%</t>
         </is>
       </c>
       <c r="F398" t="inlineStr">
         <is>
-          <t>215.0K</t>
+          <t>3%</t>
         </is>
       </c>
       <c r="G398" t="n">
@@ -12176,27 +12180,23 @@
       </c>
       <c r="B399" t="inlineStr">
         <is>
-          <t>Continuing Jobless ClaimsJAN/25</t>
+          <t>Jobless Claims 4-week AverageFEB/01</t>
         </is>
       </c>
       <c r="C399" t="inlineStr">
         <is>
-          <t>1886K</t>
+          <t>216.75K</t>
         </is>
       </c>
       <c r="D399" t="inlineStr">
         <is>
-          <t>1850K</t>
-        </is>
-      </c>
-      <c r="E399" t="inlineStr">
-        <is>
-          <t>1870K</t>
-        </is>
-      </c>
+          <t>212.75K</t>
+        </is>
+      </c>
+      <c r="E399" t="inlineStr"/>
       <c r="F399" t="inlineStr">
         <is>
-          <t>1855.0K</t>
+          <t>215.5K</t>
         </is>
       </c>
       <c r="G399" t="n">
@@ -12442,31 +12442,27 @@
       </c>
       <c r="B409" t="inlineStr">
         <is>
-          <t>Non Farm PayrollsJAN</t>
+          <t>Government PayrollsJAN</t>
         </is>
       </c>
       <c r="C409" t="inlineStr">
         <is>
-          <t>143K</t>
+          <t>32K</t>
         </is>
       </c>
       <c r="D409" t="inlineStr">
         <is>
-          <t>307K</t>
-        </is>
-      </c>
-      <c r="E409" t="inlineStr">
-        <is>
-          <t>170K</t>
-        </is>
-      </c>
+          <t>34K</t>
+        </is>
+      </c>
+      <c r="E409" t="inlineStr"/>
       <c r="F409" t="inlineStr">
         <is>
-          <t>205K</t>
+          <t>25K</t>
         </is>
       </c>
       <c r="G409" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="410">
@@ -12477,27 +12473,23 @@
       </c>
       <c r="B410" t="inlineStr">
         <is>
-          <t>Average Weekly HoursJAN</t>
+          <t>U-6 Unemployment RateJAN</t>
         </is>
       </c>
       <c r="C410" t="inlineStr">
         <is>
-          <t>34.1</t>
+          <t>7.5%</t>
         </is>
       </c>
       <c r="D410" t="inlineStr">
         <is>
-          <t>34.2</t>
-        </is>
-      </c>
-      <c r="E410" t="inlineStr">
-        <is>
-          <t>34.3</t>
-        </is>
-      </c>
+          <t>7.5%</t>
+        </is>
+      </c>
+      <c r="E410" t="inlineStr"/>
       <c r="F410" t="inlineStr">
         <is>
-          <t>34.3</t>
+          <t>7.5%</t>
         </is>
       </c>
       <c r="G410" t="n">
@@ -12512,31 +12504,27 @@
       </c>
       <c r="B411" t="inlineStr">
         <is>
-          <t>Unemployment RateJAN</t>
+          <t>Participation RateJAN</t>
         </is>
       </c>
       <c r="C411" t="inlineStr">
         <is>
-          <t>4%</t>
+          <t>62.6%</t>
         </is>
       </c>
       <c r="D411" t="inlineStr">
         <is>
-          <t>4.1%</t>
-        </is>
-      </c>
-      <c r="E411" t="inlineStr">
-        <is>
-          <t>4.1%</t>
-        </is>
-      </c>
+          <t>62.5%</t>
+        </is>
+      </c>
+      <c r="E411" t="inlineStr"/>
       <c r="F411" t="inlineStr">
         <is>
-          <t>4.1%</t>
+          <t>62.5%</t>
         </is>
       </c>
       <c r="G411" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="412">
@@ -12547,31 +12535,31 @@
       </c>
       <c r="B412" t="inlineStr">
         <is>
-          <t>Average Hourly Earnings MoMJAN</t>
+          <t>Manufacturing PayrollsJAN</t>
         </is>
       </c>
       <c r="C412" t="inlineStr">
         <is>
-          <t>0.5%</t>
+          <t>3K</t>
         </is>
       </c>
       <c r="D412" t="inlineStr">
         <is>
-          <t>0.3%</t>
+          <t>-12K</t>
         </is>
       </c>
       <c r="E412" t="inlineStr">
         <is>
-          <t>0.3%</t>
+          <t>-2K</t>
         </is>
       </c>
       <c r="F412" t="inlineStr">
         <is>
-          <t>0.3%</t>
+          <t>-5K</t>
         </is>
       </c>
       <c r="G412" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="413">
@@ -12582,31 +12570,31 @@
       </c>
       <c r="B413" t="inlineStr">
         <is>
-          <t>Average Hourly Earnings YoYJAN</t>
+          <t>Nonfarm Payrolls PrivateJAN</t>
         </is>
       </c>
       <c r="C413" t="inlineStr">
         <is>
-          <t>4.1%</t>
+          <t>111K</t>
         </is>
       </c>
       <c r="D413" t="inlineStr">
         <is>
-          <t>4.1%</t>
+          <t>273K</t>
         </is>
       </c>
       <c r="E413" t="inlineStr">
         <is>
-          <t>3.8%</t>
+          <t>141K</t>
         </is>
       </c>
       <c r="F413" t="inlineStr">
         <is>
-          <t>3.9%</t>
+          <t>180K</t>
         </is>
       </c>
       <c r="G413" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="414">
@@ -12617,31 +12605,31 @@
       </c>
       <c r="B414" t="inlineStr">
         <is>
-          <t>Nonfarm Payrolls PrivateJAN</t>
+          <t>Unemployment RateJAN</t>
         </is>
       </c>
       <c r="C414" t="inlineStr">
         <is>
-          <t>111K</t>
+          <t>4%</t>
         </is>
       </c>
       <c r="D414" t="inlineStr">
         <is>
-          <t>273K</t>
+          <t>4.1%</t>
         </is>
       </c>
       <c r="E414" t="inlineStr">
         <is>
-          <t>141K</t>
+          <t>4.1%</t>
         </is>
       </c>
       <c r="F414" t="inlineStr">
         <is>
-          <t>180K</t>
+          <t>4.1%</t>
         </is>
       </c>
       <c r="G414" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="415">
@@ -12652,31 +12640,31 @@
       </c>
       <c r="B415" t="inlineStr">
         <is>
-          <t>Manufacturing PayrollsJAN</t>
+          <t>Average Hourly Earnings MoMJAN</t>
         </is>
       </c>
       <c r="C415" t="inlineStr">
         <is>
-          <t>3K</t>
+          <t>0.5%</t>
         </is>
       </c>
       <c r="D415" t="inlineStr">
         <is>
-          <t>-12K</t>
+          <t>0.3%</t>
         </is>
       </c>
       <c r="E415" t="inlineStr">
         <is>
-          <t>-2K</t>
+          <t>0.3%</t>
         </is>
       </c>
       <c r="F415" t="inlineStr">
         <is>
-          <t>-5K</t>
+          <t>0.3%</t>
         </is>
       </c>
       <c r="G415" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="416">
@@ -12687,27 +12675,31 @@
       </c>
       <c r="B416" t="inlineStr">
         <is>
-          <t>Participation RateJAN</t>
+          <t>Average Weekly HoursJAN</t>
         </is>
       </c>
       <c r="C416" t="inlineStr">
         <is>
-          <t>62.6%</t>
+          <t>34.1</t>
         </is>
       </c>
       <c r="D416" t="inlineStr">
         <is>
-          <t>62.5%</t>
-        </is>
-      </c>
-      <c r="E416" t="inlineStr"/>
+          <t>34.2</t>
+        </is>
+      </c>
+      <c r="E416" t="inlineStr">
+        <is>
+          <t>34.3</t>
+        </is>
+      </c>
       <c r="F416" t="inlineStr">
         <is>
-          <t>62.5%</t>
+          <t>34.3</t>
         </is>
       </c>
       <c r="G416" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="417">
@@ -12718,27 +12710,31 @@
       </c>
       <c r="B417" t="inlineStr">
         <is>
-          <t>U-6 Unemployment RateJAN</t>
+          <t>Non Farm PayrollsJAN</t>
         </is>
       </c>
       <c r="C417" t="inlineStr">
         <is>
-          <t>7.5%</t>
+          <t>143K</t>
         </is>
       </c>
       <c r="D417" t="inlineStr">
         <is>
-          <t>7.5%</t>
-        </is>
-      </c>
-      <c r="E417" t="inlineStr"/>
+          <t>307K</t>
+        </is>
+      </c>
+      <c r="E417" t="inlineStr">
+        <is>
+          <t>170K</t>
+        </is>
+      </c>
       <c r="F417" t="inlineStr">
         <is>
-          <t>7.5%</t>
+          <t>205K</t>
         </is>
       </c>
       <c r="G417" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="418">
@@ -12749,27 +12745,31 @@
       </c>
       <c r="B418" t="inlineStr">
         <is>
-          <t>Government PayrollsJAN</t>
+          <t>Average Hourly Earnings YoYJAN</t>
         </is>
       </c>
       <c r="C418" t="inlineStr">
         <is>
-          <t>32K</t>
+          <t>4.1%</t>
         </is>
       </c>
       <c r="D418" t="inlineStr">
         <is>
-          <t>34K</t>
-        </is>
-      </c>
-      <c r="E418" t="inlineStr"/>
+          <t>4.1%</t>
+        </is>
+      </c>
+      <c r="E418" t="inlineStr">
+        <is>
+          <t>3.8%</t>
+        </is>
+      </c>
       <c r="F418" t="inlineStr">
         <is>
-          <t>25K</t>
+          <t>3.9%</t>
         </is>
       </c>
       <c r="G418" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="419">
@@ -12872,31 +12872,31 @@
       </c>
       <c r="B423" t="inlineStr">
         <is>
-          <t>Michigan Consumer Sentiment PrelFEB</t>
+          <t>Michigan Current Conditions PrelFEB</t>
         </is>
       </c>
       <c r="C423" t="inlineStr">
         <is>
-          <t>67.8</t>
+          <t>68.7</t>
         </is>
       </c>
       <c r="D423" t="inlineStr">
         <is>
-          <t>71.1</t>
+          <t>74</t>
         </is>
       </c>
       <c r="E423" t="inlineStr">
         <is>
-          <t>71.1</t>
+          <t>73</t>
         </is>
       </c>
       <c r="F423" t="inlineStr">
         <is>
-          <t>72</t>
+          <t>74.3</t>
         </is>
       </c>
       <c r="G423" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="424">
@@ -12907,23 +12907,27 @@
       </c>
       <c r="B424" t="inlineStr">
         <is>
-          <t>Michigan 5 Year Inflation Expectations PrelFEB</t>
+          <t>Wholesale Inventories MoMDEC</t>
         </is>
       </c>
       <c r="C424" t="inlineStr">
         <is>
-          <t>3.3%</t>
+          <t>-0.5%</t>
         </is>
       </c>
       <c r="D424" t="inlineStr">
         <is>
-          <t>3.2%</t>
-        </is>
-      </c>
-      <c r="E424" t="inlineStr"/>
+          <t>-0.1%</t>
+        </is>
+      </c>
+      <c r="E424" t="inlineStr">
+        <is>
+          <t>-0.5%</t>
+        </is>
+      </c>
       <c r="F424" t="inlineStr">
         <is>
-          <t>3.3%</t>
+          <t>-0.5%</t>
         </is>
       </c>
       <c r="G424" t="n">
@@ -12938,27 +12942,23 @@
       </c>
       <c r="B425" t="inlineStr">
         <is>
-          <t>Michigan Consumer Expectations PrelFEB</t>
+          <t>Michigan Inflation Expectations PrelFEB</t>
         </is>
       </c>
       <c r="C425" t="inlineStr">
         <is>
-          <t>67.3</t>
+          <t>4.3%</t>
         </is>
       </c>
       <c r="D425" t="inlineStr">
         <is>
-          <t>69.3</t>
-        </is>
-      </c>
-      <c r="E425" t="inlineStr">
-        <is>
-          <t>70</t>
-        </is>
-      </c>
+          <t>3.3%</t>
+        </is>
+      </c>
+      <c r="E425" t="inlineStr"/>
       <c r="F425" t="inlineStr">
         <is>
-          <t>69.5</t>
+          <t>3.4%</t>
         </is>
       </c>
       <c r="G425" t="n">
@@ -12973,23 +12973,27 @@
       </c>
       <c r="B426" t="inlineStr">
         <is>
-          <t>Michigan Inflation Expectations PrelFEB</t>
+          <t>Michigan Consumer Expectations PrelFEB</t>
         </is>
       </c>
       <c r="C426" t="inlineStr">
         <is>
-          <t>4.3%</t>
+          <t>67.3</t>
         </is>
       </c>
       <c r="D426" t="inlineStr">
         <is>
-          <t>3.3%</t>
-        </is>
-      </c>
-      <c r="E426" t="inlineStr"/>
+          <t>69.3</t>
+        </is>
+      </c>
+      <c r="E426" t="inlineStr">
+        <is>
+          <t>70</t>
+        </is>
+      </c>
       <c r="F426" t="inlineStr">
         <is>
-          <t>3.4%</t>
+          <t>69.5</t>
         </is>
       </c>
       <c r="G426" t="n">
@@ -13004,27 +13008,23 @@
       </c>
       <c r="B427" t="inlineStr">
         <is>
-          <t>Michigan Current Conditions PrelFEB</t>
+          <t>Michigan 5 Year Inflation Expectations PrelFEB</t>
         </is>
       </c>
       <c r="C427" t="inlineStr">
         <is>
-          <t>68.7</t>
+          <t>3.3%</t>
         </is>
       </c>
       <c r="D427" t="inlineStr">
         <is>
-          <t>74</t>
-        </is>
-      </c>
-      <c r="E427" t="inlineStr">
-        <is>
-          <t>73</t>
-        </is>
-      </c>
+          <t>3.2%</t>
+        </is>
+      </c>
+      <c r="E427" t="inlineStr"/>
       <c r="F427" t="inlineStr">
         <is>
-          <t>74.3</t>
+          <t>3.3%</t>
         </is>
       </c>
       <c r="G427" t="n">
@@ -13039,31 +13039,31 @@
       </c>
       <c r="B428" t="inlineStr">
         <is>
-          <t>Wholesale Inventories MoMDEC</t>
+          <t>Michigan Consumer Sentiment PrelFEB</t>
         </is>
       </c>
       <c r="C428" t="inlineStr">
         <is>
-          <t>-0.5%</t>
+          <t>67.8</t>
         </is>
       </c>
       <c r="D428" t="inlineStr">
         <is>
-          <t>-0.1%</t>
+          <t>71.1</t>
         </is>
       </c>
       <c r="E428" t="inlineStr">
         <is>
-          <t>-0.5%</t>
+          <t>71.1</t>
         </is>
       </c>
       <c r="F428" t="inlineStr">
         <is>
-          <t>-0.5%</t>
+          <t>72</t>
         </is>
       </c>
       <c r="G428" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="429">
@@ -13636,27 +13636,27 @@
       </c>
       <c r="B451" t="inlineStr">
         <is>
-          <t>Inflation Rate YoYJAN</t>
+          <t>Core Inflation Rate MoMJAN</t>
         </is>
       </c>
       <c r="C451" t="inlineStr">
         <is>
-          <t>3%</t>
+          <t>0.4%</t>
         </is>
       </c>
       <c r="D451" t="inlineStr">
         <is>
-          <t>2.9%</t>
+          <t>0.2%</t>
         </is>
       </c>
       <c r="E451" t="inlineStr">
         <is>
-          <t>2.9%</t>
+          <t>0.3%</t>
         </is>
       </c>
       <c r="F451" t="inlineStr">
         <is>
-          <t>2.9%</t>
+          <t>0.3%</t>
         </is>
       </c>
       <c r="G451" t="n">
@@ -13671,27 +13671,31 @@
       </c>
       <c r="B452" t="inlineStr">
         <is>
-          <t>CPI s.aJAN</t>
+          <t>Core Inflation Rate YoYJAN</t>
         </is>
       </c>
       <c r="C452" t="inlineStr">
         <is>
-          <t>319.086</t>
+          <t>3.3%</t>
         </is>
       </c>
       <c r="D452" t="inlineStr">
         <is>
-          <t>317.603</t>
-        </is>
-      </c>
-      <c r="E452" t="inlineStr"/>
+          <t>3.2%</t>
+        </is>
+      </c>
+      <c r="E452" t="inlineStr">
+        <is>
+          <t>3.1%</t>
+        </is>
+      </c>
       <c r="F452" t="inlineStr">
         <is>
-          <t>318.2</t>
+          <t>3.1%</t>
         </is>
       </c>
       <c r="G452" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="453">
@@ -13702,31 +13706,31 @@
       </c>
       <c r="B453" t="inlineStr">
         <is>
-          <t>CPIJAN</t>
+          <t>Inflation Rate MoMJAN</t>
         </is>
       </c>
       <c r="C453" t="inlineStr">
         <is>
-          <t>317.67</t>
+          <t>0.5%</t>
         </is>
       </c>
       <c r="D453" t="inlineStr">
         <is>
-          <t>315.61</t>
+          <t>0.4%</t>
         </is>
       </c>
       <c r="E453" t="inlineStr">
         <is>
-          <t>317.46</t>
+          <t>0.3%</t>
         </is>
       </c>
       <c r="F453" t="inlineStr">
         <is>
-          <t>317.3</t>
+          <t>0.2%</t>
         </is>
       </c>
       <c r="G453" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="454">
@@ -13737,31 +13741,27 @@
       </c>
       <c r="B454" t="inlineStr">
         <is>
-          <t>Inflation Rate MoMJAN</t>
+          <t>CPI s.aJAN</t>
         </is>
       </c>
       <c r="C454" t="inlineStr">
         <is>
-          <t>0.5%</t>
+          <t>319.086</t>
         </is>
       </c>
       <c r="D454" t="inlineStr">
         <is>
-          <t>0.4%</t>
-        </is>
-      </c>
-      <c r="E454" t="inlineStr">
-        <is>
-          <t>0.3%</t>
-        </is>
-      </c>
+          <t>317.603</t>
+        </is>
+      </c>
+      <c r="E454" t="inlineStr"/>
       <c r="F454" t="inlineStr">
         <is>
-          <t>0.2%</t>
+          <t>318.2</t>
         </is>
       </c>
       <c r="G454" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="455">
@@ -13772,31 +13772,31 @@
       </c>
       <c r="B455" t="inlineStr">
         <is>
-          <t>Core Inflation Rate YoYJAN</t>
+          <t>CPIJAN</t>
         </is>
       </c>
       <c r="C455" t="inlineStr">
         <is>
-          <t>3.3%</t>
+          <t>317.67</t>
         </is>
       </c>
       <c r="D455" t="inlineStr">
         <is>
-          <t>3.2%</t>
+          <t>315.61</t>
         </is>
       </c>
       <c r="E455" t="inlineStr">
         <is>
-          <t>3.1%</t>
+          <t>317.46</t>
         </is>
       </c>
       <c r="F455" t="inlineStr">
         <is>
-          <t>3.1%</t>
+          <t>317.3</t>
         </is>
       </c>
       <c r="G455" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="456">
@@ -13807,27 +13807,27 @@
       </c>
       <c r="B456" t="inlineStr">
         <is>
-          <t>Core Inflation Rate MoMJAN</t>
+          <t>Inflation Rate YoYJAN</t>
         </is>
       </c>
       <c r="C456" t="inlineStr">
         <is>
-          <t>0.4%</t>
+          <t>3%</t>
         </is>
       </c>
       <c r="D456" t="inlineStr">
         <is>
-          <t>0.2%</t>
+          <t>2.9%</t>
         </is>
       </c>
       <c r="E456" t="inlineStr">
         <is>
-          <t>0.3%</t>
+          <t>2.9%</t>
         </is>
       </c>
       <c r="F456" t="inlineStr">
         <is>
-          <t>0.3%</t>
+          <t>2.9%</t>
         </is>
       </c>
       <c r="G456" t="n">
@@ -13842,23 +13842,27 @@
       </c>
       <c r="B457" t="inlineStr">
         <is>
-          <t>EIA Refinery Crude Runs ChangeFEB/07</t>
+          <t>EIA Crude Oil Stocks ChangeFEB/07</t>
         </is>
       </c>
       <c r="C457" t="inlineStr">
         <is>
-          <t>0.082M</t>
+          <t>4.07M</t>
         </is>
       </c>
       <c r="D457" t="inlineStr">
         <is>
-          <t>0.16M</t>
-        </is>
-      </c>
-      <c r="E457" t="inlineStr"/>
+          <t>8.664M</t>
+        </is>
+      </c>
+      <c r="E457" t="inlineStr">
+        <is>
+          <t>3M</t>
+        </is>
+      </c>
       <c r="F457" t="inlineStr"/>
       <c r="G457" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="458">
@@ -13869,17 +13873,17 @@
       </c>
       <c r="B458" t="inlineStr">
         <is>
-          <t>EIA Gasoline Production ChangeFEB/07</t>
+          <t>EIA Heating Oil Stocks ChangeFEB/07</t>
         </is>
       </c>
       <c r="C458" t="inlineStr">
         <is>
-          <t>0.18M</t>
+          <t>0.159M</t>
         </is>
       </c>
       <c r="D458" t="inlineStr">
         <is>
-          <t>-0.027M</t>
+          <t>0.373M</t>
         </is>
       </c>
       <c r="E458" t="inlineStr"/>
@@ -13896,27 +13900,23 @@
       </c>
       <c r="B459" t="inlineStr">
         <is>
-          <t>EIA Gasoline Stocks ChangeFEB/07</t>
+          <t>EIA Cushing Crude Oil Stocks ChangeFEB/07</t>
         </is>
       </c>
       <c r="C459" t="inlineStr">
         <is>
-          <t>-3.035M</t>
+          <t>0.872M</t>
         </is>
       </c>
       <c r="D459" t="inlineStr">
         <is>
-          <t>2.233M</t>
-        </is>
-      </c>
-      <c r="E459" t="inlineStr">
-        <is>
-          <t>1.5M</t>
-        </is>
-      </c>
+          <t>-0.034M</t>
+        </is>
+      </c>
+      <c r="E459" t="inlineStr"/>
       <c r="F459" t="inlineStr"/>
       <c r="G459" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="460">
@@ -13927,17 +13927,17 @@
       </c>
       <c r="B460" t="inlineStr">
         <is>
-          <t>EIA Crude Oil Imports ChangeFEB/07</t>
+          <t>EIA Distillate Fuel Production ChangeFEB/07</t>
         </is>
       </c>
       <c r="C460" t="inlineStr">
         <is>
-          <t>-0.184M</t>
+          <t>-0.009M</t>
         </is>
       </c>
       <c r="D460" t="inlineStr">
         <is>
-          <t>-0.178M</t>
+          <t>-0.186M</t>
         </is>
       </c>
       <c r="E460" t="inlineStr"/>
@@ -13954,20 +13954,24 @@
       </c>
       <c r="B461" t="inlineStr">
         <is>
-          <t>EIA Distillate Fuel Production ChangeFEB/07</t>
+          <t>EIA Distillate Stocks ChangeFEB/07</t>
         </is>
       </c>
       <c r="C461" t="inlineStr">
         <is>
-          <t>-0.009M</t>
+          <t>0.135M</t>
         </is>
       </c>
       <c r="D461" t="inlineStr">
         <is>
-          <t>-0.186M</t>
-        </is>
-      </c>
-      <c r="E461" t="inlineStr"/>
+          <t>-5.471M</t>
+        </is>
+      </c>
+      <c r="E461" t="inlineStr">
+        <is>
+          <t>-2M</t>
+        </is>
+      </c>
       <c r="F461" t="inlineStr"/>
       <c r="G461" t="n">
         <v>3</v>
@@ -13981,23 +13985,27 @@
       </c>
       <c r="B462" t="inlineStr">
         <is>
-          <t>EIA Cushing Crude Oil Stocks ChangeFEB/07</t>
+          <t>EIA Gasoline Stocks ChangeFEB/07</t>
         </is>
       </c>
       <c r="C462" t="inlineStr">
         <is>
-          <t>0.872M</t>
+          <t>-3.035M</t>
         </is>
       </c>
       <c r="D462" t="inlineStr">
         <is>
-          <t>-0.034M</t>
-        </is>
-      </c>
-      <c r="E462" t="inlineStr"/>
+          <t>2.233M</t>
+        </is>
+      </c>
+      <c r="E462" t="inlineStr">
+        <is>
+          <t>1.5M</t>
+        </is>
+      </c>
       <c r="F462" t="inlineStr"/>
       <c r="G462" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="463">
@@ -14008,17 +14016,17 @@
       </c>
       <c r="B463" t="inlineStr">
         <is>
-          <t>EIA Heating Oil Stocks ChangeFEB/07</t>
+          <t>EIA Gasoline Production ChangeFEB/07</t>
         </is>
       </c>
       <c r="C463" t="inlineStr">
         <is>
-          <t>0.159M</t>
+          <t>0.18M</t>
         </is>
       </c>
       <c r="D463" t="inlineStr">
         <is>
-          <t>0.373M</t>
+          <t>-0.027M</t>
         </is>
       </c>
       <c r="E463" t="inlineStr"/>
@@ -14035,27 +14043,23 @@
       </c>
       <c r="B464" t="inlineStr">
         <is>
-          <t>EIA Crude Oil Stocks ChangeFEB/07</t>
+          <t>EIA Refinery Crude Runs ChangeFEB/07</t>
         </is>
       </c>
       <c r="C464" t="inlineStr">
         <is>
-          <t>4.07M</t>
+          <t>0.082M</t>
         </is>
       </c>
       <c r="D464" t="inlineStr">
         <is>
-          <t>8.664M</t>
-        </is>
-      </c>
-      <c r="E464" t="inlineStr">
-        <is>
-          <t>3M</t>
-        </is>
-      </c>
+          <t>0.16M</t>
+        </is>
+      </c>
+      <c r="E464" t="inlineStr"/>
       <c r="F464" t="inlineStr"/>
       <c r="G464" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="465">
@@ -14066,24 +14070,20 @@
       </c>
       <c r="B465" t="inlineStr">
         <is>
-          <t>EIA Distillate Stocks ChangeFEB/07</t>
+          <t>EIA Crude Oil Imports ChangeFEB/07</t>
         </is>
       </c>
       <c r="C465" t="inlineStr">
         <is>
-          <t>0.135M</t>
+          <t>-0.184M</t>
         </is>
       </c>
       <c r="D465" t="inlineStr">
         <is>
-          <t>-5.471M</t>
-        </is>
-      </c>
-      <c r="E465" t="inlineStr">
-        <is>
-          <t>-2M</t>
-        </is>
-      </c>
+          <t>-0.178M</t>
+        </is>
+      </c>
+      <c r="E465" t="inlineStr"/>
       <c r="F465" t="inlineStr"/>
       <c r="G465" t="n">
         <v>3</v>
@@ -14224,31 +14224,31 @@
       </c>
       <c r="B471" t="inlineStr">
         <is>
-          <t>PPI YoYJAN</t>
+          <t>PPI MoMJAN</t>
         </is>
       </c>
       <c r="C471" t="inlineStr">
         <is>
-          <t>3.5%</t>
+          <t>0.4%</t>
         </is>
       </c>
       <c r="D471" t="inlineStr">
         <is>
-          <t>3.5%</t>
+          <t>0.5%</t>
         </is>
       </c>
       <c r="E471" t="inlineStr">
         <is>
-          <t>3.2%</t>
+          <t>0.3%</t>
         </is>
       </c>
       <c r="F471" t="inlineStr">
         <is>
-          <t>3.4%</t>
+          <t>0.3%</t>
         </is>
       </c>
       <c r="G471" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="472">
@@ -14259,31 +14259,31 @@
       </c>
       <c r="B472" t="inlineStr">
         <is>
-          <t>Initial Jobless ClaimsFEB/08</t>
+          <t>PPI Ex Food, Energy and Trade YoYJAN</t>
         </is>
       </c>
       <c r="C472" t="inlineStr">
         <is>
-          <t>213K</t>
+          <t>3.4%</t>
         </is>
       </c>
       <c r="D472" t="inlineStr">
         <is>
-          <t>220K</t>
+          <t>3.5%</t>
         </is>
       </c>
       <c r="E472" t="inlineStr">
         <is>
-          <t>215K</t>
+          <t>3.2%</t>
         </is>
       </c>
       <c r="F472" t="inlineStr">
         <is>
-          <t>215.0K</t>
+          <t>3.3%</t>
         </is>
       </c>
       <c r="G472" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="473">
@@ -14294,27 +14294,23 @@
       </c>
       <c r="B473" t="inlineStr">
         <is>
-          <t>Core PPI YoYJAN</t>
+          <t>PPI Ex Food, Energy and Trade MoMJAN</t>
         </is>
       </c>
       <c r="C473" t="inlineStr">
         <is>
-          <t>3.6%</t>
+          <t>0.3%</t>
         </is>
       </c>
       <c r="D473" t="inlineStr">
         <is>
-          <t>3.7%</t>
-        </is>
-      </c>
-      <c r="E473" t="inlineStr">
-        <is>
-          <t>3.3%</t>
-        </is>
-      </c>
+          <t>0.4%</t>
+        </is>
+      </c>
+      <c r="E473" t="inlineStr"/>
       <c r="F473" t="inlineStr">
         <is>
-          <t>3.5%</t>
+          <t>0.2%</t>
         </is>
       </c>
       <c r="G473" t="n">
@@ -14329,31 +14325,27 @@
       </c>
       <c r="B474" t="inlineStr">
         <is>
-          <t>Core PPI MoMJAN</t>
+          <t>Jobless Claims 4-week AverageFEB/08</t>
         </is>
       </c>
       <c r="C474" t="inlineStr">
         <is>
-          <t>0.3%</t>
+          <t>216K</t>
         </is>
       </c>
       <c r="D474" t="inlineStr">
         <is>
-          <t>0.4%</t>
-        </is>
-      </c>
-      <c r="E474" t="inlineStr">
-        <is>
-          <t>0.3%</t>
-        </is>
-      </c>
+          <t>217K</t>
+        </is>
+      </c>
+      <c r="E474" t="inlineStr"/>
       <c r="F474" t="inlineStr">
         <is>
-          <t>0.1%</t>
+          <t>216.0K</t>
         </is>
       </c>
       <c r="G474" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="475">
@@ -14364,23 +14356,27 @@
       </c>
       <c r="B475" t="inlineStr">
         <is>
-          <t>PPIJAN</t>
+          <t>Continuing Jobless ClaimsFEB/01</t>
         </is>
       </c>
       <c r="C475" t="inlineStr">
         <is>
-          <t>147.716</t>
+          <t>1850K</t>
         </is>
       </c>
       <c r="D475" t="inlineStr">
         <is>
-          <t>147.127</t>
-        </is>
-      </c>
-      <c r="E475" t="inlineStr"/>
+          <t>1886K</t>
+        </is>
+      </c>
+      <c r="E475" t="inlineStr">
+        <is>
+          <t>1880K</t>
+        </is>
+      </c>
       <c r="F475" t="inlineStr">
         <is>
-          <t>147.2</t>
+          <t>1875.0K</t>
         </is>
       </c>
       <c r="G475" t="n">
@@ -14395,31 +14391,31 @@
       </c>
       <c r="B476" t="inlineStr">
         <is>
-          <t>Continuing Jobless ClaimsFEB/01</t>
+          <t>Initial Jobless ClaimsFEB/08</t>
         </is>
       </c>
       <c r="C476" t="inlineStr">
         <is>
-          <t>1850K</t>
+          <t>213K</t>
         </is>
       </c>
       <c r="D476" t="inlineStr">
         <is>
-          <t>1886K</t>
+          <t>220K</t>
         </is>
       </c>
       <c r="E476" t="inlineStr">
         <is>
-          <t>1880K</t>
+          <t>215K</t>
         </is>
       </c>
       <c r="F476" t="inlineStr">
         <is>
-          <t>1875.0K</t>
+          <t>215.0K</t>
         </is>
       </c>
       <c r="G476" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="477">
@@ -14430,19 +14426,19 @@
       </c>
       <c r="B477" t="inlineStr">
         <is>
-          <t>PPI MoMJAN</t>
+          <t>Core PPI MoMJAN</t>
         </is>
       </c>
       <c r="C477" t="inlineStr">
         <is>
+          <t>0.3%</t>
+        </is>
+      </c>
+      <c r="D477" t="inlineStr">
+        <is>
           <t>0.4%</t>
         </is>
       </c>
-      <c r="D477" t="inlineStr">
-        <is>
-          <t>0.5%</t>
-        </is>
-      </c>
       <c r="E477" t="inlineStr">
         <is>
           <t>0.3%</t>
@@ -14450,11 +14446,11 @@
       </c>
       <c r="F477" t="inlineStr">
         <is>
-          <t>0.3%</t>
+          <t>0.1%</t>
         </is>
       </c>
       <c r="G477" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="478">
@@ -14465,23 +14461,27 @@
       </c>
       <c r="B478" t="inlineStr">
         <is>
-          <t>Jobless Claims 4-week AverageFEB/08</t>
+          <t>Core PPI YoYJAN</t>
         </is>
       </c>
       <c r="C478" t="inlineStr">
         <is>
-          <t>216K</t>
+          <t>3.6%</t>
         </is>
       </c>
       <c r="D478" t="inlineStr">
         <is>
-          <t>217K</t>
-        </is>
-      </c>
-      <c r="E478" t="inlineStr"/>
+          <t>3.7%</t>
+        </is>
+      </c>
+      <c r="E478" t="inlineStr">
+        <is>
+          <t>3.3%</t>
+        </is>
+      </c>
       <c r="F478" t="inlineStr">
         <is>
-          <t>216.0K</t>
+          <t>3.5%</t>
         </is>
       </c>
       <c r="G478" t="n">
@@ -14496,23 +14496,27 @@
       </c>
       <c r="B479" t="inlineStr">
         <is>
-          <t>PPI Ex Food, Energy and Trade MoMJAN</t>
+          <t>PPI YoYJAN</t>
         </is>
       </c>
       <c r="C479" t="inlineStr">
         <is>
-          <t>0.3%</t>
+          <t>3.5%</t>
         </is>
       </c>
       <c r="D479" t="inlineStr">
         <is>
-          <t>0.4%</t>
-        </is>
-      </c>
-      <c r="E479" t="inlineStr"/>
+          <t>3.5%</t>
+        </is>
+      </c>
+      <c r="E479" t="inlineStr">
+        <is>
+          <t>3.2%</t>
+        </is>
+      </c>
       <c r="F479" t="inlineStr">
         <is>
-          <t>0.2%</t>
+          <t>3.4%</t>
         </is>
       </c>
       <c r="G479" t="n">
@@ -14527,27 +14531,23 @@
       </c>
       <c r="B480" t="inlineStr">
         <is>
-          <t>PPI Ex Food, Energy and Trade YoYJAN</t>
+          <t>PPIJAN</t>
         </is>
       </c>
       <c r="C480" t="inlineStr">
         <is>
-          <t>3.4%</t>
+          <t>147.716</t>
         </is>
       </c>
       <c r="D480" t="inlineStr">
         <is>
-          <t>3.5%</t>
-        </is>
-      </c>
-      <c r="E480" t="inlineStr">
-        <is>
-          <t>3.2%</t>
-        </is>
-      </c>
+          <t>147.127</t>
+        </is>
+      </c>
+      <c r="E480" t="inlineStr"/>
       <c r="F480" t="inlineStr">
         <is>
-          <t>3.3%</t>
+          <t>147.2</t>
         </is>
       </c>
       <c r="G480" t="n">
@@ -14728,27 +14728,31 @@
       </c>
       <c r="B487" t="inlineStr">
         <is>
-          <t>Retail Sales Ex Gas/Autos MoMJAN</t>
+          <t>Retail Sales Ex Autos MoMJAN</t>
         </is>
       </c>
       <c r="C487" t="inlineStr">
         <is>
-          <t>-0.5%</t>
+          <t>-0.4%</t>
         </is>
       </c>
       <c r="D487" t="inlineStr">
         <is>
-          <t>0.5%</t>
-        </is>
-      </c>
-      <c r="E487" t="inlineStr"/>
+          <t>0.7%</t>
+        </is>
+      </c>
+      <c r="E487" t="inlineStr">
+        <is>
+          <t>0.3%</t>
+        </is>
+      </c>
       <c r="F487" t="inlineStr">
         <is>
-          <t>0.2%</t>
+          <t>0.3%</t>
         </is>
       </c>
       <c r="G487" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="488">
@@ -14759,22 +14763,22 @@
       </c>
       <c r="B488" t="inlineStr">
         <is>
-          <t>Export Prices MoMJAN</t>
+          <t>Import Prices MoMJAN</t>
         </is>
       </c>
       <c r="C488" t="inlineStr">
         <is>
-          <t>1.3%</t>
+          <t>0.3%</t>
         </is>
       </c>
       <c r="D488" t="inlineStr">
         <is>
-          <t>0.5%</t>
+          <t>0.2%</t>
         </is>
       </c>
       <c r="E488" t="inlineStr">
         <is>
-          <t>0.3%</t>
+          <t>0.4%</t>
         </is>
       </c>
       <c r="F488" t="inlineStr">
@@ -14794,23 +14798,23 @@
       </c>
       <c r="B489" t="inlineStr">
         <is>
-          <t>Export Prices YoYJAN</t>
+          <t>Retail Sales YoYJAN</t>
         </is>
       </c>
       <c r="C489" t="inlineStr">
         <is>
-          <t>2.7%</t>
+          <t>4.2%</t>
         </is>
       </c>
       <c r="D489" t="inlineStr">
         <is>
-          <t>2%</t>
+          <t>4.4%</t>
         </is>
       </c>
       <c r="E489" t="inlineStr"/>
       <c r="F489" t="inlineStr">
         <is>
-          <t>2.3%</t>
+          <t>3.7%</t>
         </is>
       </c>
       <c r="G489" t="n">
@@ -14825,27 +14829,31 @@
       </c>
       <c r="B490" t="inlineStr">
         <is>
-          <t>Import Prices YoYJAN</t>
+          <t>Retail Sales Control Group MoMJAN</t>
         </is>
       </c>
       <c r="C490" t="inlineStr">
         <is>
-          <t>1.9%</t>
+          <t>-0.8%</t>
         </is>
       </c>
       <c r="D490" t="inlineStr">
         <is>
-          <t>2.2%</t>
-        </is>
-      </c>
-      <c r="E490" t="inlineStr"/>
+          <t>0.8%</t>
+        </is>
+      </c>
+      <c r="E490" t="inlineStr">
+        <is>
+          <t>0.3%</t>
+        </is>
+      </c>
       <c r="F490" t="inlineStr">
         <is>
-          <t>2.8%</t>
+          <t>0.4%</t>
         </is>
       </c>
       <c r="G490" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="491">
@@ -14856,31 +14864,31 @@
       </c>
       <c r="B491" t="inlineStr">
         <is>
-          <t>Retail Sales Control Group MoMJAN</t>
+          <t>Retail Sales MoMJAN</t>
         </is>
       </c>
       <c r="C491" t="inlineStr">
         <is>
-          <t>-0.8%</t>
+          <t>-0.9%</t>
         </is>
       </c>
       <c r="D491" t="inlineStr">
         <is>
-          <t>0.8%</t>
+          <t>0.7%</t>
         </is>
       </c>
       <c r="E491" t="inlineStr">
         <is>
-          <t>0.3%</t>
+          <t>-0.1%</t>
         </is>
       </c>
       <c r="F491" t="inlineStr">
         <is>
-          <t>0.4%</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="G491" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="492">
@@ -14891,31 +14899,27 @@
       </c>
       <c r="B492" t="inlineStr">
         <is>
-          <t>Retail Sales Ex Autos MoMJAN</t>
+          <t>Export Prices YoYJAN</t>
         </is>
       </c>
       <c r="C492" t="inlineStr">
         <is>
-          <t>-0.4%</t>
+          <t>2.7%</t>
         </is>
       </c>
       <c r="D492" t="inlineStr">
         <is>
-          <t>0.7%</t>
-        </is>
-      </c>
-      <c r="E492" t="inlineStr">
-        <is>
-          <t>0.3%</t>
-        </is>
-      </c>
+          <t>2%</t>
+        </is>
+      </c>
+      <c r="E492" t="inlineStr"/>
       <c r="F492" t="inlineStr">
         <is>
-          <t>0.3%</t>
+          <t>2.3%</t>
         </is>
       </c>
       <c r="G492" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="493">
@@ -14926,23 +14930,23 @@
       </c>
       <c r="B493" t="inlineStr">
         <is>
-          <t>Retail Sales YoYJAN</t>
+          <t>Import Prices YoYJAN</t>
         </is>
       </c>
       <c r="C493" t="inlineStr">
         <is>
-          <t>4.2%</t>
+          <t>1.9%</t>
         </is>
       </c>
       <c r="D493" t="inlineStr">
         <is>
-          <t>4.4%</t>
+          <t>2.2%</t>
         </is>
       </c>
       <c r="E493" t="inlineStr"/>
       <c r="F493" t="inlineStr">
         <is>
-          <t>3.7%</t>
+          <t>2.8%</t>
         </is>
       </c>
       <c r="G493" t="n">
@@ -14957,31 +14961,27 @@
       </c>
       <c r="B494" t="inlineStr">
         <is>
-          <t>Retail Sales MoMJAN</t>
+          <t>Retail Sales Ex Gas/Autos MoMJAN</t>
         </is>
       </c>
       <c r="C494" t="inlineStr">
         <is>
-          <t>-0.9%</t>
+          <t>-0.5%</t>
         </is>
       </c>
       <c r="D494" t="inlineStr">
         <is>
-          <t>0.7%</t>
-        </is>
-      </c>
-      <c r="E494" t="inlineStr">
-        <is>
-          <t>-0.1%</t>
-        </is>
-      </c>
+          <t>0.5%</t>
+        </is>
+      </c>
+      <c r="E494" t="inlineStr"/>
       <c r="F494" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>0.2%</t>
         </is>
       </c>
       <c r="G494" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="495">
@@ -14992,22 +14992,22 @@
       </c>
       <c r="B495" t="inlineStr">
         <is>
-          <t>Import Prices MoMJAN</t>
+          <t>Export Prices MoMJAN</t>
         </is>
       </c>
       <c r="C495" t="inlineStr">
         <is>
+          <t>1.3%</t>
+        </is>
+      </c>
+      <c r="D495" t="inlineStr">
+        <is>
+          <t>0.5%</t>
+        </is>
+      </c>
+      <c r="E495" t="inlineStr">
+        <is>
           <t>0.3%</t>
-        </is>
-      </c>
-      <c r="D495" t="inlineStr">
-        <is>
-          <t>0.2%</t>
-        </is>
-      </c>
-      <c r="E495" t="inlineStr">
-        <is>
-          <t>0.4%</t>
         </is>
       </c>
       <c r="F495" t="inlineStr">
@@ -15714,17 +15714,17 @@
       </c>
       <c r="B521" t="inlineStr">
         <is>
-          <t>MBA Mortgage ApplicationsFEB/14</t>
+          <t>MBA Purchase IndexFEB/14</t>
         </is>
       </c>
       <c r="C521" t="inlineStr">
         <is>
-          <t>-6.6%</t>
+          <t>144.0</t>
         </is>
       </c>
       <c r="D521" t="inlineStr">
         <is>
-          <t>2.3%</t>
+          <t>153.1</t>
         </is>
       </c>
       <c r="E521" t="inlineStr"/>
@@ -15741,23 +15741,23 @@
       </c>
       <c r="B522" t="inlineStr">
         <is>
-          <t>MBA 30-Year Mortgage RateFEB/14</t>
+          <t>MBA Mortgage Refinance IndexFEB/14</t>
         </is>
       </c>
       <c r="C522" t="inlineStr">
         <is>
-          <t>6.93%</t>
+          <t>593.6</t>
         </is>
       </c>
       <c r="D522" t="inlineStr">
         <is>
-          <t>6.95%</t>
+          <t>640.6</t>
         </is>
       </c>
       <c r="E522" t="inlineStr"/>
       <c r="F522" t="inlineStr"/>
       <c r="G522" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="523">
@@ -15795,17 +15795,17 @@
       </c>
       <c r="B524" t="inlineStr">
         <is>
-          <t>MBA Mortgage Refinance IndexFEB/14</t>
+          <t>MBA Mortgage ApplicationsFEB/14</t>
         </is>
       </c>
       <c r="C524" t="inlineStr">
         <is>
-          <t>593.6</t>
+          <t>-6.6%</t>
         </is>
       </c>
       <c r="D524" t="inlineStr">
         <is>
-          <t>640.6</t>
+          <t>2.3%</t>
         </is>
       </c>
       <c r="E524" t="inlineStr"/>
@@ -15822,23 +15822,23 @@
       </c>
       <c r="B525" t="inlineStr">
         <is>
-          <t>MBA Purchase IndexFEB/14</t>
+          <t>MBA 30-Year Mortgage RateFEB/14</t>
         </is>
       </c>
       <c r="C525" t="inlineStr">
         <is>
-          <t>144.0</t>
+          <t>6.93%</t>
         </is>
       </c>
       <c r="D525" t="inlineStr">
         <is>
-          <t>153.1</t>
+          <t>6.95%</t>
         </is>
       </c>
       <c r="E525" t="inlineStr"/>
       <c r="F525" t="inlineStr"/>
       <c r="G525" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="526">
@@ -16510,17 +16510,17 @@
       </c>
       <c r="B549" t="inlineStr">
         <is>
-          <t>4-Week Bill Auction</t>
+          <t>8-Week Bill Auction</t>
         </is>
       </c>
       <c r="C549" t="inlineStr">
         <is>
-          <t>4.245%</t>
+          <t>4.235%</t>
         </is>
       </c>
       <c r="D549" t="inlineStr">
         <is>
-          <t>4.250%</t>
+          <t>4.240%</t>
         </is>
       </c>
       <c r="E549" t="inlineStr"/>
@@ -16537,17 +16537,17 @@
       </c>
       <c r="B550" t="inlineStr">
         <is>
-          <t>8-Week Bill Auction</t>
+          <t>4-Week Bill Auction</t>
         </is>
       </c>
       <c r="C550" t="inlineStr">
         <is>
-          <t>4.235%</t>
+          <t>4.245%</t>
         </is>
       </c>
       <c r="D550" t="inlineStr">
         <is>
-          <t>4.240%</t>
+          <t>4.250%</t>
         </is>
       </c>
       <c r="E550" t="inlineStr"/>
@@ -17326,7 +17326,7 @@
       </c>
       <c r="B577" t="inlineStr">
         <is>
-          <t>Fed Jefferson Speech</t>
+          <t>Fed Daly Speech</t>
         </is>
       </c>
       <c r="C577" t="inlineStr"/>
@@ -17345,7 +17345,7 @@
       </c>
       <c r="B578" t="inlineStr">
         <is>
-          <t>Fed Daly Speech</t>
+          <t>Fed Jefferson Speech</t>
         </is>
       </c>
       <c r="C578" t="inlineStr"/>
@@ -17630,31 +17630,27 @@
       </c>
       <c r="B589" t="inlineStr">
         <is>
-          <t>S&amp;P/Case-Shiller Home Price YoYDEC</t>
+          <t>House Price IndexDEC</t>
         </is>
       </c>
       <c r="C589" t="inlineStr">
         <is>
-          <t>4.5%</t>
+          <t>436.1</t>
         </is>
       </c>
       <c r="D589" t="inlineStr">
         <is>
-          <t>4.3%</t>
-        </is>
-      </c>
-      <c r="E589" t="inlineStr">
-        <is>
-          <t>4.4%</t>
-        </is>
-      </c>
+          <t>434.3</t>
+        </is>
+      </c>
+      <c r="E589" t="inlineStr"/>
       <c r="F589" t="inlineStr">
         <is>
-          <t>4.4%</t>
+          <t>434.3</t>
         </is>
       </c>
       <c r="G589" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="590">
@@ -17668,10 +17664,14 @@
           <t>House Price Index YoYDEC</t>
         </is>
       </c>
-      <c r="C590" t="inlineStr"/>
+      <c r="C590" t="inlineStr">
+        <is>
+          <t>4.7%</t>
+        </is>
+      </c>
       <c r="D590" t="inlineStr">
         <is>
-          <t>4.2%</t>
+          <t>4.5%</t>
         </is>
       </c>
       <c r="E590" t="inlineStr"/>
@@ -17692,19 +17692,23 @@
       </c>
       <c r="B591" t="inlineStr">
         <is>
-          <t>House Price IndexDEC</t>
-        </is>
-      </c>
-      <c r="C591" t="inlineStr"/>
+          <t>S&amp;P/Case-Shiller Home Price MoMDEC</t>
+        </is>
+      </c>
+      <c r="C591" t="inlineStr">
+        <is>
+          <t>-0.1%</t>
+        </is>
+      </c>
       <c r="D591" t="inlineStr">
         <is>
-          <t>433.4</t>
+          <t>-0.1%</t>
         </is>
       </c>
       <c r="E591" t="inlineStr"/>
       <c r="F591" t="inlineStr">
         <is>
-          <t>434.3</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="G591" t="n">
@@ -17719,19 +17723,27 @@
       </c>
       <c r="B592" t="inlineStr">
         <is>
-          <t>S&amp;P/Case-Shiller Home Price MoMDEC</t>
-        </is>
-      </c>
-      <c r="C592" t="inlineStr"/>
+          <t>House Price Index MoMDEC</t>
+        </is>
+      </c>
+      <c r="C592" t="inlineStr">
+        <is>
+          <t>0.4%</t>
+        </is>
+      </c>
       <c r="D592" t="inlineStr">
         <is>
-          <t>-0.1%</t>
-        </is>
-      </c>
-      <c r="E592" t="inlineStr"/>
+          <t>0.4%</t>
+        </is>
+      </c>
+      <c r="E592" t="inlineStr">
+        <is>
+          <t>0.2%</t>
+        </is>
+      </c>
       <c r="F592" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>0.2%</t>
         </is>
       </c>
       <c r="G592" t="n">
@@ -17746,27 +17758,27 @@
       </c>
       <c r="B593" t="inlineStr">
         <is>
-          <t>S&amp;P/Case-Shiller Home Price YoYDEC</t>
+          <t>House Price Index MoMDEC</t>
         </is>
       </c>
       <c r="C593" t="inlineStr"/>
       <c r="D593" t="inlineStr">
         <is>
-          <t>4.3%</t>
+          <t>0.3%</t>
         </is>
       </c>
       <c r="E593" t="inlineStr">
         <is>
-          <t>4.4%</t>
+          <t>0.2%</t>
         </is>
       </c>
       <c r="F593" t="inlineStr">
         <is>
-          <t>4.4%</t>
+          <t>0.2%</t>
         </is>
       </c>
       <c r="G593" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="594">
@@ -17777,27 +17789,19 @@
       </c>
       <c r="B594" t="inlineStr">
         <is>
-          <t>House Price Index MoMDEC</t>
-        </is>
-      </c>
-      <c r="C594" t="inlineStr">
-        <is>
-          <t>0.4%</t>
-        </is>
-      </c>
+          <t>S&amp;P/Case-Shiller Home Price MoMDEC</t>
+        </is>
+      </c>
+      <c r="C594" t="inlineStr"/>
       <c r="D594" t="inlineStr">
         <is>
-          <t>0.4%</t>
-        </is>
-      </c>
-      <c r="E594" t="inlineStr">
-        <is>
-          <t>0.2%</t>
-        </is>
-      </c>
+          <t>-0.1%</t>
+        </is>
+      </c>
+      <c r="E594" t="inlineStr"/>
       <c r="F594" t="inlineStr">
         <is>
-          <t>0.2%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="G594" t="n">
@@ -17812,23 +17816,19 @@
       </c>
       <c r="B595" t="inlineStr">
         <is>
-          <t>House Price Index MoMDEC</t>
+          <t>House Price IndexDEC</t>
         </is>
       </c>
       <c r="C595" t="inlineStr"/>
       <c r="D595" t="inlineStr">
         <is>
-          <t>0.3%</t>
-        </is>
-      </c>
-      <c r="E595" t="inlineStr">
-        <is>
-          <t>0.2%</t>
-        </is>
-      </c>
+          <t>433.4</t>
+        </is>
+      </c>
+      <c r="E595" t="inlineStr"/>
       <c r="F595" t="inlineStr">
         <is>
-          <t>0.2%</t>
+          <t>434.3</t>
         </is>
       </c>
       <c r="G595" t="n">
@@ -17843,23 +17843,19 @@
       </c>
       <c r="B596" t="inlineStr">
         <is>
-          <t>S&amp;P/Case-Shiller Home Price MoMDEC</t>
-        </is>
-      </c>
-      <c r="C596" t="inlineStr">
-        <is>
-          <t>-0.1%</t>
-        </is>
-      </c>
+          <t>House Price Index YoYDEC</t>
+        </is>
+      </c>
+      <c r="C596" t="inlineStr"/>
       <c r="D596" t="inlineStr">
         <is>
-          <t>-0.1%</t>
+          <t>4.2%</t>
         </is>
       </c>
       <c r="E596" t="inlineStr"/>
       <c r="F596" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>4.1%</t>
         </is>
       </c>
       <c r="G596" t="n">
@@ -17874,27 +17870,31 @@
       </c>
       <c r="B597" t="inlineStr">
         <is>
-          <t>House Price Index YoYDEC</t>
+          <t>S&amp;P/Case-Shiller Home Price YoYDEC</t>
         </is>
       </c>
       <c r="C597" t="inlineStr">
         <is>
-          <t>4.7%</t>
+          <t>4.5%</t>
         </is>
       </c>
       <c r="D597" t="inlineStr">
         <is>
-          <t>4.5%</t>
-        </is>
-      </c>
-      <c r="E597" t="inlineStr"/>
+          <t>4.3%</t>
+        </is>
+      </c>
+      <c r="E597" t="inlineStr">
+        <is>
+          <t>4.4%</t>
+        </is>
+      </c>
       <c r="F597" t="inlineStr">
         <is>
-          <t>4.1%</t>
+          <t>4.4%</t>
         </is>
       </c>
       <c r="G597" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="598">
@@ -17905,27 +17905,27 @@
       </c>
       <c r="B598" t="inlineStr">
         <is>
-          <t>House Price IndexDEC</t>
-        </is>
-      </c>
-      <c r="C598" t="inlineStr">
-        <is>
-          <t>436.1</t>
-        </is>
-      </c>
+          <t>S&amp;P/Case-Shiller Home Price YoYDEC</t>
+        </is>
+      </c>
+      <c r="C598" t="inlineStr"/>
       <c r="D598" t="inlineStr">
         <is>
-          <t>434.3</t>
-        </is>
-      </c>
-      <c r="E598" t="inlineStr"/>
+          <t>4.3%</t>
+        </is>
+      </c>
+      <c r="E598" t="inlineStr">
+        <is>
+          <t>4.4%</t>
+        </is>
+      </c>
       <c r="F598" t="inlineStr">
         <is>
-          <t>434.3</t>
+          <t>4.4%</t>
         </is>
       </c>
       <c r="G598" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="599">
@@ -17939,11 +17939,7 @@
           <t>Richmond Fed Manufacturing Shipments IndexFEB</t>
         </is>
       </c>
-      <c r="C599" t="inlineStr">
-        <is>
-          <t>12</t>
-        </is>
-      </c>
+      <c r="C599" t="inlineStr"/>
       <c r="D599" t="inlineStr">
         <is>
           <t>-9</t>
@@ -17970,11 +17966,7 @@
           <t>Richmond Fed Manufacturing IndexFEB</t>
         </is>
       </c>
-      <c r="C600" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
+      <c r="C600" t="inlineStr"/>
       <c r="D600" t="inlineStr">
         <is>
           <t>-4</t>
@@ -18002,31 +17994,23 @@
       </c>
       <c r="B601" t="inlineStr">
         <is>
-          <t>CB Consumer ConfidenceFEB</t>
-        </is>
-      </c>
-      <c r="C601" t="inlineStr">
-        <is>
-          <t>98.3</t>
-        </is>
-      </c>
+          <t>Richmond Fed Services Revenues IndexFEB</t>
+        </is>
+      </c>
+      <c r="C601" t="inlineStr"/>
       <c r="D601" t="inlineStr">
         <is>
-          <t>105.3</t>
-        </is>
-      </c>
-      <c r="E601" t="inlineStr">
-        <is>
-          <t>102.5</t>
-        </is>
-      </c>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="E601" t="inlineStr"/>
       <c r="F601" t="inlineStr">
         <is>
-          <t>103</t>
+          <t>7</t>
         </is>
       </c>
       <c r="G601" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="602">
@@ -18037,27 +18021,27 @@
       </c>
       <c r="B602" t="inlineStr">
         <is>
-          <t>Richmond Fed Services Revenues IndexFEB</t>
-        </is>
-      </c>
-      <c r="C602" t="inlineStr">
-        <is>
-          <t>11</t>
-        </is>
-      </c>
+          <t>CB Consumer ConfidenceFEB</t>
+        </is>
+      </c>
+      <c r="C602" t="inlineStr"/>
       <c r="D602" t="inlineStr">
         <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="E602" t="inlineStr"/>
+          <t>104.1</t>
+        </is>
+      </c>
+      <c r="E602" t="inlineStr">
+        <is>
+          <t>103</t>
+        </is>
+      </c>
       <c r="F602" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>103</t>
         </is>
       </c>
       <c r="G602" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="603">
@@ -18068,23 +18052,31 @@
       </c>
       <c r="B603" t="inlineStr">
         <is>
-          <t>Richmond Fed Services Revenues IndexFEB</t>
-        </is>
-      </c>
-      <c r="C603" t="inlineStr"/>
+          <t>CB Consumer ConfidenceFEB</t>
+        </is>
+      </c>
+      <c r="C603" t="inlineStr">
+        <is>
+          <t>98.3</t>
+        </is>
+      </c>
       <c r="D603" t="inlineStr">
         <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="E603" t="inlineStr"/>
+          <t>105.3</t>
+        </is>
+      </c>
+      <c r="E603" t="inlineStr">
+        <is>
+          <t>102.5</t>
+        </is>
+      </c>
       <c r="F603" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>103</t>
         </is>
       </c>
       <c r="G603" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="604">
@@ -18098,7 +18090,11 @@
           <t>Richmond Fed Manufacturing IndexFEB</t>
         </is>
       </c>
-      <c r="C604" t="inlineStr"/>
+      <c r="C604" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
       <c r="D604" t="inlineStr">
         <is>
           <t>-4</t>
@@ -18126,27 +18122,27 @@
       </c>
       <c r="B605" t="inlineStr">
         <is>
-          <t>CB Consumer ConfidenceFEB</t>
-        </is>
-      </c>
-      <c r="C605" t="inlineStr"/>
+          <t>Richmond Fed Manufacturing Shipments IndexFEB</t>
+        </is>
+      </c>
+      <c r="C605" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
       <c r="D605" t="inlineStr">
         <is>
-          <t>104.1</t>
-        </is>
-      </c>
-      <c r="E605" t="inlineStr">
-        <is>
-          <t>103</t>
-        </is>
-      </c>
+          <t>-9</t>
+        </is>
+      </c>
+      <c r="E605" t="inlineStr"/>
       <c r="F605" t="inlineStr">
         <is>
-          <t>103</t>
+          <t>-4</t>
         </is>
       </c>
       <c r="G605" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="606">
@@ -18157,19 +18153,23 @@
       </c>
       <c r="B606" t="inlineStr">
         <is>
-          <t>Richmond Fed Manufacturing Shipments IndexFEB</t>
-        </is>
-      </c>
-      <c r="C606" t="inlineStr"/>
+          <t>Richmond Fed Services Revenues IndexFEB</t>
+        </is>
+      </c>
+      <c r="C606" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
       <c r="D606" t="inlineStr">
         <is>
-          <t>-9</t>
+          <t>4</t>
         </is>
       </c>
       <c r="E606" t="inlineStr"/>
       <c r="F606" t="inlineStr">
         <is>
-          <t>-4</t>
+          <t>7</t>
         </is>
       </c>
       <c r="G606" t="n">
@@ -18322,7 +18322,11 @@
           <t>Money SupplyJAN</t>
         </is>
       </c>
-      <c r="C612" t="inlineStr"/>
+      <c r="C612" t="inlineStr">
+        <is>
+          <t>$21.56T</t>
+        </is>
+      </c>
       <c r="D612" t="inlineStr">
         <is>
           <t>$21.53T</t>
@@ -18342,13 +18346,13 @@
       </c>
       <c r="B613" t="inlineStr">
         <is>
-          <t>5-Year Note Auction</t>
+          <t>Money SupplyJAN</t>
         </is>
       </c>
       <c r="C613" t="inlineStr"/>
       <c r="D613" t="inlineStr">
         <is>
-          <t>4.33%</t>
+          <t>$21.53T</t>
         </is>
       </c>
       <c r="E613" t="inlineStr"/>
@@ -18365,15 +18369,19 @@
       </c>
       <c r="B614" t="inlineStr">
         <is>
-          <t>Fed Barkin Speech</t>
+          <t>5-Year Note Auction</t>
         </is>
       </c>
       <c r="C614" t="inlineStr"/>
-      <c r="D614" t="inlineStr"/>
+      <c r="D614" t="inlineStr">
+        <is>
+          <t>4.33%</t>
+        </is>
+      </c>
       <c r="E614" t="inlineStr"/>
       <c r="F614" t="inlineStr"/>
       <c r="G614" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="615">
@@ -18384,23 +18392,15 @@
       </c>
       <c r="B615" t="inlineStr">
         <is>
-          <t>Money SupplyJAN</t>
-        </is>
-      </c>
-      <c r="C615" t="inlineStr">
-        <is>
-          <t>$21.56T</t>
-        </is>
-      </c>
-      <c r="D615" t="inlineStr">
-        <is>
-          <t>$21.53T</t>
-        </is>
-      </c>
+          <t>Fed Barkin Speech</t>
+        </is>
+      </c>
+      <c r="C615" t="inlineStr"/>
+      <c r="D615" t="inlineStr"/>
       <c r="E615" t="inlineStr"/>
       <c r="F615" t="inlineStr"/>
       <c r="G615" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="616">
@@ -18654,13 +18654,13 @@
       </c>
       <c r="B625" t="inlineStr">
         <is>
-          <t>MBA Mortgage ApplicationsFEB/21</t>
+          <t>MBA Mortgage Refinance IndexFEB/21</t>
         </is>
       </c>
       <c r="C625" t="inlineStr"/>
       <c r="D625" t="inlineStr">
         <is>
-          <t>-6.6%</t>
+          <t>593.6</t>
         </is>
       </c>
       <c r="E625" t="inlineStr"/>
@@ -18677,19 +18677,19 @@
       </c>
       <c r="B626" t="inlineStr">
         <is>
-          <t>MBA 30-Year Mortgage RateFEB/21</t>
+          <t>MBA Purchase IndexFEB/21</t>
         </is>
       </c>
       <c r="C626" t="inlineStr"/>
       <c r="D626" t="inlineStr">
         <is>
-          <t>6.93%</t>
+          <t>144.0</t>
         </is>
       </c>
       <c r="E626" t="inlineStr"/>
       <c r="F626" t="inlineStr"/>
       <c r="G626" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="627">
@@ -18700,19 +18700,19 @@
       </c>
       <c r="B627" t="inlineStr">
         <is>
-          <t>MBA Purchase IndexFEB/21</t>
+          <t>MBA 30-Year Mortgage RateFEB/21</t>
         </is>
       </c>
       <c r="C627" t="inlineStr"/>
       <c r="D627" t="inlineStr">
         <is>
-          <t>144.0</t>
+          <t>6.93%</t>
         </is>
       </c>
       <c r="E627" t="inlineStr"/>
       <c r="F627" t="inlineStr"/>
       <c r="G627" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="628">
@@ -18723,13 +18723,13 @@
       </c>
       <c r="B628" t="inlineStr">
         <is>
-          <t>MBA Mortgage Refinance IndexFEB/21</t>
+          <t>MBA Mortgage ApplicationsFEB/21</t>
         </is>
       </c>
       <c r="C628" t="inlineStr"/>
       <c r="D628" t="inlineStr">
         <is>
-          <t>593.6</t>
+          <t>-6.6%</t>
         </is>
       </c>
       <c r="E628" t="inlineStr"/>
@@ -19048,13 +19048,13 @@
       </c>
       <c r="B639" t="inlineStr">
         <is>
-          <t>EIA Heating Oil Stocks ChangeFEB/21</t>
+          <t>EIA Cushing Crude Oil Stocks ChangeFEB/21</t>
         </is>
       </c>
       <c r="C639" t="inlineStr"/>
       <c r="D639" t="inlineStr">
         <is>
-          <t>-0.343M</t>
+          <t>1.472M</t>
         </is>
       </c>
       <c r="E639" t="inlineStr"/>
@@ -19071,19 +19071,23 @@
       </c>
       <c r="B640" t="inlineStr">
         <is>
-          <t>EIA Gasoline Production ChangeFEB/21</t>
+          <t>EIA Gasoline Stocks ChangeFEB/21</t>
         </is>
       </c>
       <c r="C640" t="inlineStr"/>
       <c r="D640" t="inlineStr">
         <is>
-          <t>-0.156M</t>
-        </is>
-      </c>
-      <c r="E640" t="inlineStr"/>
+          <t>-0.151M</t>
+        </is>
+      </c>
+      <c r="E640" t="inlineStr">
+        <is>
+          <t>-1.30M</t>
+        </is>
+      </c>
       <c r="F640" t="inlineStr"/>
       <c r="G640" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="641">
@@ -19094,23 +19098,23 @@
       </c>
       <c r="B641" t="inlineStr">
         <is>
-          <t>EIA Distillate Stocks ChangeFEB/21</t>
+          <t>EIA Crude Oil Stocks ChangeFEB/21</t>
         </is>
       </c>
       <c r="C641" t="inlineStr"/>
       <c r="D641" t="inlineStr">
         <is>
-          <t>-2.051M</t>
+          <t>4.633M</t>
         </is>
       </c>
       <c r="E641" t="inlineStr">
         <is>
-          <t>1.63M</t>
+          <t>2.34M</t>
         </is>
       </c>
       <c r="F641" t="inlineStr"/>
       <c r="G641" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="642">
@@ -19144,23 +19148,23 @@
       </c>
       <c r="B643" t="inlineStr">
         <is>
-          <t>EIA Crude Oil Stocks ChangeFEB/21</t>
+          <t>EIA Distillate Stocks ChangeFEB/21</t>
         </is>
       </c>
       <c r="C643" t="inlineStr"/>
       <c r="D643" t="inlineStr">
         <is>
-          <t>4.633M</t>
+          <t>-2.051M</t>
         </is>
       </c>
       <c r="E643" t="inlineStr">
         <is>
-          <t>2.34M</t>
+          <t>1.63M</t>
         </is>
       </c>
       <c r="F643" t="inlineStr"/>
       <c r="G643" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="644">
@@ -19171,23 +19175,19 @@
       </c>
       <c r="B644" t="inlineStr">
         <is>
-          <t>EIA Gasoline Stocks ChangeFEB/21</t>
+          <t>EIA Gasoline Production ChangeFEB/21</t>
         </is>
       </c>
       <c r="C644" t="inlineStr"/>
       <c r="D644" t="inlineStr">
         <is>
-          <t>-0.151M</t>
-        </is>
-      </c>
-      <c r="E644" t="inlineStr">
-        <is>
-          <t>-1.30M</t>
-        </is>
-      </c>
+          <t>-0.156M</t>
+        </is>
+      </c>
+      <c r="E644" t="inlineStr"/>
       <c r="F644" t="inlineStr"/>
       <c r="G644" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="645">
@@ -19198,13 +19198,13 @@
       </c>
       <c r="B645" t="inlineStr">
         <is>
-          <t>EIA Cushing Crude Oil Stocks ChangeFEB/21</t>
+          <t>EIA Heating Oil Stocks ChangeFEB/21</t>
         </is>
       </c>
       <c r="C645" t="inlineStr"/>
       <c r="D645" t="inlineStr">
         <is>
-          <t>1.472M</t>
+          <t>-0.343M</t>
         </is>
       </c>
       <c r="E645" t="inlineStr"/>
@@ -19221,13 +19221,13 @@
       </c>
       <c r="B646" t="inlineStr">
         <is>
-          <t>EIA Crude Oil Imports ChangeFEB/21</t>
+          <t>EIA Refinery Crude Runs ChangeFEB/21</t>
         </is>
       </c>
       <c r="C646" t="inlineStr"/>
       <c r="D646" t="inlineStr">
         <is>
-          <t>-0.961M</t>
+          <t>-0.015M</t>
         </is>
       </c>
       <c r="E646" t="inlineStr"/>
@@ -19499,13 +19499,13 @@
       </c>
       <c r="B656" t="inlineStr">
         <is>
-          <t>EIA Refinery Crude Runs ChangeFEB/21</t>
+          <t>EIA Crude Oil Imports ChangeFEB/21</t>
         </is>
       </c>
       <c r="C656" t="inlineStr"/>
       <c r="D656" t="inlineStr">
         <is>
-          <t>-0.015M</t>
+          <t>-0.961M</t>
         </is>
       </c>
       <c r="E656" t="inlineStr"/>
@@ -19772,27 +19772,23 @@
       </c>
       <c r="B667" t="inlineStr">
         <is>
-          <t>Durable Goods Orders MoMJAN</t>
+          <t>Jobless Claims 4-week AverageFEB/22</t>
         </is>
       </c>
       <c r="C667" t="inlineStr"/>
       <c r="D667" t="inlineStr">
         <is>
-          <t>-2.2%</t>
-        </is>
-      </c>
-      <c r="E667" t="inlineStr">
-        <is>
-          <t>2%</t>
-        </is>
-      </c>
+          <t>215.25K</t>
+        </is>
+      </c>
+      <c r="E667" t="inlineStr"/>
       <c r="F667" t="inlineStr">
         <is>
-          <t>2.2%</t>
+          <t>220.0K</t>
         </is>
       </c>
       <c r="G667" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="668">
@@ -20198,23 +20194,19 @@
       </c>
       <c r="B681" t="inlineStr">
         <is>
-          <t>Real Consumer Spending QoQ 2nd EstQ4</t>
+          <t>Continuing Jobless ClaimsFEB/15</t>
         </is>
       </c>
       <c r="C681" t="inlineStr"/>
       <c r="D681" t="inlineStr">
         <is>
-          <t>3.7%</t>
-        </is>
-      </c>
-      <c r="E681" t="inlineStr">
-        <is>
-          <t>4.2%</t>
-        </is>
-      </c>
+          <t>1869K</t>
+        </is>
+      </c>
+      <c r="E681" t="inlineStr"/>
       <c r="F681" t="inlineStr">
         <is>
-          <t>4.2%</t>
+          <t>1874.0K</t>
         </is>
       </c>
       <c r="G681" t="n">
@@ -20229,27 +20221,27 @@
       </c>
       <c r="B682" t="inlineStr">
         <is>
-          <t>PCE Prices QoQ 2nd EstQ4</t>
+          <t>Durable Goods Orders MoMJAN</t>
         </is>
       </c>
       <c r="C682" t="inlineStr"/>
       <c r="D682" t="inlineStr">
         <is>
-          <t>1.5%</t>
+          <t>-2.2%</t>
         </is>
       </c>
       <c r="E682" t="inlineStr">
         <is>
-          <t>2.3%</t>
+          <t>2%</t>
         </is>
       </c>
       <c r="F682" t="inlineStr">
         <is>
-          <t>2.3%</t>
+          <t>2.2%</t>
         </is>
       </c>
       <c r="G682" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="683">
@@ -20260,27 +20252,27 @@
       </c>
       <c r="B683" t="inlineStr">
         <is>
-          <t>Initial Jobless ClaimsFEB/22</t>
+          <t>Real Consumer Spending QoQ 2nd EstQ4</t>
         </is>
       </c>
       <c r="C683" t="inlineStr"/>
       <c r="D683" t="inlineStr">
         <is>
-          <t>219K</t>
+          <t>3.7%</t>
         </is>
       </c>
       <c r="E683" t="inlineStr">
         <is>
-          <t>221K</t>
+          <t>4.2%</t>
         </is>
       </c>
       <c r="F683" t="inlineStr">
         <is>
-          <t>225.0K</t>
+          <t>4.2%</t>
         </is>
       </c>
       <c r="G683" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="684">
@@ -20291,13 +20283,13 @@
       </c>
       <c r="B684" t="inlineStr">
         <is>
-          <t>GDP Growth Rate QoQ 2nd EstQ4</t>
+          <t>PCE Prices QoQ 2nd EstQ4</t>
         </is>
       </c>
       <c r="C684" t="inlineStr"/>
       <c r="D684" t="inlineStr">
         <is>
-          <t>3.1%</t>
+          <t>1.5%</t>
         </is>
       </c>
       <c r="E684" t="inlineStr">
@@ -20311,7 +20303,7 @@
         </is>
       </c>
       <c r="G684" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="685">
@@ -20322,23 +20314,27 @@
       </c>
       <c r="B685" t="inlineStr">
         <is>
-          <t>Jobless Claims 4-week AverageFEB/22</t>
+          <t>GDP Price Index QoQ 2nd EstQ4</t>
         </is>
       </c>
       <c r="C685" t="inlineStr"/>
       <c r="D685" t="inlineStr">
         <is>
-          <t>215.25K</t>
-        </is>
-      </c>
-      <c r="E685" t="inlineStr"/>
+          <t>1.9%</t>
+        </is>
+      </c>
+      <c r="E685" t="inlineStr">
+        <is>
+          <t>2.2%</t>
+        </is>
+      </c>
       <c r="F685" t="inlineStr">
         <is>
-          <t>220.0K</t>
+          <t>2.2%</t>
         </is>
       </c>
       <c r="G685" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="686">
@@ -20349,27 +20345,27 @@
       </c>
       <c r="B686" t="inlineStr">
         <is>
-          <t>GDP Price Index QoQ 2nd EstQ4</t>
+          <t>GDP Growth Rate QoQ 2nd EstQ4</t>
         </is>
       </c>
       <c r="C686" t="inlineStr"/>
       <c r="D686" t="inlineStr">
         <is>
-          <t>1.9%</t>
+          <t>3.1%</t>
         </is>
       </c>
       <c r="E686" t="inlineStr">
         <is>
-          <t>2.2%</t>
+          <t>2.3%</t>
         </is>
       </c>
       <c r="F686" t="inlineStr">
         <is>
-          <t>2.2%</t>
+          <t>2.3%</t>
         </is>
       </c>
       <c r="G686" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="687">
@@ -20380,23 +20376,27 @@
       </c>
       <c r="B687" t="inlineStr">
         <is>
-          <t>Continuing Jobless ClaimsFEB/15</t>
+          <t>Initial Jobless ClaimsFEB/22</t>
         </is>
       </c>
       <c r="C687" t="inlineStr"/>
       <c r="D687" t="inlineStr">
         <is>
-          <t>1869K</t>
-        </is>
-      </c>
-      <c r="E687" t="inlineStr"/>
+          <t>219K</t>
+        </is>
+      </c>
+      <c r="E687" t="inlineStr">
+        <is>
+          <t>221K</t>
+        </is>
+      </c>
       <c r="F687" t="inlineStr">
         <is>
-          <t>1874.0K</t>
+          <t>225.0K</t>
         </is>
       </c>
       <c r="G687" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="688">
@@ -20407,23 +20407,27 @@
       </c>
       <c r="B688" t="inlineStr">
         <is>
-          <t>Durable Goods Orders ex Defense MoMJAN</t>
+          <t>Durable Goods Orders Ex Transp MoMJAN</t>
         </is>
       </c>
       <c r="C688" t="inlineStr"/>
       <c r="D688" t="inlineStr">
         <is>
-          <t>-2.4%</t>
-        </is>
-      </c>
-      <c r="E688" t="inlineStr"/>
+          <t>0.3%</t>
+        </is>
+      </c>
+      <c r="E688" t="inlineStr">
+        <is>
+          <t>0.3%</t>
+        </is>
+      </c>
       <c r="F688" t="inlineStr">
         <is>
-          <t>1.4%</t>
+          <t>0.3%</t>
         </is>
       </c>
       <c r="G688" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="689">
@@ -20434,23 +20438,23 @@
       </c>
       <c r="B689" t="inlineStr">
         <is>
-          <t>Core PCE Prices QoQ 2nd EstQ4</t>
+          <t>Non Defense Goods Orders Ex AirJAN</t>
         </is>
       </c>
       <c r="C689" t="inlineStr"/>
       <c r="D689" t="inlineStr">
         <is>
-          <t>2.2%</t>
+          <t>0.5%</t>
         </is>
       </c>
       <c r="E689" t="inlineStr">
         <is>
-          <t>2.5%</t>
+          <t>0.3%</t>
         </is>
       </c>
       <c r="F689" t="inlineStr">
         <is>
-          <t>2.5%</t>
+          <t>0.4%</t>
         </is>
       </c>
       <c r="G689" t="n">
@@ -20496,23 +20500,23 @@
       </c>
       <c r="B691" t="inlineStr">
         <is>
-          <t>Non Defense Goods Orders Ex AirJAN</t>
+          <t>Core PCE Prices QoQ 2nd EstQ4</t>
         </is>
       </c>
       <c r="C691" t="inlineStr"/>
       <c r="D691" t="inlineStr">
         <is>
-          <t>0.5%</t>
+          <t>2.2%</t>
         </is>
       </c>
       <c r="E691" t="inlineStr">
         <is>
-          <t>0.3%</t>
+          <t>2.5%</t>
         </is>
       </c>
       <c r="F691" t="inlineStr">
         <is>
-          <t>0.4%</t>
+          <t>2.5%</t>
         </is>
       </c>
       <c r="G691" t="n">
@@ -20527,27 +20531,23 @@
       </c>
       <c r="B692" t="inlineStr">
         <is>
-          <t>Durable Goods Orders Ex Transp MoMJAN</t>
+          <t>Durable Goods Orders ex Defense MoMJAN</t>
         </is>
       </c>
       <c r="C692" t="inlineStr"/>
       <c r="D692" t="inlineStr">
         <is>
-          <t>0.3%</t>
-        </is>
-      </c>
-      <c r="E692" t="inlineStr">
-        <is>
-          <t>0.3%</t>
-        </is>
-      </c>
+          <t>-2.4%</t>
+        </is>
+      </c>
+      <c r="E692" t="inlineStr"/>
       <c r="F692" t="inlineStr">
         <is>
-          <t>0.3%</t>
+          <t>1.4%</t>
         </is>
       </c>
       <c r="G692" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="693">
@@ -20577,19 +20577,23 @@
       </c>
       <c r="B694" t="inlineStr">
         <is>
-          <t>Pending Home Sales YoYJAN</t>
+          <t>Pending Home Sales MoMJAN</t>
         </is>
       </c>
       <c r="C694" t="inlineStr"/>
       <c r="D694" t="inlineStr">
         <is>
-          <t>-5.0%</t>
-        </is>
-      </c>
-      <c r="E694" t="inlineStr"/>
+          <t>-5.5%</t>
+        </is>
+      </c>
+      <c r="E694" t="inlineStr">
+        <is>
+          <t>-1.3%</t>
+        </is>
+      </c>
       <c r="F694" t="inlineStr">
         <is>
-          <t>6.0%</t>
+          <t>-0.9%</t>
         </is>
       </c>
       <c r="G694" t="n">
@@ -20681,23 +20685,19 @@
       </c>
       <c r="B698" t="inlineStr">
         <is>
-          <t>Pending Home Sales MoMJAN</t>
+          <t>Pending Home Sales YoYJAN</t>
         </is>
       </c>
       <c r="C698" t="inlineStr"/>
       <c r="D698" t="inlineStr">
         <is>
-          <t>-5.5%</t>
-        </is>
-      </c>
-      <c r="E698" t="inlineStr">
-        <is>
-          <t>-1.3%</t>
-        </is>
-      </c>
+          <t>-5.0%</t>
+        </is>
+      </c>
+      <c r="E698" t="inlineStr"/>
       <c r="F698" t="inlineStr">
         <is>
-          <t>-0.9%</t>
+          <t>6.0%</t>
         </is>
       </c>
       <c r="G698" t="n">
@@ -20920,13 +20920,13 @@
       </c>
       <c r="B707" t="inlineStr">
         <is>
-          <t>4-Week Bill Auction</t>
+          <t>8-Week Bill Auction</t>
         </is>
       </c>
       <c r="C707" t="inlineStr"/>
       <c r="D707" t="inlineStr">
         <is>
-          <t>4.245%</t>
+          <t>4.235%</t>
         </is>
       </c>
       <c r="E707" t="inlineStr"/>
@@ -20989,13 +20989,13 @@
       </c>
       <c r="B710" t="inlineStr">
         <is>
-          <t>8-Week Bill Auction</t>
+          <t>4-Week Bill Auction</t>
         </is>
       </c>
       <c r="C710" t="inlineStr"/>
       <c r="D710" t="inlineStr">
         <is>
-          <t>4.235%</t>
+          <t>4.245%</t>
         </is>
       </c>
       <c r="E710" t="inlineStr"/>
@@ -21577,23 +21577,23 @@
       </c>
       <c r="B734" t="inlineStr">
         <is>
-          <t>Wholesale Inventories MoM AdvJAN</t>
+          <t>PCE Price Index YoYJAN</t>
         </is>
       </c>
       <c r="C734" t="inlineStr"/>
       <c r="D734" t="inlineStr">
         <is>
-          <t>-0.5%</t>
+          <t>2.6%</t>
         </is>
       </c>
       <c r="E734" t="inlineStr">
         <is>
-          <t>0.1%</t>
+          <t>2.5%</t>
         </is>
       </c>
       <c r="F734" t="inlineStr">
         <is>
-          <t>0.2%</t>
+          <t>2.5%</t>
         </is>
       </c>
       <c r="G734" t="n">
@@ -21608,27 +21608,27 @@
       </c>
       <c r="B735" t="inlineStr">
         <is>
-          <t>Goods Trade Balance AdvJAN</t>
+          <t>Personal Spending MoMJAN</t>
         </is>
       </c>
       <c r="C735" t="inlineStr"/>
       <c r="D735" t="inlineStr">
         <is>
-          <t>$-122.11B</t>
+          <t>0.7%</t>
         </is>
       </c>
       <c r="E735" t="inlineStr">
         <is>
-          <t>$-114.7B</t>
+          <t>0.1%</t>
         </is>
       </c>
       <c r="F735" t="inlineStr">
         <is>
-          <t>$ -116.0B</t>
+          <t>0.3%</t>
         </is>
       </c>
       <c r="G735" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="736">
@@ -21639,27 +21639,23 @@
       </c>
       <c r="B736" t="inlineStr">
         <is>
-          <t>Core PCE Price Index MoMJAN</t>
+          <t>Retail Inventories Ex Autos MoM AdvJAN</t>
         </is>
       </c>
       <c r="C736" t="inlineStr"/>
       <c r="D736" t="inlineStr">
         <is>
-          <t>0.2%</t>
-        </is>
-      </c>
-      <c r="E736" t="inlineStr">
-        <is>
-          <t>0.3%</t>
-        </is>
-      </c>
+          <t>-0.1%</t>
+        </is>
+      </c>
+      <c r="E736" t="inlineStr"/>
       <c r="F736" t="inlineStr">
         <is>
-          <t>0.4%</t>
+          <t>0.1%</t>
         </is>
       </c>
       <c r="G736" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="737">
@@ -21670,23 +21666,27 @@
       </c>
       <c r="B737" t="inlineStr">
         <is>
-          <t>Retail Inventories Ex Autos MoM AdvJAN</t>
+          <t>Core PCE Price Index YoYJAN</t>
         </is>
       </c>
       <c r="C737" t="inlineStr"/>
       <c r="D737" t="inlineStr">
         <is>
-          <t>-0.1%</t>
-        </is>
-      </c>
-      <c r="E737" t="inlineStr"/>
+          <t>2.8%</t>
+        </is>
+      </c>
+      <c r="E737" t="inlineStr">
+        <is>
+          <t>2.6%</t>
+        </is>
+      </c>
       <c r="F737" t="inlineStr">
         <is>
-          <t>0.1%</t>
+          <t>2.7%</t>
         </is>
       </c>
       <c r="G737" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="738">
@@ -21697,18 +21697,18 @@
       </c>
       <c r="B738" t="inlineStr">
         <is>
-          <t>Personal Spending MoMJAN</t>
+          <t>Personal Income MoMJAN</t>
         </is>
       </c>
       <c r="C738" t="inlineStr"/>
       <c r="D738" t="inlineStr">
         <is>
-          <t>0.7%</t>
+          <t>0.4%</t>
         </is>
       </c>
       <c r="E738" t="inlineStr">
         <is>
-          <t>0.1%</t>
+          <t>0.3%</t>
         </is>
       </c>
       <c r="F738" t="inlineStr">
@@ -21759,27 +21759,27 @@
       </c>
       <c r="B740" t="inlineStr">
         <is>
-          <t>PCE Price Index YoYJAN</t>
+          <t>Core PCE Price Index MoMJAN</t>
         </is>
       </c>
       <c r="C740" t="inlineStr"/>
       <c r="D740" t="inlineStr">
         <is>
-          <t>2.6%</t>
+          <t>0.2%</t>
         </is>
       </c>
       <c r="E740" t="inlineStr">
         <is>
-          <t>2.5%</t>
+          <t>0.3%</t>
         </is>
       </c>
       <c r="F740" t="inlineStr">
         <is>
-          <t>2.5%</t>
+          <t>0.4%</t>
         </is>
       </c>
       <c r="G740" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="741">
@@ -21790,27 +21790,27 @@
       </c>
       <c r="B741" t="inlineStr">
         <is>
-          <t>Personal Income MoMJAN</t>
+          <t>Wholesale Inventories MoM AdvJAN</t>
         </is>
       </c>
       <c r="C741" t="inlineStr"/>
       <c r="D741" t="inlineStr">
         <is>
-          <t>0.4%</t>
+          <t>-0.5%</t>
         </is>
       </c>
       <c r="E741" t="inlineStr">
         <is>
-          <t>0.3%</t>
+          <t>0.1%</t>
         </is>
       </c>
       <c r="F741" t="inlineStr">
         <is>
-          <t>0.3%</t>
+          <t>0.2%</t>
         </is>
       </c>
       <c r="G741" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="742">
@@ -21821,27 +21821,27 @@
       </c>
       <c r="B742" t="inlineStr">
         <is>
-          <t>Core PCE Price Index YoYJAN</t>
+          <t>Goods Trade Balance AdvJAN</t>
         </is>
       </c>
       <c r="C742" t="inlineStr"/>
       <c r="D742" t="inlineStr">
         <is>
-          <t>2.8%</t>
+          <t>$-122.11B</t>
         </is>
       </c>
       <c r="E742" t="inlineStr">
         <is>
-          <t>2.6%</t>
+          <t>$-114.7B</t>
         </is>
       </c>
       <c r="F742" t="inlineStr">
         <is>
-          <t>2.7%</t>
+          <t>$ -116.0B</t>
         </is>
       </c>
       <c r="G742" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="743">
@@ -21914,13 +21914,13 @@
       </c>
       <c r="B745" t="inlineStr">
         <is>
-          <t>Baker Hughes Oil Rig CountFEB/28</t>
+          <t>Baker Hughes Total Rigs CountFEB/28</t>
         </is>
       </c>
       <c r="C745" t="inlineStr"/>
       <c r="D745" t="inlineStr">
         <is>
-          <t>487</t>
+          <t>592</t>
         </is>
       </c>
       <c r="E745" t="inlineStr"/>
@@ -21983,13 +21983,13 @@
       </c>
       <c r="B748" t="inlineStr">
         <is>
-          <t>Baker Hughes Total Rigs CountFEB/28</t>
+          <t>Baker Hughes Oil Rig CountFEB/28</t>
         </is>
       </c>
       <c r="C748" t="inlineStr"/>
       <c r="D748" t="inlineStr">
         <is>
-          <t>592</t>
+          <t>487</t>
         </is>
       </c>
       <c r="E748" t="inlineStr"/>
@@ -22095,19 +22095,19 @@
       </c>
       <c r="B752" t="inlineStr">
         <is>
-          <t>ISM Manufacturing PricesFEB</t>
+          <t>ISM Manufacturing New OrdersFEB</t>
         </is>
       </c>
       <c r="C752" t="inlineStr"/>
       <c r="D752" t="inlineStr">
         <is>
-          <t>54.9</t>
+          <t>55.1</t>
         </is>
       </c>
       <c r="E752" t="inlineStr"/>
       <c r="F752" t="inlineStr">
         <is>
-          <t>55</t>
+          <t>55.4</t>
         </is>
       </c>
       <c r="G752" t="n">
@@ -22230,23 +22230,23 @@
       </c>
       <c r="B757" t="inlineStr">
         <is>
-          <t>ISM Manufacturing New OrdersFEB</t>
+          <t>ISM Manufacturing EmploymentFEB</t>
         </is>
       </c>
       <c r="C757" t="inlineStr"/>
       <c r="D757" t="inlineStr">
         <is>
-          <t>55.1</t>
+          <t>50.3</t>
         </is>
       </c>
       <c r="E757" t="inlineStr"/>
       <c r="F757" t="inlineStr">
         <is>
-          <t>55.4</t>
+          <t>50.6</t>
         </is>
       </c>
       <c r="G757" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="758">
@@ -22311,23 +22311,23 @@
       </c>
       <c r="B760" t="inlineStr">
         <is>
-          <t>ISM Manufacturing EmploymentFEB</t>
+          <t>ISM Manufacturing PricesFEB</t>
         </is>
       </c>
       <c r="C760" t="inlineStr"/>
       <c r="D760" t="inlineStr">
         <is>
-          <t>50.3</t>
+          <t>54.9</t>
         </is>
       </c>
       <c r="E760" t="inlineStr"/>
       <c r="F760" t="inlineStr">
         <is>
-          <t>50.6</t>
+          <t>55</t>
         </is>
       </c>
       <c r="G760" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="761">
@@ -22840,7 +22840,7 @@
       </c>
       <c r="B783" t="inlineStr">
         <is>
-          <t>MBA 30-Year Mortgage RateFEB/28</t>
+          <t>MBA Mortgage Market IndexFEB/28</t>
         </is>
       </c>
       <c r="C783" t="inlineStr"/>
@@ -22848,7 +22848,7 @@
       <c r="E783" t="inlineStr"/>
       <c r="F783" t="inlineStr"/>
       <c r="G783" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="784">
@@ -22859,7 +22859,7 @@
       </c>
       <c r="B784" t="inlineStr">
         <is>
-          <t>MBA Mortgage Market IndexFEB/28</t>
+          <t>MBA 30-Year Mortgage RateFEB/28</t>
         </is>
       </c>
       <c r="C784" t="inlineStr"/>
@@ -22867,7 +22867,7 @@
       <c r="E784" t="inlineStr"/>
       <c r="F784" t="inlineStr"/>
       <c r="G784" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="785">
@@ -22994,23 +22994,23 @@
       </c>
       <c r="B789" t="inlineStr">
         <is>
-          <t>S&amp;P Global Services PMI FinalFEB</t>
+          <t>S&amp;P Global Composite PMI FinalFEB</t>
         </is>
       </c>
       <c r="C789" t="inlineStr"/>
       <c r="D789" t="inlineStr">
         <is>
-          <t>52.9</t>
+          <t>52.7</t>
         </is>
       </c>
       <c r="E789" t="inlineStr">
         <is>
-          <t>49.7</t>
+          <t>50.4</t>
         </is>
       </c>
       <c r="F789" t="inlineStr">
         <is>
-          <t>49.7</t>
+          <t>50.4</t>
         </is>
       </c>
       <c r="G789" t="n">
@@ -23025,23 +23025,23 @@
       </c>
       <c r="B790" t="inlineStr">
         <is>
-          <t>S&amp;P Global Composite PMI FinalFEB</t>
+          <t>S&amp;P Global Services PMI FinalFEB</t>
         </is>
       </c>
       <c r="C790" t="inlineStr"/>
       <c r="D790" t="inlineStr">
         <is>
-          <t>52.7</t>
+          <t>52.9</t>
         </is>
       </c>
       <c r="E790" t="inlineStr">
         <is>
-          <t>50.4</t>
+          <t>49.7</t>
         </is>
       </c>
       <c r="F790" t="inlineStr">
         <is>
-          <t>50.4</t>
+          <t>49.7</t>
         </is>
       </c>
       <c r="G790" t="n">
@@ -23503,19 +23503,19 @@
       </c>
       <c r="B808" t="inlineStr">
         <is>
-          <t>EIA Distillate Stocks ChangeFEB/28</t>
+          <t>EIA Gasoline Stocks ChangeFEB/28</t>
         </is>
       </c>
       <c r="C808" t="inlineStr"/>
       <c r="D808" t="inlineStr">
         <is>
-          <t>3.908M</t>
+          <t>0.369M</t>
         </is>
       </c>
       <c r="E808" t="inlineStr"/>
       <c r="F808" t="inlineStr"/>
       <c r="G808" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="809">
@@ -23595,11 +23595,15 @@
       </c>
       <c r="B812" t="inlineStr">
         <is>
-          <t>EIA Crude Oil Imports ChangeFEB/28</t>
+          <t>EIA Refinery Crude Runs ChangeFEB/28</t>
         </is>
       </c>
       <c r="C812" t="inlineStr"/>
-      <c r="D812" t="inlineStr"/>
+      <c r="D812" t="inlineStr">
+        <is>
+          <t>0.317M</t>
+        </is>
+      </c>
       <c r="E812" t="inlineStr"/>
       <c r="F812" t="inlineStr"/>
       <c r="G812" t="n">
@@ -23683,19 +23687,19 @@
       </c>
       <c r="B816" t="inlineStr">
         <is>
-          <t>EIA Gasoline Stocks ChangeFEB/28</t>
+          <t>EIA Gasoline Production ChangeFEB/28</t>
         </is>
       </c>
       <c r="C816" t="inlineStr"/>
       <c r="D816" t="inlineStr">
         <is>
-          <t>0.369M</t>
+          <t>-0.02M</t>
         </is>
       </c>
       <c r="E816" t="inlineStr"/>
       <c r="F816" t="inlineStr"/>
       <c r="G816" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="817">
@@ -23706,13 +23710,13 @@
       </c>
       <c r="B817" t="inlineStr">
         <is>
-          <t>EIA Refinery Crude Runs ChangeFEB/28</t>
+          <t>EIA Cushing Crude Oil Stocks ChangeFEB/28</t>
         </is>
       </c>
       <c r="C817" t="inlineStr"/>
       <c r="D817" t="inlineStr">
         <is>
-          <t>0.317M</t>
+          <t>1.282M</t>
         </is>
       </c>
       <c r="E817" t="inlineStr"/>
@@ -23748,15 +23752,11 @@
       </c>
       <c r="B819" t="inlineStr">
         <is>
-          <t>EIA Cushing Crude Oil Stocks ChangeFEB/28</t>
+          <t>EIA Crude Oil Imports ChangeFEB/28</t>
         </is>
       </c>
       <c r="C819" t="inlineStr"/>
-      <c r="D819" t="inlineStr">
-        <is>
-          <t>1.282M</t>
-        </is>
-      </c>
+      <c r="D819" t="inlineStr"/>
       <c r="E819" t="inlineStr"/>
       <c r="F819" t="inlineStr"/>
       <c r="G819" t="n">
@@ -23771,13 +23771,13 @@
       </c>
       <c r="B820" t="inlineStr">
         <is>
-          <t>EIA Gasoline Production ChangeFEB/28</t>
+          <t>EIA Distillate Stocks ChangeFEB/28</t>
         </is>
       </c>
       <c r="C820" t="inlineStr"/>
       <c r="D820" t="inlineStr">
         <is>
-          <t>-0.02M</t>
+          <t>3.908M</t>
         </is>
       </c>
       <c r="E820" t="inlineStr"/>
@@ -24024,21 +24024,13 @@
       </c>
       <c r="B831" t="inlineStr">
         <is>
-          <t>Balance of TradeJAN</t>
+          <t>Initial Jobless ClaimsMAR/01</t>
         </is>
       </c>
       <c r="C831" t="inlineStr"/>
-      <c r="D831" t="inlineStr">
-        <is>
-          <t>$-98.4B</t>
-        </is>
-      </c>
+      <c r="D831" t="inlineStr"/>
       <c r="E831" t="inlineStr"/>
-      <c r="F831" t="inlineStr">
-        <is>
-          <t>$-103B</t>
-        </is>
-      </c>
+      <c r="F831" t="inlineStr"/>
       <c r="G831" t="n">
         <v>2</v>
       </c>
@@ -24078,7 +24070,7 @@
       </c>
       <c r="B833" t="inlineStr">
         <is>
-          <t>Continuing Jobless ClaimsFEB/22</t>
+          <t>Jobless Claims 4-week AverageMAR/01</t>
         </is>
       </c>
       <c r="C833" t="inlineStr"/>
@@ -24297,7 +24289,7 @@
       </c>
       <c r="B842" t="inlineStr">
         <is>
-          <t>Jobless Claims 4-week AverageMAR/01</t>
+          <t>Continuing Jobless ClaimsFEB/22</t>
         </is>
       </c>
       <c r="C842" t="inlineStr"/>
@@ -24343,19 +24335,19 @@
       </c>
       <c r="B844" t="inlineStr">
         <is>
-          <t>ImportsJAN</t>
+          <t>Balance of TradeJAN</t>
         </is>
       </c>
       <c r="C844" t="inlineStr"/>
       <c r="D844" t="inlineStr">
         <is>
-          <t>$364.9B</t>
+          <t>$-98.4B</t>
         </is>
       </c>
       <c r="E844" t="inlineStr"/>
       <c r="F844" t="inlineStr">
         <is>
-          <t>$376.0B</t>
+          <t>$-103B</t>
         </is>
       </c>
       <c r="G844" t="n">
@@ -24397,13 +24389,21 @@
       </c>
       <c r="B846" t="inlineStr">
         <is>
-          <t>Initial Jobless ClaimsMAR/01</t>
+          <t>ImportsJAN</t>
         </is>
       </c>
       <c r="C846" t="inlineStr"/>
-      <c r="D846" t="inlineStr"/>
+      <c r="D846" t="inlineStr">
+        <is>
+          <t>$364.9B</t>
+        </is>
+      </c>
       <c r="E846" t="inlineStr"/>
-      <c r="F846" t="inlineStr"/>
+      <c r="F846" t="inlineStr">
+        <is>
+          <t>$376.0B</t>
+        </is>
+      </c>
       <c r="G846" t="n">
         <v>2</v>
       </c>
@@ -24948,23 +24948,19 @@
       </c>
       <c r="B871" t="inlineStr">
         <is>
-          <t>Average Hourly Earnings MoMFEB</t>
+          <t>Used Car Prices MoMFEB</t>
         </is>
       </c>
       <c r="C871" t="inlineStr"/>
       <c r="D871" t="inlineStr">
         <is>
-          <t>0.5%</t>
+          <t>0.4%</t>
         </is>
       </c>
       <c r="E871" t="inlineStr"/>
-      <c r="F871" t="inlineStr">
-        <is>
-          <t>0.3%</t>
-        </is>
-      </c>
+      <c r="F871" t="inlineStr"/>
       <c r="G871" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="872">
@@ -24975,19 +24971,23 @@
       </c>
       <c r="B872" t="inlineStr">
         <is>
-          <t>Used Car Prices MoMFEB</t>
+          <t>Participation RateFEB</t>
         </is>
       </c>
       <c r="C872" t="inlineStr"/>
       <c r="D872" t="inlineStr">
         <is>
-          <t>0.4%</t>
+          <t>62.6%</t>
         </is>
       </c>
       <c r="E872" t="inlineStr"/>
-      <c r="F872" t="inlineStr"/>
+      <c r="F872" t="inlineStr">
+        <is>
+          <t>62.6%</t>
+        </is>
+      </c>
       <c r="G872" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="873">
@@ -25079,19 +25079,19 @@
       </c>
       <c r="B876" t="inlineStr">
         <is>
-          <t>Participation RateFEB</t>
+          <t>Average Hourly Earnings YoYFEB</t>
         </is>
       </c>
       <c r="C876" t="inlineStr"/>
       <c r="D876" t="inlineStr">
         <is>
-          <t>62.6%</t>
+          <t>4.1%</t>
         </is>
       </c>
       <c r="E876" t="inlineStr"/>
       <c r="F876" t="inlineStr">
         <is>
-          <t>62.6%</t>
+          <t>4.1%</t>
         </is>
       </c>
       <c r="G876" t="n">
@@ -25214,19 +25214,19 @@
       </c>
       <c r="B881" t="inlineStr">
         <is>
-          <t>Average Hourly Earnings YoYFEB</t>
+          <t>Average Hourly Earnings MoMFEB</t>
         </is>
       </c>
       <c r="C881" t="inlineStr"/>
       <c r="D881" t="inlineStr">
         <is>
-          <t>4.1%</t>
+          <t>0.5%</t>
         </is>
       </c>
       <c r="E881" t="inlineStr"/>
       <c r="F881" t="inlineStr">
         <is>
-          <t>4.1%</t>
+          <t>0.3%</t>
         </is>
       </c>
       <c r="G881" t="n">

--- a/Input_data/IST_US_trad_eco_cal_2025-01-01_to_2025-03-09.xlsx
+++ b/Input_data/IST_US_trad_eco_cal_2025-01-01_to_2025-03-09.xlsx
@@ -806,23 +806,27 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>EIA Refinery Crude Runs ChangeDEC/27</t>
+          <t>EIA Crude Oil Stocks ChangeDEC/27</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>0.041M</t>
+          <t>-1.178M</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>0.205M</t>
-        </is>
-      </c>
-      <c r="E13" t="inlineStr"/>
+          <t>-4.237M</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>-2.75M</t>
+        </is>
+      </c>
       <c r="F13" t="inlineStr"/>
       <c r="G13" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="14">
@@ -833,17 +837,17 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>EIA Gasoline Production ChangeDEC/27</t>
+          <t>EIA Cushing Crude Oil Stocks ChangeDEC/27</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>-0.959M</t>
+          <t>-0.142M</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>0.051M</t>
+          <t>-0.32M</t>
         </is>
       </c>
       <c r="E14" t="inlineStr"/>
@@ -860,17 +864,17 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>EIA Distillate Fuel Production ChangeDEC/27</t>
+          <t>EIA Crude Oil Imports ChangeDEC/27</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>0.099M</t>
+          <t>0.323M</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>0.178M</t>
+          <t>0.995M</t>
         </is>
       </c>
       <c r="E15" t="inlineStr"/>
@@ -887,23 +891,27 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>EIA Heating Oil Stocks ChangeDEC/27</t>
+          <t>EIA Gasoline Stocks ChangeDEC/27</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>-0.416M</t>
+          <t>7.717M</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>-0.062M</t>
-        </is>
-      </c>
-      <c r="E16" t="inlineStr"/>
+          <t>1.63M</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>0.7M</t>
+        </is>
+      </c>
       <c r="F16" t="inlineStr"/>
       <c r="G16" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="17">
@@ -914,24 +922,20 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>EIA Distillate Stocks ChangeDEC/27</t>
+          <t>EIA Distillate Fuel Production ChangeDEC/27</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>6.406M</t>
+          <t>0.099M</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>-1.694M</t>
-        </is>
-      </c>
-      <c r="E17" t="inlineStr">
-        <is>
-          <t>-0.1M</t>
-        </is>
-      </c>
+          <t>0.178M</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr"/>
       <c r="F17" t="inlineStr"/>
       <c r="G17" t="n">
         <v>3</v>
@@ -945,27 +949,23 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>EIA Gasoline Stocks ChangeDEC/27</t>
+          <t>EIA Heating Oil Stocks ChangeDEC/27</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>7.717M</t>
+          <t>-0.416M</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>1.63M</t>
-        </is>
-      </c>
-      <c r="E18" t="inlineStr">
-        <is>
-          <t>0.7M</t>
-        </is>
-      </c>
+          <t>-0.062M</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr"/>
       <c r="F18" t="inlineStr"/>
       <c r="G18" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="19">
@@ -976,17 +976,17 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>EIA Crude Oil Imports ChangeDEC/27</t>
+          <t>EIA Gasoline Production ChangeDEC/27</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>0.323M</t>
+          <t>-0.959M</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>0.995M</t>
+          <t>0.051M</t>
         </is>
       </c>
       <c r="E19" t="inlineStr"/>
@@ -1003,17 +1003,17 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>EIA Cushing Crude Oil Stocks ChangeDEC/27</t>
+          <t>EIA Refinery Crude Runs ChangeDEC/27</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>-0.142M</t>
+          <t>0.041M</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>-0.32M</t>
+          <t>0.205M</t>
         </is>
       </c>
       <c r="E20" t="inlineStr"/>
@@ -1030,27 +1030,27 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>EIA Crude Oil Stocks ChangeDEC/27</t>
+          <t>EIA Distillate Stocks ChangeDEC/27</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>-1.178M</t>
+          <t>6.406M</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>-4.237M</t>
+          <t>-1.694M</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>-2.75M</t>
+          <t>-0.1M</t>
         </is>
       </c>
       <c r="F21" t="inlineStr"/>
       <c r="G21" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="22">
@@ -1223,31 +1223,31 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>ISM Manufacturing PMIDEC</t>
+          <t>ISM Manufacturing PricesDEC</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>49.3</t>
+          <t>52.5</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>48.4</t>
+          <t>50.3</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>48.4</t>
+          <t>51.7</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>48.5</t>
+          <t>50.4</t>
         </is>
       </c>
       <c r="G28" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="29">
@@ -1258,31 +1258,27 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>ISM Manufacturing EmploymentDEC</t>
+          <t>ISM Manufacturing New OrdersDEC</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>45.3</t>
+          <t>52.5</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>48.1</t>
-        </is>
-      </c>
-      <c r="E29" t="inlineStr">
-        <is>
-          <t>48</t>
-        </is>
-      </c>
+          <t>50.4</t>
+        </is>
+      </c>
+      <c r="E29" t="inlineStr"/>
       <c r="F29" t="inlineStr">
         <is>
-          <t>48.3</t>
+          <t>50.5</t>
         </is>
       </c>
       <c r="G29" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="30">
@@ -1293,27 +1289,31 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>ISM Manufacturing New OrdersDEC</t>
+          <t>ISM Manufacturing EmploymentDEC</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>52.5</t>
+          <t>45.3</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>50.4</t>
-        </is>
-      </c>
-      <c r="E30" t="inlineStr"/>
+          <t>48.1</t>
+        </is>
+      </c>
+      <c r="E30" t="inlineStr">
+        <is>
+          <t>48</t>
+        </is>
+      </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>50.5</t>
+          <t>48.3</t>
         </is>
       </c>
       <c r="G30" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="31">
@@ -1324,31 +1324,31 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>ISM Manufacturing PricesDEC</t>
+          <t>ISM Manufacturing PMIDEC</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>52.5</t>
+          <t>49.3</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>50.3</t>
+          <t>48.4</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>51.7</t>
+          <t>48.4</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>50.4</t>
+          <t>48.5</t>
         </is>
       </c>
       <c r="G31" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="32">
@@ -1609,31 +1609,27 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>Factory Orders MoMNOV</t>
+          <t>Factory Orders ex TransportationNOV</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>-0.4%</t>
+          <t>0.2%</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>0.5%</t>
-        </is>
-      </c>
-      <c r="E42" t="inlineStr">
-        <is>
-          <t>-0.3%</t>
-        </is>
-      </c>
+          <t>0.2%</t>
+        </is>
+      </c>
+      <c r="E42" t="inlineStr"/>
       <c r="F42" t="inlineStr">
         <is>
-          <t>0.3%</t>
+          <t>0.2%</t>
         </is>
       </c>
       <c r="G42" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="43">
@@ -1644,27 +1640,31 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>Factory Orders ex TransportationNOV</t>
+          <t>Factory Orders MoMNOV</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>0.2%</t>
+          <t>-0.4%</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>0.2%</t>
-        </is>
-      </c>
-      <c r="E43" t="inlineStr"/>
+          <t>0.5%</t>
+        </is>
+      </c>
+      <c r="E43" t="inlineStr">
+        <is>
+          <t>-0.3%</t>
+        </is>
+      </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>0.2%</t>
+          <t>0.3%</t>
         </is>
       </c>
       <c r="G43" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="44">
@@ -1949,31 +1949,31 @@
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>ISM Services New OrdersDEC</t>
+          <t>ISM Services PMIDEC</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>54.2</t>
+          <t>54.1</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>53.7</t>
+          <t>52.1</t>
         </is>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>54.2</t>
+          <t>53.3</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>54.1</t>
+          <t>54</t>
         </is>
       </c>
       <c r="G54" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="55">
@@ -1984,23 +1984,23 @@
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>JOLTs Job QuitsNOV</t>
+          <t>ISM Services Business ActivityDEC</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>3.065M</t>
+          <t>58.2</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>3.283M</t>
+          <t>53.7</t>
         </is>
       </c>
       <c r="E55" t="inlineStr"/>
       <c r="F55" t="inlineStr">
         <is>
-          <t>3.31M</t>
+          <t>54.1</t>
         </is>
       </c>
       <c r="G55" t="n">
@@ -2015,31 +2015,31 @@
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>ISM Services PricesDEC</t>
+          <t>JOLTs Job OpeningsNOV</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>64.4</t>
+          <t>8.098M</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>58.2</t>
+          <t>7.839M</t>
         </is>
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>57.5</t>
+          <t>7.70M</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>58.4</t>
+          <t>7.69M</t>
         </is>
       </c>
       <c r="G56" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="57">
@@ -2050,27 +2050,27 @@
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>ISM Services EmploymentDEC</t>
+          <t>ISM Services New OrdersDEC</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>51.4</t>
+          <t>54.2</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>51.5</t>
+          <t>53.7</t>
         </is>
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>51.4</t>
+          <t>54.2</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>52</t>
+          <t>54.1</t>
         </is>
       </c>
       <c r="G57" t="n">
@@ -2085,31 +2085,31 @@
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>JOLTs Job OpeningsNOV</t>
+          <t>ISM Services PricesDEC</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>8.098M</t>
+          <t>64.4</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>7.839M</t>
+          <t>58.2</t>
         </is>
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>7.70M</t>
+          <t>57.5</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>7.69M</t>
+          <t>58.4</t>
         </is>
       </c>
       <c r="G58" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="59">
@@ -2120,31 +2120,31 @@
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>ISM Services PMIDEC</t>
+          <t>ISM Services EmploymentDEC</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>54.1</t>
+          <t>51.4</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>52.1</t>
+          <t>51.5</t>
         </is>
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>53.3</t>
+          <t>51.4</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>54</t>
+          <t>52</t>
         </is>
       </c>
       <c r="G59" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="60">
@@ -2155,23 +2155,23 @@
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>ISM Services Business ActivityDEC</t>
+          <t>JOLTs Job QuitsNOV</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>58.2</t>
+          <t>3.065M</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>53.7</t>
+          <t>3.283M</t>
         </is>
       </c>
       <c r="E60" t="inlineStr"/>
       <c r="F60" t="inlineStr">
         <is>
-          <t>54.1</t>
+          <t>3.31M</t>
         </is>
       </c>
       <c r="G60" t="n">
@@ -2441,27 +2441,27 @@
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>Total Vehicle SalesDEC</t>
+          <t>Continuing Jobless ClaimsDEC/28</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>16.8M</t>
+          <t>1867K</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>16.7M</t>
+          <t>1834K</t>
         </is>
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>16.5M</t>
+          <t>1870K</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>16.3M</t>
+          <t>1848K</t>
         </is>
       </c>
       <c r="G70" t="n">
@@ -2476,27 +2476,15 @@
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>Jobless Claims 4-week AverageJAN/04</t>
-        </is>
-      </c>
-      <c r="C71" t="inlineStr">
-        <is>
-          <t>213K</t>
-        </is>
-      </c>
-      <c r="D71" t="inlineStr">
-        <is>
-          <t>223.25K</t>
-        </is>
-      </c>
+          <t>Fed Waller Speech</t>
+        </is>
+      </c>
+      <c r="C71" t="inlineStr"/>
+      <c r="D71" t="inlineStr"/>
       <c r="E71" t="inlineStr"/>
-      <c r="F71" t="inlineStr">
-        <is>
-          <t>224K</t>
-        </is>
-      </c>
+      <c r="F71" t="inlineStr"/>
       <c r="G71" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="72">
@@ -2507,31 +2495,31 @@
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>Initial Jobless ClaimsJAN/04</t>
+          <t>Total Vehicle SalesDEC</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>201K</t>
+          <t>16.8M</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>211K</t>
+          <t>16.7M</t>
         </is>
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>218K</t>
+          <t>16.5M</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>213K</t>
+          <t>16.3M</t>
         </is>
       </c>
       <c r="G72" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="73">
@@ -2542,15 +2530,27 @@
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>Fed Waller Speech</t>
-        </is>
-      </c>
-      <c r="C73" t="inlineStr"/>
-      <c r="D73" t="inlineStr"/>
+          <t>Jobless Claims 4-week AverageJAN/04</t>
+        </is>
+      </c>
+      <c r="C73" t="inlineStr">
+        <is>
+          <t>213K</t>
+        </is>
+      </c>
+      <c r="D73" t="inlineStr">
+        <is>
+          <t>223.25K</t>
+        </is>
+      </c>
       <c r="E73" t="inlineStr"/>
-      <c r="F73" t="inlineStr"/>
+      <c r="F73" t="inlineStr">
+        <is>
+          <t>224K</t>
+        </is>
+      </c>
       <c r="G73" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="74">
@@ -2561,31 +2561,31 @@
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>Continuing Jobless ClaimsDEC/28</t>
+          <t>Initial Jobless ClaimsJAN/04</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>1867K</t>
+          <t>201K</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>1834K</t>
+          <t>211K</t>
         </is>
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>1870K</t>
+          <t>218K</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>1848K</t>
+          <t>213K</t>
         </is>
       </c>
       <c r="G74" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="75">
@@ -2685,27 +2685,23 @@
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>EIA Crude Oil Stocks ChangeJAN/03</t>
+          <t>EIA Gasoline Production ChangeJAN/03</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
+          <t>-0.081M</t>
+        </is>
+      </c>
+      <c r="D78" t="inlineStr">
+        <is>
           <t>-0.959M</t>
         </is>
       </c>
-      <c r="D78" t="inlineStr">
-        <is>
-          <t>-1.178M</t>
-        </is>
-      </c>
-      <c r="E78" t="inlineStr">
-        <is>
-          <t>-0.6M</t>
-        </is>
-      </c>
+      <c r="E78" t="inlineStr"/>
       <c r="F78" t="inlineStr"/>
       <c r="G78" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="79">
@@ -2716,17 +2712,17 @@
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>EIA Distillate Fuel Production ChangeJAN/03</t>
+          <t>EIA Heating Oil Stocks ChangeJAN/03</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>-0.167M</t>
+          <t>-0.632M</t>
         </is>
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>0.099M</t>
+          <t>-0.416M</t>
         </is>
       </c>
       <c r="E79" t="inlineStr"/>
@@ -2743,23 +2739,27 @@
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>EIA Crude Oil Imports ChangeJAN/03</t>
+          <t>EIA Gasoline Stocks ChangeJAN/03</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>0.278M</t>
+          <t>6.33M</t>
         </is>
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>0.323M</t>
-        </is>
-      </c>
-      <c r="E80" t="inlineStr"/>
+          <t>7.717M</t>
+        </is>
+      </c>
+      <c r="E80" t="inlineStr">
+        <is>
+          <t>1.5M</t>
+        </is>
+      </c>
       <c r="F80" t="inlineStr"/>
       <c r="G80" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="81">
@@ -2770,20 +2770,24 @@
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>EIA Cushing Crude Oil Stocks ChangeJAN/03</t>
+          <t>EIA Distillate Stocks ChangeJAN/03</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>-2.502M</t>
+          <t>6.071M</t>
         </is>
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>-0.142M</t>
-        </is>
-      </c>
-      <c r="E81" t="inlineStr"/>
+          <t>6.406M</t>
+        </is>
+      </c>
+      <c r="E81" t="inlineStr">
+        <is>
+          <t>1M</t>
+        </is>
+      </c>
       <c r="F81" t="inlineStr"/>
       <c r="G81" t="n">
         <v>3</v>
@@ -2824,17 +2828,17 @@
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>EIA Gasoline Production ChangeJAN/03</t>
+          <t>EIA Crude Oil Imports ChangeJAN/03</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>-0.081M</t>
+          <t>0.278M</t>
         </is>
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>-0.959M</t>
+          <t>0.323M</t>
         </is>
       </c>
       <c r="E83" t="inlineStr"/>
@@ -2851,27 +2855,23 @@
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>EIA Gasoline Stocks ChangeJAN/03</t>
+          <t>EIA Distillate Fuel Production ChangeJAN/03</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>6.33M</t>
+          <t>-0.167M</t>
         </is>
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>7.717M</t>
-        </is>
-      </c>
-      <c r="E84" t="inlineStr">
-        <is>
-          <t>1.5M</t>
-        </is>
-      </c>
+          <t>0.099M</t>
+        </is>
+      </c>
+      <c r="E84" t="inlineStr"/>
       <c r="F84" t="inlineStr"/>
       <c r="G84" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="85">
@@ -2882,23 +2882,27 @@
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>EIA Heating Oil Stocks ChangeJAN/03</t>
+          <t>EIA Crude Oil Stocks ChangeJAN/03</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>-0.632M</t>
+          <t>-0.959M</t>
         </is>
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>-0.416M</t>
-        </is>
-      </c>
-      <c r="E85" t="inlineStr"/>
+          <t>-1.178M</t>
+        </is>
+      </c>
+      <c r="E85" t="inlineStr">
+        <is>
+          <t>-0.6M</t>
+        </is>
+      </c>
       <c r="F85" t="inlineStr"/>
       <c r="G85" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="86">
@@ -2909,24 +2913,20 @@
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>EIA Distillate Stocks ChangeJAN/03</t>
+          <t>EIA Cushing Crude Oil Stocks ChangeJAN/03</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>6.071M</t>
+          <t>-2.502M</t>
         </is>
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>6.406M</t>
-        </is>
-      </c>
-      <c r="E86" t="inlineStr">
-        <is>
-          <t>1M</t>
-        </is>
-      </c>
+          <t>-0.142M</t>
+        </is>
+      </c>
+      <c r="E86" t="inlineStr"/>
       <c r="F86" t="inlineStr"/>
       <c r="G86" t="n">
         <v>3</v>
@@ -3336,27 +3336,31 @@
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>U-6 Unemployment Rate</t>
+          <t>Average Hourly Earnings MoMDEC</t>
         </is>
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>7.5%</t>
+          <t>0.3%</t>
         </is>
       </c>
       <c r="D103" t="inlineStr">
         <is>
-          <t>7.7%</t>
-        </is>
-      </c>
-      <c r="E103" t="inlineStr"/>
+          <t>0.4%</t>
+        </is>
+      </c>
+      <c r="E103" t="inlineStr">
+        <is>
+          <t>0.3%</t>
+        </is>
+      </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>7.9%</t>
+          <t>0.3%</t>
         </is>
       </c>
       <c r="G103" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="104">
@@ -3367,31 +3371,31 @@
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>Average Weekly HoursDEC</t>
+          <t>Average Hourly Earnings YoY</t>
         </is>
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>34.3</t>
+          <t>3.9%</t>
         </is>
       </c>
       <c r="D104" t="inlineStr">
         <is>
-          <t>34.3</t>
+          <t>4%</t>
         </is>
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>34.3</t>
+          <t>4%</t>
         </is>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>34.3</t>
+          <t>4%</t>
         </is>
       </c>
       <c r="G104" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="105">
@@ -3402,27 +3406,31 @@
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>Government PayrollsDEC</t>
+          <t>Non Farm PayrollsDEC</t>
         </is>
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>33K</t>
+          <t>256K</t>
         </is>
       </c>
       <c r="D105" t="inlineStr">
         <is>
-          <t>30K</t>
-        </is>
-      </c>
-      <c r="E105" t="inlineStr"/>
+          <t>212K</t>
+        </is>
+      </c>
+      <c r="E105" t="inlineStr">
+        <is>
+          <t>160K</t>
+        </is>
+      </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>15K</t>
+          <t>200K</t>
         </is>
       </c>
       <c r="G105" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="106">
@@ -3433,31 +3441,27 @@
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>Nonfarm Payrolls PrivateDEC</t>
+          <t>Participation RateDEC</t>
         </is>
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>223K</t>
+          <t>62.5%</t>
         </is>
       </c>
       <c r="D106" t="inlineStr">
         <is>
-          <t>182K</t>
-        </is>
-      </c>
-      <c r="E106" t="inlineStr">
-        <is>
-          <t>135K</t>
-        </is>
-      </c>
+          <t>62.5%</t>
+        </is>
+      </c>
+      <c r="E106" t="inlineStr"/>
       <c r="F106" t="inlineStr">
         <is>
-          <t>185K</t>
+          <t>62.8%</t>
         </is>
       </c>
       <c r="G106" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="107">
@@ -3468,31 +3472,31 @@
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>Manufacturing PayrollsDEC</t>
+          <t>Unemployment RateDEC</t>
         </is>
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>-13K</t>
+          <t>4.1%</t>
         </is>
       </c>
       <c r="D107" t="inlineStr">
         <is>
-          <t>25K</t>
+          <t>4.2%</t>
         </is>
       </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t>5K</t>
+          <t>4.2%</t>
         </is>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>29K</t>
+          <t>4.30%</t>
         </is>
       </c>
       <c r="G107" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="108">
@@ -3503,27 +3507,31 @@
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>Participation RateDEC</t>
+          <t>Nonfarm Payrolls PrivateDEC</t>
         </is>
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>62.5%</t>
+          <t>223K</t>
         </is>
       </c>
       <c r="D108" t="inlineStr">
         <is>
-          <t>62.5%</t>
-        </is>
-      </c>
-      <c r="E108" t="inlineStr"/>
+          <t>182K</t>
+        </is>
+      </c>
+      <c r="E108" t="inlineStr">
+        <is>
+          <t>135K</t>
+        </is>
+      </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>62.8%</t>
+          <t>185K</t>
         </is>
       </c>
       <c r="G108" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="109">
@@ -3534,31 +3542,27 @@
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>Non Farm PayrollsDEC</t>
+          <t>Government PayrollsDEC</t>
         </is>
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>256K</t>
+          <t>33K</t>
         </is>
       </c>
       <c r="D109" t="inlineStr">
         <is>
-          <t>212K</t>
-        </is>
-      </c>
-      <c r="E109" t="inlineStr">
-        <is>
-          <t>160K</t>
-        </is>
-      </c>
+          <t>30K</t>
+        </is>
+      </c>
+      <c r="E109" t="inlineStr"/>
       <c r="F109" t="inlineStr">
         <is>
-          <t>200K</t>
+          <t>15K</t>
         </is>
       </c>
       <c r="G109" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="110">
@@ -3569,31 +3573,31 @@
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>Average Hourly Earnings YoY</t>
+          <t>Average Weekly HoursDEC</t>
         </is>
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>3.9%</t>
+          <t>34.3</t>
         </is>
       </c>
       <c r="D110" t="inlineStr">
         <is>
-          <t>4%</t>
+          <t>34.3</t>
         </is>
       </c>
       <c r="E110" t="inlineStr">
         <is>
-          <t>4%</t>
+          <t>34.3</t>
         </is>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>4%</t>
+          <t>34.3</t>
         </is>
       </c>
       <c r="G110" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="111">
@@ -3604,31 +3608,27 @@
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>Average Hourly Earnings MoMDEC</t>
+          <t>U-6 Unemployment Rate</t>
         </is>
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>0.3%</t>
+          <t>7.5%</t>
         </is>
       </c>
       <c r="D111" t="inlineStr">
         <is>
-          <t>0.4%</t>
-        </is>
-      </c>
-      <c r="E111" t="inlineStr">
-        <is>
-          <t>0.3%</t>
-        </is>
-      </c>
+          <t>7.7%</t>
+        </is>
+      </c>
+      <c r="E111" t="inlineStr"/>
       <c r="F111" t="inlineStr">
         <is>
-          <t>0.3%</t>
+          <t>7.9%</t>
         </is>
       </c>
       <c r="G111" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="112">
@@ -3639,31 +3639,31 @@
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>Unemployment RateDEC</t>
+          <t>Manufacturing PayrollsDEC</t>
         </is>
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>4.1%</t>
+          <t>-13K</t>
         </is>
       </c>
       <c r="D112" t="inlineStr">
         <is>
-          <t>4.2%</t>
+          <t>25K</t>
         </is>
       </c>
       <c r="E112" t="inlineStr">
         <is>
-          <t>4.2%</t>
+          <t>5K</t>
         </is>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>4.30%</t>
+          <t>29K</t>
         </is>
       </c>
       <c r="G112" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="113">
@@ -3833,11 +3833,19 @@
       </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t>WASDE Report</t>
-        </is>
-      </c>
-      <c r="C118" t="inlineStr"/>
-      <c r="D118" t="inlineStr"/>
+          <t>Quarterly Grain Stocks - SoyDEC</t>
+        </is>
+      </c>
+      <c r="C118" t="inlineStr">
+        <is>
+          <t>3.1B</t>
+        </is>
+      </c>
+      <c r="D118" t="inlineStr">
+        <is>
+          <t>0.342B</t>
+        </is>
+      </c>
       <c r="E118" t="inlineStr"/>
       <c r="F118" t="inlineStr"/>
       <c r="G118" t="n">
@@ -3852,17 +3860,17 @@
       </c>
       <c r="B119" t="inlineStr">
         <is>
-          <t>Quarterly Grain Stocks - WheatDEC</t>
+          <t>Quarterly Grain Stocks - CornDEC</t>
         </is>
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>1.57B</t>
+          <t>12.074B</t>
         </is>
       </c>
       <c r="D119" t="inlineStr">
         <is>
-          <t>1.98B</t>
+          <t>1.760B</t>
         </is>
       </c>
       <c r="E119" t="inlineStr"/>
@@ -3879,17 +3887,17 @@
       </c>
       <c r="B120" t="inlineStr">
         <is>
-          <t>Quarterly Grain Stocks - CornDEC</t>
+          <t>Quarterly Grain Stocks - WheatDEC</t>
         </is>
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>12.074B</t>
+          <t>1.57B</t>
         </is>
       </c>
       <c r="D120" t="inlineStr">
         <is>
-          <t>1.760B</t>
+          <t>1.98B</t>
         </is>
       </c>
       <c r="E120" t="inlineStr"/>
@@ -3906,19 +3914,11 @@
       </c>
       <c r="B121" t="inlineStr">
         <is>
-          <t>Quarterly Grain Stocks - SoyDEC</t>
-        </is>
-      </c>
-      <c r="C121" t="inlineStr">
-        <is>
-          <t>3.1B</t>
-        </is>
-      </c>
-      <c r="D121" t="inlineStr">
-        <is>
-          <t>0.342B</t>
-        </is>
-      </c>
+          <t>WASDE Report</t>
+        </is>
+      </c>
+      <c r="C121" t="inlineStr"/>
+      <c r="D121" t="inlineStr"/>
       <c r="E121" t="inlineStr"/>
       <c r="F121" t="inlineStr"/>
       <c r="G121" t="n">
@@ -4134,31 +4134,31 @@
       </c>
       <c r="B129" t="inlineStr">
         <is>
-          <t>Core PPI MoMDEC</t>
+          <t>PPI YoYDEC</t>
         </is>
       </c>
       <c r="C129" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>3.3%</t>
         </is>
       </c>
       <c r="D129" t="inlineStr">
         <is>
-          <t>0.2%</t>
+          <t>3%</t>
         </is>
       </c>
       <c r="E129" t="inlineStr">
         <is>
-          <t>0.3%</t>
+          <t>3.4%</t>
         </is>
       </c>
       <c r="F129" t="inlineStr">
         <is>
-          <t>0.2%</t>
+          <t>3.3%</t>
         </is>
       </c>
       <c r="G129" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="130">
@@ -4169,27 +4169,31 @@
       </c>
       <c r="B130" t="inlineStr">
         <is>
-          <t>PPI Ex Food, Energy and Trade YoYDEC</t>
+          <t>PPI MoMDEC</t>
         </is>
       </c>
       <c r="C130" t="inlineStr">
         <is>
-          <t>3.3%</t>
+          <t>0.2%</t>
         </is>
       </c>
       <c r="D130" t="inlineStr">
         <is>
-          <t>3.5%</t>
-        </is>
-      </c>
-      <c r="E130" t="inlineStr"/>
+          <t>0.4%</t>
+        </is>
+      </c>
+      <c r="E130" t="inlineStr">
+        <is>
+          <t>0.3%</t>
+        </is>
+      </c>
       <c r="F130" t="inlineStr">
         <is>
-          <t>3.6%</t>
+          <t>0.3%</t>
         </is>
       </c>
       <c r="G130" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="131">
@@ -4200,27 +4204,23 @@
       </c>
       <c r="B131" t="inlineStr">
         <is>
-          <t>PPI Ex Food, Energy and Trade MoMDEC</t>
+          <t>PPIDEC</t>
         </is>
       </c>
       <c r="C131" t="inlineStr">
         <is>
-          <t>0.1%</t>
+          <t>146.842</t>
         </is>
       </c>
       <c r="D131" t="inlineStr">
         <is>
-          <t>0.1%</t>
-        </is>
-      </c>
-      <c r="E131" t="inlineStr">
-        <is>
-          <t>0.3%</t>
-        </is>
-      </c>
+          <t>146.521</t>
+        </is>
+      </c>
+      <c r="E131" t="inlineStr"/>
       <c r="F131" t="inlineStr">
         <is>
-          <t>0.2%</t>
+          <t>146.8</t>
         </is>
       </c>
       <c r="G131" t="n">
@@ -4235,23 +4235,27 @@
       </c>
       <c r="B132" t="inlineStr">
         <is>
-          <t>PPIDEC</t>
+          <t>Core PPI YoYDEC</t>
         </is>
       </c>
       <c r="C132" t="inlineStr">
         <is>
-          <t>146.842</t>
+          <t>3.5%</t>
         </is>
       </c>
       <c r="D132" t="inlineStr">
         <is>
-          <t>146.521</t>
-        </is>
-      </c>
-      <c r="E132" t="inlineStr"/>
+          <t>3.5%</t>
+        </is>
+      </c>
+      <c r="E132" t="inlineStr">
+        <is>
+          <t>3.8%</t>
+        </is>
+      </c>
       <c r="F132" t="inlineStr">
         <is>
-          <t>146.8</t>
+          <t>3.5%</t>
         </is>
       </c>
       <c r="G132" t="n">
@@ -4266,31 +4270,27 @@
       </c>
       <c r="B133" t="inlineStr">
         <is>
-          <t>PPI MoMDEC</t>
+          <t>PPI Ex Food, Energy and Trade YoYDEC</t>
         </is>
       </c>
       <c r="C133" t="inlineStr">
         <is>
-          <t>0.2%</t>
+          <t>3.3%</t>
         </is>
       </c>
       <c r="D133" t="inlineStr">
         <is>
-          <t>0.4%</t>
-        </is>
-      </c>
-      <c r="E133" t="inlineStr">
-        <is>
-          <t>0.3%</t>
-        </is>
-      </c>
+          <t>3.5%</t>
+        </is>
+      </c>
+      <c r="E133" t="inlineStr"/>
       <c r="F133" t="inlineStr">
         <is>
-          <t>0.3%</t>
+          <t>3.6%</t>
         </is>
       </c>
       <c r="G133" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="134">
@@ -4301,31 +4301,31 @@
       </c>
       <c r="B134" t="inlineStr">
         <is>
-          <t>Core PPI YoYDEC</t>
+          <t>Core PPI MoMDEC</t>
         </is>
       </c>
       <c r="C134" t="inlineStr">
         <is>
-          <t>3.5%</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="D134" t="inlineStr">
         <is>
-          <t>3.5%</t>
+          <t>0.2%</t>
         </is>
       </c>
       <c r="E134" t="inlineStr">
         <is>
-          <t>3.8%</t>
+          <t>0.3%</t>
         </is>
       </c>
       <c r="F134" t="inlineStr">
         <is>
-          <t>3.5%</t>
+          <t>0.2%</t>
         </is>
       </c>
       <c r="G134" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="135">
@@ -4336,27 +4336,27 @@
       </c>
       <c r="B135" t="inlineStr">
         <is>
-          <t>PPI YoYDEC</t>
+          <t>PPI Ex Food, Energy and Trade MoMDEC</t>
         </is>
       </c>
       <c r="C135" t="inlineStr">
         <is>
-          <t>3.3%</t>
+          <t>0.1%</t>
         </is>
       </c>
       <c r="D135" t="inlineStr">
         <is>
-          <t>3%</t>
+          <t>0.1%</t>
         </is>
       </c>
       <c r="E135" t="inlineStr">
         <is>
-          <t>3.4%</t>
+          <t>0.3%</t>
         </is>
       </c>
       <c r="F135" t="inlineStr">
         <is>
-          <t>3.3%</t>
+          <t>0.2%</t>
         </is>
       </c>
       <c r="G135" t="n">
@@ -4564,17 +4564,17 @@
       </c>
       <c r="B143" t="inlineStr">
         <is>
-          <t>MBA Purchase IndexJAN/10</t>
+          <t>MBA Mortgage Market IndexJAN/10</t>
         </is>
       </c>
       <c r="C143" t="inlineStr">
         <is>
-          <t>162</t>
+          <t>224.4</t>
         </is>
       </c>
       <c r="D143" t="inlineStr">
         <is>
-          <t>127.7000</t>
+          <t>168.4</t>
         </is>
       </c>
       <c r="E143" t="inlineStr"/>
@@ -4591,23 +4591,23 @@
       </c>
       <c r="B144" t="inlineStr">
         <is>
-          <t>MBA 30-Year Mortgage RateJAN/10</t>
+          <t>MBA Mortgage Refinance IndexJAN/10</t>
         </is>
       </c>
       <c r="C144" t="inlineStr">
         <is>
-          <t>7.09%</t>
+          <t>575.6</t>
         </is>
       </c>
       <c r="D144" t="inlineStr">
         <is>
-          <t>6.99%</t>
+          <t>401.1000</t>
         </is>
       </c>
       <c r="E144" t="inlineStr"/>
       <c r="F144" t="inlineStr"/>
       <c r="G144" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="145">
@@ -4618,17 +4618,17 @@
       </c>
       <c r="B145" t="inlineStr">
         <is>
-          <t>MBA Mortgage Refinance IndexJAN/10</t>
+          <t>MBA Mortgage ApplicationsJAN/10</t>
         </is>
       </c>
       <c r="C145" t="inlineStr">
         <is>
-          <t>575.6</t>
+          <t>33.3%</t>
         </is>
       </c>
       <c r="D145" t="inlineStr">
         <is>
-          <t>401.1000</t>
+          <t>-3.7%</t>
         </is>
       </c>
       <c r="E145" t="inlineStr"/>
@@ -4645,17 +4645,17 @@
       </c>
       <c r="B146" t="inlineStr">
         <is>
-          <t>MBA Mortgage ApplicationsJAN/10</t>
+          <t>MBA Purchase IndexJAN/10</t>
         </is>
       </c>
       <c r="C146" t="inlineStr">
         <is>
-          <t>33.3%</t>
+          <t>162</t>
         </is>
       </c>
       <c r="D146" t="inlineStr">
         <is>
-          <t>-3.7%</t>
+          <t>127.7000</t>
         </is>
       </c>
       <c r="E146" t="inlineStr"/>
@@ -4672,23 +4672,23 @@
       </c>
       <c r="B147" t="inlineStr">
         <is>
-          <t>MBA Mortgage Market IndexJAN/10</t>
+          <t>MBA 30-Year Mortgage RateJAN/10</t>
         </is>
       </c>
       <c r="C147" t="inlineStr">
         <is>
-          <t>224.4</t>
+          <t>7.09%</t>
         </is>
       </c>
       <c r="D147" t="inlineStr">
         <is>
-          <t>168.4</t>
+          <t>6.99%</t>
         </is>
       </c>
       <c r="E147" t="inlineStr"/>
       <c r="F147" t="inlineStr"/>
       <c r="G147" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="148">
@@ -4978,22 +4978,22 @@
       </c>
       <c r="B157" t="inlineStr">
         <is>
-          <t>EIA Crude Oil Stocks ChangeJAN/10</t>
+          <t>EIA Gasoline Stocks ChangeJAN/10</t>
         </is>
       </c>
       <c r="C157" t="inlineStr">
         <is>
-          <t>-1.961M</t>
+          <t>5.852M</t>
         </is>
       </c>
       <c r="D157" t="inlineStr">
         <is>
-          <t>-0.959M</t>
+          <t>6.33M</t>
         </is>
       </c>
       <c r="E157" t="inlineStr">
         <is>
-          <t>-1.6M</t>
+          <t>2.60M</t>
         </is>
       </c>
       <c r="F157" t="inlineStr"/>
@@ -5009,24 +5009,20 @@
       </c>
       <c r="B158" t="inlineStr">
         <is>
-          <t>EIA Distillate Stocks ChangeJAN/10</t>
+          <t>EIA Refinery Crude Runs ChangeJAN/10</t>
         </is>
       </c>
       <c r="C158" t="inlineStr">
         <is>
-          <t>3.077M</t>
+          <t>-0.255M</t>
         </is>
       </c>
       <c r="D158" t="inlineStr">
         <is>
-          <t>6.071M</t>
-        </is>
-      </c>
-      <c r="E158" t="inlineStr">
-        <is>
-          <t>1.1M</t>
-        </is>
-      </c>
+          <t>0.045M</t>
+        </is>
+      </c>
+      <c r="E158" t="inlineStr"/>
       <c r="F158" t="inlineStr"/>
       <c r="G158" t="n">
         <v>3</v>
@@ -5040,17 +5036,17 @@
       </c>
       <c r="B159" t="inlineStr">
         <is>
-          <t>EIA Gasoline Production ChangeJAN/10</t>
+          <t>EIA Heating Oil Stocks ChangeJAN/10</t>
         </is>
       </c>
       <c r="C159" t="inlineStr">
         <is>
-          <t>0.397M</t>
+          <t>0.646M</t>
         </is>
       </c>
       <c r="D159" t="inlineStr">
         <is>
-          <t>-0.081M</t>
+          <t>-0.632M</t>
         </is>
       </c>
       <c r="E159" t="inlineStr"/>
@@ -5067,17 +5063,17 @@
       </c>
       <c r="B160" t="inlineStr">
         <is>
-          <t>EIA Crude Oil Imports ChangeJAN/10</t>
+          <t>EIA Cushing Crude Oil Stocks ChangeJAN/10</t>
         </is>
       </c>
       <c r="C160" t="inlineStr">
         <is>
-          <t>-1.304M</t>
+          <t>0.765M</t>
         </is>
       </c>
       <c r="D160" t="inlineStr">
         <is>
-          <t>0.278M</t>
+          <t>-2.502M</t>
         </is>
       </c>
       <c r="E160" t="inlineStr"/>
@@ -5094,17 +5090,17 @@
       </c>
       <c r="B161" t="inlineStr">
         <is>
-          <t>EIA Cushing Crude Oil Stocks ChangeJAN/10</t>
+          <t>EIA Distillate Fuel Production ChangeJAN/10</t>
         </is>
       </c>
       <c r="C161" t="inlineStr">
         <is>
-          <t>0.765M</t>
+          <t>-0.021M</t>
         </is>
       </c>
       <c r="D161" t="inlineStr">
         <is>
-          <t>-2.502M</t>
+          <t>-0.167M</t>
         </is>
       </c>
       <c r="E161" t="inlineStr"/>
@@ -5121,27 +5117,23 @@
       </c>
       <c r="B162" t="inlineStr">
         <is>
-          <t>EIA Gasoline Stocks ChangeJAN/10</t>
+          <t>EIA Gasoline Production ChangeJAN/10</t>
         </is>
       </c>
       <c r="C162" t="inlineStr">
         <is>
-          <t>5.852M</t>
+          <t>0.397M</t>
         </is>
       </c>
       <c r="D162" t="inlineStr">
         <is>
-          <t>6.33M</t>
-        </is>
-      </c>
-      <c r="E162" t="inlineStr">
-        <is>
-          <t>2.60M</t>
-        </is>
-      </c>
+          <t>-0.081M</t>
+        </is>
+      </c>
+      <c r="E162" t="inlineStr"/>
       <c r="F162" t="inlineStr"/>
       <c r="G162" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="163">
@@ -5152,23 +5144,27 @@
       </c>
       <c r="B163" t="inlineStr">
         <is>
-          <t>EIA Heating Oil Stocks ChangeJAN/10</t>
+          <t>EIA Crude Oil Stocks ChangeJAN/10</t>
         </is>
       </c>
       <c r="C163" t="inlineStr">
         <is>
-          <t>0.646M</t>
+          <t>-1.961M</t>
         </is>
       </c>
       <c r="D163" t="inlineStr">
         <is>
-          <t>-0.632M</t>
-        </is>
-      </c>
-      <c r="E163" t="inlineStr"/>
+          <t>-0.959M</t>
+        </is>
+      </c>
+      <c r="E163" t="inlineStr">
+        <is>
+          <t>-1.6M</t>
+        </is>
+      </c>
       <c r="F163" t="inlineStr"/>
       <c r="G163" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="164">
@@ -5179,17 +5175,17 @@
       </c>
       <c r="B164" t="inlineStr">
         <is>
-          <t>EIA Refinery Crude Runs ChangeJAN/10</t>
+          <t>EIA Crude Oil Imports ChangeJAN/10</t>
         </is>
       </c>
       <c r="C164" t="inlineStr">
         <is>
-          <t>-0.255M</t>
+          <t>-1.304M</t>
         </is>
       </c>
       <c r="D164" t="inlineStr">
         <is>
-          <t>0.045M</t>
+          <t>0.278M</t>
         </is>
       </c>
       <c r="E164" t="inlineStr"/>
@@ -5206,20 +5202,24 @@
       </c>
       <c r="B165" t="inlineStr">
         <is>
-          <t>EIA Distillate Fuel Production ChangeJAN/10</t>
+          <t>EIA Distillate Stocks ChangeJAN/10</t>
         </is>
       </c>
       <c r="C165" t="inlineStr">
         <is>
-          <t>-0.021M</t>
+          <t>3.077M</t>
         </is>
       </c>
       <c r="D165" t="inlineStr">
         <is>
-          <t>-0.167M</t>
-        </is>
-      </c>
-      <c r="E165" t="inlineStr"/>
+          <t>6.071M</t>
+        </is>
+      </c>
+      <c r="E165" t="inlineStr">
+        <is>
+          <t>1.1M</t>
+        </is>
+      </c>
       <c r="F165" t="inlineStr"/>
       <c r="G165" t="n">
         <v>3</v>
@@ -5336,31 +5336,31 @@
       </c>
       <c r="B171" t="inlineStr">
         <is>
-          <t>Continuing Jobless ClaimsJAN/04</t>
+          <t>Retail Sales MoMDEC</t>
         </is>
       </c>
       <c r="C171" t="inlineStr">
         <is>
-          <t>1859K</t>
+          <t>0.4%</t>
         </is>
       </c>
       <c r="D171" t="inlineStr">
         <is>
-          <t>1867K</t>
+          <t>0.8%</t>
         </is>
       </c>
       <c r="E171" t="inlineStr">
         <is>
-          <t>1870K</t>
+          <t>0.6%</t>
         </is>
       </c>
       <c r="F171" t="inlineStr">
         <is>
-          <t>1870.0K</t>
+          <t>0.5%</t>
         </is>
       </c>
       <c r="G171" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="172">
@@ -5371,7 +5371,7 @@
       </c>
       <c r="B172" t="inlineStr">
         <is>
-          <t>Retail Sales Ex Gas/Autos MoMDEC</t>
+          <t>Export Prices MoMDEC</t>
         </is>
       </c>
       <c r="C172" t="inlineStr">
@@ -5381,21 +5381,21 @@
       </c>
       <c r="D172" t="inlineStr">
         <is>
+          <t>0%</t>
+        </is>
+      </c>
+      <c r="E172" t="inlineStr">
+        <is>
           <t>0.2%</t>
         </is>
       </c>
-      <c r="E172" t="inlineStr">
-        <is>
-          <t>0.4%</t>
-        </is>
-      </c>
       <c r="F172" t="inlineStr">
         <is>
-          <t>0.4%</t>
+          <t>0.5%</t>
         </is>
       </c>
       <c r="G172" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="173">
@@ -5406,23 +5406,31 @@
       </c>
       <c r="B173" t="inlineStr">
         <is>
-          <t>Philly Fed New OrdersJAN</t>
+          <t>Initial Jobless ClaimsJAN/11</t>
         </is>
       </c>
       <c r="C173" t="inlineStr">
         <is>
-          <t>42.9</t>
+          <t>217K</t>
         </is>
       </c>
       <c r="D173" t="inlineStr">
         <is>
-          <t>-3.6</t>
-        </is>
-      </c>
-      <c r="E173" t="inlineStr"/>
-      <c r="F173" t="inlineStr"/>
+          <t>203K</t>
+        </is>
+      </c>
+      <c r="E173" t="inlineStr">
+        <is>
+          <t>210K</t>
+        </is>
+      </c>
+      <c r="F173" t="inlineStr">
+        <is>
+          <t>209.0K</t>
+        </is>
+      </c>
       <c r="G173" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="174">
@@ -5433,27 +5441,31 @@
       </c>
       <c r="B174" t="inlineStr">
         <is>
-          <t>Jobless Claims 4-week AverageJAN/11</t>
+          <t>Retail Sales Ex Autos MoMDEC</t>
         </is>
       </c>
       <c r="C174" t="inlineStr">
         <is>
-          <t>212.75K</t>
+          <t>0.4%</t>
         </is>
       </c>
       <c r="D174" t="inlineStr">
         <is>
-          <t>213.5K</t>
-        </is>
-      </c>
-      <c r="E174" t="inlineStr"/>
+          <t>0.2%</t>
+        </is>
+      </c>
+      <c r="E174" t="inlineStr">
+        <is>
+          <t>0.4%</t>
+        </is>
+      </c>
       <c r="F174" t="inlineStr">
         <is>
-          <t>215.0K</t>
+          <t>0.4%</t>
         </is>
       </c>
       <c r="G174" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="175">
@@ -5464,31 +5476,23 @@
       </c>
       <c r="B175" t="inlineStr">
         <is>
-          <t>Import Prices MoMDEC</t>
+          <t>Philly Fed Prices PaidJAN</t>
         </is>
       </c>
       <c r="C175" t="inlineStr">
         <is>
-          <t>0.1%</t>
+          <t>31.90</t>
         </is>
       </c>
       <c r="D175" t="inlineStr">
         <is>
-          <t>0.1%</t>
-        </is>
-      </c>
-      <c r="E175" t="inlineStr">
-        <is>
-          <t>0.1%</t>
-        </is>
-      </c>
-      <c r="F175" t="inlineStr">
-        <is>
-          <t>0.1%</t>
-        </is>
-      </c>
+          <t>26.60</t>
+        </is>
+      </c>
+      <c r="E175" t="inlineStr"/>
+      <c r="F175" t="inlineStr"/>
       <c r="G175" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="176">
@@ -5499,25 +5503,21 @@
       </c>
       <c r="B176" t="inlineStr">
         <is>
-          <t>Export Prices YoYDEC</t>
+          <t>Philly Fed Business ConditionsJAN</t>
         </is>
       </c>
       <c r="C176" t="inlineStr">
         <is>
-          <t>1.8%</t>
+          <t>46.3</t>
         </is>
       </c>
       <c r="D176" t="inlineStr">
         <is>
-          <t>0.9%</t>
+          <t>33.8</t>
         </is>
       </c>
       <c r="E176" t="inlineStr"/>
-      <c r="F176" t="inlineStr">
-        <is>
-          <t>1.9%</t>
-        </is>
-      </c>
+      <c r="F176" t="inlineStr"/>
       <c r="G176" t="n">
         <v>3</v>
       </c>
@@ -5530,31 +5530,23 @@
       </c>
       <c r="B177" t="inlineStr">
         <is>
-          <t>Philadelphia Fed Manufacturing IndexJAN</t>
+          <t>Philly Fed CAPEX IndexJAN</t>
         </is>
       </c>
       <c r="C177" t="inlineStr">
         <is>
-          <t>44.3</t>
+          <t>39.00</t>
         </is>
       </c>
       <c r="D177" t="inlineStr">
         <is>
-          <t>-10.9</t>
-        </is>
-      </c>
-      <c r="E177" t="inlineStr">
-        <is>
-          <t>-5</t>
-        </is>
-      </c>
-      <c r="F177" t="inlineStr">
-        <is>
-          <t>-10</t>
-        </is>
-      </c>
+          <t>22.20</t>
+        </is>
+      </c>
+      <c r="E177" t="inlineStr"/>
+      <c r="F177" t="inlineStr"/>
       <c r="G177" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="178">
@@ -5565,31 +5557,31 @@
       </c>
       <c r="B178" t="inlineStr">
         <is>
-          <t>Retail Sales MoMDEC</t>
+          <t>Import Prices YoYDEC</t>
         </is>
       </c>
       <c r="C178" t="inlineStr">
         <is>
-          <t>0.4%</t>
+          <t>2.2%</t>
         </is>
       </c>
       <c r="D178" t="inlineStr">
         <is>
-          <t>0.8%</t>
+          <t>1.4%</t>
         </is>
       </c>
       <c r="E178" t="inlineStr">
         <is>
-          <t>0.6%</t>
+          <t>2.1%</t>
         </is>
       </c>
       <c r="F178" t="inlineStr">
         <is>
-          <t>0.5%</t>
+          <t>1.6%</t>
         </is>
       </c>
       <c r="G178" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="179">
@@ -5600,21 +5592,25 @@
       </c>
       <c r="B179" t="inlineStr">
         <is>
-          <t>Philly Fed EmploymentJAN</t>
+          <t>Retail Sales YoYDEC</t>
         </is>
       </c>
       <c r="C179" t="inlineStr">
         <is>
-          <t>11.9</t>
+          <t>3.9%</t>
         </is>
       </c>
       <c r="D179" t="inlineStr">
         <is>
-          <t>4.8</t>
+          <t>4.1%</t>
         </is>
       </c>
       <c r="E179" t="inlineStr"/>
-      <c r="F179" t="inlineStr"/>
+      <c r="F179" t="inlineStr">
+        <is>
+          <t>4.0%</t>
+        </is>
+      </c>
       <c r="G179" t="n">
         <v>3</v>
       </c>
@@ -5627,27 +5623,31 @@
       </c>
       <c r="B180" t="inlineStr">
         <is>
-          <t>Retail Sales YoYDEC</t>
+          <t>Philadelphia Fed Manufacturing IndexJAN</t>
         </is>
       </c>
       <c r="C180" t="inlineStr">
         <is>
-          <t>3.9%</t>
+          <t>44.3</t>
         </is>
       </c>
       <c r="D180" t="inlineStr">
         <is>
-          <t>4.1%</t>
-        </is>
-      </c>
-      <c r="E180" t="inlineStr"/>
+          <t>-10.9</t>
+        </is>
+      </c>
+      <c r="E180" t="inlineStr">
+        <is>
+          <t>-5</t>
+        </is>
+      </c>
       <c r="F180" t="inlineStr">
         <is>
-          <t>4.0%</t>
+          <t>-10</t>
         </is>
       </c>
       <c r="G180" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="181">
@@ -5658,27 +5658,23 @@
       </c>
       <c r="B181" t="inlineStr">
         <is>
-          <t>Import Prices YoYDEC</t>
+          <t>Export Prices YoYDEC</t>
         </is>
       </c>
       <c r="C181" t="inlineStr">
         <is>
-          <t>2.2%</t>
+          <t>1.8%</t>
         </is>
       </c>
       <c r="D181" t="inlineStr">
         <is>
-          <t>1.4%</t>
-        </is>
-      </c>
-      <c r="E181" t="inlineStr">
-        <is>
-          <t>2.1%</t>
-        </is>
-      </c>
+          <t>0.9%</t>
+        </is>
+      </c>
+      <c r="E181" t="inlineStr"/>
       <c r="F181" t="inlineStr">
         <is>
-          <t>1.6%</t>
+          <t>1.9%</t>
         </is>
       </c>
       <c r="G181" t="n">
@@ -5693,23 +5689,31 @@
       </c>
       <c r="B182" t="inlineStr">
         <is>
-          <t>Philly Fed CAPEX IndexJAN</t>
+          <t>Import Prices MoMDEC</t>
         </is>
       </c>
       <c r="C182" t="inlineStr">
         <is>
-          <t>39.00</t>
+          <t>0.1%</t>
         </is>
       </c>
       <c r="D182" t="inlineStr">
         <is>
-          <t>22.20</t>
-        </is>
-      </c>
-      <c r="E182" t="inlineStr"/>
-      <c r="F182" t="inlineStr"/>
+          <t>0.1%</t>
+        </is>
+      </c>
+      <c r="E182" t="inlineStr">
+        <is>
+          <t>0.1%</t>
+        </is>
+      </c>
+      <c r="F182" t="inlineStr">
+        <is>
+          <t>0.1%</t>
+        </is>
+      </c>
       <c r="G182" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="183">
@@ -5720,21 +5724,25 @@
       </c>
       <c r="B183" t="inlineStr">
         <is>
-          <t>Philly Fed Business ConditionsJAN</t>
+          <t>Jobless Claims 4-week AverageJAN/11</t>
         </is>
       </c>
       <c r="C183" t="inlineStr">
         <is>
-          <t>46.3</t>
+          <t>212.75K</t>
         </is>
       </c>
       <c r="D183" t="inlineStr">
         <is>
-          <t>33.8</t>
+          <t>213.5K</t>
         </is>
       </c>
       <c r="E183" t="inlineStr"/>
-      <c r="F183" t="inlineStr"/>
+      <c r="F183" t="inlineStr">
+        <is>
+          <t>215.0K</t>
+        </is>
+      </c>
       <c r="G183" t="n">
         <v>3</v>
       </c>
@@ -5747,17 +5755,17 @@
       </c>
       <c r="B184" t="inlineStr">
         <is>
-          <t>Philly Fed Prices PaidJAN</t>
+          <t>Philly Fed New OrdersJAN</t>
         </is>
       </c>
       <c r="C184" t="inlineStr">
         <is>
-          <t>31.90</t>
+          <t>42.9</t>
         </is>
       </c>
       <c r="D184" t="inlineStr">
         <is>
-          <t>26.60</t>
+          <t>-3.6</t>
         </is>
       </c>
       <c r="E184" t="inlineStr"/>
@@ -5774,31 +5782,31 @@
       </c>
       <c r="B185" t="inlineStr">
         <is>
-          <t>Retail Sales Ex Autos MoMDEC</t>
+          <t>Retail Sales Ex Gas/Autos MoMDEC</t>
         </is>
       </c>
       <c r="C185" t="inlineStr">
         <is>
+          <t>0.3%</t>
+        </is>
+      </c>
+      <c r="D185" t="inlineStr">
+        <is>
+          <t>0.2%</t>
+        </is>
+      </c>
+      <c r="E185" t="inlineStr">
+        <is>
           <t>0.4%</t>
         </is>
       </c>
-      <c r="D185" t="inlineStr">
-        <is>
-          <t>0.2%</t>
-        </is>
-      </c>
-      <c r="E185" t="inlineStr">
+      <c r="F185" t="inlineStr">
         <is>
           <t>0.4%</t>
         </is>
       </c>
-      <c r="F185" t="inlineStr">
-        <is>
-          <t>0.4%</t>
-        </is>
-      </c>
       <c r="G185" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="186">
@@ -5809,31 +5817,31 @@
       </c>
       <c r="B186" t="inlineStr">
         <is>
-          <t>Initial Jobless ClaimsJAN/11</t>
+          <t>Continuing Jobless ClaimsJAN/04</t>
         </is>
       </c>
       <c r="C186" t="inlineStr">
         <is>
-          <t>217K</t>
+          <t>1859K</t>
         </is>
       </c>
       <c r="D186" t="inlineStr">
         <is>
-          <t>203K</t>
+          <t>1867K</t>
         </is>
       </c>
       <c r="E186" t="inlineStr">
         <is>
-          <t>210K</t>
+          <t>1870K</t>
         </is>
       </c>
       <c r="F186" t="inlineStr">
         <is>
-          <t>209.0K</t>
+          <t>1870.0K</t>
         </is>
       </c>
       <c r="G186" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="187">
@@ -5844,31 +5852,23 @@
       </c>
       <c r="B187" t="inlineStr">
         <is>
-          <t>Export Prices MoMDEC</t>
+          <t>Philly Fed EmploymentJAN</t>
         </is>
       </c>
       <c r="C187" t="inlineStr">
         <is>
-          <t>0.3%</t>
+          <t>11.9</t>
         </is>
       </c>
       <c r="D187" t="inlineStr">
         <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="E187" t="inlineStr">
-        <is>
-          <t>0.2%</t>
-        </is>
-      </c>
-      <c r="F187" t="inlineStr">
-        <is>
-          <t>0.5%</t>
-        </is>
-      </c>
+          <t>4.8</t>
+        </is>
+      </c>
+      <c r="E187" t="inlineStr"/>
+      <c r="F187" t="inlineStr"/>
       <c r="G187" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="188">
@@ -6015,17 +6015,17 @@
       </c>
       <c r="B192" t="inlineStr">
         <is>
-          <t>8-Week Bill Auction</t>
+          <t>4-Week Bill Auction</t>
         </is>
       </c>
       <c r="C192" t="inlineStr">
         <is>
-          <t>4.235%</t>
+          <t>4.240%</t>
         </is>
       </c>
       <c r="D192" t="inlineStr">
         <is>
-          <t>4.240%</t>
+          <t>4.245%</t>
         </is>
       </c>
       <c r="E192" t="inlineStr"/>
@@ -6042,17 +6042,17 @@
       </c>
       <c r="B193" t="inlineStr">
         <is>
-          <t>4-Week Bill Auction</t>
+          <t>8-Week Bill Auction</t>
         </is>
       </c>
       <c r="C193" t="inlineStr">
         <is>
+          <t>4.235%</t>
+        </is>
+      </c>
+      <c r="D193" t="inlineStr">
+        <is>
           <t>4.240%</t>
-        </is>
-      </c>
-      <c r="D193" t="inlineStr">
-        <is>
-          <t>4.245%</t>
         </is>
       </c>
       <c r="E193" t="inlineStr"/>
@@ -6503,17 +6503,17 @@
       </c>
       <c r="B208" t="inlineStr">
         <is>
-          <t>Foreign Bond InvestmentNOV</t>
+          <t>Overall Net Capital FlowsNOV</t>
         </is>
       </c>
       <c r="C208" t="inlineStr">
         <is>
-          <t>$-15.8B</t>
+          <t>$159.9B</t>
         </is>
       </c>
       <c r="D208" t="inlineStr">
         <is>
-          <t>$92B</t>
+          <t>$201.8B</t>
         </is>
       </c>
       <c r="E208" t="inlineStr"/>
@@ -6530,27 +6530,23 @@
       </c>
       <c r="B209" t="inlineStr">
         <is>
-          <t>Net Long-term TIC FlowsNOV</t>
+          <t>Foreign Bond InvestmentNOV</t>
         </is>
       </c>
       <c r="C209" t="inlineStr">
         <is>
-          <t>$79B</t>
+          <t>$-15.8B</t>
         </is>
       </c>
       <c r="D209" t="inlineStr">
         <is>
-          <t>$159.1B</t>
-        </is>
-      </c>
-      <c r="E209" t="inlineStr">
-        <is>
-          <t>$159.9B</t>
-        </is>
-      </c>
+          <t>$92B</t>
+        </is>
+      </c>
+      <c r="E209" t="inlineStr"/>
       <c r="F209" t="inlineStr"/>
       <c r="G209" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="210">
@@ -6561,23 +6557,27 @@
       </c>
       <c r="B210" t="inlineStr">
         <is>
-          <t>Overall Net Capital FlowsNOV</t>
+          <t>Net Long-term TIC FlowsNOV</t>
         </is>
       </c>
       <c r="C210" t="inlineStr">
         <is>
+          <t>$79B</t>
+        </is>
+      </c>
+      <c r="D210" t="inlineStr">
+        <is>
+          <t>$159.1B</t>
+        </is>
+      </c>
+      <c r="E210" t="inlineStr">
+        <is>
           <t>$159.9B</t>
         </is>
       </c>
-      <c r="D210" t="inlineStr">
-        <is>
-          <t>$201.8B</t>
-        </is>
-      </c>
-      <c r="E210" t="inlineStr"/>
       <c r="F210" t="inlineStr"/>
       <c r="G210" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="211">
@@ -7241,27 +7241,23 @@
       </c>
       <c r="B234" t="inlineStr">
         <is>
-          <t>EIA Crude Oil Stocks ChangeJAN/17</t>
+          <t>EIA Gasoline Production ChangeJAN/17</t>
         </is>
       </c>
       <c r="C234" t="inlineStr">
         <is>
-          <t>-1.017M</t>
+          <t>-0.043M</t>
         </is>
       </c>
       <c r="D234" t="inlineStr">
         <is>
-          <t>-1.962M</t>
-        </is>
-      </c>
-      <c r="E234" t="inlineStr">
-        <is>
-          <t>-2.1M</t>
-        </is>
-      </c>
+          <t>0.397M</t>
+        </is>
+      </c>
+      <c r="E234" t="inlineStr"/>
       <c r="F234" t="inlineStr"/>
       <c r="G234" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="235">
@@ -7272,17 +7268,17 @@
       </c>
       <c r="B235" t="inlineStr">
         <is>
-          <t>15-Year Mortgage RateJAN/23</t>
+          <t>EIA Cushing Crude Oil Stocks ChangeJAN/17</t>
         </is>
       </c>
       <c r="C235" t="inlineStr">
         <is>
-          <t>6.16%</t>
+          <t>-0.148M</t>
         </is>
       </c>
       <c r="D235" t="inlineStr">
         <is>
-          <t>6.27%</t>
+          <t>0.765M</t>
         </is>
       </c>
       <c r="E235" t="inlineStr"/>
@@ -7299,27 +7295,23 @@
       </c>
       <c r="B236" t="inlineStr">
         <is>
-          <t>EIA Gasoline Stocks ChangeJAN/17</t>
+          <t>30-Year Mortgage RateJAN/23</t>
         </is>
       </c>
       <c r="C236" t="inlineStr">
         <is>
-          <t>2.332M</t>
+          <t>6.96%</t>
         </is>
       </c>
       <c r="D236" t="inlineStr">
         <is>
-          <t>5.852M</t>
-        </is>
-      </c>
-      <c r="E236" t="inlineStr">
-        <is>
-          <t>2.5M</t>
-        </is>
-      </c>
+          <t>7.04%</t>
+        </is>
+      </c>
+      <c r="E236" t="inlineStr"/>
       <c r="F236" t="inlineStr"/>
       <c r="G236" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="237">
@@ -7330,17 +7322,17 @@
       </c>
       <c r="B237" t="inlineStr">
         <is>
-          <t>EIA Refinery Crude Runs ChangeJAN/17</t>
+          <t>EIA Distillate Fuel Production ChangeJAN/17</t>
         </is>
       </c>
       <c r="C237" t="inlineStr">
         <is>
-          <t>-1.125M</t>
+          <t>-0.473M</t>
         </is>
       </c>
       <c r="D237" t="inlineStr">
         <is>
-          <t>-0.255M</t>
+          <t>-0.021M</t>
         </is>
       </c>
       <c r="E237" t="inlineStr"/>
@@ -7357,20 +7349,24 @@
       </c>
       <c r="B238" t="inlineStr">
         <is>
-          <t>EIA Crude Oil Imports ChangeJAN/17</t>
+          <t>EIA Distillate Stocks ChangeJAN/17</t>
         </is>
       </c>
       <c r="C238" t="inlineStr">
         <is>
-          <t>0.184M</t>
+          <t>-3.07M</t>
         </is>
       </c>
       <c r="D238" t="inlineStr">
         <is>
-          <t>-1.304M</t>
-        </is>
-      </c>
-      <c r="E238" t="inlineStr"/>
+          <t>3.077M</t>
+        </is>
+      </c>
+      <c r="E238" t="inlineStr">
+        <is>
+          <t>0.6M</t>
+        </is>
+      </c>
       <c r="F238" t="inlineStr"/>
       <c r="G238" t="n">
         <v>3</v>
@@ -7384,17 +7380,17 @@
       </c>
       <c r="B239" t="inlineStr">
         <is>
-          <t>EIA Heating Oil Stocks ChangeJAN/17</t>
+          <t>EIA Crude Oil Imports ChangeJAN/17</t>
         </is>
       </c>
       <c r="C239" t="inlineStr">
         <is>
-          <t>0.068M</t>
+          <t>0.184M</t>
         </is>
       </c>
       <c r="D239" t="inlineStr">
         <is>
-          <t>0.646M</t>
+          <t>-1.304M</t>
         </is>
       </c>
       <c r="E239" t="inlineStr"/>
@@ -7411,24 +7407,20 @@
       </c>
       <c r="B240" t="inlineStr">
         <is>
-          <t>EIA Distillate Stocks ChangeJAN/17</t>
+          <t>EIA Refinery Crude Runs ChangeJAN/17</t>
         </is>
       </c>
       <c r="C240" t="inlineStr">
         <is>
-          <t>-3.07M</t>
+          <t>-1.125M</t>
         </is>
       </c>
       <c r="D240" t="inlineStr">
         <is>
-          <t>3.077M</t>
-        </is>
-      </c>
-      <c r="E240" t="inlineStr">
-        <is>
-          <t>0.6M</t>
-        </is>
-      </c>
+          <t>-0.255M</t>
+        </is>
+      </c>
+      <c r="E240" t="inlineStr"/>
       <c r="F240" t="inlineStr"/>
       <c r="G240" t="n">
         <v>3</v>
@@ -7442,23 +7434,27 @@
       </c>
       <c r="B241" t="inlineStr">
         <is>
-          <t>EIA Distillate Fuel Production ChangeJAN/17</t>
+          <t>EIA Gasoline Stocks ChangeJAN/17</t>
         </is>
       </c>
       <c r="C241" t="inlineStr">
         <is>
-          <t>-0.473M</t>
+          <t>2.332M</t>
         </is>
       </c>
       <c r="D241" t="inlineStr">
         <is>
-          <t>-0.021M</t>
-        </is>
-      </c>
-      <c r="E241" t="inlineStr"/>
+          <t>5.852M</t>
+        </is>
+      </c>
+      <c r="E241" t="inlineStr">
+        <is>
+          <t>2.5M</t>
+        </is>
+      </c>
       <c r="F241" t="inlineStr"/>
       <c r="G241" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="242">
@@ -7469,17 +7465,17 @@
       </c>
       <c r="B242" t="inlineStr">
         <is>
-          <t>30-Year Mortgage RateJAN/23</t>
+          <t>15-Year Mortgage RateJAN/23</t>
         </is>
       </c>
       <c r="C242" t="inlineStr">
         <is>
-          <t>6.96%</t>
+          <t>6.16%</t>
         </is>
       </c>
       <c r="D242" t="inlineStr">
         <is>
-          <t>7.04%</t>
+          <t>6.27%</t>
         </is>
       </c>
       <c r="E242" t="inlineStr"/>
@@ -7496,23 +7492,27 @@
       </c>
       <c r="B243" t="inlineStr">
         <is>
-          <t>EIA Cushing Crude Oil Stocks ChangeJAN/17</t>
+          <t>EIA Crude Oil Stocks ChangeJAN/17</t>
         </is>
       </c>
       <c r="C243" t="inlineStr">
         <is>
-          <t>-0.148M</t>
+          <t>-1.017M</t>
         </is>
       </c>
       <c r="D243" t="inlineStr">
         <is>
-          <t>0.765M</t>
-        </is>
-      </c>
-      <c r="E243" t="inlineStr"/>
+          <t>-1.962M</t>
+        </is>
+      </c>
+      <c r="E243" t="inlineStr">
+        <is>
+          <t>-2.1M</t>
+        </is>
+      </c>
       <c r="F243" t="inlineStr"/>
       <c r="G243" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="244">
@@ -7523,17 +7523,17 @@
       </c>
       <c r="B244" t="inlineStr">
         <is>
-          <t>EIA Gasoline Production ChangeJAN/17</t>
+          <t>EIA Heating Oil Stocks ChangeJAN/17</t>
         </is>
       </c>
       <c r="C244" t="inlineStr">
         <is>
-          <t>-0.043M</t>
+          <t>0.068M</t>
         </is>
       </c>
       <c r="D244" t="inlineStr">
         <is>
-          <t>0.397M</t>
+          <t>0.646M</t>
         </is>
       </c>
       <c r="E244" t="inlineStr"/>
@@ -7705,31 +7705,27 @@
       </c>
       <c r="B250" t="inlineStr">
         <is>
-          <t>Michigan Current Conditions FinalJAN</t>
+          <t>Existing Home Sales MoMDEC</t>
         </is>
       </c>
       <c r="C250" t="inlineStr">
         <is>
-          <t>74.0</t>
+          <t>2.2%</t>
         </is>
       </c>
       <c r="D250" t="inlineStr">
         <is>
-          <t>75.1</t>
-        </is>
-      </c>
-      <c r="E250" t="inlineStr">
-        <is>
-          <t>77.9</t>
-        </is>
-      </c>
+          <t>4.8%</t>
+        </is>
+      </c>
+      <c r="E250" t="inlineStr"/>
       <c r="F250" t="inlineStr">
         <is>
-          <t>77.9</t>
+          <t>0.3%</t>
         </is>
       </c>
       <c r="G250" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="251">
@@ -7740,31 +7736,31 @@
       </c>
       <c r="B251" t="inlineStr">
         <is>
-          <t>Existing Home SalesDEC</t>
+          <t>Michigan Inflation Expectations FinalJAN</t>
         </is>
       </c>
       <c r="C251" t="inlineStr">
         <is>
-          <t>4.24M</t>
+          <t>3.3%</t>
         </is>
       </c>
       <c r="D251" t="inlineStr">
         <is>
-          <t>4.15M</t>
+          <t>2.8%</t>
         </is>
       </c>
       <c r="E251" t="inlineStr">
         <is>
-          <t>4.19M</t>
+          <t>3.3%</t>
         </is>
       </c>
       <c r="F251" t="inlineStr">
         <is>
-          <t>4.1M</t>
+          <t>3.3%</t>
         </is>
       </c>
       <c r="G251" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="252">
@@ -7775,27 +7771,27 @@
       </c>
       <c r="B252" t="inlineStr">
         <is>
-          <t>Michigan Consumer Expectations FinalJAN</t>
+          <t>Michigan 5 Year Inflation Expectations FinalJAN</t>
         </is>
       </c>
       <c r="C252" t="inlineStr">
         <is>
-          <t>69.3</t>
+          <t>3.2%</t>
         </is>
       </c>
       <c r="D252" t="inlineStr">
         <is>
-          <t>73.3</t>
+          <t>3%</t>
         </is>
       </c>
       <c r="E252" t="inlineStr">
         <is>
-          <t>70.2</t>
+          <t>3.3%</t>
         </is>
       </c>
       <c r="F252" t="inlineStr">
         <is>
-          <t>70.2</t>
+          <t>3.3%</t>
         </is>
       </c>
       <c r="G252" t="n">
@@ -7810,31 +7806,31 @@
       </c>
       <c r="B253" t="inlineStr">
         <is>
-          <t>Michigan Consumer Sentiment FinalJAN</t>
+          <t>Michigan Current Conditions FinalJAN</t>
         </is>
       </c>
       <c r="C253" t="inlineStr">
         <is>
-          <t>71.1</t>
+          <t>74.0</t>
         </is>
       </c>
       <c r="D253" t="inlineStr">
         <is>
-          <t>74.0</t>
+          <t>75.1</t>
         </is>
       </c>
       <c r="E253" t="inlineStr">
         <is>
-          <t>73.2</t>
+          <t>77.9</t>
         </is>
       </c>
       <c r="F253" t="inlineStr">
         <is>
-          <t>73.2</t>
+          <t>77.9</t>
         </is>
       </c>
       <c r="G253" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="254">
@@ -7845,27 +7841,27 @@
       </c>
       <c r="B254" t="inlineStr">
         <is>
-          <t>Michigan 5 Year Inflation Expectations FinalJAN</t>
+          <t>Michigan Consumer Expectations FinalJAN</t>
         </is>
       </c>
       <c r="C254" t="inlineStr">
         <is>
-          <t>3.2%</t>
+          <t>69.3</t>
         </is>
       </c>
       <c r="D254" t="inlineStr">
         <is>
-          <t>3%</t>
+          <t>73.3</t>
         </is>
       </c>
       <c r="E254" t="inlineStr">
         <is>
-          <t>3.3%</t>
+          <t>70.2</t>
         </is>
       </c>
       <c r="F254" t="inlineStr">
         <is>
-          <t>3.3%</t>
+          <t>70.2</t>
         </is>
       </c>
       <c r="G254" t="n">
@@ -7880,27 +7876,31 @@
       </c>
       <c r="B255" t="inlineStr">
         <is>
-          <t>Existing Home Sales MoMDEC</t>
+          <t>Existing Home SalesDEC</t>
         </is>
       </c>
       <c r="C255" t="inlineStr">
         <is>
-          <t>2.2%</t>
+          <t>4.24M</t>
         </is>
       </c>
       <c r="D255" t="inlineStr">
         <is>
-          <t>4.8%</t>
-        </is>
-      </c>
-      <c r="E255" t="inlineStr"/>
+          <t>4.15M</t>
+        </is>
+      </c>
+      <c r="E255" t="inlineStr">
+        <is>
+          <t>4.19M</t>
+        </is>
+      </c>
       <c r="F255" t="inlineStr">
         <is>
-          <t>0.3%</t>
+          <t>4.1M</t>
         </is>
       </c>
       <c r="G255" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="256">
@@ -7911,31 +7911,31 @@
       </c>
       <c r="B256" t="inlineStr">
         <is>
-          <t>Michigan Inflation Expectations FinalJAN</t>
+          <t>Michigan Consumer Sentiment FinalJAN</t>
         </is>
       </c>
       <c r="C256" t="inlineStr">
         <is>
-          <t>3.3%</t>
+          <t>71.1</t>
         </is>
       </c>
       <c r="D256" t="inlineStr">
         <is>
-          <t>2.8%</t>
+          <t>74.0</t>
         </is>
       </c>
       <c r="E256" t="inlineStr">
         <is>
-          <t>3.3%</t>
+          <t>73.2</t>
         </is>
       </c>
       <c r="F256" t="inlineStr">
         <is>
-          <t>3.3%</t>
+          <t>73.2</t>
         </is>
       </c>
       <c r="G256" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="257">
@@ -8469,23 +8469,27 @@
       </c>
       <c r="B274" t="inlineStr">
         <is>
-          <t>S&amp;P/Case-Shiller Home Price MoMNOV</t>
+          <t>House Price Index MoMNOV</t>
         </is>
       </c>
       <c r="C274" t="inlineStr">
         <is>
-          <t>-0.1%</t>
+          <t>0.3%</t>
         </is>
       </c>
       <c r="D274" t="inlineStr">
         <is>
-          <t>-0.2%</t>
-        </is>
-      </c>
-      <c r="E274" t="inlineStr"/>
+          <t>0.5%</t>
+        </is>
+      </c>
+      <c r="E274" t="inlineStr">
+        <is>
+          <t>0.2%</t>
+        </is>
+      </c>
       <c r="F274" t="inlineStr">
         <is>
-          <t>-0.1%</t>
+          <t>0.3%</t>
         </is>
       </c>
       <c r="G274" t="n">
@@ -8500,23 +8504,23 @@
       </c>
       <c r="B275" t="inlineStr">
         <is>
-          <t>House Price IndexNOV</t>
+          <t>House Price Index YoYNOV</t>
         </is>
       </c>
       <c r="C275" t="inlineStr">
         <is>
-          <t>433.4</t>
+          <t>4.2%</t>
         </is>
       </c>
       <c r="D275" t="inlineStr">
         <is>
-          <t>432.3</t>
+          <t>4.5%</t>
         </is>
       </c>
       <c r="E275" t="inlineStr"/>
       <c r="F275" t="inlineStr">
         <is>
-          <t>433</t>
+          <t>4.3%</t>
         </is>
       </c>
       <c r="G275" t="n">
@@ -8531,27 +8535,31 @@
       </c>
       <c r="B276" t="inlineStr">
         <is>
-          <t>House Price Index YoYNOV</t>
+          <t>S&amp;P/Case-Shiller Home Price YoYNOV</t>
         </is>
       </c>
       <c r="C276" t="inlineStr">
         <is>
+          <t>4.3%</t>
+        </is>
+      </c>
+      <c r="D276" t="inlineStr">
+        <is>
           <t>4.2%</t>
         </is>
       </c>
-      <c r="D276" t="inlineStr">
-        <is>
-          <t>4.5%</t>
-        </is>
-      </c>
-      <c r="E276" t="inlineStr"/>
+      <c r="E276" t="inlineStr">
+        <is>
+          <t>4.3%</t>
+        </is>
+      </c>
       <c r="F276" t="inlineStr">
         <is>
-          <t>4.3%</t>
+          <t>4%</t>
         </is>
       </c>
       <c r="G276" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="277">
@@ -8562,31 +8570,27 @@
       </c>
       <c r="B277" t="inlineStr">
         <is>
-          <t>S&amp;P/Case-Shiller Home Price YoYNOV</t>
+          <t>House Price IndexNOV</t>
         </is>
       </c>
       <c r="C277" t="inlineStr">
         <is>
-          <t>4.3%</t>
+          <t>433.4</t>
         </is>
       </c>
       <c r="D277" t="inlineStr">
         <is>
-          <t>4.2%</t>
-        </is>
-      </c>
-      <c r="E277" t="inlineStr">
-        <is>
-          <t>4.3%</t>
-        </is>
-      </c>
+          <t>432.3</t>
+        </is>
+      </c>
+      <c r="E277" t="inlineStr"/>
       <c r="F277" t="inlineStr">
         <is>
-          <t>4%</t>
+          <t>433</t>
         </is>
       </c>
       <c r="G277" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="278">
@@ -8597,27 +8601,23 @@
       </c>
       <c r="B278" t="inlineStr">
         <is>
-          <t>House Price Index MoMNOV</t>
+          <t>S&amp;P/Case-Shiller Home Price MoMNOV</t>
         </is>
       </c>
       <c r="C278" t="inlineStr">
         <is>
-          <t>0.3%</t>
+          <t>-0.1%</t>
         </is>
       </c>
       <c r="D278" t="inlineStr">
         <is>
-          <t>0.5%</t>
-        </is>
-      </c>
-      <c r="E278" t="inlineStr">
-        <is>
-          <t>0.2%</t>
-        </is>
-      </c>
+          <t>-0.2%</t>
+        </is>
+      </c>
+      <c r="E278" t="inlineStr"/>
       <c r="F278" t="inlineStr">
         <is>
-          <t>0.3%</t>
+          <t>-0.1%</t>
         </is>
       </c>
       <c r="G278" t="n">
@@ -9201,17 +9201,17 @@
       </c>
       <c r="B298" t="inlineStr">
         <is>
-          <t>EIA Cushing Crude Oil Stocks ChangeJAN/24</t>
+          <t>EIA Gasoline Production ChangeJAN/24</t>
         </is>
       </c>
       <c r="C298" t="inlineStr">
         <is>
-          <t>0.326M</t>
+          <t>-0.044M</t>
         </is>
       </c>
       <c r="D298" t="inlineStr">
         <is>
-          <t>-0.148M</t>
+          <t>-0.043M</t>
         </is>
       </c>
       <c r="E298" t="inlineStr"/>
@@ -9228,27 +9228,23 @@
       </c>
       <c r="B299" t="inlineStr">
         <is>
-          <t>EIA Crude Oil Stocks ChangeJAN/24</t>
+          <t>EIA Crude Oil Imports ChangeJAN/24</t>
         </is>
       </c>
       <c r="C299" t="inlineStr">
         <is>
-          <t>3.463M</t>
+          <t>0.532M</t>
         </is>
       </c>
       <c r="D299" t="inlineStr">
         <is>
-          <t>-1.017M</t>
-        </is>
-      </c>
-      <c r="E299" t="inlineStr">
-        <is>
-          <t>3.2M</t>
-        </is>
-      </c>
+          <t>0.184M</t>
+        </is>
+      </c>
+      <c r="E299" t="inlineStr"/>
       <c r="F299" t="inlineStr"/>
       <c r="G299" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="300">
@@ -9259,24 +9255,20 @@
       </c>
       <c r="B300" t="inlineStr">
         <is>
-          <t>EIA Distillate Stocks ChangeJAN/24</t>
+          <t>EIA Distillate Fuel Production ChangeJAN/24</t>
         </is>
       </c>
       <c r="C300" t="inlineStr">
         <is>
-          <t>-4.994M</t>
+          <t>0.028M</t>
         </is>
       </c>
       <c r="D300" t="inlineStr">
         <is>
-          <t>-3.07M</t>
-        </is>
-      </c>
-      <c r="E300" t="inlineStr">
-        <is>
-          <t>-2.1M</t>
-        </is>
-      </c>
+          <t>-0.473M</t>
+        </is>
+      </c>
+      <c r="E300" t="inlineStr"/>
       <c r="F300" t="inlineStr"/>
       <c r="G300" t="n">
         <v>3</v>
@@ -9290,23 +9282,27 @@
       </c>
       <c r="B301" t="inlineStr">
         <is>
-          <t>EIA Heating Oil Stocks ChangeJAN/24</t>
+          <t>EIA Gasoline Stocks ChangeJAN/24</t>
         </is>
       </c>
       <c r="C301" t="inlineStr">
         <is>
-          <t>0.128M</t>
+          <t>2.957M</t>
         </is>
       </c>
       <c r="D301" t="inlineStr">
         <is>
-          <t>0.068M</t>
-        </is>
-      </c>
-      <c r="E301" t="inlineStr"/>
+          <t>2.332M</t>
+        </is>
+      </c>
+      <c r="E301" t="inlineStr">
+        <is>
+          <t>1.5M</t>
+        </is>
+      </c>
       <c r="F301" t="inlineStr"/>
       <c r="G301" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="302">
@@ -9344,27 +9340,23 @@
       </c>
       <c r="B303" t="inlineStr">
         <is>
-          <t>EIA Gasoline Stocks ChangeJAN/24</t>
+          <t>EIA Heating Oil Stocks ChangeJAN/24</t>
         </is>
       </c>
       <c r="C303" t="inlineStr">
         <is>
-          <t>2.957M</t>
+          <t>0.128M</t>
         </is>
       </c>
       <c r="D303" t="inlineStr">
         <is>
-          <t>2.332M</t>
-        </is>
-      </c>
-      <c r="E303" t="inlineStr">
-        <is>
-          <t>1.5M</t>
-        </is>
-      </c>
+          <t>0.068M</t>
+        </is>
+      </c>
+      <c r="E303" t="inlineStr"/>
       <c r="F303" t="inlineStr"/>
       <c r="G303" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="304">
@@ -9375,20 +9367,24 @@
       </c>
       <c r="B304" t="inlineStr">
         <is>
-          <t>EIA Distillate Fuel Production ChangeJAN/24</t>
+          <t>EIA Distillate Stocks ChangeJAN/24</t>
         </is>
       </c>
       <c r="C304" t="inlineStr">
         <is>
-          <t>0.028M</t>
+          <t>-4.994M</t>
         </is>
       </c>
       <c r="D304" t="inlineStr">
         <is>
-          <t>-0.473M</t>
-        </is>
-      </c>
-      <c r="E304" t="inlineStr"/>
+          <t>-3.07M</t>
+        </is>
+      </c>
+      <c r="E304" t="inlineStr">
+        <is>
+          <t>-2.1M</t>
+        </is>
+      </c>
       <c r="F304" t="inlineStr"/>
       <c r="G304" t="n">
         <v>3</v>
@@ -9402,23 +9398,27 @@
       </c>
       <c r="B305" t="inlineStr">
         <is>
-          <t>EIA Crude Oil Imports ChangeJAN/24</t>
+          <t>EIA Crude Oil Stocks ChangeJAN/24</t>
         </is>
       </c>
       <c r="C305" t="inlineStr">
         <is>
-          <t>0.532M</t>
+          <t>3.463M</t>
         </is>
       </c>
       <c r="D305" t="inlineStr">
         <is>
-          <t>0.184M</t>
-        </is>
-      </c>
-      <c r="E305" t="inlineStr"/>
+          <t>-1.017M</t>
+        </is>
+      </c>
+      <c r="E305" t="inlineStr">
+        <is>
+          <t>3.2M</t>
+        </is>
+      </c>
       <c r="F305" t="inlineStr"/>
       <c r="G305" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="306">
@@ -9429,17 +9429,17 @@
       </c>
       <c r="B306" t="inlineStr">
         <is>
-          <t>EIA Gasoline Production ChangeJAN/24</t>
+          <t>EIA Cushing Crude Oil Stocks ChangeJAN/24</t>
         </is>
       </c>
       <c r="C306" t="inlineStr">
         <is>
-          <t>-0.044M</t>
+          <t>0.326M</t>
         </is>
       </c>
       <c r="D306" t="inlineStr">
         <is>
-          <t>-0.043M</t>
+          <t>-0.148M</t>
         </is>
       </c>
       <c r="E306" t="inlineStr"/>
@@ -9537,23 +9537,27 @@
       </c>
       <c r="B310" t="inlineStr">
         <is>
-          <t>Jobless Claims 4-week AverageJAN/25</t>
+          <t>Core PCE Prices QoQ AdvQ4</t>
         </is>
       </c>
       <c r="C310" t="inlineStr">
         <is>
-          <t>212.5K</t>
+          <t>2.5%</t>
         </is>
       </c>
       <c r="D310" t="inlineStr">
         <is>
-          <t>213.5K</t>
-        </is>
-      </c>
-      <c r="E310" t="inlineStr"/>
+          <t>2.2%</t>
+        </is>
+      </c>
+      <c r="E310" t="inlineStr">
+        <is>
+          <t>2.5%</t>
+        </is>
+      </c>
       <c r="F310" t="inlineStr">
         <is>
-          <t>214.0K</t>
+          <t>2.3%</t>
         </is>
       </c>
       <c r="G310" t="n">
@@ -9568,27 +9572,23 @@
       </c>
       <c r="B311" t="inlineStr">
         <is>
-          <t>Continuing Jobless ClaimsJAN/18</t>
+          <t>PCE Prices QoQ AdvQ4</t>
         </is>
       </c>
       <c r="C311" t="inlineStr">
         <is>
-          <t>1858K</t>
+          <t>2.3%</t>
         </is>
       </c>
       <c r="D311" t="inlineStr">
         <is>
-          <t>1900K</t>
-        </is>
-      </c>
-      <c r="E311" t="inlineStr">
-        <is>
-          <t>1890K</t>
-        </is>
-      </c>
+          <t>1.5%</t>
+        </is>
+      </c>
+      <c r="E311" t="inlineStr"/>
       <c r="F311" t="inlineStr">
         <is>
-          <t>1885.0K</t>
+          <t>1.1%</t>
         </is>
       </c>
       <c r="G311" t="n">
@@ -9603,31 +9603,27 @@
       </c>
       <c r="B312" t="inlineStr">
         <is>
-          <t>GDP Growth Rate QoQ AdvQ4</t>
+          <t>Real Consumer Spending QoQ AdvQ4</t>
         </is>
       </c>
       <c r="C312" t="inlineStr">
         <is>
-          <t>2.3%</t>
+          <t>4.2%</t>
         </is>
       </c>
       <c r="D312" t="inlineStr">
         <is>
-          <t>3.1%</t>
-        </is>
-      </c>
-      <c r="E312" t="inlineStr">
-        <is>
-          <t>2.6%</t>
-        </is>
-      </c>
+          <t>3.7%</t>
+        </is>
+      </c>
+      <c r="E312" t="inlineStr"/>
       <c r="F312" t="inlineStr">
         <is>
-          <t>3%</t>
+          <t>2.9%</t>
         </is>
       </c>
       <c r="G312" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="313">
@@ -9638,27 +9634,31 @@
       </c>
       <c r="B313" t="inlineStr">
         <is>
-          <t>GDP Sales QoQ AdvQ4</t>
+          <t>GDP Price Index QoQ AdvQ4</t>
         </is>
       </c>
       <c r="C313" t="inlineStr">
         <is>
-          <t>3.2%</t>
+          <t>2.2%</t>
         </is>
       </c>
       <c r="D313" t="inlineStr">
         <is>
-          <t>3.3%</t>
-        </is>
-      </c>
-      <c r="E313" t="inlineStr"/>
+          <t>1.9%</t>
+        </is>
+      </c>
+      <c r="E313" t="inlineStr">
+        <is>
+          <t>2.5%</t>
+        </is>
+      </c>
       <c r="F313" t="inlineStr">
         <is>
-          <t>2.9%</t>
+          <t>2.3%</t>
         </is>
       </c>
       <c r="G313" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="314">
@@ -9669,27 +9669,27 @@
       </c>
       <c r="B314" t="inlineStr">
         <is>
-          <t>GDP Price Index QoQ AdvQ4</t>
+          <t>Initial Jobless ClaimsJAN/25</t>
         </is>
       </c>
       <c r="C314" t="inlineStr">
         <is>
-          <t>2.2%</t>
+          <t>207K</t>
         </is>
       </c>
       <c r="D314" t="inlineStr">
         <is>
-          <t>1.9%</t>
+          <t>223K</t>
         </is>
       </c>
       <c r="E314" t="inlineStr">
         <is>
-          <t>2.5%</t>
+          <t>220K</t>
         </is>
       </c>
       <c r="F314" t="inlineStr">
         <is>
-          <t>2.3%</t>
+          <t>228.0K</t>
         </is>
       </c>
       <c r="G314" t="n">
@@ -9704,31 +9704,31 @@
       </c>
       <c r="B315" t="inlineStr">
         <is>
-          <t>Initial Jobless ClaimsJAN/25</t>
+          <t>GDP Growth Rate QoQ AdvQ4</t>
         </is>
       </c>
       <c r="C315" t="inlineStr">
         <is>
-          <t>207K</t>
+          <t>2.3%</t>
         </is>
       </c>
       <c r="D315" t="inlineStr">
         <is>
-          <t>223K</t>
+          <t>3.1%</t>
         </is>
       </c>
       <c r="E315" t="inlineStr">
         <is>
-          <t>220K</t>
+          <t>2.6%</t>
         </is>
       </c>
       <c r="F315" t="inlineStr">
         <is>
-          <t>228.0K</t>
+          <t>3%</t>
         </is>
       </c>
       <c r="G315" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="316">
@@ -9739,23 +9739,27 @@
       </c>
       <c r="B316" t="inlineStr">
         <is>
-          <t>Real Consumer Spending QoQ AdvQ4</t>
+          <t>Continuing Jobless ClaimsJAN/18</t>
         </is>
       </c>
       <c r="C316" t="inlineStr">
         <is>
-          <t>4.2%</t>
+          <t>1858K</t>
         </is>
       </c>
       <c r="D316" t="inlineStr">
         <is>
-          <t>3.7%</t>
-        </is>
-      </c>
-      <c r="E316" t="inlineStr"/>
+          <t>1900K</t>
+        </is>
+      </c>
+      <c r="E316" t="inlineStr">
+        <is>
+          <t>1890K</t>
+        </is>
+      </c>
       <c r="F316" t="inlineStr">
         <is>
-          <t>2.9%</t>
+          <t>1885.0K</t>
         </is>
       </c>
       <c r="G316" t="n">
@@ -9770,23 +9774,23 @@
       </c>
       <c r="B317" t="inlineStr">
         <is>
-          <t>PCE Prices QoQ AdvQ4</t>
+          <t>Jobless Claims 4-week AverageJAN/25</t>
         </is>
       </c>
       <c r="C317" t="inlineStr">
         <is>
-          <t>2.3%</t>
+          <t>212.5K</t>
         </is>
       </c>
       <c r="D317" t="inlineStr">
         <is>
-          <t>1.5%</t>
+          <t>213.5K</t>
         </is>
       </c>
       <c r="E317" t="inlineStr"/>
       <c r="F317" t="inlineStr">
         <is>
-          <t>1.1%</t>
+          <t>214.0K</t>
         </is>
       </c>
       <c r="G317" t="n">
@@ -9801,27 +9805,23 @@
       </c>
       <c r="B318" t="inlineStr">
         <is>
-          <t>Core PCE Prices QoQ AdvQ4</t>
+          <t>GDP Sales QoQ AdvQ4</t>
         </is>
       </c>
       <c r="C318" t="inlineStr">
         <is>
-          <t>2.5%</t>
+          <t>3.2%</t>
         </is>
       </c>
       <c r="D318" t="inlineStr">
         <is>
-          <t>2.2%</t>
-        </is>
-      </c>
-      <c r="E318" t="inlineStr">
-        <is>
-          <t>2.5%</t>
-        </is>
-      </c>
+          <t>3.3%</t>
+        </is>
+      </c>
+      <c r="E318" t="inlineStr"/>
       <c r="F318" t="inlineStr">
         <is>
-          <t>2.3%</t>
+          <t>2.9%</t>
         </is>
       </c>
       <c r="G318" t="n">
@@ -10068,12 +10068,12 @@
       </c>
       <c r="B327" t="inlineStr">
         <is>
-          <t>Employment Cost Index QoQQ4</t>
+          <t>Employment Cost - Benefits QoQQ4</t>
         </is>
       </c>
       <c r="C327" t="inlineStr">
         <is>
-          <t>0.9%</t>
+          <t>0.8%</t>
         </is>
       </c>
       <c r="D327" t="inlineStr">
@@ -10081,11 +10081,7 @@
           <t>0.8%</t>
         </is>
       </c>
-      <c r="E327" t="inlineStr">
-        <is>
-          <t>0.9%</t>
-        </is>
-      </c>
+      <c r="E327" t="inlineStr"/>
       <c r="F327" t="inlineStr">
         <is>
           <t>0.7%</t>
@@ -10103,12 +10099,12 @@
       </c>
       <c r="B328" t="inlineStr">
         <is>
-          <t>PCE Price Index MoMDEC</t>
+          <t>Core PCE Price Index MoMDEC</t>
         </is>
       </c>
       <c r="C328" t="inlineStr">
         <is>
-          <t>0.3%</t>
+          <t>0.2%</t>
         </is>
       </c>
       <c r="D328" t="inlineStr">
@@ -10118,16 +10114,16 @@
       </c>
       <c r="E328" t="inlineStr">
         <is>
-          <t>0.3%</t>
+          <t>0.2%</t>
         </is>
       </c>
       <c r="F328" t="inlineStr">
         <is>
-          <t>0.3%</t>
+          <t>0.2%</t>
         </is>
       </c>
       <c r="G328" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="329">
@@ -10138,31 +10134,31 @@
       </c>
       <c r="B329" t="inlineStr">
         <is>
-          <t>Core PCE Price Index YoYDEC</t>
+          <t>Personal Spending MoMDEC</t>
         </is>
       </c>
       <c r="C329" t="inlineStr">
         <is>
-          <t>2.8%</t>
+          <t>0.7%</t>
         </is>
       </c>
       <c r="D329" t="inlineStr">
         <is>
-          <t>2.8%</t>
+          <t>0.6%</t>
         </is>
       </c>
       <c r="E329" t="inlineStr">
         <is>
-          <t>2.8%</t>
+          <t>0.5%</t>
         </is>
       </c>
       <c r="F329" t="inlineStr">
         <is>
-          <t>2.8%</t>
+          <t>0.5%</t>
         </is>
       </c>
       <c r="G329" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="330">
@@ -10173,29 +10169,13 @@
       </c>
       <c r="B330" t="inlineStr">
         <is>
-          <t>PCE Price Index YoYDEC</t>
-        </is>
-      </c>
-      <c r="C330" t="inlineStr">
-        <is>
-          <t>2.6%</t>
-        </is>
-      </c>
-      <c r="D330" t="inlineStr">
-        <is>
-          <t>2.4%</t>
-        </is>
-      </c>
-      <c r="E330" t="inlineStr">
-        <is>
-          <t>2.6%</t>
-        </is>
-      </c>
-      <c r="F330" t="inlineStr">
-        <is>
-          <t>2.6%</t>
-        </is>
-      </c>
+          <t>Fed Bowman Speech</t>
+        </is>
+      </c>
+      <c r="C330" t="inlineStr"/>
+      <c r="D330" t="inlineStr"/>
+      <c r="E330" t="inlineStr"/>
+      <c r="F330" t="inlineStr"/>
       <c r="G330" t="n">
         <v>2</v>
       </c>
@@ -10208,27 +10188,31 @@
       </c>
       <c r="B331" t="inlineStr">
         <is>
-          <t>Employment Cost - Wages QoQQ4</t>
+          <t>Personal Income MoMDEC</t>
         </is>
       </c>
       <c r="C331" t="inlineStr">
         <is>
-          <t>0.9%</t>
+          <t>0.4%</t>
         </is>
       </c>
       <c r="D331" t="inlineStr">
         <is>
-          <t>0.8%</t>
-        </is>
-      </c>
-      <c r="E331" t="inlineStr"/>
+          <t>0.3%</t>
+        </is>
+      </c>
+      <c r="E331" t="inlineStr">
+        <is>
+          <t>0.4%</t>
+        </is>
+      </c>
       <c r="F331" t="inlineStr">
         <is>
-          <t>0.7%</t>
+          <t>0.3%</t>
         </is>
       </c>
       <c r="G331" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="332">
@@ -10239,13 +10223,29 @@
       </c>
       <c r="B332" t="inlineStr">
         <is>
-          <t>Fed Bowman Speech</t>
-        </is>
-      </c>
-      <c r="C332" t="inlineStr"/>
-      <c r="D332" t="inlineStr"/>
-      <c r="E332" t="inlineStr"/>
-      <c r="F332" t="inlineStr"/>
+          <t>PCE Price Index YoYDEC</t>
+        </is>
+      </c>
+      <c r="C332" t="inlineStr">
+        <is>
+          <t>2.6%</t>
+        </is>
+      </c>
+      <c r="D332" t="inlineStr">
+        <is>
+          <t>2.4%</t>
+        </is>
+      </c>
+      <c r="E332" t="inlineStr">
+        <is>
+          <t>2.6%</t>
+        </is>
+      </c>
+      <c r="F332" t="inlineStr">
+        <is>
+          <t>2.6%</t>
+        </is>
+      </c>
       <c r="G332" t="n">
         <v>2</v>
       </c>
@@ -10258,31 +10258,31 @@
       </c>
       <c r="B333" t="inlineStr">
         <is>
-          <t>Core PCE Price Index MoMDEC</t>
+          <t>Core PCE Price Index YoYDEC</t>
         </is>
       </c>
       <c r="C333" t="inlineStr">
         <is>
-          <t>0.2%</t>
+          <t>2.8%</t>
         </is>
       </c>
       <c r="D333" t="inlineStr">
         <is>
-          <t>0.1%</t>
+          <t>2.8%</t>
         </is>
       </c>
       <c r="E333" t="inlineStr">
         <is>
-          <t>0.2%</t>
+          <t>2.8%</t>
         </is>
       </c>
       <c r="F333" t="inlineStr">
         <is>
-          <t>0.2%</t>
+          <t>2.8%</t>
         </is>
       </c>
       <c r="G333" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="334">
@@ -10293,23 +10293,27 @@
       </c>
       <c r="B334" t="inlineStr">
         <is>
-          <t>Employment Cost - Benefits QoQQ4</t>
+          <t>PCE Price Index MoMDEC</t>
         </is>
       </c>
       <c r="C334" t="inlineStr">
         <is>
-          <t>0.8%</t>
+          <t>0.3%</t>
         </is>
       </c>
       <c r="D334" t="inlineStr">
         <is>
-          <t>0.8%</t>
-        </is>
-      </c>
-      <c r="E334" t="inlineStr"/>
+          <t>0.1%</t>
+        </is>
+      </c>
+      <c r="E334" t="inlineStr">
+        <is>
+          <t>0.3%</t>
+        </is>
+      </c>
       <c r="F334" t="inlineStr">
         <is>
-          <t>0.7%</t>
+          <t>0.3%</t>
         </is>
       </c>
       <c r="G334" t="n">
@@ -10324,31 +10328,31 @@
       </c>
       <c r="B335" t="inlineStr">
         <is>
-          <t>Personal Spending MoMDEC</t>
+          <t>Employment Cost Index QoQQ4</t>
         </is>
       </c>
       <c r="C335" t="inlineStr">
         <is>
+          <t>0.9%</t>
+        </is>
+      </c>
+      <c r="D335" t="inlineStr">
+        <is>
+          <t>0.8%</t>
+        </is>
+      </c>
+      <c r="E335" t="inlineStr">
+        <is>
+          <t>0.9%</t>
+        </is>
+      </c>
+      <c r="F335" t="inlineStr">
+        <is>
           <t>0.7%</t>
         </is>
       </c>
-      <c r="D335" t="inlineStr">
-        <is>
-          <t>0.6%</t>
-        </is>
-      </c>
-      <c r="E335" t="inlineStr">
-        <is>
-          <t>0.5%</t>
-        </is>
-      </c>
-      <c r="F335" t="inlineStr">
-        <is>
-          <t>0.5%</t>
-        </is>
-      </c>
       <c r="G335" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="336">
@@ -10359,31 +10363,27 @@
       </c>
       <c r="B336" t="inlineStr">
         <is>
-          <t>Personal Income MoMDEC</t>
+          <t>Employment Cost - Wages QoQQ4</t>
         </is>
       </c>
       <c r="C336" t="inlineStr">
         <is>
-          <t>0.4%</t>
+          <t>0.9%</t>
         </is>
       </c>
       <c r="D336" t="inlineStr">
         <is>
-          <t>0.3%</t>
-        </is>
-      </c>
-      <c r="E336" t="inlineStr">
-        <is>
-          <t>0.4%</t>
-        </is>
-      </c>
+          <t>0.8%</t>
+        </is>
+      </c>
+      <c r="E336" t="inlineStr"/>
       <c r="F336" t="inlineStr">
         <is>
-          <t>0.3%</t>
+          <t>0.7%</t>
         </is>
       </c>
       <c r="G336" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="337">
@@ -10522,31 +10522,31 @@
       </c>
       <c r="B341" t="inlineStr">
         <is>
-          <t>Construction Spending MoMDEC</t>
+          <t>ISM Manufacturing PMIJAN</t>
         </is>
       </c>
       <c r="C341" t="inlineStr">
         <is>
-          <t>0.5%</t>
+          <t>50.9</t>
         </is>
       </c>
       <c r="D341" t="inlineStr">
         <is>
-          <t>0.2%</t>
+          <t>49.2</t>
         </is>
       </c>
       <c r="E341" t="inlineStr">
         <is>
-          <t>0.2%</t>
+          <t>49.8</t>
         </is>
       </c>
       <c r="F341" t="inlineStr">
         <is>
-          <t>0.3%</t>
+          <t>49.8</t>
         </is>
       </c>
       <c r="G341" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="342">
@@ -10557,23 +10557,27 @@
       </c>
       <c r="B342" t="inlineStr">
         <is>
-          <t>ISM Manufacturing New OrdersJAN</t>
+          <t>ISM Manufacturing PricesJAN</t>
         </is>
       </c>
       <c r="C342" t="inlineStr">
         <is>
-          <t>55.1</t>
+          <t>54.9</t>
         </is>
       </c>
       <c r="D342" t="inlineStr">
         <is>
-          <t>52.1</t>
-        </is>
-      </c>
-      <c r="E342" t="inlineStr"/>
+          <t>52.5</t>
+        </is>
+      </c>
+      <c r="E342" t="inlineStr">
+        <is>
+          <t>52.6</t>
+        </is>
+      </c>
       <c r="F342" t="inlineStr">
         <is>
-          <t>52.8</t>
+          <t>53</t>
         </is>
       </c>
       <c r="G342" t="n">
@@ -10588,31 +10592,27 @@
       </c>
       <c r="B343" t="inlineStr">
         <is>
-          <t>ISM Manufacturing PricesJAN</t>
+          <t>ISM Manufacturing EmploymentJAN</t>
         </is>
       </c>
       <c r="C343" t="inlineStr">
         <is>
-          <t>54.9</t>
+          <t>50.3</t>
         </is>
       </c>
       <c r="D343" t="inlineStr">
         <is>
-          <t>52.5</t>
-        </is>
-      </c>
-      <c r="E343" t="inlineStr">
-        <is>
-          <t>52.6</t>
-        </is>
-      </c>
+          <t>45.4</t>
+        </is>
+      </c>
+      <c r="E343" t="inlineStr"/>
       <c r="F343" t="inlineStr">
         <is>
-          <t>53</t>
+          <t>47</t>
         </is>
       </c>
       <c r="G343" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="344">
@@ -10623,27 +10623,31 @@
       </c>
       <c r="B344" t="inlineStr">
         <is>
-          <t>ISM Manufacturing EmploymentJAN</t>
+          <t>Construction Spending MoMDEC</t>
         </is>
       </c>
       <c r="C344" t="inlineStr">
         <is>
-          <t>50.3</t>
+          <t>0.5%</t>
         </is>
       </c>
       <c r="D344" t="inlineStr">
         <is>
-          <t>45.4</t>
-        </is>
-      </c>
-      <c r="E344" t="inlineStr"/>
+          <t>0.2%</t>
+        </is>
+      </c>
+      <c r="E344" t="inlineStr">
+        <is>
+          <t>0.2%</t>
+        </is>
+      </c>
       <c r="F344" t="inlineStr">
         <is>
-          <t>47</t>
+          <t>0.3%</t>
         </is>
       </c>
       <c r="G344" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="345">
@@ -10654,31 +10658,27 @@
       </c>
       <c r="B345" t="inlineStr">
         <is>
-          <t>ISM Manufacturing PMIJAN</t>
+          <t>ISM Manufacturing New OrdersJAN</t>
         </is>
       </c>
       <c r="C345" t="inlineStr">
         <is>
-          <t>50.9</t>
+          <t>55.1</t>
         </is>
       </c>
       <c r="D345" t="inlineStr">
         <is>
-          <t>49.2</t>
-        </is>
-      </c>
-      <c r="E345" t="inlineStr">
-        <is>
-          <t>49.8</t>
-        </is>
-      </c>
+          <t>52.1</t>
+        </is>
+      </c>
+      <c r="E345" t="inlineStr"/>
       <c r="F345" t="inlineStr">
         <is>
-          <t>49.8</t>
+          <t>52.8</t>
         </is>
       </c>
       <c r="G345" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="346">
@@ -10873,27 +10873,31 @@
       </c>
       <c r="B354" t="inlineStr">
         <is>
-          <t>JOLTs Job QuitsDEC</t>
+          <t>Factory Orders MoMDEC</t>
         </is>
       </c>
       <c r="C354" t="inlineStr">
         <is>
-          <t>3.197M</t>
+          <t>-0.9%</t>
         </is>
       </c>
       <c r="D354" t="inlineStr">
         <is>
-          <t>3.130M</t>
-        </is>
-      </c>
-      <c r="E354" t="inlineStr"/>
+          <t>-0.8%</t>
+        </is>
+      </c>
+      <c r="E354" t="inlineStr">
+        <is>
+          <t>-0.7%</t>
+        </is>
+      </c>
       <c r="F354" t="inlineStr">
         <is>
-          <t>3.1M</t>
+          <t>-0.7%</t>
         </is>
       </c>
       <c r="G354" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="355">
@@ -10904,31 +10908,27 @@
       </c>
       <c r="B355" t="inlineStr">
         <is>
-          <t>JOLTs Job OpeningsDEC</t>
+          <t>JOLTs Job QuitsDEC</t>
         </is>
       </c>
       <c r="C355" t="inlineStr">
         <is>
-          <t>7.6M</t>
+          <t>3.197M</t>
         </is>
       </c>
       <c r="D355" t="inlineStr">
         <is>
-          <t>8.156M</t>
-        </is>
-      </c>
-      <c r="E355" t="inlineStr">
-        <is>
-          <t>8M</t>
-        </is>
-      </c>
+          <t>3.130M</t>
+        </is>
+      </c>
+      <c r="E355" t="inlineStr"/>
       <c r="F355" t="inlineStr">
         <is>
-          <t>7.8M</t>
+          <t>3.1M</t>
         </is>
       </c>
       <c r="G355" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="356">
@@ -10939,31 +10939,31 @@
       </c>
       <c r="B356" t="inlineStr">
         <is>
-          <t>Factory Orders MoMDEC</t>
+          <t>JOLTs Job OpeningsDEC</t>
         </is>
       </c>
       <c r="C356" t="inlineStr">
         <is>
-          <t>-0.9%</t>
+          <t>7.6M</t>
         </is>
       </c>
       <c r="D356" t="inlineStr">
         <is>
-          <t>-0.8%</t>
+          <t>8.156M</t>
         </is>
       </c>
       <c r="E356" t="inlineStr">
         <is>
-          <t>-0.7%</t>
+          <t>8M</t>
         </is>
       </c>
       <c r="F356" t="inlineStr">
         <is>
-          <t>-0.7%</t>
+          <t>7.8M</t>
         </is>
       </c>
       <c r="G356" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="357">
@@ -11325,27 +11325,23 @@
       </c>
       <c r="B370" t="inlineStr">
         <is>
-          <t>Balance of TradeDEC</t>
+          <t>ExportsDEC</t>
         </is>
       </c>
       <c r="C370" t="inlineStr">
         <is>
-          <t>$-98.4B</t>
+          <t>$266.5B</t>
         </is>
       </c>
       <c r="D370" t="inlineStr">
         <is>
-          <t>$-78.9B</t>
-        </is>
-      </c>
-      <c r="E370" t="inlineStr">
-        <is>
-          <t>$-96.6B</t>
-        </is>
-      </c>
+          <t>$273.6B</t>
+        </is>
+      </c>
+      <c r="E370" t="inlineStr"/>
       <c r="F370" t="inlineStr">
         <is>
-          <t>$ -93.0B</t>
+          <t>$ 262B</t>
         </is>
       </c>
       <c r="G370" t="n">
@@ -11360,15 +11356,27 @@
       </c>
       <c r="B371" t="inlineStr">
         <is>
-          <t>Treasury Refunding Announcement</t>
-        </is>
-      </c>
-      <c r="C371" t="inlineStr"/>
-      <c r="D371" t="inlineStr"/>
+          <t>ImportsDEC</t>
+        </is>
+      </c>
+      <c r="C371" t="inlineStr">
+        <is>
+          <t>$364.9B</t>
+        </is>
+      </c>
+      <c r="D371" t="inlineStr">
+        <is>
+          <t>$352.5B</t>
+        </is>
+      </c>
       <c r="E371" t="inlineStr"/>
-      <c r="F371" t="inlineStr"/>
+      <c r="F371" t="inlineStr">
+        <is>
+          <t>$ 355.0B</t>
+        </is>
+      </c>
       <c r="G371" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="372">
@@ -11379,23 +11387,27 @@
       </c>
       <c r="B372" t="inlineStr">
         <is>
-          <t>ImportsDEC</t>
+          <t>Balance of TradeDEC</t>
         </is>
       </c>
       <c r="C372" t="inlineStr">
         <is>
-          <t>$364.9B</t>
+          <t>$-98.4B</t>
         </is>
       </c>
       <c r="D372" t="inlineStr">
         <is>
-          <t>$352.5B</t>
-        </is>
-      </c>
-      <c r="E372" t="inlineStr"/>
+          <t>$-78.9B</t>
+        </is>
+      </c>
+      <c r="E372" t="inlineStr">
+        <is>
+          <t>$-96.6B</t>
+        </is>
+      </c>
       <c r="F372" t="inlineStr">
         <is>
-          <t>$ 355.0B</t>
+          <t>$ -93.0B</t>
         </is>
       </c>
       <c r="G372" t="n">
@@ -11410,27 +11422,15 @@
       </c>
       <c r="B373" t="inlineStr">
         <is>
-          <t>ExportsDEC</t>
-        </is>
-      </c>
-      <c r="C373" t="inlineStr">
-        <is>
-          <t>$266.5B</t>
-        </is>
-      </c>
-      <c r="D373" t="inlineStr">
-        <is>
-          <t>$273.6B</t>
-        </is>
-      </c>
+          <t>Treasury Refunding Announcement</t>
+        </is>
+      </c>
+      <c r="C373" t="inlineStr"/>
+      <c r="D373" t="inlineStr"/>
       <c r="E373" t="inlineStr"/>
-      <c r="F373" t="inlineStr">
-        <is>
-          <t>$ 262B</t>
-        </is>
-      </c>
+      <c r="F373" t="inlineStr"/>
       <c r="G373" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="374">
@@ -11689,23 +11689,27 @@
       </c>
       <c r="B382" t="inlineStr">
         <is>
-          <t>EIA Heating Oil Stocks ChangeJAN/31</t>
+          <t>EIA Gasoline Stocks ChangeJAN/31</t>
         </is>
       </c>
       <c r="C382" t="inlineStr">
         <is>
-          <t>0.373M</t>
+          <t>2.233M</t>
         </is>
       </c>
       <c r="D382" t="inlineStr">
         <is>
-          <t>0.128M</t>
-        </is>
-      </c>
-      <c r="E382" t="inlineStr"/>
+          <t>2.957M</t>
+        </is>
+      </c>
+      <c r="E382" t="inlineStr">
+        <is>
+          <t>1.2M</t>
+        </is>
+      </c>
       <c r="F382" t="inlineStr"/>
       <c r="G382" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="383">
@@ -11716,17 +11720,17 @@
       </c>
       <c r="B383" t="inlineStr">
         <is>
-          <t>EIA Refinery Crude Runs ChangeJAN/31</t>
+          <t>EIA Crude Oil Imports ChangeJAN/31</t>
         </is>
       </c>
       <c r="C383" t="inlineStr">
         <is>
-          <t>0.16M</t>
+          <t>-0.178M</t>
         </is>
       </c>
       <c r="D383" t="inlineStr">
         <is>
-          <t>-0.333M</t>
+          <t>0.532M</t>
         </is>
       </c>
       <c r="E383" t="inlineStr"/>
@@ -11743,27 +11747,23 @@
       </c>
       <c r="B384" t="inlineStr">
         <is>
-          <t>EIA Crude Oil Stocks ChangeJAN/31</t>
+          <t>EIA Cushing Crude Oil Stocks ChangeJAN/31</t>
         </is>
       </c>
       <c r="C384" t="inlineStr">
         <is>
-          <t>8.664M</t>
+          <t>-0.034M</t>
         </is>
       </c>
       <c r="D384" t="inlineStr">
         <is>
-          <t>3.463M</t>
-        </is>
-      </c>
-      <c r="E384" t="inlineStr">
-        <is>
-          <t>2.6M</t>
-        </is>
-      </c>
+          <t>0.326M</t>
+        </is>
+      </c>
+      <c r="E384" t="inlineStr"/>
       <c r="F384" t="inlineStr"/>
       <c r="G384" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="385">
@@ -11774,17 +11774,17 @@
       </c>
       <c r="B385" t="inlineStr">
         <is>
-          <t>EIA Distillate Fuel Production ChangeJAN/31</t>
+          <t>EIA Gasoline Production ChangeJAN/31</t>
         </is>
       </c>
       <c r="C385" t="inlineStr">
         <is>
-          <t>-0.186M</t>
+          <t>-0.027M</t>
         </is>
       </c>
       <c r="D385" t="inlineStr">
         <is>
-          <t>0.028M</t>
+          <t>-0.044M</t>
         </is>
       </c>
       <c r="E385" t="inlineStr"/>
@@ -11801,20 +11801,24 @@
       </c>
       <c r="B386" t="inlineStr">
         <is>
-          <t>EIA Gasoline Production ChangeJAN/31</t>
+          <t>EIA Distillate Stocks ChangeJAN/31</t>
         </is>
       </c>
       <c r="C386" t="inlineStr">
         <is>
-          <t>-0.027M</t>
+          <t>-5.471M</t>
         </is>
       </c>
       <c r="D386" t="inlineStr">
         <is>
-          <t>-0.044M</t>
-        </is>
-      </c>
-      <c r="E386" t="inlineStr"/>
+          <t>-4.994M</t>
+        </is>
+      </c>
+      <c r="E386" t="inlineStr">
+        <is>
+          <t>-1.5M</t>
+        </is>
+      </c>
       <c r="F386" t="inlineStr"/>
       <c r="G386" t="n">
         <v>3</v>
@@ -11828,22 +11832,22 @@
       </c>
       <c r="B387" t="inlineStr">
         <is>
-          <t>EIA Gasoline Stocks ChangeJAN/31</t>
+          <t>EIA Crude Oil Stocks ChangeJAN/31</t>
         </is>
       </c>
       <c r="C387" t="inlineStr">
         <is>
-          <t>2.233M</t>
+          <t>8.664M</t>
         </is>
       </c>
       <c r="D387" t="inlineStr">
         <is>
-          <t>2.957M</t>
+          <t>3.463M</t>
         </is>
       </c>
       <c r="E387" t="inlineStr">
         <is>
-          <t>1.2M</t>
+          <t>2.6M</t>
         </is>
       </c>
       <c r="F387" t="inlineStr"/>
@@ -11859,17 +11863,17 @@
       </c>
       <c r="B388" t="inlineStr">
         <is>
-          <t>EIA Cushing Crude Oil Stocks ChangeJAN/31</t>
+          <t>EIA Refinery Crude Runs ChangeJAN/31</t>
         </is>
       </c>
       <c r="C388" t="inlineStr">
         <is>
-          <t>-0.034M</t>
+          <t>0.16M</t>
         </is>
       </c>
       <c r="D388" t="inlineStr">
         <is>
-          <t>0.326M</t>
+          <t>-0.333M</t>
         </is>
       </c>
       <c r="E388" t="inlineStr"/>
@@ -11886,24 +11890,20 @@
       </c>
       <c r="B389" t="inlineStr">
         <is>
-          <t>EIA Distillate Stocks ChangeJAN/31</t>
+          <t>EIA Heating Oil Stocks ChangeJAN/31</t>
         </is>
       </c>
       <c r="C389" t="inlineStr">
         <is>
-          <t>-5.471M</t>
+          <t>0.373M</t>
         </is>
       </c>
       <c r="D389" t="inlineStr">
         <is>
-          <t>-4.994M</t>
-        </is>
-      </c>
-      <c r="E389" t="inlineStr">
-        <is>
-          <t>-1.5M</t>
-        </is>
-      </c>
+          <t>0.128M</t>
+        </is>
+      </c>
+      <c r="E389" t="inlineStr"/>
       <c r="F389" t="inlineStr"/>
       <c r="G389" t="n">
         <v>3</v>
@@ -11917,17 +11917,17 @@
       </c>
       <c r="B390" t="inlineStr">
         <is>
-          <t>EIA Crude Oil Imports ChangeJAN/31</t>
+          <t>EIA Distillate Fuel Production ChangeJAN/31</t>
         </is>
       </c>
       <c r="C390" t="inlineStr">
         <is>
-          <t>-0.178M</t>
+          <t>-0.186M</t>
         </is>
       </c>
       <c r="D390" t="inlineStr">
         <is>
-          <t>0.532M</t>
+          <t>0.028M</t>
         </is>
       </c>
       <c r="E390" t="inlineStr"/>
@@ -12040,31 +12040,31 @@
       </c>
       <c r="B395" t="inlineStr">
         <is>
-          <t>Continuing Jobless ClaimsJAN/25</t>
+          <t>Unit Labour Costs QoQ PrelQ4</t>
         </is>
       </c>
       <c r="C395" t="inlineStr">
         <is>
-          <t>1886K</t>
+          <t>3%</t>
         </is>
       </c>
       <c r="D395" t="inlineStr">
         <is>
-          <t>1850K</t>
+          <t>0.5%</t>
         </is>
       </c>
       <c r="E395" t="inlineStr">
         <is>
-          <t>1870K</t>
+          <t>3.4%</t>
         </is>
       </c>
       <c r="F395" t="inlineStr">
         <is>
-          <t>1855.0K</t>
+          <t>3%</t>
         </is>
       </c>
       <c r="G395" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="396">
@@ -12075,27 +12075,31 @@
       </c>
       <c r="B396" t="inlineStr">
         <is>
-          <t>Jobless Claims 4-week AverageFEB/01</t>
+          <t>Initial Jobless ClaimsFEB/01</t>
         </is>
       </c>
       <c r="C396" t="inlineStr">
         <is>
-          <t>216.75K</t>
+          <t>219K</t>
         </is>
       </c>
       <c r="D396" t="inlineStr">
         <is>
-          <t>212.75K</t>
-        </is>
-      </c>
-      <c r="E396" t="inlineStr"/>
+          <t>208K</t>
+        </is>
+      </c>
+      <c r="E396" t="inlineStr">
+        <is>
+          <t>213K</t>
+        </is>
+      </c>
       <c r="F396" t="inlineStr">
         <is>
-          <t>215.5K</t>
+          <t>215.0K</t>
         </is>
       </c>
       <c r="G396" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="397">
@@ -12106,27 +12110,27 @@
       </c>
       <c r="B397" t="inlineStr">
         <is>
-          <t>Initial Jobless ClaimsFEB/01</t>
+          <t>Nonfarm Productivity QoQ PrelQ4</t>
         </is>
       </c>
       <c r="C397" t="inlineStr">
         <is>
-          <t>219K</t>
+          <t>1.2%</t>
         </is>
       </c>
       <c r="D397" t="inlineStr">
         <is>
-          <t>208K</t>
+          <t>2.3%</t>
         </is>
       </c>
       <c r="E397" t="inlineStr">
         <is>
-          <t>213K</t>
+          <t>1.4%</t>
         </is>
       </c>
       <c r="F397" t="inlineStr">
         <is>
-          <t>215.0K</t>
+          <t>1.9%</t>
         </is>
       </c>
       <c r="G397" t="n">
@@ -12141,31 +12145,31 @@
       </c>
       <c r="B398" t="inlineStr">
         <is>
-          <t>Unit Labour Costs QoQ PrelQ4</t>
+          <t>Continuing Jobless ClaimsJAN/25</t>
         </is>
       </c>
       <c r="C398" t="inlineStr">
         <is>
-          <t>3%</t>
+          <t>1886K</t>
         </is>
       </c>
       <c r="D398" t="inlineStr">
         <is>
-          <t>0.5%</t>
+          <t>1850K</t>
         </is>
       </c>
       <c r="E398" t="inlineStr">
         <is>
-          <t>3.4%</t>
+          <t>1870K</t>
         </is>
       </c>
       <c r="F398" t="inlineStr">
         <is>
-          <t>3%</t>
+          <t>1855.0K</t>
         </is>
       </c>
       <c r="G398" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="399">
@@ -12176,31 +12180,27 @@
       </c>
       <c r="B399" t="inlineStr">
         <is>
-          <t>Nonfarm Productivity QoQ PrelQ4</t>
+          <t>Jobless Claims 4-week AverageFEB/01</t>
         </is>
       </c>
       <c r="C399" t="inlineStr">
         <is>
-          <t>1.2%</t>
+          <t>216.75K</t>
         </is>
       </c>
       <c r="D399" t="inlineStr">
         <is>
-          <t>2.3%</t>
-        </is>
-      </c>
-      <c r="E399" t="inlineStr">
-        <is>
-          <t>1.4%</t>
-        </is>
-      </c>
+          <t>212.75K</t>
+        </is>
+      </c>
+      <c r="E399" t="inlineStr"/>
       <c r="F399" t="inlineStr">
         <is>
-          <t>1.9%</t>
+          <t>215.5K</t>
         </is>
       </c>
       <c r="G399" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="400">
@@ -12442,27 +12442,31 @@
       </c>
       <c r="B409" t="inlineStr">
         <is>
-          <t>Participation RateJAN</t>
+          <t>Average Weekly HoursJAN</t>
         </is>
       </c>
       <c r="C409" t="inlineStr">
         <is>
-          <t>62.6%</t>
+          <t>34.1</t>
         </is>
       </c>
       <c r="D409" t="inlineStr">
         <is>
-          <t>62.5%</t>
-        </is>
-      </c>
-      <c r="E409" t="inlineStr"/>
+          <t>34.2</t>
+        </is>
+      </c>
+      <c r="E409" t="inlineStr">
+        <is>
+          <t>34.3</t>
+        </is>
+      </c>
       <c r="F409" t="inlineStr">
         <is>
-          <t>62.5%</t>
+          <t>34.3</t>
         </is>
       </c>
       <c r="G409" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="410">
@@ -12473,31 +12477,31 @@
       </c>
       <c r="B410" t="inlineStr">
         <is>
-          <t>Nonfarm Payrolls PrivateJAN</t>
+          <t>Non Farm PayrollsJAN</t>
         </is>
       </c>
       <c r="C410" t="inlineStr">
         <is>
-          <t>111K</t>
+          <t>143K</t>
         </is>
       </c>
       <c r="D410" t="inlineStr">
         <is>
-          <t>273K</t>
+          <t>307K</t>
         </is>
       </c>
       <c r="E410" t="inlineStr">
         <is>
-          <t>141K</t>
+          <t>170K</t>
         </is>
       </c>
       <c r="F410" t="inlineStr">
         <is>
-          <t>180K</t>
+          <t>205K</t>
         </is>
       </c>
       <c r="G410" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="411">
@@ -12508,27 +12512,31 @@
       </c>
       <c r="B411" t="inlineStr">
         <is>
-          <t>U-6 Unemployment RateJAN</t>
+          <t>Average Hourly Earnings YoYJAN</t>
         </is>
       </c>
       <c r="C411" t="inlineStr">
         <is>
-          <t>7.5%</t>
+          <t>4.1%</t>
         </is>
       </c>
       <c r="D411" t="inlineStr">
         <is>
-          <t>7.5%</t>
-        </is>
-      </c>
-      <c r="E411" t="inlineStr"/>
+          <t>4.1%</t>
+        </is>
+      </c>
+      <c r="E411" t="inlineStr">
+        <is>
+          <t>3.8%</t>
+        </is>
+      </c>
       <c r="F411" t="inlineStr">
         <is>
-          <t>7.5%</t>
+          <t>3.9%</t>
         </is>
       </c>
       <c r="G411" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="412">
@@ -12539,31 +12547,31 @@
       </c>
       <c r="B412" t="inlineStr">
         <is>
-          <t>Manufacturing PayrollsJAN</t>
+          <t>Unemployment RateJAN</t>
         </is>
       </c>
       <c r="C412" t="inlineStr">
         <is>
-          <t>3K</t>
+          <t>4%</t>
         </is>
       </c>
       <c r="D412" t="inlineStr">
         <is>
-          <t>-12K</t>
+          <t>4.1%</t>
         </is>
       </c>
       <c r="E412" t="inlineStr">
         <is>
-          <t>-2K</t>
+          <t>4.1%</t>
         </is>
       </c>
       <c r="F412" t="inlineStr">
         <is>
-          <t>-5K</t>
+          <t>4.1%</t>
         </is>
       </c>
       <c r="G412" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="413">
@@ -12574,27 +12582,31 @@
       </c>
       <c r="B413" t="inlineStr">
         <is>
-          <t>Government PayrollsJAN</t>
+          <t>Average Hourly Earnings MoMJAN</t>
         </is>
       </c>
       <c r="C413" t="inlineStr">
         <is>
-          <t>32K</t>
+          <t>0.5%</t>
         </is>
       </c>
       <c r="D413" t="inlineStr">
         <is>
-          <t>34K</t>
-        </is>
-      </c>
-      <c r="E413" t="inlineStr"/>
+          <t>0.3%</t>
+        </is>
+      </c>
+      <c r="E413" t="inlineStr">
+        <is>
+          <t>0.3%</t>
+        </is>
+      </c>
       <c r="F413" t="inlineStr">
         <is>
-          <t>25K</t>
+          <t>0.3%</t>
         </is>
       </c>
       <c r="G413" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="414">
@@ -12605,31 +12617,31 @@
       </c>
       <c r="B414" t="inlineStr">
         <is>
-          <t>Unemployment RateJAN</t>
+          <t>Manufacturing PayrollsJAN</t>
         </is>
       </c>
       <c r="C414" t="inlineStr">
         <is>
-          <t>4%</t>
+          <t>3K</t>
         </is>
       </c>
       <c r="D414" t="inlineStr">
         <is>
-          <t>4.1%</t>
+          <t>-12K</t>
         </is>
       </c>
       <c r="E414" t="inlineStr">
         <is>
-          <t>4.1%</t>
+          <t>-2K</t>
         </is>
       </c>
       <c r="F414" t="inlineStr">
         <is>
-          <t>4.1%</t>
+          <t>-5K</t>
         </is>
       </c>
       <c r="G414" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="415">
@@ -12640,27 +12652,23 @@
       </c>
       <c r="B415" t="inlineStr">
         <is>
-          <t>Average Weekly HoursJAN</t>
+          <t>U-6 Unemployment RateJAN</t>
         </is>
       </c>
       <c r="C415" t="inlineStr">
         <is>
-          <t>34.1</t>
+          <t>7.5%</t>
         </is>
       </c>
       <c r="D415" t="inlineStr">
         <is>
-          <t>34.2</t>
-        </is>
-      </c>
-      <c r="E415" t="inlineStr">
-        <is>
-          <t>34.3</t>
-        </is>
-      </c>
+          <t>7.5%</t>
+        </is>
+      </c>
+      <c r="E415" t="inlineStr"/>
       <c r="F415" t="inlineStr">
         <is>
-          <t>34.3</t>
+          <t>7.5%</t>
         </is>
       </c>
       <c r="G415" t="n">
@@ -12675,31 +12683,31 @@
       </c>
       <c r="B416" t="inlineStr">
         <is>
-          <t>Average Hourly Earnings YoYJAN</t>
+          <t>Nonfarm Payrolls PrivateJAN</t>
         </is>
       </c>
       <c r="C416" t="inlineStr">
         <is>
-          <t>4.1%</t>
+          <t>111K</t>
         </is>
       </c>
       <c r="D416" t="inlineStr">
         <is>
-          <t>4.1%</t>
+          <t>273K</t>
         </is>
       </c>
       <c r="E416" t="inlineStr">
         <is>
-          <t>3.8%</t>
+          <t>141K</t>
         </is>
       </c>
       <c r="F416" t="inlineStr">
         <is>
-          <t>3.9%</t>
+          <t>180K</t>
         </is>
       </c>
       <c r="G416" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="417">
@@ -12710,27 +12718,23 @@
       </c>
       <c r="B417" t="inlineStr">
         <is>
-          <t>Average Hourly Earnings MoMJAN</t>
+          <t>Participation RateJAN</t>
         </is>
       </c>
       <c r="C417" t="inlineStr">
         <is>
-          <t>0.5%</t>
+          <t>62.6%</t>
         </is>
       </c>
       <c r="D417" t="inlineStr">
         <is>
-          <t>0.3%</t>
-        </is>
-      </c>
-      <c r="E417" t="inlineStr">
-        <is>
-          <t>0.3%</t>
-        </is>
-      </c>
+          <t>62.5%</t>
+        </is>
+      </c>
+      <c r="E417" t="inlineStr"/>
       <c r="F417" t="inlineStr">
         <is>
-          <t>0.3%</t>
+          <t>62.5%</t>
         </is>
       </c>
       <c r="G417" t="n">
@@ -12745,31 +12749,27 @@
       </c>
       <c r="B418" t="inlineStr">
         <is>
-          <t>Non Farm PayrollsJAN</t>
+          <t>Government PayrollsJAN</t>
         </is>
       </c>
       <c r="C418" t="inlineStr">
         <is>
-          <t>143K</t>
+          <t>32K</t>
         </is>
       </c>
       <c r="D418" t="inlineStr">
         <is>
-          <t>307K</t>
-        </is>
-      </c>
-      <c r="E418" t="inlineStr">
-        <is>
-          <t>170K</t>
-        </is>
-      </c>
+          <t>34K</t>
+        </is>
+      </c>
+      <c r="E418" t="inlineStr"/>
       <c r="F418" t="inlineStr">
         <is>
-          <t>205K</t>
+          <t>25K</t>
         </is>
       </c>
       <c r="G418" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="419">
@@ -13501,23 +13501,23 @@
       </c>
       <c r="B446" t="inlineStr">
         <is>
-          <t>MBA Mortgage ApplicationsFEB/07</t>
+          <t>MBA 30-Year Mortgage RateFEB/07</t>
         </is>
       </c>
       <c r="C446" t="inlineStr">
         <is>
-          <t>2.3%</t>
+          <t>6.95%</t>
         </is>
       </c>
       <c r="D446" t="inlineStr">
         <is>
-          <t>2.2%</t>
+          <t>6.97%</t>
         </is>
       </c>
       <c r="E446" t="inlineStr"/>
       <c r="F446" t="inlineStr"/>
       <c r="G446" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="447">
@@ -13528,17 +13528,17 @@
       </c>
       <c r="B447" t="inlineStr">
         <is>
-          <t>MBA Mortgage Market IndexFEB/07</t>
+          <t>MBA Mortgage Refinance IndexFEB/07</t>
         </is>
       </c>
       <c r="C447" t="inlineStr">
         <is>
-          <t>230.0</t>
+          <t>640.6</t>
         </is>
       </c>
       <c r="D447" t="inlineStr">
         <is>
-          <t>224.8</t>
+          <t>584.3</t>
         </is>
       </c>
       <c r="E447" t="inlineStr"/>
@@ -13555,17 +13555,17 @@
       </c>
       <c r="B448" t="inlineStr">
         <is>
-          <t>MBA Mortgage Refinance IndexFEB/07</t>
+          <t>MBA Purchase IndexFEB/07</t>
         </is>
       </c>
       <c r="C448" t="inlineStr">
         <is>
-          <t>640.6</t>
+          <t>153.1</t>
         </is>
       </c>
       <c r="D448" t="inlineStr">
         <is>
-          <t>584.3</t>
+          <t>156.7</t>
         </is>
       </c>
       <c r="E448" t="inlineStr"/>
@@ -13582,23 +13582,23 @@
       </c>
       <c r="B449" t="inlineStr">
         <is>
-          <t>MBA 30-Year Mortgage RateFEB/07</t>
+          <t>MBA Mortgage ApplicationsFEB/07</t>
         </is>
       </c>
       <c r="C449" t="inlineStr">
         <is>
-          <t>6.95%</t>
+          <t>2.3%</t>
         </is>
       </c>
       <c r="D449" t="inlineStr">
         <is>
-          <t>6.97%</t>
+          <t>2.2%</t>
         </is>
       </c>
       <c r="E449" t="inlineStr"/>
       <c r="F449" t="inlineStr"/>
       <c r="G449" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="450">
@@ -13609,17 +13609,17 @@
       </c>
       <c r="B450" t="inlineStr">
         <is>
-          <t>MBA Purchase IndexFEB/07</t>
+          <t>MBA Mortgage Market IndexFEB/07</t>
         </is>
       </c>
       <c r="C450" t="inlineStr">
         <is>
-          <t>153.1</t>
+          <t>230.0</t>
         </is>
       </c>
       <c r="D450" t="inlineStr">
         <is>
-          <t>156.7</t>
+          <t>224.8</t>
         </is>
       </c>
       <c r="E450" t="inlineStr"/>
@@ -13842,27 +13842,23 @@
       </c>
       <c r="B457" t="inlineStr">
         <is>
-          <t>EIA Crude Oil Stocks ChangeFEB/07</t>
+          <t>EIA Crude Oil Imports ChangeFEB/07</t>
         </is>
       </c>
       <c r="C457" t="inlineStr">
         <is>
-          <t>4.07M</t>
+          <t>-0.184M</t>
         </is>
       </c>
       <c r="D457" t="inlineStr">
         <is>
-          <t>8.664M</t>
-        </is>
-      </c>
-      <c r="E457" t="inlineStr">
-        <is>
-          <t>3M</t>
-        </is>
-      </c>
+          <t>-0.178M</t>
+        </is>
+      </c>
+      <c r="E457" t="inlineStr"/>
       <c r="F457" t="inlineStr"/>
       <c r="G457" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="458">
@@ -13873,17 +13869,17 @@
       </c>
       <c r="B458" t="inlineStr">
         <is>
-          <t>EIA Heating Oil Stocks ChangeFEB/07</t>
+          <t>EIA Refinery Crude Runs ChangeFEB/07</t>
         </is>
       </c>
       <c r="C458" t="inlineStr">
         <is>
-          <t>0.159M</t>
+          <t>0.082M</t>
         </is>
       </c>
       <c r="D458" t="inlineStr">
         <is>
-          <t>0.373M</t>
+          <t>0.16M</t>
         </is>
       </c>
       <c r="E458" t="inlineStr"/>
@@ -13900,17 +13896,17 @@
       </c>
       <c r="B459" t="inlineStr">
         <is>
-          <t>EIA Cushing Crude Oil Stocks ChangeFEB/07</t>
+          <t>EIA Gasoline Production ChangeFEB/07</t>
         </is>
       </c>
       <c r="C459" t="inlineStr">
         <is>
-          <t>0.872M</t>
+          <t>0.18M</t>
         </is>
       </c>
       <c r="D459" t="inlineStr">
         <is>
-          <t>-0.034M</t>
+          <t>-0.027M</t>
         </is>
       </c>
       <c r="E459" t="inlineStr"/>
@@ -13927,23 +13923,27 @@
       </c>
       <c r="B460" t="inlineStr">
         <is>
-          <t>EIA Distillate Fuel Production ChangeFEB/07</t>
+          <t>EIA Gasoline Stocks ChangeFEB/07</t>
         </is>
       </c>
       <c r="C460" t="inlineStr">
         <is>
-          <t>-0.009M</t>
+          <t>-3.035M</t>
         </is>
       </c>
       <c r="D460" t="inlineStr">
         <is>
-          <t>-0.186M</t>
-        </is>
-      </c>
-      <c r="E460" t="inlineStr"/>
+          <t>2.233M</t>
+        </is>
+      </c>
+      <c r="E460" t="inlineStr">
+        <is>
+          <t>1.5M</t>
+        </is>
+      </c>
       <c r="F460" t="inlineStr"/>
       <c r="G460" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="461">
@@ -13985,27 +13985,23 @@
       </c>
       <c r="B462" t="inlineStr">
         <is>
-          <t>EIA Gasoline Stocks ChangeFEB/07</t>
+          <t>EIA Distillate Fuel Production ChangeFEB/07</t>
         </is>
       </c>
       <c r="C462" t="inlineStr">
         <is>
-          <t>-3.035M</t>
+          <t>-0.009M</t>
         </is>
       </c>
       <c r="D462" t="inlineStr">
         <is>
-          <t>2.233M</t>
-        </is>
-      </c>
-      <c r="E462" t="inlineStr">
-        <is>
-          <t>1.5M</t>
-        </is>
-      </c>
+          <t>-0.186M</t>
+        </is>
+      </c>
+      <c r="E462" t="inlineStr"/>
       <c r="F462" t="inlineStr"/>
       <c r="G462" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="463">
@@ -14016,17 +14012,17 @@
       </c>
       <c r="B463" t="inlineStr">
         <is>
-          <t>EIA Gasoline Production ChangeFEB/07</t>
+          <t>EIA Cushing Crude Oil Stocks ChangeFEB/07</t>
         </is>
       </c>
       <c r="C463" t="inlineStr">
         <is>
-          <t>0.18M</t>
+          <t>0.872M</t>
         </is>
       </c>
       <c r="D463" t="inlineStr">
         <is>
-          <t>-0.027M</t>
+          <t>-0.034M</t>
         </is>
       </c>
       <c r="E463" t="inlineStr"/>
@@ -14043,17 +14039,17 @@
       </c>
       <c r="B464" t="inlineStr">
         <is>
-          <t>EIA Refinery Crude Runs ChangeFEB/07</t>
+          <t>EIA Heating Oil Stocks ChangeFEB/07</t>
         </is>
       </c>
       <c r="C464" t="inlineStr">
         <is>
-          <t>0.082M</t>
+          <t>0.159M</t>
         </is>
       </c>
       <c r="D464" t="inlineStr">
         <is>
-          <t>0.16M</t>
+          <t>0.373M</t>
         </is>
       </c>
       <c r="E464" t="inlineStr"/>
@@ -14070,23 +14066,27 @@
       </c>
       <c r="B465" t="inlineStr">
         <is>
-          <t>EIA Crude Oil Imports ChangeFEB/07</t>
+          <t>EIA Crude Oil Stocks ChangeFEB/07</t>
         </is>
       </c>
       <c r="C465" t="inlineStr">
         <is>
-          <t>-0.184M</t>
+          <t>4.07M</t>
         </is>
       </c>
       <c r="D465" t="inlineStr">
         <is>
-          <t>-0.178M</t>
-        </is>
-      </c>
-      <c r="E465" t="inlineStr"/>
+          <t>8.664M</t>
+        </is>
+      </c>
+      <c r="E465" t="inlineStr">
+        <is>
+          <t>3M</t>
+        </is>
+      </c>
       <c r="F465" t="inlineStr"/>
       <c r="G465" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="466">
@@ -14224,31 +14224,31 @@
       </c>
       <c r="B471" t="inlineStr">
         <is>
-          <t>Continuing Jobless ClaimsFEB/01</t>
+          <t>Initial Jobless ClaimsFEB/08</t>
         </is>
       </c>
       <c r="C471" t="inlineStr">
         <is>
-          <t>1850K</t>
+          <t>213K</t>
         </is>
       </c>
       <c r="D471" t="inlineStr">
         <is>
-          <t>1886K</t>
+          <t>220K</t>
         </is>
       </c>
       <c r="E471" t="inlineStr">
         <is>
-          <t>1880K</t>
+          <t>215K</t>
         </is>
       </c>
       <c r="F471" t="inlineStr">
         <is>
-          <t>1875.0K</t>
+          <t>215.0K</t>
         </is>
       </c>
       <c r="G471" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="472">
@@ -14259,31 +14259,27 @@
       </c>
       <c r="B472" t="inlineStr">
         <is>
-          <t>PPI MoMJAN</t>
+          <t>PPIJAN</t>
         </is>
       </c>
       <c r="C472" t="inlineStr">
         <is>
-          <t>0.4%</t>
+          <t>147.716</t>
         </is>
       </c>
       <c r="D472" t="inlineStr">
         <is>
-          <t>0.5%</t>
-        </is>
-      </c>
-      <c r="E472" t="inlineStr">
-        <is>
-          <t>0.3%</t>
-        </is>
-      </c>
+          <t>147.127</t>
+        </is>
+      </c>
+      <c r="E472" t="inlineStr"/>
       <c r="F472" t="inlineStr">
         <is>
-          <t>0.3%</t>
+          <t>147.2</t>
         </is>
       </c>
       <c r="G472" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="473">
@@ -14294,27 +14290,27 @@
       </c>
       <c r="B473" t="inlineStr">
         <is>
-          <t>PPI Ex Food, Energy and Trade YoYJAN</t>
+          <t>PPI YoYJAN</t>
         </is>
       </c>
       <c r="C473" t="inlineStr">
         <is>
+          <t>3.5%</t>
+        </is>
+      </c>
+      <c r="D473" t="inlineStr">
+        <is>
+          <t>3.5%</t>
+        </is>
+      </c>
+      <c r="E473" t="inlineStr">
+        <is>
+          <t>3.2%</t>
+        </is>
+      </c>
+      <c r="F473" t="inlineStr">
+        <is>
           <t>3.4%</t>
-        </is>
-      </c>
-      <c r="D473" t="inlineStr">
-        <is>
-          <t>3.5%</t>
-        </is>
-      </c>
-      <c r="E473" t="inlineStr">
-        <is>
-          <t>3.2%</t>
-        </is>
-      </c>
-      <c r="F473" t="inlineStr">
-        <is>
-          <t>3.3%</t>
         </is>
       </c>
       <c r="G473" t="n">
@@ -14329,23 +14325,27 @@
       </c>
       <c r="B474" t="inlineStr">
         <is>
-          <t>PPI Ex Food, Energy and Trade MoMJAN</t>
+          <t>Core PPI YoYJAN</t>
         </is>
       </c>
       <c r="C474" t="inlineStr">
         <is>
-          <t>0.3%</t>
+          <t>3.6%</t>
         </is>
       </c>
       <c r="D474" t="inlineStr">
         <is>
-          <t>0.4%</t>
-        </is>
-      </c>
-      <c r="E474" t="inlineStr"/>
+          <t>3.7%</t>
+        </is>
+      </c>
+      <c r="E474" t="inlineStr">
+        <is>
+          <t>3.3%</t>
+        </is>
+      </c>
       <c r="F474" t="inlineStr">
         <is>
-          <t>0.2%</t>
+          <t>3.5%</t>
         </is>
       </c>
       <c r="G474" t="n">
@@ -14360,27 +14360,31 @@
       </c>
       <c r="B475" t="inlineStr">
         <is>
-          <t>Jobless Claims 4-week AverageFEB/08</t>
+          <t>Core PPI MoMJAN</t>
         </is>
       </c>
       <c r="C475" t="inlineStr">
         <is>
-          <t>216K</t>
+          <t>0.3%</t>
         </is>
       </c>
       <c r="D475" t="inlineStr">
         <is>
-          <t>217K</t>
-        </is>
-      </c>
-      <c r="E475" t="inlineStr"/>
+          <t>0.4%</t>
+        </is>
+      </c>
+      <c r="E475" t="inlineStr">
+        <is>
+          <t>0.3%</t>
+        </is>
+      </c>
       <c r="F475" t="inlineStr">
         <is>
-          <t>216.0K</t>
+          <t>0.1%</t>
         </is>
       </c>
       <c r="G475" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="476">
@@ -14391,7 +14395,7 @@
       </c>
       <c r="B476" t="inlineStr">
         <is>
-          <t>Core PPI MoMJAN</t>
+          <t>PPI Ex Food, Energy and Trade MoMJAN</t>
         </is>
       </c>
       <c r="C476" t="inlineStr">
@@ -14404,18 +14408,14 @@
           <t>0.4%</t>
         </is>
       </c>
-      <c r="E476" t="inlineStr">
-        <is>
-          <t>0.3%</t>
-        </is>
-      </c>
+      <c r="E476" t="inlineStr"/>
       <c r="F476" t="inlineStr">
         <is>
-          <t>0.1%</t>
+          <t>0.2%</t>
         </is>
       </c>
       <c r="G476" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="477">
@@ -14426,27 +14426,27 @@
       </c>
       <c r="B477" t="inlineStr">
         <is>
-          <t>Core PPI YoYJAN</t>
+          <t>PPI Ex Food, Energy and Trade YoYJAN</t>
         </is>
       </c>
       <c r="C477" t="inlineStr">
         <is>
-          <t>3.6%</t>
+          <t>3.4%</t>
         </is>
       </c>
       <c r="D477" t="inlineStr">
         <is>
-          <t>3.7%</t>
+          <t>3.5%</t>
         </is>
       </c>
       <c r="E477" t="inlineStr">
         <is>
+          <t>3.2%</t>
+        </is>
+      </c>
+      <c r="F477" t="inlineStr">
+        <is>
           <t>3.3%</t>
-        </is>
-      </c>
-      <c r="F477" t="inlineStr">
-        <is>
-          <t>3.5%</t>
         </is>
       </c>
       <c r="G477" t="n">
@@ -14461,31 +14461,31 @@
       </c>
       <c r="B478" t="inlineStr">
         <is>
-          <t>PPI YoYJAN</t>
+          <t>PPI MoMJAN</t>
         </is>
       </c>
       <c r="C478" t="inlineStr">
         <is>
-          <t>3.5%</t>
+          <t>0.4%</t>
         </is>
       </c>
       <c r="D478" t="inlineStr">
         <is>
-          <t>3.5%</t>
+          <t>0.5%</t>
         </is>
       </c>
       <c r="E478" t="inlineStr">
         <is>
-          <t>3.2%</t>
+          <t>0.3%</t>
         </is>
       </c>
       <c r="F478" t="inlineStr">
         <is>
-          <t>3.4%</t>
+          <t>0.3%</t>
         </is>
       </c>
       <c r="G478" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="479">
@@ -14496,23 +14496,27 @@
       </c>
       <c r="B479" t="inlineStr">
         <is>
-          <t>PPIJAN</t>
+          <t>Continuing Jobless ClaimsFEB/01</t>
         </is>
       </c>
       <c r="C479" t="inlineStr">
         <is>
-          <t>147.716</t>
+          <t>1850K</t>
         </is>
       </c>
       <c r="D479" t="inlineStr">
         <is>
-          <t>147.127</t>
-        </is>
-      </c>
-      <c r="E479" t="inlineStr"/>
+          <t>1886K</t>
+        </is>
+      </c>
+      <c r="E479" t="inlineStr">
+        <is>
+          <t>1880K</t>
+        </is>
+      </c>
       <c r="F479" t="inlineStr">
         <is>
-          <t>147.2</t>
+          <t>1875.0K</t>
         </is>
       </c>
       <c r="G479" t="n">
@@ -14527,31 +14531,27 @@
       </c>
       <c r="B480" t="inlineStr">
         <is>
-          <t>Initial Jobless ClaimsFEB/08</t>
+          <t>Jobless Claims 4-week AverageFEB/08</t>
         </is>
       </c>
       <c r="C480" t="inlineStr">
         <is>
-          <t>213K</t>
+          <t>216K</t>
         </is>
       </c>
       <c r="D480" t="inlineStr">
         <is>
-          <t>220K</t>
-        </is>
-      </c>
-      <c r="E480" t="inlineStr">
-        <is>
-          <t>215K</t>
-        </is>
-      </c>
+          <t>217K</t>
+        </is>
+      </c>
+      <c r="E480" t="inlineStr"/>
       <c r="F480" t="inlineStr">
         <is>
-          <t>215.0K</t>
+          <t>216.0K</t>
         </is>
       </c>
       <c r="G480" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="481">
@@ -14728,27 +14728,31 @@
       </c>
       <c r="B487" t="inlineStr">
         <is>
-          <t>Import Prices YoYJAN</t>
+          <t>Import Prices MoMJAN</t>
         </is>
       </c>
       <c r="C487" t="inlineStr">
         <is>
-          <t>1.9%</t>
+          <t>0.3%</t>
         </is>
       </c>
       <c r="D487" t="inlineStr">
         <is>
-          <t>2.2%</t>
-        </is>
-      </c>
-      <c r="E487" t="inlineStr"/>
+          <t>0.2%</t>
+        </is>
+      </c>
+      <c r="E487" t="inlineStr">
+        <is>
+          <t>0.4%</t>
+        </is>
+      </c>
       <c r="F487" t="inlineStr">
         <is>
-          <t>2.8%</t>
+          <t>0.3%</t>
         </is>
       </c>
       <c r="G487" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="488">
@@ -14759,31 +14763,27 @@
       </c>
       <c r="B488" t="inlineStr">
         <is>
-          <t>Retail Sales MoMJAN</t>
+          <t>Export Prices YoYJAN</t>
         </is>
       </c>
       <c r="C488" t="inlineStr">
         <is>
-          <t>-0.9%</t>
+          <t>2.7%</t>
         </is>
       </c>
       <c r="D488" t="inlineStr">
         <is>
-          <t>0.7%</t>
-        </is>
-      </c>
-      <c r="E488" t="inlineStr">
-        <is>
-          <t>-0.1%</t>
-        </is>
-      </c>
+          <t>2%</t>
+        </is>
+      </c>
+      <c r="E488" t="inlineStr"/>
       <c r="F488" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>2.3%</t>
         </is>
       </c>
       <c r="G488" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="489">
@@ -14794,17 +14794,17 @@
       </c>
       <c r="B489" t="inlineStr">
         <is>
-          <t>Retail Sales Ex Autos MoMJAN</t>
+          <t>Retail Sales Control Group MoMJAN</t>
         </is>
       </c>
       <c r="C489" t="inlineStr">
         <is>
-          <t>-0.4%</t>
+          <t>-0.8%</t>
         </is>
       </c>
       <c r="D489" t="inlineStr">
         <is>
-          <t>0.7%</t>
+          <t>0.8%</t>
         </is>
       </c>
       <c r="E489" t="inlineStr">
@@ -14814,7 +14814,7 @@
       </c>
       <c r="F489" t="inlineStr">
         <is>
-          <t>0.3%</t>
+          <t>0.4%</t>
         </is>
       </c>
       <c r="G489" t="n">
@@ -14829,22 +14829,22 @@
       </c>
       <c r="B490" t="inlineStr">
         <is>
-          <t>Import Prices MoMJAN</t>
+          <t>Export Prices MoMJAN</t>
         </is>
       </c>
       <c r="C490" t="inlineStr">
         <is>
+          <t>1.3%</t>
+        </is>
+      </c>
+      <c r="D490" t="inlineStr">
+        <is>
+          <t>0.5%</t>
+        </is>
+      </c>
+      <c r="E490" t="inlineStr">
+        <is>
           <t>0.3%</t>
-        </is>
-      </c>
-      <c r="D490" t="inlineStr">
-        <is>
-          <t>0.2%</t>
-        </is>
-      </c>
-      <c r="E490" t="inlineStr">
-        <is>
-          <t>0.4%</t>
         </is>
       </c>
       <c r="F490" t="inlineStr">
@@ -14864,23 +14864,23 @@
       </c>
       <c r="B491" t="inlineStr">
         <is>
-          <t>Retail Sales YoYJAN</t>
+          <t>Retail Sales Ex Gas/Autos MoMJAN</t>
         </is>
       </c>
       <c r="C491" t="inlineStr">
         <is>
-          <t>4.2%</t>
+          <t>-0.5%</t>
         </is>
       </c>
       <c r="D491" t="inlineStr">
         <is>
-          <t>4.4%</t>
+          <t>0.5%</t>
         </is>
       </c>
       <c r="E491" t="inlineStr"/>
       <c r="F491" t="inlineStr">
         <is>
-          <t>3.7%</t>
+          <t>0.2%</t>
         </is>
       </c>
       <c r="G491" t="n">
@@ -14895,27 +14895,31 @@
       </c>
       <c r="B492" t="inlineStr">
         <is>
-          <t>Retail Sales Ex Gas/Autos MoMJAN</t>
+          <t>Retail Sales Ex Autos MoMJAN</t>
         </is>
       </c>
       <c r="C492" t="inlineStr">
         <is>
-          <t>-0.5%</t>
+          <t>-0.4%</t>
         </is>
       </c>
       <c r="D492" t="inlineStr">
         <is>
-          <t>0.5%</t>
-        </is>
-      </c>
-      <c r="E492" t="inlineStr"/>
+          <t>0.7%</t>
+        </is>
+      </c>
+      <c r="E492" t="inlineStr">
+        <is>
+          <t>0.3%</t>
+        </is>
+      </c>
       <c r="F492" t="inlineStr">
         <is>
-          <t>0.2%</t>
+          <t>0.3%</t>
         </is>
       </c>
       <c r="G492" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="493">
@@ -14926,31 +14930,31 @@
       </c>
       <c r="B493" t="inlineStr">
         <is>
-          <t>Export Prices MoMJAN</t>
+          <t>Retail Sales MoMJAN</t>
         </is>
       </c>
       <c r="C493" t="inlineStr">
         <is>
-          <t>1.3%</t>
+          <t>-0.9%</t>
         </is>
       </c>
       <c r="D493" t="inlineStr">
         <is>
-          <t>0.5%</t>
+          <t>0.7%</t>
         </is>
       </c>
       <c r="E493" t="inlineStr">
         <is>
-          <t>0.3%</t>
+          <t>-0.1%</t>
         </is>
       </c>
       <c r="F493" t="inlineStr">
         <is>
-          <t>0.3%</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="G493" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="494">
@@ -14961,31 +14965,27 @@
       </c>
       <c r="B494" t="inlineStr">
         <is>
-          <t>Retail Sales Control Group MoMJAN</t>
+          <t>Import Prices YoYJAN</t>
         </is>
       </c>
       <c r="C494" t="inlineStr">
         <is>
-          <t>-0.8%</t>
+          <t>1.9%</t>
         </is>
       </c>
       <c r="D494" t="inlineStr">
         <is>
-          <t>0.8%</t>
-        </is>
-      </c>
-      <c r="E494" t="inlineStr">
-        <is>
-          <t>0.3%</t>
-        </is>
-      </c>
+          <t>2.2%</t>
+        </is>
+      </c>
+      <c r="E494" t="inlineStr"/>
       <c r="F494" t="inlineStr">
         <is>
-          <t>0.4%</t>
+          <t>2.8%</t>
         </is>
       </c>
       <c r="G494" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="495">
@@ -14996,23 +14996,23 @@
       </c>
       <c r="B495" t="inlineStr">
         <is>
-          <t>Export Prices YoYJAN</t>
+          <t>Retail Sales YoYJAN</t>
         </is>
       </c>
       <c r="C495" t="inlineStr">
         <is>
-          <t>2.7%</t>
+          <t>4.2%</t>
         </is>
       </c>
       <c r="D495" t="inlineStr">
         <is>
-          <t>2%</t>
+          <t>4.4%</t>
         </is>
       </c>
       <c r="E495" t="inlineStr"/>
       <c r="F495" t="inlineStr">
         <is>
-          <t>2.3%</t>
+          <t>3.7%</t>
         </is>
       </c>
       <c r="G495" t="n">
@@ -15629,17 +15629,17 @@
       </c>
       <c r="B518" t="inlineStr">
         <is>
-          <t>Overall Net Capital FlowsDEC</t>
+          <t>Foreign Bond InvestmentDEC</t>
         </is>
       </c>
       <c r="C518" t="inlineStr">
         <is>
-          <t>$87.1B</t>
+          <t>$-49.7B</t>
         </is>
       </c>
       <c r="D518" t="inlineStr">
         <is>
-          <t>$134.1B</t>
+          <t>$-34.4B</t>
         </is>
       </c>
       <c r="E518" t="inlineStr"/>
@@ -15687,17 +15687,17 @@
       </c>
       <c r="B520" t="inlineStr">
         <is>
-          <t>Foreign Bond InvestmentDEC</t>
+          <t>Overall Net Capital FlowsDEC</t>
         </is>
       </c>
       <c r="C520" t="inlineStr">
         <is>
-          <t>$-49.7B</t>
+          <t>$87.1B</t>
         </is>
       </c>
       <c r="D520" t="inlineStr">
         <is>
-          <t>$-34.4B</t>
+          <t>$134.1B</t>
         </is>
       </c>
       <c r="E520" t="inlineStr"/>
@@ -17326,7 +17326,7 @@
       </c>
       <c r="B577" t="inlineStr">
         <is>
-          <t>Fed Daly Speech</t>
+          <t>Fed Jefferson Speech</t>
         </is>
       </c>
       <c r="C577" t="inlineStr"/>
@@ -17345,7 +17345,7 @@
       </c>
       <c r="B578" t="inlineStr">
         <is>
-          <t>Fed Jefferson Speech</t>
+          <t>Fed Daly Speech</t>
         </is>
       </c>
       <c r="C578" t="inlineStr"/>
@@ -17630,27 +17630,19 @@
       </c>
       <c r="B589" t="inlineStr">
         <is>
-          <t>House Price Index MoMDEC</t>
-        </is>
-      </c>
-      <c r="C589" t="inlineStr">
-        <is>
-          <t>0.4%</t>
-        </is>
-      </c>
+          <t>House Price Index YoYDEC</t>
+        </is>
+      </c>
+      <c r="C589" t="inlineStr"/>
       <c r="D589" t="inlineStr">
         <is>
-          <t>0.4%</t>
-        </is>
-      </c>
-      <c r="E589" t="inlineStr">
-        <is>
-          <t>0.2%</t>
-        </is>
-      </c>
+          <t>4.2%</t>
+        </is>
+      </c>
+      <c r="E589" t="inlineStr"/>
       <c r="F589" t="inlineStr">
         <is>
-          <t>0.2%</t>
+          <t>4.1%</t>
         </is>
       </c>
       <c r="G589" t="n">
@@ -17668,14 +17660,10 @@
           <t>House Price IndexDEC</t>
         </is>
       </c>
-      <c r="C590" t="inlineStr">
-        <is>
-          <t>436.1</t>
-        </is>
-      </c>
+      <c r="C590" t="inlineStr"/>
       <c r="D590" t="inlineStr">
         <is>
-          <t>434.3</t>
+          <t>433.4</t>
         </is>
       </c>
       <c r="E590" t="inlineStr"/>
@@ -17696,27 +17684,27 @@
       </c>
       <c r="B591" t="inlineStr">
         <is>
-          <t>House Price Index YoYDEC</t>
-        </is>
-      </c>
-      <c r="C591" t="inlineStr">
-        <is>
-          <t>4.7%</t>
-        </is>
-      </c>
+          <t>S&amp;P/Case-Shiller Home Price YoYDEC</t>
+        </is>
+      </c>
+      <c r="C591" t="inlineStr"/>
       <c r="D591" t="inlineStr">
         <is>
-          <t>4.5%</t>
-        </is>
-      </c>
-      <c r="E591" t="inlineStr"/>
+          <t>4.3%</t>
+        </is>
+      </c>
+      <c r="E591" t="inlineStr">
+        <is>
+          <t>4.4%</t>
+        </is>
+      </c>
       <c r="F591" t="inlineStr">
         <is>
-          <t>4.1%</t>
+          <t>4.4%</t>
         </is>
       </c>
       <c r="G591" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="592">
@@ -17727,27 +17715,31 @@
       </c>
       <c r="B592" t="inlineStr">
         <is>
-          <t>S&amp;P/Case-Shiller Home Price MoMDEC</t>
+          <t>S&amp;P/Case-Shiller Home Price YoYDEC</t>
         </is>
       </c>
       <c r="C592" t="inlineStr">
         <is>
-          <t>-0.1%</t>
+          <t>4.5%</t>
         </is>
       </c>
       <c r="D592" t="inlineStr">
         <is>
-          <t>-0.1%</t>
-        </is>
-      </c>
-      <c r="E592" t="inlineStr"/>
+          <t>4.3%</t>
+        </is>
+      </c>
+      <c r="E592" t="inlineStr">
+        <is>
+          <t>4.4%</t>
+        </is>
+      </c>
       <c r="F592" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>4.4%</t>
         </is>
       </c>
       <c r="G592" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="593">
@@ -17758,23 +17750,19 @@
       </c>
       <c r="B593" t="inlineStr">
         <is>
-          <t>House Price Index MoMDEC</t>
+          <t>S&amp;P/Case-Shiller Home Price MoMDEC</t>
         </is>
       </c>
       <c r="C593" t="inlineStr"/>
       <c r="D593" t="inlineStr">
         <is>
-          <t>0.3%</t>
-        </is>
-      </c>
-      <c r="E593" t="inlineStr">
-        <is>
-          <t>0.2%</t>
-        </is>
-      </c>
+          <t>-0.1%</t>
+        </is>
+      </c>
+      <c r="E593" t="inlineStr"/>
       <c r="F593" t="inlineStr">
         <is>
-          <t>0.2%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="G593" t="n">
@@ -17789,19 +17777,23 @@
       </c>
       <c r="B594" t="inlineStr">
         <is>
-          <t>S&amp;P/Case-Shiller Home Price MoMDEC</t>
+          <t>House Price Index MoMDEC</t>
         </is>
       </c>
       <c r="C594" t="inlineStr"/>
       <c r="D594" t="inlineStr">
         <is>
-          <t>-0.1%</t>
-        </is>
-      </c>
-      <c r="E594" t="inlineStr"/>
+          <t>0.3%</t>
+        </is>
+      </c>
+      <c r="E594" t="inlineStr">
+        <is>
+          <t>0.2%</t>
+        </is>
+      </c>
       <c r="F594" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>0.2%</t>
         </is>
       </c>
       <c r="G594" t="n">
@@ -17816,19 +17808,23 @@
       </c>
       <c r="B595" t="inlineStr">
         <is>
-          <t>House Price Index YoYDEC</t>
-        </is>
-      </c>
-      <c r="C595" t="inlineStr"/>
+          <t>S&amp;P/Case-Shiller Home Price MoMDEC</t>
+        </is>
+      </c>
+      <c r="C595" t="inlineStr">
+        <is>
+          <t>-0.1%</t>
+        </is>
+      </c>
       <c r="D595" t="inlineStr">
         <is>
-          <t>4.2%</t>
+          <t>-0.1%</t>
         </is>
       </c>
       <c r="E595" t="inlineStr"/>
       <c r="F595" t="inlineStr">
         <is>
-          <t>4.1%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="G595" t="n">
@@ -17843,31 +17839,27 @@
       </c>
       <c r="B596" t="inlineStr">
         <is>
-          <t>S&amp;P/Case-Shiller Home Price YoYDEC</t>
+          <t>House Price Index YoYDEC</t>
         </is>
       </c>
       <c r="C596" t="inlineStr">
         <is>
+          <t>4.7%</t>
+        </is>
+      </c>
+      <c r="D596" t="inlineStr">
+        <is>
           <t>4.5%</t>
         </is>
       </c>
-      <c r="D596" t="inlineStr">
-        <is>
-          <t>4.3%</t>
-        </is>
-      </c>
-      <c r="E596" t="inlineStr">
-        <is>
-          <t>4.4%</t>
-        </is>
-      </c>
+      <c r="E596" t="inlineStr"/>
       <c r="F596" t="inlineStr">
         <is>
-          <t>4.4%</t>
+          <t>4.1%</t>
         </is>
       </c>
       <c r="G596" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="597">
@@ -17878,27 +17870,27 @@
       </c>
       <c r="B597" t="inlineStr">
         <is>
-          <t>S&amp;P/Case-Shiller Home Price YoYDEC</t>
-        </is>
-      </c>
-      <c r="C597" t="inlineStr"/>
+          <t>House Price IndexDEC</t>
+        </is>
+      </c>
+      <c r="C597" t="inlineStr">
+        <is>
+          <t>436.1</t>
+        </is>
+      </c>
       <c r="D597" t="inlineStr">
         <is>
-          <t>4.3%</t>
-        </is>
-      </c>
-      <c r="E597" t="inlineStr">
-        <is>
-          <t>4.4%</t>
-        </is>
-      </c>
+          <t>434.3</t>
+        </is>
+      </c>
+      <c r="E597" t="inlineStr"/>
       <c r="F597" t="inlineStr">
         <is>
-          <t>4.4%</t>
+          <t>434.3</t>
         </is>
       </c>
       <c r="G597" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="598">
@@ -17909,19 +17901,27 @@
       </c>
       <c r="B598" t="inlineStr">
         <is>
-          <t>House Price IndexDEC</t>
-        </is>
-      </c>
-      <c r="C598" t="inlineStr"/>
+          <t>House Price Index MoMDEC</t>
+        </is>
+      </c>
+      <c r="C598" t="inlineStr">
+        <is>
+          <t>0.4%</t>
+        </is>
+      </c>
       <c r="D598" t="inlineStr">
         <is>
-          <t>433.4</t>
-        </is>
-      </c>
-      <c r="E598" t="inlineStr"/>
+          <t>0.4%</t>
+        </is>
+      </c>
+      <c r="E598" t="inlineStr">
+        <is>
+          <t>0.2%</t>
+        </is>
+      </c>
       <c r="F598" t="inlineStr">
         <is>
-          <t>434.3</t>
+          <t>0.2%</t>
         </is>
       </c>
       <c r="G598" t="n">
@@ -18184,23 +18184,19 @@
       </c>
       <c r="B607" t="inlineStr">
         <is>
-          <t>Dallas Fed Services Revenues IndexFEB</t>
-        </is>
-      </c>
-      <c r="C607" t="inlineStr">
-        <is>
-          <t>8.2</t>
-        </is>
-      </c>
+          <t>Dallas Fed Services IndexFEB</t>
+        </is>
+      </c>
+      <c r="C607" t="inlineStr"/>
       <c r="D607" t="inlineStr">
         <is>
-          <t>5.7</t>
+          <t>7.4</t>
         </is>
       </c>
       <c r="E607" t="inlineStr"/>
       <c r="F607" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>9</t>
         </is>
       </c>
       <c r="G607" t="n">
@@ -18215,23 +18211,19 @@
       </c>
       <c r="B608" t="inlineStr">
         <is>
-          <t>Dallas Fed Services IndexFEB</t>
-        </is>
-      </c>
-      <c r="C608" t="inlineStr">
-        <is>
-          <t>4.6</t>
-        </is>
-      </c>
+          <t>Dallas Fed Services Revenues IndexFEB</t>
+        </is>
+      </c>
+      <c r="C608" t="inlineStr"/>
       <c r="D608" t="inlineStr">
         <is>
-          <t>7.4</t>
+          <t>5.7</t>
         </is>
       </c>
       <c r="E608" t="inlineStr"/>
       <c r="F608" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>7</t>
         </is>
       </c>
       <c r="G608" t="n">
@@ -18249,7 +18241,11 @@
           <t>Dallas Fed Services Revenues IndexFEB</t>
         </is>
       </c>
-      <c r="C609" t="inlineStr"/>
+      <c r="C609" t="inlineStr">
+        <is>
+          <t>8.2</t>
+        </is>
+      </c>
       <c r="D609" t="inlineStr">
         <is>
           <t>5.7</t>
@@ -18276,7 +18272,11 @@
           <t>Dallas Fed Services IndexFEB</t>
         </is>
       </c>
-      <c r="C610" t="inlineStr"/>
+      <c r="C610" t="inlineStr">
+        <is>
+          <t>4.6</t>
+        </is>
+      </c>
       <c r="D610" t="inlineStr">
         <is>
           <t>7.4</t>
@@ -18496,23 +18496,19 @@
       </c>
       <c r="B619" t="inlineStr">
         <is>
-          <t>MBA 30-Year Mortgage RateFEB/21</t>
-        </is>
-      </c>
-      <c r="C619" t="inlineStr">
-        <is>
-          <t>6.88%</t>
-        </is>
-      </c>
+          <t>MBA Purchase IndexFEB/21</t>
+        </is>
+      </c>
+      <c r="C619" t="inlineStr"/>
       <c r="D619" t="inlineStr">
         <is>
-          <t>6.93%</t>
+          <t>144.0</t>
         </is>
       </c>
       <c r="E619" t="inlineStr"/>
       <c r="F619" t="inlineStr"/>
       <c r="G619" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="620">
@@ -18523,13 +18519,13 @@
       </c>
       <c r="B620" t="inlineStr">
         <is>
-          <t>MBA Mortgage Market IndexFEB/21</t>
+          <t>MBA Mortgage Refinance IndexFEB/21</t>
         </is>
       </c>
       <c r="C620" t="inlineStr"/>
       <c r="D620" t="inlineStr">
         <is>
-          <t>214.9</t>
+          <t>593.6</t>
         </is>
       </c>
       <c r="E620" t="inlineStr"/>
@@ -18546,17 +18542,17 @@
       </c>
       <c r="B621" t="inlineStr">
         <is>
-          <t>MBA Mortgage Market IndexFEB/21</t>
+          <t>MBA Mortgage ApplicationsFEB/21</t>
         </is>
       </c>
       <c r="C621" t="inlineStr">
         <is>
-          <t>212.3</t>
+          <t>-1.2%</t>
         </is>
       </c>
       <c r="D621" t="inlineStr">
         <is>
-          <t>214.9</t>
+          <t>-6.6%</t>
         </is>
       </c>
       <c r="E621" t="inlineStr"/>
@@ -18573,23 +18569,19 @@
       </c>
       <c r="B622" t="inlineStr">
         <is>
-          <t>MBA Purchase IndexFEB/21</t>
-        </is>
-      </c>
-      <c r="C622" t="inlineStr">
-        <is>
-          <t>144.3</t>
-        </is>
-      </c>
+          <t>MBA 30-Year Mortgage RateFEB/21</t>
+        </is>
+      </c>
+      <c r="C622" t="inlineStr"/>
       <c r="D622" t="inlineStr">
         <is>
-          <t>144.0</t>
+          <t>6.93%</t>
         </is>
       </c>
       <c r="E622" t="inlineStr"/>
       <c r="F622" t="inlineStr"/>
       <c r="G622" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="623">
@@ -18600,17 +18592,13 @@
       </c>
       <c r="B623" t="inlineStr">
         <is>
-          <t>MBA Mortgage Refinance IndexFEB/21</t>
-        </is>
-      </c>
-      <c r="C623" t="inlineStr">
-        <is>
-          <t>572.5</t>
-        </is>
-      </c>
+          <t>MBA Mortgage ApplicationsFEB/21</t>
+        </is>
+      </c>
+      <c r="C623" t="inlineStr"/>
       <c r="D623" t="inlineStr">
         <is>
-          <t>593.6</t>
+          <t>-6.6%</t>
         </is>
       </c>
       <c r="E623" t="inlineStr"/>
@@ -18627,13 +18615,13 @@
       </c>
       <c r="B624" t="inlineStr">
         <is>
-          <t>MBA Mortgage ApplicationsFEB/21</t>
+          <t>MBA Mortgage Market IndexFEB/21</t>
         </is>
       </c>
       <c r="C624" t="inlineStr"/>
       <c r="D624" t="inlineStr">
         <is>
-          <t>-6.6%</t>
+          <t>214.9</t>
         </is>
       </c>
       <c r="E624" t="inlineStr"/>
@@ -18653,7 +18641,11 @@
           <t>MBA Purchase IndexFEB/21</t>
         </is>
       </c>
-      <c r="C625" t="inlineStr"/>
+      <c r="C625" t="inlineStr">
+        <is>
+          <t>144.3</t>
+        </is>
+      </c>
       <c r="D625" t="inlineStr">
         <is>
           <t>144.0</t>
@@ -18673,19 +18665,23 @@
       </c>
       <c r="B626" t="inlineStr">
         <is>
-          <t>MBA 30-Year Mortgage RateFEB/21</t>
-        </is>
-      </c>
-      <c r="C626" t="inlineStr"/>
+          <t>MBA Mortgage Market IndexFEB/21</t>
+        </is>
+      </c>
+      <c r="C626" t="inlineStr">
+        <is>
+          <t>212.3</t>
+        </is>
+      </c>
       <c r="D626" t="inlineStr">
         <is>
-          <t>6.93%</t>
+          <t>214.9</t>
         </is>
       </c>
       <c r="E626" t="inlineStr"/>
       <c r="F626" t="inlineStr"/>
       <c r="G626" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="627">
@@ -18696,17 +18692,17 @@
       </c>
       <c r="B627" t="inlineStr">
         <is>
-          <t>MBA Mortgage ApplicationsFEB/21</t>
+          <t>MBA Mortgage Refinance IndexFEB/21</t>
         </is>
       </c>
       <c r="C627" t="inlineStr">
         <is>
-          <t>-1.2%</t>
+          <t>572.5</t>
         </is>
       </c>
       <c r="D627" t="inlineStr">
         <is>
-          <t>-6.6%</t>
+          <t>593.6</t>
         </is>
       </c>
       <c r="E627" t="inlineStr"/>
@@ -18723,19 +18719,23 @@
       </c>
       <c r="B628" t="inlineStr">
         <is>
-          <t>MBA Mortgage Refinance IndexFEB/21</t>
-        </is>
-      </c>
-      <c r="C628" t="inlineStr"/>
+          <t>MBA 30-Year Mortgage RateFEB/21</t>
+        </is>
+      </c>
+      <c r="C628" t="inlineStr">
+        <is>
+          <t>6.88%</t>
+        </is>
+      </c>
       <c r="D628" t="inlineStr">
         <is>
-          <t>593.6</t>
+          <t>6.93%</t>
         </is>
       </c>
       <c r="E628" t="inlineStr"/>
       <c r="F628" t="inlineStr"/>
       <c r="G628" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="629">
@@ -18908,14 +18908,10 @@
           <t>New Home SalesJAN</t>
         </is>
       </c>
-      <c r="C634" t="inlineStr">
-        <is>
-          <t>0.657M</t>
-        </is>
-      </c>
+      <c r="C634" t="inlineStr"/>
       <c r="D634" t="inlineStr">
         <is>
-          <t>0.734M</t>
+          <t>0.698M</t>
         </is>
       </c>
       <c r="E634" t="inlineStr">
@@ -18943,14 +18939,10 @@
           <t>New Home Sales MoMJAN</t>
         </is>
       </c>
-      <c r="C635" t="inlineStr">
-        <is>
-          <t>-10.5%</t>
-        </is>
-      </c>
+      <c r="C635" t="inlineStr"/>
       <c r="D635" t="inlineStr">
         <is>
-          <t>8.1%</t>
+          <t>3.6%</t>
         </is>
       </c>
       <c r="E635" t="inlineStr"/>
@@ -18974,10 +18966,14 @@
           <t>New Home Sales MoMJAN</t>
         </is>
       </c>
-      <c r="C636" t="inlineStr"/>
+      <c r="C636" t="inlineStr">
+        <is>
+          <t>-10.5%</t>
+        </is>
+      </c>
       <c r="D636" t="inlineStr">
         <is>
-          <t>3.6%</t>
+          <t>8.1%</t>
         </is>
       </c>
       <c r="E636" t="inlineStr"/>
@@ -19001,10 +18997,14 @@
           <t>New Home SalesJAN</t>
         </is>
       </c>
-      <c r="C637" t="inlineStr"/>
+      <c r="C637" t="inlineStr">
+        <is>
+          <t>0.657M</t>
+        </is>
+      </c>
       <c r="D637" t="inlineStr">
         <is>
-          <t>0.698M</t>
+          <t>0.734M</t>
         </is>
       </c>
       <c r="E637" t="inlineStr">
@@ -19029,19 +19029,27 @@
       </c>
       <c r="B638" t="inlineStr">
         <is>
-          <t>EIA Cushing Crude Oil Stocks ChangeFEB/21</t>
-        </is>
-      </c>
-      <c r="C638" t="inlineStr"/>
+          <t>EIA Gasoline Stocks ChangeFEB/21</t>
+        </is>
+      </c>
+      <c r="C638" t="inlineStr">
+        <is>
+          <t>0.369M</t>
+        </is>
+      </c>
       <c r="D638" t="inlineStr">
         <is>
-          <t>1.472M</t>
-        </is>
-      </c>
-      <c r="E638" t="inlineStr"/>
+          <t>-0.151M</t>
+        </is>
+      </c>
+      <c r="E638" t="inlineStr">
+        <is>
+          <t>-1.30M</t>
+        </is>
+      </c>
       <c r="F638" t="inlineStr"/>
       <c r="G638" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="639">
@@ -19052,23 +19060,23 @@
       </c>
       <c r="B639" t="inlineStr">
         <is>
-          <t>EIA Gasoline Stocks ChangeFEB/21</t>
-        </is>
-      </c>
-      <c r="C639" t="inlineStr"/>
+          <t>EIA Crude Oil Imports ChangeFEB/21</t>
+        </is>
+      </c>
+      <c r="C639" t="inlineStr">
+        <is>
+          <t>0.292M</t>
+        </is>
+      </c>
       <c r="D639" t="inlineStr">
         <is>
-          <t>-0.151M</t>
-        </is>
-      </c>
-      <c r="E639" t="inlineStr">
-        <is>
-          <t>-1.30M</t>
-        </is>
-      </c>
+          <t>-0.961M</t>
+        </is>
+      </c>
+      <c r="E639" t="inlineStr"/>
       <c r="F639" t="inlineStr"/>
       <c r="G639" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="640">
@@ -19079,23 +19087,23 @@
       </c>
       <c r="B640" t="inlineStr">
         <is>
-          <t>EIA Crude Oil Stocks ChangeFEB/21</t>
-        </is>
-      </c>
-      <c r="C640" t="inlineStr"/>
+          <t>EIA Cushing Crude Oil Stocks ChangeFEB/21</t>
+        </is>
+      </c>
+      <c r="C640" t="inlineStr">
+        <is>
+          <t>1.282M</t>
+        </is>
+      </c>
       <c r="D640" t="inlineStr">
         <is>
-          <t>4.633M</t>
-        </is>
-      </c>
-      <c r="E640" t="inlineStr">
-        <is>
-          <t>2.34M</t>
-        </is>
-      </c>
+          <t>1.472M</t>
+        </is>
+      </c>
+      <c r="E640" t="inlineStr"/>
       <c r="F640" t="inlineStr"/>
       <c r="G640" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="641">
@@ -19106,27 +19114,23 @@
       </c>
       <c r="B641" t="inlineStr">
         <is>
-          <t>EIA Crude Oil Stocks ChangeFEB/21</t>
+          <t>EIA Distillate Fuel Production ChangeFEB/21</t>
         </is>
       </c>
       <c r="C641" t="inlineStr">
         <is>
-          <t>-2.332M</t>
+          <t>0.439M</t>
         </is>
       </c>
       <c r="D641" t="inlineStr">
         <is>
-          <t>4.633M</t>
-        </is>
-      </c>
-      <c r="E641" t="inlineStr">
-        <is>
-          <t>2.54M</t>
-        </is>
-      </c>
+          <t>0.18M</t>
+        </is>
+      </c>
+      <c r="E641" t="inlineStr"/>
       <c r="F641" t="inlineStr"/>
       <c r="G641" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="642">
@@ -19140,7 +19144,11 @@
           <t>EIA Distillate Stocks ChangeFEB/21</t>
         </is>
       </c>
-      <c r="C642" t="inlineStr"/>
+      <c r="C642" t="inlineStr">
+        <is>
+          <t>3.908M</t>
+        </is>
+      </c>
       <c r="D642" t="inlineStr">
         <is>
           <t>-2.051M</t>
@@ -19167,7 +19175,11 @@
           <t>EIA Gasoline Production ChangeFEB/21</t>
         </is>
       </c>
-      <c r="C643" t="inlineStr"/>
+      <c r="C643" t="inlineStr">
+        <is>
+          <t>-0.02M</t>
+        </is>
+      </c>
       <c r="D643" t="inlineStr">
         <is>
           <t>-0.156M</t>
@@ -19190,7 +19202,11 @@
           <t>EIA Heating Oil Stocks ChangeFEB/21</t>
         </is>
       </c>
-      <c r="C644" t="inlineStr"/>
+      <c r="C644" t="inlineStr">
+        <is>
+          <t>0.134M</t>
+        </is>
+      </c>
       <c r="D644" t="inlineStr">
         <is>
           <t>-0.343M</t>
@@ -19213,7 +19229,11 @@
           <t>EIA Refinery Crude Runs ChangeFEB/21</t>
         </is>
       </c>
-      <c r="C645" t="inlineStr"/>
+      <c r="C645" t="inlineStr">
+        <is>
+          <t>0.317M</t>
+        </is>
+      </c>
       <c r="D645" t="inlineStr">
         <is>
           <t>-0.015M</t>
@@ -19233,13 +19253,13 @@
       </c>
       <c r="B646" t="inlineStr">
         <is>
-          <t>EIA Distillate Fuel Production ChangeFEB/21</t>
+          <t>EIA Crude Oil Imports ChangeFEB/21</t>
         </is>
       </c>
       <c r="C646" t="inlineStr"/>
       <c r="D646" t="inlineStr">
         <is>
-          <t>0.18M</t>
+          <t>-0.961M</t>
         </is>
       </c>
       <c r="E646" t="inlineStr"/>
@@ -19259,11 +19279,7 @@
           <t>EIA Refinery Crude Runs ChangeFEB/21</t>
         </is>
       </c>
-      <c r="C647" t="inlineStr">
-        <is>
-          <t>0.317M</t>
-        </is>
-      </c>
+      <c r="C647" t="inlineStr"/>
       <c r="D647" t="inlineStr">
         <is>
           <t>-0.015M</t>
@@ -19286,11 +19302,7 @@
           <t>EIA Heating Oil Stocks ChangeFEB/21</t>
         </is>
       </c>
-      <c r="C648" t="inlineStr">
-        <is>
-          <t>0.134M</t>
-        </is>
-      </c>
+      <c r="C648" t="inlineStr"/>
       <c r="D648" t="inlineStr">
         <is>
           <t>-0.343M</t>
@@ -19313,11 +19325,7 @@
           <t>EIA Gasoline Production ChangeFEB/21</t>
         </is>
       </c>
-      <c r="C649" t="inlineStr">
-        <is>
-          <t>-0.02M</t>
-        </is>
-      </c>
+      <c r="C649" t="inlineStr"/>
       <c r="D649" t="inlineStr">
         <is>
           <t>-0.156M</t>
@@ -19340,11 +19348,7 @@
           <t>EIA Distillate Stocks ChangeFEB/21</t>
         </is>
       </c>
-      <c r="C650" t="inlineStr">
-        <is>
-          <t>3.908M</t>
-        </is>
-      </c>
+      <c r="C650" t="inlineStr"/>
       <c r="D650" t="inlineStr">
         <is>
           <t>-2.051M</t>
@@ -19368,19 +19372,27 @@
       </c>
       <c r="B651" t="inlineStr">
         <is>
-          <t>EIA Crude Oil Imports ChangeFEB/21</t>
-        </is>
-      </c>
-      <c r="C651" t="inlineStr"/>
+          <t>EIA Crude Oil Stocks ChangeFEB/21</t>
+        </is>
+      </c>
+      <c r="C651" t="inlineStr">
+        <is>
+          <t>-2.332M</t>
+        </is>
+      </c>
       <c r="D651" t="inlineStr">
         <is>
-          <t>-0.961M</t>
-        </is>
-      </c>
-      <c r="E651" t="inlineStr"/>
+          <t>4.633M</t>
+        </is>
+      </c>
+      <c r="E651" t="inlineStr">
+        <is>
+          <t>2.54M</t>
+        </is>
+      </c>
       <c r="F651" t="inlineStr"/>
       <c r="G651" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="652">
@@ -19391,23 +19403,23 @@
       </c>
       <c r="B652" t="inlineStr">
         <is>
-          <t>EIA Cushing Crude Oil Stocks ChangeFEB/21</t>
-        </is>
-      </c>
-      <c r="C652" t="inlineStr">
-        <is>
-          <t>1.282M</t>
-        </is>
-      </c>
+          <t>EIA Crude Oil Stocks ChangeFEB/21</t>
+        </is>
+      </c>
+      <c r="C652" t="inlineStr"/>
       <c r="D652" t="inlineStr">
         <is>
-          <t>1.472M</t>
-        </is>
-      </c>
-      <c r="E652" t="inlineStr"/>
+          <t>4.633M</t>
+        </is>
+      </c>
+      <c r="E652" t="inlineStr">
+        <is>
+          <t>2.34M</t>
+        </is>
+      </c>
       <c r="F652" t="inlineStr"/>
       <c r="G652" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="653">
@@ -19418,23 +19430,23 @@
       </c>
       <c r="B653" t="inlineStr">
         <is>
-          <t>EIA Crude Oil Imports ChangeFEB/21</t>
-        </is>
-      </c>
-      <c r="C653" t="inlineStr">
-        <is>
-          <t>0.292M</t>
-        </is>
-      </c>
+          <t>EIA Gasoline Stocks ChangeFEB/21</t>
+        </is>
+      </c>
+      <c r="C653" t="inlineStr"/>
       <c r="D653" t="inlineStr">
         <is>
-          <t>-0.961M</t>
-        </is>
-      </c>
-      <c r="E653" t="inlineStr"/>
+          <t>-0.151M</t>
+        </is>
+      </c>
+      <c r="E653" t="inlineStr">
+        <is>
+          <t>-1.30M</t>
+        </is>
+      </c>
       <c r="F653" t="inlineStr"/>
       <c r="G653" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="654">
@@ -19445,27 +19457,19 @@
       </c>
       <c r="B654" t="inlineStr">
         <is>
-          <t>EIA Gasoline Stocks ChangeFEB/21</t>
-        </is>
-      </c>
-      <c r="C654" t="inlineStr">
-        <is>
-          <t>0.369M</t>
-        </is>
-      </c>
+          <t>EIA Cushing Crude Oil Stocks ChangeFEB/21</t>
+        </is>
+      </c>
+      <c r="C654" t="inlineStr"/>
       <c r="D654" t="inlineStr">
         <is>
-          <t>-0.151M</t>
-        </is>
-      </c>
-      <c r="E654" t="inlineStr">
-        <is>
-          <t>-1.30M</t>
-        </is>
-      </c>
+          <t>1.472M</t>
+        </is>
+      </c>
+      <c r="E654" t="inlineStr"/>
       <c r="F654" t="inlineStr"/>
       <c r="G654" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="655">
@@ -19479,11 +19483,7 @@
           <t>EIA Distillate Fuel Production ChangeFEB/21</t>
         </is>
       </c>
-      <c r="C655" t="inlineStr">
-        <is>
-          <t>0.439M</t>
-        </is>
-      </c>
+      <c r="C655" t="inlineStr"/>
       <c r="D655" t="inlineStr">
         <is>
           <t>0.18M</t>
@@ -19622,25 +19622,21 @@
       </c>
       <c r="B661" t="inlineStr">
         <is>
-          <t>Building Permits FinalJAN</t>
-        </is>
-      </c>
-      <c r="C661" t="inlineStr"/>
+          <t>7-Year Note Auction</t>
+        </is>
+      </c>
+      <c r="C661" t="inlineStr">
+        <is>
+          <t>4.194%</t>
+        </is>
+      </c>
       <c r="D661" t="inlineStr">
         <is>
-          <t>1.482M</t>
-        </is>
-      </c>
-      <c r="E661" t="inlineStr">
-        <is>
-          <t>1.483M</t>
-        </is>
-      </c>
-      <c r="F661" t="inlineStr">
-        <is>
-          <t>1.483M</t>
-        </is>
-      </c>
+          <t>4.457%</t>
+        </is>
+      </c>
+      <c r="E661" t="inlineStr"/>
+      <c r="F661" t="inlineStr"/>
       <c r="G661" t="n">
         <v>3</v>
       </c>
@@ -19653,25 +19649,17 @@
       </c>
       <c r="B662" t="inlineStr">
         <is>
-          <t>Building Permits MoM FinalJAN</t>
+          <t>7-Year Note Auction</t>
         </is>
       </c>
       <c r="C662" t="inlineStr"/>
       <c r="D662" t="inlineStr">
         <is>
-          <t>-0.7%</t>
-        </is>
-      </c>
-      <c r="E662" t="inlineStr">
-        <is>
-          <t>0.1%</t>
-        </is>
-      </c>
-      <c r="F662" t="inlineStr">
-        <is>
-          <t>0.1%</t>
-        </is>
-      </c>
+          <t>4.457%</t>
+        </is>
+      </c>
+      <c r="E662" t="inlineStr"/>
+      <c r="F662" t="inlineStr"/>
       <c r="G662" t="n">
         <v>3</v>
       </c>
@@ -19684,17 +19672,25 @@
       </c>
       <c r="B663" t="inlineStr">
         <is>
-          <t>7-Year Note Auction</t>
+          <t>Building Permits MoM FinalJAN</t>
         </is>
       </c>
       <c r="C663" t="inlineStr"/>
       <c r="D663" t="inlineStr">
         <is>
-          <t>4.457%</t>
-        </is>
-      </c>
-      <c r="E663" t="inlineStr"/>
-      <c r="F663" t="inlineStr"/>
+          <t>-0.7%</t>
+        </is>
+      </c>
+      <c r="E663" t="inlineStr">
+        <is>
+          <t>0.1%</t>
+        </is>
+      </c>
+      <c r="F663" t="inlineStr">
+        <is>
+          <t>0.1%</t>
+        </is>
+      </c>
       <c r="G663" t="n">
         <v>3</v>
       </c>
@@ -19707,21 +19703,25 @@
       </c>
       <c r="B664" t="inlineStr">
         <is>
-          <t>7-Year Note Auction</t>
-        </is>
-      </c>
-      <c r="C664" t="inlineStr">
-        <is>
-          <t>4.194%</t>
-        </is>
-      </c>
+          <t>Building Permits FinalJAN</t>
+        </is>
+      </c>
+      <c r="C664" t="inlineStr"/>
       <c r="D664" t="inlineStr">
         <is>
-          <t>4.457%</t>
-        </is>
-      </c>
-      <c r="E664" t="inlineStr"/>
-      <c r="F664" t="inlineStr"/>
+          <t>1.482M</t>
+        </is>
+      </c>
+      <c r="E664" t="inlineStr">
+        <is>
+          <t>1.483M</t>
+        </is>
+      </c>
+      <c r="F664" t="inlineStr">
+        <is>
+          <t>1.483M</t>
+        </is>
+      </c>
       <c r="G664" t="n">
         <v>3</v>
       </c>
@@ -20129,23 +20129,23 @@
       </c>
       <c r="B678" t="inlineStr">
         <is>
-          <t>Durable Goods Orders Ex Transp MoMJAN</t>
+          <t>Initial Jobless ClaimsFEB/22</t>
         </is>
       </c>
       <c r="C678" t="inlineStr"/>
       <c r="D678" t="inlineStr">
         <is>
-          <t>0.3%</t>
+          <t>219K</t>
         </is>
       </c>
       <c r="E678" t="inlineStr">
         <is>
-          <t>0.3%</t>
+          <t>221K</t>
         </is>
       </c>
       <c r="F678" t="inlineStr">
         <is>
-          <t>0.3%</t>
+          <t>225.0K</t>
         </is>
       </c>
       <c r="G678" t="n">
@@ -20187,13 +20187,13 @@
       </c>
       <c r="B680" t="inlineStr">
         <is>
-          <t>Non Defense Goods Orders Ex AirJAN</t>
+          <t>Durable Goods Orders Ex Transp MoMJAN</t>
         </is>
       </c>
       <c r="C680" t="inlineStr"/>
       <c r="D680" t="inlineStr">
         <is>
-          <t>0.5%</t>
+          <t>0.3%</t>
         </is>
       </c>
       <c r="E680" t="inlineStr">
@@ -20203,11 +20203,11 @@
       </c>
       <c r="F680" t="inlineStr">
         <is>
-          <t>0.4%</t>
+          <t>0.3%</t>
         </is>
       </c>
       <c r="G680" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="681">
@@ -20218,19 +20218,23 @@
       </c>
       <c r="B681" t="inlineStr">
         <is>
-          <t>Jobless Claims 4-week AverageFEB/22</t>
+          <t>Non Defense Goods Orders Ex AirJAN</t>
         </is>
       </c>
       <c r="C681" t="inlineStr"/>
       <c r="D681" t="inlineStr">
         <is>
-          <t>215.25K</t>
-        </is>
-      </c>
-      <c r="E681" t="inlineStr"/>
+          <t>0.5%</t>
+        </is>
+      </c>
+      <c r="E681" t="inlineStr">
+        <is>
+          <t>0.3%</t>
+        </is>
+      </c>
       <c r="F681" t="inlineStr">
         <is>
-          <t>220.0K</t>
+          <t>0.4%</t>
         </is>
       </c>
       <c r="G681" t="n">
@@ -20245,27 +20249,23 @@
       </c>
       <c r="B682" t="inlineStr">
         <is>
-          <t>Durable Goods Orders MoMJAN</t>
+          <t>Jobless Claims 4-week AverageFEB/22</t>
         </is>
       </c>
       <c r="C682" t="inlineStr"/>
       <c r="D682" t="inlineStr">
         <is>
-          <t>-2.2%</t>
-        </is>
-      </c>
-      <c r="E682" t="inlineStr">
-        <is>
-          <t>2%</t>
-        </is>
-      </c>
+          <t>215.25K</t>
+        </is>
+      </c>
+      <c r="E682" t="inlineStr"/>
       <c r="F682" t="inlineStr">
         <is>
-          <t>2.2%</t>
+          <t>220.0K</t>
         </is>
       </c>
       <c r="G682" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="683">
@@ -20276,27 +20276,27 @@
       </c>
       <c r="B683" t="inlineStr">
         <is>
-          <t>Real Consumer Spending QoQ 2nd EstQ4</t>
+          <t>Durable Goods Orders MoMJAN</t>
         </is>
       </c>
       <c r="C683" t="inlineStr"/>
       <c r="D683" t="inlineStr">
         <is>
-          <t>3.7%</t>
+          <t>-2.2%</t>
         </is>
       </c>
       <c r="E683" t="inlineStr">
         <is>
-          <t>4.2%</t>
+          <t>2%</t>
         </is>
       </c>
       <c r="F683" t="inlineStr">
         <is>
-          <t>4.2%</t>
+          <t>2.2%</t>
         </is>
       </c>
       <c r="G683" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="684">
@@ -20307,23 +20307,23 @@
       </c>
       <c r="B684" t="inlineStr">
         <is>
-          <t>PCE Prices QoQ 2nd EstQ4</t>
+          <t>Real Consumer Spending QoQ 2nd EstQ4</t>
         </is>
       </c>
       <c r="C684" t="inlineStr"/>
       <c r="D684" t="inlineStr">
         <is>
-          <t>1.5%</t>
+          <t>3.7%</t>
         </is>
       </c>
       <c r="E684" t="inlineStr">
         <is>
-          <t>2.3%</t>
+          <t>4.2%</t>
         </is>
       </c>
       <c r="F684" t="inlineStr">
         <is>
-          <t>2.3%</t>
+          <t>4.2%</t>
         </is>
       </c>
       <c r="G684" t="n">
@@ -20338,27 +20338,27 @@
       </c>
       <c r="B685" t="inlineStr">
         <is>
-          <t>GDP Price Index QoQ 2nd EstQ4</t>
+          <t>PCE Prices QoQ 2nd EstQ4</t>
         </is>
       </c>
       <c r="C685" t="inlineStr"/>
       <c r="D685" t="inlineStr">
         <is>
-          <t>1.9%</t>
+          <t>1.5%</t>
         </is>
       </c>
       <c r="E685" t="inlineStr">
         <is>
-          <t>2.2%</t>
+          <t>2.3%</t>
         </is>
       </c>
       <c r="F685" t="inlineStr">
         <is>
-          <t>2.2%</t>
+          <t>2.3%</t>
         </is>
       </c>
       <c r="G685" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="686">
@@ -20369,27 +20369,27 @@
       </c>
       <c r="B686" t="inlineStr">
         <is>
-          <t>GDP Growth Rate QoQ 2nd EstQ4</t>
+          <t>GDP Price Index QoQ 2nd EstQ4</t>
         </is>
       </c>
       <c r="C686" t="inlineStr"/>
       <c r="D686" t="inlineStr">
         <is>
-          <t>3.1%</t>
+          <t>1.9%</t>
         </is>
       </c>
       <c r="E686" t="inlineStr">
         <is>
-          <t>2.3%</t>
+          <t>2.2%</t>
         </is>
       </c>
       <c r="F686" t="inlineStr">
         <is>
-          <t>2.3%</t>
+          <t>2.2%</t>
         </is>
       </c>
       <c r="G686" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="687">
@@ -20400,27 +20400,27 @@
       </c>
       <c r="B687" t="inlineStr">
         <is>
-          <t>Initial Jobless ClaimsFEB/22</t>
+          <t>GDP Growth Rate QoQ 2nd EstQ4</t>
         </is>
       </c>
       <c r="C687" t="inlineStr"/>
       <c r="D687" t="inlineStr">
         <is>
-          <t>219K</t>
+          <t>3.1%</t>
         </is>
       </c>
       <c r="E687" t="inlineStr">
         <is>
-          <t>221K</t>
+          <t>2.3%</t>
         </is>
       </c>
       <c r="F687" t="inlineStr">
         <is>
-          <t>225.0K</t>
+          <t>2.3%</t>
         </is>
       </c>
       <c r="G687" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="688">
@@ -21058,13 +21058,13 @@
       </c>
       <c r="B713" t="inlineStr">
         <is>
-          <t>15-Year Mortgage RateFEB/27</t>
+          <t>30-Year Mortgage RateFEB/27</t>
         </is>
       </c>
       <c r="C713" t="inlineStr"/>
       <c r="D713" t="inlineStr">
         <is>
-          <t>6.04%</t>
+          <t>6.85%</t>
         </is>
       </c>
       <c r="E713" t="inlineStr"/>
@@ -21081,13 +21081,13 @@
       </c>
       <c r="B714" t="inlineStr">
         <is>
-          <t>30-Year Mortgage RateFEB/27</t>
+          <t>15-Year Mortgage RateFEB/27</t>
         </is>
       </c>
       <c r="C714" t="inlineStr"/>
       <c r="D714" t="inlineStr">
         <is>
-          <t>6.85%</t>
+          <t>6.04%</t>
         </is>
       </c>
       <c r="E714" t="inlineStr"/>
@@ -21508,27 +21508,27 @@
       </c>
       <c r="B731" t="inlineStr">
         <is>
-          <t>PCE Price Index YoYJAN</t>
+          <t>Personal Spending MoMJAN</t>
         </is>
       </c>
       <c r="C731" t="inlineStr"/>
       <c r="D731" t="inlineStr">
         <is>
-          <t>2.6%</t>
+          <t>0.7%</t>
         </is>
       </c>
       <c r="E731" t="inlineStr">
         <is>
-          <t>2.5%</t>
+          <t>0.1%</t>
         </is>
       </c>
       <c r="F731" t="inlineStr">
         <is>
-          <t>2.5%</t>
+          <t>0.3%</t>
         </is>
       </c>
       <c r="G731" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="732">
@@ -21570,27 +21570,27 @@
       </c>
       <c r="B733" t="inlineStr">
         <is>
-          <t>Personal Spending MoMJAN</t>
+          <t>PCE Price Index YoYJAN</t>
         </is>
       </c>
       <c r="C733" t="inlineStr"/>
       <c r="D733" t="inlineStr">
         <is>
-          <t>0.7%</t>
+          <t>2.6%</t>
         </is>
       </c>
       <c r="E733" t="inlineStr">
         <is>
-          <t>0.1%</t>
+          <t>2.5%</t>
         </is>
       </c>
       <c r="F733" t="inlineStr">
         <is>
-          <t>0.3%</t>
+          <t>2.5%</t>
         </is>
       </c>
       <c r="G733" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="734">
@@ -21659,27 +21659,27 @@
       </c>
       <c r="B736" t="inlineStr">
         <is>
-          <t>Goods Trade Balance AdvJAN</t>
+          <t>Personal Income MoMJAN</t>
         </is>
       </c>
       <c r="C736" t="inlineStr"/>
       <c r="D736" t="inlineStr">
         <is>
-          <t>$-122.11B</t>
+          <t>0.4%</t>
         </is>
       </c>
       <c r="E736" t="inlineStr">
         <is>
-          <t>$-114.7B</t>
+          <t>0.3%</t>
         </is>
       </c>
       <c r="F736" t="inlineStr">
         <is>
-          <t>$ -116.0B</t>
+          <t>0.3%</t>
         </is>
       </c>
       <c r="G736" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="737">
@@ -21690,23 +21690,23 @@
       </c>
       <c r="B737" t="inlineStr">
         <is>
-          <t>PCE Price Index MoMJAN</t>
+          <t>Wholesale Inventories MoM AdvJAN</t>
         </is>
       </c>
       <c r="C737" t="inlineStr"/>
       <c r="D737" t="inlineStr">
         <is>
-          <t>0.3%</t>
+          <t>-0.5%</t>
         </is>
       </c>
       <c r="E737" t="inlineStr">
         <is>
-          <t>0.3%</t>
+          <t>0.1%</t>
         </is>
       </c>
       <c r="F737" t="inlineStr">
         <is>
-          <t>0.4%</t>
+          <t>0.2%</t>
         </is>
       </c>
       <c r="G737" t="n">
@@ -21721,23 +21721,23 @@
       </c>
       <c r="B738" t="inlineStr">
         <is>
-          <t>Personal Income MoMJAN</t>
+          <t>Core PCE Price Index MoMJAN</t>
         </is>
       </c>
       <c r="C738" t="inlineStr"/>
       <c r="D738" t="inlineStr">
         <is>
+          <t>0.2%</t>
+        </is>
+      </c>
+      <c r="E738" t="inlineStr">
+        <is>
+          <t>0.3%</t>
+        </is>
+      </c>
+      <c r="F738" t="inlineStr">
+        <is>
           <t>0.4%</t>
-        </is>
-      </c>
-      <c r="E738" t="inlineStr">
-        <is>
-          <t>0.3%</t>
-        </is>
-      </c>
-      <c r="F738" t="inlineStr">
-        <is>
-          <t>0.3%</t>
         </is>
       </c>
       <c r="G738" t="n">
@@ -21752,23 +21752,23 @@
       </c>
       <c r="B739" t="inlineStr">
         <is>
-          <t>Wholesale Inventories MoM AdvJAN</t>
+          <t>PCE Price Index MoMJAN</t>
         </is>
       </c>
       <c r="C739" t="inlineStr"/>
       <c r="D739" t="inlineStr">
         <is>
-          <t>-0.5%</t>
+          <t>0.3%</t>
         </is>
       </c>
       <c r="E739" t="inlineStr">
         <is>
-          <t>0.1%</t>
+          <t>0.3%</t>
         </is>
       </c>
       <c r="F739" t="inlineStr">
         <is>
-          <t>0.2%</t>
+          <t>0.4%</t>
         </is>
       </c>
       <c r="G739" t="n">
@@ -21783,27 +21783,27 @@
       </c>
       <c r="B740" t="inlineStr">
         <is>
-          <t>Core PCE Price Index MoMJAN</t>
+          <t>Goods Trade Balance AdvJAN</t>
         </is>
       </c>
       <c r="C740" t="inlineStr"/>
       <c r="D740" t="inlineStr">
         <is>
-          <t>0.2%</t>
+          <t>$-122.11B</t>
         </is>
       </c>
       <c r="E740" t="inlineStr">
         <is>
-          <t>0.3%</t>
+          <t>$-114.7B</t>
         </is>
       </c>
       <c r="F740" t="inlineStr">
         <is>
-          <t>0.4%</t>
+          <t>$ -116.0B</t>
         </is>
       </c>
       <c r="G740" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="741">
@@ -22165,23 +22165,23 @@
       </c>
       <c r="B754" t="inlineStr">
         <is>
-          <t>ISM Manufacturing New OrdersFEB</t>
+          <t>ISM Manufacturing PMIFEB</t>
         </is>
       </c>
       <c r="C754" t="inlineStr"/>
       <c r="D754" t="inlineStr">
         <is>
-          <t>55.1</t>
+          <t>50.9</t>
         </is>
       </c>
       <c r="E754" t="inlineStr"/>
       <c r="F754" t="inlineStr">
         <is>
-          <t>55.4</t>
+          <t>51</t>
         </is>
       </c>
       <c r="G754" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="755">
@@ -22219,23 +22219,23 @@
       </c>
       <c r="B756" t="inlineStr">
         <is>
-          <t>ISM Manufacturing PMIFEB</t>
+          <t>ISM Manufacturing New OrdersFEB</t>
         </is>
       </c>
       <c r="C756" t="inlineStr"/>
       <c r="D756" t="inlineStr">
         <is>
-          <t>50.9</t>
+          <t>55.1</t>
         </is>
       </c>
       <c r="E756" t="inlineStr"/>
       <c r="F756" t="inlineStr">
         <is>
-          <t>51</t>
+          <t>55.4</t>
         </is>
       </c>
       <c r="G756" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="757">
@@ -23254,23 +23254,23 @@
       </c>
       <c r="B797" t="inlineStr">
         <is>
-          <t>ISM Services PMIFEB</t>
+          <t>ISM Services EmploymentFEB</t>
         </is>
       </c>
       <c r="C797" t="inlineStr"/>
       <c r="D797" t="inlineStr">
         <is>
-          <t>52.8</t>
+          <t>52.3</t>
         </is>
       </c>
       <c r="E797" t="inlineStr"/>
       <c r="F797" t="inlineStr">
         <is>
-          <t>52.7</t>
+          <t>52.1</t>
         </is>
       </c>
       <c r="G797" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="798">
@@ -23281,19 +23281,19 @@
       </c>
       <c r="B798" t="inlineStr">
         <is>
-          <t>Factory Orders ex TransportationJAN</t>
+          <t>ISM Services New OrdersFEB</t>
         </is>
       </c>
       <c r="C798" t="inlineStr"/>
       <c r="D798" t="inlineStr">
         <is>
-          <t>0.2%</t>
+          <t>51.3</t>
         </is>
       </c>
       <c r="E798" t="inlineStr"/>
       <c r="F798" t="inlineStr">
         <is>
-          <t>0.3%</t>
+          <t>51.2</t>
         </is>
       </c>
       <c r="G798" t="n">
@@ -23308,19 +23308,19 @@
       </c>
       <c r="B799" t="inlineStr">
         <is>
-          <t>ISM Services Business ActivityFEB</t>
+          <t>ISM Services PricesFEB</t>
         </is>
       </c>
       <c r="C799" t="inlineStr"/>
       <c r="D799" t="inlineStr">
         <is>
-          <t>54.5</t>
+          <t>60.4</t>
         </is>
       </c>
       <c r="E799" t="inlineStr"/>
       <c r="F799" t="inlineStr">
         <is>
-          <t>54.2</t>
+          <t>60.6</t>
         </is>
       </c>
       <c r="G799" t="n">
@@ -23335,19 +23335,19 @@
       </c>
       <c r="B800" t="inlineStr">
         <is>
-          <t>ISM Services PricesFEB</t>
+          <t>ISM Services Business ActivityFEB</t>
         </is>
       </c>
       <c r="C800" t="inlineStr"/>
       <c r="D800" t="inlineStr">
         <is>
-          <t>60.4</t>
+          <t>54.5</t>
         </is>
       </c>
       <c r="E800" t="inlineStr"/>
       <c r="F800" t="inlineStr">
         <is>
-          <t>60.6</t>
+          <t>54.2</t>
         </is>
       </c>
       <c r="G800" t="n">
@@ -23362,19 +23362,19 @@
       </c>
       <c r="B801" t="inlineStr">
         <is>
-          <t>ISM Services New OrdersFEB</t>
+          <t>Factory Orders ex TransportationJAN</t>
         </is>
       </c>
       <c r="C801" t="inlineStr"/>
       <c r="D801" t="inlineStr">
         <is>
-          <t>51.3</t>
+          <t>0.2%</t>
         </is>
       </c>
       <c r="E801" t="inlineStr"/>
       <c r="F801" t="inlineStr">
         <is>
-          <t>51.2</t>
+          <t>0.3%</t>
         </is>
       </c>
       <c r="G801" t="n">
@@ -23389,23 +23389,23 @@
       </c>
       <c r="B802" t="inlineStr">
         <is>
-          <t>ISM Services EmploymentFEB</t>
+          <t>ISM Services PMIFEB</t>
         </is>
       </c>
       <c r="C802" t="inlineStr"/>
       <c r="D802" t="inlineStr">
         <is>
-          <t>52.3</t>
+          <t>52.8</t>
         </is>
       </c>
       <c r="E802" t="inlineStr"/>
       <c r="F802" t="inlineStr">
         <is>
-          <t>52.1</t>
+          <t>52.7</t>
         </is>
       </c>
       <c r="G802" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="803">
@@ -23623,15 +23623,19 @@
       </c>
       <c r="B812" t="inlineStr">
         <is>
-          <t>EIA Crude Oil Imports ChangeFEB/28</t>
+          <t>EIA Gasoline Stocks ChangeFEB/28</t>
         </is>
       </c>
       <c r="C812" t="inlineStr"/>
-      <c r="D812" t="inlineStr"/>
+      <c r="D812" t="inlineStr">
+        <is>
+          <t>0.369M</t>
+        </is>
+      </c>
       <c r="E812" t="inlineStr"/>
       <c r="F812" t="inlineStr"/>
       <c r="G812" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="813">
@@ -23642,19 +23646,19 @@
       </c>
       <c r="B813" t="inlineStr">
         <is>
-          <t>EIA Gasoline Stocks ChangeFEB/28</t>
+          <t>EIA Refinery Crude Runs ChangeFEB/28</t>
         </is>
       </c>
       <c r="C813" t="inlineStr"/>
       <c r="D813" t="inlineStr">
         <is>
-          <t>0.369M</t>
+          <t>0.317M</t>
         </is>
       </c>
       <c r="E813" t="inlineStr"/>
       <c r="F813" t="inlineStr"/>
       <c r="G813" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="814">
@@ -23730,15 +23734,11 @@
       </c>
       <c r="B817" t="inlineStr">
         <is>
-          <t>EIA Refinery Crude Runs ChangeFEB/28</t>
+          <t>EIA Crude Oil Imports ChangeFEB/28</t>
         </is>
       </c>
       <c r="C817" t="inlineStr"/>
-      <c r="D817" t="inlineStr">
-        <is>
-          <t>0.317M</t>
-        </is>
-      </c>
+      <c r="D817" t="inlineStr"/>
       <c r="E817" t="inlineStr"/>
       <c r="F817" t="inlineStr"/>
       <c r="G817" t="n">
@@ -23776,19 +23776,19 @@
       </c>
       <c r="B819" t="inlineStr">
         <is>
-          <t>EIA Crude Oil Stocks ChangeFEB/28</t>
+          <t>EIA Heating Oil Stocks ChangeFEB/28</t>
         </is>
       </c>
       <c r="C819" t="inlineStr"/>
       <c r="D819" t="inlineStr">
         <is>
-          <t>-2.332M</t>
+          <t>0.134M</t>
         </is>
       </c>
       <c r="E819" t="inlineStr"/>
       <c r="F819" t="inlineStr"/>
       <c r="G819" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="820">
@@ -23799,19 +23799,19 @@
       </c>
       <c r="B820" t="inlineStr">
         <is>
-          <t>EIA Heating Oil Stocks ChangeFEB/28</t>
+          <t>EIA Crude Oil Stocks ChangeFEB/28</t>
         </is>
       </c>
       <c r="C820" t="inlineStr"/>
       <c r="D820" t="inlineStr">
         <is>
-          <t>0.134M</t>
+          <t>-2.332M</t>
         </is>
       </c>
       <c r="E820" t="inlineStr"/>
       <c r="F820" t="inlineStr"/>
       <c r="G820" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="821">
@@ -23868,13 +23868,13 @@
       </c>
       <c r="B823" t="inlineStr">
         <is>
-          <t>17-Week Bill Auction</t>
+          <t>Total Vehicle SalesFEB</t>
         </is>
       </c>
       <c r="C823" t="inlineStr"/>
       <c r="D823" t="inlineStr">
         <is>
-          <t>4.200%</t>
+          <t>15.6M</t>
         </is>
       </c>
       <c r="E823" t="inlineStr"/>
@@ -23891,13 +23891,13 @@
       </c>
       <c r="B824" t="inlineStr">
         <is>
-          <t>Total Vehicle SalesFEB</t>
+          <t>17-Week Bill Auction</t>
         </is>
       </c>
       <c r="C824" t="inlineStr"/>
       <c r="D824" t="inlineStr">
         <is>
-          <t>15.6M</t>
+          <t>4.200%</t>
         </is>
       </c>
       <c r="E824" t="inlineStr"/>
@@ -24321,19 +24321,19 @@
       </c>
       <c r="B842" t="inlineStr">
         <is>
-          <t>ImportsJAN</t>
+          <t>Balance of TradeJAN</t>
         </is>
       </c>
       <c r="C842" t="inlineStr"/>
       <c r="D842" t="inlineStr">
         <is>
-          <t>$364.9B</t>
+          <t>$-98.4B</t>
         </is>
       </c>
       <c r="E842" t="inlineStr"/>
       <c r="F842" t="inlineStr">
         <is>
-          <t>$376.0B</t>
+          <t>$-103B</t>
         </is>
       </c>
       <c r="G842" t="n">
@@ -24348,19 +24348,19 @@
       </c>
       <c r="B843" t="inlineStr">
         <is>
-          <t>Balance of TradeJAN</t>
+          <t>ExportsJAN</t>
         </is>
       </c>
       <c r="C843" t="inlineStr"/>
       <c r="D843" t="inlineStr">
         <is>
-          <t>$-98.4B</t>
+          <t>$266.5B</t>
         </is>
       </c>
       <c r="E843" t="inlineStr"/>
       <c r="F843" t="inlineStr">
         <is>
-          <t>$-103B</t>
+          <t>$273.0B</t>
         </is>
       </c>
       <c r="G843" t="n">
@@ -24375,19 +24375,19 @@
       </c>
       <c r="B844" t="inlineStr">
         <is>
-          <t>ExportsJAN</t>
+          <t>ImportsJAN</t>
         </is>
       </c>
       <c r="C844" t="inlineStr"/>
       <c r="D844" t="inlineStr">
         <is>
-          <t>$266.5B</t>
+          <t>$364.9B</t>
         </is>
       </c>
       <c r="E844" t="inlineStr"/>
       <c r="F844" t="inlineStr">
         <is>
-          <t>$273.0B</t>
+          <t>$376.0B</t>
         </is>
       </c>
       <c r="G844" t="n">
@@ -24516,7 +24516,7 @@
       </c>
       <c r="B851" t="inlineStr">
         <is>
-          <t>8-Week Bill Auction</t>
+          <t>4-Week Bill Auction</t>
         </is>
       </c>
       <c r="C851" t="inlineStr"/>
@@ -24535,7 +24535,7 @@
       </c>
       <c r="B852" t="inlineStr">
         <is>
-          <t>4-Week Bill Auction</t>
+          <t>8-Week Bill Auction</t>
         </is>
       </c>
       <c r="C852" t="inlineStr"/>
@@ -24830,23 +24830,23 @@
       </c>
       <c r="B865" t="inlineStr">
         <is>
-          <t>Government PayrollsFEB</t>
+          <t>Average Hourly Earnings MoMFEB</t>
         </is>
       </c>
       <c r="C865" t="inlineStr"/>
       <c r="D865" t="inlineStr">
         <is>
-          <t>32K</t>
+          <t>0.5%</t>
         </is>
       </c>
       <c r="E865" t="inlineStr"/>
       <c r="F865" t="inlineStr">
         <is>
-          <t>-20.0K</t>
+          <t>0.3%</t>
         </is>
       </c>
       <c r="G865" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="866">
@@ -24911,23 +24911,23 @@
       </c>
       <c r="B868" t="inlineStr">
         <is>
-          <t>Non Farm PayrollsFEB</t>
+          <t>U-6 Unemployment RateFEB</t>
         </is>
       </c>
       <c r="C868" t="inlineStr"/>
       <c r="D868" t="inlineStr">
         <is>
-          <t>143K</t>
+          <t>7.5%</t>
         </is>
       </c>
       <c r="E868" t="inlineStr"/>
       <c r="F868" t="inlineStr">
         <is>
-          <t>180.0K</t>
+          <t>7.6%</t>
         </is>
       </c>
       <c r="G868" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="869">
@@ -24938,19 +24938,23 @@
       </c>
       <c r="B869" t="inlineStr">
         <is>
-          <t>Used Car Prices YoYFEB</t>
+          <t>Average Hourly Earnings YoYFEB</t>
         </is>
       </c>
       <c r="C869" t="inlineStr"/>
       <c r="D869" t="inlineStr">
         <is>
-          <t>0.8%</t>
+          <t>4.1%</t>
         </is>
       </c>
       <c r="E869" t="inlineStr"/>
-      <c r="F869" t="inlineStr"/>
+      <c r="F869" t="inlineStr">
+        <is>
+          <t>4.1%</t>
+        </is>
+      </c>
       <c r="G869" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="870">
@@ -24961,23 +24965,23 @@
       </c>
       <c r="B870" t="inlineStr">
         <is>
-          <t>Unemployment RateFEB</t>
+          <t>Government PayrollsFEB</t>
         </is>
       </c>
       <c r="C870" t="inlineStr"/>
       <c r="D870" t="inlineStr">
         <is>
-          <t>4%</t>
+          <t>32K</t>
         </is>
       </c>
       <c r="E870" t="inlineStr"/>
       <c r="F870" t="inlineStr">
         <is>
-          <t>4.0%</t>
+          <t>-20.0K</t>
         </is>
       </c>
       <c r="G870" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="871">
@@ -25038,23 +25042,23 @@
       </c>
       <c r="B873" t="inlineStr">
         <is>
-          <t>Average Hourly Earnings YoYFEB</t>
+          <t>Unemployment RateFEB</t>
         </is>
       </c>
       <c r="C873" t="inlineStr"/>
       <c r="D873" t="inlineStr">
         <is>
-          <t>4.1%</t>
+          <t>4%</t>
         </is>
       </c>
       <c r="E873" t="inlineStr"/>
       <c r="F873" t="inlineStr">
         <is>
-          <t>4.1%</t>
+          <t>4.0%</t>
         </is>
       </c>
       <c r="G873" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="874">
@@ -25065,23 +25069,23 @@
       </c>
       <c r="B874" t="inlineStr">
         <is>
-          <t>U-6 Unemployment RateFEB</t>
+          <t>Non Farm PayrollsFEB</t>
         </is>
       </c>
       <c r="C874" t="inlineStr"/>
       <c r="D874" t="inlineStr">
         <is>
-          <t>7.5%</t>
+          <t>143K</t>
         </is>
       </c>
       <c r="E874" t="inlineStr"/>
       <c r="F874" t="inlineStr">
         <is>
-          <t>7.6%</t>
+          <t>180.0K</t>
         </is>
       </c>
       <c r="G874" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="875">
@@ -25200,23 +25204,19 @@
       </c>
       <c r="B879" t="inlineStr">
         <is>
-          <t>Average Hourly Earnings MoMFEB</t>
+          <t>Used Car Prices YoYFEB</t>
         </is>
       </c>
       <c r="C879" t="inlineStr"/>
       <c r="D879" t="inlineStr">
         <is>
-          <t>0.5%</t>
+          <t>0.8%</t>
         </is>
       </c>
       <c r="E879" t="inlineStr"/>
-      <c r="F879" t="inlineStr">
-        <is>
-          <t>0.3%</t>
-        </is>
-      </c>
+      <c r="F879" t="inlineStr"/>
       <c r="G879" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="880">

--- a/Input_data/IST_US_trad_eco_cal_2025-01-01_to_2025-03-09.xlsx
+++ b/Input_data/IST_US_trad_eco_cal_2025-01-01_to_2025-03-09.xlsx
@@ -806,27 +806,27 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>EIA Crude Oil Stocks ChangeDEC/27</t>
+          <t>EIA Distillate Stocks ChangeDEC/27</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>-1.178M</t>
+          <t>6.406M</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>-4.237M</t>
+          <t>-1.694M</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>-2.75M</t>
+          <t>-0.1M</t>
         </is>
       </c>
       <c r="F13" t="inlineStr"/>
       <c r="G13" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="14">
@@ -837,17 +837,17 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>EIA Cushing Crude Oil Stocks ChangeDEC/27</t>
+          <t>EIA Refinery Crude Runs ChangeDEC/27</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>-0.142M</t>
+          <t>0.041M</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>-0.32M</t>
+          <t>0.205M</t>
         </is>
       </c>
       <c r="E14" t="inlineStr"/>
@@ -864,17 +864,17 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>EIA Crude Oil Imports ChangeDEC/27</t>
+          <t>EIA Gasoline Production ChangeDEC/27</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>0.323M</t>
+          <t>-0.959M</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>0.995M</t>
+          <t>0.051M</t>
         </is>
       </c>
       <c r="E15" t="inlineStr"/>
@@ -891,27 +891,23 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>EIA Gasoline Stocks ChangeDEC/27</t>
+          <t>EIA Heating Oil Stocks ChangeDEC/27</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>7.717M</t>
+          <t>-0.416M</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>1.63M</t>
-        </is>
-      </c>
-      <c r="E16" t="inlineStr">
-        <is>
-          <t>0.7M</t>
-        </is>
-      </c>
+          <t>-0.062M</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr"/>
       <c r="F16" t="inlineStr"/>
       <c r="G16" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="17">
@@ -922,17 +918,17 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>EIA Distillate Fuel Production ChangeDEC/27</t>
+          <t>EIA Crude Oil Imports ChangeDEC/27</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>0.099M</t>
+          <t>0.323M</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>0.178M</t>
+          <t>0.995M</t>
         </is>
       </c>
       <c r="E17" t="inlineStr"/>
@@ -949,23 +945,27 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>EIA Heating Oil Stocks ChangeDEC/27</t>
+          <t>EIA Gasoline Stocks ChangeDEC/27</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>-0.416M</t>
+          <t>7.717M</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>-0.062M</t>
-        </is>
-      </c>
-      <c r="E18" t="inlineStr"/>
+          <t>1.63M</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>0.7M</t>
+        </is>
+      </c>
       <c r="F18" t="inlineStr"/>
       <c r="G18" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="19">
@@ -976,17 +976,17 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>EIA Gasoline Production ChangeDEC/27</t>
+          <t>EIA Cushing Crude Oil Stocks ChangeDEC/27</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>-0.959M</t>
+          <t>-0.142M</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>0.051M</t>
+          <t>-0.32M</t>
         </is>
       </c>
       <c r="E19" t="inlineStr"/>
@@ -1003,23 +1003,27 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>EIA Refinery Crude Runs ChangeDEC/27</t>
+          <t>EIA Crude Oil Stocks ChangeDEC/27</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>0.041M</t>
+          <t>-1.178M</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>0.205M</t>
-        </is>
-      </c>
-      <c r="E20" t="inlineStr"/>
+          <t>-4.237M</t>
+        </is>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>-2.75M</t>
+        </is>
+      </c>
       <c r="F20" t="inlineStr"/>
       <c r="G20" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="21">
@@ -1030,24 +1034,20 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>EIA Distillate Stocks ChangeDEC/27</t>
+          <t>EIA Distillate Fuel Production ChangeDEC/27</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>6.406M</t>
+          <t>0.099M</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>-1.694M</t>
-        </is>
-      </c>
-      <c r="E21" t="inlineStr">
-        <is>
-          <t>-0.1M</t>
-        </is>
-      </c>
+          <t>0.178M</t>
+        </is>
+      </c>
+      <c r="E21" t="inlineStr"/>
       <c r="F21" t="inlineStr"/>
       <c r="G21" t="n">
         <v>3</v>
@@ -1223,31 +1223,31 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>ISM Manufacturing PricesDEC</t>
+          <t>ISM Manufacturing PMIDEC</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>52.5</t>
+          <t>49.3</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>50.3</t>
+          <t>48.4</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>51.7</t>
+          <t>48.4</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>50.4</t>
+          <t>48.5</t>
         </is>
       </c>
       <c r="G28" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="29">
@@ -1258,27 +1258,31 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>ISM Manufacturing New OrdersDEC</t>
+          <t>ISM Manufacturing EmploymentDEC</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>52.5</t>
+          <t>45.3</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>50.4</t>
-        </is>
-      </c>
-      <c r="E29" t="inlineStr"/>
+          <t>48.1</t>
+        </is>
+      </c>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t>48</t>
+        </is>
+      </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>50.5</t>
+          <t>48.3</t>
         </is>
       </c>
       <c r="G29" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="30">
@@ -1289,31 +1293,27 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>ISM Manufacturing EmploymentDEC</t>
+          <t>ISM Manufacturing New OrdersDEC</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>45.3</t>
+          <t>52.5</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>48.1</t>
-        </is>
-      </c>
-      <c r="E30" t="inlineStr">
-        <is>
-          <t>48</t>
-        </is>
-      </c>
+          <t>50.4</t>
+        </is>
+      </c>
+      <c r="E30" t="inlineStr"/>
       <c r="F30" t="inlineStr">
         <is>
-          <t>48.3</t>
+          <t>50.5</t>
         </is>
       </c>
       <c r="G30" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="31">
@@ -1324,31 +1324,31 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>ISM Manufacturing PMIDEC</t>
+          <t>ISM Manufacturing PricesDEC</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>49.3</t>
+          <t>52.5</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>48.4</t>
+          <t>50.3</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>48.4</t>
+          <t>51.7</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>48.5</t>
+          <t>50.4</t>
         </is>
       </c>
       <c r="G31" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="32">
@@ -1609,27 +1609,31 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>Factory Orders ex TransportationNOV</t>
+          <t>Factory Orders MoMNOV</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>0.2%</t>
+          <t>-0.4%</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>0.2%</t>
-        </is>
-      </c>
-      <c r="E42" t="inlineStr"/>
+          <t>0.5%</t>
+        </is>
+      </c>
+      <c r="E42" t="inlineStr">
+        <is>
+          <t>-0.3%</t>
+        </is>
+      </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>0.2%</t>
+          <t>0.3%</t>
         </is>
       </c>
       <c r="G42" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="43">
@@ -1640,31 +1644,27 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>Factory Orders MoMNOV</t>
+          <t>Factory Orders ex TransportationNOV</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>-0.4%</t>
+          <t>0.2%</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>0.5%</t>
-        </is>
-      </c>
-      <c r="E43" t="inlineStr">
-        <is>
-          <t>-0.3%</t>
-        </is>
-      </c>
+          <t>0.2%</t>
+        </is>
+      </c>
+      <c r="E43" t="inlineStr"/>
       <c r="F43" t="inlineStr">
         <is>
-          <t>0.3%</t>
+          <t>0.2%</t>
         </is>
       </c>
       <c r="G43" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="44">
@@ -1949,31 +1949,31 @@
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>ISM Services PMIDEC</t>
+          <t>ISM Services EmploymentDEC</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>54.1</t>
+          <t>51.4</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>52.1</t>
+          <t>51.5</t>
         </is>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>53.3</t>
+          <t>51.4</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>54</t>
+          <t>52</t>
         </is>
       </c>
       <c r="G54" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="55">
@@ -1984,23 +1984,23 @@
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>ISM Services Business ActivityDEC</t>
+          <t>JOLTs Job QuitsNOV</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>58.2</t>
+          <t>3.065M</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>53.7</t>
+          <t>3.283M</t>
         </is>
       </c>
       <c r="E55" t="inlineStr"/>
       <c r="F55" t="inlineStr">
         <is>
-          <t>54.1</t>
+          <t>3.31M</t>
         </is>
       </c>
       <c r="G55" t="n">
@@ -2015,31 +2015,31 @@
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>JOLTs Job OpeningsNOV</t>
+          <t>ISM Services PricesDEC</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>8.098M</t>
+          <t>64.4</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>7.839M</t>
+          <t>58.2</t>
         </is>
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>7.70M</t>
+          <t>57.5</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>7.69M</t>
+          <t>58.4</t>
         </is>
       </c>
       <c r="G56" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="57">
@@ -2050,31 +2050,31 @@
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>ISM Services New OrdersDEC</t>
+          <t>ISM Services PMIDEC</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>54.2</t>
+          <t>54.1</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>53.7</t>
+          <t>52.1</t>
         </is>
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>54.2</t>
+          <t>53.3</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>54.1</t>
+          <t>54</t>
         </is>
       </c>
       <c r="G57" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="58">
@@ -2085,31 +2085,31 @@
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>ISM Services PricesDEC</t>
+          <t>JOLTs Job OpeningsNOV</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>64.4</t>
+          <t>8.098M</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>58.2</t>
+          <t>7.839M</t>
         </is>
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>57.5</t>
+          <t>7.70M</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>58.4</t>
+          <t>7.69M</t>
         </is>
       </c>
       <c r="G58" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="59">
@@ -2120,27 +2120,27 @@
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>ISM Services EmploymentDEC</t>
+          <t>ISM Services New OrdersDEC</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>51.4</t>
+          <t>54.2</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>51.5</t>
+          <t>53.7</t>
         </is>
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>51.4</t>
+          <t>54.2</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>52</t>
+          <t>54.1</t>
         </is>
       </c>
       <c r="G59" t="n">
@@ -2155,23 +2155,23 @@
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>JOLTs Job QuitsNOV</t>
+          <t>ISM Services Business ActivityDEC</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>3.065M</t>
+          <t>58.2</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>3.283M</t>
+          <t>53.7</t>
         </is>
       </c>
       <c r="E60" t="inlineStr"/>
       <c r="F60" t="inlineStr">
         <is>
-          <t>3.31M</t>
+          <t>54.1</t>
         </is>
       </c>
       <c r="G60" t="n">
@@ -2441,31 +2441,31 @@
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>Continuing Jobless ClaimsDEC/28</t>
+          <t>Initial Jobless ClaimsJAN/04</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>1867K</t>
+          <t>201K</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>1834K</t>
+          <t>211K</t>
         </is>
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>1870K</t>
+          <t>218K</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>1848K</t>
+          <t>213K</t>
         </is>
       </c>
       <c r="G70" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="71">
@@ -2476,15 +2476,27 @@
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>Fed Waller Speech</t>
-        </is>
-      </c>
-      <c r="C71" t="inlineStr"/>
-      <c r="D71" t="inlineStr"/>
+          <t>Jobless Claims 4-week AverageJAN/04</t>
+        </is>
+      </c>
+      <c r="C71" t="inlineStr">
+        <is>
+          <t>213K</t>
+        </is>
+      </c>
+      <c r="D71" t="inlineStr">
+        <is>
+          <t>223.25K</t>
+        </is>
+      </c>
       <c r="E71" t="inlineStr"/>
-      <c r="F71" t="inlineStr"/>
+      <c r="F71" t="inlineStr">
+        <is>
+          <t>224K</t>
+        </is>
+      </c>
       <c r="G71" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="72">
@@ -2495,27 +2507,27 @@
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>Total Vehicle SalesDEC</t>
+          <t>Continuing Jobless ClaimsDEC/28</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>16.8M</t>
+          <t>1867K</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>16.7M</t>
+          <t>1834K</t>
         </is>
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>16.5M</t>
+          <t>1870K</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>16.3M</t>
+          <t>1848K</t>
         </is>
       </c>
       <c r="G72" t="n">
@@ -2530,27 +2542,15 @@
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>Jobless Claims 4-week AverageJAN/04</t>
-        </is>
-      </c>
-      <c r="C73" t="inlineStr">
-        <is>
-          <t>213K</t>
-        </is>
-      </c>
-      <c r="D73" t="inlineStr">
-        <is>
-          <t>223.25K</t>
-        </is>
-      </c>
+          <t>Fed Waller Speech</t>
+        </is>
+      </c>
+      <c r="C73" t="inlineStr"/>
+      <c r="D73" t="inlineStr"/>
       <c r="E73" t="inlineStr"/>
-      <c r="F73" t="inlineStr">
-        <is>
-          <t>224K</t>
-        </is>
-      </c>
+      <c r="F73" t="inlineStr"/>
       <c r="G73" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="74">
@@ -2561,31 +2561,31 @@
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>Initial Jobless ClaimsJAN/04</t>
+          <t>Total Vehicle SalesDEC</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>201K</t>
+          <t>16.8M</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>211K</t>
+          <t>16.7M</t>
         </is>
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>218K</t>
+          <t>16.5M</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>213K</t>
+          <t>16.3M</t>
         </is>
       </c>
       <c r="G74" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="75">
@@ -2685,17 +2685,17 @@
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>EIA Gasoline Production ChangeJAN/03</t>
+          <t>EIA Crude Oil Imports ChangeJAN/03</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>-0.081M</t>
+          <t>0.278M</t>
         </is>
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>-0.959M</t>
+          <t>0.323M</t>
         </is>
       </c>
       <c r="E78" t="inlineStr"/>
@@ -2712,23 +2712,27 @@
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>EIA Heating Oil Stocks ChangeJAN/03</t>
+          <t>EIA Crude Oil Stocks ChangeJAN/03</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>-0.632M</t>
+          <t>-0.959M</t>
         </is>
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>-0.416M</t>
-        </is>
-      </c>
-      <c r="E79" t="inlineStr"/>
+          <t>-1.178M</t>
+        </is>
+      </c>
+      <c r="E79" t="inlineStr">
+        <is>
+          <t>-0.6M</t>
+        </is>
+      </c>
       <c r="F79" t="inlineStr"/>
       <c r="G79" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="80">
@@ -2739,27 +2743,23 @@
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>EIA Gasoline Stocks ChangeJAN/03</t>
+          <t>EIA Distillate Fuel Production ChangeJAN/03</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>6.33M</t>
+          <t>-0.167M</t>
         </is>
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>7.717M</t>
-        </is>
-      </c>
-      <c r="E80" t="inlineStr">
-        <is>
-          <t>1.5M</t>
-        </is>
-      </c>
+          <t>0.099M</t>
+        </is>
+      </c>
+      <c r="E80" t="inlineStr"/>
       <c r="F80" t="inlineStr"/>
       <c r="G80" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="81">
@@ -2770,24 +2770,20 @@
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>EIA Distillate Stocks ChangeJAN/03</t>
+          <t>EIA Cushing Crude Oil Stocks ChangeJAN/03</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>6.071M</t>
+          <t>-2.502M</t>
         </is>
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>6.406M</t>
-        </is>
-      </c>
-      <c r="E81" t="inlineStr">
-        <is>
-          <t>1M</t>
-        </is>
-      </c>
+          <t>-0.142M</t>
+        </is>
+      </c>
+      <c r="E81" t="inlineStr"/>
       <c r="F81" t="inlineStr"/>
       <c r="G81" t="n">
         <v>3</v>
@@ -2828,23 +2824,27 @@
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>EIA Crude Oil Imports ChangeJAN/03</t>
+          <t>EIA Gasoline Stocks ChangeJAN/03</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>0.278M</t>
+          <t>6.33M</t>
         </is>
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>0.323M</t>
-        </is>
-      </c>
-      <c r="E83" t="inlineStr"/>
+          <t>7.717M</t>
+        </is>
+      </c>
+      <c r="E83" t="inlineStr">
+        <is>
+          <t>1.5M</t>
+        </is>
+      </c>
       <c r="F83" t="inlineStr"/>
       <c r="G83" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="84">
@@ -2855,17 +2855,17 @@
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>EIA Distillate Fuel Production ChangeJAN/03</t>
+          <t>EIA Heating Oil Stocks ChangeJAN/03</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>-0.167M</t>
+          <t>-0.632M</t>
         </is>
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>0.099M</t>
+          <t>-0.416M</t>
         </is>
       </c>
       <c r="E84" t="inlineStr"/>
@@ -2882,27 +2882,23 @@
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>EIA Crude Oil Stocks ChangeJAN/03</t>
+          <t>EIA Gasoline Production ChangeJAN/03</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
+          <t>-0.081M</t>
+        </is>
+      </c>
+      <c r="D85" t="inlineStr">
+        <is>
           <t>-0.959M</t>
         </is>
       </c>
-      <c r="D85" t="inlineStr">
-        <is>
-          <t>-1.178M</t>
-        </is>
-      </c>
-      <c r="E85" t="inlineStr">
-        <is>
-          <t>-0.6M</t>
-        </is>
-      </c>
+      <c r="E85" t="inlineStr"/>
       <c r="F85" t="inlineStr"/>
       <c r="G85" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="86">
@@ -2913,20 +2909,24 @@
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>EIA Cushing Crude Oil Stocks ChangeJAN/03</t>
+          <t>EIA Distillate Stocks ChangeJAN/03</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>-2.502M</t>
+          <t>6.071M</t>
         </is>
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>-0.142M</t>
-        </is>
-      </c>
-      <c r="E86" t="inlineStr"/>
+          <t>6.406M</t>
+        </is>
+      </c>
+      <c r="E86" t="inlineStr">
+        <is>
+          <t>1M</t>
+        </is>
+      </c>
       <c r="F86" t="inlineStr"/>
       <c r="G86" t="n">
         <v>3</v>
@@ -3336,31 +3336,27 @@
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>Average Hourly Earnings MoMDEC</t>
+          <t>U-6 Unemployment Rate</t>
         </is>
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>0.3%</t>
+          <t>7.5%</t>
         </is>
       </c>
       <c r="D103" t="inlineStr">
         <is>
-          <t>0.4%</t>
-        </is>
-      </c>
-      <c r="E103" t="inlineStr">
-        <is>
-          <t>0.3%</t>
-        </is>
-      </c>
+          <t>7.7%</t>
+        </is>
+      </c>
+      <c r="E103" t="inlineStr"/>
       <c r="F103" t="inlineStr">
         <is>
-          <t>0.3%</t>
+          <t>7.9%</t>
         </is>
       </c>
       <c r="G103" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="104">
@@ -3371,31 +3367,31 @@
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>Average Hourly Earnings YoY</t>
+          <t>Average Weekly HoursDEC</t>
         </is>
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>3.9%</t>
+          <t>34.3</t>
         </is>
       </c>
       <c r="D104" t="inlineStr">
         <is>
-          <t>4%</t>
+          <t>34.3</t>
         </is>
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>4%</t>
+          <t>34.3</t>
         </is>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>4%</t>
+          <t>34.3</t>
         </is>
       </c>
       <c r="G104" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="105">
@@ -3406,31 +3402,27 @@
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>Non Farm PayrollsDEC</t>
+          <t>Government PayrollsDEC</t>
         </is>
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>256K</t>
+          <t>33K</t>
         </is>
       </c>
       <c r="D105" t="inlineStr">
         <is>
-          <t>212K</t>
-        </is>
-      </c>
-      <c r="E105" t="inlineStr">
-        <is>
-          <t>160K</t>
-        </is>
-      </c>
+          <t>30K</t>
+        </is>
+      </c>
+      <c r="E105" t="inlineStr"/>
       <c r="F105" t="inlineStr">
         <is>
-          <t>200K</t>
+          <t>15K</t>
         </is>
       </c>
       <c r="G105" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="106">
@@ -3441,27 +3433,31 @@
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>Participation RateDEC</t>
+          <t>Nonfarm Payrolls PrivateDEC</t>
         </is>
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>62.5%</t>
+          <t>223K</t>
         </is>
       </c>
       <c r="D106" t="inlineStr">
         <is>
-          <t>62.5%</t>
-        </is>
-      </c>
-      <c r="E106" t="inlineStr"/>
+          <t>182K</t>
+        </is>
+      </c>
+      <c r="E106" t="inlineStr">
+        <is>
+          <t>135K</t>
+        </is>
+      </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>62.8%</t>
+          <t>185K</t>
         </is>
       </c>
       <c r="G106" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="107">
@@ -3472,31 +3468,31 @@
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>Unemployment RateDEC</t>
+          <t>Manufacturing PayrollsDEC</t>
         </is>
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>4.1%</t>
+          <t>-13K</t>
         </is>
       </c>
       <c r="D107" t="inlineStr">
         <is>
-          <t>4.2%</t>
+          <t>25K</t>
         </is>
       </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t>4.2%</t>
+          <t>5K</t>
         </is>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>4.30%</t>
+          <t>29K</t>
         </is>
       </c>
       <c r="G107" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="108">
@@ -3507,31 +3503,27 @@
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>Nonfarm Payrolls PrivateDEC</t>
+          <t>Participation RateDEC</t>
         </is>
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>223K</t>
+          <t>62.5%</t>
         </is>
       </c>
       <c r="D108" t="inlineStr">
         <is>
-          <t>182K</t>
-        </is>
-      </c>
-      <c r="E108" t="inlineStr">
-        <is>
-          <t>135K</t>
-        </is>
-      </c>
+          <t>62.5%</t>
+        </is>
+      </c>
+      <c r="E108" t="inlineStr"/>
       <c r="F108" t="inlineStr">
         <is>
-          <t>185K</t>
+          <t>62.8%</t>
         </is>
       </c>
       <c r="G108" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="109">
@@ -3542,27 +3534,31 @@
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>Government PayrollsDEC</t>
+          <t>Non Farm PayrollsDEC</t>
         </is>
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>33K</t>
+          <t>256K</t>
         </is>
       </c>
       <c r="D109" t="inlineStr">
         <is>
-          <t>30K</t>
-        </is>
-      </c>
-      <c r="E109" t="inlineStr"/>
+          <t>212K</t>
+        </is>
+      </c>
+      <c r="E109" t="inlineStr">
+        <is>
+          <t>160K</t>
+        </is>
+      </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>15K</t>
+          <t>200K</t>
         </is>
       </c>
       <c r="G109" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="110">
@@ -3573,31 +3569,31 @@
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>Average Weekly HoursDEC</t>
+          <t>Average Hourly Earnings YoY</t>
         </is>
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>34.3</t>
+          <t>3.9%</t>
         </is>
       </c>
       <c r="D110" t="inlineStr">
         <is>
-          <t>34.3</t>
+          <t>4%</t>
         </is>
       </c>
       <c r="E110" t="inlineStr">
         <is>
-          <t>34.3</t>
+          <t>4%</t>
         </is>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>34.3</t>
+          <t>4%</t>
         </is>
       </c>
       <c r="G110" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="111">
@@ -3608,27 +3604,31 @@
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>U-6 Unemployment Rate</t>
+          <t>Average Hourly Earnings MoMDEC</t>
         </is>
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>7.5%</t>
+          <t>0.3%</t>
         </is>
       </c>
       <c r="D111" t="inlineStr">
         <is>
-          <t>7.7%</t>
-        </is>
-      </c>
-      <c r="E111" t="inlineStr"/>
+          <t>0.4%</t>
+        </is>
+      </c>
+      <c r="E111" t="inlineStr">
+        <is>
+          <t>0.3%</t>
+        </is>
+      </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>7.9%</t>
+          <t>0.3%</t>
         </is>
       </c>
       <c r="G111" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="112">
@@ -3639,31 +3639,31 @@
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>Manufacturing PayrollsDEC</t>
+          <t>Unemployment RateDEC</t>
         </is>
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>-13K</t>
+          <t>4.1%</t>
         </is>
       </c>
       <c r="D112" t="inlineStr">
         <is>
-          <t>25K</t>
+          <t>4.2%</t>
         </is>
       </c>
       <c r="E112" t="inlineStr">
         <is>
-          <t>5K</t>
+          <t>4.2%</t>
         </is>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>29K</t>
+          <t>4.30%</t>
         </is>
       </c>
       <c r="G112" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="113">
@@ -3833,19 +3833,11 @@
       </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t>Quarterly Grain Stocks - SoyDEC</t>
-        </is>
-      </c>
-      <c r="C118" t="inlineStr">
-        <is>
-          <t>3.1B</t>
-        </is>
-      </c>
-      <c r="D118" t="inlineStr">
-        <is>
-          <t>0.342B</t>
-        </is>
-      </c>
+          <t>WASDE Report</t>
+        </is>
+      </c>
+      <c r="C118" t="inlineStr"/>
+      <c r="D118" t="inlineStr"/>
       <c r="E118" t="inlineStr"/>
       <c r="F118" t="inlineStr"/>
       <c r="G118" t="n">
@@ -3860,17 +3852,17 @@
       </c>
       <c r="B119" t="inlineStr">
         <is>
-          <t>Quarterly Grain Stocks - CornDEC</t>
+          <t>Quarterly Grain Stocks - WheatDEC</t>
         </is>
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>12.074B</t>
+          <t>1.57B</t>
         </is>
       </c>
       <c r="D119" t="inlineStr">
         <is>
-          <t>1.760B</t>
+          <t>1.98B</t>
         </is>
       </c>
       <c r="E119" t="inlineStr"/>
@@ -3887,17 +3879,17 @@
       </c>
       <c r="B120" t="inlineStr">
         <is>
-          <t>Quarterly Grain Stocks - WheatDEC</t>
+          <t>Quarterly Grain Stocks - CornDEC</t>
         </is>
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>1.57B</t>
+          <t>12.074B</t>
         </is>
       </c>
       <c r="D120" t="inlineStr">
         <is>
-          <t>1.98B</t>
+          <t>1.760B</t>
         </is>
       </c>
       <c r="E120" t="inlineStr"/>
@@ -3914,11 +3906,19 @@
       </c>
       <c r="B121" t="inlineStr">
         <is>
-          <t>WASDE Report</t>
-        </is>
-      </c>
-      <c r="C121" t="inlineStr"/>
-      <c r="D121" t="inlineStr"/>
+          <t>Quarterly Grain Stocks - SoyDEC</t>
+        </is>
+      </c>
+      <c r="C121" t="inlineStr">
+        <is>
+          <t>3.1B</t>
+        </is>
+      </c>
+      <c r="D121" t="inlineStr">
+        <is>
+          <t>0.342B</t>
+        </is>
+      </c>
       <c r="E121" t="inlineStr"/>
       <c r="F121" t="inlineStr"/>
       <c r="G121" t="n">
@@ -4134,27 +4134,27 @@
       </c>
       <c r="B129" t="inlineStr">
         <is>
-          <t>PPI YoYDEC</t>
+          <t>PPI Ex Food, Energy and Trade MoMDEC</t>
         </is>
       </c>
       <c r="C129" t="inlineStr">
         <is>
-          <t>3.3%</t>
+          <t>0.1%</t>
         </is>
       </c>
       <c r="D129" t="inlineStr">
         <is>
-          <t>3%</t>
+          <t>0.1%</t>
         </is>
       </c>
       <c r="E129" t="inlineStr">
         <is>
-          <t>3.4%</t>
+          <t>0.3%</t>
         </is>
       </c>
       <c r="F129" t="inlineStr">
         <is>
-          <t>3.3%</t>
+          <t>0.2%</t>
         </is>
       </c>
       <c r="G129" t="n">
@@ -4169,31 +4169,27 @@
       </c>
       <c r="B130" t="inlineStr">
         <is>
-          <t>PPI MoMDEC</t>
+          <t>PPI Ex Food, Energy and Trade YoYDEC</t>
         </is>
       </c>
       <c r="C130" t="inlineStr">
         <is>
-          <t>0.2%</t>
+          <t>3.3%</t>
         </is>
       </c>
       <c r="D130" t="inlineStr">
         <is>
-          <t>0.4%</t>
-        </is>
-      </c>
-      <c r="E130" t="inlineStr">
-        <is>
-          <t>0.3%</t>
-        </is>
-      </c>
+          <t>3.5%</t>
+        </is>
+      </c>
+      <c r="E130" t="inlineStr"/>
       <c r="F130" t="inlineStr">
         <is>
-          <t>0.3%</t>
+          <t>3.6%</t>
         </is>
       </c>
       <c r="G130" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="131">
@@ -4204,23 +4200,27 @@
       </c>
       <c r="B131" t="inlineStr">
         <is>
-          <t>PPIDEC</t>
+          <t>Core PPI YoYDEC</t>
         </is>
       </c>
       <c r="C131" t="inlineStr">
         <is>
-          <t>146.842</t>
+          <t>3.5%</t>
         </is>
       </c>
       <c r="D131" t="inlineStr">
         <is>
-          <t>146.521</t>
-        </is>
-      </c>
-      <c r="E131" t="inlineStr"/>
+          <t>3.5%</t>
+        </is>
+      </c>
+      <c r="E131" t="inlineStr">
+        <is>
+          <t>3.8%</t>
+        </is>
+      </c>
       <c r="F131" t="inlineStr">
         <is>
-          <t>146.8</t>
+          <t>3.5%</t>
         </is>
       </c>
       <c r="G131" t="n">
@@ -4235,31 +4235,31 @@
       </c>
       <c r="B132" t="inlineStr">
         <is>
-          <t>Core PPI YoYDEC</t>
+          <t>Core PPI MoMDEC</t>
         </is>
       </c>
       <c r="C132" t="inlineStr">
         <is>
-          <t>3.5%</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="D132" t="inlineStr">
         <is>
-          <t>3.5%</t>
+          <t>0.2%</t>
         </is>
       </c>
       <c r="E132" t="inlineStr">
         <is>
-          <t>3.8%</t>
+          <t>0.3%</t>
         </is>
       </c>
       <c r="F132" t="inlineStr">
         <is>
-          <t>3.5%</t>
+          <t>0.2%</t>
         </is>
       </c>
       <c r="G132" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="133">
@@ -4270,27 +4270,31 @@
       </c>
       <c r="B133" t="inlineStr">
         <is>
-          <t>PPI Ex Food, Energy and Trade YoYDEC</t>
+          <t>PPI MoMDEC</t>
         </is>
       </c>
       <c r="C133" t="inlineStr">
         <is>
-          <t>3.3%</t>
+          <t>0.2%</t>
         </is>
       </c>
       <c r="D133" t="inlineStr">
         <is>
-          <t>3.5%</t>
-        </is>
-      </c>
-      <c r="E133" t="inlineStr"/>
+          <t>0.4%</t>
+        </is>
+      </c>
+      <c r="E133" t="inlineStr">
+        <is>
+          <t>0.3%</t>
+        </is>
+      </c>
       <c r="F133" t="inlineStr">
         <is>
-          <t>3.6%</t>
+          <t>0.3%</t>
         </is>
       </c>
       <c r="G133" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="134">
@@ -4301,31 +4305,31 @@
       </c>
       <c r="B134" t="inlineStr">
         <is>
-          <t>Core PPI MoMDEC</t>
+          <t>PPI YoYDEC</t>
         </is>
       </c>
       <c r="C134" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>3.3%</t>
         </is>
       </c>
       <c r="D134" t="inlineStr">
         <is>
-          <t>0.2%</t>
+          <t>3%</t>
         </is>
       </c>
       <c r="E134" t="inlineStr">
         <is>
-          <t>0.3%</t>
+          <t>3.4%</t>
         </is>
       </c>
       <c r="F134" t="inlineStr">
         <is>
-          <t>0.2%</t>
+          <t>3.3%</t>
         </is>
       </c>
       <c r="G134" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="135">
@@ -4336,27 +4340,23 @@
       </c>
       <c r="B135" t="inlineStr">
         <is>
-          <t>PPI Ex Food, Energy and Trade MoMDEC</t>
+          <t>PPIDEC</t>
         </is>
       </c>
       <c r="C135" t="inlineStr">
         <is>
-          <t>0.1%</t>
+          <t>146.842</t>
         </is>
       </c>
       <c r="D135" t="inlineStr">
         <is>
-          <t>0.1%</t>
-        </is>
-      </c>
-      <c r="E135" t="inlineStr">
-        <is>
-          <t>0.3%</t>
-        </is>
-      </c>
+          <t>146.521</t>
+        </is>
+      </c>
+      <c r="E135" t="inlineStr"/>
       <c r="F135" t="inlineStr">
         <is>
-          <t>0.2%</t>
+          <t>146.8</t>
         </is>
       </c>
       <c r="G135" t="n">
@@ -4564,23 +4564,23 @@
       </c>
       <c r="B143" t="inlineStr">
         <is>
-          <t>MBA Mortgage Market IndexJAN/10</t>
+          <t>MBA 30-Year Mortgage RateJAN/10</t>
         </is>
       </c>
       <c r="C143" t="inlineStr">
         <is>
-          <t>224.4</t>
+          <t>7.09%</t>
         </is>
       </c>
       <c r="D143" t="inlineStr">
         <is>
-          <t>168.4</t>
+          <t>6.99%</t>
         </is>
       </c>
       <c r="E143" t="inlineStr"/>
       <c r="F143" t="inlineStr"/>
       <c r="G143" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="144">
@@ -4591,17 +4591,17 @@
       </c>
       <c r="B144" t="inlineStr">
         <is>
-          <t>MBA Mortgage Refinance IndexJAN/10</t>
+          <t>MBA Mortgage ApplicationsJAN/10</t>
         </is>
       </c>
       <c r="C144" t="inlineStr">
         <is>
-          <t>575.6</t>
+          <t>33.3%</t>
         </is>
       </c>
       <c r="D144" t="inlineStr">
         <is>
-          <t>401.1000</t>
+          <t>-3.7%</t>
         </is>
       </c>
       <c r="E144" t="inlineStr"/>
@@ -4618,17 +4618,17 @@
       </c>
       <c r="B145" t="inlineStr">
         <is>
-          <t>MBA Mortgage ApplicationsJAN/10</t>
+          <t>MBA Purchase IndexJAN/10</t>
         </is>
       </c>
       <c r="C145" t="inlineStr">
         <is>
-          <t>33.3%</t>
+          <t>162</t>
         </is>
       </c>
       <c r="D145" t="inlineStr">
         <is>
-          <t>-3.7%</t>
+          <t>127.7000</t>
         </is>
       </c>
       <c r="E145" t="inlineStr"/>
@@ -4645,17 +4645,17 @@
       </c>
       <c r="B146" t="inlineStr">
         <is>
-          <t>MBA Purchase IndexJAN/10</t>
+          <t>MBA Mortgage Market IndexJAN/10</t>
         </is>
       </c>
       <c r="C146" t="inlineStr">
         <is>
-          <t>162</t>
+          <t>224.4</t>
         </is>
       </c>
       <c r="D146" t="inlineStr">
         <is>
-          <t>127.7000</t>
+          <t>168.4</t>
         </is>
       </c>
       <c r="E146" t="inlineStr"/>
@@ -4672,23 +4672,23 @@
       </c>
       <c r="B147" t="inlineStr">
         <is>
-          <t>MBA 30-Year Mortgage RateJAN/10</t>
+          <t>MBA Mortgage Refinance IndexJAN/10</t>
         </is>
       </c>
       <c r="C147" t="inlineStr">
         <is>
-          <t>7.09%</t>
+          <t>575.6</t>
         </is>
       </c>
       <c r="D147" t="inlineStr">
         <is>
-          <t>6.99%</t>
+          <t>401.1000</t>
         </is>
       </c>
       <c r="E147" t="inlineStr"/>
       <c r="F147" t="inlineStr"/>
       <c r="G147" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="148">
@@ -4978,27 +4978,23 @@
       </c>
       <c r="B157" t="inlineStr">
         <is>
-          <t>EIA Gasoline Stocks ChangeJAN/10</t>
+          <t>EIA Gasoline Production ChangeJAN/10</t>
         </is>
       </c>
       <c r="C157" t="inlineStr">
         <is>
-          <t>5.852M</t>
+          <t>0.397M</t>
         </is>
       </c>
       <c r="D157" t="inlineStr">
         <is>
-          <t>6.33M</t>
-        </is>
-      </c>
-      <c r="E157" t="inlineStr">
-        <is>
-          <t>2.60M</t>
-        </is>
-      </c>
+          <t>-0.081M</t>
+        </is>
+      </c>
+      <c r="E157" t="inlineStr"/>
       <c r="F157" t="inlineStr"/>
       <c r="G157" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="158">
@@ -5009,17 +5005,17 @@
       </c>
       <c r="B158" t="inlineStr">
         <is>
-          <t>EIA Refinery Crude Runs ChangeJAN/10</t>
+          <t>EIA Crude Oil Imports ChangeJAN/10</t>
         </is>
       </c>
       <c r="C158" t="inlineStr">
         <is>
-          <t>-0.255M</t>
+          <t>-1.304M</t>
         </is>
       </c>
       <c r="D158" t="inlineStr">
         <is>
-          <t>0.045M</t>
+          <t>0.278M</t>
         </is>
       </c>
       <c r="E158" t="inlineStr"/>
@@ -5036,23 +5032,27 @@
       </c>
       <c r="B159" t="inlineStr">
         <is>
-          <t>EIA Heating Oil Stocks ChangeJAN/10</t>
+          <t>EIA Crude Oil Stocks ChangeJAN/10</t>
         </is>
       </c>
       <c r="C159" t="inlineStr">
         <is>
-          <t>0.646M</t>
+          <t>-1.961M</t>
         </is>
       </c>
       <c r="D159" t="inlineStr">
         <is>
-          <t>-0.632M</t>
-        </is>
-      </c>
-      <c r="E159" t="inlineStr"/>
+          <t>-0.959M</t>
+        </is>
+      </c>
+      <c r="E159" t="inlineStr">
+        <is>
+          <t>-1.6M</t>
+        </is>
+      </c>
       <c r="F159" t="inlineStr"/>
       <c r="G159" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="160">
@@ -5063,17 +5063,17 @@
       </c>
       <c r="B160" t="inlineStr">
         <is>
-          <t>EIA Cushing Crude Oil Stocks ChangeJAN/10</t>
+          <t>EIA Distillate Fuel Production ChangeJAN/10</t>
         </is>
       </c>
       <c r="C160" t="inlineStr">
         <is>
-          <t>0.765M</t>
+          <t>-0.021M</t>
         </is>
       </c>
       <c r="D160" t="inlineStr">
         <is>
-          <t>-2.502M</t>
+          <t>-0.167M</t>
         </is>
       </c>
       <c r="E160" t="inlineStr"/>
@@ -5090,20 +5090,24 @@
       </c>
       <c r="B161" t="inlineStr">
         <is>
-          <t>EIA Distillate Fuel Production ChangeJAN/10</t>
+          <t>EIA Distillate Stocks ChangeJAN/10</t>
         </is>
       </c>
       <c r="C161" t="inlineStr">
         <is>
-          <t>-0.021M</t>
+          <t>3.077M</t>
         </is>
       </c>
       <c r="D161" t="inlineStr">
         <is>
-          <t>-0.167M</t>
-        </is>
-      </c>
-      <c r="E161" t="inlineStr"/>
+          <t>6.071M</t>
+        </is>
+      </c>
+      <c r="E161" t="inlineStr">
+        <is>
+          <t>1.1M</t>
+        </is>
+      </c>
       <c r="F161" t="inlineStr"/>
       <c r="G161" t="n">
         <v>3</v>
@@ -5117,17 +5121,17 @@
       </c>
       <c r="B162" t="inlineStr">
         <is>
-          <t>EIA Gasoline Production ChangeJAN/10</t>
+          <t>EIA Heating Oil Stocks ChangeJAN/10</t>
         </is>
       </c>
       <c r="C162" t="inlineStr">
         <is>
-          <t>0.397M</t>
+          <t>0.646M</t>
         </is>
       </c>
       <c r="D162" t="inlineStr">
         <is>
-          <t>-0.081M</t>
+          <t>-0.632M</t>
         </is>
       </c>
       <c r="E162" t="inlineStr"/>
@@ -5144,22 +5148,22 @@
       </c>
       <c r="B163" t="inlineStr">
         <is>
-          <t>EIA Crude Oil Stocks ChangeJAN/10</t>
+          <t>EIA Gasoline Stocks ChangeJAN/10</t>
         </is>
       </c>
       <c r="C163" t="inlineStr">
         <is>
-          <t>-1.961M</t>
+          <t>5.852M</t>
         </is>
       </c>
       <c r="D163" t="inlineStr">
         <is>
-          <t>-0.959M</t>
+          <t>6.33M</t>
         </is>
       </c>
       <c r="E163" t="inlineStr">
         <is>
-          <t>-1.6M</t>
+          <t>2.60M</t>
         </is>
       </c>
       <c r="F163" t="inlineStr"/>
@@ -5175,17 +5179,17 @@
       </c>
       <c r="B164" t="inlineStr">
         <is>
-          <t>EIA Crude Oil Imports ChangeJAN/10</t>
+          <t>EIA Cushing Crude Oil Stocks ChangeJAN/10</t>
         </is>
       </c>
       <c r="C164" t="inlineStr">
         <is>
-          <t>-1.304M</t>
+          <t>0.765M</t>
         </is>
       </c>
       <c r="D164" t="inlineStr">
         <is>
-          <t>0.278M</t>
+          <t>-2.502M</t>
         </is>
       </c>
       <c r="E164" t="inlineStr"/>
@@ -5202,24 +5206,20 @@
       </c>
       <c r="B165" t="inlineStr">
         <is>
-          <t>EIA Distillate Stocks ChangeJAN/10</t>
+          <t>EIA Refinery Crude Runs ChangeJAN/10</t>
         </is>
       </c>
       <c r="C165" t="inlineStr">
         <is>
-          <t>3.077M</t>
+          <t>-0.255M</t>
         </is>
       </c>
       <c r="D165" t="inlineStr">
         <is>
-          <t>6.071M</t>
-        </is>
-      </c>
-      <c r="E165" t="inlineStr">
-        <is>
-          <t>1.1M</t>
-        </is>
-      </c>
+          <t>0.045M</t>
+        </is>
+      </c>
+      <c r="E165" t="inlineStr"/>
       <c r="F165" t="inlineStr"/>
       <c r="G165" t="n">
         <v>3</v>
@@ -5336,31 +5336,31 @@
       </c>
       <c r="B171" t="inlineStr">
         <is>
-          <t>Retail Sales MoMDEC</t>
+          <t>Import Prices YoYDEC</t>
         </is>
       </c>
       <c r="C171" t="inlineStr">
         <is>
-          <t>0.4%</t>
+          <t>2.2%</t>
         </is>
       </c>
       <c r="D171" t="inlineStr">
         <is>
-          <t>0.8%</t>
+          <t>1.4%</t>
         </is>
       </c>
       <c r="E171" t="inlineStr">
         <is>
-          <t>0.6%</t>
+          <t>2.1%</t>
         </is>
       </c>
       <c r="F171" t="inlineStr">
         <is>
-          <t>0.5%</t>
+          <t>1.6%</t>
         </is>
       </c>
       <c r="G171" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="172">
@@ -5371,31 +5371,23 @@
       </c>
       <c r="B172" t="inlineStr">
         <is>
-          <t>Export Prices MoMDEC</t>
+          <t>Philly Fed EmploymentJAN</t>
         </is>
       </c>
       <c r="C172" t="inlineStr">
         <is>
-          <t>0.3%</t>
+          <t>11.9</t>
         </is>
       </c>
       <c r="D172" t="inlineStr">
         <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="E172" t="inlineStr">
-        <is>
-          <t>0.2%</t>
-        </is>
-      </c>
-      <c r="F172" t="inlineStr">
-        <is>
-          <t>0.5%</t>
-        </is>
-      </c>
+          <t>4.8</t>
+        </is>
+      </c>
+      <c r="E172" t="inlineStr"/>
+      <c r="F172" t="inlineStr"/>
       <c r="G172" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="173">
@@ -5406,31 +5398,31 @@
       </c>
       <c r="B173" t="inlineStr">
         <is>
-          <t>Initial Jobless ClaimsJAN/11</t>
+          <t>Continuing Jobless ClaimsJAN/04</t>
         </is>
       </c>
       <c r="C173" t="inlineStr">
         <is>
-          <t>217K</t>
+          <t>1859K</t>
         </is>
       </c>
       <c r="D173" t="inlineStr">
         <is>
-          <t>203K</t>
+          <t>1867K</t>
         </is>
       </c>
       <c r="E173" t="inlineStr">
         <is>
-          <t>210K</t>
+          <t>1870K</t>
         </is>
       </c>
       <c r="F173" t="inlineStr">
         <is>
-          <t>209.0K</t>
+          <t>1870.0K</t>
         </is>
       </c>
       <c r="G173" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="174">
@@ -5441,31 +5433,31 @@
       </c>
       <c r="B174" t="inlineStr">
         <is>
-          <t>Retail Sales Ex Autos MoMDEC</t>
+          <t>Retail Sales Ex Gas/Autos MoMDEC</t>
         </is>
       </c>
       <c r="C174" t="inlineStr">
         <is>
+          <t>0.3%</t>
+        </is>
+      </c>
+      <c r="D174" t="inlineStr">
+        <is>
+          <t>0.2%</t>
+        </is>
+      </c>
+      <c r="E174" t="inlineStr">
+        <is>
           <t>0.4%</t>
         </is>
       </c>
-      <c r="D174" t="inlineStr">
-        <is>
-          <t>0.2%</t>
-        </is>
-      </c>
-      <c r="E174" t="inlineStr">
+      <c r="F174" t="inlineStr">
         <is>
           <t>0.4%</t>
         </is>
       </c>
-      <c r="F174" t="inlineStr">
-        <is>
-          <t>0.4%</t>
-        </is>
-      </c>
       <c r="G174" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="175">
@@ -5476,17 +5468,17 @@
       </c>
       <c r="B175" t="inlineStr">
         <is>
-          <t>Philly Fed Prices PaidJAN</t>
+          <t>Philly Fed New OrdersJAN</t>
         </is>
       </c>
       <c r="C175" t="inlineStr">
         <is>
-          <t>31.90</t>
+          <t>42.9</t>
         </is>
       </c>
       <c r="D175" t="inlineStr">
         <is>
-          <t>26.60</t>
+          <t>-3.6</t>
         </is>
       </c>
       <c r="E175" t="inlineStr"/>
@@ -5503,21 +5495,25 @@
       </c>
       <c r="B176" t="inlineStr">
         <is>
-          <t>Philly Fed Business ConditionsJAN</t>
+          <t>Jobless Claims 4-week AverageJAN/11</t>
         </is>
       </c>
       <c r="C176" t="inlineStr">
         <is>
-          <t>46.3</t>
+          <t>212.75K</t>
         </is>
       </c>
       <c r="D176" t="inlineStr">
         <is>
-          <t>33.8</t>
+          <t>213.5K</t>
         </is>
       </c>
       <c r="E176" t="inlineStr"/>
-      <c r="F176" t="inlineStr"/>
+      <c r="F176" t="inlineStr">
+        <is>
+          <t>215.0K</t>
+        </is>
+      </c>
       <c r="G176" t="n">
         <v>3</v>
       </c>
@@ -5530,23 +5526,31 @@
       </c>
       <c r="B177" t="inlineStr">
         <is>
-          <t>Philly Fed CAPEX IndexJAN</t>
+          <t>Import Prices MoMDEC</t>
         </is>
       </c>
       <c r="C177" t="inlineStr">
         <is>
-          <t>39.00</t>
+          <t>0.1%</t>
         </is>
       </c>
       <c r="D177" t="inlineStr">
         <is>
-          <t>22.20</t>
-        </is>
-      </c>
-      <c r="E177" t="inlineStr"/>
-      <c r="F177" t="inlineStr"/>
+          <t>0.1%</t>
+        </is>
+      </c>
+      <c r="E177" t="inlineStr">
+        <is>
+          <t>0.1%</t>
+        </is>
+      </c>
+      <c r="F177" t="inlineStr">
+        <is>
+          <t>0.1%</t>
+        </is>
+      </c>
       <c r="G177" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="178">
@@ -5557,27 +5561,23 @@
       </c>
       <c r="B178" t="inlineStr">
         <is>
-          <t>Import Prices YoYDEC</t>
+          <t>Export Prices YoYDEC</t>
         </is>
       </c>
       <c r="C178" t="inlineStr">
         <is>
-          <t>2.2%</t>
+          <t>1.8%</t>
         </is>
       </c>
       <c r="D178" t="inlineStr">
         <is>
-          <t>1.4%</t>
-        </is>
-      </c>
-      <c r="E178" t="inlineStr">
-        <is>
-          <t>2.1%</t>
-        </is>
-      </c>
+          <t>0.9%</t>
+        </is>
+      </c>
+      <c r="E178" t="inlineStr"/>
       <c r="F178" t="inlineStr">
         <is>
-          <t>1.6%</t>
+          <t>1.9%</t>
         </is>
       </c>
       <c r="G178" t="n">
@@ -5592,27 +5592,31 @@
       </c>
       <c r="B179" t="inlineStr">
         <is>
-          <t>Retail Sales YoYDEC</t>
+          <t>Philadelphia Fed Manufacturing IndexJAN</t>
         </is>
       </c>
       <c r="C179" t="inlineStr">
         <is>
-          <t>3.9%</t>
+          <t>44.3</t>
         </is>
       </c>
       <c r="D179" t="inlineStr">
         <is>
-          <t>4.1%</t>
-        </is>
-      </c>
-      <c r="E179" t="inlineStr"/>
+          <t>-10.9</t>
+        </is>
+      </c>
+      <c r="E179" t="inlineStr">
+        <is>
+          <t>-5</t>
+        </is>
+      </c>
       <c r="F179" t="inlineStr">
         <is>
-          <t>4.0%</t>
+          <t>-10</t>
         </is>
       </c>
       <c r="G179" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="180">
@@ -5623,31 +5627,23 @@
       </c>
       <c r="B180" t="inlineStr">
         <is>
-          <t>Philadelphia Fed Manufacturing IndexJAN</t>
+          <t>Philly Fed CAPEX IndexJAN</t>
         </is>
       </c>
       <c r="C180" t="inlineStr">
         <is>
-          <t>44.3</t>
+          <t>39.00</t>
         </is>
       </c>
       <c r="D180" t="inlineStr">
         <is>
-          <t>-10.9</t>
-        </is>
-      </c>
-      <c r="E180" t="inlineStr">
-        <is>
-          <t>-5</t>
-        </is>
-      </c>
-      <c r="F180" t="inlineStr">
-        <is>
-          <t>-10</t>
-        </is>
-      </c>
+          <t>22.20</t>
+        </is>
+      </c>
+      <c r="E180" t="inlineStr"/>
+      <c r="F180" t="inlineStr"/>
       <c r="G180" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="181">
@@ -5658,25 +5654,21 @@
       </c>
       <c r="B181" t="inlineStr">
         <is>
-          <t>Export Prices YoYDEC</t>
+          <t>Philly Fed Business ConditionsJAN</t>
         </is>
       </c>
       <c r="C181" t="inlineStr">
         <is>
-          <t>1.8%</t>
+          <t>46.3</t>
         </is>
       </c>
       <c r="D181" t="inlineStr">
         <is>
-          <t>0.9%</t>
+          <t>33.8</t>
         </is>
       </c>
       <c r="E181" t="inlineStr"/>
-      <c r="F181" t="inlineStr">
-        <is>
-          <t>1.9%</t>
-        </is>
-      </c>
+      <c r="F181" t="inlineStr"/>
       <c r="G181" t="n">
         <v>3</v>
       </c>
@@ -5689,31 +5681,23 @@
       </c>
       <c r="B182" t="inlineStr">
         <is>
-          <t>Import Prices MoMDEC</t>
+          <t>Philly Fed Prices PaidJAN</t>
         </is>
       </c>
       <c r="C182" t="inlineStr">
         <is>
-          <t>0.1%</t>
+          <t>31.90</t>
         </is>
       </c>
       <c r="D182" t="inlineStr">
         <is>
-          <t>0.1%</t>
-        </is>
-      </c>
-      <c r="E182" t="inlineStr">
-        <is>
-          <t>0.1%</t>
-        </is>
-      </c>
-      <c r="F182" t="inlineStr">
-        <is>
-          <t>0.1%</t>
-        </is>
-      </c>
+          <t>26.60</t>
+        </is>
+      </c>
+      <c r="E182" t="inlineStr"/>
+      <c r="F182" t="inlineStr"/>
       <c r="G182" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="183">
@@ -5724,27 +5708,31 @@
       </c>
       <c r="B183" t="inlineStr">
         <is>
-          <t>Jobless Claims 4-week AverageJAN/11</t>
+          <t>Retail Sales Ex Autos MoMDEC</t>
         </is>
       </c>
       <c r="C183" t="inlineStr">
         <is>
-          <t>212.75K</t>
+          <t>0.4%</t>
         </is>
       </c>
       <c r="D183" t="inlineStr">
         <is>
-          <t>213.5K</t>
-        </is>
-      </c>
-      <c r="E183" t="inlineStr"/>
+          <t>0.2%</t>
+        </is>
+      </c>
+      <c r="E183" t="inlineStr">
+        <is>
+          <t>0.4%</t>
+        </is>
+      </c>
       <c r="F183" t="inlineStr">
         <is>
-          <t>215.0K</t>
+          <t>0.4%</t>
         </is>
       </c>
       <c r="G183" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="184">
@@ -5755,23 +5743,31 @@
       </c>
       <c r="B184" t="inlineStr">
         <is>
-          <t>Philly Fed New OrdersJAN</t>
+          <t>Initial Jobless ClaimsJAN/11</t>
         </is>
       </c>
       <c r="C184" t="inlineStr">
         <is>
-          <t>42.9</t>
+          <t>217K</t>
         </is>
       </c>
       <c r="D184" t="inlineStr">
         <is>
-          <t>-3.6</t>
-        </is>
-      </c>
-      <c r="E184" t="inlineStr"/>
-      <c r="F184" t="inlineStr"/>
+          <t>203K</t>
+        </is>
+      </c>
+      <c r="E184" t="inlineStr">
+        <is>
+          <t>210K</t>
+        </is>
+      </c>
+      <c r="F184" t="inlineStr">
+        <is>
+          <t>209.0K</t>
+        </is>
+      </c>
       <c r="G184" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="185">
@@ -5782,7 +5778,7 @@
       </c>
       <c r="B185" t="inlineStr">
         <is>
-          <t>Retail Sales Ex Gas/Autos MoMDEC</t>
+          <t>Export Prices MoMDEC</t>
         </is>
       </c>
       <c r="C185" t="inlineStr">
@@ -5792,21 +5788,21 @@
       </c>
       <c r="D185" t="inlineStr">
         <is>
+          <t>0%</t>
+        </is>
+      </c>
+      <c r="E185" t="inlineStr">
+        <is>
           <t>0.2%</t>
         </is>
       </c>
-      <c r="E185" t="inlineStr">
-        <is>
-          <t>0.4%</t>
-        </is>
-      </c>
       <c r="F185" t="inlineStr">
         <is>
-          <t>0.4%</t>
+          <t>0.5%</t>
         </is>
       </c>
       <c r="G185" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="186">
@@ -5817,31 +5813,31 @@
       </c>
       <c r="B186" t="inlineStr">
         <is>
-          <t>Continuing Jobless ClaimsJAN/04</t>
+          <t>Retail Sales MoMDEC</t>
         </is>
       </c>
       <c r="C186" t="inlineStr">
         <is>
-          <t>1859K</t>
+          <t>0.4%</t>
         </is>
       </c>
       <c r="D186" t="inlineStr">
         <is>
-          <t>1867K</t>
+          <t>0.8%</t>
         </is>
       </c>
       <c r="E186" t="inlineStr">
         <is>
-          <t>1870K</t>
+          <t>0.6%</t>
         </is>
       </c>
       <c r="F186" t="inlineStr">
         <is>
-          <t>1870.0K</t>
+          <t>0.5%</t>
         </is>
       </c>
       <c r="G186" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="187">
@@ -5852,21 +5848,25 @@
       </c>
       <c r="B187" t="inlineStr">
         <is>
-          <t>Philly Fed EmploymentJAN</t>
+          <t>Retail Sales YoYDEC</t>
         </is>
       </c>
       <c r="C187" t="inlineStr">
         <is>
-          <t>11.9</t>
+          <t>3.9%</t>
         </is>
       </c>
       <c r="D187" t="inlineStr">
         <is>
-          <t>4.8</t>
+          <t>4.1%</t>
         </is>
       </c>
       <c r="E187" t="inlineStr"/>
-      <c r="F187" t="inlineStr"/>
+      <c r="F187" t="inlineStr">
+        <is>
+          <t>4.0%</t>
+        </is>
+      </c>
       <c r="G187" t="n">
         <v>3</v>
       </c>
@@ -6015,17 +6015,17 @@
       </c>
       <c r="B192" t="inlineStr">
         <is>
-          <t>4-Week Bill Auction</t>
+          <t>8-Week Bill Auction</t>
         </is>
       </c>
       <c r="C192" t="inlineStr">
         <is>
+          <t>4.235%</t>
+        </is>
+      </c>
+      <c r="D192" t="inlineStr">
+        <is>
           <t>4.240%</t>
-        </is>
-      </c>
-      <c r="D192" t="inlineStr">
-        <is>
-          <t>4.245%</t>
         </is>
       </c>
       <c r="E192" t="inlineStr"/>
@@ -6042,17 +6042,17 @@
       </c>
       <c r="B193" t="inlineStr">
         <is>
-          <t>8-Week Bill Auction</t>
+          <t>4-Week Bill Auction</t>
         </is>
       </c>
       <c r="C193" t="inlineStr">
         <is>
-          <t>4.235%</t>
+          <t>4.240%</t>
         </is>
       </c>
       <c r="D193" t="inlineStr">
         <is>
-          <t>4.240%</t>
+          <t>4.245%</t>
         </is>
       </c>
       <c r="E193" t="inlineStr"/>
@@ -6503,23 +6503,27 @@
       </c>
       <c r="B208" t="inlineStr">
         <is>
-          <t>Overall Net Capital FlowsNOV</t>
+          <t>Net Long-term TIC FlowsNOV</t>
         </is>
       </c>
       <c r="C208" t="inlineStr">
         <is>
+          <t>$79B</t>
+        </is>
+      </c>
+      <c r="D208" t="inlineStr">
+        <is>
+          <t>$159.1B</t>
+        </is>
+      </c>
+      <c r="E208" t="inlineStr">
+        <is>
           <t>$159.9B</t>
         </is>
       </c>
-      <c r="D208" t="inlineStr">
-        <is>
-          <t>$201.8B</t>
-        </is>
-      </c>
-      <c r="E208" t="inlineStr"/>
       <c r="F208" t="inlineStr"/>
       <c r="G208" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="209">
@@ -6530,17 +6534,17 @@
       </c>
       <c r="B209" t="inlineStr">
         <is>
-          <t>Foreign Bond InvestmentNOV</t>
+          <t>Overall Net Capital FlowsNOV</t>
         </is>
       </c>
       <c r="C209" t="inlineStr">
         <is>
-          <t>$-15.8B</t>
+          <t>$159.9B</t>
         </is>
       </c>
       <c r="D209" t="inlineStr">
         <is>
-          <t>$92B</t>
+          <t>$201.8B</t>
         </is>
       </c>
       <c r="E209" t="inlineStr"/>
@@ -6557,27 +6561,23 @@
       </c>
       <c r="B210" t="inlineStr">
         <is>
-          <t>Net Long-term TIC FlowsNOV</t>
+          <t>Foreign Bond InvestmentNOV</t>
         </is>
       </c>
       <c r="C210" t="inlineStr">
         <is>
-          <t>$79B</t>
+          <t>$-15.8B</t>
         </is>
       </c>
       <c r="D210" t="inlineStr">
         <is>
-          <t>$159.1B</t>
-        </is>
-      </c>
-      <c r="E210" t="inlineStr">
-        <is>
-          <t>$159.9B</t>
-        </is>
-      </c>
+          <t>$92B</t>
+        </is>
+      </c>
+      <c r="E210" t="inlineStr"/>
       <c r="F210" t="inlineStr"/>
       <c r="G210" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="211">
@@ -7241,17 +7241,17 @@
       </c>
       <c r="B234" t="inlineStr">
         <is>
-          <t>EIA Gasoline Production ChangeJAN/17</t>
+          <t>EIA Heating Oil Stocks ChangeJAN/17</t>
         </is>
       </c>
       <c r="C234" t="inlineStr">
         <is>
-          <t>-0.043M</t>
+          <t>0.068M</t>
         </is>
       </c>
       <c r="D234" t="inlineStr">
         <is>
-          <t>0.397M</t>
+          <t>0.646M</t>
         </is>
       </c>
       <c r="E234" t="inlineStr"/>
@@ -7268,23 +7268,27 @@
       </c>
       <c r="B235" t="inlineStr">
         <is>
-          <t>EIA Cushing Crude Oil Stocks ChangeJAN/17</t>
+          <t>EIA Crude Oil Stocks ChangeJAN/17</t>
         </is>
       </c>
       <c r="C235" t="inlineStr">
         <is>
-          <t>-0.148M</t>
+          <t>-1.017M</t>
         </is>
       </c>
       <c r="D235" t="inlineStr">
         <is>
-          <t>0.765M</t>
-        </is>
-      </c>
-      <c r="E235" t="inlineStr"/>
+          <t>-1.962M</t>
+        </is>
+      </c>
+      <c r="E235" t="inlineStr">
+        <is>
+          <t>-2.1M</t>
+        </is>
+      </c>
       <c r="F235" t="inlineStr"/>
       <c r="G235" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="236">
@@ -7295,17 +7299,17 @@
       </c>
       <c r="B236" t="inlineStr">
         <is>
-          <t>30-Year Mortgage RateJAN/23</t>
+          <t>15-Year Mortgage RateJAN/23</t>
         </is>
       </c>
       <c r="C236" t="inlineStr">
         <is>
-          <t>6.96%</t>
+          <t>6.16%</t>
         </is>
       </c>
       <c r="D236" t="inlineStr">
         <is>
-          <t>7.04%</t>
+          <t>6.27%</t>
         </is>
       </c>
       <c r="E236" t="inlineStr"/>
@@ -7322,23 +7326,27 @@
       </c>
       <c r="B237" t="inlineStr">
         <is>
-          <t>EIA Distillate Fuel Production ChangeJAN/17</t>
+          <t>EIA Gasoline Stocks ChangeJAN/17</t>
         </is>
       </c>
       <c r="C237" t="inlineStr">
         <is>
-          <t>-0.473M</t>
+          <t>2.332M</t>
         </is>
       </c>
       <c r="D237" t="inlineStr">
         <is>
-          <t>-0.021M</t>
-        </is>
-      </c>
-      <c r="E237" t="inlineStr"/>
+          <t>5.852M</t>
+        </is>
+      </c>
+      <c r="E237" t="inlineStr">
+        <is>
+          <t>2.5M</t>
+        </is>
+      </c>
       <c r="F237" t="inlineStr"/>
       <c r="G237" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="238">
@@ -7349,24 +7357,20 @@
       </c>
       <c r="B238" t="inlineStr">
         <is>
-          <t>EIA Distillate Stocks ChangeJAN/17</t>
+          <t>EIA Refinery Crude Runs ChangeJAN/17</t>
         </is>
       </c>
       <c r="C238" t="inlineStr">
         <is>
-          <t>-3.07M</t>
+          <t>-1.125M</t>
         </is>
       </c>
       <c r="D238" t="inlineStr">
         <is>
-          <t>3.077M</t>
-        </is>
-      </c>
-      <c r="E238" t="inlineStr">
-        <is>
-          <t>0.6M</t>
-        </is>
-      </c>
+          <t>-0.255M</t>
+        </is>
+      </c>
+      <c r="E238" t="inlineStr"/>
       <c r="F238" t="inlineStr"/>
       <c r="G238" t="n">
         <v>3</v>
@@ -7380,20 +7384,24 @@
       </c>
       <c r="B239" t="inlineStr">
         <is>
-          <t>EIA Crude Oil Imports ChangeJAN/17</t>
+          <t>EIA Distillate Stocks ChangeJAN/17</t>
         </is>
       </c>
       <c r="C239" t="inlineStr">
         <is>
-          <t>0.184M</t>
+          <t>-3.07M</t>
         </is>
       </c>
       <c r="D239" t="inlineStr">
         <is>
-          <t>-1.304M</t>
-        </is>
-      </c>
-      <c r="E239" t="inlineStr"/>
+          <t>3.077M</t>
+        </is>
+      </c>
+      <c r="E239" t="inlineStr">
+        <is>
+          <t>0.6M</t>
+        </is>
+      </c>
       <c r="F239" t="inlineStr"/>
       <c r="G239" t="n">
         <v>3</v>
@@ -7407,17 +7415,17 @@
       </c>
       <c r="B240" t="inlineStr">
         <is>
-          <t>EIA Refinery Crude Runs ChangeJAN/17</t>
+          <t>EIA Distillate Fuel Production ChangeJAN/17</t>
         </is>
       </c>
       <c r="C240" t="inlineStr">
         <is>
-          <t>-1.125M</t>
+          <t>-0.473M</t>
         </is>
       </c>
       <c r="D240" t="inlineStr">
         <is>
-          <t>-0.255M</t>
+          <t>-0.021M</t>
         </is>
       </c>
       <c r="E240" t="inlineStr"/>
@@ -7434,27 +7442,23 @@
       </c>
       <c r="B241" t="inlineStr">
         <is>
-          <t>EIA Gasoline Stocks ChangeJAN/17</t>
+          <t>30-Year Mortgage RateJAN/23</t>
         </is>
       </c>
       <c r="C241" t="inlineStr">
         <is>
-          <t>2.332M</t>
+          <t>6.96%</t>
         </is>
       </c>
       <c r="D241" t="inlineStr">
         <is>
-          <t>5.852M</t>
-        </is>
-      </c>
-      <c r="E241" t="inlineStr">
-        <is>
-          <t>2.5M</t>
-        </is>
-      </c>
+          <t>7.04%</t>
+        </is>
+      </c>
+      <c r="E241" t="inlineStr"/>
       <c r="F241" t="inlineStr"/>
       <c r="G241" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="242">
@@ -7465,17 +7469,17 @@
       </c>
       <c r="B242" t="inlineStr">
         <is>
-          <t>15-Year Mortgage RateJAN/23</t>
+          <t>EIA Cushing Crude Oil Stocks ChangeJAN/17</t>
         </is>
       </c>
       <c r="C242" t="inlineStr">
         <is>
-          <t>6.16%</t>
+          <t>-0.148M</t>
         </is>
       </c>
       <c r="D242" t="inlineStr">
         <is>
-          <t>6.27%</t>
+          <t>0.765M</t>
         </is>
       </c>
       <c r="E242" t="inlineStr"/>
@@ -7492,27 +7496,23 @@
       </c>
       <c r="B243" t="inlineStr">
         <is>
-          <t>EIA Crude Oil Stocks ChangeJAN/17</t>
+          <t>EIA Gasoline Production ChangeJAN/17</t>
         </is>
       </c>
       <c r="C243" t="inlineStr">
         <is>
-          <t>-1.017M</t>
+          <t>-0.043M</t>
         </is>
       </c>
       <c r="D243" t="inlineStr">
         <is>
-          <t>-1.962M</t>
-        </is>
-      </c>
-      <c r="E243" t="inlineStr">
-        <is>
-          <t>-2.1M</t>
-        </is>
-      </c>
+          <t>0.397M</t>
+        </is>
+      </c>
+      <c r="E243" t="inlineStr"/>
       <c r="F243" t="inlineStr"/>
       <c r="G243" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="244">
@@ -7523,17 +7523,17 @@
       </c>
       <c r="B244" t="inlineStr">
         <is>
-          <t>EIA Heating Oil Stocks ChangeJAN/17</t>
+          <t>EIA Crude Oil Imports ChangeJAN/17</t>
         </is>
       </c>
       <c r="C244" t="inlineStr">
         <is>
-          <t>0.068M</t>
+          <t>0.184M</t>
         </is>
       </c>
       <c r="D244" t="inlineStr">
         <is>
-          <t>0.646M</t>
+          <t>-1.304M</t>
         </is>
       </c>
       <c r="E244" t="inlineStr"/>
@@ -7705,27 +7705,31 @@
       </c>
       <c r="B250" t="inlineStr">
         <is>
-          <t>Existing Home Sales MoMDEC</t>
+          <t>Existing Home SalesDEC</t>
         </is>
       </c>
       <c r="C250" t="inlineStr">
         <is>
-          <t>2.2%</t>
+          <t>4.24M</t>
         </is>
       </c>
       <c r="D250" t="inlineStr">
         <is>
-          <t>4.8%</t>
-        </is>
-      </c>
-      <c r="E250" t="inlineStr"/>
+          <t>4.15M</t>
+        </is>
+      </c>
+      <c r="E250" t="inlineStr">
+        <is>
+          <t>4.19M</t>
+        </is>
+      </c>
       <c r="F250" t="inlineStr">
         <is>
-          <t>0.3%</t>
+          <t>4.1M</t>
         </is>
       </c>
       <c r="G250" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="251">
@@ -7736,31 +7740,31 @@
       </c>
       <c r="B251" t="inlineStr">
         <is>
-          <t>Michigan Inflation Expectations FinalJAN</t>
+          <t>Michigan Consumer Sentiment FinalJAN</t>
         </is>
       </c>
       <c r="C251" t="inlineStr">
         <is>
-          <t>3.3%</t>
+          <t>71.1</t>
         </is>
       </c>
       <c r="D251" t="inlineStr">
         <is>
-          <t>2.8%</t>
+          <t>74.0</t>
         </is>
       </c>
       <c r="E251" t="inlineStr">
         <is>
-          <t>3.3%</t>
+          <t>73.2</t>
         </is>
       </c>
       <c r="F251" t="inlineStr">
         <is>
-          <t>3.3%</t>
+          <t>73.2</t>
         </is>
       </c>
       <c r="G251" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="252">
@@ -7771,27 +7775,27 @@
       </c>
       <c r="B252" t="inlineStr">
         <is>
-          <t>Michigan 5 Year Inflation Expectations FinalJAN</t>
+          <t>Michigan Consumer Expectations FinalJAN</t>
         </is>
       </c>
       <c r="C252" t="inlineStr">
         <is>
-          <t>3.2%</t>
+          <t>69.3</t>
         </is>
       </c>
       <c r="D252" t="inlineStr">
         <is>
-          <t>3%</t>
+          <t>73.3</t>
         </is>
       </c>
       <c r="E252" t="inlineStr">
         <is>
-          <t>3.3%</t>
+          <t>70.2</t>
         </is>
       </c>
       <c r="F252" t="inlineStr">
         <is>
-          <t>3.3%</t>
+          <t>70.2</t>
         </is>
       </c>
       <c r="G252" t="n">
@@ -7806,31 +7810,27 @@
       </c>
       <c r="B253" t="inlineStr">
         <is>
-          <t>Michigan Current Conditions FinalJAN</t>
+          <t>Existing Home Sales MoMDEC</t>
         </is>
       </c>
       <c r="C253" t="inlineStr">
         <is>
-          <t>74.0</t>
+          <t>2.2%</t>
         </is>
       </c>
       <c r="D253" t="inlineStr">
         <is>
-          <t>75.1</t>
-        </is>
-      </c>
-      <c r="E253" t="inlineStr">
-        <is>
-          <t>77.9</t>
-        </is>
-      </c>
+          <t>4.8%</t>
+        </is>
+      </c>
+      <c r="E253" t="inlineStr"/>
       <c r="F253" t="inlineStr">
         <is>
-          <t>77.9</t>
+          <t>0.3%</t>
         </is>
       </c>
       <c r="G253" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="254">
@@ -7841,27 +7841,27 @@
       </c>
       <c r="B254" t="inlineStr">
         <is>
-          <t>Michigan Consumer Expectations FinalJAN</t>
+          <t>Michigan 5 Year Inflation Expectations FinalJAN</t>
         </is>
       </c>
       <c r="C254" t="inlineStr">
         <is>
-          <t>69.3</t>
+          <t>3.2%</t>
         </is>
       </c>
       <c r="D254" t="inlineStr">
         <is>
-          <t>73.3</t>
+          <t>3%</t>
         </is>
       </c>
       <c r="E254" t="inlineStr">
         <is>
-          <t>70.2</t>
+          <t>3.3%</t>
         </is>
       </c>
       <c r="F254" t="inlineStr">
         <is>
-          <t>70.2</t>
+          <t>3.3%</t>
         </is>
       </c>
       <c r="G254" t="n">
@@ -7876,31 +7876,31 @@
       </c>
       <c r="B255" t="inlineStr">
         <is>
-          <t>Existing Home SalesDEC</t>
+          <t>Michigan Inflation Expectations FinalJAN</t>
         </is>
       </c>
       <c r="C255" t="inlineStr">
         <is>
-          <t>4.24M</t>
+          <t>3.3%</t>
         </is>
       </c>
       <c r="D255" t="inlineStr">
         <is>
-          <t>4.15M</t>
+          <t>2.8%</t>
         </is>
       </c>
       <c r="E255" t="inlineStr">
         <is>
-          <t>4.19M</t>
+          <t>3.3%</t>
         </is>
       </c>
       <c r="F255" t="inlineStr">
         <is>
-          <t>4.1M</t>
+          <t>3.3%</t>
         </is>
       </c>
       <c r="G255" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="256">
@@ -7911,31 +7911,31 @@
       </c>
       <c r="B256" t="inlineStr">
         <is>
-          <t>Michigan Consumer Sentiment FinalJAN</t>
+          <t>Michigan Current Conditions FinalJAN</t>
         </is>
       </c>
       <c r="C256" t="inlineStr">
         <is>
-          <t>71.1</t>
+          <t>74.0</t>
         </is>
       </c>
       <c r="D256" t="inlineStr">
         <is>
-          <t>74.0</t>
+          <t>75.1</t>
         </is>
       </c>
       <c r="E256" t="inlineStr">
         <is>
-          <t>73.2</t>
+          <t>77.9</t>
         </is>
       </c>
       <c r="F256" t="inlineStr">
         <is>
-          <t>73.2</t>
+          <t>77.9</t>
         </is>
       </c>
       <c r="G256" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="257">
@@ -8469,27 +8469,23 @@
       </c>
       <c r="B274" t="inlineStr">
         <is>
-          <t>House Price Index MoMNOV</t>
+          <t>S&amp;P/Case-Shiller Home Price MoMNOV</t>
         </is>
       </c>
       <c r="C274" t="inlineStr">
         <is>
-          <t>0.3%</t>
+          <t>-0.1%</t>
         </is>
       </c>
       <c r="D274" t="inlineStr">
         <is>
-          <t>0.5%</t>
-        </is>
-      </c>
-      <c r="E274" t="inlineStr">
-        <is>
-          <t>0.2%</t>
-        </is>
-      </c>
+          <t>-0.2%</t>
+        </is>
+      </c>
+      <c r="E274" t="inlineStr"/>
       <c r="F274" t="inlineStr">
         <is>
-          <t>0.3%</t>
+          <t>-0.1%</t>
         </is>
       </c>
       <c r="G274" t="n">
@@ -8504,27 +8500,31 @@
       </c>
       <c r="B275" t="inlineStr">
         <is>
-          <t>House Price Index YoYNOV</t>
+          <t>S&amp;P/Case-Shiller Home Price YoYNOV</t>
         </is>
       </c>
       <c r="C275" t="inlineStr">
         <is>
+          <t>4.3%</t>
+        </is>
+      </c>
+      <c r="D275" t="inlineStr">
+        <is>
           <t>4.2%</t>
         </is>
       </c>
-      <c r="D275" t="inlineStr">
-        <is>
-          <t>4.5%</t>
-        </is>
-      </c>
-      <c r="E275" t="inlineStr"/>
+      <c r="E275" t="inlineStr">
+        <is>
+          <t>4.3%</t>
+        </is>
+      </c>
       <c r="F275" t="inlineStr">
         <is>
-          <t>4.3%</t>
+          <t>4%</t>
         </is>
       </c>
       <c r="G275" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="276">
@@ -8535,31 +8535,27 @@
       </c>
       <c r="B276" t="inlineStr">
         <is>
-          <t>S&amp;P/Case-Shiller Home Price YoYNOV</t>
+          <t>House Price IndexNOV</t>
         </is>
       </c>
       <c r="C276" t="inlineStr">
         <is>
-          <t>4.3%</t>
+          <t>433.4</t>
         </is>
       </c>
       <c r="D276" t="inlineStr">
         <is>
-          <t>4.2%</t>
-        </is>
-      </c>
-      <c r="E276" t="inlineStr">
-        <is>
-          <t>4.3%</t>
-        </is>
-      </c>
+          <t>432.3</t>
+        </is>
+      </c>
+      <c r="E276" t="inlineStr"/>
       <c r="F276" t="inlineStr">
         <is>
-          <t>4%</t>
+          <t>433</t>
         </is>
       </c>
       <c r="G276" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="277">
@@ -8570,23 +8566,23 @@
       </c>
       <c r="B277" t="inlineStr">
         <is>
-          <t>House Price IndexNOV</t>
+          <t>House Price Index YoYNOV</t>
         </is>
       </c>
       <c r="C277" t="inlineStr">
         <is>
-          <t>433.4</t>
+          <t>4.2%</t>
         </is>
       </c>
       <c r="D277" t="inlineStr">
         <is>
-          <t>432.3</t>
+          <t>4.5%</t>
         </is>
       </c>
       <c r="E277" t="inlineStr"/>
       <c r="F277" t="inlineStr">
         <is>
-          <t>433</t>
+          <t>4.3%</t>
         </is>
       </c>
       <c r="G277" t="n">
@@ -8601,23 +8597,27 @@
       </c>
       <c r="B278" t="inlineStr">
         <is>
-          <t>S&amp;P/Case-Shiller Home Price MoMNOV</t>
+          <t>House Price Index MoMNOV</t>
         </is>
       </c>
       <c r="C278" t="inlineStr">
         <is>
-          <t>-0.1%</t>
+          <t>0.3%</t>
         </is>
       </c>
       <c r="D278" t="inlineStr">
         <is>
-          <t>-0.2%</t>
-        </is>
-      </c>
-      <c r="E278" t="inlineStr"/>
+          <t>0.5%</t>
+        </is>
+      </c>
+      <c r="E278" t="inlineStr">
+        <is>
+          <t>0.2%</t>
+        </is>
+      </c>
       <c r="F278" t="inlineStr">
         <is>
-          <t>-0.1%</t>
+          <t>0.3%</t>
         </is>
       </c>
       <c r="G278" t="n">
@@ -9201,17 +9201,17 @@
       </c>
       <c r="B298" t="inlineStr">
         <is>
-          <t>EIA Gasoline Production ChangeJAN/24</t>
+          <t>EIA Cushing Crude Oil Stocks ChangeJAN/24</t>
         </is>
       </c>
       <c r="C298" t="inlineStr">
         <is>
-          <t>-0.044M</t>
+          <t>0.326M</t>
         </is>
       </c>
       <c r="D298" t="inlineStr">
         <is>
-          <t>-0.043M</t>
+          <t>-0.148M</t>
         </is>
       </c>
       <c r="E298" t="inlineStr"/>
@@ -9228,23 +9228,27 @@
       </c>
       <c r="B299" t="inlineStr">
         <is>
-          <t>EIA Crude Oil Imports ChangeJAN/24</t>
+          <t>EIA Crude Oil Stocks ChangeJAN/24</t>
         </is>
       </c>
       <c r="C299" t="inlineStr">
         <is>
-          <t>0.532M</t>
+          <t>3.463M</t>
         </is>
       </c>
       <c r="D299" t="inlineStr">
         <is>
-          <t>0.184M</t>
-        </is>
-      </c>
-      <c r="E299" t="inlineStr"/>
+          <t>-1.017M</t>
+        </is>
+      </c>
+      <c r="E299" t="inlineStr">
+        <is>
+          <t>3.2M</t>
+        </is>
+      </c>
       <c r="F299" t="inlineStr"/>
       <c r="G299" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="300">
@@ -9255,20 +9259,24 @@
       </c>
       <c r="B300" t="inlineStr">
         <is>
-          <t>EIA Distillate Fuel Production ChangeJAN/24</t>
+          <t>EIA Distillate Stocks ChangeJAN/24</t>
         </is>
       </c>
       <c r="C300" t="inlineStr">
         <is>
-          <t>0.028M</t>
+          <t>-4.994M</t>
         </is>
       </c>
       <c r="D300" t="inlineStr">
         <is>
-          <t>-0.473M</t>
-        </is>
-      </c>
-      <c r="E300" t="inlineStr"/>
+          <t>-3.07M</t>
+        </is>
+      </c>
+      <c r="E300" t="inlineStr">
+        <is>
+          <t>-2.1M</t>
+        </is>
+      </c>
       <c r="F300" t="inlineStr"/>
       <c r="G300" t="n">
         <v>3</v>
@@ -9282,27 +9290,23 @@
       </c>
       <c r="B301" t="inlineStr">
         <is>
-          <t>EIA Gasoline Stocks ChangeJAN/24</t>
+          <t>EIA Heating Oil Stocks ChangeJAN/24</t>
         </is>
       </c>
       <c r="C301" t="inlineStr">
         <is>
-          <t>2.957M</t>
+          <t>0.128M</t>
         </is>
       </c>
       <c r="D301" t="inlineStr">
         <is>
-          <t>2.332M</t>
-        </is>
-      </c>
-      <c r="E301" t="inlineStr">
-        <is>
-          <t>1.5M</t>
-        </is>
-      </c>
+          <t>0.068M</t>
+        </is>
+      </c>
+      <c r="E301" t="inlineStr"/>
       <c r="F301" t="inlineStr"/>
       <c r="G301" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="302">
@@ -9340,23 +9344,27 @@
       </c>
       <c r="B303" t="inlineStr">
         <is>
-          <t>EIA Heating Oil Stocks ChangeJAN/24</t>
+          <t>EIA Gasoline Stocks ChangeJAN/24</t>
         </is>
       </c>
       <c r="C303" t="inlineStr">
         <is>
-          <t>0.128M</t>
+          <t>2.957M</t>
         </is>
       </c>
       <c r="D303" t="inlineStr">
         <is>
-          <t>0.068M</t>
-        </is>
-      </c>
-      <c r="E303" t="inlineStr"/>
+          <t>2.332M</t>
+        </is>
+      </c>
+      <c r="E303" t="inlineStr">
+        <is>
+          <t>1.5M</t>
+        </is>
+      </c>
       <c r="F303" t="inlineStr"/>
       <c r="G303" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="304">
@@ -9367,24 +9375,20 @@
       </c>
       <c r="B304" t="inlineStr">
         <is>
-          <t>EIA Distillate Stocks ChangeJAN/24</t>
+          <t>EIA Distillate Fuel Production ChangeJAN/24</t>
         </is>
       </c>
       <c r="C304" t="inlineStr">
         <is>
-          <t>-4.994M</t>
+          <t>0.028M</t>
         </is>
       </c>
       <c r="D304" t="inlineStr">
         <is>
-          <t>-3.07M</t>
-        </is>
-      </c>
-      <c r="E304" t="inlineStr">
-        <is>
-          <t>-2.1M</t>
-        </is>
-      </c>
+          <t>-0.473M</t>
+        </is>
+      </c>
+      <c r="E304" t="inlineStr"/>
       <c r="F304" t="inlineStr"/>
       <c r="G304" t="n">
         <v>3</v>
@@ -9398,27 +9402,23 @@
       </c>
       <c r="B305" t="inlineStr">
         <is>
-          <t>EIA Crude Oil Stocks ChangeJAN/24</t>
+          <t>EIA Crude Oil Imports ChangeJAN/24</t>
         </is>
       </c>
       <c r="C305" t="inlineStr">
         <is>
-          <t>3.463M</t>
+          <t>0.532M</t>
         </is>
       </c>
       <c r="D305" t="inlineStr">
         <is>
-          <t>-1.017M</t>
-        </is>
-      </c>
-      <c r="E305" t="inlineStr">
-        <is>
-          <t>3.2M</t>
-        </is>
-      </c>
+          <t>0.184M</t>
+        </is>
+      </c>
+      <c r="E305" t="inlineStr"/>
       <c r="F305" t="inlineStr"/>
       <c r="G305" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="306">
@@ -9429,17 +9429,17 @@
       </c>
       <c r="B306" t="inlineStr">
         <is>
-          <t>EIA Cushing Crude Oil Stocks ChangeJAN/24</t>
+          <t>EIA Gasoline Production ChangeJAN/24</t>
         </is>
       </c>
       <c r="C306" t="inlineStr">
         <is>
-          <t>0.326M</t>
+          <t>-0.044M</t>
         </is>
       </c>
       <c r="D306" t="inlineStr">
         <is>
-          <t>-0.148M</t>
+          <t>-0.043M</t>
         </is>
       </c>
       <c r="E306" t="inlineStr"/>
@@ -9537,27 +9537,23 @@
       </c>
       <c r="B310" t="inlineStr">
         <is>
-          <t>Core PCE Prices QoQ AdvQ4</t>
+          <t>GDP Sales QoQ AdvQ4</t>
         </is>
       </c>
       <c r="C310" t="inlineStr">
         <is>
-          <t>2.5%</t>
+          <t>3.2%</t>
         </is>
       </c>
       <c r="D310" t="inlineStr">
         <is>
-          <t>2.2%</t>
-        </is>
-      </c>
-      <c r="E310" t="inlineStr">
-        <is>
-          <t>2.5%</t>
-        </is>
-      </c>
+          <t>3.3%</t>
+        </is>
+      </c>
+      <c r="E310" t="inlineStr"/>
       <c r="F310" t="inlineStr">
         <is>
-          <t>2.3%</t>
+          <t>2.9%</t>
         </is>
       </c>
       <c r="G310" t="n">
@@ -9572,23 +9568,23 @@
       </c>
       <c r="B311" t="inlineStr">
         <is>
-          <t>PCE Prices QoQ AdvQ4</t>
+          <t>Jobless Claims 4-week AverageJAN/25</t>
         </is>
       </c>
       <c r="C311" t="inlineStr">
         <is>
-          <t>2.3%</t>
+          <t>212.5K</t>
         </is>
       </c>
       <c r="D311" t="inlineStr">
         <is>
-          <t>1.5%</t>
+          <t>213.5K</t>
         </is>
       </c>
       <c r="E311" t="inlineStr"/>
       <c r="F311" t="inlineStr">
         <is>
-          <t>1.1%</t>
+          <t>214.0K</t>
         </is>
       </c>
       <c r="G311" t="n">
@@ -9603,23 +9599,27 @@
       </c>
       <c r="B312" t="inlineStr">
         <is>
-          <t>Real Consumer Spending QoQ AdvQ4</t>
+          <t>Continuing Jobless ClaimsJAN/18</t>
         </is>
       </c>
       <c r="C312" t="inlineStr">
         <is>
-          <t>4.2%</t>
+          <t>1858K</t>
         </is>
       </c>
       <c r="D312" t="inlineStr">
         <is>
-          <t>3.7%</t>
-        </is>
-      </c>
-      <c r="E312" t="inlineStr"/>
+          <t>1900K</t>
+        </is>
+      </c>
+      <c r="E312" t="inlineStr">
+        <is>
+          <t>1890K</t>
+        </is>
+      </c>
       <c r="F312" t="inlineStr">
         <is>
-          <t>2.9%</t>
+          <t>1885.0K</t>
         </is>
       </c>
       <c r="G312" t="n">
@@ -9634,27 +9634,27 @@
       </c>
       <c r="B313" t="inlineStr">
         <is>
-          <t>GDP Price Index QoQ AdvQ4</t>
+          <t>Initial Jobless ClaimsJAN/25</t>
         </is>
       </c>
       <c r="C313" t="inlineStr">
         <is>
-          <t>2.2%</t>
+          <t>207K</t>
         </is>
       </c>
       <c r="D313" t="inlineStr">
         <is>
-          <t>1.9%</t>
+          <t>223K</t>
         </is>
       </c>
       <c r="E313" t="inlineStr">
         <is>
-          <t>2.5%</t>
+          <t>220K</t>
         </is>
       </c>
       <c r="F313" t="inlineStr">
         <is>
-          <t>2.3%</t>
+          <t>228.0K</t>
         </is>
       </c>
       <c r="G313" t="n">
@@ -9669,31 +9669,31 @@
       </c>
       <c r="B314" t="inlineStr">
         <is>
-          <t>Initial Jobless ClaimsJAN/25</t>
+          <t>GDP Growth Rate QoQ AdvQ4</t>
         </is>
       </c>
       <c r="C314" t="inlineStr">
         <is>
-          <t>207K</t>
+          <t>2.3%</t>
         </is>
       </c>
       <c r="D314" t="inlineStr">
         <is>
-          <t>223K</t>
+          <t>3.1%</t>
         </is>
       </c>
       <c r="E314" t="inlineStr">
         <is>
-          <t>220K</t>
+          <t>2.6%</t>
         </is>
       </c>
       <c r="F314" t="inlineStr">
         <is>
-          <t>228.0K</t>
+          <t>3%</t>
         </is>
       </c>
       <c r="G314" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="315">
@@ -9704,31 +9704,27 @@
       </c>
       <c r="B315" t="inlineStr">
         <is>
-          <t>GDP Growth Rate QoQ AdvQ4</t>
+          <t>Real Consumer Spending QoQ AdvQ4</t>
         </is>
       </c>
       <c r="C315" t="inlineStr">
         <is>
-          <t>2.3%</t>
+          <t>4.2%</t>
         </is>
       </c>
       <c r="D315" t="inlineStr">
         <is>
-          <t>3.1%</t>
-        </is>
-      </c>
-      <c r="E315" t="inlineStr">
-        <is>
-          <t>2.6%</t>
-        </is>
-      </c>
+          <t>3.7%</t>
+        </is>
+      </c>
+      <c r="E315" t="inlineStr"/>
       <c r="F315" t="inlineStr">
         <is>
-          <t>3%</t>
+          <t>2.9%</t>
         </is>
       </c>
       <c r="G315" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="316">
@@ -9739,27 +9735,23 @@
       </c>
       <c r="B316" t="inlineStr">
         <is>
-          <t>Continuing Jobless ClaimsJAN/18</t>
+          <t>PCE Prices QoQ AdvQ4</t>
         </is>
       </c>
       <c r="C316" t="inlineStr">
         <is>
-          <t>1858K</t>
+          <t>2.3%</t>
         </is>
       </c>
       <c r="D316" t="inlineStr">
         <is>
-          <t>1900K</t>
-        </is>
-      </c>
-      <c r="E316" t="inlineStr">
-        <is>
-          <t>1890K</t>
-        </is>
-      </c>
+          <t>1.5%</t>
+        </is>
+      </c>
+      <c r="E316" t="inlineStr"/>
       <c r="F316" t="inlineStr">
         <is>
-          <t>1885.0K</t>
+          <t>1.1%</t>
         </is>
       </c>
       <c r="G316" t="n">
@@ -9774,23 +9766,27 @@
       </c>
       <c r="B317" t="inlineStr">
         <is>
-          <t>Jobless Claims 4-week AverageJAN/25</t>
+          <t>Core PCE Prices QoQ AdvQ4</t>
         </is>
       </c>
       <c r="C317" t="inlineStr">
         <is>
-          <t>212.5K</t>
+          <t>2.5%</t>
         </is>
       </c>
       <c r="D317" t="inlineStr">
         <is>
-          <t>213.5K</t>
-        </is>
-      </c>
-      <c r="E317" t="inlineStr"/>
+          <t>2.2%</t>
+        </is>
+      </c>
+      <c r="E317" t="inlineStr">
+        <is>
+          <t>2.5%</t>
+        </is>
+      </c>
       <c r="F317" t="inlineStr">
         <is>
-          <t>214.0K</t>
+          <t>2.3%</t>
         </is>
       </c>
       <c r="G317" t="n">
@@ -9805,27 +9801,31 @@
       </c>
       <c r="B318" t="inlineStr">
         <is>
-          <t>GDP Sales QoQ AdvQ4</t>
+          <t>GDP Price Index QoQ AdvQ4</t>
         </is>
       </c>
       <c r="C318" t="inlineStr">
         <is>
-          <t>3.2%</t>
+          <t>2.2%</t>
         </is>
       </c>
       <c r="D318" t="inlineStr">
         <is>
-          <t>3.3%</t>
-        </is>
-      </c>
-      <c r="E318" t="inlineStr"/>
+          <t>1.9%</t>
+        </is>
+      </c>
+      <c r="E318" t="inlineStr">
+        <is>
+          <t>2.5%</t>
+        </is>
+      </c>
       <c r="F318" t="inlineStr">
         <is>
-          <t>2.9%</t>
+          <t>2.3%</t>
         </is>
       </c>
       <c r="G318" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="319">
@@ -10068,23 +10068,27 @@
       </c>
       <c r="B327" t="inlineStr">
         <is>
-          <t>Employment Cost - Benefits QoQQ4</t>
+          <t>PCE Price Index MoMDEC</t>
         </is>
       </c>
       <c r="C327" t="inlineStr">
         <is>
-          <t>0.8%</t>
+          <t>0.3%</t>
         </is>
       </c>
       <c r="D327" t="inlineStr">
         <is>
-          <t>0.8%</t>
-        </is>
-      </c>
-      <c r="E327" t="inlineStr"/>
+          <t>0.1%</t>
+        </is>
+      </c>
+      <c r="E327" t="inlineStr">
+        <is>
+          <t>0.3%</t>
+        </is>
+      </c>
       <c r="F327" t="inlineStr">
         <is>
-          <t>0.7%</t>
+          <t>0.3%</t>
         </is>
       </c>
       <c r="G327" t="n">
@@ -10099,31 +10103,31 @@
       </c>
       <c r="B328" t="inlineStr">
         <is>
-          <t>Core PCE Price Index MoMDEC</t>
+          <t>Core PCE Price Index YoYDEC</t>
         </is>
       </c>
       <c r="C328" t="inlineStr">
         <is>
-          <t>0.2%</t>
+          <t>2.8%</t>
         </is>
       </c>
       <c r="D328" t="inlineStr">
         <is>
-          <t>0.1%</t>
+          <t>2.8%</t>
         </is>
       </c>
       <c r="E328" t="inlineStr">
         <is>
-          <t>0.2%</t>
+          <t>2.8%</t>
         </is>
       </c>
       <c r="F328" t="inlineStr">
         <is>
-          <t>0.2%</t>
+          <t>2.8%</t>
         </is>
       </c>
       <c r="G328" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="329">
@@ -10134,31 +10138,31 @@
       </c>
       <c r="B329" t="inlineStr">
         <is>
-          <t>Personal Spending MoMDEC</t>
+          <t>Employment Cost Index QoQQ4</t>
         </is>
       </c>
       <c r="C329" t="inlineStr">
         <is>
+          <t>0.9%</t>
+        </is>
+      </c>
+      <c r="D329" t="inlineStr">
+        <is>
+          <t>0.8%</t>
+        </is>
+      </c>
+      <c r="E329" t="inlineStr">
+        <is>
+          <t>0.9%</t>
+        </is>
+      </c>
+      <c r="F329" t="inlineStr">
+        <is>
           <t>0.7%</t>
         </is>
       </c>
-      <c r="D329" t="inlineStr">
-        <is>
-          <t>0.6%</t>
-        </is>
-      </c>
-      <c r="E329" t="inlineStr">
-        <is>
-          <t>0.5%</t>
-        </is>
-      </c>
-      <c r="F329" t="inlineStr">
-        <is>
-          <t>0.5%</t>
-        </is>
-      </c>
       <c r="G329" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="330">
@@ -10169,13 +10173,29 @@
       </c>
       <c r="B330" t="inlineStr">
         <is>
-          <t>Fed Bowman Speech</t>
-        </is>
-      </c>
-      <c r="C330" t="inlineStr"/>
-      <c r="D330" t="inlineStr"/>
-      <c r="E330" t="inlineStr"/>
-      <c r="F330" t="inlineStr"/>
+          <t>PCE Price Index YoYDEC</t>
+        </is>
+      </c>
+      <c r="C330" t="inlineStr">
+        <is>
+          <t>2.6%</t>
+        </is>
+      </c>
+      <c r="D330" t="inlineStr">
+        <is>
+          <t>2.4%</t>
+        </is>
+      </c>
+      <c r="E330" t="inlineStr">
+        <is>
+          <t>2.6%</t>
+        </is>
+      </c>
+      <c r="F330" t="inlineStr">
+        <is>
+          <t>2.6%</t>
+        </is>
+      </c>
       <c r="G330" t="n">
         <v>2</v>
       </c>
@@ -10188,31 +10208,27 @@
       </c>
       <c r="B331" t="inlineStr">
         <is>
-          <t>Personal Income MoMDEC</t>
+          <t>Employment Cost - Wages QoQQ4</t>
         </is>
       </c>
       <c r="C331" t="inlineStr">
         <is>
-          <t>0.4%</t>
+          <t>0.9%</t>
         </is>
       </c>
       <c r="D331" t="inlineStr">
         <is>
-          <t>0.3%</t>
-        </is>
-      </c>
-      <c r="E331" t="inlineStr">
-        <is>
-          <t>0.4%</t>
-        </is>
-      </c>
+          <t>0.8%</t>
+        </is>
+      </c>
+      <c r="E331" t="inlineStr"/>
       <c r="F331" t="inlineStr">
         <is>
-          <t>0.3%</t>
+          <t>0.7%</t>
         </is>
       </c>
       <c r="G331" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="332">
@@ -10223,29 +10239,13 @@
       </c>
       <c r="B332" t="inlineStr">
         <is>
-          <t>PCE Price Index YoYDEC</t>
-        </is>
-      </c>
-      <c r="C332" t="inlineStr">
-        <is>
-          <t>2.6%</t>
-        </is>
-      </c>
-      <c r="D332" t="inlineStr">
-        <is>
-          <t>2.4%</t>
-        </is>
-      </c>
-      <c r="E332" t="inlineStr">
-        <is>
-          <t>2.6%</t>
-        </is>
-      </c>
-      <c r="F332" t="inlineStr">
-        <is>
-          <t>2.6%</t>
-        </is>
-      </c>
+          <t>Fed Bowman Speech</t>
+        </is>
+      </c>
+      <c r="C332" t="inlineStr"/>
+      <c r="D332" t="inlineStr"/>
+      <c r="E332" t="inlineStr"/>
+      <c r="F332" t="inlineStr"/>
       <c r="G332" t="n">
         <v>2</v>
       </c>
@@ -10258,31 +10258,31 @@
       </c>
       <c r="B333" t="inlineStr">
         <is>
-          <t>Core PCE Price Index YoYDEC</t>
+          <t>Personal Spending MoMDEC</t>
         </is>
       </c>
       <c r="C333" t="inlineStr">
         <is>
-          <t>2.8%</t>
+          <t>0.7%</t>
         </is>
       </c>
       <c r="D333" t="inlineStr">
         <is>
-          <t>2.8%</t>
+          <t>0.6%</t>
         </is>
       </c>
       <c r="E333" t="inlineStr">
         <is>
-          <t>2.8%</t>
+          <t>0.5%</t>
         </is>
       </c>
       <c r="F333" t="inlineStr">
         <is>
-          <t>2.8%</t>
+          <t>0.5%</t>
         </is>
       </c>
       <c r="G333" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="334">
@@ -10293,12 +10293,12 @@
       </c>
       <c r="B334" t="inlineStr">
         <is>
-          <t>PCE Price Index MoMDEC</t>
+          <t>Core PCE Price Index MoMDEC</t>
         </is>
       </c>
       <c r="C334" t="inlineStr">
         <is>
-          <t>0.3%</t>
+          <t>0.2%</t>
         </is>
       </c>
       <c r="D334" t="inlineStr">
@@ -10308,16 +10308,16 @@
       </c>
       <c r="E334" t="inlineStr">
         <is>
-          <t>0.3%</t>
+          <t>0.2%</t>
         </is>
       </c>
       <c r="F334" t="inlineStr">
         <is>
-          <t>0.3%</t>
+          <t>0.2%</t>
         </is>
       </c>
       <c r="G334" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="335">
@@ -10328,12 +10328,12 @@
       </c>
       <c r="B335" t="inlineStr">
         <is>
-          <t>Employment Cost Index QoQQ4</t>
+          <t>Employment Cost - Benefits QoQQ4</t>
         </is>
       </c>
       <c r="C335" t="inlineStr">
         <is>
-          <t>0.9%</t>
+          <t>0.8%</t>
         </is>
       </c>
       <c r="D335" t="inlineStr">
@@ -10341,11 +10341,7 @@
           <t>0.8%</t>
         </is>
       </c>
-      <c r="E335" t="inlineStr">
-        <is>
-          <t>0.9%</t>
-        </is>
-      </c>
+      <c r="E335" t="inlineStr"/>
       <c r="F335" t="inlineStr">
         <is>
           <t>0.7%</t>
@@ -10363,27 +10359,31 @@
       </c>
       <c r="B336" t="inlineStr">
         <is>
-          <t>Employment Cost - Wages QoQQ4</t>
+          <t>Personal Income MoMDEC</t>
         </is>
       </c>
       <c r="C336" t="inlineStr">
         <is>
-          <t>0.9%</t>
+          <t>0.4%</t>
         </is>
       </c>
       <c r="D336" t="inlineStr">
         <is>
-          <t>0.8%</t>
-        </is>
-      </c>
-      <c r="E336" t="inlineStr"/>
+          <t>0.3%</t>
+        </is>
+      </c>
+      <c r="E336" t="inlineStr">
+        <is>
+          <t>0.4%</t>
+        </is>
+      </c>
       <c r="F336" t="inlineStr">
         <is>
-          <t>0.7%</t>
+          <t>0.3%</t>
         </is>
       </c>
       <c r="G336" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="337">
@@ -10522,31 +10522,27 @@
       </c>
       <c r="B341" t="inlineStr">
         <is>
-          <t>ISM Manufacturing PMIJAN</t>
+          <t>ISM Manufacturing New OrdersJAN</t>
         </is>
       </c>
       <c r="C341" t="inlineStr">
         <is>
-          <t>50.9</t>
+          <t>55.1</t>
         </is>
       </c>
       <c r="D341" t="inlineStr">
         <is>
-          <t>49.2</t>
-        </is>
-      </c>
-      <c r="E341" t="inlineStr">
-        <is>
-          <t>49.8</t>
-        </is>
-      </c>
+          <t>52.1</t>
+        </is>
+      </c>
+      <c r="E341" t="inlineStr"/>
       <c r="F341" t="inlineStr">
         <is>
-          <t>49.8</t>
+          <t>52.8</t>
         </is>
       </c>
       <c r="G341" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="342">
@@ -10557,31 +10553,27 @@
       </c>
       <c r="B342" t="inlineStr">
         <is>
-          <t>ISM Manufacturing PricesJAN</t>
+          <t>ISM Manufacturing EmploymentJAN</t>
         </is>
       </c>
       <c r="C342" t="inlineStr">
         <is>
-          <t>54.9</t>
+          <t>50.3</t>
         </is>
       </c>
       <c r="D342" t="inlineStr">
         <is>
-          <t>52.5</t>
-        </is>
-      </c>
-      <c r="E342" t="inlineStr">
-        <is>
-          <t>52.6</t>
-        </is>
-      </c>
+          <t>45.4</t>
+        </is>
+      </c>
+      <c r="E342" t="inlineStr"/>
       <c r="F342" t="inlineStr">
         <is>
-          <t>53</t>
+          <t>47</t>
         </is>
       </c>
       <c r="G342" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="343">
@@ -10592,27 +10584,31 @@
       </c>
       <c r="B343" t="inlineStr">
         <is>
-          <t>ISM Manufacturing EmploymentJAN</t>
+          <t>Construction Spending MoMDEC</t>
         </is>
       </c>
       <c r="C343" t="inlineStr">
         <is>
-          <t>50.3</t>
+          <t>0.5%</t>
         </is>
       </c>
       <c r="D343" t="inlineStr">
         <is>
-          <t>45.4</t>
-        </is>
-      </c>
-      <c r="E343" t="inlineStr"/>
+          <t>0.2%</t>
+        </is>
+      </c>
+      <c r="E343" t="inlineStr">
+        <is>
+          <t>0.2%</t>
+        </is>
+      </c>
       <c r="F343" t="inlineStr">
         <is>
-          <t>47</t>
+          <t>0.3%</t>
         </is>
       </c>
       <c r="G343" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="344">
@@ -10623,31 +10619,31 @@
       </c>
       <c r="B344" t="inlineStr">
         <is>
-          <t>Construction Spending MoMDEC</t>
+          <t>ISM Manufacturing PMIJAN</t>
         </is>
       </c>
       <c r="C344" t="inlineStr">
         <is>
-          <t>0.5%</t>
+          <t>50.9</t>
         </is>
       </c>
       <c r="D344" t="inlineStr">
         <is>
-          <t>0.2%</t>
+          <t>49.2</t>
         </is>
       </c>
       <c r="E344" t="inlineStr">
         <is>
-          <t>0.2%</t>
+          <t>49.8</t>
         </is>
       </c>
       <c r="F344" t="inlineStr">
         <is>
-          <t>0.3%</t>
+          <t>49.8</t>
         </is>
       </c>
       <c r="G344" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="345">
@@ -10658,23 +10654,27 @@
       </c>
       <c r="B345" t="inlineStr">
         <is>
-          <t>ISM Manufacturing New OrdersJAN</t>
+          <t>ISM Manufacturing PricesJAN</t>
         </is>
       </c>
       <c r="C345" t="inlineStr">
         <is>
-          <t>55.1</t>
+          <t>54.9</t>
         </is>
       </c>
       <c r="D345" t="inlineStr">
         <is>
-          <t>52.1</t>
-        </is>
-      </c>
-      <c r="E345" t="inlineStr"/>
+          <t>52.5</t>
+        </is>
+      </c>
+      <c r="E345" t="inlineStr">
+        <is>
+          <t>52.6</t>
+        </is>
+      </c>
       <c r="F345" t="inlineStr">
         <is>
-          <t>52.8</t>
+          <t>53</t>
         </is>
       </c>
       <c r="G345" t="n">
@@ -10873,31 +10873,31 @@
       </c>
       <c r="B354" t="inlineStr">
         <is>
-          <t>Factory Orders MoMDEC</t>
+          <t>JOLTs Job OpeningsDEC</t>
         </is>
       </c>
       <c r="C354" t="inlineStr">
         <is>
-          <t>-0.9%</t>
+          <t>7.6M</t>
         </is>
       </c>
       <c r="D354" t="inlineStr">
         <is>
-          <t>-0.8%</t>
+          <t>8.156M</t>
         </is>
       </c>
       <c r="E354" t="inlineStr">
         <is>
-          <t>-0.7%</t>
+          <t>8M</t>
         </is>
       </c>
       <c r="F354" t="inlineStr">
         <is>
-          <t>-0.7%</t>
+          <t>7.8M</t>
         </is>
       </c>
       <c r="G354" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="355">
@@ -10908,27 +10908,31 @@
       </c>
       <c r="B355" t="inlineStr">
         <is>
-          <t>JOLTs Job QuitsDEC</t>
+          <t>Factory Orders MoMDEC</t>
         </is>
       </c>
       <c r="C355" t="inlineStr">
         <is>
-          <t>3.197M</t>
+          <t>-0.9%</t>
         </is>
       </c>
       <c r="D355" t="inlineStr">
         <is>
-          <t>3.130M</t>
-        </is>
-      </c>
-      <c r="E355" t="inlineStr"/>
+          <t>-0.8%</t>
+        </is>
+      </c>
+      <c r="E355" t="inlineStr">
+        <is>
+          <t>-0.7%</t>
+        </is>
+      </c>
       <c r="F355" t="inlineStr">
         <is>
-          <t>3.1M</t>
+          <t>-0.7%</t>
         </is>
       </c>
       <c r="G355" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="356">
@@ -10939,31 +10943,27 @@
       </c>
       <c r="B356" t="inlineStr">
         <is>
-          <t>JOLTs Job OpeningsDEC</t>
+          <t>JOLTs Job QuitsDEC</t>
         </is>
       </c>
       <c r="C356" t="inlineStr">
         <is>
-          <t>7.6M</t>
+          <t>3.197M</t>
         </is>
       </c>
       <c r="D356" t="inlineStr">
         <is>
-          <t>8.156M</t>
-        </is>
-      </c>
-      <c r="E356" t="inlineStr">
-        <is>
-          <t>8M</t>
-        </is>
-      </c>
+          <t>3.130M</t>
+        </is>
+      </c>
+      <c r="E356" t="inlineStr"/>
       <c r="F356" t="inlineStr">
         <is>
-          <t>7.8M</t>
+          <t>3.1M</t>
         </is>
       </c>
       <c r="G356" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="357">
@@ -11325,27 +11325,15 @@
       </c>
       <c r="B370" t="inlineStr">
         <is>
-          <t>ExportsDEC</t>
-        </is>
-      </c>
-      <c r="C370" t="inlineStr">
-        <is>
-          <t>$266.5B</t>
-        </is>
-      </c>
-      <c r="D370" t="inlineStr">
-        <is>
-          <t>$273.6B</t>
-        </is>
-      </c>
+          <t>Treasury Refunding Announcement</t>
+        </is>
+      </c>
+      <c r="C370" t="inlineStr"/>
+      <c r="D370" t="inlineStr"/>
       <c r="E370" t="inlineStr"/>
-      <c r="F370" t="inlineStr">
-        <is>
-          <t>$ 262B</t>
-        </is>
-      </c>
+      <c r="F370" t="inlineStr"/>
       <c r="G370" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="371">
@@ -11356,23 +11344,27 @@
       </c>
       <c r="B371" t="inlineStr">
         <is>
-          <t>ImportsDEC</t>
+          <t>Balance of TradeDEC</t>
         </is>
       </c>
       <c r="C371" t="inlineStr">
         <is>
-          <t>$364.9B</t>
+          <t>$-98.4B</t>
         </is>
       </c>
       <c r="D371" t="inlineStr">
         <is>
-          <t>$352.5B</t>
-        </is>
-      </c>
-      <c r="E371" t="inlineStr"/>
+          <t>$-78.9B</t>
+        </is>
+      </c>
+      <c r="E371" t="inlineStr">
+        <is>
+          <t>$-96.6B</t>
+        </is>
+      </c>
       <c r="F371" t="inlineStr">
         <is>
-          <t>$ 355.0B</t>
+          <t>$ -93.0B</t>
         </is>
       </c>
       <c r="G371" t="n">
@@ -11387,27 +11379,23 @@
       </c>
       <c r="B372" t="inlineStr">
         <is>
-          <t>Balance of TradeDEC</t>
+          <t>ExportsDEC</t>
         </is>
       </c>
       <c r="C372" t="inlineStr">
         <is>
-          <t>$-98.4B</t>
+          <t>$266.5B</t>
         </is>
       </c>
       <c r="D372" t="inlineStr">
         <is>
-          <t>$-78.9B</t>
-        </is>
-      </c>
-      <c r="E372" t="inlineStr">
-        <is>
-          <t>$-96.6B</t>
-        </is>
-      </c>
+          <t>$273.6B</t>
+        </is>
+      </c>
+      <c r="E372" t="inlineStr"/>
       <c r="F372" t="inlineStr">
         <is>
-          <t>$ -93.0B</t>
+          <t>$ 262B</t>
         </is>
       </c>
       <c r="G372" t="n">
@@ -11422,15 +11410,27 @@
       </c>
       <c r="B373" t="inlineStr">
         <is>
-          <t>Treasury Refunding Announcement</t>
-        </is>
-      </c>
-      <c r="C373" t="inlineStr"/>
-      <c r="D373" t="inlineStr"/>
+          <t>ImportsDEC</t>
+        </is>
+      </c>
+      <c r="C373" t="inlineStr">
+        <is>
+          <t>$364.9B</t>
+        </is>
+      </c>
+      <c r="D373" t="inlineStr">
+        <is>
+          <t>$352.5B</t>
+        </is>
+      </c>
       <c r="E373" t="inlineStr"/>
-      <c r="F373" t="inlineStr"/>
+      <c r="F373" t="inlineStr">
+        <is>
+          <t>$ 355.0B</t>
+        </is>
+      </c>
       <c r="G373" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="374">
@@ -11689,22 +11689,22 @@
       </c>
       <c r="B382" t="inlineStr">
         <is>
-          <t>EIA Gasoline Stocks ChangeJAN/31</t>
+          <t>EIA Crude Oil Stocks ChangeJAN/31</t>
         </is>
       </c>
       <c r="C382" t="inlineStr">
         <is>
-          <t>2.233M</t>
+          <t>8.664M</t>
         </is>
       </c>
       <c r="D382" t="inlineStr">
         <is>
-          <t>2.957M</t>
+          <t>3.463M</t>
         </is>
       </c>
       <c r="E382" t="inlineStr">
         <is>
-          <t>1.2M</t>
+          <t>2.6M</t>
         </is>
       </c>
       <c r="F382" t="inlineStr"/>
@@ -11720,17 +11720,17 @@
       </c>
       <c r="B383" t="inlineStr">
         <is>
-          <t>EIA Crude Oil Imports ChangeJAN/31</t>
+          <t>EIA Distillate Fuel Production ChangeJAN/31</t>
         </is>
       </c>
       <c r="C383" t="inlineStr">
         <is>
-          <t>-0.178M</t>
+          <t>-0.186M</t>
         </is>
       </c>
       <c r="D383" t="inlineStr">
         <is>
-          <t>0.532M</t>
+          <t>0.028M</t>
         </is>
       </c>
       <c r="E383" t="inlineStr"/>
@@ -11747,17 +11747,17 @@
       </c>
       <c r="B384" t="inlineStr">
         <is>
-          <t>EIA Cushing Crude Oil Stocks ChangeJAN/31</t>
+          <t>EIA Refinery Crude Runs ChangeJAN/31</t>
         </is>
       </c>
       <c r="C384" t="inlineStr">
         <is>
-          <t>-0.034M</t>
+          <t>0.16M</t>
         </is>
       </c>
       <c r="D384" t="inlineStr">
         <is>
-          <t>0.326M</t>
+          <t>-0.333M</t>
         </is>
       </c>
       <c r="E384" t="inlineStr"/>
@@ -11774,20 +11774,24 @@
       </c>
       <c r="B385" t="inlineStr">
         <is>
-          <t>EIA Gasoline Production ChangeJAN/31</t>
+          <t>EIA Distillate Stocks ChangeJAN/31</t>
         </is>
       </c>
       <c r="C385" t="inlineStr">
         <is>
-          <t>-0.027M</t>
+          <t>-5.471M</t>
         </is>
       </c>
       <c r="D385" t="inlineStr">
         <is>
-          <t>-0.044M</t>
-        </is>
-      </c>
-      <c r="E385" t="inlineStr"/>
+          <t>-4.994M</t>
+        </is>
+      </c>
+      <c r="E385" t="inlineStr">
+        <is>
+          <t>-1.5M</t>
+        </is>
+      </c>
       <c r="F385" t="inlineStr"/>
       <c r="G385" t="n">
         <v>3</v>
@@ -11801,24 +11805,20 @@
       </c>
       <c r="B386" t="inlineStr">
         <is>
-          <t>EIA Distillate Stocks ChangeJAN/31</t>
+          <t>EIA Heating Oil Stocks ChangeJAN/31</t>
         </is>
       </c>
       <c r="C386" t="inlineStr">
         <is>
-          <t>-5.471M</t>
+          <t>0.373M</t>
         </is>
       </c>
       <c r="D386" t="inlineStr">
         <is>
-          <t>-4.994M</t>
-        </is>
-      </c>
-      <c r="E386" t="inlineStr">
-        <is>
-          <t>-1.5M</t>
-        </is>
-      </c>
+          <t>0.128M</t>
+        </is>
+      </c>
+      <c r="E386" t="inlineStr"/>
       <c r="F386" t="inlineStr"/>
       <c r="G386" t="n">
         <v>3</v>
@@ -11832,27 +11832,23 @@
       </c>
       <c r="B387" t="inlineStr">
         <is>
-          <t>EIA Crude Oil Stocks ChangeJAN/31</t>
+          <t>EIA Cushing Crude Oil Stocks ChangeJAN/31</t>
         </is>
       </c>
       <c r="C387" t="inlineStr">
         <is>
-          <t>8.664M</t>
+          <t>-0.034M</t>
         </is>
       </c>
       <c r="D387" t="inlineStr">
         <is>
-          <t>3.463M</t>
-        </is>
-      </c>
-      <c r="E387" t="inlineStr">
-        <is>
-          <t>2.6M</t>
-        </is>
-      </c>
+          <t>0.326M</t>
+        </is>
+      </c>
+      <c r="E387" t="inlineStr"/>
       <c r="F387" t="inlineStr"/>
       <c r="G387" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="388">
@@ -11863,17 +11859,17 @@
       </c>
       <c r="B388" t="inlineStr">
         <is>
-          <t>EIA Refinery Crude Runs ChangeJAN/31</t>
+          <t>EIA Crude Oil Imports ChangeJAN/31</t>
         </is>
       </c>
       <c r="C388" t="inlineStr">
         <is>
-          <t>0.16M</t>
+          <t>-0.178M</t>
         </is>
       </c>
       <c r="D388" t="inlineStr">
         <is>
-          <t>-0.333M</t>
+          <t>0.532M</t>
         </is>
       </c>
       <c r="E388" t="inlineStr"/>
@@ -11890,23 +11886,27 @@
       </c>
       <c r="B389" t="inlineStr">
         <is>
-          <t>EIA Heating Oil Stocks ChangeJAN/31</t>
+          <t>EIA Gasoline Stocks ChangeJAN/31</t>
         </is>
       </c>
       <c r="C389" t="inlineStr">
         <is>
-          <t>0.373M</t>
+          <t>2.233M</t>
         </is>
       </c>
       <c r="D389" t="inlineStr">
         <is>
-          <t>0.128M</t>
-        </is>
-      </c>
-      <c r="E389" t="inlineStr"/>
+          <t>2.957M</t>
+        </is>
+      </c>
+      <c r="E389" t="inlineStr">
+        <is>
+          <t>1.2M</t>
+        </is>
+      </c>
       <c r="F389" t="inlineStr"/>
       <c r="G389" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="390">
@@ -11917,17 +11917,17 @@
       </c>
       <c r="B390" t="inlineStr">
         <is>
-          <t>EIA Distillate Fuel Production ChangeJAN/31</t>
+          <t>EIA Gasoline Production ChangeJAN/31</t>
         </is>
       </c>
       <c r="C390" t="inlineStr">
         <is>
-          <t>-0.186M</t>
+          <t>-0.027M</t>
         </is>
       </c>
       <c r="D390" t="inlineStr">
         <is>
-          <t>0.028M</t>
+          <t>-0.044M</t>
         </is>
       </c>
       <c r="E390" t="inlineStr"/>
@@ -12040,31 +12040,31 @@
       </c>
       <c r="B395" t="inlineStr">
         <is>
-          <t>Unit Labour Costs QoQ PrelQ4</t>
+          <t>Continuing Jobless ClaimsJAN/25</t>
         </is>
       </c>
       <c r="C395" t="inlineStr">
         <is>
-          <t>3%</t>
+          <t>1886K</t>
         </is>
       </c>
       <c r="D395" t="inlineStr">
         <is>
-          <t>0.5%</t>
+          <t>1850K</t>
         </is>
       </c>
       <c r="E395" t="inlineStr">
         <is>
-          <t>3.4%</t>
+          <t>1870K</t>
         </is>
       </c>
       <c r="F395" t="inlineStr">
         <is>
-          <t>3%</t>
+          <t>1855.0K</t>
         </is>
       </c>
       <c r="G395" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="396">
@@ -12075,27 +12075,27 @@
       </c>
       <c r="B396" t="inlineStr">
         <is>
-          <t>Initial Jobless ClaimsFEB/01</t>
+          <t>Nonfarm Productivity QoQ PrelQ4</t>
         </is>
       </c>
       <c r="C396" t="inlineStr">
         <is>
-          <t>219K</t>
+          <t>1.2%</t>
         </is>
       </c>
       <c r="D396" t="inlineStr">
         <is>
-          <t>208K</t>
+          <t>2.3%</t>
         </is>
       </c>
       <c r="E396" t="inlineStr">
         <is>
-          <t>213K</t>
+          <t>1.4%</t>
         </is>
       </c>
       <c r="F396" t="inlineStr">
         <is>
-          <t>215.0K</t>
+          <t>1.9%</t>
         </is>
       </c>
       <c r="G396" t="n">
@@ -12110,31 +12110,27 @@
       </c>
       <c r="B397" t="inlineStr">
         <is>
-          <t>Nonfarm Productivity QoQ PrelQ4</t>
+          <t>Jobless Claims 4-week AverageFEB/01</t>
         </is>
       </c>
       <c r="C397" t="inlineStr">
         <is>
-          <t>1.2%</t>
+          <t>216.75K</t>
         </is>
       </c>
       <c r="D397" t="inlineStr">
         <is>
-          <t>2.3%</t>
-        </is>
-      </c>
-      <c r="E397" t="inlineStr">
-        <is>
-          <t>1.4%</t>
-        </is>
-      </c>
+          <t>212.75K</t>
+        </is>
+      </c>
+      <c r="E397" t="inlineStr"/>
       <c r="F397" t="inlineStr">
         <is>
-          <t>1.9%</t>
+          <t>215.5K</t>
         </is>
       </c>
       <c r="G397" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="398">
@@ -12145,31 +12141,31 @@
       </c>
       <c r="B398" t="inlineStr">
         <is>
-          <t>Continuing Jobless ClaimsJAN/25</t>
+          <t>Unit Labour Costs QoQ PrelQ4</t>
         </is>
       </c>
       <c r="C398" t="inlineStr">
         <is>
-          <t>1886K</t>
+          <t>3%</t>
         </is>
       </c>
       <c r="D398" t="inlineStr">
         <is>
-          <t>1850K</t>
+          <t>0.5%</t>
         </is>
       </c>
       <c r="E398" t="inlineStr">
         <is>
-          <t>1870K</t>
+          <t>3.4%</t>
         </is>
       </c>
       <c r="F398" t="inlineStr">
         <is>
-          <t>1855.0K</t>
+          <t>3%</t>
         </is>
       </c>
       <c r="G398" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="399">
@@ -12180,27 +12176,31 @@
       </c>
       <c r="B399" t="inlineStr">
         <is>
-          <t>Jobless Claims 4-week AverageFEB/01</t>
+          <t>Initial Jobless ClaimsFEB/01</t>
         </is>
       </c>
       <c r="C399" t="inlineStr">
         <is>
-          <t>216.75K</t>
+          <t>219K</t>
         </is>
       </c>
       <c r="D399" t="inlineStr">
         <is>
-          <t>212.75K</t>
-        </is>
-      </c>
-      <c r="E399" t="inlineStr"/>
+          <t>208K</t>
+        </is>
+      </c>
+      <c r="E399" t="inlineStr">
+        <is>
+          <t>213K</t>
+        </is>
+      </c>
       <c r="F399" t="inlineStr">
         <is>
-          <t>215.5K</t>
+          <t>215.0K</t>
         </is>
       </c>
       <c r="G399" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="400">
@@ -12442,27 +12442,23 @@
       </c>
       <c r="B409" t="inlineStr">
         <is>
-          <t>Average Weekly HoursJAN</t>
+          <t>U-6 Unemployment RateJAN</t>
         </is>
       </c>
       <c r="C409" t="inlineStr">
         <is>
-          <t>34.1</t>
+          <t>7.5%</t>
         </is>
       </c>
       <c r="D409" t="inlineStr">
         <is>
-          <t>34.2</t>
-        </is>
-      </c>
-      <c r="E409" t="inlineStr">
-        <is>
-          <t>34.3</t>
-        </is>
-      </c>
+          <t>7.5%</t>
+        </is>
+      </c>
+      <c r="E409" t="inlineStr"/>
       <c r="F409" t="inlineStr">
         <is>
-          <t>34.3</t>
+          <t>7.5%</t>
         </is>
       </c>
       <c r="G409" t="n">
@@ -12477,31 +12473,27 @@
       </c>
       <c r="B410" t="inlineStr">
         <is>
-          <t>Non Farm PayrollsJAN</t>
+          <t>Government PayrollsJAN</t>
         </is>
       </c>
       <c r="C410" t="inlineStr">
         <is>
-          <t>143K</t>
+          <t>32K</t>
         </is>
       </c>
       <c r="D410" t="inlineStr">
         <is>
-          <t>307K</t>
-        </is>
-      </c>
-      <c r="E410" t="inlineStr">
-        <is>
-          <t>170K</t>
-        </is>
-      </c>
+          <t>34K</t>
+        </is>
+      </c>
+      <c r="E410" t="inlineStr"/>
       <c r="F410" t="inlineStr">
         <is>
-          <t>205K</t>
+          <t>25K</t>
         </is>
       </c>
       <c r="G410" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="411">
@@ -12512,31 +12504,31 @@
       </c>
       <c r="B411" t="inlineStr">
         <is>
-          <t>Average Hourly Earnings YoYJAN</t>
+          <t>Nonfarm Payrolls PrivateJAN</t>
         </is>
       </c>
       <c r="C411" t="inlineStr">
         <is>
-          <t>4.1%</t>
+          <t>111K</t>
         </is>
       </c>
       <c r="D411" t="inlineStr">
         <is>
-          <t>4.1%</t>
+          <t>273K</t>
         </is>
       </c>
       <c r="E411" t="inlineStr">
         <is>
-          <t>3.8%</t>
+          <t>141K</t>
         </is>
       </c>
       <c r="F411" t="inlineStr">
         <is>
-          <t>3.9%</t>
+          <t>180K</t>
         </is>
       </c>
       <c r="G411" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="412">
@@ -12547,31 +12539,31 @@
       </c>
       <c r="B412" t="inlineStr">
         <is>
-          <t>Unemployment RateJAN</t>
+          <t>Manufacturing PayrollsJAN</t>
         </is>
       </c>
       <c r="C412" t="inlineStr">
         <is>
-          <t>4%</t>
+          <t>3K</t>
         </is>
       </c>
       <c r="D412" t="inlineStr">
         <is>
-          <t>4.1%</t>
+          <t>-12K</t>
         </is>
       </c>
       <c r="E412" t="inlineStr">
         <is>
-          <t>4.1%</t>
+          <t>-2K</t>
         </is>
       </c>
       <c r="F412" t="inlineStr">
         <is>
-          <t>4.1%</t>
+          <t>-5K</t>
         </is>
       </c>
       <c r="G412" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="413">
@@ -12582,27 +12574,23 @@
       </c>
       <c r="B413" t="inlineStr">
         <is>
-          <t>Average Hourly Earnings MoMJAN</t>
+          <t>Participation RateJAN</t>
         </is>
       </c>
       <c r="C413" t="inlineStr">
         <is>
-          <t>0.5%</t>
+          <t>62.6%</t>
         </is>
       </c>
       <c r="D413" t="inlineStr">
         <is>
-          <t>0.3%</t>
-        </is>
-      </c>
-      <c r="E413" t="inlineStr">
-        <is>
-          <t>0.3%</t>
-        </is>
-      </c>
+          <t>62.5%</t>
+        </is>
+      </c>
+      <c r="E413" t="inlineStr"/>
       <c r="F413" t="inlineStr">
         <is>
-          <t>0.3%</t>
+          <t>62.5%</t>
         </is>
       </c>
       <c r="G413" t="n">
@@ -12617,31 +12605,31 @@
       </c>
       <c r="B414" t="inlineStr">
         <is>
-          <t>Manufacturing PayrollsJAN</t>
+          <t>Unemployment RateJAN</t>
         </is>
       </c>
       <c r="C414" t="inlineStr">
         <is>
-          <t>3K</t>
+          <t>4%</t>
         </is>
       </c>
       <c r="D414" t="inlineStr">
         <is>
-          <t>-12K</t>
+          <t>4.1%</t>
         </is>
       </c>
       <c r="E414" t="inlineStr">
         <is>
-          <t>-2K</t>
+          <t>4.1%</t>
         </is>
       </c>
       <c r="F414" t="inlineStr">
         <is>
-          <t>-5K</t>
+          <t>4.1%</t>
         </is>
       </c>
       <c r="G414" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="415">
@@ -12652,27 +12640,31 @@
       </c>
       <c r="B415" t="inlineStr">
         <is>
-          <t>U-6 Unemployment RateJAN</t>
+          <t>Average Hourly Earnings YoYJAN</t>
         </is>
       </c>
       <c r="C415" t="inlineStr">
         <is>
-          <t>7.5%</t>
+          <t>4.1%</t>
         </is>
       </c>
       <c r="D415" t="inlineStr">
         <is>
-          <t>7.5%</t>
-        </is>
-      </c>
-      <c r="E415" t="inlineStr"/>
+          <t>4.1%</t>
+        </is>
+      </c>
+      <c r="E415" t="inlineStr">
+        <is>
+          <t>3.8%</t>
+        </is>
+      </c>
       <c r="F415" t="inlineStr">
         <is>
-          <t>7.5%</t>
+          <t>3.9%</t>
         </is>
       </c>
       <c r="G415" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="416">
@@ -12683,31 +12675,31 @@
       </c>
       <c r="B416" t="inlineStr">
         <is>
-          <t>Nonfarm Payrolls PrivateJAN</t>
+          <t>Non Farm PayrollsJAN</t>
         </is>
       </c>
       <c r="C416" t="inlineStr">
         <is>
-          <t>111K</t>
+          <t>143K</t>
         </is>
       </c>
       <c r="D416" t="inlineStr">
         <is>
-          <t>273K</t>
+          <t>307K</t>
         </is>
       </c>
       <c r="E416" t="inlineStr">
         <is>
-          <t>141K</t>
+          <t>170K</t>
         </is>
       </c>
       <c r="F416" t="inlineStr">
         <is>
-          <t>180K</t>
+          <t>205K</t>
         </is>
       </c>
       <c r="G416" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="417">
@@ -12718,27 +12710,31 @@
       </c>
       <c r="B417" t="inlineStr">
         <is>
-          <t>Participation RateJAN</t>
+          <t>Average Weekly HoursJAN</t>
         </is>
       </c>
       <c r="C417" t="inlineStr">
         <is>
-          <t>62.6%</t>
+          <t>34.1</t>
         </is>
       </c>
       <c r="D417" t="inlineStr">
         <is>
-          <t>62.5%</t>
-        </is>
-      </c>
-      <c r="E417" t="inlineStr"/>
+          <t>34.2</t>
+        </is>
+      </c>
+      <c r="E417" t="inlineStr">
+        <is>
+          <t>34.3</t>
+        </is>
+      </c>
       <c r="F417" t="inlineStr">
         <is>
-          <t>62.5%</t>
+          <t>34.3</t>
         </is>
       </c>
       <c r="G417" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="418">
@@ -12749,27 +12745,31 @@
       </c>
       <c r="B418" t="inlineStr">
         <is>
-          <t>Government PayrollsJAN</t>
+          <t>Average Hourly Earnings MoMJAN</t>
         </is>
       </c>
       <c r="C418" t="inlineStr">
         <is>
-          <t>32K</t>
+          <t>0.5%</t>
         </is>
       </c>
       <c r="D418" t="inlineStr">
         <is>
-          <t>34K</t>
-        </is>
-      </c>
-      <c r="E418" t="inlineStr"/>
+          <t>0.3%</t>
+        </is>
+      </c>
+      <c r="E418" t="inlineStr">
+        <is>
+          <t>0.3%</t>
+        </is>
+      </c>
       <c r="F418" t="inlineStr">
         <is>
-          <t>25K</t>
+          <t>0.3%</t>
         </is>
       </c>
       <c r="G418" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="419">
@@ -13501,23 +13501,23 @@
       </c>
       <c r="B446" t="inlineStr">
         <is>
-          <t>MBA 30-Year Mortgage RateFEB/07</t>
+          <t>MBA Mortgage ApplicationsFEB/07</t>
         </is>
       </c>
       <c r="C446" t="inlineStr">
         <is>
-          <t>6.95%</t>
+          <t>2.3%</t>
         </is>
       </c>
       <c r="D446" t="inlineStr">
         <is>
-          <t>6.97%</t>
+          <t>2.2%</t>
         </is>
       </c>
       <c r="E446" t="inlineStr"/>
       <c r="F446" t="inlineStr"/>
       <c r="G446" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="447">
@@ -13528,17 +13528,17 @@
       </c>
       <c r="B447" t="inlineStr">
         <is>
-          <t>MBA Mortgage Refinance IndexFEB/07</t>
+          <t>MBA Purchase IndexFEB/07</t>
         </is>
       </c>
       <c r="C447" t="inlineStr">
         <is>
-          <t>640.6</t>
+          <t>153.1</t>
         </is>
       </c>
       <c r="D447" t="inlineStr">
         <is>
-          <t>584.3</t>
+          <t>156.7</t>
         </is>
       </c>
       <c r="E447" t="inlineStr"/>
@@ -13555,17 +13555,17 @@
       </c>
       <c r="B448" t="inlineStr">
         <is>
-          <t>MBA Purchase IndexFEB/07</t>
+          <t>MBA Mortgage Market IndexFEB/07</t>
         </is>
       </c>
       <c r="C448" t="inlineStr">
         <is>
-          <t>153.1</t>
+          <t>230.0</t>
         </is>
       </c>
       <c r="D448" t="inlineStr">
         <is>
-          <t>156.7</t>
+          <t>224.8</t>
         </is>
       </c>
       <c r="E448" t="inlineStr"/>
@@ -13582,23 +13582,23 @@
       </c>
       <c r="B449" t="inlineStr">
         <is>
-          <t>MBA Mortgage ApplicationsFEB/07</t>
+          <t>MBA 30-Year Mortgage RateFEB/07</t>
         </is>
       </c>
       <c r="C449" t="inlineStr">
         <is>
-          <t>2.3%</t>
+          <t>6.95%</t>
         </is>
       </c>
       <c r="D449" t="inlineStr">
         <is>
-          <t>2.2%</t>
+          <t>6.97%</t>
         </is>
       </c>
       <c r="E449" t="inlineStr"/>
       <c r="F449" t="inlineStr"/>
       <c r="G449" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="450">
@@ -13609,17 +13609,17 @@
       </c>
       <c r="B450" t="inlineStr">
         <is>
-          <t>MBA Mortgage Market IndexFEB/07</t>
+          <t>MBA Mortgage Refinance IndexFEB/07</t>
         </is>
       </c>
       <c r="C450" t="inlineStr">
         <is>
-          <t>230.0</t>
+          <t>640.6</t>
         </is>
       </c>
       <c r="D450" t="inlineStr">
         <is>
-          <t>224.8</t>
+          <t>584.3</t>
         </is>
       </c>
       <c r="E450" t="inlineStr"/>
@@ -13842,23 +13842,27 @@
       </c>
       <c r="B457" t="inlineStr">
         <is>
-          <t>EIA Crude Oil Imports ChangeFEB/07</t>
+          <t>EIA Crude Oil Stocks ChangeFEB/07</t>
         </is>
       </c>
       <c r="C457" t="inlineStr">
         <is>
-          <t>-0.184M</t>
+          <t>4.07M</t>
         </is>
       </c>
       <c r="D457" t="inlineStr">
         <is>
-          <t>-0.178M</t>
-        </is>
-      </c>
-      <c r="E457" t="inlineStr"/>
+          <t>8.664M</t>
+        </is>
+      </c>
+      <c r="E457" t="inlineStr">
+        <is>
+          <t>3M</t>
+        </is>
+      </c>
       <c r="F457" t="inlineStr"/>
       <c r="G457" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="458">
@@ -13869,17 +13873,17 @@
       </c>
       <c r="B458" t="inlineStr">
         <is>
-          <t>EIA Refinery Crude Runs ChangeFEB/07</t>
+          <t>EIA Heating Oil Stocks ChangeFEB/07</t>
         </is>
       </c>
       <c r="C458" t="inlineStr">
         <is>
-          <t>0.082M</t>
+          <t>0.159M</t>
         </is>
       </c>
       <c r="D458" t="inlineStr">
         <is>
-          <t>0.16M</t>
+          <t>0.373M</t>
         </is>
       </c>
       <c r="E458" t="inlineStr"/>
@@ -13896,17 +13900,17 @@
       </c>
       <c r="B459" t="inlineStr">
         <is>
-          <t>EIA Gasoline Production ChangeFEB/07</t>
+          <t>EIA Cushing Crude Oil Stocks ChangeFEB/07</t>
         </is>
       </c>
       <c r="C459" t="inlineStr">
         <is>
-          <t>0.18M</t>
+          <t>0.872M</t>
         </is>
       </c>
       <c r="D459" t="inlineStr">
         <is>
-          <t>-0.027M</t>
+          <t>-0.034M</t>
         </is>
       </c>
       <c r="E459" t="inlineStr"/>
@@ -13923,27 +13927,23 @@
       </c>
       <c r="B460" t="inlineStr">
         <is>
-          <t>EIA Gasoline Stocks ChangeFEB/07</t>
+          <t>EIA Distillate Fuel Production ChangeFEB/07</t>
         </is>
       </c>
       <c r="C460" t="inlineStr">
         <is>
-          <t>-3.035M</t>
+          <t>-0.009M</t>
         </is>
       </c>
       <c r="D460" t="inlineStr">
         <is>
-          <t>2.233M</t>
-        </is>
-      </c>
-      <c r="E460" t="inlineStr">
-        <is>
-          <t>1.5M</t>
-        </is>
-      </c>
+          <t>-0.186M</t>
+        </is>
+      </c>
+      <c r="E460" t="inlineStr"/>
       <c r="F460" t="inlineStr"/>
       <c r="G460" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="461">
@@ -13985,23 +13985,27 @@
       </c>
       <c r="B462" t="inlineStr">
         <is>
-          <t>EIA Distillate Fuel Production ChangeFEB/07</t>
+          <t>EIA Gasoline Stocks ChangeFEB/07</t>
         </is>
       </c>
       <c r="C462" t="inlineStr">
         <is>
-          <t>-0.009M</t>
+          <t>-3.035M</t>
         </is>
       </c>
       <c r="D462" t="inlineStr">
         <is>
-          <t>-0.186M</t>
-        </is>
-      </c>
-      <c r="E462" t="inlineStr"/>
+          <t>2.233M</t>
+        </is>
+      </c>
+      <c r="E462" t="inlineStr">
+        <is>
+          <t>1.5M</t>
+        </is>
+      </c>
       <c r="F462" t="inlineStr"/>
       <c r="G462" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="463">
@@ -14012,17 +14016,17 @@
       </c>
       <c r="B463" t="inlineStr">
         <is>
-          <t>EIA Cushing Crude Oil Stocks ChangeFEB/07</t>
+          <t>EIA Gasoline Production ChangeFEB/07</t>
         </is>
       </c>
       <c r="C463" t="inlineStr">
         <is>
-          <t>0.872M</t>
+          <t>0.18M</t>
         </is>
       </c>
       <c r="D463" t="inlineStr">
         <is>
-          <t>-0.034M</t>
+          <t>-0.027M</t>
         </is>
       </c>
       <c r="E463" t="inlineStr"/>
@@ -14039,17 +14043,17 @@
       </c>
       <c r="B464" t="inlineStr">
         <is>
-          <t>EIA Heating Oil Stocks ChangeFEB/07</t>
+          <t>EIA Refinery Crude Runs ChangeFEB/07</t>
         </is>
       </c>
       <c r="C464" t="inlineStr">
         <is>
-          <t>0.159M</t>
+          <t>0.082M</t>
         </is>
       </c>
       <c r="D464" t="inlineStr">
         <is>
-          <t>0.373M</t>
+          <t>0.16M</t>
         </is>
       </c>
       <c r="E464" t="inlineStr"/>
@@ -14066,27 +14070,23 @@
       </c>
       <c r="B465" t="inlineStr">
         <is>
-          <t>EIA Crude Oil Stocks ChangeFEB/07</t>
+          <t>EIA Crude Oil Imports ChangeFEB/07</t>
         </is>
       </c>
       <c r="C465" t="inlineStr">
         <is>
-          <t>4.07M</t>
+          <t>-0.184M</t>
         </is>
       </c>
       <c r="D465" t="inlineStr">
         <is>
-          <t>8.664M</t>
-        </is>
-      </c>
-      <c r="E465" t="inlineStr">
-        <is>
-          <t>3M</t>
-        </is>
-      </c>
+          <t>-0.178M</t>
+        </is>
+      </c>
+      <c r="E465" t="inlineStr"/>
       <c r="F465" t="inlineStr"/>
       <c r="G465" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="466">
@@ -14224,31 +14224,27 @@
       </c>
       <c r="B471" t="inlineStr">
         <is>
-          <t>Initial Jobless ClaimsFEB/08</t>
+          <t>Jobless Claims 4-week AverageFEB/08</t>
         </is>
       </c>
       <c r="C471" t="inlineStr">
         <is>
-          <t>213K</t>
+          <t>216K</t>
         </is>
       </c>
       <c r="D471" t="inlineStr">
         <is>
-          <t>220K</t>
-        </is>
-      </c>
-      <c r="E471" t="inlineStr">
-        <is>
-          <t>215K</t>
-        </is>
-      </c>
+          <t>217K</t>
+        </is>
+      </c>
+      <c r="E471" t="inlineStr"/>
       <c r="F471" t="inlineStr">
         <is>
-          <t>215.0K</t>
+          <t>216.0K</t>
         </is>
       </c>
       <c r="G471" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="472">
@@ -14259,23 +14255,27 @@
       </c>
       <c r="B472" t="inlineStr">
         <is>
-          <t>PPIJAN</t>
+          <t>Continuing Jobless ClaimsFEB/01</t>
         </is>
       </c>
       <c r="C472" t="inlineStr">
         <is>
-          <t>147.716</t>
+          <t>1850K</t>
         </is>
       </c>
       <c r="D472" t="inlineStr">
         <is>
-          <t>147.127</t>
-        </is>
-      </c>
-      <c r="E472" t="inlineStr"/>
+          <t>1886K</t>
+        </is>
+      </c>
+      <c r="E472" t="inlineStr">
+        <is>
+          <t>1880K</t>
+        </is>
+      </c>
       <c r="F472" t="inlineStr">
         <is>
-          <t>147.2</t>
+          <t>1875.0K</t>
         </is>
       </c>
       <c r="G472" t="n">
@@ -14290,31 +14290,31 @@
       </c>
       <c r="B473" t="inlineStr">
         <is>
-          <t>PPI YoYJAN</t>
+          <t>PPI MoMJAN</t>
         </is>
       </c>
       <c r="C473" t="inlineStr">
         <is>
-          <t>3.5%</t>
+          <t>0.4%</t>
         </is>
       </c>
       <c r="D473" t="inlineStr">
         <is>
-          <t>3.5%</t>
+          <t>0.5%</t>
         </is>
       </c>
       <c r="E473" t="inlineStr">
         <is>
-          <t>3.2%</t>
+          <t>0.3%</t>
         </is>
       </c>
       <c r="F473" t="inlineStr">
         <is>
-          <t>3.4%</t>
+          <t>0.3%</t>
         </is>
       </c>
       <c r="G473" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="474">
@@ -14325,27 +14325,27 @@
       </c>
       <c r="B474" t="inlineStr">
         <is>
-          <t>Core PPI YoYJAN</t>
+          <t>PPI Ex Food, Energy and Trade YoYJAN</t>
         </is>
       </c>
       <c r="C474" t="inlineStr">
         <is>
-          <t>3.6%</t>
+          <t>3.4%</t>
         </is>
       </c>
       <c r="D474" t="inlineStr">
         <is>
-          <t>3.7%</t>
+          <t>3.5%</t>
         </is>
       </c>
       <c r="E474" t="inlineStr">
         <is>
+          <t>3.2%</t>
+        </is>
+      </c>
+      <c r="F474" t="inlineStr">
+        <is>
           <t>3.3%</t>
-        </is>
-      </c>
-      <c r="F474" t="inlineStr">
-        <is>
-          <t>3.5%</t>
         </is>
       </c>
       <c r="G474" t="n">
@@ -14360,7 +14360,7 @@
       </c>
       <c r="B475" t="inlineStr">
         <is>
-          <t>Core PPI MoMJAN</t>
+          <t>PPI Ex Food, Energy and Trade MoMJAN</t>
         </is>
       </c>
       <c r="C475" t="inlineStr">
@@ -14373,18 +14373,14 @@
           <t>0.4%</t>
         </is>
       </c>
-      <c r="E475" t="inlineStr">
-        <is>
-          <t>0.3%</t>
-        </is>
-      </c>
+      <c r="E475" t="inlineStr"/>
       <c r="F475" t="inlineStr">
         <is>
-          <t>0.1%</t>
+          <t>0.2%</t>
         </is>
       </c>
       <c r="G475" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="476">
@@ -14395,23 +14391,27 @@
       </c>
       <c r="B476" t="inlineStr">
         <is>
-          <t>PPI Ex Food, Energy and Trade MoMJAN</t>
+          <t>Core PPI YoYJAN</t>
         </is>
       </c>
       <c r="C476" t="inlineStr">
         <is>
-          <t>0.3%</t>
+          <t>3.6%</t>
         </is>
       </c>
       <c r="D476" t="inlineStr">
         <is>
-          <t>0.4%</t>
-        </is>
-      </c>
-      <c r="E476" t="inlineStr"/>
+          <t>3.7%</t>
+        </is>
+      </c>
+      <c r="E476" t="inlineStr">
+        <is>
+          <t>3.3%</t>
+        </is>
+      </c>
       <c r="F476" t="inlineStr">
         <is>
-          <t>0.2%</t>
+          <t>3.5%</t>
         </is>
       </c>
       <c r="G476" t="n">
@@ -14426,27 +14426,27 @@
       </c>
       <c r="B477" t="inlineStr">
         <is>
-          <t>PPI Ex Food, Energy and Trade YoYJAN</t>
+          <t>PPI YoYJAN</t>
         </is>
       </c>
       <c r="C477" t="inlineStr">
         <is>
+          <t>3.5%</t>
+        </is>
+      </c>
+      <c r="D477" t="inlineStr">
+        <is>
+          <t>3.5%</t>
+        </is>
+      </c>
+      <c r="E477" t="inlineStr">
+        <is>
+          <t>3.2%</t>
+        </is>
+      </c>
+      <c r="F477" t="inlineStr">
+        <is>
           <t>3.4%</t>
-        </is>
-      </c>
-      <c r="D477" t="inlineStr">
-        <is>
-          <t>3.5%</t>
-        </is>
-      </c>
-      <c r="E477" t="inlineStr">
-        <is>
-          <t>3.2%</t>
-        </is>
-      </c>
-      <c r="F477" t="inlineStr">
-        <is>
-          <t>3.3%</t>
         </is>
       </c>
       <c r="G477" t="n">
@@ -14461,31 +14461,27 @@
       </c>
       <c r="B478" t="inlineStr">
         <is>
-          <t>PPI MoMJAN</t>
+          <t>PPIJAN</t>
         </is>
       </c>
       <c r="C478" t="inlineStr">
         <is>
-          <t>0.4%</t>
+          <t>147.716</t>
         </is>
       </c>
       <c r="D478" t="inlineStr">
         <is>
-          <t>0.5%</t>
-        </is>
-      </c>
-      <c r="E478" t="inlineStr">
-        <is>
-          <t>0.3%</t>
-        </is>
-      </c>
+          <t>147.127</t>
+        </is>
+      </c>
+      <c r="E478" t="inlineStr"/>
       <c r="F478" t="inlineStr">
         <is>
-          <t>0.3%</t>
+          <t>147.2</t>
         </is>
       </c>
       <c r="G478" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="479">
@@ -14496,31 +14492,31 @@
       </c>
       <c r="B479" t="inlineStr">
         <is>
-          <t>Continuing Jobless ClaimsFEB/01</t>
+          <t>Initial Jobless ClaimsFEB/08</t>
         </is>
       </c>
       <c r="C479" t="inlineStr">
         <is>
-          <t>1850K</t>
+          <t>213K</t>
         </is>
       </c>
       <c r="D479" t="inlineStr">
         <is>
-          <t>1886K</t>
+          <t>220K</t>
         </is>
       </c>
       <c r="E479" t="inlineStr">
         <is>
-          <t>1880K</t>
+          <t>215K</t>
         </is>
       </c>
       <c r="F479" t="inlineStr">
         <is>
-          <t>1875.0K</t>
+          <t>215.0K</t>
         </is>
       </c>
       <c r="G479" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="480">
@@ -14531,27 +14527,31 @@
       </c>
       <c r="B480" t="inlineStr">
         <is>
-          <t>Jobless Claims 4-week AverageFEB/08</t>
+          <t>Core PPI MoMJAN</t>
         </is>
       </c>
       <c r="C480" t="inlineStr">
         <is>
-          <t>216K</t>
+          <t>0.3%</t>
         </is>
       </c>
       <c r="D480" t="inlineStr">
         <is>
-          <t>217K</t>
-        </is>
-      </c>
-      <c r="E480" t="inlineStr"/>
+          <t>0.4%</t>
+        </is>
+      </c>
+      <c r="E480" t="inlineStr">
+        <is>
+          <t>0.3%</t>
+        </is>
+      </c>
       <c r="F480" t="inlineStr">
         <is>
-          <t>216.0K</t>
+          <t>0.1%</t>
         </is>
       </c>
       <c r="G480" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="481">
@@ -14728,22 +14728,22 @@
       </c>
       <c r="B487" t="inlineStr">
         <is>
-          <t>Import Prices MoMJAN</t>
+          <t>Export Prices MoMJAN</t>
         </is>
       </c>
       <c r="C487" t="inlineStr">
         <is>
+          <t>1.3%</t>
+        </is>
+      </c>
+      <c r="D487" t="inlineStr">
+        <is>
+          <t>0.5%</t>
+        </is>
+      </c>
+      <c r="E487" t="inlineStr">
+        <is>
           <t>0.3%</t>
-        </is>
-      </c>
-      <c r="D487" t="inlineStr">
-        <is>
-          <t>0.2%</t>
-        </is>
-      </c>
-      <c r="E487" t="inlineStr">
-        <is>
-          <t>0.4%</t>
         </is>
       </c>
       <c r="F487" t="inlineStr">
@@ -14763,23 +14763,23 @@
       </c>
       <c r="B488" t="inlineStr">
         <is>
-          <t>Export Prices YoYJAN</t>
+          <t>Retail Sales YoYJAN</t>
         </is>
       </c>
       <c r="C488" t="inlineStr">
         <is>
-          <t>2.7%</t>
+          <t>4.2%</t>
         </is>
       </c>
       <c r="D488" t="inlineStr">
         <is>
-          <t>2%</t>
+          <t>4.4%</t>
         </is>
       </c>
       <c r="E488" t="inlineStr"/>
       <c r="F488" t="inlineStr">
         <is>
-          <t>2.3%</t>
+          <t>3.7%</t>
         </is>
       </c>
       <c r="G488" t="n">
@@ -14794,31 +14794,27 @@
       </c>
       <c r="B489" t="inlineStr">
         <is>
-          <t>Retail Sales Control Group MoMJAN</t>
+          <t>Import Prices YoYJAN</t>
         </is>
       </c>
       <c r="C489" t="inlineStr">
         <is>
-          <t>-0.8%</t>
+          <t>1.9%</t>
         </is>
       </c>
       <c r="D489" t="inlineStr">
         <is>
-          <t>0.8%</t>
-        </is>
-      </c>
-      <c r="E489" t="inlineStr">
-        <is>
-          <t>0.3%</t>
-        </is>
-      </c>
+          <t>2.2%</t>
+        </is>
+      </c>
+      <c r="E489" t="inlineStr"/>
       <c r="F489" t="inlineStr">
         <is>
-          <t>0.4%</t>
+          <t>2.8%</t>
         </is>
       </c>
       <c r="G489" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="490">
@@ -14829,31 +14825,31 @@
       </c>
       <c r="B490" t="inlineStr">
         <is>
-          <t>Export Prices MoMJAN</t>
+          <t>Retail Sales MoMJAN</t>
         </is>
       </c>
       <c r="C490" t="inlineStr">
         <is>
-          <t>1.3%</t>
+          <t>-0.9%</t>
         </is>
       </c>
       <c r="D490" t="inlineStr">
         <is>
-          <t>0.5%</t>
+          <t>0.7%</t>
         </is>
       </c>
       <c r="E490" t="inlineStr">
         <is>
-          <t>0.3%</t>
+          <t>-0.1%</t>
         </is>
       </c>
       <c r="F490" t="inlineStr">
         <is>
-          <t>0.3%</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="G490" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="491">
@@ -14864,27 +14860,31 @@
       </c>
       <c r="B491" t="inlineStr">
         <is>
-          <t>Retail Sales Ex Gas/Autos MoMJAN</t>
+          <t>Retail Sales Ex Autos MoMJAN</t>
         </is>
       </c>
       <c r="C491" t="inlineStr">
         <is>
-          <t>-0.5%</t>
+          <t>-0.4%</t>
         </is>
       </c>
       <c r="D491" t="inlineStr">
         <is>
-          <t>0.5%</t>
-        </is>
-      </c>
-      <c r="E491" t="inlineStr"/>
+          <t>0.7%</t>
+        </is>
+      </c>
+      <c r="E491" t="inlineStr">
+        <is>
+          <t>0.3%</t>
+        </is>
+      </c>
       <c r="F491" t="inlineStr">
         <is>
-          <t>0.2%</t>
+          <t>0.3%</t>
         </is>
       </c>
       <c r="G491" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="492">
@@ -14895,17 +14895,17 @@
       </c>
       <c r="B492" t="inlineStr">
         <is>
-          <t>Retail Sales Ex Autos MoMJAN</t>
+          <t>Retail Sales Control Group MoMJAN</t>
         </is>
       </c>
       <c r="C492" t="inlineStr">
         <is>
-          <t>-0.4%</t>
+          <t>-0.8%</t>
         </is>
       </c>
       <c r="D492" t="inlineStr">
         <is>
-          <t>0.7%</t>
+          <t>0.8%</t>
         </is>
       </c>
       <c r="E492" t="inlineStr">
@@ -14915,7 +14915,7 @@
       </c>
       <c r="F492" t="inlineStr">
         <is>
-          <t>0.3%</t>
+          <t>0.4%</t>
         </is>
       </c>
       <c r="G492" t="n">
@@ -14930,31 +14930,27 @@
       </c>
       <c r="B493" t="inlineStr">
         <is>
-          <t>Retail Sales MoMJAN</t>
+          <t>Export Prices YoYJAN</t>
         </is>
       </c>
       <c r="C493" t="inlineStr">
         <is>
-          <t>-0.9%</t>
+          <t>2.7%</t>
         </is>
       </c>
       <c r="D493" t="inlineStr">
         <is>
-          <t>0.7%</t>
-        </is>
-      </c>
-      <c r="E493" t="inlineStr">
-        <is>
-          <t>-0.1%</t>
-        </is>
-      </c>
+          <t>2%</t>
+        </is>
+      </c>
+      <c r="E493" t="inlineStr"/>
       <c r="F493" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>2.3%</t>
         </is>
       </c>
       <c r="G493" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="494">
@@ -14965,27 +14961,31 @@
       </c>
       <c r="B494" t="inlineStr">
         <is>
-          <t>Import Prices YoYJAN</t>
+          <t>Import Prices MoMJAN</t>
         </is>
       </c>
       <c r="C494" t="inlineStr">
         <is>
-          <t>1.9%</t>
+          <t>0.3%</t>
         </is>
       </c>
       <c r="D494" t="inlineStr">
         <is>
-          <t>2.2%</t>
-        </is>
-      </c>
-      <c r="E494" t="inlineStr"/>
+          <t>0.2%</t>
+        </is>
+      </c>
+      <c r="E494" t="inlineStr">
+        <is>
+          <t>0.4%</t>
+        </is>
+      </c>
       <c r="F494" t="inlineStr">
         <is>
-          <t>2.8%</t>
+          <t>0.3%</t>
         </is>
       </c>
       <c r="G494" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="495">
@@ -14996,23 +14996,23 @@
       </c>
       <c r="B495" t="inlineStr">
         <is>
-          <t>Retail Sales YoYJAN</t>
+          <t>Retail Sales Ex Gas/Autos MoMJAN</t>
         </is>
       </c>
       <c r="C495" t="inlineStr">
         <is>
-          <t>4.2%</t>
+          <t>-0.5%</t>
         </is>
       </c>
       <c r="D495" t="inlineStr">
         <is>
-          <t>4.4%</t>
+          <t>0.5%</t>
         </is>
       </c>
       <c r="E495" t="inlineStr"/>
       <c r="F495" t="inlineStr">
         <is>
-          <t>3.7%</t>
+          <t>0.2%</t>
         </is>
       </c>
       <c r="G495" t="n">
@@ -15629,17 +15629,17 @@
       </c>
       <c r="B518" t="inlineStr">
         <is>
-          <t>Foreign Bond InvestmentDEC</t>
+          <t>Overall Net Capital FlowsDEC</t>
         </is>
       </c>
       <c r="C518" t="inlineStr">
         <is>
-          <t>$-49.7B</t>
+          <t>$87.1B</t>
         </is>
       </c>
       <c r="D518" t="inlineStr">
         <is>
-          <t>$-34.4B</t>
+          <t>$134.1B</t>
         </is>
       </c>
       <c r="E518" t="inlineStr"/>
@@ -15687,17 +15687,17 @@
       </c>
       <c r="B520" t="inlineStr">
         <is>
-          <t>Overall Net Capital FlowsDEC</t>
+          <t>Foreign Bond InvestmentDEC</t>
         </is>
       </c>
       <c r="C520" t="inlineStr">
         <is>
-          <t>$87.1B</t>
+          <t>$-49.7B</t>
         </is>
       </c>
       <c r="D520" t="inlineStr">
         <is>
-          <t>$134.1B</t>
+          <t>$-34.4B</t>
         </is>
       </c>
       <c r="E520" t="inlineStr"/>
@@ -17326,7 +17326,7 @@
       </c>
       <c r="B577" t="inlineStr">
         <is>
-          <t>Fed Jefferson Speech</t>
+          <t>Fed Daly Speech</t>
         </is>
       </c>
       <c r="C577" t="inlineStr"/>
@@ -17345,7 +17345,7 @@
       </c>
       <c r="B578" t="inlineStr">
         <is>
-          <t>Fed Daly Speech</t>
+          <t>Fed Jefferson Speech</t>
         </is>
       </c>
       <c r="C578" t="inlineStr"/>
@@ -17630,19 +17630,23 @@
       </c>
       <c r="B589" t="inlineStr">
         <is>
-          <t>House Price Index YoYDEC</t>
-        </is>
-      </c>
-      <c r="C589" t="inlineStr"/>
+          <t>S&amp;P/Case-Shiller Home Price MoMDEC</t>
+        </is>
+      </c>
+      <c r="C589" t="inlineStr">
+        <is>
+          <t>-0.1%</t>
+        </is>
+      </c>
       <c r="D589" t="inlineStr">
         <is>
-          <t>4.2%</t>
+          <t>-0.1%</t>
         </is>
       </c>
       <c r="E589" t="inlineStr"/>
       <c r="F589" t="inlineStr">
         <is>
-          <t>4.1%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="G589" t="n">
@@ -17657,19 +17661,27 @@
       </c>
       <c r="B590" t="inlineStr">
         <is>
-          <t>House Price IndexDEC</t>
-        </is>
-      </c>
-      <c r="C590" t="inlineStr"/>
+          <t>House Price Index MoMDEC</t>
+        </is>
+      </c>
+      <c r="C590" t="inlineStr">
+        <is>
+          <t>0.4%</t>
+        </is>
+      </c>
       <c r="D590" t="inlineStr">
         <is>
-          <t>433.4</t>
-        </is>
-      </c>
-      <c r="E590" t="inlineStr"/>
+          <t>0.4%</t>
+        </is>
+      </c>
+      <c r="E590" t="inlineStr">
+        <is>
+          <t>0.2%</t>
+        </is>
+      </c>
       <c r="F590" t="inlineStr">
         <is>
-          <t>434.3</t>
+          <t>0.2%</t>
         </is>
       </c>
       <c r="G590" t="n">
@@ -17684,27 +17696,27 @@
       </c>
       <c r="B591" t="inlineStr">
         <is>
-          <t>S&amp;P/Case-Shiller Home Price YoYDEC</t>
-        </is>
-      </c>
-      <c r="C591" t="inlineStr"/>
+          <t>House Price IndexDEC</t>
+        </is>
+      </c>
+      <c r="C591" t="inlineStr">
+        <is>
+          <t>436.1</t>
+        </is>
+      </c>
       <c r="D591" t="inlineStr">
         <is>
-          <t>4.3%</t>
-        </is>
-      </c>
-      <c r="E591" t="inlineStr">
-        <is>
-          <t>4.4%</t>
-        </is>
-      </c>
+          <t>434.3</t>
+        </is>
+      </c>
+      <c r="E591" t="inlineStr"/>
       <c r="F591" t="inlineStr">
         <is>
-          <t>4.4%</t>
+          <t>434.3</t>
         </is>
       </c>
       <c r="G591" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="592">
@@ -17715,31 +17727,27 @@
       </c>
       <c r="B592" t="inlineStr">
         <is>
-          <t>S&amp;P/Case-Shiller Home Price YoYDEC</t>
+          <t>House Price Index YoYDEC</t>
         </is>
       </c>
       <c r="C592" t="inlineStr">
         <is>
+          <t>4.7%</t>
+        </is>
+      </c>
+      <c r="D592" t="inlineStr">
+        <is>
           <t>4.5%</t>
         </is>
       </c>
-      <c r="D592" t="inlineStr">
-        <is>
-          <t>4.3%</t>
-        </is>
-      </c>
-      <c r="E592" t="inlineStr">
-        <is>
-          <t>4.4%</t>
-        </is>
-      </c>
+      <c r="E592" t="inlineStr"/>
       <c r="F592" t="inlineStr">
         <is>
-          <t>4.4%</t>
+          <t>4.1%</t>
         </is>
       </c>
       <c r="G592" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="593">
@@ -17750,19 +17758,23 @@
       </c>
       <c r="B593" t="inlineStr">
         <is>
-          <t>S&amp;P/Case-Shiller Home Price MoMDEC</t>
+          <t>House Price Index MoMDEC</t>
         </is>
       </c>
       <c r="C593" t="inlineStr"/>
       <c r="D593" t="inlineStr">
         <is>
-          <t>-0.1%</t>
-        </is>
-      </c>
-      <c r="E593" t="inlineStr"/>
+          <t>0.3%</t>
+        </is>
+      </c>
+      <c r="E593" t="inlineStr">
+        <is>
+          <t>0.2%</t>
+        </is>
+      </c>
       <c r="F593" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>0.2%</t>
         </is>
       </c>
       <c r="G593" t="n">
@@ -17777,23 +17789,19 @@
       </c>
       <c r="B594" t="inlineStr">
         <is>
-          <t>House Price Index MoMDEC</t>
+          <t>S&amp;P/Case-Shiller Home Price MoMDEC</t>
         </is>
       </c>
       <c r="C594" t="inlineStr"/>
       <c r="D594" t="inlineStr">
         <is>
-          <t>0.3%</t>
-        </is>
-      </c>
-      <c r="E594" t="inlineStr">
-        <is>
-          <t>0.2%</t>
-        </is>
-      </c>
+          <t>-0.1%</t>
+        </is>
+      </c>
+      <c r="E594" t="inlineStr"/>
       <c r="F594" t="inlineStr">
         <is>
-          <t>0.2%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="G594" t="n">
@@ -17808,27 +17816,31 @@
       </c>
       <c r="B595" t="inlineStr">
         <is>
-          <t>S&amp;P/Case-Shiller Home Price MoMDEC</t>
+          <t>S&amp;P/Case-Shiller Home Price YoYDEC</t>
         </is>
       </c>
       <c r="C595" t="inlineStr">
         <is>
-          <t>-0.1%</t>
+          <t>4.5%</t>
         </is>
       </c>
       <c r="D595" t="inlineStr">
         <is>
-          <t>-0.1%</t>
-        </is>
-      </c>
-      <c r="E595" t="inlineStr"/>
+          <t>4.3%</t>
+        </is>
+      </c>
+      <c r="E595" t="inlineStr">
+        <is>
+          <t>4.4%</t>
+        </is>
+      </c>
       <c r="F595" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>4.4%</t>
         </is>
       </c>
       <c r="G595" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="596">
@@ -17839,27 +17851,27 @@
       </c>
       <c r="B596" t="inlineStr">
         <is>
-          <t>House Price Index YoYDEC</t>
-        </is>
-      </c>
-      <c r="C596" t="inlineStr">
-        <is>
-          <t>4.7%</t>
-        </is>
-      </c>
+          <t>S&amp;P/Case-Shiller Home Price YoYDEC</t>
+        </is>
+      </c>
+      <c r="C596" t="inlineStr"/>
       <c r="D596" t="inlineStr">
         <is>
-          <t>4.5%</t>
-        </is>
-      </c>
-      <c r="E596" t="inlineStr"/>
+          <t>4.3%</t>
+        </is>
+      </c>
+      <c r="E596" t="inlineStr">
+        <is>
+          <t>4.4%</t>
+        </is>
+      </c>
       <c r="F596" t="inlineStr">
         <is>
-          <t>4.1%</t>
+          <t>4.4%</t>
         </is>
       </c>
       <c r="G596" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="597">
@@ -17873,14 +17885,10 @@
           <t>House Price IndexDEC</t>
         </is>
       </c>
-      <c r="C597" t="inlineStr">
-        <is>
-          <t>436.1</t>
-        </is>
-      </c>
+      <c r="C597" t="inlineStr"/>
       <c r="D597" t="inlineStr">
         <is>
-          <t>434.3</t>
+          <t>433.4</t>
         </is>
       </c>
       <c r="E597" t="inlineStr"/>
@@ -17901,27 +17909,19 @@
       </c>
       <c r="B598" t="inlineStr">
         <is>
-          <t>House Price Index MoMDEC</t>
-        </is>
-      </c>
-      <c r="C598" t="inlineStr">
-        <is>
-          <t>0.4%</t>
-        </is>
-      </c>
+          <t>House Price Index YoYDEC</t>
+        </is>
+      </c>
+      <c r="C598" t="inlineStr"/>
       <c r="D598" t="inlineStr">
         <is>
-          <t>0.4%</t>
-        </is>
-      </c>
-      <c r="E598" t="inlineStr">
-        <is>
-          <t>0.2%</t>
-        </is>
-      </c>
+          <t>4.2%</t>
+        </is>
+      </c>
+      <c r="E598" t="inlineStr"/>
       <c r="F598" t="inlineStr">
         <is>
-          <t>0.2%</t>
+          <t>4.1%</t>
         </is>
       </c>
       <c r="G598" t="n">
@@ -18187,7 +18187,11 @@
           <t>Dallas Fed Services IndexFEB</t>
         </is>
       </c>
-      <c r="C607" t="inlineStr"/>
+      <c r="C607" t="inlineStr">
+        <is>
+          <t>4.6</t>
+        </is>
+      </c>
       <c r="D607" t="inlineStr">
         <is>
           <t>7.4</t>
@@ -18214,7 +18218,11 @@
           <t>Dallas Fed Services Revenues IndexFEB</t>
         </is>
       </c>
-      <c r="C608" t="inlineStr"/>
+      <c r="C608" t="inlineStr">
+        <is>
+          <t>8.2</t>
+        </is>
+      </c>
       <c r="D608" t="inlineStr">
         <is>
           <t>5.7</t>
@@ -18238,23 +18246,19 @@
       </c>
       <c r="B609" t="inlineStr">
         <is>
-          <t>Dallas Fed Services Revenues IndexFEB</t>
-        </is>
-      </c>
-      <c r="C609" t="inlineStr">
-        <is>
-          <t>8.2</t>
-        </is>
-      </c>
+          <t>Dallas Fed Services IndexFEB</t>
+        </is>
+      </c>
+      <c r="C609" t="inlineStr"/>
       <c r="D609" t="inlineStr">
         <is>
-          <t>5.7</t>
+          <t>7.4</t>
         </is>
       </c>
       <c r="E609" t="inlineStr"/>
       <c r="F609" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>9</t>
         </is>
       </c>
       <c r="G609" t="n">
@@ -18269,23 +18273,19 @@
       </c>
       <c r="B610" t="inlineStr">
         <is>
-          <t>Dallas Fed Services IndexFEB</t>
-        </is>
-      </c>
-      <c r="C610" t="inlineStr">
-        <is>
-          <t>4.6</t>
-        </is>
-      </c>
+          <t>Dallas Fed Services Revenues IndexFEB</t>
+        </is>
+      </c>
+      <c r="C610" t="inlineStr"/>
       <c r="D610" t="inlineStr">
         <is>
-          <t>7.4</t>
+          <t>5.7</t>
         </is>
       </c>
       <c r="E610" t="inlineStr"/>
       <c r="F610" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>7</t>
         </is>
       </c>
       <c r="G610" t="n">
@@ -18499,7 +18499,11 @@
           <t>MBA Purchase IndexFEB/21</t>
         </is>
       </c>
-      <c r="C619" t="inlineStr"/>
+      <c r="C619" t="inlineStr">
+        <is>
+          <t>144.3</t>
+        </is>
+      </c>
       <c r="D619" t="inlineStr">
         <is>
           <t>144.0</t>
@@ -18519,19 +18523,23 @@
       </c>
       <c r="B620" t="inlineStr">
         <is>
-          <t>MBA Mortgage Refinance IndexFEB/21</t>
-        </is>
-      </c>
-      <c r="C620" t="inlineStr"/>
+          <t>MBA 30-Year Mortgage RateFEB/21</t>
+        </is>
+      </c>
+      <c r="C620" t="inlineStr">
+        <is>
+          <t>6.88%</t>
+        </is>
+      </c>
       <c r="D620" t="inlineStr">
         <is>
-          <t>593.6</t>
+          <t>6.93%</t>
         </is>
       </c>
       <c r="E620" t="inlineStr"/>
       <c r="F620" t="inlineStr"/>
       <c r="G620" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="621">
@@ -18542,17 +18550,17 @@
       </c>
       <c r="B621" t="inlineStr">
         <is>
-          <t>MBA Mortgage ApplicationsFEB/21</t>
+          <t>MBA Mortgage Refinance IndexFEB/21</t>
         </is>
       </c>
       <c r="C621" t="inlineStr">
         <is>
-          <t>-1.2%</t>
+          <t>572.5</t>
         </is>
       </c>
       <c r="D621" t="inlineStr">
         <is>
-          <t>-6.6%</t>
+          <t>593.6</t>
         </is>
       </c>
       <c r="E621" t="inlineStr"/>
@@ -18569,19 +18577,23 @@
       </c>
       <c r="B622" t="inlineStr">
         <is>
-          <t>MBA 30-Year Mortgage RateFEB/21</t>
-        </is>
-      </c>
-      <c r="C622" t="inlineStr"/>
+          <t>MBA Mortgage Market IndexFEB/21</t>
+        </is>
+      </c>
+      <c r="C622" t="inlineStr">
+        <is>
+          <t>212.3</t>
+        </is>
+      </c>
       <c r="D622" t="inlineStr">
         <is>
-          <t>6.93%</t>
+          <t>214.9</t>
         </is>
       </c>
       <c r="E622" t="inlineStr"/>
       <c r="F622" t="inlineStr"/>
       <c r="G622" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="623">
@@ -18592,13 +18604,13 @@
       </c>
       <c r="B623" t="inlineStr">
         <is>
-          <t>MBA Mortgage ApplicationsFEB/21</t>
+          <t>MBA Mortgage Market IndexFEB/21</t>
         </is>
       </c>
       <c r="C623" t="inlineStr"/>
       <c r="D623" t="inlineStr">
         <is>
-          <t>-6.6%</t>
+          <t>214.9</t>
         </is>
       </c>
       <c r="E623" t="inlineStr"/>
@@ -18615,13 +18627,13 @@
       </c>
       <c r="B624" t="inlineStr">
         <is>
-          <t>MBA Mortgage Market IndexFEB/21</t>
+          <t>MBA Mortgage Refinance IndexFEB/21</t>
         </is>
       </c>
       <c r="C624" t="inlineStr"/>
       <c r="D624" t="inlineStr">
         <is>
-          <t>214.9</t>
+          <t>593.6</t>
         </is>
       </c>
       <c r="E624" t="inlineStr"/>
@@ -18638,23 +18650,19 @@
       </c>
       <c r="B625" t="inlineStr">
         <is>
-          <t>MBA Purchase IndexFEB/21</t>
-        </is>
-      </c>
-      <c r="C625" t="inlineStr">
-        <is>
-          <t>144.3</t>
-        </is>
-      </c>
+          <t>MBA 30-Year Mortgage RateFEB/21</t>
+        </is>
+      </c>
+      <c r="C625" t="inlineStr"/>
       <c r="D625" t="inlineStr">
         <is>
-          <t>144.0</t>
+          <t>6.93%</t>
         </is>
       </c>
       <c r="E625" t="inlineStr"/>
       <c r="F625" t="inlineStr"/>
       <c r="G625" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="626">
@@ -18665,17 +18673,17 @@
       </c>
       <c r="B626" t="inlineStr">
         <is>
-          <t>MBA Mortgage Market IndexFEB/21</t>
+          <t>MBA Mortgage ApplicationsFEB/21</t>
         </is>
       </c>
       <c r="C626" t="inlineStr">
         <is>
-          <t>212.3</t>
+          <t>-1.2%</t>
         </is>
       </c>
       <c r="D626" t="inlineStr">
         <is>
-          <t>214.9</t>
+          <t>-6.6%</t>
         </is>
       </c>
       <c r="E626" t="inlineStr"/>
@@ -18692,17 +18700,13 @@
       </c>
       <c r="B627" t="inlineStr">
         <is>
-          <t>MBA Mortgage Refinance IndexFEB/21</t>
-        </is>
-      </c>
-      <c r="C627" t="inlineStr">
-        <is>
-          <t>572.5</t>
-        </is>
-      </c>
+          <t>MBA Mortgage ApplicationsFEB/21</t>
+        </is>
+      </c>
+      <c r="C627" t="inlineStr"/>
       <c r="D627" t="inlineStr">
         <is>
-          <t>593.6</t>
+          <t>-6.6%</t>
         </is>
       </c>
       <c r="E627" t="inlineStr"/>
@@ -18719,23 +18723,19 @@
       </c>
       <c r="B628" t="inlineStr">
         <is>
-          <t>MBA 30-Year Mortgage RateFEB/21</t>
-        </is>
-      </c>
-      <c r="C628" t="inlineStr">
-        <is>
-          <t>6.88%</t>
-        </is>
-      </c>
+          <t>MBA Purchase IndexFEB/21</t>
+        </is>
+      </c>
+      <c r="C628" t="inlineStr"/>
       <c r="D628" t="inlineStr">
         <is>
-          <t>6.93%</t>
+          <t>144.0</t>
         </is>
       </c>
       <c r="E628" t="inlineStr"/>
       <c r="F628" t="inlineStr"/>
       <c r="G628" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="629">
@@ -18908,10 +18908,14 @@
           <t>New Home SalesJAN</t>
         </is>
       </c>
-      <c r="C634" t="inlineStr"/>
+      <c r="C634" t="inlineStr">
+        <is>
+          <t>0.657M</t>
+        </is>
+      </c>
       <c r="D634" t="inlineStr">
         <is>
-          <t>0.698M</t>
+          <t>0.734M</t>
         </is>
       </c>
       <c r="E634" t="inlineStr">
@@ -18939,10 +18943,14 @@
           <t>New Home Sales MoMJAN</t>
         </is>
       </c>
-      <c r="C635" t="inlineStr"/>
+      <c r="C635" t="inlineStr">
+        <is>
+          <t>-10.5%</t>
+        </is>
+      </c>
       <c r="D635" t="inlineStr">
         <is>
-          <t>3.6%</t>
+          <t>8.1%</t>
         </is>
       </c>
       <c r="E635" t="inlineStr"/>
@@ -18966,14 +18974,10 @@
           <t>New Home Sales MoMJAN</t>
         </is>
       </c>
-      <c r="C636" t="inlineStr">
-        <is>
-          <t>-10.5%</t>
-        </is>
-      </c>
+      <c r="C636" t="inlineStr"/>
       <c r="D636" t="inlineStr">
         <is>
-          <t>8.1%</t>
+          <t>3.6%</t>
         </is>
       </c>
       <c r="E636" t="inlineStr"/>
@@ -18997,14 +19001,10 @@
           <t>New Home SalesJAN</t>
         </is>
       </c>
-      <c r="C637" t="inlineStr">
-        <is>
-          <t>0.657M</t>
-        </is>
-      </c>
+      <c r="C637" t="inlineStr"/>
       <c r="D637" t="inlineStr">
         <is>
-          <t>0.734M</t>
+          <t>0.698M</t>
         </is>
       </c>
       <c r="E637" t="inlineStr">
@@ -19029,27 +19029,19 @@
       </c>
       <c r="B638" t="inlineStr">
         <is>
-          <t>EIA Gasoline Stocks ChangeFEB/21</t>
-        </is>
-      </c>
-      <c r="C638" t="inlineStr">
-        <is>
-          <t>0.369M</t>
-        </is>
-      </c>
+          <t>EIA Cushing Crude Oil Stocks ChangeFEB/21</t>
+        </is>
+      </c>
+      <c r="C638" t="inlineStr"/>
       <c r="D638" t="inlineStr">
         <is>
-          <t>-0.151M</t>
-        </is>
-      </c>
-      <c r="E638" t="inlineStr">
-        <is>
-          <t>-1.30M</t>
-        </is>
-      </c>
+          <t>1.472M</t>
+        </is>
+      </c>
+      <c r="E638" t="inlineStr"/>
       <c r="F638" t="inlineStr"/>
       <c r="G638" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="639">
@@ -19060,23 +19052,23 @@
       </c>
       <c r="B639" t="inlineStr">
         <is>
-          <t>EIA Crude Oil Imports ChangeFEB/21</t>
-        </is>
-      </c>
-      <c r="C639" t="inlineStr">
-        <is>
-          <t>0.292M</t>
-        </is>
-      </c>
+          <t>EIA Gasoline Stocks ChangeFEB/21</t>
+        </is>
+      </c>
+      <c r="C639" t="inlineStr"/>
       <c r="D639" t="inlineStr">
         <is>
-          <t>-0.961M</t>
-        </is>
-      </c>
-      <c r="E639" t="inlineStr"/>
+          <t>-0.151M</t>
+        </is>
+      </c>
+      <c r="E639" t="inlineStr">
+        <is>
+          <t>-1.30M</t>
+        </is>
+      </c>
       <c r="F639" t="inlineStr"/>
       <c r="G639" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="640">
@@ -19087,23 +19079,23 @@
       </c>
       <c r="B640" t="inlineStr">
         <is>
-          <t>EIA Cushing Crude Oil Stocks ChangeFEB/21</t>
-        </is>
-      </c>
-      <c r="C640" t="inlineStr">
-        <is>
-          <t>1.282M</t>
-        </is>
-      </c>
+          <t>EIA Crude Oil Stocks ChangeFEB/21</t>
+        </is>
+      </c>
+      <c r="C640" t="inlineStr"/>
       <c r="D640" t="inlineStr">
         <is>
-          <t>1.472M</t>
-        </is>
-      </c>
-      <c r="E640" t="inlineStr"/>
+          <t>4.633M</t>
+        </is>
+      </c>
+      <c r="E640" t="inlineStr">
+        <is>
+          <t>2.34M</t>
+        </is>
+      </c>
       <c r="F640" t="inlineStr"/>
       <c r="G640" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="641">
@@ -19117,11 +19109,7 @@
           <t>EIA Distillate Fuel Production ChangeFEB/21</t>
         </is>
       </c>
-      <c r="C641" t="inlineStr">
-        <is>
-          <t>0.439M</t>
-        </is>
-      </c>
+      <c r="C641" t="inlineStr"/>
       <c r="D641" t="inlineStr">
         <is>
           <t>0.18M</t>
@@ -19144,11 +19132,7 @@
           <t>EIA Distillate Stocks ChangeFEB/21</t>
         </is>
       </c>
-      <c r="C642" t="inlineStr">
-        <is>
-          <t>3.908M</t>
-        </is>
-      </c>
+      <c r="C642" t="inlineStr"/>
       <c r="D642" t="inlineStr">
         <is>
           <t>-2.051M</t>
@@ -19175,11 +19159,7 @@
           <t>EIA Gasoline Production ChangeFEB/21</t>
         </is>
       </c>
-      <c r="C643" t="inlineStr">
-        <is>
-          <t>-0.02M</t>
-        </is>
-      </c>
+      <c r="C643" t="inlineStr"/>
       <c r="D643" t="inlineStr">
         <is>
           <t>-0.156M</t>
@@ -19202,11 +19182,7 @@
           <t>EIA Heating Oil Stocks ChangeFEB/21</t>
         </is>
       </c>
-      <c r="C644" t="inlineStr">
-        <is>
-          <t>0.134M</t>
-        </is>
-      </c>
+      <c r="C644" t="inlineStr"/>
       <c r="D644" t="inlineStr">
         <is>
           <t>-0.343M</t>
@@ -19229,11 +19205,7 @@
           <t>EIA Refinery Crude Runs ChangeFEB/21</t>
         </is>
       </c>
-      <c r="C645" t="inlineStr">
-        <is>
-          <t>0.317M</t>
-        </is>
-      </c>
+      <c r="C645" t="inlineStr"/>
       <c r="D645" t="inlineStr">
         <is>
           <t>-0.015M</t>
@@ -19253,19 +19225,27 @@
       </c>
       <c r="B646" t="inlineStr">
         <is>
-          <t>EIA Crude Oil Imports ChangeFEB/21</t>
-        </is>
-      </c>
-      <c r="C646" t="inlineStr"/>
+          <t>EIA Crude Oil Stocks ChangeFEB/21</t>
+        </is>
+      </c>
+      <c r="C646" t="inlineStr">
+        <is>
+          <t>-2.332M</t>
+        </is>
+      </c>
       <c r="D646" t="inlineStr">
         <is>
-          <t>-0.961M</t>
-        </is>
-      </c>
-      <c r="E646" t="inlineStr"/>
+          <t>4.633M</t>
+        </is>
+      </c>
+      <c r="E646" t="inlineStr">
+        <is>
+          <t>2.54M</t>
+        </is>
+      </c>
       <c r="F646" t="inlineStr"/>
       <c r="G646" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="647">
@@ -19279,7 +19259,11 @@
           <t>EIA Refinery Crude Runs ChangeFEB/21</t>
         </is>
       </c>
-      <c r="C647" t="inlineStr"/>
+      <c r="C647" t="inlineStr">
+        <is>
+          <t>0.317M</t>
+        </is>
+      </c>
       <c r="D647" t="inlineStr">
         <is>
           <t>-0.015M</t>
@@ -19302,7 +19286,11 @@
           <t>EIA Heating Oil Stocks ChangeFEB/21</t>
         </is>
       </c>
-      <c r="C648" t="inlineStr"/>
+      <c r="C648" t="inlineStr">
+        <is>
+          <t>0.134M</t>
+        </is>
+      </c>
       <c r="D648" t="inlineStr">
         <is>
           <t>-0.343M</t>
@@ -19325,7 +19313,11 @@
           <t>EIA Gasoline Production ChangeFEB/21</t>
         </is>
       </c>
-      <c r="C649" t="inlineStr"/>
+      <c r="C649" t="inlineStr">
+        <is>
+          <t>-0.02M</t>
+        </is>
+      </c>
       <c r="D649" t="inlineStr">
         <is>
           <t>-0.156M</t>
@@ -19348,7 +19340,11 @@
           <t>EIA Distillate Stocks ChangeFEB/21</t>
         </is>
       </c>
-      <c r="C650" t="inlineStr"/>
+      <c r="C650" t="inlineStr">
+        <is>
+          <t>3.908M</t>
+        </is>
+      </c>
       <c r="D650" t="inlineStr">
         <is>
           <t>-2.051M</t>
@@ -19372,27 +19368,23 @@
       </c>
       <c r="B651" t="inlineStr">
         <is>
-          <t>EIA Crude Oil Stocks ChangeFEB/21</t>
+          <t>EIA Distillate Fuel Production ChangeFEB/21</t>
         </is>
       </c>
       <c r="C651" t="inlineStr">
         <is>
-          <t>-2.332M</t>
+          <t>0.439M</t>
         </is>
       </c>
       <c r="D651" t="inlineStr">
         <is>
-          <t>4.633M</t>
-        </is>
-      </c>
-      <c r="E651" t="inlineStr">
-        <is>
-          <t>2.54M</t>
-        </is>
-      </c>
+          <t>0.18M</t>
+        </is>
+      </c>
+      <c r="E651" t="inlineStr"/>
       <c r="F651" t="inlineStr"/>
       <c r="G651" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="652">
@@ -19403,23 +19395,23 @@
       </c>
       <c r="B652" t="inlineStr">
         <is>
-          <t>EIA Crude Oil Stocks ChangeFEB/21</t>
-        </is>
-      </c>
-      <c r="C652" t="inlineStr"/>
+          <t>EIA Cushing Crude Oil Stocks ChangeFEB/21</t>
+        </is>
+      </c>
+      <c r="C652" t="inlineStr">
+        <is>
+          <t>1.282M</t>
+        </is>
+      </c>
       <c r="D652" t="inlineStr">
         <is>
-          <t>4.633M</t>
-        </is>
-      </c>
-      <c r="E652" t="inlineStr">
-        <is>
-          <t>2.34M</t>
-        </is>
-      </c>
+          <t>1.472M</t>
+        </is>
+      </c>
+      <c r="E652" t="inlineStr"/>
       <c r="F652" t="inlineStr"/>
       <c r="G652" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="653">
@@ -19430,23 +19422,23 @@
       </c>
       <c r="B653" t="inlineStr">
         <is>
-          <t>EIA Gasoline Stocks ChangeFEB/21</t>
-        </is>
-      </c>
-      <c r="C653" t="inlineStr"/>
+          <t>EIA Crude Oil Imports ChangeFEB/21</t>
+        </is>
+      </c>
+      <c r="C653" t="inlineStr">
+        <is>
+          <t>0.292M</t>
+        </is>
+      </c>
       <c r="D653" t="inlineStr">
         <is>
-          <t>-0.151M</t>
-        </is>
-      </c>
-      <c r="E653" t="inlineStr">
-        <is>
-          <t>-1.30M</t>
-        </is>
-      </c>
+          <t>-0.961M</t>
+        </is>
+      </c>
+      <c r="E653" t="inlineStr"/>
       <c r="F653" t="inlineStr"/>
       <c r="G653" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="654">
@@ -19457,19 +19449,27 @@
       </c>
       <c r="B654" t="inlineStr">
         <is>
-          <t>EIA Cushing Crude Oil Stocks ChangeFEB/21</t>
-        </is>
-      </c>
-      <c r="C654" t="inlineStr"/>
+          <t>EIA Gasoline Stocks ChangeFEB/21</t>
+        </is>
+      </c>
+      <c r="C654" t="inlineStr">
+        <is>
+          <t>0.369M</t>
+        </is>
+      </c>
       <c r="D654" t="inlineStr">
         <is>
-          <t>1.472M</t>
-        </is>
-      </c>
-      <c r="E654" t="inlineStr"/>
+          <t>-0.151M</t>
+        </is>
+      </c>
+      <c r="E654" t="inlineStr">
+        <is>
+          <t>-1.30M</t>
+        </is>
+      </c>
       <c r="F654" t="inlineStr"/>
       <c r="G654" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="655">
@@ -19480,13 +19480,13 @@
       </c>
       <c r="B655" t="inlineStr">
         <is>
-          <t>EIA Distillate Fuel Production ChangeFEB/21</t>
+          <t>EIA Crude Oil Imports ChangeFEB/21</t>
         </is>
       </c>
       <c r="C655" t="inlineStr"/>
       <c r="D655" t="inlineStr">
         <is>
-          <t>0.18M</t>
+          <t>-0.961M</t>
         </is>
       </c>
       <c r="E655" t="inlineStr"/>
@@ -19622,21 +19622,25 @@
       </c>
       <c r="B661" t="inlineStr">
         <is>
-          <t>7-Year Note Auction</t>
-        </is>
-      </c>
-      <c r="C661" t="inlineStr">
-        <is>
-          <t>4.194%</t>
-        </is>
-      </c>
+          <t>Building Permits FinalJAN</t>
+        </is>
+      </c>
+      <c r="C661" t="inlineStr"/>
       <c r="D661" t="inlineStr">
         <is>
-          <t>4.457%</t>
-        </is>
-      </c>
-      <c r="E661" t="inlineStr"/>
-      <c r="F661" t="inlineStr"/>
+          <t>1.482M</t>
+        </is>
+      </c>
+      <c r="E661" t="inlineStr">
+        <is>
+          <t>1.483M</t>
+        </is>
+      </c>
+      <c r="F661" t="inlineStr">
+        <is>
+          <t>1.483M</t>
+        </is>
+      </c>
       <c r="G661" t="n">
         <v>3</v>
       </c>
@@ -19649,17 +19653,25 @@
       </c>
       <c r="B662" t="inlineStr">
         <is>
-          <t>7-Year Note Auction</t>
+          <t>Building Permits MoM FinalJAN</t>
         </is>
       </c>
       <c r="C662" t="inlineStr"/>
       <c r="D662" t="inlineStr">
         <is>
-          <t>4.457%</t>
-        </is>
-      </c>
-      <c r="E662" t="inlineStr"/>
-      <c r="F662" t="inlineStr"/>
+          <t>-0.7%</t>
+        </is>
+      </c>
+      <c r="E662" t="inlineStr">
+        <is>
+          <t>0.1%</t>
+        </is>
+      </c>
+      <c r="F662" t="inlineStr">
+        <is>
+          <t>0.1%</t>
+        </is>
+      </c>
       <c r="G662" t="n">
         <v>3</v>
       </c>
@@ -19672,25 +19684,17 @@
       </c>
       <c r="B663" t="inlineStr">
         <is>
-          <t>Building Permits MoM FinalJAN</t>
+          <t>7-Year Note Auction</t>
         </is>
       </c>
       <c r="C663" t="inlineStr"/>
       <c r="D663" t="inlineStr">
         <is>
-          <t>-0.7%</t>
-        </is>
-      </c>
-      <c r="E663" t="inlineStr">
-        <is>
-          <t>0.1%</t>
-        </is>
-      </c>
-      <c r="F663" t="inlineStr">
-        <is>
-          <t>0.1%</t>
-        </is>
-      </c>
+          <t>4.457%</t>
+        </is>
+      </c>
+      <c r="E663" t="inlineStr"/>
+      <c r="F663" t="inlineStr"/>
       <c r="G663" t="n">
         <v>3</v>
       </c>
@@ -19703,25 +19707,21 @@
       </c>
       <c r="B664" t="inlineStr">
         <is>
-          <t>Building Permits FinalJAN</t>
-        </is>
-      </c>
-      <c r="C664" t="inlineStr"/>
+          <t>7-Year Note Auction</t>
+        </is>
+      </c>
+      <c r="C664" t="inlineStr">
+        <is>
+          <t>4.194%</t>
+        </is>
+      </c>
       <c r="D664" t="inlineStr">
         <is>
-          <t>1.482M</t>
-        </is>
-      </c>
-      <c r="E664" t="inlineStr">
-        <is>
-          <t>1.483M</t>
-        </is>
-      </c>
-      <c r="F664" t="inlineStr">
-        <is>
-          <t>1.483M</t>
-        </is>
-      </c>
+          <t>4.457%</t>
+        </is>
+      </c>
+      <c r="E664" t="inlineStr"/>
+      <c r="F664" t="inlineStr"/>
       <c r="G664" t="n">
         <v>3</v>
       </c>
@@ -20129,27 +20129,27 @@
       </c>
       <c r="B678" t="inlineStr">
         <is>
-          <t>Initial Jobless ClaimsFEB/22</t>
+          <t>GDP Growth Rate QoQ 2nd EstQ4</t>
         </is>
       </c>
       <c r="C678" t="inlineStr"/>
       <c r="D678" t="inlineStr">
         <is>
-          <t>219K</t>
+          <t>3.1%</t>
         </is>
       </c>
       <c r="E678" t="inlineStr">
         <is>
-          <t>221K</t>
+          <t>2.3%</t>
         </is>
       </c>
       <c r="F678" t="inlineStr">
         <is>
-          <t>225.0K</t>
+          <t>2.3%</t>
         </is>
       </c>
       <c r="G678" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="679">
@@ -20187,23 +20187,23 @@
       </c>
       <c r="B680" t="inlineStr">
         <is>
-          <t>Durable Goods Orders Ex Transp MoMJAN</t>
+          <t>Initial Jobless ClaimsFEB/22</t>
         </is>
       </c>
       <c r="C680" t="inlineStr"/>
       <c r="D680" t="inlineStr">
         <is>
-          <t>0.3%</t>
+          <t>219K</t>
         </is>
       </c>
       <c r="E680" t="inlineStr">
         <is>
-          <t>0.3%</t>
+          <t>221K</t>
         </is>
       </c>
       <c r="F680" t="inlineStr">
         <is>
-          <t>0.3%</t>
+          <t>225.0K</t>
         </is>
       </c>
       <c r="G680" t="n">
@@ -20218,13 +20218,13 @@
       </c>
       <c r="B681" t="inlineStr">
         <is>
-          <t>Non Defense Goods Orders Ex AirJAN</t>
+          <t>Durable Goods Orders Ex Transp MoMJAN</t>
         </is>
       </c>
       <c r="C681" t="inlineStr"/>
       <c r="D681" t="inlineStr">
         <is>
-          <t>0.5%</t>
+          <t>0.3%</t>
         </is>
       </c>
       <c r="E681" t="inlineStr">
@@ -20234,11 +20234,11 @@
       </c>
       <c r="F681" t="inlineStr">
         <is>
-          <t>0.4%</t>
+          <t>0.3%</t>
         </is>
       </c>
       <c r="G681" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="682">
@@ -20249,19 +20249,23 @@
       </c>
       <c r="B682" t="inlineStr">
         <is>
-          <t>Jobless Claims 4-week AverageFEB/22</t>
+          <t>Non Defense Goods Orders Ex AirJAN</t>
         </is>
       </c>
       <c r="C682" t="inlineStr"/>
       <c r="D682" t="inlineStr">
         <is>
-          <t>215.25K</t>
-        </is>
-      </c>
-      <c r="E682" t="inlineStr"/>
+          <t>0.5%</t>
+        </is>
+      </c>
+      <c r="E682" t="inlineStr">
+        <is>
+          <t>0.3%</t>
+        </is>
+      </c>
       <c r="F682" t="inlineStr">
         <is>
-          <t>220.0K</t>
+          <t>0.4%</t>
         </is>
       </c>
       <c r="G682" t="n">
@@ -20276,27 +20280,23 @@
       </c>
       <c r="B683" t="inlineStr">
         <is>
-          <t>Durable Goods Orders MoMJAN</t>
+          <t>Jobless Claims 4-week AverageFEB/22</t>
         </is>
       </c>
       <c r="C683" t="inlineStr"/>
       <c r="D683" t="inlineStr">
         <is>
-          <t>-2.2%</t>
-        </is>
-      </c>
-      <c r="E683" t="inlineStr">
-        <is>
-          <t>2%</t>
-        </is>
-      </c>
+          <t>215.25K</t>
+        </is>
+      </c>
+      <c r="E683" t="inlineStr"/>
       <c r="F683" t="inlineStr">
         <is>
-          <t>2.2%</t>
+          <t>220.0K</t>
         </is>
       </c>
       <c r="G683" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="684">
@@ -20307,27 +20307,27 @@
       </c>
       <c r="B684" t="inlineStr">
         <is>
-          <t>Real Consumer Spending QoQ 2nd EstQ4</t>
+          <t>Durable Goods Orders MoMJAN</t>
         </is>
       </c>
       <c r="C684" t="inlineStr"/>
       <c r="D684" t="inlineStr">
         <is>
-          <t>3.7%</t>
+          <t>-2.2%</t>
         </is>
       </c>
       <c r="E684" t="inlineStr">
         <is>
-          <t>4.2%</t>
+          <t>2%</t>
         </is>
       </c>
       <c r="F684" t="inlineStr">
         <is>
-          <t>4.2%</t>
+          <t>2.2%</t>
         </is>
       </c>
       <c r="G684" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="685">
@@ -20338,23 +20338,23 @@
       </c>
       <c r="B685" t="inlineStr">
         <is>
-          <t>PCE Prices QoQ 2nd EstQ4</t>
+          <t>Real Consumer Spending QoQ 2nd EstQ4</t>
         </is>
       </c>
       <c r="C685" t="inlineStr"/>
       <c r="D685" t="inlineStr">
         <is>
-          <t>1.5%</t>
+          <t>3.7%</t>
         </is>
       </c>
       <c r="E685" t="inlineStr">
         <is>
-          <t>2.3%</t>
+          <t>4.2%</t>
         </is>
       </c>
       <c r="F685" t="inlineStr">
         <is>
-          <t>2.3%</t>
+          <t>4.2%</t>
         </is>
       </c>
       <c r="G685" t="n">
@@ -20369,27 +20369,27 @@
       </c>
       <c r="B686" t="inlineStr">
         <is>
-          <t>GDP Price Index QoQ 2nd EstQ4</t>
+          <t>PCE Prices QoQ 2nd EstQ4</t>
         </is>
       </c>
       <c r="C686" t="inlineStr"/>
       <c r="D686" t="inlineStr">
         <is>
-          <t>1.9%</t>
+          <t>1.5%</t>
         </is>
       </c>
       <c r="E686" t="inlineStr">
         <is>
-          <t>2.2%</t>
+          <t>2.3%</t>
         </is>
       </c>
       <c r="F686" t="inlineStr">
         <is>
-          <t>2.2%</t>
+          <t>2.3%</t>
         </is>
       </c>
       <c r="G686" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="687">
@@ -20400,27 +20400,27 @@
       </c>
       <c r="B687" t="inlineStr">
         <is>
-          <t>GDP Growth Rate QoQ 2nd EstQ4</t>
+          <t>GDP Price Index QoQ 2nd EstQ4</t>
         </is>
       </c>
       <c r="C687" t="inlineStr"/>
       <c r="D687" t="inlineStr">
         <is>
-          <t>3.1%</t>
+          <t>1.9%</t>
         </is>
       </c>
       <c r="E687" t="inlineStr">
         <is>
-          <t>2.3%</t>
+          <t>2.2%</t>
         </is>
       </c>
       <c r="F687" t="inlineStr">
         <is>
-          <t>2.3%</t>
+          <t>2.2%</t>
         </is>
       </c>
       <c r="G687" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="688">
@@ -21058,13 +21058,13 @@
       </c>
       <c r="B713" t="inlineStr">
         <is>
-          <t>30-Year Mortgage RateFEB/27</t>
+          <t>15-Year Mortgage RateFEB/27</t>
         </is>
       </c>
       <c r="C713" t="inlineStr"/>
       <c r="D713" t="inlineStr">
         <is>
-          <t>6.85%</t>
+          <t>6.04%</t>
         </is>
       </c>
       <c r="E713" t="inlineStr"/>
@@ -21081,13 +21081,13 @@
       </c>
       <c r="B714" t="inlineStr">
         <is>
-          <t>15-Year Mortgage RateFEB/27</t>
+          <t>30-Year Mortgage RateFEB/27</t>
         </is>
       </c>
       <c r="C714" t="inlineStr"/>
       <c r="D714" t="inlineStr">
         <is>
-          <t>6.04%</t>
+          <t>6.85%</t>
         </is>
       </c>
       <c r="E714" t="inlineStr"/>
@@ -21508,27 +21508,27 @@
       </c>
       <c r="B731" t="inlineStr">
         <is>
-          <t>Personal Spending MoMJAN</t>
+          <t>PCE Price Index YoYJAN</t>
         </is>
       </c>
       <c r="C731" t="inlineStr"/>
       <c r="D731" t="inlineStr">
         <is>
-          <t>0.7%</t>
+          <t>2.6%</t>
         </is>
       </c>
       <c r="E731" t="inlineStr">
         <is>
-          <t>0.1%</t>
+          <t>2.5%</t>
         </is>
       </c>
       <c r="F731" t="inlineStr">
         <is>
-          <t>0.3%</t>
+          <t>2.5%</t>
         </is>
       </c>
       <c r="G731" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="732">
@@ -21570,27 +21570,27 @@
       </c>
       <c r="B733" t="inlineStr">
         <is>
-          <t>PCE Price Index YoYJAN</t>
+          <t>Personal Spending MoMJAN</t>
         </is>
       </c>
       <c r="C733" t="inlineStr"/>
       <c r="D733" t="inlineStr">
         <is>
-          <t>2.6%</t>
+          <t>0.7%</t>
         </is>
       </c>
       <c r="E733" t="inlineStr">
         <is>
-          <t>2.5%</t>
+          <t>0.1%</t>
         </is>
       </c>
       <c r="F733" t="inlineStr">
         <is>
-          <t>2.5%</t>
+          <t>0.3%</t>
         </is>
       </c>
       <c r="G733" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="734">
@@ -21659,23 +21659,23 @@
       </c>
       <c r="B736" t="inlineStr">
         <is>
-          <t>Personal Income MoMJAN</t>
+          <t>Core PCE Price Index MoMJAN</t>
         </is>
       </c>
       <c r="C736" t="inlineStr"/>
       <c r="D736" t="inlineStr">
         <is>
+          <t>0.2%</t>
+        </is>
+      </c>
+      <c r="E736" t="inlineStr">
+        <is>
+          <t>0.3%</t>
+        </is>
+      </c>
+      <c r="F736" t="inlineStr">
+        <is>
           <t>0.4%</t>
-        </is>
-      </c>
-      <c r="E736" t="inlineStr">
-        <is>
-          <t>0.3%</t>
-        </is>
-      </c>
-      <c r="F736" t="inlineStr">
-        <is>
-          <t>0.3%</t>
         </is>
       </c>
       <c r="G736" t="n">
@@ -21690,23 +21690,23 @@
       </c>
       <c r="B737" t="inlineStr">
         <is>
-          <t>Wholesale Inventories MoM AdvJAN</t>
+          <t>PCE Price Index MoMJAN</t>
         </is>
       </c>
       <c r="C737" t="inlineStr"/>
       <c r="D737" t="inlineStr">
         <is>
-          <t>-0.5%</t>
+          <t>0.3%</t>
         </is>
       </c>
       <c r="E737" t="inlineStr">
         <is>
-          <t>0.1%</t>
+          <t>0.3%</t>
         </is>
       </c>
       <c r="F737" t="inlineStr">
         <is>
-          <t>0.2%</t>
+          <t>0.4%</t>
         </is>
       </c>
       <c r="G737" t="n">
@@ -21721,27 +21721,27 @@
       </c>
       <c r="B738" t="inlineStr">
         <is>
-          <t>Core PCE Price Index MoMJAN</t>
+          <t>Goods Trade Balance AdvJAN</t>
         </is>
       </c>
       <c r="C738" t="inlineStr"/>
       <c r="D738" t="inlineStr">
         <is>
-          <t>0.2%</t>
+          <t>$-122.11B</t>
         </is>
       </c>
       <c r="E738" t="inlineStr">
         <is>
-          <t>0.3%</t>
+          <t>$-114.7B</t>
         </is>
       </c>
       <c r="F738" t="inlineStr">
         <is>
-          <t>0.4%</t>
+          <t>$ -116.0B</t>
         </is>
       </c>
       <c r="G738" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="739">
@@ -21752,23 +21752,23 @@
       </c>
       <c r="B739" t="inlineStr">
         <is>
-          <t>PCE Price Index MoMJAN</t>
+          <t>Wholesale Inventories MoM AdvJAN</t>
         </is>
       </c>
       <c r="C739" t="inlineStr"/>
       <c r="D739" t="inlineStr">
         <is>
-          <t>0.3%</t>
+          <t>-0.5%</t>
         </is>
       </c>
       <c r="E739" t="inlineStr">
         <is>
-          <t>0.3%</t>
+          <t>0.1%</t>
         </is>
       </c>
       <c r="F739" t="inlineStr">
         <is>
-          <t>0.4%</t>
+          <t>0.2%</t>
         </is>
       </c>
       <c r="G739" t="n">
@@ -21783,27 +21783,27 @@
       </c>
       <c r="B740" t="inlineStr">
         <is>
-          <t>Goods Trade Balance AdvJAN</t>
+          <t>Personal Income MoMJAN</t>
         </is>
       </c>
       <c r="C740" t="inlineStr"/>
       <c r="D740" t="inlineStr">
         <is>
-          <t>$-122.11B</t>
+          <t>0.4%</t>
         </is>
       </c>
       <c r="E740" t="inlineStr">
         <is>
-          <t>$-114.7B</t>
+          <t>0.3%</t>
         </is>
       </c>
       <c r="F740" t="inlineStr">
         <is>
-          <t>$ -116.0B</t>
+          <t>0.3%</t>
         </is>
       </c>
       <c r="G740" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="741">
@@ -22165,23 +22165,23 @@
       </c>
       <c r="B754" t="inlineStr">
         <is>
-          <t>ISM Manufacturing PMIFEB</t>
+          <t>ISM Manufacturing New OrdersFEB</t>
         </is>
       </c>
       <c r="C754" t="inlineStr"/>
       <c r="D754" t="inlineStr">
         <is>
-          <t>50.9</t>
+          <t>55.1</t>
         </is>
       </c>
       <c r="E754" t="inlineStr"/>
       <c r="F754" t="inlineStr">
         <is>
-          <t>51</t>
+          <t>55.4</t>
         </is>
       </c>
       <c r="G754" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="755">
@@ -22219,23 +22219,23 @@
       </c>
       <c r="B756" t="inlineStr">
         <is>
-          <t>ISM Manufacturing New OrdersFEB</t>
+          <t>ISM Manufacturing PMIFEB</t>
         </is>
       </c>
       <c r="C756" t="inlineStr"/>
       <c r="D756" t="inlineStr">
         <is>
-          <t>55.1</t>
+          <t>50.9</t>
         </is>
       </c>
       <c r="E756" t="inlineStr"/>
       <c r="F756" t="inlineStr">
         <is>
-          <t>55.4</t>
+          <t>51</t>
         </is>
       </c>
       <c r="G756" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="757">
@@ -23254,23 +23254,23 @@
       </c>
       <c r="B797" t="inlineStr">
         <is>
-          <t>ISM Services EmploymentFEB</t>
+          <t>ISM Services PMIFEB</t>
         </is>
       </c>
       <c r="C797" t="inlineStr"/>
       <c r="D797" t="inlineStr">
         <is>
-          <t>52.3</t>
+          <t>52.8</t>
         </is>
       </c>
       <c r="E797" t="inlineStr"/>
       <c r="F797" t="inlineStr">
         <is>
-          <t>52.1</t>
+          <t>52.7</t>
         </is>
       </c>
       <c r="G797" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="798">
@@ -23281,19 +23281,19 @@
       </c>
       <c r="B798" t="inlineStr">
         <is>
-          <t>ISM Services New OrdersFEB</t>
+          <t>Factory Orders ex TransportationJAN</t>
         </is>
       </c>
       <c r="C798" t="inlineStr"/>
       <c r="D798" t="inlineStr">
         <is>
-          <t>51.3</t>
+          <t>0.2%</t>
         </is>
       </c>
       <c r="E798" t="inlineStr"/>
       <c r="F798" t="inlineStr">
         <is>
-          <t>51.2</t>
+          <t>0.3%</t>
         </is>
       </c>
       <c r="G798" t="n">
@@ -23308,19 +23308,19 @@
       </c>
       <c r="B799" t="inlineStr">
         <is>
-          <t>ISM Services PricesFEB</t>
+          <t>ISM Services Business ActivityFEB</t>
         </is>
       </c>
       <c r="C799" t="inlineStr"/>
       <c r="D799" t="inlineStr">
         <is>
-          <t>60.4</t>
+          <t>54.5</t>
         </is>
       </c>
       <c r="E799" t="inlineStr"/>
       <c r="F799" t="inlineStr">
         <is>
-          <t>60.6</t>
+          <t>54.2</t>
         </is>
       </c>
       <c r="G799" t="n">
@@ -23335,19 +23335,19 @@
       </c>
       <c r="B800" t="inlineStr">
         <is>
-          <t>ISM Services Business ActivityFEB</t>
+          <t>ISM Services PricesFEB</t>
         </is>
       </c>
       <c r="C800" t="inlineStr"/>
       <c r="D800" t="inlineStr">
         <is>
-          <t>54.5</t>
+          <t>60.4</t>
         </is>
       </c>
       <c r="E800" t="inlineStr"/>
       <c r="F800" t="inlineStr">
         <is>
-          <t>54.2</t>
+          <t>60.6</t>
         </is>
       </c>
       <c r="G800" t="n">
@@ -23362,19 +23362,19 @@
       </c>
       <c r="B801" t="inlineStr">
         <is>
-          <t>Factory Orders ex TransportationJAN</t>
+          <t>ISM Services New OrdersFEB</t>
         </is>
       </c>
       <c r="C801" t="inlineStr"/>
       <c r="D801" t="inlineStr">
         <is>
-          <t>0.2%</t>
+          <t>51.3</t>
         </is>
       </c>
       <c r="E801" t="inlineStr"/>
       <c r="F801" t="inlineStr">
         <is>
-          <t>0.3%</t>
+          <t>51.2</t>
         </is>
       </c>
       <c r="G801" t="n">
@@ -23389,23 +23389,23 @@
       </c>
       <c r="B802" t="inlineStr">
         <is>
-          <t>ISM Services PMIFEB</t>
+          <t>ISM Services EmploymentFEB</t>
         </is>
       </c>
       <c r="C802" t="inlineStr"/>
       <c r="D802" t="inlineStr">
         <is>
-          <t>52.8</t>
+          <t>52.3</t>
         </is>
       </c>
       <c r="E802" t="inlineStr"/>
       <c r="F802" t="inlineStr">
         <is>
-          <t>52.7</t>
+          <t>52.1</t>
         </is>
       </c>
       <c r="G802" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="803">
@@ -23623,19 +23623,19 @@
       </c>
       <c r="B812" t="inlineStr">
         <is>
-          <t>EIA Gasoline Stocks ChangeFEB/28</t>
+          <t>EIA Refinery Crude Runs ChangeFEB/28</t>
         </is>
       </c>
       <c r="C812" t="inlineStr"/>
       <c r="D812" t="inlineStr">
         <is>
-          <t>0.369M</t>
+          <t>0.317M</t>
         </is>
       </c>
       <c r="E812" t="inlineStr"/>
       <c r="F812" t="inlineStr"/>
       <c r="G812" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="813">
@@ -23646,15 +23646,11 @@
       </c>
       <c r="B813" t="inlineStr">
         <is>
-          <t>EIA Refinery Crude Runs ChangeFEB/28</t>
+          <t>EIA Crude Oil Imports ChangeFEB/28</t>
         </is>
       </c>
       <c r="C813" t="inlineStr"/>
-      <c r="D813" t="inlineStr">
-        <is>
-          <t>0.317M</t>
-        </is>
-      </c>
+      <c r="D813" t="inlineStr"/>
       <c r="E813" t="inlineStr"/>
       <c r="F813" t="inlineStr"/>
       <c r="G813" t="n">
@@ -23734,15 +23730,19 @@
       </c>
       <c r="B817" t="inlineStr">
         <is>
-          <t>EIA Crude Oil Imports ChangeFEB/28</t>
+          <t>EIA Gasoline Stocks ChangeFEB/28</t>
         </is>
       </c>
       <c r="C817" t="inlineStr"/>
-      <c r="D817" t="inlineStr"/>
+      <c r="D817" t="inlineStr">
+        <is>
+          <t>0.369M</t>
+        </is>
+      </c>
       <c r="E817" t="inlineStr"/>
       <c r="F817" t="inlineStr"/>
       <c r="G817" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="818">
@@ -23776,19 +23776,19 @@
       </c>
       <c r="B819" t="inlineStr">
         <is>
-          <t>EIA Heating Oil Stocks ChangeFEB/28</t>
+          <t>EIA Crude Oil Stocks ChangeFEB/28</t>
         </is>
       </c>
       <c r="C819" t="inlineStr"/>
       <c r="D819" t="inlineStr">
         <is>
-          <t>0.134M</t>
+          <t>-2.332M</t>
         </is>
       </c>
       <c r="E819" t="inlineStr"/>
       <c r="F819" t="inlineStr"/>
       <c r="G819" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="820">
@@ -23799,19 +23799,19 @@
       </c>
       <c r="B820" t="inlineStr">
         <is>
-          <t>EIA Crude Oil Stocks ChangeFEB/28</t>
+          <t>EIA Heating Oil Stocks ChangeFEB/28</t>
         </is>
       </c>
       <c r="C820" t="inlineStr"/>
       <c r="D820" t="inlineStr">
         <is>
-          <t>-2.332M</t>
+          <t>0.134M</t>
         </is>
       </c>
       <c r="E820" t="inlineStr"/>
       <c r="F820" t="inlineStr"/>
       <c r="G820" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="821">
@@ -23868,13 +23868,13 @@
       </c>
       <c r="B823" t="inlineStr">
         <is>
-          <t>Total Vehicle SalesFEB</t>
+          <t>17-Week Bill Auction</t>
         </is>
       </c>
       <c r="C823" t="inlineStr"/>
       <c r="D823" t="inlineStr">
         <is>
-          <t>15.6M</t>
+          <t>4.200%</t>
         </is>
       </c>
       <c r="E823" t="inlineStr"/>
@@ -23891,13 +23891,13 @@
       </c>
       <c r="B824" t="inlineStr">
         <is>
-          <t>17-Week Bill Auction</t>
+          <t>Total Vehicle SalesFEB</t>
         </is>
       </c>
       <c r="C824" t="inlineStr"/>
       <c r="D824" t="inlineStr">
         <is>
-          <t>4.200%</t>
+          <t>15.6M</t>
         </is>
       </c>
       <c r="E824" t="inlineStr"/>
@@ -24321,19 +24321,19 @@
       </c>
       <c r="B842" t="inlineStr">
         <is>
-          <t>Balance of TradeJAN</t>
+          <t>ExportsJAN</t>
         </is>
       </c>
       <c r="C842" t="inlineStr"/>
       <c r="D842" t="inlineStr">
         <is>
-          <t>$-98.4B</t>
+          <t>$266.5B</t>
         </is>
       </c>
       <c r="E842" t="inlineStr"/>
       <c r="F842" t="inlineStr">
         <is>
-          <t>$-103B</t>
+          <t>$273.0B</t>
         </is>
       </c>
       <c r="G842" t="n">
@@ -24348,19 +24348,19 @@
       </c>
       <c r="B843" t="inlineStr">
         <is>
-          <t>ExportsJAN</t>
+          <t>ImportsJAN</t>
         </is>
       </c>
       <c r="C843" t="inlineStr"/>
       <c r="D843" t="inlineStr">
         <is>
-          <t>$266.5B</t>
+          <t>$364.9B</t>
         </is>
       </c>
       <c r="E843" t="inlineStr"/>
       <c r="F843" t="inlineStr">
         <is>
-          <t>$273.0B</t>
+          <t>$376.0B</t>
         </is>
       </c>
       <c r="G843" t="n">
@@ -24375,19 +24375,19 @@
       </c>
       <c r="B844" t="inlineStr">
         <is>
-          <t>ImportsJAN</t>
+          <t>Balance of TradeJAN</t>
         </is>
       </c>
       <c r="C844" t="inlineStr"/>
       <c r="D844" t="inlineStr">
         <is>
-          <t>$364.9B</t>
+          <t>$-98.4B</t>
         </is>
       </c>
       <c r="E844" t="inlineStr"/>
       <c r="F844" t="inlineStr">
         <is>
-          <t>$376.0B</t>
+          <t>$-103B</t>
         </is>
       </c>
       <c r="G844" t="n">
@@ -24516,7 +24516,7 @@
       </c>
       <c r="B851" t="inlineStr">
         <is>
-          <t>4-Week Bill Auction</t>
+          <t>8-Week Bill Auction</t>
         </is>
       </c>
       <c r="C851" t="inlineStr"/>
@@ -24535,7 +24535,7 @@
       </c>
       <c r="B852" t="inlineStr">
         <is>
-          <t>8-Week Bill Auction</t>
+          <t>4-Week Bill Auction</t>
         </is>
       </c>
       <c r="C852" t="inlineStr"/>
@@ -24830,23 +24830,19 @@
       </c>
       <c r="B865" t="inlineStr">
         <is>
-          <t>Average Hourly Earnings MoMFEB</t>
+          <t>Used Car Prices YoYFEB</t>
         </is>
       </c>
       <c r="C865" t="inlineStr"/>
       <c r="D865" t="inlineStr">
         <is>
-          <t>0.5%</t>
+          <t>0.8%</t>
         </is>
       </c>
       <c r="E865" t="inlineStr"/>
-      <c r="F865" t="inlineStr">
-        <is>
-          <t>0.3%</t>
-        </is>
-      </c>
+      <c r="F865" t="inlineStr"/>
       <c r="G865" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="866">
@@ -24911,23 +24907,23 @@
       </c>
       <c r="B868" t="inlineStr">
         <is>
-          <t>U-6 Unemployment RateFEB</t>
+          <t>Non Farm PayrollsFEB</t>
         </is>
       </c>
       <c r="C868" t="inlineStr"/>
       <c r="D868" t="inlineStr">
         <is>
-          <t>7.5%</t>
+          <t>143K</t>
         </is>
       </c>
       <c r="E868" t="inlineStr"/>
       <c r="F868" t="inlineStr">
         <is>
-          <t>7.6%</t>
+          <t>180.0K</t>
         </is>
       </c>
       <c r="G868" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="869">
@@ -24938,23 +24934,23 @@
       </c>
       <c r="B869" t="inlineStr">
         <is>
-          <t>Average Hourly Earnings YoYFEB</t>
+          <t>Unemployment RateFEB</t>
         </is>
       </c>
       <c r="C869" t="inlineStr"/>
       <c r="D869" t="inlineStr">
         <is>
-          <t>4.1%</t>
+          <t>4%</t>
         </is>
       </c>
       <c r="E869" t="inlineStr"/>
       <c r="F869" t="inlineStr">
         <is>
-          <t>4.1%</t>
+          <t>4.0%</t>
         </is>
       </c>
       <c r="G869" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="870">
@@ -25042,23 +25038,23 @@
       </c>
       <c r="B873" t="inlineStr">
         <is>
-          <t>Unemployment RateFEB</t>
+          <t>Average Hourly Earnings YoYFEB</t>
         </is>
       </c>
       <c r="C873" t="inlineStr"/>
       <c r="D873" t="inlineStr">
         <is>
-          <t>4%</t>
+          <t>4.1%</t>
         </is>
       </c>
       <c r="E873" t="inlineStr"/>
       <c r="F873" t="inlineStr">
         <is>
-          <t>4.0%</t>
+          <t>4.1%</t>
         </is>
       </c>
       <c r="G873" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="874">
@@ -25069,23 +25065,23 @@
       </c>
       <c r="B874" t="inlineStr">
         <is>
-          <t>Non Farm PayrollsFEB</t>
+          <t>Average Hourly Earnings MoMFEB</t>
         </is>
       </c>
       <c r="C874" t="inlineStr"/>
       <c r="D874" t="inlineStr">
         <is>
-          <t>143K</t>
+          <t>0.5%</t>
         </is>
       </c>
       <c r="E874" t="inlineStr"/>
       <c r="F874" t="inlineStr">
         <is>
-          <t>180.0K</t>
+          <t>0.3%</t>
         </is>
       </c>
       <c r="G874" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="875">
@@ -25204,17 +25200,21 @@
       </c>
       <c r="B879" t="inlineStr">
         <is>
-          <t>Used Car Prices YoYFEB</t>
+          <t>U-6 Unemployment RateFEB</t>
         </is>
       </c>
       <c r="C879" t="inlineStr"/>
       <c r="D879" t="inlineStr">
         <is>
-          <t>0.8%</t>
+          <t>7.5%</t>
         </is>
       </c>
       <c r="E879" t="inlineStr"/>
-      <c r="F879" t="inlineStr"/>
+      <c r="F879" t="inlineStr">
+        <is>
+          <t>7.6%</t>
+        </is>
+      </c>
       <c r="G879" t="n">
         <v>3</v>
       </c>

--- a/Input_data/IST_US_trad_eco_cal_2025-01-01_to_2025-03-09.xlsx
+++ b/Input_data/IST_US_trad_eco_cal_2025-01-01_to_2025-03-09.xlsx
@@ -806,24 +806,20 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>EIA Distillate Stocks ChangeDEC/27</t>
+          <t>EIA Distillate Fuel Production ChangeDEC/27</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>6.406M</t>
+          <t>0.099M</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>-1.694M</t>
-        </is>
-      </c>
-      <c r="E13" t="inlineStr">
-        <is>
-          <t>-0.1M</t>
-        </is>
-      </c>
+          <t>0.178M</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr"/>
       <c r="F13" t="inlineStr"/>
       <c r="G13" t="n">
         <v>3</v>
@@ -837,23 +833,27 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>EIA Refinery Crude Runs ChangeDEC/27</t>
+          <t>EIA Crude Oil Stocks ChangeDEC/27</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>0.041M</t>
+          <t>-1.178M</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>0.205M</t>
-        </is>
-      </c>
-      <c r="E14" t="inlineStr"/>
+          <t>-4.237M</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>-2.75M</t>
+        </is>
+      </c>
       <c r="F14" t="inlineStr"/>
       <c r="G14" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="15">
@@ -864,17 +864,17 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>EIA Gasoline Production ChangeDEC/27</t>
+          <t>EIA Cushing Crude Oil Stocks ChangeDEC/27</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>-0.959M</t>
+          <t>-0.142M</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>0.051M</t>
+          <t>-0.32M</t>
         </is>
       </c>
       <c r="E15" t="inlineStr"/>
@@ -891,23 +891,27 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>EIA Heating Oil Stocks ChangeDEC/27</t>
+          <t>EIA Gasoline Stocks ChangeDEC/27</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>-0.416M</t>
+          <t>7.717M</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>-0.062M</t>
-        </is>
-      </c>
-      <c r="E16" t="inlineStr"/>
+          <t>1.63M</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>0.7M</t>
+        </is>
+      </c>
       <c r="F16" t="inlineStr"/>
       <c r="G16" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="17">
@@ -918,17 +922,17 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>EIA Crude Oil Imports ChangeDEC/27</t>
+          <t>EIA Gasoline Production ChangeDEC/27</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>0.323M</t>
+          <t>-0.959M</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>0.995M</t>
+          <t>0.051M</t>
         </is>
       </c>
       <c r="E17" t="inlineStr"/>
@@ -945,27 +949,23 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>EIA Gasoline Stocks ChangeDEC/27</t>
+          <t>EIA Heating Oil Stocks ChangeDEC/27</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>7.717M</t>
+          <t>-0.416M</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>1.63M</t>
-        </is>
-      </c>
-      <c r="E18" t="inlineStr">
-        <is>
-          <t>0.7M</t>
-        </is>
-      </c>
+          <t>-0.062M</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr"/>
       <c r="F18" t="inlineStr"/>
       <c r="G18" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="19">
@@ -976,17 +976,17 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>EIA Cushing Crude Oil Stocks ChangeDEC/27</t>
+          <t>EIA Refinery Crude Runs ChangeDEC/27</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>-0.142M</t>
+          <t>0.041M</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>-0.32M</t>
+          <t>0.205M</t>
         </is>
       </c>
       <c r="E19" t="inlineStr"/>
@@ -1003,27 +1003,27 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>EIA Crude Oil Stocks ChangeDEC/27</t>
+          <t>EIA Distillate Stocks ChangeDEC/27</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>-1.178M</t>
+          <t>6.406M</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>-4.237M</t>
+          <t>-1.694M</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>-2.75M</t>
+          <t>-0.1M</t>
         </is>
       </c>
       <c r="F20" t="inlineStr"/>
       <c r="G20" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="21">
@@ -1034,17 +1034,17 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>EIA Distillate Fuel Production ChangeDEC/27</t>
+          <t>EIA Crude Oil Imports ChangeDEC/27</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>0.099M</t>
+          <t>0.323M</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>0.178M</t>
+          <t>0.995M</t>
         </is>
       </c>
       <c r="E21" t="inlineStr"/>
@@ -1223,31 +1223,31 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>ISM Manufacturing PMIDEC</t>
+          <t>ISM Manufacturing PricesDEC</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>49.3</t>
+          <t>52.5</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>48.4</t>
+          <t>50.3</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>48.4</t>
+          <t>51.7</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>48.5</t>
+          <t>50.4</t>
         </is>
       </c>
       <c r="G28" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="29">
@@ -1258,31 +1258,27 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>ISM Manufacturing EmploymentDEC</t>
+          <t>ISM Manufacturing New OrdersDEC</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>45.3</t>
+          <t>52.5</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>48.1</t>
-        </is>
-      </c>
-      <c r="E29" t="inlineStr">
-        <is>
-          <t>48</t>
-        </is>
-      </c>
+          <t>50.4</t>
+        </is>
+      </c>
+      <c r="E29" t="inlineStr"/>
       <c r="F29" t="inlineStr">
         <is>
-          <t>48.3</t>
+          <t>50.5</t>
         </is>
       </c>
       <c r="G29" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="30">
@@ -1293,27 +1289,31 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>ISM Manufacturing New OrdersDEC</t>
+          <t>ISM Manufacturing EmploymentDEC</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>52.5</t>
+          <t>45.3</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>50.4</t>
-        </is>
-      </c>
-      <c r="E30" t="inlineStr"/>
+          <t>48.1</t>
+        </is>
+      </c>
+      <c r="E30" t="inlineStr">
+        <is>
+          <t>48</t>
+        </is>
+      </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>50.5</t>
+          <t>48.3</t>
         </is>
       </c>
       <c r="G30" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="31">
@@ -1324,31 +1324,31 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>ISM Manufacturing PricesDEC</t>
+          <t>ISM Manufacturing PMIDEC</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>52.5</t>
+          <t>49.3</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>50.3</t>
+          <t>48.4</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>51.7</t>
+          <t>48.4</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>50.4</t>
+          <t>48.5</t>
         </is>
       </c>
       <c r="G31" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="32">
@@ -1609,31 +1609,27 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>Factory Orders MoMNOV</t>
+          <t>Factory Orders ex TransportationNOV</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>-0.4%</t>
+          <t>0.2%</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>0.5%</t>
-        </is>
-      </c>
-      <c r="E42" t="inlineStr">
-        <is>
-          <t>-0.3%</t>
-        </is>
-      </c>
+          <t>0.2%</t>
+        </is>
+      </c>
+      <c r="E42" t="inlineStr"/>
       <c r="F42" t="inlineStr">
         <is>
-          <t>0.3%</t>
+          <t>0.2%</t>
         </is>
       </c>
       <c r="G42" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="43">
@@ -1644,27 +1640,31 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>Factory Orders ex TransportationNOV</t>
+          <t>Factory Orders MoMNOV</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>0.2%</t>
+          <t>-0.4%</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>0.2%</t>
-        </is>
-      </c>
-      <c r="E43" t="inlineStr"/>
+          <t>0.5%</t>
+        </is>
+      </c>
+      <c r="E43" t="inlineStr">
+        <is>
+          <t>-0.3%</t>
+        </is>
+      </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>0.2%</t>
+          <t>0.3%</t>
         </is>
       </c>
       <c r="G43" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="44">
@@ -1949,27 +1949,27 @@
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>ISM Services EmploymentDEC</t>
+          <t>ISM Services New OrdersDEC</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>51.4</t>
+          <t>54.2</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>51.5</t>
+          <t>53.7</t>
         </is>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>51.4</t>
+          <t>54.2</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>52</t>
+          <t>54.1</t>
         </is>
       </c>
       <c r="G54" t="n">
@@ -1984,23 +1984,23 @@
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>JOLTs Job QuitsNOV</t>
+          <t>ISM Services Business ActivityDEC</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>3.065M</t>
+          <t>58.2</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>3.283M</t>
+          <t>53.7</t>
         </is>
       </c>
       <c r="E55" t="inlineStr"/>
       <c r="F55" t="inlineStr">
         <is>
-          <t>3.31M</t>
+          <t>54.1</t>
         </is>
       </c>
       <c r="G55" t="n">
@@ -2015,31 +2015,31 @@
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>ISM Services PricesDEC</t>
+          <t>JOLTs Job OpeningsNOV</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>64.4</t>
+          <t>8.098M</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>58.2</t>
+          <t>7.839M</t>
         </is>
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>57.5</t>
+          <t>7.70M</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>58.4</t>
+          <t>7.69M</t>
         </is>
       </c>
       <c r="G56" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="57">
@@ -2050,31 +2050,31 @@
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>ISM Services PMIDEC</t>
+          <t>ISM Services EmploymentDEC</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>54.1</t>
+          <t>51.4</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>52.1</t>
+          <t>51.5</t>
         </is>
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>53.3</t>
+          <t>51.4</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>54</t>
+          <t>52</t>
         </is>
       </c>
       <c r="G57" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="58">
@@ -2085,31 +2085,31 @@
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>JOLTs Job OpeningsNOV</t>
+          <t>ISM Services PricesDEC</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>8.098M</t>
+          <t>64.4</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>7.839M</t>
+          <t>58.2</t>
         </is>
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>7.70M</t>
+          <t>57.5</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>7.69M</t>
+          <t>58.4</t>
         </is>
       </c>
       <c r="G58" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="59">
@@ -2120,31 +2120,31 @@
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>ISM Services New OrdersDEC</t>
+          <t>ISM Services PMIDEC</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>54.2</t>
+          <t>54.1</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>53.7</t>
+          <t>52.1</t>
         </is>
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>54.2</t>
+          <t>53.3</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>54.1</t>
+          <t>54</t>
         </is>
       </c>
       <c r="G59" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="60">
@@ -2155,23 +2155,23 @@
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>ISM Services Business ActivityDEC</t>
+          <t>JOLTs Job QuitsNOV</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>58.2</t>
+          <t>3.065M</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>53.7</t>
+          <t>3.283M</t>
         </is>
       </c>
       <c r="E60" t="inlineStr"/>
       <c r="F60" t="inlineStr">
         <is>
-          <t>54.1</t>
+          <t>3.31M</t>
         </is>
       </c>
       <c r="G60" t="n">
@@ -2441,31 +2441,31 @@
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>Initial Jobless ClaimsJAN/04</t>
+          <t>Total Vehicle SalesDEC</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>201K</t>
+          <t>16.8M</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>211K</t>
+          <t>16.7M</t>
         </is>
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>218K</t>
+          <t>16.5M</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>213K</t>
+          <t>16.3M</t>
         </is>
       </c>
       <c r="G70" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="71">
@@ -2476,27 +2476,15 @@
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>Jobless Claims 4-week AverageJAN/04</t>
-        </is>
-      </c>
-      <c r="C71" t="inlineStr">
-        <is>
-          <t>213K</t>
-        </is>
-      </c>
-      <c r="D71" t="inlineStr">
-        <is>
-          <t>223.25K</t>
-        </is>
-      </c>
+          <t>Fed Waller Speech</t>
+        </is>
+      </c>
+      <c r="C71" t="inlineStr"/>
+      <c r="D71" t="inlineStr"/>
       <c r="E71" t="inlineStr"/>
-      <c r="F71" t="inlineStr">
-        <is>
-          <t>224K</t>
-        </is>
-      </c>
+      <c r="F71" t="inlineStr"/>
       <c r="G71" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="72">
@@ -2507,31 +2495,31 @@
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>Continuing Jobless ClaimsDEC/28</t>
+          <t>Initial Jobless ClaimsJAN/04</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>1867K</t>
+          <t>201K</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>1834K</t>
+          <t>211K</t>
         </is>
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>1870K</t>
+          <t>218K</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>1848K</t>
+          <t>213K</t>
         </is>
       </c>
       <c r="G72" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="73">
@@ -2542,15 +2530,27 @@
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>Fed Waller Speech</t>
-        </is>
-      </c>
-      <c r="C73" t="inlineStr"/>
-      <c r="D73" t="inlineStr"/>
+          <t>Jobless Claims 4-week AverageJAN/04</t>
+        </is>
+      </c>
+      <c r="C73" t="inlineStr">
+        <is>
+          <t>213K</t>
+        </is>
+      </c>
+      <c r="D73" t="inlineStr">
+        <is>
+          <t>223.25K</t>
+        </is>
+      </c>
       <c r="E73" t="inlineStr"/>
-      <c r="F73" t="inlineStr"/>
+      <c r="F73" t="inlineStr">
+        <is>
+          <t>224K</t>
+        </is>
+      </c>
       <c r="G73" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="74">
@@ -2561,27 +2561,27 @@
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>Total Vehicle SalesDEC</t>
+          <t>Continuing Jobless ClaimsDEC/28</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>16.8M</t>
+          <t>1867K</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>16.7M</t>
+          <t>1834K</t>
         </is>
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>16.5M</t>
+          <t>1870K</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>16.3M</t>
+          <t>1848K</t>
         </is>
       </c>
       <c r="G74" t="n">
@@ -2685,23 +2685,27 @@
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>EIA Crude Oil Imports ChangeJAN/03</t>
+          <t>EIA Gasoline Stocks ChangeJAN/03</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>0.278M</t>
+          <t>6.33M</t>
         </is>
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>0.323M</t>
-        </is>
-      </c>
-      <c r="E78" t="inlineStr"/>
+          <t>7.717M</t>
+        </is>
+      </c>
+      <c r="E78" t="inlineStr">
+        <is>
+          <t>1.5M</t>
+        </is>
+      </c>
       <c r="F78" t="inlineStr"/>
       <c r="G78" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="79">
@@ -2712,27 +2716,23 @@
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>EIA Crude Oil Stocks ChangeJAN/03</t>
+          <t>EIA Gasoline Production ChangeJAN/03</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
+          <t>-0.081M</t>
+        </is>
+      </c>
+      <c r="D79" t="inlineStr">
+        <is>
           <t>-0.959M</t>
         </is>
       </c>
-      <c r="D79" t="inlineStr">
-        <is>
-          <t>-1.178M</t>
-        </is>
-      </c>
-      <c r="E79" t="inlineStr">
-        <is>
-          <t>-0.6M</t>
-        </is>
-      </c>
+      <c r="E79" t="inlineStr"/>
       <c r="F79" t="inlineStr"/>
       <c r="G79" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="80">
@@ -2743,17 +2743,17 @@
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>EIA Distillate Fuel Production ChangeJAN/03</t>
+          <t>EIA Heating Oil Stocks ChangeJAN/03</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>-0.167M</t>
+          <t>-0.632M</t>
         </is>
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>0.099M</t>
+          <t>-0.416M</t>
         </is>
       </c>
       <c r="E80" t="inlineStr"/>
@@ -2770,20 +2770,24 @@
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>EIA Cushing Crude Oil Stocks ChangeJAN/03</t>
+          <t>EIA Distillate Stocks ChangeJAN/03</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>-2.502M</t>
+          <t>6.071M</t>
         </is>
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>-0.142M</t>
-        </is>
-      </c>
-      <c r="E81" t="inlineStr"/>
+          <t>6.406M</t>
+        </is>
+      </c>
+      <c r="E81" t="inlineStr">
+        <is>
+          <t>1M</t>
+        </is>
+      </c>
       <c r="F81" t="inlineStr"/>
       <c r="G81" t="n">
         <v>3</v>
@@ -2824,27 +2828,23 @@
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>EIA Gasoline Stocks ChangeJAN/03</t>
+          <t>EIA Distillate Fuel Production ChangeJAN/03</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>6.33M</t>
+          <t>-0.167M</t>
         </is>
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>7.717M</t>
-        </is>
-      </c>
-      <c r="E83" t="inlineStr">
-        <is>
-          <t>1.5M</t>
-        </is>
-      </c>
+          <t>0.099M</t>
+        </is>
+      </c>
+      <c r="E83" t="inlineStr"/>
       <c r="F83" t="inlineStr"/>
       <c r="G83" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="84">
@@ -2855,23 +2855,27 @@
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>EIA Heating Oil Stocks ChangeJAN/03</t>
+          <t>EIA Crude Oil Stocks ChangeJAN/03</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>-0.632M</t>
+          <t>-0.959M</t>
         </is>
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>-0.416M</t>
-        </is>
-      </c>
-      <c r="E84" t="inlineStr"/>
+          <t>-1.178M</t>
+        </is>
+      </c>
+      <c r="E84" t="inlineStr">
+        <is>
+          <t>-0.6M</t>
+        </is>
+      </c>
       <c r="F84" t="inlineStr"/>
       <c r="G84" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="85">
@@ -2882,17 +2886,17 @@
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>EIA Gasoline Production ChangeJAN/03</t>
+          <t>EIA Crude Oil Imports ChangeJAN/03</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>-0.081M</t>
+          <t>0.278M</t>
         </is>
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>-0.959M</t>
+          <t>0.323M</t>
         </is>
       </c>
       <c r="E85" t="inlineStr"/>
@@ -2909,24 +2913,20 @@
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>EIA Distillate Stocks ChangeJAN/03</t>
+          <t>EIA Cushing Crude Oil Stocks ChangeJAN/03</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>6.071M</t>
+          <t>-2.502M</t>
         </is>
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>6.406M</t>
-        </is>
-      </c>
-      <c r="E86" t="inlineStr">
-        <is>
-          <t>1M</t>
-        </is>
-      </c>
+          <t>-0.142M</t>
+        </is>
+      </c>
+      <c r="E86" t="inlineStr"/>
       <c r="F86" t="inlineStr"/>
       <c r="G86" t="n">
         <v>3</v>
@@ -3336,27 +3336,31 @@
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>U-6 Unemployment Rate</t>
+          <t>Average Hourly Earnings MoMDEC</t>
         </is>
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>7.5%</t>
+          <t>0.3%</t>
         </is>
       </c>
       <c r="D103" t="inlineStr">
         <is>
-          <t>7.7%</t>
-        </is>
-      </c>
-      <c r="E103" t="inlineStr"/>
+          <t>0.4%</t>
+        </is>
+      </c>
+      <c r="E103" t="inlineStr">
+        <is>
+          <t>0.3%</t>
+        </is>
+      </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>7.9%</t>
+          <t>0.3%</t>
         </is>
       </c>
       <c r="G103" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="104">
@@ -3367,31 +3371,31 @@
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>Average Weekly HoursDEC</t>
+          <t>Average Hourly Earnings YoY</t>
         </is>
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>34.3</t>
+          <t>3.9%</t>
         </is>
       </c>
       <c r="D104" t="inlineStr">
         <is>
-          <t>34.3</t>
+          <t>4%</t>
         </is>
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>34.3</t>
+          <t>4%</t>
         </is>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>34.3</t>
+          <t>4%</t>
         </is>
       </c>
       <c r="G104" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="105">
@@ -3402,27 +3406,31 @@
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>Government PayrollsDEC</t>
+          <t>Non Farm PayrollsDEC</t>
         </is>
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>33K</t>
+          <t>256K</t>
         </is>
       </c>
       <c r="D105" t="inlineStr">
         <is>
-          <t>30K</t>
-        </is>
-      </c>
-      <c r="E105" t="inlineStr"/>
+          <t>212K</t>
+        </is>
+      </c>
+      <c r="E105" t="inlineStr">
+        <is>
+          <t>160K</t>
+        </is>
+      </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>15K</t>
+          <t>200K</t>
         </is>
       </c>
       <c r="G105" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="106">
@@ -3433,31 +3441,27 @@
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>Nonfarm Payrolls PrivateDEC</t>
+          <t>Participation RateDEC</t>
         </is>
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>223K</t>
+          <t>62.5%</t>
         </is>
       </c>
       <c r="D106" t="inlineStr">
         <is>
-          <t>182K</t>
-        </is>
-      </c>
-      <c r="E106" t="inlineStr">
-        <is>
-          <t>135K</t>
-        </is>
-      </c>
+          <t>62.5%</t>
+        </is>
+      </c>
+      <c r="E106" t="inlineStr"/>
       <c r="F106" t="inlineStr">
         <is>
-          <t>185K</t>
+          <t>62.8%</t>
         </is>
       </c>
       <c r="G106" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="107">
@@ -3468,31 +3472,31 @@
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>Manufacturing PayrollsDEC</t>
+          <t>Unemployment RateDEC</t>
         </is>
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>-13K</t>
+          <t>4.1%</t>
         </is>
       </c>
       <c r="D107" t="inlineStr">
         <is>
-          <t>25K</t>
+          <t>4.2%</t>
         </is>
       </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t>5K</t>
+          <t>4.2%</t>
         </is>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>29K</t>
+          <t>4.30%</t>
         </is>
       </c>
       <c r="G107" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="108">
@@ -3503,27 +3507,31 @@
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>Participation RateDEC</t>
+          <t>Nonfarm Payrolls PrivateDEC</t>
         </is>
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>62.5%</t>
+          <t>223K</t>
         </is>
       </c>
       <c r="D108" t="inlineStr">
         <is>
-          <t>62.5%</t>
-        </is>
-      </c>
-      <c r="E108" t="inlineStr"/>
+          <t>182K</t>
+        </is>
+      </c>
+      <c r="E108" t="inlineStr">
+        <is>
+          <t>135K</t>
+        </is>
+      </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>62.8%</t>
+          <t>185K</t>
         </is>
       </c>
       <c r="G108" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="109">
@@ -3534,31 +3542,27 @@
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>Non Farm PayrollsDEC</t>
+          <t>Government PayrollsDEC</t>
         </is>
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>256K</t>
+          <t>33K</t>
         </is>
       </c>
       <c r="D109" t="inlineStr">
         <is>
-          <t>212K</t>
-        </is>
-      </c>
-      <c r="E109" t="inlineStr">
-        <is>
-          <t>160K</t>
-        </is>
-      </c>
+          <t>30K</t>
+        </is>
+      </c>
+      <c r="E109" t="inlineStr"/>
       <c r="F109" t="inlineStr">
         <is>
-          <t>200K</t>
+          <t>15K</t>
         </is>
       </c>
       <c r="G109" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="110">
@@ -3569,31 +3573,31 @@
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>Average Hourly Earnings YoY</t>
+          <t>Average Weekly HoursDEC</t>
         </is>
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>3.9%</t>
+          <t>34.3</t>
         </is>
       </c>
       <c r="D110" t="inlineStr">
         <is>
-          <t>4%</t>
+          <t>34.3</t>
         </is>
       </c>
       <c r="E110" t="inlineStr">
         <is>
-          <t>4%</t>
+          <t>34.3</t>
         </is>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>4%</t>
+          <t>34.3</t>
         </is>
       </c>
       <c r="G110" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="111">
@@ -3604,31 +3608,27 @@
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>Average Hourly Earnings MoMDEC</t>
+          <t>U-6 Unemployment Rate</t>
         </is>
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>0.3%</t>
+          <t>7.5%</t>
         </is>
       </c>
       <c r="D111" t="inlineStr">
         <is>
-          <t>0.4%</t>
-        </is>
-      </c>
-      <c r="E111" t="inlineStr">
-        <is>
-          <t>0.3%</t>
-        </is>
-      </c>
+          <t>7.7%</t>
+        </is>
+      </c>
+      <c r="E111" t="inlineStr"/>
       <c r="F111" t="inlineStr">
         <is>
-          <t>0.3%</t>
+          <t>7.9%</t>
         </is>
       </c>
       <c r="G111" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="112">
@@ -3639,31 +3639,31 @@
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>Unemployment RateDEC</t>
+          <t>Manufacturing PayrollsDEC</t>
         </is>
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>4.1%</t>
+          <t>-13K</t>
         </is>
       </c>
       <c r="D112" t="inlineStr">
         <is>
-          <t>4.2%</t>
+          <t>25K</t>
         </is>
       </c>
       <c r="E112" t="inlineStr">
         <is>
-          <t>4.2%</t>
+          <t>5K</t>
         </is>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>4.30%</t>
+          <t>29K</t>
         </is>
       </c>
       <c r="G112" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="113">
@@ -3833,11 +3833,19 @@
       </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t>WASDE Report</t>
-        </is>
-      </c>
-      <c r="C118" t="inlineStr"/>
-      <c r="D118" t="inlineStr"/>
+          <t>Quarterly Grain Stocks - SoyDEC</t>
+        </is>
+      </c>
+      <c r="C118" t="inlineStr">
+        <is>
+          <t>3.1B</t>
+        </is>
+      </c>
+      <c r="D118" t="inlineStr">
+        <is>
+          <t>0.342B</t>
+        </is>
+      </c>
       <c r="E118" t="inlineStr"/>
       <c r="F118" t="inlineStr"/>
       <c r="G118" t="n">
@@ -3852,17 +3860,17 @@
       </c>
       <c r="B119" t="inlineStr">
         <is>
-          <t>Quarterly Grain Stocks - WheatDEC</t>
+          <t>Quarterly Grain Stocks - CornDEC</t>
         </is>
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>1.57B</t>
+          <t>12.074B</t>
         </is>
       </c>
       <c r="D119" t="inlineStr">
         <is>
-          <t>1.98B</t>
+          <t>1.760B</t>
         </is>
       </c>
       <c r="E119" t="inlineStr"/>
@@ -3879,17 +3887,17 @@
       </c>
       <c r="B120" t="inlineStr">
         <is>
-          <t>Quarterly Grain Stocks - CornDEC</t>
+          <t>Quarterly Grain Stocks - WheatDEC</t>
         </is>
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>12.074B</t>
+          <t>1.57B</t>
         </is>
       </c>
       <c r="D120" t="inlineStr">
         <is>
-          <t>1.760B</t>
+          <t>1.98B</t>
         </is>
       </c>
       <c r="E120" t="inlineStr"/>
@@ -3906,19 +3914,11 @@
       </c>
       <c r="B121" t="inlineStr">
         <is>
-          <t>Quarterly Grain Stocks - SoyDEC</t>
-        </is>
-      </c>
-      <c r="C121" t="inlineStr">
-        <is>
-          <t>3.1B</t>
-        </is>
-      </c>
-      <c r="D121" t="inlineStr">
-        <is>
-          <t>0.342B</t>
-        </is>
-      </c>
+          <t>WASDE Report</t>
+        </is>
+      </c>
+      <c r="C121" t="inlineStr"/>
+      <c r="D121" t="inlineStr"/>
       <c r="E121" t="inlineStr"/>
       <c r="F121" t="inlineStr"/>
       <c r="G121" t="n">
@@ -4134,27 +4134,23 @@
       </c>
       <c r="B129" t="inlineStr">
         <is>
-          <t>PPI Ex Food, Energy and Trade MoMDEC</t>
+          <t>PPIDEC</t>
         </is>
       </c>
       <c r="C129" t="inlineStr">
         <is>
-          <t>0.1%</t>
+          <t>146.842</t>
         </is>
       </c>
       <c r="D129" t="inlineStr">
         <is>
-          <t>0.1%</t>
-        </is>
-      </c>
-      <c r="E129" t="inlineStr">
-        <is>
-          <t>0.3%</t>
-        </is>
-      </c>
+          <t>146.521</t>
+        </is>
+      </c>
+      <c r="E129" t="inlineStr"/>
       <c r="F129" t="inlineStr">
         <is>
-          <t>0.2%</t>
+          <t>146.8</t>
         </is>
       </c>
       <c r="G129" t="n">
@@ -4169,27 +4165,31 @@
       </c>
       <c r="B130" t="inlineStr">
         <is>
-          <t>PPI Ex Food, Energy and Trade YoYDEC</t>
+          <t>PPI MoMDEC</t>
         </is>
       </c>
       <c r="C130" t="inlineStr">
         <is>
-          <t>3.3%</t>
+          <t>0.2%</t>
         </is>
       </c>
       <c r="D130" t="inlineStr">
         <is>
-          <t>3.5%</t>
-        </is>
-      </c>
-      <c r="E130" t="inlineStr"/>
+          <t>0.4%</t>
+        </is>
+      </c>
+      <c r="E130" t="inlineStr">
+        <is>
+          <t>0.3%</t>
+        </is>
+      </c>
       <c r="F130" t="inlineStr">
         <is>
-          <t>3.6%</t>
+          <t>0.3%</t>
         </is>
       </c>
       <c r="G130" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="131">
@@ -4200,31 +4200,31 @@
       </c>
       <c r="B131" t="inlineStr">
         <is>
-          <t>Core PPI YoYDEC</t>
+          <t>Core PPI MoMDEC</t>
         </is>
       </c>
       <c r="C131" t="inlineStr">
         <is>
-          <t>3.5%</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="D131" t="inlineStr">
         <is>
-          <t>3.5%</t>
+          <t>0.2%</t>
         </is>
       </c>
       <c r="E131" t="inlineStr">
         <is>
-          <t>3.8%</t>
+          <t>0.3%</t>
         </is>
       </c>
       <c r="F131" t="inlineStr">
         <is>
-          <t>3.5%</t>
+          <t>0.2%</t>
         </is>
       </c>
       <c r="G131" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="132">
@@ -4235,31 +4235,31 @@
       </c>
       <c r="B132" t="inlineStr">
         <is>
-          <t>Core PPI MoMDEC</t>
+          <t>PPI YoYDEC</t>
         </is>
       </c>
       <c r="C132" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>3.3%</t>
         </is>
       </c>
       <c r="D132" t="inlineStr">
         <is>
-          <t>0.2%</t>
+          <t>3%</t>
         </is>
       </c>
       <c r="E132" t="inlineStr">
         <is>
-          <t>0.3%</t>
+          <t>3.4%</t>
         </is>
       </c>
       <c r="F132" t="inlineStr">
         <is>
-          <t>0.2%</t>
+          <t>3.3%</t>
         </is>
       </c>
       <c r="G132" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="133">
@@ -4270,31 +4270,27 @@
       </c>
       <c r="B133" t="inlineStr">
         <is>
-          <t>PPI MoMDEC</t>
+          <t>PPI Ex Food, Energy and Trade YoYDEC</t>
         </is>
       </c>
       <c r="C133" t="inlineStr">
         <is>
-          <t>0.2%</t>
+          <t>3.3%</t>
         </is>
       </c>
       <c r="D133" t="inlineStr">
         <is>
-          <t>0.4%</t>
-        </is>
-      </c>
-      <c r="E133" t="inlineStr">
-        <is>
-          <t>0.3%</t>
-        </is>
-      </c>
+          <t>3.5%</t>
+        </is>
+      </c>
+      <c r="E133" t="inlineStr"/>
       <c r="F133" t="inlineStr">
         <is>
-          <t>0.3%</t>
+          <t>3.6%</t>
         </is>
       </c>
       <c r="G133" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="134">
@@ -4305,27 +4301,27 @@
       </c>
       <c r="B134" t="inlineStr">
         <is>
-          <t>PPI YoYDEC</t>
+          <t>PPI Ex Food, Energy and Trade MoMDEC</t>
         </is>
       </c>
       <c r="C134" t="inlineStr">
         <is>
-          <t>3.3%</t>
+          <t>0.1%</t>
         </is>
       </c>
       <c r="D134" t="inlineStr">
         <is>
-          <t>3%</t>
+          <t>0.1%</t>
         </is>
       </c>
       <c r="E134" t="inlineStr">
         <is>
-          <t>3.4%</t>
+          <t>0.3%</t>
         </is>
       </c>
       <c r="F134" t="inlineStr">
         <is>
-          <t>3.3%</t>
+          <t>0.2%</t>
         </is>
       </c>
       <c r="G134" t="n">
@@ -4340,23 +4336,27 @@
       </c>
       <c r="B135" t="inlineStr">
         <is>
-          <t>PPIDEC</t>
+          <t>Core PPI YoYDEC</t>
         </is>
       </c>
       <c r="C135" t="inlineStr">
         <is>
-          <t>146.842</t>
+          <t>3.5%</t>
         </is>
       </c>
       <c r="D135" t="inlineStr">
         <is>
-          <t>146.521</t>
-        </is>
-      </c>
-      <c r="E135" t="inlineStr"/>
+          <t>3.5%</t>
+        </is>
+      </c>
+      <c r="E135" t="inlineStr">
+        <is>
+          <t>3.8%</t>
+        </is>
+      </c>
       <c r="F135" t="inlineStr">
         <is>
-          <t>146.8</t>
+          <t>3.5%</t>
         </is>
       </c>
       <c r="G135" t="n">
@@ -4564,23 +4564,23 @@
       </c>
       <c r="B143" t="inlineStr">
         <is>
-          <t>MBA 30-Year Mortgage RateJAN/10</t>
+          <t>MBA Mortgage Refinance IndexJAN/10</t>
         </is>
       </c>
       <c r="C143" t="inlineStr">
         <is>
-          <t>7.09%</t>
+          <t>575.6</t>
         </is>
       </c>
       <c r="D143" t="inlineStr">
         <is>
-          <t>6.99%</t>
+          <t>401.1000</t>
         </is>
       </c>
       <c r="E143" t="inlineStr"/>
       <c r="F143" t="inlineStr"/>
       <c r="G143" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="144">
@@ -4591,17 +4591,17 @@
       </c>
       <c r="B144" t="inlineStr">
         <is>
-          <t>MBA Mortgage ApplicationsJAN/10</t>
+          <t>MBA Purchase IndexJAN/10</t>
         </is>
       </c>
       <c r="C144" t="inlineStr">
         <is>
-          <t>33.3%</t>
+          <t>162</t>
         </is>
       </c>
       <c r="D144" t="inlineStr">
         <is>
-          <t>-3.7%</t>
+          <t>127.7000</t>
         </is>
       </c>
       <c r="E144" t="inlineStr"/>
@@ -4618,17 +4618,17 @@
       </c>
       <c r="B145" t="inlineStr">
         <is>
-          <t>MBA Purchase IndexJAN/10</t>
+          <t>MBA Mortgage Market IndexJAN/10</t>
         </is>
       </c>
       <c r="C145" t="inlineStr">
         <is>
-          <t>162</t>
+          <t>224.4</t>
         </is>
       </c>
       <c r="D145" t="inlineStr">
         <is>
-          <t>127.7000</t>
+          <t>168.4</t>
         </is>
       </c>
       <c r="E145" t="inlineStr"/>
@@ -4645,23 +4645,23 @@
       </c>
       <c r="B146" t="inlineStr">
         <is>
-          <t>MBA Mortgage Market IndexJAN/10</t>
+          <t>MBA 30-Year Mortgage RateJAN/10</t>
         </is>
       </c>
       <c r="C146" t="inlineStr">
         <is>
-          <t>224.4</t>
+          <t>7.09%</t>
         </is>
       </c>
       <c r="D146" t="inlineStr">
         <is>
-          <t>168.4</t>
+          <t>6.99%</t>
         </is>
       </c>
       <c r="E146" t="inlineStr"/>
       <c r="F146" t="inlineStr"/>
       <c r="G146" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="147">
@@ -4672,17 +4672,17 @@
       </c>
       <c r="B147" t="inlineStr">
         <is>
-          <t>MBA Mortgage Refinance IndexJAN/10</t>
+          <t>MBA Mortgage ApplicationsJAN/10</t>
         </is>
       </c>
       <c r="C147" t="inlineStr">
         <is>
-          <t>575.6</t>
+          <t>33.3%</t>
         </is>
       </c>
       <c r="D147" t="inlineStr">
         <is>
-          <t>401.1000</t>
+          <t>-3.7%</t>
         </is>
       </c>
       <c r="E147" t="inlineStr"/>
@@ -4978,17 +4978,17 @@
       </c>
       <c r="B157" t="inlineStr">
         <is>
-          <t>EIA Gasoline Production ChangeJAN/10</t>
+          <t>EIA Heating Oil Stocks ChangeJAN/10</t>
         </is>
       </c>
       <c r="C157" t="inlineStr">
         <is>
-          <t>0.397M</t>
+          <t>0.646M</t>
         </is>
       </c>
       <c r="D157" t="inlineStr">
         <is>
-          <t>-0.081M</t>
+          <t>-0.632M</t>
         </is>
       </c>
       <c r="E157" t="inlineStr"/>
@@ -5005,17 +5005,17 @@
       </c>
       <c r="B158" t="inlineStr">
         <is>
-          <t>EIA Crude Oil Imports ChangeJAN/10</t>
+          <t>EIA Cushing Crude Oil Stocks ChangeJAN/10</t>
         </is>
       </c>
       <c r="C158" t="inlineStr">
         <is>
-          <t>-1.304M</t>
+          <t>0.765M</t>
         </is>
       </c>
       <c r="D158" t="inlineStr">
         <is>
-          <t>0.278M</t>
+          <t>-2.502M</t>
         </is>
       </c>
       <c r="E158" t="inlineStr"/>
@@ -5032,22 +5032,22 @@
       </c>
       <c r="B159" t="inlineStr">
         <is>
-          <t>EIA Crude Oil Stocks ChangeJAN/10</t>
+          <t>EIA Gasoline Stocks ChangeJAN/10</t>
         </is>
       </c>
       <c r="C159" t="inlineStr">
         <is>
-          <t>-1.961M</t>
+          <t>5.852M</t>
         </is>
       </c>
       <c r="D159" t="inlineStr">
         <is>
-          <t>-0.959M</t>
+          <t>6.33M</t>
         </is>
       </c>
       <c r="E159" t="inlineStr">
         <is>
-          <t>-1.6M</t>
+          <t>2.60M</t>
         </is>
       </c>
       <c r="F159" t="inlineStr"/>
@@ -5063,20 +5063,24 @@
       </c>
       <c r="B160" t="inlineStr">
         <is>
-          <t>EIA Distillate Fuel Production ChangeJAN/10</t>
+          <t>EIA Distillate Stocks ChangeJAN/10</t>
         </is>
       </c>
       <c r="C160" t="inlineStr">
         <is>
-          <t>-0.021M</t>
+          <t>3.077M</t>
         </is>
       </c>
       <c r="D160" t="inlineStr">
         <is>
-          <t>-0.167M</t>
-        </is>
-      </c>
-      <c r="E160" t="inlineStr"/>
+          <t>6.071M</t>
+        </is>
+      </c>
+      <c r="E160" t="inlineStr">
+        <is>
+          <t>1.1M</t>
+        </is>
+      </c>
       <c r="F160" t="inlineStr"/>
       <c r="G160" t="n">
         <v>3</v>
@@ -5090,24 +5094,20 @@
       </c>
       <c r="B161" t="inlineStr">
         <is>
-          <t>EIA Distillate Stocks ChangeJAN/10</t>
+          <t>EIA Refinery Crude Runs ChangeJAN/10</t>
         </is>
       </c>
       <c r="C161" t="inlineStr">
         <is>
-          <t>3.077M</t>
+          <t>-0.255M</t>
         </is>
       </c>
       <c r="D161" t="inlineStr">
         <is>
-          <t>6.071M</t>
-        </is>
-      </c>
-      <c r="E161" t="inlineStr">
-        <is>
-          <t>1.1M</t>
-        </is>
-      </c>
+          <t>0.045M</t>
+        </is>
+      </c>
+      <c r="E161" t="inlineStr"/>
       <c r="F161" t="inlineStr"/>
       <c r="G161" t="n">
         <v>3</v>
@@ -5121,23 +5121,27 @@
       </c>
       <c r="B162" t="inlineStr">
         <is>
-          <t>EIA Heating Oil Stocks ChangeJAN/10</t>
+          <t>EIA Crude Oil Stocks ChangeJAN/10</t>
         </is>
       </c>
       <c r="C162" t="inlineStr">
         <is>
-          <t>0.646M</t>
+          <t>-1.961M</t>
         </is>
       </c>
       <c r="D162" t="inlineStr">
         <is>
-          <t>-0.632M</t>
-        </is>
-      </c>
-      <c r="E162" t="inlineStr"/>
+          <t>-0.959M</t>
+        </is>
+      </c>
+      <c r="E162" t="inlineStr">
+        <is>
+          <t>-1.6M</t>
+        </is>
+      </c>
       <c r="F162" t="inlineStr"/>
       <c r="G162" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="163">
@@ -5148,27 +5152,23 @@
       </c>
       <c r="B163" t="inlineStr">
         <is>
-          <t>EIA Gasoline Stocks ChangeJAN/10</t>
+          <t>EIA Gasoline Production ChangeJAN/10</t>
         </is>
       </c>
       <c r="C163" t="inlineStr">
         <is>
-          <t>5.852M</t>
+          <t>0.397M</t>
         </is>
       </c>
       <c r="D163" t="inlineStr">
         <is>
-          <t>6.33M</t>
-        </is>
-      </c>
-      <c r="E163" t="inlineStr">
-        <is>
-          <t>2.60M</t>
-        </is>
-      </c>
+          <t>-0.081M</t>
+        </is>
+      </c>
+      <c r="E163" t="inlineStr"/>
       <c r="F163" t="inlineStr"/>
       <c r="G163" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="164">
@@ -5179,17 +5179,17 @@
       </c>
       <c r="B164" t="inlineStr">
         <is>
-          <t>EIA Cushing Crude Oil Stocks ChangeJAN/10</t>
+          <t>EIA Distillate Fuel Production ChangeJAN/10</t>
         </is>
       </c>
       <c r="C164" t="inlineStr">
         <is>
-          <t>0.765M</t>
+          <t>-0.021M</t>
         </is>
       </c>
       <c r="D164" t="inlineStr">
         <is>
-          <t>-2.502M</t>
+          <t>-0.167M</t>
         </is>
       </c>
       <c r="E164" t="inlineStr"/>
@@ -5206,17 +5206,17 @@
       </c>
       <c r="B165" t="inlineStr">
         <is>
-          <t>EIA Refinery Crude Runs ChangeJAN/10</t>
+          <t>EIA Crude Oil Imports ChangeJAN/10</t>
         </is>
       </c>
       <c r="C165" t="inlineStr">
         <is>
-          <t>-0.255M</t>
+          <t>-1.304M</t>
         </is>
       </c>
       <c r="D165" t="inlineStr">
         <is>
-          <t>0.045M</t>
+          <t>0.278M</t>
         </is>
       </c>
       <c r="E165" t="inlineStr"/>
@@ -5336,27 +5336,23 @@
       </c>
       <c r="B171" t="inlineStr">
         <is>
-          <t>Import Prices YoYDEC</t>
+          <t>Export Prices YoYDEC</t>
         </is>
       </c>
       <c r="C171" t="inlineStr">
         <is>
-          <t>2.2%</t>
+          <t>1.8%</t>
         </is>
       </c>
       <c r="D171" t="inlineStr">
         <is>
-          <t>1.4%</t>
-        </is>
-      </c>
-      <c r="E171" t="inlineStr">
-        <is>
-          <t>2.1%</t>
-        </is>
-      </c>
+          <t>0.9%</t>
+        </is>
+      </c>
+      <c r="E171" t="inlineStr"/>
       <c r="F171" t="inlineStr">
         <is>
-          <t>1.6%</t>
+          <t>1.9%</t>
         </is>
       </c>
       <c r="G171" t="n">
@@ -5371,21 +5367,25 @@
       </c>
       <c r="B172" t="inlineStr">
         <is>
-          <t>Philly Fed EmploymentJAN</t>
+          <t>Retail Sales YoYDEC</t>
         </is>
       </c>
       <c r="C172" t="inlineStr">
         <is>
-          <t>11.9</t>
+          <t>3.9%</t>
         </is>
       </c>
       <c r="D172" t="inlineStr">
         <is>
-          <t>4.8</t>
+          <t>4.1%</t>
         </is>
       </c>
       <c r="E172" t="inlineStr"/>
-      <c r="F172" t="inlineStr"/>
+      <c r="F172" t="inlineStr">
+        <is>
+          <t>4.0%</t>
+        </is>
+      </c>
       <c r="G172" t="n">
         <v>3</v>
       </c>
@@ -5398,31 +5398,31 @@
       </c>
       <c r="B173" t="inlineStr">
         <is>
-          <t>Continuing Jobless ClaimsJAN/04</t>
+          <t>Retail Sales MoMDEC</t>
         </is>
       </c>
       <c r="C173" t="inlineStr">
         <is>
-          <t>1859K</t>
+          <t>0.4%</t>
         </is>
       </c>
       <c r="D173" t="inlineStr">
         <is>
-          <t>1867K</t>
+          <t>0.8%</t>
         </is>
       </c>
       <c r="E173" t="inlineStr">
         <is>
-          <t>1870K</t>
+          <t>0.6%</t>
         </is>
       </c>
       <c r="F173" t="inlineStr">
         <is>
-          <t>1870.0K</t>
+          <t>0.5%</t>
         </is>
       </c>
       <c r="G173" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="174">
@@ -5433,7 +5433,7 @@
       </c>
       <c r="B174" t="inlineStr">
         <is>
-          <t>Retail Sales Ex Gas/Autos MoMDEC</t>
+          <t>Export Prices MoMDEC</t>
         </is>
       </c>
       <c r="C174" t="inlineStr">
@@ -5443,21 +5443,21 @@
       </c>
       <c r="D174" t="inlineStr">
         <is>
+          <t>0%</t>
+        </is>
+      </c>
+      <c r="E174" t="inlineStr">
+        <is>
           <t>0.2%</t>
         </is>
       </c>
-      <c r="E174" t="inlineStr">
-        <is>
-          <t>0.4%</t>
-        </is>
-      </c>
       <c r="F174" t="inlineStr">
         <is>
-          <t>0.4%</t>
+          <t>0.5%</t>
         </is>
       </c>
       <c r="G174" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="175">
@@ -5468,23 +5468,31 @@
       </c>
       <c r="B175" t="inlineStr">
         <is>
-          <t>Philly Fed New OrdersJAN</t>
+          <t>Initial Jobless ClaimsJAN/11</t>
         </is>
       </c>
       <c r="C175" t="inlineStr">
         <is>
-          <t>42.9</t>
+          <t>217K</t>
         </is>
       </c>
       <c r="D175" t="inlineStr">
         <is>
-          <t>-3.6</t>
-        </is>
-      </c>
-      <c r="E175" t="inlineStr"/>
-      <c r="F175" t="inlineStr"/>
+          <t>203K</t>
+        </is>
+      </c>
+      <c r="E175" t="inlineStr">
+        <is>
+          <t>210K</t>
+        </is>
+      </c>
+      <c r="F175" t="inlineStr">
+        <is>
+          <t>209.0K</t>
+        </is>
+      </c>
       <c r="G175" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="176">
@@ -5495,27 +5503,31 @@
       </c>
       <c r="B176" t="inlineStr">
         <is>
-          <t>Jobless Claims 4-week AverageJAN/11</t>
+          <t>Retail Sales Ex Autos MoMDEC</t>
         </is>
       </c>
       <c r="C176" t="inlineStr">
         <is>
-          <t>212.75K</t>
+          <t>0.4%</t>
         </is>
       </c>
       <c r="D176" t="inlineStr">
         <is>
-          <t>213.5K</t>
-        </is>
-      </c>
-      <c r="E176" t="inlineStr"/>
+          <t>0.2%</t>
+        </is>
+      </c>
+      <c r="E176" t="inlineStr">
+        <is>
+          <t>0.4%</t>
+        </is>
+      </c>
       <c r="F176" t="inlineStr">
         <is>
-          <t>215.0K</t>
+          <t>0.4%</t>
         </is>
       </c>
       <c r="G176" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="177">
@@ -5526,31 +5538,23 @@
       </c>
       <c r="B177" t="inlineStr">
         <is>
-          <t>Import Prices MoMDEC</t>
+          <t>Philly Fed Prices PaidJAN</t>
         </is>
       </c>
       <c r="C177" t="inlineStr">
         <is>
-          <t>0.1%</t>
+          <t>31.90</t>
         </is>
       </c>
       <c r="D177" t="inlineStr">
         <is>
-          <t>0.1%</t>
-        </is>
-      </c>
-      <c r="E177" t="inlineStr">
-        <is>
-          <t>0.1%</t>
-        </is>
-      </c>
-      <c r="F177" t="inlineStr">
-        <is>
-          <t>0.1%</t>
-        </is>
-      </c>
+          <t>26.60</t>
+        </is>
+      </c>
+      <c r="E177" t="inlineStr"/>
+      <c r="F177" t="inlineStr"/>
       <c r="G177" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="178">
@@ -5561,25 +5565,21 @@
       </c>
       <c r="B178" t="inlineStr">
         <is>
-          <t>Export Prices YoYDEC</t>
+          <t>Philly Fed Business ConditionsJAN</t>
         </is>
       </c>
       <c r="C178" t="inlineStr">
         <is>
-          <t>1.8%</t>
+          <t>46.3</t>
         </is>
       </c>
       <c r="D178" t="inlineStr">
         <is>
-          <t>0.9%</t>
+          <t>33.8</t>
         </is>
       </c>
       <c r="E178" t="inlineStr"/>
-      <c r="F178" t="inlineStr">
-        <is>
-          <t>1.9%</t>
-        </is>
-      </c>
+      <c r="F178" t="inlineStr"/>
       <c r="G178" t="n">
         <v>3</v>
       </c>
@@ -5592,31 +5592,23 @@
       </c>
       <c r="B179" t="inlineStr">
         <is>
-          <t>Philadelphia Fed Manufacturing IndexJAN</t>
+          <t>Philly Fed CAPEX IndexJAN</t>
         </is>
       </c>
       <c r="C179" t="inlineStr">
         <is>
-          <t>44.3</t>
+          <t>39.00</t>
         </is>
       </c>
       <c r="D179" t="inlineStr">
         <is>
-          <t>-10.9</t>
-        </is>
-      </c>
-      <c r="E179" t="inlineStr">
-        <is>
-          <t>-5</t>
-        </is>
-      </c>
-      <c r="F179" t="inlineStr">
-        <is>
-          <t>-10</t>
-        </is>
-      </c>
+          <t>22.20</t>
+        </is>
+      </c>
+      <c r="E179" t="inlineStr"/>
+      <c r="F179" t="inlineStr"/>
       <c r="G179" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="180">
@@ -5627,23 +5619,31 @@
       </c>
       <c r="B180" t="inlineStr">
         <is>
-          <t>Philly Fed CAPEX IndexJAN</t>
+          <t>Import Prices MoMDEC</t>
         </is>
       </c>
       <c r="C180" t="inlineStr">
         <is>
-          <t>39.00</t>
+          <t>0.1%</t>
         </is>
       </c>
       <c r="D180" t="inlineStr">
         <is>
-          <t>22.20</t>
-        </is>
-      </c>
-      <c r="E180" t="inlineStr"/>
-      <c r="F180" t="inlineStr"/>
+          <t>0.1%</t>
+        </is>
+      </c>
+      <c r="E180" t="inlineStr">
+        <is>
+          <t>0.1%</t>
+        </is>
+      </c>
+      <c r="F180" t="inlineStr">
+        <is>
+          <t>0.1%</t>
+        </is>
+      </c>
       <c r="G180" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="181">
@@ -5654,21 +5654,25 @@
       </c>
       <c r="B181" t="inlineStr">
         <is>
-          <t>Philly Fed Business ConditionsJAN</t>
+          <t>Jobless Claims 4-week AverageJAN/11</t>
         </is>
       </c>
       <c r="C181" t="inlineStr">
         <is>
-          <t>46.3</t>
+          <t>212.75K</t>
         </is>
       </c>
       <c r="D181" t="inlineStr">
         <is>
-          <t>33.8</t>
+          <t>213.5K</t>
         </is>
       </c>
       <c r="E181" t="inlineStr"/>
-      <c r="F181" t="inlineStr"/>
+      <c r="F181" t="inlineStr">
+        <is>
+          <t>215.0K</t>
+        </is>
+      </c>
       <c r="G181" t="n">
         <v>3</v>
       </c>
@@ -5681,17 +5685,17 @@
       </c>
       <c r="B182" t="inlineStr">
         <is>
-          <t>Philly Fed Prices PaidJAN</t>
+          <t>Philly Fed New OrdersJAN</t>
         </is>
       </c>
       <c r="C182" t="inlineStr">
         <is>
-          <t>31.90</t>
+          <t>42.9</t>
         </is>
       </c>
       <c r="D182" t="inlineStr">
         <is>
-          <t>26.60</t>
+          <t>-3.6</t>
         </is>
       </c>
       <c r="E182" t="inlineStr"/>
@@ -5708,31 +5712,31 @@
       </c>
       <c r="B183" t="inlineStr">
         <is>
-          <t>Retail Sales Ex Autos MoMDEC</t>
+          <t>Retail Sales Ex Gas/Autos MoMDEC</t>
         </is>
       </c>
       <c r="C183" t="inlineStr">
         <is>
+          <t>0.3%</t>
+        </is>
+      </c>
+      <c r="D183" t="inlineStr">
+        <is>
+          <t>0.2%</t>
+        </is>
+      </c>
+      <c r="E183" t="inlineStr">
+        <is>
           <t>0.4%</t>
         </is>
       </c>
-      <c r="D183" t="inlineStr">
-        <is>
-          <t>0.2%</t>
-        </is>
-      </c>
-      <c r="E183" t="inlineStr">
+      <c r="F183" t="inlineStr">
         <is>
           <t>0.4%</t>
         </is>
       </c>
-      <c r="F183" t="inlineStr">
-        <is>
-          <t>0.4%</t>
-        </is>
-      </c>
       <c r="G183" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="184">
@@ -5743,31 +5747,31 @@
       </c>
       <c r="B184" t="inlineStr">
         <is>
-          <t>Initial Jobless ClaimsJAN/11</t>
+          <t>Continuing Jobless ClaimsJAN/04</t>
         </is>
       </c>
       <c r="C184" t="inlineStr">
         <is>
-          <t>217K</t>
+          <t>1859K</t>
         </is>
       </c>
       <c r="D184" t="inlineStr">
         <is>
-          <t>203K</t>
+          <t>1867K</t>
         </is>
       </c>
       <c r="E184" t="inlineStr">
         <is>
-          <t>210K</t>
+          <t>1870K</t>
         </is>
       </c>
       <c r="F184" t="inlineStr">
         <is>
-          <t>209.0K</t>
+          <t>1870.0K</t>
         </is>
       </c>
       <c r="G184" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="185">
@@ -5778,31 +5782,23 @@
       </c>
       <c r="B185" t="inlineStr">
         <is>
-          <t>Export Prices MoMDEC</t>
+          <t>Philly Fed EmploymentJAN</t>
         </is>
       </c>
       <c r="C185" t="inlineStr">
         <is>
-          <t>0.3%</t>
+          <t>11.9</t>
         </is>
       </c>
       <c r="D185" t="inlineStr">
         <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="E185" t="inlineStr">
-        <is>
-          <t>0.2%</t>
-        </is>
-      </c>
-      <c r="F185" t="inlineStr">
-        <is>
-          <t>0.5%</t>
-        </is>
-      </c>
+          <t>4.8</t>
+        </is>
+      </c>
+      <c r="E185" t="inlineStr"/>
+      <c r="F185" t="inlineStr"/>
       <c r="G185" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="186">
@@ -5813,31 +5809,31 @@
       </c>
       <c r="B186" t="inlineStr">
         <is>
-          <t>Retail Sales MoMDEC</t>
+          <t>Import Prices YoYDEC</t>
         </is>
       </c>
       <c r="C186" t="inlineStr">
         <is>
-          <t>0.4%</t>
+          <t>2.2%</t>
         </is>
       </c>
       <c r="D186" t="inlineStr">
         <is>
-          <t>0.8%</t>
+          <t>1.4%</t>
         </is>
       </c>
       <c r="E186" t="inlineStr">
         <is>
-          <t>0.6%</t>
+          <t>2.1%</t>
         </is>
       </c>
       <c r="F186" t="inlineStr">
         <is>
-          <t>0.5%</t>
+          <t>1.6%</t>
         </is>
       </c>
       <c r="G186" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="187">
@@ -5848,27 +5844,31 @@
       </c>
       <c r="B187" t="inlineStr">
         <is>
-          <t>Retail Sales YoYDEC</t>
+          <t>Philadelphia Fed Manufacturing IndexJAN</t>
         </is>
       </c>
       <c r="C187" t="inlineStr">
         <is>
-          <t>3.9%</t>
+          <t>44.3</t>
         </is>
       </c>
       <c r="D187" t="inlineStr">
         <is>
-          <t>4.1%</t>
-        </is>
-      </c>
-      <c r="E187" t="inlineStr"/>
+          <t>-10.9</t>
+        </is>
+      </c>
+      <c r="E187" t="inlineStr">
+        <is>
+          <t>-5</t>
+        </is>
+      </c>
       <c r="F187" t="inlineStr">
         <is>
-          <t>4.0%</t>
+          <t>-10</t>
         </is>
       </c>
       <c r="G187" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="188">
@@ -6015,17 +6015,17 @@
       </c>
       <c r="B192" t="inlineStr">
         <is>
-          <t>8-Week Bill Auction</t>
+          <t>4-Week Bill Auction</t>
         </is>
       </c>
       <c r="C192" t="inlineStr">
         <is>
-          <t>4.235%</t>
+          <t>4.240%</t>
         </is>
       </c>
       <c r="D192" t="inlineStr">
         <is>
-          <t>4.240%</t>
+          <t>4.245%</t>
         </is>
       </c>
       <c r="E192" t="inlineStr"/>
@@ -6042,17 +6042,17 @@
       </c>
       <c r="B193" t="inlineStr">
         <is>
-          <t>4-Week Bill Auction</t>
+          <t>8-Week Bill Auction</t>
         </is>
       </c>
       <c r="C193" t="inlineStr">
         <is>
+          <t>4.235%</t>
+        </is>
+      </c>
+      <c r="D193" t="inlineStr">
+        <is>
           <t>4.240%</t>
-        </is>
-      </c>
-      <c r="D193" t="inlineStr">
-        <is>
-          <t>4.245%</t>
         </is>
       </c>
       <c r="E193" t="inlineStr"/>
@@ -6503,27 +6503,23 @@
       </c>
       <c r="B208" t="inlineStr">
         <is>
-          <t>Net Long-term TIC FlowsNOV</t>
+          <t>Foreign Bond InvestmentNOV</t>
         </is>
       </c>
       <c r="C208" t="inlineStr">
         <is>
-          <t>$79B</t>
+          <t>$-15.8B</t>
         </is>
       </c>
       <c r="D208" t="inlineStr">
         <is>
-          <t>$159.1B</t>
-        </is>
-      </c>
-      <c r="E208" t="inlineStr">
-        <is>
-          <t>$159.9B</t>
-        </is>
-      </c>
+          <t>$92B</t>
+        </is>
+      </c>
+      <c r="E208" t="inlineStr"/>
       <c r="F208" t="inlineStr"/>
       <c r="G208" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="209">
@@ -6534,23 +6530,27 @@
       </c>
       <c r="B209" t="inlineStr">
         <is>
-          <t>Overall Net Capital FlowsNOV</t>
+          <t>Net Long-term TIC FlowsNOV</t>
         </is>
       </c>
       <c r="C209" t="inlineStr">
         <is>
+          <t>$79B</t>
+        </is>
+      </c>
+      <c r="D209" t="inlineStr">
+        <is>
+          <t>$159.1B</t>
+        </is>
+      </c>
+      <c r="E209" t="inlineStr">
+        <is>
           <t>$159.9B</t>
         </is>
       </c>
-      <c r="D209" t="inlineStr">
-        <is>
-          <t>$201.8B</t>
-        </is>
-      </c>
-      <c r="E209" t="inlineStr"/>
       <c r="F209" t="inlineStr"/>
       <c r="G209" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="210">
@@ -6561,17 +6561,17 @@
       </c>
       <c r="B210" t="inlineStr">
         <is>
-          <t>Foreign Bond InvestmentNOV</t>
+          <t>Overall Net Capital FlowsNOV</t>
         </is>
       </c>
       <c r="C210" t="inlineStr">
         <is>
-          <t>$-15.8B</t>
+          <t>$159.9B</t>
         </is>
       </c>
       <c r="D210" t="inlineStr">
         <is>
-          <t>$92B</t>
+          <t>$201.8B</t>
         </is>
       </c>
       <c r="E210" t="inlineStr"/>
@@ -7241,17 +7241,17 @@
       </c>
       <c r="B234" t="inlineStr">
         <is>
-          <t>EIA Heating Oil Stocks ChangeJAN/17</t>
+          <t>EIA Crude Oil Imports ChangeJAN/17</t>
         </is>
       </c>
       <c r="C234" t="inlineStr">
         <is>
-          <t>0.068M</t>
+          <t>0.184M</t>
         </is>
       </c>
       <c r="D234" t="inlineStr">
         <is>
-          <t>0.646M</t>
+          <t>-1.304M</t>
         </is>
       </c>
       <c r="E234" t="inlineStr"/>
@@ -7268,27 +7268,23 @@
       </c>
       <c r="B235" t="inlineStr">
         <is>
-          <t>EIA Crude Oil Stocks ChangeJAN/17</t>
+          <t>EIA Gasoline Production ChangeJAN/17</t>
         </is>
       </c>
       <c r="C235" t="inlineStr">
         <is>
-          <t>-1.017M</t>
+          <t>-0.043M</t>
         </is>
       </c>
       <c r="D235" t="inlineStr">
         <is>
-          <t>-1.962M</t>
-        </is>
-      </c>
-      <c r="E235" t="inlineStr">
-        <is>
-          <t>-2.1M</t>
-        </is>
-      </c>
+          <t>0.397M</t>
+        </is>
+      </c>
+      <c r="E235" t="inlineStr"/>
       <c r="F235" t="inlineStr"/>
       <c r="G235" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="236">
@@ -7299,17 +7295,17 @@
       </c>
       <c r="B236" t="inlineStr">
         <is>
-          <t>15-Year Mortgage RateJAN/23</t>
+          <t>EIA Cushing Crude Oil Stocks ChangeJAN/17</t>
         </is>
       </c>
       <c r="C236" t="inlineStr">
         <is>
-          <t>6.16%</t>
+          <t>-0.148M</t>
         </is>
       </c>
       <c r="D236" t="inlineStr">
         <is>
-          <t>6.27%</t>
+          <t>0.765M</t>
         </is>
       </c>
       <c r="E236" t="inlineStr"/>
@@ -7326,27 +7322,23 @@
       </c>
       <c r="B237" t="inlineStr">
         <is>
-          <t>EIA Gasoline Stocks ChangeJAN/17</t>
+          <t>30-Year Mortgage RateJAN/23</t>
         </is>
       </c>
       <c r="C237" t="inlineStr">
         <is>
-          <t>2.332M</t>
+          <t>6.96%</t>
         </is>
       </c>
       <c r="D237" t="inlineStr">
         <is>
-          <t>5.852M</t>
-        </is>
-      </c>
-      <c r="E237" t="inlineStr">
-        <is>
-          <t>2.5M</t>
-        </is>
-      </c>
+          <t>7.04%</t>
+        </is>
+      </c>
+      <c r="E237" t="inlineStr"/>
       <c r="F237" t="inlineStr"/>
       <c r="G237" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="238">
@@ -7357,17 +7349,17 @@
       </c>
       <c r="B238" t="inlineStr">
         <is>
-          <t>EIA Refinery Crude Runs ChangeJAN/17</t>
+          <t>EIA Distillate Fuel Production ChangeJAN/17</t>
         </is>
       </c>
       <c r="C238" t="inlineStr">
         <is>
-          <t>-1.125M</t>
+          <t>-0.473M</t>
         </is>
       </c>
       <c r="D238" t="inlineStr">
         <is>
-          <t>-0.255M</t>
+          <t>-0.021M</t>
         </is>
       </c>
       <c r="E238" t="inlineStr"/>
@@ -7384,24 +7376,20 @@
       </c>
       <c r="B239" t="inlineStr">
         <is>
-          <t>EIA Distillate Stocks ChangeJAN/17</t>
+          <t>EIA Refinery Crude Runs ChangeJAN/17</t>
         </is>
       </c>
       <c r="C239" t="inlineStr">
         <is>
-          <t>-3.07M</t>
+          <t>-1.125M</t>
         </is>
       </c>
       <c r="D239" t="inlineStr">
         <is>
-          <t>3.077M</t>
-        </is>
-      </c>
-      <c r="E239" t="inlineStr">
-        <is>
-          <t>0.6M</t>
-        </is>
-      </c>
+          <t>-0.255M</t>
+        </is>
+      </c>
+      <c r="E239" t="inlineStr"/>
       <c r="F239" t="inlineStr"/>
       <c r="G239" t="n">
         <v>3</v>
@@ -7415,23 +7403,27 @@
       </c>
       <c r="B240" t="inlineStr">
         <is>
-          <t>EIA Distillate Fuel Production ChangeJAN/17</t>
+          <t>EIA Gasoline Stocks ChangeJAN/17</t>
         </is>
       </c>
       <c r="C240" t="inlineStr">
         <is>
-          <t>-0.473M</t>
+          <t>2.332M</t>
         </is>
       </c>
       <c r="D240" t="inlineStr">
         <is>
-          <t>-0.021M</t>
-        </is>
-      </c>
-      <c r="E240" t="inlineStr"/>
+          <t>5.852M</t>
+        </is>
+      </c>
+      <c r="E240" t="inlineStr">
+        <is>
+          <t>2.5M</t>
+        </is>
+      </c>
       <c r="F240" t="inlineStr"/>
       <c r="G240" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="241">
@@ -7442,17 +7434,17 @@
       </c>
       <c r="B241" t="inlineStr">
         <is>
-          <t>30-Year Mortgage RateJAN/23</t>
+          <t>15-Year Mortgage RateJAN/23</t>
         </is>
       </c>
       <c r="C241" t="inlineStr">
         <is>
-          <t>6.96%</t>
+          <t>6.16%</t>
         </is>
       </c>
       <c r="D241" t="inlineStr">
         <is>
-          <t>7.04%</t>
+          <t>6.27%</t>
         </is>
       </c>
       <c r="E241" t="inlineStr"/>
@@ -7469,23 +7461,27 @@
       </c>
       <c r="B242" t="inlineStr">
         <is>
-          <t>EIA Cushing Crude Oil Stocks ChangeJAN/17</t>
+          <t>EIA Crude Oil Stocks ChangeJAN/17</t>
         </is>
       </c>
       <c r="C242" t="inlineStr">
         <is>
-          <t>-0.148M</t>
+          <t>-1.017M</t>
         </is>
       </c>
       <c r="D242" t="inlineStr">
         <is>
-          <t>0.765M</t>
-        </is>
-      </c>
-      <c r="E242" t="inlineStr"/>
+          <t>-1.962M</t>
+        </is>
+      </c>
+      <c r="E242" t="inlineStr">
+        <is>
+          <t>-2.1M</t>
+        </is>
+      </c>
       <c r="F242" t="inlineStr"/>
       <c r="G242" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="243">
@@ -7496,17 +7492,17 @@
       </c>
       <c r="B243" t="inlineStr">
         <is>
-          <t>EIA Gasoline Production ChangeJAN/17</t>
+          <t>EIA Heating Oil Stocks ChangeJAN/17</t>
         </is>
       </c>
       <c r="C243" t="inlineStr">
         <is>
-          <t>-0.043M</t>
+          <t>0.068M</t>
         </is>
       </c>
       <c r="D243" t="inlineStr">
         <is>
-          <t>0.397M</t>
+          <t>0.646M</t>
         </is>
       </c>
       <c r="E243" t="inlineStr"/>
@@ -7523,20 +7519,24 @@
       </c>
       <c r="B244" t="inlineStr">
         <is>
-          <t>EIA Crude Oil Imports ChangeJAN/17</t>
+          <t>EIA Distillate Stocks ChangeJAN/17</t>
         </is>
       </c>
       <c r="C244" t="inlineStr">
         <is>
-          <t>0.184M</t>
+          <t>-3.07M</t>
         </is>
       </c>
       <c r="D244" t="inlineStr">
         <is>
-          <t>-1.304M</t>
-        </is>
-      </c>
-      <c r="E244" t="inlineStr"/>
+          <t>3.077M</t>
+        </is>
+      </c>
+      <c r="E244" t="inlineStr">
+        <is>
+          <t>0.6M</t>
+        </is>
+      </c>
       <c r="F244" t="inlineStr"/>
       <c r="G244" t="n">
         <v>3</v>
@@ -7705,31 +7705,31 @@
       </c>
       <c r="B250" t="inlineStr">
         <is>
-          <t>Existing Home SalesDEC</t>
+          <t>Michigan Inflation Expectations FinalJAN</t>
         </is>
       </c>
       <c r="C250" t="inlineStr">
         <is>
-          <t>4.24M</t>
+          <t>3.3%</t>
         </is>
       </c>
       <c r="D250" t="inlineStr">
         <is>
-          <t>4.15M</t>
+          <t>2.8%</t>
         </is>
       </c>
       <c r="E250" t="inlineStr">
         <is>
-          <t>4.19M</t>
+          <t>3.3%</t>
         </is>
       </c>
       <c r="F250" t="inlineStr">
         <is>
-          <t>4.1M</t>
+          <t>3.3%</t>
         </is>
       </c>
       <c r="G250" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="251">
@@ -7740,31 +7740,31 @@
       </c>
       <c r="B251" t="inlineStr">
         <is>
-          <t>Michigan Consumer Sentiment FinalJAN</t>
+          <t>Michigan Current Conditions FinalJAN</t>
         </is>
       </c>
       <c r="C251" t="inlineStr">
         <is>
-          <t>71.1</t>
+          <t>74.0</t>
         </is>
       </c>
       <c r="D251" t="inlineStr">
         <is>
-          <t>74.0</t>
+          <t>75.1</t>
         </is>
       </c>
       <c r="E251" t="inlineStr">
         <is>
-          <t>73.2</t>
+          <t>77.9</t>
         </is>
       </c>
       <c r="F251" t="inlineStr">
         <is>
-          <t>73.2</t>
+          <t>77.9</t>
         </is>
       </c>
       <c r="G251" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="252">
@@ -7775,27 +7775,27 @@
       </c>
       <c r="B252" t="inlineStr">
         <is>
-          <t>Michigan Consumer Expectations FinalJAN</t>
+          <t>Michigan 5 Year Inflation Expectations FinalJAN</t>
         </is>
       </c>
       <c r="C252" t="inlineStr">
         <is>
-          <t>69.3</t>
+          <t>3.2%</t>
         </is>
       </c>
       <c r="D252" t="inlineStr">
         <is>
-          <t>73.3</t>
+          <t>3%</t>
         </is>
       </c>
       <c r="E252" t="inlineStr">
         <is>
-          <t>70.2</t>
+          <t>3.3%</t>
         </is>
       </c>
       <c r="F252" t="inlineStr">
         <is>
-          <t>70.2</t>
+          <t>3.3%</t>
         </is>
       </c>
       <c r="G252" t="n">
@@ -7810,27 +7810,31 @@
       </c>
       <c r="B253" t="inlineStr">
         <is>
-          <t>Existing Home Sales MoMDEC</t>
+          <t>Existing Home SalesDEC</t>
         </is>
       </c>
       <c r="C253" t="inlineStr">
         <is>
-          <t>2.2%</t>
+          <t>4.24M</t>
         </is>
       </c>
       <c r="D253" t="inlineStr">
         <is>
-          <t>4.8%</t>
-        </is>
-      </c>
-      <c r="E253" t="inlineStr"/>
+          <t>4.15M</t>
+        </is>
+      </c>
+      <c r="E253" t="inlineStr">
+        <is>
+          <t>4.19M</t>
+        </is>
+      </c>
       <c r="F253" t="inlineStr">
         <is>
-          <t>0.3%</t>
+          <t>4.1M</t>
         </is>
       </c>
       <c r="G253" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="254">
@@ -7841,27 +7845,27 @@
       </c>
       <c r="B254" t="inlineStr">
         <is>
-          <t>Michigan 5 Year Inflation Expectations FinalJAN</t>
+          <t>Michigan Consumer Expectations FinalJAN</t>
         </is>
       </c>
       <c r="C254" t="inlineStr">
         <is>
-          <t>3.2%</t>
+          <t>69.3</t>
         </is>
       </c>
       <c r="D254" t="inlineStr">
         <is>
-          <t>3%</t>
+          <t>73.3</t>
         </is>
       </c>
       <c r="E254" t="inlineStr">
         <is>
-          <t>3.3%</t>
+          <t>70.2</t>
         </is>
       </c>
       <c r="F254" t="inlineStr">
         <is>
-          <t>3.3%</t>
+          <t>70.2</t>
         </is>
       </c>
       <c r="G254" t="n">
@@ -7876,31 +7880,31 @@
       </c>
       <c r="B255" t="inlineStr">
         <is>
-          <t>Michigan Inflation Expectations FinalJAN</t>
+          <t>Michigan Consumer Sentiment FinalJAN</t>
         </is>
       </c>
       <c r="C255" t="inlineStr">
         <is>
-          <t>3.3%</t>
+          <t>71.1</t>
         </is>
       </c>
       <c r="D255" t="inlineStr">
         <is>
-          <t>2.8%</t>
+          <t>74.0</t>
         </is>
       </c>
       <c r="E255" t="inlineStr">
         <is>
-          <t>3.3%</t>
+          <t>73.2</t>
         </is>
       </c>
       <c r="F255" t="inlineStr">
         <is>
-          <t>3.3%</t>
+          <t>73.2</t>
         </is>
       </c>
       <c r="G255" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="256">
@@ -7911,31 +7915,27 @@
       </c>
       <c r="B256" t="inlineStr">
         <is>
-          <t>Michigan Current Conditions FinalJAN</t>
+          <t>Existing Home Sales MoMDEC</t>
         </is>
       </c>
       <c r="C256" t="inlineStr">
         <is>
-          <t>74.0</t>
+          <t>2.2%</t>
         </is>
       </c>
       <c r="D256" t="inlineStr">
         <is>
-          <t>75.1</t>
-        </is>
-      </c>
-      <c r="E256" t="inlineStr">
-        <is>
-          <t>77.9</t>
-        </is>
-      </c>
+          <t>4.8%</t>
+        </is>
+      </c>
+      <c r="E256" t="inlineStr"/>
       <c r="F256" t="inlineStr">
         <is>
-          <t>77.9</t>
+          <t>0.3%</t>
         </is>
       </c>
       <c r="G256" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="257">
@@ -8469,23 +8469,27 @@
       </c>
       <c r="B274" t="inlineStr">
         <is>
-          <t>S&amp;P/Case-Shiller Home Price MoMNOV</t>
+          <t>House Price Index MoMNOV</t>
         </is>
       </c>
       <c r="C274" t="inlineStr">
         <is>
-          <t>-0.1%</t>
+          <t>0.3%</t>
         </is>
       </c>
       <c r="D274" t="inlineStr">
         <is>
-          <t>-0.2%</t>
-        </is>
-      </c>
-      <c r="E274" t="inlineStr"/>
+          <t>0.5%</t>
+        </is>
+      </c>
+      <c r="E274" t="inlineStr">
+        <is>
+          <t>0.2%</t>
+        </is>
+      </c>
       <c r="F274" t="inlineStr">
         <is>
-          <t>-0.1%</t>
+          <t>0.3%</t>
         </is>
       </c>
       <c r="G274" t="n">
@@ -8500,31 +8504,27 @@
       </c>
       <c r="B275" t="inlineStr">
         <is>
-          <t>S&amp;P/Case-Shiller Home Price YoYNOV</t>
+          <t>House Price IndexNOV</t>
         </is>
       </c>
       <c r="C275" t="inlineStr">
         <is>
-          <t>4.3%</t>
+          <t>433.4</t>
         </is>
       </c>
       <c r="D275" t="inlineStr">
         <is>
-          <t>4.2%</t>
-        </is>
-      </c>
-      <c r="E275" t="inlineStr">
-        <is>
-          <t>4.3%</t>
-        </is>
-      </c>
+          <t>432.3</t>
+        </is>
+      </c>
+      <c r="E275" t="inlineStr"/>
       <c r="F275" t="inlineStr">
         <is>
-          <t>4%</t>
+          <t>433</t>
         </is>
       </c>
       <c r="G275" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="276">
@@ -8535,23 +8535,23 @@
       </c>
       <c r="B276" t="inlineStr">
         <is>
-          <t>House Price IndexNOV</t>
+          <t>House Price Index YoYNOV</t>
         </is>
       </c>
       <c r="C276" t="inlineStr">
         <is>
-          <t>433.4</t>
+          <t>4.2%</t>
         </is>
       </c>
       <c r="D276" t="inlineStr">
         <is>
-          <t>432.3</t>
+          <t>4.5%</t>
         </is>
       </c>
       <c r="E276" t="inlineStr"/>
       <c r="F276" t="inlineStr">
         <is>
-          <t>433</t>
+          <t>4.3%</t>
         </is>
       </c>
       <c r="G276" t="n">
@@ -8566,27 +8566,31 @@
       </c>
       <c r="B277" t="inlineStr">
         <is>
-          <t>House Price Index YoYNOV</t>
+          <t>S&amp;P/Case-Shiller Home Price YoYNOV</t>
         </is>
       </c>
       <c r="C277" t="inlineStr">
         <is>
+          <t>4.3%</t>
+        </is>
+      </c>
+      <c r="D277" t="inlineStr">
+        <is>
           <t>4.2%</t>
         </is>
       </c>
-      <c r="D277" t="inlineStr">
-        <is>
-          <t>4.5%</t>
-        </is>
-      </c>
-      <c r="E277" t="inlineStr"/>
+      <c r="E277" t="inlineStr">
+        <is>
+          <t>4.3%</t>
+        </is>
+      </c>
       <c r="F277" t="inlineStr">
         <is>
-          <t>4.3%</t>
+          <t>4%</t>
         </is>
       </c>
       <c r="G277" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="278">
@@ -8597,27 +8601,23 @@
       </c>
       <c r="B278" t="inlineStr">
         <is>
-          <t>House Price Index MoMNOV</t>
+          <t>S&amp;P/Case-Shiller Home Price MoMNOV</t>
         </is>
       </c>
       <c r="C278" t="inlineStr">
         <is>
-          <t>0.3%</t>
+          <t>-0.1%</t>
         </is>
       </c>
       <c r="D278" t="inlineStr">
         <is>
-          <t>0.5%</t>
-        </is>
-      </c>
-      <c r="E278" t="inlineStr">
-        <is>
-          <t>0.2%</t>
-        </is>
-      </c>
+          <t>-0.2%</t>
+        </is>
+      </c>
+      <c r="E278" t="inlineStr"/>
       <c r="F278" t="inlineStr">
         <is>
-          <t>0.3%</t>
+          <t>-0.1%</t>
         </is>
       </c>
       <c r="G278" t="n">
@@ -9201,17 +9201,17 @@
       </c>
       <c r="B298" t="inlineStr">
         <is>
-          <t>EIA Cushing Crude Oil Stocks ChangeJAN/24</t>
+          <t>EIA Gasoline Production ChangeJAN/24</t>
         </is>
       </c>
       <c r="C298" t="inlineStr">
         <is>
-          <t>0.326M</t>
+          <t>-0.044M</t>
         </is>
       </c>
       <c r="D298" t="inlineStr">
         <is>
-          <t>-0.148M</t>
+          <t>-0.043M</t>
         </is>
       </c>
       <c r="E298" t="inlineStr"/>
@@ -9228,27 +9228,23 @@
       </c>
       <c r="B299" t="inlineStr">
         <is>
-          <t>EIA Crude Oil Stocks ChangeJAN/24</t>
+          <t>EIA Crude Oil Imports ChangeJAN/24</t>
         </is>
       </c>
       <c r="C299" t="inlineStr">
         <is>
-          <t>3.463M</t>
+          <t>0.532M</t>
         </is>
       </c>
       <c r="D299" t="inlineStr">
         <is>
-          <t>-1.017M</t>
-        </is>
-      </c>
-      <c r="E299" t="inlineStr">
-        <is>
-          <t>3.2M</t>
-        </is>
-      </c>
+          <t>0.184M</t>
+        </is>
+      </c>
+      <c r="E299" t="inlineStr"/>
       <c r="F299" t="inlineStr"/>
       <c r="G299" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="300">
@@ -9259,24 +9255,20 @@
       </c>
       <c r="B300" t="inlineStr">
         <is>
-          <t>EIA Distillate Stocks ChangeJAN/24</t>
+          <t>EIA Distillate Fuel Production ChangeJAN/24</t>
         </is>
       </c>
       <c r="C300" t="inlineStr">
         <is>
-          <t>-4.994M</t>
+          <t>0.028M</t>
         </is>
       </c>
       <c r="D300" t="inlineStr">
         <is>
-          <t>-3.07M</t>
-        </is>
-      </c>
-      <c r="E300" t="inlineStr">
-        <is>
-          <t>-2.1M</t>
-        </is>
-      </c>
+          <t>-0.473M</t>
+        </is>
+      </c>
+      <c r="E300" t="inlineStr"/>
       <c r="F300" t="inlineStr"/>
       <c r="G300" t="n">
         <v>3</v>
@@ -9290,23 +9282,27 @@
       </c>
       <c r="B301" t="inlineStr">
         <is>
-          <t>EIA Heating Oil Stocks ChangeJAN/24</t>
+          <t>EIA Gasoline Stocks ChangeJAN/24</t>
         </is>
       </c>
       <c r="C301" t="inlineStr">
         <is>
-          <t>0.128M</t>
+          <t>2.957M</t>
         </is>
       </c>
       <c r="D301" t="inlineStr">
         <is>
-          <t>0.068M</t>
-        </is>
-      </c>
-      <c r="E301" t="inlineStr"/>
+          <t>2.332M</t>
+        </is>
+      </c>
+      <c r="E301" t="inlineStr">
+        <is>
+          <t>1.5M</t>
+        </is>
+      </c>
       <c r="F301" t="inlineStr"/>
       <c r="G301" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="302">
@@ -9344,27 +9340,23 @@
       </c>
       <c r="B303" t="inlineStr">
         <is>
-          <t>EIA Gasoline Stocks ChangeJAN/24</t>
+          <t>EIA Heating Oil Stocks ChangeJAN/24</t>
         </is>
       </c>
       <c r="C303" t="inlineStr">
         <is>
-          <t>2.957M</t>
+          <t>0.128M</t>
         </is>
       </c>
       <c r="D303" t="inlineStr">
         <is>
-          <t>2.332M</t>
-        </is>
-      </c>
-      <c r="E303" t="inlineStr">
-        <is>
-          <t>1.5M</t>
-        </is>
-      </c>
+          <t>0.068M</t>
+        </is>
+      </c>
+      <c r="E303" t="inlineStr"/>
       <c r="F303" t="inlineStr"/>
       <c r="G303" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="304">
@@ -9375,20 +9367,24 @@
       </c>
       <c r="B304" t="inlineStr">
         <is>
-          <t>EIA Distillate Fuel Production ChangeJAN/24</t>
+          <t>EIA Distillate Stocks ChangeJAN/24</t>
         </is>
       </c>
       <c r="C304" t="inlineStr">
         <is>
-          <t>0.028M</t>
+          <t>-4.994M</t>
         </is>
       </c>
       <c r="D304" t="inlineStr">
         <is>
-          <t>-0.473M</t>
-        </is>
-      </c>
-      <c r="E304" t="inlineStr"/>
+          <t>-3.07M</t>
+        </is>
+      </c>
+      <c r="E304" t="inlineStr">
+        <is>
+          <t>-2.1M</t>
+        </is>
+      </c>
       <c r="F304" t="inlineStr"/>
       <c r="G304" t="n">
         <v>3</v>
@@ -9402,23 +9398,27 @@
       </c>
       <c r="B305" t="inlineStr">
         <is>
-          <t>EIA Crude Oil Imports ChangeJAN/24</t>
+          <t>EIA Crude Oil Stocks ChangeJAN/24</t>
         </is>
       </c>
       <c r="C305" t="inlineStr">
         <is>
-          <t>0.532M</t>
+          <t>3.463M</t>
         </is>
       </c>
       <c r="D305" t="inlineStr">
         <is>
-          <t>0.184M</t>
-        </is>
-      </c>
-      <c r="E305" t="inlineStr"/>
+          <t>-1.017M</t>
+        </is>
+      </c>
+      <c r="E305" t="inlineStr">
+        <is>
+          <t>3.2M</t>
+        </is>
+      </c>
       <c r="F305" t="inlineStr"/>
       <c r="G305" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="306">
@@ -9429,17 +9429,17 @@
       </c>
       <c r="B306" t="inlineStr">
         <is>
-          <t>EIA Gasoline Production ChangeJAN/24</t>
+          <t>EIA Cushing Crude Oil Stocks ChangeJAN/24</t>
         </is>
       </c>
       <c r="C306" t="inlineStr">
         <is>
-          <t>-0.044M</t>
+          <t>0.326M</t>
         </is>
       </c>
       <c r="D306" t="inlineStr">
         <is>
-          <t>-0.043M</t>
+          <t>-0.148M</t>
         </is>
       </c>
       <c r="E306" t="inlineStr"/>
@@ -9537,27 +9537,31 @@
       </c>
       <c r="B310" t="inlineStr">
         <is>
-          <t>GDP Sales QoQ AdvQ4</t>
+          <t>GDP Price Index QoQ AdvQ4</t>
         </is>
       </c>
       <c r="C310" t="inlineStr">
         <is>
-          <t>3.2%</t>
+          <t>2.2%</t>
         </is>
       </c>
       <c r="D310" t="inlineStr">
         <is>
-          <t>3.3%</t>
-        </is>
-      </c>
-      <c r="E310" t="inlineStr"/>
+          <t>1.9%</t>
+        </is>
+      </c>
+      <c r="E310" t="inlineStr">
+        <is>
+          <t>2.5%</t>
+        </is>
+      </c>
       <c r="F310" t="inlineStr">
         <is>
-          <t>2.9%</t>
+          <t>2.3%</t>
         </is>
       </c>
       <c r="G310" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="311">
@@ -9568,23 +9572,27 @@
       </c>
       <c r="B311" t="inlineStr">
         <is>
-          <t>Jobless Claims 4-week AverageJAN/25</t>
+          <t>Core PCE Prices QoQ AdvQ4</t>
         </is>
       </c>
       <c r="C311" t="inlineStr">
         <is>
-          <t>212.5K</t>
+          <t>2.5%</t>
         </is>
       </c>
       <c r="D311" t="inlineStr">
         <is>
-          <t>213.5K</t>
-        </is>
-      </c>
-      <c r="E311" t="inlineStr"/>
+          <t>2.2%</t>
+        </is>
+      </c>
+      <c r="E311" t="inlineStr">
+        <is>
+          <t>2.5%</t>
+        </is>
+      </c>
       <c r="F311" t="inlineStr">
         <is>
-          <t>214.0K</t>
+          <t>2.3%</t>
         </is>
       </c>
       <c r="G311" t="n">
@@ -9599,27 +9607,23 @@
       </c>
       <c r="B312" t="inlineStr">
         <is>
-          <t>Continuing Jobless ClaimsJAN/18</t>
+          <t>PCE Prices QoQ AdvQ4</t>
         </is>
       </c>
       <c r="C312" t="inlineStr">
         <is>
-          <t>1858K</t>
+          <t>2.3%</t>
         </is>
       </c>
       <c r="D312" t="inlineStr">
         <is>
-          <t>1900K</t>
-        </is>
-      </c>
-      <c r="E312" t="inlineStr">
-        <is>
-          <t>1890K</t>
-        </is>
-      </c>
+          <t>1.5%</t>
+        </is>
+      </c>
+      <c r="E312" t="inlineStr"/>
       <c r="F312" t="inlineStr">
         <is>
-          <t>1885.0K</t>
+          <t>1.1%</t>
         </is>
       </c>
       <c r="G312" t="n">
@@ -9634,31 +9638,31 @@
       </c>
       <c r="B313" t="inlineStr">
         <is>
-          <t>Initial Jobless ClaimsJAN/25</t>
+          <t>GDP Growth Rate QoQ AdvQ4</t>
         </is>
       </c>
       <c r="C313" t="inlineStr">
         <is>
-          <t>207K</t>
+          <t>2.3%</t>
         </is>
       </c>
       <c r="D313" t="inlineStr">
         <is>
-          <t>223K</t>
+          <t>3.1%</t>
         </is>
       </c>
       <c r="E313" t="inlineStr">
         <is>
-          <t>220K</t>
+          <t>2.6%</t>
         </is>
       </c>
       <c r="F313" t="inlineStr">
         <is>
-          <t>228.0K</t>
+          <t>3%</t>
         </is>
       </c>
       <c r="G313" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="314">
@@ -9669,31 +9673,27 @@
       </c>
       <c r="B314" t="inlineStr">
         <is>
-          <t>GDP Growth Rate QoQ AdvQ4</t>
+          <t>Real Consumer Spending QoQ AdvQ4</t>
         </is>
       </c>
       <c r="C314" t="inlineStr">
         <is>
-          <t>2.3%</t>
+          <t>4.2%</t>
         </is>
       </c>
       <c r="D314" t="inlineStr">
         <is>
-          <t>3.1%</t>
-        </is>
-      </c>
-      <c r="E314" t="inlineStr">
-        <is>
-          <t>2.6%</t>
-        </is>
-      </c>
+          <t>3.7%</t>
+        </is>
+      </c>
+      <c r="E314" t="inlineStr"/>
       <c r="F314" t="inlineStr">
         <is>
-          <t>3%</t>
+          <t>2.9%</t>
         </is>
       </c>
       <c r="G314" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="315">
@@ -9704,23 +9704,27 @@
       </c>
       <c r="B315" t="inlineStr">
         <is>
-          <t>Real Consumer Spending QoQ AdvQ4</t>
+          <t>Continuing Jobless ClaimsJAN/18</t>
         </is>
       </c>
       <c r="C315" t="inlineStr">
         <is>
-          <t>4.2%</t>
+          <t>1858K</t>
         </is>
       </c>
       <c r="D315" t="inlineStr">
         <is>
-          <t>3.7%</t>
-        </is>
-      </c>
-      <c r="E315" t="inlineStr"/>
+          <t>1900K</t>
+        </is>
+      </c>
+      <c r="E315" t="inlineStr">
+        <is>
+          <t>1890K</t>
+        </is>
+      </c>
       <c r="F315" t="inlineStr">
         <is>
-          <t>2.9%</t>
+          <t>1885.0K</t>
         </is>
       </c>
       <c r="G315" t="n">
@@ -9735,23 +9739,23 @@
       </c>
       <c r="B316" t="inlineStr">
         <is>
-          <t>PCE Prices QoQ AdvQ4</t>
+          <t>Jobless Claims 4-week AverageJAN/25</t>
         </is>
       </c>
       <c r="C316" t="inlineStr">
         <is>
-          <t>2.3%</t>
+          <t>212.5K</t>
         </is>
       </c>
       <c r="D316" t="inlineStr">
         <is>
-          <t>1.5%</t>
+          <t>213.5K</t>
         </is>
       </c>
       <c r="E316" t="inlineStr"/>
       <c r="F316" t="inlineStr">
         <is>
-          <t>1.1%</t>
+          <t>214.0K</t>
         </is>
       </c>
       <c r="G316" t="n">
@@ -9766,27 +9770,23 @@
       </c>
       <c r="B317" t="inlineStr">
         <is>
-          <t>Core PCE Prices QoQ AdvQ4</t>
+          <t>GDP Sales QoQ AdvQ4</t>
         </is>
       </c>
       <c r="C317" t="inlineStr">
         <is>
-          <t>2.5%</t>
+          <t>3.2%</t>
         </is>
       </c>
       <c r="D317" t="inlineStr">
         <is>
-          <t>2.2%</t>
-        </is>
-      </c>
-      <c r="E317" t="inlineStr">
-        <is>
-          <t>2.5%</t>
-        </is>
-      </c>
+          <t>3.3%</t>
+        </is>
+      </c>
+      <c r="E317" t="inlineStr"/>
       <c r="F317" t="inlineStr">
         <is>
-          <t>2.3%</t>
+          <t>2.9%</t>
         </is>
       </c>
       <c r="G317" t="n">
@@ -9801,27 +9801,27 @@
       </c>
       <c r="B318" t="inlineStr">
         <is>
-          <t>GDP Price Index QoQ AdvQ4</t>
+          <t>Initial Jobless ClaimsJAN/25</t>
         </is>
       </c>
       <c r="C318" t="inlineStr">
         <is>
-          <t>2.2%</t>
+          <t>207K</t>
         </is>
       </c>
       <c r="D318" t="inlineStr">
         <is>
-          <t>1.9%</t>
+          <t>223K</t>
         </is>
       </c>
       <c r="E318" t="inlineStr">
         <is>
-          <t>2.5%</t>
+          <t>220K</t>
         </is>
       </c>
       <c r="F318" t="inlineStr">
         <is>
-          <t>2.3%</t>
+          <t>228.0K</t>
         </is>
       </c>
       <c r="G318" t="n">
@@ -10068,12 +10068,12 @@
       </c>
       <c r="B327" t="inlineStr">
         <is>
-          <t>PCE Price Index MoMDEC</t>
+          <t>Core PCE Price Index MoMDEC</t>
         </is>
       </c>
       <c r="C327" t="inlineStr">
         <is>
-          <t>0.3%</t>
+          <t>0.2%</t>
         </is>
       </c>
       <c r="D327" t="inlineStr">
@@ -10083,16 +10083,16 @@
       </c>
       <c r="E327" t="inlineStr">
         <is>
-          <t>0.3%</t>
+          <t>0.2%</t>
         </is>
       </c>
       <c r="F327" t="inlineStr">
         <is>
-          <t>0.3%</t>
+          <t>0.2%</t>
         </is>
       </c>
       <c r="G327" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="328">
@@ -10103,31 +10103,31 @@
       </c>
       <c r="B328" t="inlineStr">
         <is>
-          <t>Core PCE Price Index YoYDEC</t>
+          <t>Personal Spending MoMDEC</t>
         </is>
       </c>
       <c r="C328" t="inlineStr">
         <is>
-          <t>2.8%</t>
+          <t>0.7%</t>
         </is>
       </c>
       <c r="D328" t="inlineStr">
         <is>
-          <t>2.8%</t>
+          <t>0.6%</t>
         </is>
       </c>
       <c r="E328" t="inlineStr">
         <is>
-          <t>2.8%</t>
+          <t>0.5%</t>
         </is>
       </c>
       <c r="F328" t="inlineStr">
         <is>
-          <t>2.8%</t>
+          <t>0.5%</t>
         </is>
       </c>
       <c r="G328" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="329">
@@ -10138,12 +10138,12 @@
       </c>
       <c r="B329" t="inlineStr">
         <is>
-          <t>Employment Cost Index QoQQ4</t>
+          <t>Employment Cost - Benefits QoQQ4</t>
         </is>
       </c>
       <c r="C329" t="inlineStr">
         <is>
-          <t>0.9%</t>
+          <t>0.8%</t>
         </is>
       </c>
       <c r="D329" t="inlineStr">
@@ -10151,11 +10151,7 @@
           <t>0.8%</t>
         </is>
       </c>
-      <c r="E329" t="inlineStr">
-        <is>
-          <t>0.9%</t>
-        </is>
-      </c>
+      <c r="E329" t="inlineStr"/>
       <c r="F329" t="inlineStr">
         <is>
           <t>0.7%</t>
@@ -10173,29 +10169,13 @@
       </c>
       <c r="B330" t="inlineStr">
         <is>
-          <t>PCE Price Index YoYDEC</t>
-        </is>
-      </c>
-      <c r="C330" t="inlineStr">
-        <is>
-          <t>2.6%</t>
-        </is>
-      </c>
-      <c r="D330" t="inlineStr">
-        <is>
-          <t>2.4%</t>
-        </is>
-      </c>
-      <c r="E330" t="inlineStr">
-        <is>
-          <t>2.6%</t>
-        </is>
-      </c>
-      <c r="F330" t="inlineStr">
-        <is>
-          <t>2.6%</t>
-        </is>
-      </c>
+          <t>Fed Bowman Speech</t>
+        </is>
+      </c>
+      <c r="C330" t="inlineStr"/>
+      <c r="D330" t="inlineStr"/>
+      <c r="E330" t="inlineStr"/>
+      <c r="F330" t="inlineStr"/>
       <c r="G330" t="n">
         <v>2</v>
       </c>
@@ -10208,27 +10188,31 @@
       </c>
       <c r="B331" t="inlineStr">
         <is>
-          <t>Employment Cost - Wages QoQQ4</t>
+          <t>Personal Income MoMDEC</t>
         </is>
       </c>
       <c r="C331" t="inlineStr">
         <is>
-          <t>0.9%</t>
+          <t>0.4%</t>
         </is>
       </c>
       <c r="D331" t="inlineStr">
         <is>
-          <t>0.8%</t>
-        </is>
-      </c>
-      <c r="E331" t="inlineStr"/>
+          <t>0.3%</t>
+        </is>
+      </c>
+      <c r="E331" t="inlineStr">
+        <is>
+          <t>0.4%</t>
+        </is>
+      </c>
       <c r="F331" t="inlineStr">
         <is>
-          <t>0.7%</t>
+          <t>0.3%</t>
         </is>
       </c>
       <c r="G331" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="332">
@@ -10239,13 +10223,29 @@
       </c>
       <c r="B332" t="inlineStr">
         <is>
-          <t>Fed Bowman Speech</t>
-        </is>
-      </c>
-      <c r="C332" t="inlineStr"/>
-      <c r="D332" t="inlineStr"/>
-      <c r="E332" t="inlineStr"/>
-      <c r="F332" t="inlineStr"/>
+          <t>PCE Price Index YoYDEC</t>
+        </is>
+      </c>
+      <c r="C332" t="inlineStr">
+        <is>
+          <t>2.6%</t>
+        </is>
+      </c>
+      <c r="D332" t="inlineStr">
+        <is>
+          <t>2.4%</t>
+        </is>
+      </c>
+      <c r="E332" t="inlineStr">
+        <is>
+          <t>2.6%</t>
+        </is>
+      </c>
+      <c r="F332" t="inlineStr">
+        <is>
+          <t>2.6%</t>
+        </is>
+      </c>
       <c r="G332" t="n">
         <v>2</v>
       </c>
@@ -10258,31 +10258,31 @@
       </c>
       <c r="B333" t="inlineStr">
         <is>
-          <t>Personal Spending MoMDEC</t>
+          <t>Employment Cost Index QoQQ4</t>
         </is>
       </c>
       <c r="C333" t="inlineStr">
         <is>
+          <t>0.9%</t>
+        </is>
+      </c>
+      <c r="D333" t="inlineStr">
+        <is>
+          <t>0.8%</t>
+        </is>
+      </c>
+      <c r="E333" t="inlineStr">
+        <is>
+          <t>0.9%</t>
+        </is>
+      </c>
+      <c r="F333" t="inlineStr">
+        <is>
           <t>0.7%</t>
         </is>
       </c>
-      <c r="D333" t="inlineStr">
-        <is>
-          <t>0.6%</t>
-        </is>
-      </c>
-      <c r="E333" t="inlineStr">
-        <is>
-          <t>0.5%</t>
-        </is>
-      </c>
-      <c r="F333" t="inlineStr">
-        <is>
-          <t>0.5%</t>
-        </is>
-      </c>
       <c r="G333" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="334">
@@ -10293,31 +10293,31 @@
       </c>
       <c r="B334" t="inlineStr">
         <is>
-          <t>Core PCE Price Index MoMDEC</t>
+          <t>Core PCE Price Index YoYDEC</t>
         </is>
       </c>
       <c r="C334" t="inlineStr">
         <is>
-          <t>0.2%</t>
+          <t>2.8%</t>
         </is>
       </c>
       <c r="D334" t="inlineStr">
         <is>
-          <t>0.1%</t>
+          <t>2.8%</t>
         </is>
       </c>
       <c r="E334" t="inlineStr">
         <is>
-          <t>0.2%</t>
+          <t>2.8%</t>
         </is>
       </c>
       <c r="F334" t="inlineStr">
         <is>
-          <t>0.2%</t>
+          <t>2.8%</t>
         </is>
       </c>
       <c r="G334" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="335">
@@ -10328,23 +10328,27 @@
       </c>
       <c r="B335" t="inlineStr">
         <is>
-          <t>Employment Cost - Benefits QoQQ4</t>
+          <t>PCE Price Index MoMDEC</t>
         </is>
       </c>
       <c r="C335" t="inlineStr">
         <is>
-          <t>0.8%</t>
+          <t>0.3%</t>
         </is>
       </c>
       <c r="D335" t="inlineStr">
         <is>
-          <t>0.8%</t>
-        </is>
-      </c>
-      <c r="E335" t="inlineStr"/>
+          <t>0.1%</t>
+        </is>
+      </c>
+      <c r="E335" t="inlineStr">
+        <is>
+          <t>0.3%</t>
+        </is>
+      </c>
       <c r="F335" t="inlineStr">
         <is>
-          <t>0.7%</t>
+          <t>0.3%</t>
         </is>
       </c>
       <c r="G335" t="n">
@@ -10359,31 +10363,27 @@
       </c>
       <c r="B336" t="inlineStr">
         <is>
-          <t>Personal Income MoMDEC</t>
+          <t>Employment Cost - Wages QoQQ4</t>
         </is>
       </c>
       <c r="C336" t="inlineStr">
         <is>
-          <t>0.4%</t>
+          <t>0.9%</t>
         </is>
       </c>
       <c r="D336" t="inlineStr">
         <is>
-          <t>0.3%</t>
-        </is>
-      </c>
-      <c r="E336" t="inlineStr">
-        <is>
-          <t>0.4%</t>
-        </is>
-      </c>
+          <t>0.8%</t>
+        </is>
+      </c>
+      <c r="E336" t="inlineStr"/>
       <c r="F336" t="inlineStr">
         <is>
-          <t>0.3%</t>
+          <t>0.7%</t>
         </is>
       </c>
       <c r="G336" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="337">
@@ -10522,23 +10522,27 @@
       </c>
       <c r="B341" t="inlineStr">
         <is>
-          <t>ISM Manufacturing New OrdersJAN</t>
+          <t>ISM Manufacturing PricesJAN</t>
         </is>
       </c>
       <c r="C341" t="inlineStr">
         <is>
-          <t>55.1</t>
+          <t>54.9</t>
         </is>
       </c>
       <c r="D341" t="inlineStr">
         <is>
-          <t>52.1</t>
-        </is>
-      </c>
-      <c r="E341" t="inlineStr"/>
+          <t>52.5</t>
+        </is>
+      </c>
+      <c r="E341" t="inlineStr">
+        <is>
+          <t>52.6</t>
+        </is>
+      </c>
       <c r="F341" t="inlineStr">
         <is>
-          <t>52.8</t>
+          <t>53</t>
         </is>
       </c>
       <c r="G341" t="n">
@@ -10553,27 +10557,31 @@
       </c>
       <c r="B342" t="inlineStr">
         <is>
-          <t>ISM Manufacturing EmploymentJAN</t>
+          <t>Construction Spending MoMDEC</t>
         </is>
       </c>
       <c r="C342" t="inlineStr">
         <is>
-          <t>50.3</t>
+          <t>0.5%</t>
         </is>
       </c>
       <c r="D342" t="inlineStr">
         <is>
-          <t>45.4</t>
-        </is>
-      </c>
-      <c r="E342" t="inlineStr"/>
+          <t>0.2%</t>
+        </is>
+      </c>
+      <c r="E342" t="inlineStr">
+        <is>
+          <t>0.2%</t>
+        </is>
+      </c>
       <c r="F342" t="inlineStr">
         <is>
-          <t>47</t>
+          <t>0.3%</t>
         </is>
       </c>
       <c r="G342" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="343">
@@ -10584,31 +10592,31 @@
       </c>
       <c r="B343" t="inlineStr">
         <is>
-          <t>Construction Spending MoMDEC</t>
+          <t>ISM Manufacturing PMIJAN</t>
         </is>
       </c>
       <c r="C343" t="inlineStr">
         <is>
-          <t>0.5%</t>
+          <t>50.9</t>
         </is>
       </c>
       <c r="D343" t="inlineStr">
         <is>
-          <t>0.2%</t>
+          <t>49.2</t>
         </is>
       </c>
       <c r="E343" t="inlineStr">
         <is>
-          <t>0.2%</t>
+          <t>49.8</t>
         </is>
       </c>
       <c r="F343" t="inlineStr">
         <is>
-          <t>0.3%</t>
+          <t>49.8</t>
         </is>
       </c>
       <c r="G343" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="344">
@@ -10619,31 +10627,27 @@
       </c>
       <c r="B344" t="inlineStr">
         <is>
-          <t>ISM Manufacturing PMIJAN</t>
+          <t>ISM Manufacturing New OrdersJAN</t>
         </is>
       </c>
       <c r="C344" t="inlineStr">
         <is>
-          <t>50.9</t>
+          <t>55.1</t>
         </is>
       </c>
       <c r="D344" t="inlineStr">
         <is>
-          <t>49.2</t>
-        </is>
-      </c>
-      <c r="E344" t="inlineStr">
-        <is>
-          <t>49.8</t>
-        </is>
-      </c>
+          <t>52.1</t>
+        </is>
+      </c>
+      <c r="E344" t="inlineStr"/>
       <c r="F344" t="inlineStr">
         <is>
-          <t>49.8</t>
+          <t>52.8</t>
         </is>
       </c>
       <c r="G344" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="345">
@@ -10654,31 +10658,27 @@
       </c>
       <c r="B345" t="inlineStr">
         <is>
-          <t>ISM Manufacturing PricesJAN</t>
+          <t>ISM Manufacturing EmploymentJAN</t>
         </is>
       </c>
       <c r="C345" t="inlineStr">
         <is>
-          <t>54.9</t>
+          <t>50.3</t>
         </is>
       </c>
       <c r="D345" t="inlineStr">
         <is>
-          <t>52.5</t>
-        </is>
-      </c>
-      <c r="E345" t="inlineStr">
-        <is>
-          <t>52.6</t>
-        </is>
-      </c>
+          <t>45.4</t>
+        </is>
+      </c>
+      <c r="E345" t="inlineStr"/>
       <c r="F345" t="inlineStr">
         <is>
-          <t>53</t>
+          <t>47</t>
         </is>
       </c>
       <c r="G345" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="346">
@@ -10873,31 +10873,27 @@
       </c>
       <c r="B354" t="inlineStr">
         <is>
-          <t>JOLTs Job OpeningsDEC</t>
+          <t>JOLTs Job QuitsDEC</t>
         </is>
       </c>
       <c r="C354" t="inlineStr">
         <is>
-          <t>7.6M</t>
+          <t>3.197M</t>
         </is>
       </c>
       <c r="D354" t="inlineStr">
         <is>
-          <t>8.156M</t>
-        </is>
-      </c>
-      <c r="E354" t="inlineStr">
-        <is>
-          <t>8M</t>
-        </is>
-      </c>
+          <t>3.130M</t>
+        </is>
+      </c>
+      <c r="E354" t="inlineStr"/>
       <c r="F354" t="inlineStr">
         <is>
-          <t>7.8M</t>
+          <t>3.1M</t>
         </is>
       </c>
       <c r="G354" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="355">
@@ -10908,31 +10904,31 @@
       </c>
       <c r="B355" t="inlineStr">
         <is>
-          <t>Factory Orders MoMDEC</t>
+          <t>JOLTs Job OpeningsDEC</t>
         </is>
       </c>
       <c r="C355" t="inlineStr">
         <is>
-          <t>-0.9%</t>
+          <t>7.6M</t>
         </is>
       </c>
       <c r="D355" t="inlineStr">
         <is>
-          <t>-0.8%</t>
+          <t>8.156M</t>
         </is>
       </c>
       <c r="E355" t="inlineStr">
         <is>
-          <t>-0.7%</t>
+          <t>8M</t>
         </is>
       </c>
       <c r="F355" t="inlineStr">
         <is>
-          <t>-0.7%</t>
+          <t>7.8M</t>
         </is>
       </c>
       <c r="G355" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="356">
@@ -10943,27 +10939,31 @@
       </c>
       <c r="B356" t="inlineStr">
         <is>
-          <t>JOLTs Job QuitsDEC</t>
+          <t>Factory Orders MoMDEC</t>
         </is>
       </c>
       <c r="C356" t="inlineStr">
         <is>
-          <t>3.197M</t>
+          <t>-0.9%</t>
         </is>
       </c>
       <c r="D356" t="inlineStr">
         <is>
-          <t>3.130M</t>
-        </is>
-      </c>
-      <c r="E356" t="inlineStr"/>
+          <t>-0.8%</t>
+        </is>
+      </c>
+      <c r="E356" t="inlineStr">
+        <is>
+          <t>-0.7%</t>
+        </is>
+      </c>
       <c r="F356" t="inlineStr">
         <is>
-          <t>3.1M</t>
+          <t>-0.7%</t>
         </is>
       </c>
       <c r="G356" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="357">
@@ -11325,15 +11325,27 @@
       </c>
       <c r="B370" t="inlineStr">
         <is>
-          <t>Treasury Refunding Announcement</t>
-        </is>
-      </c>
-      <c r="C370" t="inlineStr"/>
-      <c r="D370" t="inlineStr"/>
+          <t>ImportsDEC</t>
+        </is>
+      </c>
+      <c r="C370" t="inlineStr">
+        <is>
+          <t>$364.9B</t>
+        </is>
+      </c>
+      <c r="D370" t="inlineStr">
+        <is>
+          <t>$352.5B</t>
+        </is>
+      </c>
       <c r="E370" t="inlineStr"/>
-      <c r="F370" t="inlineStr"/>
+      <c r="F370" t="inlineStr">
+        <is>
+          <t>$ 355.0B</t>
+        </is>
+      </c>
       <c r="G370" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="371">
@@ -11344,27 +11356,23 @@
       </c>
       <c r="B371" t="inlineStr">
         <is>
-          <t>Balance of TradeDEC</t>
+          <t>ExportsDEC</t>
         </is>
       </c>
       <c r="C371" t="inlineStr">
         <is>
-          <t>$-98.4B</t>
+          <t>$266.5B</t>
         </is>
       </c>
       <c r="D371" t="inlineStr">
         <is>
-          <t>$-78.9B</t>
-        </is>
-      </c>
-      <c r="E371" t="inlineStr">
-        <is>
-          <t>$-96.6B</t>
-        </is>
-      </c>
+          <t>$273.6B</t>
+        </is>
+      </c>
+      <c r="E371" t="inlineStr"/>
       <c r="F371" t="inlineStr">
         <is>
-          <t>$ -93.0B</t>
+          <t>$ 262B</t>
         </is>
       </c>
       <c r="G371" t="n">
@@ -11379,27 +11387,15 @@
       </c>
       <c r="B372" t="inlineStr">
         <is>
-          <t>ExportsDEC</t>
-        </is>
-      </c>
-      <c r="C372" t="inlineStr">
-        <is>
-          <t>$266.5B</t>
-        </is>
-      </c>
-      <c r="D372" t="inlineStr">
-        <is>
-          <t>$273.6B</t>
-        </is>
-      </c>
+          <t>Treasury Refunding Announcement</t>
+        </is>
+      </c>
+      <c r="C372" t="inlineStr"/>
+      <c r="D372" t="inlineStr"/>
       <c r="E372" t="inlineStr"/>
-      <c r="F372" t="inlineStr">
-        <is>
-          <t>$ 262B</t>
-        </is>
-      </c>
+      <c r="F372" t="inlineStr"/>
       <c r="G372" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="373">
@@ -11410,23 +11406,27 @@
       </c>
       <c r="B373" t="inlineStr">
         <is>
-          <t>ImportsDEC</t>
+          <t>Balance of TradeDEC</t>
         </is>
       </c>
       <c r="C373" t="inlineStr">
         <is>
-          <t>$364.9B</t>
+          <t>$-98.4B</t>
         </is>
       </c>
       <c r="D373" t="inlineStr">
         <is>
-          <t>$352.5B</t>
-        </is>
-      </c>
-      <c r="E373" t="inlineStr"/>
+          <t>$-78.9B</t>
+        </is>
+      </c>
+      <c r="E373" t="inlineStr">
+        <is>
+          <t>$-96.6B</t>
+        </is>
+      </c>
       <c r="F373" t="inlineStr">
         <is>
-          <t>$ 355.0B</t>
+          <t>$ -93.0B</t>
         </is>
       </c>
       <c r="G373" t="n">
@@ -11689,27 +11689,23 @@
       </c>
       <c r="B382" t="inlineStr">
         <is>
-          <t>EIA Crude Oil Stocks ChangeJAN/31</t>
+          <t>EIA Cushing Crude Oil Stocks ChangeJAN/31</t>
         </is>
       </c>
       <c r="C382" t="inlineStr">
         <is>
-          <t>8.664M</t>
+          <t>-0.034M</t>
         </is>
       </c>
       <c r="D382" t="inlineStr">
         <is>
-          <t>3.463M</t>
-        </is>
-      </c>
-      <c r="E382" t="inlineStr">
-        <is>
-          <t>2.6M</t>
-        </is>
-      </c>
+          <t>0.326M</t>
+        </is>
+      </c>
+      <c r="E382" t="inlineStr"/>
       <c r="F382" t="inlineStr"/>
       <c r="G382" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="383">
@@ -11720,17 +11716,17 @@
       </c>
       <c r="B383" t="inlineStr">
         <is>
-          <t>EIA Distillate Fuel Production ChangeJAN/31</t>
+          <t>EIA Gasoline Production ChangeJAN/31</t>
         </is>
       </c>
       <c r="C383" t="inlineStr">
         <is>
-          <t>-0.186M</t>
+          <t>-0.027M</t>
         </is>
       </c>
       <c r="D383" t="inlineStr">
         <is>
-          <t>0.028M</t>
+          <t>-0.044M</t>
         </is>
       </c>
       <c r="E383" t="inlineStr"/>
@@ -11747,17 +11743,17 @@
       </c>
       <c r="B384" t="inlineStr">
         <is>
-          <t>EIA Refinery Crude Runs ChangeJAN/31</t>
+          <t>EIA Crude Oil Imports ChangeJAN/31</t>
         </is>
       </c>
       <c r="C384" t="inlineStr">
         <is>
-          <t>0.16M</t>
+          <t>-0.178M</t>
         </is>
       </c>
       <c r="D384" t="inlineStr">
         <is>
-          <t>-0.333M</t>
+          <t>0.532M</t>
         </is>
       </c>
       <c r="E384" t="inlineStr"/>
@@ -11774,24 +11770,20 @@
       </c>
       <c r="B385" t="inlineStr">
         <is>
-          <t>EIA Distillate Stocks ChangeJAN/31</t>
+          <t>EIA Heating Oil Stocks ChangeJAN/31</t>
         </is>
       </c>
       <c r="C385" t="inlineStr">
         <is>
-          <t>-5.471M</t>
+          <t>0.373M</t>
         </is>
       </c>
       <c r="D385" t="inlineStr">
         <is>
-          <t>-4.994M</t>
-        </is>
-      </c>
-      <c r="E385" t="inlineStr">
-        <is>
-          <t>-1.5M</t>
-        </is>
-      </c>
+          <t>0.128M</t>
+        </is>
+      </c>
+      <c r="E385" t="inlineStr"/>
       <c r="F385" t="inlineStr"/>
       <c r="G385" t="n">
         <v>3</v>
@@ -11805,23 +11797,27 @@
       </c>
       <c r="B386" t="inlineStr">
         <is>
-          <t>EIA Heating Oil Stocks ChangeJAN/31</t>
+          <t>EIA Gasoline Stocks ChangeJAN/31</t>
         </is>
       </c>
       <c r="C386" t="inlineStr">
         <is>
-          <t>0.373M</t>
+          <t>2.233M</t>
         </is>
       </c>
       <c r="D386" t="inlineStr">
         <is>
-          <t>0.128M</t>
-        </is>
-      </c>
-      <c r="E386" t="inlineStr"/>
+          <t>2.957M</t>
+        </is>
+      </c>
+      <c r="E386" t="inlineStr">
+        <is>
+          <t>1.2M</t>
+        </is>
+      </c>
       <c r="F386" t="inlineStr"/>
       <c r="G386" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="387">
@@ -11832,17 +11828,17 @@
       </c>
       <c r="B387" t="inlineStr">
         <is>
-          <t>EIA Cushing Crude Oil Stocks ChangeJAN/31</t>
+          <t>EIA Refinery Crude Runs ChangeJAN/31</t>
         </is>
       </c>
       <c r="C387" t="inlineStr">
         <is>
-          <t>-0.034M</t>
+          <t>0.16M</t>
         </is>
       </c>
       <c r="D387" t="inlineStr">
         <is>
-          <t>0.326M</t>
+          <t>-0.333M</t>
         </is>
       </c>
       <c r="E387" t="inlineStr"/>
@@ -11859,17 +11855,17 @@
       </c>
       <c r="B388" t="inlineStr">
         <is>
-          <t>EIA Crude Oil Imports ChangeJAN/31</t>
+          <t>EIA Distillate Fuel Production ChangeJAN/31</t>
         </is>
       </c>
       <c r="C388" t="inlineStr">
         <is>
-          <t>-0.178M</t>
+          <t>-0.186M</t>
         </is>
       </c>
       <c r="D388" t="inlineStr">
         <is>
-          <t>0.532M</t>
+          <t>0.028M</t>
         </is>
       </c>
       <c r="E388" t="inlineStr"/>
@@ -11886,22 +11882,22 @@
       </c>
       <c r="B389" t="inlineStr">
         <is>
-          <t>EIA Gasoline Stocks ChangeJAN/31</t>
+          <t>EIA Crude Oil Stocks ChangeJAN/31</t>
         </is>
       </c>
       <c r="C389" t="inlineStr">
         <is>
-          <t>2.233M</t>
+          <t>8.664M</t>
         </is>
       </c>
       <c r="D389" t="inlineStr">
         <is>
-          <t>2.957M</t>
+          <t>3.463M</t>
         </is>
       </c>
       <c r="E389" t="inlineStr">
         <is>
-          <t>1.2M</t>
+          <t>2.6M</t>
         </is>
       </c>
       <c r="F389" t="inlineStr"/>
@@ -11917,20 +11913,24 @@
       </c>
       <c r="B390" t="inlineStr">
         <is>
-          <t>EIA Gasoline Production ChangeJAN/31</t>
+          <t>EIA Distillate Stocks ChangeJAN/31</t>
         </is>
       </c>
       <c r="C390" t="inlineStr">
         <is>
-          <t>-0.027M</t>
+          <t>-5.471M</t>
         </is>
       </c>
       <c r="D390" t="inlineStr">
         <is>
-          <t>-0.044M</t>
-        </is>
-      </c>
-      <c r="E390" t="inlineStr"/>
+          <t>-4.994M</t>
+        </is>
+      </c>
+      <c r="E390" t="inlineStr">
+        <is>
+          <t>-1.5M</t>
+        </is>
+      </c>
       <c r="F390" t="inlineStr"/>
       <c r="G390" t="n">
         <v>3</v>
@@ -12040,31 +12040,31 @@
       </c>
       <c r="B395" t="inlineStr">
         <is>
-          <t>Continuing Jobless ClaimsJAN/25</t>
+          <t>Unit Labour Costs QoQ PrelQ4</t>
         </is>
       </c>
       <c r="C395" t="inlineStr">
         <is>
-          <t>1886K</t>
+          <t>3%</t>
         </is>
       </c>
       <c r="D395" t="inlineStr">
         <is>
-          <t>1850K</t>
+          <t>0.5%</t>
         </is>
       </c>
       <c r="E395" t="inlineStr">
         <is>
-          <t>1870K</t>
+          <t>3.4%</t>
         </is>
       </c>
       <c r="F395" t="inlineStr">
         <is>
-          <t>1855.0K</t>
+          <t>3%</t>
         </is>
       </c>
       <c r="G395" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="396">
@@ -12075,31 +12075,27 @@
       </c>
       <c r="B396" t="inlineStr">
         <is>
-          <t>Nonfarm Productivity QoQ PrelQ4</t>
+          <t>Jobless Claims 4-week AverageFEB/01</t>
         </is>
       </c>
       <c r="C396" t="inlineStr">
         <is>
-          <t>1.2%</t>
+          <t>216.75K</t>
         </is>
       </c>
       <c r="D396" t="inlineStr">
         <is>
-          <t>2.3%</t>
-        </is>
-      </c>
-      <c r="E396" t="inlineStr">
-        <is>
-          <t>1.4%</t>
-        </is>
-      </c>
+          <t>212.75K</t>
+        </is>
+      </c>
+      <c r="E396" t="inlineStr"/>
       <c r="F396" t="inlineStr">
         <is>
-          <t>1.9%</t>
+          <t>215.5K</t>
         </is>
       </c>
       <c r="G396" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="397">
@@ -12110,27 +12106,31 @@
       </c>
       <c r="B397" t="inlineStr">
         <is>
-          <t>Jobless Claims 4-week AverageFEB/01</t>
+          <t>Initial Jobless ClaimsFEB/01</t>
         </is>
       </c>
       <c r="C397" t="inlineStr">
         <is>
-          <t>216.75K</t>
+          <t>219K</t>
         </is>
       </c>
       <c r="D397" t="inlineStr">
         <is>
-          <t>212.75K</t>
-        </is>
-      </c>
-      <c r="E397" t="inlineStr"/>
+          <t>208K</t>
+        </is>
+      </c>
+      <c r="E397" t="inlineStr">
+        <is>
+          <t>213K</t>
+        </is>
+      </c>
       <c r="F397" t="inlineStr">
         <is>
-          <t>215.5K</t>
+          <t>215.0K</t>
         </is>
       </c>
       <c r="G397" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="398">
@@ -12141,31 +12141,31 @@
       </c>
       <c r="B398" t="inlineStr">
         <is>
-          <t>Unit Labour Costs QoQ PrelQ4</t>
+          <t>Continuing Jobless ClaimsJAN/25</t>
         </is>
       </c>
       <c r="C398" t="inlineStr">
         <is>
-          <t>3%</t>
+          <t>1886K</t>
         </is>
       </c>
       <c r="D398" t="inlineStr">
         <is>
-          <t>0.5%</t>
+          <t>1850K</t>
         </is>
       </c>
       <c r="E398" t="inlineStr">
         <is>
-          <t>3.4%</t>
+          <t>1870K</t>
         </is>
       </c>
       <c r="F398" t="inlineStr">
         <is>
-          <t>3%</t>
+          <t>1855.0K</t>
         </is>
       </c>
       <c r="G398" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="399">
@@ -12176,27 +12176,27 @@
       </c>
       <c r="B399" t="inlineStr">
         <is>
-          <t>Initial Jobless ClaimsFEB/01</t>
+          <t>Nonfarm Productivity QoQ PrelQ4</t>
         </is>
       </c>
       <c r="C399" t="inlineStr">
         <is>
-          <t>219K</t>
+          <t>1.2%</t>
         </is>
       </c>
       <c r="D399" t="inlineStr">
         <is>
-          <t>208K</t>
+          <t>2.3%</t>
         </is>
       </c>
       <c r="E399" t="inlineStr">
         <is>
-          <t>213K</t>
+          <t>1.4%</t>
         </is>
       </c>
       <c r="F399" t="inlineStr">
         <is>
-          <t>215.0K</t>
+          <t>1.9%</t>
         </is>
       </c>
       <c r="G399" t="n">
@@ -12442,27 +12442,31 @@
       </c>
       <c r="B409" t="inlineStr">
         <is>
-          <t>U-6 Unemployment RateJAN</t>
+          <t>Average Hourly Earnings YoYJAN</t>
         </is>
       </c>
       <c r="C409" t="inlineStr">
         <is>
-          <t>7.5%</t>
+          <t>4.1%</t>
         </is>
       </c>
       <c r="D409" t="inlineStr">
         <is>
-          <t>7.5%</t>
-        </is>
-      </c>
-      <c r="E409" t="inlineStr"/>
+          <t>4.1%</t>
+        </is>
+      </c>
+      <c r="E409" t="inlineStr">
+        <is>
+          <t>3.8%</t>
+        </is>
+      </c>
       <c r="F409" t="inlineStr">
         <is>
-          <t>7.5%</t>
+          <t>3.9%</t>
         </is>
       </c>
       <c r="G409" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="410">
@@ -12473,27 +12477,31 @@
       </c>
       <c r="B410" t="inlineStr">
         <is>
-          <t>Government PayrollsJAN</t>
+          <t>Average Hourly Earnings MoMJAN</t>
         </is>
       </c>
       <c r="C410" t="inlineStr">
         <is>
-          <t>32K</t>
+          <t>0.5%</t>
         </is>
       </c>
       <c r="D410" t="inlineStr">
         <is>
-          <t>34K</t>
-        </is>
-      </c>
-      <c r="E410" t="inlineStr"/>
+          <t>0.3%</t>
+        </is>
+      </c>
+      <c r="E410" t="inlineStr">
+        <is>
+          <t>0.3%</t>
+        </is>
+      </c>
       <c r="F410" t="inlineStr">
         <is>
-          <t>25K</t>
+          <t>0.3%</t>
         </is>
       </c>
       <c r="G410" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="411">
@@ -12504,31 +12512,31 @@
       </c>
       <c r="B411" t="inlineStr">
         <is>
-          <t>Nonfarm Payrolls PrivateJAN</t>
+          <t>Non Farm PayrollsJAN</t>
         </is>
       </c>
       <c r="C411" t="inlineStr">
         <is>
-          <t>111K</t>
+          <t>143K</t>
         </is>
       </c>
       <c r="D411" t="inlineStr">
         <is>
-          <t>273K</t>
+          <t>307K</t>
         </is>
       </c>
       <c r="E411" t="inlineStr">
         <is>
-          <t>141K</t>
+          <t>170K</t>
         </is>
       </c>
       <c r="F411" t="inlineStr">
         <is>
-          <t>180K</t>
+          <t>205K</t>
         </is>
       </c>
       <c r="G411" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="412">
@@ -12539,31 +12547,31 @@
       </c>
       <c r="B412" t="inlineStr">
         <is>
-          <t>Manufacturing PayrollsJAN</t>
+          <t>Unemployment RateJAN</t>
         </is>
       </c>
       <c r="C412" t="inlineStr">
         <is>
-          <t>3K</t>
+          <t>4%</t>
         </is>
       </c>
       <c r="D412" t="inlineStr">
         <is>
-          <t>-12K</t>
+          <t>4.1%</t>
         </is>
       </c>
       <c r="E412" t="inlineStr">
         <is>
-          <t>-2K</t>
+          <t>4.1%</t>
         </is>
       </c>
       <c r="F412" t="inlineStr">
         <is>
-          <t>-5K</t>
+          <t>4.1%</t>
         </is>
       </c>
       <c r="G412" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="413">
@@ -12574,27 +12582,31 @@
       </c>
       <c r="B413" t="inlineStr">
         <is>
-          <t>Participation RateJAN</t>
+          <t>Average Weekly HoursJAN</t>
         </is>
       </c>
       <c r="C413" t="inlineStr">
         <is>
-          <t>62.6%</t>
+          <t>34.1</t>
         </is>
       </c>
       <c r="D413" t="inlineStr">
         <is>
-          <t>62.5%</t>
-        </is>
-      </c>
-      <c r="E413" t="inlineStr"/>
+          <t>34.2</t>
+        </is>
+      </c>
+      <c r="E413" t="inlineStr">
+        <is>
+          <t>34.3</t>
+        </is>
+      </c>
       <c r="F413" t="inlineStr">
         <is>
-          <t>62.5%</t>
+          <t>34.3</t>
         </is>
       </c>
       <c r="G413" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="414">
@@ -12605,31 +12617,31 @@
       </c>
       <c r="B414" t="inlineStr">
         <is>
-          <t>Unemployment RateJAN</t>
+          <t>Manufacturing PayrollsJAN</t>
         </is>
       </c>
       <c r="C414" t="inlineStr">
         <is>
-          <t>4%</t>
+          <t>3K</t>
         </is>
       </c>
       <c r="D414" t="inlineStr">
         <is>
-          <t>4.1%</t>
+          <t>-12K</t>
         </is>
       </c>
       <c r="E414" t="inlineStr">
         <is>
-          <t>4.1%</t>
+          <t>-2K</t>
         </is>
       </c>
       <c r="F414" t="inlineStr">
         <is>
-          <t>4.1%</t>
+          <t>-5K</t>
         </is>
       </c>
       <c r="G414" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="415">
@@ -12640,31 +12652,31 @@
       </c>
       <c r="B415" t="inlineStr">
         <is>
-          <t>Average Hourly Earnings YoYJAN</t>
+          <t>Nonfarm Payrolls PrivateJAN</t>
         </is>
       </c>
       <c r="C415" t="inlineStr">
         <is>
-          <t>4.1%</t>
+          <t>111K</t>
         </is>
       </c>
       <c r="D415" t="inlineStr">
         <is>
-          <t>4.1%</t>
+          <t>273K</t>
         </is>
       </c>
       <c r="E415" t="inlineStr">
         <is>
-          <t>3.8%</t>
+          <t>141K</t>
         </is>
       </c>
       <c r="F415" t="inlineStr">
         <is>
-          <t>3.9%</t>
+          <t>180K</t>
         </is>
       </c>
       <c r="G415" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="416">
@@ -12675,31 +12687,27 @@
       </c>
       <c r="B416" t="inlineStr">
         <is>
-          <t>Non Farm PayrollsJAN</t>
+          <t>Government PayrollsJAN</t>
         </is>
       </c>
       <c r="C416" t="inlineStr">
         <is>
-          <t>143K</t>
+          <t>32K</t>
         </is>
       </c>
       <c r="D416" t="inlineStr">
         <is>
-          <t>307K</t>
-        </is>
-      </c>
-      <c r="E416" t="inlineStr">
-        <is>
-          <t>170K</t>
-        </is>
-      </c>
+          <t>34K</t>
+        </is>
+      </c>
+      <c r="E416" t="inlineStr"/>
       <c r="F416" t="inlineStr">
         <is>
-          <t>205K</t>
+          <t>25K</t>
         </is>
       </c>
       <c r="G416" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="417">
@@ -12710,27 +12718,23 @@
       </c>
       <c r="B417" t="inlineStr">
         <is>
-          <t>Average Weekly HoursJAN</t>
+          <t>U-6 Unemployment RateJAN</t>
         </is>
       </c>
       <c r="C417" t="inlineStr">
         <is>
-          <t>34.1</t>
+          <t>7.5%</t>
         </is>
       </c>
       <c r="D417" t="inlineStr">
         <is>
-          <t>34.2</t>
-        </is>
-      </c>
-      <c r="E417" t="inlineStr">
-        <is>
-          <t>34.3</t>
-        </is>
-      </c>
+          <t>7.5%</t>
+        </is>
+      </c>
+      <c r="E417" t="inlineStr"/>
       <c r="F417" t="inlineStr">
         <is>
-          <t>34.3</t>
+          <t>7.5%</t>
         </is>
       </c>
       <c r="G417" t="n">
@@ -12745,27 +12749,23 @@
       </c>
       <c r="B418" t="inlineStr">
         <is>
-          <t>Average Hourly Earnings MoMJAN</t>
+          <t>Participation RateJAN</t>
         </is>
       </c>
       <c r="C418" t="inlineStr">
         <is>
-          <t>0.5%</t>
+          <t>62.6%</t>
         </is>
       </c>
       <c r="D418" t="inlineStr">
         <is>
-          <t>0.3%</t>
-        </is>
-      </c>
-      <c r="E418" t="inlineStr">
-        <is>
-          <t>0.3%</t>
-        </is>
-      </c>
+          <t>62.5%</t>
+        </is>
+      </c>
+      <c r="E418" t="inlineStr"/>
       <c r="F418" t="inlineStr">
         <is>
-          <t>0.3%</t>
+          <t>62.5%</t>
         </is>
       </c>
       <c r="G418" t="n">
@@ -13501,23 +13501,23 @@
       </c>
       <c r="B446" t="inlineStr">
         <is>
-          <t>MBA Mortgage ApplicationsFEB/07</t>
+          <t>MBA 30-Year Mortgage RateFEB/07</t>
         </is>
       </c>
       <c r="C446" t="inlineStr">
         <is>
-          <t>2.3%</t>
+          <t>6.95%</t>
         </is>
       </c>
       <c r="D446" t="inlineStr">
         <is>
-          <t>2.2%</t>
+          <t>6.97%</t>
         </is>
       </c>
       <c r="E446" t="inlineStr"/>
       <c r="F446" t="inlineStr"/>
       <c r="G446" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="447">
@@ -13528,17 +13528,17 @@
       </c>
       <c r="B447" t="inlineStr">
         <is>
-          <t>MBA Purchase IndexFEB/07</t>
+          <t>MBA Mortgage Market IndexFEB/07</t>
         </is>
       </c>
       <c r="C447" t="inlineStr">
         <is>
-          <t>153.1</t>
+          <t>230.0</t>
         </is>
       </c>
       <c r="D447" t="inlineStr">
         <is>
-          <t>156.7</t>
+          <t>224.8</t>
         </is>
       </c>
       <c r="E447" t="inlineStr"/>
@@ -13555,17 +13555,17 @@
       </c>
       <c r="B448" t="inlineStr">
         <is>
-          <t>MBA Mortgage Market IndexFEB/07</t>
+          <t>MBA Mortgage Refinance IndexFEB/07</t>
         </is>
       </c>
       <c r="C448" t="inlineStr">
         <is>
-          <t>230.0</t>
+          <t>640.6</t>
         </is>
       </c>
       <c r="D448" t="inlineStr">
         <is>
-          <t>224.8</t>
+          <t>584.3</t>
         </is>
       </c>
       <c r="E448" t="inlineStr"/>
@@ -13582,23 +13582,23 @@
       </c>
       <c r="B449" t="inlineStr">
         <is>
-          <t>MBA 30-Year Mortgage RateFEB/07</t>
+          <t>MBA Mortgage ApplicationsFEB/07</t>
         </is>
       </c>
       <c r="C449" t="inlineStr">
         <is>
-          <t>6.95%</t>
+          <t>2.3%</t>
         </is>
       </c>
       <c r="D449" t="inlineStr">
         <is>
-          <t>6.97%</t>
+          <t>2.2%</t>
         </is>
       </c>
       <c r="E449" t="inlineStr"/>
       <c r="F449" t="inlineStr"/>
       <c r="G449" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="450">
@@ -13609,17 +13609,17 @@
       </c>
       <c r="B450" t="inlineStr">
         <is>
-          <t>MBA Mortgage Refinance IndexFEB/07</t>
+          <t>MBA Purchase IndexFEB/07</t>
         </is>
       </c>
       <c r="C450" t="inlineStr">
         <is>
-          <t>640.6</t>
+          <t>153.1</t>
         </is>
       </c>
       <c r="D450" t="inlineStr">
         <is>
-          <t>584.3</t>
+          <t>156.7</t>
         </is>
       </c>
       <c r="E450" t="inlineStr"/>
@@ -13842,27 +13842,23 @@
       </c>
       <c r="B457" t="inlineStr">
         <is>
-          <t>EIA Crude Oil Stocks ChangeFEB/07</t>
+          <t>EIA Crude Oil Imports ChangeFEB/07</t>
         </is>
       </c>
       <c r="C457" t="inlineStr">
         <is>
-          <t>4.07M</t>
+          <t>-0.184M</t>
         </is>
       </c>
       <c r="D457" t="inlineStr">
         <is>
-          <t>8.664M</t>
-        </is>
-      </c>
-      <c r="E457" t="inlineStr">
-        <is>
-          <t>3M</t>
-        </is>
-      </c>
+          <t>-0.178M</t>
+        </is>
+      </c>
+      <c r="E457" t="inlineStr"/>
       <c r="F457" t="inlineStr"/>
       <c r="G457" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="458">
@@ -13873,17 +13869,17 @@
       </c>
       <c r="B458" t="inlineStr">
         <is>
-          <t>EIA Heating Oil Stocks ChangeFEB/07</t>
+          <t>EIA Refinery Crude Runs ChangeFEB/07</t>
         </is>
       </c>
       <c r="C458" t="inlineStr">
         <is>
-          <t>0.159M</t>
+          <t>0.082M</t>
         </is>
       </c>
       <c r="D458" t="inlineStr">
         <is>
-          <t>0.373M</t>
+          <t>0.16M</t>
         </is>
       </c>
       <c r="E458" t="inlineStr"/>
@@ -13900,17 +13896,17 @@
       </c>
       <c r="B459" t="inlineStr">
         <is>
-          <t>EIA Cushing Crude Oil Stocks ChangeFEB/07</t>
+          <t>EIA Gasoline Production ChangeFEB/07</t>
         </is>
       </c>
       <c r="C459" t="inlineStr">
         <is>
-          <t>0.872M</t>
+          <t>0.18M</t>
         </is>
       </c>
       <c r="D459" t="inlineStr">
         <is>
-          <t>-0.034M</t>
+          <t>-0.027M</t>
         </is>
       </c>
       <c r="E459" t="inlineStr"/>
@@ -13927,23 +13923,27 @@
       </c>
       <c r="B460" t="inlineStr">
         <is>
-          <t>EIA Distillate Fuel Production ChangeFEB/07</t>
+          <t>EIA Gasoline Stocks ChangeFEB/07</t>
         </is>
       </c>
       <c r="C460" t="inlineStr">
         <is>
-          <t>-0.009M</t>
+          <t>-3.035M</t>
         </is>
       </c>
       <c r="D460" t="inlineStr">
         <is>
-          <t>-0.186M</t>
-        </is>
-      </c>
-      <c r="E460" t="inlineStr"/>
+          <t>2.233M</t>
+        </is>
+      </c>
+      <c r="E460" t="inlineStr">
+        <is>
+          <t>1.5M</t>
+        </is>
+      </c>
       <c r="F460" t="inlineStr"/>
       <c r="G460" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="461">
@@ -13985,27 +13985,23 @@
       </c>
       <c r="B462" t="inlineStr">
         <is>
-          <t>EIA Gasoline Stocks ChangeFEB/07</t>
+          <t>EIA Distillate Fuel Production ChangeFEB/07</t>
         </is>
       </c>
       <c r="C462" t="inlineStr">
         <is>
-          <t>-3.035M</t>
+          <t>-0.009M</t>
         </is>
       </c>
       <c r="D462" t="inlineStr">
         <is>
-          <t>2.233M</t>
-        </is>
-      </c>
-      <c r="E462" t="inlineStr">
-        <is>
-          <t>1.5M</t>
-        </is>
-      </c>
+          <t>-0.186M</t>
+        </is>
+      </c>
+      <c r="E462" t="inlineStr"/>
       <c r="F462" t="inlineStr"/>
       <c r="G462" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="463">
@@ -14016,17 +14012,17 @@
       </c>
       <c r="B463" t="inlineStr">
         <is>
-          <t>EIA Gasoline Production ChangeFEB/07</t>
+          <t>EIA Cushing Crude Oil Stocks ChangeFEB/07</t>
         </is>
       </c>
       <c r="C463" t="inlineStr">
         <is>
-          <t>0.18M</t>
+          <t>0.872M</t>
         </is>
       </c>
       <c r="D463" t="inlineStr">
         <is>
-          <t>-0.027M</t>
+          <t>-0.034M</t>
         </is>
       </c>
       <c r="E463" t="inlineStr"/>
@@ -14043,17 +14039,17 @@
       </c>
       <c r="B464" t="inlineStr">
         <is>
-          <t>EIA Refinery Crude Runs ChangeFEB/07</t>
+          <t>EIA Heating Oil Stocks ChangeFEB/07</t>
         </is>
       </c>
       <c r="C464" t="inlineStr">
         <is>
-          <t>0.082M</t>
+          <t>0.159M</t>
         </is>
       </c>
       <c r="D464" t="inlineStr">
         <is>
-          <t>0.16M</t>
+          <t>0.373M</t>
         </is>
       </c>
       <c r="E464" t="inlineStr"/>
@@ -14070,23 +14066,27 @@
       </c>
       <c r="B465" t="inlineStr">
         <is>
-          <t>EIA Crude Oil Imports ChangeFEB/07</t>
+          <t>EIA Crude Oil Stocks ChangeFEB/07</t>
         </is>
       </c>
       <c r="C465" t="inlineStr">
         <is>
-          <t>-0.184M</t>
+          <t>4.07M</t>
         </is>
       </c>
       <c r="D465" t="inlineStr">
         <is>
-          <t>-0.178M</t>
-        </is>
-      </c>
-      <c r="E465" t="inlineStr"/>
+          <t>8.664M</t>
+        </is>
+      </c>
+      <c r="E465" t="inlineStr">
+        <is>
+          <t>3M</t>
+        </is>
+      </c>
       <c r="F465" t="inlineStr"/>
       <c r="G465" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="466">
@@ -14224,27 +14224,31 @@
       </c>
       <c r="B471" t="inlineStr">
         <is>
-          <t>Jobless Claims 4-week AverageFEB/08</t>
+          <t>Core PPI MoMJAN</t>
         </is>
       </c>
       <c r="C471" t="inlineStr">
         <is>
-          <t>216K</t>
+          <t>0.3%</t>
         </is>
       </c>
       <c r="D471" t="inlineStr">
         <is>
-          <t>217K</t>
-        </is>
-      </c>
-      <c r="E471" t="inlineStr"/>
+          <t>0.4%</t>
+        </is>
+      </c>
+      <c r="E471" t="inlineStr">
+        <is>
+          <t>0.3%</t>
+        </is>
+      </c>
       <c r="F471" t="inlineStr">
         <is>
-          <t>216.0K</t>
+          <t>0.1%</t>
         </is>
       </c>
       <c r="G471" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="472">
@@ -14255,31 +14259,31 @@
       </c>
       <c r="B472" t="inlineStr">
         <is>
-          <t>Continuing Jobless ClaimsFEB/01</t>
+          <t>Initial Jobless ClaimsFEB/08</t>
         </is>
       </c>
       <c r="C472" t="inlineStr">
         <is>
-          <t>1850K</t>
+          <t>213K</t>
         </is>
       </c>
       <c r="D472" t="inlineStr">
         <is>
-          <t>1886K</t>
+          <t>220K</t>
         </is>
       </c>
       <c r="E472" t="inlineStr">
         <is>
-          <t>1880K</t>
+          <t>215K</t>
         </is>
       </c>
       <c r="F472" t="inlineStr">
         <is>
-          <t>1875.0K</t>
+          <t>215.0K</t>
         </is>
       </c>
       <c r="G472" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="473">
@@ -14290,31 +14294,27 @@
       </c>
       <c r="B473" t="inlineStr">
         <is>
-          <t>PPI MoMJAN</t>
+          <t>PPIJAN</t>
         </is>
       </c>
       <c r="C473" t="inlineStr">
         <is>
-          <t>0.4%</t>
+          <t>147.716</t>
         </is>
       </c>
       <c r="D473" t="inlineStr">
         <is>
-          <t>0.5%</t>
-        </is>
-      </c>
-      <c r="E473" t="inlineStr">
-        <is>
-          <t>0.3%</t>
-        </is>
-      </c>
+          <t>147.127</t>
+        </is>
+      </c>
+      <c r="E473" t="inlineStr"/>
       <c r="F473" t="inlineStr">
         <is>
-          <t>0.3%</t>
+          <t>147.2</t>
         </is>
       </c>
       <c r="G473" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="474">
@@ -14325,27 +14325,27 @@
       </c>
       <c r="B474" t="inlineStr">
         <is>
-          <t>PPI Ex Food, Energy and Trade YoYJAN</t>
+          <t>PPI YoYJAN</t>
         </is>
       </c>
       <c r="C474" t="inlineStr">
         <is>
+          <t>3.5%</t>
+        </is>
+      </c>
+      <c r="D474" t="inlineStr">
+        <is>
+          <t>3.5%</t>
+        </is>
+      </c>
+      <c r="E474" t="inlineStr">
+        <is>
+          <t>3.2%</t>
+        </is>
+      </c>
+      <c r="F474" t="inlineStr">
+        <is>
           <t>3.4%</t>
-        </is>
-      </c>
-      <c r="D474" t="inlineStr">
-        <is>
-          <t>3.5%</t>
-        </is>
-      </c>
-      <c r="E474" t="inlineStr">
-        <is>
-          <t>3.2%</t>
-        </is>
-      </c>
-      <c r="F474" t="inlineStr">
-        <is>
-          <t>3.3%</t>
         </is>
       </c>
       <c r="G474" t="n">
@@ -14360,23 +14360,27 @@
       </c>
       <c r="B475" t="inlineStr">
         <is>
-          <t>PPI Ex Food, Energy and Trade MoMJAN</t>
+          <t>Core PPI YoYJAN</t>
         </is>
       </c>
       <c r="C475" t="inlineStr">
         <is>
-          <t>0.3%</t>
+          <t>3.6%</t>
         </is>
       </c>
       <c r="D475" t="inlineStr">
         <is>
-          <t>0.4%</t>
-        </is>
-      </c>
-      <c r="E475" t="inlineStr"/>
+          <t>3.7%</t>
+        </is>
+      </c>
+      <c r="E475" t="inlineStr">
+        <is>
+          <t>3.3%</t>
+        </is>
+      </c>
       <c r="F475" t="inlineStr">
         <is>
-          <t>0.2%</t>
+          <t>3.5%</t>
         </is>
       </c>
       <c r="G475" t="n">
@@ -14391,27 +14395,27 @@
       </c>
       <c r="B476" t="inlineStr">
         <is>
-          <t>Core PPI YoYJAN</t>
+          <t>PPI Ex Food, Energy and Trade YoYJAN</t>
         </is>
       </c>
       <c r="C476" t="inlineStr">
         <is>
-          <t>3.6%</t>
+          <t>3.4%</t>
         </is>
       </c>
       <c r="D476" t="inlineStr">
         <is>
-          <t>3.7%</t>
+          <t>3.5%</t>
         </is>
       </c>
       <c r="E476" t="inlineStr">
         <is>
+          <t>3.2%</t>
+        </is>
+      </c>
+      <c r="F476" t="inlineStr">
+        <is>
           <t>3.3%</t>
-        </is>
-      </c>
-      <c r="F476" t="inlineStr">
-        <is>
-          <t>3.5%</t>
         </is>
       </c>
       <c r="G476" t="n">
@@ -14426,31 +14430,31 @@
       </c>
       <c r="B477" t="inlineStr">
         <is>
-          <t>PPI YoYJAN</t>
+          <t>PPI MoMJAN</t>
         </is>
       </c>
       <c r="C477" t="inlineStr">
         <is>
-          <t>3.5%</t>
+          <t>0.4%</t>
         </is>
       </c>
       <c r="D477" t="inlineStr">
         <is>
-          <t>3.5%</t>
+          <t>0.5%</t>
         </is>
       </c>
       <c r="E477" t="inlineStr">
         <is>
-          <t>3.2%</t>
+          <t>0.3%</t>
         </is>
       </c>
       <c r="F477" t="inlineStr">
         <is>
-          <t>3.4%</t>
+          <t>0.3%</t>
         </is>
       </c>
       <c r="G477" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="478">
@@ -14461,23 +14465,27 @@
       </c>
       <c r="B478" t="inlineStr">
         <is>
-          <t>PPIJAN</t>
+          <t>Continuing Jobless ClaimsFEB/01</t>
         </is>
       </c>
       <c r="C478" t="inlineStr">
         <is>
-          <t>147.716</t>
+          <t>1850K</t>
         </is>
       </c>
       <c r="D478" t="inlineStr">
         <is>
-          <t>147.127</t>
-        </is>
-      </c>
-      <c r="E478" t="inlineStr"/>
+          <t>1886K</t>
+        </is>
+      </c>
+      <c r="E478" t="inlineStr">
+        <is>
+          <t>1880K</t>
+        </is>
+      </c>
       <c r="F478" t="inlineStr">
         <is>
-          <t>147.2</t>
+          <t>1875.0K</t>
         </is>
       </c>
       <c r="G478" t="n">
@@ -14492,31 +14500,27 @@
       </c>
       <c r="B479" t="inlineStr">
         <is>
-          <t>Initial Jobless ClaimsFEB/08</t>
+          <t>Jobless Claims 4-week AverageFEB/08</t>
         </is>
       </c>
       <c r="C479" t="inlineStr">
         <is>
-          <t>213K</t>
+          <t>216K</t>
         </is>
       </c>
       <c r="D479" t="inlineStr">
         <is>
-          <t>220K</t>
-        </is>
-      </c>
-      <c r="E479" t="inlineStr">
-        <is>
-          <t>215K</t>
-        </is>
-      </c>
+          <t>217K</t>
+        </is>
+      </c>
+      <c r="E479" t="inlineStr"/>
       <c r="F479" t="inlineStr">
         <is>
-          <t>215.0K</t>
+          <t>216.0K</t>
         </is>
       </c>
       <c r="G479" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="480">
@@ -14527,7 +14531,7 @@
       </c>
       <c r="B480" t="inlineStr">
         <is>
-          <t>Core PPI MoMJAN</t>
+          <t>PPI Ex Food, Energy and Trade MoMJAN</t>
         </is>
       </c>
       <c r="C480" t="inlineStr">
@@ -14540,18 +14544,14 @@
           <t>0.4%</t>
         </is>
       </c>
-      <c r="E480" t="inlineStr">
-        <is>
-          <t>0.3%</t>
-        </is>
-      </c>
+      <c r="E480" t="inlineStr"/>
       <c r="F480" t="inlineStr">
         <is>
-          <t>0.1%</t>
+          <t>0.2%</t>
         </is>
       </c>
       <c r="G480" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="481">
@@ -14728,31 +14728,31 @@
       </c>
       <c r="B487" t="inlineStr">
         <is>
-          <t>Export Prices MoMJAN</t>
+          <t>Retail Sales MoMJAN</t>
         </is>
       </c>
       <c r="C487" t="inlineStr">
         <is>
-          <t>1.3%</t>
+          <t>-0.9%</t>
         </is>
       </c>
       <c r="D487" t="inlineStr">
         <is>
-          <t>0.5%</t>
+          <t>0.7%</t>
         </is>
       </c>
       <c r="E487" t="inlineStr">
         <is>
-          <t>0.3%</t>
+          <t>-0.1%</t>
         </is>
       </c>
       <c r="F487" t="inlineStr">
         <is>
-          <t>0.3%</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="G487" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="488">
@@ -14763,23 +14763,23 @@
       </c>
       <c r="B488" t="inlineStr">
         <is>
-          <t>Retail Sales YoYJAN</t>
+          <t>Retail Sales Ex Gas/Autos MoMJAN</t>
         </is>
       </c>
       <c r="C488" t="inlineStr">
         <is>
-          <t>4.2%</t>
+          <t>-0.5%</t>
         </is>
       </c>
       <c r="D488" t="inlineStr">
         <is>
-          <t>4.4%</t>
+          <t>0.5%</t>
         </is>
       </c>
       <c r="E488" t="inlineStr"/>
       <c r="F488" t="inlineStr">
         <is>
-          <t>3.7%</t>
+          <t>0.2%</t>
         </is>
       </c>
       <c r="G488" t="n">
@@ -14794,27 +14794,31 @@
       </c>
       <c r="B489" t="inlineStr">
         <is>
-          <t>Import Prices YoYJAN</t>
+          <t>Import Prices MoMJAN</t>
         </is>
       </c>
       <c r="C489" t="inlineStr">
         <is>
-          <t>1.9%</t>
+          <t>0.3%</t>
         </is>
       </c>
       <c r="D489" t="inlineStr">
         <is>
-          <t>2.2%</t>
-        </is>
-      </c>
-      <c r="E489" t="inlineStr"/>
+          <t>0.2%</t>
+        </is>
+      </c>
+      <c r="E489" t="inlineStr">
+        <is>
+          <t>0.4%</t>
+        </is>
+      </c>
       <c r="F489" t="inlineStr">
         <is>
-          <t>2.8%</t>
+          <t>0.3%</t>
         </is>
       </c>
       <c r="G489" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="490">
@@ -14825,31 +14829,27 @@
       </c>
       <c r="B490" t="inlineStr">
         <is>
-          <t>Retail Sales MoMJAN</t>
+          <t>Export Prices YoYJAN</t>
         </is>
       </c>
       <c r="C490" t="inlineStr">
         <is>
-          <t>-0.9%</t>
+          <t>2.7%</t>
         </is>
       </c>
       <c r="D490" t="inlineStr">
         <is>
-          <t>0.7%</t>
-        </is>
-      </c>
-      <c r="E490" t="inlineStr">
-        <is>
-          <t>-0.1%</t>
-        </is>
-      </c>
+          <t>2%</t>
+        </is>
+      </c>
+      <c r="E490" t="inlineStr"/>
       <c r="F490" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>2.3%</t>
         </is>
       </c>
       <c r="G490" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="491">
@@ -14860,17 +14860,17 @@
       </c>
       <c r="B491" t="inlineStr">
         <is>
-          <t>Retail Sales Ex Autos MoMJAN</t>
+          <t>Retail Sales Control Group MoMJAN</t>
         </is>
       </c>
       <c r="C491" t="inlineStr">
         <is>
-          <t>-0.4%</t>
+          <t>-0.8%</t>
         </is>
       </c>
       <c r="D491" t="inlineStr">
         <is>
-          <t>0.7%</t>
+          <t>0.8%</t>
         </is>
       </c>
       <c r="E491" t="inlineStr">
@@ -14880,7 +14880,7 @@
       </c>
       <c r="F491" t="inlineStr">
         <is>
-          <t>0.3%</t>
+          <t>0.4%</t>
         </is>
       </c>
       <c r="G491" t="n">
@@ -14895,31 +14895,27 @@
       </c>
       <c r="B492" t="inlineStr">
         <is>
-          <t>Retail Sales Control Group MoMJAN</t>
+          <t>Import Prices YoYJAN</t>
         </is>
       </c>
       <c r="C492" t="inlineStr">
         <is>
-          <t>-0.8%</t>
+          <t>1.9%</t>
         </is>
       </c>
       <c r="D492" t="inlineStr">
         <is>
-          <t>0.8%</t>
-        </is>
-      </c>
-      <c r="E492" t="inlineStr">
-        <is>
-          <t>0.3%</t>
-        </is>
-      </c>
+          <t>2.2%</t>
+        </is>
+      </c>
+      <c r="E492" t="inlineStr"/>
       <c r="F492" t="inlineStr">
         <is>
-          <t>0.4%</t>
+          <t>2.8%</t>
         </is>
       </c>
       <c r="G492" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="493">
@@ -14930,23 +14926,23 @@
       </c>
       <c r="B493" t="inlineStr">
         <is>
-          <t>Export Prices YoYJAN</t>
+          <t>Retail Sales YoYJAN</t>
         </is>
       </c>
       <c r="C493" t="inlineStr">
         <is>
-          <t>2.7%</t>
+          <t>4.2%</t>
         </is>
       </c>
       <c r="D493" t="inlineStr">
         <is>
-          <t>2%</t>
+          <t>4.4%</t>
         </is>
       </c>
       <c r="E493" t="inlineStr"/>
       <c r="F493" t="inlineStr">
         <is>
-          <t>2.3%</t>
+          <t>3.7%</t>
         </is>
       </c>
       <c r="G493" t="n">
@@ -14961,22 +14957,22 @@
       </c>
       <c r="B494" t="inlineStr">
         <is>
-          <t>Import Prices MoMJAN</t>
+          <t>Export Prices MoMJAN</t>
         </is>
       </c>
       <c r="C494" t="inlineStr">
         <is>
+          <t>1.3%</t>
+        </is>
+      </c>
+      <c r="D494" t="inlineStr">
+        <is>
+          <t>0.5%</t>
+        </is>
+      </c>
+      <c r="E494" t="inlineStr">
+        <is>
           <t>0.3%</t>
-        </is>
-      </c>
-      <c r="D494" t="inlineStr">
-        <is>
-          <t>0.2%</t>
-        </is>
-      </c>
-      <c r="E494" t="inlineStr">
-        <is>
-          <t>0.4%</t>
         </is>
       </c>
       <c r="F494" t="inlineStr">
@@ -14996,27 +14992,31 @@
       </c>
       <c r="B495" t="inlineStr">
         <is>
-          <t>Retail Sales Ex Gas/Autos MoMJAN</t>
+          <t>Retail Sales Ex Autos MoMJAN</t>
         </is>
       </c>
       <c r="C495" t="inlineStr">
         <is>
-          <t>-0.5%</t>
+          <t>-0.4%</t>
         </is>
       </c>
       <c r="D495" t="inlineStr">
         <is>
-          <t>0.5%</t>
-        </is>
-      </c>
-      <c r="E495" t="inlineStr"/>
+          <t>0.7%</t>
+        </is>
+      </c>
+      <c r="E495" t="inlineStr">
+        <is>
+          <t>0.3%</t>
+        </is>
+      </c>
       <c r="F495" t="inlineStr">
         <is>
-          <t>0.2%</t>
+          <t>0.3%</t>
         </is>
       </c>
       <c r="G495" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="496">
@@ -15629,17 +15629,17 @@
       </c>
       <c r="B518" t="inlineStr">
         <is>
-          <t>Overall Net Capital FlowsDEC</t>
+          <t>Foreign Bond InvestmentDEC</t>
         </is>
       </c>
       <c r="C518" t="inlineStr">
         <is>
-          <t>$87.1B</t>
+          <t>$-49.7B</t>
         </is>
       </c>
       <c r="D518" t="inlineStr">
         <is>
-          <t>$134.1B</t>
+          <t>$-34.4B</t>
         </is>
       </c>
       <c r="E518" t="inlineStr"/>
@@ -15687,17 +15687,17 @@
       </c>
       <c r="B520" t="inlineStr">
         <is>
-          <t>Foreign Bond InvestmentDEC</t>
+          <t>Overall Net Capital FlowsDEC</t>
         </is>
       </c>
       <c r="C520" t="inlineStr">
         <is>
-          <t>$-49.7B</t>
+          <t>$87.1B</t>
         </is>
       </c>
       <c r="D520" t="inlineStr">
         <is>
-          <t>$-34.4B</t>
+          <t>$134.1B</t>
         </is>
       </c>
       <c r="E520" t="inlineStr"/>
@@ -17326,7 +17326,7 @@
       </c>
       <c r="B577" t="inlineStr">
         <is>
-          <t>Fed Daly Speech</t>
+          <t>Fed Jefferson Speech</t>
         </is>
       </c>
       <c r="C577" t="inlineStr"/>
@@ -17345,7 +17345,7 @@
       </c>
       <c r="B578" t="inlineStr">
         <is>
-          <t>Fed Jefferson Speech</t>
+          <t>Fed Daly Speech</t>
         </is>
       </c>
       <c r="C578" t="inlineStr"/>
@@ -17630,27 +17630,31 @@
       </c>
       <c r="B589" t="inlineStr">
         <is>
-          <t>S&amp;P/Case-Shiller Home Price MoMDEC</t>
+          <t>S&amp;P/Case-Shiller Home Price YoYDEC</t>
         </is>
       </c>
       <c r="C589" t="inlineStr">
         <is>
-          <t>-0.1%</t>
+          <t>4.5%</t>
         </is>
       </c>
       <c r="D589" t="inlineStr">
         <is>
-          <t>-0.1%</t>
-        </is>
-      </c>
-      <c r="E589" t="inlineStr"/>
+          <t>4.3%</t>
+        </is>
+      </c>
+      <c r="E589" t="inlineStr">
+        <is>
+          <t>4.4%</t>
+        </is>
+      </c>
       <c r="F589" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>4.4%</t>
         </is>
       </c>
       <c r="G589" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="590">
@@ -17661,27 +17665,19 @@
       </c>
       <c r="B590" t="inlineStr">
         <is>
-          <t>House Price Index MoMDEC</t>
-        </is>
-      </c>
-      <c r="C590" t="inlineStr">
-        <is>
-          <t>0.4%</t>
-        </is>
-      </c>
+          <t>House Price Index YoYDEC</t>
+        </is>
+      </c>
+      <c r="C590" t="inlineStr"/>
       <c r="D590" t="inlineStr">
         <is>
-          <t>0.4%</t>
-        </is>
-      </c>
-      <c r="E590" t="inlineStr">
-        <is>
-          <t>0.2%</t>
-        </is>
-      </c>
+          <t>4.2%</t>
+        </is>
+      </c>
+      <c r="E590" t="inlineStr"/>
       <c r="F590" t="inlineStr">
         <is>
-          <t>0.2%</t>
+          <t>4.1%</t>
         </is>
       </c>
       <c r="G590" t="n">
@@ -17699,14 +17695,10 @@
           <t>House Price IndexDEC</t>
         </is>
       </c>
-      <c r="C591" t="inlineStr">
-        <is>
-          <t>436.1</t>
-        </is>
-      </c>
+      <c r="C591" t="inlineStr"/>
       <c r="D591" t="inlineStr">
         <is>
-          <t>434.3</t>
+          <t>433.4</t>
         </is>
       </c>
       <c r="E591" t="inlineStr"/>
@@ -17727,27 +17719,27 @@
       </c>
       <c r="B592" t="inlineStr">
         <is>
-          <t>House Price Index YoYDEC</t>
-        </is>
-      </c>
-      <c r="C592" t="inlineStr">
-        <is>
-          <t>4.7%</t>
-        </is>
-      </c>
+          <t>S&amp;P/Case-Shiller Home Price YoYDEC</t>
+        </is>
+      </c>
+      <c r="C592" t="inlineStr"/>
       <c r="D592" t="inlineStr">
         <is>
-          <t>4.5%</t>
-        </is>
-      </c>
-      <c r="E592" t="inlineStr"/>
+          <t>4.3%</t>
+        </is>
+      </c>
+      <c r="E592" t="inlineStr">
+        <is>
+          <t>4.4%</t>
+        </is>
+      </c>
       <c r="F592" t="inlineStr">
         <is>
-          <t>4.1%</t>
+          <t>4.4%</t>
         </is>
       </c>
       <c r="G592" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="593">
@@ -17758,23 +17750,19 @@
       </c>
       <c r="B593" t="inlineStr">
         <is>
-          <t>House Price Index MoMDEC</t>
+          <t>S&amp;P/Case-Shiller Home Price MoMDEC</t>
         </is>
       </c>
       <c r="C593" t="inlineStr"/>
       <c r="D593" t="inlineStr">
         <is>
-          <t>0.3%</t>
-        </is>
-      </c>
-      <c r="E593" t="inlineStr">
-        <is>
-          <t>0.2%</t>
-        </is>
-      </c>
+          <t>-0.1%</t>
+        </is>
+      </c>
+      <c r="E593" t="inlineStr"/>
       <c r="F593" t="inlineStr">
         <is>
-          <t>0.2%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="G593" t="n">
@@ -17789,19 +17777,23 @@
       </c>
       <c r="B594" t="inlineStr">
         <is>
-          <t>S&amp;P/Case-Shiller Home Price MoMDEC</t>
+          <t>House Price Index MoMDEC</t>
         </is>
       </c>
       <c r="C594" t="inlineStr"/>
       <c r="D594" t="inlineStr">
         <is>
-          <t>-0.1%</t>
-        </is>
-      </c>
-      <c r="E594" t="inlineStr"/>
+          <t>0.3%</t>
+        </is>
+      </c>
+      <c r="E594" t="inlineStr">
+        <is>
+          <t>0.2%</t>
+        </is>
+      </c>
       <c r="F594" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>0.2%</t>
         </is>
       </c>
       <c r="G594" t="n">
@@ -17816,31 +17808,27 @@
       </c>
       <c r="B595" t="inlineStr">
         <is>
-          <t>S&amp;P/Case-Shiller Home Price YoYDEC</t>
+          <t>House Price Index YoYDEC</t>
         </is>
       </c>
       <c r="C595" t="inlineStr">
         <is>
+          <t>4.7%</t>
+        </is>
+      </c>
+      <c r="D595" t="inlineStr">
+        <is>
           <t>4.5%</t>
         </is>
       </c>
-      <c r="D595" t="inlineStr">
-        <is>
-          <t>4.3%</t>
-        </is>
-      </c>
-      <c r="E595" t="inlineStr">
-        <is>
-          <t>4.4%</t>
-        </is>
-      </c>
+      <c r="E595" t="inlineStr"/>
       <c r="F595" t="inlineStr">
         <is>
-          <t>4.4%</t>
+          <t>4.1%</t>
         </is>
       </c>
       <c r="G595" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="596">
@@ -17851,27 +17839,27 @@
       </c>
       <c r="B596" t="inlineStr">
         <is>
-          <t>S&amp;P/Case-Shiller Home Price YoYDEC</t>
-        </is>
-      </c>
-      <c r="C596" t="inlineStr"/>
+          <t>House Price IndexDEC</t>
+        </is>
+      </c>
+      <c r="C596" t="inlineStr">
+        <is>
+          <t>436.1</t>
+        </is>
+      </c>
       <c r="D596" t="inlineStr">
         <is>
-          <t>4.3%</t>
-        </is>
-      </c>
-      <c r="E596" t="inlineStr">
-        <is>
-          <t>4.4%</t>
-        </is>
-      </c>
+          <t>434.3</t>
+        </is>
+      </c>
+      <c r="E596" t="inlineStr"/>
       <c r="F596" t="inlineStr">
         <is>
-          <t>4.4%</t>
+          <t>434.3</t>
         </is>
       </c>
       <c r="G596" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="597">
@@ -17882,19 +17870,27 @@
       </c>
       <c r="B597" t="inlineStr">
         <is>
-          <t>House Price IndexDEC</t>
-        </is>
-      </c>
-      <c r="C597" t="inlineStr"/>
+          <t>House Price Index MoMDEC</t>
+        </is>
+      </c>
+      <c r="C597" t="inlineStr">
+        <is>
+          <t>0.4%</t>
+        </is>
+      </c>
       <c r="D597" t="inlineStr">
         <is>
-          <t>433.4</t>
-        </is>
-      </c>
-      <c r="E597" t="inlineStr"/>
+          <t>0.4%</t>
+        </is>
+      </c>
+      <c r="E597" t="inlineStr">
+        <is>
+          <t>0.2%</t>
+        </is>
+      </c>
       <c r="F597" t="inlineStr">
         <is>
-          <t>434.3</t>
+          <t>0.2%</t>
         </is>
       </c>
       <c r="G597" t="n">
@@ -17909,19 +17905,23 @@
       </c>
       <c r="B598" t="inlineStr">
         <is>
-          <t>House Price Index YoYDEC</t>
-        </is>
-      </c>
-      <c r="C598" t="inlineStr"/>
+          <t>S&amp;P/Case-Shiller Home Price MoMDEC</t>
+        </is>
+      </c>
+      <c r="C598" t="inlineStr">
+        <is>
+          <t>-0.1%</t>
+        </is>
+      </c>
       <c r="D598" t="inlineStr">
         <is>
-          <t>4.2%</t>
+          <t>-0.1%</t>
         </is>
       </c>
       <c r="E598" t="inlineStr"/>
       <c r="F598" t="inlineStr">
         <is>
-          <t>4.1%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="G598" t="n">
@@ -18184,23 +18184,19 @@
       </c>
       <c r="B607" t="inlineStr">
         <is>
-          <t>Dallas Fed Services IndexFEB</t>
-        </is>
-      </c>
-      <c r="C607" t="inlineStr">
-        <is>
-          <t>4.6</t>
-        </is>
-      </c>
+          <t>Dallas Fed Services Revenues IndexFEB</t>
+        </is>
+      </c>
+      <c r="C607" t="inlineStr"/>
       <c r="D607" t="inlineStr">
         <is>
-          <t>7.4</t>
+          <t>5.7</t>
         </is>
       </c>
       <c r="E607" t="inlineStr"/>
       <c r="F607" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>7</t>
         </is>
       </c>
       <c r="G607" t="n">
@@ -18215,23 +18211,19 @@
       </c>
       <c r="B608" t="inlineStr">
         <is>
-          <t>Dallas Fed Services Revenues IndexFEB</t>
-        </is>
-      </c>
-      <c r="C608" t="inlineStr">
-        <is>
-          <t>8.2</t>
-        </is>
-      </c>
+          <t>Dallas Fed Services IndexFEB</t>
+        </is>
+      </c>
+      <c r="C608" t="inlineStr"/>
       <c r="D608" t="inlineStr">
         <is>
-          <t>5.7</t>
+          <t>7.4</t>
         </is>
       </c>
       <c r="E608" t="inlineStr"/>
       <c r="F608" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>9</t>
         </is>
       </c>
       <c r="G608" t="n">
@@ -18249,7 +18241,11 @@
           <t>Dallas Fed Services IndexFEB</t>
         </is>
       </c>
-      <c r="C609" t="inlineStr"/>
+      <c r="C609" t="inlineStr">
+        <is>
+          <t>4.6</t>
+        </is>
+      </c>
       <c r="D609" t="inlineStr">
         <is>
           <t>7.4</t>
@@ -18276,7 +18272,11 @@
           <t>Dallas Fed Services Revenues IndexFEB</t>
         </is>
       </c>
-      <c r="C610" t="inlineStr"/>
+      <c r="C610" t="inlineStr">
+        <is>
+          <t>8.2</t>
+        </is>
+      </c>
       <c r="D610" t="inlineStr">
         <is>
           <t>5.7</t>
@@ -18496,23 +18496,19 @@
       </c>
       <c r="B619" t="inlineStr">
         <is>
-          <t>MBA Purchase IndexFEB/21</t>
-        </is>
-      </c>
-      <c r="C619" t="inlineStr">
-        <is>
-          <t>144.3</t>
-        </is>
-      </c>
+          <t>MBA 30-Year Mortgage RateFEB/21</t>
+        </is>
+      </c>
+      <c r="C619" t="inlineStr"/>
       <c r="D619" t="inlineStr">
         <is>
-          <t>144.0</t>
+          <t>6.93%</t>
         </is>
       </c>
       <c r="E619" t="inlineStr"/>
       <c r="F619" t="inlineStr"/>
       <c r="G619" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="620">
@@ -18523,23 +18519,19 @@
       </c>
       <c r="B620" t="inlineStr">
         <is>
-          <t>MBA 30-Year Mortgage RateFEB/21</t>
-        </is>
-      </c>
-      <c r="C620" t="inlineStr">
-        <is>
-          <t>6.88%</t>
-        </is>
-      </c>
+          <t>MBA Purchase IndexFEB/21</t>
+        </is>
+      </c>
+      <c r="C620" t="inlineStr"/>
       <c r="D620" t="inlineStr">
         <is>
-          <t>6.93%</t>
+          <t>144.0</t>
         </is>
       </c>
       <c r="E620" t="inlineStr"/>
       <c r="F620" t="inlineStr"/>
       <c r="G620" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="621">
@@ -18550,17 +18542,13 @@
       </c>
       <c r="B621" t="inlineStr">
         <is>
-          <t>MBA Mortgage Refinance IndexFEB/21</t>
-        </is>
-      </c>
-      <c r="C621" t="inlineStr">
-        <is>
-          <t>572.5</t>
-        </is>
-      </c>
+          <t>MBA Mortgage ApplicationsFEB/21</t>
+        </is>
+      </c>
+      <c r="C621" t="inlineStr"/>
       <c r="D621" t="inlineStr">
         <is>
-          <t>593.6</t>
+          <t>-6.6%</t>
         </is>
       </c>
       <c r="E621" t="inlineStr"/>
@@ -18577,17 +18565,17 @@
       </c>
       <c r="B622" t="inlineStr">
         <is>
-          <t>MBA Mortgage Market IndexFEB/21</t>
+          <t>MBA Mortgage ApplicationsFEB/21</t>
         </is>
       </c>
       <c r="C622" t="inlineStr">
         <is>
-          <t>212.3</t>
+          <t>-1.2%</t>
         </is>
       </c>
       <c r="D622" t="inlineStr">
         <is>
-          <t>214.9</t>
+          <t>-6.6%</t>
         </is>
       </c>
       <c r="E622" t="inlineStr"/>
@@ -18604,13 +18592,13 @@
       </c>
       <c r="B623" t="inlineStr">
         <is>
-          <t>MBA Mortgage Market IndexFEB/21</t>
+          <t>MBA Mortgage Refinance IndexFEB/21</t>
         </is>
       </c>
       <c r="C623" t="inlineStr"/>
       <c r="D623" t="inlineStr">
         <is>
-          <t>214.9</t>
+          <t>593.6</t>
         </is>
       </c>
       <c r="E623" t="inlineStr"/>
@@ -18627,19 +18615,23 @@
       </c>
       <c r="B624" t="inlineStr">
         <is>
-          <t>MBA Mortgage Refinance IndexFEB/21</t>
-        </is>
-      </c>
-      <c r="C624" t="inlineStr"/>
+          <t>MBA 30-Year Mortgage RateFEB/21</t>
+        </is>
+      </c>
+      <c r="C624" t="inlineStr">
+        <is>
+          <t>6.88%</t>
+        </is>
+      </c>
       <c r="D624" t="inlineStr">
         <is>
-          <t>593.6</t>
+          <t>6.93%</t>
         </is>
       </c>
       <c r="E624" t="inlineStr"/>
       <c r="F624" t="inlineStr"/>
       <c r="G624" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="625">
@@ -18650,19 +18642,23 @@
       </c>
       <c r="B625" t="inlineStr">
         <is>
-          <t>MBA 30-Year Mortgage RateFEB/21</t>
-        </is>
-      </c>
-      <c r="C625" t="inlineStr"/>
+          <t>MBA Mortgage Market IndexFEB/21</t>
+        </is>
+      </c>
+      <c r="C625" t="inlineStr">
+        <is>
+          <t>212.3</t>
+        </is>
+      </c>
       <c r="D625" t="inlineStr">
         <is>
-          <t>6.93%</t>
+          <t>214.9</t>
         </is>
       </c>
       <c r="E625" t="inlineStr"/>
       <c r="F625" t="inlineStr"/>
       <c r="G625" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="626">
@@ -18673,17 +18669,17 @@
       </c>
       <c r="B626" t="inlineStr">
         <is>
-          <t>MBA Mortgage ApplicationsFEB/21</t>
+          <t>MBA Mortgage Refinance IndexFEB/21</t>
         </is>
       </c>
       <c r="C626" t="inlineStr">
         <is>
-          <t>-1.2%</t>
+          <t>572.5</t>
         </is>
       </c>
       <c r="D626" t="inlineStr">
         <is>
-          <t>-6.6%</t>
+          <t>593.6</t>
         </is>
       </c>
       <c r="E626" t="inlineStr"/>
@@ -18700,13 +18696,13 @@
       </c>
       <c r="B627" t="inlineStr">
         <is>
-          <t>MBA Mortgage ApplicationsFEB/21</t>
+          <t>MBA Mortgage Market IndexFEB/21</t>
         </is>
       </c>
       <c r="C627" t="inlineStr"/>
       <c r="D627" t="inlineStr">
         <is>
-          <t>-6.6%</t>
+          <t>214.9</t>
         </is>
       </c>
       <c r="E627" t="inlineStr"/>
@@ -18726,7 +18722,11 @@
           <t>MBA Purchase IndexFEB/21</t>
         </is>
       </c>
-      <c r="C628" t="inlineStr"/>
+      <c r="C628" t="inlineStr">
+        <is>
+          <t>144.3</t>
+        </is>
+      </c>
       <c r="D628" t="inlineStr">
         <is>
           <t>144.0</t>
@@ -18908,14 +18908,10 @@
           <t>New Home SalesJAN</t>
         </is>
       </c>
-      <c r="C634" t="inlineStr">
-        <is>
-          <t>0.657M</t>
-        </is>
-      </c>
+      <c r="C634" t="inlineStr"/>
       <c r="D634" t="inlineStr">
         <is>
-          <t>0.734M</t>
+          <t>0.698M</t>
         </is>
       </c>
       <c r="E634" t="inlineStr">
@@ -18943,14 +18939,10 @@
           <t>New Home Sales MoMJAN</t>
         </is>
       </c>
-      <c r="C635" t="inlineStr">
-        <is>
-          <t>-10.5%</t>
-        </is>
-      </c>
+      <c r="C635" t="inlineStr"/>
       <c r="D635" t="inlineStr">
         <is>
-          <t>8.1%</t>
+          <t>3.6%</t>
         </is>
       </c>
       <c r="E635" t="inlineStr"/>
@@ -18974,10 +18966,14 @@
           <t>New Home Sales MoMJAN</t>
         </is>
       </c>
-      <c r="C636" t="inlineStr"/>
+      <c r="C636" t="inlineStr">
+        <is>
+          <t>-10.5%</t>
+        </is>
+      </c>
       <c r="D636" t="inlineStr">
         <is>
-          <t>3.6%</t>
+          <t>8.1%</t>
         </is>
       </c>
       <c r="E636" t="inlineStr"/>
@@ -19001,10 +18997,14 @@
           <t>New Home SalesJAN</t>
         </is>
       </c>
-      <c r="C637" t="inlineStr"/>
+      <c r="C637" t="inlineStr">
+        <is>
+          <t>0.657M</t>
+        </is>
+      </c>
       <c r="D637" t="inlineStr">
         <is>
-          <t>0.698M</t>
+          <t>0.734M</t>
         </is>
       </c>
       <c r="E637" t="inlineStr">
@@ -19029,19 +19029,27 @@
       </c>
       <c r="B638" t="inlineStr">
         <is>
-          <t>EIA Cushing Crude Oil Stocks ChangeFEB/21</t>
-        </is>
-      </c>
-      <c r="C638" t="inlineStr"/>
+          <t>EIA Gasoline Stocks ChangeFEB/21</t>
+        </is>
+      </c>
+      <c r="C638" t="inlineStr">
+        <is>
+          <t>0.369M</t>
+        </is>
+      </c>
       <c r="D638" t="inlineStr">
         <is>
-          <t>1.472M</t>
-        </is>
-      </c>
-      <c r="E638" t="inlineStr"/>
+          <t>-0.151M</t>
+        </is>
+      </c>
+      <c r="E638" t="inlineStr">
+        <is>
+          <t>-1.30M</t>
+        </is>
+      </c>
       <c r="F638" t="inlineStr"/>
       <c r="G638" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="639">
@@ -19052,23 +19060,23 @@
       </c>
       <c r="B639" t="inlineStr">
         <is>
-          <t>EIA Gasoline Stocks ChangeFEB/21</t>
-        </is>
-      </c>
-      <c r="C639" t="inlineStr"/>
+          <t>EIA Crude Oil Imports ChangeFEB/21</t>
+        </is>
+      </c>
+      <c r="C639" t="inlineStr">
+        <is>
+          <t>0.292M</t>
+        </is>
+      </c>
       <c r="D639" t="inlineStr">
         <is>
-          <t>-0.151M</t>
-        </is>
-      </c>
-      <c r="E639" t="inlineStr">
-        <is>
-          <t>-1.30M</t>
-        </is>
-      </c>
+          <t>-0.961M</t>
+        </is>
+      </c>
+      <c r="E639" t="inlineStr"/>
       <c r="F639" t="inlineStr"/>
       <c r="G639" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="640">
@@ -19079,23 +19087,23 @@
       </c>
       <c r="B640" t="inlineStr">
         <is>
-          <t>EIA Crude Oil Stocks ChangeFEB/21</t>
-        </is>
-      </c>
-      <c r="C640" t="inlineStr"/>
+          <t>EIA Cushing Crude Oil Stocks ChangeFEB/21</t>
+        </is>
+      </c>
+      <c r="C640" t="inlineStr">
+        <is>
+          <t>1.282M</t>
+        </is>
+      </c>
       <c r="D640" t="inlineStr">
         <is>
-          <t>4.633M</t>
-        </is>
-      </c>
-      <c r="E640" t="inlineStr">
-        <is>
-          <t>2.34M</t>
-        </is>
-      </c>
+          <t>1.472M</t>
+        </is>
+      </c>
+      <c r="E640" t="inlineStr"/>
       <c r="F640" t="inlineStr"/>
       <c r="G640" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="641">
@@ -19106,13 +19114,13 @@
       </c>
       <c r="B641" t="inlineStr">
         <is>
-          <t>EIA Distillate Fuel Production ChangeFEB/21</t>
+          <t>EIA Crude Oil Imports ChangeFEB/21</t>
         </is>
       </c>
       <c r="C641" t="inlineStr"/>
       <c r="D641" t="inlineStr">
         <is>
-          <t>0.18M</t>
+          <t>-0.961M</t>
         </is>
       </c>
       <c r="E641" t="inlineStr"/>
@@ -19132,7 +19140,11 @@
           <t>EIA Distillate Stocks ChangeFEB/21</t>
         </is>
       </c>
-      <c r="C642" t="inlineStr"/>
+      <c r="C642" t="inlineStr">
+        <is>
+          <t>3.908M</t>
+        </is>
+      </c>
       <c r="D642" t="inlineStr">
         <is>
           <t>-2.051M</t>
@@ -19159,7 +19171,11 @@
           <t>EIA Gasoline Production ChangeFEB/21</t>
         </is>
       </c>
-      <c r="C643" t="inlineStr"/>
+      <c r="C643" t="inlineStr">
+        <is>
+          <t>-0.02M</t>
+        </is>
+      </c>
       <c r="D643" t="inlineStr">
         <is>
           <t>-0.156M</t>
@@ -19182,7 +19198,11 @@
           <t>EIA Heating Oil Stocks ChangeFEB/21</t>
         </is>
       </c>
-      <c r="C644" t="inlineStr"/>
+      <c r="C644" t="inlineStr">
+        <is>
+          <t>0.134M</t>
+        </is>
+      </c>
       <c r="D644" t="inlineStr">
         <is>
           <t>-0.343M</t>
@@ -19205,7 +19225,11 @@
           <t>EIA Refinery Crude Runs ChangeFEB/21</t>
         </is>
       </c>
-      <c r="C645" t="inlineStr"/>
+      <c r="C645" t="inlineStr">
+        <is>
+          <t>0.317M</t>
+        </is>
+      </c>
       <c r="D645" t="inlineStr">
         <is>
           <t>-0.015M</t>
@@ -19225,27 +19249,23 @@
       </c>
       <c r="B646" t="inlineStr">
         <is>
-          <t>EIA Crude Oil Stocks ChangeFEB/21</t>
+          <t>EIA Distillate Fuel Production ChangeFEB/21</t>
         </is>
       </c>
       <c r="C646" t="inlineStr">
         <is>
-          <t>-2.332M</t>
+          <t>0.439M</t>
         </is>
       </c>
       <c r="D646" t="inlineStr">
         <is>
-          <t>4.633M</t>
-        </is>
-      </c>
-      <c r="E646" t="inlineStr">
-        <is>
-          <t>2.54M</t>
-        </is>
-      </c>
+          <t>0.18M</t>
+        </is>
+      </c>
+      <c r="E646" t="inlineStr"/>
       <c r="F646" t="inlineStr"/>
       <c r="G646" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="647">
@@ -19259,11 +19279,7 @@
           <t>EIA Refinery Crude Runs ChangeFEB/21</t>
         </is>
       </c>
-      <c r="C647" t="inlineStr">
-        <is>
-          <t>0.317M</t>
-        </is>
-      </c>
+      <c r="C647" t="inlineStr"/>
       <c r="D647" t="inlineStr">
         <is>
           <t>-0.015M</t>
@@ -19286,11 +19302,7 @@
           <t>EIA Heating Oil Stocks ChangeFEB/21</t>
         </is>
       </c>
-      <c r="C648" t="inlineStr">
-        <is>
-          <t>0.134M</t>
-        </is>
-      </c>
+      <c r="C648" t="inlineStr"/>
       <c r="D648" t="inlineStr">
         <is>
           <t>-0.343M</t>
@@ -19313,11 +19325,7 @@
           <t>EIA Gasoline Production ChangeFEB/21</t>
         </is>
       </c>
-      <c r="C649" t="inlineStr">
-        <is>
-          <t>-0.02M</t>
-        </is>
-      </c>
+      <c r="C649" t="inlineStr"/>
       <c r="D649" t="inlineStr">
         <is>
           <t>-0.156M</t>
@@ -19340,11 +19348,7 @@
           <t>EIA Distillate Stocks ChangeFEB/21</t>
         </is>
       </c>
-      <c r="C650" t="inlineStr">
-        <is>
-          <t>3.908M</t>
-        </is>
-      </c>
+      <c r="C650" t="inlineStr"/>
       <c r="D650" t="inlineStr">
         <is>
           <t>-2.051M</t>
@@ -19371,11 +19375,7 @@
           <t>EIA Distillate Fuel Production ChangeFEB/21</t>
         </is>
       </c>
-      <c r="C651" t="inlineStr">
-        <is>
-          <t>0.439M</t>
-        </is>
-      </c>
+      <c r="C651" t="inlineStr"/>
       <c r="D651" t="inlineStr">
         <is>
           <t>0.18M</t>
@@ -19395,23 +19395,23 @@
       </c>
       <c r="B652" t="inlineStr">
         <is>
-          <t>EIA Cushing Crude Oil Stocks ChangeFEB/21</t>
-        </is>
-      </c>
-      <c r="C652" t="inlineStr">
-        <is>
-          <t>1.282M</t>
-        </is>
-      </c>
+          <t>EIA Crude Oil Stocks ChangeFEB/21</t>
+        </is>
+      </c>
+      <c r="C652" t="inlineStr"/>
       <c r="D652" t="inlineStr">
         <is>
-          <t>1.472M</t>
-        </is>
-      </c>
-      <c r="E652" t="inlineStr"/>
+          <t>4.633M</t>
+        </is>
+      </c>
+      <c r="E652" t="inlineStr">
+        <is>
+          <t>2.34M</t>
+        </is>
+      </c>
       <c r="F652" t="inlineStr"/>
       <c r="G652" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="653">
@@ -19422,23 +19422,23 @@
       </c>
       <c r="B653" t="inlineStr">
         <is>
-          <t>EIA Crude Oil Imports ChangeFEB/21</t>
-        </is>
-      </c>
-      <c r="C653" t="inlineStr">
-        <is>
-          <t>0.292M</t>
-        </is>
-      </c>
+          <t>EIA Gasoline Stocks ChangeFEB/21</t>
+        </is>
+      </c>
+      <c r="C653" t="inlineStr"/>
       <c r="D653" t="inlineStr">
         <is>
-          <t>-0.961M</t>
-        </is>
-      </c>
-      <c r="E653" t="inlineStr"/>
+          <t>-0.151M</t>
+        </is>
+      </c>
+      <c r="E653" t="inlineStr">
+        <is>
+          <t>-1.30M</t>
+        </is>
+      </c>
       <c r="F653" t="inlineStr"/>
       <c r="G653" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="654">
@@ -19449,27 +19449,19 @@
       </c>
       <c r="B654" t="inlineStr">
         <is>
-          <t>EIA Gasoline Stocks ChangeFEB/21</t>
-        </is>
-      </c>
-      <c r="C654" t="inlineStr">
-        <is>
-          <t>0.369M</t>
-        </is>
-      </c>
+          <t>EIA Cushing Crude Oil Stocks ChangeFEB/21</t>
+        </is>
+      </c>
+      <c r="C654" t="inlineStr"/>
       <c r="D654" t="inlineStr">
         <is>
-          <t>-0.151M</t>
-        </is>
-      </c>
-      <c r="E654" t="inlineStr">
-        <is>
-          <t>-1.30M</t>
-        </is>
-      </c>
+          <t>1.472M</t>
+        </is>
+      </c>
+      <c r="E654" t="inlineStr"/>
       <c r="F654" t="inlineStr"/>
       <c r="G654" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="655">
@@ -19480,19 +19472,27 @@
       </c>
       <c r="B655" t="inlineStr">
         <is>
-          <t>EIA Crude Oil Imports ChangeFEB/21</t>
-        </is>
-      </c>
-      <c r="C655" t="inlineStr"/>
+          <t>EIA Crude Oil Stocks ChangeFEB/21</t>
+        </is>
+      </c>
+      <c r="C655" t="inlineStr">
+        <is>
+          <t>-2.332M</t>
+        </is>
+      </c>
       <c r="D655" t="inlineStr">
         <is>
-          <t>-0.961M</t>
-        </is>
-      </c>
-      <c r="E655" t="inlineStr"/>
+          <t>4.633M</t>
+        </is>
+      </c>
+      <c r="E655" t="inlineStr">
+        <is>
+          <t>2.54M</t>
+        </is>
+      </c>
       <c r="F655" t="inlineStr"/>
       <c r="G655" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="656">
@@ -19622,25 +19622,21 @@
       </c>
       <c r="B661" t="inlineStr">
         <is>
-          <t>Building Permits FinalJAN</t>
-        </is>
-      </c>
-      <c r="C661" t="inlineStr"/>
+          <t>7-Year Note Auction</t>
+        </is>
+      </c>
+      <c r="C661" t="inlineStr">
+        <is>
+          <t>4.194%</t>
+        </is>
+      </c>
       <c r="D661" t="inlineStr">
         <is>
-          <t>1.482M</t>
-        </is>
-      </c>
-      <c r="E661" t="inlineStr">
-        <is>
-          <t>1.483M</t>
-        </is>
-      </c>
-      <c r="F661" t="inlineStr">
-        <is>
-          <t>1.483M</t>
-        </is>
-      </c>
+          <t>4.457%</t>
+        </is>
+      </c>
+      <c r="E661" t="inlineStr"/>
+      <c r="F661" t="inlineStr"/>
       <c r="G661" t="n">
         <v>3</v>
       </c>
@@ -19653,25 +19649,17 @@
       </c>
       <c r="B662" t="inlineStr">
         <is>
-          <t>Building Permits MoM FinalJAN</t>
+          <t>7-Year Note Auction</t>
         </is>
       </c>
       <c r="C662" t="inlineStr"/>
       <c r="D662" t="inlineStr">
         <is>
-          <t>-0.7%</t>
-        </is>
-      </c>
-      <c r="E662" t="inlineStr">
-        <is>
-          <t>0.1%</t>
-        </is>
-      </c>
-      <c r="F662" t="inlineStr">
-        <is>
-          <t>0.1%</t>
-        </is>
-      </c>
+          <t>4.457%</t>
+        </is>
+      </c>
+      <c r="E662" t="inlineStr"/>
+      <c r="F662" t="inlineStr"/>
       <c r="G662" t="n">
         <v>3</v>
       </c>
@@ -19684,17 +19672,25 @@
       </c>
       <c r="B663" t="inlineStr">
         <is>
-          <t>7-Year Note Auction</t>
+          <t>Building Permits MoM FinalJAN</t>
         </is>
       </c>
       <c r="C663" t="inlineStr"/>
       <c r="D663" t="inlineStr">
         <is>
-          <t>4.457%</t>
-        </is>
-      </c>
-      <c r="E663" t="inlineStr"/>
-      <c r="F663" t="inlineStr"/>
+          <t>-0.7%</t>
+        </is>
+      </c>
+      <c r="E663" t="inlineStr">
+        <is>
+          <t>0.1%</t>
+        </is>
+      </c>
+      <c r="F663" t="inlineStr">
+        <is>
+          <t>0.1%</t>
+        </is>
+      </c>
       <c r="G663" t="n">
         <v>3</v>
       </c>
@@ -19707,21 +19703,25 @@
       </c>
       <c r="B664" t="inlineStr">
         <is>
-          <t>7-Year Note Auction</t>
-        </is>
-      </c>
-      <c r="C664" t="inlineStr">
-        <is>
-          <t>4.194%</t>
-        </is>
-      </c>
+          <t>Building Permits FinalJAN</t>
+        </is>
+      </c>
+      <c r="C664" t="inlineStr"/>
       <c r="D664" t="inlineStr">
         <is>
-          <t>4.457%</t>
-        </is>
-      </c>
-      <c r="E664" t="inlineStr"/>
-      <c r="F664" t="inlineStr"/>
+          <t>1.482M</t>
+        </is>
+      </c>
+      <c r="E664" t="inlineStr">
+        <is>
+          <t>1.483M</t>
+        </is>
+      </c>
+      <c r="F664" t="inlineStr">
+        <is>
+          <t>1.483M</t>
+        </is>
+      </c>
       <c r="G664" t="n">
         <v>3</v>
       </c>
@@ -20129,27 +20129,27 @@
       </c>
       <c r="B678" t="inlineStr">
         <is>
-          <t>GDP Growth Rate QoQ 2nd EstQ4</t>
+          <t>GDP Price Index QoQ 2nd EstQ4</t>
         </is>
       </c>
       <c r="C678" t="inlineStr"/>
       <c r="D678" t="inlineStr">
         <is>
-          <t>3.1%</t>
+          <t>1.9%</t>
         </is>
       </c>
       <c r="E678" t="inlineStr">
         <is>
-          <t>2.3%</t>
+          <t>2.2%</t>
         </is>
       </c>
       <c r="F678" t="inlineStr">
         <is>
-          <t>2.3%</t>
+          <t>2.2%</t>
         </is>
       </c>
       <c r="G678" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="679">
@@ -20187,27 +20187,27 @@
       </c>
       <c r="B680" t="inlineStr">
         <is>
-          <t>Initial Jobless ClaimsFEB/22</t>
+          <t>GDP Growth Rate QoQ 2nd EstQ4</t>
         </is>
       </c>
       <c r="C680" t="inlineStr"/>
       <c r="D680" t="inlineStr">
         <is>
-          <t>219K</t>
+          <t>3.1%</t>
         </is>
       </c>
       <c r="E680" t="inlineStr">
         <is>
-          <t>221K</t>
+          <t>2.3%</t>
         </is>
       </c>
       <c r="F680" t="inlineStr">
         <is>
-          <t>225.0K</t>
+          <t>2.3%</t>
         </is>
       </c>
       <c r="G680" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="681">
@@ -20218,23 +20218,23 @@
       </c>
       <c r="B681" t="inlineStr">
         <is>
-          <t>Durable Goods Orders Ex Transp MoMJAN</t>
+          <t>Initial Jobless ClaimsFEB/22</t>
         </is>
       </c>
       <c r="C681" t="inlineStr"/>
       <c r="D681" t="inlineStr">
         <is>
-          <t>0.3%</t>
+          <t>219K</t>
         </is>
       </c>
       <c r="E681" t="inlineStr">
         <is>
-          <t>0.3%</t>
+          <t>221K</t>
         </is>
       </c>
       <c r="F681" t="inlineStr">
         <is>
-          <t>0.3%</t>
+          <t>225.0K</t>
         </is>
       </c>
       <c r="G681" t="n">
@@ -20249,13 +20249,13 @@
       </c>
       <c r="B682" t="inlineStr">
         <is>
-          <t>Non Defense Goods Orders Ex AirJAN</t>
+          <t>Durable Goods Orders Ex Transp MoMJAN</t>
         </is>
       </c>
       <c r="C682" t="inlineStr"/>
       <c r="D682" t="inlineStr">
         <is>
-          <t>0.5%</t>
+          <t>0.3%</t>
         </is>
       </c>
       <c r="E682" t="inlineStr">
@@ -20265,11 +20265,11 @@
       </c>
       <c r="F682" t="inlineStr">
         <is>
-          <t>0.4%</t>
+          <t>0.3%</t>
         </is>
       </c>
       <c r="G682" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="683">
@@ -20280,19 +20280,23 @@
       </c>
       <c r="B683" t="inlineStr">
         <is>
-          <t>Jobless Claims 4-week AverageFEB/22</t>
+          <t>Non Defense Goods Orders Ex AirJAN</t>
         </is>
       </c>
       <c r="C683" t="inlineStr"/>
       <c r="D683" t="inlineStr">
         <is>
-          <t>215.25K</t>
-        </is>
-      </c>
-      <c r="E683" t="inlineStr"/>
+          <t>0.5%</t>
+        </is>
+      </c>
+      <c r="E683" t="inlineStr">
+        <is>
+          <t>0.3%</t>
+        </is>
+      </c>
       <c r="F683" t="inlineStr">
         <is>
-          <t>220.0K</t>
+          <t>0.4%</t>
         </is>
       </c>
       <c r="G683" t="n">
@@ -20307,27 +20311,23 @@
       </c>
       <c r="B684" t="inlineStr">
         <is>
-          <t>Durable Goods Orders MoMJAN</t>
+          <t>Jobless Claims 4-week AverageFEB/22</t>
         </is>
       </c>
       <c r="C684" t="inlineStr"/>
       <c r="D684" t="inlineStr">
         <is>
-          <t>-2.2%</t>
-        </is>
-      </c>
-      <c r="E684" t="inlineStr">
-        <is>
-          <t>2%</t>
-        </is>
-      </c>
+          <t>215.25K</t>
+        </is>
+      </c>
+      <c r="E684" t="inlineStr"/>
       <c r="F684" t="inlineStr">
         <is>
-          <t>2.2%</t>
+          <t>220.0K</t>
         </is>
       </c>
       <c r="G684" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="685">
@@ -20338,27 +20338,27 @@
       </c>
       <c r="B685" t="inlineStr">
         <is>
-          <t>Real Consumer Spending QoQ 2nd EstQ4</t>
+          <t>Durable Goods Orders MoMJAN</t>
         </is>
       </c>
       <c r="C685" t="inlineStr"/>
       <c r="D685" t="inlineStr">
         <is>
-          <t>3.7%</t>
+          <t>-2.2%</t>
         </is>
       </c>
       <c r="E685" t="inlineStr">
         <is>
-          <t>4.2%</t>
+          <t>2%</t>
         </is>
       </c>
       <c r="F685" t="inlineStr">
         <is>
-          <t>4.2%</t>
+          <t>2.2%</t>
         </is>
       </c>
       <c r="G685" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="686">
@@ -20369,23 +20369,23 @@
       </c>
       <c r="B686" t="inlineStr">
         <is>
-          <t>PCE Prices QoQ 2nd EstQ4</t>
+          <t>Real Consumer Spending QoQ 2nd EstQ4</t>
         </is>
       </c>
       <c r="C686" t="inlineStr"/>
       <c r="D686" t="inlineStr">
         <is>
-          <t>1.5%</t>
+          <t>3.7%</t>
         </is>
       </c>
       <c r="E686" t="inlineStr">
         <is>
-          <t>2.3%</t>
+          <t>4.2%</t>
         </is>
       </c>
       <c r="F686" t="inlineStr">
         <is>
-          <t>2.3%</t>
+          <t>4.2%</t>
         </is>
       </c>
       <c r="G686" t="n">
@@ -20400,27 +20400,27 @@
       </c>
       <c r="B687" t="inlineStr">
         <is>
-          <t>GDP Price Index QoQ 2nd EstQ4</t>
+          <t>PCE Prices QoQ 2nd EstQ4</t>
         </is>
       </c>
       <c r="C687" t="inlineStr"/>
       <c r="D687" t="inlineStr">
         <is>
-          <t>1.9%</t>
+          <t>1.5%</t>
         </is>
       </c>
       <c r="E687" t="inlineStr">
         <is>
-          <t>2.2%</t>
+          <t>2.3%</t>
         </is>
       </c>
       <c r="F687" t="inlineStr">
         <is>
-          <t>2.2%</t>
+          <t>2.3%</t>
         </is>
       </c>
       <c r="G687" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="688">
@@ -21058,13 +21058,13 @@
       </c>
       <c r="B713" t="inlineStr">
         <is>
-          <t>15-Year Mortgage RateFEB/27</t>
+          <t>30-Year Mortgage RateFEB/27</t>
         </is>
       </c>
       <c r="C713" t="inlineStr"/>
       <c r="D713" t="inlineStr">
         <is>
-          <t>6.04%</t>
+          <t>6.85%</t>
         </is>
       </c>
       <c r="E713" t="inlineStr"/>
@@ -21081,13 +21081,13 @@
       </c>
       <c r="B714" t="inlineStr">
         <is>
-          <t>30-Year Mortgage RateFEB/27</t>
+          <t>15-Year Mortgage RateFEB/27</t>
         </is>
       </c>
       <c r="C714" t="inlineStr"/>
       <c r="D714" t="inlineStr">
         <is>
-          <t>6.85%</t>
+          <t>6.04%</t>
         </is>
       </c>
       <c r="E714" t="inlineStr"/>
@@ -21508,27 +21508,27 @@
       </c>
       <c r="B731" t="inlineStr">
         <is>
-          <t>PCE Price Index YoYJAN</t>
+          <t>Personal Spending MoMJAN</t>
         </is>
       </c>
       <c r="C731" t="inlineStr"/>
       <c r="D731" t="inlineStr">
         <is>
-          <t>2.6%</t>
+          <t>0.7%</t>
         </is>
       </c>
       <c r="E731" t="inlineStr">
         <is>
-          <t>2.5%</t>
+          <t>0.1%</t>
         </is>
       </c>
       <c r="F731" t="inlineStr">
         <is>
-          <t>2.5%</t>
+          <t>0.3%</t>
         </is>
       </c>
       <c r="G731" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="732">
@@ -21570,27 +21570,27 @@
       </c>
       <c r="B733" t="inlineStr">
         <is>
-          <t>Personal Spending MoMJAN</t>
+          <t>PCE Price Index YoYJAN</t>
         </is>
       </c>
       <c r="C733" t="inlineStr"/>
       <c r="D733" t="inlineStr">
         <is>
-          <t>0.7%</t>
+          <t>2.6%</t>
         </is>
       </c>
       <c r="E733" t="inlineStr">
         <is>
-          <t>0.1%</t>
+          <t>2.5%</t>
         </is>
       </c>
       <c r="F733" t="inlineStr">
         <is>
-          <t>0.3%</t>
+          <t>2.5%</t>
         </is>
       </c>
       <c r="G733" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="734">
@@ -21659,27 +21659,27 @@
       </c>
       <c r="B736" t="inlineStr">
         <is>
-          <t>Core PCE Price Index MoMJAN</t>
+          <t>Goods Trade Balance AdvJAN</t>
         </is>
       </c>
       <c r="C736" t="inlineStr"/>
       <c r="D736" t="inlineStr">
         <is>
-          <t>0.2%</t>
+          <t>$-122.11B</t>
         </is>
       </c>
       <c r="E736" t="inlineStr">
         <is>
-          <t>0.3%</t>
+          <t>$-114.7B</t>
         </is>
       </c>
       <c r="F736" t="inlineStr">
         <is>
-          <t>0.4%</t>
+          <t>$ -116.0B</t>
         </is>
       </c>
       <c r="G736" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="737">
@@ -21690,23 +21690,23 @@
       </c>
       <c r="B737" t="inlineStr">
         <is>
-          <t>PCE Price Index MoMJAN</t>
+          <t>Wholesale Inventories MoM AdvJAN</t>
         </is>
       </c>
       <c r="C737" t="inlineStr"/>
       <c r="D737" t="inlineStr">
         <is>
-          <t>0.3%</t>
+          <t>-0.5%</t>
         </is>
       </c>
       <c r="E737" t="inlineStr">
         <is>
-          <t>0.3%</t>
+          <t>0.1%</t>
         </is>
       </c>
       <c r="F737" t="inlineStr">
         <is>
-          <t>0.4%</t>
+          <t>0.2%</t>
         </is>
       </c>
       <c r="G737" t="n">
@@ -21721,27 +21721,27 @@
       </c>
       <c r="B738" t="inlineStr">
         <is>
-          <t>Goods Trade Balance AdvJAN</t>
+          <t>Personal Income MoMJAN</t>
         </is>
       </c>
       <c r="C738" t="inlineStr"/>
       <c r="D738" t="inlineStr">
         <is>
-          <t>$-122.11B</t>
+          <t>0.4%</t>
         </is>
       </c>
       <c r="E738" t="inlineStr">
         <is>
-          <t>$-114.7B</t>
+          <t>0.3%</t>
         </is>
       </c>
       <c r="F738" t="inlineStr">
         <is>
-          <t>$ -116.0B</t>
+          <t>0.3%</t>
         </is>
       </c>
       <c r="G738" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="739">
@@ -21752,23 +21752,23 @@
       </c>
       <c r="B739" t="inlineStr">
         <is>
-          <t>Wholesale Inventories MoM AdvJAN</t>
+          <t>PCE Price Index MoMJAN</t>
         </is>
       </c>
       <c r="C739" t="inlineStr"/>
       <c r="D739" t="inlineStr">
         <is>
-          <t>-0.5%</t>
+          <t>0.3%</t>
         </is>
       </c>
       <c r="E739" t="inlineStr">
         <is>
-          <t>0.1%</t>
+          <t>0.3%</t>
         </is>
       </c>
       <c r="F739" t="inlineStr">
         <is>
-          <t>0.2%</t>
+          <t>0.4%</t>
         </is>
       </c>
       <c r="G739" t="n">
@@ -21783,23 +21783,23 @@
       </c>
       <c r="B740" t="inlineStr">
         <is>
-          <t>Personal Income MoMJAN</t>
+          <t>Core PCE Price Index MoMJAN</t>
         </is>
       </c>
       <c r="C740" t="inlineStr"/>
       <c r="D740" t="inlineStr">
         <is>
+          <t>0.2%</t>
+        </is>
+      </c>
+      <c r="E740" t="inlineStr">
+        <is>
+          <t>0.3%</t>
+        </is>
+      </c>
+      <c r="F740" t="inlineStr">
+        <is>
           <t>0.4%</t>
-        </is>
-      </c>
-      <c r="E740" t="inlineStr">
-        <is>
-          <t>0.3%</t>
-        </is>
-      </c>
-      <c r="F740" t="inlineStr">
-        <is>
-          <t>0.3%</t>
         </is>
       </c>
       <c r="G740" t="n">
@@ -22165,23 +22165,23 @@
       </c>
       <c r="B754" t="inlineStr">
         <is>
-          <t>ISM Manufacturing New OrdersFEB</t>
+          <t>ISM Manufacturing PMIFEB</t>
         </is>
       </c>
       <c r="C754" t="inlineStr"/>
       <c r="D754" t="inlineStr">
         <is>
-          <t>55.1</t>
+          <t>50.9</t>
         </is>
       </c>
       <c r="E754" t="inlineStr"/>
       <c r="F754" t="inlineStr">
         <is>
-          <t>55.4</t>
+          <t>51</t>
         </is>
       </c>
       <c r="G754" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="755">
@@ -22219,23 +22219,23 @@
       </c>
       <c r="B756" t="inlineStr">
         <is>
-          <t>ISM Manufacturing PMIFEB</t>
+          <t>ISM Manufacturing New OrdersFEB</t>
         </is>
       </c>
       <c r="C756" t="inlineStr"/>
       <c r="D756" t="inlineStr">
         <is>
-          <t>50.9</t>
+          <t>55.1</t>
         </is>
       </c>
       <c r="E756" t="inlineStr"/>
       <c r="F756" t="inlineStr">
         <is>
-          <t>51</t>
+          <t>55.4</t>
         </is>
       </c>
       <c r="G756" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="757">
@@ -23254,23 +23254,23 @@
       </c>
       <c r="B797" t="inlineStr">
         <is>
-          <t>ISM Services PMIFEB</t>
+          <t>ISM Services EmploymentFEB</t>
         </is>
       </c>
       <c r="C797" t="inlineStr"/>
       <c r="D797" t="inlineStr">
         <is>
-          <t>52.8</t>
+          <t>52.3</t>
         </is>
       </c>
       <c r="E797" t="inlineStr"/>
       <c r="F797" t="inlineStr">
         <is>
-          <t>52.7</t>
+          <t>52.1</t>
         </is>
       </c>
       <c r="G797" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="798">
@@ -23281,19 +23281,19 @@
       </c>
       <c r="B798" t="inlineStr">
         <is>
-          <t>Factory Orders ex TransportationJAN</t>
+          <t>ISM Services New OrdersFEB</t>
         </is>
       </c>
       <c r="C798" t="inlineStr"/>
       <c r="D798" t="inlineStr">
         <is>
-          <t>0.2%</t>
+          <t>51.3</t>
         </is>
       </c>
       <c r="E798" t="inlineStr"/>
       <c r="F798" t="inlineStr">
         <is>
-          <t>0.3%</t>
+          <t>51.2</t>
         </is>
       </c>
       <c r="G798" t="n">
@@ -23308,19 +23308,19 @@
       </c>
       <c r="B799" t="inlineStr">
         <is>
-          <t>ISM Services Business ActivityFEB</t>
+          <t>ISM Services PricesFEB</t>
         </is>
       </c>
       <c r="C799" t="inlineStr"/>
       <c r="D799" t="inlineStr">
         <is>
-          <t>54.5</t>
+          <t>60.4</t>
         </is>
       </c>
       <c r="E799" t="inlineStr"/>
       <c r="F799" t="inlineStr">
         <is>
-          <t>54.2</t>
+          <t>60.6</t>
         </is>
       </c>
       <c r="G799" t="n">
@@ -23335,19 +23335,19 @@
       </c>
       <c r="B800" t="inlineStr">
         <is>
-          <t>ISM Services PricesFEB</t>
+          <t>ISM Services Business ActivityFEB</t>
         </is>
       </c>
       <c r="C800" t="inlineStr"/>
       <c r="D800" t="inlineStr">
         <is>
-          <t>60.4</t>
+          <t>54.5</t>
         </is>
       </c>
       <c r="E800" t="inlineStr"/>
       <c r="F800" t="inlineStr">
         <is>
-          <t>60.6</t>
+          <t>54.2</t>
         </is>
       </c>
       <c r="G800" t="n">
@@ -23362,19 +23362,19 @@
       </c>
       <c r="B801" t="inlineStr">
         <is>
-          <t>ISM Services New OrdersFEB</t>
+          <t>Factory Orders ex TransportationJAN</t>
         </is>
       </c>
       <c r="C801" t="inlineStr"/>
       <c r="D801" t="inlineStr">
         <is>
-          <t>51.3</t>
+          <t>0.2%</t>
         </is>
       </c>
       <c r="E801" t="inlineStr"/>
       <c r="F801" t="inlineStr">
         <is>
-          <t>51.2</t>
+          <t>0.3%</t>
         </is>
       </c>
       <c r="G801" t="n">
@@ -23389,23 +23389,23 @@
       </c>
       <c r="B802" t="inlineStr">
         <is>
-          <t>ISM Services EmploymentFEB</t>
+          <t>ISM Services PMIFEB</t>
         </is>
       </c>
       <c r="C802" t="inlineStr"/>
       <c r="D802" t="inlineStr">
         <is>
-          <t>52.3</t>
+          <t>52.8</t>
         </is>
       </c>
       <c r="E802" t="inlineStr"/>
       <c r="F802" t="inlineStr">
         <is>
-          <t>52.1</t>
+          <t>52.7</t>
         </is>
       </c>
       <c r="G802" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="803">
@@ -23623,15 +23623,11 @@
       </c>
       <c r="B812" t="inlineStr">
         <is>
-          <t>EIA Refinery Crude Runs ChangeFEB/28</t>
+          <t>EIA Crude Oil Imports ChangeFEB/28</t>
         </is>
       </c>
       <c r="C812" t="inlineStr"/>
-      <c r="D812" t="inlineStr">
-        <is>
-          <t>0.317M</t>
-        </is>
-      </c>
+      <c r="D812" t="inlineStr"/>
       <c r="E812" t="inlineStr"/>
       <c r="F812" t="inlineStr"/>
       <c r="G812" t="n">
@@ -23646,15 +23642,19 @@
       </c>
       <c r="B813" t="inlineStr">
         <is>
-          <t>EIA Crude Oil Imports ChangeFEB/28</t>
+          <t>EIA Gasoline Stocks ChangeFEB/28</t>
         </is>
       </c>
       <c r="C813" t="inlineStr"/>
-      <c r="D813" t="inlineStr"/>
+      <c r="D813" t="inlineStr">
+        <is>
+          <t>0.369M</t>
+        </is>
+      </c>
       <c r="E813" t="inlineStr"/>
       <c r="F813" t="inlineStr"/>
       <c r="G813" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="814">
@@ -23730,19 +23730,19 @@
       </c>
       <c r="B817" t="inlineStr">
         <is>
-          <t>EIA Gasoline Stocks ChangeFEB/28</t>
+          <t>EIA Refinery Crude Runs ChangeFEB/28</t>
         </is>
       </c>
       <c r="C817" t="inlineStr"/>
       <c r="D817" t="inlineStr">
         <is>
-          <t>0.369M</t>
+          <t>0.317M</t>
         </is>
       </c>
       <c r="E817" t="inlineStr"/>
       <c r="F817" t="inlineStr"/>
       <c r="G817" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="818">
@@ -23776,19 +23776,19 @@
       </c>
       <c r="B819" t="inlineStr">
         <is>
-          <t>EIA Crude Oil Stocks ChangeFEB/28</t>
+          <t>EIA Heating Oil Stocks ChangeFEB/28</t>
         </is>
       </c>
       <c r="C819" t="inlineStr"/>
       <c r="D819" t="inlineStr">
         <is>
-          <t>-2.332M</t>
+          <t>0.134M</t>
         </is>
       </c>
       <c r="E819" t="inlineStr"/>
       <c r="F819" t="inlineStr"/>
       <c r="G819" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="820">
@@ -23799,19 +23799,19 @@
       </c>
       <c r="B820" t="inlineStr">
         <is>
-          <t>EIA Heating Oil Stocks ChangeFEB/28</t>
+          <t>EIA Crude Oil Stocks ChangeFEB/28</t>
         </is>
       </c>
       <c r="C820" t="inlineStr"/>
       <c r="D820" t="inlineStr">
         <is>
-          <t>0.134M</t>
+          <t>-2.332M</t>
         </is>
       </c>
       <c r="E820" t="inlineStr"/>
       <c r="F820" t="inlineStr"/>
       <c r="G820" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="821">
@@ -23868,13 +23868,13 @@
       </c>
       <c r="B823" t="inlineStr">
         <is>
-          <t>17-Week Bill Auction</t>
+          <t>Total Vehicle SalesFEB</t>
         </is>
       </c>
       <c r="C823" t="inlineStr"/>
       <c r="D823" t="inlineStr">
         <is>
-          <t>4.200%</t>
+          <t>15.6M</t>
         </is>
       </c>
       <c r="E823" t="inlineStr"/>
@@ -23891,13 +23891,13 @@
       </c>
       <c r="B824" t="inlineStr">
         <is>
-          <t>Total Vehicle SalesFEB</t>
+          <t>17-Week Bill Auction</t>
         </is>
       </c>
       <c r="C824" t="inlineStr"/>
       <c r="D824" t="inlineStr">
         <is>
-          <t>15.6M</t>
+          <t>4.200%</t>
         </is>
       </c>
       <c r="E824" t="inlineStr"/>
@@ -24321,19 +24321,19 @@
       </c>
       <c r="B842" t="inlineStr">
         <is>
-          <t>ExportsJAN</t>
+          <t>ImportsJAN</t>
         </is>
       </c>
       <c r="C842" t="inlineStr"/>
       <c r="D842" t="inlineStr">
         <is>
-          <t>$266.5B</t>
+          <t>$364.9B</t>
         </is>
       </c>
       <c r="E842" t="inlineStr"/>
       <c r="F842" t="inlineStr">
         <is>
-          <t>$273.0B</t>
+          <t>$376.0B</t>
         </is>
       </c>
       <c r="G842" t="n">
@@ -24348,19 +24348,19 @@
       </c>
       <c r="B843" t="inlineStr">
         <is>
-          <t>ImportsJAN</t>
+          <t>Balance of TradeJAN</t>
         </is>
       </c>
       <c r="C843" t="inlineStr"/>
       <c r="D843" t="inlineStr">
         <is>
-          <t>$364.9B</t>
+          <t>$-98.4B</t>
         </is>
       </c>
       <c r="E843" t="inlineStr"/>
       <c r="F843" t="inlineStr">
         <is>
-          <t>$376.0B</t>
+          <t>$-103B</t>
         </is>
       </c>
       <c r="G843" t="n">
@@ -24375,19 +24375,19 @@
       </c>
       <c r="B844" t="inlineStr">
         <is>
-          <t>Balance of TradeJAN</t>
+          <t>ExportsJAN</t>
         </is>
       </c>
       <c r="C844" t="inlineStr"/>
       <c r="D844" t="inlineStr">
         <is>
-          <t>$-98.4B</t>
+          <t>$266.5B</t>
         </is>
       </c>
       <c r="E844" t="inlineStr"/>
       <c r="F844" t="inlineStr">
         <is>
-          <t>$-103B</t>
+          <t>$273.0B</t>
         </is>
       </c>
       <c r="G844" t="n">
@@ -24516,7 +24516,7 @@
       </c>
       <c r="B851" t="inlineStr">
         <is>
-          <t>8-Week Bill Auction</t>
+          <t>4-Week Bill Auction</t>
         </is>
       </c>
       <c r="C851" t="inlineStr"/>
@@ -24535,7 +24535,7 @@
       </c>
       <c r="B852" t="inlineStr">
         <is>
-          <t>4-Week Bill Auction</t>
+          <t>8-Week Bill Auction</t>
         </is>
       </c>
       <c r="C852" t="inlineStr"/>
@@ -24830,17 +24830,21 @@
       </c>
       <c r="B865" t="inlineStr">
         <is>
-          <t>Used Car Prices YoYFEB</t>
+          <t>U-6 Unemployment RateFEB</t>
         </is>
       </c>
       <c r="C865" t="inlineStr"/>
       <c r="D865" t="inlineStr">
         <is>
-          <t>0.8%</t>
+          <t>7.5%</t>
         </is>
       </c>
       <c r="E865" t="inlineStr"/>
-      <c r="F865" t="inlineStr"/>
+      <c r="F865" t="inlineStr">
+        <is>
+          <t>7.6%</t>
+        </is>
+      </c>
       <c r="G865" t="n">
         <v>3</v>
       </c>
@@ -24907,23 +24911,23 @@
       </c>
       <c r="B868" t="inlineStr">
         <is>
-          <t>Non Farm PayrollsFEB</t>
+          <t>Average Hourly Earnings MoMFEB</t>
         </is>
       </c>
       <c r="C868" t="inlineStr"/>
       <c r="D868" t="inlineStr">
         <is>
-          <t>143K</t>
+          <t>0.5%</t>
         </is>
       </c>
       <c r="E868" t="inlineStr"/>
       <c r="F868" t="inlineStr">
         <is>
-          <t>180.0K</t>
+          <t>0.3%</t>
         </is>
       </c>
       <c r="G868" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="869">
@@ -24934,23 +24938,23 @@
       </c>
       <c r="B869" t="inlineStr">
         <is>
-          <t>Unemployment RateFEB</t>
+          <t>Average Hourly Earnings YoYFEB</t>
         </is>
       </c>
       <c r="C869" t="inlineStr"/>
       <c r="D869" t="inlineStr">
         <is>
-          <t>4%</t>
+          <t>4.1%</t>
         </is>
       </c>
       <c r="E869" t="inlineStr"/>
       <c r="F869" t="inlineStr">
         <is>
-          <t>4.0%</t>
+          <t>4.1%</t>
         </is>
       </c>
       <c r="G869" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="870">
@@ -25038,23 +25042,23 @@
       </c>
       <c r="B873" t="inlineStr">
         <is>
-          <t>Average Hourly Earnings YoYFEB</t>
+          <t>Unemployment RateFEB</t>
         </is>
       </c>
       <c r="C873" t="inlineStr"/>
       <c r="D873" t="inlineStr">
         <is>
-          <t>4.1%</t>
+          <t>4%</t>
         </is>
       </c>
       <c r="E873" t="inlineStr"/>
       <c r="F873" t="inlineStr">
         <is>
-          <t>4.1%</t>
+          <t>4.0%</t>
         </is>
       </c>
       <c r="G873" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="874">
@@ -25065,23 +25069,19 @@
       </c>
       <c r="B874" t="inlineStr">
         <is>
-          <t>Average Hourly Earnings MoMFEB</t>
+          <t>Used Car Prices YoYFEB</t>
         </is>
       </c>
       <c r="C874" t="inlineStr"/>
       <c r="D874" t="inlineStr">
         <is>
-          <t>0.5%</t>
+          <t>0.8%</t>
         </is>
       </c>
       <c r="E874" t="inlineStr"/>
-      <c r="F874" t="inlineStr">
-        <is>
-          <t>0.3%</t>
-        </is>
-      </c>
+      <c r="F874" t="inlineStr"/>
       <c r="G874" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="875">
@@ -25200,23 +25200,23 @@
       </c>
       <c r="B879" t="inlineStr">
         <is>
-          <t>U-6 Unemployment RateFEB</t>
+          <t>Non Farm PayrollsFEB</t>
         </is>
       </c>
       <c r="C879" t="inlineStr"/>
       <c r="D879" t="inlineStr">
         <is>
-          <t>7.5%</t>
+          <t>143K</t>
         </is>
       </c>
       <c r="E879" t="inlineStr"/>
       <c r="F879" t="inlineStr">
         <is>
-          <t>7.6%</t>
+          <t>180.0K</t>
         </is>
       </c>
       <c r="G879" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="880">

--- a/Input_data/IST_US_trad_eco_cal_2025-01-01_to_2025-03-09.xlsx
+++ b/Input_data/IST_US_trad_eco_cal_2025-01-01_to_2025-03-09.xlsx
@@ -806,17 +806,17 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>EIA Distillate Fuel Production ChangeDEC/27</t>
+          <t>EIA Crude Oil Imports ChangeDEC/27</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>0.099M</t>
+          <t>0.323M</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>0.178M</t>
+          <t>0.995M</t>
         </is>
       </c>
       <c r="E13" t="inlineStr"/>
@@ -833,27 +833,27 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>EIA Crude Oil Stocks ChangeDEC/27</t>
+          <t>EIA Distillate Stocks ChangeDEC/27</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>-1.178M</t>
+          <t>6.406M</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>-4.237M</t>
+          <t>-1.694M</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>-2.75M</t>
+          <t>-0.1M</t>
         </is>
       </c>
       <c r="F14" t="inlineStr"/>
       <c r="G14" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="15">
@@ -864,17 +864,17 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>EIA Cushing Crude Oil Stocks ChangeDEC/27</t>
+          <t>EIA Refinery Crude Runs ChangeDEC/27</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>-0.142M</t>
+          <t>0.041M</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>-0.32M</t>
+          <t>0.205M</t>
         </is>
       </c>
       <c r="E15" t="inlineStr"/>
@@ -891,27 +891,23 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>EIA Gasoline Stocks ChangeDEC/27</t>
+          <t>EIA Heating Oil Stocks ChangeDEC/27</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>7.717M</t>
+          <t>-0.416M</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>1.63M</t>
-        </is>
-      </c>
-      <c r="E16" t="inlineStr">
-        <is>
-          <t>0.7M</t>
-        </is>
-      </c>
+          <t>-0.062M</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr"/>
       <c r="F16" t="inlineStr"/>
       <c r="G16" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="17">
@@ -922,17 +918,17 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>EIA Gasoline Production ChangeDEC/27</t>
+          <t>EIA Cushing Crude Oil Stocks ChangeDEC/27</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>-0.959M</t>
+          <t>-0.142M</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>0.051M</t>
+          <t>-0.32M</t>
         </is>
       </c>
       <c r="E17" t="inlineStr"/>
@@ -949,23 +945,27 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>EIA Heating Oil Stocks ChangeDEC/27</t>
+          <t>EIA Gasoline Stocks ChangeDEC/27</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>-0.416M</t>
+          <t>7.717M</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>-0.062M</t>
-        </is>
-      </c>
-      <c r="E18" t="inlineStr"/>
+          <t>1.63M</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>0.7M</t>
+        </is>
+      </c>
       <c r="F18" t="inlineStr"/>
       <c r="G18" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="19">
@@ -976,23 +976,27 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>EIA Refinery Crude Runs ChangeDEC/27</t>
+          <t>EIA Crude Oil Stocks ChangeDEC/27</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>0.041M</t>
+          <t>-1.178M</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>0.205M</t>
-        </is>
-      </c>
-      <c r="E19" t="inlineStr"/>
+          <t>-4.237M</t>
+        </is>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>-2.75M</t>
+        </is>
+      </c>
       <c r="F19" t="inlineStr"/>
       <c r="G19" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="20">
@@ -1003,24 +1007,20 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>EIA Distillate Stocks ChangeDEC/27</t>
+          <t>EIA Distillate Fuel Production ChangeDEC/27</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>6.406M</t>
+          <t>0.099M</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>-1.694M</t>
-        </is>
-      </c>
-      <c r="E20" t="inlineStr">
-        <is>
-          <t>-0.1M</t>
-        </is>
-      </c>
+          <t>0.178M</t>
+        </is>
+      </c>
+      <c r="E20" t="inlineStr"/>
       <c r="F20" t="inlineStr"/>
       <c r="G20" t="n">
         <v>3</v>
@@ -1034,17 +1034,17 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>EIA Crude Oil Imports ChangeDEC/27</t>
+          <t>EIA Gasoline Production ChangeDEC/27</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>0.323M</t>
+          <t>-0.959M</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>0.995M</t>
+          <t>0.051M</t>
         </is>
       </c>
       <c r="E21" t="inlineStr"/>
@@ -1223,31 +1223,31 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>ISM Manufacturing PricesDEC</t>
+          <t>ISM Manufacturing PMIDEC</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>52.5</t>
+          <t>49.3</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>50.3</t>
+          <t>48.4</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>51.7</t>
+          <t>48.4</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>50.4</t>
+          <t>48.5</t>
         </is>
       </c>
       <c r="G28" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="29">
@@ -1258,27 +1258,31 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>ISM Manufacturing New OrdersDEC</t>
+          <t>ISM Manufacturing EmploymentDEC</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>52.5</t>
+          <t>45.3</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>50.4</t>
-        </is>
-      </c>
-      <c r="E29" t="inlineStr"/>
+          <t>48.1</t>
+        </is>
+      </c>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t>48</t>
+        </is>
+      </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>50.5</t>
+          <t>48.3</t>
         </is>
       </c>
       <c r="G29" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="30">
@@ -1289,31 +1293,27 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>ISM Manufacturing EmploymentDEC</t>
+          <t>ISM Manufacturing New OrdersDEC</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>45.3</t>
+          <t>52.5</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>48.1</t>
-        </is>
-      </c>
-      <c r="E30" t="inlineStr">
-        <is>
-          <t>48</t>
-        </is>
-      </c>
+          <t>50.4</t>
+        </is>
+      </c>
+      <c r="E30" t="inlineStr"/>
       <c r="F30" t="inlineStr">
         <is>
-          <t>48.3</t>
+          <t>50.5</t>
         </is>
       </c>
       <c r="G30" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="31">
@@ -1324,31 +1324,31 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>ISM Manufacturing PMIDEC</t>
+          <t>ISM Manufacturing PricesDEC</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>49.3</t>
+          <t>52.5</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>48.4</t>
+          <t>50.3</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>48.4</t>
+          <t>51.7</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>48.5</t>
+          <t>50.4</t>
         </is>
       </c>
       <c r="G31" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="32">
@@ -1609,27 +1609,31 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>Factory Orders ex TransportationNOV</t>
+          <t>Factory Orders MoMNOV</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>0.2%</t>
+          <t>-0.4%</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>0.2%</t>
-        </is>
-      </c>
-      <c r="E42" t="inlineStr"/>
+          <t>0.5%</t>
+        </is>
+      </c>
+      <c r="E42" t="inlineStr">
+        <is>
+          <t>-0.3%</t>
+        </is>
+      </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>0.2%</t>
+          <t>0.3%</t>
         </is>
       </c>
       <c r="G42" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="43">
@@ -1640,31 +1644,27 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>Factory Orders MoMNOV</t>
+          <t>Factory Orders ex TransportationNOV</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>-0.4%</t>
+          <t>0.2%</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>0.5%</t>
-        </is>
-      </c>
-      <c r="E43" t="inlineStr">
-        <is>
-          <t>-0.3%</t>
-        </is>
-      </c>
+          <t>0.2%</t>
+        </is>
+      </c>
+      <c r="E43" t="inlineStr"/>
       <c r="F43" t="inlineStr">
         <is>
-          <t>0.3%</t>
+          <t>0.2%</t>
         </is>
       </c>
       <c r="G43" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="44">
@@ -1949,31 +1949,31 @@
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>ISM Services New OrdersDEC</t>
+          <t>ISM Services PMIDEC</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>54.2</t>
+          <t>54.1</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>53.7</t>
+          <t>52.1</t>
         </is>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>54.2</t>
+          <t>53.3</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>54.1</t>
+          <t>54</t>
         </is>
       </c>
       <c r="G54" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="55">
@@ -1984,23 +1984,23 @@
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>ISM Services Business ActivityDEC</t>
+          <t>JOLTs Job QuitsNOV</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>58.2</t>
+          <t>3.065M</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>53.7</t>
+          <t>3.283M</t>
         </is>
       </c>
       <c r="E55" t="inlineStr"/>
       <c r="F55" t="inlineStr">
         <is>
-          <t>54.1</t>
+          <t>3.31M</t>
         </is>
       </c>
       <c r="G55" t="n">
@@ -2015,31 +2015,31 @@
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>JOLTs Job OpeningsNOV</t>
+          <t>ISM Services PricesDEC</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>8.098M</t>
+          <t>64.4</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>7.839M</t>
+          <t>58.2</t>
         </is>
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>7.70M</t>
+          <t>57.5</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>7.69M</t>
+          <t>58.4</t>
         </is>
       </c>
       <c r="G56" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="57">
@@ -2050,27 +2050,27 @@
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>ISM Services EmploymentDEC</t>
+          <t>ISM Services New OrdersDEC</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>51.4</t>
+          <t>54.2</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>51.5</t>
+          <t>53.7</t>
         </is>
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>51.4</t>
+          <t>54.2</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>52</t>
+          <t>54.1</t>
         </is>
       </c>
       <c r="G57" t="n">
@@ -2085,31 +2085,31 @@
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>ISM Services PricesDEC</t>
+          <t>JOLTs Job OpeningsNOV</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>64.4</t>
+          <t>8.098M</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>58.2</t>
+          <t>7.839M</t>
         </is>
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>57.5</t>
+          <t>7.70M</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>58.4</t>
+          <t>7.69M</t>
         </is>
       </c>
       <c r="G58" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="59">
@@ -2120,31 +2120,31 @@
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>ISM Services PMIDEC</t>
+          <t>ISM Services EmploymentDEC</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>54.1</t>
+          <t>51.4</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>52.1</t>
+          <t>51.5</t>
         </is>
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>53.3</t>
+          <t>51.4</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>54</t>
+          <t>52</t>
         </is>
       </c>
       <c r="G59" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="60">
@@ -2155,23 +2155,23 @@
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>JOLTs Job QuitsNOV</t>
+          <t>ISM Services Business ActivityDEC</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>3.065M</t>
+          <t>58.2</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>3.283M</t>
+          <t>53.7</t>
         </is>
       </c>
       <c r="E60" t="inlineStr"/>
       <c r="F60" t="inlineStr">
         <is>
-          <t>3.31M</t>
+          <t>54.1</t>
         </is>
       </c>
       <c r="G60" t="n">
@@ -2441,27 +2441,27 @@
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>Total Vehicle SalesDEC</t>
+          <t>Continuing Jobless ClaimsDEC/28</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>16.8M</t>
+          <t>1867K</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>16.7M</t>
+          <t>1834K</t>
         </is>
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>16.5M</t>
+          <t>1870K</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>16.3M</t>
+          <t>1848K</t>
         </is>
       </c>
       <c r="G70" t="n">
@@ -2476,15 +2476,27 @@
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>Fed Waller Speech</t>
-        </is>
-      </c>
-      <c r="C71" t="inlineStr"/>
-      <c r="D71" t="inlineStr"/>
+          <t>Jobless Claims 4-week AverageJAN/04</t>
+        </is>
+      </c>
+      <c r="C71" t="inlineStr">
+        <is>
+          <t>213K</t>
+        </is>
+      </c>
+      <c r="D71" t="inlineStr">
+        <is>
+          <t>223.25K</t>
+        </is>
+      </c>
       <c r="E71" t="inlineStr"/>
-      <c r="F71" t="inlineStr"/>
+      <c r="F71" t="inlineStr">
+        <is>
+          <t>224K</t>
+        </is>
+      </c>
       <c r="G71" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="72">
@@ -2495,31 +2507,31 @@
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>Initial Jobless ClaimsJAN/04</t>
+          <t>Total Vehicle SalesDEC</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>201K</t>
+          <t>16.8M</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>211K</t>
+          <t>16.7M</t>
         </is>
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>218K</t>
+          <t>16.5M</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>213K</t>
+          <t>16.3M</t>
         </is>
       </c>
       <c r="G72" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="73">
@@ -2530,27 +2542,15 @@
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>Jobless Claims 4-week AverageJAN/04</t>
-        </is>
-      </c>
-      <c r="C73" t="inlineStr">
-        <is>
-          <t>213K</t>
-        </is>
-      </c>
-      <c r="D73" t="inlineStr">
-        <is>
-          <t>223.25K</t>
-        </is>
-      </c>
+          <t>Fed Waller Speech</t>
+        </is>
+      </c>
+      <c r="C73" t="inlineStr"/>
+      <c r="D73" t="inlineStr"/>
       <c r="E73" t="inlineStr"/>
-      <c r="F73" t="inlineStr">
-        <is>
-          <t>224K</t>
-        </is>
-      </c>
+      <c r="F73" t="inlineStr"/>
       <c r="G73" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="74">
@@ -2561,31 +2561,31 @@
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>Continuing Jobless ClaimsDEC/28</t>
+          <t>Initial Jobless ClaimsJAN/04</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>1867K</t>
+          <t>201K</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>1834K</t>
+          <t>211K</t>
         </is>
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>1870K</t>
+          <t>218K</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>1848K</t>
+          <t>213K</t>
         </is>
       </c>
       <c r="G74" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="75">
@@ -2685,27 +2685,23 @@
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>EIA Gasoline Stocks ChangeJAN/03</t>
+          <t>EIA Distillate Fuel Production ChangeJAN/03</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>6.33M</t>
+          <t>-0.167M</t>
         </is>
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>7.717M</t>
-        </is>
-      </c>
-      <c r="E78" t="inlineStr">
-        <is>
-          <t>1.5M</t>
-        </is>
-      </c>
+          <t>0.099M</t>
+        </is>
+      </c>
+      <c r="E78" t="inlineStr"/>
       <c r="F78" t="inlineStr"/>
       <c r="G78" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="79">
@@ -2716,17 +2712,17 @@
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>EIA Gasoline Production ChangeJAN/03</t>
+          <t>EIA Crude Oil Imports ChangeJAN/03</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>-0.081M</t>
+          <t>0.278M</t>
         </is>
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>-0.959M</t>
+          <t>0.323M</t>
         </is>
       </c>
       <c r="E79" t="inlineStr"/>
@@ -2743,23 +2739,27 @@
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>EIA Heating Oil Stocks ChangeJAN/03</t>
+          <t>EIA Crude Oil Stocks ChangeJAN/03</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>-0.632M</t>
+          <t>-0.959M</t>
         </is>
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>-0.416M</t>
-        </is>
-      </c>
-      <c r="E80" t="inlineStr"/>
+          <t>-1.178M</t>
+        </is>
+      </c>
+      <c r="E80" t="inlineStr">
+        <is>
+          <t>-0.6M</t>
+        </is>
+      </c>
       <c r="F80" t="inlineStr"/>
       <c r="G80" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="81">
@@ -2770,24 +2770,20 @@
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>EIA Distillate Stocks ChangeJAN/03</t>
+          <t>EIA Cushing Crude Oil Stocks ChangeJAN/03</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>6.071M</t>
+          <t>-2.502M</t>
         </is>
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>6.406M</t>
-        </is>
-      </c>
-      <c r="E81" t="inlineStr">
-        <is>
-          <t>1M</t>
-        </is>
-      </c>
+          <t>-0.142M</t>
+        </is>
+      </c>
+      <c r="E81" t="inlineStr"/>
       <c r="F81" t="inlineStr"/>
       <c r="G81" t="n">
         <v>3</v>
@@ -2828,17 +2824,17 @@
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>EIA Distillate Fuel Production ChangeJAN/03</t>
+          <t>EIA Heating Oil Stocks ChangeJAN/03</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>-0.167M</t>
+          <t>-0.632M</t>
         </is>
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>0.099M</t>
+          <t>-0.416M</t>
         </is>
       </c>
       <c r="E83" t="inlineStr"/>
@@ -2855,27 +2851,23 @@
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>EIA Crude Oil Stocks ChangeJAN/03</t>
+          <t>EIA Gasoline Production ChangeJAN/03</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
+          <t>-0.081M</t>
+        </is>
+      </c>
+      <c r="D84" t="inlineStr">
+        <is>
           <t>-0.959M</t>
         </is>
       </c>
-      <c r="D84" t="inlineStr">
-        <is>
-          <t>-1.178M</t>
-        </is>
-      </c>
-      <c r="E84" t="inlineStr">
-        <is>
-          <t>-0.6M</t>
-        </is>
-      </c>
+      <c r="E84" t="inlineStr"/>
       <c r="F84" t="inlineStr"/>
       <c r="G84" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="85">
@@ -2886,23 +2878,27 @@
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>EIA Crude Oil Imports ChangeJAN/03</t>
+          <t>EIA Gasoline Stocks ChangeJAN/03</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>0.278M</t>
+          <t>6.33M</t>
         </is>
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>0.323M</t>
-        </is>
-      </c>
-      <c r="E85" t="inlineStr"/>
+          <t>7.717M</t>
+        </is>
+      </c>
+      <c r="E85" t="inlineStr">
+        <is>
+          <t>1.5M</t>
+        </is>
+      </c>
       <c r="F85" t="inlineStr"/>
       <c r="G85" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="86">
@@ -2913,20 +2909,24 @@
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>EIA Cushing Crude Oil Stocks ChangeJAN/03</t>
+          <t>EIA Distillate Stocks ChangeJAN/03</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>-2.502M</t>
+          <t>6.071M</t>
         </is>
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>-0.142M</t>
-        </is>
-      </c>
-      <c r="E86" t="inlineStr"/>
+          <t>6.406M</t>
+        </is>
+      </c>
+      <c r="E86" t="inlineStr">
+        <is>
+          <t>1M</t>
+        </is>
+      </c>
       <c r="F86" t="inlineStr"/>
       <c r="G86" t="n">
         <v>3</v>
@@ -3336,31 +3336,27 @@
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>Average Hourly Earnings MoMDEC</t>
+          <t>U-6 Unemployment Rate</t>
         </is>
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>0.3%</t>
+          <t>7.5%</t>
         </is>
       </c>
       <c r="D103" t="inlineStr">
         <is>
-          <t>0.4%</t>
-        </is>
-      </c>
-      <c r="E103" t="inlineStr">
-        <is>
-          <t>0.3%</t>
-        </is>
-      </c>
+          <t>7.7%</t>
+        </is>
+      </c>
+      <c r="E103" t="inlineStr"/>
       <c r="F103" t="inlineStr">
         <is>
-          <t>0.3%</t>
+          <t>7.9%</t>
         </is>
       </c>
       <c r="G103" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="104">
@@ -3371,31 +3367,31 @@
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>Average Hourly Earnings YoY</t>
+          <t>Average Weekly HoursDEC</t>
         </is>
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>3.9%</t>
+          <t>34.3</t>
         </is>
       </c>
       <c r="D104" t="inlineStr">
         <is>
-          <t>4%</t>
+          <t>34.3</t>
         </is>
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>4%</t>
+          <t>34.3</t>
         </is>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>4%</t>
+          <t>34.3</t>
         </is>
       </c>
       <c r="G104" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="105">
@@ -3406,31 +3402,27 @@
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>Non Farm PayrollsDEC</t>
+          <t>Government PayrollsDEC</t>
         </is>
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>256K</t>
+          <t>33K</t>
         </is>
       </c>
       <c r="D105" t="inlineStr">
         <is>
-          <t>212K</t>
-        </is>
-      </c>
-      <c r="E105" t="inlineStr">
-        <is>
-          <t>160K</t>
-        </is>
-      </c>
+          <t>30K</t>
+        </is>
+      </c>
+      <c r="E105" t="inlineStr"/>
       <c r="F105" t="inlineStr">
         <is>
-          <t>200K</t>
+          <t>15K</t>
         </is>
       </c>
       <c r="G105" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="106">
@@ -3441,27 +3433,31 @@
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>Participation RateDEC</t>
+          <t>Nonfarm Payrolls PrivateDEC</t>
         </is>
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>62.5%</t>
+          <t>223K</t>
         </is>
       </c>
       <c r="D106" t="inlineStr">
         <is>
-          <t>62.5%</t>
-        </is>
-      </c>
-      <c r="E106" t="inlineStr"/>
+          <t>182K</t>
+        </is>
+      </c>
+      <c r="E106" t="inlineStr">
+        <is>
+          <t>135K</t>
+        </is>
+      </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>62.8%</t>
+          <t>185K</t>
         </is>
       </c>
       <c r="G106" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="107">
@@ -3472,31 +3468,31 @@
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>Unemployment RateDEC</t>
+          <t>Manufacturing PayrollsDEC</t>
         </is>
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>4.1%</t>
+          <t>-13K</t>
         </is>
       </c>
       <c r="D107" t="inlineStr">
         <is>
-          <t>4.2%</t>
+          <t>25K</t>
         </is>
       </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t>4.2%</t>
+          <t>5K</t>
         </is>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>4.30%</t>
+          <t>29K</t>
         </is>
       </c>
       <c r="G107" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="108">
@@ -3507,31 +3503,27 @@
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>Nonfarm Payrolls PrivateDEC</t>
+          <t>Participation RateDEC</t>
         </is>
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>223K</t>
+          <t>62.5%</t>
         </is>
       </c>
       <c r="D108" t="inlineStr">
         <is>
-          <t>182K</t>
-        </is>
-      </c>
-      <c r="E108" t="inlineStr">
-        <is>
-          <t>135K</t>
-        </is>
-      </c>
+          <t>62.5%</t>
+        </is>
+      </c>
+      <c r="E108" t="inlineStr"/>
       <c r="F108" t="inlineStr">
         <is>
-          <t>185K</t>
+          <t>62.8%</t>
         </is>
       </c>
       <c r="G108" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="109">
@@ -3542,27 +3534,31 @@
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>Government PayrollsDEC</t>
+          <t>Non Farm PayrollsDEC</t>
         </is>
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>33K</t>
+          <t>256K</t>
         </is>
       </c>
       <c r="D109" t="inlineStr">
         <is>
-          <t>30K</t>
-        </is>
-      </c>
-      <c r="E109" t="inlineStr"/>
+          <t>212K</t>
+        </is>
+      </c>
+      <c r="E109" t="inlineStr">
+        <is>
+          <t>160K</t>
+        </is>
+      </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>15K</t>
+          <t>200K</t>
         </is>
       </c>
       <c r="G109" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="110">
@@ -3573,31 +3569,31 @@
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>Average Weekly HoursDEC</t>
+          <t>Average Hourly Earnings YoY</t>
         </is>
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>34.3</t>
+          <t>3.9%</t>
         </is>
       </c>
       <c r="D110" t="inlineStr">
         <is>
-          <t>34.3</t>
+          <t>4%</t>
         </is>
       </c>
       <c r="E110" t="inlineStr">
         <is>
-          <t>34.3</t>
+          <t>4%</t>
         </is>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>34.3</t>
+          <t>4%</t>
         </is>
       </c>
       <c r="G110" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="111">
@@ -3608,27 +3604,31 @@
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>U-6 Unemployment Rate</t>
+          <t>Average Hourly Earnings MoMDEC</t>
         </is>
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>7.5%</t>
+          <t>0.3%</t>
         </is>
       </c>
       <c r="D111" t="inlineStr">
         <is>
-          <t>7.7%</t>
-        </is>
-      </c>
-      <c r="E111" t="inlineStr"/>
+          <t>0.4%</t>
+        </is>
+      </c>
+      <c r="E111" t="inlineStr">
+        <is>
+          <t>0.3%</t>
+        </is>
+      </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>7.9%</t>
+          <t>0.3%</t>
         </is>
       </c>
       <c r="G111" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="112">
@@ -3639,31 +3639,31 @@
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>Manufacturing PayrollsDEC</t>
+          <t>Unemployment RateDEC</t>
         </is>
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>-13K</t>
+          <t>4.1%</t>
         </is>
       </c>
       <c r="D112" t="inlineStr">
         <is>
-          <t>25K</t>
+          <t>4.2%</t>
         </is>
       </c>
       <c r="E112" t="inlineStr">
         <is>
-          <t>5K</t>
+          <t>4.2%</t>
         </is>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>29K</t>
+          <t>4.30%</t>
         </is>
       </c>
       <c r="G112" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="113">
@@ -3833,19 +3833,11 @@
       </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t>Quarterly Grain Stocks - SoyDEC</t>
-        </is>
-      </c>
-      <c r="C118" t="inlineStr">
-        <is>
-          <t>3.1B</t>
-        </is>
-      </c>
-      <c r="D118" t="inlineStr">
-        <is>
-          <t>0.342B</t>
-        </is>
-      </c>
+          <t>WASDE Report</t>
+        </is>
+      </c>
+      <c r="C118" t="inlineStr"/>
+      <c r="D118" t="inlineStr"/>
       <c r="E118" t="inlineStr"/>
       <c r="F118" t="inlineStr"/>
       <c r="G118" t="n">
@@ -3860,17 +3852,17 @@
       </c>
       <c r="B119" t="inlineStr">
         <is>
-          <t>Quarterly Grain Stocks - CornDEC</t>
+          <t>Quarterly Grain Stocks - WheatDEC</t>
         </is>
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>12.074B</t>
+          <t>1.57B</t>
         </is>
       </c>
       <c r="D119" t="inlineStr">
         <is>
-          <t>1.760B</t>
+          <t>1.98B</t>
         </is>
       </c>
       <c r="E119" t="inlineStr"/>
@@ -3887,17 +3879,17 @@
       </c>
       <c r="B120" t="inlineStr">
         <is>
-          <t>Quarterly Grain Stocks - WheatDEC</t>
+          <t>Quarterly Grain Stocks - CornDEC</t>
         </is>
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>1.57B</t>
+          <t>12.074B</t>
         </is>
       </c>
       <c r="D120" t="inlineStr">
         <is>
-          <t>1.98B</t>
+          <t>1.760B</t>
         </is>
       </c>
       <c r="E120" t="inlineStr"/>
@@ -3914,11 +3906,19 @@
       </c>
       <c r="B121" t="inlineStr">
         <is>
-          <t>WASDE Report</t>
-        </is>
-      </c>
-      <c r="C121" t="inlineStr"/>
-      <c r="D121" t="inlineStr"/>
+          <t>Quarterly Grain Stocks - SoyDEC</t>
+        </is>
+      </c>
+      <c r="C121" t="inlineStr">
+        <is>
+          <t>3.1B</t>
+        </is>
+      </c>
+      <c r="D121" t="inlineStr">
+        <is>
+          <t>0.342B</t>
+        </is>
+      </c>
       <c r="E121" t="inlineStr"/>
       <c r="F121" t="inlineStr"/>
       <c r="G121" t="n">
@@ -4134,23 +4134,27 @@
       </c>
       <c r="B129" t="inlineStr">
         <is>
-          <t>PPIDEC</t>
+          <t>Core PPI YoYDEC</t>
         </is>
       </c>
       <c r="C129" t="inlineStr">
         <is>
-          <t>146.842</t>
+          <t>3.5%</t>
         </is>
       </c>
       <c r="D129" t="inlineStr">
         <is>
-          <t>146.521</t>
-        </is>
-      </c>
-      <c r="E129" t="inlineStr"/>
+          <t>3.5%</t>
+        </is>
+      </c>
+      <c r="E129" t="inlineStr">
+        <is>
+          <t>3.8%</t>
+        </is>
+      </c>
       <c r="F129" t="inlineStr">
         <is>
-          <t>146.8</t>
+          <t>3.5%</t>
         </is>
       </c>
       <c r="G129" t="n">
@@ -4165,31 +4169,27 @@
       </c>
       <c r="B130" t="inlineStr">
         <is>
-          <t>PPI MoMDEC</t>
+          <t>PPI Ex Food, Energy and Trade YoYDEC</t>
         </is>
       </c>
       <c r="C130" t="inlineStr">
         <is>
-          <t>0.2%</t>
+          <t>3.3%</t>
         </is>
       </c>
       <c r="D130" t="inlineStr">
         <is>
-          <t>0.4%</t>
-        </is>
-      </c>
-      <c r="E130" t="inlineStr">
-        <is>
-          <t>0.3%</t>
-        </is>
-      </c>
+          <t>3.5%</t>
+        </is>
+      </c>
+      <c r="E130" t="inlineStr"/>
       <c r="F130" t="inlineStr">
         <is>
-          <t>0.3%</t>
+          <t>3.6%</t>
         </is>
       </c>
       <c r="G130" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="131">
@@ -4200,31 +4200,31 @@
       </c>
       <c r="B131" t="inlineStr">
         <is>
-          <t>Core PPI MoMDEC</t>
+          <t>PPI YoYDEC</t>
         </is>
       </c>
       <c r="C131" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>3.3%</t>
         </is>
       </c>
       <c r="D131" t="inlineStr">
         <is>
-          <t>0.2%</t>
+          <t>3%</t>
         </is>
       </c>
       <c r="E131" t="inlineStr">
         <is>
-          <t>0.3%</t>
+          <t>3.4%</t>
         </is>
       </c>
       <c r="F131" t="inlineStr">
         <is>
-          <t>0.2%</t>
+          <t>3.3%</t>
         </is>
       </c>
       <c r="G131" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="132">
@@ -4235,27 +4235,27 @@
       </c>
       <c r="B132" t="inlineStr">
         <is>
-          <t>PPI YoYDEC</t>
+          <t>PPI Ex Food, Energy and Trade MoMDEC</t>
         </is>
       </c>
       <c r="C132" t="inlineStr">
         <is>
-          <t>3.3%</t>
+          <t>0.1%</t>
         </is>
       </c>
       <c r="D132" t="inlineStr">
         <is>
-          <t>3%</t>
+          <t>0.1%</t>
         </is>
       </c>
       <c r="E132" t="inlineStr">
         <is>
-          <t>3.4%</t>
+          <t>0.3%</t>
         </is>
       </c>
       <c r="F132" t="inlineStr">
         <is>
-          <t>3.3%</t>
+          <t>0.2%</t>
         </is>
       </c>
       <c r="G132" t="n">
@@ -4270,27 +4270,31 @@
       </c>
       <c r="B133" t="inlineStr">
         <is>
-          <t>PPI Ex Food, Energy and Trade YoYDEC</t>
+          <t>PPI MoMDEC</t>
         </is>
       </c>
       <c r="C133" t="inlineStr">
         <is>
-          <t>3.3%</t>
+          <t>0.2%</t>
         </is>
       </c>
       <c r="D133" t="inlineStr">
         <is>
-          <t>3.5%</t>
-        </is>
-      </c>
-      <c r="E133" t="inlineStr"/>
+          <t>0.4%</t>
+        </is>
+      </c>
+      <c r="E133" t="inlineStr">
+        <is>
+          <t>0.3%</t>
+        </is>
+      </c>
       <c r="F133" t="inlineStr">
         <is>
-          <t>3.6%</t>
+          <t>0.3%</t>
         </is>
       </c>
       <c r="G133" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="134">
@@ -4301,27 +4305,23 @@
       </c>
       <c r="B134" t="inlineStr">
         <is>
-          <t>PPI Ex Food, Energy and Trade MoMDEC</t>
+          <t>PPIDEC</t>
         </is>
       </c>
       <c r="C134" t="inlineStr">
         <is>
-          <t>0.1%</t>
+          <t>146.842</t>
         </is>
       </c>
       <c r="D134" t="inlineStr">
         <is>
-          <t>0.1%</t>
-        </is>
-      </c>
-      <c r="E134" t="inlineStr">
-        <is>
-          <t>0.3%</t>
-        </is>
-      </c>
+          <t>146.521</t>
+        </is>
+      </c>
+      <c r="E134" t="inlineStr"/>
       <c r="F134" t="inlineStr">
         <is>
-          <t>0.2%</t>
+          <t>146.8</t>
         </is>
       </c>
       <c r="G134" t="n">
@@ -4336,31 +4336,31 @@
       </c>
       <c r="B135" t="inlineStr">
         <is>
-          <t>Core PPI YoYDEC</t>
+          <t>Core PPI MoMDEC</t>
         </is>
       </c>
       <c r="C135" t="inlineStr">
         <is>
-          <t>3.5%</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="D135" t="inlineStr">
         <is>
-          <t>3.5%</t>
+          <t>0.2%</t>
         </is>
       </c>
       <c r="E135" t="inlineStr">
         <is>
-          <t>3.8%</t>
+          <t>0.3%</t>
         </is>
       </c>
       <c r="F135" t="inlineStr">
         <is>
-          <t>3.5%</t>
+          <t>0.2%</t>
         </is>
       </c>
       <c r="G135" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="136">
@@ -4564,17 +4564,17 @@
       </c>
       <c r="B143" t="inlineStr">
         <is>
-          <t>MBA Mortgage Refinance IndexJAN/10</t>
+          <t>MBA Mortgage ApplicationsJAN/10</t>
         </is>
       </c>
       <c r="C143" t="inlineStr">
         <is>
-          <t>575.6</t>
+          <t>33.3%</t>
         </is>
       </c>
       <c r="D143" t="inlineStr">
         <is>
-          <t>401.1000</t>
+          <t>-3.7%</t>
         </is>
       </c>
       <c r="E143" t="inlineStr"/>
@@ -4591,17 +4591,17 @@
       </c>
       <c r="B144" t="inlineStr">
         <is>
-          <t>MBA Purchase IndexJAN/10</t>
+          <t>MBA Mortgage Market IndexJAN/10</t>
         </is>
       </c>
       <c r="C144" t="inlineStr">
         <is>
-          <t>162</t>
+          <t>224.4</t>
         </is>
       </c>
       <c r="D144" t="inlineStr">
         <is>
-          <t>127.7000</t>
+          <t>168.4</t>
         </is>
       </c>
       <c r="E144" t="inlineStr"/>
@@ -4618,23 +4618,23 @@
       </c>
       <c r="B145" t="inlineStr">
         <is>
-          <t>MBA Mortgage Market IndexJAN/10</t>
+          <t>MBA 30-Year Mortgage RateJAN/10</t>
         </is>
       </c>
       <c r="C145" t="inlineStr">
         <is>
-          <t>224.4</t>
+          <t>7.09%</t>
         </is>
       </c>
       <c r="D145" t="inlineStr">
         <is>
-          <t>168.4</t>
+          <t>6.99%</t>
         </is>
       </c>
       <c r="E145" t="inlineStr"/>
       <c r="F145" t="inlineStr"/>
       <c r="G145" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="146">
@@ -4645,23 +4645,23 @@
       </c>
       <c r="B146" t="inlineStr">
         <is>
-          <t>MBA 30-Year Mortgage RateJAN/10</t>
+          <t>MBA Mortgage Refinance IndexJAN/10</t>
         </is>
       </c>
       <c r="C146" t="inlineStr">
         <is>
-          <t>7.09%</t>
+          <t>575.6</t>
         </is>
       </c>
       <c r="D146" t="inlineStr">
         <is>
-          <t>6.99%</t>
+          <t>401.1000</t>
         </is>
       </c>
       <c r="E146" t="inlineStr"/>
       <c r="F146" t="inlineStr"/>
       <c r="G146" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="147">
@@ -4672,17 +4672,17 @@
       </c>
       <c r="B147" t="inlineStr">
         <is>
-          <t>MBA Mortgage ApplicationsJAN/10</t>
+          <t>MBA Purchase IndexJAN/10</t>
         </is>
       </c>
       <c r="C147" t="inlineStr">
         <is>
-          <t>33.3%</t>
+          <t>162</t>
         </is>
       </c>
       <c r="D147" t="inlineStr">
         <is>
-          <t>-3.7%</t>
+          <t>127.7000</t>
         </is>
       </c>
       <c r="E147" t="inlineStr"/>
@@ -4978,23 +4978,27 @@
       </c>
       <c r="B157" t="inlineStr">
         <is>
-          <t>EIA Heating Oil Stocks ChangeJAN/10</t>
+          <t>EIA Crude Oil Stocks ChangeJAN/10</t>
         </is>
       </c>
       <c r="C157" t="inlineStr">
         <is>
-          <t>0.646M</t>
+          <t>-1.961M</t>
         </is>
       </c>
       <c r="D157" t="inlineStr">
         <is>
-          <t>-0.632M</t>
-        </is>
-      </c>
-      <c r="E157" t="inlineStr"/>
+          <t>-0.959M</t>
+        </is>
+      </c>
+      <c r="E157" t="inlineStr">
+        <is>
+          <t>-1.6M</t>
+        </is>
+      </c>
       <c r="F157" t="inlineStr"/>
       <c r="G157" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="158">
@@ -5005,17 +5009,17 @@
       </c>
       <c r="B158" t="inlineStr">
         <is>
-          <t>EIA Cushing Crude Oil Stocks ChangeJAN/10</t>
+          <t>EIA Distillate Fuel Production ChangeJAN/10</t>
         </is>
       </c>
       <c r="C158" t="inlineStr">
         <is>
-          <t>0.765M</t>
+          <t>-0.021M</t>
         </is>
       </c>
       <c r="D158" t="inlineStr">
         <is>
-          <t>-2.502M</t>
+          <t>-0.167M</t>
         </is>
       </c>
       <c r="E158" t="inlineStr"/>
@@ -5032,27 +5036,23 @@
       </c>
       <c r="B159" t="inlineStr">
         <is>
-          <t>EIA Gasoline Stocks ChangeJAN/10</t>
+          <t>EIA Gasoline Production ChangeJAN/10</t>
         </is>
       </c>
       <c r="C159" t="inlineStr">
         <is>
-          <t>5.852M</t>
+          <t>0.397M</t>
         </is>
       </c>
       <c r="D159" t="inlineStr">
         <is>
-          <t>6.33M</t>
-        </is>
-      </c>
-      <c r="E159" t="inlineStr">
-        <is>
-          <t>2.60M</t>
-        </is>
-      </c>
+          <t>-0.081M</t>
+        </is>
+      </c>
+      <c r="E159" t="inlineStr"/>
       <c r="F159" t="inlineStr"/>
       <c r="G159" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="160">
@@ -5063,24 +5063,20 @@
       </c>
       <c r="B160" t="inlineStr">
         <is>
-          <t>EIA Distillate Stocks ChangeJAN/10</t>
+          <t>EIA Refinery Crude Runs ChangeJAN/10</t>
         </is>
       </c>
       <c r="C160" t="inlineStr">
         <is>
-          <t>3.077M</t>
+          <t>-0.255M</t>
         </is>
       </c>
       <c r="D160" t="inlineStr">
         <is>
-          <t>6.071M</t>
-        </is>
-      </c>
-      <c r="E160" t="inlineStr">
-        <is>
-          <t>1.1M</t>
-        </is>
-      </c>
+          <t>0.045M</t>
+        </is>
+      </c>
+      <c r="E160" t="inlineStr"/>
       <c r="F160" t="inlineStr"/>
       <c r="G160" t="n">
         <v>3</v>
@@ -5094,17 +5090,17 @@
       </c>
       <c r="B161" t="inlineStr">
         <is>
-          <t>EIA Refinery Crude Runs ChangeJAN/10</t>
+          <t>EIA Crude Oil Imports ChangeJAN/10</t>
         </is>
       </c>
       <c r="C161" t="inlineStr">
         <is>
-          <t>-0.255M</t>
+          <t>-1.304M</t>
         </is>
       </c>
       <c r="D161" t="inlineStr">
         <is>
-          <t>0.045M</t>
+          <t>0.278M</t>
         </is>
       </c>
       <c r="E161" t="inlineStr"/>
@@ -5121,22 +5117,22 @@
       </c>
       <c r="B162" t="inlineStr">
         <is>
-          <t>EIA Crude Oil Stocks ChangeJAN/10</t>
+          <t>EIA Gasoline Stocks ChangeJAN/10</t>
         </is>
       </c>
       <c r="C162" t="inlineStr">
         <is>
-          <t>-1.961M</t>
+          <t>5.852M</t>
         </is>
       </c>
       <c r="D162" t="inlineStr">
         <is>
-          <t>-0.959M</t>
+          <t>6.33M</t>
         </is>
       </c>
       <c r="E162" t="inlineStr">
         <is>
-          <t>-1.6M</t>
+          <t>2.60M</t>
         </is>
       </c>
       <c r="F162" t="inlineStr"/>
@@ -5152,17 +5148,17 @@
       </c>
       <c r="B163" t="inlineStr">
         <is>
-          <t>EIA Gasoline Production ChangeJAN/10</t>
+          <t>EIA Heating Oil Stocks ChangeJAN/10</t>
         </is>
       </c>
       <c r="C163" t="inlineStr">
         <is>
-          <t>0.397M</t>
+          <t>0.646M</t>
         </is>
       </c>
       <c r="D163" t="inlineStr">
         <is>
-          <t>-0.081M</t>
+          <t>-0.632M</t>
         </is>
       </c>
       <c r="E163" t="inlineStr"/>
@@ -5179,20 +5175,24 @@
       </c>
       <c r="B164" t="inlineStr">
         <is>
-          <t>EIA Distillate Fuel Production ChangeJAN/10</t>
+          <t>EIA Distillate Stocks ChangeJAN/10</t>
         </is>
       </c>
       <c r="C164" t="inlineStr">
         <is>
-          <t>-0.021M</t>
+          <t>3.077M</t>
         </is>
       </c>
       <c r="D164" t="inlineStr">
         <is>
-          <t>-0.167M</t>
-        </is>
-      </c>
-      <c r="E164" t="inlineStr"/>
+          <t>6.071M</t>
+        </is>
+      </c>
+      <c r="E164" t="inlineStr">
+        <is>
+          <t>1.1M</t>
+        </is>
+      </c>
       <c r="F164" t="inlineStr"/>
       <c r="G164" t="n">
         <v>3</v>
@@ -5206,17 +5206,17 @@
       </c>
       <c r="B165" t="inlineStr">
         <is>
-          <t>EIA Crude Oil Imports ChangeJAN/10</t>
+          <t>EIA Cushing Crude Oil Stocks ChangeJAN/10</t>
         </is>
       </c>
       <c r="C165" t="inlineStr">
         <is>
-          <t>-1.304M</t>
+          <t>0.765M</t>
         </is>
       </c>
       <c r="D165" t="inlineStr">
         <is>
-          <t>0.278M</t>
+          <t>-2.502M</t>
         </is>
       </c>
       <c r="E165" t="inlineStr"/>
@@ -5336,25 +5336,21 @@
       </c>
       <c r="B171" t="inlineStr">
         <is>
-          <t>Export Prices YoYDEC</t>
+          <t>Philly Fed Business ConditionsJAN</t>
         </is>
       </c>
       <c r="C171" t="inlineStr">
         <is>
-          <t>1.8%</t>
+          <t>46.3</t>
         </is>
       </c>
       <c r="D171" t="inlineStr">
         <is>
-          <t>0.9%</t>
+          <t>33.8</t>
         </is>
       </c>
       <c r="E171" t="inlineStr"/>
-      <c r="F171" t="inlineStr">
-        <is>
-          <t>1.9%</t>
-        </is>
-      </c>
+      <c r="F171" t="inlineStr"/>
       <c r="G171" t="n">
         <v>3</v>
       </c>
@@ -5367,27 +5363,31 @@
       </c>
       <c r="B172" t="inlineStr">
         <is>
-          <t>Retail Sales YoYDEC</t>
+          <t>Philadelphia Fed Manufacturing IndexJAN</t>
         </is>
       </c>
       <c r="C172" t="inlineStr">
         <is>
-          <t>3.9%</t>
+          <t>44.3</t>
         </is>
       </c>
       <c r="D172" t="inlineStr">
         <is>
-          <t>4.1%</t>
-        </is>
-      </c>
-      <c r="E172" t="inlineStr"/>
+          <t>-10.9</t>
+        </is>
+      </c>
+      <c r="E172" t="inlineStr">
+        <is>
+          <t>-5</t>
+        </is>
+      </c>
       <c r="F172" t="inlineStr">
         <is>
-          <t>4.0%</t>
+          <t>-10</t>
         </is>
       </c>
       <c r="G172" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="173">
@@ -5398,31 +5398,31 @@
       </c>
       <c r="B173" t="inlineStr">
         <is>
-          <t>Retail Sales MoMDEC</t>
+          <t>Import Prices YoYDEC</t>
         </is>
       </c>
       <c r="C173" t="inlineStr">
         <is>
-          <t>0.4%</t>
+          <t>2.2%</t>
         </is>
       </c>
       <c r="D173" t="inlineStr">
         <is>
-          <t>0.8%</t>
+          <t>1.4%</t>
         </is>
       </c>
       <c r="E173" t="inlineStr">
         <is>
-          <t>0.6%</t>
+          <t>2.1%</t>
         </is>
       </c>
       <c r="F173" t="inlineStr">
         <is>
-          <t>0.5%</t>
+          <t>1.6%</t>
         </is>
       </c>
       <c r="G173" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="174">
@@ -5433,31 +5433,23 @@
       </c>
       <c r="B174" t="inlineStr">
         <is>
-          <t>Export Prices MoMDEC</t>
+          <t>Philly Fed EmploymentJAN</t>
         </is>
       </c>
       <c r="C174" t="inlineStr">
         <is>
-          <t>0.3%</t>
+          <t>11.9</t>
         </is>
       </c>
       <c r="D174" t="inlineStr">
         <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="E174" t="inlineStr">
-        <is>
-          <t>0.2%</t>
-        </is>
-      </c>
-      <c r="F174" t="inlineStr">
-        <is>
-          <t>0.5%</t>
-        </is>
-      </c>
+          <t>4.8</t>
+        </is>
+      </c>
+      <c r="E174" t="inlineStr"/>
+      <c r="F174" t="inlineStr"/>
       <c r="G174" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="175">
@@ -5468,31 +5460,31 @@
       </c>
       <c r="B175" t="inlineStr">
         <is>
-          <t>Initial Jobless ClaimsJAN/11</t>
+          <t>Continuing Jobless ClaimsJAN/04</t>
         </is>
       </c>
       <c r="C175" t="inlineStr">
         <is>
-          <t>217K</t>
+          <t>1859K</t>
         </is>
       </c>
       <c r="D175" t="inlineStr">
         <is>
-          <t>203K</t>
+          <t>1867K</t>
         </is>
       </c>
       <c r="E175" t="inlineStr">
         <is>
-          <t>210K</t>
+          <t>1870K</t>
         </is>
       </c>
       <c r="F175" t="inlineStr">
         <is>
-          <t>209.0K</t>
+          <t>1870.0K</t>
         </is>
       </c>
       <c r="G175" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="176">
@@ -5503,31 +5495,31 @@
       </c>
       <c r="B176" t="inlineStr">
         <is>
-          <t>Retail Sales Ex Autos MoMDEC</t>
+          <t>Retail Sales Ex Gas/Autos MoMDEC</t>
         </is>
       </c>
       <c r="C176" t="inlineStr">
         <is>
+          <t>0.3%</t>
+        </is>
+      </c>
+      <c r="D176" t="inlineStr">
+        <is>
+          <t>0.2%</t>
+        </is>
+      </c>
+      <c r="E176" t="inlineStr">
+        <is>
           <t>0.4%</t>
         </is>
       </c>
-      <c r="D176" t="inlineStr">
-        <is>
-          <t>0.2%</t>
-        </is>
-      </c>
-      <c r="E176" t="inlineStr">
+      <c r="F176" t="inlineStr">
         <is>
           <t>0.4%</t>
         </is>
       </c>
-      <c r="F176" t="inlineStr">
-        <is>
-          <t>0.4%</t>
-        </is>
-      </c>
       <c r="G176" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="177">
@@ -5538,17 +5530,17 @@
       </c>
       <c r="B177" t="inlineStr">
         <is>
-          <t>Philly Fed Prices PaidJAN</t>
+          <t>Philly Fed New OrdersJAN</t>
         </is>
       </c>
       <c r="C177" t="inlineStr">
         <is>
-          <t>31.90</t>
+          <t>42.9</t>
         </is>
       </c>
       <c r="D177" t="inlineStr">
         <is>
-          <t>26.60</t>
+          <t>-3.6</t>
         </is>
       </c>
       <c r="E177" t="inlineStr"/>
@@ -5565,21 +5557,25 @@
       </c>
       <c r="B178" t="inlineStr">
         <is>
-          <t>Philly Fed Business ConditionsJAN</t>
+          <t>Jobless Claims 4-week AverageJAN/11</t>
         </is>
       </c>
       <c r="C178" t="inlineStr">
         <is>
-          <t>46.3</t>
+          <t>212.75K</t>
         </is>
       </c>
       <c r="D178" t="inlineStr">
         <is>
-          <t>33.8</t>
+          <t>213.5K</t>
         </is>
       </c>
       <c r="E178" t="inlineStr"/>
-      <c r="F178" t="inlineStr"/>
+      <c r="F178" t="inlineStr">
+        <is>
+          <t>215.0K</t>
+        </is>
+      </c>
       <c r="G178" t="n">
         <v>3</v>
       </c>
@@ -5592,23 +5588,31 @@
       </c>
       <c r="B179" t="inlineStr">
         <is>
-          <t>Philly Fed CAPEX IndexJAN</t>
+          <t>Import Prices MoMDEC</t>
         </is>
       </c>
       <c r="C179" t="inlineStr">
         <is>
-          <t>39.00</t>
+          <t>0.1%</t>
         </is>
       </c>
       <c r="D179" t="inlineStr">
         <is>
-          <t>22.20</t>
-        </is>
-      </c>
-      <c r="E179" t="inlineStr"/>
-      <c r="F179" t="inlineStr"/>
+          <t>0.1%</t>
+        </is>
+      </c>
+      <c r="E179" t="inlineStr">
+        <is>
+          <t>0.1%</t>
+        </is>
+      </c>
+      <c r="F179" t="inlineStr">
+        <is>
+          <t>0.1%</t>
+        </is>
+      </c>
       <c r="G179" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="180">
@@ -5619,31 +5623,23 @@
       </c>
       <c r="B180" t="inlineStr">
         <is>
-          <t>Import Prices MoMDEC</t>
+          <t>Philly Fed Prices PaidJAN</t>
         </is>
       </c>
       <c r="C180" t="inlineStr">
         <is>
-          <t>0.1%</t>
+          <t>31.90</t>
         </is>
       </c>
       <c r="D180" t="inlineStr">
         <is>
-          <t>0.1%</t>
-        </is>
-      </c>
-      <c r="E180" t="inlineStr">
-        <is>
-          <t>0.1%</t>
-        </is>
-      </c>
-      <c r="F180" t="inlineStr">
-        <is>
-          <t>0.1%</t>
-        </is>
-      </c>
+          <t>26.60</t>
+        </is>
+      </c>
+      <c r="E180" t="inlineStr"/>
+      <c r="F180" t="inlineStr"/>
       <c r="G180" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="181">
@@ -5654,27 +5650,31 @@
       </c>
       <c r="B181" t="inlineStr">
         <is>
-          <t>Jobless Claims 4-week AverageJAN/11</t>
+          <t>Retail Sales Ex Autos MoMDEC</t>
         </is>
       </c>
       <c r="C181" t="inlineStr">
         <is>
-          <t>212.75K</t>
+          <t>0.4%</t>
         </is>
       </c>
       <c r="D181" t="inlineStr">
         <is>
-          <t>213.5K</t>
-        </is>
-      </c>
-      <c r="E181" t="inlineStr"/>
+          <t>0.2%</t>
+        </is>
+      </c>
+      <c r="E181" t="inlineStr">
+        <is>
+          <t>0.4%</t>
+        </is>
+      </c>
       <c r="F181" t="inlineStr">
         <is>
-          <t>215.0K</t>
+          <t>0.4%</t>
         </is>
       </c>
       <c r="G181" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="182">
@@ -5685,23 +5685,31 @@
       </c>
       <c r="B182" t="inlineStr">
         <is>
-          <t>Philly Fed New OrdersJAN</t>
+          <t>Initial Jobless ClaimsJAN/11</t>
         </is>
       </c>
       <c r="C182" t="inlineStr">
         <is>
-          <t>42.9</t>
+          <t>217K</t>
         </is>
       </c>
       <c r="D182" t="inlineStr">
         <is>
-          <t>-3.6</t>
-        </is>
-      </c>
-      <c r="E182" t="inlineStr"/>
-      <c r="F182" t="inlineStr"/>
+          <t>203K</t>
+        </is>
+      </c>
+      <c r="E182" t="inlineStr">
+        <is>
+          <t>210K</t>
+        </is>
+      </c>
+      <c r="F182" t="inlineStr">
+        <is>
+          <t>209.0K</t>
+        </is>
+      </c>
       <c r="G182" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="183">
@@ -5712,7 +5720,7 @@
       </c>
       <c r="B183" t="inlineStr">
         <is>
-          <t>Retail Sales Ex Gas/Autos MoMDEC</t>
+          <t>Export Prices MoMDEC</t>
         </is>
       </c>
       <c r="C183" t="inlineStr">
@@ -5722,21 +5730,21 @@
       </c>
       <c r="D183" t="inlineStr">
         <is>
+          <t>0%</t>
+        </is>
+      </c>
+      <c r="E183" t="inlineStr">
+        <is>
           <t>0.2%</t>
         </is>
       </c>
-      <c r="E183" t="inlineStr">
-        <is>
-          <t>0.4%</t>
-        </is>
-      </c>
       <c r="F183" t="inlineStr">
         <is>
-          <t>0.4%</t>
+          <t>0.5%</t>
         </is>
       </c>
       <c r="G183" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="184">
@@ -5747,31 +5755,31 @@
       </c>
       <c r="B184" t="inlineStr">
         <is>
-          <t>Continuing Jobless ClaimsJAN/04</t>
+          <t>Retail Sales MoMDEC</t>
         </is>
       </c>
       <c r="C184" t="inlineStr">
         <is>
-          <t>1859K</t>
+          <t>0.4%</t>
         </is>
       </c>
       <c r="D184" t="inlineStr">
         <is>
-          <t>1867K</t>
+          <t>0.8%</t>
         </is>
       </c>
       <c r="E184" t="inlineStr">
         <is>
-          <t>1870K</t>
+          <t>0.6%</t>
         </is>
       </c>
       <c r="F184" t="inlineStr">
         <is>
-          <t>1870.0K</t>
+          <t>0.5%</t>
         </is>
       </c>
       <c r="G184" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="185">
@@ -5782,21 +5790,25 @@
       </c>
       <c r="B185" t="inlineStr">
         <is>
-          <t>Philly Fed EmploymentJAN</t>
+          <t>Retail Sales YoYDEC</t>
         </is>
       </c>
       <c r="C185" t="inlineStr">
         <is>
-          <t>11.9</t>
+          <t>3.9%</t>
         </is>
       </c>
       <c r="D185" t="inlineStr">
         <is>
-          <t>4.8</t>
+          <t>4.1%</t>
         </is>
       </c>
       <c r="E185" t="inlineStr"/>
-      <c r="F185" t="inlineStr"/>
+      <c r="F185" t="inlineStr">
+        <is>
+          <t>4.0%</t>
+        </is>
+      </c>
       <c r="G185" t="n">
         <v>3</v>
       </c>
@@ -5809,27 +5821,23 @@
       </c>
       <c r="B186" t="inlineStr">
         <is>
-          <t>Import Prices YoYDEC</t>
+          <t>Export Prices YoYDEC</t>
         </is>
       </c>
       <c r="C186" t="inlineStr">
         <is>
-          <t>2.2%</t>
+          <t>1.8%</t>
         </is>
       </c>
       <c r="D186" t="inlineStr">
         <is>
-          <t>1.4%</t>
-        </is>
-      </c>
-      <c r="E186" t="inlineStr">
-        <is>
-          <t>2.1%</t>
-        </is>
-      </c>
+          <t>0.9%</t>
+        </is>
+      </c>
+      <c r="E186" t="inlineStr"/>
       <c r="F186" t="inlineStr">
         <is>
-          <t>1.6%</t>
+          <t>1.9%</t>
         </is>
       </c>
       <c r="G186" t="n">
@@ -5844,31 +5852,23 @@
       </c>
       <c r="B187" t="inlineStr">
         <is>
-          <t>Philadelphia Fed Manufacturing IndexJAN</t>
+          <t>Philly Fed CAPEX IndexJAN</t>
         </is>
       </c>
       <c r="C187" t="inlineStr">
         <is>
-          <t>44.3</t>
+          <t>39.00</t>
         </is>
       </c>
       <c r="D187" t="inlineStr">
         <is>
-          <t>-10.9</t>
-        </is>
-      </c>
-      <c r="E187" t="inlineStr">
-        <is>
-          <t>-5</t>
-        </is>
-      </c>
-      <c r="F187" t="inlineStr">
-        <is>
-          <t>-10</t>
-        </is>
-      </c>
+          <t>22.20</t>
+        </is>
+      </c>
+      <c r="E187" t="inlineStr"/>
+      <c r="F187" t="inlineStr"/>
       <c r="G187" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="188">
@@ -6015,17 +6015,17 @@
       </c>
       <c r="B192" t="inlineStr">
         <is>
-          <t>4-Week Bill Auction</t>
+          <t>8-Week Bill Auction</t>
         </is>
       </c>
       <c r="C192" t="inlineStr">
         <is>
+          <t>4.235%</t>
+        </is>
+      </c>
+      <c r="D192" t="inlineStr">
+        <is>
           <t>4.240%</t>
-        </is>
-      </c>
-      <c r="D192" t="inlineStr">
-        <is>
-          <t>4.245%</t>
         </is>
       </c>
       <c r="E192" t="inlineStr"/>
@@ -6042,17 +6042,17 @@
       </c>
       <c r="B193" t="inlineStr">
         <is>
-          <t>8-Week Bill Auction</t>
+          <t>4-Week Bill Auction</t>
         </is>
       </c>
       <c r="C193" t="inlineStr">
         <is>
-          <t>4.235%</t>
+          <t>4.240%</t>
         </is>
       </c>
       <c r="D193" t="inlineStr">
         <is>
-          <t>4.240%</t>
+          <t>4.245%</t>
         </is>
       </c>
       <c r="E193" t="inlineStr"/>
@@ -6503,17 +6503,17 @@
       </c>
       <c r="B208" t="inlineStr">
         <is>
-          <t>Foreign Bond InvestmentNOV</t>
+          <t>Overall Net Capital FlowsNOV</t>
         </is>
       </c>
       <c r="C208" t="inlineStr">
         <is>
-          <t>$-15.8B</t>
+          <t>$159.9B</t>
         </is>
       </c>
       <c r="D208" t="inlineStr">
         <is>
-          <t>$92B</t>
+          <t>$201.8B</t>
         </is>
       </c>
       <c r="E208" t="inlineStr"/>
@@ -6530,27 +6530,23 @@
       </c>
       <c r="B209" t="inlineStr">
         <is>
-          <t>Net Long-term TIC FlowsNOV</t>
+          <t>Foreign Bond InvestmentNOV</t>
         </is>
       </c>
       <c r="C209" t="inlineStr">
         <is>
-          <t>$79B</t>
+          <t>$-15.8B</t>
         </is>
       </c>
       <c r="D209" t="inlineStr">
         <is>
-          <t>$159.1B</t>
-        </is>
-      </c>
-      <c r="E209" t="inlineStr">
-        <is>
-          <t>$159.9B</t>
-        </is>
-      </c>
+          <t>$92B</t>
+        </is>
+      </c>
+      <c r="E209" t="inlineStr"/>
       <c r="F209" t="inlineStr"/>
       <c r="G209" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="210">
@@ -6561,23 +6557,27 @@
       </c>
       <c r="B210" t="inlineStr">
         <is>
-          <t>Overall Net Capital FlowsNOV</t>
+          <t>Net Long-term TIC FlowsNOV</t>
         </is>
       </c>
       <c r="C210" t="inlineStr">
         <is>
+          <t>$79B</t>
+        </is>
+      </c>
+      <c r="D210" t="inlineStr">
+        <is>
+          <t>$159.1B</t>
+        </is>
+      </c>
+      <c r="E210" t="inlineStr">
+        <is>
           <t>$159.9B</t>
         </is>
       </c>
-      <c r="D210" t="inlineStr">
-        <is>
-          <t>$201.8B</t>
-        </is>
-      </c>
-      <c r="E210" t="inlineStr"/>
       <c r="F210" t="inlineStr"/>
       <c r="G210" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="211">
@@ -7241,20 +7241,24 @@
       </c>
       <c r="B234" t="inlineStr">
         <is>
-          <t>EIA Crude Oil Imports ChangeJAN/17</t>
+          <t>EIA Distillate Stocks ChangeJAN/17</t>
         </is>
       </c>
       <c r="C234" t="inlineStr">
         <is>
-          <t>0.184M</t>
+          <t>-3.07M</t>
         </is>
       </c>
       <c r="D234" t="inlineStr">
         <is>
-          <t>-1.304M</t>
-        </is>
-      </c>
-      <c r="E234" t="inlineStr"/>
+          <t>3.077M</t>
+        </is>
+      </c>
+      <c r="E234" t="inlineStr">
+        <is>
+          <t>0.6M</t>
+        </is>
+      </c>
       <c r="F234" t="inlineStr"/>
       <c r="G234" t="n">
         <v>3</v>
@@ -7268,17 +7272,17 @@
       </c>
       <c r="B235" t="inlineStr">
         <is>
-          <t>EIA Gasoline Production ChangeJAN/17</t>
+          <t>EIA Heating Oil Stocks ChangeJAN/17</t>
         </is>
       </c>
       <c r="C235" t="inlineStr">
         <is>
-          <t>-0.043M</t>
+          <t>0.068M</t>
         </is>
       </c>
       <c r="D235" t="inlineStr">
         <is>
-          <t>0.397M</t>
+          <t>0.646M</t>
         </is>
       </c>
       <c r="E235" t="inlineStr"/>
@@ -7295,23 +7299,27 @@
       </c>
       <c r="B236" t="inlineStr">
         <is>
-          <t>EIA Cushing Crude Oil Stocks ChangeJAN/17</t>
+          <t>EIA Crude Oil Stocks ChangeJAN/17</t>
         </is>
       </c>
       <c r="C236" t="inlineStr">
         <is>
-          <t>-0.148M</t>
+          <t>-1.017M</t>
         </is>
       </c>
       <c r="D236" t="inlineStr">
         <is>
-          <t>0.765M</t>
-        </is>
-      </c>
-      <c r="E236" t="inlineStr"/>
+          <t>-1.962M</t>
+        </is>
+      </c>
+      <c r="E236" t="inlineStr">
+        <is>
+          <t>-2.1M</t>
+        </is>
+      </c>
       <c r="F236" t="inlineStr"/>
       <c r="G236" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="237">
@@ -7322,17 +7330,17 @@
       </c>
       <c r="B237" t="inlineStr">
         <is>
-          <t>30-Year Mortgage RateJAN/23</t>
+          <t>15-Year Mortgage RateJAN/23</t>
         </is>
       </c>
       <c r="C237" t="inlineStr">
         <is>
-          <t>6.96%</t>
+          <t>6.16%</t>
         </is>
       </c>
       <c r="D237" t="inlineStr">
         <is>
-          <t>7.04%</t>
+          <t>6.27%</t>
         </is>
       </c>
       <c r="E237" t="inlineStr"/>
@@ -7349,23 +7357,27 @@
       </c>
       <c r="B238" t="inlineStr">
         <is>
-          <t>EIA Distillate Fuel Production ChangeJAN/17</t>
+          <t>EIA Gasoline Stocks ChangeJAN/17</t>
         </is>
       </c>
       <c r="C238" t="inlineStr">
         <is>
-          <t>-0.473M</t>
+          <t>2.332M</t>
         </is>
       </c>
       <c r="D238" t="inlineStr">
         <is>
-          <t>-0.021M</t>
-        </is>
-      </c>
-      <c r="E238" t="inlineStr"/>
+          <t>5.852M</t>
+        </is>
+      </c>
+      <c r="E238" t="inlineStr">
+        <is>
+          <t>2.5M</t>
+        </is>
+      </c>
       <c r="F238" t="inlineStr"/>
       <c r="G238" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="239">
@@ -7376,17 +7388,17 @@
       </c>
       <c r="B239" t="inlineStr">
         <is>
-          <t>EIA Refinery Crude Runs ChangeJAN/17</t>
+          <t>EIA Distillate Fuel Production ChangeJAN/17</t>
         </is>
       </c>
       <c r="C239" t="inlineStr">
         <is>
-          <t>-1.125M</t>
+          <t>-0.473M</t>
         </is>
       </c>
       <c r="D239" t="inlineStr">
         <is>
-          <t>-0.255M</t>
+          <t>-0.021M</t>
         </is>
       </c>
       <c r="E239" t="inlineStr"/>
@@ -7403,27 +7415,23 @@
       </c>
       <c r="B240" t="inlineStr">
         <is>
-          <t>EIA Gasoline Stocks ChangeJAN/17</t>
+          <t>30-Year Mortgage RateJAN/23</t>
         </is>
       </c>
       <c r="C240" t="inlineStr">
         <is>
-          <t>2.332M</t>
+          <t>6.96%</t>
         </is>
       </c>
       <c r="D240" t="inlineStr">
         <is>
-          <t>5.852M</t>
-        </is>
-      </c>
-      <c r="E240" t="inlineStr">
-        <is>
-          <t>2.5M</t>
-        </is>
-      </c>
+          <t>7.04%</t>
+        </is>
+      </c>
+      <c r="E240" t="inlineStr"/>
       <c r="F240" t="inlineStr"/>
       <c r="G240" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="241">
@@ -7434,17 +7442,17 @@
       </c>
       <c r="B241" t="inlineStr">
         <is>
-          <t>15-Year Mortgage RateJAN/23</t>
+          <t>EIA Cushing Crude Oil Stocks ChangeJAN/17</t>
         </is>
       </c>
       <c r="C241" t="inlineStr">
         <is>
-          <t>6.16%</t>
+          <t>-0.148M</t>
         </is>
       </c>
       <c r="D241" t="inlineStr">
         <is>
-          <t>6.27%</t>
+          <t>0.765M</t>
         </is>
       </c>
       <c r="E241" t="inlineStr"/>
@@ -7461,27 +7469,23 @@
       </c>
       <c r="B242" t="inlineStr">
         <is>
-          <t>EIA Crude Oil Stocks ChangeJAN/17</t>
+          <t>EIA Gasoline Production ChangeJAN/17</t>
         </is>
       </c>
       <c r="C242" t="inlineStr">
         <is>
-          <t>-1.017M</t>
+          <t>-0.043M</t>
         </is>
       </c>
       <c r="D242" t="inlineStr">
         <is>
-          <t>-1.962M</t>
-        </is>
-      </c>
-      <c r="E242" t="inlineStr">
-        <is>
-          <t>-2.1M</t>
-        </is>
-      </c>
+          <t>0.397M</t>
+        </is>
+      </c>
+      <c r="E242" t="inlineStr"/>
       <c r="F242" t="inlineStr"/>
       <c r="G242" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="243">
@@ -7492,17 +7496,17 @@
       </c>
       <c r="B243" t="inlineStr">
         <is>
-          <t>EIA Heating Oil Stocks ChangeJAN/17</t>
+          <t>EIA Crude Oil Imports ChangeJAN/17</t>
         </is>
       </c>
       <c r="C243" t="inlineStr">
         <is>
-          <t>0.068M</t>
+          <t>0.184M</t>
         </is>
       </c>
       <c r="D243" t="inlineStr">
         <is>
-          <t>0.646M</t>
+          <t>-1.304M</t>
         </is>
       </c>
       <c r="E243" t="inlineStr"/>
@@ -7519,24 +7523,20 @@
       </c>
       <c r="B244" t="inlineStr">
         <is>
-          <t>EIA Distillate Stocks ChangeJAN/17</t>
+          <t>EIA Refinery Crude Runs ChangeJAN/17</t>
         </is>
       </c>
       <c r="C244" t="inlineStr">
         <is>
-          <t>-3.07M</t>
+          <t>-1.125M</t>
         </is>
       </c>
       <c r="D244" t="inlineStr">
         <is>
-          <t>3.077M</t>
-        </is>
-      </c>
-      <c r="E244" t="inlineStr">
-        <is>
-          <t>0.6M</t>
-        </is>
-      </c>
+          <t>-0.255M</t>
+        </is>
+      </c>
+      <c r="E244" t="inlineStr"/>
       <c r="F244" t="inlineStr"/>
       <c r="G244" t="n">
         <v>3</v>
@@ -7705,31 +7705,31 @@
       </c>
       <c r="B250" t="inlineStr">
         <is>
-          <t>Michigan Inflation Expectations FinalJAN</t>
+          <t>Michigan Consumer Sentiment FinalJAN</t>
         </is>
       </c>
       <c r="C250" t="inlineStr">
         <is>
-          <t>3.3%</t>
+          <t>71.1</t>
         </is>
       </c>
       <c r="D250" t="inlineStr">
         <is>
-          <t>2.8%</t>
+          <t>74.0</t>
         </is>
       </c>
       <c r="E250" t="inlineStr">
         <is>
-          <t>3.3%</t>
+          <t>73.2</t>
         </is>
       </c>
       <c r="F250" t="inlineStr">
         <is>
-          <t>3.3%</t>
+          <t>73.2</t>
         </is>
       </c>
       <c r="G250" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="251">
@@ -7740,31 +7740,27 @@
       </c>
       <c r="B251" t="inlineStr">
         <is>
-          <t>Michigan Current Conditions FinalJAN</t>
+          <t>Existing Home Sales MoMDEC</t>
         </is>
       </c>
       <c r="C251" t="inlineStr">
         <is>
-          <t>74.0</t>
+          <t>2.2%</t>
         </is>
       </c>
       <c r="D251" t="inlineStr">
         <is>
-          <t>75.1</t>
-        </is>
-      </c>
-      <c r="E251" t="inlineStr">
-        <is>
-          <t>77.9</t>
-        </is>
-      </c>
+          <t>4.8%</t>
+        </is>
+      </c>
+      <c r="E251" t="inlineStr"/>
       <c r="F251" t="inlineStr">
         <is>
-          <t>77.9</t>
+          <t>0.3%</t>
         </is>
       </c>
       <c r="G251" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="252">
@@ -7775,27 +7771,27 @@
       </c>
       <c r="B252" t="inlineStr">
         <is>
-          <t>Michigan 5 Year Inflation Expectations FinalJAN</t>
+          <t>Michigan Consumer Expectations FinalJAN</t>
         </is>
       </c>
       <c r="C252" t="inlineStr">
         <is>
-          <t>3.2%</t>
+          <t>69.3</t>
         </is>
       </c>
       <c r="D252" t="inlineStr">
         <is>
-          <t>3%</t>
+          <t>73.3</t>
         </is>
       </c>
       <c r="E252" t="inlineStr">
         <is>
-          <t>3.3%</t>
+          <t>70.2</t>
         </is>
       </c>
       <c r="F252" t="inlineStr">
         <is>
-          <t>3.3%</t>
+          <t>70.2</t>
         </is>
       </c>
       <c r="G252" t="n">
@@ -7810,31 +7806,31 @@
       </c>
       <c r="B253" t="inlineStr">
         <is>
-          <t>Existing Home SalesDEC</t>
+          <t>Michigan Inflation Expectations FinalJAN</t>
         </is>
       </c>
       <c r="C253" t="inlineStr">
         <is>
-          <t>4.24M</t>
+          <t>3.3%</t>
         </is>
       </c>
       <c r="D253" t="inlineStr">
         <is>
-          <t>4.15M</t>
+          <t>2.8%</t>
         </is>
       </c>
       <c r="E253" t="inlineStr">
         <is>
-          <t>4.19M</t>
+          <t>3.3%</t>
         </is>
       </c>
       <c r="F253" t="inlineStr">
         <is>
-          <t>4.1M</t>
+          <t>3.3%</t>
         </is>
       </c>
       <c r="G253" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="254">
@@ -7845,27 +7841,27 @@
       </c>
       <c r="B254" t="inlineStr">
         <is>
-          <t>Michigan Consumer Expectations FinalJAN</t>
+          <t>Michigan 5 Year Inflation Expectations FinalJAN</t>
         </is>
       </c>
       <c r="C254" t="inlineStr">
         <is>
-          <t>69.3</t>
+          <t>3.2%</t>
         </is>
       </c>
       <c r="D254" t="inlineStr">
         <is>
-          <t>73.3</t>
+          <t>3%</t>
         </is>
       </c>
       <c r="E254" t="inlineStr">
         <is>
-          <t>70.2</t>
+          <t>3.3%</t>
         </is>
       </c>
       <c r="F254" t="inlineStr">
         <is>
-          <t>70.2</t>
+          <t>3.3%</t>
         </is>
       </c>
       <c r="G254" t="n">
@@ -7880,31 +7876,31 @@
       </c>
       <c r="B255" t="inlineStr">
         <is>
-          <t>Michigan Consumer Sentiment FinalJAN</t>
+          <t>Michigan Current Conditions FinalJAN</t>
         </is>
       </c>
       <c r="C255" t="inlineStr">
         <is>
-          <t>71.1</t>
+          <t>74.0</t>
         </is>
       </c>
       <c r="D255" t="inlineStr">
         <is>
-          <t>74.0</t>
+          <t>75.1</t>
         </is>
       </c>
       <c r="E255" t="inlineStr">
         <is>
-          <t>73.2</t>
+          <t>77.9</t>
         </is>
       </c>
       <c r="F255" t="inlineStr">
         <is>
-          <t>73.2</t>
+          <t>77.9</t>
         </is>
       </c>
       <c r="G255" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="256">
@@ -7915,27 +7911,31 @@
       </c>
       <c r="B256" t="inlineStr">
         <is>
-          <t>Existing Home Sales MoMDEC</t>
+          <t>Existing Home SalesDEC</t>
         </is>
       </c>
       <c r="C256" t="inlineStr">
         <is>
-          <t>2.2%</t>
+          <t>4.24M</t>
         </is>
       </c>
       <c r="D256" t="inlineStr">
         <is>
-          <t>4.8%</t>
-        </is>
-      </c>
-      <c r="E256" t="inlineStr"/>
+          <t>4.15M</t>
+        </is>
+      </c>
+      <c r="E256" t="inlineStr">
+        <is>
+          <t>4.19M</t>
+        </is>
+      </c>
       <c r="F256" t="inlineStr">
         <is>
-          <t>0.3%</t>
+          <t>4.1M</t>
         </is>
       </c>
       <c r="G256" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="257">
@@ -8469,27 +8469,23 @@
       </c>
       <c r="B274" t="inlineStr">
         <is>
-          <t>House Price Index MoMNOV</t>
+          <t>S&amp;P/Case-Shiller Home Price MoMNOV</t>
         </is>
       </c>
       <c r="C274" t="inlineStr">
         <is>
-          <t>0.3%</t>
+          <t>-0.1%</t>
         </is>
       </c>
       <c r="D274" t="inlineStr">
         <is>
-          <t>0.5%</t>
-        </is>
-      </c>
-      <c r="E274" t="inlineStr">
-        <is>
-          <t>0.2%</t>
-        </is>
-      </c>
+          <t>-0.2%</t>
+        </is>
+      </c>
+      <c r="E274" t="inlineStr"/>
       <c r="F274" t="inlineStr">
         <is>
-          <t>0.3%</t>
+          <t>-0.1%</t>
         </is>
       </c>
       <c r="G274" t="n">
@@ -8504,23 +8500,23 @@
       </c>
       <c r="B275" t="inlineStr">
         <is>
-          <t>House Price IndexNOV</t>
+          <t>House Price Index YoYNOV</t>
         </is>
       </c>
       <c r="C275" t="inlineStr">
         <is>
-          <t>433.4</t>
+          <t>4.2%</t>
         </is>
       </c>
       <c r="D275" t="inlineStr">
         <is>
-          <t>432.3</t>
+          <t>4.5%</t>
         </is>
       </c>
       <c r="E275" t="inlineStr"/>
       <c r="F275" t="inlineStr">
         <is>
-          <t>433</t>
+          <t>4.3%</t>
         </is>
       </c>
       <c r="G275" t="n">
@@ -8535,27 +8531,31 @@
       </c>
       <c r="B276" t="inlineStr">
         <is>
-          <t>House Price Index YoYNOV</t>
+          <t>S&amp;P/Case-Shiller Home Price YoYNOV</t>
         </is>
       </c>
       <c r="C276" t="inlineStr">
         <is>
+          <t>4.3%</t>
+        </is>
+      </c>
+      <c r="D276" t="inlineStr">
+        <is>
           <t>4.2%</t>
         </is>
       </c>
-      <c r="D276" t="inlineStr">
-        <is>
-          <t>4.5%</t>
-        </is>
-      </c>
-      <c r="E276" t="inlineStr"/>
+      <c r="E276" t="inlineStr">
+        <is>
+          <t>4.3%</t>
+        </is>
+      </c>
       <c r="F276" t="inlineStr">
         <is>
-          <t>4.3%</t>
+          <t>4%</t>
         </is>
       </c>
       <c r="G276" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="277">
@@ -8566,31 +8566,27 @@
       </c>
       <c r="B277" t="inlineStr">
         <is>
-          <t>S&amp;P/Case-Shiller Home Price YoYNOV</t>
+          <t>House Price IndexNOV</t>
         </is>
       </c>
       <c r="C277" t="inlineStr">
         <is>
-          <t>4.3%</t>
+          <t>433.4</t>
         </is>
       </c>
       <c r="D277" t="inlineStr">
         <is>
-          <t>4.2%</t>
-        </is>
-      </c>
-      <c r="E277" t="inlineStr">
-        <is>
-          <t>4.3%</t>
-        </is>
-      </c>
+          <t>432.3</t>
+        </is>
+      </c>
+      <c r="E277" t="inlineStr"/>
       <c r="F277" t="inlineStr">
         <is>
-          <t>4%</t>
+          <t>433</t>
         </is>
       </c>
       <c r="G277" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="278">
@@ -8601,23 +8597,27 @@
       </c>
       <c r="B278" t="inlineStr">
         <is>
-          <t>S&amp;P/Case-Shiller Home Price MoMNOV</t>
+          <t>House Price Index MoMNOV</t>
         </is>
       </c>
       <c r="C278" t="inlineStr">
         <is>
-          <t>-0.1%</t>
+          <t>0.3%</t>
         </is>
       </c>
       <c r="D278" t="inlineStr">
         <is>
-          <t>-0.2%</t>
-        </is>
-      </c>
-      <c r="E278" t="inlineStr"/>
+          <t>0.5%</t>
+        </is>
+      </c>
+      <c r="E278" t="inlineStr">
+        <is>
+          <t>0.2%</t>
+        </is>
+      </c>
       <c r="F278" t="inlineStr">
         <is>
-          <t>-0.1%</t>
+          <t>0.3%</t>
         </is>
       </c>
       <c r="G278" t="n">
@@ -9201,17 +9201,17 @@
       </c>
       <c r="B298" t="inlineStr">
         <is>
-          <t>EIA Gasoline Production ChangeJAN/24</t>
+          <t>EIA Cushing Crude Oil Stocks ChangeJAN/24</t>
         </is>
       </c>
       <c r="C298" t="inlineStr">
         <is>
-          <t>-0.044M</t>
+          <t>0.326M</t>
         </is>
       </c>
       <c r="D298" t="inlineStr">
         <is>
-          <t>-0.043M</t>
+          <t>-0.148M</t>
         </is>
       </c>
       <c r="E298" t="inlineStr"/>
@@ -9228,23 +9228,27 @@
       </c>
       <c r="B299" t="inlineStr">
         <is>
-          <t>EIA Crude Oil Imports ChangeJAN/24</t>
+          <t>EIA Crude Oil Stocks ChangeJAN/24</t>
         </is>
       </c>
       <c r="C299" t="inlineStr">
         <is>
-          <t>0.532M</t>
+          <t>3.463M</t>
         </is>
       </c>
       <c r="D299" t="inlineStr">
         <is>
-          <t>0.184M</t>
-        </is>
-      </c>
-      <c r="E299" t="inlineStr"/>
+          <t>-1.017M</t>
+        </is>
+      </c>
+      <c r="E299" t="inlineStr">
+        <is>
+          <t>3.2M</t>
+        </is>
+      </c>
       <c r="F299" t="inlineStr"/>
       <c r="G299" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="300">
@@ -9255,20 +9259,24 @@
       </c>
       <c r="B300" t="inlineStr">
         <is>
-          <t>EIA Distillate Fuel Production ChangeJAN/24</t>
+          <t>EIA Distillate Stocks ChangeJAN/24</t>
         </is>
       </c>
       <c r="C300" t="inlineStr">
         <is>
-          <t>0.028M</t>
+          <t>-4.994M</t>
         </is>
       </c>
       <c r="D300" t="inlineStr">
         <is>
-          <t>-0.473M</t>
-        </is>
-      </c>
-      <c r="E300" t="inlineStr"/>
+          <t>-3.07M</t>
+        </is>
+      </c>
+      <c r="E300" t="inlineStr">
+        <is>
+          <t>-2.1M</t>
+        </is>
+      </c>
       <c r="F300" t="inlineStr"/>
       <c r="G300" t="n">
         <v>3</v>
@@ -9282,27 +9290,23 @@
       </c>
       <c r="B301" t="inlineStr">
         <is>
-          <t>EIA Gasoline Stocks ChangeJAN/24</t>
+          <t>EIA Heating Oil Stocks ChangeJAN/24</t>
         </is>
       </c>
       <c r="C301" t="inlineStr">
         <is>
-          <t>2.957M</t>
+          <t>0.128M</t>
         </is>
       </c>
       <c r="D301" t="inlineStr">
         <is>
-          <t>2.332M</t>
-        </is>
-      </c>
-      <c r="E301" t="inlineStr">
-        <is>
-          <t>1.5M</t>
-        </is>
-      </c>
+          <t>0.068M</t>
+        </is>
+      </c>
+      <c r="E301" t="inlineStr"/>
       <c r="F301" t="inlineStr"/>
       <c r="G301" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="302">
@@ -9340,23 +9344,27 @@
       </c>
       <c r="B303" t="inlineStr">
         <is>
-          <t>EIA Heating Oil Stocks ChangeJAN/24</t>
+          <t>EIA Gasoline Stocks ChangeJAN/24</t>
         </is>
       </c>
       <c r="C303" t="inlineStr">
         <is>
-          <t>0.128M</t>
+          <t>2.957M</t>
         </is>
       </c>
       <c r="D303" t="inlineStr">
         <is>
-          <t>0.068M</t>
-        </is>
-      </c>
-      <c r="E303" t="inlineStr"/>
+          <t>2.332M</t>
+        </is>
+      </c>
+      <c r="E303" t="inlineStr">
+        <is>
+          <t>1.5M</t>
+        </is>
+      </c>
       <c r="F303" t="inlineStr"/>
       <c r="G303" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="304">
@@ -9367,24 +9375,20 @@
       </c>
       <c r="B304" t="inlineStr">
         <is>
-          <t>EIA Distillate Stocks ChangeJAN/24</t>
+          <t>EIA Distillate Fuel Production ChangeJAN/24</t>
         </is>
       </c>
       <c r="C304" t="inlineStr">
         <is>
-          <t>-4.994M</t>
+          <t>0.028M</t>
         </is>
       </c>
       <c r="D304" t="inlineStr">
         <is>
-          <t>-3.07M</t>
-        </is>
-      </c>
-      <c r="E304" t="inlineStr">
-        <is>
-          <t>-2.1M</t>
-        </is>
-      </c>
+          <t>-0.473M</t>
+        </is>
+      </c>
+      <c r="E304" t="inlineStr"/>
       <c r="F304" t="inlineStr"/>
       <c r="G304" t="n">
         <v>3</v>
@@ -9398,27 +9402,23 @@
       </c>
       <c r="B305" t="inlineStr">
         <is>
-          <t>EIA Crude Oil Stocks ChangeJAN/24</t>
+          <t>EIA Crude Oil Imports ChangeJAN/24</t>
         </is>
       </c>
       <c r="C305" t="inlineStr">
         <is>
-          <t>3.463M</t>
+          <t>0.532M</t>
         </is>
       </c>
       <c r="D305" t="inlineStr">
         <is>
-          <t>-1.017M</t>
-        </is>
-      </c>
-      <c r="E305" t="inlineStr">
-        <is>
-          <t>3.2M</t>
-        </is>
-      </c>
+          <t>0.184M</t>
+        </is>
+      </c>
+      <c r="E305" t="inlineStr"/>
       <c r="F305" t="inlineStr"/>
       <c r="G305" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="306">
@@ -9429,17 +9429,17 @@
       </c>
       <c r="B306" t="inlineStr">
         <is>
-          <t>EIA Cushing Crude Oil Stocks ChangeJAN/24</t>
+          <t>EIA Gasoline Production ChangeJAN/24</t>
         </is>
       </c>
       <c r="C306" t="inlineStr">
         <is>
-          <t>0.326M</t>
+          <t>-0.044M</t>
         </is>
       </c>
       <c r="D306" t="inlineStr">
         <is>
-          <t>-0.148M</t>
+          <t>-0.043M</t>
         </is>
       </c>
       <c r="E306" t="inlineStr"/>
@@ -9537,27 +9537,27 @@
       </c>
       <c r="B310" t="inlineStr">
         <is>
-          <t>GDP Price Index QoQ AdvQ4</t>
+          <t>Initial Jobless ClaimsJAN/25</t>
         </is>
       </c>
       <c r="C310" t="inlineStr">
         <is>
-          <t>2.2%</t>
+          <t>207K</t>
         </is>
       </c>
       <c r="D310" t="inlineStr">
         <is>
-          <t>1.9%</t>
+          <t>223K</t>
         </is>
       </c>
       <c r="E310" t="inlineStr">
         <is>
-          <t>2.5%</t>
+          <t>220K</t>
         </is>
       </c>
       <c r="F310" t="inlineStr">
         <is>
-          <t>2.3%</t>
+          <t>228.0K</t>
         </is>
       </c>
       <c r="G310" t="n">
@@ -9572,27 +9572,23 @@
       </c>
       <c r="B311" t="inlineStr">
         <is>
-          <t>Core PCE Prices QoQ AdvQ4</t>
+          <t>GDP Sales QoQ AdvQ4</t>
         </is>
       </c>
       <c r="C311" t="inlineStr">
         <is>
-          <t>2.5%</t>
+          <t>3.2%</t>
         </is>
       </c>
       <c r="D311" t="inlineStr">
         <is>
-          <t>2.2%</t>
-        </is>
-      </c>
-      <c r="E311" t="inlineStr">
-        <is>
-          <t>2.5%</t>
-        </is>
-      </c>
+          <t>3.3%</t>
+        </is>
+      </c>
+      <c r="E311" t="inlineStr"/>
       <c r="F311" t="inlineStr">
         <is>
-          <t>2.3%</t>
+          <t>2.9%</t>
         </is>
       </c>
       <c r="G311" t="n">
@@ -9607,23 +9603,23 @@
       </c>
       <c r="B312" t="inlineStr">
         <is>
-          <t>PCE Prices QoQ AdvQ4</t>
+          <t>Jobless Claims 4-week AverageJAN/25</t>
         </is>
       </c>
       <c r="C312" t="inlineStr">
         <is>
-          <t>2.3%</t>
+          <t>212.5K</t>
         </is>
       </c>
       <c r="D312" t="inlineStr">
         <is>
-          <t>1.5%</t>
+          <t>213.5K</t>
         </is>
       </c>
       <c r="E312" t="inlineStr"/>
       <c r="F312" t="inlineStr">
         <is>
-          <t>1.1%</t>
+          <t>214.0K</t>
         </is>
       </c>
       <c r="G312" t="n">
@@ -9638,31 +9634,27 @@
       </c>
       <c r="B313" t="inlineStr">
         <is>
-          <t>GDP Growth Rate QoQ AdvQ4</t>
+          <t>Real Consumer Spending QoQ AdvQ4</t>
         </is>
       </c>
       <c r="C313" t="inlineStr">
         <is>
-          <t>2.3%</t>
+          <t>4.2%</t>
         </is>
       </c>
       <c r="D313" t="inlineStr">
         <is>
-          <t>3.1%</t>
-        </is>
-      </c>
-      <c r="E313" t="inlineStr">
-        <is>
-          <t>2.6%</t>
-        </is>
-      </c>
+          <t>3.7%</t>
+        </is>
+      </c>
+      <c r="E313" t="inlineStr"/>
       <c r="F313" t="inlineStr">
         <is>
-          <t>3%</t>
+          <t>2.9%</t>
         </is>
       </c>
       <c r="G313" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="314">
@@ -9673,23 +9665,27 @@
       </c>
       <c r="B314" t="inlineStr">
         <is>
-          <t>Real Consumer Spending QoQ AdvQ4</t>
+          <t>Continuing Jobless ClaimsJAN/18</t>
         </is>
       </c>
       <c r="C314" t="inlineStr">
         <is>
-          <t>4.2%</t>
+          <t>1858K</t>
         </is>
       </c>
       <c r="D314" t="inlineStr">
         <is>
-          <t>3.7%</t>
-        </is>
-      </c>
-      <c r="E314" t="inlineStr"/>
+          <t>1900K</t>
+        </is>
+      </c>
+      <c r="E314" t="inlineStr">
+        <is>
+          <t>1890K</t>
+        </is>
+      </c>
       <c r="F314" t="inlineStr">
         <is>
-          <t>2.9%</t>
+          <t>1885.0K</t>
         </is>
       </c>
       <c r="G314" t="n">
@@ -9704,27 +9700,23 @@
       </c>
       <c r="B315" t="inlineStr">
         <is>
-          <t>Continuing Jobless ClaimsJAN/18</t>
+          <t>PCE Prices QoQ AdvQ4</t>
         </is>
       </c>
       <c r="C315" t="inlineStr">
         <is>
-          <t>1858K</t>
+          <t>2.3%</t>
         </is>
       </c>
       <c r="D315" t="inlineStr">
         <is>
-          <t>1900K</t>
-        </is>
-      </c>
-      <c r="E315" t="inlineStr">
-        <is>
-          <t>1890K</t>
-        </is>
-      </c>
+          <t>1.5%</t>
+        </is>
+      </c>
+      <c r="E315" t="inlineStr"/>
       <c r="F315" t="inlineStr">
         <is>
-          <t>1885.0K</t>
+          <t>1.1%</t>
         </is>
       </c>
       <c r="G315" t="n">
@@ -9739,23 +9731,27 @@
       </c>
       <c r="B316" t="inlineStr">
         <is>
-          <t>Jobless Claims 4-week AverageJAN/25</t>
+          <t>Core PCE Prices QoQ AdvQ4</t>
         </is>
       </c>
       <c r="C316" t="inlineStr">
         <is>
-          <t>212.5K</t>
+          <t>2.5%</t>
         </is>
       </c>
       <c r="D316" t="inlineStr">
         <is>
-          <t>213.5K</t>
-        </is>
-      </c>
-      <c r="E316" t="inlineStr"/>
+          <t>2.2%</t>
+        </is>
+      </c>
+      <c r="E316" t="inlineStr">
+        <is>
+          <t>2.5%</t>
+        </is>
+      </c>
       <c r="F316" t="inlineStr">
         <is>
-          <t>214.0K</t>
+          <t>2.3%</t>
         </is>
       </c>
       <c r="G316" t="n">
@@ -9770,27 +9766,31 @@
       </c>
       <c r="B317" t="inlineStr">
         <is>
-          <t>GDP Sales QoQ AdvQ4</t>
+          <t>GDP Price Index QoQ AdvQ4</t>
         </is>
       </c>
       <c r="C317" t="inlineStr">
         <is>
-          <t>3.2%</t>
+          <t>2.2%</t>
         </is>
       </c>
       <c r="D317" t="inlineStr">
         <is>
-          <t>3.3%</t>
-        </is>
-      </c>
-      <c r="E317" t="inlineStr"/>
+          <t>1.9%</t>
+        </is>
+      </c>
+      <c r="E317" t="inlineStr">
+        <is>
+          <t>2.5%</t>
+        </is>
+      </c>
       <c r="F317" t="inlineStr">
         <is>
-          <t>2.9%</t>
+          <t>2.3%</t>
         </is>
       </c>
       <c r="G317" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="318">
@@ -9801,31 +9801,31 @@
       </c>
       <c r="B318" t="inlineStr">
         <is>
-          <t>Initial Jobless ClaimsJAN/25</t>
+          <t>GDP Growth Rate QoQ AdvQ4</t>
         </is>
       </c>
       <c r="C318" t="inlineStr">
         <is>
-          <t>207K</t>
+          <t>2.3%</t>
         </is>
       </c>
       <c r="D318" t="inlineStr">
         <is>
-          <t>223K</t>
+          <t>3.1%</t>
         </is>
       </c>
       <c r="E318" t="inlineStr">
         <is>
-          <t>220K</t>
+          <t>2.6%</t>
         </is>
       </c>
       <c r="F318" t="inlineStr">
         <is>
-          <t>228.0K</t>
+          <t>3%</t>
         </is>
       </c>
       <c r="G318" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="319">
@@ -10068,31 +10068,31 @@
       </c>
       <c r="B327" t="inlineStr">
         <is>
-          <t>Core PCE Price Index MoMDEC</t>
+          <t>Core PCE Price Index YoYDEC</t>
         </is>
       </c>
       <c r="C327" t="inlineStr">
         <is>
-          <t>0.2%</t>
+          <t>2.8%</t>
         </is>
       </c>
       <c r="D327" t="inlineStr">
         <is>
-          <t>0.1%</t>
+          <t>2.8%</t>
         </is>
       </c>
       <c r="E327" t="inlineStr">
         <is>
-          <t>0.2%</t>
+          <t>2.8%</t>
         </is>
       </c>
       <c r="F327" t="inlineStr">
         <is>
-          <t>0.2%</t>
+          <t>2.8%</t>
         </is>
       </c>
       <c r="G327" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="328">
@@ -10103,31 +10103,31 @@
       </c>
       <c r="B328" t="inlineStr">
         <is>
-          <t>Personal Spending MoMDEC</t>
+          <t>Employment Cost Index QoQQ4</t>
         </is>
       </c>
       <c r="C328" t="inlineStr">
         <is>
+          <t>0.9%</t>
+        </is>
+      </c>
+      <c r="D328" t="inlineStr">
+        <is>
+          <t>0.8%</t>
+        </is>
+      </c>
+      <c r="E328" t="inlineStr">
+        <is>
+          <t>0.9%</t>
+        </is>
+      </c>
+      <c r="F328" t="inlineStr">
+        <is>
           <t>0.7%</t>
         </is>
       </c>
-      <c r="D328" t="inlineStr">
-        <is>
-          <t>0.6%</t>
-        </is>
-      </c>
-      <c r="E328" t="inlineStr">
-        <is>
-          <t>0.5%</t>
-        </is>
-      </c>
-      <c r="F328" t="inlineStr">
-        <is>
-          <t>0.5%</t>
-        </is>
-      </c>
       <c r="G328" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="329">
@@ -10138,23 +10138,27 @@
       </c>
       <c r="B329" t="inlineStr">
         <is>
-          <t>Employment Cost - Benefits QoQQ4</t>
+          <t>PCE Price Index MoMDEC</t>
         </is>
       </c>
       <c r="C329" t="inlineStr">
         <is>
-          <t>0.8%</t>
+          <t>0.3%</t>
         </is>
       </c>
       <c r="D329" t="inlineStr">
         <is>
-          <t>0.8%</t>
-        </is>
-      </c>
-      <c r="E329" t="inlineStr"/>
+          <t>0.1%</t>
+        </is>
+      </c>
+      <c r="E329" t="inlineStr">
+        <is>
+          <t>0.3%</t>
+        </is>
+      </c>
       <c r="F329" t="inlineStr">
         <is>
-          <t>0.7%</t>
+          <t>0.3%</t>
         </is>
       </c>
       <c r="G329" t="n">
@@ -10169,13 +10173,29 @@
       </c>
       <c r="B330" t="inlineStr">
         <is>
-          <t>Fed Bowman Speech</t>
-        </is>
-      </c>
-      <c r="C330" t="inlineStr"/>
-      <c r="D330" t="inlineStr"/>
-      <c r="E330" t="inlineStr"/>
-      <c r="F330" t="inlineStr"/>
+          <t>PCE Price Index YoYDEC</t>
+        </is>
+      </c>
+      <c r="C330" t="inlineStr">
+        <is>
+          <t>2.6%</t>
+        </is>
+      </c>
+      <c r="D330" t="inlineStr">
+        <is>
+          <t>2.4%</t>
+        </is>
+      </c>
+      <c r="E330" t="inlineStr">
+        <is>
+          <t>2.6%</t>
+        </is>
+      </c>
+      <c r="F330" t="inlineStr">
+        <is>
+          <t>2.6%</t>
+        </is>
+      </c>
       <c r="G330" t="n">
         <v>2</v>
       </c>
@@ -10188,31 +10208,27 @@
       </c>
       <c r="B331" t="inlineStr">
         <is>
-          <t>Personal Income MoMDEC</t>
+          <t>Employment Cost - Wages QoQQ4</t>
         </is>
       </c>
       <c r="C331" t="inlineStr">
         <is>
-          <t>0.4%</t>
+          <t>0.9%</t>
         </is>
       </c>
       <c r="D331" t="inlineStr">
         <is>
-          <t>0.3%</t>
-        </is>
-      </c>
-      <c r="E331" t="inlineStr">
-        <is>
-          <t>0.4%</t>
-        </is>
-      </c>
+          <t>0.8%</t>
+        </is>
+      </c>
+      <c r="E331" t="inlineStr"/>
       <c r="F331" t="inlineStr">
         <is>
-          <t>0.3%</t>
+          <t>0.7%</t>
         </is>
       </c>
       <c r="G331" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="332">
@@ -10223,29 +10239,13 @@
       </c>
       <c r="B332" t="inlineStr">
         <is>
-          <t>PCE Price Index YoYDEC</t>
-        </is>
-      </c>
-      <c r="C332" t="inlineStr">
-        <is>
-          <t>2.6%</t>
-        </is>
-      </c>
-      <c r="D332" t="inlineStr">
-        <is>
-          <t>2.4%</t>
-        </is>
-      </c>
-      <c r="E332" t="inlineStr">
-        <is>
-          <t>2.6%</t>
-        </is>
-      </c>
-      <c r="F332" t="inlineStr">
-        <is>
-          <t>2.6%</t>
-        </is>
-      </c>
+          <t>Fed Bowman Speech</t>
+        </is>
+      </c>
+      <c r="C332" t="inlineStr"/>
+      <c r="D332" t="inlineStr"/>
+      <c r="E332" t="inlineStr"/>
+      <c r="F332" t="inlineStr"/>
       <c r="G332" t="n">
         <v>2</v>
       </c>
@@ -10258,12 +10258,12 @@
       </c>
       <c r="B333" t="inlineStr">
         <is>
-          <t>Employment Cost Index QoQQ4</t>
+          <t>Employment Cost - Benefits QoQQ4</t>
         </is>
       </c>
       <c r="C333" t="inlineStr">
         <is>
-          <t>0.9%</t>
+          <t>0.8%</t>
         </is>
       </c>
       <c r="D333" t="inlineStr">
@@ -10271,11 +10271,7 @@
           <t>0.8%</t>
         </is>
       </c>
-      <c r="E333" t="inlineStr">
-        <is>
-          <t>0.9%</t>
-        </is>
-      </c>
+      <c r="E333" t="inlineStr"/>
       <c r="F333" t="inlineStr">
         <is>
           <t>0.7%</t>
@@ -10293,31 +10289,31 @@
       </c>
       <c r="B334" t="inlineStr">
         <is>
-          <t>Core PCE Price Index YoYDEC</t>
+          <t>Personal Spending MoMDEC</t>
         </is>
       </c>
       <c r="C334" t="inlineStr">
         <is>
-          <t>2.8%</t>
+          <t>0.7%</t>
         </is>
       </c>
       <c r="D334" t="inlineStr">
         <is>
-          <t>2.8%</t>
+          <t>0.6%</t>
         </is>
       </c>
       <c r="E334" t="inlineStr">
         <is>
-          <t>2.8%</t>
+          <t>0.5%</t>
         </is>
       </c>
       <c r="F334" t="inlineStr">
         <is>
-          <t>2.8%</t>
+          <t>0.5%</t>
         </is>
       </c>
       <c r="G334" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="335">
@@ -10328,12 +10324,12 @@
       </c>
       <c r="B335" t="inlineStr">
         <is>
-          <t>PCE Price Index MoMDEC</t>
+          <t>Core PCE Price Index MoMDEC</t>
         </is>
       </c>
       <c r="C335" t="inlineStr">
         <is>
-          <t>0.3%</t>
+          <t>0.2%</t>
         </is>
       </c>
       <c r="D335" t="inlineStr">
@@ -10343,16 +10339,16 @@
       </c>
       <c r="E335" t="inlineStr">
         <is>
-          <t>0.3%</t>
+          <t>0.2%</t>
         </is>
       </c>
       <c r="F335" t="inlineStr">
         <is>
-          <t>0.3%</t>
+          <t>0.2%</t>
         </is>
       </c>
       <c r="G335" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="336">
@@ -10363,27 +10359,31 @@
       </c>
       <c r="B336" t="inlineStr">
         <is>
-          <t>Employment Cost - Wages QoQQ4</t>
+          <t>Personal Income MoMDEC</t>
         </is>
       </c>
       <c r="C336" t="inlineStr">
         <is>
-          <t>0.9%</t>
+          <t>0.4%</t>
         </is>
       </c>
       <c r="D336" t="inlineStr">
         <is>
-          <t>0.8%</t>
-        </is>
-      </c>
-      <c r="E336" t="inlineStr"/>
+          <t>0.3%</t>
+        </is>
+      </c>
+      <c r="E336" t="inlineStr">
+        <is>
+          <t>0.4%</t>
+        </is>
+      </c>
       <c r="F336" t="inlineStr">
         <is>
-          <t>0.7%</t>
+          <t>0.3%</t>
         </is>
       </c>
       <c r="G336" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="337">
@@ -10522,31 +10522,27 @@
       </c>
       <c r="B341" t="inlineStr">
         <is>
-          <t>ISM Manufacturing PricesJAN</t>
+          <t>ISM Manufacturing EmploymentJAN</t>
         </is>
       </c>
       <c r="C341" t="inlineStr">
         <is>
-          <t>54.9</t>
+          <t>50.3</t>
         </is>
       </c>
       <c r="D341" t="inlineStr">
         <is>
-          <t>52.5</t>
-        </is>
-      </c>
-      <c r="E341" t="inlineStr">
-        <is>
-          <t>52.6</t>
-        </is>
-      </c>
+          <t>45.4</t>
+        </is>
+      </c>
+      <c r="E341" t="inlineStr"/>
       <c r="F341" t="inlineStr">
         <is>
-          <t>53</t>
+          <t>47</t>
         </is>
       </c>
       <c r="G341" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="342">
@@ -10557,31 +10553,31 @@
       </c>
       <c r="B342" t="inlineStr">
         <is>
-          <t>Construction Spending MoMDEC</t>
+          <t>ISM Manufacturing PMIJAN</t>
         </is>
       </c>
       <c r="C342" t="inlineStr">
         <is>
-          <t>0.5%</t>
+          <t>50.9</t>
         </is>
       </c>
       <c r="D342" t="inlineStr">
         <is>
-          <t>0.2%</t>
+          <t>49.2</t>
         </is>
       </c>
       <c r="E342" t="inlineStr">
         <is>
-          <t>0.2%</t>
+          <t>49.8</t>
         </is>
       </c>
       <c r="F342" t="inlineStr">
         <is>
-          <t>0.3%</t>
+          <t>49.8</t>
         </is>
       </c>
       <c r="G342" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="343">
@@ -10592,31 +10588,27 @@
       </c>
       <c r="B343" t="inlineStr">
         <is>
-          <t>ISM Manufacturing PMIJAN</t>
+          <t>ISM Manufacturing New OrdersJAN</t>
         </is>
       </c>
       <c r="C343" t="inlineStr">
         <is>
-          <t>50.9</t>
+          <t>55.1</t>
         </is>
       </c>
       <c r="D343" t="inlineStr">
         <is>
-          <t>49.2</t>
-        </is>
-      </c>
-      <c r="E343" t="inlineStr">
-        <is>
-          <t>49.8</t>
-        </is>
-      </c>
+          <t>52.1</t>
+        </is>
+      </c>
+      <c r="E343" t="inlineStr"/>
       <c r="F343" t="inlineStr">
         <is>
-          <t>49.8</t>
+          <t>52.8</t>
         </is>
       </c>
       <c r="G343" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="344">
@@ -10627,23 +10619,27 @@
       </c>
       <c r="B344" t="inlineStr">
         <is>
-          <t>ISM Manufacturing New OrdersJAN</t>
+          <t>ISM Manufacturing PricesJAN</t>
         </is>
       </c>
       <c r="C344" t="inlineStr">
         <is>
-          <t>55.1</t>
+          <t>54.9</t>
         </is>
       </c>
       <c r="D344" t="inlineStr">
         <is>
-          <t>52.1</t>
-        </is>
-      </c>
-      <c r="E344" t="inlineStr"/>
+          <t>52.5</t>
+        </is>
+      </c>
+      <c r="E344" t="inlineStr">
+        <is>
+          <t>52.6</t>
+        </is>
+      </c>
       <c r="F344" t="inlineStr">
         <is>
-          <t>52.8</t>
+          <t>53</t>
         </is>
       </c>
       <c r="G344" t="n">
@@ -10658,27 +10654,31 @@
       </c>
       <c r="B345" t="inlineStr">
         <is>
-          <t>ISM Manufacturing EmploymentJAN</t>
+          <t>Construction Spending MoMDEC</t>
         </is>
       </c>
       <c r="C345" t="inlineStr">
         <is>
-          <t>50.3</t>
+          <t>0.5%</t>
         </is>
       </c>
       <c r="D345" t="inlineStr">
         <is>
-          <t>45.4</t>
-        </is>
-      </c>
-      <c r="E345" t="inlineStr"/>
+          <t>0.2%</t>
+        </is>
+      </c>
+      <c r="E345" t="inlineStr">
+        <is>
+          <t>0.2%</t>
+        </is>
+      </c>
       <c r="F345" t="inlineStr">
         <is>
-          <t>47</t>
+          <t>0.3%</t>
         </is>
       </c>
       <c r="G345" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="346">
@@ -10873,27 +10873,31 @@
       </c>
       <c r="B354" t="inlineStr">
         <is>
-          <t>JOLTs Job QuitsDEC</t>
+          <t>Factory Orders MoMDEC</t>
         </is>
       </c>
       <c r="C354" t="inlineStr">
         <is>
-          <t>3.197M</t>
+          <t>-0.9%</t>
         </is>
       </c>
       <c r="D354" t="inlineStr">
         <is>
-          <t>3.130M</t>
-        </is>
-      </c>
-      <c r="E354" t="inlineStr"/>
+          <t>-0.8%</t>
+        </is>
+      </c>
+      <c r="E354" t="inlineStr">
+        <is>
+          <t>-0.7%</t>
+        </is>
+      </c>
       <c r="F354" t="inlineStr">
         <is>
-          <t>3.1M</t>
+          <t>-0.7%</t>
         </is>
       </c>
       <c r="G354" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="355">
@@ -10904,31 +10908,27 @@
       </c>
       <c r="B355" t="inlineStr">
         <is>
-          <t>JOLTs Job OpeningsDEC</t>
+          <t>JOLTs Job QuitsDEC</t>
         </is>
       </c>
       <c r="C355" t="inlineStr">
         <is>
-          <t>7.6M</t>
+          <t>3.197M</t>
         </is>
       </c>
       <c r="D355" t="inlineStr">
         <is>
-          <t>8.156M</t>
-        </is>
-      </c>
-      <c r="E355" t="inlineStr">
-        <is>
-          <t>8M</t>
-        </is>
-      </c>
+          <t>3.130M</t>
+        </is>
+      </c>
+      <c r="E355" t="inlineStr"/>
       <c r="F355" t="inlineStr">
         <is>
-          <t>7.8M</t>
+          <t>3.1M</t>
         </is>
       </c>
       <c r="G355" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="356">
@@ -10939,31 +10939,31 @@
       </c>
       <c r="B356" t="inlineStr">
         <is>
-          <t>Factory Orders MoMDEC</t>
+          <t>JOLTs Job OpeningsDEC</t>
         </is>
       </c>
       <c r="C356" t="inlineStr">
         <is>
-          <t>-0.9%</t>
+          <t>7.6M</t>
         </is>
       </c>
       <c r="D356" t="inlineStr">
         <is>
-          <t>-0.8%</t>
+          <t>8.156M</t>
         </is>
       </c>
       <c r="E356" t="inlineStr">
         <is>
-          <t>-0.7%</t>
+          <t>8M</t>
         </is>
       </c>
       <c r="F356" t="inlineStr">
         <is>
-          <t>-0.7%</t>
+          <t>7.8M</t>
         </is>
       </c>
       <c r="G356" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="357">
@@ -11325,23 +11325,27 @@
       </c>
       <c r="B370" t="inlineStr">
         <is>
-          <t>ImportsDEC</t>
+          <t>Balance of TradeDEC</t>
         </is>
       </c>
       <c r="C370" t="inlineStr">
         <is>
-          <t>$364.9B</t>
+          <t>$-98.4B</t>
         </is>
       </c>
       <c r="D370" t="inlineStr">
         <is>
-          <t>$352.5B</t>
-        </is>
-      </c>
-      <c r="E370" t="inlineStr"/>
+          <t>$-78.9B</t>
+        </is>
+      </c>
+      <c r="E370" t="inlineStr">
+        <is>
+          <t>$-96.6B</t>
+        </is>
+      </c>
       <c r="F370" t="inlineStr">
         <is>
-          <t>$ 355.0B</t>
+          <t>$ -93.0B</t>
         </is>
       </c>
       <c r="G370" t="n">
@@ -11356,27 +11360,15 @@
       </c>
       <c r="B371" t="inlineStr">
         <is>
-          <t>ExportsDEC</t>
-        </is>
-      </c>
-      <c r="C371" t="inlineStr">
-        <is>
-          <t>$266.5B</t>
-        </is>
-      </c>
-      <c r="D371" t="inlineStr">
-        <is>
-          <t>$273.6B</t>
-        </is>
-      </c>
+          <t>Treasury Refunding Announcement</t>
+        </is>
+      </c>
+      <c r="C371" t="inlineStr"/>
+      <c r="D371" t="inlineStr"/>
       <c r="E371" t="inlineStr"/>
-      <c r="F371" t="inlineStr">
-        <is>
-          <t>$ 262B</t>
-        </is>
-      </c>
+      <c r="F371" t="inlineStr"/>
       <c r="G371" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="372">
@@ -11387,15 +11379,27 @@
       </c>
       <c r="B372" t="inlineStr">
         <is>
-          <t>Treasury Refunding Announcement</t>
-        </is>
-      </c>
-      <c r="C372" t="inlineStr"/>
-      <c r="D372" t="inlineStr"/>
+          <t>ImportsDEC</t>
+        </is>
+      </c>
+      <c r="C372" t="inlineStr">
+        <is>
+          <t>$364.9B</t>
+        </is>
+      </c>
+      <c r="D372" t="inlineStr">
+        <is>
+          <t>$352.5B</t>
+        </is>
+      </c>
       <c r="E372" t="inlineStr"/>
-      <c r="F372" t="inlineStr"/>
+      <c r="F372" t="inlineStr">
+        <is>
+          <t>$ 355.0B</t>
+        </is>
+      </c>
       <c r="G372" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="373">
@@ -11406,27 +11410,23 @@
       </c>
       <c r="B373" t="inlineStr">
         <is>
-          <t>Balance of TradeDEC</t>
+          <t>ExportsDEC</t>
         </is>
       </c>
       <c r="C373" t="inlineStr">
         <is>
-          <t>$-98.4B</t>
+          <t>$266.5B</t>
         </is>
       </c>
       <c r="D373" t="inlineStr">
         <is>
-          <t>$-78.9B</t>
-        </is>
-      </c>
-      <c r="E373" t="inlineStr">
-        <is>
-          <t>$-96.6B</t>
-        </is>
-      </c>
+          <t>$273.6B</t>
+        </is>
+      </c>
+      <c r="E373" t="inlineStr"/>
       <c r="F373" t="inlineStr">
         <is>
-          <t>$ -93.0B</t>
+          <t>$ 262B</t>
         </is>
       </c>
       <c r="G373" t="n">
@@ -11689,17 +11689,17 @@
       </c>
       <c r="B382" t="inlineStr">
         <is>
-          <t>EIA Cushing Crude Oil Stocks ChangeJAN/31</t>
+          <t>EIA Refinery Crude Runs ChangeJAN/31</t>
         </is>
       </c>
       <c r="C382" t="inlineStr">
         <is>
-          <t>-0.034M</t>
+          <t>0.16M</t>
         </is>
       </c>
       <c r="D382" t="inlineStr">
         <is>
-          <t>0.326M</t>
+          <t>-0.333M</t>
         </is>
       </c>
       <c r="E382" t="inlineStr"/>
@@ -11716,20 +11716,24 @@
       </c>
       <c r="B383" t="inlineStr">
         <is>
-          <t>EIA Gasoline Production ChangeJAN/31</t>
+          <t>EIA Distillate Stocks ChangeJAN/31</t>
         </is>
       </c>
       <c r="C383" t="inlineStr">
         <is>
-          <t>-0.027M</t>
+          <t>-5.471M</t>
         </is>
       </c>
       <c r="D383" t="inlineStr">
         <is>
-          <t>-0.044M</t>
-        </is>
-      </c>
-      <c r="E383" t="inlineStr"/>
+          <t>-4.994M</t>
+        </is>
+      </c>
+      <c r="E383" t="inlineStr">
+        <is>
+          <t>-1.5M</t>
+        </is>
+      </c>
       <c r="F383" t="inlineStr"/>
       <c r="G383" t="n">
         <v>3</v>
@@ -11743,17 +11747,17 @@
       </c>
       <c r="B384" t="inlineStr">
         <is>
-          <t>EIA Crude Oil Imports ChangeJAN/31</t>
+          <t>EIA Distillate Fuel Production ChangeJAN/31</t>
         </is>
       </c>
       <c r="C384" t="inlineStr">
         <is>
-          <t>-0.178M</t>
+          <t>-0.186M</t>
         </is>
       </c>
       <c r="D384" t="inlineStr">
         <is>
-          <t>0.532M</t>
+          <t>0.028M</t>
         </is>
       </c>
       <c r="E384" t="inlineStr"/>
@@ -11770,23 +11774,27 @@
       </c>
       <c r="B385" t="inlineStr">
         <is>
-          <t>EIA Heating Oil Stocks ChangeJAN/31</t>
+          <t>EIA Gasoline Stocks ChangeJAN/31</t>
         </is>
       </c>
       <c r="C385" t="inlineStr">
         <is>
-          <t>0.373M</t>
+          <t>2.233M</t>
         </is>
       </c>
       <c r="D385" t="inlineStr">
         <is>
-          <t>0.128M</t>
-        </is>
-      </c>
-      <c r="E385" t="inlineStr"/>
+          <t>2.957M</t>
+        </is>
+      </c>
+      <c r="E385" t="inlineStr">
+        <is>
+          <t>1.2M</t>
+        </is>
+      </c>
       <c r="F385" t="inlineStr"/>
       <c r="G385" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="386">
@@ -11797,22 +11805,22 @@
       </c>
       <c r="B386" t="inlineStr">
         <is>
-          <t>EIA Gasoline Stocks ChangeJAN/31</t>
+          <t>EIA Crude Oil Stocks ChangeJAN/31</t>
         </is>
       </c>
       <c r="C386" t="inlineStr">
         <is>
-          <t>2.233M</t>
+          <t>8.664M</t>
         </is>
       </c>
       <c r="D386" t="inlineStr">
         <is>
-          <t>2.957M</t>
+          <t>3.463M</t>
         </is>
       </c>
       <c r="E386" t="inlineStr">
         <is>
-          <t>1.2M</t>
+          <t>2.6M</t>
         </is>
       </c>
       <c r="F386" t="inlineStr"/>
@@ -11828,17 +11836,17 @@
       </c>
       <c r="B387" t="inlineStr">
         <is>
-          <t>EIA Refinery Crude Runs ChangeJAN/31</t>
+          <t>EIA Crude Oil Imports ChangeJAN/31</t>
         </is>
       </c>
       <c r="C387" t="inlineStr">
         <is>
-          <t>0.16M</t>
+          <t>-0.178M</t>
         </is>
       </c>
       <c r="D387" t="inlineStr">
         <is>
-          <t>-0.333M</t>
+          <t>0.532M</t>
         </is>
       </c>
       <c r="E387" t="inlineStr"/>
@@ -11855,17 +11863,17 @@
       </c>
       <c r="B388" t="inlineStr">
         <is>
-          <t>EIA Distillate Fuel Production ChangeJAN/31</t>
+          <t>EIA Gasoline Production ChangeJAN/31</t>
         </is>
       </c>
       <c r="C388" t="inlineStr">
         <is>
-          <t>-0.186M</t>
+          <t>-0.027M</t>
         </is>
       </c>
       <c r="D388" t="inlineStr">
         <is>
-          <t>0.028M</t>
+          <t>-0.044M</t>
         </is>
       </c>
       <c r="E388" t="inlineStr"/>
@@ -11882,27 +11890,23 @@
       </c>
       <c r="B389" t="inlineStr">
         <is>
-          <t>EIA Crude Oil Stocks ChangeJAN/31</t>
+          <t>EIA Cushing Crude Oil Stocks ChangeJAN/31</t>
         </is>
       </c>
       <c r="C389" t="inlineStr">
         <is>
-          <t>8.664M</t>
+          <t>-0.034M</t>
         </is>
       </c>
       <c r="D389" t="inlineStr">
         <is>
-          <t>3.463M</t>
-        </is>
-      </c>
-      <c r="E389" t="inlineStr">
-        <is>
-          <t>2.6M</t>
-        </is>
-      </c>
+          <t>0.326M</t>
+        </is>
+      </c>
+      <c r="E389" t="inlineStr"/>
       <c r="F389" t="inlineStr"/>
       <c r="G389" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="390">
@@ -11913,24 +11917,20 @@
       </c>
       <c r="B390" t="inlineStr">
         <is>
-          <t>EIA Distillate Stocks ChangeJAN/31</t>
+          <t>EIA Heating Oil Stocks ChangeJAN/31</t>
         </is>
       </c>
       <c r="C390" t="inlineStr">
         <is>
-          <t>-5.471M</t>
+          <t>0.373M</t>
         </is>
       </c>
       <c r="D390" t="inlineStr">
         <is>
-          <t>-4.994M</t>
-        </is>
-      </c>
-      <c r="E390" t="inlineStr">
-        <is>
-          <t>-1.5M</t>
-        </is>
-      </c>
+          <t>0.128M</t>
+        </is>
+      </c>
+      <c r="E390" t="inlineStr"/>
       <c r="F390" t="inlineStr"/>
       <c r="G390" t="n">
         <v>3</v>
@@ -12040,31 +12040,31 @@
       </c>
       <c r="B395" t="inlineStr">
         <is>
-          <t>Unit Labour Costs QoQ PrelQ4</t>
+          <t>Continuing Jobless ClaimsJAN/25</t>
         </is>
       </c>
       <c r="C395" t="inlineStr">
         <is>
-          <t>3%</t>
+          <t>1886K</t>
         </is>
       </c>
       <c r="D395" t="inlineStr">
         <is>
-          <t>0.5%</t>
+          <t>1850K</t>
         </is>
       </c>
       <c r="E395" t="inlineStr">
         <is>
-          <t>3.4%</t>
+          <t>1870K</t>
         </is>
       </c>
       <c r="F395" t="inlineStr">
         <is>
-          <t>3%</t>
+          <t>1855.0K</t>
         </is>
       </c>
       <c r="G395" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="396">
@@ -12075,27 +12075,31 @@
       </c>
       <c r="B396" t="inlineStr">
         <is>
-          <t>Jobless Claims 4-week AverageFEB/01</t>
+          <t>Initial Jobless ClaimsFEB/01</t>
         </is>
       </c>
       <c r="C396" t="inlineStr">
         <is>
-          <t>216.75K</t>
+          <t>219K</t>
         </is>
       </c>
       <c r="D396" t="inlineStr">
         <is>
-          <t>212.75K</t>
-        </is>
-      </c>
-      <c r="E396" t="inlineStr"/>
+          <t>208K</t>
+        </is>
+      </c>
+      <c r="E396" t="inlineStr">
+        <is>
+          <t>213K</t>
+        </is>
+      </c>
       <c r="F396" t="inlineStr">
         <is>
-          <t>215.5K</t>
+          <t>215.0K</t>
         </is>
       </c>
       <c r="G396" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="397">
@@ -12106,27 +12110,27 @@
       </c>
       <c r="B397" t="inlineStr">
         <is>
-          <t>Initial Jobless ClaimsFEB/01</t>
+          <t>Nonfarm Productivity QoQ PrelQ4</t>
         </is>
       </c>
       <c r="C397" t="inlineStr">
         <is>
-          <t>219K</t>
+          <t>1.2%</t>
         </is>
       </c>
       <c r="D397" t="inlineStr">
         <is>
-          <t>208K</t>
+          <t>2.3%</t>
         </is>
       </c>
       <c r="E397" t="inlineStr">
         <is>
-          <t>213K</t>
+          <t>1.4%</t>
         </is>
       </c>
       <c r="F397" t="inlineStr">
         <is>
-          <t>215.0K</t>
+          <t>1.9%</t>
         </is>
       </c>
       <c r="G397" t="n">
@@ -12141,31 +12145,31 @@
       </c>
       <c r="B398" t="inlineStr">
         <is>
-          <t>Continuing Jobless ClaimsJAN/25</t>
+          <t>Unit Labour Costs QoQ PrelQ4</t>
         </is>
       </c>
       <c r="C398" t="inlineStr">
         <is>
-          <t>1886K</t>
+          <t>3%</t>
         </is>
       </c>
       <c r="D398" t="inlineStr">
         <is>
-          <t>1850K</t>
+          <t>0.5%</t>
         </is>
       </c>
       <c r="E398" t="inlineStr">
         <is>
-          <t>1870K</t>
+          <t>3.4%</t>
         </is>
       </c>
       <c r="F398" t="inlineStr">
         <is>
-          <t>1855.0K</t>
+          <t>3%</t>
         </is>
       </c>
       <c r="G398" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="399">
@@ -12176,31 +12180,27 @@
       </c>
       <c r="B399" t="inlineStr">
         <is>
-          <t>Nonfarm Productivity QoQ PrelQ4</t>
+          <t>Jobless Claims 4-week AverageFEB/01</t>
         </is>
       </c>
       <c r="C399" t="inlineStr">
         <is>
-          <t>1.2%</t>
+          <t>216.75K</t>
         </is>
       </c>
       <c r="D399" t="inlineStr">
         <is>
-          <t>2.3%</t>
-        </is>
-      </c>
-      <c r="E399" t="inlineStr">
-        <is>
-          <t>1.4%</t>
-        </is>
-      </c>
+          <t>212.75K</t>
+        </is>
+      </c>
+      <c r="E399" t="inlineStr"/>
       <c r="F399" t="inlineStr">
         <is>
-          <t>1.9%</t>
+          <t>215.5K</t>
         </is>
       </c>
       <c r="G399" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="400">
@@ -12442,31 +12442,31 @@
       </c>
       <c r="B409" t="inlineStr">
         <is>
-          <t>Average Hourly Earnings YoYJAN</t>
+          <t>Nonfarm Payrolls PrivateJAN</t>
         </is>
       </c>
       <c r="C409" t="inlineStr">
         <is>
-          <t>4.1%</t>
+          <t>111K</t>
         </is>
       </c>
       <c r="D409" t="inlineStr">
         <is>
-          <t>4.1%</t>
+          <t>273K</t>
         </is>
       </c>
       <c r="E409" t="inlineStr">
         <is>
-          <t>3.8%</t>
+          <t>141K</t>
         </is>
       </c>
       <c r="F409" t="inlineStr">
         <is>
-          <t>3.9%</t>
+          <t>180K</t>
         </is>
       </c>
       <c r="G409" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="410">
@@ -12477,27 +12477,23 @@
       </c>
       <c r="B410" t="inlineStr">
         <is>
-          <t>Average Hourly Earnings MoMJAN</t>
+          <t>Participation RateJAN</t>
         </is>
       </c>
       <c r="C410" t="inlineStr">
         <is>
-          <t>0.5%</t>
+          <t>62.6%</t>
         </is>
       </c>
       <c r="D410" t="inlineStr">
         <is>
-          <t>0.3%</t>
-        </is>
-      </c>
-      <c r="E410" t="inlineStr">
-        <is>
-          <t>0.3%</t>
-        </is>
-      </c>
+          <t>62.5%</t>
+        </is>
+      </c>
+      <c r="E410" t="inlineStr"/>
       <c r="F410" t="inlineStr">
         <is>
-          <t>0.3%</t>
+          <t>62.5%</t>
         </is>
       </c>
       <c r="G410" t="n">
@@ -12512,31 +12508,27 @@
       </c>
       <c r="B411" t="inlineStr">
         <is>
-          <t>Non Farm PayrollsJAN</t>
+          <t>Government PayrollsJAN</t>
         </is>
       </c>
       <c r="C411" t="inlineStr">
         <is>
-          <t>143K</t>
+          <t>32K</t>
         </is>
       </c>
       <c r="D411" t="inlineStr">
         <is>
-          <t>307K</t>
-        </is>
-      </c>
-      <c r="E411" t="inlineStr">
-        <is>
-          <t>170K</t>
-        </is>
-      </c>
+          <t>34K</t>
+        </is>
+      </c>
+      <c r="E411" t="inlineStr"/>
       <c r="F411" t="inlineStr">
         <is>
-          <t>205K</t>
+          <t>25K</t>
         </is>
       </c>
       <c r="G411" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="412">
@@ -12547,31 +12539,31 @@
       </c>
       <c r="B412" t="inlineStr">
         <is>
-          <t>Unemployment RateJAN</t>
+          <t>Manufacturing PayrollsJAN</t>
         </is>
       </c>
       <c r="C412" t="inlineStr">
         <is>
-          <t>4%</t>
+          <t>3K</t>
         </is>
       </c>
       <c r="D412" t="inlineStr">
         <is>
-          <t>4.1%</t>
+          <t>-12K</t>
         </is>
       </c>
       <c r="E412" t="inlineStr">
         <is>
-          <t>4.1%</t>
+          <t>-2K</t>
         </is>
       </c>
       <c r="F412" t="inlineStr">
         <is>
-          <t>4.1%</t>
+          <t>-5K</t>
         </is>
       </c>
       <c r="G412" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="413">
@@ -12582,27 +12574,23 @@
       </c>
       <c r="B413" t="inlineStr">
         <is>
-          <t>Average Weekly HoursJAN</t>
+          <t>U-6 Unemployment RateJAN</t>
         </is>
       </c>
       <c r="C413" t="inlineStr">
         <is>
-          <t>34.1</t>
+          <t>7.5%</t>
         </is>
       </c>
       <c r="D413" t="inlineStr">
         <is>
-          <t>34.2</t>
-        </is>
-      </c>
-      <c r="E413" t="inlineStr">
-        <is>
-          <t>34.3</t>
-        </is>
-      </c>
+          <t>7.5%</t>
+        </is>
+      </c>
+      <c r="E413" t="inlineStr"/>
       <c r="F413" t="inlineStr">
         <is>
-          <t>34.3</t>
+          <t>7.5%</t>
         </is>
       </c>
       <c r="G413" t="n">
@@ -12617,31 +12605,31 @@
       </c>
       <c r="B414" t="inlineStr">
         <is>
-          <t>Manufacturing PayrollsJAN</t>
+          <t>Unemployment RateJAN</t>
         </is>
       </c>
       <c r="C414" t="inlineStr">
         <is>
-          <t>3K</t>
+          <t>4%</t>
         </is>
       </c>
       <c r="D414" t="inlineStr">
         <is>
-          <t>-12K</t>
+          <t>4.1%</t>
         </is>
       </c>
       <c r="E414" t="inlineStr">
         <is>
-          <t>-2K</t>
+          <t>4.1%</t>
         </is>
       </c>
       <c r="F414" t="inlineStr">
         <is>
-          <t>-5K</t>
+          <t>4.1%</t>
         </is>
       </c>
       <c r="G414" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="415">
@@ -12652,31 +12640,31 @@
       </c>
       <c r="B415" t="inlineStr">
         <is>
-          <t>Nonfarm Payrolls PrivateJAN</t>
+          <t>Non Farm PayrollsJAN</t>
         </is>
       </c>
       <c r="C415" t="inlineStr">
         <is>
-          <t>111K</t>
+          <t>143K</t>
         </is>
       </c>
       <c r="D415" t="inlineStr">
         <is>
-          <t>273K</t>
+          <t>307K</t>
         </is>
       </c>
       <c r="E415" t="inlineStr">
         <is>
-          <t>141K</t>
+          <t>170K</t>
         </is>
       </c>
       <c r="F415" t="inlineStr">
         <is>
-          <t>180K</t>
+          <t>205K</t>
         </is>
       </c>
       <c r="G415" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="416">
@@ -12687,27 +12675,31 @@
       </c>
       <c r="B416" t="inlineStr">
         <is>
-          <t>Government PayrollsJAN</t>
+          <t>Average Hourly Earnings MoMJAN</t>
         </is>
       </c>
       <c r="C416" t="inlineStr">
         <is>
-          <t>32K</t>
+          <t>0.5%</t>
         </is>
       </c>
       <c r="D416" t="inlineStr">
         <is>
-          <t>34K</t>
-        </is>
-      </c>
-      <c r="E416" t="inlineStr"/>
+          <t>0.3%</t>
+        </is>
+      </c>
+      <c r="E416" t="inlineStr">
+        <is>
+          <t>0.3%</t>
+        </is>
+      </c>
       <c r="F416" t="inlineStr">
         <is>
-          <t>25K</t>
+          <t>0.3%</t>
         </is>
       </c>
       <c r="G416" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="417">
@@ -12718,27 +12710,31 @@
       </c>
       <c r="B417" t="inlineStr">
         <is>
-          <t>U-6 Unemployment RateJAN</t>
+          <t>Average Hourly Earnings YoYJAN</t>
         </is>
       </c>
       <c r="C417" t="inlineStr">
         <is>
-          <t>7.5%</t>
+          <t>4.1%</t>
         </is>
       </c>
       <c r="D417" t="inlineStr">
         <is>
-          <t>7.5%</t>
-        </is>
-      </c>
-      <c r="E417" t="inlineStr"/>
+          <t>4.1%</t>
+        </is>
+      </c>
+      <c r="E417" t="inlineStr">
+        <is>
+          <t>3.8%</t>
+        </is>
+      </c>
       <c r="F417" t="inlineStr">
         <is>
-          <t>7.5%</t>
+          <t>3.9%</t>
         </is>
       </c>
       <c r="G417" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="418">
@@ -12749,27 +12745,31 @@
       </c>
       <c r="B418" t="inlineStr">
         <is>
-          <t>Participation RateJAN</t>
+          <t>Average Weekly HoursJAN</t>
         </is>
       </c>
       <c r="C418" t="inlineStr">
         <is>
-          <t>62.6%</t>
+          <t>34.1</t>
         </is>
       </c>
       <c r="D418" t="inlineStr">
         <is>
-          <t>62.5%</t>
-        </is>
-      </c>
-      <c r="E418" t="inlineStr"/>
+          <t>34.2</t>
+        </is>
+      </c>
+      <c r="E418" t="inlineStr">
+        <is>
+          <t>34.3</t>
+        </is>
+      </c>
       <c r="F418" t="inlineStr">
         <is>
-          <t>62.5%</t>
+          <t>34.3</t>
         </is>
       </c>
       <c r="G418" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="419">
@@ -13501,23 +13501,23 @@
       </c>
       <c r="B446" t="inlineStr">
         <is>
-          <t>MBA 30-Year Mortgage RateFEB/07</t>
+          <t>MBA Mortgage ApplicationsFEB/07</t>
         </is>
       </c>
       <c r="C446" t="inlineStr">
         <is>
-          <t>6.95%</t>
+          <t>2.3%</t>
         </is>
       </c>
       <c r="D446" t="inlineStr">
         <is>
-          <t>6.97%</t>
+          <t>2.2%</t>
         </is>
       </c>
       <c r="E446" t="inlineStr"/>
       <c r="F446" t="inlineStr"/>
       <c r="G446" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="447">
@@ -13528,17 +13528,17 @@
       </c>
       <c r="B447" t="inlineStr">
         <is>
-          <t>MBA Mortgage Market IndexFEB/07</t>
+          <t>MBA Mortgage Refinance IndexFEB/07</t>
         </is>
       </c>
       <c r="C447" t="inlineStr">
         <is>
-          <t>230.0</t>
+          <t>640.6</t>
         </is>
       </c>
       <c r="D447" t="inlineStr">
         <is>
-          <t>224.8</t>
+          <t>584.3</t>
         </is>
       </c>
       <c r="E447" t="inlineStr"/>
@@ -13555,17 +13555,17 @@
       </c>
       <c r="B448" t="inlineStr">
         <is>
-          <t>MBA Mortgage Refinance IndexFEB/07</t>
+          <t>MBA Purchase IndexFEB/07</t>
         </is>
       </c>
       <c r="C448" t="inlineStr">
         <is>
-          <t>640.6</t>
+          <t>153.1</t>
         </is>
       </c>
       <c r="D448" t="inlineStr">
         <is>
-          <t>584.3</t>
+          <t>156.7</t>
         </is>
       </c>
       <c r="E448" t="inlineStr"/>
@@ -13582,23 +13582,23 @@
       </c>
       <c r="B449" t="inlineStr">
         <is>
-          <t>MBA Mortgage ApplicationsFEB/07</t>
+          <t>MBA 30-Year Mortgage RateFEB/07</t>
         </is>
       </c>
       <c r="C449" t="inlineStr">
         <is>
-          <t>2.3%</t>
+          <t>6.95%</t>
         </is>
       </c>
       <c r="D449" t="inlineStr">
         <is>
-          <t>2.2%</t>
+          <t>6.97%</t>
         </is>
       </c>
       <c r="E449" t="inlineStr"/>
       <c r="F449" t="inlineStr"/>
       <c r="G449" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="450">
@@ -13609,17 +13609,17 @@
       </c>
       <c r="B450" t="inlineStr">
         <is>
-          <t>MBA Purchase IndexFEB/07</t>
+          <t>MBA Mortgage Market IndexFEB/07</t>
         </is>
       </c>
       <c r="C450" t="inlineStr">
         <is>
-          <t>153.1</t>
+          <t>230.0</t>
         </is>
       </c>
       <c r="D450" t="inlineStr">
         <is>
-          <t>156.7</t>
+          <t>224.8</t>
         </is>
       </c>
       <c r="E450" t="inlineStr"/>
@@ -13842,23 +13842,27 @@
       </c>
       <c r="B457" t="inlineStr">
         <is>
-          <t>EIA Crude Oil Imports ChangeFEB/07</t>
+          <t>EIA Crude Oil Stocks ChangeFEB/07</t>
         </is>
       </c>
       <c r="C457" t="inlineStr">
         <is>
-          <t>-0.184M</t>
+          <t>4.07M</t>
         </is>
       </c>
       <c r="D457" t="inlineStr">
         <is>
-          <t>-0.178M</t>
-        </is>
-      </c>
-      <c r="E457" t="inlineStr"/>
+          <t>8.664M</t>
+        </is>
+      </c>
+      <c r="E457" t="inlineStr">
+        <is>
+          <t>3M</t>
+        </is>
+      </c>
       <c r="F457" t="inlineStr"/>
       <c r="G457" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="458">
@@ -13869,17 +13873,17 @@
       </c>
       <c r="B458" t="inlineStr">
         <is>
-          <t>EIA Refinery Crude Runs ChangeFEB/07</t>
+          <t>EIA Heating Oil Stocks ChangeFEB/07</t>
         </is>
       </c>
       <c r="C458" t="inlineStr">
         <is>
-          <t>0.082M</t>
+          <t>0.159M</t>
         </is>
       </c>
       <c r="D458" t="inlineStr">
         <is>
-          <t>0.16M</t>
+          <t>0.373M</t>
         </is>
       </c>
       <c r="E458" t="inlineStr"/>
@@ -13896,17 +13900,17 @@
       </c>
       <c r="B459" t="inlineStr">
         <is>
-          <t>EIA Gasoline Production ChangeFEB/07</t>
+          <t>EIA Cushing Crude Oil Stocks ChangeFEB/07</t>
         </is>
       </c>
       <c r="C459" t="inlineStr">
         <is>
-          <t>0.18M</t>
+          <t>0.872M</t>
         </is>
       </c>
       <c r="D459" t="inlineStr">
         <is>
-          <t>-0.027M</t>
+          <t>-0.034M</t>
         </is>
       </c>
       <c r="E459" t="inlineStr"/>
@@ -13923,27 +13927,23 @@
       </c>
       <c r="B460" t="inlineStr">
         <is>
-          <t>EIA Gasoline Stocks ChangeFEB/07</t>
+          <t>EIA Distillate Fuel Production ChangeFEB/07</t>
         </is>
       </c>
       <c r="C460" t="inlineStr">
         <is>
-          <t>-3.035M</t>
+          <t>-0.009M</t>
         </is>
       </c>
       <c r="D460" t="inlineStr">
         <is>
-          <t>2.233M</t>
-        </is>
-      </c>
-      <c r="E460" t="inlineStr">
-        <is>
-          <t>1.5M</t>
-        </is>
-      </c>
+          <t>-0.186M</t>
+        </is>
+      </c>
+      <c r="E460" t="inlineStr"/>
       <c r="F460" t="inlineStr"/>
       <c r="G460" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="461">
@@ -13985,23 +13985,27 @@
       </c>
       <c r="B462" t="inlineStr">
         <is>
-          <t>EIA Distillate Fuel Production ChangeFEB/07</t>
+          <t>EIA Gasoline Stocks ChangeFEB/07</t>
         </is>
       </c>
       <c r="C462" t="inlineStr">
         <is>
-          <t>-0.009M</t>
+          <t>-3.035M</t>
         </is>
       </c>
       <c r="D462" t="inlineStr">
         <is>
-          <t>-0.186M</t>
-        </is>
-      </c>
-      <c r="E462" t="inlineStr"/>
+          <t>2.233M</t>
+        </is>
+      </c>
+      <c r="E462" t="inlineStr">
+        <is>
+          <t>1.5M</t>
+        </is>
+      </c>
       <c r="F462" t="inlineStr"/>
       <c r="G462" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="463">
@@ -14012,17 +14016,17 @@
       </c>
       <c r="B463" t="inlineStr">
         <is>
-          <t>EIA Cushing Crude Oil Stocks ChangeFEB/07</t>
+          <t>EIA Gasoline Production ChangeFEB/07</t>
         </is>
       </c>
       <c r="C463" t="inlineStr">
         <is>
-          <t>0.872M</t>
+          <t>0.18M</t>
         </is>
       </c>
       <c r="D463" t="inlineStr">
         <is>
-          <t>-0.034M</t>
+          <t>-0.027M</t>
         </is>
       </c>
       <c r="E463" t="inlineStr"/>
@@ -14039,17 +14043,17 @@
       </c>
       <c r="B464" t="inlineStr">
         <is>
-          <t>EIA Heating Oil Stocks ChangeFEB/07</t>
+          <t>EIA Refinery Crude Runs ChangeFEB/07</t>
         </is>
       </c>
       <c r="C464" t="inlineStr">
         <is>
-          <t>0.159M</t>
+          <t>0.082M</t>
         </is>
       </c>
       <c r="D464" t="inlineStr">
         <is>
-          <t>0.373M</t>
+          <t>0.16M</t>
         </is>
       </c>
       <c r="E464" t="inlineStr"/>
@@ -14066,27 +14070,23 @@
       </c>
       <c r="B465" t="inlineStr">
         <is>
-          <t>EIA Crude Oil Stocks ChangeFEB/07</t>
+          <t>EIA Crude Oil Imports ChangeFEB/07</t>
         </is>
       </c>
       <c r="C465" t="inlineStr">
         <is>
-          <t>4.07M</t>
+          <t>-0.184M</t>
         </is>
       </c>
       <c r="D465" t="inlineStr">
         <is>
-          <t>8.664M</t>
-        </is>
-      </c>
-      <c r="E465" t="inlineStr">
-        <is>
-          <t>3M</t>
-        </is>
-      </c>
+          <t>-0.178M</t>
+        </is>
+      </c>
+      <c r="E465" t="inlineStr"/>
       <c r="F465" t="inlineStr"/>
       <c r="G465" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="466">
@@ -14224,7 +14224,7 @@
       </c>
       <c r="B471" t="inlineStr">
         <is>
-          <t>Core PPI MoMJAN</t>
+          <t>PPI Ex Food, Energy and Trade MoMJAN</t>
         </is>
       </c>
       <c r="C471" t="inlineStr">
@@ -14237,18 +14237,14 @@
           <t>0.4%</t>
         </is>
       </c>
-      <c r="E471" t="inlineStr">
-        <is>
-          <t>0.3%</t>
-        </is>
-      </c>
+      <c r="E471" t="inlineStr"/>
       <c r="F471" t="inlineStr">
         <is>
-          <t>0.1%</t>
+          <t>0.2%</t>
         </is>
       </c>
       <c r="G471" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="472">
@@ -14259,31 +14255,27 @@
       </c>
       <c r="B472" t="inlineStr">
         <is>
-          <t>Initial Jobless ClaimsFEB/08</t>
+          <t>Jobless Claims 4-week AverageFEB/08</t>
         </is>
       </c>
       <c r="C472" t="inlineStr">
         <is>
-          <t>213K</t>
+          <t>216K</t>
         </is>
       </c>
       <c r="D472" t="inlineStr">
         <is>
-          <t>220K</t>
-        </is>
-      </c>
-      <c r="E472" t="inlineStr">
-        <is>
-          <t>215K</t>
-        </is>
-      </c>
+          <t>217K</t>
+        </is>
+      </c>
+      <c r="E472" t="inlineStr"/>
       <c r="F472" t="inlineStr">
         <is>
-          <t>215.0K</t>
+          <t>216.0K</t>
         </is>
       </c>
       <c r="G472" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="473">
@@ -14294,23 +14286,27 @@
       </c>
       <c r="B473" t="inlineStr">
         <is>
-          <t>PPIJAN</t>
+          <t>Continuing Jobless ClaimsFEB/01</t>
         </is>
       </c>
       <c r="C473" t="inlineStr">
         <is>
-          <t>147.716</t>
+          <t>1850K</t>
         </is>
       </c>
       <c r="D473" t="inlineStr">
         <is>
-          <t>147.127</t>
-        </is>
-      </c>
-      <c r="E473" t="inlineStr"/>
+          <t>1886K</t>
+        </is>
+      </c>
+      <c r="E473" t="inlineStr">
+        <is>
+          <t>1880K</t>
+        </is>
+      </c>
       <c r="F473" t="inlineStr">
         <is>
-          <t>147.2</t>
+          <t>1875.0K</t>
         </is>
       </c>
       <c r="G473" t="n">
@@ -14325,31 +14321,31 @@
       </c>
       <c r="B474" t="inlineStr">
         <is>
-          <t>PPI YoYJAN</t>
+          <t>PPI MoMJAN</t>
         </is>
       </c>
       <c r="C474" t="inlineStr">
         <is>
-          <t>3.5%</t>
+          <t>0.4%</t>
         </is>
       </c>
       <c r="D474" t="inlineStr">
         <is>
-          <t>3.5%</t>
+          <t>0.5%</t>
         </is>
       </c>
       <c r="E474" t="inlineStr">
         <is>
-          <t>3.2%</t>
+          <t>0.3%</t>
         </is>
       </c>
       <c r="F474" t="inlineStr">
         <is>
-          <t>3.4%</t>
+          <t>0.3%</t>
         </is>
       </c>
       <c r="G474" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="475">
@@ -14360,27 +14356,27 @@
       </c>
       <c r="B475" t="inlineStr">
         <is>
-          <t>Core PPI YoYJAN</t>
+          <t>PPI Ex Food, Energy and Trade YoYJAN</t>
         </is>
       </c>
       <c r="C475" t="inlineStr">
         <is>
-          <t>3.6%</t>
+          <t>3.4%</t>
         </is>
       </c>
       <c r="D475" t="inlineStr">
         <is>
-          <t>3.7%</t>
+          <t>3.5%</t>
         </is>
       </c>
       <c r="E475" t="inlineStr">
         <is>
+          <t>3.2%</t>
+        </is>
+      </c>
+      <c r="F475" t="inlineStr">
+        <is>
           <t>3.3%</t>
-        </is>
-      </c>
-      <c r="F475" t="inlineStr">
-        <is>
-          <t>3.5%</t>
         </is>
       </c>
       <c r="G475" t="n">
@@ -14395,27 +14391,27 @@
       </c>
       <c r="B476" t="inlineStr">
         <is>
-          <t>PPI Ex Food, Energy and Trade YoYJAN</t>
+          <t>PPI YoYJAN</t>
         </is>
       </c>
       <c r="C476" t="inlineStr">
         <is>
+          <t>3.5%</t>
+        </is>
+      </c>
+      <c r="D476" t="inlineStr">
+        <is>
+          <t>3.5%</t>
+        </is>
+      </c>
+      <c r="E476" t="inlineStr">
+        <is>
+          <t>3.2%</t>
+        </is>
+      </c>
+      <c r="F476" t="inlineStr">
+        <is>
           <t>3.4%</t>
-        </is>
-      </c>
-      <c r="D476" t="inlineStr">
-        <is>
-          <t>3.5%</t>
-        </is>
-      </c>
-      <c r="E476" t="inlineStr">
-        <is>
-          <t>3.2%</t>
-        </is>
-      </c>
-      <c r="F476" t="inlineStr">
-        <is>
-          <t>3.3%</t>
         </is>
       </c>
       <c r="G476" t="n">
@@ -14430,31 +14426,27 @@
       </c>
       <c r="B477" t="inlineStr">
         <is>
-          <t>PPI MoMJAN</t>
+          <t>PPIJAN</t>
         </is>
       </c>
       <c r="C477" t="inlineStr">
         <is>
-          <t>0.4%</t>
+          <t>147.716</t>
         </is>
       </c>
       <c r="D477" t="inlineStr">
         <is>
-          <t>0.5%</t>
-        </is>
-      </c>
-      <c r="E477" t="inlineStr">
-        <is>
-          <t>0.3%</t>
-        </is>
-      </c>
+          <t>147.127</t>
+        </is>
+      </c>
+      <c r="E477" t="inlineStr"/>
       <c r="F477" t="inlineStr">
         <is>
-          <t>0.3%</t>
+          <t>147.2</t>
         </is>
       </c>
       <c r="G477" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="478">
@@ -14465,31 +14457,31 @@
       </c>
       <c r="B478" t="inlineStr">
         <is>
-          <t>Continuing Jobless ClaimsFEB/01</t>
+          <t>Initial Jobless ClaimsFEB/08</t>
         </is>
       </c>
       <c r="C478" t="inlineStr">
         <is>
-          <t>1850K</t>
+          <t>213K</t>
         </is>
       </c>
       <c r="D478" t="inlineStr">
         <is>
-          <t>1886K</t>
+          <t>220K</t>
         </is>
       </c>
       <c r="E478" t="inlineStr">
         <is>
-          <t>1880K</t>
+          <t>215K</t>
         </is>
       </c>
       <c r="F478" t="inlineStr">
         <is>
-          <t>1875.0K</t>
+          <t>215.0K</t>
         </is>
       </c>
       <c r="G478" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="479">
@@ -14500,27 +14492,31 @@
       </c>
       <c r="B479" t="inlineStr">
         <is>
-          <t>Jobless Claims 4-week AverageFEB/08</t>
+          <t>Core PPI MoMJAN</t>
         </is>
       </c>
       <c r="C479" t="inlineStr">
         <is>
-          <t>216K</t>
+          <t>0.3%</t>
         </is>
       </c>
       <c r="D479" t="inlineStr">
         <is>
-          <t>217K</t>
-        </is>
-      </c>
-      <c r="E479" t="inlineStr"/>
+          <t>0.4%</t>
+        </is>
+      </c>
+      <c r="E479" t="inlineStr">
+        <is>
+          <t>0.3%</t>
+        </is>
+      </c>
       <c r="F479" t="inlineStr">
         <is>
-          <t>216.0K</t>
+          <t>0.1%</t>
         </is>
       </c>
       <c r="G479" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="480">
@@ -14531,23 +14527,27 @@
       </c>
       <c r="B480" t="inlineStr">
         <is>
-          <t>PPI Ex Food, Energy and Trade MoMJAN</t>
+          <t>Core PPI YoYJAN</t>
         </is>
       </c>
       <c r="C480" t="inlineStr">
         <is>
-          <t>0.3%</t>
+          <t>3.6%</t>
         </is>
       </c>
       <c r="D480" t="inlineStr">
         <is>
-          <t>0.4%</t>
-        </is>
-      </c>
-      <c r="E480" t="inlineStr"/>
+          <t>3.7%</t>
+        </is>
+      </c>
+      <c r="E480" t="inlineStr">
+        <is>
+          <t>3.3%</t>
+        </is>
+      </c>
       <c r="F480" t="inlineStr">
         <is>
-          <t>0.2%</t>
+          <t>3.5%</t>
         </is>
       </c>
       <c r="G480" t="n">
@@ -14728,31 +14728,27 @@
       </c>
       <c r="B487" t="inlineStr">
         <is>
-          <t>Retail Sales MoMJAN</t>
+          <t>Export Prices YoYJAN</t>
         </is>
       </c>
       <c r="C487" t="inlineStr">
         <is>
-          <t>-0.9%</t>
+          <t>2.7%</t>
         </is>
       </c>
       <c r="D487" t="inlineStr">
         <is>
-          <t>0.7%</t>
-        </is>
-      </c>
-      <c r="E487" t="inlineStr">
-        <is>
-          <t>-0.1%</t>
-        </is>
-      </c>
+          <t>2%</t>
+        </is>
+      </c>
+      <c r="E487" t="inlineStr"/>
       <c r="F487" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>2.3%</t>
         </is>
       </c>
       <c r="G487" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="488">
@@ -14763,27 +14759,31 @@
       </c>
       <c r="B488" t="inlineStr">
         <is>
-          <t>Retail Sales Ex Gas/Autos MoMJAN</t>
+          <t>Retail Sales Ex Autos MoMJAN</t>
         </is>
       </c>
       <c r="C488" t="inlineStr">
         <is>
-          <t>-0.5%</t>
+          <t>-0.4%</t>
         </is>
       </c>
       <c r="D488" t="inlineStr">
         <is>
-          <t>0.5%</t>
-        </is>
-      </c>
-      <c r="E488" t="inlineStr"/>
+          <t>0.7%</t>
+        </is>
+      </c>
+      <c r="E488" t="inlineStr">
+        <is>
+          <t>0.3%</t>
+        </is>
+      </c>
       <c r="F488" t="inlineStr">
         <is>
-          <t>0.2%</t>
+          <t>0.3%</t>
         </is>
       </c>
       <c r="G488" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="489">
@@ -14794,22 +14794,22 @@
       </c>
       <c r="B489" t="inlineStr">
         <is>
-          <t>Import Prices MoMJAN</t>
+          <t>Export Prices MoMJAN</t>
         </is>
       </c>
       <c r="C489" t="inlineStr">
         <is>
+          <t>1.3%</t>
+        </is>
+      </c>
+      <c r="D489" t="inlineStr">
+        <is>
+          <t>0.5%</t>
+        </is>
+      </c>
+      <c r="E489" t="inlineStr">
+        <is>
           <t>0.3%</t>
-        </is>
-      </c>
-      <c r="D489" t="inlineStr">
-        <is>
-          <t>0.2%</t>
-        </is>
-      </c>
-      <c r="E489" t="inlineStr">
-        <is>
-          <t>0.4%</t>
         </is>
       </c>
       <c r="F489" t="inlineStr">
@@ -14829,23 +14829,23 @@
       </c>
       <c r="B490" t="inlineStr">
         <is>
-          <t>Export Prices YoYJAN</t>
+          <t>Retail Sales YoYJAN</t>
         </is>
       </c>
       <c r="C490" t="inlineStr">
         <is>
-          <t>2.7%</t>
+          <t>4.2%</t>
         </is>
       </c>
       <c r="D490" t="inlineStr">
         <is>
-          <t>2%</t>
+          <t>4.4%</t>
         </is>
       </c>
       <c r="E490" t="inlineStr"/>
       <c r="F490" t="inlineStr">
         <is>
-          <t>2.3%</t>
+          <t>3.7%</t>
         </is>
       </c>
       <c r="G490" t="n">
@@ -14860,31 +14860,27 @@
       </c>
       <c r="B491" t="inlineStr">
         <is>
-          <t>Retail Sales Control Group MoMJAN</t>
+          <t>Import Prices YoYJAN</t>
         </is>
       </c>
       <c r="C491" t="inlineStr">
         <is>
-          <t>-0.8%</t>
+          <t>1.9%</t>
         </is>
       </c>
       <c r="D491" t="inlineStr">
         <is>
-          <t>0.8%</t>
-        </is>
-      </c>
-      <c r="E491" t="inlineStr">
-        <is>
-          <t>0.3%</t>
-        </is>
-      </c>
+          <t>2.2%</t>
+        </is>
+      </c>
+      <c r="E491" t="inlineStr"/>
       <c r="F491" t="inlineStr">
         <is>
-          <t>0.4%</t>
+          <t>2.8%</t>
         </is>
       </c>
       <c r="G491" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="492">
@@ -14895,27 +14891,31 @@
       </c>
       <c r="B492" t="inlineStr">
         <is>
-          <t>Import Prices YoYJAN</t>
+          <t>Import Prices MoMJAN</t>
         </is>
       </c>
       <c r="C492" t="inlineStr">
         <is>
-          <t>1.9%</t>
+          <t>0.3%</t>
         </is>
       </c>
       <c r="D492" t="inlineStr">
         <is>
-          <t>2.2%</t>
-        </is>
-      </c>
-      <c r="E492" t="inlineStr"/>
+          <t>0.2%</t>
+        </is>
+      </c>
+      <c r="E492" t="inlineStr">
+        <is>
+          <t>0.4%</t>
+        </is>
+      </c>
       <c r="F492" t="inlineStr">
         <is>
-          <t>2.8%</t>
+          <t>0.3%</t>
         </is>
       </c>
       <c r="G492" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="493">
@@ -14926,23 +14926,23 @@
       </c>
       <c r="B493" t="inlineStr">
         <is>
-          <t>Retail Sales YoYJAN</t>
+          <t>Retail Sales Ex Gas/Autos MoMJAN</t>
         </is>
       </c>
       <c r="C493" t="inlineStr">
         <is>
-          <t>4.2%</t>
+          <t>-0.5%</t>
         </is>
       </c>
       <c r="D493" t="inlineStr">
         <is>
-          <t>4.4%</t>
+          <t>0.5%</t>
         </is>
       </c>
       <c r="E493" t="inlineStr"/>
       <c r="F493" t="inlineStr">
         <is>
-          <t>3.7%</t>
+          <t>0.2%</t>
         </is>
       </c>
       <c r="G493" t="n">
@@ -14957,31 +14957,31 @@
       </c>
       <c r="B494" t="inlineStr">
         <is>
-          <t>Export Prices MoMJAN</t>
+          <t>Retail Sales MoMJAN</t>
         </is>
       </c>
       <c r="C494" t="inlineStr">
         <is>
-          <t>1.3%</t>
+          <t>-0.9%</t>
         </is>
       </c>
       <c r="D494" t="inlineStr">
         <is>
-          <t>0.5%</t>
+          <t>0.7%</t>
         </is>
       </c>
       <c r="E494" t="inlineStr">
         <is>
-          <t>0.3%</t>
+          <t>-0.1%</t>
         </is>
       </c>
       <c r="F494" t="inlineStr">
         <is>
-          <t>0.3%</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="G494" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="495">
@@ -14992,17 +14992,17 @@
       </c>
       <c r="B495" t="inlineStr">
         <is>
-          <t>Retail Sales Ex Autos MoMJAN</t>
+          <t>Retail Sales Control Group MoMJAN</t>
         </is>
       </c>
       <c r="C495" t="inlineStr">
         <is>
-          <t>-0.4%</t>
+          <t>-0.8%</t>
         </is>
       </c>
       <c r="D495" t="inlineStr">
         <is>
-          <t>0.7%</t>
+          <t>0.8%</t>
         </is>
       </c>
       <c r="E495" t="inlineStr">
@@ -15012,7 +15012,7 @@
       </c>
       <c r="F495" t="inlineStr">
         <is>
-          <t>0.3%</t>
+          <t>0.4%</t>
         </is>
       </c>
       <c r="G495" t="n">
@@ -15629,17 +15629,17 @@
       </c>
       <c r="B518" t="inlineStr">
         <is>
-          <t>Foreign Bond InvestmentDEC</t>
+          <t>Overall Net Capital FlowsDEC</t>
         </is>
       </c>
       <c r="C518" t="inlineStr">
         <is>
-          <t>$-49.7B</t>
+          <t>$87.1B</t>
         </is>
       </c>
       <c r="D518" t="inlineStr">
         <is>
-          <t>$-34.4B</t>
+          <t>$134.1B</t>
         </is>
       </c>
       <c r="E518" t="inlineStr"/>
@@ -15687,17 +15687,17 @@
       </c>
       <c r="B520" t="inlineStr">
         <is>
-          <t>Overall Net Capital FlowsDEC</t>
+          <t>Foreign Bond InvestmentDEC</t>
         </is>
       </c>
       <c r="C520" t="inlineStr">
         <is>
-          <t>$87.1B</t>
+          <t>$-49.7B</t>
         </is>
       </c>
       <c r="D520" t="inlineStr">
         <is>
-          <t>$134.1B</t>
+          <t>$-34.4B</t>
         </is>
       </c>
       <c r="E520" t="inlineStr"/>
@@ -17326,7 +17326,7 @@
       </c>
       <c r="B577" t="inlineStr">
         <is>
-          <t>Fed Jefferson Speech</t>
+          <t>Fed Daly Speech</t>
         </is>
       </c>
       <c r="C577" t="inlineStr"/>
@@ -17345,7 +17345,7 @@
       </c>
       <c r="B578" t="inlineStr">
         <is>
-          <t>Fed Daly Speech</t>
+          <t>Fed Jefferson Speech</t>
         </is>
       </c>
       <c r="C578" t="inlineStr"/>
@@ -17630,31 +17630,27 @@
       </c>
       <c r="B589" t="inlineStr">
         <is>
-          <t>S&amp;P/Case-Shiller Home Price YoYDEC</t>
+          <t>House Price Index YoYDEC</t>
         </is>
       </c>
       <c r="C589" t="inlineStr">
         <is>
+          <t>4.7%</t>
+        </is>
+      </c>
+      <c r="D589" t="inlineStr">
+        <is>
           <t>4.5%</t>
         </is>
       </c>
-      <c r="D589" t="inlineStr">
-        <is>
-          <t>4.3%</t>
-        </is>
-      </c>
-      <c r="E589" t="inlineStr">
-        <is>
-          <t>4.4%</t>
-        </is>
-      </c>
+      <c r="E589" t="inlineStr"/>
       <c r="F589" t="inlineStr">
         <is>
-          <t>4.4%</t>
+          <t>4.1%</t>
         </is>
       </c>
       <c r="G589" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="590">
@@ -17665,19 +17661,23 @@
       </c>
       <c r="B590" t="inlineStr">
         <is>
-          <t>House Price Index YoYDEC</t>
-        </is>
-      </c>
-      <c r="C590" t="inlineStr"/>
+          <t>S&amp;P/Case-Shiller Home Price MoMDEC</t>
+        </is>
+      </c>
+      <c r="C590" t="inlineStr">
+        <is>
+          <t>-0.1%</t>
+        </is>
+      </c>
       <c r="D590" t="inlineStr">
         <is>
-          <t>4.2%</t>
+          <t>-0.1%</t>
         </is>
       </c>
       <c r="E590" t="inlineStr"/>
       <c r="F590" t="inlineStr">
         <is>
-          <t>4.1%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="G590" t="n">
@@ -17692,19 +17692,27 @@
       </c>
       <c r="B591" t="inlineStr">
         <is>
-          <t>House Price IndexDEC</t>
-        </is>
-      </c>
-      <c r="C591" t="inlineStr"/>
+          <t>House Price Index MoMDEC</t>
+        </is>
+      </c>
+      <c r="C591" t="inlineStr">
+        <is>
+          <t>0.4%</t>
+        </is>
+      </c>
       <c r="D591" t="inlineStr">
         <is>
-          <t>433.4</t>
-        </is>
-      </c>
-      <c r="E591" t="inlineStr"/>
+          <t>0.4%</t>
+        </is>
+      </c>
+      <c r="E591" t="inlineStr">
+        <is>
+          <t>0.2%</t>
+        </is>
+      </c>
       <c r="F591" t="inlineStr">
         <is>
-          <t>434.3</t>
+          <t>0.2%</t>
         </is>
       </c>
       <c r="G591" t="n">
@@ -17719,27 +17727,27 @@
       </c>
       <c r="B592" t="inlineStr">
         <is>
-          <t>S&amp;P/Case-Shiller Home Price YoYDEC</t>
-        </is>
-      </c>
-      <c r="C592" t="inlineStr"/>
+          <t>House Price IndexDEC</t>
+        </is>
+      </c>
+      <c r="C592" t="inlineStr">
+        <is>
+          <t>436.1</t>
+        </is>
+      </c>
       <c r="D592" t="inlineStr">
         <is>
-          <t>4.3%</t>
-        </is>
-      </c>
-      <c r="E592" t="inlineStr">
-        <is>
-          <t>4.4%</t>
-        </is>
-      </c>
+          <t>434.3</t>
+        </is>
+      </c>
+      <c r="E592" t="inlineStr"/>
       <c r="F592" t="inlineStr">
         <is>
-          <t>4.4%</t>
+          <t>434.3</t>
         </is>
       </c>
       <c r="G592" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="593">
@@ -17750,19 +17758,23 @@
       </c>
       <c r="B593" t="inlineStr">
         <is>
-          <t>S&amp;P/Case-Shiller Home Price MoMDEC</t>
+          <t>House Price Index MoMDEC</t>
         </is>
       </c>
       <c r="C593" t="inlineStr"/>
       <c r="D593" t="inlineStr">
         <is>
-          <t>-0.1%</t>
-        </is>
-      </c>
-      <c r="E593" t="inlineStr"/>
+          <t>0.3%</t>
+        </is>
+      </c>
+      <c r="E593" t="inlineStr">
+        <is>
+          <t>0.2%</t>
+        </is>
+      </c>
       <c r="F593" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>0.2%</t>
         </is>
       </c>
       <c r="G593" t="n">
@@ -17777,23 +17789,19 @@
       </c>
       <c r="B594" t="inlineStr">
         <is>
-          <t>House Price Index MoMDEC</t>
+          <t>S&amp;P/Case-Shiller Home Price MoMDEC</t>
         </is>
       </c>
       <c r="C594" t="inlineStr"/>
       <c r="D594" t="inlineStr">
         <is>
-          <t>0.3%</t>
-        </is>
-      </c>
-      <c r="E594" t="inlineStr">
-        <is>
-          <t>0.2%</t>
-        </is>
-      </c>
+          <t>-0.1%</t>
+        </is>
+      </c>
+      <c r="E594" t="inlineStr"/>
       <c r="F594" t="inlineStr">
         <is>
-          <t>0.2%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="G594" t="n">
@@ -17808,27 +17816,27 @@
       </c>
       <c r="B595" t="inlineStr">
         <is>
-          <t>House Price Index YoYDEC</t>
-        </is>
-      </c>
-      <c r="C595" t="inlineStr">
-        <is>
-          <t>4.7%</t>
-        </is>
-      </c>
+          <t>S&amp;P/Case-Shiller Home Price YoYDEC</t>
+        </is>
+      </c>
+      <c r="C595" t="inlineStr"/>
       <c r="D595" t="inlineStr">
         <is>
-          <t>4.5%</t>
-        </is>
-      </c>
-      <c r="E595" t="inlineStr"/>
+          <t>4.3%</t>
+        </is>
+      </c>
+      <c r="E595" t="inlineStr">
+        <is>
+          <t>4.4%</t>
+        </is>
+      </c>
       <c r="F595" t="inlineStr">
         <is>
-          <t>4.1%</t>
+          <t>4.4%</t>
         </is>
       </c>
       <c r="G595" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="596">
@@ -17842,14 +17850,10 @@
           <t>House Price IndexDEC</t>
         </is>
       </c>
-      <c r="C596" t="inlineStr">
-        <is>
-          <t>436.1</t>
-        </is>
-      </c>
+      <c r="C596" t="inlineStr"/>
       <c r="D596" t="inlineStr">
         <is>
-          <t>434.3</t>
+          <t>433.4</t>
         </is>
       </c>
       <c r="E596" t="inlineStr"/>
@@ -17870,27 +17874,19 @@
       </c>
       <c r="B597" t="inlineStr">
         <is>
-          <t>House Price Index MoMDEC</t>
-        </is>
-      </c>
-      <c r="C597" t="inlineStr">
-        <is>
-          <t>0.4%</t>
-        </is>
-      </c>
+          <t>House Price Index YoYDEC</t>
+        </is>
+      </c>
+      <c r="C597" t="inlineStr"/>
       <c r="D597" t="inlineStr">
         <is>
-          <t>0.4%</t>
-        </is>
-      </c>
-      <c r="E597" t="inlineStr">
-        <is>
-          <t>0.2%</t>
-        </is>
-      </c>
+          <t>4.2%</t>
+        </is>
+      </c>
+      <c r="E597" t="inlineStr"/>
       <c r="F597" t="inlineStr">
         <is>
-          <t>0.2%</t>
+          <t>4.1%</t>
         </is>
       </c>
       <c r="G597" t="n">
@@ -17905,27 +17901,31 @@
       </c>
       <c r="B598" t="inlineStr">
         <is>
-          <t>S&amp;P/Case-Shiller Home Price MoMDEC</t>
+          <t>S&amp;P/Case-Shiller Home Price YoYDEC</t>
         </is>
       </c>
       <c r="C598" t="inlineStr">
         <is>
-          <t>-0.1%</t>
+          <t>4.5%</t>
         </is>
       </c>
       <c r="D598" t="inlineStr">
         <is>
-          <t>-0.1%</t>
-        </is>
-      </c>
-      <c r="E598" t="inlineStr"/>
+          <t>4.3%</t>
+        </is>
+      </c>
+      <c r="E598" t="inlineStr">
+        <is>
+          <t>4.4%</t>
+        </is>
+      </c>
       <c r="F598" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>4.4%</t>
         </is>
       </c>
       <c r="G598" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="599">
@@ -18187,7 +18187,11 @@
           <t>Dallas Fed Services Revenues IndexFEB</t>
         </is>
       </c>
-      <c r="C607" t="inlineStr"/>
+      <c r="C607" t="inlineStr">
+        <is>
+          <t>8.2</t>
+        </is>
+      </c>
       <c r="D607" t="inlineStr">
         <is>
           <t>5.7</t>
@@ -18214,7 +18218,11 @@
           <t>Dallas Fed Services IndexFEB</t>
         </is>
       </c>
-      <c r="C608" t="inlineStr"/>
+      <c r="C608" t="inlineStr">
+        <is>
+          <t>4.6</t>
+        </is>
+      </c>
       <c r="D608" t="inlineStr">
         <is>
           <t>7.4</t>
@@ -18238,23 +18246,19 @@
       </c>
       <c r="B609" t="inlineStr">
         <is>
-          <t>Dallas Fed Services IndexFEB</t>
-        </is>
-      </c>
-      <c r="C609" t="inlineStr">
-        <is>
-          <t>4.6</t>
-        </is>
-      </c>
+          <t>Dallas Fed Services Revenues IndexFEB</t>
+        </is>
+      </c>
+      <c r="C609" t="inlineStr"/>
       <c r="D609" t="inlineStr">
         <is>
-          <t>7.4</t>
+          <t>5.7</t>
         </is>
       </c>
       <c r="E609" t="inlineStr"/>
       <c r="F609" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>7</t>
         </is>
       </c>
       <c r="G609" t="n">
@@ -18269,23 +18273,19 @@
       </c>
       <c r="B610" t="inlineStr">
         <is>
-          <t>Dallas Fed Services Revenues IndexFEB</t>
-        </is>
-      </c>
-      <c r="C610" t="inlineStr">
-        <is>
-          <t>8.2</t>
-        </is>
-      </c>
+          <t>Dallas Fed Services IndexFEB</t>
+        </is>
+      </c>
+      <c r="C610" t="inlineStr"/>
       <c r="D610" t="inlineStr">
         <is>
-          <t>5.7</t>
+          <t>7.4</t>
         </is>
       </c>
       <c r="E610" t="inlineStr"/>
       <c r="F610" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>9</t>
         </is>
       </c>
       <c r="G610" t="n">
@@ -18496,19 +18496,23 @@
       </c>
       <c r="B619" t="inlineStr">
         <is>
-          <t>MBA 30-Year Mortgage RateFEB/21</t>
-        </is>
-      </c>
-      <c r="C619" t="inlineStr"/>
+          <t>MBA Mortgage Market IndexFEB/21</t>
+        </is>
+      </c>
+      <c r="C619" t="inlineStr">
+        <is>
+          <t>212.3</t>
+        </is>
+      </c>
       <c r="D619" t="inlineStr">
         <is>
-          <t>6.93%</t>
+          <t>214.9</t>
         </is>
       </c>
       <c r="E619" t="inlineStr"/>
       <c r="F619" t="inlineStr"/>
       <c r="G619" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="620">
@@ -18522,7 +18526,11 @@
           <t>MBA Purchase IndexFEB/21</t>
         </is>
       </c>
-      <c r="C620" t="inlineStr"/>
+      <c r="C620" t="inlineStr">
+        <is>
+          <t>144.3</t>
+        </is>
+      </c>
       <c r="D620" t="inlineStr">
         <is>
           <t>144.0</t>
@@ -18542,13 +18550,13 @@
       </c>
       <c r="B621" t="inlineStr">
         <is>
-          <t>MBA Mortgage ApplicationsFEB/21</t>
+          <t>MBA Mortgage Market IndexFEB/21</t>
         </is>
       </c>
       <c r="C621" t="inlineStr"/>
       <c r="D621" t="inlineStr">
         <is>
-          <t>-6.6%</t>
+          <t>214.9</t>
         </is>
       </c>
       <c r="E621" t="inlineStr"/>
@@ -18565,17 +18573,17 @@
       </c>
       <c r="B622" t="inlineStr">
         <is>
-          <t>MBA Mortgage ApplicationsFEB/21</t>
+          <t>MBA Mortgage Refinance IndexFEB/21</t>
         </is>
       </c>
       <c r="C622" t="inlineStr">
         <is>
-          <t>-1.2%</t>
+          <t>572.5</t>
         </is>
       </c>
       <c r="D622" t="inlineStr">
         <is>
-          <t>-6.6%</t>
+          <t>593.6</t>
         </is>
       </c>
       <c r="E622" t="inlineStr"/>
@@ -18592,19 +18600,23 @@
       </c>
       <c r="B623" t="inlineStr">
         <is>
-          <t>MBA Mortgage Refinance IndexFEB/21</t>
-        </is>
-      </c>
-      <c r="C623" t="inlineStr"/>
+          <t>MBA 30-Year Mortgage RateFEB/21</t>
+        </is>
+      </c>
+      <c r="C623" t="inlineStr">
+        <is>
+          <t>6.88%</t>
+        </is>
+      </c>
       <c r="D623" t="inlineStr">
         <is>
-          <t>593.6</t>
+          <t>6.93%</t>
         </is>
       </c>
       <c r="E623" t="inlineStr"/>
       <c r="F623" t="inlineStr"/>
       <c r="G623" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="624">
@@ -18615,23 +18627,19 @@
       </c>
       <c r="B624" t="inlineStr">
         <is>
-          <t>MBA 30-Year Mortgage RateFEB/21</t>
-        </is>
-      </c>
-      <c r="C624" t="inlineStr">
-        <is>
-          <t>6.88%</t>
-        </is>
-      </c>
+          <t>MBA Purchase IndexFEB/21</t>
+        </is>
+      </c>
+      <c r="C624" t="inlineStr"/>
       <c r="D624" t="inlineStr">
         <is>
-          <t>6.93%</t>
+          <t>144.0</t>
         </is>
       </c>
       <c r="E624" t="inlineStr"/>
       <c r="F624" t="inlineStr"/>
       <c r="G624" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="625">
@@ -18642,17 +18650,17 @@
       </c>
       <c r="B625" t="inlineStr">
         <is>
-          <t>MBA Mortgage Market IndexFEB/21</t>
+          <t>MBA Mortgage ApplicationsFEB/21</t>
         </is>
       </c>
       <c r="C625" t="inlineStr">
         <is>
-          <t>212.3</t>
+          <t>-1.2%</t>
         </is>
       </c>
       <c r="D625" t="inlineStr">
         <is>
-          <t>214.9</t>
+          <t>-6.6%</t>
         </is>
       </c>
       <c r="E625" t="inlineStr"/>
@@ -18669,17 +18677,13 @@
       </c>
       <c r="B626" t="inlineStr">
         <is>
-          <t>MBA Mortgage Refinance IndexFEB/21</t>
-        </is>
-      </c>
-      <c r="C626" t="inlineStr">
-        <is>
-          <t>572.5</t>
-        </is>
-      </c>
+          <t>MBA Mortgage ApplicationsFEB/21</t>
+        </is>
+      </c>
+      <c r="C626" t="inlineStr"/>
       <c r="D626" t="inlineStr">
         <is>
-          <t>593.6</t>
+          <t>-6.6%</t>
         </is>
       </c>
       <c r="E626" t="inlineStr"/>
@@ -18696,13 +18700,13 @@
       </c>
       <c r="B627" t="inlineStr">
         <is>
-          <t>MBA Mortgage Market IndexFEB/21</t>
+          <t>MBA Mortgage Refinance IndexFEB/21</t>
         </is>
       </c>
       <c r="C627" t="inlineStr"/>
       <c r="D627" t="inlineStr">
         <is>
-          <t>214.9</t>
+          <t>593.6</t>
         </is>
       </c>
       <c r="E627" t="inlineStr"/>
@@ -18719,23 +18723,19 @@
       </c>
       <c r="B628" t="inlineStr">
         <is>
-          <t>MBA Purchase IndexFEB/21</t>
-        </is>
-      </c>
-      <c r="C628" t="inlineStr">
-        <is>
-          <t>144.3</t>
-        </is>
-      </c>
+          <t>MBA 30-Year Mortgage RateFEB/21</t>
+        </is>
+      </c>
+      <c r="C628" t="inlineStr"/>
       <c r="D628" t="inlineStr">
         <is>
-          <t>144.0</t>
+          <t>6.93%</t>
         </is>
       </c>
       <c r="E628" t="inlineStr"/>
       <c r="F628" t="inlineStr"/>
       <c r="G628" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="629">
@@ -18908,10 +18908,14 @@
           <t>New Home SalesJAN</t>
         </is>
       </c>
-      <c r="C634" t="inlineStr"/>
+      <c r="C634" t="inlineStr">
+        <is>
+          <t>0.657M</t>
+        </is>
+      </c>
       <c r="D634" t="inlineStr">
         <is>
-          <t>0.698M</t>
+          <t>0.734M</t>
         </is>
       </c>
       <c r="E634" t="inlineStr">
@@ -18939,10 +18943,14 @@
           <t>New Home Sales MoMJAN</t>
         </is>
       </c>
-      <c r="C635" t="inlineStr"/>
+      <c r="C635" t="inlineStr">
+        <is>
+          <t>-10.5%</t>
+        </is>
+      </c>
       <c r="D635" t="inlineStr">
         <is>
-          <t>3.6%</t>
+          <t>8.1%</t>
         </is>
       </c>
       <c r="E635" t="inlineStr"/>
@@ -18966,14 +18974,10 @@
           <t>New Home Sales MoMJAN</t>
         </is>
       </c>
-      <c r="C636" t="inlineStr">
-        <is>
-          <t>-10.5%</t>
-        </is>
-      </c>
+      <c r="C636" t="inlineStr"/>
       <c r="D636" t="inlineStr">
         <is>
-          <t>8.1%</t>
+          <t>3.6%</t>
         </is>
       </c>
       <c r="E636" t="inlineStr"/>
@@ -18997,14 +19001,10 @@
           <t>New Home SalesJAN</t>
         </is>
       </c>
-      <c r="C637" t="inlineStr">
-        <is>
-          <t>0.657M</t>
-        </is>
-      </c>
+      <c r="C637" t="inlineStr"/>
       <c r="D637" t="inlineStr">
         <is>
-          <t>0.734M</t>
+          <t>0.698M</t>
         </is>
       </c>
       <c r="E637" t="inlineStr">
@@ -19029,27 +19029,19 @@
       </c>
       <c r="B638" t="inlineStr">
         <is>
-          <t>EIA Gasoline Stocks ChangeFEB/21</t>
-        </is>
-      </c>
-      <c r="C638" t="inlineStr">
-        <is>
-          <t>0.369M</t>
-        </is>
-      </c>
+          <t>EIA Cushing Crude Oil Stocks ChangeFEB/21</t>
+        </is>
+      </c>
+      <c r="C638" t="inlineStr"/>
       <c r="D638" t="inlineStr">
         <is>
-          <t>-0.151M</t>
-        </is>
-      </c>
-      <c r="E638" t="inlineStr">
-        <is>
-          <t>-1.30M</t>
-        </is>
-      </c>
+          <t>1.472M</t>
+        </is>
+      </c>
+      <c r="E638" t="inlineStr"/>
       <c r="F638" t="inlineStr"/>
       <c r="G638" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="639">
@@ -19060,23 +19052,23 @@
       </c>
       <c r="B639" t="inlineStr">
         <is>
-          <t>EIA Crude Oil Imports ChangeFEB/21</t>
-        </is>
-      </c>
-      <c r="C639" t="inlineStr">
-        <is>
-          <t>0.292M</t>
-        </is>
-      </c>
+          <t>EIA Gasoline Stocks ChangeFEB/21</t>
+        </is>
+      </c>
+      <c r="C639" t="inlineStr"/>
       <c r="D639" t="inlineStr">
         <is>
-          <t>-0.961M</t>
-        </is>
-      </c>
-      <c r="E639" t="inlineStr"/>
+          <t>-0.151M</t>
+        </is>
+      </c>
+      <c r="E639" t="inlineStr">
+        <is>
+          <t>-1.30M</t>
+        </is>
+      </c>
       <c r="F639" t="inlineStr"/>
       <c r="G639" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="640">
@@ -19087,23 +19079,23 @@
       </c>
       <c r="B640" t="inlineStr">
         <is>
-          <t>EIA Cushing Crude Oil Stocks ChangeFEB/21</t>
-        </is>
-      </c>
-      <c r="C640" t="inlineStr">
-        <is>
-          <t>1.282M</t>
-        </is>
-      </c>
+          <t>EIA Crude Oil Stocks ChangeFEB/21</t>
+        </is>
+      </c>
+      <c r="C640" t="inlineStr"/>
       <c r="D640" t="inlineStr">
         <is>
-          <t>1.472M</t>
-        </is>
-      </c>
-      <c r="E640" t="inlineStr"/>
+          <t>4.633M</t>
+        </is>
+      </c>
+      <c r="E640" t="inlineStr">
+        <is>
+          <t>2.34M</t>
+        </is>
+      </c>
       <c r="F640" t="inlineStr"/>
       <c r="G640" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="641">
@@ -19114,19 +19106,27 @@
       </c>
       <c r="B641" t="inlineStr">
         <is>
-          <t>EIA Crude Oil Imports ChangeFEB/21</t>
-        </is>
-      </c>
-      <c r="C641" t="inlineStr"/>
+          <t>EIA Crude Oil Stocks ChangeFEB/21</t>
+        </is>
+      </c>
+      <c r="C641" t="inlineStr">
+        <is>
+          <t>-2.332M</t>
+        </is>
+      </c>
       <c r="D641" t="inlineStr">
         <is>
-          <t>-0.961M</t>
-        </is>
-      </c>
-      <c r="E641" t="inlineStr"/>
+          <t>4.633M</t>
+        </is>
+      </c>
+      <c r="E641" t="inlineStr">
+        <is>
+          <t>2.54M</t>
+        </is>
+      </c>
       <c r="F641" t="inlineStr"/>
       <c r="G641" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="642">
@@ -19140,11 +19140,7 @@
           <t>EIA Distillate Stocks ChangeFEB/21</t>
         </is>
       </c>
-      <c r="C642" t="inlineStr">
-        <is>
-          <t>3.908M</t>
-        </is>
-      </c>
+      <c r="C642" t="inlineStr"/>
       <c r="D642" t="inlineStr">
         <is>
           <t>-2.051M</t>
@@ -19171,11 +19167,7 @@
           <t>EIA Gasoline Production ChangeFEB/21</t>
         </is>
       </c>
-      <c r="C643" t="inlineStr">
-        <is>
-          <t>-0.02M</t>
-        </is>
-      </c>
+      <c r="C643" t="inlineStr"/>
       <c r="D643" t="inlineStr">
         <is>
           <t>-0.156M</t>
@@ -19198,11 +19190,7 @@
           <t>EIA Heating Oil Stocks ChangeFEB/21</t>
         </is>
       </c>
-      <c r="C644" t="inlineStr">
-        <is>
-          <t>0.134M</t>
-        </is>
-      </c>
+      <c r="C644" t="inlineStr"/>
       <c r="D644" t="inlineStr">
         <is>
           <t>-0.343M</t>
@@ -19225,11 +19213,7 @@
           <t>EIA Refinery Crude Runs ChangeFEB/21</t>
         </is>
       </c>
-      <c r="C645" t="inlineStr">
-        <is>
-          <t>0.317M</t>
-        </is>
-      </c>
+      <c r="C645" t="inlineStr"/>
       <c r="D645" t="inlineStr">
         <is>
           <t>-0.015M</t>
@@ -19252,11 +19236,7 @@
           <t>EIA Distillate Fuel Production ChangeFEB/21</t>
         </is>
       </c>
-      <c r="C646" t="inlineStr">
-        <is>
-          <t>0.439M</t>
-        </is>
-      </c>
+      <c r="C646" t="inlineStr"/>
       <c r="D646" t="inlineStr">
         <is>
           <t>0.18M</t>
@@ -19279,7 +19259,11 @@
           <t>EIA Refinery Crude Runs ChangeFEB/21</t>
         </is>
       </c>
-      <c r="C647" t="inlineStr"/>
+      <c r="C647" t="inlineStr">
+        <is>
+          <t>0.317M</t>
+        </is>
+      </c>
       <c r="D647" t="inlineStr">
         <is>
           <t>-0.015M</t>
@@ -19302,7 +19286,11 @@
           <t>EIA Heating Oil Stocks ChangeFEB/21</t>
         </is>
       </c>
-      <c r="C648" t="inlineStr"/>
+      <c r="C648" t="inlineStr">
+        <is>
+          <t>0.134M</t>
+        </is>
+      </c>
       <c r="D648" t="inlineStr">
         <is>
           <t>-0.343M</t>
@@ -19325,7 +19313,11 @@
           <t>EIA Gasoline Production ChangeFEB/21</t>
         </is>
       </c>
-      <c r="C649" t="inlineStr"/>
+      <c r="C649" t="inlineStr">
+        <is>
+          <t>-0.02M</t>
+        </is>
+      </c>
       <c r="D649" t="inlineStr">
         <is>
           <t>-0.156M</t>
@@ -19348,7 +19340,11 @@
           <t>EIA Distillate Stocks ChangeFEB/21</t>
         </is>
       </c>
-      <c r="C650" t="inlineStr"/>
+      <c r="C650" t="inlineStr">
+        <is>
+          <t>3.908M</t>
+        </is>
+      </c>
       <c r="D650" t="inlineStr">
         <is>
           <t>-2.051M</t>
@@ -19372,13 +19368,13 @@
       </c>
       <c r="B651" t="inlineStr">
         <is>
-          <t>EIA Distillate Fuel Production ChangeFEB/21</t>
+          <t>EIA Crude Oil Imports ChangeFEB/21</t>
         </is>
       </c>
       <c r="C651" t="inlineStr"/>
       <c r="D651" t="inlineStr">
         <is>
-          <t>0.18M</t>
+          <t>-0.961M</t>
         </is>
       </c>
       <c r="E651" t="inlineStr"/>
@@ -19395,23 +19391,23 @@
       </c>
       <c r="B652" t="inlineStr">
         <is>
-          <t>EIA Crude Oil Stocks ChangeFEB/21</t>
-        </is>
-      </c>
-      <c r="C652" t="inlineStr"/>
+          <t>EIA Cushing Crude Oil Stocks ChangeFEB/21</t>
+        </is>
+      </c>
+      <c r="C652" t="inlineStr">
+        <is>
+          <t>1.282M</t>
+        </is>
+      </c>
       <c r="D652" t="inlineStr">
         <is>
-          <t>4.633M</t>
-        </is>
-      </c>
-      <c r="E652" t="inlineStr">
-        <is>
-          <t>2.34M</t>
-        </is>
-      </c>
+          <t>1.472M</t>
+        </is>
+      </c>
+      <c r="E652" t="inlineStr"/>
       <c r="F652" t="inlineStr"/>
       <c r="G652" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="653">
@@ -19422,23 +19418,23 @@
       </c>
       <c r="B653" t="inlineStr">
         <is>
-          <t>EIA Gasoline Stocks ChangeFEB/21</t>
-        </is>
-      </c>
-      <c r="C653" t="inlineStr"/>
+          <t>EIA Crude Oil Imports ChangeFEB/21</t>
+        </is>
+      </c>
+      <c r="C653" t="inlineStr">
+        <is>
+          <t>0.292M</t>
+        </is>
+      </c>
       <c r="D653" t="inlineStr">
         <is>
-          <t>-0.151M</t>
-        </is>
-      </c>
-      <c r="E653" t="inlineStr">
-        <is>
-          <t>-1.30M</t>
-        </is>
-      </c>
+          <t>-0.961M</t>
+        </is>
+      </c>
+      <c r="E653" t="inlineStr"/>
       <c r="F653" t="inlineStr"/>
       <c r="G653" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="654">
@@ -19449,19 +19445,27 @@
       </c>
       <c r="B654" t="inlineStr">
         <is>
-          <t>EIA Cushing Crude Oil Stocks ChangeFEB/21</t>
-        </is>
-      </c>
-      <c r="C654" t="inlineStr"/>
+          <t>EIA Gasoline Stocks ChangeFEB/21</t>
+        </is>
+      </c>
+      <c r="C654" t="inlineStr">
+        <is>
+          <t>0.369M</t>
+        </is>
+      </c>
       <c r="D654" t="inlineStr">
         <is>
-          <t>1.472M</t>
-        </is>
-      </c>
-      <c r="E654" t="inlineStr"/>
+          <t>-0.151M</t>
+        </is>
+      </c>
+      <c r="E654" t="inlineStr">
+        <is>
+          <t>-1.30M</t>
+        </is>
+      </c>
       <c r="F654" t="inlineStr"/>
       <c r="G654" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="655">
@@ -19472,27 +19476,23 @@
       </c>
       <c r="B655" t="inlineStr">
         <is>
-          <t>EIA Crude Oil Stocks ChangeFEB/21</t>
+          <t>EIA Distillate Fuel Production ChangeFEB/21</t>
         </is>
       </c>
       <c r="C655" t="inlineStr">
         <is>
-          <t>-2.332M</t>
+          <t>0.439M</t>
         </is>
       </c>
       <c r="D655" t="inlineStr">
         <is>
-          <t>4.633M</t>
-        </is>
-      </c>
-      <c r="E655" t="inlineStr">
-        <is>
-          <t>2.54M</t>
-        </is>
-      </c>
+          <t>0.18M</t>
+        </is>
+      </c>
+      <c r="E655" t="inlineStr"/>
       <c r="F655" t="inlineStr"/>
       <c r="G655" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="656">
@@ -19622,21 +19622,25 @@
       </c>
       <c r="B661" t="inlineStr">
         <is>
-          <t>7-Year Note Auction</t>
-        </is>
-      </c>
-      <c r="C661" t="inlineStr">
-        <is>
-          <t>4.194%</t>
-        </is>
-      </c>
+          <t>Building Permits FinalJAN</t>
+        </is>
+      </c>
+      <c r="C661" t="inlineStr"/>
       <c r="D661" t="inlineStr">
         <is>
-          <t>4.457%</t>
-        </is>
-      </c>
-      <c r="E661" t="inlineStr"/>
-      <c r="F661" t="inlineStr"/>
+          <t>1.482M</t>
+        </is>
+      </c>
+      <c r="E661" t="inlineStr">
+        <is>
+          <t>1.483M</t>
+        </is>
+      </c>
+      <c r="F661" t="inlineStr">
+        <is>
+          <t>1.483M</t>
+        </is>
+      </c>
       <c r="G661" t="n">
         <v>3</v>
       </c>
@@ -19649,17 +19653,25 @@
       </c>
       <c r="B662" t="inlineStr">
         <is>
-          <t>7-Year Note Auction</t>
+          <t>Building Permits MoM FinalJAN</t>
         </is>
       </c>
       <c r="C662" t="inlineStr"/>
       <c r="D662" t="inlineStr">
         <is>
-          <t>4.457%</t>
-        </is>
-      </c>
-      <c r="E662" t="inlineStr"/>
-      <c r="F662" t="inlineStr"/>
+          <t>-0.7%</t>
+        </is>
+      </c>
+      <c r="E662" t="inlineStr">
+        <is>
+          <t>0.1%</t>
+        </is>
+      </c>
+      <c r="F662" t="inlineStr">
+        <is>
+          <t>0.1%</t>
+        </is>
+      </c>
       <c r="G662" t="n">
         <v>3</v>
       </c>
@@ -19672,25 +19684,17 @@
       </c>
       <c r="B663" t="inlineStr">
         <is>
-          <t>Building Permits MoM FinalJAN</t>
+          <t>7-Year Note Auction</t>
         </is>
       </c>
       <c r="C663" t="inlineStr"/>
       <c r="D663" t="inlineStr">
         <is>
-          <t>-0.7%</t>
-        </is>
-      </c>
-      <c r="E663" t="inlineStr">
-        <is>
-          <t>0.1%</t>
-        </is>
-      </c>
-      <c r="F663" t="inlineStr">
-        <is>
-          <t>0.1%</t>
-        </is>
-      </c>
+          <t>4.457%</t>
+        </is>
+      </c>
+      <c r="E663" t="inlineStr"/>
+      <c r="F663" t="inlineStr"/>
       <c r="G663" t="n">
         <v>3</v>
       </c>
@@ -19703,25 +19707,21 @@
       </c>
       <c r="B664" t="inlineStr">
         <is>
-          <t>Building Permits FinalJAN</t>
-        </is>
-      </c>
-      <c r="C664" t="inlineStr"/>
+          <t>7-Year Note Auction</t>
+        </is>
+      </c>
+      <c r="C664" t="inlineStr">
+        <is>
+          <t>4.194%</t>
+        </is>
+      </c>
       <c r="D664" t="inlineStr">
         <is>
-          <t>1.482M</t>
-        </is>
-      </c>
-      <c r="E664" t="inlineStr">
-        <is>
-          <t>1.483M</t>
-        </is>
-      </c>
-      <c r="F664" t="inlineStr">
-        <is>
-          <t>1.483M</t>
-        </is>
-      </c>
+          <t>4.457%</t>
+        </is>
+      </c>
+      <c r="E664" t="inlineStr"/>
+      <c r="F664" t="inlineStr"/>
       <c r="G664" t="n">
         <v>3</v>
       </c>
@@ -19737,7 +19737,11 @@
           <t>GDP Growth Rate QoQ 2nd EstQ4</t>
         </is>
       </c>
-      <c r="C665" t="inlineStr"/>
+      <c r="C665" t="inlineStr">
+        <is>
+          <t>2.3%</t>
+        </is>
+      </c>
       <c r="D665" t="inlineStr">
         <is>
           <t>3.1%</t>
@@ -19768,7 +19772,11 @@
           <t>PCE Prices QoQ 2nd EstQ4</t>
         </is>
       </c>
-      <c r="C666" t="inlineStr"/>
+      <c r="C666" t="inlineStr">
+        <is>
+          <t>2.4%</t>
+        </is>
+      </c>
       <c r="D666" t="inlineStr">
         <is>
           <t>1.5%</t>
@@ -19799,10 +19807,14 @@
           <t>Non Defense Goods Orders Ex AirJAN</t>
         </is>
       </c>
-      <c r="C667" t="inlineStr"/>
+      <c r="C667" t="inlineStr">
+        <is>
+          <t>0.8%</t>
+        </is>
+      </c>
       <c r="D667" t="inlineStr">
         <is>
-          <t>0.5%</t>
+          <t>0.2%</t>
         </is>
       </c>
       <c r="E667" t="inlineStr">
@@ -19830,10 +19842,14 @@
           <t>Jobless Claims 4-week AverageFEB/22</t>
         </is>
       </c>
-      <c r="C668" t="inlineStr"/>
+      <c r="C668" t="inlineStr">
+        <is>
+          <t>224K</t>
+        </is>
+      </c>
       <c r="D668" t="inlineStr">
         <is>
-          <t>215.25K</t>
+          <t>215.5K</t>
         </is>
       </c>
       <c r="E668" t="inlineStr"/>
@@ -19857,7 +19873,11 @@
           <t>GDP Sales QoQ 2nd EstQ4</t>
         </is>
       </c>
-      <c r="C669" t="inlineStr"/>
+      <c r="C669" t="inlineStr">
+        <is>
+          <t>3.2%</t>
+        </is>
+      </c>
       <c r="D669" t="inlineStr">
         <is>
           <t>3.3%</t>
@@ -19888,10 +19908,14 @@
           <t>Durable Goods Orders ex Defense MoMJAN</t>
         </is>
       </c>
-      <c r="C670" t="inlineStr"/>
+      <c r="C670" t="inlineStr">
+        <is>
+          <t>3.5%</t>
+        </is>
+      </c>
       <c r="D670" t="inlineStr">
         <is>
-          <t>-2.4%</t>
+          <t>-1.8%</t>
         </is>
       </c>
       <c r="E670" t="inlineStr"/>
@@ -19915,7 +19939,11 @@
           <t>Core PCE Prices QoQ 2nd EstQ4</t>
         </is>
       </c>
-      <c r="C671" t="inlineStr"/>
+      <c r="C671" t="inlineStr">
+        <is>
+          <t>2.7%</t>
+        </is>
+      </c>
       <c r="D671" t="inlineStr">
         <is>
           <t>2.2%</t>
@@ -19946,10 +19974,14 @@
           <t>Continuing Jobless ClaimsFEB/15</t>
         </is>
       </c>
-      <c r="C672" t="inlineStr"/>
+      <c r="C672" t="inlineStr">
+        <is>
+          <t>1862K</t>
+        </is>
+      </c>
       <c r="D672" t="inlineStr">
         <is>
-          <t>1869K</t>
+          <t>1867K</t>
         </is>
       </c>
       <c r="E672" t="inlineStr">
@@ -19977,10 +20009,14 @@
           <t>Initial Jobless ClaimsFEB/22</t>
         </is>
       </c>
-      <c r="C673" t="inlineStr"/>
+      <c r="C673" t="inlineStr">
+        <is>
+          <t>242K</t>
+        </is>
+      </c>
       <c r="D673" t="inlineStr">
         <is>
-          <t>219K</t>
+          <t>220K</t>
         </is>
       </c>
       <c r="E673" t="inlineStr">
@@ -20008,7 +20044,11 @@
           <t>GDP Price Index QoQ 2nd EstQ4</t>
         </is>
       </c>
-      <c r="C674" t="inlineStr"/>
+      <c r="C674" t="inlineStr">
+        <is>
+          <t>2.4%</t>
+        </is>
+      </c>
       <c r="D674" t="inlineStr">
         <is>
           <t>1.9%</t>
@@ -20039,7 +20079,11 @@
           <t>Real Consumer Spending QoQ 2nd EstQ4</t>
         </is>
       </c>
-      <c r="C675" t="inlineStr"/>
+      <c r="C675" t="inlineStr">
+        <is>
+          <t>4.2%</t>
+        </is>
+      </c>
       <c r="D675" t="inlineStr">
         <is>
           <t>3.7%</t>
@@ -20070,10 +20114,14 @@
           <t>Durable Goods Orders Ex Transp MoMJAN</t>
         </is>
       </c>
-      <c r="C676" t="inlineStr"/>
+      <c r="C676" t="inlineStr">
+        <is>
+          <t>0%</t>
+        </is>
+      </c>
       <c r="D676" t="inlineStr">
         <is>
-          <t>0.3%</t>
+          <t>0.1%</t>
         </is>
       </c>
       <c r="E676" t="inlineStr">
@@ -20101,10 +20149,14 @@
           <t>Durable Goods Orders MoMJAN</t>
         </is>
       </c>
-      <c r="C677" t="inlineStr"/>
+      <c r="C677" t="inlineStr">
+        <is>
+          <t>3.1%</t>
+        </is>
+      </c>
       <c r="D677" t="inlineStr">
         <is>
-          <t>-2.2%</t>
+          <t>-1.8%</t>
         </is>
       </c>
       <c r="E677" t="inlineStr">
@@ -20129,27 +20181,27 @@
       </c>
       <c r="B678" t="inlineStr">
         <is>
-          <t>GDP Price Index QoQ 2nd EstQ4</t>
+          <t>PCE Prices QoQ 2nd EstQ4</t>
         </is>
       </c>
       <c r="C678" t="inlineStr"/>
       <c r="D678" t="inlineStr">
         <is>
-          <t>1.9%</t>
+          <t>1.5%</t>
         </is>
       </c>
       <c r="E678" t="inlineStr">
         <is>
-          <t>2.2%</t>
+          <t>2.3%</t>
         </is>
       </c>
       <c r="F678" t="inlineStr">
         <is>
-          <t>2.2%</t>
+          <t>2.3%</t>
         </is>
       </c>
       <c r="G678" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="679">
@@ -20187,27 +20239,27 @@
       </c>
       <c r="B680" t="inlineStr">
         <is>
-          <t>GDP Growth Rate QoQ 2nd EstQ4</t>
+          <t>GDP Price Index QoQ 2nd EstQ4</t>
         </is>
       </c>
       <c r="C680" t="inlineStr"/>
       <c r="D680" t="inlineStr">
         <is>
-          <t>3.1%</t>
+          <t>1.9%</t>
         </is>
       </c>
       <c r="E680" t="inlineStr">
         <is>
-          <t>2.3%</t>
+          <t>2.2%</t>
         </is>
       </c>
       <c r="F680" t="inlineStr">
         <is>
-          <t>2.3%</t>
+          <t>2.2%</t>
         </is>
       </c>
       <c r="G680" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="681">
@@ -20218,27 +20270,27 @@
       </c>
       <c r="B681" t="inlineStr">
         <is>
-          <t>Initial Jobless ClaimsFEB/22</t>
+          <t>GDP Growth Rate QoQ 2nd EstQ4</t>
         </is>
       </c>
       <c r="C681" t="inlineStr"/>
       <c r="D681" t="inlineStr">
         <is>
-          <t>219K</t>
+          <t>3.1%</t>
         </is>
       </c>
       <c r="E681" t="inlineStr">
         <is>
-          <t>221K</t>
+          <t>2.3%</t>
         </is>
       </c>
       <c r="F681" t="inlineStr">
         <is>
-          <t>225.0K</t>
+          <t>2.3%</t>
         </is>
       </c>
       <c r="G681" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="682">
@@ -20249,23 +20301,23 @@
       </c>
       <c r="B682" t="inlineStr">
         <is>
-          <t>Durable Goods Orders Ex Transp MoMJAN</t>
+          <t>Initial Jobless ClaimsFEB/22</t>
         </is>
       </c>
       <c r="C682" t="inlineStr"/>
       <c r="D682" t="inlineStr">
         <is>
-          <t>0.3%</t>
+          <t>219K</t>
         </is>
       </c>
       <c r="E682" t="inlineStr">
         <is>
-          <t>0.3%</t>
+          <t>221K</t>
         </is>
       </c>
       <c r="F682" t="inlineStr">
         <is>
-          <t>0.3%</t>
+          <t>225.0K</t>
         </is>
       </c>
       <c r="G682" t="n">
@@ -20280,13 +20332,13 @@
       </c>
       <c r="B683" t="inlineStr">
         <is>
-          <t>Non Defense Goods Orders Ex AirJAN</t>
+          <t>Durable Goods Orders Ex Transp MoMJAN</t>
         </is>
       </c>
       <c r="C683" t="inlineStr"/>
       <c r="D683" t="inlineStr">
         <is>
-          <t>0.5%</t>
+          <t>0.3%</t>
         </is>
       </c>
       <c r="E683" t="inlineStr">
@@ -20296,11 +20348,11 @@
       </c>
       <c r="F683" t="inlineStr">
         <is>
-          <t>0.4%</t>
+          <t>0.3%</t>
         </is>
       </c>
       <c r="G683" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="684">
@@ -20311,19 +20363,23 @@
       </c>
       <c r="B684" t="inlineStr">
         <is>
-          <t>Jobless Claims 4-week AverageFEB/22</t>
+          <t>Non Defense Goods Orders Ex AirJAN</t>
         </is>
       </c>
       <c r="C684" t="inlineStr"/>
       <c r="D684" t="inlineStr">
         <is>
-          <t>215.25K</t>
-        </is>
-      </c>
-      <c r="E684" t="inlineStr"/>
+          <t>0.5%</t>
+        </is>
+      </c>
+      <c r="E684" t="inlineStr">
+        <is>
+          <t>0.3%</t>
+        </is>
+      </c>
       <c r="F684" t="inlineStr">
         <is>
-          <t>220.0K</t>
+          <t>0.4%</t>
         </is>
       </c>
       <c r="G684" t="n">
@@ -20338,27 +20394,23 @@
       </c>
       <c r="B685" t="inlineStr">
         <is>
-          <t>Durable Goods Orders MoMJAN</t>
+          <t>Jobless Claims 4-week AverageFEB/22</t>
         </is>
       </c>
       <c r="C685" t="inlineStr"/>
       <c r="D685" t="inlineStr">
         <is>
-          <t>-2.2%</t>
-        </is>
-      </c>
-      <c r="E685" t="inlineStr">
-        <is>
-          <t>2%</t>
-        </is>
-      </c>
+          <t>215.25K</t>
+        </is>
+      </c>
+      <c r="E685" t="inlineStr"/>
       <c r="F685" t="inlineStr">
         <is>
-          <t>2.2%</t>
+          <t>220.0K</t>
         </is>
       </c>
       <c r="G685" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="686">
@@ -20369,27 +20421,27 @@
       </c>
       <c r="B686" t="inlineStr">
         <is>
-          <t>Real Consumer Spending QoQ 2nd EstQ4</t>
+          <t>Durable Goods Orders MoMJAN</t>
         </is>
       </c>
       <c r="C686" t="inlineStr"/>
       <c r="D686" t="inlineStr">
         <is>
-          <t>3.7%</t>
+          <t>-2.2%</t>
         </is>
       </c>
       <c r="E686" t="inlineStr">
         <is>
-          <t>4.2%</t>
+          <t>2%</t>
         </is>
       </c>
       <c r="F686" t="inlineStr">
         <is>
-          <t>4.2%</t>
+          <t>2.2%</t>
         </is>
       </c>
       <c r="G686" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="687">
@@ -20400,23 +20452,23 @@
       </c>
       <c r="B687" t="inlineStr">
         <is>
-          <t>PCE Prices QoQ 2nd EstQ4</t>
+          <t>Real Consumer Spending QoQ 2nd EstQ4</t>
         </is>
       </c>
       <c r="C687" t="inlineStr"/>
       <c r="D687" t="inlineStr">
         <is>
-          <t>1.5%</t>
+          <t>3.7%</t>
         </is>
       </c>
       <c r="E687" t="inlineStr">
         <is>
-          <t>2.3%</t>
+          <t>4.2%</t>
         </is>
       </c>
       <c r="F687" t="inlineStr">
         <is>
-          <t>2.3%</t>
+          <t>4.2%</t>
         </is>
       </c>
       <c r="G687" t="n">
@@ -21058,13 +21110,13 @@
       </c>
       <c r="B713" t="inlineStr">
         <is>
-          <t>30-Year Mortgage RateFEB/27</t>
+          <t>15-Year Mortgage RateFEB/27</t>
         </is>
       </c>
       <c r="C713" t="inlineStr"/>
       <c r="D713" t="inlineStr">
         <is>
-          <t>6.85%</t>
+          <t>6.04%</t>
         </is>
       </c>
       <c r="E713" t="inlineStr"/>
@@ -21081,13 +21133,13 @@
       </c>
       <c r="B714" t="inlineStr">
         <is>
-          <t>15-Year Mortgage RateFEB/27</t>
+          <t>30-Year Mortgage RateFEB/27</t>
         </is>
       </c>
       <c r="C714" t="inlineStr"/>
       <c r="D714" t="inlineStr">
         <is>
-          <t>6.04%</t>
+          <t>6.85%</t>
         </is>
       </c>
       <c r="E714" t="inlineStr"/>
@@ -21508,27 +21560,27 @@
       </c>
       <c r="B731" t="inlineStr">
         <is>
-          <t>Personal Spending MoMJAN</t>
+          <t>PCE Price Index YoYJAN</t>
         </is>
       </c>
       <c r="C731" t="inlineStr"/>
       <c r="D731" t="inlineStr">
         <is>
-          <t>0.7%</t>
+          <t>2.6%</t>
         </is>
       </c>
       <c r="E731" t="inlineStr">
         <is>
-          <t>0.1%</t>
+          <t>2.5%</t>
         </is>
       </c>
       <c r="F731" t="inlineStr">
         <is>
-          <t>0.3%</t>
+          <t>2.5%</t>
         </is>
       </c>
       <c r="G731" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="732">
@@ -21570,27 +21622,27 @@
       </c>
       <c r="B733" t="inlineStr">
         <is>
-          <t>PCE Price Index YoYJAN</t>
+          <t>Personal Spending MoMJAN</t>
         </is>
       </c>
       <c r="C733" t="inlineStr"/>
       <c r="D733" t="inlineStr">
         <is>
-          <t>2.6%</t>
+          <t>0.7%</t>
         </is>
       </c>
       <c r="E733" t="inlineStr">
         <is>
-          <t>2.5%</t>
+          <t>0.1%</t>
         </is>
       </c>
       <c r="F733" t="inlineStr">
         <is>
-          <t>2.5%</t>
+          <t>0.3%</t>
         </is>
       </c>
       <c r="G733" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="734">
@@ -21659,27 +21711,27 @@
       </c>
       <c r="B736" t="inlineStr">
         <is>
-          <t>Goods Trade Balance AdvJAN</t>
+          <t>Personal Income MoMJAN</t>
         </is>
       </c>
       <c r="C736" t="inlineStr"/>
       <c r="D736" t="inlineStr">
         <is>
-          <t>$-122.11B</t>
+          <t>0.4%</t>
         </is>
       </c>
       <c r="E736" t="inlineStr">
         <is>
-          <t>$-114.7B</t>
+          <t>0.3%</t>
         </is>
       </c>
       <c r="F736" t="inlineStr">
         <is>
-          <t>$ -116.0B</t>
+          <t>0.3%</t>
         </is>
       </c>
       <c r="G736" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="737">
@@ -21690,23 +21742,23 @@
       </c>
       <c r="B737" t="inlineStr">
         <is>
-          <t>Wholesale Inventories MoM AdvJAN</t>
+          <t>PCE Price Index MoMJAN</t>
         </is>
       </c>
       <c r="C737" t="inlineStr"/>
       <c r="D737" t="inlineStr">
         <is>
-          <t>-0.5%</t>
+          <t>0.3%</t>
         </is>
       </c>
       <c r="E737" t="inlineStr">
         <is>
-          <t>0.1%</t>
+          <t>0.3%</t>
         </is>
       </c>
       <c r="F737" t="inlineStr">
         <is>
-          <t>0.2%</t>
+          <t>0.4%</t>
         </is>
       </c>
       <c r="G737" t="n">
@@ -21721,23 +21773,23 @@
       </c>
       <c r="B738" t="inlineStr">
         <is>
-          <t>Personal Income MoMJAN</t>
+          <t>Core PCE Price Index MoMJAN</t>
         </is>
       </c>
       <c r="C738" t="inlineStr"/>
       <c r="D738" t="inlineStr">
         <is>
+          <t>0.2%</t>
+        </is>
+      </c>
+      <c r="E738" t="inlineStr">
+        <is>
+          <t>0.3%</t>
+        </is>
+      </c>
+      <c r="F738" t="inlineStr">
+        <is>
           <t>0.4%</t>
-        </is>
-      </c>
-      <c r="E738" t="inlineStr">
-        <is>
-          <t>0.3%</t>
-        </is>
-      </c>
-      <c r="F738" t="inlineStr">
-        <is>
-          <t>0.3%</t>
         </is>
       </c>
       <c r="G738" t="n">
@@ -21752,23 +21804,23 @@
       </c>
       <c r="B739" t="inlineStr">
         <is>
-          <t>PCE Price Index MoMJAN</t>
+          <t>Wholesale Inventories MoM AdvJAN</t>
         </is>
       </c>
       <c r="C739" t="inlineStr"/>
       <c r="D739" t="inlineStr">
         <is>
-          <t>0.3%</t>
+          <t>-0.5%</t>
         </is>
       </c>
       <c r="E739" t="inlineStr">
         <is>
-          <t>0.3%</t>
+          <t>0.1%</t>
         </is>
       </c>
       <c r="F739" t="inlineStr">
         <is>
-          <t>0.4%</t>
+          <t>0.2%</t>
         </is>
       </c>
       <c r="G739" t="n">
@@ -21783,27 +21835,27 @@
       </c>
       <c r="B740" t="inlineStr">
         <is>
-          <t>Core PCE Price Index MoMJAN</t>
+          <t>Goods Trade Balance AdvJAN</t>
         </is>
       </c>
       <c r="C740" t="inlineStr"/>
       <c r="D740" t="inlineStr">
         <is>
-          <t>0.2%</t>
+          <t>$-122.11B</t>
         </is>
       </c>
       <c r="E740" t="inlineStr">
         <is>
-          <t>0.3%</t>
+          <t>$-114.7B</t>
         </is>
       </c>
       <c r="F740" t="inlineStr">
         <is>
-          <t>0.4%</t>
+          <t>$ -116.0B</t>
         </is>
       </c>
       <c r="G740" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="741">
@@ -22165,23 +22217,23 @@
       </c>
       <c r="B754" t="inlineStr">
         <is>
-          <t>ISM Manufacturing PMIFEB</t>
+          <t>ISM Manufacturing New OrdersFEB</t>
         </is>
       </c>
       <c r="C754" t="inlineStr"/>
       <c r="D754" t="inlineStr">
         <is>
-          <t>50.9</t>
+          <t>55.1</t>
         </is>
       </c>
       <c r="E754" t="inlineStr"/>
       <c r="F754" t="inlineStr">
         <is>
-          <t>51</t>
+          <t>55.4</t>
         </is>
       </c>
       <c r="G754" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="755">
@@ -22219,23 +22271,23 @@
       </c>
       <c r="B756" t="inlineStr">
         <is>
-          <t>ISM Manufacturing New OrdersFEB</t>
+          <t>ISM Manufacturing PMIFEB</t>
         </is>
       </c>
       <c r="C756" t="inlineStr"/>
       <c r="D756" t="inlineStr">
         <is>
-          <t>55.1</t>
+          <t>50.9</t>
         </is>
       </c>
       <c r="E756" t="inlineStr"/>
       <c r="F756" t="inlineStr">
         <is>
-          <t>55.4</t>
+          <t>51</t>
         </is>
       </c>
       <c r="G756" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="757">
@@ -23254,23 +23306,23 @@
       </c>
       <c r="B797" t="inlineStr">
         <is>
-          <t>ISM Services EmploymentFEB</t>
+          <t>ISM Services PMIFEB</t>
         </is>
       </c>
       <c r="C797" t="inlineStr"/>
       <c r="D797" t="inlineStr">
         <is>
-          <t>52.3</t>
+          <t>52.8</t>
         </is>
       </c>
       <c r="E797" t="inlineStr"/>
       <c r="F797" t="inlineStr">
         <is>
-          <t>52.1</t>
+          <t>52.7</t>
         </is>
       </c>
       <c r="G797" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="798">
@@ -23281,19 +23333,19 @@
       </c>
       <c r="B798" t="inlineStr">
         <is>
-          <t>ISM Services New OrdersFEB</t>
+          <t>Factory Orders ex TransportationJAN</t>
         </is>
       </c>
       <c r="C798" t="inlineStr"/>
       <c r="D798" t="inlineStr">
         <is>
-          <t>51.3</t>
+          <t>0.2%</t>
         </is>
       </c>
       <c r="E798" t="inlineStr"/>
       <c r="F798" t="inlineStr">
         <is>
-          <t>51.2</t>
+          <t>0.3%</t>
         </is>
       </c>
       <c r="G798" t="n">
@@ -23308,19 +23360,19 @@
       </c>
       <c r="B799" t="inlineStr">
         <is>
-          <t>ISM Services PricesFEB</t>
+          <t>ISM Services Business ActivityFEB</t>
         </is>
       </c>
       <c r="C799" t="inlineStr"/>
       <c r="D799" t="inlineStr">
         <is>
-          <t>60.4</t>
+          <t>54.5</t>
         </is>
       </c>
       <c r="E799" t="inlineStr"/>
       <c r="F799" t="inlineStr">
         <is>
-          <t>60.6</t>
+          <t>54.2</t>
         </is>
       </c>
       <c r="G799" t="n">
@@ -23335,19 +23387,19 @@
       </c>
       <c r="B800" t="inlineStr">
         <is>
-          <t>ISM Services Business ActivityFEB</t>
+          <t>ISM Services PricesFEB</t>
         </is>
       </c>
       <c r="C800" t="inlineStr"/>
       <c r="D800" t="inlineStr">
         <is>
-          <t>54.5</t>
+          <t>60.4</t>
         </is>
       </c>
       <c r="E800" t="inlineStr"/>
       <c r="F800" t="inlineStr">
         <is>
-          <t>54.2</t>
+          <t>60.6</t>
         </is>
       </c>
       <c r="G800" t="n">
@@ -23362,19 +23414,19 @@
       </c>
       <c r="B801" t="inlineStr">
         <is>
-          <t>Factory Orders ex TransportationJAN</t>
+          <t>ISM Services New OrdersFEB</t>
         </is>
       </c>
       <c r="C801" t="inlineStr"/>
       <c r="D801" t="inlineStr">
         <is>
-          <t>0.2%</t>
+          <t>51.3</t>
         </is>
       </c>
       <c r="E801" t="inlineStr"/>
       <c r="F801" t="inlineStr">
         <is>
-          <t>0.3%</t>
+          <t>51.2</t>
         </is>
       </c>
       <c r="G801" t="n">
@@ -23389,23 +23441,23 @@
       </c>
       <c r="B802" t="inlineStr">
         <is>
-          <t>ISM Services PMIFEB</t>
+          <t>ISM Services EmploymentFEB</t>
         </is>
       </c>
       <c r="C802" t="inlineStr"/>
       <c r="D802" t="inlineStr">
         <is>
-          <t>52.8</t>
+          <t>52.3</t>
         </is>
       </c>
       <c r="E802" t="inlineStr"/>
       <c r="F802" t="inlineStr">
         <is>
-          <t>52.7</t>
+          <t>52.1</t>
         </is>
       </c>
       <c r="G802" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="803">
@@ -23623,15 +23675,19 @@
       </c>
       <c r="B812" t="inlineStr">
         <is>
-          <t>EIA Crude Oil Imports ChangeFEB/28</t>
+          <t>EIA Gasoline Stocks ChangeFEB/28</t>
         </is>
       </c>
       <c r="C812" t="inlineStr"/>
-      <c r="D812" t="inlineStr"/>
+      <c r="D812" t="inlineStr">
+        <is>
+          <t>0.369M</t>
+        </is>
+      </c>
       <c r="E812" t="inlineStr"/>
       <c r="F812" t="inlineStr"/>
       <c r="G812" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="813">
@@ -23642,19 +23698,19 @@
       </c>
       <c r="B813" t="inlineStr">
         <is>
-          <t>EIA Gasoline Stocks ChangeFEB/28</t>
+          <t>EIA Refinery Crude Runs ChangeFEB/28</t>
         </is>
       </c>
       <c r="C813" t="inlineStr"/>
       <c r="D813" t="inlineStr">
         <is>
-          <t>0.369M</t>
+          <t>0.317M</t>
         </is>
       </c>
       <c r="E813" t="inlineStr"/>
       <c r="F813" t="inlineStr"/>
       <c r="G813" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="814">
@@ -23730,15 +23786,11 @@
       </c>
       <c r="B817" t="inlineStr">
         <is>
-          <t>EIA Refinery Crude Runs ChangeFEB/28</t>
+          <t>EIA Crude Oil Imports ChangeFEB/28</t>
         </is>
       </c>
       <c r="C817" t="inlineStr"/>
-      <c r="D817" t="inlineStr">
-        <is>
-          <t>0.317M</t>
-        </is>
-      </c>
+      <c r="D817" t="inlineStr"/>
       <c r="E817" t="inlineStr"/>
       <c r="F817" t="inlineStr"/>
       <c r="G817" t="n">
@@ -23776,19 +23828,19 @@
       </c>
       <c r="B819" t="inlineStr">
         <is>
-          <t>EIA Heating Oil Stocks ChangeFEB/28</t>
+          <t>EIA Crude Oil Stocks ChangeFEB/28</t>
         </is>
       </c>
       <c r="C819" t="inlineStr"/>
       <c r="D819" t="inlineStr">
         <is>
-          <t>0.134M</t>
+          <t>-2.332M</t>
         </is>
       </c>
       <c r="E819" t="inlineStr"/>
       <c r="F819" t="inlineStr"/>
       <c r="G819" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="820">
@@ -23799,19 +23851,19 @@
       </c>
       <c r="B820" t="inlineStr">
         <is>
-          <t>EIA Crude Oil Stocks ChangeFEB/28</t>
+          <t>EIA Heating Oil Stocks ChangeFEB/28</t>
         </is>
       </c>
       <c r="C820" t="inlineStr"/>
       <c r="D820" t="inlineStr">
         <is>
-          <t>-2.332M</t>
+          <t>0.134M</t>
         </is>
       </c>
       <c r="E820" t="inlineStr"/>
       <c r="F820" t="inlineStr"/>
       <c r="G820" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="821">
@@ -23868,13 +23920,13 @@
       </c>
       <c r="B823" t="inlineStr">
         <is>
-          <t>Total Vehicle SalesFEB</t>
+          <t>17-Week Bill Auction</t>
         </is>
       </c>
       <c r="C823" t="inlineStr"/>
       <c r="D823" t="inlineStr">
         <is>
-          <t>15.6M</t>
+          <t>4.200%</t>
         </is>
       </c>
       <c r="E823" t="inlineStr"/>
@@ -23891,13 +23943,13 @@
       </c>
       <c r="B824" t="inlineStr">
         <is>
-          <t>17-Week Bill Auction</t>
+          <t>Total Vehicle SalesFEB</t>
         </is>
       </c>
       <c r="C824" t="inlineStr"/>
       <c r="D824" t="inlineStr">
         <is>
-          <t>4.200%</t>
+          <t>15.6M</t>
         </is>
       </c>
       <c r="E824" t="inlineStr"/>
@@ -24321,19 +24373,19 @@
       </c>
       <c r="B842" t="inlineStr">
         <is>
-          <t>ImportsJAN</t>
+          <t>Balance of TradeJAN</t>
         </is>
       </c>
       <c r="C842" t="inlineStr"/>
       <c r="D842" t="inlineStr">
         <is>
-          <t>$364.9B</t>
+          <t>$-98.4B</t>
         </is>
       </c>
       <c r="E842" t="inlineStr"/>
       <c r="F842" t="inlineStr">
         <is>
-          <t>$376.0B</t>
+          <t>$-103B</t>
         </is>
       </c>
       <c r="G842" t="n">
@@ -24348,19 +24400,19 @@
       </c>
       <c r="B843" t="inlineStr">
         <is>
-          <t>Balance of TradeJAN</t>
+          <t>ExportsJAN</t>
         </is>
       </c>
       <c r="C843" t="inlineStr"/>
       <c r="D843" t="inlineStr">
         <is>
-          <t>$-98.4B</t>
+          <t>$266.5B</t>
         </is>
       </c>
       <c r="E843" t="inlineStr"/>
       <c r="F843" t="inlineStr">
         <is>
-          <t>$-103B</t>
+          <t>$273.0B</t>
         </is>
       </c>
       <c r="G843" t="n">
@@ -24375,19 +24427,19 @@
       </c>
       <c r="B844" t="inlineStr">
         <is>
-          <t>ExportsJAN</t>
+          <t>ImportsJAN</t>
         </is>
       </c>
       <c r="C844" t="inlineStr"/>
       <c r="D844" t="inlineStr">
         <is>
-          <t>$266.5B</t>
+          <t>$364.9B</t>
         </is>
       </c>
       <c r="E844" t="inlineStr"/>
       <c r="F844" t="inlineStr">
         <is>
-          <t>$273.0B</t>
+          <t>$376.0B</t>
         </is>
       </c>
       <c r="G844" t="n">
@@ -24516,7 +24568,7 @@
       </c>
       <c r="B851" t="inlineStr">
         <is>
-          <t>4-Week Bill Auction</t>
+          <t>8-Week Bill Auction</t>
         </is>
       </c>
       <c r="C851" t="inlineStr"/>
@@ -24535,7 +24587,7 @@
       </c>
       <c r="B852" t="inlineStr">
         <is>
-          <t>8-Week Bill Auction</t>
+          <t>4-Week Bill Auction</t>
         </is>
       </c>
       <c r="C852" t="inlineStr"/>
@@ -24830,23 +24882,23 @@
       </c>
       <c r="B865" t="inlineStr">
         <is>
-          <t>U-6 Unemployment RateFEB</t>
+          <t>Non Farm PayrollsFEB</t>
         </is>
       </c>
       <c r="C865" t="inlineStr"/>
       <c r="D865" t="inlineStr">
         <is>
-          <t>7.5%</t>
+          <t>143K</t>
         </is>
       </c>
       <c r="E865" t="inlineStr"/>
       <c r="F865" t="inlineStr">
         <is>
-          <t>7.6%</t>
+          <t>180.0K</t>
         </is>
       </c>
       <c r="G865" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="866">
@@ -24911,23 +24963,19 @@
       </c>
       <c r="B868" t="inlineStr">
         <is>
-          <t>Average Hourly Earnings MoMFEB</t>
+          <t>Used Car Prices YoYFEB</t>
         </is>
       </c>
       <c r="C868" t="inlineStr"/>
       <c r="D868" t="inlineStr">
         <is>
-          <t>0.5%</t>
+          <t>0.8%</t>
         </is>
       </c>
       <c r="E868" t="inlineStr"/>
-      <c r="F868" t="inlineStr">
-        <is>
-          <t>0.3%</t>
-        </is>
-      </c>
+      <c r="F868" t="inlineStr"/>
       <c r="G868" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="869">
@@ -24938,23 +24986,23 @@
       </c>
       <c r="B869" t="inlineStr">
         <is>
-          <t>Average Hourly Earnings YoYFEB</t>
+          <t>Unemployment RateFEB</t>
         </is>
       </c>
       <c r="C869" t="inlineStr"/>
       <c r="D869" t="inlineStr">
         <is>
-          <t>4.1%</t>
+          <t>4%</t>
         </is>
       </c>
       <c r="E869" t="inlineStr"/>
       <c r="F869" t="inlineStr">
         <is>
-          <t>4.1%</t>
+          <t>4.0%</t>
         </is>
       </c>
       <c r="G869" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="870">
@@ -25042,23 +25090,23 @@
       </c>
       <c r="B873" t="inlineStr">
         <is>
-          <t>Unemployment RateFEB</t>
+          <t>Average Hourly Earnings YoYFEB</t>
         </is>
       </c>
       <c r="C873" t="inlineStr"/>
       <c r="D873" t="inlineStr">
         <is>
-          <t>4%</t>
+          <t>4.1%</t>
         </is>
       </c>
       <c r="E873" t="inlineStr"/>
       <c r="F873" t="inlineStr">
         <is>
-          <t>4.0%</t>
+          <t>4.1%</t>
         </is>
       </c>
       <c r="G873" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="874">
@@ -25069,17 +25117,21 @@
       </c>
       <c r="B874" t="inlineStr">
         <is>
-          <t>Used Car Prices YoYFEB</t>
+          <t>U-6 Unemployment RateFEB</t>
         </is>
       </c>
       <c r="C874" t="inlineStr"/>
       <c r="D874" t="inlineStr">
         <is>
-          <t>0.8%</t>
+          <t>7.5%</t>
         </is>
       </c>
       <c r="E874" t="inlineStr"/>
-      <c r="F874" t="inlineStr"/>
+      <c r="F874" t="inlineStr">
+        <is>
+          <t>7.6%</t>
+        </is>
+      </c>
       <c r="G874" t="n">
         <v>3</v>
       </c>
@@ -25200,23 +25252,23 @@
       </c>
       <c r="B879" t="inlineStr">
         <is>
-          <t>Non Farm PayrollsFEB</t>
+          <t>Average Hourly Earnings MoMFEB</t>
         </is>
       </c>
       <c r="C879" t="inlineStr"/>
       <c r="D879" t="inlineStr">
         <is>
-          <t>143K</t>
+          <t>0.5%</t>
         </is>
       </c>
       <c r="E879" t="inlineStr"/>
       <c r="F879" t="inlineStr">
         <is>
-          <t>180.0K</t>
+          <t>0.3%</t>
         </is>
       </c>
       <c r="G879" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="880">

--- a/Input_data/IST_US_trad_eco_cal_2025-01-01_to_2025-03-09.xlsx
+++ b/Input_data/IST_US_trad_eco_cal_2025-01-01_to_2025-03-09.xlsx
@@ -806,17 +806,17 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>EIA Crude Oil Imports ChangeDEC/27</t>
+          <t>EIA Gasoline Production ChangeDEC/27</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>0.323M</t>
+          <t>-0.959M</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>0.995M</t>
+          <t>0.051M</t>
         </is>
       </c>
       <c r="E13" t="inlineStr"/>
@@ -833,24 +833,20 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>EIA Distillate Stocks ChangeDEC/27</t>
+          <t>EIA Distillate Fuel Production ChangeDEC/27</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>6.406M</t>
+          <t>0.099M</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>-1.694M</t>
-        </is>
-      </c>
-      <c r="E14" t="inlineStr">
-        <is>
-          <t>-0.1M</t>
-        </is>
-      </c>
+          <t>0.178M</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr"/>
       <c r="F14" t="inlineStr"/>
       <c r="G14" t="n">
         <v>3</v>
@@ -864,23 +860,27 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>EIA Refinery Crude Runs ChangeDEC/27</t>
+          <t>EIA Crude Oil Stocks ChangeDEC/27</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>0.041M</t>
+          <t>-1.178M</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>0.205M</t>
-        </is>
-      </c>
-      <c r="E15" t="inlineStr"/>
+          <t>-4.237M</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>-2.75M</t>
+        </is>
+      </c>
       <c r="F15" t="inlineStr"/>
       <c r="G15" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="16">
@@ -891,23 +891,27 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>EIA Heating Oil Stocks ChangeDEC/27</t>
+          <t>EIA Gasoline Stocks ChangeDEC/27</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>-0.416M</t>
+          <t>7.717M</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>-0.062M</t>
-        </is>
-      </c>
-      <c r="E16" t="inlineStr"/>
+          <t>1.63M</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>0.7M</t>
+        </is>
+      </c>
       <c r="F16" t="inlineStr"/>
       <c r="G16" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="17">
@@ -918,17 +922,17 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>EIA Cushing Crude Oil Stocks ChangeDEC/27</t>
+          <t>EIA Refinery Crude Runs ChangeDEC/27</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>-0.142M</t>
+          <t>0.041M</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>-0.32M</t>
+          <t>0.205M</t>
         </is>
       </c>
       <c r="E17" t="inlineStr"/>
@@ -945,27 +949,23 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>EIA Gasoline Stocks ChangeDEC/27</t>
+          <t>EIA Heating Oil Stocks ChangeDEC/27</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>7.717M</t>
+          <t>-0.416M</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>1.63M</t>
-        </is>
-      </c>
-      <c r="E18" t="inlineStr">
-        <is>
-          <t>0.7M</t>
-        </is>
-      </c>
+          <t>-0.062M</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr"/>
       <c r="F18" t="inlineStr"/>
       <c r="G18" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="19">
@@ -976,27 +976,27 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>EIA Crude Oil Stocks ChangeDEC/27</t>
+          <t>EIA Distillate Stocks ChangeDEC/27</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>-1.178M</t>
+          <t>6.406M</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>-4.237M</t>
+          <t>-1.694M</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>-2.75M</t>
+          <t>-0.1M</t>
         </is>
       </c>
       <c r="F19" t="inlineStr"/>
       <c r="G19" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="20">
@@ -1007,17 +1007,17 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>EIA Distillate Fuel Production ChangeDEC/27</t>
+          <t>EIA Crude Oil Imports ChangeDEC/27</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>0.099M</t>
+          <t>0.323M</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>0.178M</t>
+          <t>0.995M</t>
         </is>
       </c>
       <c r="E20" t="inlineStr"/>
@@ -1034,17 +1034,17 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>EIA Gasoline Production ChangeDEC/27</t>
+          <t>EIA Cushing Crude Oil Stocks ChangeDEC/27</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>-0.959M</t>
+          <t>-0.142M</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>0.051M</t>
+          <t>-0.32M</t>
         </is>
       </c>
       <c r="E21" t="inlineStr"/>
@@ -1223,31 +1223,31 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>ISM Manufacturing PMIDEC</t>
+          <t>ISM Manufacturing PricesDEC</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>49.3</t>
+          <t>52.5</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>48.4</t>
+          <t>50.3</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>48.4</t>
+          <t>51.7</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>48.5</t>
+          <t>50.4</t>
         </is>
       </c>
       <c r="G28" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="29">
@@ -1258,31 +1258,27 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>ISM Manufacturing EmploymentDEC</t>
+          <t>ISM Manufacturing New OrdersDEC</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>45.3</t>
+          <t>52.5</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>48.1</t>
-        </is>
-      </c>
-      <c r="E29" t="inlineStr">
-        <is>
-          <t>48</t>
-        </is>
-      </c>
+          <t>50.4</t>
+        </is>
+      </c>
+      <c r="E29" t="inlineStr"/>
       <c r="F29" t="inlineStr">
         <is>
-          <t>48.3</t>
+          <t>50.5</t>
         </is>
       </c>
       <c r="G29" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="30">
@@ -1293,27 +1289,31 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>ISM Manufacturing New OrdersDEC</t>
+          <t>ISM Manufacturing EmploymentDEC</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>52.5</t>
+          <t>45.3</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>50.4</t>
-        </is>
-      </c>
-      <c r="E30" t="inlineStr"/>
+          <t>48.1</t>
+        </is>
+      </c>
+      <c r="E30" t="inlineStr">
+        <is>
+          <t>48</t>
+        </is>
+      </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>50.5</t>
+          <t>48.3</t>
         </is>
       </c>
       <c r="G30" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="31">
@@ -1324,31 +1324,31 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>ISM Manufacturing PricesDEC</t>
+          <t>ISM Manufacturing PMIDEC</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>52.5</t>
+          <t>49.3</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>50.3</t>
+          <t>48.4</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>51.7</t>
+          <t>48.4</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>50.4</t>
+          <t>48.5</t>
         </is>
       </c>
       <c r="G31" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="32">
@@ -1609,31 +1609,27 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>Factory Orders MoMNOV</t>
+          <t>Factory Orders ex TransportationNOV</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>-0.4%</t>
+          <t>0.2%</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>0.5%</t>
-        </is>
-      </c>
-      <c r="E42" t="inlineStr">
-        <is>
-          <t>-0.3%</t>
-        </is>
-      </c>
+          <t>0.2%</t>
+        </is>
+      </c>
+      <c r="E42" t="inlineStr"/>
       <c r="F42" t="inlineStr">
         <is>
-          <t>0.3%</t>
+          <t>0.2%</t>
         </is>
       </c>
       <c r="G42" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="43">
@@ -1644,27 +1640,31 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>Factory Orders ex TransportationNOV</t>
+          <t>Factory Orders MoMNOV</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>0.2%</t>
+          <t>-0.4%</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>0.2%</t>
-        </is>
-      </c>
-      <c r="E43" t="inlineStr"/>
+          <t>0.5%</t>
+        </is>
+      </c>
+      <c r="E43" t="inlineStr">
+        <is>
+          <t>-0.3%</t>
+        </is>
+      </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>0.2%</t>
+          <t>0.3%</t>
         </is>
       </c>
       <c r="G43" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="44">
@@ -1949,31 +1949,31 @@
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>ISM Services PMIDEC</t>
+          <t>ISM Services EmploymentDEC</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>54.1</t>
+          <t>51.4</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>52.1</t>
+          <t>51.5</t>
         </is>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>53.3</t>
+          <t>51.4</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>54</t>
+          <t>52</t>
         </is>
       </c>
       <c r="G54" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="55">
@@ -1984,23 +1984,23 @@
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>JOLTs Job QuitsNOV</t>
+          <t>ISM Services Business ActivityDEC</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>3.065M</t>
+          <t>58.2</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>3.283M</t>
+          <t>53.7</t>
         </is>
       </c>
       <c r="E55" t="inlineStr"/>
       <c r="F55" t="inlineStr">
         <is>
-          <t>3.31M</t>
+          <t>54.1</t>
         </is>
       </c>
       <c r="G55" t="n">
@@ -2015,31 +2015,31 @@
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>ISM Services PricesDEC</t>
+          <t>JOLTs Job OpeningsNOV</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>64.4</t>
+          <t>8.098M</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>58.2</t>
+          <t>7.839M</t>
         </is>
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>57.5</t>
+          <t>7.70M</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>58.4</t>
+          <t>7.69M</t>
         </is>
       </c>
       <c r="G56" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="57">
@@ -2050,31 +2050,31 @@
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>ISM Services New OrdersDEC</t>
+          <t>ISM Services PMIDEC</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>54.2</t>
+          <t>54.1</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>53.7</t>
+          <t>52.1</t>
         </is>
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>54.2</t>
+          <t>53.3</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>54.1</t>
+          <t>54</t>
         </is>
       </c>
       <c r="G57" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="58">
@@ -2085,31 +2085,31 @@
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>JOLTs Job OpeningsNOV</t>
+          <t>ISM Services PricesDEC</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>8.098M</t>
+          <t>64.4</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>7.839M</t>
+          <t>58.2</t>
         </is>
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>7.70M</t>
+          <t>57.5</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>7.69M</t>
+          <t>58.4</t>
         </is>
       </c>
       <c r="G58" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="59">
@@ -2120,27 +2120,27 @@
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>ISM Services EmploymentDEC</t>
+          <t>ISM Services New OrdersDEC</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>51.4</t>
+          <t>54.2</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>51.5</t>
+          <t>53.7</t>
         </is>
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>51.4</t>
+          <t>54.2</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>52</t>
+          <t>54.1</t>
         </is>
       </c>
       <c r="G59" t="n">
@@ -2155,23 +2155,23 @@
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>ISM Services Business ActivityDEC</t>
+          <t>JOLTs Job QuitsNOV</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>58.2</t>
+          <t>3.065M</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>53.7</t>
+          <t>3.283M</t>
         </is>
       </c>
       <c r="E60" t="inlineStr"/>
       <c r="F60" t="inlineStr">
         <is>
-          <t>54.1</t>
+          <t>3.31M</t>
         </is>
       </c>
       <c r="G60" t="n">
@@ -2441,31 +2441,31 @@
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>Continuing Jobless ClaimsDEC/28</t>
+          <t>Initial Jobless ClaimsJAN/04</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>1867K</t>
+          <t>201K</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>1834K</t>
+          <t>211K</t>
         </is>
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>1870K</t>
+          <t>218K</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>1848K</t>
+          <t>213K</t>
         </is>
       </c>
       <c r="G70" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="71">
@@ -2476,27 +2476,15 @@
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>Jobless Claims 4-week AverageJAN/04</t>
-        </is>
-      </c>
-      <c r="C71" t="inlineStr">
-        <is>
-          <t>213K</t>
-        </is>
-      </c>
-      <c r="D71" t="inlineStr">
-        <is>
-          <t>223.25K</t>
-        </is>
-      </c>
+          <t>Fed Waller Speech</t>
+        </is>
+      </c>
+      <c r="C71" t="inlineStr"/>
+      <c r="D71" t="inlineStr"/>
       <c r="E71" t="inlineStr"/>
-      <c r="F71" t="inlineStr">
-        <is>
-          <t>224K</t>
-        </is>
-      </c>
+      <c r="F71" t="inlineStr"/>
       <c r="G71" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="72">
@@ -2507,27 +2495,27 @@
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>Total Vehicle SalesDEC</t>
+          <t>Continuing Jobless ClaimsDEC/28</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>16.8M</t>
+          <t>1867K</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>16.7M</t>
+          <t>1834K</t>
         </is>
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>16.5M</t>
+          <t>1870K</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>16.3M</t>
+          <t>1848K</t>
         </is>
       </c>
       <c r="G72" t="n">
@@ -2542,15 +2530,27 @@
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>Fed Waller Speech</t>
-        </is>
-      </c>
-      <c r="C73" t="inlineStr"/>
-      <c r="D73" t="inlineStr"/>
+          <t>Jobless Claims 4-week AverageJAN/04</t>
+        </is>
+      </c>
+      <c r="C73" t="inlineStr">
+        <is>
+          <t>213K</t>
+        </is>
+      </c>
+      <c r="D73" t="inlineStr">
+        <is>
+          <t>223.25K</t>
+        </is>
+      </c>
       <c r="E73" t="inlineStr"/>
-      <c r="F73" t="inlineStr"/>
+      <c r="F73" t="inlineStr">
+        <is>
+          <t>224K</t>
+        </is>
+      </c>
       <c r="G73" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="74">
@@ -2561,31 +2561,31 @@
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>Initial Jobless ClaimsJAN/04</t>
+          <t>Total Vehicle SalesDEC</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>201K</t>
+          <t>16.8M</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>211K</t>
+          <t>16.7M</t>
         </is>
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>218K</t>
+          <t>16.5M</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>213K</t>
+          <t>16.3M</t>
         </is>
       </c>
       <c r="G74" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="75">
@@ -2685,17 +2685,17 @@
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>EIA Distillate Fuel Production ChangeJAN/03</t>
+          <t>EIA Heating Oil Stocks ChangeJAN/03</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>-0.167M</t>
+          <t>-0.632M</t>
         </is>
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>0.099M</t>
+          <t>-0.416M</t>
         </is>
       </c>
       <c r="E78" t="inlineStr"/>
@@ -2712,23 +2712,27 @@
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>EIA Crude Oil Imports ChangeJAN/03</t>
+          <t>EIA Gasoline Stocks ChangeJAN/03</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>0.278M</t>
+          <t>6.33M</t>
         </is>
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>0.323M</t>
-        </is>
-      </c>
-      <c r="E79" t="inlineStr"/>
+          <t>7.717M</t>
+        </is>
+      </c>
+      <c r="E79" t="inlineStr">
+        <is>
+          <t>1.5M</t>
+        </is>
+      </c>
       <c r="F79" t="inlineStr"/>
       <c r="G79" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="80">
@@ -2739,27 +2743,23 @@
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>EIA Crude Oil Stocks ChangeJAN/03</t>
+          <t>EIA Gasoline Production ChangeJAN/03</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
+          <t>-0.081M</t>
+        </is>
+      </c>
+      <c r="D80" t="inlineStr">
+        <is>
           <t>-0.959M</t>
         </is>
       </c>
-      <c r="D80" t="inlineStr">
-        <is>
-          <t>-1.178M</t>
-        </is>
-      </c>
-      <c r="E80" t="inlineStr">
-        <is>
-          <t>-0.6M</t>
-        </is>
-      </c>
+      <c r="E80" t="inlineStr"/>
       <c r="F80" t="inlineStr"/>
       <c r="G80" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="81">
@@ -2770,20 +2770,24 @@
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>EIA Cushing Crude Oil Stocks ChangeJAN/03</t>
+          <t>EIA Distillate Stocks ChangeJAN/03</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>-2.502M</t>
+          <t>6.071M</t>
         </is>
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>-0.142M</t>
-        </is>
-      </c>
-      <c r="E81" t="inlineStr"/>
+          <t>6.406M</t>
+        </is>
+      </c>
+      <c r="E81" t="inlineStr">
+        <is>
+          <t>1M</t>
+        </is>
+      </c>
       <c r="F81" t="inlineStr"/>
       <c r="G81" t="n">
         <v>3</v>
@@ -2824,23 +2828,27 @@
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>EIA Heating Oil Stocks ChangeJAN/03</t>
+          <t>EIA Crude Oil Stocks ChangeJAN/03</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>-0.632M</t>
+          <t>-0.959M</t>
         </is>
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>-0.416M</t>
-        </is>
-      </c>
-      <c r="E83" t="inlineStr"/>
+          <t>-1.178M</t>
+        </is>
+      </c>
+      <c r="E83" t="inlineStr">
+        <is>
+          <t>-0.6M</t>
+        </is>
+      </c>
       <c r="F83" t="inlineStr"/>
       <c r="G83" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="84">
@@ -2851,17 +2859,17 @@
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>EIA Gasoline Production ChangeJAN/03</t>
+          <t>EIA Crude Oil Imports ChangeJAN/03</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>-0.081M</t>
+          <t>0.278M</t>
         </is>
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>-0.959M</t>
+          <t>0.323M</t>
         </is>
       </c>
       <c r="E84" t="inlineStr"/>
@@ -2878,27 +2886,23 @@
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>EIA Gasoline Stocks ChangeJAN/03</t>
+          <t>EIA Distillate Fuel Production ChangeJAN/03</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>6.33M</t>
+          <t>-0.167M</t>
         </is>
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>7.717M</t>
-        </is>
-      </c>
-      <c r="E85" t="inlineStr">
-        <is>
-          <t>1.5M</t>
-        </is>
-      </c>
+          <t>0.099M</t>
+        </is>
+      </c>
+      <c r="E85" t="inlineStr"/>
       <c r="F85" t="inlineStr"/>
       <c r="G85" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="86">
@@ -2909,24 +2913,20 @@
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>EIA Distillate Stocks ChangeJAN/03</t>
+          <t>EIA Cushing Crude Oil Stocks ChangeJAN/03</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>6.071M</t>
+          <t>-2.502M</t>
         </is>
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>6.406M</t>
-        </is>
-      </c>
-      <c r="E86" t="inlineStr">
-        <is>
-          <t>1M</t>
-        </is>
-      </c>
+          <t>-0.142M</t>
+        </is>
+      </c>
+      <c r="E86" t="inlineStr"/>
       <c r="F86" t="inlineStr"/>
       <c r="G86" t="n">
         <v>3</v>
@@ -3336,27 +3336,31 @@
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>U-6 Unemployment Rate</t>
+          <t>Average Hourly Earnings MoMDEC</t>
         </is>
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>7.5%</t>
+          <t>0.3%</t>
         </is>
       </c>
       <c r="D103" t="inlineStr">
         <is>
-          <t>7.7%</t>
-        </is>
-      </c>
-      <c r="E103" t="inlineStr"/>
+          <t>0.4%</t>
+        </is>
+      </c>
+      <c r="E103" t="inlineStr">
+        <is>
+          <t>0.3%</t>
+        </is>
+      </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>7.9%</t>
+          <t>0.3%</t>
         </is>
       </c>
       <c r="G103" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="104">
@@ -3367,31 +3371,31 @@
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>Average Weekly HoursDEC</t>
+          <t>Average Hourly Earnings YoY</t>
         </is>
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>34.3</t>
+          <t>3.9%</t>
         </is>
       </c>
       <c r="D104" t="inlineStr">
         <is>
-          <t>34.3</t>
+          <t>4%</t>
         </is>
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>34.3</t>
+          <t>4%</t>
         </is>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>34.3</t>
+          <t>4%</t>
         </is>
       </c>
       <c r="G104" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="105">
@@ -3402,27 +3406,31 @@
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>Government PayrollsDEC</t>
+          <t>Non Farm PayrollsDEC</t>
         </is>
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>33K</t>
+          <t>256K</t>
         </is>
       </c>
       <c r="D105" t="inlineStr">
         <is>
-          <t>30K</t>
-        </is>
-      </c>
-      <c r="E105" t="inlineStr"/>
+          <t>212K</t>
+        </is>
+      </c>
+      <c r="E105" t="inlineStr">
+        <is>
+          <t>160K</t>
+        </is>
+      </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>15K</t>
+          <t>200K</t>
         </is>
       </c>
       <c r="G105" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="106">
@@ -3433,31 +3441,27 @@
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>Nonfarm Payrolls PrivateDEC</t>
+          <t>Participation RateDEC</t>
         </is>
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>223K</t>
+          <t>62.5%</t>
         </is>
       </c>
       <c r="D106" t="inlineStr">
         <is>
-          <t>182K</t>
-        </is>
-      </c>
-      <c r="E106" t="inlineStr">
-        <is>
-          <t>135K</t>
-        </is>
-      </c>
+          <t>62.5%</t>
+        </is>
+      </c>
+      <c r="E106" t="inlineStr"/>
       <c r="F106" t="inlineStr">
         <is>
-          <t>185K</t>
+          <t>62.8%</t>
         </is>
       </c>
       <c r="G106" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="107">
@@ -3468,31 +3472,31 @@
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>Manufacturing PayrollsDEC</t>
+          <t>Unemployment RateDEC</t>
         </is>
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>-13K</t>
+          <t>4.1%</t>
         </is>
       </c>
       <c r="D107" t="inlineStr">
         <is>
-          <t>25K</t>
+          <t>4.2%</t>
         </is>
       </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t>5K</t>
+          <t>4.2%</t>
         </is>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>29K</t>
+          <t>4.30%</t>
         </is>
       </c>
       <c r="G107" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="108">
@@ -3503,27 +3507,31 @@
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>Participation RateDEC</t>
+          <t>Nonfarm Payrolls PrivateDEC</t>
         </is>
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>62.5%</t>
+          <t>223K</t>
         </is>
       </c>
       <c r="D108" t="inlineStr">
         <is>
-          <t>62.5%</t>
-        </is>
-      </c>
-      <c r="E108" t="inlineStr"/>
+          <t>182K</t>
+        </is>
+      </c>
+      <c r="E108" t="inlineStr">
+        <is>
+          <t>135K</t>
+        </is>
+      </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>62.8%</t>
+          <t>185K</t>
         </is>
       </c>
       <c r="G108" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="109">
@@ -3534,31 +3542,27 @@
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>Non Farm PayrollsDEC</t>
+          <t>Government PayrollsDEC</t>
         </is>
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>256K</t>
+          <t>33K</t>
         </is>
       </c>
       <c r="D109" t="inlineStr">
         <is>
-          <t>212K</t>
-        </is>
-      </c>
-      <c r="E109" t="inlineStr">
-        <is>
-          <t>160K</t>
-        </is>
-      </c>
+          <t>30K</t>
+        </is>
+      </c>
+      <c r="E109" t="inlineStr"/>
       <c r="F109" t="inlineStr">
         <is>
-          <t>200K</t>
+          <t>15K</t>
         </is>
       </c>
       <c r="G109" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="110">
@@ -3569,31 +3573,31 @@
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>Average Hourly Earnings YoY</t>
+          <t>Average Weekly HoursDEC</t>
         </is>
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>3.9%</t>
+          <t>34.3</t>
         </is>
       </c>
       <c r="D110" t="inlineStr">
         <is>
-          <t>4%</t>
+          <t>34.3</t>
         </is>
       </c>
       <c r="E110" t="inlineStr">
         <is>
-          <t>4%</t>
+          <t>34.3</t>
         </is>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>4%</t>
+          <t>34.3</t>
         </is>
       </c>
       <c r="G110" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="111">
@@ -3604,31 +3608,27 @@
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>Average Hourly Earnings MoMDEC</t>
+          <t>U-6 Unemployment Rate</t>
         </is>
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>0.3%</t>
+          <t>7.5%</t>
         </is>
       </c>
       <c r="D111" t="inlineStr">
         <is>
-          <t>0.4%</t>
-        </is>
-      </c>
-      <c r="E111" t="inlineStr">
-        <is>
-          <t>0.3%</t>
-        </is>
-      </c>
+          <t>7.7%</t>
+        </is>
+      </c>
+      <c r="E111" t="inlineStr"/>
       <c r="F111" t="inlineStr">
         <is>
-          <t>0.3%</t>
+          <t>7.9%</t>
         </is>
       </c>
       <c r="G111" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="112">
@@ -3639,31 +3639,31 @@
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>Unemployment RateDEC</t>
+          <t>Manufacturing PayrollsDEC</t>
         </is>
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>4.1%</t>
+          <t>-13K</t>
         </is>
       </c>
       <c r="D112" t="inlineStr">
         <is>
-          <t>4.2%</t>
+          <t>25K</t>
         </is>
       </c>
       <c r="E112" t="inlineStr">
         <is>
-          <t>4.2%</t>
+          <t>5K</t>
         </is>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>4.30%</t>
+          <t>29K</t>
         </is>
       </c>
       <c r="G112" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="113">
@@ -3833,11 +3833,19 @@
       </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t>WASDE Report</t>
-        </is>
-      </c>
-      <c r="C118" t="inlineStr"/>
-      <c r="D118" t="inlineStr"/>
+          <t>Quarterly Grain Stocks - SoyDEC</t>
+        </is>
+      </c>
+      <c r="C118" t="inlineStr">
+        <is>
+          <t>3.1B</t>
+        </is>
+      </c>
+      <c r="D118" t="inlineStr">
+        <is>
+          <t>0.342B</t>
+        </is>
+      </c>
       <c r="E118" t="inlineStr"/>
       <c r="F118" t="inlineStr"/>
       <c r="G118" t="n">
@@ -3852,17 +3860,17 @@
       </c>
       <c r="B119" t="inlineStr">
         <is>
-          <t>Quarterly Grain Stocks - WheatDEC</t>
+          <t>Quarterly Grain Stocks - CornDEC</t>
         </is>
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>1.57B</t>
+          <t>12.074B</t>
         </is>
       </c>
       <c r="D119" t="inlineStr">
         <is>
-          <t>1.98B</t>
+          <t>1.760B</t>
         </is>
       </c>
       <c r="E119" t="inlineStr"/>
@@ -3879,17 +3887,17 @@
       </c>
       <c r="B120" t="inlineStr">
         <is>
-          <t>Quarterly Grain Stocks - CornDEC</t>
+          <t>Quarterly Grain Stocks - WheatDEC</t>
         </is>
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>12.074B</t>
+          <t>1.57B</t>
         </is>
       </c>
       <c r="D120" t="inlineStr">
         <is>
-          <t>1.760B</t>
+          <t>1.98B</t>
         </is>
       </c>
       <c r="E120" t="inlineStr"/>
@@ -3906,19 +3914,11 @@
       </c>
       <c r="B121" t="inlineStr">
         <is>
-          <t>Quarterly Grain Stocks - SoyDEC</t>
-        </is>
-      </c>
-      <c r="C121" t="inlineStr">
-        <is>
-          <t>3.1B</t>
-        </is>
-      </c>
-      <c r="D121" t="inlineStr">
-        <is>
-          <t>0.342B</t>
-        </is>
-      </c>
+          <t>WASDE Report</t>
+        </is>
+      </c>
+      <c r="C121" t="inlineStr"/>
+      <c r="D121" t="inlineStr"/>
       <c r="E121" t="inlineStr"/>
       <c r="F121" t="inlineStr"/>
       <c r="G121" t="n">
@@ -4134,31 +4134,31 @@
       </c>
       <c r="B129" t="inlineStr">
         <is>
-          <t>Core PPI YoYDEC</t>
+          <t>Core PPI MoMDEC</t>
         </is>
       </c>
       <c r="C129" t="inlineStr">
         <is>
-          <t>3.5%</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="D129" t="inlineStr">
         <is>
-          <t>3.5%</t>
+          <t>0.2%</t>
         </is>
       </c>
       <c r="E129" t="inlineStr">
         <is>
-          <t>3.8%</t>
+          <t>0.3%</t>
         </is>
       </c>
       <c r="F129" t="inlineStr">
         <is>
-          <t>3.5%</t>
+          <t>0.2%</t>
         </is>
       </c>
       <c r="G129" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="130">
@@ -4169,27 +4169,31 @@
       </c>
       <c r="B130" t="inlineStr">
         <is>
-          <t>PPI Ex Food, Energy and Trade YoYDEC</t>
+          <t>PPI MoMDEC</t>
         </is>
       </c>
       <c r="C130" t="inlineStr">
         <is>
-          <t>3.3%</t>
+          <t>0.2%</t>
         </is>
       </c>
       <c r="D130" t="inlineStr">
         <is>
-          <t>3.5%</t>
-        </is>
-      </c>
-      <c r="E130" t="inlineStr"/>
+          <t>0.4%</t>
+        </is>
+      </c>
+      <c r="E130" t="inlineStr">
+        <is>
+          <t>0.3%</t>
+        </is>
+      </c>
       <c r="F130" t="inlineStr">
         <is>
-          <t>3.6%</t>
+          <t>0.3%</t>
         </is>
       </c>
       <c r="G130" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="131">
@@ -4200,27 +4204,27 @@
       </c>
       <c r="B131" t="inlineStr">
         <is>
-          <t>PPI YoYDEC</t>
+          <t>PPI Ex Food, Energy and Trade MoMDEC</t>
         </is>
       </c>
       <c r="C131" t="inlineStr">
         <is>
-          <t>3.3%</t>
+          <t>0.1%</t>
         </is>
       </c>
       <c r="D131" t="inlineStr">
         <is>
-          <t>3%</t>
+          <t>0.1%</t>
         </is>
       </c>
       <c r="E131" t="inlineStr">
         <is>
-          <t>3.4%</t>
+          <t>0.3%</t>
         </is>
       </c>
       <c r="F131" t="inlineStr">
         <is>
-          <t>3.3%</t>
+          <t>0.2%</t>
         </is>
       </c>
       <c r="G131" t="n">
@@ -4235,27 +4239,23 @@
       </c>
       <c r="B132" t="inlineStr">
         <is>
-          <t>PPI Ex Food, Energy and Trade MoMDEC</t>
+          <t>PPIDEC</t>
         </is>
       </c>
       <c r="C132" t="inlineStr">
         <is>
-          <t>0.1%</t>
+          <t>146.842</t>
         </is>
       </c>
       <c r="D132" t="inlineStr">
         <is>
-          <t>0.1%</t>
-        </is>
-      </c>
-      <c r="E132" t="inlineStr">
-        <is>
-          <t>0.3%</t>
-        </is>
-      </c>
+          <t>146.521</t>
+        </is>
+      </c>
+      <c r="E132" t="inlineStr"/>
       <c r="F132" t="inlineStr">
         <is>
-          <t>0.2%</t>
+          <t>146.8</t>
         </is>
       </c>
       <c r="G132" t="n">
@@ -4270,31 +4270,27 @@
       </c>
       <c r="B133" t="inlineStr">
         <is>
-          <t>PPI MoMDEC</t>
+          <t>PPI Ex Food, Energy and Trade YoYDEC</t>
         </is>
       </c>
       <c r="C133" t="inlineStr">
         <is>
-          <t>0.2%</t>
+          <t>3.3%</t>
         </is>
       </c>
       <c r="D133" t="inlineStr">
         <is>
-          <t>0.4%</t>
-        </is>
-      </c>
-      <c r="E133" t="inlineStr">
-        <is>
-          <t>0.3%</t>
-        </is>
-      </c>
+          <t>3.5%</t>
+        </is>
+      </c>
+      <c r="E133" t="inlineStr"/>
       <c r="F133" t="inlineStr">
         <is>
-          <t>0.3%</t>
+          <t>3.6%</t>
         </is>
       </c>
       <c r="G133" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="134">
@@ -4305,23 +4301,27 @@
       </c>
       <c r="B134" t="inlineStr">
         <is>
-          <t>PPIDEC</t>
+          <t>Core PPI YoYDEC</t>
         </is>
       </c>
       <c r="C134" t="inlineStr">
         <is>
-          <t>146.842</t>
+          <t>3.5%</t>
         </is>
       </c>
       <c r="D134" t="inlineStr">
         <is>
-          <t>146.521</t>
-        </is>
-      </c>
-      <c r="E134" t="inlineStr"/>
+          <t>3.5%</t>
+        </is>
+      </c>
+      <c r="E134" t="inlineStr">
+        <is>
+          <t>3.8%</t>
+        </is>
+      </c>
       <c r="F134" t="inlineStr">
         <is>
-          <t>146.8</t>
+          <t>3.5%</t>
         </is>
       </c>
       <c r="G134" t="n">
@@ -4336,31 +4336,31 @@
       </c>
       <c r="B135" t="inlineStr">
         <is>
-          <t>Core PPI MoMDEC</t>
+          <t>PPI YoYDEC</t>
         </is>
       </c>
       <c r="C135" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>3.3%</t>
         </is>
       </c>
       <c r="D135" t="inlineStr">
         <is>
-          <t>0.2%</t>
+          <t>3%</t>
         </is>
       </c>
       <c r="E135" t="inlineStr">
         <is>
-          <t>0.3%</t>
+          <t>3.4%</t>
         </is>
       </c>
       <c r="F135" t="inlineStr">
         <is>
-          <t>0.2%</t>
+          <t>3.3%</t>
         </is>
       </c>
       <c r="G135" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="136">
@@ -4564,17 +4564,17 @@
       </c>
       <c r="B143" t="inlineStr">
         <is>
-          <t>MBA Mortgage ApplicationsJAN/10</t>
+          <t>MBA Purchase IndexJAN/10</t>
         </is>
       </c>
       <c r="C143" t="inlineStr">
         <is>
-          <t>33.3%</t>
+          <t>162</t>
         </is>
       </c>
       <c r="D143" t="inlineStr">
         <is>
-          <t>-3.7%</t>
+          <t>127.7000</t>
         </is>
       </c>
       <c r="E143" t="inlineStr"/>
@@ -4591,23 +4591,23 @@
       </c>
       <c r="B144" t="inlineStr">
         <is>
-          <t>MBA Mortgage Market IndexJAN/10</t>
+          <t>MBA 30-Year Mortgage RateJAN/10</t>
         </is>
       </c>
       <c r="C144" t="inlineStr">
         <is>
-          <t>224.4</t>
+          <t>7.09%</t>
         </is>
       </c>
       <c r="D144" t="inlineStr">
         <is>
-          <t>168.4</t>
+          <t>6.99%</t>
         </is>
       </c>
       <c r="E144" t="inlineStr"/>
       <c r="F144" t="inlineStr"/>
       <c r="G144" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="145">
@@ -4618,23 +4618,23 @@
       </c>
       <c r="B145" t="inlineStr">
         <is>
-          <t>MBA 30-Year Mortgage RateJAN/10</t>
+          <t>MBA Mortgage Refinance IndexJAN/10</t>
         </is>
       </c>
       <c r="C145" t="inlineStr">
         <is>
-          <t>7.09%</t>
+          <t>575.6</t>
         </is>
       </c>
       <c r="D145" t="inlineStr">
         <is>
-          <t>6.99%</t>
+          <t>401.1000</t>
         </is>
       </c>
       <c r="E145" t="inlineStr"/>
       <c r="F145" t="inlineStr"/>
       <c r="G145" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="146">
@@ -4645,17 +4645,17 @@
       </c>
       <c r="B146" t="inlineStr">
         <is>
-          <t>MBA Mortgage Refinance IndexJAN/10</t>
+          <t>MBA Mortgage ApplicationsJAN/10</t>
         </is>
       </c>
       <c r="C146" t="inlineStr">
         <is>
-          <t>575.6</t>
+          <t>33.3%</t>
         </is>
       </c>
       <c r="D146" t="inlineStr">
         <is>
-          <t>401.1000</t>
+          <t>-3.7%</t>
         </is>
       </c>
       <c r="E146" t="inlineStr"/>
@@ -4672,17 +4672,17 @@
       </c>
       <c r="B147" t="inlineStr">
         <is>
-          <t>MBA Purchase IndexJAN/10</t>
+          <t>MBA Mortgage Market IndexJAN/10</t>
         </is>
       </c>
       <c r="C147" t="inlineStr">
         <is>
-          <t>162</t>
+          <t>224.4</t>
         </is>
       </c>
       <c r="D147" t="inlineStr">
         <is>
-          <t>127.7000</t>
+          <t>168.4</t>
         </is>
       </c>
       <c r="E147" t="inlineStr"/>
@@ -4978,22 +4978,22 @@
       </c>
       <c r="B157" t="inlineStr">
         <is>
-          <t>EIA Crude Oil Stocks ChangeJAN/10</t>
+          <t>EIA Gasoline Stocks ChangeJAN/10</t>
         </is>
       </c>
       <c r="C157" t="inlineStr">
         <is>
-          <t>-1.961M</t>
+          <t>5.852M</t>
         </is>
       </c>
       <c r="D157" t="inlineStr">
         <is>
-          <t>-0.959M</t>
+          <t>6.33M</t>
         </is>
       </c>
       <c r="E157" t="inlineStr">
         <is>
-          <t>-1.6M</t>
+          <t>2.60M</t>
         </is>
       </c>
       <c r="F157" t="inlineStr"/>
@@ -5009,20 +5009,24 @@
       </c>
       <c r="B158" t="inlineStr">
         <is>
-          <t>EIA Distillate Fuel Production ChangeJAN/10</t>
+          <t>EIA Distillate Stocks ChangeJAN/10</t>
         </is>
       </c>
       <c r="C158" t="inlineStr">
         <is>
-          <t>-0.021M</t>
+          <t>3.077M</t>
         </is>
       </c>
       <c r="D158" t="inlineStr">
         <is>
-          <t>-0.167M</t>
-        </is>
-      </c>
-      <c r="E158" t="inlineStr"/>
+          <t>6.071M</t>
+        </is>
+      </c>
+      <c r="E158" t="inlineStr">
+        <is>
+          <t>1.1M</t>
+        </is>
+      </c>
       <c r="F158" t="inlineStr"/>
       <c r="G158" t="n">
         <v>3</v>
@@ -5036,17 +5040,17 @@
       </c>
       <c r="B159" t="inlineStr">
         <is>
-          <t>EIA Gasoline Production ChangeJAN/10</t>
+          <t>EIA Heating Oil Stocks ChangeJAN/10</t>
         </is>
       </c>
       <c r="C159" t="inlineStr">
         <is>
-          <t>0.397M</t>
+          <t>0.646M</t>
         </is>
       </c>
       <c r="D159" t="inlineStr">
         <is>
-          <t>-0.081M</t>
+          <t>-0.632M</t>
         </is>
       </c>
       <c r="E159" t="inlineStr"/>
@@ -5063,17 +5067,17 @@
       </c>
       <c r="B160" t="inlineStr">
         <is>
-          <t>EIA Refinery Crude Runs ChangeJAN/10</t>
+          <t>EIA Crude Oil Imports ChangeJAN/10</t>
         </is>
       </c>
       <c r="C160" t="inlineStr">
         <is>
-          <t>-0.255M</t>
+          <t>-1.304M</t>
         </is>
       </c>
       <c r="D160" t="inlineStr">
         <is>
-          <t>0.045M</t>
+          <t>0.278M</t>
         </is>
       </c>
       <c r="E160" t="inlineStr"/>
@@ -5090,17 +5094,17 @@
       </c>
       <c r="B161" t="inlineStr">
         <is>
-          <t>EIA Crude Oil Imports ChangeJAN/10</t>
+          <t>EIA Cushing Crude Oil Stocks ChangeJAN/10</t>
         </is>
       </c>
       <c r="C161" t="inlineStr">
         <is>
-          <t>-1.304M</t>
+          <t>0.765M</t>
         </is>
       </c>
       <c r="D161" t="inlineStr">
         <is>
-          <t>0.278M</t>
+          <t>-2.502M</t>
         </is>
       </c>
       <c r="E161" t="inlineStr"/>
@@ -5117,27 +5121,23 @@
       </c>
       <c r="B162" t="inlineStr">
         <is>
-          <t>EIA Gasoline Stocks ChangeJAN/10</t>
+          <t>EIA Gasoline Production ChangeJAN/10</t>
         </is>
       </c>
       <c r="C162" t="inlineStr">
         <is>
-          <t>5.852M</t>
+          <t>0.397M</t>
         </is>
       </c>
       <c r="D162" t="inlineStr">
         <is>
-          <t>6.33M</t>
-        </is>
-      </c>
-      <c r="E162" t="inlineStr">
-        <is>
-          <t>2.60M</t>
-        </is>
-      </c>
+          <t>-0.081M</t>
+        </is>
+      </c>
+      <c r="E162" t="inlineStr"/>
       <c r="F162" t="inlineStr"/>
       <c r="G162" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="163">
@@ -5148,23 +5148,27 @@
       </c>
       <c r="B163" t="inlineStr">
         <is>
-          <t>EIA Heating Oil Stocks ChangeJAN/10</t>
+          <t>EIA Crude Oil Stocks ChangeJAN/10</t>
         </is>
       </c>
       <c r="C163" t="inlineStr">
         <is>
-          <t>0.646M</t>
+          <t>-1.961M</t>
         </is>
       </c>
       <c r="D163" t="inlineStr">
         <is>
-          <t>-0.632M</t>
-        </is>
-      </c>
-      <c r="E163" t="inlineStr"/>
+          <t>-0.959M</t>
+        </is>
+      </c>
+      <c r="E163" t="inlineStr">
+        <is>
+          <t>-1.6M</t>
+        </is>
+      </c>
       <c r="F163" t="inlineStr"/>
       <c r="G163" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="164">
@@ -5175,24 +5179,20 @@
       </c>
       <c r="B164" t="inlineStr">
         <is>
-          <t>EIA Distillate Stocks ChangeJAN/10</t>
+          <t>EIA Refinery Crude Runs ChangeJAN/10</t>
         </is>
       </c>
       <c r="C164" t="inlineStr">
         <is>
-          <t>3.077M</t>
+          <t>-0.255M</t>
         </is>
       </c>
       <c r="D164" t="inlineStr">
         <is>
-          <t>6.071M</t>
-        </is>
-      </c>
-      <c r="E164" t="inlineStr">
-        <is>
-          <t>1.1M</t>
-        </is>
-      </c>
+          <t>0.045M</t>
+        </is>
+      </c>
+      <c r="E164" t="inlineStr"/>
       <c r="F164" t="inlineStr"/>
       <c r="G164" t="n">
         <v>3</v>
@@ -5206,17 +5206,17 @@
       </c>
       <c r="B165" t="inlineStr">
         <is>
-          <t>EIA Cushing Crude Oil Stocks ChangeJAN/10</t>
+          <t>EIA Distillate Fuel Production ChangeJAN/10</t>
         </is>
       </c>
       <c r="C165" t="inlineStr">
         <is>
-          <t>0.765M</t>
+          <t>-0.021M</t>
         </is>
       </c>
       <c r="D165" t="inlineStr">
         <is>
-          <t>-2.502M</t>
+          <t>-0.167M</t>
         </is>
       </c>
       <c r="E165" t="inlineStr"/>
@@ -5336,21 +5336,25 @@
       </c>
       <c r="B171" t="inlineStr">
         <is>
-          <t>Philly Fed Business ConditionsJAN</t>
+          <t>Jobless Claims 4-week AverageJAN/11</t>
         </is>
       </c>
       <c r="C171" t="inlineStr">
         <is>
-          <t>46.3</t>
+          <t>212.75K</t>
         </is>
       </c>
       <c r="D171" t="inlineStr">
         <is>
-          <t>33.8</t>
+          <t>213.5K</t>
         </is>
       </c>
       <c r="E171" t="inlineStr"/>
-      <c r="F171" t="inlineStr"/>
+      <c r="F171" t="inlineStr">
+        <is>
+          <t>215.0K</t>
+        </is>
+      </c>
       <c r="G171" t="n">
         <v>3</v>
       </c>
@@ -5363,31 +5367,23 @@
       </c>
       <c r="B172" t="inlineStr">
         <is>
-          <t>Philadelphia Fed Manufacturing IndexJAN</t>
+          <t>Philly Fed CAPEX IndexJAN</t>
         </is>
       </c>
       <c r="C172" t="inlineStr">
         <is>
-          <t>44.3</t>
+          <t>39.00</t>
         </is>
       </c>
       <c r="D172" t="inlineStr">
         <is>
-          <t>-10.9</t>
-        </is>
-      </c>
-      <c r="E172" t="inlineStr">
-        <is>
-          <t>-5</t>
-        </is>
-      </c>
-      <c r="F172" t="inlineStr">
-        <is>
-          <t>-10</t>
-        </is>
-      </c>
+          <t>22.20</t>
+        </is>
+      </c>
+      <c r="E172" t="inlineStr"/>
+      <c r="F172" t="inlineStr"/>
       <c r="G172" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="173">
@@ -5398,27 +5394,23 @@
       </c>
       <c r="B173" t="inlineStr">
         <is>
-          <t>Import Prices YoYDEC</t>
+          <t>Export Prices YoYDEC</t>
         </is>
       </c>
       <c r="C173" t="inlineStr">
         <is>
-          <t>2.2%</t>
+          <t>1.8%</t>
         </is>
       </c>
       <c r="D173" t="inlineStr">
         <is>
-          <t>1.4%</t>
-        </is>
-      </c>
-      <c r="E173" t="inlineStr">
-        <is>
-          <t>2.1%</t>
-        </is>
-      </c>
+          <t>0.9%</t>
+        </is>
+      </c>
+      <c r="E173" t="inlineStr"/>
       <c r="F173" t="inlineStr">
         <is>
-          <t>1.6%</t>
+          <t>1.9%</t>
         </is>
       </c>
       <c r="G173" t="n">
@@ -5433,21 +5425,25 @@
       </c>
       <c r="B174" t="inlineStr">
         <is>
-          <t>Philly Fed EmploymentJAN</t>
+          <t>Retail Sales YoYDEC</t>
         </is>
       </c>
       <c r="C174" t="inlineStr">
         <is>
-          <t>11.9</t>
+          <t>3.9%</t>
         </is>
       </c>
       <c r="D174" t="inlineStr">
         <is>
-          <t>4.8</t>
+          <t>4.1%</t>
         </is>
       </c>
       <c r="E174" t="inlineStr"/>
-      <c r="F174" t="inlineStr"/>
+      <c r="F174" t="inlineStr">
+        <is>
+          <t>4.0%</t>
+        </is>
+      </c>
       <c r="G174" t="n">
         <v>3</v>
       </c>
@@ -5460,31 +5456,31 @@
       </c>
       <c r="B175" t="inlineStr">
         <is>
-          <t>Continuing Jobless ClaimsJAN/04</t>
+          <t>Retail Sales MoMDEC</t>
         </is>
       </c>
       <c r="C175" t="inlineStr">
         <is>
-          <t>1859K</t>
+          <t>0.4%</t>
         </is>
       </c>
       <c r="D175" t="inlineStr">
         <is>
-          <t>1867K</t>
+          <t>0.8%</t>
         </is>
       </c>
       <c r="E175" t="inlineStr">
         <is>
-          <t>1870K</t>
+          <t>0.6%</t>
         </is>
       </c>
       <c r="F175" t="inlineStr">
         <is>
-          <t>1870.0K</t>
+          <t>0.5%</t>
         </is>
       </c>
       <c r="G175" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="176">
@@ -5495,7 +5491,7 @@
       </c>
       <c r="B176" t="inlineStr">
         <is>
-          <t>Retail Sales Ex Gas/Autos MoMDEC</t>
+          <t>Export Prices MoMDEC</t>
         </is>
       </c>
       <c r="C176" t="inlineStr">
@@ -5505,21 +5501,21 @@
       </c>
       <c r="D176" t="inlineStr">
         <is>
+          <t>0%</t>
+        </is>
+      </c>
+      <c r="E176" t="inlineStr">
+        <is>
           <t>0.2%</t>
         </is>
       </c>
-      <c r="E176" t="inlineStr">
-        <is>
-          <t>0.4%</t>
-        </is>
-      </c>
       <c r="F176" t="inlineStr">
         <is>
-          <t>0.4%</t>
+          <t>0.5%</t>
         </is>
       </c>
       <c r="G176" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="177">
@@ -5530,23 +5526,31 @@
       </c>
       <c r="B177" t="inlineStr">
         <is>
-          <t>Philly Fed New OrdersJAN</t>
+          <t>Initial Jobless ClaimsJAN/11</t>
         </is>
       </c>
       <c r="C177" t="inlineStr">
         <is>
-          <t>42.9</t>
+          <t>217K</t>
         </is>
       </c>
       <c r="D177" t="inlineStr">
         <is>
-          <t>-3.6</t>
-        </is>
-      </c>
-      <c r="E177" t="inlineStr"/>
-      <c r="F177" t="inlineStr"/>
+          <t>203K</t>
+        </is>
+      </c>
+      <c r="E177" t="inlineStr">
+        <is>
+          <t>210K</t>
+        </is>
+      </c>
+      <c r="F177" t="inlineStr">
+        <is>
+          <t>209.0K</t>
+        </is>
+      </c>
       <c r="G177" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="178">
@@ -5557,27 +5561,31 @@
       </c>
       <c r="B178" t="inlineStr">
         <is>
-          <t>Jobless Claims 4-week AverageJAN/11</t>
+          <t>Retail Sales Ex Autos MoMDEC</t>
         </is>
       </c>
       <c r="C178" t="inlineStr">
         <is>
-          <t>212.75K</t>
+          <t>0.4%</t>
         </is>
       </c>
       <c r="D178" t="inlineStr">
         <is>
-          <t>213.5K</t>
-        </is>
-      </c>
-      <c r="E178" t="inlineStr"/>
+          <t>0.2%</t>
+        </is>
+      </c>
+      <c r="E178" t="inlineStr">
+        <is>
+          <t>0.4%</t>
+        </is>
+      </c>
       <c r="F178" t="inlineStr">
         <is>
-          <t>215.0K</t>
+          <t>0.4%</t>
         </is>
       </c>
       <c r="G178" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="179">
@@ -5588,31 +5596,23 @@
       </c>
       <c r="B179" t="inlineStr">
         <is>
-          <t>Import Prices MoMDEC</t>
+          <t>Philly Fed Prices PaidJAN</t>
         </is>
       </c>
       <c r="C179" t="inlineStr">
         <is>
-          <t>0.1%</t>
+          <t>31.90</t>
         </is>
       </c>
       <c r="D179" t="inlineStr">
         <is>
-          <t>0.1%</t>
-        </is>
-      </c>
-      <c r="E179" t="inlineStr">
-        <is>
-          <t>0.1%</t>
-        </is>
-      </c>
-      <c r="F179" t="inlineStr">
-        <is>
-          <t>0.1%</t>
-        </is>
-      </c>
+          <t>26.60</t>
+        </is>
+      </c>
+      <c r="E179" t="inlineStr"/>
+      <c r="F179" t="inlineStr"/>
       <c r="G179" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="180">
@@ -5623,17 +5623,17 @@
       </c>
       <c r="B180" t="inlineStr">
         <is>
-          <t>Philly Fed Prices PaidJAN</t>
+          <t>Philly Fed New OrdersJAN</t>
         </is>
       </c>
       <c r="C180" t="inlineStr">
         <is>
-          <t>31.90</t>
+          <t>42.9</t>
         </is>
       </c>
       <c r="D180" t="inlineStr">
         <is>
-          <t>26.60</t>
+          <t>-3.6</t>
         </is>
       </c>
       <c r="E180" t="inlineStr"/>
@@ -5650,31 +5650,31 @@
       </c>
       <c r="B181" t="inlineStr">
         <is>
-          <t>Retail Sales Ex Autos MoMDEC</t>
+          <t>Retail Sales Ex Gas/Autos MoMDEC</t>
         </is>
       </c>
       <c r="C181" t="inlineStr">
         <is>
+          <t>0.3%</t>
+        </is>
+      </c>
+      <c r="D181" t="inlineStr">
+        <is>
+          <t>0.2%</t>
+        </is>
+      </c>
+      <c r="E181" t="inlineStr">
+        <is>
           <t>0.4%</t>
         </is>
       </c>
-      <c r="D181" t="inlineStr">
-        <is>
-          <t>0.2%</t>
-        </is>
-      </c>
-      <c r="E181" t="inlineStr">
+      <c r="F181" t="inlineStr">
         <is>
           <t>0.4%</t>
         </is>
       </c>
-      <c r="F181" t="inlineStr">
-        <is>
-          <t>0.4%</t>
-        </is>
-      </c>
       <c r="G181" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="182">
@@ -5685,31 +5685,31 @@
       </c>
       <c r="B182" t="inlineStr">
         <is>
-          <t>Initial Jobless ClaimsJAN/11</t>
+          <t>Continuing Jobless ClaimsJAN/04</t>
         </is>
       </c>
       <c r="C182" t="inlineStr">
         <is>
-          <t>217K</t>
+          <t>1859K</t>
         </is>
       </c>
       <c r="D182" t="inlineStr">
         <is>
-          <t>203K</t>
+          <t>1867K</t>
         </is>
       </c>
       <c r="E182" t="inlineStr">
         <is>
-          <t>210K</t>
+          <t>1870K</t>
         </is>
       </c>
       <c r="F182" t="inlineStr">
         <is>
-          <t>209.0K</t>
+          <t>1870.0K</t>
         </is>
       </c>
       <c r="G182" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="183">
@@ -5720,31 +5720,23 @@
       </c>
       <c r="B183" t="inlineStr">
         <is>
-          <t>Export Prices MoMDEC</t>
+          <t>Philly Fed EmploymentJAN</t>
         </is>
       </c>
       <c r="C183" t="inlineStr">
         <is>
-          <t>0.3%</t>
+          <t>11.9</t>
         </is>
       </c>
       <c r="D183" t="inlineStr">
         <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="E183" t="inlineStr">
-        <is>
-          <t>0.2%</t>
-        </is>
-      </c>
-      <c r="F183" t="inlineStr">
-        <is>
-          <t>0.5%</t>
-        </is>
-      </c>
+          <t>4.8</t>
+        </is>
+      </c>
+      <c r="E183" t="inlineStr"/>
+      <c r="F183" t="inlineStr"/>
       <c r="G183" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="184">
@@ -5755,31 +5747,31 @@
       </c>
       <c r="B184" t="inlineStr">
         <is>
-          <t>Retail Sales MoMDEC</t>
+          <t>Import Prices YoYDEC</t>
         </is>
       </c>
       <c r="C184" t="inlineStr">
         <is>
-          <t>0.4%</t>
+          <t>2.2%</t>
         </is>
       </c>
       <c r="D184" t="inlineStr">
         <is>
-          <t>0.8%</t>
+          <t>1.4%</t>
         </is>
       </c>
       <c r="E184" t="inlineStr">
         <is>
-          <t>0.6%</t>
+          <t>2.1%</t>
         </is>
       </c>
       <c r="F184" t="inlineStr">
         <is>
-          <t>0.5%</t>
+          <t>1.6%</t>
         </is>
       </c>
       <c r="G184" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="185">
@@ -5790,27 +5782,31 @@
       </c>
       <c r="B185" t="inlineStr">
         <is>
-          <t>Retail Sales YoYDEC</t>
+          <t>Philadelphia Fed Manufacturing IndexJAN</t>
         </is>
       </c>
       <c r="C185" t="inlineStr">
         <is>
-          <t>3.9%</t>
+          <t>44.3</t>
         </is>
       </c>
       <c r="D185" t="inlineStr">
         <is>
-          <t>4.1%</t>
-        </is>
-      </c>
-      <c r="E185" t="inlineStr"/>
+          <t>-10.9</t>
+        </is>
+      </c>
+      <c r="E185" t="inlineStr">
+        <is>
+          <t>-5</t>
+        </is>
+      </c>
       <c r="F185" t="inlineStr">
         <is>
-          <t>4.0%</t>
+          <t>-10</t>
         </is>
       </c>
       <c r="G185" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="186">
@@ -5821,25 +5817,21 @@
       </c>
       <c r="B186" t="inlineStr">
         <is>
-          <t>Export Prices YoYDEC</t>
+          <t>Philly Fed Business ConditionsJAN</t>
         </is>
       </c>
       <c r="C186" t="inlineStr">
         <is>
-          <t>1.8%</t>
+          <t>46.3</t>
         </is>
       </c>
       <c r="D186" t="inlineStr">
         <is>
-          <t>0.9%</t>
+          <t>33.8</t>
         </is>
       </c>
       <c r="E186" t="inlineStr"/>
-      <c r="F186" t="inlineStr">
-        <is>
-          <t>1.9%</t>
-        </is>
-      </c>
+      <c r="F186" t="inlineStr"/>
       <c r="G186" t="n">
         <v>3</v>
       </c>
@@ -5852,23 +5844,31 @@
       </c>
       <c r="B187" t="inlineStr">
         <is>
-          <t>Philly Fed CAPEX IndexJAN</t>
+          <t>Import Prices MoMDEC</t>
         </is>
       </c>
       <c r="C187" t="inlineStr">
         <is>
-          <t>39.00</t>
+          <t>0.1%</t>
         </is>
       </c>
       <c r="D187" t="inlineStr">
         <is>
-          <t>22.20</t>
-        </is>
-      </c>
-      <c r="E187" t="inlineStr"/>
-      <c r="F187" t="inlineStr"/>
+          <t>0.1%</t>
+        </is>
+      </c>
+      <c r="E187" t="inlineStr">
+        <is>
+          <t>0.1%</t>
+        </is>
+      </c>
+      <c r="F187" t="inlineStr">
+        <is>
+          <t>0.1%</t>
+        </is>
+      </c>
       <c r="G187" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="188">
@@ -6015,17 +6015,17 @@
       </c>
       <c r="B192" t="inlineStr">
         <is>
-          <t>8-Week Bill Auction</t>
+          <t>4-Week Bill Auction</t>
         </is>
       </c>
       <c r="C192" t="inlineStr">
         <is>
-          <t>4.235%</t>
+          <t>4.240%</t>
         </is>
       </c>
       <c r="D192" t="inlineStr">
         <is>
-          <t>4.240%</t>
+          <t>4.245%</t>
         </is>
       </c>
       <c r="E192" t="inlineStr"/>
@@ -6042,17 +6042,17 @@
       </c>
       <c r="B193" t="inlineStr">
         <is>
-          <t>4-Week Bill Auction</t>
+          <t>8-Week Bill Auction</t>
         </is>
       </c>
       <c r="C193" t="inlineStr">
         <is>
+          <t>4.235%</t>
+        </is>
+      </c>
+      <c r="D193" t="inlineStr">
+        <is>
           <t>4.240%</t>
-        </is>
-      </c>
-      <c r="D193" t="inlineStr">
-        <is>
-          <t>4.245%</t>
         </is>
       </c>
       <c r="E193" t="inlineStr"/>
@@ -6503,23 +6503,27 @@
       </c>
       <c r="B208" t="inlineStr">
         <is>
-          <t>Overall Net Capital FlowsNOV</t>
+          <t>Net Long-term TIC FlowsNOV</t>
         </is>
       </c>
       <c r="C208" t="inlineStr">
         <is>
+          <t>$79B</t>
+        </is>
+      </c>
+      <c r="D208" t="inlineStr">
+        <is>
+          <t>$159.1B</t>
+        </is>
+      </c>
+      <c r="E208" t="inlineStr">
+        <is>
           <t>$159.9B</t>
         </is>
       </c>
-      <c r="D208" t="inlineStr">
-        <is>
-          <t>$201.8B</t>
-        </is>
-      </c>
-      <c r="E208" t="inlineStr"/>
       <c r="F208" t="inlineStr"/>
       <c r="G208" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="209">
@@ -6530,17 +6534,17 @@
       </c>
       <c r="B209" t="inlineStr">
         <is>
-          <t>Foreign Bond InvestmentNOV</t>
+          <t>Overall Net Capital FlowsNOV</t>
         </is>
       </c>
       <c r="C209" t="inlineStr">
         <is>
-          <t>$-15.8B</t>
+          <t>$159.9B</t>
         </is>
       </c>
       <c r="D209" t="inlineStr">
         <is>
-          <t>$92B</t>
+          <t>$201.8B</t>
         </is>
       </c>
       <c r="E209" t="inlineStr"/>
@@ -6557,27 +6561,23 @@
       </c>
       <c r="B210" t="inlineStr">
         <is>
-          <t>Net Long-term TIC FlowsNOV</t>
+          <t>Foreign Bond InvestmentNOV</t>
         </is>
       </c>
       <c r="C210" t="inlineStr">
         <is>
-          <t>$79B</t>
+          <t>$-15.8B</t>
         </is>
       </c>
       <c r="D210" t="inlineStr">
         <is>
-          <t>$159.1B</t>
-        </is>
-      </c>
-      <c r="E210" t="inlineStr">
-        <is>
-          <t>$159.9B</t>
-        </is>
-      </c>
+          <t>$92B</t>
+        </is>
+      </c>
+      <c r="E210" t="inlineStr"/>
       <c r="F210" t="inlineStr"/>
       <c r="G210" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="211">
@@ -7241,24 +7241,20 @@
       </c>
       <c r="B234" t="inlineStr">
         <is>
-          <t>EIA Distillate Stocks ChangeJAN/17</t>
+          <t>EIA Refinery Crude Runs ChangeJAN/17</t>
         </is>
       </c>
       <c r="C234" t="inlineStr">
         <is>
-          <t>-3.07M</t>
+          <t>-1.125M</t>
         </is>
       </c>
       <c r="D234" t="inlineStr">
         <is>
-          <t>3.077M</t>
-        </is>
-      </c>
-      <c r="E234" t="inlineStr">
-        <is>
-          <t>0.6M</t>
-        </is>
-      </c>
+          <t>-0.255M</t>
+        </is>
+      </c>
+      <c r="E234" t="inlineStr"/>
       <c r="F234" t="inlineStr"/>
       <c r="G234" t="n">
         <v>3</v>
@@ -7272,17 +7268,17 @@
       </c>
       <c r="B235" t="inlineStr">
         <is>
-          <t>EIA Heating Oil Stocks ChangeJAN/17</t>
+          <t>EIA Crude Oil Imports ChangeJAN/17</t>
         </is>
       </c>
       <c r="C235" t="inlineStr">
         <is>
-          <t>0.068M</t>
+          <t>0.184M</t>
         </is>
       </c>
       <c r="D235" t="inlineStr">
         <is>
-          <t>0.646M</t>
+          <t>-1.304M</t>
         </is>
       </c>
       <c r="E235" t="inlineStr"/>
@@ -7299,27 +7295,23 @@
       </c>
       <c r="B236" t="inlineStr">
         <is>
-          <t>EIA Crude Oil Stocks ChangeJAN/17</t>
+          <t>EIA Gasoline Production ChangeJAN/17</t>
         </is>
       </c>
       <c r="C236" t="inlineStr">
         <is>
-          <t>-1.017M</t>
+          <t>-0.043M</t>
         </is>
       </c>
       <c r="D236" t="inlineStr">
         <is>
-          <t>-1.962M</t>
-        </is>
-      </c>
-      <c r="E236" t="inlineStr">
-        <is>
-          <t>-2.1M</t>
-        </is>
-      </c>
+          <t>0.397M</t>
+        </is>
+      </c>
+      <c r="E236" t="inlineStr"/>
       <c r="F236" t="inlineStr"/>
       <c r="G236" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="237">
@@ -7330,17 +7322,17 @@
       </c>
       <c r="B237" t="inlineStr">
         <is>
-          <t>15-Year Mortgage RateJAN/23</t>
+          <t>EIA Cushing Crude Oil Stocks ChangeJAN/17</t>
         </is>
       </c>
       <c r="C237" t="inlineStr">
         <is>
-          <t>6.16%</t>
+          <t>-0.148M</t>
         </is>
       </c>
       <c r="D237" t="inlineStr">
         <is>
-          <t>6.27%</t>
+          <t>0.765M</t>
         </is>
       </c>
       <c r="E237" t="inlineStr"/>
@@ -7357,27 +7349,23 @@
       </c>
       <c r="B238" t="inlineStr">
         <is>
-          <t>EIA Gasoline Stocks ChangeJAN/17</t>
+          <t>30-Year Mortgage RateJAN/23</t>
         </is>
       </c>
       <c r="C238" t="inlineStr">
         <is>
-          <t>2.332M</t>
+          <t>6.96%</t>
         </is>
       </c>
       <c r="D238" t="inlineStr">
         <is>
-          <t>5.852M</t>
-        </is>
-      </c>
-      <c r="E238" t="inlineStr">
-        <is>
-          <t>2.5M</t>
-        </is>
-      </c>
+          <t>7.04%</t>
+        </is>
+      </c>
+      <c r="E238" t="inlineStr"/>
       <c r="F238" t="inlineStr"/>
       <c r="G238" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="239">
@@ -7388,23 +7376,27 @@
       </c>
       <c r="B239" t="inlineStr">
         <is>
-          <t>EIA Distillate Fuel Production ChangeJAN/17</t>
+          <t>EIA Gasoline Stocks ChangeJAN/17</t>
         </is>
       </c>
       <c r="C239" t="inlineStr">
         <is>
-          <t>-0.473M</t>
+          <t>2.332M</t>
         </is>
       </c>
       <c r="D239" t="inlineStr">
         <is>
-          <t>-0.021M</t>
-        </is>
-      </c>
-      <c r="E239" t="inlineStr"/>
+          <t>5.852M</t>
+        </is>
+      </c>
+      <c r="E239" t="inlineStr">
+        <is>
+          <t>2.5M</t>
+        </is>
+      </c>
       <c r="F239" t="inlineStr"/>
       <c r="G239" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="240">
@@ -7415,17 +7407,17 @@
       </c>
       <c r="B240" t="inlineStr">
         <is>
-          <t>30-Year Mortgage RateJAN/23</t>
+          <t>15-Year Mortgage RateJAN/23</t>
         </is>
       </c>
       <c r="C240" t="inlineStr">
         <is>
-          <t>6.96%</t>
+          <t>6.16%</t>
         </is>
       </c>
       <c r="D240" t="inlineStr">
         <is>
-          <t>7.04%</t>
+          <t>6.27%</t>
         </is>
       </c>
       <c r="E240" t="inlineStr"/>
@@ -7442,23 +7434,27 @@
       </c>
       <c r="B241" t="inlineStr">
         <is>
-          <t>EIA Cushing Crude Oil Stocks ChangeJAN/17</t>
+          <t>EIA Crude Oil Stocks ChangeJAN/17</t>
         </is>
       </c>
       <c r="C241" t="inlineStr">
         <is>
-          <t>-0.148M</t>
+          <t>-1.017M</t>
         </is>
       </c>
       <c r="D241" t="inlineStr">
         <is>
-          <t>0.765M</t>
-        </is>
-      </c>
-      <c r="E241" t="inlineStr"/>
+          <t>-1.962M</t>
+        </is>
+      </c>
+      <c r="E241" t="inlineStr">
+        <is>
+          <t>-2.1M</t>
+        </is>
+      </c>
       <c r="F241" t="inlineStr"/>
       <c r="G241" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="242">
@@ -7469,17 +7465,17 @@
       </c>
       <c r="B242" t="inlineStr">
         <is>
-          <t>EIA Gasoline Production ChangeJAN/17</t>
+          <t>EIA Heating Oil Stocks ChangeJAN/17</t>
         </is>
       </c>
       <c r="C242" t="inlineStr">
         <is>
-          <t>-0.043M</t>
+          <t>0.068M</t>
         </is>
       </c>
       <c r="D242" t="inlineStr">
         <is>
-          <t>0.397M</t>
+          <t>0.646M</t>
         </is>
       </c>
       <c r="E242" t="inlineStr"/>
@@ -7496,20 +7492,24 @@
       </c>
       <c r="B243" t="inlineStr">
         <is>
-          <t>EIA Crude Oil Imports ChangeJAN/17</t>
+          <t>EIA Distillate Stocks ChangeJAN/17</t>
         </is>
       </c>
       <c r="C243" t="inlineStr">
         <is>
-          <t>0.184M</t>
+          <t>-3.07M</t>
         </is>
       </c>
       <c r="D243" t="inlineStr">
         <is>
-          <t>-1.304M</t>
-        </is>
-      </c>
-      <c r="E243" t="inlineStr"/>
+          <t>3.077M</t>
+        </is>
+      </c>
+      <c r="E243" t="inlineStr">
+        <is>
+          <t>0.6M</t>
+        </is>
+      </c>
       <c r="F243" t="inlineStr"/>
       <c r="G243" t="n">
         <v>3</v>
@@ -7523,17 +7523,17 @@
       </c>
       <c r="B244" t="inlineStr">
         <is>
-          <t>EIA Refinery Crude Runs ChangeJAN/17</t>
+          <t>EIA Distillate Fuel Production ChangeJAN/17</t>
         </is>
       </c>
       <c r="C244" t="inlineStr">
         <is>
-          <t>-1.125M</t>
+          <t>-0.473M</t>
         </is>
       </c>
       <c r="D244" t="inlineStr">
         <is>
-          <t>-0.255M</t>
+          <t>-0.021M</t>
         </is>
       </c>
       <c r="E244" t="inlineStr"/>
@@ -7705,31 +7705,31 @@
       </c>
       <c r="B250" t="inlineStr">
         <is>
-          <t>Michigan Consumer Sentiment FinalJAN</t>
+          <t>Michigan Current Conditions FinalJAN</t>
         </is>
       </c>
       <c r="C250" t="inlineStr">
         <is>
-          <t>71.1</t>
+          <t>74.0</t>
         </is>
       </c>
       <c r="D250" t="inlineStr">
         <is>
-          <t>74.0</t>
+          <t>75.1</t>
         </is>
       </c>
       <c r="E250" t="inlineStr">
         <is>
-          <t>73.2</t>
+          <t>77.9</t>
         </is>
       </c>
       <c r="F250" t="inlineStr">
         <is>
-          <t>73.2</t>
+          <t>77.9</t>
         </is>
       </c>
       <c r="G250" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="251">
@@ -7740,27 +7740,31 @@
       </c>
       <c r="B251" t="inlineStr">
         <is>
-          <t>Existing Home Sales MoMDEC</t>
+          <t>Existing Home SalesDEC</t>
         </is>
       </c>
       <c r="C251" t="inlineStr">
         <is>
-          <t>2.2%</t>
+          <t>4.24M</t>
         </is>
       </c>
       <c r="D251" t="inlineStr">
         <is>
-          <t>4.8%</t>
-        </is>
-      </c>
-      <c r="E251" t="inlineStr"/>
+          <t>4.15M</t>
+        </is>
+      </c>
+      <c r="E251" t="inlineStr">
+        <is>
+          <t>4.19M</t>
+        </is>
+      </c>
       <c r="F251" t="inlineStr">
         <is>
-          <t>0.3%</t>
+          <t>4.1M</t>
         </is>
       </c>
       <c r="G251" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="252">
@@ -7771,27 +7775,27 @@
       </c>
       <c r="B252" t="inlineStr">
         <is>
-          <t>Michigan Consumer Expectations FinalJAN</t>
+          <t>Michigan 5 Year Inflation Expectations FinalJAN</t>
         </is>
       </c>
       <c r="C252" t="inlineStr">
         <is>
-          <t>69.3</t>
+          <t>3.2%</t>
         </is>
       </c>
       <c r="D252" t="inlineStr">
         <is>
-          <t>73.3</t>
+          <t>3%</t>
         </is>
       </c>
       <c r="E252" t="inlineStr">
         <is>
-          <t>70.2</t>
+          <t>3.3%</t>
         </is>
       </c>
       <c r="F252" t="inlineStr">
         <is>
-          <t>70.2</t>
+          <t>3.3%</t>
         </is>
       </c>
       <c r="G252" t="n">
@@ -7806,31 +7810,31 @@
       </c>
       <c r="B253" t="inlineStr">
         <is>
-          <t>Michigan Inflation Expectations FinalJAN</t>
+          <t>Michigan Consumer Sentiment FinalJAN</t>
         </is>
       </c>
       <c r="C253" t="inlineStr">
         <is>
-          <t>3.3%</t>
+          <t>71.1</t>
         </is>
       </c>
       <c r="D253" t="inlineStr">
         <is>
-          <t>2.8%</t>
+          <t>74.0</t>
         </is>
       </c>
       <c r="E253" t="inlineStr">
         <is>
-          <t>3.3%</t>
+          <t>73.2</t>
         </is>
       </c>
       <c r="F253" t="inlineStr">
         <is>
-          <t>3.3%</t>
+          <t>73.2</t>
         </is>
       </c>
       <c r="G253" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="254">
@@ -7841,27 +7845,27 @@
       </c>
       <c r="B254" t="inlineStr">
         <is>
-          <t>Michigan 5 Year Inflation Expectations FinalJAN</t>
+          <t>Michigan Consumer Expectations FinalJAN</t>
         </is>
       </c>
       <c r="C254" t="inlineStr">
         <is>
-          <t>3.2%</t>
+          <t>69.3</t>
         </is>
       </c>
       <c r="D254" t="inlineStr">
         <is>
-          <t>3%</t>
+          <t>73.3</t>
         </is>
       </c>
       <c r="E254" t="inlineStr">
         <is>
-          <t>3.3%</t>
+          <t>70.2</t>
         </is>
       </c>
       <c r="F254" t="inlineStr">
         <is>
-          <t>3.3%</t>
+          <t>70.2</t>
         </is>
       </c>
       <c r="G254" t="n">
@@ -7876,31 +7880,27 @@
       </c>
       <c r="B255" t="inlineStr">
         <is>
-          <t>Michigan Current Conditions FinalJAN</t>
+          <t>Existing Home Sales MoMDEC</t>
         </is>
       </c>
       <c r="C255" t="inlineStr">
         <is>
-          <t>74.0</t>
+          <t>2.2%</t>
         </is>
       </c>
       <c r="D255" t="inlineStr">
         <is>
-          <t>75.1</t>
-        </is>
-      </c>
-      <c r="E255" t="inlineStr">
-        <is>
-          <t>77.9</t>
-        </is>
-      </c>
+          <t>4.8%</t>
+        </is>
+      </c>
+      <c r="E255" t="inlineStr"/>
       <c r="F255" t="inlineStr">
         <is>
-          <t>77.9</t>
+          <t>0.3%</t>
         </is>
       </c>
       <c r="G255" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="256">
@@ -7911,31 +7911,31 @@
       </c>
       <c r="B256" t="inlineStr">
         <is>
-          <t>Existing Home SalesDEC</t>
+          <t>Michigan Inflation Expectations FinalJAN</t>
         </is>
       </c>
       <c r="C256" t="inlineStr">
         <is>
-          <t>4.24M</t>
+          <t>3.3%</t>
         </is>
       </c>
       <c r="D256" t="inlineStr">
         <is>
-          <t>4.15M</t>
+          <t>2.8%</t>
         </is>
       </c>
       <c r="E256" t="inlineStr">
         <is>
-          <t>4.19M</t>
+          <t>3.3%</t>
         </is>
       </c>
       <c r="F256" t="inlineStr">
         <is>
-          <t>4.1M</t>
+          <t>3.3%</t>
         </is>
       </c>
       <c r="G256" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="257">
@@ -8469,23 +8469,27 @@
       </c>
       <c r="B274" t="inlineStr">
         <is>
-          <t>S&amp;P/Case-Shiller Home Price MoMNOV</t>
+          <t>House Price Index MoMNOV</t>
         </is>
       </c>
       <c r="C274" t="inlineStr">
         <is>
-          <t>-0.1%</t>
+          <t>0.3%</t>
         </is>
       </c>
       <c r="D274" t="inlineStr">
         <is>
-          <t>-0.2%</t>
-        </is>
-      </c>
-      <c r="E274" t="inlineStr"/>
+          <t>0.5%</t>
+        </is>
+      </c>
+      <c r="E274" t="inlineStr">
+        <is>
+          <t>0.2%</t>
+        </is>
+      </c>
       <c r="F274" t="inlineStr">
         <is>
-          <t>-0.1%</t>
+          <t>0.3%</t>
         </is>
       </c>
       <c r="G274" t="n">
@@ -8500,27 +8504,31 @@
       </c>
       <c r="B275" t="inlineStr">
         <is>
-          <t>House Price Index YoYNOV</t>
+          <t>S&amp;P/Case-Shiller Home Price YoYNOV</t>
         </is>
       </c>
       <c r="C275" t="inlineStr">
         <is>
+          <t>4.3%</t>
+        </is>
+      </c>
+      <c r="D275" t="inlineStr">
+        <is>
           <t>4.2%</t>
         </is>
       </c>
-      <c r="D275" t="inlineStr">
-        <is>
-          <t>4.5%</t>
-        </is>
-      </c>
-      <c r="E275" t="inlineStr"/>
+      <c r="E275" t="inlineStr">
+        <is>
+          <t>4.3%</t>
+        </is>
+      </c>
       <c r="F275" t="inlineStr">
         <is>
-          <t>4.3%</t>
+          <t>4%</t>
         </is>
       </c>
       <c r="G275" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="276">
@@ -8531,31 +8539,27 @@
       </c>
       <c r="B276" t="inlineStr">
         <is>
-          <t>S&amp;P/Case-Shiller Home Price YoYNOV</t>
+          <t>House Price IndexNOV</t>
         </is>
       </c>
       <c r="C276" t="inlineStr">
         <is>
-          <t>4.3%</t>
+          <t>433.4</t>
         </is>
       </c>
       <c r="D276" t="inlineStr">
         <is>
-          <t>4.2%</t>
-        </is>
-      </c>
-      <c r="E276" t="inlineStr">
-        <is>
-          <t>4.3%</t>
-        </is>
-      </c>
+          <t>432.3</t>
+        </is>
+      </c>
+      <c r="E276" t="inlineStr"/>
       <c r="F276" t="inlineStr">
         <is>
-          <t>4%</t>
+          <t>433</t>
         </is>
       </c>
       <c r="G276" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="277">
@@ -8566,23 +8570,23 @@
       </c>
       <c r="B277" t="inlineStr">
         <is>
-          <t>House Price IndexNOV</t>
+          <t>House Price Index YoYNOV</t>
         </is>
       </c>
       <c r="C277" t="inlineStr">
         <is>
-          <t>433.4</t>
+          <t>4.2%</t>
         </is>
       </c>
       <c r="D277" t="inlineStr">
         <is>
-          <t>432.3</t>
+          <t>4.5%</t>
         </is>
       </c>
       <c r="E277" t="inlineStr"/>
       <c r="F277" t="inlineStr">
         <is>
-          <t>433</t>
+          <t>4.3%</t>
         </is>
       </c>
       <c r="G277" t="n">
@@ -8597,27 +8601,23 @@
       </c>
       <c r="B278" t="inlineStr">
         <is>
-          <t>House Price Index MoMNOV</t>
+          <t>S&amp;P/Case-Shiller Home Price MoMNOV</t>
         </is>
       </c>
       <c r="C278" t="inlineStr">
         <is>
-          <t>0.3%</t>
+          <t>-0.1%</t>
         </is>
       </c>
       <c r="D278" t="inlineStr">
         <is>
-          <t>0.5%</t>
-        </is>
-      </c>
-      <c r="E278" t="inlineStr">
-        <is>
-          <t>0.2%</t>
-        </is>
-      </c>
+          <t>-0.2%</t>
+        </is>
+      </c>
+      <c r="E278" t="inlineStr"/>
       <c r="F278" t="inlineStr">
         <is>
-          <t>0.3%</t>
+          <t>-0.1%</t>
         </is>
       </c>
       <c r="G278" t="n">
@@ -9201,17 +9201,17 @@
       </c>
       <c r="B298" t="inlineStr">
         <is>
-          <t>EIA Cushing Crude Oil Stocks ChangeJAN/24</t>
+          <t>EIA Gasoline Production ChangeJAN/24</t>
         </is>
       </c>
       <c r="C298" t="inlineStr">
         <is>
-          <t>0.326M</t>
+          <t>-0.044M</t>
         </is>
       </c>
       <c r="D298" t="inlineStr">
         <is>
-          <t>-0.148M</t>
+          <t>-0.043M</t>
         </is>
       </c>
       <c r="E298" t="inlineStr"/>
@@ -9228,27 +9228,23 @@
       </c>
       <c r="B299" t="inlineStr">
         <is>
-          <t>EIA Crude Oil Stocks ChangeJAN/24</t>
+          <t>EIA Crude Oil Imports ChangeJAN/24</t>
         </is>
       </c>
       <c r="C299" t="inlineStr">
         <is>
-          <t>3.463M</t>
+          <t>0.532M</t>
         </is>
       </c>
       <c r="D299" t="inlineStr">
         <is>
-          <t>-1.017M</t>
-        </is>
-      </c>
-      <c r="E299" t="inlineStr">
-        <is>
-          <t>3.2M</t>
-        </is>
-      </c>
+          <t>0.184M</t>
+        </is>
+      </c>
+      <c r="E299" t="inlineStr"/>
       <c r="F299" t="inlineStr"/>
       <c r="G299" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="300">
@@ -9259,24 +9255,20 @@
       </c>
       <c r="B300" t="inlineStr">
         <is>
-          <t>EIA Distillate Stocks ChangeJAN/24</t>
+          <t>EIA Distillate Fuel Production ChangeJAN/24</t>
         </is>
       </c>
       <c r="C300" t="inlineStr">
         <is>
-          <t>-4.994M</t>
+          <t>0.028M</t>
         </is>
       </c>
       <c r="D300" t="inlineStr">
         <is>
-          <t>-3.07M</t>
-        </is>
-      </c>
-      <c r="E300" t="inlineStr">
-        <is>
-          <t>-2.1M</t>
-        </is>
-      </c>
+          <t>-0.473M</t>
+        </is>
+      </c>
+      <c r="E300" t="inlineStr"/>
       <c r="F300" t="inlineStr"/>
       <c r="G300" t="n">
         <v>3</v>
@@ -9290,23 +9282,27 @@
       </c>
       <c r="B301" t="inlineStr">
         <is>
-          <t>EIA Heating Oil Stocks ChangeJAN/24</t>
+          <t>EIA Gasoline Stocks ChangeJAN/24</t>
         </is>
       </c>
       <c r="C301" t="inlineStr">
         <is>
-          <t>0.128M</t>
+          <t>2.957M</t>
         </is>
       </c>
       <c r="D301" t="inlineStr">
         <is>
-          <t>0.068M</t>
-        </is>
-      </c>
-      <c r="E301" t="inlineStr"/>
+          <t>2.332M</t>
+        </is>
+      </c>
+      <c r="E301" t="inlineStr">
+        <is>
+          <t>1.5M</t>
+        </is>
+      </c>
       <c r="F301" t="inlineStr"/>
       <c r="G301" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="302">
@@ -9344,27 +9340,23 @@
       </c>
       <c r="B303" t="inlineStr">
         <is>
-          <t>EIA Gasoline Stocks ChangeJAN/24</t>
+          <t>EIA Heating Oil Stocks ChangeJAN/24</t>
         </is>
       </c>
       <c r="C303" t="inlineStr">
         <is>
-          <t>2.957M</t>
+          <t>0.128M</t>
         </is>
       </c>
       <c r="D303" t="inlineStr">
         <is>
-          <t>2.332M</t>
-        </is>
-      </c>
-      <c r="E303" t="inlineStr">
-        <is>
-          <t>1.5M</t>
-        </is>
-      </c>
+          <t>0.068M</t>
+        </is>
+      </c>
+      <c r="E303" t="inlineStr"/>
       <c r="F303" t="inlineStr"/>
       <c r="G303" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="304">
@@ -9375,20 +9367,24 @@
       </c>
       <c r="B304" t="inlineStr">
         <is>
-          <t>EIA Distillate Fuel Production ChangeJAN/24</t>
+          <t>EIA Distillate Stocks ChangeJAN/24</t>
         </is>
       </c>
       <c r="C304" t="inlineStr">
         <is>
-          <t>0.028M</t>
+          <t>-4.994M</t>
         </is>
       </c>
       <c r="D304" t="inlineStr">
         <is>
-          <t>-0.473M</t>
-        </is>
-      </c>
-      <c r="E304" t="inlineStr"/>
+          <t>-3.07M</t>
+        </is>
+      </c>
+      <c r="E304" t="inlineStr">
+        <is>
+          <t>-2.1M</t>
+        </is>
+      </c>
       <c r="F304" t="inlineStr"/>
       <c r="G304" t="n">
         <v>3</v>
@@ -9402,23 +9398,27 @@
       </c>
       <c r="B305" t="inlineStr">
         <is>
-          <t>EIA Crude Oil Imports ChangeJAN/24</t>
+          <t>EIA Crude Oil Stocks ChangeJAN/24</t>
         </is>
       </c>
       <c r="C305" t="inlineStr">
         <is>
-          <t>0.532M</t>
+          <t>3.463M</t>
         </is>
       </c>
       <c r="D305" t="inlineStr">
         <is>
-          <t>0.184M</t>
-        </is>
-      </c>
-      <c r="E305" t="inlineStr"/>
+          <t>-1.017M</t>
+        </is>
+      </c>
+      <c r="E305" t="inlineStr">
+        <is>
+          <t>3.2M</t>
+        </is>
+      </c>
       <c r="F305" t="inlineStr"/>
       <c r="G305" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="306">
@@ -9429,17 +9429,17 @@
       </c>
       <c r="B306" t="inlineStr">
         <is>
-          <t>EIA Gasoline Production ChangeJAN/24</t>
+          <t>EIA Cushing Crude Oil Stocks ChangeJAN/24</t>
         </is>
       </c>
       <c r="C306" t="inlineStr">
         <is>
-          <t>-0.044M</t>
+          <t>0.326M</t>
         </is>
       </c>
       <c r="D306" t="inlineStr">
         <is>
-          <t>-0.043M</t>
+          <t>-0.148M</t>
         </is>
       </c>
       <c r="E306" t="inlineStr"/>
@@ -9537,31 +9537,31 @@
       </c>
       <c r="B310" t="inlineStr">
         <is>
-          <t>Initial Jobless ClaimsJAN/25</t>
+          <t>GDP Growth Rate QoQ AdvQ4</t>
         </is>
       </c>
       <c r="C310" t="inlineStr">
         <is>
-          <t>207K</t>
+          <t>2.3%</t>
         </is>
       </c>
       <c r="D310" t="inlineStr">
         <is>
-          <t>223K</t>
+          <t>3.1%</t>
         </is>
       </c>
       <c r="E310" t="inlineStr">
         <is>
-          <t>220K</t>
+          <t>2.6%</t>
         </is>
       </c>
       <c r="F310" t="inlineStr">
         <is>
-          <t>228.0K</t>
+          <t>3%</t>
         </is>
       </c>
       <c r="G310" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="311">
@@ -9572,27 +9572,31 @@
       </c>
       <c r="B311" t="inlineStr">
         <is>
-          <t>GDP Sales QoQ AdvQ4</t>
+          <t>GDP Price Index QoQ AdvQ4</t>
         </is>
       </c>
       <c r="C311" t="inlineStr">
         <is>
-          <t>3.2%</t>
+          <t>2.2%</t>
         </is>
       </c>
       <c r="D311" t="inlineStr">
         <is>
-          <t>3.3%</t>
-        </is>
-      </c>
-      <c r="E311" t="inlineStr"/>
+          <t>1.9%</t>
+        </is>
+      </c>
+      <c r="E311" t="inlineStr">
+        <is>
+          <t>2.5%</t>
+        </is>
+      </c>
       <c r="F311" t="inlineStr">
         <is>
-          <t>2.9%</t>
+          <t>2.3%</t>
         </is>
       </c>
       <c r="G311" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="312">
@@ -9603,23 +9607,27 @@
       </c>
       <c r="B312" t="inlineStr">
         <is>
-          <t>Jobless Claims 4-week AverageJAN/25</t>
+          <t>Core PCE Prices QoQ AdvQ4</t>
         </is>
       </c>
       <c r="C312" t="inlineStr">
         <is>
-          <t>212.5K</t>
+          <t>2.5%</t>
         </is>
       </c>
       <c r="D312" t="inlineStr">
         <is>
-          <t>213.5K</t>
-        </is>
-      </c>
-      <c r="E312" t="inlineStr"/>
+          <t>2.2%</t>
+        </is>
+      </c>
+      <c r="E312" t="inlineStr">
+        <is>
+          <t>2.5%</t>
+        </is>
+      </c>
       <c r="F312" t="inlineStr">
         <is>
-          <t>214.0K</t>
+          <t>2.3%</t>
         </is>
       </c>
       <c r="G312" t="n">
@@ -9634,23 +9642,27 @@
       </c>
       <c r="B313" t="inlineStr">
         <is>
-          <t>Real Consumer Spending QoQ AdvQ4</t>
+          <t>Continuing Jobless ClaimsJAN/18</t>
         </is>
       </c>
       <c r="C313" t="inlineStr">
         <is>
-          <t>4.2%</t>
+          <t>1858K</t>
         </is>
       </c>
       <c r="D313" t="inlineStr">
         <is>
-          <t>3.7%</t>
-        </is>
-      </c>
-      <c r="E313" t="inlineStr"/>
+          <t>1900K</t>
+        </is>
+      </c>
+      <c r="E313" t="inlineStr">
+        <is>
+          <t>1890K</t>
+        </is>
+      </c>
       <c r="F313" t="inlineStr">
         <is>
-          <t>2.9%</t>
+          <t>1885.0K</t>
         </is>
       </c>
       <c r="G313" t="n">
@@ -9665,27 +9677,23 @@
       </c>
       <c r="B314" t="inlineStr">
         <is>
-          <t>Continuing Jobless ClaimsJAN/18</t>
+          <t>PCE Prices QoQ AdvQ4</t>
         </is>
       </c>
       <c r="C314" t="inlineStr">
         <is>
-          <t>1858K</t>
+          <t>2.3%</t>
         </is>
       </c>
       <c r="D314" t="inlineStr">
         <is>
-          <t>1900K</t>
-        </is>
-      </c>
-      <c r="E314" t="inlineStr">
-        <is>
-          <t>1890K</t>
-        </is>
-      </c>
+          <t>1.5%</t>
+        </is>
+      </c>
+      <c r="E314" t="inlineStr"/>
       <c r="F314" t="inlineStr">
         <is>
-          <t>1885.0K</t>
+          <t>1.1%</t>
         </is>
       </c>
       <c r="G314" t="n">
@@ -9700,23 +9708,23 @@
       </c>
       <c r="B315" t="inlineStr">
         <is>
-          <t>PCE Prices QoQ AdvQ4</t>
+          <t>Jobless Claims 4-week AverageJAN/25</t>
         </is>
       </c>
       <c r="C315" t="inlineStr">
         <is>
-          <t>2.3%</t>
+          <t>212.5K</t>
         </is>
       </c>
       <c r="D315" t="inlineStr">
         <is>
-          <t>1.5%</t>
+          <t>213.5K</t>
         </is>
       </c>
       <c r="E315" t="inlineStr"/>
       <c r="F315" t="inlineStr">
         <is>
-          <t>1.1%</t>
+          <t>214.0K</t>
         </is>
       </c>
       <c r="G315" t="n">
@@ -9731,27 +9739,23 @@
       </c>
       <c r="B316" t="inlineStr">
         <is>
-          <t>Core PCE Prices QoQ AdvQ4</t>
+          <t>GDP Sales QoQ AdvQ4</t>
         </is>
       </c>
       <c r="C316" t="inlineStr">
         <is>
-          <t>2.5%</t>
+          <t>3.2%</t>
         </is>
       </c>
       <c r="D316" t="inlineStr">
         <is>
-          <t>2.2%</t>
-        </is>
-      </c>
-      <c r="E316" t="inlineStr">
-        <is>
-          <t>2.5%</t>
-        </is>
-      </c>
+          <t>3.3%</t>
+        </is>
+      </c>
+      <c r="E316" t="inlineStr"/>
       <c r="F316" t="inlineStr">
         <is>
-          <t>2.3%</t>
+          <t>2.9%</t>
         </is>
       </c>
       <c r="G316" t="n">
@@ -9766,27 +9770,27 @@
       </c>
       <c r="B317" t="inlineStr">
         <is>
-          <t>GDP Price Index QoQ AdvQ4</t>
+          <t>Initial Jobless ClaimsJAN/25</t>
         </is>
       </c>
       <c r="C317" t="inlineStr">
         <is>
-          <t>2.2%</t>
+          <t>207K</t>
         </is>
       </c>
       <c r="D317" t="inlineStr">
         <is>
-          <t>1.9%</t>
+          <t>223K</t>
         </is>
       </c>
       <c r="E317" t="inlineStr">
         <is>
-          <t>2.5%</t>
+          <t>220K</t>
         </is>
       </c>
       <c r="F317" t="inlineStr">
         <is>
-          <t>2.3%</t>
+          <t>228.0K</t>
         </is>
       </c>
       <c r="G317" t="n">
@@ -9801,31 +9805,27 @@
       </c>
       <c r="B318" t="inlineStr">
         <is>
-          <t>GDP Growth Rate QoQ AdvQ4</t>
+          <t>Real Consumer Spending QoQ AdvQ4</t>
         </is>
       </c>
       <c r="C318" t="inlineStr">
         <is>
-          <t>2.3%</t>
+          <t>4.2%</t>
         </is>
       </c>
       <c r="D318" t="inlineStr">
         <is>
-          <t>3.1%</t>
-        </is>
-      </c>
-      <c r="E318" t="inlineStr">
-        <is>
-          <t>2.6%</t>
-        </is>
-      </c>
+          <t>3.7%</t>
+        </is>
+      </c>
+      <c r="E318" t="inlineStr"/>
       <c r="F318" t="inlineStr">
         <is>
-          <t>3%</t>
+          <t>2.9%</t>
         </is>
       </c>
       <c r="G318" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="319">
@@ -10068,31 +10068,31 @@
       </c>
       <c r="B327" t="inlineStr">
         <is>
-          <t>Core PCE Price Index YoYDEC</t>
+          <t>Personal Spending MoMDEC</t>
         </is>
       </c>
       <c r="C327" t="inlineStr">
         <is>
-          <t>2.8%</t>
+          <t>0.7%</t>
         </is>
       </c>
       <c r="D327" t="inlineStr">
         <is>
-          <t>2.8%</t>
+          <t>0.6%</t>
         </is>
       </c>
       <c r="E327" t="inlineStr">
         <is>
-          <t>2.8%</t>
+          <t>0.5%</t>
         </is>
       </c>
       <c r="F327" t="inlineStr">
         <is>
-          <t>2.8%</t>
+          <t>0.5%</t>
         </is>
       </c>
       <c r="G327" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="328">
@@ -10103,12 +10103,12 @@
       </c>
       <c r="B328" t="inlineStr">
         <is>
-          <t>Employment Cost Index QoQQ4</t>
+          <t>Employment Cost - Benefits QoQQ4</t>
         </is>
       </c>
       <c r="C328" t="inlineStr">
         <is>
-          <t>0.9%</t>
+          <t>0.8%</t>
         </is>
       </c>
       <c r="D328" t="inlineStr">
@@ -10116,11 +10116,7 @@
           <t>0.8%</t>
         </is>
       </c>
-      <c r="E328" t="inlineStr">
-        <is>
-          <t>0.9%</t>
-        </is>
-      </c>
+      <c r="E328" t="inlineStr"/>
       <c r="F328" t="inlineStr">
         <is>
           <t>0.7%</t>
@@ -10138,12 +10134,12 @@
       </c>
       <c r="B329" t="inlineStr">
         <is>
-          <t>PCE Price Index MoMDEC</t>
+          <t>Core PCE Price Index MoMDEC</t>
         </is>
       </c>
       <c r="C329" t="inlineStr">
         <is>
-          <t>0.3%</t>
+          <t>0.2%</t>
         </is>
       </c>
       <c r="D329" t="inlineStr">
@@ -10153,16 +10149,16 @@
       </c>
       <c r="E329" t="inlineStr">
         <is>
-          <t>0.3%</t>
+          <t>0.2%</t>
         </is>
       </c>
       <c r="F329" t="inlineStr">
         <is>
-          <t>0.3%</t>
+          <t>0.2%</t>
         </is>
       </c>
       <c r="G329" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="330">
@@ -10173,29 +10169,13 @@
       </c>
       <c r="B330" t="inlineStr">
         <is>
-          <t>PCE Price Index YoYDEC</t>
-        </is>
-      </c>
-      <c r="C330" t="inlineStr">
-        <is>
-          <t>2.6%</t>
-        </is>
-      </c>
-      <c r="D330" t="inlineStr">
-        <is>
-          <t>2.4%</t>
-        </is>
-      </c>
-      <c r="E330" t="inlineStr">
-        <is>
-          <t>2.6%</t>
-        </is>
-      </c>
-      <c r="F330" t="inlineStr">
-        <is>
-          <t>2.6%</t>
-        </is>
-      </c>
+          <t>Fed Bowman Speech</t>
+        </is>
+      </c>
+      <c r="C330" t="inlineStr"/>
+      <c r="D330" t="inlineStr"/>
+      <c r="E330" t="inlineStr"/>
+      <c r="F330" t="inlineStr"/>
       <c r="G330" t="n">
         <v>2</v>
       </c>
@@ -10208,27 +10188,31 @@
       </c>
       <c r="B331" t="inlineStr">
         <is>
-          <t>Employment Cost - Wages QoQQ4</t>
+          <t>Personal Income MoMDEC</t>
         </is>
       </c>
       <c r="C331" t="inlineStr">
         <is>
-          <t>0.9%</t>
+          <t>0.4%</t>
         </is>
       </c>
       <c r="D331" t="inlineStr">
         <is>
-          <t>0.8%</t>
-        </is>
-      </c>
-      <c r="E331" t="inlineStr"/>
+          <t>0.3%</t>
+        </is>
+      </c>
+      <c r="E331" t="inlineStr">
+        <is>
+          <t>0.4%</t>
+        </is>
+      </c>
       <c r="F331" t="inlineStr">
         <is>
-          <t>0.7%</t>
+          <t>0.3%</t>
         </is>
       </c>
       <c r="G331" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="332">
@@ -10239,13 +10223,29 @@
       </c>
       <c r="B332" t="inlineStr">
         <is>
-          <t>Fed Bowman Speech</t>
-        </is>
-      </c>
-      <c r="C332" t="inlineStr"/>
-      <c r="D332" t="inlineStr"/>
-      <c r="E332" t="inlineStr"/>
-      <c r="F332" t="inlineStr"/>
+          <t>PCE Price Index YoYDEC</t>
+        </is>
+      </c>
+      <c r="C332" t="inlineStr">
+        <is>
+          <t>2.6%</t>
+        </is>
+      </c>
+      <c r="D332" t="inlineStr">
+        <is>
+          <t>2.4%</t>
+        </is>
+      </c>
+      <c r="E332" t="inlineStr">
+        <is>
+          <t>2.6%</t>
+        </is>
+      </c>
+      <c r="F332" t="inlineStr">
+        <is>
+          <t>2.6%</t>
+        </is>
+      </c>
       <c r="G332" t="n">
         <v>2</v>
       </c>
@@ -10258,23 +10258,27 @@
       </c>
       <c r="B333" t="inlineStr">
         <is>
-          <t>Employment Cost - Benefits QoQQ4</t>
+          <t>PCE Price Index MoMDEC</t>
         </is>
       </c>
       <c r="C333" t="inlineStr">
         <is>
-          <t>0.8%</t>
+          <t>0.3%</t>
         </is>
       </c>
       <c r="D333" t="inlineStr">
         <is>
-          <t>0.8%</t>
-        </is>
-      </c>
-      <c r="E333" t="inlineStr"/>
+          <t>0.1%</t>
+        </is>
+      </c>
+      <c r="E333" t="inlineStr">
+        <is>
+          <t>0.3%</t>
+        </is>
+      </c>
       <c r="F333" t="inlineStr">
         <is>
-          <t>0.7%</t>
+          <t>0.3%</t>
         </is>
       </c>
       <c r="G333" t="n">
@@ -10289,31 +10293,31 @@
       </c>
       <c r="B334" t="inlineStr">
         <is>
-          <t>Personal Spending MoMDEC</t>
+          <t>Employment Cost Index QoQQ4</t>
         </is>
       </c>
       <c r="C334" t="inlineStr">
         <is>
+          <t>0.9%</t>
+        </is>
+      </c>
+      <c r="D334" t="inlineStr">
+        <is>
+          <t>0.8%</t>
+        </is>
+      </c>
+      <c r="E334" t="inlineStr">
+        <is>
+          <t>0.9%</t>
+        </is>
+      </c>
+      <c r="F334" t="inlineStr">
+        <is>
           <t>0.7%</t>
         </is>
       </c>
-      <c r="D334" t="inlineStr">
-        <is>
-          <t>0.6%</t>
-        </is>
-      </c>
-      <c r="E334" t="inlineStr">
-        <is>
-          <t>0.5%</t>
-        </is>
-      </c>
-      <c r="F334" t="inlineStr">
-        <is>
-          <t>0.5%</t>
-        </is>
-      </c>
       <c r="G334" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="335">
@@ -10324,31 +10328,31 @@
       </c>
       <c r="B335" t="inlineStr">
         <is>
-          <t>Core PCE Price Index MoMDEC</t>
+          <t>Core PCE Price Index YoYDEC</t>
         </is>
       </c>
       <c r="C335" t="inlineStr">
         <is>
-          <t>0.2%</t>
+          <t>2.8%</t>
         </is>
       </c>
       <c r="D335" t="inlineStr">
         <is>
-          <t>0.1%</t>
+          <t>2.8%</t>
         </is>
       </c>
       <c r="E335" t="inlineStr">
         <is>
-          <t>0.2%</t>
+          <t>2.8%</t>
         </is>
       </c>
       <c r="F335" t="inlineStr">
         <is>
-          <t>0.2%</t>
+          <t>2.8%</t>
         </is>
       </c>
       <c r="G335" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="336">
@@ -10359,31 +10363,27 @@
       </c>
       <c r="B336" t="inlineStr">
         <is>
-          <t>Personal Income MoMDEC</t>
+          <t>Employment Cost - Wages QoQQ4</t>
         </is>
       </c>
       <c r="C336" t="inlineStr">
         <is>
-          <t>0.4%</t>
+          <t>0.9%</t>
         </is>
       </c>
       <c r="D336" t="inlineStr">
         <is>
-          <t>0.3%</t>
-        </is>
-      </c>
-      <c r="E336" t="inlineStr">
-        <is>
-          <t>0.4%</t>
-        </is>
-      </c>
+          <t>0.8%</t>
+        </is>
+      </c>
+      <c r="E336" t="inlineStr"/>
       <c r="F336" t="inlineStr">
         <is>
-          <t>0.3%</t>
+          <t>0.7%</t>
         </is>
       </c>
       <c r="G336" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="337">
@@ -10522,27 +10522,31 @@
       </c>
       <c r="B341" t="inlineStr">
         <is>
-          <t>ISM Manufacturing EmploymentJAN</t>
+          <t>Construction Spending MoMDEC</t>
         </is>
       </c>
       <c r="C341" t="inlineStr">
         <is>
-          <t>50.3</t>
+          <t>0.5%</t>
         </is>
       </c>
       <c r="D341" t="inlineStr">
         <is>
-          <t>45.4</t>
-        </is>
-      </c>
-      <c r="E341" t="inlineStr"/>
+          <t>0.2%</t>
+        </is>
+      </c>
+      <c r="E341" t="inlineStr">
+        <is>
+          <t>0.2%</t>
+        </is>
+      </c>
       <c r="F341" t="inlineStr">
         <is>
-          <t>47</t>
+          <t>0.3%</t>
         </is>
       </c>
       <c r="G341" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="342">
@@ -10553,31 +10557,27 @@
       </c>
       <c r="B342" t="inlineStr">
         <is>
-          <t>ISM Manufacturing PMIJAN</t>
+          <t>ISM Manufacturing New OrdersJAN</t>
         </is>
       </c>
       <c r="C342" t="inlineStr">
         <is>
-          <t>50.9</t>
+          <t>55.1</t>
         </is>
       </c>
       <c r="D342" t="inlineStr">
         <is>
-          <t>49.2</t>
-        </is>
-      </c>
-      <c r="E342" t="inlineStr">
-        <is>
-          <t>49.8</t>
-        </is>
-      </c>
+          <t>52.1</t>
+        </is>
+      </c>
+      <c r="E342" t="inlineStr"/>
       <c r="F342" t="inlineStr">
         <is>
-          <t>49.8</t>
+          <t>52.8</t>
         </is>
       </c>
       <c r="G342" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="343">
@@ -10588,23 +10588,27 @@
       </c>
       <c r="B343" t="inlineStr">
         <is>
-          <t>ISM Manufacturing New OrdersJAN</t>
+          <t>ISM Manufacturing PricesJAN</t>
         </is>
       </c>
       <c r="C343" t="inlineStr">
         <is>
-          <t>55.1</t>
+          <t>54.9</t>
         </is>
       </c>
       <c r="D343" t="inlineStr">
         <is>
-          <t>52.1</t>
-        </is>
-      </c>
-      <c r="E343" t="inlineStr"/>
+          <t>52.5</t>
+        </is>
+      </c>
+      <c r="E343" t="inlineStr">
+        <is>
+          <t>52.6</t>
+        </is>
+      </c>
       <c r="F343" t="inlineStr">
         <is>
-          <t>52.8</t>
+          <t>53</t>
         </is>
       </c>
       <c r="G343" t="n">
@@ -10619,31 +10623,27 @@
       </c>
       <c r="B344" t="inlineStr">
         <is>
-          <t>ISM Manufacturing PricesJAN</t>
+          <t>ISM Manufacturing EmploymentJAN</t>
         </is>
       </c>
       <c r="C344" t="inlineStr">
         <is>
-          <t>54.9</t>
+          <t>50.3</t>
         </is>
       </c>
       <c r="D344" t="inlineStr">
         <is>
-          <t>52.5</t>
-        </is>
-      </c>
-      <c r="E344" t="inlineStr">
-        <is>
-          <t>52.6</t>
-        </is>
-      </c>
+          <t>45.4</t>
+        </is>
+      </c>
+      <c r="E344" t="inlineStr"/>
       <c r="F344" t="inlineStr">
         <is>
-          <t>53</t>
+          <t>47</t>
         </is>
       </c>
       <c r="G344" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="345">
@@ -10654,31 +10654,31 @@
       </c>
       <c r="B345" t="inlineStr">
         <is>
-          <t>Construction Spending MoMDEC</t>
+          <t>ISM Manufacturing PMIJAN</t>
         </is>
       </c>
       <c r="C345" t="inlineStr">
         <is>
-          <t>0.5%</t>
+          <t>50.9</t>
         </is>
       </c>
       <c r="D345" t="inlineStr">
         <is>
-          <t>0.2%</t>
+          <t>49.2</t>
         </is>
       </c>
       <c r="E345" t="inlineStr">
         <is>
-          <t>0.2%</t>
+          <t>49.8</t>
         </is>
       </c>
       <c r="F345" t="inlineStr">
         <is>
-          <t>0.3%</t>
+          <t>49.8</t>
         </is>
       </c>
       <c r="G345" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="346">
@@ -10873,31 +10873,31 @@
       </c>
       <c r="B354" t="inlineStr">
         <is>
-          <t>Factory Orders MoMDEC</t>
+          <t>JOLTs Job OpeningsDEC</t>
         </is>
       </c>
       <c r="C354" t="inlineStr">
         <is>
-          <t>-0.9%</t>
+          <t>7.6M</t>
         </is>
       </c>
       <c r="D354" t="inlineStr">
         <is>
-          <t>-0.8%</t>
+          <t>8.156M</t>
         </is>
       </c>
       <c r="E354" t="inlineStr">
         <is>
-          <t>-0.7%</t>
+          <t>8M</t>
         </is>
       </c>
       <c r="F354" t="inlineStr">
         <is>
-          <t>-0.7%</t>
+          <t>7.8M</t>
         </is>
       </c>
       <c r="G354" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="355">
@@ -10908,27 +10908,31 @@
       </c>
       <c r="B355" t="inlineStr">
         <is>
-          <t>JOLTs Job QuitsDEC</t>
+          <t>Factory Orders MoMDEC</t>
         </is>
       </c>
       <c r="C355" t="inlineStr">
         <is>
-          <t>3.197M</t>
+          <t>-0.9%</t>
         </is>
       </c>
       <c r="D355" t="inlineStr">
         <is>
-          <t>3.130M</t>
-        </is>
-      </c>
-      <c r="E355" t="inlineStr"/>
+          <t>-0.8%</t>
+        </is>
+      </c>
+      <c r="E355" t="inlineStr">
+        <is>
+          <t>-0.7%</t>
+        </is>
+      </c>
       <c r="F355" t="inlineStr">
         <is>
-          <t>3.1M</t>
+          <t>-0.7%</t>
         </is>
       </c>
       <c r="G355" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="356">
@@ -10939,31 +10943,27 @@
       </c>
       <c r="B356" t="inlineStr">
         <is>
-          <t>JOLTs Job OpeningsDEC</t>
+          <t>JOLTs Job QuitsDEC</t>
         </is>
       </c>
       <c r="C356" t="inlineStr">
         <is>
-          <t>7.6M</t>
+          <t>3.197M</t>
         </is>
       </c>
       <c r="D356" t="inlineStr">
         <is>
-          <t>8.156M</t>
-        </is>
-      </c>
-      <c r="E356" t="inlineStr">
-        <is>
-          <t>8M</t>
-        </is>
-      </c>
+          <t>3.130M</t>
+        </is>
+      </c>
+      <c r="E356" t="inlineStr"/>
       <c r="F356" t="inlineStr">
         <is>
-          <t>7.8M</t>
+          <t>3.1M</t>
         </is>
       </c>
       <c r="G356" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="357">
@@ -11325,27 +11325,23 @@
       </c>
       <c r="B370" t="inlineStr">
         <is>
-          <t>Balance of TradeDEC</t>
+          <t>ExportsDEC</t>
         </is>
       </c>
       <c r="C370" t="inlineStr">
         <is>
-          <t>$-98.4B</t>
+          <t>$266.5B</t>
         </is>
       </c>
       <c r="D370" t="inlineStr">
         <is>
-          <t>$-78.9B</t>
-        </is>
-      </c>
-      <c r="E370" t="inlineStr">
-        <is>
-          <t>$-96.6B</t>
-        </is>
-      </c>
+          <t>$273.6B</t>
+        </is>
+      </c>
+      <c r="E370" t="inlineStr"/>
       <c r="F370" t="inlineStr">
         <is>
-          <t>$ -93.0B</t>
+          <t>$ 262B</t>
         </is>
       </c>
       <c r="G370" t="n">
@@ -11360,15 +11356,27 @@
       </c>
       <c r="B371" t="inlineStr">
         <is>
-          <t>Treasury Refunding Announcement</t>
-        </is>
-      </c>
-      <c r="C371" t="inlineStr"/>
-      <c r="D371" t="inlineStr"/>
+          <t>ImportsDEC</t>
+        </is>
+      </c>
+      <c r="C371" t="inlineStr">
+        <is>
+          <t>$364.9B</t>
+        </is>
+      </c>
+      <c r="D371" t="inlineStr">
+        <is>
+          <t>$352.5B</t>
+        </is>
+      </c>
       <c r="E371" t="inlineStr"/>
-      <c r="F371" t="inlineStr"/>
+      <c r="F371" t="inlineStr">
+        <is>
+          <t>$ 355.0B</t>
+        </is>
+      </c>
       <c r="G371" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="372">
@@ -11379,23 +11387,27 @@
       </c>
       <c r="B372" t="inlineStr">
         <is>
-          <t>ImportsDEC</t>
+          <t>Balance of TradeDEC</t>
         </is>
       </c>
       <c r="C372" t="inlineStr">
         <is>
-          <t>$364.9B</t>
+          <t>$-98.4B</t>
         </is>
       </c>
       <c r="D372" t="inlineStr">
         <is>
-          <t>$352.5B</t>
-        </is>
-      </c>
-      <c r="E372" t="inlineStr"/>
+          <t>$-78.9B</t>
+        </is>
+      </c>
+      <c r="E372" t="inlineStr">
+        <is>
+          <t>$-96.6B</t>
+        </is>
+      </c>
       <c r="F372" t="inlineStr">
         <is>
-          <t>$ 355.0B</t>
+          <t>$ -93.0B</t>
         </is>
       </c>
       <c r="G372" t="n">
@@ -11410,27 +11422,15 @@
       </c>
       <c r="B373" t="inlineStr">
         <is>
-          <t>ExportsDEC</t>
-        </is>
-      </c>
-      <c r="C373" t="inlineStr">
-        <is>
-          <t>$266.5B</t>
-        </is>
-      </c>
-      <c r="D373" t="inlineStr">
-        <is>
-          <t>$273.6B</t>
-        </is>
-      </c>
+          <t>Treasury Refunding Announcement</t>
+        </is>
+      </c>
+      <c r="C373" t="inlineStr"/>
+      <c r="D373" t="inlineStr"/>
       <c r="E373" t="inlineStr"/>
-      <c r="F373" t="inlineStr">
-        <is>
-          <t>$ 262B</t>
-        </is>
-      </c>
+      <c r="F373" t="inlineStr"/>
       <c r="G373" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="374">
@@ -11689,17 +11689,17 @@
       </c>
       <c r="B382" t="inlineStr">
         <is>
-          <t>EIA Refinery Crude Runs ChangeJAN/31</t>
+          <t>EIA Crude Oil Imports ChangeJAN/31</t>
         </is>
       </c>
       <c r="C382" t="inlineStr">
         <is>
-          <t>0.16M</t>
+          <t>-0.178M</t>
         </is>
       </c>
       <c r="D382" t="inlineStr">
         <is>
-          <t>-0.333M</t>
+          <t>0.532M</t>
         </is>
       </c>
       <c r="E382" t="inlineStr"/>
@@ -11716,24 +11716,20 @@
       </c>
       <c r="B383" t="inlineStr">
         <is>
-          <t>EIA Distillate Stocks ChangeJAN/31</t>
+          <t>EIA Heating Oil Stocks ChangeJAN/31</t>
         </is>
       </c>
       <c r="C383" t="inlineStr">
         <is>
-          <t>-5.471M</t>
+          <t>0.373M</t>
         </is>
       </c>
       <c r="D383" t="inlineStr">
         <is>
-          <t>-4.994M</t>
-        </is>
-      </c>
-      <c r="E383" t="inlineStr">
-        <is>
-          <t>-1.5M</t>
-        </is>
-      </c>
+          <t>0.128M</t>
+        </is>
+      </c>
+      <c r="E383" t="inlineStr"/>
       <c r="F383" t="inlineStr"/>
       <c r="G383" t="n">
         <v>3</v>
@@ -11747,17 +11743,17 @@
       </c>
       <c r="B384" t="inlineStr">
         <is>
-          <t>EIA Distillate Fuel Production ChangeJAN/31</t>
+          <t>EIA Gasoline Production ChangeJAN/31</t>
         </is>
       </c>
       <c r="C384" t="inlineStr">
         <is>
-          <t>-0.186M</t>
+          <t>-0.027M</t>
         </is>
       </c>
       <c r="D384" t="inlineStr">
         <is>
-          <t>0.028M</t>
+          <t>-0.044M</t>
         </is>
       </c>
       <c r="E384" t="inlineStr"/>
@@ -11774,22 +11770,22 @@
       </c>
       <c r="B385" t="inlineStr">
         <is>
-          <t>EIA Gasoline Stocks ChangeJAN/31</t>
+          <t>EIA Crude Oil Stocks ChangeJAN/31</t>
         </is>
       </c>
       <c r="C385" t="inlineStr">
         <is>
-          <t>2.233M</t>
+          <t>8.664M</t>
         </is>
       </c>
       <c r="D385" t="inlineStr">
         <is>
-          <t>2.957M</t>
+          <t>3.463M</t>
         </is>
       </c>
       <c r="E385" t="inlineStr">
         <is>
-          <t>1.2M</t>
+          <t>2.6M</t>
         </is>
       </c>
       <c r="F385" t="inlineStr"/>
@@ -11805,27 +11801,23 @@
       </c>
       <c r="B386" t="inlineStr">
         <is>
-          <t>EIA Crude Oil Stocks ChangeJAN/31</t>
+          <t>EIA Cushing Crude Oil Stocks ChangeJAN/31</t>
         </is>
       </c>
       <c r="C386" t="inlineStr">
         <is>
-          <t>8.664M</t>
+          <t>-0.034M</t>
         </is>
       </c>
       <c r="D386" t="inlineStr">
         <is>
-          <t>3.463M</t>
-        </is>
-      </c>
-      <c r="E386" t="inlineStr">
-        <is>
-          <t>2.6M</t>
-        </is>
-      </c>
+          <t>0.326M</t>
+        </is>
+      </c>
+      <c r="E386" t="inlineStr"/>
       <c r="F386" t="inlineStr"/>
       <c r="G386" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="387">
@@ -11836,17 +11828,17 @@
       </c>
       <c r="B387" t="inlineStr">
         <is>
-          <t>EIA Crude Oil Imports ChangeJAN/31</t>
+          <t>EIA Distillate Fuel Production ChangeJAN/31</t>
         </is>
       </c>
       <c r="C387" t="inlineStr">
         <is>
-          <t>-0.178M</t>
+          <t>-0.186M</t>
         </is>
       </c>
       <c r="D387" t="inlineStr">
         <is>
-          <t>0.532M</t>
+          <t>0.028M</t>
         </is>
       </c>
       <c r="E387" t="inlineStr"/>
@@ -11863,20 +11855,24 @@
       </c>
       <c r="B388" t="inlineStr">
         <is>
-          <t>EIA Gasoline Production ChangeJAN/31</t>
+          <t>EIA Distillate Stocks ChangeJAN/31</t>
         </is>
       </c>
       <c r="C388" t="inlineStr">
         <is>
-          <t>-0.027M</t>
+          <t>-5.471M</t>
         </is>
       </c>
       <c r="D388" t="inlineStr">
         <is>
-          <t>-0.044M</t>
-        </is>
-      </c>
-      <c r="E388" t="inlineStr"/>
+          <t>-4.994M</t>
+        </is>
+      </c>
+      <c r="E388" t="inlineStr">
+        <is>
+          <t>-1.5M</t>
+        </is>
+      </c>
       <c r="F388" t="inlineStr"/>
       <c r="G388" t="n">
         <v>3</v>
@@ -11890,17 +11886,17 @@
       </c>
       <c r="B389" t="inlineStr">
         <is>
-          <t>EIA Cushing Crude Oil Stocks ChangeJAN/31</t>
+          <t>EIA Refinery Crude Runs ChangeJAN/31</t>
         </is>
       </c>
       <c r="C389" t="inlineStr">
         <is>
-          <t>-0.034M</t>
+          <t>0.16M</t>
         </is>
       </c>
       <c r="D389" t="inlineStr">
         <is>
-          <t>0.326M</t>
+          <t>-0.333M</t>
         </is>
       </c>
       <c r="E389" t="inlineStr"/>
@@ -11917,23 +11913,27 @@
       </c>
       <c r="B390" t="inlineStr">
         <is>
-          <t>EIA Heating Oil Stocks ChangeJAN/31</t>
+          <t>EIA Gasoline Stocks ChangeJAN/31</t>
         </is>
       </c>
       <c r="C390" t="inlineStr">
         <is>
-          <t>0.373M</t>
+          <t>2.233M</t>
         </is>
       </c>
       <c r="D390" t="inlineStr">
         <is>
-          <t>0.128M</t>
-        </is>
-      </c>
-      <c r="E390" t="inlineStr"/>
+          <t>2.957M</t>
+        </is>
+      </c>
+      <c r="E390" t="inlineStr">
+        <is>
+          <t>1.2M</t>
+        </is>
+      </c>
       <c r="F390" t="inlineStr"/>
       <c r="G390" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="391">
@@ -12040,31 +12040,31 @@
       </c>
       <c r="B395" t="inlineStr">
         <is>
-          <t>Continuing Jobless ClaimsJAN/25</t>
+          <t>Unit Labour Costs QoQ PrelQ4</t>
         </is>
       </c>
       <c r="C395" t="inlineStr">
         <is>
-          <t>1886K</t>
+          <t>3%</t>
         </is>
       </c>
       <c r="D395" t="inlineStr">
         <is>
-          <t>1850K</t>
+          <t>0.5%</t>
         </is>
       </c>
       <c r="E395" t="inlineStr">
         <is>
-          <t>1870K</t>
+          <t>3.4%</t>
         </is>
       </c>
       <c r="F395" t="inlineStr">
         <is>
-          <t>1855.0K</t>
+          <t>3%</t>
         </is>
       </c>
       <c r="G395" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="396">
@@ -12075,27 +12075,27 @@
       </c>
       <c r="B396" t="inlineStr">
         <is>
-          <t>Initial Jobless ClaimsFEB/01</t>
+          <t>Nonfarm Productivity QoQ PrelQ4</t>
         </is>
       </c>
       <c r="C396" t="inlineStr">
         <is>
-          <t>219K</t>
+          <t>1.2%</t>
         </is>
       </c>
       <c r="D396" t="inlineStr">
         <is>
-          <t>208K</t>
+          <t>2.3%</t>
         </is>
       </c>
       <c r="E396" t="inlineStr">
         <is>
-          <t>213K</t>
+          <t>1.4%</t>
         </is>
       </c>
       <c r="F396" t="inlineStr">
         <is>
-          <t>215.0K</t>
+          <t>1.9%</t>
         </is>
       </c>
       <c r="G396" t="n">
@@ -12110,31 +12110,27 @@
       </c>
       <c r="B397" t="inlineStr">
         <is>
-          <t>Nonfarm Productivity QoQ PrelQ4</t>
+          <t>Jobless Claims 4-week AverageFEB/01</t>
         </is>
       </c>
       <c r="C397" t="inlineStr">
         <is>
-          <t>1.2%</t>
+          <t>216.75K</t>
         </is>
       </c>
       <c r="D397" t="inlineStr">
         <is>
-          <t>2.3%</t>
-        </is>
-      </c>
-      <c r="E397" t="inlineStr">
-        <is>
-          <t>1.4%</t>
-        </is>
-      </c>
+          <t>212.75K</t>
+        </is>
+      </c>
+      <c r="E397" t="inlineStr"/>
       <c r="F397" t="inlineStr">
         <is>
-          <t>1.9%</t>
+          <t>215.5K</t>
         </is>
       </c>
       <c r="G397" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="398">
@@ -12145,31 +12141,31 @@
       </c>
       <c r="B398" t="inlineStr">
         <is>
-          <t>Unit Labour Costs QoQ PrelQ4</t>
+          <t>Continuing Jobless ClaimsJAN/25</t>
         </is>
       </c>
       <c r="C398" t="inlineStr">
         <is>
-          <t>3%</t>
+          <t>1886K</t>
         </is>
       </c>
       <c r="D398" t="inlineStr">
         <is>
-          <t>0.5%</t>
+          <t>1850K</t>
         </is>
       </c>
       <c r="E398" t="inlineStr">
         <is>
-          <t>3.4%</t>
+          <t>1870K</t>
         </is>
       </c>
       <c r="F398" t="inlineStr">
         <is>
-          <t>3%</t>
+          <t>1855.0K</t>
         </is>
       </c>
       <c r="G398" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="399">
@@ -12180,27 +12176,31 @@
       </c>
       <c r="B399" t="inlineStr">
         <is>
-          <t>Jobless Claims 4-week AverageFEB/01</t>
+          <t>Initial Jobless ClaimsFEB/01</t>
         </is>
       </c>
       <c r="C399" t="inlineStr">
         <is>
-          <t>216.75K</t>
+          <t>219K</t>
         </is>
       </c>
       <c r="D399" t="inlineStr">
         <is>
-          <t>212.75K</t>
-        </is>
-      </c>
-      <c r="E399" t="inlineStr"/>
+          <t>208K</t>
+        </is>
+      </c>
+      <c r="E399" t="inlineStr">
+        <is>
+          <t>213K</t>
+        </is>
+      </c>
       <c r="F399" t="inlineStr">
         <is>
-          <t>215.5K</t>
+          <t>215.0K</t>
         </is>
       </c>
       <c r="G399" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="400">
@@ -12442,31 +12442,31 @@
       </c>
       <c r="B409" t="inlineStr">
         <is>
-          <t>Nonfarm Payrolls PrivateJAN</t>
+          <t>Non Farm PayrollsJAN</t>
         </is>
       </c>
       <c r="C409" t="inlineStr">
         <is>
-          <t>111K</t>
+          <t>143K</t>
         </is>
       </c>
       <c r="D409" t="inlineStr">
         <is>
-          <t>273K</t>
+          <t>307K</t>
         </is>
       </c>
       <c r="E409" t="inlineStr">
         <is>
-          <t>141K</t>
+          <t>170K</t>
         </is>
       </c>
       <c r="F409" t="inlineStr">
         <is>
-          <t>180K</t>
+          <t>205K</t>
         </is>
       </c>
       <c r="G409" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="410">
@@ -12477,27 +12477,31 @@
       </c>
       <c r="B410" t="inlineStr">
         <is>
-          <t>Participation RateJAN</t>
+          <t>Average Weekly HoursJAN</t>
         </is>
       </c>
       <c r="C410" t="inlineStr">
         <is>
-          <t>62.6%</t>
+          <t>34.1</t>
         </is>
       </c>
       <c r="D410" t="inlineStr">
         <is>
-          <t>62.5%</t>
-        </is>
-      </c>
-      <c r="E410" t="inlineStr"/>
+          <t>34.2</t>
+        </is>
+      </c>
+      <c r="E410" t="inlineStr">
+        <is>
+          <t>34.3</t>
+        </is>
+      </c>
       <c r="F410" t="inlineStr">
         <is>
-          <t>62.5%</t>
+          <t>34.3</t>
         </is>
       </c>
       <c r="G410" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="411">
@@ -12508,27 +12512,31 @@
       </c>
       <c r="B411" t="inlineStr">
         <is>
-          <t>Government PayrollsJAN</t>
+          <t>Average Hourly Earnings MoMJAN</t>
         </is>
       </c>
       <c r="C411" t="inlineStr">
         <is>
-          <t>32K</t>
+          <t>0.5%</t>
         </is>
       </c>
       <c r="D411" t="inlineStr">
         <is>
-          <t>34K</t>
-        </is>
-      </c>
-      <c r="E411" t="inlineStr"/>
+          <t>0.3%</t>
+        </is>
+      </c>
+      <c r="E411" t="inlineStr">
+        <is>
+          <t>0.3%</t>
+        </is>
+      </c>
       <c r="F411" t="inlineStr">
         <is>
-          <t>25K</t>
+          <t>0.3%</t>
         </is>
       </c>
       <c r="G411" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="412">
@@ -12539,31 +12547,31 @@
       </c>
       <c r="B412" t="inlineStr">
         <is>
-          <t>Manufacturing PayrollsJAN</t>
+          <t>Unemployment RateJAN</t>
         </is>
       </c>
       <c r="C412" t="inlineStr">
         <is>
-          <t>3K</t>
+          <t>4%</t>
         </is>
       </c>
       <c r="D412" t="inlineStr">
         <is>
-          <t>-12K</t>
+          <t>4.1%</t>
         </is>
       </c>
       <c r="E412" t="inlineStr">
         <is>
-          <t>-2K</t>
+          <t>4.1%</t>
         </is>
       </c>
       <c r="F412" t="inlineStr">
         <is>
-          <t>-5K</t>
+          <t>4.1%</t>
         </is>
       </c>
       <c r="G412" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="413">
@@ -12574,27 +12582,31 @@
       </c>
       <c r="B413" t="inlineStr">
         <is>
-          <t>U-6 Unemployment RateJAN</t>
+          <t>Average Hourly Earnings YoYJAN</t>
         </is>
       </c>
       <c r="C413" t="inlineStr">
         <is>
-          <t>7.5%</t>
+          <t>4.1%</t>
         </is>
       </c>
       <c r="D413" t="inlineStr">
         <is>
-          <t>7.5%</t>
-        </is>
-      </c>
-      <c r="E413" t="inlineStr"/>
+          <t>4.1%</t>
+        </is>
+      </c>
+      <c r="E413" t="inlineStr">
+        <is>
+          <t>3.8%</t>
+        </is>
+      </c>
       <c r="F413" t="inlineStr">
         <is>
-          <t>7.5%</t>
+          <t>3.9%</t>
         </is>
       </c>
       <c r="G413" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="414">
@@ -12605,31 +12617,31 @@
       </c>
       <c r="B414" t="inlineStr">
         <is>
-          <t>Unemployment RateJAN</t>
+          <t>Manufacturing PayrollsJAN</t>
         </is>
       </c>
       <c r="C414" t="inlineStr">
         <is>
-          <t>4%</t>
+          <t>3K</t>
         </is>
       </c>
       <c r="D414" t="inlineStr">
         <is>
-          <t>4.1%</t>
+          <t>-12K</t>
         </is>
       </c>
       <c r="E414" t="inlineStr">
         <is>
-          <t>4.1%</t>
+          <t>-2K</t>
         </is>
       </c>
       <c r="F414" t="inlineStr">
         <is>
-          <t>4.1%</t>
+          <t>-5K</t>
         </is>
       </c>
       <c r="G414" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="415">
@@ -12640,31 +12652,27 @@
       </c>
       <c r="B415" t="inlineStr">
         <is>
-          <t>Non Farm PayrollsJAN</t>
+          <t>Government PayrollsJAN</t>
         </is>
       </c>
       <c r="C415" t="inlineStr">
         <is>
-          <t>143K</t>
+          <t>32K</t>
         </is>
       </c>
       <c r="D415" t="inlineStr">
         <is>
-          <t>307K</t>
-        </is>
-      </c>
-      <c r="E415" t="inlineStr">
-        <is>
-          <t>170K</t>
-        </is>
-      </c>
+          <t>34K</t>
+        </is>
+      </c>
+      <c r="E415" t="inlineStr"/>
       <c r="F415" t="inlineStr">
         <is>
-          <t>205K</t>
+          <t>25K</t>
         </is>
       </c>
       <c r="G415" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="416">
@@ -12675,27 +12683,23 @@
       </c>
       <c r="B416" t="inlineStr">
         <is>
-          <t>Average Hourly Earnings MoMJAN</t>
+          <t>Participation RateJAN</t>
         </is>
       </c>
       <c r="C416" t="inlineStr">
         <is>
-          <t>0.5%</t>
+          <t>62.6%</t>
         </is>
       </c>
       <c r="D416" t="inlineStr">
         <is>
-          <t>0.3%</t>
-        </is>
-      </c>
-      <c r="E416" t="inlineStr">
-        <is>
-          <t>0.3%</t>
-        </is>
-      </c>
+          <t>62.5%</t>
+        </is>
+      </c>
+      <c r="E416" t="inlineStr"/>
       <c r="F416" t="inlineStr">
         <is>
-          <t>0.3%</t>
+          <t>62.5%</t>
         </is>
       </c>
       <c r="G416" t="n">
@@ -12710,31 +12714,31 @@
       </c>
       <c r="B417" t="inlineStr">
         <is>
-          <t>Average Hourly Earnings YoYJAN</t>
+          <t>Nonfarm Payrolls PrivateJAN</t>
         </is>
       </c>
       <c r="C417" t="inlineStr">
         <is>
-          <t>4.1%</t>
+          <t>111K</t>
         </is>
       </c>
       <c r="D417" t="inlineStr">
         <is>
-          <t>4.1%</t>
+          <t>273K</t>
         </is>
       </c>
       <c r="E417" t="inlineStr">
         <is>
-          <t>3.8%</t>
+          <t>141K</t>
         </is>
       </c>
       <c r="F417" t="inlineStr">
         <is>
-          <t>3.9%</t>
+          <t>180K</t>
         </is>
       </c>
       <c r="G417" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="418">
@@ -12745,27 +12749,23 @@
       </c>
       <c r="B418" t="inlineStr">
         <is>
-          <t>Average Weekly HoursJAN</t>
+          <t>U-6 Unemployment RateJAN</t>
         </is>
       </c>
       <c r="C418" t="inlineStr">
         <is>
-          <t>34.1</t>
+          <t>7.5%</t>
         </is>
       </c>
       <c r="D418" t="inlineStr">
         <is>
-          <t>34.2</t>
-        </is>
-      </c>
-      <c r="E418" t="inlineStr">
-        <is>
-          <t>34.3</t>
-        </is>
-      </c>
+          <t>7.5%</t>
+        </is>
+      </c>
+      <c r="E418" t="inlineStr"/>
       <c r="F418" t="inlineStr">
         <is>
-          <t>34.3</t>
+          <t>7.5%</t>
         </is>
       </c>
       <c r="G418" t="n">
@@ -13501,23 +13501,23 @@
       </c>
       <c r="B446" t="inlineStr">
         <is>
-          <t>MBA Mortgage ApplicationsFEB/07</t>
+          <t>MBA 30-Year Mortgage RateFEB/07</t>
         </is>
       </c>
       <c r="C446" t="inlineStr">
         <is>
-          <t>2.3%</t>
+          <t>6.95%</t>
         </is>
       </c>
       <c r="D446" t="inlineStr">
         <is>
-          <t>2.2%</t>
+          <t>6.97%</t>
         </is>
       </c>
       <c r="E446" t="inlineStr"/>
       <c r="F446" t="inlineStr"/>
       <c r="G446" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="447">
@@ -13528,17 +13528,17 @@
       </c>
       <c r="B447" t="inlineStr">
         <is>
-          <t>MBA Mortgage Refinance IndexFEB/07</t>
+          <t>MBA Purchase IndexFEB/07</t>
         </is>
       </c>
       <c r="C447" t="inlineStr">
         <is>
-          <t>640.6</t>
+          <t>153.1</t>
         </is>
       </c>
       <c r="D447" t="inlineStr">
         <is>
-          <t>584.3</t>
+          <t>156.7</t>
         </is>
       </c>
       <c r="E447" t="inlineStr"/>
@@ -13555,17 +13555,17 @@
       </c>
       <c r="B448" t="inlineStr">
         <is>
-          <t>MBA Purchase IndexFEB/07</t>
+          <t>MBA Mortgage Market IndexFEB/07</t>
         </is>
       </c>
       <c r="C448" t="inlineStr">
         <is>
-          <t>153.1</t>
+          <t>230.0</t>
         </is>
       </c>
       <c r="D448" t="inlineStr">
         <is>
-          <t>156.7</t>
+          <t>224.8</t>
         </is>
       </c>
       <c r="E448" t="inlineStr"/>
@@ -13582,23 +13582,23 @@
       </c>
       <c r="B449" t="inlineStr">
         <is>
-          <t>MBA 30-Year Mortgage RateFEB/07</t>
+          <t>MBA Mortgage ApplicationsFEB/07</t>
         </is>
       </c>
       <c r="C449" t="inlineStr">
         <is>
-          <t>6.95%</t>
+          <t>2.3%</t>
         </is>
       </c>
       <c r="D449" t="inlineStr">
         <is>
-          <t>6.97%</t>
+          <t>2.2%</t>
         </is>
       </c>
       <c r="E449" t="inlineStr"/>
       <c r="F449" t="inlineStr"/>
       <c r="G449" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="450">
@@ -13609,17 +13609,17 @@
       </c>
       <c r="B450" t="inlineStr">
         <is>
-          <t>MBA Mortgage Market IndexFEB/07</t>
+          <t>MBA Mortgage Refinance IndexFEB/07</t>
         </is>
       </c>
       <c r="C450" t="inlineStr">
         <is>
-          <t>230.0</t>
+          <t>640.6</t>
         </is>
       </c>
       <c r="D450" t="inlineStr">
         <is>
-          <t>224.8</t>
+          <t>584.3</t>
         </is>
       </c>
       <c r="E450" t="inlineStr"/>
@@ -13842,27 +13842,23 @@
       </c>
       <c r="B457" t="inlineStr">
         <is>
-          <t>EIA Crude Oil Stocks ChangeFEB/07</t>
+          <t>EIA Crude Oil Imports ChangeFEB/07</t>
         </is>
       </c>
       <c r="C457" t="inlineStr">
         <is>
-          <t>4.07M</t>
+          <t>-0.184M</t>
         </is>
       </c>
       <c r="D457" t="inlineStr">
         <is>
-          <t>8.664M</t>
-        </is>
-      </c>
-      <c r="E457" t="inlineStr">
-        <is>
-          <t>3M</t>
-        </is>
-      </c>
+          <t>-0.178M</t>
+        </is>
+      </c>
+      <c r="E457" t="inlineStr"/>
       <c r="F457" t="inlineStr"/>
       <c r="G457" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="458">
@@ -13873,17 +13869,17 @@
       </c>
       <c r="B458" t="inlineStr">
         <is>
-          <t>EIA Heating Oil Stocks ChangeFEB/07</t>
+          <t>EIA Refinery Crude Runs ChangeFEB/07</t>
         </is>
       </c>
       <c r="C458" t="inlineStr">
         <is>
-          <t>0.159M</t>
+          <t>0.082M</t>
         </is>
       </c>
       <c r="D458" t="inlineStr">
         <is>
-          <t>0.373M</t>
+          <t>0.16M</t>
         </is>
       </c>
       <c r="E458" t="inlineStr"/>
@@ -13900,17 +13896,17 @@
       </c>
       <c r="B459" t="inlineStr">
         <is>
-          <t>EIA Cushing Crude Oil Stocks ChangeFEB/07</t>
+          <t>EIA Gasoline Production ChangeFEB/07</t>
         </is>
       </c>
       <c r="C459" t="inlineStr">
         <is>
-          <t>0.872M</t>
+          <t>0.18M</t>
         </is>
       </c>
       <c r="D459" t="inlineStr">
         <is>
-          <t>-0.034M</t>
+          <t>-0.027M</t>
         </is>
       </c>
       <c r="E459" t="inlineStr"/>
@@ -13927,23 +13923,27 @@
       </c>
       <c r="B460" t="inlineStr">
         <is>
-          <t>EIA Distillate Fuel Production ChangeFEB/07</t>
+          <t>EIA Gasoline Stocks ChangeFEB/07</t>
         </is>
       </c>
       <c r="C460" t="inlineStr">
         <is>
-          <t>-0.009M</t>
+          <t>-3.035M</t>
         </is>
       </c>
       <c r="D460" t="inlineStr">
         <is>
-          <t>-0.186M</t>
-        </is>
-      </c>
-      <c r="E460" t="inlineStr"/>
+          <t>2.233M</t>
+        </is>
+      </c>
+      <c r="E460" t="inlineStr">
+        <is>
+          <t>1.5M</t>
+        </is>
+      </c>
       <c r="F460" t="inlineStr"/>
       <c r="G460" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="461">
@@ -13985,27 +13985,23 @@
       </c>
       <c r="B462" t="inlineStr">
         <is>
-          <t>EIA Gasoline Stocks ChangeFEB/07</t>
+          <t>EIA Distillate Fuel Production ChangeFEB/07</t>
         </is>
       </c>
       <c r="C462" t="inlineStr">
         <is>
-          <t>-3.035M</t>
+          <t>-0.009M</t>
         </is>
       </c>
       <c r="D462" t="inlineStr">
         <is>
-          <t>2.233M</t>
-        </is>
-      </c>
-      <c r="E462" t="inlineStr">
-        <is>
-          <t>1.5M</t>
-        </is>
-      </c>
+          <t>-0.186M</t>
+        </is>
+      </c>
+      <c r="E462" t="inlineStr"/>
       <c r="F462" t="inlineStr"/>
       <c r="G462" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="463">
@@ -14016,17 +14012,17 @@
       </c>
       <c r="B463" t="inlineStr">
         <is>
-          <t>EIA Gasoline Production ChangeFEB/07</t>
+          <t>EIA Cushing Crude Oil Stocks ChangeFEB/07</t>
         </is>
       </c>
       <c r="C463" t="inlineStr">
         <is>
-          <t>0.18M</t>
+          <t>0.872M</t>
         </is>
       </c>
       <c r="D463" t="inlineStr">
         <is>
-          <t>-0.027M</t>
+          <t>-0.034M</t>
         </is>
       </c>
       <c r="E463" t="inlineStr"/>
@@ -14043,17 +14039,17 @@
       </c>
       <c r="B464" t="inlineStr">
         <is>
-          <t>EIA Refinery Crude Runs ChangeFEB/07</t>
+          <t>EIA Heating Oil Stocks ChangeFEB/07</t>
         </is>
       </c>
       <c r="C464" t="inlineStr">
         <is>
-          <t>0.082M</t>
+          <t>0.159M</t>
         </is>
       </c>
       <c r="D464" t="inlineStr">
         <is>
-          <t>0.16M</t>
+          <t>0.373M</t>
         </is>
       </c>
       <c r="E464" t="inlineStr"/>
@@ -14070,23 +14066,27 @@
       </c>
       <c r="B465" t="inlineStr">
         <is>
-          <t>EIA Crude Oil Imports ChangeFEB/07</t>
+          <t>EIA Crude Oil Stocks ChangeFEB/07</t>
         </is>
       </c>
       <c r="C465" t="inlineStr">
         <is>
-          <t>-0.184M</t>
+          <t>4.07M</t>
         </is>
       </c>
       <c r="D465" t="inlineStr">
         <is>
-          <t>-0.178M</t>
-        </is>
-      </c>
-      <c r="E465" t="inlineStr"/>
+          <t>8.664M</t>
+        </is>
+      </c>
+      <c r="E465" t="inlineStr">
+        <is>
+          <t>3M</t>
+        </is>
+      </c>
       <c r="F465" t="inlineStr"/>
       <c r="G465" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="466">
@@ -14224,23 +14224,27 @@
       </c>
       <c r="B471" t="inlineStr">
         <is>
-          <t>PPI Ex Food, Energy and Trade MoMJAN</t>
+          <t>Core PPI YoYJAN</t>
         </is>
       </c>
       <c r="C471" t="inlineStr">
         <is>
-          <t>0.3%</t>
+          <t>3.6%</t>
         </is>
       </c>
       <c r="D471" t="inlineStr">
         <is>
-          <t>0.4%</t>
-        </is>
-      </c>
-      <c r="E471" t="inlineStr"/>
+          <t>3.7%</t>
+        </is>
+      </c>
+      <c r="E471" t="inlineStr">
+        <is>
+          <t>3.3%</t>
+        </is>
+      </c>
       <c r="F471" t="inlineStr">
         <is>
-          <t>0.2%</t>
+          <t>3.5%</t>
         </is>
       </c>
       <c r="G471" t="n">
@@ -14255,27 +14259,31 @@
       </c>
       <c r="B472" t="inlineStr">
         <is>
-          <t>Jobless Claims 4-week AverageFEB/08</t>
+          <t>Core PPI MoMJAN</t>
         </is>
       </c>
       <c r="C472" t="inlineStr">
         <is>
-          <t>216K</t>
+          <t>0.3%</t>
         </is>
       </c>
       <c r="D472" t="inlineStr">
         <is>
-          <t>217K</t>
-        </is>
-      </c>
-      <c r="E472" t="inlineStr"/>
+          <t>0.4%</t>
+        </is>
+      </c>
+      <c r="E472" t="inlineStr">
+        <is>
+          <t>0.3%</t>
+        </is>
+      </c>
       <c r="F472" t="inlineStr">
         <is>
-          <t>216.0K</t>
+          <t>0.1%</t>
         </is>
       </c>
       <c r="G472" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="473">
@@ -14286,31 +14294,31 @@
       </c>
       <c r="B473" t="inlineStr">
         <is>
-          <t>Continuing Jobless ClaimsFEB/01</t>
+          <t>Initial Jobless ClaimsFEB/08</t>
         </is>
       </c>
       <c r="C473" t="inlineStr">
         <is>
-          <t>1850K</t>
+          <t>213K</t>
         </is>
       </c>
       <c r="D473" t="inlineStr">
         <is>
-          <t>1886K</t>
+          <t>220K</t>
         </is>
       </c>
       <c r="E473" t="inlineStr">
         <is>
-          <t>1880K</t>
+          <t>215K</t>
         </is>
       </c>
       <c r="F473" t="inlineStr">
         <is>
-          <t>1875.0K</t>
+          <t>215.0K</t>
         </is>
       </c>
       <c r="G473" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="474">
@@ -14321,31 +14329,27 @@
       </c>
       <c r="B474" t="inlineStr">
         <is>
-          <t>PPI MoMJAN</t>
+          <t>PPIJAN</t>
         </is>
       </c>
       <c r="C474" t="inlineStr">
         <is>
-          <t>0.4%</t>
+          <t>147.716</t>
         </is>
       </c>
       <c r="D474" t="inlineStr">
         <is>
-          <t>0.5%</t>
-        </is>
-      </c>
-      <c r="E474" t="inlineStr">
-        <is>
-          <t>0.3%</t>
-        </is>
-      </c>
+          <t>147.127</t>
+        </is>
+      </c>
+      <c r="E474" t="inlineStr"/>
       <c r="F474" t="inlineStr">
         <is>
-          <t>0.3%</t>
+          <t>147.2</t>
         </is>
       </c>
       <c r="G474" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="475">
@@ -14356,27 +14360,27 @@
       </c>
       <c r="B475" t="inlineStr">
         <is>
-          <t>PPI Ex Food, Energy and Trade YoYJAN</t>
+          <t>PPI YoYJAN</t>
         </is>
       </c>
       <c r="C475" t="inlineStr">
         <is>
+          <t>3.5%</t>
+        </is>
+      </c>
+      <c r="D475" t="inlineStr">
+        <is>
+          <t>3.5%</t>
+        </is>
+      </c>
+      <c r="E475" t="inlineStr">
+        <is>
+          <t>3.2%</t>
+        </is>
+      </c>
+      <c r="F475" t="inlineStr">
+        <is>
           <t>3.4%</t>
-        </is>
-      </c>
-      <c r="D475" t="inlineStr">
-        <is>
-          <t>3.5%</t>
-        </is>
-      </c>
-      <c r="E475" t="inlineStr">
-        <is>
-          <t>3.2%</t>
-        </is>
-      </c>
-      <c r="F475" t="inlineStr">
-        <is>
-          <t>3.3%</t>
         </is>
       </c>
       <c r="G475" t="n">
@@ -14391,31 +14395,31 @@
       </c>
       <c r="B476" t="inlineStr">
         <is>
-          <t>PPI YoYJAN</t>
+          <t>PPI MoMJAN</t>
         </is>
       </c>
       <c r="C476" t="inlineStr">
         <is>
-          <t>3.5%</t>
+          <t>0.4%</t>
         </is>
       </c>
       <c r="D476" t="inlineStr">
         <is>
-          <t>3.5%</t>
+          <t>0.5%</t>
         </is>
       </c>
       <c r="E476" t="inlineStr">
         <is>
-          <t>3.2%</t>
+          <t>0.3%</t>
         </is>
       </c>
       <c r="F476" t="inlineStr">
         <is>
-          <t>3.4%</t>
+          <t>0.3%</t>
         </is>
       </c>
       <c r="G476" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="477">
@@ -14426,23 +14430,27 @@
       </c>
       <c r="B477" t="inlineStr">
         <is>
-          <t>PPIJAN</t>
+          <t>Continuing Jobless ClaimsFEB/01</t>
         </is>
       </c>
       <c r="C477" t="inlineStr">
         <is>
-          <t>147.716</t>
+          <t>1850K</t>
         </is>
       </c>
       <c r="D477" t="inlineStr">
         <is>
-          <t>147.127</t>
-        </is>
-      </c>
-      <c r="E477" t="inlineStr"/>
+          <t>1886K</t>
+        </is>
+      </c>
+      <c r="E477" t="inlineStr">
+        <is>
+          <t>1880K</t>
+        </is>
+      </c>
       <c r="F477" t="inlineStr">
         <is>
-          <t>147.2</t>
+          <t>1875.0K</t>
         </is>
       </c>
       <c r="G477" t="n">
@@ -14457,31 +14465,27 @@
       </c>
       <c r="B478" t="inlineStr">
         <is>
-          <t>Initial Jobless ClaimsFEB/08</t>
+          <t>Jobless Claims 4-week AverageFEB/08</t>
         </is>
       </c>
       <c r="C478" t="inlineStr">
         <is>
-          <t>213K</t>
+          <t>216K</t>
         </is>
       </c>
       <c r="D478" t="inlineStr">
         <is>
-          <t>220K</t>
-        </is>
-      </c>
-      <c r="E478" t="inlineStr">
-        <is>
-          <t>215K</t>
-        </is>
-      </c>
+          <t>217K</t>
+        </is>
+      </c>
+      <c r="E478" t="inlineStr"/>
       <c r="F478" t="inlineStr">
         <is>
-          <t>215.0K</t>
+          <t>216.0K</t>
         </is>
       </c>
       <c r="G478" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="479">
@@ -14492,7 +14496,7 @@
       </c>
       <c r="B479" t="inlineStr">
         <is>
-          <t>Core PPI MoMJAN</t>
+          <t>PPI Ex Food, Energy and Trade MoMJAN</t>
         </is>
       </c>
       <c r="C479" t="inlineStr">
@@ -14505,18 +14509,14 @@
           <t>0.4%</t>
         </is>
       </c>
-      <c r="E479" t="inlineStr">
-        <is>
-          <t>0.3%</t>
-        </is>
-      </c>
+      <c r="E479" t="inlineStr"/>
       <c r="F479" t="inlineStr">
         <is>
-          <t>0.1%</t>
+          <t>0.2%</t>
         </is>
       </c>
       <c r="G479" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="480">
@@ -14527,27 +14527,27 @@
       </c>
       <c r="B480" t="inlineStr">
         <is>
-          <t>Core PPI YoYJAN</t>
+          <t>PPI Ex Food, Energy and Trade YoYJAN</t>
         </is>
       </c>
       <c r="C480" t="inlineStr">
         <is>
-          <t>3.6%</t>
+          <t>3.4%</t>
         </is>
       </c>
       <c r="D480" t="inlineStr">
         <is>
-          <t>3.7%</t>
+          <t>3.5%</t>
         </is>
       </c>
       <c r="E480" t="inlineStr">
         <is>
+          <t>3.2%</t>
+        </is>
+      </c>
+      <c r="F480" t="inlineStr">
+        <is>
           <t>3.3%</t>
-        </is>
-      </c>
-      <c r="F480" t="inlineStr">
-        <is>
-          <t>3.5%</t>
         </is>
       </c>
       <c r="G480" t="n">
@@ -14728,23 +14728,23 @@
       </c>
       <c r="B487" t="inlineStr">
         <is>
-          <t>Export Prices YoYJAN</t>
+          <t>Retail Sales YoYJAN</t>
         </is>
       </c>
       <c r="C487" t="inlineStr">
         <is>
-          <t>2.7%</t>
+          <t>4.2%</t>
         </is>
       </c>
       <c r="D487" t="inlineStr">
         <is>
-          <t>2%</t>
+          <t>4.4%</t>
         </is>
       </c>
       <c r="E487" t="inlineStr"/>
       <c r="F487" t="inlineStr">
         <is>
-          <t>2.3%</t>
+          <t>3.7%</t>
         </is>
       </c>
       <c r="G487" t="n">
@@ -14759,17 +14759,17 @@
       </c>
       <c r="B488" t="inlineStr">
         <is>
-          <t>Retail Sales Ex Autos MoMJAN</t>
+          <t>Retail Sales Control Group MoMJAN</t>
         </is>
       </c>
       <c r="C488" t="inlineStr">
         <is>
-          <t>-0.4%</t>
+          <t>-0.8%</t>
         </is>
       </c>
       <c r="D488" t="inlineStr">
         <is>
-          <t>0.7%</t>
+          <t>0.8%</t>
         </is>
       </c>
       <c r="E488" t="inlineStr">
@@ -14779,7 +14779,7 @@
       </c>
       <c r="F488" t="inlineStr">
         <is>
-          <t>0.3%</t>
+          <t>0.4%</t>
         </is>
       </c>
       <c r="G488" t="n">
@@ -14794,31 +14794,31 @@
       </c>
       <c r="B489" t="inlineStr">
         <is>
-          <t>Export Prices MoMJAN</t>
+          <t>Retail Sales MoMJAN</t>
         </is>
       </c>
       <c r="C489" t="inlineStr">
         <is>
-          <t>1.3%</t>
+          <t>-0.9%</t>
         </is>
       </c>
       <c r="D489" t="inlineStr">
         <is>
-          <t>0.5%</t>
+          <t>0.7%</t>
         </is>
       </c>
       <c r="E489" t="inlineStr">
         <is>
-          <t>0.3%</t>
+          <t>-0.1%</t>
         </is>
       </c>
       <c r="F489" t="inlineStr">
         <is>
-          <t>0.3%</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="G489" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="490">
@@ -14829,23 +14829,23 @@
       </c>
       <c r="B490" t="inlineStr">
         <is>
-          <t>Retail Sales YoYJAN</t>
+          <t>Retail Sales Ex Gas/Autos MoMJAN</t>
         </is>
       </c>
       <c r="C490" t="inlineStr">
         <is>
-          <t>4.2%</t>
+          <t>-0.5%</t>
         </is>
       </c>
       <c r="D490" t="inlineStr">
         <is>
-          <t>4.4%</t>
+          <t>0.5%</t>
         </is>
       </c>
       <c r="E490" t="inlineStr"/>
       <c r="F490" t="inlineStr">
         <is>
-          <t>3.7%</t>
+          <t>0.2%</t>
         </is>
       </c>
       <c r="G490" t="n">
@@ -14860,27 +14860,31 @@
       </c>
       <c r="B491" t="inlineStr">
         <is>
-          <t>Import Prices YoYJAN</t>
+          <t>Import Prices MoMJAN</t>
         </is>
       </c>
       <c r="C491" t="inlineStr">
         <is>
-          <t>1.9%</t>
+          <t>0.3%</t>
         </is>
       </c>
       <c r="D491" t="inlineStr">
         <is>
-          <t>2.2%</t>
-        </is>
-      </c>
-      <c r="E491" t="inlineStr"/>
+          <t>0.2%</t>
+        </is>
+      </c>
+      <c r="E491" t="inlineStr">
+        <is>
+          <t>0.4%</t>
+        </is>
+      </c>
       <c r="F491" t="inlineStr">
         <is>
-          <t>2.8%</t>
+          <t>0.3%</t>
         </is>
       </c>
       <c r="G491" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="492">
@@ -14891,22 +14895,22 @@
       </c>
       <c r="B492" t="inlineStr">
         <is>
-          <t>Import Prices MoMJAN</t>
+          <t>Export Prices MoMJAN</t>
         </is>
       </c>
       <c r="C492" t="inlineStr">
         <is>
+          <t>1.3%</t>
+        </is>
+      </c>
+      <c r="D492" t="inlineStr">
+        <is>
+          <t>0.5%</t>
+        </is>
+      </c>
+      <c r="E492" t="inlineStr">
+        <is>
           <t>0.3%</t>
-        </is>
-      </c>
-      <c r="D492" t="inlineStr">
-        <is>
-          <t>0.2%</t>
-        </is>
-      </c>
-      <c r="E492" t="inlineStr">
-        <is>
-          <t>0.4%</t>
         </is>
       </c>
       <c r="F492" t="inlineStr">
@@ -14926,27 +14930,31 @@
       </c>
       <c r="B493" t="inlineStr">
         <is>
-          <t>Retail Sales Ex Gas/Autos MoMJAN</t>
+          <t>Retail Sales Ex Autos MoMJAN</t>
         </is>
       </c>
       <c r="C493" t="inlineStr">
         <is>
-          <t>-0.5%</t>
+          <t>-0.4%</t>
         </is>
       </c>
       <c r="D493" t="inlineStr">
         <is>
-          <t>0.5%</t>
-        </is>
-      </c>
-      <c r="E493" t="inlineStr"/>
+          <t>0.7%</t>
+        </is>
+      </c>
+      <c r="E493" t="inlineStr">
+        <is>
+          <t>0.3%</t>
+        </is>
+      </c>
       <c r="F493" t="inlineStr">
         <is>
-          <t>0.2%</t>
+          <t>0.3%</t>
         </is>
       </c>
       <c r="G493" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="494">
@@ -14957,31 +14965,27 @@
       </c>
       <c r="B494" t="inlineStr">
         <is>
-          <t>Retail Sales MoMJAN</t>
+          <t>Export Prices YoYJAN</t>
         </is>
       </c>
       <c r="C494" t="inlineStr">
         <is>
-          <t>-0.9%</t>
+          <t>2.7%</t>
         </is>
       </c>
       <c r="D494" t="inlineStr">
         <is>
-          <t>0.7%</t>
-        </is>
-      </c>
-      <c r="E494" t="inlineStr">
-        <is>
-          <t>-0.1%</t>
-        </is>
-      </c>
+          <t>2%</t>
+        </is>
+      </c>
+      <c r="E494" t="inlineStr"/>
       <c r="F494" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>2.3%</t>
         </is>
       </c>
       <c r="G494" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="495">
@@ -14992,31 +14996,27 @@
       </c>
       <c r="B495" t="inlineStr">
         <is>
-          <t>Retail Sales Control Group MoMJAN</t>
+          <t>Import Prices YoYJAN</t>
         </is>
       </c>
       <c r="C495" t="inlineStr">
         <is>
-          <t>-0.8%</t>
+          <t>1.9%</t>
         </is>
       </c>
       <c r="D495" t="inlineStr">
         <is>
-          <t>0.8%</t>
-        </is>
-      </c>
-      <c r="E495" t="inlineStr">
-        <is>
-          <t>0.3%</t>
-        </is>
-      </c>
+          <t>2.2%</t>
+        </is>
+      </c>
+      <c r="E495" t="inlineStr"/>
       <c r="F495" t="inlineStr">
         <is>
-          <t>0.4%</t>
+          <t>2.8%</t>
         </is>
       </c>
       <c r="G495" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="496">
@@ -15629,17 +15629,17 @@
       </c>
       <c r="B518" t="inlineStr">
         <is>
-          <t>Overall Net Capital FlowsDEC</t>
+          <t>Foreign Bond InvestmentDEC</t>
         </is>
       </c>
       <c r="C518" t="inlineStr">
         <is>
-          <t>$87.1B</t>
+          <t>$-49.7B</t>
         </is>
       </c>
       <c r="D518" t="inlineStr">
         <is>
-          <t>$134.1B</t>
+          <t>$-34.4B</t>
         </is>
       </c>
       <c r="E518" t="inlineStr"/>
@@ -15687,17 +15687,17 @@
       </c>
       <c r="B520" t="inlineStr">
         <is>
-          <t>Foreign Bond InvestmentDEC</t>
+          <t>Overall Net Capital FlowsDEC</t>
         </is>
       </c>
       <c r="C520" t="inlineStr">
         <is>
-          <t>$-49.7B</t>
+          <t>$87.1B</t>
         </is>
       </c>
       <c r="D520" t="inlineStr">
         <is>
-          <t>$-34.4B</t>
+          <t>$134.1B</t>
         </is>
       </c>
       <c r="E520" t="inlineStr"/>
@@ -17326,7 +17326,7 @@
       </c>
       <c r="B577" t="inlineStr">
         <is>
-          <t>Fed Daly Speech</t>
+          <t>Fed Jefferson Speech</t>
         </is>
       </c>
       <c r="C577" t="inlineStr"/>
@@ -17345,7 +17345,7 @@
       </c>
       <c r="B578" t="inlineStr">
         <is>
-          <t>Fed Jefferson Speech</t>
+          <t>Fed Daly Speech</t>
         </is>
       </c>
       <c r="C578" t="inlineStr"/>
@@ -17630,27 +17630,27 @@
       </c>
       <c r="B589" t="inlineStr">
         <is>
-          <t>House Price Index YoYDEC</t>
-        </is>
-      </c>
-      <c r="C589" t="inlineStr">
-        <is>
-          <t>4.7%</t>
-        </is>
-      </c>
+          <t>S&amp;P/Case-Shiller Home Price YoYDEC</t>
+        </is>
+      </c>
+      <c r="C589" t="inlineStr"/>
       <c r="D589" t="inlineStr">
         <is>
-          <t>4.5%</t>
-        </is>
-      </c>
-      <c r="E589" t="inlineStr"/>
+          <t>4.3%</t>
+        </is>
+      </c>
+      <c r="E589" t="inlineStr">
+        <is>
+          <t>4.4%</t>
+        </is>
+      </c>
       <c r="F589" t="inlineStr">
         <is>
-          <t>4.1%</t>
+          <t>4.4%</t>
         </is>
       </c>
       <c r="G589" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="590">
@@ -17661,27 +17661,31 @@
       </c>
       <c r="B590" t="inlineStr">
         <is>
-          <t>S&amp;P/Case-Shiller Home Price MoMDEC</t>
+          <t>S&amp;P/Case-Shiller Home Price YoYDEC</t>
         </is>
       </c>
       <c r="C590" t="inlineStr">
         <is>
-          <t>-0.1%</t>
+          <t>4.5%</t>
         </is>
       </c>
       <c r="D590" t="inlineStr">
         <is>
-          <t>-0.1%</t>
-        </is>
-      </c>
-      <c r="E590" t="inlineStr"/>
+          <t>4.3%</t>
+        </is>
+      </c>
+      <c r="E590" t="inlineStr">
+        <is>
+          <t>4.4%</t>
+        </is>
+      </c>
       <c r="F590" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>4.4%</t>
         </is>
       </c>
       <c r="G590" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="591">
@@ -17692,27 +17696,19 @@
       </c>
       <c r="B591" t="inlineStr">
         <is>
-          <t>House Price Index MoMDEC</t>
-        </is>
-      </c>
-      <c r="C591" t="inlineStr">
-        <is>
-          <t>0.4%</t>
-        </is>
-      </c>
+          <t>House Price Index YoYDEC</t>
+        </is>
+      </c>
+      <c r="C591" t="inlineStr"/>
       <c r="D591" t="inlineStr">
         <is>
-          <t>0.4%</t>
-        </is>
-      </c>
-      <c r="E591" t="inlineStr">
-        <is>
-          <t>0.2%</t>
-        </is>
-      </c>
+          <t>4.2%</t>
+        </is>
+      </c>
+      <c r="E591" t="inlineStr"/>
       <c r="F591" t="inlineStr">
         <is>
-          <t>0.2%</t>
+          <t>4.1%</t>
         </is>
       </c>
       <c r="G591" t="n">
@@ -17730,14 +17726,10 @@
           <t>House Price IndexDEC</t>
         </is>
       </c>
-      <c r="C592" t="inlineStr">
-        <is>
-          <t>436.1</t>
-        </is>
-      </c>
+      <c r="C592" t="inlineStr"/>
       <c r="D592" t="inlineStr">
         <is>
-          <t>434.3</t>
+          <t>433.4</t>
         </is>
       </c>
       <c r="E592" t="inlineStr"/>
@@ -17758,23 +17750,19 @@
       </c>
       <c r="B593" t="inlineStr">
         <is>
-          <t>House Price Index MoMDEC</t>
+          <t>S&amp;P/Case-Shiller Home Price MoMDEC</t>
         </is>
       </c>
       <c r="C593" t="inlineStr"/>
       <c r="D593" t="inlineStr">
         <is>
-          <t>0.3%</t>
-        </is>
-      </c>
-      <c r="E593" t="inlineStr">
-        <is>
-          <t>0.2%</t>
-        </is>
-      </c>
+          <t>-0.1%</t>
+        </is>
+      </c>
+      <c r="E593" t="inlineStr"/>
       <c r="F593" t="inlineStr">
         <is>
-          <t>0.2%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="G593" t="n">
@@ -17789,19 +17777,23 @@
       </c>
       <c r="B594" t="inlineStr">
         <is>
-          <t>S&amp;P/Case-Shiller Home Price MoMDEC</t>
+          <t>House Price Index MoMDEC</t>
         </is>
       </c>
       <c r="C594" t="inlineStr"/>
       <c r="D594" t="inlineStr">
         <is>
-          <t>-0.1%</t>
-        </is>
-      </c>
-      <c r="E594" t="inlineStr"/>
+          <t>0.3%</t>
+        </is>
+      </c>
+      <c r="E594" t="inlineStr">
+        <is>
+          <t>0.2%</t>
+        </is>
+      </c>
       <c r="F594" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>0.2%</t>
         </is>
       </c>
       <c r="G594" t="n">
@@ -17816,27 +17808,27 @@
       </c>
       <c r="B595" t="inlineStr">
         <is>
-          <t>S&amp;P/Case-Shiller Home Price YoYDEC</t>
-        </is>
-      </c>
-      <c r="C595" t="inlineStr"/>
+          <t>House Price IndexDEC</t>
+        </is>
+      </c>
+      <c r="C595" t="inlineStr">
+        <is>
+          <t>436.1</t>
+        </is>
+      </c>
       <c r="D595" t="inlineStr">
         <is>
-          <t>4.3%</t>
-        </is>
-      </c>
-      <c r="E595" t="inlineStr">
-        <is>
-          <t>4.4%</t>
-        </is>
-      </c>
+          <t>434.3</t>
+        </is>
+      </c>
+      <c r="E595" t="inlineStr"/>
       <c r="F595" t="inlineStr">
         <is>
-          <t>4.4%</t>
+          <t>434.3</t>
         </is>
       </c>
       <c r="G595" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="596">
@@ -17847,19 +17839,27 @@
       </c>
       <c r="B596" t="inlineStr">
         <is>
-          <t>House Price IndexDEC</t>
-        </is>
-      </c>
-      <c r="C596" t="inlineStr"/>
+          <t>House Price Index MoMDEC</t>
+        </is>
+      </c>
+      <c r="C596" t="inlineStr">
+        <is>
+          <t>0.4%</t>
+        </is>
+      </c>
       <c r="D596" t="inlineStr">
         <is>
-          <t>433.4</t>
-        </is>
-      </c>
-      <c r="E596" t="inlineStr"/>
+          <t>0.4%</t>
+        </is>
+      </c>
+      <c r="E596" t="inlineStr">
+        <is>
+          <t>0.2%</t>
+        </is>
+      </c>
       <c r="F596" t="inlineStr">
         <is>
-          <t>434.3</t>
+          <t>0.2%</t>
         </is>
       </c>
       <c r="G596" t="n">
@@ -17874,19 +17874,23 @@
       </c>
       <c r="B597" t="inlineStr">
         <is>
-          <t>House Price Index YoYDEC</t>
-        </is>
-      </c>
-      <c r="C597" t="inlineStr"/>
+          <t>S&amp;P/Case-Shiller Home Price MoMDEC</t>
+        </is>
+      </c>
+      <c r="C597" t="inlineStr">
+        <is>
+          <t>-0.1%</t>
+        </is>
+      </c>
       <c r="D597" t="inlineStr">
         <is>
-          <t>4.2%</t>
+          <t>-0.1%</t>
         </is>
       </c>
       <c r="E597" t="inlineStr"/>
       <c r="F597" t="inlineStr">
         <is>
-          <t>4.1%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="G597" t="n">
@@ -17901,31 +17905,27 @@
       </c>
       <c r="B598" t="inlineStr">
         <is>
-          <t>S&amp;P/Case-Shiller Home Price YoYDEC</t>
+          <t>House Price Index YoYDEC</t>
         </is>
       </c>
       <c r="C598" t="inlineStr">
         <is>
+          <t>4.7%</t>
+        </is>
+      </c>
+      <c r="D598" t="inlineStr">
+        <is>
           <t>4.5%</t>
         </is>
       </c>
-      <c r="D598" t="inlineStr">
-        <is>
-          <t>4.3%</t>
-        </is>
-      </c>
-      <c r="E598" t="inlineStr">
-        <is>
-          <t>4.4%</t>
-        </is>
-      </c>
+      <c r="E598" t="inlineStr"/>
       <c r="F598" t="inlineStr">
         <is>
-          <t>4.4%</t>
+          <t>4.1%</t>
         </is>
       </c>
       <c r="G598" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="599">
@@ -18184,23 +18184,19 @@
       </c>
       <c r="B607" t="inlineStr">
         <is>
-          <t>Dallas Fed Services Revenues IndexFEB</t>
-        </is>
-      </c>
-      <c r="C607" t="inlineStr">
-        <is>
-          <t>8.2</t>
-        </is>
-      </c>
+          <t>Dallas Fed Services IndexFEB</t>
+        </is>
+      </c>
+      <c r="C607" t="inlineStr"/>
       <c r="D607" t="inlineStr">
         <is>
-          <t>5.7</t>
+          <t>7.4</t>
         </is>
       </c>
       <c r="E607" t="inlineStr"/>
       <c r="F607" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>9</t>
         </is>
       </c>
       <c r="G607" t="n">
@@ -18215,23 +18211,19 @@
       </c>
       <c r="B608" t="inlineStr">
         <is>
-          <t>Dallas Fed Services IndexFEB</t>
-        </is>
-      </c>
-      <c r="C608" t="inlineStr">
-        <is>
-          <t>4.6</t>
-        </is>
-      </c>
+          <t>Dallas Fed Services Revenues IndexFEB</t>
+        </is>
+      </c>
+      <c r="C608" t="inlineStr"/>
       <c r="D608" t="inlineStr">
         <is>
-          <t>7.4</t>
+          <t>5.7</t>
         </is>
       </c>
       <c r="E608" t="inlineStr"/>
       <c r="F608" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>7</t>
         </is>
       </c>
       <c r="G608" t="n">
@@ -18249,7 +18241,11 @@
           <t>Dallas Fed Services Revenues IndexFEB</t>
         </is>
       </c>
-      <c r="C609" t="inlineStr"/>
+      <c r="C609" t="inlineStr">
+        <is>
+          <t>8.2</t>
+        </is>
+      </c>
       <c r="D609" t="inlineStr">
         <is>
           <t>5.7</t>
@@ -18276,7 +18272,11 @@
           <t>Dallas Fed Services IndexFEB</t>
         </is>
       </c>
-      <c r="C610" t="inlineStr"/>
+      <c r="C610" t="inlineStr">
+        <is>
+          <t>4.6</t>
+        </is>
+      </c>
       <c r="D610" t="inlineStr">
         <is>
           <t>7.4</t>
@@ -18496,17 +18496,17 @@
       </c>
       <c r="B619" t="inlineStr">
         <is>
-          <t>MBA Mortgage Market IndexFEB/21</t>
+          <t>MBA Mortgage ApplicationsFEB/21</t>
         </is>
       </c>
       <c r="C619" t="inlineStr">
         <is>
-          <t>212.3</t>
+          <t>-1.2%</t>
         </is>
       </c>
       <c r="D619" t="inlineStr">
         <is>
-          <t>214.9</t>
+          <t>-6.6%</t>
         </is>
       </c>
       <c r="E619" t="inlineStr"/>
@@ -18523,23 +18523,19 @@
       </c>
       <c r="B620" t="inlineStr">
         <is>
-          <t>MBA Purchase IndexFEB/21</t>
-        </is>
-      </c>
-      <c r="C620" t="inlineStr">
-        <is>
-          <t>144.3</t>
-        </is>
-      </c>
+          <t>MBA 30-Year Mortgage RateFEB/21</t>
+        </is>
+      </c>
+      <c r="C620" t="inlineStr"/>
       <c r="D620" t="inlineStr">
         <is>
-          <t>144.0</t>
+          <t>6.93%</t>
         </is>
       </c>
       <c r="E620" t="inlineStr"/>
       <c r="F620" t="inlineStr"/>
       <c r="G620" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="621">
@@ -18550,13 +18546,13 @@
       </c>
       <c r="B621" t="inlineStr">
         <is>
-          <t>MBA Mortgage Market IndexFEB/21</t>
+          <t>MBA Mortgage Refinance IndexFEB/21</t>
         </is>
       </c>
       <c r="C621" t="inlineStr"/>
       <c r="D621" t="inlineStr">
         <is>
-          <t>214.9</t>
+          <t>593.6</t>
         </is>
       </c>
       <c r="E621" t="inlineStr"/>
@@ -18573,17 +18569,13 @@
       </c>
       <c r="B622" t="inlineStr">
         <is>
-          <t>MBA Mortgage Refinance IndexFEB/21</t>
-        </is>
-      </c>
-      <c r="C622" t="inlineStr">
-        <is>
-          <t>572.5</t>
-        </is>
-      </c>
+          <t>MBA Mortgage ApplicationsFEB/21</t>
+        </is>
+      </c>
+      <c r="C622" t="inlineStr"/>
       <c r="D622" t="inlineStr">
         <is>
-          <t>593.6</t>
+          <t>-6.6%</t>
         </is>
       </c>
       <c r="E622" t="inlineStr"/>
@@ -18600,23 +18592,19 @@
       </c>
       <c r="B623" t="inlineStr">
         <is>
-          <t>MBA 30-Year Mortgage RateFEB/21</t>
-        </is>
-      </c>
-      <c r="C623" t="inlineStr">
-        <is>
-          <t>6.88%</t>
-        </is>
-      </c>
+          <t>MBA Purchase IndexFEB/21</t>
+        </is>
+      </c>
+      <c r="C623" t="inlineStr"/>
       <c r="D623" t="inlineStr">
         <is>
-          <t>6.93%</t>
+          <t>144.0</t>
         </is>
       </c>
       <c r="E623" t="inlineStr"/>
       <c r="F623" t="inlineStr"/>
       <c r="G623" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="624">
@@ -18630,7 +18618,11 @@
           <t>MBA Purchase IndexFEB/21</t>
         </is>
       </c>
-      <c r="C624" t="inlineStr"/>
+      <c r="C624" t="inlineStr">
+        <is>
+          <t>144.3</t>
+        </is>
+      </c>
       <c r="D624" t="inlineStr">
         <is>
           <t>144.0</t>
@@ -18650,17 +18642,17 @@
       </c>
       <c r="B625" t="inlineStr">
         <is>
-          <t>MBA Mortgage ApplicationsFEB/21</t>
+          <t>MBA Mortgage Refinance IndexFEB/21</t>
         </is>
       </c>
       <c r="C625" t="inlineStr">
         <is>
-          <t>-1.2%</t>
+          <t>572.5</t>
         </is>
       </c>
       <c r="D625" t="inlineStr">
         <is>
-          <t>-6.6%</t>
+          <t>593.6</t>
         </is>
       </c>
       <c r="E625" t="inlineStr"/>
@@ -18677,13 +18669,13 @@
       </c>
       <c r="B626" t="inlineStr">
         <is>
-          <t>MBA Mortgage ApplicationsFEB/21</t>
+          <t>MBA Mortgage Market IndexFEB/21</t>
         </is>
       </c>
       <c r="C626" t="inlineStr"/>
       <c r="D626" t="inlineStr">
         <is>
-          <t>-6.6%</t>
+          <t>214.9</t>
         </is>
       </c>
       <c r="E626" t="inlineStr"/>
@@ -18700,19 +18692,23 @@
       </c>
       <c r="B627" t="inlineStr">
         <is>
-          <t>MBA Mortgage Refinance IndexFEB/21</t>
-        </is>
-      </c>
-      <c r="C627" t="inlineStr"/>
+          <t>MBA 30-Year Mortgage RateFEB/21</t>
+        </is>
+      </c>
+      <c r="C627" t="inlineStr">
+        <is>
+          <t>6.88%</t>
+        </is>
+      </c>
       <c r="D627" t="inlineStr">
         <is>
-          <t>593.6</t>
+          <t>6.93%</t>
         </is>
       </c>
       <c r="E627" t="inlineStr"/>
       <c r="F627" t="inlineStr"/>
       <c r="G627" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="628">
@@ -18723,19 +18719,23 @@
       </c>
       <c r="B628" t="inlineStr">
         <is>
-          <t>MBA 30-Year Mortgage RateFEB/21</t>
-        </is>
-      </c>
-      <c r="C628" t="inlineStr"/>
+          <t>MBA Mortgage Market IndexFEB/21</t>
+        </is>
+      </c>
+      <c r="C628" t="inlineStr">
+        <is>
+          <t>212.3</t>
+        </is>
+      </c>
       <c r="D628" t="inlineStr">
         <is>
-          <t>6.93%</t>
+          <t>214.9</t>
         </is>
       </c>
       <c r="E628" t="inlineStr"/>
       <c r="F628" t="inlineStr"/>
       <c r="G628" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="629">
@@ -18908,14 +18908,10 @@
           <t>New Home SalesJAN</t>
         </is>
       </c>
-      <c r="C634" t="inlineStr">
-        <is>
-          <t>0.657M</t>
-        </is>
-      </c>
+      <c r="C634" t="inlineStr"/>
       <c r="D634" t="inlineStr">
         <is>
-          <t>0.734M</t>
+          <t>0.698M</t>
         </is>
       </c>
       <c r="E634" t="inlineStr">
@@ -18943,14 +18939,10 @@
           <t>New Home Sales MoMJAN</t>
         </is>
       </c>
-      <c r="C635" t="inlineStr">
-        <is>
-          <t>-10.5%</t>
-        </is>
-      </c>
+      <c r="C635" t="inlineStr"/>
       <c r="D635" t="inlineStr">
         <is>
-          <t>8.1%</t>
+          <t>3.6%</t>
         </is>
       </c>
       <c r="E635" t="inlineStr"/>
@@ -18974,10 +18966,14 @@
           <t>New Home Sales MoMJAN</t>
         </is>
       </c>
-      <c r="C636" t="inlineStr"/>
+      <c r="C636" t="inlineStr">
+        <is>
+          <t>-10.5%</t>
+        </is>
+      </c>
       <c r="D636" t="inlineStr">
         <is>
-          <t>3.6%</t>
+          <t>8.1%</t>
         </is>
       </c>
       <c r="E636" t="inlineStr"/>
@@ -19001,10 +18997,14 @@
           <t>New Home SalesJAN</t>
         </is>
       </c>
-      <c r="C637" t="inlineStr"/>
+      <c r="C637" t="inlineStr">
+        <is>
+          <t>0.657M</t>
+        </is>
+      </c>
       <c r="D637" t="inlineStr">
         <is>
-          <t>0.698M</t>
+          <t>0.734M</t>
         </is>
       </c>
       <c r="E637" t="inlineStr">
@@ -19029,19 +19029,27 @@
       </c>
       <c r="B638" t="inlineStr">
         <is>
-          <t>EIA Cushing Crude Oil Stocks ChangeFEB/21</t>
-        </is>
-      </c>
-      <c r="C638" t="inlineStr"/>
+          <t>EIA Gasoline Stocks ChangeFEB/21</t>
+        </is>
+      </c>
+      <c r="C638" t="inlineStr">
+        <is>
+          <t>0.369M</t>
+        </is>
+      </c>
       <c r="D638" t="inlineStr">
         <is>
-          <t>1.472M</t>
-        </is>
-      </c>
-      <c r="E638" t="inlineStr"/>
+          <t>-0.151M</t>
+        </is>
+      </c>
+      <c r="E638" t="inlineStr">
+        <is>
+          <t>-1.30M</t>
+        </is>
+      </c>
       <c r="F638" t="inlineStr"/>
       <c r="G638" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="639">
@@ -19052,23 +19060,23 @@
       </c>
       <c r="B639" t="inlineStr">
         <is>
-          <t>EIA Gasoline Stocks ChangeFEB/21</t>
-        </is>
-      </c>
-      <c r="C639" t="inlineStr"/>
+          <t>EIA Crude Oil Imports ChangeFEB/21</t>
+        </is>
+      </c>
+      <c r="C639" t="inlineStr">
+        <is>
+          <t>0.292M</t>
+        </is>
+      </c>
       <c r="D639" t="inlineStr">
         <is>
-          <t>-0.151M</t>
-        </is>
-      </c>
-      <c r="E639" t="inlineStr">
-        <is>
-          <t>-1.30M</t>
-        </is>
-      </c>
+          <t>-0.961M</t>
+        </is>
+      </c>
+      <c r="E639" t="inlineStr"/>
       <c r="F639" t="inlineStr"/>
       <c r="G639" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="640">
@@ -19079,23 +19087,23 @@
       </c>
       <c r="B640" t="inlineStr">
         <is>
-          <t>EIA Crude Oil Stocks ChangeFEB/21</t>
-        </is>
-      </c>
-      <c r="C640" t="inlineStr"/>
+          <t>EIA Cushing Crude Oil Stocks ChangeFEB/21</t>
+        </is>
+      </c>
+      <c r="C640" t="inlineStr">
+        <is>
+          <t>1.282M</t>
+        </is>
+      </c>
       <c r="D640" t="inlineStr">
         <is>
-          <t>4.633M</t>
-        </is>
-      </c>
-      <c r="E640" t="inlineStr">
-        <is>
-          <t>2.34M</t>
-        </is>
-      </c>
+          <t>1.472M</t>
+        </is>
+      </c>
+      <c r="E640" t="inlineStr"/>
       <c r="F640" t="inlineStr"/>
       <c r="G640" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="641">
@@ -19106,27 +19114,23 @@
       </c>
       <c r="B641" t="inlineStr">
         <is>
-          <t>EIA Crude Oil Stocks ChangeFEB/21</t>
+          <t>EIA Distillate Fuel Production ChangeFEB/21</t>
         </is>
       </c>
       <c r="C641" t="inlineStr">
         <is>
-          <t>-2.332M</t>
+          <t>0.439M</t>
         </is>
       </c>
       <c r="D641" t="inlineStr">
         <is>
-          <t>4.633M</t>
-        </is>
-      </c>
-      <c r="E641" t="inlineStr">
-        <is>
-          <t>2.54M</t>
-        </is>
-      </c>
+          <t>0.18M</t>
+        </is>
+      </c>
+      <c r="E641" t="inlineStr"/>
       <c r="F641" t="inlineStr"/>
       <c r="G641" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="642">
@@ -19140,7 +19144,11 @@
           <t>EIA Distillate Stocks ChangeFEB/21</t>
         </is>
       </c>
-      <c r="C642" t="inlineStr"/>
+      <c r="C642" t="inlineStr">
+        <is>
+          <t>3.908M</t>
+        </is>
+      </c>
       <c r="D642" t="inlineStr">
         <is>
           <t>-2.051M</t>
@@ -19167,7 +19175,11 @@
           <t>EIA Gasoline Production ChangeFEB/21</t>
         </is>
       </c>
-      <c r="C643" t="inlineStr"/>
+      <c r="C643" t="inlineStr">
+        <is>
+          <t>-0.02M</t>
+        </is>
+      </c>
       <c r="D643" t="inlineStr">
         <is>
           <t>-0.156M</t>
@@ -19190,7 +19202,11 @@
           <t>EIA Heating Oil Stocks ChangeFEB/21</t>
         </is>
       </c>
-      <c r="C644" t="inlineStr"/>
+      <c r="C644" t="inlineStr">
+        <is>
+          <t>0.134M</t>
+        </is>
+      </c>
       <c r="D644" t="inlineStr">
         <is>
           <t>-0.343M</t>
@@ -19213,7 +19229,11 @@
           <t>EIA Refinery Crude Runs ChangeFEB/21</t>
         </is>
       </c>
-      <c r="C645" t="inlineStr"/>
+      <c r="C645" t="inlineStr">
+        <is>
+          <t>0.317M</t>
+        </is>
+      </c>
       <c r="D645" t="inlineStr">
         <is>
           <t>-0.015M</t>
@@ -19233,13 +19253,13 @@
       </c>
       <c r="B646" t="inlineStr">
         <is>
-          <t>EIA Distillate Fuel Production ChangeFEB/21</t>
+          <t>EIA Crude Oil Imports ChangeFEB/21</t>
         </is>
       </c>
       <c r="C646" t="inlineStr"/>
       <c r="D646" t="inlineStr">
         <is>
-          <t>0.18M</t>
+          <t>-0.961M</t>
         </is>
       </c>
       <c r="E646" t="inlineStr"/>
@@ -19259,11 +19279,7 @@
           <t>EIA Refinery Crude Runs ChangeFEB/21</t>
         </is>
       </c>
-      <c r="C647" t="inlineStr">
-        <is>
-          <t>0.317M</t>
-        </is>
-      </c>
+      <c r="C647" t="inlineStr"/>
       <c r="D647" t="inlineStr">
         <is>
           <t>-0.015M</t>
@@ -19286,11 +19302,7 @@
           <t>EIA Heating Oil Stocks ChangeFEB/21</t>
         </is>
       </c>
-      <c r="C648" t="inlineStr">
-        <is>
-          <t>0.134M</t>
-        </is>
-      </c>
+      <c r="C648" t="inlineStr"/>
       <c r="D648" t="inlineStr">
         <is>
           <t>-0.343M</t>
@@ -19313,11 +19325,7 @@
           <t>EIA Gasoline Production ChangeFEB/21</t>
         </is>
       </c>
-      <c r="C649" t="inlineStr">
-        <is>
-          <t>-0.02M</t>
-        </is>
-      </c>
+      <c r="C649" t="inlineStr"/>
       <c r="D649" t="inlineStr">
         <is>
           <t>-0.156M</t>
@@ -19340,11 +19348,7 @@
           <t>EIA Distillate Stocks ChangeFEB/21</t>
         </is>
       </c>
-      <c r="C650" t="inlineStr">
-        <is>
-          <t>3.908M</t>
-        </is>
-      </c>
+      <c r="C650" t="inlineStr"/>
       <c r="D650" t="inlineStr">
         <is>
           <t>-2.051M</t>
@@ -19368,19 +19372,27 @@
       </c>
       <c r="B651" t="inlineStr">
         <is>
-          <t>EIA Crude Oil Imports ChangeFEB/21</t>
-        </is>
-      </c>
-      <c r="C651" t="inlineStr"/>
+          <t>EIA Crude Oil Stocks ChangeFEB/21</t>
+        </is>
+      </c>
+      <c r="C651" t="inlineStr">
+        <is>
+          <t>-2.332M</t>
+        </is>
+      </c>
       <c r="D651" t="inlineStr">
         <is>
-          <t>-0.961M</t>
-        </is>
-      </c>
-      <c r="E651" t="inlineStr"/>
+          <t>4.633M</t>
+        </is>
+      </c>
+      <c r="E651" t="inlineStr">
+        <is>
+          <t>2.54M</t>
+        </is>
+      </c>
       <c r="F651" t="inlineStr"/>
       <c r="G651" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="652">
@@ -19391,23 +19403,23 @@
       </c>
       <c r="B652" t="inlineStr">
         <is>
-          <t>EIA Cushing Crude Oil Stocks ChangeFEB/21</t>
-        </is>
-      </c>
-      <c r="C652" t="inlineStr">
-        <is>
-          <t>1.282M</t>
-        </is>
-      </c>
+          <t>EIA Crude Oil Stocks ChangeFEB/21</t>
+        </is>
+      </c>
+      <c r="C652" t="inlineStr"/>
       <c r="D652" t="inlineStr">
         <is>
-          <t>1.472M</t>
-        </is>
-      </c>
-      <c r="E652" t="inlineStr"/>
+          <t>4.633M</t>
+        </is>
+      </c>
+      <c r="E652" t="inlineStr">
+        <is>
+          <t>2.34M</t>
+        </is>
+      </c>
       <c r="F652" t="inlineStr"/>
       <c r="G652" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="653">
@@ -19418,23 +19430,23 @@
       </c>
       <c r="B653" t="inlineStr">
         <is>
-          <t>EIA Crude Oil Imports ChangeFEB/21</t>
-        </is>
-      </c>
-      <c r="C653" t="inlineStr">
-        <is>
-          <t>0.292M</t>
-        </is>
-      </c>
+          <t>EIA Gasoline Stocks ChangeFEB/21</t>
+        </is>
+      </c>
+      <c r="C653" t="inlineStr"/>
       <c r="D653" t="inlineStr">
         <is>
-          <t>-0.961M</t>
-        </is>
-      </c>
-      <c r="E653" t="inlineStr"/>
+          <t>-0.151M</t>
+        </is>
+      </c>
+      <c r="E653" t="inlineStr">
+        <is>
+          <t>-1.30M</t>
+        </is>
+      </c>
       <c r="F653" t="inlineStr"/>
       <c r="G653" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="654">
@@ -19445,27 +19457,19 @@
       </c>
       <c r="B654" t="inlineStr">
         <is>
-          <t>EIA Gasoline Stocks ChangeFEB/21</t>
-        </is>
-      </c>
-      <c r="C654" t="inlineStr">
-        <is>
-          <t>0.369M</t>
-        </is>
-      </c>
+          <t>EIA Cushing Crude Oil Stocks ChangeFEB/21</t>
+        </is>
+      </c>
+      <c r="C654" t="inlineStr"/>
       <c r="D654" t="inlineStr">
         <is>
-          <t>-0.151M</t>
-        </is>
-      </c>
-      <c r="E654" t="inlineStr">
-        <is>
-          <t>-1.30M</t>
-        </is>
-      </c>
+          <t>1.472M</t>
+        </is>
+      </c>
+      <c r="E654" t="inlineStr"/>
       <c r="F654" t="inlineStr"/>
       <c r="G654" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="655">
@@ -19479,11 +19483,7 @@
           <t>EIA Distillate Fuel Production ChangeFEB/21</t>
         </is>
       </c>
-      <c r="C655" t="inlineStr">
-        <is>
-          <t>0.439M</t>
-        </is>
-      </c>
+      <c r="C655" t="inlineStr"/>
       <c r="D655" t="inlineStr">
         <is>
           <t>0.18M</t>
@@ -19622,25 +19622,21 @@
       </c>
       <c r="B661" t="inlineStr">
         <is>
-          <t>Building Permits FinalJAN</t>
-        </is>
-      </c>
-      <c r="C661" t="inlineStr"/>
+          <t>7-Year Note Auction</t>
+        </is>
+      </c>
+      <c r="C661" t="inlineStr">
+        <is>
+          <t>4.194%</t>
+        </is>
+      </c>
       <c r="D661" t="inlineStr">
         <is>
-          <t>1.482M</t>
-        </is>
-      </c>
-      <c r="E661" t="inlineStr">
-        <is>
-          <t>1.483M</t>
-        </is>
-      </c>
-      <c r="F661" t="inlineStr">
-        <is>
-          <t>1.483M</t>
-        </is>
-      </c>
+          <t>4.457%</t>
+        </is>
+      </c>
+      <c r="E661" t="inlineStr"/>
+      <c r="F661" t="inlineStr"/>
       <c r="G661" t="n">
         <v>3</v>
       </c>
@@ -19653,25 +19649,17 @@
       </c>
       <c r="B662" t="inlineStr">
         <is>
-          <t>Building Permits MoM FinalJAN</t>
+          <t>7-Year Note Auction</t>
         </is>
       </c>
       <c r="C662" t="inlineStr"/>
       <c r="D662" t="inlineStr">
         <is>
-          <t>-0.7%</t>
-        </is>
-      </c>
-      <c r="E662" t="inlineStr">
-        <is>
-          <t>0.1%</t>
-        </is>
-      </c>
-      <c r="F662" t="inlineStr">
-        <is>
-          <t>0.1%</t>
-        </is>
-      </c>
+          <t>4.457%</t>
+        </is>
+      </c>
+      <c r="E662" t="inlineStr"/>
+      <c r="F662" t="inlineStr"/>
       <c r="G662" t="n">
         <v>3</v>
       </c>
@@ -19684,17 +19672,25 @@
       </c>
       <c r="B663" t="inlineStr">
         <is>
-          <t>7-Year Note Auction</t>
+          <t>Building Permits MoM FinalJAN</t>
         </is>
       </c>
       <c r="C663" t="inlineStr"/>
       <c r="D663" t="inlineStr">
         <is>
-          <t>4.457%</t>
-        </is>
-      </c>
-      <c r="E663" t="inlineStr"/>
-      <c r="F663" t="inlineStr"/>
+          <t>-0.7%</t>
+        </is>
+      </c>
+      <c r="E663" t="inlineStr">
+        <is>
+          <t>0.1%</t>
+        </is>
+      </c>
+      <c r="F663" t="inlineStr">
+        <is>
+          <t>0.1%</t>
+        </is>
+      </c>
       <c r="G663" t="n">
         <v>3</v>
       </c>
@@ -19707,21 +19703,25 @@
       </c>
       <c r="B664" t="inlineStr">
         <is>
-          <t>7-Year Note Auction</t>
-        </is>
-      </c>
-      <c r="C664" t="inlineStr">
-        <is>
-          <t>4.194%</t>
-        </is>
-      </c>
+          <t>Building Permits FinalJAN</t>
+        </is>
+      </c>
+      <c r="C664" t="inlineStr"/>
       <c r="D664" t="inlineStr">
         <is>
-          <t>4.457%</t>
-        </is>
-      </c>
-      <c r="E664" t="inlineStr"/>
-      <c r="F664" t="inlineStr"/>
+          <t>1.482M</t>
+        </is>
+      </c>
+      <c r="E664" t="inlineStr">
+        <is>
+          <t>1.483M</t>
+        </is>
+      </c>
+      <c r="F664" t="inlineStr">
+        <is>
+          <t>1.483M</t>
+        </is>
+      </c>
       <c r="G664" t="n">
         <v>3</v>
       </c>
@@ -20181,23 +20181,23 @@
       </c>
       <c r="B678" t="inlineStr">
         <is>
-          <t>PCE Prices QoQ 2nd EstQ4</t>
+          <t>Real Consumer Spending QoQ 2nd EstQ4</t>
         </is>
       </c>
       <c r="C678" t="inlineStr"/>
       <c r="D678" t="inlineStr">
         <is>
-          <t>1.5%</t>
+          <t>3.7%</t>
         </is>
       </c>
       <c r="E678" t="inlineStr">
         <is>
-          <t>2.3%</t>
+          <t>4.2%</t>
         </is>
       </c>
       <c r="F678" t="inlineStr">
         <is>
-          <t>2.3%</t>
+          <t>4.2%</t>
         </is>
       </c>
       <c r="G678" t="n">
@@ -20239,27 +20239,27 @@
       </c>
       <c r="B680" t="inlineStr">
         <is>
-          <t>GDP Price Index QoQ 2nd EstQ4</t>
+          <t>PCE Prices QoQ 2nd EstQ4</t>
         </is>
       </c>
       <c r="C680" t="inlineStr"/>
       <c r="D680" t="inlineStr">
         <is>
-          <t>1.9%</t>
+          <t>1.5%</t>
         </is>
       </c>
       <c r="E680" t="inlineStr">
         <is>
-          <t>2.2%</t>
+          <t>2.3%</t>
         </is>
       </c>
       <c r="F680" t="inlineStr">
         <is>
-          <t>2.2%</t>
+          <t>2.3%</t>
         </is>
       </c>
       <c r="G680" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="681">
@@ -20270,27 +20270,27 @@
       </c>
       <c r="B681" t="inlineStr">
         <is>
-          <t>GDP Growth Rate QoQ 2nd EstQ4</t>
+          <t>GDP Price Index QoQ 2nd EstQ4</t>
         </is>
       </c>
       <c r="C681" t="inlineStr"/>
       <c r="D681" t="inlineStr">
         <is>
-          <t>3.1%</t>
+          <t>1.9%</t>
         </is>
       </c>
       <c r="E681" t="inlineStr">
         <is>
-          <t>2.3%</t>
+          <t>2.2%</t>
         </is>
       </c>
       <c r="F681" t="inlineStr">
         <is>
-          <t>2.3%</t>
+          <t>2.2%</t>
         </is>
       </c>
       <c r="G681" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="682">
@@ -20301,27 +20301,27 @@
       </c>
       <c r="B682" t="inlineStr">
         <is>
-          <t>Initial Jobless ClaimsFEB/22</t>
+          <t>GDP Growth Rate QoQ 2nd EstQ4</t>
         </is>
       </c>
       <c r="C682" t="inlineStr"/>
       <c r="D682" t="inlineStr">
         <is>
-          <t>219K</t>
+          <t>3.1%</t>
         </is>
       </c>
       <c r="E682" t="inlineStr">
         <is>
-          <t>221K</t>
+          <t>2.3%</t>
         </is>
       </c>
       <c r="F682" t="inlineStr">
         <is>
-          <t>225.0K</t>
+          <t>2.3%</t>
         </is>
       </c>
       <c r="G682" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="683">
@@ -20332,23 +20332,23 @@
       </c>
       <c r="B683" t="inlineStr">
         <is>
-          <t>Durable Goods Orders Ex Transp MoMJAN</t>
+          <t>Initial Jobless ClaimsFEB/22</t>
         </is>
       </c>
       <c r="C683" t="inlineStr"/>
       <c r="D683" t="inlineStr">
         <is>
-          <t>0.3%</t>
+          <t>219K</t>
         </is>
       </c>
       <c r="E683" t="inlineStr">
         <is>
-          <t>0.3%</t>
+          <t>221K</t>
         </is>
       </c>
       <c r="F683" t="inlineStr">
         <is>
-          <t>0.3%</t>
+          <t>225.0K</t>
         </is>
       </c>
       <c r="G683" t="n">
@@ -20363,13 +20363,13 @@
       </c>
       <c r="B684" t="inlineStr">
         <is>
-          <t>Non Defense Goods Orders Ex AirJAN</t>
+          <t>Durable Goods Orders Ex Transp MoMJAN</t>
         </is>
       </c>
       <c r="C684" t="inlineStr"/>
       <c r="D684" t="inlineStr">
         <is>
-          <t>0.5%</t>
+          <t>0.3%</t>
         </is>
       </c>
       <c r="E684" t="inlineStr">
@@ -20379,11 +20379,11 @@
       </c>
       <c r="F684" t="inlineStr">
         <is>
-          <t>0.4%</t>
+          <t>0.3%</t>
         </is>
       </c>
       <c r="G684" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="685">
@@ -20394,19 +20394,23 @@
       </c>
       <c r="B685" t="inlineStr">
         <is>
-          <t>Jobless Claims 4-week AverageFEB/22</t>
+          <t>Non Defense Goods Orders Ex AirJAN</t>
         </is>
       </c>
       <c r="C685" t="inlineStr"/>
       <c r="D685" t="inlineStr">
         <is>
-          <t>215.25K</t>
-        </is>
-      </c>
-      <c r="E685" t="inlineStr"/>
+          <t>0.5%</t>
+        </is>
+      </c>
+      <c r="E685" t="inlineStr">
+        <is>
+          <t>0.3%</t>
+        </is>
+      </c>
       <c r="F685" t="inlineStr">
         <is>
-          <t>220.0K</t>
+          <t>0.4%</t>
         </is>
       </c>
       <c r="G685" t="n">
@@ -20421,27 +20425,23 @@
       </c>
       <c r="B686" t="inlineStr">
         <is>
-          <t>Durable Goods Orders MoMJAN</t>
+          <t>Jobless Claims 4-week AverageFEB/22</t>
         </is>
       </c>
       <c r="C686" t="inlineStr"/>
       <c r="D686" t="inlineStr">
         <is>
-          <t>-2.2%</t>
-        </is>
-      </c>
-      <c r="E686" t="inlineStr">
-        <is>
-          <t>2%</t>
-        </is>
-      </c>
+          <t>215.25K</t>
+        </is>
+      </c>
+      <c r="E686" t="inlineStr"/>
       <c r="F686" t="inlineStr">
         <is>
-          <t>2.2%</t>
+          <t>220.0K</t>
         </is>
       </c>
       <c r="G686" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="687">
@@ -20452,27 +20452,27 @@
       </c>
       <c r="B687" t="inlineStr">
         <is>
-          <t>Real Consumer Spending QoQ 2nd EstQ4</t>
+          <t>Durable Goods Orders MoMJAN</t>
         </is>
       </c>
       <c r="C687" t="inlineStr"/>
       <c r="D687" t="inlineStr">
         <is>
-          <t>3.7%</t>
+          <t>-2.2%</t>
         </is>
       </c>
       <c r="E687" t="inlineStr">
         <is>
-          <t>4.2%</t>
+          <t>2%</t>
         </is>
       </c>
       <c r="F687" t="inlineStr">
         <is>
-          <t>4.2%</t>
+          <t>2.2%</t>
         </is>
       </c>
       <c r="G687" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="688">
@@ -20787,7 +20787,7 @@
       </c>
       <c r="E699" t="inlineStr">
         <is>
-          <t>-276Bcf</t>
+          <t>-265Bcf</t>
         </is>
       </c>
       <c r="F699" t="inlineStr"/>
@@ -21110,13 +21110,13 @@
       </c>
       <c r="B713" t="inlineStr">
         <is>
-          <t>15-Year Mortgage RateFEB/27</t>
+          <t>30-Year Mortgage RateFEB/27</t>
         </is>
       </c>
       <c r="C713" t="inlineStr"/>
       <c r="D713" t="inlineStr">
         <is>
-          <t>6.04%</t>
+          <t>6.85%</t>
         </is>
       </c>
       <c r="E713" t="inlineStr"/>
@@ -21133,13 +21133,13 @@
       </c>
       <c r="B714" t="inlineStr">
         <is>
-          <t>30-Year Mortgage RateFEB/27</t>
+          <t>15-Year Mortgage RateFEB/27</t>
         </is>
       </c>
       <c r="C714" t="inlineStr"/>
       <c r="D714" t="inlineStr">
         <is>
-          <t>6.85%</t>
+          <t>6.04%</t>
         </is>
       </c>
       <c r="E714" t="inlineStr"/>
@@ -21560,27 +21560,27 @@
       </c>
       <c r="B731" t="inlineStr">
         <is>
-          <t>PCE Price Index YoYJAN</t>
+          <t>Personal Spending MoMJAN</t>
         </is>
       </c>
       <c r="C731" t="inlineStr"/>
       <c r="D731" t="inlineStr">
         <is>
-          <t>2.6%</t>
+          <t>0.7%</t>
         </is>
       </c>
       <c r="E731" t="inlineStr">
         <is>
-          <t>2.5%</t>
+          <t>0.1%</t>
         </is>
       </c>
       <c r="F731" t="inlineStr">
         <is>
-          <t>2.5%</t>
+          <t>0.3%</t>
         </is>
       </c>
       <c r="G731" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="732">
@@ -21622,27 +21622,27 @@
       </c>
       <c r="B733" t="inlineStr">
         <is>
-          <t>Personal Spending MoMJAN</t>
+          <t>PCE Price Index YoYJAN</t>
         </is>
       </c>
       <c r="C733" t="inlineStr"/>
       <c r="D733" t="inlineStr">
         <is>
-          <t>0.7%</t>
+          <t>2.6%</t>
         </is>
       </c>
       <c r="E733" t="inlineStr">
         <is>
-          <t>0.1%</t>
+          <t>2.5%</t>
         </is>
       </c>
       <c r="F733" t="inlineStr">
         <is>
-          <t>0.3%</t>
+          <t>2.5%</t>
         </is>
       </c>
       <c r="G733" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="734">
@@ -21711,23 +21711,23 @@
       </c>
       <c r="B736" t="inlineStr">
         <is>
-          <t>Personal Income MoMJAN</t>
+          <t>Core PCE Price Index MoMJAN</t>
         </is>
       </c>
       <c r="C736" t="inlineStr"/>
       <c r="D736" t="inlineStr">
         <is>
+          <t>0.2%</t>
+        </is>
+      </c>
+      <c r="E736" t="inlineStr">
+        <is>
+          <t>0.3%</t>
+        </is>
+      </c>
+      <c r="F736" t="inlineStr">
+        <is>
           <t>0.4%</t>
-        </is>
-      </c>
-      <c r="E736" t="inlineStr">
-        <is>
-          <t>0.3%</t>
-        </is>
-      </c>
-      <c r="F736" t="inlineStr">
-        <is>
-          <t>0.3%</t>
         </is>
       </c>
       <c r="G736" t="n">
@@ -21742,23 +21742,23 @@
       </c>
       <c r="B737" t="inlineStr">
         <is>
-          <t>PCE Price Index MoMJAN</t>
+          <t>Wholesale Inventories MoM AdvJAN</t>
         </is>
       </c>
       <c r="C737" t="inlineStr"/>
       <c r="D737" t="inlineStr">
         <is>
-          <t>0.3%</t>
+          <t>-0.5%</t>
         </is>
       </c>
       <c r="E737" t="inlineStr">
         <is>
-          <t>0.3%</t>
+          <t>0.1%</t>
         </is>
       </c>
       <c r="F737" t="inlineStr">
         <is>
-          <t>0.4%</t>
+          <t>0.2%</t>
         </is>
       </c>
       <c r="G737" t="n">
@@ -21773,27 +21773,27 @@
       </c>
       <c r="B738" t="inlineStr">
         <is>
-          <t>Core PCE Price Index MoMJAN</t>
+          <t>Goods Trade Balance AdvJAN</t>
         </is>
       </c>
       <c r="C738" t="inlineStr"/>
       <c r="D738" t="inlineStr">
         <is>
-          <t>0.2%</t>
+          <t>$-122.11B</t>
         </is>
       </c>
       <c r="E738" t="inlineStr">
         <is>
-          <t>0.3%</t>
+          <t>$-114.7B</t>
         </is>
       </c>
       <c r="F738" t="inlineStr">
         <is>
-          <t>0.4%</t>
+          <t>$ -116.0B</t>
         </is>
       </c>
       <c r="G738" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="739">
@@ -21804,23 +21804,23 @@
       </c>
       <c r="B739" t="inlineStr">
         <is>
-          <t>Wholesale Inventories MoM AdvJAN</t>
+          <t>PCE Price Index MoMJAN</t>
         </is>
       </c>
       <c r="C739" t="inlineStr"/>
       <c r="D739" t="inlineStr">
         <is>
-          <t>-0.5%</t>
+          <t>0.3%</t>
         </is>
       </c>
       <c r="E739" t="inlineStr">
         <is>
-          <t>0.1%</t>
+          <t>0.3%</t>
         </is>
       </c>
       <c r="F739" t="inlineStr">
         <is>
-          <t>0.2%</t>
+          <t>0.4%</t>
         </is>
       </c>
       <c r="G739" t="n">
@@ -21835,27 +21835,27 @@
       </c>
       <c r="B740" t="inlineStr">
         <is>
-          <t>Goods Trade Balance AdvJAN</t>
+          <t>Personal Income MoMJAN</t>
         </is>
       </c>
       <c r="C740" t="inlineStr"/>
       <c r="D740" t="inlineStr">
         <is>
-          <t>$-122.11B</t>
+          <t>0.4%</t>
         </is>
       </c>
       <c r="E740" t="inlineStr">
         <is>
-          <t>$-114.7B</t>
+          <t>0.3%</t>
         </is>
       </c>
       <c r="F740" t="inlineStr">
         <is>
-          <t>$ -116.0B</t>
+          <t>0.3%</t>
         </is>
       </c>
       <c r="G740" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="741">
@@ -22217,23 +22217,23 @@
       </c>
       <c r="B754" t="inlineStr">
         <is>
-          <t>ISM Manufacturing New OrdersFEB</t>
+          <t>ISM Manufacturing PMIFEB</t>
         </is>
       </c>
       <c r="C754" t="inlineStr"/>
       <c r="D754" t="inlineStr">
         <is>
-          <t>55.1</t>
+          <t>50.9</t>
         </is>
       </c>
       <c r="E754" t="inlineStr"/>
       <c r="F754" t="inlineStr">
         <is>
-          <t>55.4</t>
+          <t>51</t>
         </is>
       </c>
       <c r="G754" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="755">
@@ -22271,23 +22271,23 @@
       </c>
       <c r="B756" t="inlineStr">
         <is>
-          <t>ISM Manufacturing PMIFEB</t>
+          <t>ISM Manufacturing New OrdersFEB</t>
         </is>
       </c>
       <c r="C756" t="inlineStr"/>
       <c r="D756" t="inlineStr">
         <is>
-          <t>50.9</t>
+          <t>55.1</t>
         </is>
       </c>
       <c r="E756" t="inlineStr"/>
       <c r="F756" t="inlineStr">
         <is>
-          <t>51</t>
+          <t>55.4</t>
         </is>
       </c>
       <c r="G756" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="757">
@@ -23306,23 +23306,23 @@
       </c>
       <c r="B797" t="inlineStr">
         <is>
-          <t>ISM Services PMIFEB</t>
+          <t>ISM Services EmploymentFEB</t>
         </is>
       </c>
       <c r="C797" t="inlineStr"/>
       <c r="D797" t="inlineStr">
         <is>
-          <t>52.8</t>
+          <t>52.3</t>
         </is>
       </c>
       <c r="E797" t="inlineStr"/>
       <c r="F797" t="inlineStr">
         <is>
-          <t>52.7</t>
+          <t>52.1</t>
         </is>
       </c>
       <c r="G797" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="798">
@@ -23333,19 +23333,19 @@
       </c>
       <c r="B798" t="inlineStr">
         <is>
-          <t>Factory Orders ex TransportationJAN</t>
+          <t>ISM Services New OrdersFEB</t>
         </is>
       </c>
       <c r="C798" t="inlineStr"/>
       <c r="D798" t="inlineStr">
         <is>
-          <t>0.2%</t>
+          <t>51.3</t>
         </is>
       </c>
       <c r="E798" t="inlineStr"/>
       <c r="F798" t="inlineStr">
         <is>
-          <t>0.3%</t>
+          <t>51.2</t>
         </is>
       </c>
       <c r="G798" t="n">
@@ -23360,19 +23360,19 @@
       </c>
       <c r="B799" t="inlineStr">
         <is>
-          <t>ISM Services Business ActivityFEB</t>
+          <t>ISM Services PricesFEB</t>
         </is>
       </c>
       <c r="C799" t="inlineStr"/>
       <c r="D799" t="inlineStr">
         <is>
-          <t>54.5</t>
+          <t>60.4</t>
         </is>
       </c>
       <c r="E799" t="inlineStr"/>
       <c r="F799" t="inlineStr">
         <is>
-          <t>54.2</t>
+          <t>60.6</t>
         </is>
       </c>
       <c r="G799" t="n">
@@ -23387,19 +23387,19 @@
       </c>
       <c r="B800" t="inlineStr">
         <is>
-          <t>ISM Services PricesFEB</t>
+          <t>ISM Services Business ActivityFEB</t>
         </is>
       </c>
       <c r="C800" t="inlineStr"/>
       <c r="D800" t="inlineStr">
         <is>
-          <t>60.4</t>
+          <t>54.5</t>
         </is>
       </c>
       <c r="E800" t="inlineStr"/>
       <c r="F800" t="inlineStr">
         <is>
-          <t>60.6</t>
+          <t>54.2</t>
         </is>
       </c>
       <c r="G800" t="n">
@@ -23414,19 +23414,19 @@
       </c>
       <c r="B801" t="inlineStr">
         <is>
-          <t>ISM Services New OrdersFEB</t>
+          <t>Factory Orders ex TransportationJAN</t>
         </is>
       </c>
       <c r="C801" t="inlineStr"/>
       <c r="D801" t="inlineStr">
         <is>
-          <t>51.3</t>
+          <t>0.2%</t>
         </is>
       </c>
       <c r="E801" t="inlineStr"/>
       <c r="F801" t="inlineStr">
         <is>
-          <t>51.2</t>
+          <t>0.3%</t>
         </is>
       </c>
       <c r="G801" t="n">
@@ -23441,23 +23441,23 @@
       </c>
       <c r="B802" t="inlineStr">
         <is>
-          <t>ISM Services EmploymentFEB</t>
+          <t>ISM Services PMIFEB</t>
         </is>
       </c>
       <c r="C802" t="inlineStr"/>
       <c r="D802" t="inlineStr">
         <is>
-          <t>52.3</t>
+          <t>52.8</t>
         </is>
       </c>
       <c r="E802" t="inlineStr"/>
       <c r="F802" t="inlineStr">
         <is>
-          <t>52.1</t>
+          <t>52.7</t>
         </is>
       </c>
       <c r="G802" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="803">
@@ -23675,19 +23675,19 @@
       </c>
       <c r="B812" t="inlineStr">
         <is>
-          <t>EIA Gasoline Stocks ChangeFEB/28</t>
+          <t>EIA Refinery Crude Runs ChangeFEB/28</t>
         </is>
       </c>
       <c r="C812" t="inlineStr"/>
       <c r="D812" t="inlineStr">
         <is>
-          <t>0.369M</t>
+          <t>0.317M</t>
         </is>
       </c>
       <c r="E812" t="inlineStr"/>
       <c r="F812" t="inlineStr"/>
       <c r="G812" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="813">
@@ -23698,15 +23698,11 @@
       </c>
       <c r="B813" t="inlineStr">
         <is>
-          <t>EIA Refinery Crude Runs ChangeFEB/28</t>
+          <t>EIA Crude Oil Imports ChangeFEB/28</t>
         </is>
       </c>
       <c r="C813" t="inlineStr"/>
-      <c r="D813" t="inlineStr">
-        <is>
-          <t>0.317M</t>
-        </is>
-      </c>
+      <c r="D813" t="inlineStr"/>
       <c r="E813" t="inlineStr"/>
       <c r="F813" t="inlineStr"/>
       <c r="G813" t="n">
@@ -23786,15 +23782,19 @@
       </c>
       <c r="B817" t="inlineStr">
         <is>
-          <t>EIA Crude Oil Imports ChangeFEB/28</t>
+          <t>EIA Gasoline Stocks ChangeFEB/28</t>
         </is>
       </c>
       <c r="C817" t="inlineStr"/>
-      <c r="D817" t="inlineStr"/>
+      <c r="D817" t="inlineStr">
+        <is>
+          <t>0.369M</t>
+        </is>
+      </c>
       <c r="E817" t="inlineStr"/>
       <c r="F817" t="inlineStr"/>
       <c r="G817" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="818">
@@ -23828,19 +23828,19 @@
       </c>
       <c r="B819" t="inlineStr">
         <is>
-          <t>EIA Crude Oil Stocks ChangeFEB/28</t>
+          <t>EIA Heating Oil Stocks ChangeFEB/28</t>
         </is>
       </c>
       <c r="C819" t="inlineStr"/>
       <c r="D819" t="inlineStr">
         <is>
-          <t>-2.332M</t>
+          <t>0.134M</t>
         </is>
       </c>
       <c r="E819" t="inlineStr"/>
       <c r="F819" t="inlineStr"/>
       <c r="G819" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="820">
@@ -23851,19 +23851,19 @@
       </c>
       <c r="B820" t="inlineStr">
         <is>
-          <t>EIA Heating Oil Stocks ChangeFEB/28</t>
+          <t>EIA Crude Oil Stocks ChangeFEB/28</t>
         </is>
       </c>
       <c r="C820" t="inlineStr"/>
       <c r="D820" t="inlineStr">
         <is>
-          <t>0.134M</t>
+          <t>-2.332M</t>
         </is>
       </c>
       <c r="E820" t="inlineStr"/>
       <c r="F820" t="inlineStr"/>
       <c r="G820" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="821">
@@ -23920,13 +23920,13 @@
       </c>
       <c r="B823" t="inlineStr">
         <is>
-          <t>17-Week Bill Auction</t>
+          <t>Total Vehicle SalesFEB</t>
         </is>
       </c>
       <c r="C823" t="inlineStr"/>
       <c r="D823" t="inlineStr">
         <is>
-          <t>4.200%</t>
+          <t>15.6M</t>
         </is>
       </c>
       <c r="E823" t="inlineStr"/>
@@ -23943,13 +23943,13 @@
       </c>
       <c r="B824" t="inlineStr">
         <is>
-          <t>Total Vehicle SalesFEB</t>
+          <t>17-Week Bill Auction</t>
         </is>
       </c>
       <c r="C824" t="inlineStr"/>
       <c r="D824" t="inlineStr">
         <is>
-          <t>15.6M</t>
+          <t>4.200%</t>
         </is>
       </c>
       <c r="E824" t="inlineStr"/>
@@ -24373,19 +24373,19 @@
       </c>
       <c r="B842" t="inlineStr">
         <is>
-          <t>Balance of TradeJAN</t>
+          <t>ExportsJAN</t>
         </is>
       </c>
       <c r="C842" t="inlineStr"/>
       <c r="D842" t="inlineStr">
         <is>
-          <t>$-98.4B</t>
+          <t>$266.5B</t>
         </is>
       </c>
       <c r="E842" t="inlineStr"/>
       <c r="F842" t="inlineStr">
         <is>
-          <t>$-103B</t>
+          <t>$273.0B</t>
         </is>
       </c>
       <c r="G842" t="n">
@@ -24400,19 +24400,19 @@
       </c>
       <c r="B843" t="inlineStr">
         <is>
-          <t>ExportsJAN</t>
+          <t>ImportsJAN</t>
         </is>
       </c>
       <c r="C843" t="inlineStr"/>
       <c r="D843" t="inlineStr">
         <is>
-          <t>$266.5B</t>
+          <t>$364.9B</t>
         </is>
       </c>
       <c r="E843" t="inlineStr"/>
       <c r="F843" t="inlineStr">
         <is>
-          <t>$273.0B</t>
+          <t>$376.0B</t>
         </is>
       </c>
       <c r="G843" t="n">
@@ -24427,19 +24427,19 @@
       </c>
       <c r="B844" t="inlineStr">
         <is>
-          <t>ImportsJAN</t>
+          <t>Balance of TradeJAN</t>
         </is>
       </c>
       <c r="C844" t="inlineStr"/>
       <c r="D844" t="inlineStr">
         <is>
-          <t>$364.9B</t>
+          <t>$-98.4B</t>
         </is>
       </c>
       <c r="E844" t="inlineStr"/>
       <c r="F844" t="inlineStr">
         <is>
-          <t>$376.0B</t>
+          <t>$-103B</t>
         </is>
       </c>
       <c r="G844" t="n">
@@ -24568,7 +24568,7 @@
       </c>
       <c r="B851" t="inlineStr">
         <is>
-          <t>8-Week Bill Auction</t>
+          <t>4-Week Bill Auction</t>
         </is>
       </c>
       <c r="C851" t="inlineStr"/>
@@ -24587,7 +24587,7 @@
       </c>
       <c r="B852" t="inlineStr">
         <is>
-          <t>4-Week Bill Auction</t>
+          <t>8-Week Bill Auction</t>
         </is>
       </c>
       <c r="C852" t="inlineStr"/>
@@ -24882,23 +24882,23 @@
       </c>
       <c r="B865" t="inlineStr">
         <is>
-          <t>Non Farm PayrollsFEB</t>
+          <t>Average Hourly Earnings MoMFEB</t>
         </is>
       </c>
       <c r="C865" t="inlineStr"/>
       <c r="D865" t="inlineStr">
         <is>
-          <t>143K</t>
+          <t>0.5%</t>
         </is>
       </c>
       <c r="E865" t="inlineStr"/>
       <c r="F865" t="inlineStr">
         <is>
-          <t>180.0K</t>
+          <t>0.3%</t>
         </is>
       </c>
       <c r="G865" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="866">
@@ -24963,17 +24963,21 @@
       </c>
       <c r="B868" t="inlineStr">
         <is>
-          <t>Used Car Prices YoYFEB</t>
+          <t>U-6 Unemployment RateFEB</t>
         </is>
       </c>
       <c r="C868" t="inlineStr"/>
       <c r="D868" t="inlineStr">
         <is>
-          <t>0.8%</t>
+          <t>7.5%</t>
         </is>
       </c>
       <c r="E868" t="inlineStr"/>
-      <c r="F868" t="inlineStr"/>
+      <c r="F868" t="inlineStr">
+        <is>
+          <t>7.6%</t>
+        </is>
+      </c>
       <c r="G868" t="n">
         <v>3</v>
       </c>
@@ -24986,23 +24990,23 @@
       </c>
       <c r="B869" t="inlineStr">
         <is>
-          <t>Unemployment RateFEB</t>
+          <t>Average Hourly Earnings YoYFEB</t>
         </is>
       </c>
       <c r="C869" t="inlineStr"/>
       <c r="D869" t="inlineStr">
         <is>
-          <t>4%</t>
+          <t>4.1%</t>
         </is>
       </c>
       <c r="E869" t="inlineStr"/>
       <c r="F869" t="inlineStr">
         <is>
-          <t>4.0%</t>
+          <t>4.1%</t>
         </is>
       </c>
       <c r="G869" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="870">
@@ -25090,23 +25094,23 @@
       </c>
       <c r="B873" t="inlineStr">
         <is>
-          <t>Average Hourly Earnings YoYFEB</t>
+          <t>Unemployment RateFEB</t>
         </is>
       </c>
       <c r="C873" t="inlineStr"/>
       <c r="D873" t="inlineStr">
         <is>
-          <t>4.1%</t>
+          <t>4%</t>
         </is>
       </c>
       <c r="E873" t="inlineStr"/>
       <c r="F873" t="inlineStr">
         <is>
-          <t>4.1%</t>
+          <t>4.0%</t>
         </is>
       </c>
       <c r="G873" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="874">
@@ -25117,23 +25121,23 @@
       </c>
       <c r="B874" t="inlineStr">
         <is>
-          <t>U-6 Unemployment RateFEB</t>
+          <t>Non Farm PayrollsFEB</t>
         </is>
       </c>
       <c r="C874" t="inlineStr"/>
       <c r="D874" t="inlineStr">
         <is>
-          <t>7.5%</t>
+          <t>143K</t>
         </is>
       </c>
       <c r="E874" t="inlineStr"/>
       <c r="F874" t="inlineStr">
         <is>
-          <t>7.6%</t>
+          <t>180.0K</t>
         </is>
       </c>
       <c r="G874" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="875">
@@ -25252,23 +25256,19 @@
       </c>
       <c r="B879" t="inlineStr">
         <is>
-          <t>Average Hourly Earnings MoMFEB</t>
+          <t>Used Car Prices YoYFEB</t>
         </is>
       </c>
       <c r="C879" t="inlineStr"/>
       <c r="D879" t="inlineStr">
         <is>
-          <t>0.5%</t>
+          <t>0.8%</t>
         </is>
       </c>
       <c r="E879" t="inlineStr"/>
-      <c r="F879" t="inlineStr">
-        <is>
-          <t>0.3%</t>
-        </is>
-      </c>
+      <c r="F879" t="inlineStr"/>
       <c r="G879" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="880">

--- a/Input_data/IST_US_trad_eco_cal_2025-01-01_to_2025-03-09.xlsx
+++ b/Input_data/IST_US_trad_eco_cal_2025-01-01_to_2025-03-09.xlsx
@@ -806,17 +806,17 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>EIA Gasoline Production ChangeDEC/27</t>
+          <t>EIA Cushing Crude Oil Stocks ChangeDEC/27</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>-0.959M</t>
+          <t>-0.142M</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>0.051M</t>
+          <t>-0.32M</t>
         </is>
       </c>
       <c r="E13" t="inlineStr"/>
@@ -833,17 +833,17 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>EIA Distillate Fuel Production ChangeDEC/27</t>
+          <t>EIA Crude Oil Imports ChangeDEC/27</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>0.099M</t>
+          <t>0.323M</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>0.178M</t>
+          <t>0.995M</t>
         </is>
       </c>
       <c r="E14" t="inlineStr"/>
@@ -860,27 +860,27 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>EIA Crude Oil Stocks ChangeDEC/27</t>
+          <t>EIA Distillate Stocks ChangeDEC/27</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>-1.178M</t>
+          <t>6.406M</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>-4.237M</t>
+          <t>-1.694M</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>-2.75M</t>
+          <t>-0.1M</t>
         </is>
       </c>
       <c r="F15" t="inlineStr"/>
       <c r="G15" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="16">
@@ -891,27 +891,23 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>EIA Gasoline Stocks ChangeDEC/27</t>
+          <t>EIA Heating Oil Stocks ChangeDEC/27</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>7.717M</t>
+          <t>-0.416M</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>1.63M</t>
-        </is>
-      </c>
-      <c r="E16" t="inlineStr">
-        <is>
-          <t>0.7M</t>
-        </is>
-      </c>
+          <t>-0.062M</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr"/>
       <c r="F16" t="inlineStr"/>
       <c r="G16" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="17">
@@ -922,23 +918,27 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>EIA Refinery Crude Runs ChangeDEC/27</t>
+          <t>EIA Crude Oil Stocks ChangeDEC/27</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>0.041M</t>
+          <t>-1.178M</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>0.205M</t>
-        </is>
-      </c>
-      <c r="E17" t="inlineStr"/>
+          <t>-4.237M</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>-2.75M</t>
+        </is>
+      </c>
       <c r="F17" t="inlineStr"/>
       <c r="G17" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="18">
@@ -949,23 +949,27 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>EIA Heating Oil Stocks ChangeDEC/27</t>
+          <t>EIA Gasoline Stocks ChangeDEC/27</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>-0.416M</t>
+          <t>7.717M</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>-0.062M</t>
-        </is>
-      </c>
-      <c r="E18" t="inlineStr"/>
+          <t>1.63M</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>0.7M</t>
+        </is>
+      </c>
       <c r="F18" t="inlineStr"/>
       <c r="G18" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="19">
@@ -976,24 +980,20 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>EIA Distillate Stocks ChangeDEC/27</t>
+          <t>EIA Distillate Fuel Production ChangeDEC/27</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>6.406M</t>
+          <t>0.099M</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>-1.694M</t>
-        </is>
-      </c>
-      <c r="E19" t="inlineStr">
-        <is>
-          <t>-0.1M</t>
-        </is>
-      </c>
+          <t>0.178M</t>
+        </is>
+      </c>
+      <c r="E19" t="inlineStr"/>
       <c r="F19" t="inlineStr"/>
       <c r="G19" t="n">
         <v>3</v>
@@ -1007,17 +1007,17 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>EIA Crude Oil Imports ChangeDEC/27</t>
+          <t>EIA Gasoline Production ChangeDEC/27</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>0.323M</t>
+          <t>-0.959M</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>0.995M</t>
+          <t>0.051M</t>
         </is>
       </c>
       <c r="E20" t="inlineStr"/>
@@ -1034,17 +1034,17 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>EIA Cushing Crude Oil Stocks ChangeDEC/27</t>
+          <t>EIA Refinery Crude Runs ChangeDEC/27</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>-0.142M</t>
+          <t>0.041M</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>-0.32M</t>
+          <t>0.205M</t>
         </is>
       </c>
       <c r="E21" t="inlineStr"/>
@@ -1223,31 +1223,31 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>ISM Manufacturing PricesDEC</t>
+          <t>ISM Manufacturing PMIDEC</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>52.5</t>
+          <t>49.3</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>50.3</t>
+          <t>48.4</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>51.7</t>
+          <t>48.4</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>50.4</t>
+          <t>48.5</t>
         </is>
       </c>
       <c r="G28" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="29">
@@ -1258,27 +1258,31 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>ISM Manufacturing New OrdersDEC</t>
+          <t>ISM Manufacturing EmploymentDEC</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>52.5</t>
+          <t>45.3</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>50.4</t>
-        </is>
-      </c>
-      <c r="E29" t="inlineStr"/>
+          <t>48.1</t>
+        </is>
+      </c>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t>48</t>
+        </is>
+      </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>50.5</t>
+          <t>48.3</t>
         </is>
       </c>
       <c r="G29" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="30">
@@ -1289,31 +1293,27 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>ISM Manufacturing EmploymentDEC</t>
+          <t>ISM Manufacturing New OrdersDEC</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>45.3</t>
+          <t>52.5</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>48.1</t>
-        </is>
-      </c>
-      <c r="E30" t="inlineStr">
-        <is>
-          <t>48</t>
-        </is>
-      </c>
+          <t>50.4</t>
+        </is>
+      </c>
+      <c r="E30" t="inlineStr"/>
       <c r="F30" t="inlineStr">
         <is>
-          <t>48.3</t>
+          <t>50.5</t>
         </is>
       </c>
       <c r="G30" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="31">
@@ -1324,31 +1324,31 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>ISM Manufacturing PMIDEC</t>
+          <t>ISM Manufacturing PricesDEC</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>49.3</t>
+          <t>52.5</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>48.4</t>
+          <t>50.3</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>48.4</t>
+          <t>51.7</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>48.5</t>
+          <t>50.4</t>
         </is>
       </c>
       <c r="G31" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="32">
@@ -1609,27 +1609,31 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>Factory Orders ex TransportationNOV</t>
+          <t>Factory Orders MoMNOV</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>0.2%</t>
+          <t>-0.4%</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>0.2%</t>
-        </is>
-      </c>
-      <c r="E42" t="inlineStr"/>
+          <t>0.5%</t>
+        </is>
+      </c>
+      <c r="E42" t="inlineStr">
+        <is>
+          <t>-0.3%</t>
+        </is>
+      </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>0.2%</t>
+          <t>0.3%</t>
         </is>
       </c>
       <c r="G42" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="43">
@@ -1640,31 +1644,27 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>Factory Orders MoMNOV</t>
+          <t>Factory Orders ex TransportationNOV</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>-0.4%</t>
+          <t>0.2%</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>0.5%</t>
-        </is>
-      </c>
-      <c r="E43" t="inlineStr">
-        <is>
-          <t>-0.3%</t>
-        </is>
-      </c>
+          <t>0.2%</t>
+        </is>
+      </c>
+      <c r="E43" t="inlineStr"/>
       <c r="F43" t="inlineStr">
         <is>
-          <t>0.3%</t>
+          <t>0.2%</t>
         </is>
       </c>
       <c r="G43" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="44">
@@ -1949,27 +1949,27 @@
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>ISM Services EmploymentDEC</t>
+          <t>ISM Services New OrdersDEC</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>51.4</t>
+          <t>54.2</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>51.5</t>
+          <t>53.7</t>
         </is>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>51.4</t>
+          <t>54.2</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>52</t>
+          <t>54.1</t>
         </is>
       </c>
       <c r="G54" t="n">
@@ -1984,23 +1984,23 @@
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>ISM Services Business ActivityDEC</t>
+          <t>JOLTs Job QuitsNOV</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>58.2</t>
+          <t>3.065M</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>53.7</t>
+          <t>3.283M</t>
         </is>
       </c>
       <c r="E55" t="inlineStr"/>
       <c r="F55" t="inlineStr">
         <is>
-          <t>54.1</t>
+          <t>3.31M</t>
         </is>
       </c>
       <c r="G55" t="n">
@@ -2015,31 +2015,31 @@
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>JOLTs Job OpeningsNOV</t>
+          <t>ISM Services PricesDEC</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>8.098M</t>
+          <t>64.4</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>7.839M</t>
+          <t>58.2</t>
         </is>
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>7.70M</t>
+          <t>57.5</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>7.69M</t>
+          <t>58.4</t>
         </is>
       </c>
       <c r="G56" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="57">
@@ -2050,31 +2050,31 @@
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>ISM Services PMIDEC</t>
+          <t>ISM Services EmploymentDEC</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>54.1</t>
+          <t>51.4</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>52.1</t>
+          <t>51.5</t>
         </is>
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>53.3</t>
+          <t>51.4</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>54</t>
+          <t>52</t>
         </is>
       </c>
       <c r="G57" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="58">
@@ -2085,31 +2085,31 @@
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>ISM Services PricesDEC</t>
+          <t>JOLTs Job OpeningsNOV</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>64.4</t>
+          <t>8.098M</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>58.2</t>
+          <t>7.839M</t>
         </is>
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>57.5</t>
+          <t>7.70M</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>58.4</t>
+          <t>7.69M</t>
         </is>
       </c>
       <c r="G58" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="59">
@@ -2120,31 +2120,31 @@
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>ISM Services New OrdersDEC</t>
+          <t>ISM Services PMIDEC</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>54.2</t>
+          <t>54.1</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>53.7</t>
+          <t>52.1</t>
         </is>
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>54.2</t>
+          <t>53.3</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>54.1</t>
+          <t>54</t>
         </is>
       </c>
       <c r="G59" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="60">
@@ -2155,23 +2155,23 @@
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>JOLTs Job QuitsNOV</t>
+          <t>ISM Services Business ActivityDEC</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>3.065M</t>
+          <t>58.2</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>3.283M</t>
+          <t>53.7</t>
         </is>
       </c>
       <c r="E60" t="inlineStr"/>
       <c r="F60" t="inlineStr">
         <is>
-          <t>3.31M</t>
+          <t>54.1</t>
         </is>
       </c>
       <c r="G60" t="n">
@@ -2441,31 +2441,31 @@
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>Initial Jobless ClaimsJAN/04</t>
+          <t>Total Vehicle SalesDEC</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>201K</t>
+          <t>16.8M</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>211K</t>
+          <t>16.7M</t>
         </is>
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>218K</t>
+          <t>16.5M</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>213K</t>
+          <t>16.3M</t>
         </is>
       </c>
       <c r="G70" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="71">
@@ -2476,15 +2476,27 @@
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>Fed Waller Speech</t>
-        </is>
-      </c>
-      <c r="C71" t="inlineStr"/>
-      <c r="D71" t="inlineStr"/>
+          <t>Jobless Claims 4-week AverageJAN/04</t>
+        </is>
+      </c>
+      <c r="C71" t="inlineStr">
+        <is>
+          <t>213K</t>
+        </is>
+      </c>
+      <c r="D71" t="inlineStr">
+        <is>
+          <t>223.25K</t>
+        </is>
+      </c>
       <c r="E71" t="inlineStr"/>
-      <c r="F71" t="inlineStr"/>
+      <c r="F71" t="inlineStr">
+        <is>
+          <t>224K</t>
+        </is>
+      </c>
       <c r="G71" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="72">
@@ -2495,31 +2507,31 @@
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>Continuing Jobless ClaimsDEC/28</t>
+          <t>Initial Jobless ClaimsJAN/04</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>1867K</t>
+          <t>201K</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>1834K</t>
+          <t>211K</t>
         </is>
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>1870K</t>
+          <t>218K</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>1848K</t>
+          <t>213K</t>
         </is>
       </c>
       <c r="G72" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="73">
@@ -2530,27 +2542,15 @@
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>Jobless Claims 4-week AverageJAN/04</t>
-        </is>
-      </c>
-      <c r="C73" t="inlineStr">
-        <is>
-          <t>213K</t>
-        </is>
-      </c>
-      <c r="D73" t="inlineStr">
-        <is>
-          <t>223.25K</t>
-        </is>
-      </c>
+          <t>Fed Waller Speech</t>
+        </is>
+      </c>
+      <c r="C73" t="inlineStr"/>
+      <c r="D73" t="inlineStr"/>
       <c r="E73" t="inlineStr"/>
-      <c r="F73" t="inlineStr">
-        <is>
-          <t>224K</t>
-        </is>
-      </c>
+      <c r="F73" t="inlineStr"/>
       <c r="G73" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="74">
@@ -2561,27 +2561,27 @@
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>Total Vehicle SalesDEC</t>
+          <t>Continuing Jobless ClaimsDEC/28</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>16.8M</t>
+          <t>1867K</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>16.7M</t>
+          <t>1834K</t>
         </is>
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>16.5M</t>
+          <t>1870K</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>16.3M</t>
+          <t>1848K</t>
         </is>
       </c>
       <c r="G74" t="n">
@@ -2685,23 +2685,27 @@
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>EIA Heating Oil Stocks ChangeJAN/03</t>
+          <t>EIA Crude Oil Stocks ChangeJAN/03</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>-0.632M</t>
+          <t>-0.959M</t>
         </is>
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>-0.416M</t>
-        </is>
-      </c>
-      <c r="E78" t="inlineStr"/>
+          <t>-1.178M</t>
+        </is>
+      </c>
+      <c r="E78" t="inlineStr">
+        <is>
+          <t>-0.6M</t>
+        </is>
+      </c>
       <c r="F78" t="inlineStr"/>
       <c r="G78" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="79">
@@ -2712,27 +2716,23 @@
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>EIA Gasoline Stocks ChangeJAN/03</t>
+          <t>EIA Distillate Fuel Production ChangeJAN/03</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>6.33M</t>
+          <t>-0.167M</t>
         </is>
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>7.717M</t>
-        </is>
-      </c>
-      <c r="E79" t="inlineStr">
-        <is>
-          <t>1.5M</t>
-        </is>
-      </c>
+          <t>0.099M</t>
+        </is>
+      </c>
+      <c r="E79" t="inlineStr"/>
       <c r="F79" t="inlineStr"/>
       <c r="G79" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="80">
@@ -2743,17 +2743,17 @@
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>EIA Gasoline Production ChangeJAN/03</t>
+          <t>EIA Crude Oil Imports ChangeJAN/03</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>-0.081M</t>
+          <t>0.278M</t>
         </is>
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>-0.959M</t>
+          <t>0.323M</t>
         </is>
       </c>
       <c r="E80" t="inlineStr"/>
@@ -2770,24 +2770,20 @@
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>EIA Distillate Stocks ChangeJAN/03</t>
+          <t>EIA Cushing Crude Oil Stocks ChangeJAN/03</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>6.071M</t>
+          <t>-2.502M</t>
         </is>
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>6.406M</t>
-        </is>
-      </c>
-      <c r="E81" t="inlineStr">
-        <is>
-          <t>1M</t>
-        </is>
-      </c>
+          <t>-0.142M</t>
+        </is>
+      </c>
+      <c r="E81" t="inlineStr"/>
       <c r="F81" t="inlineStr"/>
       <c r="G81" t="n">
         <v>3</v>
@@ -2828,27 +2824,23 @@
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>EIA Crude Oil Stocks ChangeJAN/03</t>
+          <t>EIA Gasoline Production ChangeJAN/03</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
+          <t>-0.081M</t>
+        </is>
+      </c>
+      <c r="D83" t="inlineStr">
+        <is>
           <t>-0.959M</t>
         </is>
       </c>
-      <c r="D83" t="inlineStr">
-        <is>
-          <t>-1.178M</t>
-        </is>
-      </c>
-      <c r="E83" t="inlineStr">
-        <is>
-          <t>-0.6M</t>
-        </is>
-      </c>
+      <c r="E83" t="inlineStr"/>
       <c r="F83" t="inlineStr"/>
       <c r="G83" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="84">
@@ -2859,23 +2851,27 @@
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>EIA Crude Oil Imports ChangeJAN/03</t>
+          <t>EIA Gasoline Stocks ChangeJAN/03</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>0.278M</t>
+          <t>6.33M</t>
         </is>
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>0.323M</t>
-        </is>
-      </c>
-      <c r="E84" t="inlineStr"/>
+          <t>7.717M</t>
+        </is>
+      </c>
+      <c r="E84" t="inlineStr">
+        <is>
+          <t>1.5M</t>
+        </is>
+      </c>
       <c r="F84" t="inlineStr"/>
       <c r="G84" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="85">
@@ -2886,17 +2882,17 @@
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>EIA Distillate Fuel Production ChangeJAN/03</t>
+          <t>EIA Heating Oil Stocks ChangeJAN/03</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>-0.167M</t>
+          <t>-0.632M</t>
         </is>
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>0.099M</t>
+          <t>-0.416M</t>
         </is>
       </c>
       <c r="E85" t="inlineStr"/>
@@ -2913,20 +2909,24 @@
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>EIA Cushing Crude Oil Stocks ChangeJAN/03</t>
+          <t>EIA Distillate Stocks ChangeJAN/03</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>-2.502M</t>
+          <t>6.071M</t>
         </is>
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>-0.142M</t>
-        </is>
-      </c>
-      <c r="E86" t="inlineStr"/>
+          <t>6.406M</t>
+        </is>
+      </c>
+      <c r="E86" t="inlineStr">
+        <is>
+          <t>1M</t>
+        </is>
+      </c>
       <c r="F86" t="inlineStr"/>
       <c r="G86" t="n">
         <v>3</v>
@@ -3336,31 +3336,27 @@
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>Average Hourly Earnings MoMDEC</t>
+          <t>U-6 Unemployment Rate</t>
         </is>
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>0.3%</t>
+          <t>7.5%</t>
         </is>
       </c>
       <c r="D103" t="inlineStr">
         <is>
-          <t>0.4%</t>
-        </is>
-      </c>
-      <c r="E103" t="inlineStr">
-        <is>
-          <t>0.3%</t>
-        </is>
-      </c>
+          <t>7.7%</t>
+        </is>
+      </c>
+      <c r="E103" t="inlineStr"/>
       <c r="F103" t="inlineStr">
         <is>
-          <t>0.3%</t>
+          <t>7.9%</t>
         </is>
       </c>
       <c r="G103" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="104">
@@ -3371,31 +3367,31 @@
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>Average Hourly Earnings YoY</t>
+          <t>Average Weekly HoursDEC</t>
         </is>
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>3.9%</t>
+          <t>34.3</t>
         </is>
       </c>
       <c r="D104" t="inlineStr">
         <is>
-          <t>4%</t>
+          <t>34.3</t>
         </is>
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>4%</t>
+          <t>34.3</t>
         </is>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>4%</t>
+          <t>34.3</t>
         </is>
       </c>
       <c r="G104" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="105">
@@ -3406,31 +3402,27 @@
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>Non Farm PayrollsDEC</t>
+          <t>Government PayrollsDEC</t>
         </is>
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>256K</t>
+          <t>33K</t>
         </is>
       </c>
       <c r="D105" t="inlineStr">
         <is>
-          <t>212K</t>
-        </is>
-      </c>
-      <c r="E105" t="inlineStr">
-        <is>
-          <t>160K</t>
-        </is>
-      </c>
+          <t>30K</t>
+        </is>
+      </c>
+      <c r="E105" t="inlineStr"/>
       <c r="F105" t="inlineStr">
         <is>
-          <t>200K</t>
+          <t>15K</t>
         </is>
       </c>
       <c r="G105" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="106">
@@ -3441,27 +3433,31 @@
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>Participation RateDEC</t>
+          <t>Nonfarm Payrolls PrivateDEC</t>
         </is>
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>62.5%</t>
+          <t>223K</t>
         </is>
       </c>
       <c r="D106" t="inlineStr">
         <is>
-          <t>62.5%</t>
-        </is>
-      </c>
-      <c r="E106" t="inlineStr"/>
+          <t>182K</t>
+        </is>
+      </c>
+      <c r="E106" t="inlineStr">
+        <is>
+          <t>135K</t>
+        </is>
+      </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>62.8%</t>
+          <t>185K</t>
         </is>
       </c>
       <c r="G106" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="107">
@@ -3472,31 +3468,31 @@
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>Unemployment RateDEC</t>
+          <t>Manufacturing PayrollsDEC</t>
         </is>
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>4.1%</t>
+          <t>-13K</t>
         </is>
       </c>
       <c r="D107" t="inlineStr">
         <is>
-          <t>4.2%</t>
+          <t>25K</t>
         </is>
       </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t>4.2%</t>
+          <t>5K</t>
         </is>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>4.30%</t>
+          <t>29K</t>
         </is>
       </c>
       <c r="G107" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="108">
@@ -3507,31 +3503,27 @@
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>Nonfarm Payrolls PrivateDEC</t>
+          <t>Participation RateDEC</t>
         </is>
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>223K</t>
+          <t>62.5%</t>
         </is>
       </c>
       <c r="D108" t="inlineStr">
         <is>
-          <t>182K</t>
-        </is>
-      </c>
-      <c r="E108" t="inlineStr">
-        <is>
-          <t>135K</t>
-        </is>
-      </c>
+          <t>62.5%</t>
+        </is>
+      </c>
+      <c r="E108" t="inlineStr"/>
       <c r="F108" t="inlineStr">
         <is>
-          <t>185K</t>
+          <t>62.8%</t>
         </is>
       </c>
       <c r="G108" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="109">
@@ -3542,27 +3534,31 @@
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>Government PayrollsDEC</t>
+          <t>Non Farm PayrollsDEC</t>
         </is>
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>33K</t>
+          <t>256K</t>
         </is>
       </c>
       <c r="D109" t="inlineStr">
         <is>
-          <t>30K</t>
-        </is>
-      </c>
-      <c r="E109" t="inlineStr"/>
+          <t>212K</t>
+        </is>
+      </c>
+      <c r="E109" t="inlineStr">
+        <is>
+          <t>160K</t>
+        </is>
+      </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>15K</t>
+          <t>200K</t>
         </is>
       </c>
       <c r="G109" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="110">
@@ -3573,31 +3569,31 @@
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>Average Weekly HoursDEC</t>
+          <t>Average Hourly Earnings YoY</t>
         </is>
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>34.3</t>
+          <t>3.9%</t>
         </is>
       </c>
       <c r="D110" t="inlineStr">
         <is>
-          <t>34.3</t>
+          <t>4%</t>
         </is>
       </c>
       <c r="E110" t="inlineStr">
         <is>
-          <t>34.3</t>
+          <t>4%</t>
         </is>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>34.3</t>
+          <t>4%</t>
         </is>
       </c>
       <c r="G110" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="111">
@@ -3608,27 +3604,31 @@
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>U-6 Unemployment Rate</t>
+          <t>Average Hourly Earnings MoMDEC</t>
         </is>
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>7.5%</t>
+          <t>0.3%</t>
         </is>
       </c>
       <c r="D111" t="inlineStr">
         <is>
-          <t>7.7%</t>
-        </is>
-      </c>
-      <c r="E111" t="inlineStr"/>
+          <t>0.4%</t>
+        </is>
+      </c>
+      <c r="E111" t="inlineStr">
+        <is>
+          <t>0.3%</t>
+        </is>
+      </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>7.9%</t>
+          <t>0.3%</t>
         </is>
       </c>
       <c r="G111" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="112">
@@ -3639,31 +3639,31 @@
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>Manufacturing PayrollsDEC</t>
+          <t>Unemployment RateDEC</t>
         </is>
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>-13K</t>
+          <t>4.1%</t>
         </is>
       </c>
       <c r="D112" t="inlineStr">
         <is>
-          <t>25K</t>
+          <t>4.2%</t>
         </is>
       </c>
       <c r="E112" t="inlineStr">
         <is>
-          <t>5K</t>
+          <t>4.2%</t>
         </is>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>29K</t>
+          <t>4.30%</t>
         </is>
       </c>
       <c r="G112" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="113">
@@ -3833,19 +3833,11 @@
       </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t>Quarterly Grain Stocks - SoyDEC</t>
-        </is>
-      </c>
-      <c r="C118" t="inlineStr">
-        <is>
-          <t>3.1B</t>
-        </is>
-      </c>
-      <c r="D118" t="inlineStr">
-        <is>
-          <t>0.342B</t>
-        </is>
-      </c>
+          <t>WASDE Report</t>
+        </is>
+      </c>
+      <c r="C118" t="inlineStr"/>
+      <c r="D118" t="inlineStr"/>
       <c r="E118" t="inlineStr"/>
       <c r="F118" t="inlineStr"/>
       <c r="G118" t="n">
@@ -3860,17 +3852,17 @@
       </c>
       <c r="B119" t="inlineStr">
         <is>
-          <t>Quarterly Grain Stocks - CornDEC</t>
+          <t>Quarterly Grain Stocks - WheatDEC</t>
         </is>
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>12.074B</t>
+          <t>1.57B</t>
         </is>
       </c>
       <c r="D119" t="inlineStr">
         <is>
-          <t>1.760B</t>
+          <t>1.98B</t>
         </is>
       </c>
       <c r="E119" t="inlineStr"/>
@@ -3887,17 +3879,17 @@
       </c>
       <c r="B120" t="inlineStr">
         <is>
-          <t>Quarterly Grain Stocks - WheatDEC</t>
+          <t>Quarterly Grain Stocks - CornDEC</t>
         </is>
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>1.57B</t>
+          <t>12.074B</t>
         </is>
       </c>
       <c r="D120" t="inlineStr">
         <is>
-          <t>1.98B</t>
+          <t>1.760B</t>
         </is>
       </c>
       <c r="E120" t="inlineStr"/>
@@ -3914,11 +3906,19 @@
       </c>
       <c r="B121" t="inlineStr">
         <is>
-          <t>WASDE Report</t>
-        </is>
-      </c>
-      <c r="C121" t="inlineStr"/>
-      <c r="D121" t="inlineStr"/>
+          <t>Quarterly Grain Stocks - SoyDEC</t>
+        </is>
+      </c>
+      <c r="C121" t="inlineStr">
+        <is>
+          <t>3.1B</t>
+        </is>
+      </c>
+      <c r="D121" t="inlineStr">
+        <is>
+          <t>0.342B</t>
+        </is>
+      </c>
       <c r="E121" t="inlineStr"/>
       <c r="F121" t="inlineStr"/>
       <c r="G121" t="n">
@@ -4134,31 +4134,31 @@
       </c>
       <c r="B129" t="inlineStr">
         <is>
-          <t>Core PPI MoMDEC</t>
+          <t>PPI YoYDEC</t>
         </is>
       </c>
       <c r="C129" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>3.3%</t>
         </is>
       </c>
       <c r="D129" t="inlineStr">
         <is>
-          <t>0.2%</t>
+          <t>3%</t>
         </is>
       </c>
       <c r="E129" t="inlineStr">
         <is>
-          <t>0.3%</t>
+          <t>3.4%</t>
         </is>
       </c>
       <c r="F129" t="inlineStr">
         <is>
-          <t>0.2%</t>
+          <t>3.3%</t>
         </is>
       </c>
       <c r="G129" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="130">
@@ -4169,31 +4169,27 @@
       </c>
       <c r="B130" t="inlineStr">
         <is>
-          <t>PPI MoMDEC</t>
+          <t>PPI Ex Food, Energy and Trade YoYDEC</t>
         </is>
       </c>
       <c r="C130" t="inlineStr">
         <is>
-          <t>0.2%</t>
+          <t>3.3%</t>
         </is>
       </c>
       <c r="D130" t="inlineStr">
         <is>
-          <t>0.4%</t>
-        </is>
-      </c>
-      <c r="E130" t="inlineStr">
-        <is>
-          <t>0.3%</t>
-        </is>
-      </c>
+          <t>3.5%</t>
+        </is>
+      </c>
+      <c r="E130" t="inlineStr"/>
       <c r="F130" t="inlineStr">
         <is>
-          <t>0.3%</t>
+          <t>3.6%</t>
         </is>
       </c>
       <c r="G130" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="131">
@@ -4204,27 +4200,23 @@
       </c>
       <c r="B131" t="inlineStr">
         <is>
-          <t>PPI Ex Food, Energy and Trade MoMDEC</t>
+          <t>PPIDEC</t>
         </is>
       </c>
       <c r="C131" t="inlineStr">
         <is>
-          <t>0.1%</t>
+          <t>146.842</t>
         </is>
       </c>
       <c r="D131" t="inlineStr">
         <is>
-          <t>0.1%</t>
-        </is>
-      </c>
-      <c r="E131" t="inlineStr">
-        <is>
-          <t>0.3%</t>
-        </is>
-      </c>
+          <t>146.521</t>
+        </is>
+      </c>
+      <c r="E131" t="inlineStr"/>
       <c r="F131" t="inlineStr">
         <is>
-          <t>0.2%</t>
+          <t>146.8</t>
         </is>
       </c>
       <c r="G131" t="n">
@@ -4239,23 +4231,27 @@
       </c>
       <c r="B132" t="inlineStr">
         <is>
-          <t>PPIDEC</t>
+          <t>Core PPI YoYDEC</t>
         </is>
       </c>
       <c r="C132" t="inlineStr">
         <is>
-          <t>146.842</t>
+          <t>3.5%</t>
         </is>
       </c>
       <c r="D132" t="inlineStr">
         <is>
-          <t>146.521</t>
-        </is>
-      </c>
-      <c r="E132" t="inlineStr"/>
+          <t>3.5%</t>
+        </is>
+      </c>
+      <c r="E132" t="inlineStr">
+        <is>
+          <t>3.8%</t>
+        </is>
+      </c>
       <c r="F132" t="inlineStr">
         <is>
-          <t>146.8</t>
+          <t>3.5%</t>
         </is>
       </c>
       <c r="G132" t="n">
@@ -4270,27 +4266,31 @@
       </c>
       <c r="B133" t="inlineStr">
         <is>
-          <t>PPI Ex Food, Energy and Trade YoYDEC</t>
+          <t>PPI MoMDEC</t>
         </is>
       </c>
       <c r="C133" t="inlineStr">
         <is>
-          <t>3.3%</t>
+          <t>0.2%</t>
         </is>
       </c>
       <c r="D133" t="inlineStr">
         <is>
-          <t>3.5%</t>
-        </is>
-      </c>
-      <c r="E133" t="inlineStr"/>
+          <t>0.4%</t>
+        </is>
+      </c>
+      <c r="E133" t="inlineStr">
+        <is>
+          <t>0.3%</t>
+        </is>
+      </c>
       <c r="F133" t="inlineStr">
         <is>
-          <t>3.6%</t>
+          <t>0.3%</t>
         </is>
       </c>
       <c r="G133" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="134">
@@ -4301,31 +4301,31 @@
       </c>
       <c r="B134" t="inlineStr">
         <is>
-          <t>Core PPI YoYDEC</t>
+          <t>Core PPI MoMDEC</t>
         </is>
       </c>
       <c r="C134" t="inlineStr">
         <is>
-          <t>3.5%</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="D134" t="inlineStr">
         <is>
-          <t>3.5%</t>
+          <t>0.2%</t>
         </is>
       </c>
       <c r="E134" t="inlineStr">
         <is>
-          <t>3.8%</t>
+          <t>0.3%</t>
         </is>
       </c>
       <c r="F134" t="inlineStr">
         <is>
-          <t>3.5%</t>
+          <t>0.2%</t>
         </is>
       </c>
       <c r="G134" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="135">
@@ -4336,27 +4336,27 @@
       </c>
       <c r="B135" t="inlineStr">
         <is>
-          <t>PPI YoYDEC</t>
+          <t>PPI Ex Food, Energy and Trade MoMDEC</t>
         </is>
       </c>
       <c r="C135" t="inlineStr">
         <is>
-          <t>3.3%</t>
+          <t>0.1%</t>
         </is>
       </c>
       <c r="D135" t="inlineStr">
         <is>
-          <t>3%</t>
+          <t>0.1%</t>
         </is>
       </c>
       <c r="E135" t="inlineStr">
         <is>
-          <t>3.4%</t>
+          <t>0.3%</t>
         </is>
       </c>
       <c r="F135" t="inlineStr">
         <is>
-          <t>3.3%</t>
+          <t>0.2%</t>
         </is>
       </c>
       <c r="G135" t="n">
@@ -4564,17 +4564,17 @@
       </c>
       <c r="B143" t="inlineStr">
         <is>
-          <t>MBA Purchase IndexJAN/10</t>
+          <t>MBA Mortgage Market IndexJAN/10</t>
         </is>
       </c>
       <c r="C143" t="inlineStr">
         <is>
-          <t>162</t>
+          <t>224.4</t>
         </is>
       </c>
       <c r="D143" t="inlineStr">
         <is>
-          <t>127.7000</t>
+          <t>168.4</t>
         </is>
       </c>
       <c r="E143" t="inlineStr"/>
@@ -4591,23 +4591,23 @@
       </c>
       <c r="B144" t="inlineStr">
         <is>
-          <t>MBA 30-Year Mortgage RateJAN/10</t>
+          <t>MBA Mortgage Refinance IndexJAN/10</t>
         </is>
       </c>
       <c r="C144" t="inlineStr">
         <is>
-          <t>7.09%</t>
+          <t>575.6</t>
         </is>
       </c>
       <c r="D144" t="inlineStr">
         <is>
-          <t>6.99%</t>
+          <t>401.1000</t>
         </is>
       </c>
       <c r="E144" t="inlineStr"/>
       <c r="F144" t="inlineStr"/>
       <c r="G144" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="145">
@@ -4618,17 +4618,17 @@
       </c>
       <c r="B145" t="inlineStr">
         <is>
-          <t>MBA Mortgage Refinance IndexJAN/10</t>
+          <t>MBA Mortgage ApplicationsJAN/10</t>
         </is>
       </c>
       <c r="C145" t="inlineStr">
         <is>
-          <t>575.6</t>
+          <t>33.3%</t>
         </is>
       </c>
       <c r="D145" t="inlineStr">
         <is>
-          <t>401.1000</t>
+          <t>-3.7%</t>
         </is>
       </c>
       <c r="E145" t="inlineStr"/>
@@ -4645,17 +4645,17 @@
       </c>
       <c r="B146" t="inlineStr">
         <is>
-          <t>MBA Mortgage ApplicationsJAN/10</t>
+          <t>MBA Purchase IndexJAN/10</t>
         </is>
       </c>
       <c r="C146" t="inlineStr">
         <is>
-          <t>33.3%</t>
+          <t>162</t>
         </is>
       </c>
       <c r="D146" t="inlineStr">
         <is>
-          <t>-3.7%</t>
+          <t>127.7000</t>
         </is>
       </c>
       <c r="E146" t="inlineStr"/>
@@ -4672,23 +4672,23 @@
       </c>
       <c r="B147" t="inlineStr">
         <is>
-          <t>MBA Mortgage Market IndexJAN/10</t>
+          <t>MBA 30-Year Mortgage RateJAN/10</t>
         </is>
       </c>
       <c r="C147" t="inlineStr">
         <is>
-          <t>224.4</t>
+          <t>7.09%</t>
         </is>
       </c>
       <c r="D147" t="inlineStr">
         <is>
-          <t>168.4</t>
+          <t>6.99%</t>
         </is>
       </c>
       <c r="E147" t="inlineStr"/>
       <c r="F147" t="inlineStr"/>
       <c r="G147" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="148">
@@ -4978,27 +4978,23 @@
       </c>
       <c r="B157" t="inlineStr">
         <is>
-          <t>EIA Gasoline Stocks ChangeJAN/10</t>
+          <t>EIA Gasoline Production ChangeJAN/10</t>
         </is>
       </c>
       <c r="C157" t="inlineStr">
         <is>
-          <t>5.852M</t>
+          <t>0.397M</t>
         </is>
       </c>
       <c r="D157" t="inlineStr">
         <is>
-          <t>6.33M</t>
-        </is>
-      </c>
-      <c r="E157" t="inlineStr">
-        <is>
-          <t>2.60M</t>
-        </is>
-      </c>
+          <t>-0.081M</t>
+        </is>
+      </c>
+      <c r="E157" t="inlineStr"/>
       <c r="F157" t="inlineStr"/>
       <c r="G157" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="158">
@@ -5009,24 +5005,20 @@
       </c>
       <c r="B158" t="inlineStr">
         <is>
-          <t>EIA Distillate Stocks ChangeJAN/10</t>
+          <t>EIA Refinery Crude Runs ChangeJAN/10</t>
         </is>
       </c>
       <c r="C158" t="inlineStr">
         <is>
-          <t>3.077M</t>
+          <t>-0.255M</t>
         </is>
       </c>
       <c r="D158" t="inlineStr">
         <is>
-          <t>6.071M</t>
-        </is>
-      </c>
-      <c r="E158" t="inlineStr">
-        <is>
-          <t>1.1M</t>
-        </is>
-      </c>
+          <t>0.045M</t>
+        </is>
+      </c>
+      <c r="E158" t="inlineStr"/>
       <c r="F158" t="inlineStr"/>
       <c r="G158" t="n">
         <v>3</v>
@@ -5040,23 +5032,27 @@
       </c>
       <c r="B159" t="inlineStr">
         <is>
-          <t>EIA Heating Oil Stocks ChangeJAN/10</t>
+          <t>EIA Crude Oil Stocks ChangeJAN/10</t>
         </is>
       </c>
       <c r="C159" t="inlineStr">
         <is>
-          <t>0.646M</t>
+          <t>-1.961M</t>
         </is>
       </c>
       <c r="D159" t="inlineStr">
         <is>
-          <t>-0.632M</t>
-        </is>
-      </c>
-      <c r="E159" t="inlineStr"/>
+          <t>-0.959M</t>
+        </is>
+      </c>
+      <c r="E159" t="inlineStr">
+        <is>
+          <t>-1.6M</t>
+        </is>
+      </c>
       <c r="F159" t="inlineStr"/>
       <c r="G159" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="160">
@@ -5067,17 +5063,17 @@
       </c>
       <c r="B160" t="inlineStr">
         <is>
-          <t>EIA Crude Oil Imports ChangeJAN/10</t>
+          <t>EIA Cushing Crude Oil Stocks ChangeJAN/10</t>
         </is>
       </c>
       <c r="C160" t="inlineStr">
         <is>
-          <t>-1.304M</t>
+          <t>0.765M</t>
         </is>
       </c>
       <c r="D160" t="inlineStr">
         <is>
-          <t>0.278M</t>
+          <t>-2.502M</t>
         </is>
       </c>
       <c r="E160" t="inlineStr"/>
@@ -5094,17 +5090,17 @@
       </c>
       <c r="B161" t="inlineStr">
         <is>
-          <t>EIA Cushing Crude Oil Stocks ChangeJAN/10</t>
+          <t>EIA Distillate Fuel Production ChangeJAN/10</t>
         </is>
       </c>
       <c r="C161" t="inlineStr">
         <is>
-          <t>0.765M</t>
+          <t>-0.021M</t>
         </is>
       </c>
       <c r="D161" t="inlineStr">
         <is>
-          <t>-2.502M</t>
+          <t>-0.167M</t>
         </is>
       </c>
       <c r="E161" t="inlineStr"/>
@@ -5121,17 +5117,17 @@
       </c>
       <c r="B162" t="inlineStr">
         <is>
-          <t>EIA Gasoline Production ChangeJAN/10</t>
+          <t>EIA Heating Oil Stocks ChangeJAN/10</t>
         </is>
       </c>
       <c r="C162" t="inlineStr">
         <is>
-          <t>0.397M</t>
+          <t>0.646M</t>
         </is>
       </c>
       <c r="D162" t="inlineStr">
         <is>
-          <t>-0.081M</t>
+          <t>-0.632M</t>
         </is>
       </c>
       <c r="E162" t="inlineStr"/>
@@ -5148,22 +5144,22 @@
       </c>
       <c r="B163" t="inlineStr">
         <is>
-          <t>EIA Crude Oil Stocks ChangeJAN/10</t>
+          <t>EIA Gasoline Stocks ChangeJAN/10</t>
         </is>
       </c>
       <c r="C163" t="inlineStr">
         <is>
-          <t>-1.961M</t>
+          <t>5.852M</t>
         </is>
       </c>
       <c r="D163" t="inlineStr">
         <is>
-          <t>-0.959M</t>
+          <t>6.33M</t>
         </is>
       </c>
       <c r="E163" t="inlineStr">
         <is>
-          <t>-1.6M</t>
+          <t>2.60M</t>
         </is>
       </c>
       <c r="F163" t="inlineStr"/>
@@ -5179,17 +5175,17 @@
       </c>
       <c r="B164" t="inlineStr">
         <is>
-          <t>EIA Refinery Crude Runs ChangeJAN/10</t>
+          <t>EIA Crude Oil Imports ChangeJAN/10</t>
         </is>
       </c>
       <c r="C164" t="inlineStr">
         <is>
-          <t>-0.255M</t>
+          <t>-1.304M</t>
         </is>
       </c>
       <c r="D164" t="inlineStr">
         <is>
-          <t>0.045M</t>
+          <t>0.278M</t>
         </is>
       </c>
       <c r="E164" t="inlineStr"/>
@@ -5206,20 +5202,24 @@
       </c>
       <c r="B165" t="inlineStr">
         <is>
-          <t>EIA Distillate Fuel Production ChangeJAN/10</t>
+          <t>EIA Distillate Stocks ChangeJAN/10</t>
         </is>
       </c>
       <c r="C165" t="inlineStr">
         <is>
-          <t>-0.021M</t>
+          <t>3.077M</t>
         </is>
       </c>
       <c r="D165" t="inlineStr">
         <is>
-          <t>-0.167M</t>
-        </is>
-      </c>
-      <c r="E165" t="inlineStr"/>
+          <t>6.071M</t>
+        </is>
+      </c>
+      <c r="E165" t="inlineStr">
+        <is>
+          <t>1.1M</t>
+        </is>
+      </c>
       <c r="F165" t="inlineStr"/>
       <c r="G165" t="n">
         <v>3</v>
@@ -5336,27 +5336,31 @@
       </c>
       <c r="B171" t="inlineStr">
         <is>
-          <t>Jobless Claims 4-week AverageJAN/11</t>
+          <t>Retail Sales Ex Autos MoMDEC</t>
         </is>
       </c>
       <c r="C171" t="inlineStr">
         <is>
-          <t>212.75K</t>
+          <t>0.4%</t>
         </is>
       </c>
       <c r="D171" t="inlineStr">
         <is>
-          <t>213.5K</t>
-        </is>
-      </c>
-      <c r="E171" t="inlineStr"/>
+          <t>0.2%</t>
+        </is>
+      </c>
+      <c r="E171" t="inlineStr">
+        <is>
+          <t>0.4%</t>
+        </is>
+      </c>
       <c r="F171" t="inlineStr">
         <is>
-          <t>215.0K</t>
+          <t>0.4%</t>
         </is>
       </c>
       <c r="G171" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="172">
@@ -5367,23 +5371,31 @@
       </c>
       <c r="B172" t="inlineStr">
         <is>
-          <t>Philly Fed CAPEX IndexJAN</t>
+          <t>Import Prices MoMDEC</t>
         </is>
       </c>
       <c r="C172" t="inlineStr">
         <is>
-          <t>39.00</t>
+          <t>0.1%</t>
         </is>
       </c>
       <c r="D172" t="inlineStr">
         <is>
-          <t>22.20</t>
-        </is>
-      </c>
-      <c r="E172" t="inlineStr"/>
-      <c r="F172" t="inlineStr"/>
+          <t>0.1%</t>
+        </is>
+      </c>
+      <c r="E172" t="inlineStr">
+        <is>
+          <t>0.1%</t>
+        </is>
+      </c>
+      <c r="F172" t="inlineStr">
+        <is>
+          <t>0.1%</t>
+        </is>
+      </c>
       <c r="G172" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="173">
@@ -5394,25 +5406,21 @@
       </c>
       <c r="B173" t="inlineStr">
         <is>
-          <t>Export Prices YoYDEC</t>
+          <t>Philly Fed Business ConditionsJAN</t>
         </is>
       </c>
       <c r="C173" t="inlineStr">
         <is>
-          <t>1.8%</t>
+          <t>46.3</t>
         </is>
       </c>
       <c r="D173" t="inlineStr">
         <is>
-          <t>0.9%</t>
+          <t>33.8</t>
         </is>
       </c>
       <c r="E173" t="inlineStr"/>
-      <c r="F173" t="inlineStr">
-        <is>
-          <t>1.9%</t>
-        </is>
-      </c>
+      <c r="F173" t="inlineStr"/>
       <c r="G173" t="n">
         <v>3</v>
       </c>
@@ -5425,27 +5433,31 @@
       </c>
       <c r="B174" t="inlineStr">
         <is>
-          <t>Retail Sales YoYDEC</t>
+          <t>Philadelphia Fed Manufacturing IndexJAN</t>
         </is>
       </c>
       <c r="C174" t="inlineStr">
         <is>
-          <t>3.9%</t>
+          <t>44.3</t>
         </is>
       </c>
       <c r="D174" t="inlineStr">
         <is>
-          <t>4.1%</t>
-        </is>
-      </c>
-      <c r="E174" t="inlineStr"/>
+          <t>-10.9</t>
+        </is>
+      </c>
+      <c r="E174" t="inlineStr">
+        <is>
+          <t>-5</t>
+        </is>
+      </c>
       <c r="F174" t="inlineStr">
         <is>
-          <t>4.0%</t>
+          <t>-10</t>
         </is>
       </c>
       <c r="G174" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="175">
@@ -5456,31 +5468,31 @@
       </c>
       <c r="B175" t="inlineStr">
         <is>
-          <t>Retail Sales MoMDEC</t>
+          <t>Import Prices YoYDEC</t>
         </is>
       </c>
       <c r="C175" t="inlineStr">
         <is>
-          <t>0.4%</t>
+          <t>2.2%</t>
         </is>
       </c>
       <c r="D175" t="inlineStr">
         <is>
-          <t>0.8%</t>
+          <t>1.4%</t>
         </is>
       </c>
       <c r="E175" t="inlineStr">
         <is>
-          <t>0.6%</t>
+          <t>2.1%</t>
         </is>
       </c>
       <c r="F175" t="inlineStr">
         <is>
-          <t>0.5%</t>
+          <t>1.6%</t>
         </is>
       </c>
       <c r="G175" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="176">
@@ -5491,31 +5503,23 @@
       </c>
       <c r="B176" t="inlineStr">
         <is>
-          <t>Export Prices MoMDEC</t>
+          <t>Philly Fed EmploymentJAN</t>
         </is>
       </c>
       <c r="C176" t="inlineStr">
         <is>
-          <t>0.3%</t>
+          <t>11.9</t>
         </is>
       </c>
       <c r="D176" t="inlineStr">
         <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="E176" t="inlineStr">
-        <is>
-          <t>0.2%</t>
-        </is>
-      </c>
-      <c r="F176" t="inlineStr">
-        <is>
-          <t>0.5%</t>
-        </is>
-      </c>
+          <t>4.8</t>
+        </is>
+      </c>
+      <c r="E176" t="inlineStr"/>
+      <c r="F176" t="inlineStr"/>
       <c r="G176" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="177">
@@ -5526,31 +5530,31 @@
       </c>
       <c r="B177" t="inlineStr">
         <is>
-          <t>Initial Jobless ClaimsJAN/11</t>
+          <t>Continuing Jobless ClaimsJAN/04</t>
         </is>
       </c>
       <c r="C177" t="inlineStr">
         <is>
-          <t>217K</t>
+          <t>1859K</t>
         </is>
       </c>
       <c r="D177" t="inlineStr">
         <is>
-          <t>203K</t>
+          <t>1867K</t>
         </is>
       </c>
       <c r="E177" t="inlineStr">
         <is>
-          <t>210K</t>
+          <t>1870K</t>
         </is>
       </c>
       <c r="F177" t="inlineStr">
         <is>
-          <t>209.0K</t>
+          <t>1870.0K</t>
         </is>
       </c>
       <c r="G177" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="178">
@@ -5561,31 +5565,31 @@
       </c>
       <c r="B178" t="inlineStr">
         <is>
-          <t>Retail Sales Ex Autos MoMDEC</t>
+          <t>Retail Sales Ex Gas/Autos MoMDEC</t>
         </is>
       </c>
       <c r="C178" t="inlineStr">
         <is>
+          <t>0.3%</t>
+        </is>
+      </c>
+      <c r="D178" t="inlineStr">
+        <is>
+          <t>0.2%</t>
+        </is>
+      </c>
+      <c r="E178" t="inlineStr">
+        <is>
           <t>0.4%</t>
         </is>
       </c>
-      <c r="D178" t="inlineStr">
-        <is>
-          <t>0.2%</t>
-        </is>
-      </c>
-      <c r="E178" t="inlineStr">
+      <c r="F178" t="inlineStr">
         <is>
           <t>0.4%</t>
         </is>
       </c>
-      <c r="F178" t="inlineStr">
-        <is>
-          <t>0.4%</t>
-        </is>
-      </c>
       <c r="G178" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="179">
@@ -5596,17 +5600,17 @@
       </c>
       <c r="B179" t="inlineStr">
         <is>
-          <t>Philly Fed Prices PaidJAN</t>
+          <t>Philly Fed New OrdersJAN</t>
         </is>
       </c>
       <c r="C179" t="inlineStr">
         <is>
-          <t>31.90</t>
+          <t>42.9</t>
         </is>
       </c>
       <c r="D179" t="inlineStr">
         <is>
-          <t>26.60</t>
+          <t>-3.6</t>
         </is>
       </c>
       <c r="E179" t="inlineStr"/>
@@ -5623,23 +5627,31 @@
       </c>
       <c r="B180" t="inlineStr">
         <is>
-          <t>Philly Fed New OrdersJAN</t>
+          <t>Initial Jobless ClaimsJAN/11</t>
         </is>
       </c>
       <c r="C180" t="inlineStr">
         <is>
-          <t>42.9</t>
+          <t>217K</t>
         </is>
       </c>
       <c r="D180" t="inlineStr">
         <is>
-          <t>-3.6</t>
-        </is>
-      </c>
-      <c r="E180" t="inlineStr"/>
-      <c r="F180" t="inlineStr"/>
+          <t>203K</t>
+        </is>
+      </c>
+      <c r="E180" t="inlineStr">
+        <is>
+          <t>210K</t>
+        </is>
+      </c>
+      <c r="F180" t="inlineStr">
+        <is>
+          <t>209.0K</t>
+        </is>
+      </c>
       <c r="G180" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="181">
@@ -5650,7 +5662,7 @@
       </c>
       <c r="B181" t="inlineStr">
         <is>
-          <t>Retail Sales Ex Gas/Autos MoMDEC</t>
+          <t>Export Prices MoMDEC</t>
         </is>
       </c>
       <c r="C181" t="inlineStr">
@@ -5660,21 +5672,21 @@
       </c>
       <c r="D181" t="inlineStr">
         <is>
+          <t>0%</t>
+        </is>
+      </c>
+      <c r="E181" t="inlineStr">
+        <is>
           <t>0.2%</t>
         </is>
       </c>
-      <c r="E181" t="inlineStr">
-        <is>
-          <t>0.4%</t>
-        </is>
-      </c>
       <c r="F181" t="inlineStr">
         <is>
-          <t>0.4%</t>
+          <t>0.5%</t>
         </is>
       </c>
       <c r="G181" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="182">
@@ -5685,31 +5697,31 @@
       </c>
       <c r="B182" t="inlineStr">
         <is>
-          <t>Continuing Jobless ClaimsJAN/04</t>
+          <t>Retail Sales MoMDEC</t>
         </is>
       </c>
       <c r="C182" t="inlineStr">
         <is>
-          <t>1859K</t>
+          <t>0.4%</t>
         </is>
       </c>
       <c r="D182" t="inlineStr">
         <is>
-          <t>1867K</t>
+          <t>0.8%</t>
         </is>
       </c>
       <c r="E182" t="inlineStr">
         <is>
-          <t>1870K</t>
+          <t>0.6%</t>
         </is>
       </c>
       <c r="F182" t="inlineStr">
         <is>
-          <t>1870.0K</t>
+          <t>0.5%</t>
         </is>
       </c>
       <c r="G182" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="183">
@@ -5720,21 +5732,25 @@
       </c>
       <c r="B183" t="inlineStr">
         <is>
-          <t>Philly Fed EmploymentJAN</t>
+          <t>Retail Sales YoYDEC</t>
         </is>
       </c>
       <c r="C183" t="inlineStr">
         <is>
-          <t>11.9</t>
+          <t>3.9%</t>
         </is>
       </c>
       <c r="D183" t="inlineStr">
         <is>
-          <t>4.8</t>
+          <t>4.1%</t>
         </is>
       </c>
       <c r="E183" t="inlineStr"/>
-      <c r="F183" t="inlineStr"/>
+      <c r="F183" t="inlineStr">
+        <is>
+          <t>4.0%</t>
+        </is>
+      </c>
       <c r="G183" t="n">
         <v>3</v>
       </c>
@@ -5747,27 +5763,23 @@
       </c>
       <c r="B184" t="inlineStr">
         <is>
-          <t>Import Prices YoYDEC</t>
+          <t>Export Prices YoYDEC</t>
         </is>
       </c>
       <c r="C184" t="inlineStr">
         <is>
-          <t>2.2%</t>
+          <t>1.8%</t>
         </is>
       </c>
       <c r="D184" t="inlineStr">
         <is>
-          <t>1.4%</t>
-        </is>
-      </c>
-      <c r="E184" t="inlineStr">
-        <is>
-          <t>2.1%</t>
-        </is>
-      </c>
+          <t>0.9%</t>
+        </is>
+      </c>
+      <c r="E184" t="inlineStr"/>
       <c r="F184" t="inlineStr">
         <is>
-          <t>1.6%</t>
+          <t>1.9%</t>
         </is>
       </c>
       <c r="G184" t="n">
@@ -5782,31 +5794,23 @@
       </c>
       <c r="B185" t="inlineStr">
         <is>
-          <t>Philadelphia Fed Manufacturing IndexJAN</t>
+          <t>Philly Fed CAPEX IndexJAN</t>
         </is>
       </c>
       <c r="C185" t="inlineStr">
         <is>
-          <t>44.3</t>
+          <t>39.00</t>
         </is>
       </c>
       <c r="D185" t="inlineStr">
         <is>
-          <t>-10.9</t>
-        </is>
-      </c>
-      <c r="E185" t="inlineStr">
-        <is>
-          <t>-5</t>
-        </is>
-      </c>
-      <c r="F185" t="inlineStr">
-        <is>
-          <t>-10</t>
-        </is>
-      </c>
+          <t>22.20</t>
+        </is>
+      </c>
+      <c r="E185" t="inlineStr"/>
+      <c r="F185" t="inlineStr"/>
       <c r="G185" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="186">
@@ -5817,21 +5821,25 @@
       </c>
       <c r="B186" t="inlineStr">
         <is>
-          <t>Philly Fed Business ConditionsJAN</t>
+          <t>Jobless Claims 4-week AverageJAN/11</t>
         </is>
       </c>
       <c r="C186" t="inlineStr">
         <is>
-          <t>46.3</t>
+          <t>212.75K</t>
         </is>
       </c>
       <c r="D186" t="inlineStr">
         <is>
-          <t>33.8</t>
+          <t>213.5K</t>
         </is>
       </c>
       <c r="E186" t="inlineStr"/>
-      <c r="F186" t="inlineStr"/>
+      <c r="F186" t="inlineStr">
+        <is>
+          <t>215.0K</t>
+        </is>
+      </c>
       <c r="G186" t="n">
         <v>3</v>
       </c>
@@ -5844,31 +5852,23 @@
       </c>
       <c r="B187" t="inlineStr">
         <is>
-          <t>Import Prices MoMDEC</t>
+          <t>Philly Fed Prices PaidJAN</t>
         </is>
       </c>
       <c r="C187" t="inlineStr">
         <is>
-          <t>0.1%</t>
+          <t>31.90</t>
         </is>
       </c>
       <c r="D187" t="inlineStr">
         <is>
-          <t>0.1%</t>
-        </is>
-      </c>
-      <c r="E187" t="inlineStr">
-        <is>
-          <t>0.1%</t>
-        </is>
-      </c>
-      <c r="F187" t="inlineStr">
-        <is>
-          <t>0.1%</t>
-        </is>
-      </c>
+          <t>26.60</t>
+        </is>
+      </c>
+      <c r="E187" t="inlineStr"/>
+      <c r="F187" t="inlineStr"/>
       <c r="G187" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="188">
@@ -6015,17 +6015,17 @@
       </c>
       <c r="B192" t="inlineStr">
         <is>
-          <t>4-Week Bill Auction</t>
+          <t>8-Week Bill Auction</t>
         </is>
       </c>
       <c r="C192" t="inlineStr">
         <is>
+          <t>4.235%</t>
+        </is>
+      </c>
+      <c r="D192" t="inlineStr">
+        <is>
           <t>4.240%</t>
-        </is>
-      </c>
-      <c r="D192" t="inlineStr">
-        <is>
-          <t>4.245%</t>
         </is>
       </c>
       <c r="E192" t="inlineStr"/>
@@ -6042,17 +6042,17 @@
       </c>
       <c r="B193" t="inlineStr">
         <is>
-          <t>8-Week Bill Auction</t>
+          <t>4-Week Bill Auction</t>
         </is>
       </c>
       <c r="C193" t="inlineStr">
         <is>
-          <t>4.235%</t>
+          <t>4.240%</t>
         </is>
       </c>
       <c r="D193" t="inlineStr">
         <is>
-          <t>4.240%</t>
+          <t>4.245%</t>
         </is>
       </c>
       <c r="E193" t="inlineStr"/>
@@ -6503,27 +6503,23 @@
       </c>
       <c r="B208" t="inlineStr">
         <is>
-          <t>Net Long-term TIC FlowsNOV</t>
+          <t>Foreign Bond InvestmentNOV</t>
         </is>
       </c>
       <c r="C208" t="inlineStr">
         <is>
-          <t>$79B</t>
+          <t>$-15.8B</t>
         </is>
       </c>
       <c r="D208" t="inlineStr">
         <is>
-          <t>$159.1B</t>
-        </is>
-      </c>
-      <c r="E208" t="inlineStr">
-        <is>
-          <t>$159.9B</t>
-        </is>
-      </c>
+          <t>$92B</t>
+        </is>
+      </c>
+      <c r="E208" t="inlineStr"/>
       <c r="F208" t="inlineStr"/>
       <c r="G208" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="209">
@@ -6534,23 +6530,27 @@
       </c>
       <c r="B209" t="inlineStr">
         <is>
-          <t>Overall Net Capital FlowsNOV</t>
+          <t>Net Long-term TIC FlowsNOV</t>
         </is>
       </c>
       <c r="C209" t="inlineStr">
         <is>
+          <t>$79B</t>
+        </is>
+      </c>
+      <c r="D209" t="inlineStr">
+        <is>
+          <t>$159.1B</t>
+        </is>
+      </c>
+      <c r="E209" t="inlineStr">
+        <is>
           <t>$159.9B</t>
         </is>
       </c>
-      <c r="D209" t="inlineStr">
-        <is>
-          <t>$201.8B</t>
-        </is>
-      </c>
-      <c r="E209" t="inlineStr"/>
       <c r="F209" t="inlineStr"/>
       <c r="G209" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="210">
@@ -6561,17 +6561,17 @@
       </c>
       <c r="B210" t="inlineStr">
         <is>
-          <t>Foreign Bond InvestmentNOV</t>
+          <t>Overall Net Capital FlowsNOV</t>
         </is>
       </c>
       <c r="C210" t="inlineStr">
         <is>
-          <t>$-15.8B</t>
+          <t>$159.9B</t>
         </is>
       </c>
       <c r="D210" t="inlineStr">
         <is>
-          <t>$92B</t>
+          <t>$201.8B</t>
         </is>
       </c>
       <c r="E210" t="inlineStr"/>
@@ -7241,17 +7241,17 @@
       </c>
       <c r="B234" t="inlineStr">
         <is>
-          <t>EIA Refinery Crude Runs ChangeJAN/17</t>
+          <t>EIA Distillate Fuel Production ChangeJAN/17</t>
         </is>
       </c>
       <c r="C234" t="inlineStr">
         <is>
-          <t>-1.125M</t>
+          <t>-0.473M</t>
         </is>
       </c>
       <c r="D234" t="inlineStr">
         <is>
-          <t>-0.255M</t>
+          <t>-0.021M</t>
         </is>
       </c>
       <c r="E234" t="inlineStr"/>
@@ -7268,20 +7268,24 @@
       </c>
       <c r="B235" t="inlineStr">
         <is>
-          <t>EIA Crude Oil Imports ChangeJAN/17</t>
+          <t>EIA Distillate Stocks ChangeJAN/17</t>
         </is>
       </c>
       <c r="C235" t="inlineStr">
         <is>
-          <t>0.184M</t>
+          <t>-3.07M</t>
         </is>
       </c>
       <c r="D235" t="inlineStr">
         <is>
-          <t>-1.304M</t>
-        </is>
-      </c>
-      <c r="E235" t="inlineStr"/>
+          <t>3.077M</t>
+        </is>
+      </c>
+      <c r="E235" t="inlineStr">
+        <is>
+          <t>0.6M</t>
+        </is>
+      </c>
       <c r="F235" t="inlineStr"/>
       <c r="G235" t="n">
         <v>3</v>
@@ -7295,17 +7299,17 @@
       </c>
       <c r="B236" t="inlineStr">
         <is>
-          <t>EIA Gasoline Production ChangeJAN/17</t>
+          <t>EIA Heating Oil Stocks ChangeJAN/17</t>
         </is>
       </c>
       <c r="C236" t="inlineStr">
         <is>
-          <t>-0.043M</t>
+          <t>0.068M</t>
         </is>
       </c>
       <c r="D236" t="inlineStr">
         <is>
-          <t>0.397M</t>
+          <t>0.646M</t>
         </is>
       </c>
       <c r="E236" t="inlineStr"/>
@@ -7322,23 +7326,27 @@
       </c>
       <c r="B237" t="inlineStr">
         <is>
-          <t>EIA Cushing Crude Oil Stocks ChangeJAN/17</t>
+          <t>EIA Crude Oil Stocks ChangeJAN/17</t>
         </is>
       </c>
       <c r="C237" t="inlineStr">
         <is>
-          <t>-0.148M</t>
+          <t>-1.017M</t>
         </is>
       </c>
       <c r="D237" t="inlineStr">
         <is>
-          <t>0.765M</t>
-        </is>
-      </c>
-      <c r="E237" t="inlineStr"/>
+          <t>-1.962M</t>
+        </is>
+      </c>
+      <c r="E237" t="inlineStr">
+        <is>
+          <t>-2.1M</t>
+        </is>
+      </c>
       <c r="F237" t="inlineStr"/>
       <c r="G237" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="238">
@@ -7349,17 +7357,17 @@
       </c>
       <c r="B238" t="inlineStr">
         <is>
-          <t>30-Year Mortgage RateJAN/23</t>
+          <t>15-Year Mortgage RateJAN/23</t>
         </is>
       </c>
       <c r="C238" t="inlineStr">
         <is>
-          <t>6.96%</t>
+          <t>6.16%</t>
         </is>
       </c>
       <c r="D238" t="inlineStr">
         <is>
-          <t>7.04%</t>
+          <t>6.27%</t>
         </is>
       </c>
       <c r="E238" t="inlineStr"/>
@@ -7376,27 +7384,23 @@
       </c>
       <c r="B239" t="inlineStr">
         <is>
-          <t>EIA Gasoline Stocks ChangeJAN/17</t>
+          <t>30-Year Mortgage RateJAN/23</t>
         </is>
       </c>
       <c r="C239" t="inlineStr">
         <is>
-          <t>2.332M</t>
+          <t>6.96%</t>
         </is>
       </c>
       <c r="D239" t="inlineStr">
         <is>
-          <t>5.852M</t>
-        </is>
-      </c>
-      <c r="E239" t="inlineStr">
-        <is>
-          <t>2.5M</t>
-        </is>
-      </c>
+          <t>7.04%</t>
+        </is>
+      </c>
+      <c r="E239" t="inlineStr"/>
       <c r="F239" t="inlineStr"/>
       <c r="G239" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="240">
@@ -7407,17 +7411,17 @@
       </c>
       <c r="B240" t="inlineStr">
         <is>
-          <t>15-Year Mortgage RateJAN/23</t>
+          <t>EIA Cushing Crude Oil Stocks ChangeJAN/17</t>
         </is>
       </c>
       <c r="C240" t="inlineStr">
         <is>
-          <t>6.16%</t>
+          <t>-0.148M</t>
         </is>
       </c>
       <c r="D240" t="inlineStr">
         <is>
-          <t>6.27%</t>
+          <t>0.765M</t>
         </is>
       </c>
       <c r="E240" t="inlineStr"/>
@@ -7434,27 +7438,23 @@
       </c>
       <c r="B241" t="inlineStr">
         <is>
-          <t>EIA Crude Oil Stocks ChangeJAN/17</t>
+          <t>EIA Gasoline Production ChangeJAN/17</t>
         </is>
       </c>
       <c r="C241" t="inlineStr">
         <is>
-          <t>-1.017M</t>
+          <t>-0.043M</t>
         </is>
       </c>
       <c r="D241" t="inlineStr">
         <is>
-          <t>-1.962M</t>
-        </is>
-      </c>
-      <c r="E241" t="inlineStr">
-        <is>
-          <t>-2.1M</t>
-        </is>
-      </c>
+          <t>0.397M</t>
+        </is>
+      </c>
+      <c r="E241" t="inlineStr"/>
       <c r="F241" t="inlineStr"/>
       <c r="G241" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="242">
@@ -7465,17 +7465,17 @@
       </c>
       <c r="B242" t="inlineStr">
         <is>
-          <t>EIA Heating Oil Stocks ChangeJAN/17</t>
+          <t>EIA Crude Oil Imports ChangeJAN/17</t>
         </is>
       </c>
       <c r="C242" t="inlineStr">
         <is>
-          <t>0.068M</t>
+          <t>0.184M</t>
         </is>
       </c>
       <c r="D242" t="inlineStr">
         <is>
-          <t>0.646M</t>
+          <t>-1.304M</t>
         </is>
       </c>
       <c r="E242" t="inlineStr"/>
@@ -7492,24 +7492,20 @@
       </c>
       <c r="B243" t="inlineStr">
         <is>
-          <t>EIA Distillate Stocks ChangeJAN/17</t>
+          <t>EIA Refinery Crude Runs ChangeJAN/17</t>
         </is>
       </c>
       <c r="C243" t="inlineStr">
         <is>
-          <t>-3.07M</t>
+          <t>-1.125M</t>
         </is>
       </c>
       <c r="D243" t="inlineStr">
         <is>
-          <t>3.077M</t>
-        </is>
-      </c>
-      <c r="E243" t="inlineStr">
-        <is>
-          <t>0.6M</t>
-        </is>
-      </c>
+          <t>-0.255M</t>
+        </is>
+      </c>
+      <c r="E243" t="inlineStr"/>
       <c r="F243" t="inlineStr"/>
       <c r="G243" t="n">
         <v>3</v>
@@ -7523,23 +7519,27 @@
       </c>
       <c r="B244" t="inlineStr">
         <is>
-          <t>EIA Distillate Fuel Production ChangeJAN/17</t>
+          <t>EIA Gasoline Stocks ChangeJAN/17</t>
         </is>
       </c>
       <c r="C244" t="inlineStr">
         <is>
-          <t>-0.473M</t>
+          <t>2.332M</t>
         </is>
       </c>
       <c r="D244" t="inlineStr">
         <is>
-          <t>-0.021M</t>
-        </is>
-      </c>
-      <c r="E244" t="inlineStr"/>
+          <t>5.852M</t>
+        </is>
+      </c>
+      <c r="E244" t="inlineStr">
+        <is>
+          <t>2.5M</t>
+        </is>
+      </c>
       <c r="F244" t="inlineStr"/>
       <c r="G244" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="245">
@@ -7705,31 +7705,27 @@
       </c>
       <c r="B250" t="inlineStr">
         <is>
-          <t>Michigan Current Conditions FinalJAN</t>
+          <t>Existing Home Sales MoMDEC</t>
         </is>
       </c>
       <c r="C250" t="inlineStr">
         <is>
-          <t>74.0</t>
+          <t>2.2%</t>
         </is>
       </c>
       <c r="D250" t="inlineStr">
         <is>
-          <t>75.1</t>
-        </is>
-      </c>
-      <c r="E250" t="inlineStr">
-        <is>
-          <t>77.9</t>
-        </is>
-      </c>
+          <t>4.8%</t>
+        </is>
+      </c>
+      <c r="E250" t="inlineStr"/>
       <c r="F250" t="inlineStr">
         <is>
-          <t>77.9</t>
+          <t>0.3%</t>
         </is>
       </c>
       <c r="G250" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="251">
@@ -7740,31 +7736,31 @@
       </c>
       <c r="B251" t="inlineStr">
         <is>
-          <t>Existing Home SalesDEC</t>
+          <t>Michigan Inflation Expectations FinalJAN</t>
         </is>
       </c>
       <c r="C251" t="inlineStr">
         <is>
-          <t>4.24M</t>
+          <t>3.3%</t>
         </is>
       </c>
       <c r="D251" t="inlineStr">
         <is>
-          <t>4.15M</t>
+          <t>2.8%</t>
         </is>
       </c>
       <c r="E251" t="inlineStr">
         <is>
-          <t>4.19M</t>
+          <t>3.3%</t>
         </is>
       </c>
       <c r="F251" t="inlineStr">
         <is>
-          <t>4.1M</t>
+          <t>3.3%</t>
         </is>
       </c>
       <c r="G251" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="252">
@@ -7775,27 +7771,27 @@
       </c>
       <c r="B252" t="inlineStr">
         <is>
-          <t>Michigan 5 Year Inflation Expectations FinalJAN</t>
+          <t>Michigan Consumer Expectations FinalJAN</t>
         </is>
       </c>
       <c r="C252" t="inlineStr">
         <is>
-          <t>3.2%</t>
+          <t>69.3</t>
         </is>
       </c>
       <c r="D252" t="inlineStr">
         <is>
-          <t>3%</t>
+          <t>73.3</t>
         </is>
       </c>
       <c r="E252" t="inlineStr">
         <is>
-          <t>3.3%</t>
+          <t>70.2</t>
         </is>
       </c>
       <c r="F252" t="inlineStr">
         <is>
-          <t>3.3%</t>
+          <t>70.2</t>
         </is>
       </c>
       <c r="G252" t="n">
@@ -7810,31 +7806,31 @@
       </c>
       <c r="B253" t="inlineStr">
         <is>
-          <t>Michigan Consumer Sentiment FinalJAN</t>
+          <t>Michigan Current Conditions FinalJAN</t>
         </is>
       </c>
       <c r="C253" t="inlineStr">
         <is>
-          <t>71.1</t>
+          <t>74.0</t>
         </is>
       </c>
       <c r="D253" t="inlineStr">
         <is>
-          <t>74.0</t>
+          <t>75.1</t>
         </is>
       </c>
       <c r="E253" t="inlineStr">
         <is>
-          <t>73.2</t>
+          <t>77.9</t>
         </is>
       </c>
       <c r="F253" t="inlineStr">
         <is>
-          <t>73.2</t>
+          <t>77.9</t>
         </is>
       </c>
       <c r="G253" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="254">
@@ -7845,27 +7841,27 @@
       </c>
       <c r="B254" t="inlineStr">
         <is>
-          <t>Michigan Consumer Expectations FinalJAN</t>
+          <t>Michigan 5 Year Inflation Expectations FinalJAN</t>
         </is>
       </c>
       <c r="C254" t="inlineStr">
         <is>
-          <t>69.3</t>
+          <t>3.2%</t>
         </is>
       </c>
       <c r="D254" t="inlineStr">
         <is>
-          <t>73.3</t>
+          <t>3%</t>
         </is>
       </c>
       <c r="E254" t="inlineStr">
         <is>
-          <t>70.2</t>
+          <t>3.3%</t>
         </is>
       </c>
       <c r="F254" t="inlineStr">
         <is>
-          <t>70.2</t>
+          <t>3.3%</t>
         </is>
       </c>
       <c r="G254" t="n">
@@ -7880,27 +7876,31 @@
       </c>
       <c r="B255" t="inlineStr">
         <is>
-          <t>Existing Home Sales MoMDEC</t>
+          <t>Existing Home SalesDEC</t>
         </is>
       </c>
       <c r="C255" t="inlineStr">
         <is>
-          <t>2.2%</t>
+          <t>4.24M</t>
         </is>
       </c>
       <c r="D255" t="inlineStr">
         <is>
-          <t>4.8%</t>
-        </is>
-      </c>
-      <c r="E255" t="inlineStr"/>
+          <t>4.15M</t>
+        </is>
+      </c>
+      <c r="E255" t="inlineStr">
+        <is>
+          <t>4.19M</t>
+        </is>
+      </c>
       <c r="F255" t="inlineStr">
         <is>
-          <t>0.3%</t>
+          <t>4.1M</t>
         </is>
       </c>
       <c r="G255" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="256">
@@ -7911,31 +7911,31 @@
       </c>
       <c r="B256" t="inlineStr">
         <is>
-          <t>Michigan Inflation Expectations FinalJAN</t>
+          <t>Michigan Consumer Sentiment FinalJAN</t>
         </is>
       </c>
       <c r="C256" t="inlineStr">
         <is>
-          <t>3.3%</t>
+          <t>71.1</t>
         </is>
       </c>
       <c r="D256" t="inlineStr">
         <is>
-          <t>2.8%</t>
+          <t>74.0</t>
         </is>
       </c>
       <c r="E256" t="inlineStr">
         <is>
-          <t>3.3%</t>
+          <t>73.2</t>
         </is>
       </c>
       <c r="F256" t="inlineStr">
         <is>
-          <t>3.3%</t>
+          <t>73.2</t>
         </is>
       </c>
       <c r="G256" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="257">
@@ -8469,27 +8469,23 @@
       </c>
       <c r="B274" t="inlineStr">
         <is>
-          <t>House Price Index MoMNOV</t>
+          <t>S&amp;P/Case-Shiller Home Price MoMNOV</t>
         </is>
       </c>
       <c r="C274" t="inlineStr">
         <is>
-          <t>0.3%</t>
+          <t>-0.1%</t>
         </is>
       </c>
       <c r="D274" t="inlineStr">
         <is>
-          <t>0.5%</t>
-        </is>
-      </c>
-      <c r="E274" t="inlineStr">
-        <is>
-          <t>0.2%</t>
-        </is>
-      </c>
+          <t>-0.2%</t>
+        </is>
+      </c>
+      <c r="E274" t="inlineStr"/>
       <c r="F274" t="inlineStr">
         <is>
-          <t>0.3%</t>
+          <t>-0.1%</t>
         </is>
       </c>
       <c r="G274" t="n">
@@ -8504,31 +8500,27 @@
       </c>
       <c r="B275" t="inlineStr">
         <is>
-          <t>S&amp;P/Case-Shiller Home Price YoYNOV</t>
+          <t>House Price IndexNOV</t>
         </is>
       </c>
       <c r="C275" t="inlineStr">
         <is>
-          <t>4.3%</t>
+          <t>433.4</t>
         </is>
       </c>
       <c r="D275" t="inlineStr">
         <is>
-          <t>4.2%</t>
-        </is>
-      </c>
-      <c r="E275" t="inlineStr">
-        <is>
-          <t>4.3%</t>
-        </is>
-      </c>
+          <t>432.3</t>
+        </is>
+      </c>
+      <c r="E275" t="inlineStr"/>
       <c r="F275" t="inlineStr">
         <is>
-          <t>4%</t>
+          <t>433</t>
         </is>
       </c>
       <c r="G275" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="276">
@@ -8539,23 +8531,23 @@
       </c>
       <c r="B276" t="inlineStr">
         <is>
-          <t>House Price IndexNOV</t>
+          <t>House Price Index YoYNOV</t>
         </is>
       </c>
       <c r="C276" t="inlineStr">
         <is>
-          <t>433.4</t>
+          <t>4.2%</t>
         </is>
       </c>
       <c r="D276" t="inlineStr">
         <is>
-          <t>432.3</t>
+          <t>4.5%</t>
         </is>
       </c>
       <c r="E276" t="inlineStr"/>
       <c r="F276" t="inlineStr">
         <is>
-          <t>433</t>
+          <t>4.3%</t>
         </is>
       </c>
       <c r="G276" t="n">
@@ -8570,27 +8562,31 @@
       </c>
       <c r="B277" t="inlineStr">
         <is>
-          <t>House Price Index YoYNOV</t>
+          <t>S&amp;P/Case-Shiller Home Price YoYNOV</t>
         </is>
       </c>
       <c r="C277" t="inlineStr">
         <is>
+          <t>4.3%</t>
+        </is>
+      </c>
+      <c r="D277" t="inlineStr">
+        <is>
           <t>4.2%</t>
         </is>
       </c>
-      <c r="D277" t="inlineStr">
-        <is>
-          <t>4.5%</t>
-        </is>
-      </c>
-      <c r="E277" t="inlineStr"/>
+      <c r="E277" t="inlineStr">
+        <is>
+          <t>4.3%</t>
+        </is>
+      </c>
       <c r="F277" t="inlineStr">
         <is>
-          <t>4.3%</t>
+          <t>4%</t>
         </is>
       </c>
       <c r="G277" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="278">
@@ -8601,23 +8597,27 @@
       </c>
       <c r="B278" t="inlineStr">
         <is>
-          <t>S&amp;P/Case-Shiller Home Price MoMNOV</t>
+          <t>House Price Index MoMNOV</t>
         </is>
       </c>
       <c r="C278" t="inlineStr">
         <is>
-          <t>-0.1%</t>
+          <t>0.3%</t>
         </is>
       </c>
       <c r="D278" t="inlineStr">
         <is>
-          <t>-0.2%</t>
-        </is>
-      </c>
-      <c r="E278" t="inlineStr"/>
+          <t>0.5%</t>
+        </is>
+      </c>
+      <c r="E278" t="inlineStr">
+        <is>
+          <t>0.2%</t>
+        </is>
+      </c>
       <c r="F278" t="inlineStr">
         <is>
-          <t>-0.1%</t>
+          <t>0.3%</t>
         </is>
       </c>
       <c r="G278" t="n">
@@ -9201,17 +9201,17 @@
       </c>
       <c r="B298" t="inlineStr">
         <is>
-          <t>EIA Gasoline Production ChangeJAN/24</t>
+          <t>EIA Cushing Crude Oil Stocks ChangeJAN/24</t>
         </is>
       </c>
       <c r="C298" t="inlineStr">
         <is>
-          <t>-0.044M</t>
+          <t>0.326M</t>
         </is>
       </c>
       <c r="D298" t="inlineStr">
         <is>
-          <t>-0.043M</t>
+          <t>-0.148M</t>
         </is>
       </c>
       <c r="E298" t="inlineStr"/>
@@ -9228,23 +9228,27 @@
       </c>
       <c r="B299" t="inlineStr">
         <is>
-          <t>EIA Crude Oil Imports ChangeJAN/24</t>
+          <t>EIA Crude Oil Stocks ChangeJAN/24</t>
         </is>
       </c>
       <c r="C299" t="inlineStr">
         <is>
-          <t>0.532M</t>
+          <t>3.463M</t>
         </is>
       </c>
       <c r="D299" t="inlineStr">
         <is>
-          <t>0.184M</t>
-        </is>
-      </c>
-      <c r="E299" t="inlineStr"/>
+          <t>-1.017M</t>
+        </is>
+      </c>
+      <c r="E299" t="inlineStr">
+        <is>
+          <t>3.2M</t>
+        </is>
+      </c>
       <c r="F299" t="inlineStr"/>
       <c r="G299" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="300">
@@ -9255,20 +9259,24 @@
       </c>
       <c r="B300" t="inlineStr">
         <is>
-          <t>EIA Distillate Fuel Production ChangeJAN/24</t>
+          <t>EIA Distillate Stocks ChangeJAN/24</t>
         </is>
       </c>
       <c r="C300" t="inlineStr">
         <is>
-          <t>0.028M</t>
+          <t>-4.994M</t>
         </is>
       </c>
       <c r="D300" t="inlineStr">
         <is>
-          <t>-0.473M</t>
-        </is>
-      </c>
-      <c r="E300" t="inlineStr"/>
+          <t>-3.07M</t>
+        </is>
+      </c>
+      <c r="E300" t="inlineStr">
+        <is>
+          <t>-2.1M</t>
+        </is>
+      </c>
       <c r="F300" t="inlineStr"/>
       <c r="G300" t="n">
         <v>3</v>
@@ -9282,27 +9290,23 @@
       </c>
       <c r="B301" t="inlineStr">
         <is>
-          <t>EIA Gasoline Stocks ChangeJAN/24</t>
+          <t>EIA Heating Oil Stocks ChangeJAN/24</t>
         </is>
       </c>
       <c r="C301" t="inlineStr">
         <is>
-          <t>2.957M</t>
+          <t>0.128M</t>
         </is>
       </c>
       <c r="D301" t="inlineStr">
         <is>
-          <t>2.332M</t>
-        </is>
-      </c>
-      <c r="E301" t="inlineStr">
-        <is>
-          <t>1.5M</t>
-        </is>
-      </c>
+          <t>0.068M</t>
+        </is>
+      </c>
+      <c r="E301" t="inlineStr"/>
       <c r="F301" t="inlineStr"/>
       <c r="G301" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="302">
@@ -9340,23 +9344,27 @@
       </c>
       <c r="B303" t="inlineStr">
         <is>
-          <t>EIA Heating Oil Stocks ChangeJAN/24</t>
+          <t>EIA Gasoline Stocks ChangeJAN/24</t>
         </is>
       </c>
       <c r="C303" t="inlineStr">
         <is>
-          <t>0.128M</t>
+          <t>2.957M</t>
         </is>
       </c>
       <c r="D303" t="inlineStr">
         <is>
-          <t>0.068M</t>
-        </is>
-      </c>
-      <c r="E303" t="inlineStr"/>
+          <t>2.332M</t>
+        </is>
+      </c>
+      <c r="E303" t="inlineStr">
+        <is>
+          <t>1.5M</t>
+        </is>
+      </c>
       <c r="F303" t="inlineStr"/>
       <c r="G303" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="304">
@@ -9367,24 +9375,20 @@
       </c>
       <c r="B304" t="inlineStr">
         <is>
-          <t>EIA Distillate Stocks ChangeJAN/24</t>
+          <t>EIA Distillate Fuel Production ChangeJAN/24</t>
         </is>
       </c>
       <c r="C304" t="inlineStr">
         <is>
-          <t>-4.994M</t>
+          <t>0.028M</t>
         </is>
       </c>
       <c r="D304" t="inlineStr">
         <is>
-          <t>-3.07M</t>
-        </is>
-      </c>
-      <c r="E304" t="inlineStr">
-        <is>
-          <t>-2.1M</t>
-        </is>
-      </c>
+          <t>-0.473M</t>
+        </is>
+      </c>
+      <c r="E304" t="inlineStr"/>
       <c r="F304" t="inlineStr"/>
       <c r="G304" t="n">
         <v>3</v>
@@ -9398,27 +9402,23 @@
       </c>
       <c r="B305" t="inlineStr">
         <is>
-          <t>EIA Crude Oil Stocks ChangeJAN/24</t>
+          <t>EIA Crude Oil Imports ChangeJAN/24</t>
         </is>
       </c>
       <c r="C305" t="inlineStr">
         <is>
-          <t>3.463M</t>
+          <t>0.532M</t>
         </is>
       </c>
       <c r="D305" t="inlineStr">
         <is>
-          <t>-1.017M</t>
-        </is>
-      </c>
-      <c r="E305" t="inlineStr">
-        <is>
-          <t>3.2M</t>
-        </is>
-      </c>
+          <t>0.184M</t>
+        </is>
+      </c>
+      <c r="E305" t="inlineStr"/>
       <c r="F305" t="inlineStr"/>
       <c r="G305" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="306">
@@ -9429,17 +9429,17 @@
       </c>
       <c r="B306" t="inlineStr">
         <is>
-          <t>EIA Cushing Crude Oil Stocks ChangeJAN/24</t>
+          <t>EIA Gasoline Production ChangeJAN/24</t>
         </is>
       </c>
       <c r="C306" t="inlineStr">
         <is>
-          <t>0.326M</t>
+          <t>-0.044M</t>
         </is>
       </c>
       <c r="D306" t="inlineStr">
         <is>
-          <t>-0.148M</t>
+          <t>-0.043M</t>
         </is>
       </c>
       <c r="E306" t="inlineStr"/>
@@ -9537,31 +9537,27 @@
       </c>
       <c r="B310" t="inlineStr">
         <is>
-          <t>GDP Growth Rate QoQ AdvQ4</t>
+          <t>Real Consumer Spending QoQ AdvQ4</t>
         </is>
       </c>
       <c r="C310" t="inlineStr">
         <is>
-          <t>2.3%</t>
+          <t>4.2%</t>
         </is>
       </c>
       <c r="D310" t="inlineStr">
         <is>
-          <t>3.1%</t>
-        </is>
-      </c>
-      <c r="E310" t="inlineStr">
-        <is>
-          <t>2.6%</t>
-        </is>
-      </c>
+          <t>3.7%</t>
+        </is>
+      </c>
+      <c r="E310" t="inlineStr"/>
       <c r="F310" t="inlineStr">
         <is>
-          <t>3%</t>
+          <t>2.9%</t>
         </is>
       </c>
       <c r="G310" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="311">
@@ -9572,27 +9568,27 @@
       </c>
       <c r="B311" t="inlineStr">
         <is>
-          <t>GDP Price Index QoQ AdvQ4</t>
+          <t>Initial Jobless ClaimsJAN/25</t>
         </is>
       </c>
       <c r="C311" t="inlineStr">
         <is>
-          <t>2.2%</t>
+          <t>207K</t>
         </is>
       </c>
       <c r="D311" t="inlineStr">
         <is>
-          <t>1.9%</t>
+          <t>223K</t>
         </is>
       </c>
       <c r="